--- a/vignettes/vignette-1/tail_exceedance_plot_data.xlsx
+++ b/vignettes/vignette-1/tail_exceedance_plot_data.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C741"/>
+  <dimension ref="A1:C745"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -456,7 +456,7 @@
         <v>9.3e-05</v>
       </c>
       <c r="C3" t="n">
-        <v>0.997297</v>
+        <v>0.997312</v>
       </c>
     </row>
     <row r="4">
@@ -469,7 +469,7 @@
         <v>0.000522</v>
       </c>
       <c r="C4" t="n">
-        <v>0.994595</v>
+        <v>0.994624</v>
       </c>
     </row>
     <row r="5">
@@ -482,7 +482,7 @@
         <v>0.000687</v>
       </c>
       <c r="C5" t="n">
-        <v>0.991892</v>
+        <v>0.991935</v>
       </c>
     </row>
     <row r="6">
@@ -492,10 +492,10 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>0.001681</v>
+        <v>0.001141</v>
       </c>
       <c r="C6" t="n">
-        <v>0.989189</v>
+        <v>0.989247</v>
       </c>
     </row>
     <row r="7">
@@ -505,10 +505,10 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>0.00295</v>
+        <v>0.001681</v>
       </c>
       <c r="C7" t="n">
-        <v>0.986486</v>
+        <v>0.986559</v>
       </c>
     </row>
     <row r="8">
@@ -518,10 +518,10 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>0.002998</v>
+        <v>0.00295</v>
       </c>
       <c r="C8" t="n">
-        <v>0.983784</v>
+        <v>0.9838710000000001</v>
       </c>
     </row>
     <row r="9">
@@ -531,10 +531,10 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>0.003455</v>
+        <v>0.002998</v>
       </c>
       <c r="C9" t="n">
-        <v>0.981081</v>
+        <v>0.981183</v>
       </c>
     </row>
     <row r="10">
@@ -544,10 +544,10 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>0.003769</v>
+        <v>0.003455</v>
       </c>
       <c r="C10" t="n">
-        <v>0.978378</v>
+        <v>0.978495</v>
       </c>
     </row>
     <row r="11">
@@ -557,10 +557,10 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>0.003788</v>
+        <v>0.003769</v>
       </c>
       <c r="C11" t="n">
-        <v>0.975676</v>
+        <v>0.975806</v>
       </c>
     </row>
     <row r="12">
@@ -570,10 +570,10 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>0.003948</v>
+        <v>0.003788</v>
       </c>
       <c r="C12" t="n">
-        <v>0.972973</v>
+        <v>0.973118</v>
       </c>
     </row>
     <row r="13">
@@ -583,10 +583,10 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>0.004497</v>
+        <v>0.003948</v>
       </c>
       <c r="C13" t="n">
-        <v>0.97027</v>
+        <v>0.97043</v>
       </c>
     </row>
     <row r="14">
@@ -596,10 +596,10 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>0.004717</v>
+        <v>0.004497</v>
       </c>
       <c r="C14" t="n">
-        <v>0.967568</v>
+        <v>0.967742</v>
       </c>
     </row>
     <row r="15">
@@ -609,10 +609,10 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>0.004912</v>
+        <v>0.004717</v>
       </c>
       <c r="C15" t="n">
-        <v>0.964865</v>
+        <v>0.965054</v>
       </c>
     </row>
     <row r="16">
@@ -622,10 +622,10 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>0.005429</v>
+        <v>0.004912</v>
       </c>
       <c r="C16" t="n">
-        <v>0.962162</v>
+        <v>0.9623660000000001</v>
       </c>
     </row>
     <row r="17">
@@ -635,10 +635,10 @@
         </is>
       </c>
       <c r="B17" t="n">
-        <v>0.00593</v>
+        <v>0.005429</v>
       </c>
       <c r="C17" t="n">
-        <v>0.959459</v>
+        <v>0.959677</v>
       </c>
     </row>
     <row r="18">
@@ -648,10 +648,10 @@
         </is>
       </c>
       <c r="B18" t="n">
-        <v>0.0071</v>
+        <v>0.00593</v>
       </c>
       <c r="C18" t="n">
-        <v>0.956757</v>
+        <v>0.956989</v>
       </c>
     </row>
     <row r="19">
@@ -661,10 +661,10 @@
         </is>
       </c>
       <c r="B19" t="n">
-        <v>0.007582</v>
+        <v>0.0071</v>
       </c>
       <c r="C19" t="n">
-        <v>0.954054</v>
+        <v>0.954301</v>
       </c>
     </row>
     <row r="20">
@@ -674,10 +674,10 @@
         </is>
       </c>
       <c r="B20" t="n">
-        <v>0.008029</v>
+        <v>0.007582</v>
       </c>
       <c r="C20" t="n">
-        <v>0.9513509999999999</v>
+        <v>0.951613</v>
       </c>
     </row>
     <row r="21">
@@ -687,10 +687,10 @@
         </is>
       </c>
       <c r="B21" t="n">
-        <v>0.008069</v>
+        <v>0.008029</v>
       </c>
       <c r="C21" t="n">
-        <v>0.948649</v>
+        <v>0.948925</v>
       </c>
     </row>
     <row r="22">
@@ -700,10 +700,10 @@
         </is>
       </c>
       <c r="B22" t="n">
-        <v>0.008137999999999999</v>
+        <v>0.008069</v>
       </c>
       <c r="C22" t="n">
-        <v>0.945946</v>
+        <v>0.946237</v>
       </c>
     </row>
     <row r="23">
@@ -713,10 +713,10 @@
         </is>
       </c>
       <c r="B23" t="n">
-        <v>0.008377000000000001</v>
+        <v>0.008137999999999999</v>
       </c>
       <c r="C23" t="n">
-        <v>0.9432430000000001</v>
+        <v>0.9435480000000001</v>
       </c>
     </row>
     <row r="24">
@@ -726,10 +726,10 @@
         </is>
       </c>
       <c r="B24" t="n">
-        <v>0.008397</v>
+        <v>0.008377000000000001</v>
       </c>
       <c r="C24" t="n">
-        <v>0.940541</v>
+        <v>0.94086</v>
       </c>
     </row>
     <row r="25">
@@ -742,7 +742,7 @@
         <v>0.008514000000000001</v>
       </c>
       <c r="C25" t="n">
-        <v>0.9378379999999999</v>
+        <v>0.938172</v>
       </c>
     </row>
     <row r="26">
@@ -755,7 +755,7 @@
         <v>0.008593999999999999</v>
       </c>
       <c r="C26" t="n">
-        <v>0.935135</v>
+        <v>0.935484</v>
       </c>
     </row>
     <row r="27">
@@ -768,7 +768,7 @@
         <v>0.008658000000000001</v>
       </c>
       <c r="C27" t="n">
-        <v>0.932432</v>
+        <v>0.932796</v>
       </c>
     </row>
     <row r="28">
@@ -781,7 +781,7 @@
         <v>0.008992</v>
       </c>
       <c r="C28" t="n">
-        <v>0.9297299999999999</v>
+        <v>0.930108</v>
       </c>
     </row>
     <row r="29">
@@ -794,7 +794,7 @@
         <v>0.009011</v>
       </c>
       <c r="C29" t="n">
-        <v>0.927027</v>
+        <v>0.927419</v>
       </c>
     </row>
     <row r="30">
@@ -807,7 +807,7 @@
         <v>0.009165</v>
       </c>
       <c r="C30" t="n">
-        <v>0.924324</v>
+        <v>0.924731</v>
       </c>
     </row>
     <row r="31">
@@ -820,7 +820,7 @@
         <v>0.009428000000000001</v>
       </c>
       <c r="C31" t="n">
-        <v>0.9216220000000001</v>
+        <v>0.9220429999999999</v>
       </c>
     </row>
     <row r="32">
@@ -833,7 +833,7 @@
         <v>0.009578</v>
       </c>
       <c r="C32" t="n">
-        <v>0.918919</v>
+        <v>0.919355</v>
       </c>
     </row>
     <row r="33">
@@ -846,7 +846,7 @@
         <v>0.009774</v>
       </c>
       <c r="C33" t="n">
-        <v>0.916216</v>
+        <v>0.916667</v>
       </c>
     </row>
     <row r="34">
@@ -859,7 +859,7 @@
         <v>0.009811</v>
       </c>
       <c r="C34" t="n">
-        <v>0.913514</v>
+        <v>0.913978</v>
       </c>
     </row>
     <row r="35">
@@ -872,7 +872,7 @@
         <v>0.010226</v>
       </c>
       <c r="C35" t="n">
-        <v>0.910811</v>
+        <v>0.91129</v>
       </c>
     </row>
     <row r="36">
@@ -885,7 +885,7 @@
         <v>0.010518</v>
       </c>
       <c r="C36" t="n">
-        <v>0.908108</v>
+        <v>0.908602</v>
       </c>
     </row>
     <row r="37">
@@ -898,7 +898,7 @@
         <v>0.010554</v>
       </c>
       <c r="C37" t="n">
-        <v>0.905405</v>
+        <v>0.905914</v>
       </c>
     </row>
     <row r="38">
@@ -911,7 +911,7 @@
         <v>0.010625</v>
       </c>
       <c r="C38" t="n">
-        <v>0.902703</v>
+        <v>0.903226</v>
       </c>
     </row>
     <row r="39">
@@ -924,7 +924,7 @@
         <v>0.011326</v>
       </c>
       <c r="C39" t="n">
-        <v>0.9</v>
+        <v>0.9005379999999999</v>
       </c>
     </row>
     <row r="40">
@@ -937,7 +937,7 @@
         <v>0.01145</v>
       </c>
       <c r="C40" t="n">
-        <v>0.897297</v>
+        <v>0.897849</v>
       </c>
     </row>
     <row r="41">
@@ -950,7 +950,7 @@
         <v>0.011999</v>
       </c>
       <c r="C41" t="n">
-        <v>0.894595</v>
+        <v>0.895161</v>
       </c>
     </row>
     <row r="42">
@@ -963,7 +963,7 @@
         <v>0.012035</v>
       </c>
       <c r="C42" t="n">
-        <v>0.891892</v>
+        <v>0.892473</v>
       </c>
     </row>
     <row r="43">
@@ -976,7 +976,7 @@
         <v>0.012657</v>
       </c>
       <c r="C43" t="n">
-        <v>0.889189</v>
+        <v>0.889785</v>
       </c>
     </row>
     <row r="44">
@@ -986,10 +986,10 @@
         </is>
       </c>
       <c r="B44" t="n">
-        <v>0.013023</v>
+        <v>0.012918</v>
       </c>
       <c r="C44" t="n">
-        <v>0.886486</v>
+        <v>0.887097</v>
       </c>
     </row>
     <row r="45">
@@ -999,10 +999,10 @@
         </is>
       </c>
       <c r="B45" t="n">
-        <v>0.013054</v>
+        <v>0.013023</v>
       </c>
       <c r="C45" t="n">
-        <v>0.883784</v>
+        <v>0.884409</v>
       </c>
     </row>
     <row r="46">
@@ -1012,10 +1012,10 @@
         </is>
       </c>
       <c r="B46" t="n">
-        <v>0.013094</v>
+        <v>0.013054</v>
       </c>
       <c r="C46" t="n">
-        <v>0.881081</v>
+        <v>0.8817199999999999</v>
       </c>
     </row>
     <row r="47">
@@ -1025,10 +1025,10 @@
         </is>
       </c>
       <c r="B47" t="n">
-        <v>0.013641</v>
+        <v>0.013094</v>
       </c>
       <c r="C47" t="n">
-        <v>0.878378</v>
+        <v>0.879032</v>
       </c>
     </row>
     <row r="48">
@@ -1038,10 +1038,10 @@
         </is>
       </c>
       <c r="B48" t="n">
-        <v>0.013714</v>
+        <v>0.013641</v>
       </c>
       <c r="C48" t="n">
-        <v>0.875676</v>
+        <v>0.876344</v>
       </c>
     </row>
     <row r="49">
@@ -1051,10 +1051,10 @@
         </is>
       </c>
       <c r="B49" t="n">
-        <v>0.014018</v>
+        <v>0.013714</v>
       </c>
       <c r="C49" t="n">
-        <v>0.872973</v>
+        <v>0.873656</v>
       </c>
     </row>
     <row r="50">
@@ -1064,10 +1064,10 @@
         </is>
       </c>
       <c r="B50" t="n">
-        <v>0.014351</v>
+        <v>0.014018</v>
       </c>
       <c r="C50" t="n">
-        <v>0.87027</v>
+        <v>0.870968</v>
       </c>
     </row>
     <row r="51">
@@ -1077,10 +1077,10 @@
         </is>
       </c>
       <c r="B51" t="n">
-        <v>0.014731</v>
+        <v>0.014351</v>
       </c>
       <c r="C51" t="n">
-        <v>0.867568</v>
+        <v>0.8682800000000001</v>
       </c>
     </row>
     <row r="52">
@@ -1090,10 +1090,10 @@
         </is>
       </c>
       <c r="B52" t="n">
-        <v>0.014841</v>
+        <v>0.014731</v>
       </c>
       <c r="C52" t="n">
-        <v>0.864865</v>
+        <v>0.865591</v>
       </c>
     </row>
     <row r="53">
@@ -1103,10 +1103,10 @@
         </is>
       </c>
       <c r="B53" t="n">
-        <v>0.01486</v>
+        <v>0.014841</v>
       </c>
       <c r="C53" t="n">
-        <v>0.862162</v>
+        <v>0.862903</v>
       </c>
     </row>
     <row r="54">
@@ -1116,10 +1116,10 @@
         </is>
       </c>
       <c r="B54" t="n">
-        <v>0.015107</v>
+        <v>0.01486</v>
       </c>
       <c r="C54" t="n">
-        <v>0.859459</v>
+        <v>0.860215</v>
       </c>
     </row>
     <row r="55">
@@ -1132,7 +1132,7 @@
         <v>0.015107</v>
       </c>
       <c r="C55" t="n">
-        <v>0.856757</v>
+        <v>0.857527</v>
       </c>
     </row>
     <row r="56">
@@ -1142,10 +1142,10 @@
         </is>
       </c>
       <c r="B56" t="n">
-        <v>0.015349</v>
+        <v>0.015107</v>
       </c>
       <c r="C56" t="n">
-        <v>0.854054</v>
+        <v>0.854839</v>
       </c>
     </row>
     <row r="57">
@@ -1155,10 +1155,10 @@
         </is>
       </c>
       <c r="B57" t="n">
-        <v>0.015553</v>
+        <v>0.015349</v>
       </c>
       <c r="C57" t="n">
-        <v>0.851351</v>
+        <v>0.852151</v>
       </c>
     </row>
     <row r="58">
@@ -1168,10 +1168,10 @@
         </is>
       </c>
       <c r="B58" t="n">
-        <v>0.016031</v>
+        <v>0.015553</v>
       </c>
       <c r="C58" t="n">
-        <v>0.848649</v>
+        <v>0.8494620000000001</v>
       </c>
     </row>
     <row r="59">
@@ -1181,10 +1181,10 @@
         </is>
       </c>
       <c r="B59" t="n">
-        <v>0.016343</v>
+        <v>0.016031</v>
       </c>
       <c r="C59" t="n">
-        <v>0.845946</v>
+        <v>0.846774</v>
       </c>
     </row>
     <row r="60">
@@ -1194,10 +1194,10 @@
         </is>
       </c>
       <c r="B60" t="n">
-        <v>0.016545</v>
+        <v>0.016343</v>
       </c>
       <c r="C60" t="n">
-        <v>0.843243</v>
+        <v>0.844086</v>
       </c>
     </row>
     <row r="61">
@@ -1207,10 +1207,10 @@
         </is>
       </c>
       <c r="B61" t="n">
-        <v>0.017135</v>
+        <v>0.016545</v>
       </c>
       <c r="C61" t="n">
-        <v>0.840541</v>
+        <v>0.841398</v>
       </c>
     </row>
     <row r="62">
@@ -1220,10 +1220,10 @@
         </is>
       </c>
       <c r="B62" t="n">
-        <v>0.017276</v>
+        <v>0.017135</v>
       </c>
       <c r="C62" t="n">
-        <v>0.837838</v>
+        <v>0.83871</v>
       </c>
     </row>
     <row r="63">
@@ -1233,10 +1233,10 @@
         </is>
       </c>
       <c r="B63" t="n">
-        <v>0.017776</v>
+        <v>0.017276</v>
       </c>
       <c r="C63" t="n">
-        <v>0.835135</v>
+        <v>0.836022</v>
       </c>
     </row>
     <row r="64">
@@ -1246,10 +1246,10 @@
         </is>
       </c>
       <c r="B64" t="n">
-        <v>0.018505</v>
+        <v>0.017776</v>
       </c>
       <c r="C64" t="n">
-        <v>0.8324319999999999</v>
+        <v>0.833333</v>
       </c>
     </row>
     <row r="65">
@@ -1259,10 +1259,10 @@
         </is>
       </c>
       <c r="B65" t="n">
-        <v>0.018629</v>
+        <v>0.018505</v>
       </c>
       <c r="C65" t="n">
-        <v>0.82973</v>
+        <v>0.830645</v>
       </c>
     </row>
     <row r="66">
@@ -1272,10 +1272,10 @@
         </is>
       </c>
       <c r="B66" t="n">
-        <v>0.018757</v>
+        <v>0.018629</v>
       </c>
       <c r="C66" t="n">
-        <v>0.827027</v>
+        <v>0.8279570000000001</v>
       </c>
     </row>
     <row r="67">
@@ -1285,10 +1285,10 @@
         </is>
       </c>
       <c r="B67" t="n">
-        <v>0.018801</v>
+        <v>0.018757</v>
       </c>
       <c r="C67" t="n">
-        <v>0.8243239999999999</v>
+        <v>0.825269</v>
       </c>
     </row>
     <row r="68">
@@ -1298,10 +1298,10 @@
         </is>
       </c>
       <c r="B68" t="n">
-        <v>0.018847</v>
+        <v>0.018801</v>
       </c>
       <c r="C68" t="n">
-        <v>0.821622</v>
+        <v>0.822581</v>
       </c>
     </row>
     <row r="69">
@@ -1311,10 +1311,10 @@
         </is>
       </c>
       <c r="B69" t="n">
-        <v>0.018931</v>
+        <v>0.018847</v>
       </c>
       <c r="C69" t="n">
-        <v>0.818919</v>
+        <v>0.819892</v>
       </c>
     </row>
     <row r="70">
@@ -1324,10 +1324,10 @@
         </is>
       </c>
       <c r="B70" t="n">
-        <v>0.019049</v>
+        <v>0.018931</v>
       </c>
       <c r="C70" t="n">
-        <v>0.8162160000000001</v>
+        <v>0.817204</v>
       </c>
     </row>
     <row r="71">
@@ -1337,10 +1337,10 @@
         </is>
       </c>
       <c r="B71" t="n">
-        <v>0.019463</v>
+        <v>0.019049</v>
       </c>
       <c r="C71" t="n">
-        <v>0.813514</v>
+        <v>0.814516</v>
       </c>
     </row>
     <row r="72">
@@ -1350,10 +1350,10 @@
         </is>
       </c>
       <c r="B72" t="n">
-        <v>0.01962</v>
+        <v>0.019463</v>
       </c>
       <c r="C72" t="n">
-        <v>0.8108109999999999</v>
+        <v>0.811828</v>
       </c>
     </row>
     <row r="73">
@@ -1363,10 +1363,10 @@
         </is>
       </c>
       <c r="B73" t="n">
-        <v>0.019953</v>
+        <v>0.01962</v>
       </c>
       <c r="C73" t="n">
-        <v>0.808108</v>
+        <v>0.80914</v>
       </c>
     </row>
     <row r="74">
@@ -1376,10 +1376,10 @@
         </is>
       </c>
       <c r="B74" t="n">
-        <v>0.020393</v>
+        <v>0.019953</v>
       </c>
       <c r="C74" t="n">
-        <v>0.805405</v>
+        <v>0.8064519999999999</v>
       </c>
     </row>
     <row r="75">
@@ -1389,10 +1389,10 @@
         </is>
       </c>
       <c r="B75" t="n">
-        <v>0.02048</v>
+        <v>0.020393</v>
       </c>
       <c r="C75" t="n">
-        <v>0.8027030000000001</v>
+        <v>0.803763</v>
       </c>
     </row>
     <row r="76">
@@ -1402,10 +1402,10 @@
         </is>
       </c>
       <c r="B76" t="n">
-        <v>0.020817</v>
+        <v>0.02048</v>
       </c>
       <c r="C76" t="n">
-        <v>0.8</v>
+        <v>0.801075</v>
       </c>
     </row>
     <row r="77">
@@ -1415,10 +1415,10 @@
         </is>
       </c>
       <c r="B77" t="n">
-        <v>0.021604</v>
+        <v>0.020817</v>
       </c>
       <c r="C77" t="n">
-        <v>0.797297</v>
+        <v>0.798387</v>
       </c>
     </row>
     <row r="78">
@@ -1428,10 +1428,10 @@
         </is>
       </c>
       <c r="B78" t="n">
-        <v>0.021918</v>
+        <v>0.021604</v>
       </c>
       <c r="C78" t="n">
-        <v>0.7945950000000001</v>
+        <v>0.795699</v>
       </c>
     </row>
     <row r="79">
@@ -1441,10 +1441,10 @@
         </is>
       </c>
       <c r="B79" t="n">
-        <v>0.021962</v>
+        <v>0.021918</v>
       </c>
       <c r="C79" t="n">
-        <v>0.791892</v>
+        <v>0.793011</v>
       </c>
     </row>
     <row r="80">
@@ -1454,10 +1454,10 @@
         </is>
       </c>
       <c r="B80" t="n">
-        <v>0.022008</v>
+        <v>0.021962</v>
       </c>
       <c r="C80" t="n">
-        <v>0.789189</v>
+        <v>0.790323</v>
       </c>
     </row>
     <row r="81">
@@ -1467,10 +1467,10 @@
         </is>
       </c>
       <c r="B81" t="n">
-        <v>0.022011</v>
+        <v>0.022008</v>
       </c>
       <c r="C81" t="n">
-        <v>0.786486</v>
+        <v>0.7876339999999999</v>
       </c>
     </row>
     <row r="82">
@@ -1480,10 +1480,10 @@
         </is>
       </c>
       <c r="B82" t="n">
-        <v>0.022121</v>
+        <v>0.022011</v>
       </c>
       <c r="C82" t="n">
-        <v>0.783784</v>
+        <v>0.784946</v>
       </c>
     </row>
     <row r="83">
@@ -1493,10 +1493,10 @@
         </is>
       </c>
       <c r="B83" t="n">
-        <v>0.022324</v>
+        <v>0.022121</v>
       </c>
       <c r="C83" t="n">
-        <v>0.781081</v>
+        <v>0.782258</v>
       </c>
     </row>
     <row r="84">
@@ -1506,10 +1506,10 @@
         </is>
       </c>
       <c r="B84" t="n">
-        <v>0.022543</v>
+        <v>0.022324</v>
       </c>
       <c r="C84" t="n">
-        <v>0.778378</v>
+        <v>0.77957</v>
       </c>
     </row>
     <row r="85">
@@ -1519,10 +1519,10 @@
         </is>
       </c>
       <c r="B85" t="n">
-        <v>0.022891</v>
+        <v>0.022543</v>
       </c>
       <c r="C85" t="n">
-        <v>0.775676</v>
+        <v>0.776882</v>
       </c>
     </row>
     <row r="86">
@@ -1532,10 +1532,10 @@
         </is>
       </c>
       <c r="B86" t="n">
-        <v>0.023483</v>
+        <v>0.022891</v>
       </c>
       <c r="C86" t="n">
-        <v>0.772973</v>
+        <v>0.774194</v>
       </c>
     </row>
     <row r="87">
@@ -1545,10 +1545,10 @@
         </is>
       </c>
       <c r="B87" t="n">
-        <v>0.023855</v>
+        <v>0.023483</v>
       </c>
       <c r="C87" t="n">
-        <v>0.77027</v>
+        <v>0.771505</v>
       </c>
     </row>
     <row r="88">
@@ -1558,10 +1558,10 @@
         </is>
       </c>
       <c r="B88" t="n">
-        <v>0.023991</v>
+        <v>0.023855</v>
       </c>
       <c r="C88" t="n">
-        <v>0.767568</v>
+        <v>0.768817</v>
       </c>
     </row>
     <row r="89">
@@ -1571,10 +1571,10 @@
         </is>
       </c>
       <c r="B89" t="n">
-        <v>0.02408</v>
+        <v>0.023991</v>
       </c>
       <c r="C89" t="n">
-        <v>0.764865</v>
+        <v>0.7661289999999999</v>
       </c>
     </row>
     <row r="90">
@@ -1584,10 +1584,10 @@
         </is>
       </c>
       <c r="B90" t="n">
-        <v>0.024556</v>
+        <v>0.02408</v>
       </c>
       <c r="C90" t="n">
-        <v>0.762162</v>
+        <v>0.763441</v>
       </c>
     </row>
     <row r="91">
@@ -1597,10 +1597,10 @@
         </is>
       </c>
       <c r="B91" t="n">
-        <v>0.024703</v>
+        <v>0.024556</v>
       </c>
       <c r="C91" t="n">
-        <v>0.759459</v>
+        <v>0.760753</v>
       </c>
     </row>
     <row r="92">
@@ -1610,10 +1610,10 @@
         </is>
       </c>
       <c r="B92" t="n">
-        <v>0.025311</v>
+        <v>0.024703</v>
       </c>
       <c r="C92" t="n">
-        <v>0.756757</v>
+        <v>0.758065</v>
       </c>
     </row>
     <row r="93">
@@ -1623,10 +1623,10 @@
         </is>
       </c>
       <c r="B93" t="n">
-        <v>0.025327</v>
+        <v>0.025311</v>
       </c>
       <c r="C93" t="n">
-        <v>0.754054</v>
+        <v>0.755376</v>
       </c>
     </row>
     <row r="94">
@@ -1636,10 +1636,10 @@
         </is>
       </c>
       <c r="B94" t="n">
-        <v>0.025544</v>
+        <v>0.025327</v>
       </c>
       <c r="C94" t="n">
-        <v>0.751351</v>
+        <v>0.752688</v>
       </c>
     </row>
     <row r="95">
@@ -1649,10 +1649,10 @@
         </is>
       </c>
       <c r="B95" t="n">
-        <v>0.025755</v>
+        <v>0.025544</v>
       </c>
       <c r="C95" t="n">
-        <v>0.748649</v>
+        <v>0.75</v>
       </c>
     </row>
     <row r="96">
@@ -1662,10 +1662,10 @@
         </is>
       </c>
       <c r="B96" t="n">
-        <v>0.025837</v>
+        <v>0.025755</v>
       </c>
       <c r="C96" t="n">
-        <v>0.745946</v>
+        <v>0.747312</v>
       </c>
     </row>
     <row r="97">
@@ -1675,10 +1675,10 @@
         </is>
       </c>
       <c r="B97" t="n">
-        <v>0.026545</v>
+        <v>0.025837</v>
       </c>
       <c r="C97" t="n">
-        <v>0.743243</v>
+        <v>0.744624</v>
       </c>
     </row>
     <row r="98">
@@ -1688,10 +1688,10 @@
         </is>
       </c>
       <c r="B98" t="n">
-        <v>0.027214</v>
+        <v>0.026545</v>
       </c>
       <c r="C98" t="n">
-        <v>0.740541</v>
+        <v>0.741935</v>
       </c>
     </row>
     <row r="99">
@@ -1701,10 +1701,10 @@
         </is>
       </c>
       <c r="B99" t="n">
-        <v>0.027413</v>
+        <v>0.027214</v>
       </c>
       <c r="C99" t="n">
-        <v>0.737838</v>
+        <v>0.739247</v>
       </c>
     </row>
     <row r="100">
@@ -1714,10 +1714,10 @@
         </is>
       </c>
       <c r="B100" t="n">
-        <v>0.028098</v>
+        <v>0.027413</v>
       </c>
       <c r="C100" t="n">
-        <v>0.735135</v>
+        <v>0.736559</v>
       </c>
     </row>
     <row r="101">
@@ -1727,10 +1727,10 @@
         </is>
       </c>
       <c r="B101" t="n">
-        <v>0.028186</v>
+        <v>0.028098</v>
       </c>
       <c r="C101" t="n">
-        <v>0.732432</v>
+        <v>0.7338710000000001</v>
       </c>
     </row>
     <row r="102">
@@ -1740,10 +1740,10 @@
         </is>
       </c>
       <c r="B102" t="n">
-        <v>0.028398</v>
+        <v>0.028186</v>
       </c>
       <c r="C102" t="n">
-        <v>0.72973</v>
+        <v>0.731183</v>
       </c>
     </row>
     <row r="103">
@@ -1753,10 +1753,10 @@
         </is>
       </c>
       <c r="B103" t="n">
-        <v>0.028421</v>
+        <v>0.028398</v>
       </c>
       <c r="C103" t="n">
-        <v>0.727027</v>
+        <v>0.728495</v>
       </c>
     </row>
     <row r="104">
@@ -1766,10 +1766,10 @@
         </is>
       </c>
       <c r="B104" t="n">
-        <v>0.029071</v>
+        <v>0.028421</v>
       </c>
       <c r="C104" t="n">
-        <v>0.724324</v>
+        <v>0.725806</v>
       </c>
     </row>
     <row r="105">
@@ -1779,10 +1779,10 @@
         </is>
       </c>
       <c r="B105" t="n">
-        <v>0.02956</v>
+        <v>0.029071</v>
       </c>
       <c r="C105" t="n">
-        <v>0.721622</v>
+        <v>0.723118</v>
       </c>
     </row>
     <row r="106">
@@ -1795,7 +1795,7 @@
         <v>0.029588</v>
       </c>
       <c r="C106" t="n">
-        <v>0.718919</v>
+        <v>0.72043</v>
       </c>
     </row>
     <row r="107">
@@ -1808,7 +1808,7 @@
         <v>0.030158</v>
       </c>
       <c r="C107" t="n">
-        <v>0.716216</v>
+        <v>0.717742</v>
       </c>
     </row>
     <row r="108">
@@ -1821,7 +1821,7 @@
         <v>0.030201</v>
       </c>
       <c r="C108" t="n">
-        <v>0.713514</v>
+        <v>0.715054</v>
       </c>
     </row>
     <row r="109">
@@ -1834,7 +1834,7 @@
         <v>0.03027</v>
       </c>
       <c r="C109" t="n">
-        <v>0.710811</v>
+        <v>0.7123660000000001</v>
       </c>
     </row>
     <row r="110">
@@ -1847,7 +1847,7 @@
         <v>0.030697</v>
       </c>
       <c r="C110" t="n">
-        <v>0.708108</v>
+        <v>0.709677</v>
       </c>
     </row>
     <row r="111">
@@ -1860,7 +1860,7 @@
         <v>0.030903</v>
       </c>
       <c r="C111" t="n">
-        <v>0.7054049999999999</v>
+        <v>0.706989</v>
       </c>
     </row>
     <row r="112">
@@ -1873,7 +1873,7 @@
         <v>0.031127</v>
       </c>
       <c r="C112" t="n">
-        <v>0.702703</v>
+        <v>0.704301</v>
       </c>
     </row>
     <row r="113">
@@ -1886,7 +1886,7 @@
         <v>0.031327</v>
       </c>
       <c r="C113" t="n">
-        <v>0.7</v>
+        <v>0.701613</v>
       </c>
     </row>
     <row r="114">
@@ -1899,7 +1899,7 @@
         <v>0.031556</v>
       </c>
       <c r="C114" t="n">
-        <v>0.6972969999999999</v>
+        <v>0.698925</v>
       </c>
     </row>
     <row r="115">
@@ -1912,7 +1912,7 @@
         <v>0.031969</v>
       </c>
       <c r="C115" t="n">
-        <v>0.694595</v>
+        <v>0.696237</v>
       </c>
     </row>
     <row r="116">
@@ -1925,7 +1925,7 @@
         <v>0.032827</v>
       </c>
       <c r="C116" t="n">
-        <v>0.691892</v>
+        <v>0.6935480000000001</v>
       </c>
     </row>
     <row r="117">
@@ -1938,7 +1938,7 @@
         <v>0.033315</v>
       </c>
       <c r="C117" t="n">
-        <v>0.6891890000000001</v>
+        <v>0.69086</v>
       </c>
     </row>
     <row r="118">
@@ -1951,7 +1951,7 @@
         <v>0.033373</v>
       </c>
       <c r="C118" t="n">
-        <v>0.686486</v>
+        <v>0.688172</v>
       </c>
     </row>
     <row r="119">
@@ -1964,7 +1964,7 @@
         <v>0.033481</v>
       </c>
       <c r="C119" t="n">
-        <v>0.6837839999999999</v>
+        <v>0.685484</v>
       </c>
     </row>
     <row r="120">
@@ -1977,7 +1977,7 @@
         <v>0.03374</v>
       </c>
       <c r="C120" t="n">
-        <v>0.681081</v>
+        <v>0.682796</v>
       </c>
     </row>
     <row r="121">
@@ -1990,7 +1990,7 @@
         <v>0.033774</v>
       </c>
       <c r="C121" t="n">
-        <v>0.678378</v>
+        <v>0.680108</v>
       </c>
     </row>
     <row r="122">
@@ -2003,7 +2003,7 @@
         <v>0.033884</v>
       </c>
       <c r="C122" t="n">
-        <v>0.6756760000000001</v>
+        <v>0.677419</v>
       </c>
     </row>
     <row r="123">
@@ -2016,7 +2016,7 @@
         <v>0.034047</v>
       </c>
       <c r="C123" t="n">
-        <v>0.672973</v>
+        <v>0.674731</v>
       </c>
     </row>
     <row r="124">
@@ -2029,7 +2029,7 @@
         <v>0.034274</v>
       </c>
       <c r="C124" t="n">
-        <v>0.67027</v>
+        <v>0.6720429999999999</v>
       </c>
     </row>
     <row r="125">
@@ -2042,7 +2042,7 @@
         <v>0.035039</v>
       </c>
       <c r="C125" t="n">
-        <v>0.6675680000000001</v>
+        <v>0.669355</v>
       </c>
     </row>
     <row r="126">
@@ -2055,7 +2055,7 @@
         <v>0.035117</v>
       </c>
       <c r="C126" t="n">
-        <v>0.664865</v>
+        <v>0.666667</v>
       </c>
     </row>
     <row r="127">
@@ -2068,7 +2068,7 @@
         <v>0.035159</v>
       </c>
       <c r="C127" t="n">
-        <v>0.662162</v>
+        <v>0.663978</v>
       </c>
     </row>
     <row r="128">
@@ -2081,7 +2081,7 @@
         <v>0.035654</v>
       </c>
       <c r="C128" t="n">
-        <v>0.659459</v>
+        <v>0.66129</v>
       </c>
     </row>
     <row r="129">
@@ -2091,10 +2091,10 @@
         </is>
       </c>
       <c r="B129" t="n">
-        <v>0.037805</v>
+        <v>0.036</v>
       </c>
       <c r="C129" t="n">
-        <v>0.656757</v>
+        <v>0.658602</v>
       </c>
     </row>
     <row r="130">
@@ -2104,10 +2104,10 @@
         </is>
       </c>
       <c r="B130" t="n">
-        <v>0.03815</v>
+        <v>0.037307</v>
       </c>
       <c r="C130" t="n">
-        <v>0.654054</v>
+        <v>0.655914</v>
       </c>
     </row>
     <row r="131">
@@ -2117,10 +2117,10 @@
         </is>
       </c>
       <c r="B131" t="n">
-        <v>0.038316</v>
+        <v>0.037805</v>
       </c>
       <c r="C131" t="n">
-        <v>0.651351</v>
+        <v>0.653226</v>
       </c>
     </row>
     <row r="132">
@@ -2130,10 +2130,10 @@
         </is>
       </c>
       <c r="B132" t="n">
-        <v>0.03876</v>
+        <v>0.03815</v>
       </c>
       <c r="C132" t="n">
-        <v>0.648649</v>
+        <v>0.6505379999999999</v>
       </c>
     </row>
     <row r="133">
@@ -2143,10 +2143,10 @@
         </is>
       </c>
       <c r="B133" t="n">
-        <v>0.039595</v>
+        <v>0.038316</v>
       </c>
       <c r="C133" t="n">
-        <v>0.645946</v>
+        <v>0.647849</v>
       </c>
     </row>
     <row r="134">
@@ -2156,10 +2156,10 @@
         </is>
       </c>
       <c r="B134" t="n">
-        <v>0.03982</v>
+        <v>0.03876</v>
       </c>
       <c r="C134" t="n">
-        <v>0.643243</v>
+        <v>0.645161</v>
       </c>
     </row>
     <row r="135">
@@ -2169,10 +2169,10 @@
         </is>
       </c>
       <c r="B135" t="n">
-        <v>0.0404</v>
+        <v>0.039595</v>
       </c>
       <c r="C135" t="n">
-        <v>0.640541</v>
+        <v>0.642473</v>
       </c>
     </row>
     <row r="136">
@@ -2182,10 +2182,10 @@
         </is>
       </c>
       <c r="B136" t="n">
-        <v>0.040915</v>
+        <v>0.03982</v>
       </c>
       <c r="C136" t="n">
-        <v>0.637838</v>
+        <v>0.639785</v>
       </c>
     </row>
     <row r="137">
@@ -2195,10 +2195,10 @@
         </is>
       </c>
       <c r="B137" t="n">
-        <v>0.040931</v>
+        <v>0.040915</v>
       </c>
       <c r="C137" t="n">
-        <v>0.635135</v>
+        <v>0.637097</v>
       </c>
     </row>
     <row r="138">
@@ -2208,10 +2208,10 @@
         </is>
       </c>
       <c r="B138" t="n">
-        <v>0.040948</v>
+        <v>0.040931</v>
       </c>
       <c r="C138" t="n">
-        <v>0.632432</v>
+        <v>0.634409</v>
       </c>
     </row>
     <row r="139">
@@ -2221,10 +2221,10 @@
         </is>
       </c>
       <c r="B139" t="n">
-        <v>0.040975</v>
+        <v>0.040948</v>
       </c>
       <c r="C139" t="n">
-        <v>0.62973</v>
+        <v>0.6317199999999999</v>
       </c>
     </row>
     <row r="140">
@@ -2234,10 +2234,10 @@
         </is>
       </c>
       <c r="B140" t="n">
-        <v>0.041132</v>
+        <v>0.040975</v>
       </c>
       <c r="C140" t="n">
-        <v>0.627027</v>
+        <v>0.629032</v>
       </c>
     </row>
     <row r="141">
@@ -2247,10 +2247,10 @@
         </is>
       </c>
       <c r="B141" t="n">
-        <v>0.041243</v>
+        <v>0.041132</v>
       </c>
       <c r="C141" t="n">
-        <v>0.624324</v>
+        <v>0.626344</v>
       </c>
     </row>
     <row r="142">
@@ -2260,10 +2260,10 @@
         </is>
       </c>
       <c r="B142" t="n">
-        <v>0.041331</v>
+        <v>0.041243</v>
       </c>
       <c r="C142" t="n">
-        <v>0.621622</v>
+        <v>0.623656</v>
       </c>
     </row>
     <row r="143">
@@ -2273,10 +2273,10 @@
         </is>
       </c>
       <c r="B143" t="n">
-        <v>0.041457</v>
+        <v>0.041331</v>
       </c>
       <c r="C143" t="n">
-        <v>0.618919</v>
+        <v>0.620968</v>
       </c>
     </row>
     <row r="144">
@@ -2286,10 +2286,10 @@
         </is>
       </c>
       <c r="B144" t="n">
-        <v>0.04197</v>
+        <v>0.041457</v>
       </c>
       <c r="C144" t="n">
-        <v>0.616216</v>
+        <v>0.6182800000000001</v>
       </c>
     </row>
     <row r="145">
@@ -2299,10 +2299,10 @@
         </is>
       </c>
       <c r="B145" t="n">
-        <v>0.042735</v>
+        <v>0.04197</v>
       </c>
       <c r="C145" t="n">
-        <v>0.613514</v>
+        <v>0.615591</v>
       </c>
     </row>
     <row r="146">
@@ -2312,10 +2312,10 @@
         </is>
       </c>
       <c r="B146" t="n">
-        <v>0.043144</v>
+        <v>0.042735</v>
       </c>
       <c r="C146" t="n">
-        <v>0.610811</v>
+        <v>0.612903</v>
       </c>
     </row>
     <row r="147">
@@ -2325,10 +2325,10 @@
         </is>
       </c>
       <c r="B147" t="n">
-        <v>0.043468</v>
+        <v>0.043144</v>
       </c>
       <c r="C147" t="n">
-        <v>0.608108</v>
+        <v>0.610215</v>
       </c>
     </row>
     <row r="148">
@@ -2338,10 +2338,10 @@
         </is>
       </c>
       <c r="B148" t="n">
-        <v>0.04427</v>
+        <v>0.043468</v>
       </c>
       <c r="C148" t="n">
-        <v>0.605405</v>
+        <v>0.607527</v>
       </c>
     </row>
     <row r="149">
@@ -2351,10 +2351,10 @@
         </is>
       </c>
       <c r="B149" t="n">
-        <v>0.044556</v>
+        <v>0.04427</v>
       </c>
       <c r="C149" t="n">
-        <v>0.602703</v>
+        <v>0.604839</v>
       </c>
     </row>
     <row r="150">
@@ -2364,10 +2364,10 @@
         </is>
       </c>
       <c r="B150" t="n">
-        <v>0.044571</v>
+        <v>0.044556</v>
       </c>
       <c r="C150" t="n">
-        <v>0.6</v>
+        <v>0.602151</v>
       </c>
     </row>
     <row r="151">
@@ -2377,10 +2377,10 @@
         </is>
       </c>
       <c r="B151" t="n">
-        <v>0.044773</v>
+        <v>0.044571</v>
       </c>
       <c r="C151" t="n">
-        <v>0.597297</v>
+        <v>0.5994620000000001</v>
       </c>
     </row>
     <row r="152">
@@ -2390,10 +2390,10 @@
         </is>
       </c>
       <c r="B152" t="n">
-        <v>0.046486</v>
+        <v>0.044773</v>
       </c>
       <c r="C152" t="n">
-        <v>0.594595</v>
+        <v>0.596774</v>
       </c>
     </row>
     <row r="153">
@@ -2403,10 +2403,10 @@
         </is>
       </c>
       <c r="B153" t="n">
-        <v>0.046763</v>
+        <v>0.046486</v>
       </c>
       <c r="C153" t="n">
-        <v>0.591892</v>
+        <v>0.594086</v>
       </c>
     </row>
     <row r="154">
@@ -2416,10 +2416,10 @@
         </is>
       </c>
       <c r="B154" t="n">
-        <v>0.046785</v>
+        <v>0.046763</v>
       </c>
       <c r="C154" t="n">
-        <v>0.589189</v>
+        <v>0.591398</v>
       </c>
     </row>
     <row r="155">
@@ -2429,10 +2429,10 @@
         </is>
       </c>
       <c r="B155" t="n">
-        <v>0.046943</v>
+        <v>0.046785</v>
       </c>
       <c r="C155" t="n">
-        <v>0.586486</v>
+        <v>0.58871</v>
       </c>
     </row>
     <row r="156">
@@ -2442,10 +2442,10 @@
         </is>
       </c>
       <c r="B156" t="n">
-        <v>0.047141</v>
+        <v>0.046943</v>
       </c>
       <c r="C156" t="n">
-        <v>0.583784</v>
+        <v>0.586022</v>
       </c>
     </row>
     <row r="157">
@@ -2455,10 +2455,10 @@
         </is>
       </c>
       <c r="B157" t="n">
-        <v>0.047421</v>
+        <v>0.047141</v>
       </c>
       <c r="C157" t="n">
-        <v>0.581081</v>
+        <v>0.583333</v>
       </c>
     </row>
     <row r="158">
@@ -2468,10 +2468,10 @@
         </is>
       </c>
       <c r="B158" t="n">
-        <v>0.047947</v>
+        <v>0.047421</v>
       </c>
       <c r="C158" t="n">
-        <v>0.5783779999999999</v>
+        <v>0.580645</v>
       </c>
     </row>
     <row r="159">
@@ -2481,10 +2481,10 @@
         </is>
       </c>
       <c r="B159" t="n">
-        <v>0.048746</v>
+        <v>0.047947</v>
       </c>
       <c r="C159" t="n">
-        <v>0.575676</v>
+        <v>0.5779570000000001</v>
       </c>
     </row>
     <row r="160">
@@ -2494,10 +2494,10 @@
         </is>
       </c>
       <c r="B160" t="n">
-        <v>0.049358</v>
+        <v>0.048746</v>
       </c>
       <c r="C160" t="n">
-        <v>0.572973</v>
+        <v>0.575269</v>
       </c>
     </row>
     <row r="161">
@@ -2507,10 +2507,10 @@
         </is>
       </c>
       <c r="B161" t="n">
-        <v>0.049478</v>
+        <v>0.049358</v>
       </c>
       <c r="C161" t="n">
-        <v>0.5702700000000001</v>
+        <v>0.572581</v>
       </c>
     </row>
     <row r="162">
@@ -2520,10 +2520,10 @@
         </is>
       </c>
       <c r="B162" t="n">
-        <v>0.049673</v>
+        <v>0.049478</v>
       </c>
       <c r="C162" t="n">
-        <v>0.567568</v>
+        <v>0.569892</v>
       </c>
     </row>
     <row r="163">
@@ -2533,10 +2533,10 @@
         </is>
       </c>
       <c r="B163" t="n">
-        <v>0.049728</v>
+        <v>0.049673</v>
       </c>
       <c r="C163" t="n">
-        <v>0.564865</v>
+        <v>0.567204</v>
       </c>
     </row>
     <row r="164">
@@ -2546,10 +2546,10 @@
         </is>
       </c>
       <c r="B164" t="n">
-        <v>0.051151</v>
+        <v>0.049728</v>
       </c>
       <c r="C164" t="n">
-        <v>0.5621620000000001</v>
+        <v>0.564516</v>
       </c>
     </row>
     <row r="165">
@@ -2559,10 +2559,10 @@
         </is>
       </c>
       <c r="B165" t="n">
-        <v>0.051423</v>
+        <v>0.051151</v>
       </c>
       <c r="C165" t="n">
-        <v>0.559459</v>
+        <v>0.561828</v>
       </c>
     </row>
     <row r="166">
@@ -2572,10 +2572,10 @@
         </is>
       </c>
       <c r="B166" t="n">
-        <v>0.051449</v>
+        <v>0.051423</v>
       </c>
       <c r="C166" t="n">
-        <v>0.5567569999999999</v>
+        <v>0.55914</v>
       </c>
     </row>
     <row r="167">
@@ -2585,10 +2585,10 @@
         </is>
       </c>
       <c r="B167" t="n">
-        <v>0.051978</v>
+        <v>0.051449</v>
       </c>
       <c r="C167" t="n">
-        <v>0.554054</v>
+        <v>0.5564519999999999</v>
       </c>
     </row>
     <row r="168">
@@ -2598,10 +2598,10 @@
         </is>
       </c>
       <c r="B168" t="n">
-        <v>0.052376</v>
+        <v>0.051978</v>
       </c>
       <c r="C168" t="n">
-        <v>0.551351</v>
+        <v>0.553763</v>
       </c>
     </row>
     <row r="169">
@@ -2611,10 +2611,10 @@
         </is>
       </c>
       <c r="B169" t="n">
-        <v>0.052398</v>
+        <v>0.052376</v>
       </c>
       <c r="C169" t="n">
-        <v>0.5486490000000001</v>
+        <v>0.551075</v>
       </c>
     </row>
     <row r="170">
@@ -2624,10 +2624,10 @@
         </is>
       </c>
       <c r="B170" t="n">
-        <v>0.052526</v>
+        <v>0.052398</v>
       </c>
       <c r="C170" t="n">
-        <v>0.545946</v>
+        <v>0.548387</v>
       </c>
     </row>
     <row r="171">
@@ -2637,10 +2637,10 @@
         </is>
       </c>
       <c r="B171" t="n">
-        <v>0.052682</v>
+        <v>0.052526</v>
       </c>
       <c r="C171" t="n">
-        <v>0.543243</v>
+        <v>0.545699</v>
       </c>
     </row>
     <row r="172">
@@ -2650,10 +2650,10 @@
         </is>
       </c>
       <c r="B172" t="n">
-        <v>0.052941</v>
+        <v>0.052682</v>
       </c>
       <c r="C172" t="n">
-        <v>0.540541</v>
+        <v>0.543011</v>
       </c>
     </row>
     <row r="173">
@@ -2663,10 +2663,10 @@
         </is>
       </c>
       <c r="B173" t="n">
-        <v>0.053316</v>
+        <v>0.052941</v>
       </c>
       <c r="C173" t="n">
-        <v>0.537838</v>
+        <v>0.540323</v>
       </c>
     </row>
     <row r="174">
@@ -2676,10 +2676,10 @@
         </is>
       </c>
       <c r="B174" t="n">
-        <v>0.05382</v>
+        <v>0.053316</v>
       </c>
       <c r="C174" t="n">
-        <v>0.535135</v>
+        <v>0.5376339999999999</v>
       </c>
     </row>
     <row r="175">
@@ -2689,10 +2689,10 @@
         </is>
       </c>
       <c r="B175" t="n">
-        <v>0.05439</v>
+        <v>0.05382</v>
       </c>
       <c r="C175" t="n">
-        <v>0.532432</v>
+        <v>0.534946</v>
       </c>
     </row>
     <row r="176">
@@ -2702,10 +2702,10 @@
         </is>
       </c>
       <c r="B176" t="n">
-        <v>0.054595</v>
+        <v>0.05439</v>
       </c>
       <c r="C176" t="n">
-        <v>0.52973</v>
+        <v>0.532258</v>
       </c>
     </row>
     <row r="177">
@@ -2715,10 +2715,10 @@
         </is>
       </c>
       <c r="B177" t="n">
-        <v>0.05496</v>
+        <v>0.054595</v>
       </c>
       <c r="C177" t="n">
-        <v>0.527027</v>
+        <v>0.52957</v>
       </c>
     </row>
     <row r="178">
@@ -2728,10 +2728,10 @@
         </is>
       </c>
       <c r="B178" t="n">
-        <v>0.0555</v>
+        <v>0.05496</v>
       </c>
       <c r="C178" t="n">
-        <v>0.524324</v>
+        <v>0.526882</v>
       </c>
     </row>
     <row r="179">
@@ -2741,10 +2741,10 @@
         </is>
       </c>
       <c r="B179" t="n">
-        <v>0.055621</v>
+        <v>0.0555</v>
       </c>
       <c r="C179" t="n">
-        <v>0.521622</v>
+        <v>0.524194</v>
       </c>
     </row>
     <row r="180">
@@ -2754,10 +2754,10 @@
         </is>
       </c>
       <c r="B180" t="n">
-        <v>0.056242</v>
+        <v>0.055621</v>
       </c>
       <c r="C180" t="n">
-        <v>0.518919</v>
+        <v>0.521505</v>
       </c>
     </row>
     <row r="181">
@@ -2767,10 +2767,10 @@
         </is>
       </c>
       <c r="B181" t="n">
-        <v>0.056487</v>
+        <v>0.056242</v>
       </c>
       <c r="C181" t="n">
-        <v>0.516216</v>
+        <v>0.518817</v>
       </c>
     </row>
     <row r="182">
@@ -2780,10 +2780,10 @@
         </is>
       </c>
       <c r="B182" t="n">
-        <v>0.056702</v>
+        <v>0.056487</v>
       </c>
       <c r="C182" t="n">
-        <v>0.513514</v>
+        <v>0.5161289999999999</v>
       </c>
     </row>
     <row r="183">
@@ -2793,10 +2793,10 @@
         </is>
       </c>
       <c r="B183" t="n">
-        <v>0.056785</v>
+        <v>0.056702</v>
       </c>
       <c r="C183" t="n">
-        <v>0.510811</v>
+        <v>0.513441</v>
       </c>
     </row>
     <row r="184">
@@ -2806,10 +2806,10 @@
         </is>
       </c>
       <c r="B184" t="n">
-        <v>0.057135</v>
+        <v>0.056785</v>
       </c>
       <c r="C184" t="n">
-        <v>0.508108</v>
+        <v>0.510753</v>
       </c>
     </row>
     <row r="185">
@@ -2819,10 +2819,10 @@
         </is>
       </c>
       <c r="B185" t="n">
-        <v>0.057253</v>
+        <v>0.057135</v>
       </c>
       <c r="C185" t="n">
-        <v>0.505405</v>
+        <v>0.508065</v>
       </c>
     </row>
     <row r="186">
@@ -2832,10 +2832,10 @@
         </is>
       </c>
       <c r="B186" t="n">
-        <v>0.05854</v>
+        <v>0.057253</v>
       </c>
       <c r="C186" t="n">
-        <v>0.502703</v>
+        <v>0.505376</v>
       </c>
     </row>
     <row r="187">
@@ -2845,10 +2845,10 @@
         </is>
       </c>
       <c r="B187" t="n">
-        <v>0.058836</v>
+        <v>0.05854</v>
       </c>
       <c r="C187" t="n">
-        <v>0.5</v>
+        <v>0.502688</v>
       </c>
     </row>
     <row r="188">
@@ -2858,10 +2858,10 @@
         </is>
       </c>
       <c r="B188" t="n">
-        <v>0.059279</v>
+        <v>0.058836</v>
       </c>
       <c r="C188" t="n">
-        <v>0.497297</v>
+        <v>0.5</v>
       </c>
     </row>
     <row r="189">
@@ -2871,10 +2871,10 @@
         </is>
       </c>
       <c r="B189" t="n">
-        <v>0.059323</v>
+        <v>0.059279</v>
       </c>
       <c r="C189" t="n">
-        <v>0.494595</v>
+        <v>0.497312</v>
       </c>
     </row>
     <row r="190">
@@ -2884,10 +2884,10 @@
         </is>
       </c>
       <c r="B190" t="n">
-        <v>0.059367</v>
+        <v>0.059323</v>
       </c>
       <c r="C190" t="n">
-        <v>0.491892</v>
+        <v>0.494624</v>
       </c>
     </row>
     <row r="191">
@@ -2897,10 +2897,10 @@
         </is>
       </c>
       <c r="B191" t="n">
-        <v>0.059553</v>
+        <v>0.059367</v>
       </c>
       <c r="C191" t="n">
-        <v>0.489189</v>
+        <v>0.491935</v>
       </c>
     </row>
     <row r="192">
@@ -2910,10 +2910,10 @@
         </is>
       </c>
       <c r="B192" t="n">
-        <v>0.059579</v>
+        <v>0.059553</v>
       </c>
       <c r="C192" t="n">
-        <v>0.486486</v>
+        <v>0.489247</v>
       </c>
     </row>
     <row r="193">
@@ -2923,10 +2923,10 @@
         </is>
       </c>
       <c r="B193" t="n">
-        <v>0.060111</v>
+        <v>0.059579</v>
       </c>
       <c r="C193" t="n">
-        <v>0.483784</v>
+        <v>0.486559</v>
       </c>
     </row>
     <row r="194">
@@ -2936,10 +2936,10 @@
         </is>
       </c>
       <c r="B194" t="n">
-        <v>0.060827</v>
+        <v>0.060111</v>
       </c>
       <c r="C194" t="n">
-        <v>0.481081</v>
+        <v>0.483871</v>
       </c>
     </row>
     <row r="195">
@@ -2949,10 +2949,10 @@
         </is>
       </c>
       <c r="B195" t="n">
-        <v>0.061784</v>
+        <v>0.060827</v>
       </c>
       <c r="C195" t="n">
-        <v>0.478378</v>
+        <v>0.481183</v>
       </c>
     </row>
     <row r="196">
@@ -2962,10 +2962,10 @@
         </is>
       </c>
       <c r="B196" t="n">
-        <v>0.06179</v>
+        <v>0.061784</v>
       </c>
       <c r="C196" t="n">
-        <v>0.475676</v>
+        <v>0.478495</v>
       </c>
     </row>
     <row r="197">
@@ -2975,10 +2975,10 @@
         </is>
       </c>
       <c r="B197" t="n">
-        <v>0.061969</v>
+        <v>0.06179</v>
       </c>
       <c r="C197" t="n">
-        <v>0.472973</v>
+        <v>0.475806</v>
       </c>
     </row>
     <row r="198">
@@ -2988,10 +2988,10 @@
         </is>
       </c>
       <c r="B198" t="n">
-        <v>0.062129</v>
+        <v>0.061969</v>
       </c>
       <c r="C198" t="n">
-        <v>0.47027</v>
+        <v>0.473118</v>
       </c>
     </row>
     <row r="199">
@@ -3001,10 +3001,10 @@
         </is>
       </c>
       <c r="B199" t="n">
-        <v>0.063808</v>
+        <v>0.062129</v>
       </c>
       <c r="C199" t="n">
-        <v>0.467568</v>
+        <v>0.47043</v>
       </c>
     </row>
     <row r="200">
@@ -3014,10 +3014,10 @@
         </is>
       </c>
       <c r="B200" t="n">
-        <v>0.06464300000000001</v>
+        <v>0.06263299999999999</v>
       </c>
       <c r="C200" t="n">
-        <v>0.464865</v>
+        <v>0.467742</v>
       </c>
     </row>
     <row r="201">
@@ -3027,10 +3027,10 @@
         </is>
       </c>
       <c r="B201" t="n">
-        <v>0.06555900000000001</v>
+        <v>0.063808</v>
       </c>
       <c r="C201" t="n">
-        <v>0.462162</v>
+        <v>0.465054</v>
       </c>
     </row>
     <row r="202">
@@ -3040,10 +3040,10 @@
         </is>
       </c>
       <c r="B202" t="n">
-        <v>0.066775</v>
+        <v>0.06464300000000001</v>
       </c>
       <c r="C202" t="n">
-        <v>0.459459</v>
+        <v>0.462366</v>
       </c>
     </row>
     <row r="203">
@@ -3053,10 +3053,10 @@
         </is>
       </c>
       <c r="B203" t="n">
-        <v>0.066914</v>
+        <v>0.06555900000000001</v>
       </c>
       <c r="C203" t="n">
-        <v>0.456757</v>
+        <v>0.459677</v>
       </c>
     </row>
     <row r="204">
@@ -3066,10 +3066,10 @@
         </is>
       </c>
       <c r="B204" t="n">
-        <v>0.067176</v>
+        <v>0.066775</v>
       </c>
       <c r="C204" t="n">
-        <v>0.454054</v>
+        <v>0.456989</v>
       </c>
     </row>
     <row r="205">
@@ -3079,10 +3079,10 @@
         </is>
       </c>
       <c r="B205" t="n">
-        <v>0.06736399999999999</v>
+        <v>0.066914</v>
       </c>
       <c r="C205" t="n">
-        <v>0.451351</v>
+        <v>0.454301</v>
       </c>
     </row>
     <row r="206">
@@ -3092,10 +3092,10 @@
         </is>
       </c>
       <c r="B206" t="n">
-        <v>0.067555</v>
+        <v>0.067176</v>
       </c>
       <c r="C206" t="n">
-        <v>0.448649</v>
+        <v>0.451613</v>
       </c>
     </row>
     <row r="207">
@@ -3105,10 +3105,10 @@
         </is>
       </c>
       <c r="B207" t="n">
-        <v>0.067644</v>
+        <v>0.06736399999999999</v>
       </c>
       <c r="C207" t="n">
-        <v>0.445946</v>
+        <v>0.448925</v>
       </c>
     </row>
     <row r="208">
@@ -3118,10 +3118,10 @@
         </is>
       </c>
       <c r="B208" t="n">
-        <v>0.068111</v>
+        <v>0.067555</v>
       </c>
       <c r="C208" t="n">
-        <v>0.443243</v>
+        <v>0.446237</v>
       </c>
     </row>
     <row r="209">
@@ -3131,10 +3131,10 @@
         </is>
       </c>
       <c r="B209" t="n">
-        <v>0.068601</v>
+        <v>0.067604</v>
       </c>
       <c r="C209" t="n">
-        <v>0.440541</v>
+        <v>0.443548</v>
       </c>
     </row>
     <row r="210">
@@ -3144,10 +3144,10 @@
         </is>
       </c>
       <c r="B210" t="n">
-        <v>0.06904200000000001</v>
+        <v>0.067644</v>
       </c>
       <c r="C210" t="n">
-        <v>0.437838</v>
+        <v>0.44086</v>
       </c>
     </row>
     <row r="211">
@@ -3157,10 +3157,10 @@
         </is>
       </c>
       <c r="B211" t="n">
-        <v>0.06909</v>
+        <v>0.068111</v>
       </c>
       <c r="C211" t="n">
-        <v>0.435135</v>
+        <v>0.438172</v>
       </c>
     </row>
     <row r="212">
@@ -3170,10 +3170,10 @@
         </is>
       </c>
       <c r="B212" t="n">
-        <v>0.069253</v>
+        <v>0.068601</v>
       </c>
       <c r="C212" t="n">
-        <v>0.432432</v>
+        <v>0.435484</v>
       </c>
     </row>
     <row r="213">
@@ -3183,10 +3183,10 @@
         </is>
       </c>
       <c r="B213" t="n">
-        <v>0.070214</v>
+        <v>0.06904200000000001</v>
       </c>
       <c r="C213" t="n">
-        <v>0.42973</v>
+        <v>0.432796</v>
       </c>
     </row>
     <row r="214">
@@ -3196,10 +3196,10 @@
         </is>
       </c>
       <c r="B214" t="n">
-        <v>0.070659</v>
+        <v>0.06909</v>
       </c>
       <c r="C214" t="n">
-        <v>0.427027</v>
+        <v>0.430108</v>
       </c>
     </row>
     <row r="215">
@@ -3209,10 +3209,10 @@
         </is>
       </c>
       <c r="B215" t="n">
-        <v>0.072684</v>
+        <v>0.069253</v>
       </c>
       <c r="C215" t="n">
-        <v>0.424324</v>
+        <v>0.427419</v>
       </c>
     </row>
     <row r="216">
@@ -3222,10 +3222,10 @@
         </is>
       </c>
       <c r="B216" t="n">
-        <v>0.072744</v>
+        <v>0.070214</v>
       </c>
       <c r="C216" t="n">
-        <v>0.421622</v>
+        <v>0.424731</v>
       </c>
     </row>
     <row r="217">
@@ -3235,10 +3235,10 @@
         </is>
       </c>
       <c r="B217" t="n">
-        <v>0.07295599999999999</v>
+        <v>0.070659</v>
       </c>
       <c r="C217" t="n">
-        <v>0.418919</v>
+        <v>0.422043</v>
       </c>
     </row>
     <row r="218">
@@ -3248,10 +3248,10 @@
         </is>
       </c>
       <c r="B218" t="n">
-        <v>0.07331</v>
+        <v>0.072684</v>
       </c>
       <c r="C218" t="n">
-        <v>0.416216</v>
+        <v>0.419355</v>
       </c>
     </row>
     <row r="219">
@@ -3261,10 +3261,10 @@
         </is>
       </c>
       <c r="B219" t="n">
-        <v>0.07380299999999999</v>
+        <v>0.072744</v>
       </c>
       <c r="C219" t="n">
-        <v>0.413514</v>
+        <v>0.416667</v>
       </c>
     </row>
     <row r="220">
@@ -3274,10 +3274,10 @@
         </is>
       </c>
       <c r="B220" t="n">
-        <v>0.07424799999999999</v>
+        <v>0.07295599999999999</v>
       </c>
       <c r="C220" t="n">
-        <v>0.410811</v>
+        <v>0.413978</v>
       </c>
     </row>
     <row r="221">
@@ -3287,10 +3287,10 @@
         </is>
       </c>
       <c r="B221" t="n">
-        <v>0.07437100000000001</v>
+        <v>0.07331</v>
       </c>
       <c r="C221" t="n">
-        <v>0.408108</v>
+        <v>0.41129</v>
       </c>
     </row>
     <row r="222">
@@ -3300,10 +3300,10 @@
         </is>
       </c>
       <c r="B222" t="n">
-        <v>0.075876</v>
+        <v>0.07380299999999999</v>
       </c>
       <c r="C222" t="n">
-        <v>0.405405</v>
+        <v>0.408602</v>
       </c>
     </row>
     <row r="223">
@@ -3313,10 +3313,10 @@
         </is>
       </c>
       <c r="B223" t="n">
-        <v>0.07708</v>
+        <v>0.07424799999999999</v>
       </c>
       <c r="C223" t="n">
-        <v>0.402703</v>
+        <v>0.405914</v>
       </c>
     </row>
     <row r="224">
@@ -3326,10 +3326,10 @@
         </is>
       </c>
       <c r="B224" t="n">
-        <v>0.07757799999999999</v>
+        <v>0.07437100000000001</v>
       </c>
       <c r="C224" t="n">
-        <v>0.4</v>
+        <v>0.403226</v>
       </c>
     </row>
     <row r="225">
@@ -3339,10 +3339,10 @@
         </is>
       </c>
       <c r="B225" t="n">
-        <v>0.077863</v>
+        <v>0.075876</v>
       </c>
       <c r="C225" t="n">
-        <v>0.397297</v>
+        <v>0.400538</v>
       </c>
     </row>
     <row r="226">
@@ -3352,10 +3352,10 @@
         </is>
       </c>
       <c r="B226" t="n">
-        <v>0.07885499999999999</v>
+        <v>0.07708</v>
       </c>
       <c r="C226" t="n">
-        <v>0.394595</v>
+        <v>0.397849</v>
       </c>
     </row>
     <row r="227">
@@ -3365,10 +3365,10 @@
         </is>
       </c>
       <c r="B227" t="n">
-        <v>0.07921499999999999</v>
+        <v>0.07757799999999999</v>
       </c>
       <c r="C227" t="n">
-        <v>0.391892</v>
+        <v>0.395161</v>
       </c>
     </row>
     <row r="228">
@@ -3378,10 +3378,10 @@
         </is>
       </c>
       <c r="B228" t="n">
-        <v>0.079239</v>
+        <v>0.07779700000000001</v>
       </c>
       <c r="C228" t="n">
-        <v>0.389189</v>
+        <v>0.392473</v>
       </c>
     </row>
     <row r="229">
@@ -3391,10 +3391,10 @@
         </is>
       </c>
       <c r="B229" t="n">
-        <v>0.081758</v>
+        <v>0.077863</v>
       </c>
       <c r="C229" t="n">
-        <v>0.386486</v>
+        <v>0.389785</v>
       </c>
     </row>
     <row r="230">
@@ -3404,10 +3404,10 @@
         </is>
       </c>
       <c r="B230" t="n">
-        <v>0.08192000000000001</v>
+        <v>0.07921499999999999</v>
       </c>
       <c r="C230" t="n">
-        <v>0.383784</v>
+        <v>0.387097</v>
       </c>
     </row>
     <row r="231">
@@ -3417,10 +3417,10 @@
         </is>
       </c>
       <c r="B231" t="n">
-        <v>0.082479</v>
+        <v>0.079239</v>
       </c>
       <c r="C231" t="n">
-        <v>0.381081</v>
+        <v>0.384409</v>
       </c>
     </row>
     <row r="232">
@@ -3430,10 +3430,10 @@
         </is>
       </c>
       <c r="B232" t="n">
-        <v>0.08254300000000001</v>
+        <v>0.081758</v>
       </c>
       <c r="C232" t="n">
-        <v>0.378378</v>
+        <v>0.38172</v>
       </c>
     </row>
     <row r="233">
@@ -3443,10 +3443,10 @@
         </is>
       </c>
       <c r="B233" t="n">
-        <v>0.08294600000000001</v>
+        <v>0.08192000000000001</v>
       </c>
       <c r="C233" t="n">
-        <v>0.375676</v>
+        <v>0.379032</v>
       </c>
     </row>
     <row r="234">
@@ -3456,10 +3456,10 @@
         </is>
       </c>
       <c r="B234" t="n">
-        <v>0.08384800000000001</v>
+        <v>0.082479</v>
       </c>
       <c r="C234" t="n">
-        <v>0.372973</v>
+        <v>0.376344</v>
       </c>
     </row>
     <row r="235">
@@ -3469,10 +3469,10 @@
         </is>
       </c>
       <c r="B235" t="n">
-        <v>0.084221</v>
+        <v>0.08254300000000001</v>
       </c>
       <c r="C235" t="n">
-        <v>0.37027</v>
+        <v>0.373656</v>
       </c>
     </row>
     <row r="236">
@@ -3482,10 +3482,10 @@
         </is>
       </c>
       <c r="B236" t="n">
-        <v>0.08483599999999999</v>
+        <v>0.08294600000000001</v>
       </c>
       <c r="C236" t="n">
-        <v>0.367568</v>
+        <v>0.370968</v>
       </c>
     </row>
     <row r="237">
@@ -3495,10 +3495,10 @@
         </is>
       </c>
       <c r="B237" t="n">
-        <v>0.08586199999999999</v>
+        <v>0.08384800000000001</v>
       </c>
       <c r="C237" t="n">
-        <v>0.364865</v>
+        <v>0.36828</v>
       </c>
     </row>
     <row r="238">
@@ -3508,10 +3508,10 @@
         </is>
       </c>
       <c r="B238" t="n">
-        <v>0.087156</v>
+        <v>0.084221</v>
       </c>
       <c r="C238" t="n">
-        <v>0.362162</v>
+        <v>0.365591</v>
       </c>
     </row>
     <row r="239">
@@ -3521,10 +3521,10 @@
         </is>
       </c>
       <c r="B239" t="n">
-        <v>0.08717999999999999</v>
+        <v>0.08483599999999999</v>
       </c>
       <c r="C239" t="n">
-        <v>0.359459</v>
+        <v>0.362903</v>
       </c>
     </row>
     <row r="240">
@@ -3534,10 +3534,10 @@
         </is>
       </c>
       <c r="B240" t="n">
-        <v>0.088464</v>
+        <v>0.08586199999999999</v>
       </c>
       <c r="C240" t="n">
-        <v>0.356757</v>
+        <v>0.360215</v>
       </c>
     </row>
     <row r="241">
@@ -3547,10 +3547,10 @@
         </is>
       </c>
       <c r="B241" t="n">
-        <v>0.088889</v>
+        <v>0.087156</v>
       </c>
       <c r="C241" t="n">
-        <v>0.354054</v>
+        <v>0.357527</v>
       </c>
     </row>
     <row r="242">
@@ -3560,10 +3560,10 @@
         </is>
       </c>
       <c r="B242" t="n">
-        <v>0.08917700000000001</v>
+        <v>0.08717999999999999</v>
       </c>
       <c r="C242" t="n">
-        <v>0.351351</v>
+        <v>0.354839</v>
       </c>
     </row>
     <row r="243">
@@ -3573,10 +3573,10 @@
         </is>
       </c>
       <c r="B243" t="n">
-        <v>0.089823</v>
+        <v>0.088464</v>
       </c>
       <c r="C243" t="n">
-        <v>0.348649</v>
+        <v>0.352151</v>
       </c>
     </row>
     <row r="244">
@@ -3586,10 +3586,10 @@
         </is>
       </c>
       <c r="B244" t="n">
-        <v>0.090265</v>
+        <v>0.088889</v>
       </c>
       <c r="C244" t="n">
-        <v>0.345946</v>
+        <v>0.349462</v>
       </c>
     </row>
     <row r="245">
@@ -3599,10 +3599,10 @@
         </is>
       </c>
       <c r="B245" t="n">
-        <v>0.090958</v>
+        <v>0.08917700000000001</v>
       </c>
       <c r="C245" t="n">
-        <v>0.343243</v>
+        <v>0.346774</v>
       </c>
     </row>
     <row r="246">
@@ -3612,10 +3612,10 @@
         </is>
       </c>
       <c r="B246" t="n">
-        <v>0.091434</v>
+        <v>0.089823</v>
       </c>
       <c r="C246" t="n">
-        <v>0.340541</v>
+        <v>0.344086</v>
       </c>
     </row>
     <row r="247">
@@ -3625,10 +3625,10 @@
         </is>
       </c>
       <c r="B247" t="n">
-        <v>0.0929</v>
+        <v>0.090265</v>
       </c>
       <c r="C247" t="n">
-        <v>0.337838</v>
+        <v>0.341398</v>
       </c>
     </row>
     <row r="248">
@@ -3638,10 +3638,10 @@
         </is>
       </c>
       <c r="B248" t="n">
-        <v>0.093237</v>
+        <v>0.090958</v>
       </c>
       <c r="C248" t="n">
-        <v>0.335135</v>
+        <v>0.33871</v>
       </c>
     </row>
     <row r="249">
@@ -3651,10 +3651,10 @@
         </is>
       </c>
       <c r="B249" t="n">
-        <v>0.095842</v>
+        <v>0.091434</v>
       </c>
       <c r="C249" t="n">
-        <v>0.332432</v>
+        <v>0.336022</v>
       </c>
     </row>
     <row r="250">
@@ -3664,10 +3664,10 @@
         </is>
       </c>
       <c r="B250" t="n">
-        <v>0.09630900000000001</v>
+        <v>0.0929</v>
       </c>
       <c r="C250" t="n">
-        <v>0.32973</v>
+        <v>0.333333</v>
       </c>
     </row>
     <row r="251">
@@ -3677,10 +3677,10 @@
         </is>
       </c>
       <c r="B251" t="n">
-        <v>0.097923</v>
+        <v>0.093237</v>
       </c>
       <c r="C251" t="n">
-        <v>0.327027</v>
+        <v>0.330645</v>
       </c>
     </row>
     <row r="252">
@@ -3690,10 +3690,10 @@
         </is>
       </c>
       <c r="B252" t="n">
-        <v>0.09847400000000001</v>
+        <v>0.095842</v>
       </c>
       <c r="C252" t="n">
-        <v>0.324324</v>
+        <v>0.327957</v>
       </c>
     </row>
     <row r="253">
@@ -3703,10 +3703,10 @@
         </is>
       </c>
       <c r="B253" t="n">
-        <v>0.099063</v>
+        <v>0.09630900000000001</v>
       </c>
       <c r="C253" t="n">
-        <v>0.321622</v>
+        <v>0.325269</v>
       </c>
     </row>
     <row r="254">
@@ -3716,10 +3716,10 @@
         </is>
       </c>
       <c r="B254" t="n">
-        <v>0.09907299999999999</v>
+        <v>0.097923</v>
       </c>
       <c r="C254" t="n">
-        <v>0.318919</v>
+        <v>0.322581</v>
       </c>
     </row>
     <row r="255">
@@ -3729,10 +3729,10 @@
         </is>
       </c>
       <c r="B255" t="n">
-        <v>0.100571</v>
+        <v>0.09847400000000001</v>
       </c>
       <c r="C255" t="n">
-        <v>0.316216</v>
+        <v>0.319892</v>
       </c>
     </row>
     <row r="256">
@@ -3742,10 +3742,10 @@
         </is>
       </c>
       <c r="B256" t="n">
-        <v>0.101335</v>
+        <v>0.099063</v>
       </c>
       <c r="C256" t="n">
-        <v>0.313514</v>
+        <v>0.317204</v>
       </c>
     </row>
     <row r="257">
@@ -3755,10 +3755,10 @@
         </is>
       </c>
       <c r="B257" t="n">
-        <v>0.10179</v>
+        <v>0.09907299999999999</v>
       </c>
       <c r="C257" t="n">
-        <v>0.310811</v>
+        <v>0.314516</v>
       </c>
     </row>
     <row r="258">
@@ -3768,10 +3768,10 @@
         </is>
       </c>
       <c r="B258" t="n">
-        <v>0.101937</v>
+        <v>0.100571</v>
       </c>
       <c r="C258" t="n">
-        <v>0.308108</v>
+        <v>0.311828</v>
       </c>
     </row>
     <row r="259">
@@ -3781,10 +3781,10 @@
         </is>
       </c>
       <c r="B259" t="n">
-        <v>0.103119</v>
+        <v>0.101335</v>
       </c>
       <c r="C259" t="n">
-        <v>0.305405</v>
+        <v>0.30914</v>
       </c>
     </row>
     <row r="260">
@@ -3794,10 +3794,10 @@
         </is>
       </c>
       <c r="B260" t="n">
-        <v>0.103451</v>
+        <v>0.10179</v>
       </c>
       <c r="C260" t="n">
-        <v>0.302703</v>
+        <v>0.306452</v>
       </c>
     </row>
     <row r="261">
@@ -3807,10 +3807,10 @@
         </is>
       </c>
       <c r="B261" t="n">
-        <v>0.103942</v>
+        <v>0.101937</v>
       </c>
       <c r="C261" t="n">
-        <v>0.3</v>
+        <v>0.303763</v>
       </c>
     </row>
     <row r="262">
@@ -3820,10 +3820,10 @@
         </is>
       </c>
       <c r="B262" t="n">
-        <v>0.10427</v>
+        <v>0.103451</v>
       </c>
       <c r="C262" t="n">
-        <v>0.297297</v>
+        <v>0.301075</v>
       </c>
     </row>
     <row r="263">
@@ -3833,10 +3833,10 @@
         </is>
       </c>
       <c r="B263" t="n">
-        <v>0.105774</v>
+        <v>0.103942</v>
       </c>
       <c r="C263" t="n">
-        <v>0.294595</v>
+        <v>0.298387</v>
       </c>
     </row>
     <row r="264">
@@ -3846,10 +3846,10 @@
         </is>
       </c>
       <c r="B264" t="n">
-        <v>0.106391</v>
+        <v>0.10427</v>
       </c>
       <c r="C264" t="n">
-        <v>0.291892</v>
+        <v>0.295699</v>
       </c>
     </row>
     <row r="265">
@@ -3859,10 +3859,10 @@
         </is>
       </c>
       <c r="B265" t="n">
-        <v>0.106564</v>
+        <v>0.105774</v>
       </c>
       <c r="C265" t="n">
-        <v>0.289189</v>
+        <v>0.293011</v>
       </c>
     </row>
     <row r="266">
@@ -3872,10 +3872,10 @@
         </is>
       </c>
       <c r="B266" t="n">
-        <v>0.106852</v>
+        <v>0.106391</v>
       </c>
       <c r="C266" t="n">
-        <v>0.286486</v>
+        <v>0.290323</v>
       </c>
     </row>
     <row r="267">
@@ -3885,10 +3885,10 @@
         </is>
       </c>
       <c r="B267" t="n">
-        <v>0.107359</v>
+        <v>0.106564</v>
       </c>
       <c r="C267" t="n">
-        <v>0.283784</v>
+        <v>0.287634</v>
       </c>
     </row>
     <row r="268">
@@ -3898,10 +3898,10 @@
         </is>
       </c>
       <c r="B268" t="n">
-        <v>0.109871</v>
+        <v>0.106852</v>
       </c>
       <c r="C268" t="n">
-        <v>0.281081</v>
+        <v>0.284946</v>
       </c>
     </row>
     <row r="269">
@@ -3911,10 +3911,10 @@
         </is>
       </c>
       <c r="B269" t="n">
-        <v>0.110708</v>
+        <v>0.107359</v>
       </c>
       <c r="C269" t="n">
-        <v>0.278378</v>
+        <v>0.282258</v>
       </c>
     </row>
     <row r="270">
@@ -3924,10 +3924,10 @@
         </is>
       </c>
       <c r="B270" t="n">
-        <v>0.111683</v>
+        <v>0.109871</v>
       </c>
       <c r="C270" t="n">
-        <v>0.275676</v>
+        <v>0.27957</v>
       </c>
     </row>
     <row r="271">
@@ -3937,10 +3937,10 @@
         </is>
       </c>
       <c r="B271" t="n">
-        <v>0.112861</v>
+        <v>0.110708</v>
       </c>
       <c r="C271" t="n">
-        <v>0.272973</v>
+        <v>0.276882</v>
       </c>
     </row>
     <row r="272">
@@ -3950,10 +3950,10 @@
         </is>
       </c>
       <c r="B272" t="n">
-        <v>0.11394</v>
+        <v>0.111683</v>
       </c>
       <c r="C272" t="n">
-        <v>0.27027</v>
+        <v>0.274194</v>
       </c>
     </row>
     <row r="273">
@@ -3963,10 +3963,10 @@
         </is>
       </c>
       <c r="B273" t="n">
-        <v>0.114179</v>
+        <v>0.112861</v>
       </c>
       <c r="C273" t="n">
-        <v>0.267568</v>
+        <v>0.271505</v>
       </c>
     </row>
     <row r="274">
@@ -3976,10 +3976,10 @@
         </is>
       </c>
       <c r="B274" t="n">
-        <v>0.11468</v>
+        <v>0.11394</v>
       </c>
       <c r="C274" t="n">
-        <v>0.264865</v>
+        <v>0.268817</v>
       </c>
     </row>
     <row r="275">
@@ -3989,10 +3989,10 @@
         </is>
       </c>
       <c r="B275" t="n">
-        <v>0.117496</v>
+        <v>0.114179</v>
       </c>
       <c r="C275" t="n">
-        <v>0.262162</v>
+        <v>0.266129</v>
       </c>
     </row>
     <row r="276">
@@ -4002,10 +4002,10 @@
         </is>
       </c>
       <c r="B276" t="n">
-        <v>0.117846</v>
+        <v>0.11468</v>
       </c>
       <c r="C276" t="n">
-        <v>0.259459</v>
+        <v>0.263441</v>
       </c>
     </row>
     <row r="277">
@@ -4015,10 +4015,10 @@
         </is>
       </c>
       <c r="B277" t="n">
-        <v>0.119464</v>
+        <v>0.117496</v>
       </c>
       <c r="C277" t="n">
-        <v>0.256757</v>
+        <v>0.260753</v>
       </c>
     </row>
     <row r="278">
@@ -4028,10 +4028,10 @@
         </is>
       </c>
       <c r="B278" t="n">
-        <v>0.120351</v>
+        <v>0.117846</v>
       </c>
       <c r="C278" t="n">
-        <v>0.254054</v>
+        <v>0.258065</v>
       </c>
     </row>
     <row r="279">
@@ -4041,10 +4041,10 @@
         </is>
       </c>
       <c r="B279" t="n">
-        <v>0.120448</v>
+        <v>0.119464</v>
       </c>
       <c r="C279" t="n">
-        <v>0.251351</v>
+        <v>0.255376</v>
       </c>
     </row>
     <row r="280">
@@ -4054,10 +4054,10 @@
         </is>
       </c>
       <c r="B280" t="n">
-        <v>0.121637</v>
+        <v>0.120351</v>
       </c>
       <c r="C280" t="n">
-        <v>0.248649</v>
+        <v>0.252688</v>
       </c>
     </row>
     <row r="281">
@@ -4067,10 +4067,10 @@
         </is>
       </c>
       <c r="B281" t="n">
-        <v>0.12397</v>
+        <v>0.120448</v>
       </c>
       <c r="C281" t="n">
-        <v>0.245946</v>
+        <v>0.25</v>
       </c>
     </row>
     <row r="282">
@@ -4080,10 +4080,10 @@
         </is>
       </c>
       <c r="B282" t="n">
-        <v>0.124167</v>
+        <v>0.121637</v>
       </c>
       <c r="C282" t="n">
-        <v>0.243243</v>
+        <v>0.247312</v>
       </c>
     </row>
     <row r="283">
@@ -4093,10 +4093,10 @@
         </is>
       </c>
       <c r="B283" t="n">
-        <v>0.126891</v>
+        <v>0.12397</v>
       </c>
       <c r="C283" t="n">
-        <v>0.240541</v>
+        <v>0.244624</v>
       </c>
     </row>
     <row r="284">
@@ -4106,10 +4106,10 @@
         </is>
       </c>
       <c r="B284" t="n">
-        <v>0.128021</v>
+        <v>0.124167</v>
       </c>
       <c r="C284" t="n">
-        <v>0.237838</v>
+        <v>0.241935</v>
       </c>
     </row>
     <row r="285">
@@ -4119,10 +4119,10 @@
         </is>
       </c>
       <c r="B285" t="n">
-        <v>0.128976</v>
+        <v>0.126891</v>
       </c>
       <c r="C285" t="n">
-        <v>0.235135</v>
+        <v>0.239247</v>
       </c>
     </row>
     <row r="286">
@@ -4132,10 +4132,10 @@
         </is>
       </c>
       <c r="B286" t="n">
-        <v>0.130439</v>
+        <v>0.128021</v>
       </c>
       <c r="C286" t="n">
-        <v>0.232432</v>
+        <v>0.236559</v>
       </c>
     </row>
     <row r="287">
@@ -4145,10 +4145,10 @@
         </is>
       </c>
       <c r="B287" t="n">
-        <v>0.130821</v>
+        <v>0.128976</v>
       </c>
       <c r="C287" t="n">
-        <v>0.22973</v>
+        <v>0.233871</v>
       </c>
     </row>
     <row r="288">
@@ -4158,10 +4158,10 @@
         </is>
       </c>
       <c r="B288" t="n">
-        <v>0.130947</v>
+        <v>0.130439</v>
       </c>
       <c r="C288" t="n">
-        <v>0.227027</v>
+        <v>0.231183</v>
       </c>
     </row>
     <row r="289">
@@ -4171,10 +4171,10 @@
         </is>
       </c>
       <c r="B289" t="n">
-        <v>0.135669</v>
+        <v>0.130821</v>
       </c>
       <c r="C289" t="n">
-        <v>0.224324</v>
+        <v>0.228495</v>
       </c>
     </row>
     <row r="290">
@@ -4184,10 +4184,10 @@
         </is>
       </c>
       <c r="B290" t="n">
-        <v>0.135827</v>
+        <v>0.130947</v>
       </c>
       <c r="C290" t="n">
-        <v>0.221622</v>
+        <v>0.225806</v>
       </c>
     </row>
     <row r="291">
@@ -4197,10 +4197,10 @@
         </is>
       </c>
       <c r="B291" t="n">
-        <v>0.137057</v>
+        <v>0.135669</v>
       </c>
       <c r="C291" t="n">
-        <v>0.218919</v>
+        <v>0.223118</v>
       </c>
     </row>
     <row r="292">
@@ -4210,10 +4210,10 @@
         </is>
       </c>
       <c r="B292" t="n">
-        <v>0.13733</v>
+        <v>0.135827</v>
       </c>
       <c r="C292" t="n">
-        <v>0.216216</v>
+        <v>0.22043</v>
       </c>
     </row>
     <row r="293">
@@ -4223,10 +4223,10 @@
         </is>
       </c>
       <c r="B293" t="n">
-        <v>0.138762</v>
+        <v>0.137057</v>
       </c>
       <c r="C293" t="n">
-        <v>0.213514</v>
+        <v>0.217742</v>
       </c>
     </row>
     <row r="294">
@@ -4236,10 +4236,10 @@
         </is>
       </c>
       <c r="B294" t="n">
-        <v>0.139275</v>
+        <v>0.13733</v>
       </c>
       <c r="C294" t="n">
-        <v>0.210811</v>
+        <v>0.215054</v>
       </c>
     </row>
     <row r="295">
@@ -4249,10 +4249,10 @@
         </is>
       </c>
       <c r="B295" t="n">
-        <v>0.140029</v>
+        <v>0.138762</v>
       </c>
       <c r="C295" t="n">
-        <v>0.208108</v>
+        <v>0.212366</v>
       </c>
     </row>
     <row r="296">
@@ -4262,10 +4262,10 @@
         </is>
       </c>
       <c r="B296" t="n">
-        <v>0.140099</v>
+        <v>0.139275</v>
       </c>
       <c r="C296" t="n">
-        <v>0.205405</v>
+        <v>0.209677</v>
       </c>
     </row>
     <row r="297">
@@ -4275,10 +4275,10 @@
         </is>
       </c>
       <c r="B297" t="n">
-        <v>0.140214</v>
+        <v>0.140029</v>
       </c>
       <c r="C297" t="n">
-        <v>0.202703</v>
+        <v>0.206989</v>
       </c>
     </row>
     <row r="298">
@@ -4288,10 +4288,10 @@
         </is>
       </c>
       <c r="B298" t="n">
-        <v>0.141591</v>
+        <v>0.140099</v>
       </c>
       <c r="C298" t="n">
-        <v>0.2</v>
+        <v>0.204301</v>
       </c>
     </row>
     <row r="299">
@@ -4301,10 +4301,10 @@
         </is>
       </c>
       <c r="B299" t="n">
-        <v>0.143233</v>
+        <v>0.140214</v>
       </c>
       <c r="C299" t="n">
-        <v>0.197297</v>
+        <v>0.201613</v>
       </c>
     </row>
     <row r="300">
@@ -4314,10 +4314,10 @@
         </is>
       </c>
       <c r="B300" t="n">
-        <v>0.144579</v>
+        <v>0.141591</v>
       </c>
       <c r="C300" t="n">
-        <v>0.194595</v>
+        <v>0.198925</v>
       </c>
     </row>
     <row r="301">
@@ -4327,10 +4327,10 @@
         </is>
       </c>
       <c r="B301" t="n">
-        <v>0.145008</v>
+        <v>0.143233</v>
       </c>
       <c r="C301" t="n">
-        <v>0.191892</v>
+        <v>0.196237</v>
       </c>
     </row>
     <row r="302">
@@ -4340,10 +4340,10 @@
         </is>
       </c>
       <c r="B302" t="n">
-        <v>0.145291</v>
+        <v>0.144579</v>
       </c>
       <c r="C302" t="n">
-        <v>0.189189</v>
+        <v>0.193548</v>
       </c>
     </row>
     <row r="303">
@@ -4353,10 +4353,10 @@
         </is>
       </c>
       <c r="B303" t="n">
-        <v>0.145554</v>
+        <v>0.145008</v>
       </c>
       <c r="C303" t="n">
-        <v>0.186486</v>
+        <v>0.19086</v>
       </c>
     </row>
     <row r="304">
@@ -4366,10 +4366,10 @@
         </is>
       </c>
       <c r="B304" t="n">
-        <v>0.151419</v>
+        <v>0.145291</v>
       </c>
       <c r="C304" t="n">
-        <v>0.183784</v>
+        <v>0.188172</v>
       </c>
     </row>
     <row r="305">
@@ -4379,10 +4379,10 @@
         </is>
       </c>
       <c r="B305" t="n">
-        <v>0.151465</v>
+        <v>0.145554</v>
       </c>
       <c r="C305" t="n">
-        <v>0.181081</v>
+        <v>0.185484</v>
       </c>
     </row>
     <row r="306">
@@ -4392,10 +4392,10 @@
         </is>
       </c>
       <c r="B306" t="n">
-        <v>0.151822</v>
+        <v>0.151419</v>
       </c>
       <c r="C306" t="n">
-        <v>0.178378</v>
+        <v>0.182796</v>
       </c>
     </row>
     <row r="307">
@@ -4405,10 +4405,10 @@
         </is>
       </c>
       <c r="B307" t="n">
-        <v>0.15511</v>
+        <v>0.151465</v>
       </c>
       <c r="C307" t="n">
-        <v>0.175676</v>
+        <v>0.180108</v>
       </c>
     </row>
     <row r="308">
@@ -4418,10 +4418,10 @@
         </is>
       </c>
       <c r="B308" t="n">
-        <v>0.15559</v>
+        <v>0.151822</v>
       </c>
       <c r="C308" t="n">
-        <v>0.172973</v>
+        <v>0.177419</v>
       </c>
     </row>
     <row r="309">
@@ -4431,10 +4431,10 @@
         </is>
       </c>
       <c r="B309" t="n">
-        <v>0.1565</v>
+        <v>0.15511</v>
       </c>
       <c r="C309" t="n">
-        <v>0.17027</v>
+        <v>0.174731</v>
       </c>
     </row>
     <row r="310">
@@ -4444,10 +4444,10 @@
         </is>
       </c>
       <c r="B310" t="n">
-        <v>0.158503</v>
+        <v>0.15559</v>
       </c>
       <c r="C310" t="n">
-        <v>0.167568</v>
+        <v>0.172043</v>
       </c>
     </row>
     <row r="311">
@@ -4457,10 +4457,10 @@
         </is>
       </c>
       <c r="B311" t="n">
-        <v>0.16241</v>
+        <v>0.1565</v>
       </c>
       <c r="C311" t="n">
-        <v>0.164865</v>
+        <v>0.169355</v>
       </c>
     </row>
     <row r="312">
@@ -4470,10 +4470,10 @@
         </is>
       </c>
       <c r="B312" t="n">
-        <v>0.167126</v>
+        <v>0.158503</v>
       </c>
       <c r="C312" t="n">
-        <v>0.162162</v>
+        <v>0.166667</v>
       </c>
     </row>
     <row r="313">
@@ -4483,10 +4483,10 @@
         </is>
       </c>
       <c r="B313" t="n">
-        <v>0.173105</v>
+        <v>0.16241</v>
       </c>
       <c r="C313" t="n">
-        <v>0.159459</v>
+        <v>0.163978</v>
       </c>
     </row>
     <row r="314">
@@ -4496,10 +4496,10 @@
         </is>
       </c>
       <c r="B314" t="n">
-        <v>0.175601</v>
+        <v>0.167126</v>
       </c>
       <c r="C314" t="n">
-        <v>0.156757</v>
+        <v>0.16129</v>
       </c>
     </row>
     <row r="315">
@@ -4509,10 +4509,10 @@
         </is>
       </c>
       <c r="B315" t="n">
-        <v>0.183042</v>
+        <v>0.173105</v>
       </c>
       <c r="C315" t="n">
-        <v>0.154054</v>
+        <v>0.158602</v>
       </c>
     </row>
     <row r="316">
@@ -4522,10 +4522,10 @@
         </is>
       </c>
       <c r="B316" t="n">
-        <v>0.187612</v>
+        <v>0.175601</v>
       </c>
       <c r="C316" t="n">
-        <v>0.151351</v>
+        <v>0.155914</v>
       </c>
     </row>
     <row r="317">
@@ -4535,10 +4535,10 @@
         </is>
       </c>
       <c r="B317" t="n">
-        <v>0.189387</v>
+        <v>0.183042</v>
       </c>
       <c r="C317" t="n">
-        <v>0.148649</v>
+        <v>0.153226</v>
       </c>
     </row>
     <row r="318">
@@ -4548,10 +4548,10 @@
         </is>
       </c>
       <c r="B318" t="n">
-        <v>0.193249</v>
+        <v>0.187612</v>
       </c>
       <c r="C318" t="n">
-        <v>0.145946</v>
+        <v>0.150538</v>
       </c>
     </row>
     <row r="319">
@@ -4561,10 +4561,10 @@
         </is>
       </c>
       <c r="B319" t="n">
-        <v>0.195388</v>
+        <v>0.189387</v>
       </c>
       <c r="C319" t="n">
-        <v>0.143243</v>
+        <v>0.147849</v>
       </c>
     </row>
     <row r="320">
@@ -4574,10 +4574,10 @@
         </is>
       </c>
       <c r="B320" t="n">
-        <v>0.200683</v>
+        <v>0.193249</v>
       </c>
       <c r="C320" t="n">
-        <v>0.140541</v>
+        <v>0.145161</v>
       </c>
     </row>
     <row r="321">
@@ -4587,10 +4587,10 @@
         </is>
       </c>
       <c r="B321" t="n">
-        <v>0.206803</v>
+        <v>0.195388</v>
       </c>
       <c r="C321" t="n">
-        <v>0.137838</v>
+        <v>0.142473</v>
       </c>
     </row>
     <row r="322">
@@ -4600,10 +4600,10 @@
         </is>
       </c>
       <c r="B322" t="n">
-        <v>0.21126</v>
+        <v>0.200683</v>
       </c>
       <c r="C322" t="n">
-        <v>0.135135</v>
+        <v>0.139785</v>
       </c>
     </row>
     <row r="323">
@@ -4613,10 +4613,10 @@
         </is>
       </c>
       <c r="B323" t="n">
-        <v>0.212282</v>
+        <v>0.206803</v>
       </c>
       <c r="C323" t="n">
-        <v>0.132432</v>
+        <v>0.137097</v>
       </c>
     </row>
     <row r="324">
@@ -4626,10 +4626,10 @@
         </is>
       </c>
       <c r="B324" t="n">
-        <v>0.213977</v>
+        <v>0.21126</v>
       </c>
       <c r="C324" t="n">
-        <v>0.12973</v>
+        <v>0.134409</v>
       </c>
     </row>
     <row r="325">
@@ -4639,10 +4639,10 @@
         </is>
       </c>
       <c r="B325" t="n">
-        <v>0.224095</v>
+        <v>0.212282</v>
       </c>
       <c r="C325" t="n">
-        <v>0.127027</v>
+        <v>0.13172</v>
       </c>
     </row>
     <row r="326">
@@ -4652,10 +4652,10 @@
         </is>
       </c>
       <c r="B326" t="n">
-        <v>0.224293</v>
+        <v>0.213977</v>
       </c>
       <c r="C326" t="n">
-        <v>0.124324</v>
+        <v>0.129032</v>
       </c>
     </row>
     <row r="327">
@@ -4665,10 +4665,10 @@
         </is>
       </c>
       <c r="B327" t="n">
-        <v>0.224867</v>
+        <v>0.224095</v>
       </c>
       <c r="C327" t="n">
-        <v>0.121622</v>
+        <v>0.126344</v>
       </c>
     </row>
     <row r="328">
@@ -4678,10 +4678,10 @@
         </is>
       </c>
       <c r="B328" t="n">
-        <v>0.225383</v>
+        <v>0.224293</v>
       </c>
       <c r="C328" t="n">
-        <v>0.118919</v>
+        <v>0.123656</v>
       </c>
     </row>
     <row r="329">
@@ -4691,10 +4691,10 @@
         </is>
       </c>
       <c r="B329" t="n">
-        <v>0.229443</v>
+        <v>0.224867</v>
       </c>
       <c r="C329" t="n">
-        <v>0.116216</v>
+        <v>0.120968</v>
       </c>
     </row>
     <row r="330">
@@ -4704,10 +4704,10 @@
         </is>
       </c>
       <c r="B330" t="n">
-        <v>0.232768</v>
+        <v>0.225383</v>
       </c>
       <c r="C330" t="n">
-        <v>0.113514</v>
+        <v>0.11828</v>
       </c>
     </row>
     <row r="331">
@@ -4717,10 +4717,10 @@
         </is>
       </c>
       <c r="B331" t="n">
-        <v>0.234669</v>
+        <v>0.229443</v>
       </c>
       <c r="C331" t="n">
-        <v>0.110811</v>
+        <v>0.115591</v>
       </c>
     </row>
     <row r="332">
@@ -4730,10 +4730,10 @@
         </is>
       </c>
       <c r="B332" t="n">
-        <v>0.235662</v>
+        <v>0.232768</v>
       </c>
       <c r="C332" t="n">
-        <v>0.108108</v>
+        <v>0.112903</v>
       </c>
     </row>
     <row r="333">
@@ -4743,10 +4743,10 @@
         </is>
       </c>
       <c r="B333" t="n">
-        <v>0.257813</v>
+        <v>0.234669</v>
       </c>
       <c r="C333" t="n">
-        <v>0.105405</v>
+        <v>0.110215</v>
       </c>
     </row>
     <row r="334">
@@ -4756,10 +4756,10 @@
         </is>
       </c>
       <c r="B334" t="n">
-        <v>0.266114</v>
+        <v>0.235662</v>
       </c>
       <c r="C334" t="n">
-        <v>0.102703</v>
+        <v>0.107527</v>
       </c>
     </row>
     <row r="335">
@@ -4769,10 +4769,10 @@
         </is>
       </c>
       <c r="B335" t="n">
-        <v>0.267301</v>
+        <v>0.257813</v>
       </c>
       <c r="C335" t="n">
-        <v>0.1</v>
+        <v>0.104839</v>
       </c>
     </row>
     <row r="336">
@@ -4782,10 +4782,10 @@
         </is>
       </c>
       <c r="B336" t="n">
-        <v>0.273424</v>
+        <v>0.266114</v>
       </c>
       <c r="C336" t="n">
-        <v>0.09729699999999999</v>
+        <v>0.102151</v>
       </c>
     </row>
     <row r="337">
@@ -4795,10 +4795,10 @@
         </is>
       </c>
       <c r="B337" t="n">
-        <v>0.274371</v>
+        <v>0.267301</v>
       </c>
       <c r="C337" t="n">
-        <v>0.094595</v>
+        <v>0.09946199999999999</v>
       </c>
     </row>
     <row r="338">
@@ -4808,10 +4808,10 @@
         </is>
       </c>
       <c r="B338" t="n">
-        <v>0.279391</v>
+        <v>0.273424</v>
       </c>
       <c r="C338" t="n">
-        <v>0.091892</v>
+        <v>0.096774</v>
       </c>
     </row>
     <row r="339">
@@ -4821,10 +4821,10 @@
         </is>
       </c>
       <c r="B339" t="n">
-        <v>0.28675</v>
+        <v>0.274371</v>
       </c>
       <c r="C339" t="n">
-        <v>0.089189</v>
+        <v>0.094086</v>
       </c>
     </row>
     <row r="340">
@@ -4834,10 +4834,10 @@
         </is>
       </c>
       <c r="B340" t="n">
-        <v>0.292707</v>
+        <v>0.279391</v>
       </c>
       <c r="C340" t="n">
-        <v>0.08648599999999999</v>
+        <v>0.09139799999999999</v>
       </c>
     </row>
     <row r="341">
@@ -4847,10 +4847,10 @@
         </is>
       </c>
       <c r="B341" t="n">
-        <v>0.295965</v>
+        <v>0.28675</v>
       </c>
       <c r="C341" t="n">
-        <v>0.083784</v>
+        <v>0.08871</v>
       </c>
     </row>
     <row r="342">
@@ -4860,10 +4860,10 @@
         </is>
       </c>
       <c r="B342" t="n">
-        <v>0.303016</v>
+        <v>0.292707</v>
       </c>
       <c r="C342" t="n">
-        <v>0.081081</v>
+        <v>0.086022</v>
       </c>
     </row>
     <row r="343">
@@ -4873,10 +4873,10 @@
         </is>
       </c>
       <c r="B343" t="n">
-        <v>0.3031</v>
+        <v>0.295965</v>
       </c>
       <c r="C343" t="n">
-        <v>0.078378</v>
+        <v>0.083333</v>
       </c>
     </row>
     <row r="344">
@@ -4886,10 +4886,10 @@
         </is>
       </c>
       <c r="B344" t="n">
-        <v>0.321789</v>
+        <v>0.303016</v>
       </c>
       <c r="C344" t="n">
-        <v>0.07567599999999999</v>
+        <v>0.08064499999999999</v>
       </c>
     </row>
     <row r="345">
@@ -4899,10 +4899,10 @@
         </is>
       </c>
       <c r="B345" t="n">
-        <v>0.359445</v>
+        <v>0.3031</v>
       </c>
       <c r="C345" t="n">
-        <v>0.072973</v>
+        <v>0.077957</v>
       </c>
     </row>
     <row r="346">
@@ -4912,10 +4912,10 @@
         </is>
       </c>
       <c r="B346" t="n">
-        <v>0.359851</v>
+        <v>0.321789</v>
       </c>
       <c r="C346" t="n">
-        <v>0.07027</v>
+        <v>0.075269</v>
       </c>
     </row>
     <row r="347">
@@ -4925,10 +4925,10 @@
         </is>
       </c>
       <c r="B347" t="n">
-        <v>0.363732</v>
+        <v>0.359445</v>
       </c>
       <c r="C347" t="n">
-        <v>0.067568</v>
+        <v>0.07258100000000001</v>
       </c>
     </row>
     <row r="348">
@@ -4938,10 +4938,10 @@
         </is>
       </c>
       <c r="B348" t="n">
-        <v>0.364791</v>
+        <v>0.359851</v>
       </c>
       <c r="C348" t="n">
-        <v>0.06486500000000001</v>
+        <v>0.069892</v>
       </c>
     </row>
     <row r="349">
@@ -4951,10 +4951,10 @@
         </is>
       </c>
       <c r="B349" t="n">
-        <v>0.366962</v>
+        <v>0.363732</v>
       </c>
       <c r="C349" t="n">
-        <v>0.062162</v>
+        <v>0.067204</v>
       </c>
     </row>
     <row r="350">
@@ -4964,10 +4964,10 @@
         </is>
       </c>
       <c r="B350" t="n">
-        <v>0.368203</v>
+        <v>0.364791</v>
       </c>
       <c r="C350" t="n">
-        <v>0.059459</v>
+        <v>0.064516</v>
       </c>
     </row>
     <row r="351">
@@ -4977,10 +4977,10 @@
         </is>
       </c>
       <c r="B351" t="n">
-        <v>0.373316</v>
+        <v>0.366962</v>
       </c>
       <c r="C351" t="n">
-        <v>0.056757</v>
+        <v>0.061828</v>
       </c>
     </row>
     <row r="352">
@@ -4990,10 +4990,10 @@
         </is>
       </c>
       <c r="B352" t="n">
-        <v>0.378466</v>
+        <v>0.368203</v>
       </c>
       <c r="C352" t="n">
-        <v>0.054054</v>
+        <v>0.05914</v>
       </c>
     </row>
     <row r="353">
@@ -5003,10 +5003,10 @@
         </is>
       </c>
       <c r="B353" t="n">
-        <v>0.389014</v>
+        <v>0.373316</v>
       </c>
       <c r="C353" t="n">
-        <v>0.051351</v>
+        <v>0.056452</v>
       </c>
     </row>
     <row r="354">
@@ -5016,10 +5016,10 @@
         </is>
       </c>
       <c r="B354" t="n">
-        <v>0.400164</v>
+        <v>0.389014</v>
       </c>
       <c r="C354" t="n">
-        <v>0.048649</v>
+        <v>0.053763</v>
       </c>
     </row>
     <row r="355">
@@ -5029,10 +5029,10 @@
         </is>
       </c>
       <c r="B355" t="n">
-        <v>0.405497</v>
+        <v>0.400164</v>
       </c>
       <c r="C355" t="n">
-        <v>0.045946</v>
+        <v>0.051075</v>
       </c>
     </row>
     <row r="356">
@@ -5042,10 +5042,10 @@
         </is>
       </c>
       <c r="B356" t="n">
-        <v>0.40983</v>
+        <v>0.405497</v>
       </c>
       <c r="C356" t="n">
-        <v>0.043243</v>
+        <v>0.048387</v>
       </c>
     </row>
     <row r="357">
@@ -5055,10 +5055,10 @@
         </is>
       </c>
       <c r="B357" t="n">
-        <v>0.438596</v>
+        <v>0.40983</v>
       </c>
       <c r="C357" t="n">
-        <v>0.040541</v>
+        <v>0.045699</v>
       </c>
     </row>
     <row r="358">
@@ -5068,10 +5068,10 @@
         </is>
       </c>
       <c r="B358" t="n">
-        <v>0.440993</v>
+        <v>0.438596</v>
       </c>
       <c r="C358" t="n">
-        <v>0.037838</v>
+        <v>0.043011</v>
       </c>
     </row>
     <row r="359">
@@ -5081,10 +5081,10 @@
         </is>
       </c>
       <c r="B359" t="n">
-        <v>0.454545</v>
+        <v>0.440993</v>
       </c>
       <c r="C359" t="n">
-        <v>0.035135</v>
+        <v>0.040323</v>
       </c>
     </row>
     <row r="360">
@@ -5094,10 +5094,10 @@
         </is>
       </c>
       <c r="B360" t="n">
-        <v>0.46057</v>
+        <v>0.454545</v>
       </c>
       <c r="C360" t="n">
-        <v>0.032432</v>
+        <v>0.037634</v>
       </c>
     </row>
     <row r="361">
@@ -5107,10 +5107,10 @@
         </is>
       </c>
       <c r="B361" t="n">
-        <v>0.476745</v>
+        <v>0.46057</v>
       </c>
       <c r="C361" t="n">
-        <v>0.02973</v>
+        <v>0.034946</v>
       </c>
     </row>
     <row r="362">
@@ -5120,10 +5120,10 @@
         </is>
       </c>
       <c r="B362" t="n">
-        <v>0.605731</v>
+        <v>0.476745</v>
       </c>
       <c r="C362" t="n">
-        <v>0.027027</v>
+        <v>0.032258</v>
       </c>
     </row>
     <row r="363">
@@ -5133,10 +5133,10 @@
         </is>
       </c>
       <c r="B363" t="n">
-        <v>0.634074</v>
+        <v>0.605731</v>
       </c>
       <c r="C363" t="n">
-        <v>0.024324</v>
+        <v>0.02957</v>
       </c>
     </row>
     <row r="364">
@@ -5146,10 +5146,10 @@
         </is>
       </c>
       <c r="B364" t="n">
-        <v>0.648021</v>
+        <v>0.634074</v>
       </c>
       <c r="C364" t="n">
-        <v>0.021622</v>
+        <v>0.026882</v>
       </c>
     </row>
     <row r="365">
@@ -5159,10 +5159,10 @@
         </is>
       </c>
       <c r="B365" t="n">
-        <v>0.678189</v>
+        <v>0.648021</v>
       </c>
       <c r="C365" t="n">
-        <v>0.018919</v>
+        <v>0.024194</v>
       </c>
     </row>
     <row r="366">
@@ -5172,10 +5172,10 @@
         </is>
       </c>
       <c r="B366" t="n">
-        <v>0.707604</v>
+        <v>0.672083</v>
       </c>
       <c r="C366" t="n">
-        <v>0.016216</v>
+        <v>0.021505</v>
       </c>
     </row>
     <row r="367">
@@ -5185,10 +5185,10 @@
         </is>
       </c>
       <c r="B367" t="n">
-        <v>0.711338</v>
+        <v>0.678189</v>
       </c>
       <c r="C367" t="n">
-        <v>0.013514</v>
+        <v>0.018817</v>
       </c>
     </row>
     <row r="368">
@@ -5198,10 +5198,10 @@
         </is>
       </c>
       <c r="B368" t="n">
-        <v>0.76535</v>
+        <v>0.707604</v>
       </c>
       <c r="C368" t="n">
-        <v>0.010811</v>
+        <v>0.016129</v>
       </c>
     </row>
     <row r="369">
@@ -5211,10 +5211,10 @@
         </is>
       </c>
       <c r="B369" t="n">
-        <v>0.838984</v>
+        <v>0.711338</v>
       </c>
       <c r="C369" t="n">
-        <v>0.008108000000000001</v>
+        <v>0.013441</v>
       </c>
     </row>
     <row r="370">
@@ -5224,10 +5224,10 @@
         </is>
       </c>
       <c r="B370" t="n">
-        <v>1.015082</v>
+        <v>0.76535</v>
       </c>
       <c r="C370" t="n">
-        <v>0.005405</v>
+        <v>0.010753</v>
       </c>
     </row>
     <row r="371">
@@ -5237,36 +5237,36 @@
         </is>
       </c>
       <c r="B371" t="n">
-        <v>1.233322</v>
+        <v>0.838984</v>
       </c>
       <c r="C371" t="n">
-        <v>0.002703</v>
+        <v>0.008064999999999999</v>
       </c>
     </row>
     <row r="372">
       <c r="A372" t="inlineStr">
         <is>
-          <t>Adjusted target</t>
+          <t>Raw market</t>
         </is>
       </c>
       <c r="B372" t="n">
-        <v>4e-06</v>
+        <v>1.015082</v>
       </c>
       <c r="C372" t="n">
-        <v>1</v>
+        <v>0.005376</v>
       </c>
     </row>
     <row r="373">
       <c r="A373" t="inlineStr">
         <is>
-          <t>Adjusted target</t>
+          <t>Raw market</t>
         </is>
       </c>
       <c r="B373" t="n">
-        <v>0.00011</v>
+        <v>1.233322</v>
       </c>
       <c r="C373" t="n">
-        <v>0.997297</v>
+        <v>0.002688</v>
       </c>
     </row>
     <row r="374">
@@ -5276,10 +5276,10 @@
         </is>
       </c>
       <c r="B374" t="n">
-        <v>0.000519</v>
+        <v>4e-06</v>
       </c>
       <c r="C374" t="n">
-        <v>0.994595</v>
+        <v>1</v>
       </c>
     </row>
     <row r="375">
@@ -5289,10 +5289,10 @@
         </is>
       </c>
       <c r="B375" t="n">
-        <v>0.00052</v>
+        <v>0.000109</v>
       </c>
       <c r="C375" t="n">
-        <v>0.991892</v>
+        <v>0.997312</v>
       </c>
     </row>
     <row r="376">
@@ -5302,10 +5302,10 @@
         </is>
       </c>
       <c r="B376" t="n">
-        <v>0.001693</v>
+        <v>0.000516</v>
       </c>
       <c r="C376" t="n">
-        <v>0.989189</v>
+        <v>0.994624</v>
       </c>
     </row>
     <row r="377">
@@ -5315,10 +5315,10 @@
         </is>
       </c>
       <c r="B377" t="n">
-        <v>0.001868</v>
+        <v>0.000518</v>
       </c>
       <c r="C377" t="n">
-        <v>0.986486</v>
+        <v>0.991935</v>
       </c>
     </row>
     <row r="378">
@@ -5328,10 +5328,10 @@
         </is>
       </c>
       <c r="B378" t="n">
-        <v>0.001979</v>
+        <v>0.000928</v>
       </c>
       <c r="C378" t="n">
-        <v>0.983784</v>
+        <v>0.989247</v>
       </c>
     </row>
     <row r="379">
@@ -5341,10 +5341,10 @@
         </is>
       </c>
       <c r="B379" t="n">
-        <v>0.001982</v>
+        <v>0.00168</v>
       </c>
       <c r="C379" t="n">
-        <v>0.981081</v>
+        <v>0.986559</v>
       </c>
     </row>
     <row r="380">
@@ -5354,10 +5354,10 @@
         </is>
       </c>
       <c r="B380" t="n">
-        <v>0.002462</v>
+        <v>0.001819</v>
       </c>
       <c r="C380" t="n">
-        <v>0.978378</v>
+        <v>0.9838710000000001</v>
       </c>
     </row>
     <row r="381">
@@ -5367,10 +5367,10 @@
         </is>
       </c>
       <c r="B381" t="n">
-        <v>0.00277</v>
+        <v>0.001962</v>
       </c>
       <c r="C381" t="n">
-        <v>0.975676</v>
+        <v>0.981183</v>
       </c>
     </row>
     <row r="382">
@@ -5380,10 +5380,10 @@
         </is>
       </c>
       <c r="B382" t="n">
-        <v>0.003111</v>
+        <v>0.001972</v>
       </c>
       <c r="C382" t="n">
-        <v>0.972973</v>
+        <v>0.978495</v>
       </c>
     </row>
     <row r="383">
@@ -5393,10 +5393,10 @@
         </is>
       </c>
       <c r="B383" t="n">
-        <v>0.003524</v>
+        <v>0.002441</v>
       </c>
       <c r="C383" t="n">
-        <v>0.97027</v>
+        <v>0.975806</v>
       </c>
     </row>
     <row r="384">
@@ -5406,10 +5406,10 @@
         </is>
       </c>
       <c r="B384" t="n">
-        <v>0.004014</v>
+        <v>0.002742</v>
       </c>
       <c r="C384" t="n">
-        <v>0.967568</v>
+        <v>0.973118</v>
       </c>
     </row>
     <row r="385">
@@ -5419,10 +5419,10 @@
         </is>
       </c>
       <c r="B385" t="n">
-        <v>0.004045</v>
+        <v>0.003089</v>
       </c>
       <c r="C385" t="n">
-        <v>0.964865</v>
+        <v>0.97043</v>
       </c>
     </row>
     <row r="386">
@@ -5432,10 +5432,10 @@
         </is>
       </c>
       <c r="B386" t="n">
-        <v>0.00425</v>
+        <v>0.003482</v>
       </c>
       <c r="C386" t="n">
-        <v>0.962162</v>
+        <v>0.967742</v>
       </c>
     </row>
     <row r="387">
@@ -5445,10 +5445,10 @@
         </is>
       </c>
       <c r="B387" t="n">
-        <v>0.004358</v>
+        <v>0.003899</v>
       </c>
       <c r="C387" t="n">
-        <v>0.959459</v>
+        <v>0.965054</v>
       </c>
     </row>
     <row r="388">
@@ -5458,10 +5458,10 @@
         </is>
       </c>
       <c r="B388" t="n">
-        <v>0.004364</v>
+        <v>0.00401</v>
       </c>
       <c r="C388" t="n">
-        <v>0.956757</v>
+        <v>0.9623660000000001</v>
       </c>
     </row>
     <row r="389">
@@ -5471,10 +5471,10 @@
         </is>
       </c>
       <c r="B389" t="n">
-        <v>0.004568</v>
+        <v>0.004228</v>
       </c>
       <c r="C389" t="n">
-        <v>0.954054</v>
+        <v>0.959677</v>
       </c>
     </row>
     <row r="390">
@@ -5484,10 +5484,10 @@
         </is>
       </c>
       <c r="B390" t="n">
-        <v>0.004836</v>
+        <v>0.004293</v>
       </c>
       <c r="C390" t="n">
-        <v>0.9513509999999999</v>
+        <v>0.956989</v>
       </c>
     </row>
     <row r="391">
@@ -5497,10 +5497,10 @@
         </is>
       </c>
       <c r="B391" t="n">
-        <v>0.004961</v>
+        <v>0.004348</v>
       </c>
       <c r="C391" t="n">
-        <v>0.948649</v>
+        <v>0.954301</v>
       </c>
     </row>
     <row r="392">
@@ -5510,10 +5510,10 @@
         </is>
       </c>
       <c r="B392" t="n">
-        <v>0.004989</v>
+        <v>0.004526</v>
       </c>
       <c r="C392" t="n">
-        <v>0.945946</v>
+        <v>0.951613</v>
       </c>
     </row>
     <row r="393">
@@ -5523,10 +5523,10 @@
         </is>
       </c>
       <c r="B393" t="n">
-        <v>0.005056</v>
+        <v>0.004821</v>
       </c>
       <c r="C393" t="n">
-        <v>0.9432430000000001</v>
+        <v>0.948925</v>
       </c>
     </row>
     <row r="394">
@@ -5536,10 +5536,10 @@
         </is>
       </c>
       <c r="B394" t="n">
-        <v>0.005096</v>
+        <v>0.004851</v>
       </c>
       <c r="C394" t="n">
-        <v>0.940541</v>
+        <v>0.946237</v>
       </c>
     </row>
     <row r="395">
@@ -5549,10 +5549,10 @@
         </is>
       </c>
       <c r="B395" t="n">
-        <v>0.00518</v>
+        <v>0.004851</v>
       </c>
       <c r="C395" t="n">
-        <v>0.9378379999999999</v>
+        <v>0.9435480000000001</v>
       </c>
     </row>
     <row r="396">
@@ -5562,10 +5562,10 @@
         </is>
       </c>
       <c r="B396" t="n">
-        <v>0.005358</v>
+        <v>0.005005</v>
       </c>
       <c r="C396" t="n">
-        <v>0.935135</v>
+        <v>0.94086</v>
       </c>
     </row>
     <row r="397">
@@ -5575,10 +5575,10 @@
         </is>
       </c>
       <c r="B397" t="n">
-        <v>0.005512</v>
+        <v>0.005028</v>
       </c>
       <c r="C397" t="n">
-        <v>0.932432</v>
+        <v>0.938172</v>
       </c>
     </row>
     <row r="398">
@@ -5588,10 +5588,10 @@
         </is>
       </c>
       <c r="B398" t="n">
-        <v>0.005892</v>
+        <v>0.005148</v>
       </c>
       <c r="C398" t="n">
-        <v>0.9297299999999999</v>
+        <v>0.935484</v>
       </c>
     </row>
     <row r="399">
@@ -5601,10 +5601,10 @@
         </is>
       </c>
       <c r="B399" t="n">
-        <v>0.005907</v>
+        <v>0.005302</v>
       </c>
       <c r="C399" t="n">
-        <v>0.927027</v>
+        <v>0.932796</v>
       </c>
     </row>
     <row r="400">
@@ -5614,10 +5614,10 @@
         </is>
       </c>
       <c r="B400" t="n">
-        <v>0.005941</v>
+        <v>0.005401</v>
       </c>
       <c r="C400" t="n">
-        <v>0.924324</v>
+        <v>0.930108</v>
       </c>
     </row>
     <row r="401">
@@ -5627,10 +5627,10 @@
         </is>
       </c>
       <c r="B401" t="n">
-        <v>0.006047</v>
+        <v>0.005836</v>
       </c>
       <c r="C401" t="n">
-        <v>0.9216220000000001</v>
+        <v>0.927419</v>
       </c>
     </row>
     <row r="402">
@@ -5640,10 +5640,10 @@
         </is>
       </c>
       <c r="B402" t="n">
-        <v>0.007163</v>
+        <v>0.005879</v>
       </c>
       <c r="C402" t="n">
-        <v>0.918919</v>
+        <v>0.924731</v>
       </c>
     </row>
     <row r="403">
@@ -5653,10 +5653,10 @@
         </is>
       </c>
       <c r="B403" t="n">
-        <v>0.007775</v>
+        <v>0.005881</v>
       </c>
       <c r="C403" t="n">
-        <v>0.916216</v>
+        <v>0.9220429999999999</v>
       </c>
     </row>
     <row r="404">
@@ -5666,10 +5666,10 @@
         </is>
       </c>
       <c r="B404" t="n">
-        <v>0.007848000000000001</v>
+        <v>0.006012</v>
       </c>
       <c r="C404" t="n">
-        <v>0.913514</v>
+        <v>0.919355</v>
       </c>
     </row>
     <row r="405">
@@ -5679,10 +5679,10 @@
         </is>
       </c>
       <c r="B405" t="n">
-        <v>0.008211</v>
+        <v>0.007077</v>
       </c>
       <c r="C405" t="n">
-        <v>0.910811</v>
+        <v>0.916667</v>
       </c>
     </row>
     <row r="406">
@@ -5692,10 +5692,10 @@
         </is>
       </c>
       <c r="B406" t="n">
-        <v>0.008734</v>
+        <v>0.007592</v>
       </c>
       <c r="C406" t="n">
-        <v>0.908108</v>
+        <v>0.913978</v>
       </c>
     </row>
     <row r="407">
@@ -5705,10 +5705,10 @@
         </is>
       </c>
       <c r="B407" t="n">
-        <v>0.009013999999999999</v>
+        <v>0.007821</v>
       </c>
       <c r="C407" t="n">
-        <v>0.905405</v>
+        <v>0.91129</v>
       </c>
     </row>
     <row r="408">
@@ -5718,10 +5718,10 @@
         </is>
       </c>
       <c r="B408" t="n">
-        <v>0.009611</v>
+        <v>0.008194999999999999</v>
       </c>
       <c r="C408" t="n">
-        <v>0.902703</v>
+        <v>0.908602</v>
       </c>
     </row>
     <row r="409">
@@ -5731,10 +5731,10 @@
         </is>
       </c>
       <c r="B409" t="n">
-        <v>0.010036</v>
+        <v>0.008689000000000001</v>
       </c>
       <c r="C409" t="n">
-        <v>0.9</v>
+        <v>0.905914</v>
       </c>
     </row>
     <row r="410">
@@ -5744,10 +5744,10 @@
         </is>
       </c>
       <c r="B410" t="n">
-        <v>0.010065</v>
+        <v>0.008987999999999999</v>
       </c>
       <c r="C410" t="n">
-        <v>0.897297</v>
+        <v>0.903226</v>
       </c>
     </row>
     <row r="411">
@@ -5757,10 +5757,10 @@
         </is>
       </c>
       <c r="B411" t="n">
-        <v>0.01009</v>
+        <v>0.009497999999999999</v>
       </c>
       <c r="C411" t="n">
-        <v>0.894595</v>
+        <v>0.9005379999999999</v>
       </c>
     </row>
     <row r="412">
@@ -5770,10 +5770,10 @@
         </is>
       </c>
       <c r="B412" t="n">
-        <v>0.010122</v>
+        <v>0.009976</v>
       </c>
       <c r="C412" t="n">
-        <v>0.891892</v>
+        <v>0.897849</v>
       </c>
     </row>
     <row r="413">
@@ -5783,10 +5783,10 @@
         </is>
       </c>
       <c r="B413" t="n">
-        <v>0.010366</v>
+        <v>0.009979</v>
       </c>
       <c r="C413" t="n">
-        <v>0.889189</v>
+        <v>0.895161</v>
       </c>
     </row>
     <row r="414">
@@ -5796,10 +5796,10 @@
         </is>
       </c>
       <c r="B414" t="n">
-        <v>0.010486</v>
+        <v>0.010052</v>
       </c>
       <c r="C414" t="n">
-        <v>0.886486</v>
+        <v>0.892473</v>
       </c>
     </row>
     <row r="415">
@@ -5809,10 +5809,10 @@
         </is>
       </c>
       <c r="B415" t="n">
-        <v>0.010488</v>
+        <v>0.010053</v>
       </c>
       <c r="C415" t="n">
-        <v>0.883784</v>
+        <v>0.889785</v>
       </c>
     </row>
     <row r="416">
@@ -5822,10 +5822,10 @@
         </is>
       </c>
       <c r="B416" t="n">
-        <v>0.010841</v>
+        <v>0.010311</v>
       </c>
       <c r="C416" t="n">
-        <v>0.881081</v>
+        <v>0.887097</v>
       </c>
     </row>
     <row r="417">
@@ -5835,10 +5835,10 @@
         </is>
       </c>
       <c r="B417" t="n">
-        <v>0.01092</v>
+        <v>0.010334</v>
       </c>
       <c r="C417" t="n">
-        <v>0.878378</v>
+        <v>0.884409</v>
       </c>
     </row>
     <row r="418">
@@ -5848,10 +5848,10 @@
         </is>
       </c>
       <c r="B418" t="n">
-        <v>0.011072</v>
+        <v>0.010409</v>
       </c>
       <c r="C418" t="n">
-        <v>0.875676</v>
+        <v>0.8817199999999999</v>
       </c>
     </row>
     <row r="419">
@@ -5861,10 +5861,10 @@
         </is>
       </c>
       <c r="B419" t="n">
-        <v>0.011274</v>
+        <v>0.010718</v>
       </c>
       <c r="C419" t="n">
-        <v>0.872973</v>
+        <v>0.879032</v>
       </c>
     </row>
     <row r="420">
@@ -5874,10 +5874,10 @@
         </is>
       </c>
       <c r="B420" t="n">
-        <v>0.011278</v>
+        <v>0.010802</v>
       </c>
       <c r="C420" t="n">
-        <v>0.87027</v>
+        <v>0.876344</v>
       </c>
     </row>
     <row r="421">
@@ -5887,10 +5887,10 @@
         </is>
       </c>
       <c r="B421" t="n">
-        <v>0.011774</v>
+        <v>0.011107</v>
       </c>
       <c r="C421" t="n">
-        <v>0.867568</v>
+        <v>0.873656</v>
       </c>
     </row>
     <row r="422">
@@ -5900,10 +5900,10 @@
         </is>
       </c>
       <c r="B422" t="n">
-        <v>0.012049</v>
+        <v>0.01117</v>
       </c>
       <c r="C422" t="n">
-        <v>0.864865</v>
+        <v>0.870968</v>
       </c>
     </row>
     <row r="423">
@@ -5913,10 +5913,10 @@
         </is>
       </c>
       <c r="B423" t="n">
-        <v>0.012339</v>
+        <v>0.011719</v>
       </c>
       <c r="C423" t="n">
-        <v>0.862162</v>
+        <v>0.8682800000000001</v>
       </c>
     </row>
     <row r="424">
@@ -5926,10 +5926,10 @@
         </is>
       </c>
       <c r="B424" t="n">
-        <v>0.012384</v>
+        <v>0.012012</v>
       </c>
       <c r="C424" t="n">
-        <v>0.859459</v>
+        <v>0.865591</v>
       </c>
     </row>
     <row r="425">
@@ -5939,10 +5939,10 @@
         </is>
       </c>
       <c r="B425" t="n">
-        <v>0.012485</v>
+        <v>0.012114</v>
       </c>
       <c r="C425" t="n">
-        <v>0.856757</v>
+        <v>0.862903</v>
       </c>
     </row>
     <row r="426">
@@ -5952,10 +5952,10 @@
         </is>
       </c>
       <c r="B426" t="n">
-        <v>0.01275</v>
+        <v>0.012221</v>
       </c>
       <c r="C426" t="n">
-        <v>0.854054</v>
+        <v>0.860215</v>
       </c>
     </row>
     <row r="427">
@@ -5965,10 +5965,10 @@
         </is>
       </c>
       <c r="B427" t="n">
-        <v>0.013125</v>
+        <v>0.012295</v>
       </c>
       <c r="C427" t="n">
-        <v>0.851351</v>
+        <v>0.857527</v>
       </c>
     </row>
     <row r="428">
@@ -5978,10 +5978,10 @@
         </is>
       </c>
       <c r="B428" t="n">
-        <v>0.013185</v>
+        <v>0.012708</v>
       </c>
       <c r="C428" t="n">
-        <v>0.848649</v>
+        <v>0.854839</v>
       </c>
     </row>
     <row r="429">
@@ -5991,10 +5991,10 @@
         </is>
       </c>
       <c r="B429" t="n">
-        <v>0.013299</v>
+        <v>0.013049</v>
       </c>
       <c r="C429" t="n">
-        <v>0.845946</v>
+        <v>0.852151</v>
       </c>
     </row>
     <row r="430">
@@ -6004,10 +6004,10 @@
         </is>
       </c>
       <c r="B430" t="n">
-        <v>0.013311</v>
+        <v>0.013127</v>
       </c>
       <c r="C430" t="n">
-        <v>0.843243</v>
+        <v>0.8494620000000001</v>
       </c>
     </row>
     <row r="431">
@@ -6017,10 +6017,10 @@
         </is>
       </c>
       <c r="B431" t="n">
-        <v>0.014166</v>
+        <v>0.013221</v>
       </c>
       <c r="C431" t="n">
-        <v>0.840541</v>
+        <v>0.846774</v>
       </c>
     </row>
     <row r="432">
@@ -6030,10 +6030,10 @@
         </is>
       </c>
       <c r="B432" t="n">
-        <v>0.01447</v>
+        <v>0.013223</v>
       </c>
       <c r="C432" t="n">
-        <v>0.837838</v>
+        <v>0.844086</v>
       </c>
     </row>
     <row r="433">
@@ -6043,10 +6043,10 @@
         </is>
       </c>
       <c r="B433" t="n">
-        <v>0.014565</v>
+        <v>0.014012</v>
       </c>
       <c r="C433" t="n">
-        <v>0.835135</v>
+        <v>0.841398</v>
       </c>
     </row>
     <row r="434">
@@ -6056,10 +6056,10 @@
         </is>
       </c>
       <c r="B434" t="n">
-        <v>0.014626</v>
+        <v>0.014434</v>
       </c>
       <c r="C434" t="n">
-        <v>0.8324319999999999</v>
+        <v>0.83871</v>
       </c>
     </row>
     <row r="435">
@@ -6069,10 +6069,10 @@
         </is>
       </c>
       <c r="B435" t="n">
-        <v>0.014712</v>
+        <v>0.01444</v>
       </c>
       <c r="C435" t="n">
-        <v>0.82973</v>
+        <v>0.836022</v>
       </c>
     </row>
     <row r="436">
@@ -6082,10 +6082,10 @@
         </is>
       </c>
       <c r="B436" t="n">
-        <v>0.014992</v>
+        <v>0.014533</v>
       </c>
       <c r="C436" t="n">
-        <v>0.827027</v>
+        <v>0.833333</v>
       </c>
     </row>
     <row r="437">
@@ -6095,10 +6095,10 @@
         </is>
       </c>
       <c r="B437" t="n">
-        <v>0.015139</v>
+        <v>0.014586</v>
       </c>
       <c r="C437" t="n">
-        <v>0.8243239999999999</v>
+        <v>0.830645</v>
       </c>
     </row>
     <row r="438">
@@ -6108,10 +6108,10 @@
         </is>
       </c>
       <c r="B438" t="n">
-        <v>0.015456</v>
+        <v>0.014879</v>
       </c>
       <c r="C438" t="n">
-        <v>0.821622</v>
+        <v>0.8279570000000001</v>
       </c>
     </row>
     <row r="439">
@@ -6121,10 +6121,10 @@
         </is>
       </c>
       <c r="B439" t="n">
-        <v>0.015475</v>
+        <v>0.015032</v>
       </c>
       <c r="C439" t="n">
-        <v>0.818919</v>
+        <v>0.825269</v>
       </c>
     </row>
     <row r="440">
@@ -6134,10 +6134,10 @@
         </is>
       </c>
       <c r="B440" t="n">
-        <v>0.01572</v>
+        <v>0.015315</v>
       </c>
       <c r="C440" t="n">
-        <v>0.8162160000000001</v>
+        <v>0.822581</v>
       </c>
     </row>
     <row r="441">
@@ -6147,10 +6147,10 @@
         </is>
       </c>
       <c r="B441" t="n">
-        <v>0.015908</v>
+        <v>0.015429</v>
       </c>
       <c r="C441" t="n">
-        <v>0.813514</v>
+        <v>0.819892</v>
       </c>
     </row>
     <row r="442">
@@ -6160,10 +6160,10 @@
         </is>
       </c>
       <c r="B442" t="n">
-        <v>0.016077</v>
+        <v>0.015639</v>
       </c>
       <c r="C442" t="n">
-        <v>0.8108109999999999</v>
+        <v>0.817204</v>
       </c>
     </row>
     <row r="443">
@@ -6173,10 +6173,10 @@
         </is>
       </c>
       <c r="B443" t="n">
-        <v>0.016086</v>
+        <v>0.015977</v>
       </c>
       <c r="C443" t="n">
-        <v>0.808108</v>
+        <v>0.814516</v>
       </c>
     </row>
     <row r="444">
@@ -6186,10 +6186,10 @@
         </is>
       </c>
       <c r="B444" t="n">
-        <v>0.016093</v>
+        <v>0.015996</v>
       </c>
       <c r="C444" t="n">
-        <v>0.805405</v>
+        <v>0.811828</v>
       </c>
     </row>
     <row r="445">
@@ -6199,10 +6199,10 @@
         </is>
       </c>
       <c r="B445" t="n">
-        <v>0.016201</v>
+        <v>0.016054</v>
       </c>
       <c r="C445" t="n">
-        <v>0.8027030000000001</v>
+        <v>0.80914</v>
       </c>
     </row>
     <row r="446">
@@ -6212,10 +6212,10 @@
         </is>
       </c>
       <c r="B446" t="n">
-        <v>0.016324</v>
+        <v>0.01606</v>
       </c>
       <c r="C446" t="n">
-        <v>0.8</v>
+        <v>0.8064519999999999</v>
       </c>
     </row>
     <row r="447">
@@ -6225,10 +6225,10 @@
         </is>
       </c>
       <c r="B447" t="n">
-        <v>0.016339</v>
+        <v>0.016241</v>
       </c>
       <c r="C447" t="n">
-        <v>0.797297</v>
+        <v>0.803763</v>
       </c>
     </row>
     <row r="448">
@@ -6238,10 +6238,10 @@
         </is>
       </c>
       <c r="B448" t="n">
-        <v>0.017143</v>
+        <v>0.01629</v>
       </c>
       <c r="C448" t="n">
-        <v>0.7945950000000001</v>
+        <v>0.801075</v>
       </c>
     </row>
     <row r="449">
@@ -6251,10 +6251,10 @@
         </is>
       </c>
       <c r="B449" t="n">
-        <v>0.0174</v>
+        <v>0.016939</v>
       </c>
       <c r="C449" t="n">
-        <v>0.791892</v>
+        <v>0.798387</v>
       </c>
     </row>
     <row r="450">
@@ -6264,10 +6264,10 @@
         </is>
       </c>
       <c r="B450" t="n">
-        <v>0.017806</v>
+        <v>0.01702</v>
       </c>
       <c r="C450" t="n">
-        <v>0.789189</v>
+        <v>0.795699</v>
       </c>
     </row>
     <row r="451">
@@ -6277,10 +6277,10 @@
         </is>
       </c>
       <c r="B451" t="n">
-        <v>0.018599</v>
+        <v>0.017278</v>
       </c>
       <c r="C451" t="n">
-        <v>0.786486</v>
+        <v>0.793011</v>
       </c>
     </row>
     <row r="452">
@@ -6290,10 +6290,10 @@
         </is>
       </c>
       <c r="B452" t="n">
-        <v>0.018705</v>
+        <v>0.017641</v>
       </c>
       <c r="C452" t="n">
-        <v>0.783784</v>
+        <v>0.790323</v>
       </c>
     </row>
     <row r="453">
@@ -6303,10 +6303,10 @@
         </is>
       </c>
       <c r="B453" t="n">
-        <v>0.018837</v>
+        <v>0.018482</v>
       </c>
       <c r="C453" t="n">
-        <v>0.781081</v>
+        <v>0.7876339999999999</v>
       </c>
     </row>
     <row r="454">
@@ -6316,10 +6316,10 @@
         </is>
       </c>
       <c r="B454" t="n">
-        <v>0.019015</v>
+        <v>0.018657</v>
       </c>
       <c r="C454" t="n">
-        <v>0.778378</v>
+        <v>0.784946</v>
       </c>
     </row>
     <row r="455">
@@ -6329,10 +6329,10 @@
         </is>
       </c>
       <c r="B455" t="n">
-        <v>0.019033</v>
+        <v>0.018675</v>
       </c>
       <c r="C455" t="n">
-        <v>0.775676</v>
+        <v>0.782258</v>
       </c>
     </row>
     <row r="456">
@@ -6342,10 +6342,10 @@
         </is>
       </c>
       <c r="B456" t="n">
-        <v>0.019656</v>
+        <v>0.018906</v>
       </c>
       <c r="C456" t="n">
-        <v>0.772973</v>
+        <v>0.77957</v>
       </c>
     </row>
     <row r="457">
@@ -6355,10 +6355,10 @@
         </is>
       </c>
       <c r="B457" t="n">
-        <v>0.020068</v>
+        <v>0.018959</v>
       </c>
       <c r="C457" t="n">
-        <v>0.77027</v>
+        <v>0.776882</v>
       </c>
     </row>
     <row r="458">
@@ -6368,10 +6368,10 @@
         </is>
       </c>
       <c r="B458" t="n">
-        <v>0.020108</v>
+        <v>0.019553</v>
       </c>
       <c r="C458" t="n">
-        <v>0.767568</v>
+        <v>0.774194</v>
       </c>
     </row>
     <row r="459">
@@ -6381,10 +6381,10 @@
         </is>
       </c>
       <c r="B459" t="n">
-        <v>0.020296</v>
+        <v>0.020013</v>
       </c>
       <c r="C459" t="n">
-        <v>0.764865</v>
+        <v>0.771505</v>
       </c>
     </row>
     <row r="460">
@@ -6394,10 +6394,10 @@
         </is>
       </c>
       <c r="B460" t="n">
-        <v>0.020454</v>
+        <v>0.020021</v>
       </c>
       <c r="C460" t="n">
-        <v>0.762162</v>
+        <v>0.768817</v>
       </c>
     </row>
     <row r="461">
@@ -6407,10 +6407,10 @@
         </is>
       </c>
       <c r="B461" t="n">
-        <v>0.020606</v>
+        <v>0.020081</v>
       </c>
       <c r="C461" t="n">
-        <v>0.759459</v>
+        <v>0.7661289999999999</v>
       </c>
     </row>
     <row r="462">
@@ -6420,10 +6420,10 @@
         </is>
       </c>
       <c r="B462" t="n">
-        <v>0.020756</v>
+        <v>0.020247</v>
       </c>
       <c r="C462" t="n">
-        <v>0.756757</v>
+        <v>0.763441</v>
       </c>
     </row>
     <row r="463">
@@ -6433,10 +6433,10 @@
         </is>
       </c>
       <c r="B463" t="n">
-        <v>0.02141</v>
+        <v>0.020568</v>
       </c>
       <c r="C463" t="n">
-        <v>0.754054</v>
+        <v>0.760753</v>
       </c>
     </row>
     <row r="464">
@@ -6446,10 +6446,10 @@
         </is>
       </c>
       <c r="B464" t="n">
-        <v>0.021422</v>
+        <v>0.020691</v>
       </c>
       <c r="C464" t="n">
-        <v>0.751351</v>
+        <v>0.758065</v>
       </c>
     </row>
     <row r="465">
@@ -6459,10 +6459,10 @@
         </is>
       </c>
       <c r="B465" t="n">
-        <v>0.022243</v>
+        <v>0.021237</v>
       </c>
       <c r="C465" t="n">
-        <v>0.748649</v>
+        <v>0.755376</v>
       </c>
     </row>
     <row r="466">
@@ -6472,10 +6472,10 @@
         </is>
       </c>
       <c r="B466" t="n">
-        <v>0.022638</v>
+        <v>0.02134</v>
       </c>
       <c r="C466" t="n">
-        <v>0.745946</v>
+        <v>0.752688</v>
       </c>
     </row>
     <row r="467">
@@ -6485,10 +6485,10 @@
         </is>
       </c>
       <c r="B467" t="n">
-        <v>0.022808</v>
+        <v>0.021451</v>
       </c>
       <c r="C467" t="n">
-        <v>0.743243</v>
+        <v>0.75</v>
       </c>
     </row>
     <row r="468">
@@ -6498,10 +6498,10 @@
         </is>
       </c>
       <c r="B468" t="n">
-        <v>0.022948</v>
+        <v>0.022102</v>
       </c>
       <c r="C468" t="n">
-        <v>0.740541</v>
+        <v>0.747312</v>
       </c>
     </row>
     <row r="469">
@@ -6511,10 +6511,10 @@
         </is>
       </c>
       <c r="B469" t="n">
-        <v>0.023546</v>
+        <v>0.022713</v>
       </c>
       <c r="C469" t="n">
-        <v>0.737838</v>
+        <v>0.744624</v>
       </c>
     </row>
     <row r="470">
@@ -6524,10 +6524,10 @@
         </is>
       </c>
       <c r="B470" t="n">
-        <v>0.024581</v>
+        <v>0.022756</v>
       </c>
       <c r="C470" t="n">
-        <v>0.735135</v>
+        <v>0.741935</v>
       </c>
     </row>
     <row r="471">
@@ -6537,10 +6537,10 @@
         </is>
       </c>
       <c r="B471" t="n">
-        <v>0.024765</v>
+        <v>0.023298</v>
       </c>
       <c r="C471" t="n">
-        <v>0.732432</v>
+        <v>0.739247</v>
       </c>
     </row>
     <row r="472">
@@ -6550,10 +6550,10 @@
         </is>
       </c>
       <c r="B472" t="n">
-        <v>0.024769</v>
+        <v>0.024539</v>
       </c>
       <c r="C472" t="n">
-        <v>0.72973</v>
+        <v>0.736559</v>
       </c>
     </row>
     <row r="473">
@@ -6563,10 +6563,10 @@
         </is>
       </c>
       <c r="B473" t="n">
-        <v>0.02525</v>
+        <v>0.024619</v>
       </c>
       <c r="C473" t="n">
-        <v>0.727027</v>
+        <v>0.7338710000000001</v>
       </c>
     </row>
     <row r="474">
@@ -6576,10 +6576,10 @@
         </is>
       </c>
       <c r="B474" t="n">
-        <v>0.025566</v>
+        <v>0.024658</v>
       </c>
       <c r="C474" t="n">
-        <v>0.724324</v>
+        <v>0.731183</v>
       </c>
     </row>
     <row r="475">
@@ -6589,10 +6589,10 @@
         </is>
       </c>
       <c r="B475" t="n">
-        <v>0.026107</v>
+        <v>0.025112</v>
       </c>
       <c r="C475" t="n">
-        <v>0.721622</v>
+        <v>0.728495</v>
       </c>
     </row>
     <row r="476">
@@ -6602,10 +6602,10 @@
         </is>
       </c>
       <c r="B476" t="n">
-        <v>0.026782</v>
+        <v>0.025337</v>
       </c>
       <c r="C476" t="n">
-        <v>0.718919</v>
+        <v>0.725806</v>
       </c>
     </row>
     <row r="477">
@@ -6615,10 +6615,10 @@
         </is>
       </c>
       <c r="B477" t="n">
-        <v>0.026812</v>
+        <v>0.02597</v>
       </c>
       <c r="C477" t="n">
-        <v>0.716216</v>
+        <v>0.723118</v>
       </c>
     </row>
     <row r="478">
@@ -6628,10 +6628,10 @@
         </is>
       </c>
       <c r="B478" t="n">
-        <v>0.027063</v>
+        <v>0.026507</v>
       </c>
       <c r="C478" t="n">
-        <v>0.713514</v>
+        <v>0.72043</v>
       </c>
     </row>
     <row r="479">
@@ -6641,10 +6641,10 @@
         </is>
       </c>
       <c r="B479" t="n">
-        <v>0.0274</v>
+        <v>0.026606</v>
       </c>
       <c r="C479" t="n">
-        <v>0.710811</v>
+        <v>0.717742</v>
       </c>
     </row>
     <row r="480">
@@ -6654,10 +6654,10 @@
         </is>
       </c>
       <c r="B480" t="n">
-        <v>0.027456</v>
+        <v>0.026654</v>
       </c>
       <c r="C480" t="n">
-        <v>0.708108</v>
+        <v>0.715054</v>
       </c>
     </row>
     <row r="481">
@@ -6667,10 +6667,10 @@
         </is>
       </c>
       <c r="B481" t="n">
-        <v>0.027538</v>
+        <v>0.026731</v>
       </c>
       <c r="C481" t="n">
-        <v>0.7054049999999999</v>
+        <v>0.7123660000000001</v>
       </c>
     </row>
     <row r="482">
@@ -6680,10 +6680,10 @@
         </is>
       </c>
       <c r="B482" t="n">
-        <v>0.027769</v>
+        <v>0.026955</v>
       </c>
       <c r="C482" t="n">
-        <v>0.702703</v>
+        <v>0.709677</v>
       </c>
     </row>
     <row r="483">
@@ -6693,10 +6693,10 @@
         </is>
       </c>
       <c r="B483" t="n">
-        <v>0.027963</v>
+        <v>0.027299</v>
       </c>
       <c r="C483" t="n">
-        <v>0.7</v>
+        <v>0.706989</v>
       </c>
     </row>
     <row r="484">
@@ -6706,10 +6706,10 @@
         </is>
       </c>
       <c r="B484" t="n">
-        <v>0.028097</v>
+        <v>0.027394</v>
       </c>
       <c r="C484" t="n">
-        <v>0.6972969999999999</v>
+        <v>0.704301</v>
       </c>
     </row>
     <row r="485">
@@ -6719,10 +6719,10 @@
         </is>
       </c>
       <c r="B485" t="n">
-        <v>0.028341</v>
+        <v>0.027557</v>
       </c>
       <c r="C485" t="n">
-        <v>0.694595</v>
+        <v>0.701613</v>
       </c>
     </row>
     <row r="486">
@@ -6732,10 +6732,10 @@
         </is>
       </c>
       <c r="B486" t="n">
-        <v>0.028708</v>
+        <v>0.027802</v>
       </c>
       <c r="C486" t="n">
-        <v>0.691892</v>
+        <v>0.698925</v>
       </c>
     </row>
     <row r="487">
@@ -6745,10 +6745,10 @@
         </is>
       </c>
       <c r="B487" t="n">
-        <v>0.028855</v>
+        <v>0.027829</v>
       </c>
       <c r="C487" t="n">
-        <v>0.6891890000000001</v>
+        <v>0.696237</v>
       </c>
     </row>
     <row r="488">
@@ -6758,10 +6758,10 @@
         </is>
       </c>
       <c r="B488" t="n">
-        <v>0.029408</v>
+        <v>0.028126</v>
       </c>
       <c r="C488" t="n">
-        <v>0.686486</v>
+        <v>0.6935480000000001</v>
       </c>
     </row>
     <row r="489">
@@ -6771,10 +6771,10 @@
         </is>
       </c>
       <c r="B489" t="n">
-        <v>0.029425</v>
+        <v>0.028233</v>
       </c>
       <c r="C489" t="n">
-        <v>0.6837839999999999</v>
+        <v>0.69086</v>
       </c>
     </row>
     <row r="490">
@@ -6784,10 +6784,10 @@
         </is>
       </c>
       <c r="B490" t="n">
-        <v>0.029623</v>
+        <v>0.028688</v>
       </c>
       <c r="C490" t="n">
-        <v>0.681081</v>
+        <v>0.688172</v>
       </c>
     </row>
     <row r="491">
@@ -6797,10 +6797,10 @@
         </is>
       </c>
       <c r="B491" t="n">
-        <v>0.030487</v>
+        <v>0.029113</v>
       </c>
       <c r="C491" t="n">
-        <v>0.678378</v>
+        <v>0.685484</v>
       </c>
     </row>
     <row r="492">
@@ -6810,10 +6810,10 @@
         </is>
       </c>
       <c r="B492" t="n">
-        <v>0.031044</v>
+        <v>0.029344</v>
       </c>
       <c r="C492" t="n">
-        <v>0.6756760000000001</v>
+        <v>0.682796</v>
       </c>
     </row>
     <row r="493">
@@ -6823,10 +6823,10 @@
         </is>
       </c>
       <c r="B493" t="n">
-        <v>0.031138</v>
+        <v>0.029523</v>
       </c>
       <c r="C493" t="n">
-        <v>0.672973</v>
+        <v>0.680108</v>
       </c>
     </row>
     <row r="494">
@@ -6836,10 +6836,10 @@
         </is>
       </c>
       <c r="B494" t="n">
-        <v>0.03149</v>
+        <v>0.030226</v>
       </c>
       <c r="C494" t="n">
-        <v>0.67027</v>
+        <v>0.677419</v>
       </c>
     </row>
     <row r="495">
@@ -6849,10 +6849,10 @@
         </is>
       </c>
       <c r="B495" t="n">
-        <v>0.031591</v>
+        <v>0.030764</v>
       </c>
       <c r="C495" t="n">
-        <v>0.6675680000000001</v>
+        <v>0.674731</v>
       </c>
     </row>
     <row r="496">
@@ -6862,10 +6862,10 @@
         </is>
       </c>
       <c r="B496" t="n">
-        <v>0.032432</v>
+        <v>0.031026</v>
       </c>
       <c r="C496" t="n">
-        <v>0.664865</v>
+        <v>0.6720429999999999</v>
       </c>
     </row>
     <row r="497">
@@ -6875,10 +6875,10 @@
         </is>
       </c>
       <c r="B497" t="n">
-        <v>0.032451</v>
+        <v>0.031377</v>
       </c>
       <c r="C497" t="n">
-        <v>0.662162</v>
+        <v>0.669355</v>
       </c>
     </row>
     <row r="498">
@@ -6888,10 +6888,10 @@
         </is>
       </c>
       <c r="B498" t="n">
-        <v>0.032557</v>
+        <v>0.031405</v>
       </c>
       <c r="C498" t="n">
-        <v>0.659459</v>
+        <v>0.666667</v>
       </c>
     </row>
     <row r="499">
@@ -6901,10 +6901,10 @@
         </is>
       </c>
       <c r="B499" t="n">
-        <v>0.032591</v>
+        <v>0.032166</v>
       </c>
       <c r="C499" t="n">
-        <v>0.656757</v>
+        <v>0.663978</v>
       </c>
     </row>
     <row r="500">
@@ -6914,10 +6914,10 @@
         </is>
       </c>
       <c r="B500" t="n">
-        <v>0.033383</v>
+        <v>0.032324</v>
       </c>
       <c r="C500" t="n">
-        <v>0.654054</v>
+        <v>0.66129</v>
       </c>
     </row>
     <row r="501">
@@ -6927,10 +6927,10 @@
         </is>
       </c>
       <c r="B501" t="n">
-        <v>0.033515</v>
+        <v>0.032462</v>
       </c>
       <c r="C501" t="n">
-        <v>0.651351</v>
+        <v>0.658602</v>
       </c>
     </row>
     <row r="502">
@@ -6940,10 +6940,10 @@
         </is>
       </c>
       <c r="B502" t="n">
-        <v>0.033602</v>
+        <v>0.0325</v>
       </c>
       <c r="C502" t="n">
-        <v>0.648649</v>
+        <v>0.655914</v>
       </c>
     </row>
     <row r="503">
@@ -6953,10 +6953,10 @@
         </is>
       </c>
       <c r="B503" t="n">
-        <v>0.033682</v>
+        <v>0.033033</v>
       </c>
       <c r="C503" t="n">
-        <v>0.645946</v>
+        <v>0.653226</v>
       </c>
     </row>
     <row r="504">
@@ -6966,10 +6966,10 @@
         </is>
       </c>
       <c r="B504" t="n">
-        <v>0.03384</v>
+        <v>0.033269</v>
       </c>
       <c r="C504" t="n">
-        <v>0.643243</v>
+        <v>0.6505379999999999</v>
       </c>
     </row>
     <row r="505">
@@ -6979,10 +6979,10 @@
         </is>
       </c>
       <c r="B505" t="n">
-        <v>0.034106</v>
+        <v>0.033374</v>
       </c>
       <c r="C505" t="n">
-        <v>0.640541</v>
+        <v>0.647849</v>
       </c>
     </row>
     <row r="506">
@@ -6992,10 +6992,10 @@
         </is>
       </c>
       <c r="B506" t="n">
-        <v>0.034301</v>
+        <v>0.033578</v>
       </c>
       <c r="C506" t="n">
-        <v>0.637838</v>
+        <v>0.645161</v>
       </c>
     </row>
     <row r="507">
@@ -7005,10 +7005,10 @@
         </is>
       </c>
       <c r="B507" t="n">
-        <v>0.034653</v>
+        <v>0.033622</v>
       </c>
       <c r="C507" t="n">
-        <v>0.635135</v>
+        <v>0.642473</v>
       </c>
     </row>
     <row r="508">
@@ -7018,10 +7018,10 @@
         </is>
       </c>
       <c r="B508" t="n">
-        <v>0.034782</v>
+        <v>0.033839</v>
       </c>
       <c r="C508" t="n">
-        <v>0.632432</v>
+        <v>0.639785</v>
       </c>
     </row>
     <row r="509">
@@ -7031,10 +7031,10 @@
         </is>
       </c>
       <c r="B509" t="n">
-        <v>0.035757</v>
+        <v>0.033871</v>
       </c>
       <c r="C509" t="n">
-        <v>0.62973</v>
+        <v>0.637097</v>
       </c>
     </row>
     <row r="510">
@@ -7044,10 +7044,10 @@
         </is>
       </c>
       <c r="B510" t="n">
-        <v>0.03579</v>
+        <v>0.034273</v>
       </c>
       <c r="C510" t="n">
-        <v>0.627027</v>
+        <v>0.634409</v>
       </c>
     </row>
     <row r="511">
@@ -7057,10 +7057,10 @@
         </is>
       </c>
       <c r="B511" t="n">
-        <v>0.036172</v>
+        <v>0.034391</v>
       </c>
       <c r="C511" t="n">
-        <v>0.624324</v>
+        <v>0.6317199999999999</v>
       </c>
     </row>
     <row r="512">
@@ -7070,10 +7070,10 @@
         </is>
       </c>
       <c r="B512" t="n">
-        <v>0.036539</v>
+        <v>0.03441</v>
       </c>
       <c r="C512" t="n">
-        <v>0.621622</v>
+        <v>0.629032</v>
       </c>
     </row>
     <row r="513">
@@ -7083,10 +7083,10 @@
         </is>
       </c>
       <c r="B513" t="n">
-        <v>0.036668</v>
+        <v>0.035435</v>
       </c>
       <c r="C513" t="n">
-        <v>0.618919</v>
+        <v>0.626344</v>
       </c>
     </row>
     <row r="514">
@@ -7096,10 +7096,10 @@
         </is>
       </c>
       <c r="B514" t="n">
-        <v>0.037921</v>
+        <v>0.035462</v>
       </c>
       <c r="C514" t="n">
-        <v>0.616216</v>
+        <v>0.623656</v>
       </c>
     </row>
     <row r="515">
@@ -7109,10 +7109,10 @@
         </is>
       </c>
       <c r="B515" t="n">
-        <v>0.038158</v>
+        <v>0.035906</v>
       </c>
       <c r="C515" t="n">
-        <v>0.613514</v>
+        <v>0.620968</v>
       </c>
     </row>
     <row r="516">
@@ -7122,10 +7122,10 @@
         </is>
       </c>
       <c r="B516" t="n">
-        <v>0.038324</v>
+        <v>0.036355</v>
       </c>
       <c r="C516" t="n">
-        <v>0.610811</v>
+        <v>0.6182800000000001</v>
       </c>
     </row>
     <row r="517">
@@ -7135,10 +7135,10 @@
         </is>
       </c>
       <c r="B517" t="n">
-        <v>0.038739</v>
+        <v>0.036545</v>
       </c>
       <c r="C517" t="n">
-        <v>0.608108</v>
+        <v>0.615591</v>
       </c>
     </row>
     <row r="518">
@@ -7148,10 +7148,10 @@
         </is>
       </c>
       <c r="B518" t="n">
-        <v>0.038799</v>
+        <v>0.037726</v>
       </c>
       <c r="C518" t="n">
-        <v>0.605405</v>
+        <v>0.612903</v>
       </c>
     </row>
     <row r="519">
@@ -7161,10 +7161,10 @@
         </is>
       </c>
       <c r="B519" t="n">
-        <v>0.039045</v>
+        <v>0.037942</v>
       </c>
       <c r="C519" t="n">
-        <v>0.602703</v>
+        <v>0.610215</v>
       </c>
     </row>
     <row r="520">
@@ -7174,10 +7174,10 @@
         </is>
       </c>
       <c r="B520" t="n">
-        <v>0.039047</v>
+        <v>0.038228</v>
       </c>
       <c r="C520" t="n">
-        <v>0.6</v>
+        <v>0.607527</v>
       </c>
     </row>
     <row r="521">
@@ -7187,10 +7187,10 @@
         </is>
       </c>
       <c r="B521" t="n">
-        <v>0.03907</v>
+        <v>0.038746</v>
       </c>
       <c r="C521" t="n">
-        <v>0.597297</v>
+        <v>0.604839</v>
       </c>
     </row>
     <row r="522">
@@ -7200,10 +7200,10 @@
         </is>
       </c>
       <c r="B522" t="n">
-        <v>0.039268</v>
+        <v>0.038784</v>
       </c>
       <c r="C522" t="n">
-        <v>0.594595</v>
+        <v>0.602151</v>
       </c>
     </row>
     <row r="523">
@@ -7213,10 +7213,10 @@
         </is>
       </c>
       <c r="B523" t="n">
-        <v>0.03974</v>
+        <v>0.038921</v>
       </c>
       <c r="C523" t="n">
-        <v>0.591892</v>
+        <v>0.5994620000000001</v>
       </c>
     </row>
     <row r="524">
@@ -7226,10 +7226,10 @@
         </is>
       </c>
       <c r="B524" t="n">
-        <v>0.039927</v>
+        <v>0.039017</v>
       </c>
       <c r="C524" t="n">
-        <v>0.589189</v>
+        <v>0.596774</v>
       </c>
     </row>
     <row r="525">
@@ -7239,10 +7239,10 @@
         </is>
       </c>
       <c r="B525" t="n">
-        <v>0.040038</v>
+        <v>0.039186</v>
       </c>
       <c r="C525" t="n">
-        <v>0.586486</v>
+        <v>0.594086</v>
       </c>
     </row>
     <row r="526">
@@ -7252,10 +7252,10 @@
         </is>
       </c>
       <c r="B526" t="n">
-        <v>0.040107</v>
+        <v>0.03923</v>
       </c>
       <c r="C526" t="n">
-        <v>0.583784</v>
+        <v>0.591398</v>
       </c>
     </row>
     <row r="527">
@@ -7265,10 +7265,10 @@
         </is>
       </c>
       <c r="B527" t="n">
-        <v>0.040128</v>
+        <v>0.039391</v>
       </c>
       <c r="C527" t="n">
-        <v>0.581081</v>
+        <v>0.58871</v>
       </c>
     </row>
     <row r="528">
@@ -7278,10 +7278,10 @@
         </is>
       </c>
       <c r="B528" t="n">
-        <v>0.040324</v>
+        <v>0.039653</v>
       </c>
       <c r="C528" t="n">
-        <v>0.5783779999999999</v>
+        <v>0.586022</v>
       </c>
     </row>
     <row r="529">
@@ -7291,10 +7291,10 @@
         </is>
       </c>
       <c r="B529" t="n">
-        <v>0.040792</v>
+        <v>0.039713</v>
       </c>
       <c r="C529" t="n">
-        <v>0.575676</v>
+        <v>0.583333</v>
       </c>
     </row>
     <row r="530">
@@ -7304,10 +7304,10 @@
         </is>
       </c>
       <c r="B530" t="n">
-        <v>0.040793</v>
+        <v>0.039806</v>
       </c>
       <c r="C530" t="n">
-        <v>0.572973</v>
+        <v>0.580645</v>
       </c>
     </row>
     <row r="531">
@@ -7317,10 +7317,10 @@
         </is>
       </c>
       <c r="B531" t="n">
-        <v>0.040882</v>
+        <v>0.039838</v>
       </c>
       <c r="C531" t="n">
-        <v>0.5702700000000001</v>
+        <v>0.5779570000000001</v>
       </c>
     </row>
     <row r="532">
@@ -7330,10 +7330,10 @@
         </is>
       </c>
       <c r="B532" t="n">
-        <v>0.041537</v>
+        <v>0.040034</v>
       </c>
       <c r="C532" t="n">
-        <v>0.567568</v>
+        <v>0.575269</v>
       </c>
     </row>
     <row r="533">
@@ -7343,10 +7343,10 @@
         </is>
       </c>
       <c r="B533" t="n">
-        <v>0.041692</v>
+        <v>0.040426</v>
       </c>
       <c r="C533" t="n">
-        <v>0.564865</v>
+        <v>0.572581</v>
       </c>
     </row>
     <row r="534">
@@ -7356,10 +7356,10 @@
         </is>
       </c>
       <c r="B534" t="n">
-        <v>0.041783</v>
+        <v>0.040511</v>
       </c>
       <c r="C534" t="n">
-        <v>0.5621620000000001</v>
+        <v>0.569892</v>
       </c>
     </row>
     <row r="535">
@@ -7369,10 +7369,10 @@
         </is>
       </c>
       <c r="B535" t="n">
-        <v>0.041967</v>
+        <v>0.040661</v>
       </c>
       <c r="C535" t="n">
-        <v>0.559459</v>
+        <v>0.567204</v>
       </c>
     </row>
     <row r="536">
@@ -7382,10 +7382,10 @@
         </is>
       </c>
       <c r="B536" t="n">
-        <v>0.042369</v>
+        <v>0.041277</v>
       </c>
       <c r="C536" t="n">
-        <v>0.5567569999999999</v>
+        <v>0.564516</v>
       </c>
     </row>
     <row r="537">
@@ -7395,10 +7395,10 @@
         </is>
       </c>
       <c r="B537" t="n">
-        <v>0.042682</v>
+        <v>0.041278</v>
       </c>
       <c r="C537" t="n">
-        <v>0.554054</v>
+        <v>0.561828</v>
       </c>
     </row>
     <row r="538">
@@ -7408,10 +7408,10 @@
         </is>
       </c>
       <c r="B538" t="n">
-        <v>0.043326</v>
+        <v>0.041563</v>
       </c>
       <c r="C538" t="n">
-        <v>0.551351</v>
+        <v>0.55914</v>
       </c>
     </row>
     <row r="539">
@@ -7421,10 +7421,10 @@
         </is>
       </c>
       <c r="B539" t="n">
-        <v>0.043581</v>
+        <v>0.041683</v>
       </c>
       <c r="C539" t="n">
-        <v>0.5486490000000001</v>
+        <v>0.5564519999999999</v>
       </c>
     </row>
     <row r="540">
@@ -7434,10 +7434,10 @@
         </is>
       </c>
       <c r="B540" t="n">
-        <v>0.043662</v>
+        <v>0.042112</v>
       </c>
       <c r="C540" t="n">
-        <v>0.545946</v>
+        <v>0.553763</v>
       </c>
     </row>
     <row r="541">
@@ -7447,10 +7447,10 @@
         </is>
       </c>
       <c r="B541" t="n">
-        <v>0.044227</v>
+        <v>0.042278</v>
       </c>
       <c r="C541" t="n">
-        <v>0.543243</v>
+        <v>0.551075</v>
       </c>
     </row>
     <row r="542">
@@ -7460,10 +7460,10 @@
         </is>
       </c>
       <c r="B542" t="n">
-        <v>0.045407</v>
+        <v>0.043166</v>
       </c>
       <c r="C542" t="n">
-        <v>0.540541</v>
+        <v>0.548387</v>
       </c>
     </row>
     <row r="543">
@@ -7473,10 +7473,10 @@
         </is>
       </c>
       <c r="B543" t="n">
-        <v>0.046258</v>
+        <v>0.043336</v>
       </c>
       <c r="C543" t="n">
-        <v>0.537838</v>
+        <v>0.545699</v>
       </c>
     </row>
     <row r="544">
@@ -7486,10 +7486,10 @@
         </is>
       </c>
       <c r="B544" t="n">
-        <v>0.046289</v>
+        <v>0.043456</v>
       </c>
       <c r="C544" t="n">
-        <v>0.535135</v>
+        <v>0.543011</v>
       </c>
     </row>
     <row r="545">
@@ -7499,10 +7499,10 @@
         </is>
       </c>
       <c r="B545" t="n">
-        <v>0.04648</v>
+        <v>0.04379</v>
       </c>
       <c r="C545" t="n">
-        <v>0.532432</v>
+        <v>0.540323</v>
       </c>
     </row>
     <row r="546">
@@ -7512,10 +7512,10 @@
         </is>
       </c>
       <c r="B546" t="n">
-        <v>0.046777</v>
+        <v>0.045214</v>
       </c>
       <c r="C546" t="n">
-        <v>0.52973</v>
+        <v>0.5376339999999999</v>
       </c>
     </row>
     <row r="547">
@@ -7525,10 +7525,10 @@
         </is>
       </c>
       <c r="B547" t="n">
-        <v>0.04684</v>
+        <v>0.045707</v>
       </c>
       <c r="C547" t="n">
-        <v>0.527027</v>
+        <v>0.534946</v>
       </c>
     </row>
     <row r="548">
@@ -7538,10 +7538,10 @@
         </is>
       </c>
       <c r="B548" t="n">
-        <v>0.047842</v>
+        <v>0.046088</v>
       </c>
       <c r="C548" t="n">
-        <v>0.524324</v>
+        <v>0.532258</v>
       </c>
     </row>
     <row r="549">
@@ -7551,10 +7551,10 @@
         </is>
       </c>
       <c r="B549" t="n">
-        <v>0.048353</v>
+        <v>0.046113</v>
       </c>
       <c r="C549" t="n">
-        <v>0.521622</v>
+        <v>0.52957</v>
       </c>
     </row>
     <row r="550">
@@ -7564,10 +7564,10 @@
         </is>
       </c>
       <c r="B550" t="n">
-        <v>0.049409</v>
+        <v>0.046333</v>
       </c>
       <c r="C550" t="n">
-        <v>0.518919</v>
+        <v>0.526882</v>
       </c>
     </row>
     <row r="551">
@@ -7577,10 +7577,10 @@
         </is>
       </c>
       <c r="B551" t="n">
-        <v>0.049529</v>
+        <v>0.046711</v>
       </c>
       <c r="C551" t="n">
-        <v>0.516216</v>
+        <v>0.524194</v>
       </c>
     </row>
     <row r="552">
@@ -7590,10 +7590,10 @@
         </is>
       </c>
       <c r="B552" t="n">
-        <v>0.050997</v>
+        <v>0.047726</v>
       </c>
       <c r="C552" t="n">
-        <v>0.513514</v>
+        <v>0.521505</v>
       </c>
     </row>
     <row r="553">
@@ -7603,10 +7603,10 @@
         </is>
       </c>
       <c r="B553" t="n">
-        <v>0.051041</v>
+        <v>0.048001</v>
       </c>
       <c r="C553" t="n">
-        <v>0.510811</v>
+        <v>0.518817</v>
       </c>
     </row>
     <row r="554">
@@ -7616,10 +7616,10 @@
         </is>
       </c>
       <c r="B554" t="n">
-        <v>0.051193</v>
+        <v>0.04889</v>
       </c>
       <c r="C554" t="n">
-        <v>0.508108</v>
+        <v>0.5161289999999999</v>
       </c>
     </row>
     <row r="555">
@@ -7629,10 +7629,10 @@
         </is>
       </c>
       <c r="B555" t="n">
-        <v>0.051741</v>
+        <v>0.049282</v>
       </c>
       <c r="C555" t="n">
-        <v>0.505405</v>
+        <v>0.513441</v>
       </c>
     </row>
     <row r="556">
@@ -7642,10 +7642,10 @@
         </is>
       </c>
       <c r="B556" t="n">
-        <v>0.052054</v>
+        <v>0.050628</v>
       </c>
       <c r="C556" t="n">
-        <v>0.502703</v>
+        <v>0.510753</v>
       </c>
     </row>
     <row r="557">
@@ -7655,10 +7655,10 @@
         </is>
       </c>
       <c r="B557" t="n">
-        <v>0.052254</v>
+        <v>0.050703</v>
       </c>
       <c r="C557" t="n">
-        <v>0.5</v>
+        <v>0.508065</v>
       </c>
     </row>
     <row r="558">
@@ -7668,10 +7668,10 @@
         </is>
       </c>
       <c r="B558" t="n">
-        <v>0.052522</v>
+        <v>0.050846</v>
       </c>
       <c r="C558" t="n">
-        <v>0.497297</v>
+        <v>0.505376</v>
       </c>
     </row>
     <row r="559">
@@ -7681,10 +7681,10 @@
         </is>
       </c>
       <c r="B559" t="n">
-        <v>0.052837</v>
+        <v>0.050946</v>
       </c>
       <c r="C559" t="n">
-        <v>0.494595</v>
+        <v>0.502688</v>
       </c>
     </row>
     <row r="560">
@@ -7694,10 +7694,10 @@
         </is>
       </c>
       <c r="B560" t="n">
-        <v>0.053391</v>
+        <v>0.051117</v>
       </c>
       <c r="C560" t="n">
-        <v>0.491892</v>
+        <v>0.5</v>
       </c>
     </row>
     <row r="561">
@@ -7707,10 +7707,10 @@
         </is>
       </c>
       <c r="B561" t="n">
-        <v>0.053487</v>
+        <v>0.051538</v>
       </c>
       <c r="C561" t="n">
-        <v>0.489189</v>
+        <v>0.497312</v>
       </c>
     </row>
     <row r="562">
@@ -7720,10 +7720,10 @@
         </is>
       </c>
       <c r="B562" t="n">
-        <v>0.053808</v>
+        <v>0.052018</v>
       </c>
       <c r="C562" t="n">
-        <v>0.486486</v>
+        <v>0.494624</v>
       </c>
     </row>
     <row r="563">
@@ -7733,10 +7733,10 @@
         </is>
       </c>
       <c r="B563" t="n">
-        <v>0.053967</v>
+        <v>0.052564</v>
       </c>
       <c r="C563" t="n">
-        <v>0.483784</v>
+        <v>0.491935</v>
       </c>
     </row>
     <row r="564">
@@ -7746,10 +7746,10 @@
         </is>
       </c>
       <c r="B564" t="n">
-        <v>0.054072</v>
+        <v>0.053229</v>
       </c>
       <c r="C564" t="n">
-        <v>0.481081</v>
+        <v>0.489247</v>
       </c>
     </row>
     <row r="565">
@@ -7759,10 +7759,10 @@
         </is>
       </c>
       <c r="B565" t="n">
-        <v>0.054353</v>
+        <v>0.05329</v>
       </c>
       <c r="C565" t="n">
-        <v>0.478378</v>
+        <v>0.486559</v>
       </c>
     </row>
     <row r="566">
@@ -7772,10 +7772,10 @@
         </is>
       </c>
       <c r="B566" t="n">
-        <v>0.054543</v>
+        <v>0.053407</v>
       </c>
       <c r="C566" t="n">
-        <v>0.475676</v>
+        <v>0.483871</v>
       </c>
     </row>
     <row r="567">
@@ -7785,10 +7785,10 @@
         </is>
       </c>
       <c r="B567" t="n">
-        <v>0.055066</v>
+        <v>0.053529</v>
       </c>
       <c r="C567" t="n">
-        <v>0.472973</v>
+        <v>0.481183</v>
       </c>
     </row>
     <row r="568">
@@ -7798,10 +7798,10 @@
         </is>
       </c>
       <c r="B568" t="n">
-        <v>0.055666</v>
+        <v>0.053665</v>
       </c>
       <c r="C568" t="n">
-        <v>0.47027</v>
+        <v>0.478495</v>
       </c>
     </row>
     <row r="569">
@@ -7811,10 +7811,10 @@
         </is>
       </c>
       <c r="B569" t="n">
-        <v>0.056194</v>
+        <v>0.054147</v>
       </c>
       <c r="C569" t="n">
-        <v>0.467568</v>
+        <v>0.475806</v>
       </c>
     </row>
     <row r="570">
@@ -7824,10 +7824,10 @@
         </is>
       </c>
       <c r="B570" t="n">
-        <v>0.056871</v>
+        <v>0.054165</v>
       </c>
       <c r="C570" t="n">
-        <v>0.464865</v>
+        <v>0.473118</v>
       </c>
     </row>
     <row r="571">
@@ -7837,10 +7837,10 @@
         </is>
       </c>
       <c r="B571" t="n">
-        <v>0.057</v>
+        <v>0.054577</v>
       </c>
       <c r="C571" t="n">
-        <v>0.462162</v>
+        <v>0.47043</v>
       </c>
     </row>
     <row r="572">
@@ -7850,10 +7850,10 @@
         </is>
       </c>
       <c r="B572" t="n">
-        <v>0.057674</v>
+        <v>0.055014</v>
       </c>
       <c r="C572" t="n">
-        <v>0.459459</v>
+        <v>0.467742</v>
       </c>
     </row>
     <row r="573">
@@ -7863,10 +7863,10 @@
         </is>
       </c>
       <c r="B573" t="n">
-        <v>0.058013</v>
+        <v>0.055491</v>
       </c>
       <c r="C573" t="n">
-        <v>0.456757</v>
+        <v>0.465054</v>
       </c>
     </row>
     <row r="574">
@@ -7876,10 +7876,10 @@
         </is>
       </c>
       <c r="B574" t="n">
-        <v>0.05864</v>
+        <v>0.0559</v>
       </c>
       <c r="C574" t="n">
-        <v>0.454054</v>
+        <v>0.462366</v>
       </c>
     </row>
     <row r="575">
@@ -7889,10 +7889,10 @@
         </is>
       </c>
       <c r="B575" t="n">
-        <v>0.05896</v>
+        <v>0.056646</v>
       </c>
       <c r="C575" t="n">
-        <v>0.451351</v>
+        <v>0.459677</v>
       </c>
     </row>
     <row r="576">
@@ -7902,10 +7902,10 @@
         </is>
       </c>
       <c r="B576" t="n">
-        <v>0.061592</v>
+        <v>0.056855</v>
       </c>
       <c r="C576" t="n">
-        <v>0.448649</v>
+        <v>0.456989</v>
       </c>
     </row>
     <row r="577">
@@ -7915,10 +7915,10 @@
         </is>
       </c>
       <c r="B577" t="n">
-        <v>0.062542</v>
+        <v>0.057529</v>
       </c>
       <c r="C577" t="n">
-        <v>0.445946</v>
+        <v>0.454301</v>
       </c>
     </row>
     <row r="578">
@@ -7928,10 +7928,10 @@
         </is>
       </c>
       <c r="B578" t="n">
-        <v>0.06307</v>
+        <v>0.058143</v>
       </c>
       <c r="C578" t="n">
-        <v>0.443243</v>
+        <v>0.451613</v>
       </c>
     </row>
     <row r="579">
@@ -7941,10 +7941,10 @@
         </is>
       </c>
       <c r="B579" t="n">
-        <v>0.06383999999999999</v>
+        <v>0.058284</v>
       </c>
       <c r="C579" t="n">
-        <v>0.440541</v>
+        <v>0.448925</v>
       </c>
     </row>
     <row r="580">
@@ -7954,10 +7954,10 @@
         </is>
       </c>
       <c r="B580" t="n">
-        <v>0.063851</v>
+        <v>0.061075</v>
       </c>
       <c r="C580" t="n">
-        <v>0.437838</v>
+        <v>0.446237</v>
       </c>
     </row>
     <row r="581">
@@ -7967,10 +7967,10 @@
         </is>
       </c>
       <c r="B581" t="n">
-        <v>0.06392399999999999</v>
+        <v>0.062133</v>
       </c>
       <c r="C581" t="n">
-        <v>0.435135</v>
+        <v>0.443548</v>
       </c>
     </row>
     <row r="582">
@@ -7980,10 +7980,10 @@
         </is>
       </c>
       <c r="B582" t="n">
-        <v>0.06408700000000001</v>
+        <v>0.062734</v>
       </c>
       <c r="C582" t="n">
-        <v>0.432432</v>
+        <v>0.44086</v>
       </c>
     </row>
     <row r="583">
@@ -7993,10 +7993,10 @@
         </is>
       </c>
       <c r="B583" t="n">
-        <v>0.064246</v>
+        <v>0.06347899999999999</v>
       </c>
       <c r="C583" t="n">
-        <v>0.42973</v>
+        <v>0.438172</v>
       </c>
     </row>
     <row r="584">
@@ -8006,10 +8006,10 @@
         </is>
       </c>
       <c r="B584" t="n">
-        <v>0.06425599999999999</v>
+        <v>0.06355</v>
       </c>
       <c r="C584" t="n">
-        <v>0.427027</v>
+        <v>0.435484</v>
       </c>
     </row>
     <row r="585">
@@ -8019,10 +8019,10 @@
         </is>
       </c>
       <c r="B585" t="n">
-        <v>0.06439400000000001</v>
+        <v>0.06367200000000001</v>
       </c>
       <c r="C585" t="n">
-        <v>0.424324</v>
+        <v>0.432796</v>
       </c>
     </row>
     <row r="586">
@@ -8032,10 +8032,10 @@
         </is>
       </c>
       <c r="B586" t="n">
-        <v>0.065664</v>
+        <v>0.063774</v>
       </c>
       <c r="C586" t="n">
-        <v>0.421622</v>
+        <v>0.430108</v>
       </c>
     </row>
     <row r="587">
@@ -8045,10 +8045,10 @@
         </is>
       </c>
       <c r="B587" t="n">
-        <v>0.065793</v>
+        <v>0.06392100000000001</v>
       </c>
       <c r="C587" t="n">
-        <v>0.418919</v>
+        <v>0.427419</v>
       </c>
     </row>
     <row r="588">
@@ -8058,10 +8058,10 @@
         </is>
       </c>
       <c r="B588" t="n">
-        <v>0.065802</v>
+        <v>0.064072</v>
       </c>
       <c r="C588" t="n">
-        <v>0.416216</v>
+        <v>0.424731</v>
       </c>
     </row>
     <row r="589">
@@ -8071,10 +8071,10 @@
         </is>
       </c>
       <c r="B589" t="n">
-        <v>0.068397</v>
+        <v>0.06422700000000001</v>
       </c>
       <c r="C589" t="n">
-        <v>0.413514</v>
+        <v>0.422043</v>
       </c>
     </row>
     <row r="590">
@@ -8084,10 +8084,10 @@
         </is>
       </c>
       <c r="B590" t="n">
-        <v>0.068818</v>
+        <v>0.065222</v>
       </c>
       <c r="C590" t="n">
-        <v>0.410811</v>
+        <v>0.419355</v>
       </c>
     </row>
     <row r="591">
@@ -8097,10 +8097,10 @@
         </is>
       </c>
       <c r="B591" t="n">
-        <v>0.069051</v>
+        <v>0.06547600000000001</v>
       </c>
       <c r="C591" t="n">
-        <v>0.408108</v>
+        <v>0.416667</v>
       </c>
     </row>
     <row r="592">
@@ -8110,10 +8110,10 @@
         </is>
       </c>
       <c r="B592" t="n">
-        <v>0.06927800000000001</v>
+        <v>0.06558700000000001</v>
       </c>
       <c r="C592" t="n">
-        <v>0.405405</v>
+        <v>0.413978</v>
       </c>
     </row>
     <row r="593">
@@ -8123,10 +8123,10 @@
         </is>
       </c>
       <c r="B593" t="n">
-        <v>0.069864</v>
+        <v>0.067699</v>
       </c>
       <c r="C593" t="n">
-        <v>0.402703</v>
+        <v>0.41129</v>
       </c>
     </row>
     <row r="594">
@@ -8136,10 +8136,10 @@
         </is>
       </c>
       <c r="B594" t="n">
-        <v>0.069964</v>
+        <v>0.068151</v>
       </c>
       <c r="C594" t="n">
-        <v>0.4</v>
+        <v>0.408602</v>
       </c>
     </row>
     <row r="595">
@@ -8149,10 +8149,10 @@
         </is>
       </c>
       <c r="B595" t="n">
-        <v>0.070268</v>
+        <v>0.068244</v>
       </c>
       <c r="C595" t="n">
-        <v>0.397297</v>
+        <v>0.405914</v>
       </c>
     </row>
     <row r="596">
@@ -8162,10 +8162,10 @@
         </is>
       </c>
       <c r="B596" t="n">
-        <v>0.07034600000000001</v>
+        <v>0.068412</v>
       </c>
       <c r="C596" t="n">
-        <v>0.394595</v>
+        <v>0.403226</v>
       </c>
     </row>
     <row r="597">
@@ -8175,10 +8175,10 @@
         </is>
       </c>
       <c r="B597" t="n">
-        <v>0.07044499999999999</v>
+        <v>0.06931</v>
       </c>
       <c r="C597" t="n">
-        <v>0.391892</v>
+        <v>0.400538</v>
       </c>
     </row>
     <row r="598">
@@ -8188,10 +8188,10 @@
         </is>
       </c>
       <c r="B598" t="n">
-        <v>0.070614</v>
+        <v>0.069476</v>
       </c>
       <c r="C598" t="n">
-        <v>0.389189</v>
+        <v>0.397849</v>
       </c>
     </row>
     <row r="599">
@@ -8201,10 +8201,10 @@
         </is>
       </c>
       <c r="B599" t="n">
-        <v>0.07065100000000001</v>
+        <v>0.069582</v>
       </c>
       <c r="C599" t="n">
-        <v>0.386486</v>
+        <v>0.395161</v>
       </c>
     </row>
     <row r="600">
@@ -8214,10 +8214,10 @@
         </is>
       </c>
       <c r="B600" t="n">
-        <v>0.07090399999999999</v>
+        <v>0.069697</v>
       </c>
       <c r="C600" t="n">
-        <v>0.383784</v>
+        <v>0.392473</v>
       </c>
     </row>
     <row r="601">
@@ -8227,10 +8227,10 @@
         </is>
       </c>
       <c r="B601" t="n">
-        <v>0.07106999999999999</v>
+        <v>0.069782</v>
       </c>
       <c r="C601" t="n">
-        <v>0.381081</v>
+        <v>0.389785</v>
       </c>
     </row>
     <row r="602">
@@ -8240,10 +8240,10 @@
         </is>
       </c>
       <c r="B602" t="n">
-        <v>0.07108200000000001</v>
+        <v>0.070008</v>
       </c>
       <c r="C602" t="n">
-        <v>0.378378</v>
+        <v>0.387097</v>
       </c>
     </row>
     <row r="603">
@@ -8253,10 +8253,10 @@
         </is>
       </c>
       <c r="B603" t="n">
-        <v>0.07174999999999999</v>
+        <v>0.070483</v>
       </c>
       <c r="C603" t="n">
-        <v>0.375676</v>
+        <v>0.384409</v>
       </c>
     </row>
     <row r="604">
@@ -8266,10 +8266,10 @@
         </is>
       </c>
       <c r="B604" t="n">
-        <v>0.072646</v>
+        <v>0.07058200000000001</v>
       </c>
       <c r="C604" t="n">
-        <v>0.372973</v>
+        <v>0.38172</v>
       </c>
     </row>
     <row r="605">
@@ -8279,10 +8279,10 @@
         </is>
       </c>
       <c r="B605" t="n">
-        <v>0.07283000000000001</v>
+        <v>0.070634</v>
       </c>
       <c r="C605" t="n">
-        <v>0.37027</v>
+        <v>0.379032</v>
       </c>
     </row>
     <row r="606">
@@ -8292,10 +8292,10 @@
         </is>
       </c>
       <c r="B606" t="n">
-        <v>0.072964</v>
+        <v>0.070712</v>
       </c>
       <c r="C606" t="n">
-        <v>0.367568</v>
+        <v>0.376344</v>
       </c>
     </row>
     <row r="607">
@@ -8305,10 +8305,10 @@
         </is>
       </c>
       <c r="B607" t="n">
-        <v>0.073199</v>
+        <v>0.07160900000000001</v>
       </c>
       <c r="C607" t="n">
-        <v>0.364865</v>
+        <v>0.373656</v>
       </c>
     </row>
     <row r="608">
@@ -8318,10 +8318,10 @@
         </is>
       </c>
       <c r="B608" t="n">
-        <v>0.07399799999999999</v>
+        <v>0.07201200000000001</v>
       </c>
       <c r="C608" t="n">
-        <v>0.362162</v>
+        <v>0.370968</v>
       </c>
     </row>
     <row r="609">
@@ -8331,10 +8331,10 @@
         </is>
       </c>
       <c r="B609" t="n">
-        <v>0.074156</v>
+        <v>0.072146</v>
       </c>
       <c r="C609" t="n">
-        <v>0.359459</v>
+        <v>0.36828</v>
       </c>
     </row>
     <row r="610">
@@ -8344,10 +8344,10 @@
         </is>
       </c>
       <c r="B610" t="n">
-        <v>0.07428</v>
+        <v>0.07244399999999999</v>
       </c>
       <c r="C610" t="n">
-        <v>0.356757</v>
+        <v>0.365591</v>
       </c>
     </row>
     <row r="611">
@@ -8357,10 +8357,10 @@
         </is>
       </c>
       <c r="B611" t="n">
-        <v>0.075574</v>
+        <v>0.072625</v>
       </c>
       <c r="C611" t="n">
-        <v>0.354054</v>
+        <v>0.362903</v>
       </c>
     </row>
     <row r="612">
@@ -8370,10 +8370,10 @@
         </is>
       </c>
       <c r="B612" t="n">
-        <v>0.076124</v>
+        <v>0.072738</v>
       </c>
       <c r="C612" t="n">
-        <v>0.351351</v>
+        <v>0.360215</v>
       </c>
     </row>
     <row r="613">
@@ -8383,10 +8383,10 @@
         </is>
       </c>
       <c r="B613" t="n">
-        <v>0.07616299999999999</v>
+        <v>0.073739</v>
       </c>
       <c r="C613" t="n">
-        <v>0.348649</v>
+        <v>0.357527</v>
       </c>
     </row>
     <row r="614">
@@ -8396,10 +8396,10 @@
         </is>
       </c>
       <c r="B614" t="n">
-        <v>0.076281</v>
+        <v>0.073985</v>
       </c>
       <c r="C614" t="n">
-        <v>0.345946</v>
+        <v>0.354839</v>
       </c>
     </row>
     <row r="615">
@@ -8409,10 +8409,10 @@
         </is>
       </c>
       <c r="B615" t="n">
-        <v>0.07639700000000001</v>
+        <v>0.074637</v>
       </c>
       <c r="C615" t="n">
-        <v>0.343243</v>
+        <v>0.352151</v>
       </c>
     </row>
     <row r="616">
@@ -8422,10 +8422,10 @@
         </is>
       </c>
       <c r="B616" t="n">
-        <v>0.076692</v>
+        <v>0.075277</v>
       </c>
       <c r="C616" t="n">
-        <v>0.340541</v>
+        <v>0.349462</v>
       </c>
     </row>
     <row r="617">
@@ -8435,10 +8435,10 @@
         </is>
       </c>
       <c r="B617" t="n">
-        <v>0.077088</v>
+        <v>0.075353</v>
       </c>
       <c r="C617" t="n">
-        <v>0.337838</v>
+        <v>0.346774</v>
       </c>
     </row>
     <row r="618">
@@ -8448,10 +8448,10 @@
         </is>
       </c>
       <c r="B618" t="n">
-        <v>0.077545</v>
+        <v>0.075672</v>
       </c>
       <c r="C618" t="n">
-        <v>0.335135</v>
+        <v>0.344086</v>
       </c>
     </row>
     <row r="619">
@@ -8461,10 +8461,10 @@
         </is>
       </c>
       <c r="B619" t="n">
-        <v>0.078858</v>
+        <v>0.075724</v>
       </c>
       <c r="C619" t="n">
-        <v>0.332432</v>
+        <v>0.341398</v>
       </c>
     </row>
     <row r="620">
@@ -8474,10 +8474,10 @@
         </is>
       </c>
       <c r="B620" t="n">
-        <v>0.079938</v>
+        <v>0.07589</v>
       </c>
       <c r="C620" t="n">
-        <v>0.32973</v>
+        <v>0.33871</v>
       </c>
     </row>
     <row r="621">
@@ -8487,10 +8487,10 @@
         </is>
       </c>
       <c r="B621" t="n">
-        <v>0.080086</v>
+        <v>0.076736</v>
       </c>
       <c r="C621" t="n">
-        <v>0.327027</v>
+        <v>0.336022</v>
       </c>
     </row>
     <row r="622">
@@ -8500,10 +8500,10 @@
         </is>
       </c>
       <c r="B622" t="n">
-        <v>0.08101</v>
+        <v>0.07705099999999999</v>
       </c>
       <c r="C622" t="n">
-        <v>0.324324</v>
+        <v>0.333333</v>
       </c>
     </row>
     <row r="623">
@@ -8513,10 +8513,10 @@
         </is>
       </c>
       <c r="B623" t="n">
-        <v>0.08201799999999999</v>
+        <v>0.07832500000000001</v>
       </c>
       <c r="C623" t="n">
-        <v>0.321622</v>
+        <v>0.330645</v>
       </c>
     </row>
     <row r="624">
@@ -8526,10 +8526,10 @@
         </is>
       </c>
       <c r="B624" t="n">
-        <v>0.082096</v>
+        <v>0.07935</v>
       </c>
       <c r="C624" t="n">
-        <v>0.318919</v>
+        <v>0.327957</v>
       </c>
     </row>
     <row r="625">
@@ -8539,10 +8539,10 @@
         </is>
       </c>
       <c r="B625" t="n">
-        <v>0.084746</v>
+        <v>0.07962</v>
       </c>
       <c r="C625" t="n">
-        <v>0.316216</v>
+        <v>0.325269</v>
       </c>
     </row>
     <row r="626">
@@ -8552,10 +8552,10 @@
         </is>
       </c>
       <c r="B626" t="n">
-        <v>0.08537699999999999</v>
+        <v>0.080682</v>
       </c>
       <c r="C626" t="n">
-        <v>0.313514</v>
+        <v>0.322581</v>
       </c>
     </row>
     <row r="627">
@@ -8565,10 +8565,10 @@
         </is>
       </c>
       <c r="B627" t="n">
-        <v>0.085808</v>
+        <v>0.081625</v>
       </c>
       <c r="C627" t="n">
-        <v>0.310811</v>
+        <v>0.319892</v>
       </c>
     </row>
     <row r="628">
@@ -8578,10 +8578,10 @@
         </is>
       </c>
       <c r="B628" t="n">
-        <v>0.08623699999999999</v>
+        <v>0.081983</v>
       </c>
       <c r="C628" t="n">
-        <v>0.308108</v>
+        <v>0.317204</v>
       </c>
     </row>
     <row r="629">
@@ -8591,10 +8591,10 @@
         </is>
       </c>
       <c r="B629" t="n">
-        <v>0.08638999999999999</v>
+        <v>0.084212</v>
       </c>
       <c r="C629" t="n">
-        <v>0.305405</v>
+        <v>0.314516</v>
       </c>
     </row>
     <row r="630">
@@ -8604,10 +8604,10 @@
         </is>
       </c>
       <c r="B630" t="n">
-        <v>0.086768</v>
+        <v>0.084313</v>
       </c>
       <c r="C630" t="n">
-        <v>0.302703</v>
+        <v>0.311828</v>
       </c>
     </row>
     <row r="631">
@@ -8617,10 +8617,10 @@
         </is>
       </c>
       <c r="B631" t="n">
-        <v>0.086897</v>
+        <v>0.084507</v>
       </c>
       <c r="C631" t="n">
-        <v>0.3</v>
+        <v>0.30914</v>
       </c>
     </row>
     <row r="632">
@@ -8630,10 +8630,10 @@
         </is>
       </c>
       <c r="B632" t="n">
-        <v>0.08715199999999999</v>
+        <v>0.085103</v>
       </c>
       <c r="C632" t="n">
-        <v>0.297297</v>
+        <v>0.306452</v>
       </c>
     </row>
     <row r="633">
@@ -8643,10 +8643,10 @@
         </is>
       </c>
       <c r="B633" t="n">
-        <v>0.087336</v>
+        <v>0.085295</v>
       </c>
       <c r="C633" t="n">
-        <v>0.294595</v>
+        <v>0.303763</v>
       </c>
     </row>
     <row r="634">
@@ -8656,10 +8656,10 @@
         </is>
       </c>
       <c r="B634" t="n">
-        <v>0.087806</v>
+        <v>0.085727</v>
       </c>
       <c r="C634" t="n">
-        <v>0.291892</v>
+        <v>0.301075</v>
       </c>
     </row>
     <row r="635">
@@ -8669,10 +8669,10 @@
         </is>
       </c>
       <c r="B635" t="n">
-        <v>0.088796</v>
+        <v>0.085993</v>
       </c>
       <c r="C635" t="n">
-        <v>0.289189</v>
+        <v>0.298387</v>
       </c>
     </row>
     <row r="636">
@@ -8682,10 +8682,10 @@
         </is>
       </c>
       <c r="B636" t="n">
-        <v>0.089006</v>
+        <v>0.08623400000000001</v>
       </c>
       <c r="C636" t="n">
-        <v>0.286486</v>
+        <v>0.295699</v>
       </c>
     </row>
     <row r="637">
@@ -8695,10 +8695,10 @@
         </is>
       </c>
       <c r="B637" t="n">
-        <v>0.089782</v>
+        <v>0.08643000000000001</v>
       </c>
       <c r="C637" t="n">
-        <v>0.283784</v>
+        <v>0.293011</v>
       </c>
     </row>
     <row r="638">
@@ -8708,10 +8708,10 @@
         </is>
       </c>
       <c r="B638" t="n">
-        <v>0.089918</v>
+        <v>0.08701</v>
       </c>
       <c r="C638" t="n">
-        <v>0.281081</v>
+        <v>0.290323</v>
       </c>
     </row>
     <row r="639">
@@ -8721,10 +8721,10 @@
         </is>
       </c>
       <c r="B639" t="n">
-        <v>0.090364</v>
+        <v>0.087683</v>
       </c>
       <c r="C639" t="n">
-        <v>0.278378</v>
+        <v>0.287634</v>
       </c>
     </row>
     <row r="640">
@@ -8734,10 +8734,10 @@
         </is>
       </c>
       <c r="B640" t="n">
-        <v>0.090603</v>
+        <v>0.087899</v>
       </c>
       <c r="C640" t="n">
-        <v>0.275676</v>
+        <v>0.284946</v>
       </c>
     </row>
     <row r="641">
@@ -8747,10 +8747,10 @@
         </is>
       </c>
       <c r="B641" t="n">
-        <v>0.09068</v>
+        <v>0.08860800000000001</v>
       </c>
       <c r="C641" t="n">
-        <v>0.272973</v>
+        <v>0.282258</v>
       </c>
     </row>
     <row r="642">
@@ -8760,10 +8760,10 @@
         </is>
       </c>
       <c r="B642" t="n">
-        <v>0.091708</v>
+        <v>0.08905200000000001</v>
       </c>
       <c r="C642" t="n">
-        <v>0.27027</v>
+        <v>0.27957</v>
       </c>
     </row>
     <row r="643">
@@ -8773,10 +8773,10 @@
         </is>
       </c>
       <c r="B643" t="n">
-        <v>0.091894</v>
+        <v>0.08945699999999999</v>
       </c>
       <c r="C643" t="n">
-        <v>0.267568</v>
+        <v>0.276882</v>
       </c>
     </row>
     <row r="644">
@@ -8786,10 +8786,10 @@
         </is>
       </c>
       <c r="B644" t="n">
-        <v>0.09207899999999999</v>
+        <v>0.089564</v>
       </c>
       <c r="C644" t="n">
-        <v>0.264865</v>
+        <v>0.274194</v>
       </c>
     </row>
     <row r="645">
@@ -8799,10 +8799,10 @@
         </is>
       </c>
       <c r="B645" t="n">
-        <v>0.093416</v>
+        <v>0.08956500000000001</v>
       </c>
       <c r="C645" t="n">
-        <v>0.262162</v>
+        <v>0.271505</v>
       </c>
     </row>
     <row r="646">
@@ -8812,10 +8812,10 @@
         </is>
       </c>
       <c r="B646" t="n">
-        <v>0.09378300000000001</v>
+        <v>0.089714</v>
       </c>
       <c r="C646" t="n">
-        <v>0.259459</v>
+        <v>0.268817</v>
       </c>
     </row>
     <row r="647">
@@ -8825,10 +8825,10 @@
         </is>
       </c>
       <c r="B647" t="n">
-        <v>0.09429999999999999</v>
+        <v>0.091044</v>
       </c>
       <c r="C647" t="n">
-        <v>0.256757</v>
+        <v>0.266129</v>
       </c>
     </row>
     <row r="648">
@@ -8838,10 +8838,10 @@
         </is>
       </c>
       <c r="B648" t="n">
-        <v>0.095598</v>
+        <v>0.091164</v>
       </c>
       <c r="C648" t="n">
-        <v>0.254054</v>
+        <v>0.263441</v>
       </c>
     </row>
     <row r="649">
@@ -8851,10 +8851,10 @@
         </is>
       </c>
       <c r="B649" t="n">
-        <v>0.097881</v>
+        <v>0.091839</v>
       </c>
       <c r="C649" t="n">
-        <v>0.251351</v>
+        <v>0.260753</v>
       </c>
     </row>
     <row r="650">
@@ -8864,10 +8864,10 @@
         </is>
       </c>
       <c r="B650" t="n">
-        <v>0.09815</v>
+        <v>0.09277100000000001</v>
       </c>
       <c r="C650" t="n">
-        <v>0.248649</v>
+        <v>0.258065</v>
       </c>
     </row>
     <row r="651">
@@ -8877,10 +8877,10 @@
         </is>
       </c>
       <c r="B651" t="n">
-        <v>0.09823800000000001</v>
+        <v>0.09286</v>
       </c>
       <c r="C651" t="n">
-        <v>0.245946</v>
+        <v>0.255376</v>
       </c>
     </row>
     <row r="652">
@@ -8890,10 +8890,10 @@
         </is>
       </c>
       <c r="B652" t="n">
-        <v>0.098588</v>
+        <v>0.094002</v>
       </c>
       <c r="C652" t="n">
-        <v>0.243243</v>
+        <v>0.252688</v>
       </c>
     </row>
     <row r="653">
@@ -8903,10 +8903,10 @@
         </is>
       </c>
       <c r="B653" t="n">
-        <v>0.09997</v>
+        <v>0.09490700000000001</v>
       </c>
       <c r="C653" t="n">
-        <v>0.240541</v>
+        <v>0.25</v>
       </c>
     </row>
     <row r="654">
@@ -8916,10 +8916,10 @@
         </is>
       </c>
       <c r="B654" t="n">
-        <v>0.10082</v>
+        <v>0.09661</v>
       </c>
       <c r="C654" t="n">
-        <v>0.237838</v>
+        <v>0.247312</v>
       </c>
     </row>
     <row r="655">
@@ -8929,10 +8929,10 @@
         </is>
       </c>
       <c r="B655" t="n">
-        <v>0.101369</v>
+        <v>0.097039</v>
       </c>
       <c r="C655" t="n">
-        <v>0.235135</v>
+        <v>0.244624</v>
       </c>
     </row>
     <row r="656">
@@ -8942,10 +8942,10 @@
         </is>
       </c>
       <c r="B656" t="n">
-        <v>0.101626</v>
+        <v>0.097856</v>
       </c>
       <c r="C656" t="n">
-        <v>0.232432</v>
+        <v>0.241935</v>
       </c>
     </row>
     <row r="657">
@@ -8955,10 +8955,10 @@
         </is>
       </c>
       <c r="B657" t="n">
-        <v>0.102339</v>
+        <v>0.09825</v>
       </c>
       <c r="C657" t="n">
-        <v>0.22973</v>
+        <v>0.239247</v>
       </c>
     </row>
     <row r="658">
@@ -8968,10 +8968,10 @@
         </is>
       </c>
       <c r="B658" t="n">
-        <v>0.102553</v>
+        <v>0.099144</v>
       </c>
       <c r="C658" t="n">
-        <v>0.227027</v>
+        <v>0.236559</v>
       </c>
     </row>
     <row r="659">
@@ -8981,10 +8981,10 @@
         </is>
       </c>
       <c r="B659" t="n">
-        <v>0.102774</v>
+        <v>0.099574</v>
       </c>
       <c r="C659" t="n">
-        <v>0.224324</v>
+        <v>0.233871</v>
       </c>
     </row>
     <row r="660">
@@ -8994,10 +8994,10 @@
         </is>
       </c>
       <c r="B660" t="n">
-        <v>0.104229</v>
+        <v>0.100559</v>
       </c>
       <c r="C660" t="n">
-        <v>0.221622</v>
+        <v>0.231183</v>
       </c>
     </row>
     <row r="661">
@@ -9007,10 +9007,10 @@
         </is>
       </c>
       <c r="B661" t="n">
-        <v>0.104626</v>
+        <v>0.101179</v>
       </c>
       <c r="C661" t="n">
-        <v>0.218919</v>
+        <v>0.228495</v>
       </c>
     </row>
     <row r="662">
@@ -9020,10 +9020,10 @@
         </is>
       </c>
       <c r="B662" t="n">
-        <v>0.105303</v>
+        <v>0.101564</v>
       </c>
       <c r="C662" t="n">
-        <v>0.216216</v>
+        <v>0.225806</v>
       </c>
     </row>
     <row r="663">
@@ -9033,10 +9033,10 @@
         </is>
       </c>
       <c r="B663" t="n">
-        <v>0.105538</v>
+        <v>0.101911</v>
       </c>
       <c r="C663" t="n">
-        <v>0.213514</v>
+        <v>0.223118</v>
       </c>
     </row>
     <row r="664">
@@ -9046,10 +9046,10 @@
         </is>
       </c>
       <c r="B664" t="n">
-        <v>0.106427</v>
+        <v>0.101967</v>
       </c>
       <c r="C664" t="n">
-        <v>0.210811</v>
+        <v>0.22043</v>
       </c>
     </row>
     <row r="665">
@@ -9059,10 +9059,10 @@
         </is>
       </c>
       <c r="B665" t="n">
-        <v>0.107038</v>
+        <v>0.103645</v>
       </c>
       <c r="C665" t="n">
-        <v>0.208108</v>
+        <v>0.217742</v>
       </c>
     </row>
     <row r="666">
@@ -9072,10 +9072,10 @@
         </is>
       </c>
       <c r="B666" t="n">
-        <v>0.111538</v>
+        <v>0.104232</v>
       </c>
       <c r="C666" t="n">
-        <v>0.205405</v>
+        <v>0.215054</v>
       </c>
     </row>
     <row r="667">
@@ -9085,10 +9085,10 @@
         </is>
       </c>
       <c r="B667" t="n">
-        <v>0.11426</v>
+        <v>0.105014</v>
       </c>
       <c r="C667" t="n">
-        <v>0.202703</v>
+        <v>0.212366</v>
       </c>
     </row>
     <row r="668">
@@ -9098,10 +9098,10 @@
         </is>
       </c>
       <c r="B668" t="n">
-        <v>0.114284</v>
+        <v>0.105229</v>
       </c>
       <c r="C668" t="n">
-        <v>0.2</v>
+        <v>0.209677</v>
       </c>
     </row>
     <row r="669">
@@ -9111,10 +9111,10 @@
         </is>
       </c>
       <c r="B669" t="n">
-        <v>0.114613</v>
+        <v>0.105369</v>
       </c>
       <c r="C669" t="n">
-        <v>0.197297</v>
+        <v>0.206989</v>
       </c>
     </row>
     <row r="670">
@@ -9124,10 +9124,10 @@
         </is>
       </c>
       <c r="B670" t="n">
-        <v>0.116521</v>
+        <v>0.106591</v>
       </c>
       <c r="C670" t="n">
-        <v>0.194595</v>
+        <v>0.204301</v>
       </c>
     </row>
     <row r="671">
@@ -9137,10 +9137,10 @@
         </is>
       </c>
       <c r="B671" t="n">
-        <v>0.117234</v>
+        <v>0.110929</v>
       </c>
       <c r="C671" t="n">
-        <v>0.191892</v>
+        <v>0.201613</v>
       </c>
     </row>
     <row r="672">
@@ -9150,10 +9150,10 @@
         </is>
       </c>
       <c r="B672" t="n">
-        <v>0.118839</v>
+        <v>0.113882</v>
       </c>
       <c r="C672" t="n">
-        <v>0.189189</v>
+        <v>0.198925</v>
       </c>
     </row>
     <row r="673">
@@ -9163,10 +9163,10 @@
         </is>
       </c>
       <c r="B673" t="n">
-        <v>0.118863</v>
+        <v>0.114167</v>
       </c>
       <c r="C673" t="n">
-        <v>0.186486</v>
+        <v>0.196237</v>
       </c>
     </row>
     <row r="674">
@@ -9176,10 +9176,10 @@
         </is>
       </c>
       <c r="B674" t="n">
-        <v>0.12124</v>
+        <v>0.115454</v>
       </c>
       <c r="C674" t="n">
-        <v>0.183784</v>
+        <v>0.193548</v>
       </c>
     </row>
     <row r="675">
@@ -9189,10 +9189,10 @@
         </is>
       </c>
       <c r="B675" t="n">
-        <v>0.121348</v>
+        <v>0.116249</v>
       </c>
       <c r="C675" t="n">
-        <v>0.181081</v>
+        <v>0.19086</v>
       </c>
     </row>
     <row r="676">
@@ -9202,10 +9202,10 @@
         </is>
       </c>
       <c r="B676" t="n">
-        <v>0.122079</v>
+        <v>0.1177</v>
       </c>
       <c r="C676" t="n">
-        <v>0.178378</v>
+        <v>0.188172</v>
       </c>
     </row>
     <row r="677">
@@ -9215,10 +9215,10 @@
         </is>
       </c>
       <c r="B677" t="n">
-        <v>0.122493</v>
+        <v>0.117744</v>
       </c>
       <c r="C677" t="n">
-        <v>0.175676</v>
+        <v>0.185484</v>
       </c>
     </row>
     <row r="678">
@@ -9228,10 +9228,10 @@
         </is>
       </c>
       <c r="B678" t="n">
-        <v>0.123283</v>
+        <v>0.12079</v>
       </c>
       <c r="C678" t="n">
-        <v>0.172973</v>
+        <v>0.182796</v>
       </c>
     </row>
     <row r="679">
@@ -9241,10 +9241,10 @@
         </is>
       </c>
       <c r="B679" t="n">
-        <v>0.124247</v>
+        <v>0.120819</v>
       </c>
       <c r="C679" t="n">
-        <v>0.17027</v>
+        <v>0.180108</v>
       </c>
     </row>
     <row r="680">
@@ -9254,10 +9254,10 @@
         </is>
       </c>
       <c r="B680" t="n">
-        <v>0.127344</v>
+        <v>0.121756</v>
       </c>
       <c r="C680" t="n">
-        <v>0.167568</v>
+        <v>0.177419</v>
       </c>
     </row>
     <row r="681">
@@ -9267,10 +9267,10 @@
         </is>
       </c>
       <c r="B681" t="n">
-        <v>0.12908</v>
+        <v>0.122035</v>
       </c>
       <c r="C681" t="n">
-        <v>0.164865</v>
+        <v>0.174731</v>
       </c>
     </row>
     <row r="682">
@@ -9280,10 +9280,10 @@
         </is>
       </c>
       <c r="B682" t="n">
-        <v>0.129154</v>
+        <v>0.1229</v>
       </c>
       <c r="C682" t="n">
-        <v>0.162162</v>
+        <v>0.172043</v>
       </c>
     </row>
     <row r="683">
@@ -9293,10 +9293,10 @@
         </is>
       </c>
       <c r="B683" t="n">
-        <v>0.130306</v>
+        <v>0.123834</v>
       </c>
       <c r="C683" t="n">
-        <v>0.159459</v>
+        <v>0.169355</v>
       </c>
     </row>
     <row r="684">
@@ -9306,10 +9306,10 @@
         </is>
       </c>
       <c r="B684" t="n">
-        <v>0.130536</v>
+        <v>0.126745</v>
       </c>
       <c r="C684" t="n">
-        <v>0.156757</v>
+        <v>0.166667</v>
       </c>
     </row>
     <row r="685">
@@ -9319,10 +9319,10 @@
         </is>
       </c>
       <c r="B685" t="n">
-        <v>0.130718</v>
+        <v>0.126914</v>
       </c>
       <c r="C685" t="n">
-        <v>0.154054</v>
+        <v>0.163978</v>
       </c>
     </row>
     <row r="686">
@@ -9332,10 +9332,10 @@
         </is>
       </c>
       <c r="B686" t="n">
-        <v>0.132481</v>
+        <v>0.128783</v>
       </c>
       <c r="C686" t="n">
-        <v>0.151351</v>
+        <v>0.16129</v>
       </c>
     </row>
     <row r="687">
@@ -9345,10 +9345,10 @@
         </is>
       </c>
       <c r="B687" t="n">
-        <v>0.133598</v>
+        <v>0.128901</v>
       </c>
       <c r="C687" t="n">
-        <v>0.148649</v>
+        <v>0.158602</v>
       </c>
     </row>
     <row r="688">
@@ -9358,10 +9358,10 @@
         </is>
       </c>
       <c r="B688" t="n">
-        <v>0.134187</v>
+        <v>0.129603</v>
       </c>
       <c r="C688" t="n">
-        <v>0.145946</v>
+        <v>0.155914</v>
       </c>
     </row>
     <row r="689">
@@ -9371,10 +9371,10 @@
         </is>
       </c>
       <c r="B689" t="n">
-        <v>0.134352</v>
+        <v>0.130131</v>
       </c>
       <c r="C689" t="n">
-        <v>0.143243</v>
+        <v>0.153226</v>
       </c>
     </row>
     <row r="690">
@@ -9384,10 +9384,10 @@
         </is>
       </c>
       <c r="B690" t="n">
-        <v>0.13445</v>
+        <v>0.132068</v>
       </c>
       <c r="C690" t="n">
-        <v>0.140541</v>
+        <v>0.150538</v>
       </c>
     </row>
     <row r="691">
@@ -9397,10 +9397,10 @@
         </is>
       </c>
       <c r="B691" t="n">
-        <v>0.134701</v>
+        <v>0.132159</v>
       </c>
       <c r="C691" t="n">
-        <v>0.137838</v>
+        <v>0.147849</v>
       </c>
     </row>
     <row r="692">
@@ -9410,10 +9410,10 @@
         </is>
       </c>
       <c r="B692" t="n">
-        <v>0.135803</v>
+        <v>0.133451</v>
       </c>
       <c r="C692" t="n">
-        <v>0.135135</v>
+        <v>0.145161</v>
       </c>
     </row>
     <row r="693">
@@ -9423,10 +9423,10 @@
         </is>
       </c>
       <c r="B693" t="n">
-        <v>0.135805</v>
+        <v>0.133596</v>
       </c>
       <c r="C693" t="n">
-        <v>0.132432</v>
+        <v>0.142473</v>
       </c>
     </row>
     <row r="694">
@@ -9436,10 +9436,10 @@
         </is>
       </c>
       <c r="B694" t="n">
-        <v>0.135937</v>
+        <v>0.133836</v>
       </c>
       <c r="C694" t="n">
-        <v>0.12973</v>
+        <v>0.139785</v>
       </c>
     </row>
     <row r="695">
@@ -9449,10 +9449,10 @@
         </is>
       </c>
       <c r="B695" t="n">
-        <v>0.136539</v>
+        <v>0.134258</v>
       </c>
       <c r="C695" t="n">
-        <v>0.127027</v>
+        <v>0.137097</v>
       </c>
     </row>
     <row r="696">
@@ -9462,10 +9462,10 @@
         </is>
       </c>
       <c r="B696" t="n">
-        <v>0.138412</v>
+        <v>0.134443</v>
       </c>
       <c r="C696" t="n">
-        <v>0.124324</v>
+        <v>0.134409</v>
       </c>
     </row>
     <row r="697">
@@ -9475,10 +9475,10 @@
         </is>
       </c>
       <c r="B697" t="n">
-        <v>0.138946</v>
+        <v>0.134772</v>
       </c>
       <c r="C697" t="n">
-        <v>0.121622</v>
+        <v>0.13172</v>
       </c>
     </row>
     <row r="698">
@@ -9488,10 +9488,10 @@
         </is>
       </c>
       <c r="B698" t="n">
-        <v>0.140752</v>
+        <v>0.134931</v>
       </c>
       <c r="C698" t="n">
-        <v>0.118919</v>
+        <v>0.129032</v>
       </c>
     </row>
     <row r="699">
@@ -9501,10 +9501,10 @@
         </is>
       </c>
       <c r="B699" t="n">
-        <v>0.141986</v>
+        <v>0.13504</v>
       </c>
       <c r="C699" t="n">
-        <v>0.116216</v>
+        <v>0.126344</v>
       </c>
     </row>
     <row r="700">
@@ -9514,10 +9514,10 @@
         </is>
       </c>
       <c r="B700" t="n">
-        <v>0.154657</v>
+        <v>0.136667</v>
       </c>
       <c r="C700" t="n">
-        <v>0.113514</v>
+        <v>0.123656</v>
       </c>
     </row>
     <row r="701">
@@ -9527,10 +9527,10 @@
         </is>
       </c>
       <c r="B701" t="n">
-        <v>0.158719</v>
+        <v>0.138716</v>
       </c>
       <c r="C701" t="n">
-        <v>0.110811</v>
+        <v>0.120968</v>
       </c>
     </row>
     <row r="702">
@@ -9540,10 +9540,10 @@
         </is>
       </c>
       <c r="B702" t="n">
-        <v>0.159263</v>
+        <v>0.139686</v>
       </c>
       <c r="C702" t="n">
-        <v>0.108108</v>
+        <v>0.11828</v>
       </c>
     </row>
     <row r="703">
@@ -9553,10 +9553,10 @@
         </is>
       </c>
       <c r="B703" t="n">
-        <v>0.160557</v>
+        <v>0.139823</v>
       </c>
       <c r="C703" t="n">
-        <v>0.105405</v>
+        <v>0.115591</v>
       </c>
     </row>
     <row r="704">
@@ -9566,10 +9566,10 @@
         </is>
       </c>
       <c r="B704" t="n">
-        <v>0.161628</v>
+        <v>0.152344</v>
       </c>
       <c r="C704" t="n">
-        <v>0.102703</v>
+        <v>0.112903</v>
       </c>
     </row>
     <row r="705">
@@ -9579,10 +9579,10 @@
         </is>
       </c>
       <c r="B705" t="n">
-        <v>0.16225</v>
+        <v>0.158002</v>
       </c>
       <c r="C705" t="n">
-        <v>0.1</v>
+        <v>0.110215</v>
       </c>
     </row>
     <row r="706">
@@ -9592,10 +9592,10 @@
         </is>
       </c>
       <c r="B706" t="n">
-        <v>0.162686</v>
+        <v>0.158281</v>
       </c>
       <c r="C706" t="n">
-        <v>0.09729699999999999</v>
+        <v>0.107527</v>
       </c>
     </row>
     <row r="707">
@@ -9605,10 +9605,10 @@
         </is>
       </c>
       <c r="B707" t="n">
-        <v>0.170157</v>
+        <v>0.159143</v>
       </c>
       <c r="C707" t="n">
-        <v>0.094595</v>
+        <v>0.104839</v>
       </c>
     </row>
     <row r="708">
@@ -9618,10 +9618,10 @@
         </is>
       </c>
       <c r="B708" t="n">
-        <v>0.172403</v>
+        <v>0.159726</v>
       </c>
       <c r="C708" t="n">
-        <v>0.091892</v>
+        <v>0.102151</v>
       </c>
     </row>
     <row r="709">
@@ -9631,10 +9631,10 @@
         </is>
       </c>
       <c r="B709" t="n">
-        <v>0.172622</v>
+        <v>0.159861</v>
       </c>
       <c r="C709" t="n">
-        <v>0.089189</v>
+        <v>0.09946199999999999</v>
       </c>
     </row>
     <row r="710">
@@ -9644,10 +9644,10 @@
         </is>
       </c>
       <c r="B710" t="n">
-        <v>0.17443</v>
+        <v>0.16141</v>
       </c>
       <c r="C710" t="n">
-        <v>0.08648599999999999</v>
+        <v>0.096774</v>
       </c>
     </row>
     <row r="711">
@@ -9657,10 +9657,10 @@
         </is>
       </c>
       <c r="B711" t="n">
-        <v>0.176572</v>
+        <v>0.169525</v>
       </c>
       <c r="C711" t="n">
-        <v>0.083784</v>
+        <v>0.094086</v>
       </c>
     </row>
     <row r="712">
@@ -9670,10 +9670,10 @@
         </is>
       </c>
       <c r="B712" t="n">
-        <v>0.179724</v>
+        <v>0.170376</v>
       </c>
       <c r="C712" t="n">
-        <v>0.081081</v>
+        <v>0.09139799999999999</v>
       </c>
     </row>
     <row r="713">
@@ -9683,10 +9683,10 @@
         </is>
       </c>
       <c r="B713" t="n">
-        <v>0.184022</v>
+        <v>0.171855</v>
       </c>
       <c r="C713" t="n">
-        <v>0.078378</v>
+        <v>0.08871</v>
       </c>
     </row>
     <row r="714">
@@ -9696,10 +9696,10 @@
         </is>
       </c>
       <c r="B714" t="n">
-        <v>0.187092</v>
+        <v>0.173539</v>
       </c>
       <c r="C714" t="n">
-        <v>0.07567599999999999</v>
+        <v>0.086022</v>
       </c>
     </row>
     <row r="715">
@@ -9709,10 +9709,10 @@
         </is>
       </c>
       <c r="B715" t="n">
-        <v>0.18755</v>
+        <v>0.174208</v>
       </c>
       <c r="C715" t="n">
-        <v>0.072973</v>
+        <v>0.083333</v>
       </c>
     </row>
     <row r="716">
@@ -9722,10 +9722,10 @@
         </is>
       </c>
       <c r="B716" t="n">
-        <v>0.188335</v>
+        <v>0.178201</v>
       </c>
       <c r="C716" t="n">
-        <v>0.07027</v>
+        <v>0.08064499999999999</v>
       </c>
     </row>
     <row r="717">
@@ -9735,10 +9735,10 @@
         </is>
       </c>
       <c r="B717" t="n">
-        <v>0.190851</v>
+        <v>0.180948</v>
       </c>
       <c r="C717" t="n">
-        <v>0.067568</v>
+        <v>0.077957</v>
       </c>
     </row>
     <row r="718">
@@ -9748,10 +9748,10 @@
         </is>
       </c>
       <c r="B718" t="n">
-        <v>0.192407</v>
+        <v>0.185535</v>
       </c>
       <c r="C718" t="n">
-        <v>0.06486500000000001</v>
+        <v>0.075269</v>
       </c>
     </row>
     <row r="719">
@@ -9761,10 +9761,10 @@
         </is>
       </c>
       <c r="B719" t="n">
-        <v>0.195206</v>
+        <v>0.18592</v>
       </c>
       <c r="C719" t="n">
-        <v>0.062162</v>
+        <v>0.07258100000000001</v>
       </c>
     </row>
     <row r="720">
@@ -9774,10 +9774,10 @@
         </is>
       </c>
       <c r="B720" t="n">
-        <v>0.213419</v>
+        <v>0.186413</v>
       </c>
       <c r="C720" t="n">
-        <v>0.059459</v>
+        <v>0.069892</v>
       </c>
     </row>
     <row r="721">
@@ -9787,10 +9787,10 @@
         </is>
       </c>
       <c r="B721" t="n">
-        <v>0.216507</v>
+        <v>0.189976</v>
       </c>
       <c r="C721" t="n">
-        <v>0.056757</v>
+        <v>0.067204</v>
       </c>
     </row>
     <row r="722">
@@ -9800,10 +9800,10 @@
         </is>
       </c>
       <c r="B722" t="n">
-        <v>0.218012</v>
+        <v>0.190804</v>
       </c>
       <c r="C722" t="n">
-        <v>0.054054</v>
+        <v>0.064516</v>
       </c>
     </row>
     <row r="723">
@@ -9813,10 +9813,10 @@
         </is>
       </c>
       <c r="B723" t="n">
-        <v>0.220076</v>
+        <v>0.194014</v>
       </c>
       <c r="C723" t="n">
-        <v>0.051351</v>
+        <v>0.061828</v>
       </c>
     </row>
     <row r="724">
@@ -9826,10 +9826,10 @@
         </is>
       </c>
       <c r="B724" t="n">
-        <v>0.221546</v>
+        <v>0.21152</v>
       </c>
       <c r="C724" t="n">
-        <v>0.048649</v>
+        <v>0.05914</v>
       </c>
     </row>
     <row r="725">
@@ -9839,10 +9839,10 @@
         </is>
       </c>
       <c r="B725" t="n">
-        <v>0.230382</v>
+        <v>0.214346</v>
       </c>
       <c r="C725" t="n">
-        <v>0.045946</v>
+        <v>0.056452</v>
       </c>
     </row>
     <row r="726">
@@ -9852,10 +9852,10 @@
         </is>
       </c>
       <c r="B726" t="n">
-        <v>0.231624</v>
+        <v>0.217108</v>
       </c>
       <c r="C726" t="n">
-        <v>0.043243</v>
+        <v>0.053763</v>
       </c>
     </row>
     <row r="727">
@@ -9865,10 +9865,10 @@
         </is>
       </c>
       <c r="B727" t="n">
-        <v>0.237343</v>
+        <v>0.219344</v>
       </c>
       <c r="C727" t="n">
-        <v>0.040541</v>
+        <v>0.051075</v>
       </c>
     </row>
     <row r="728">
@@ -9878,10 +9878,10 @@
         </is>
       </c>
       <c r="B728" t="n">
-        <v>0.241455</v>
+        <v>0.221036</v>
       </c>
       <c r="C728" t="n">
-        <v>0.037838</v>
+        <v>0.048387</v>
       </c>
     </row>
     <row r="729">
@@ -9891,10 +9891,10 @@
         </is>
       </c>
       <c r="B729" t="n">
-        <v>0.251474</v>
+        <v>0.227698</v>
       </c>
       <c r="C729" t="n">
-        <v>0.035135</v>
+        <v>0.045699</v>
       </c>
     </row>
     <row r="730">
@@ -9904,10 +9904,10 @@
         </is>
       </c>
       <c r="B730" t="n">
-        <v>0.256786</v>
+        <v>0.228679</v>
       </c>
       <c r="C730" t="n">
-        <v>0.032432</v>
+        <v>0.043011</v>
       </c>
     </row>
     <row r="731">
@@ -9917,10 +9917,10 @@
         </is>
       </c>
       <c r="B731" t="n">
-        <v>0.271031</v>
+        <v>0.231609</v>
       </c>
       <c r="C731" t="n">
-        <v>0.02973</v>
+        <v>0.040323</v>
       </c>
     </row>
     <row r="732">
@@ -9930,10 +9930,10 @@
         </is>
       </c>
       <c r="B732" t="n">
-        <v>0.287442</v>
+        <v>0.239083</v>
       </c>
       <c r="C732" t="n">
-        <v>0.027027</v>
+        <v>0.037634</v>
       </c>
     </row>
     <row r="733">
@@ -9943,10 +9943,10 @@
         </is>
       </c>
       <c r="B733" t="n">
-        <v>0.296116</v>
+        <v>0.249958</v>
       </c>
       <c r="C733" t="n">
-        <v>0.024324</v>
+        <v>0.034946</v>
       </c>
     </row>
     <row r="734">
@@ -9956,10 +9956,10 @@
         </is>
       </c>
       <c r="B734" t="n">
-        <v>0.338337</v>
+        <v>0.255318</v>
       </c>
       <c r="C734" t="n">
-        <v>0.021622</v>
+        <v>0.032258</v>
       </c>
     </row>
     <row r="735">
@@ -9969,10 +9969,10 @@
         </is>
       </c>
       <c r="B735" t="n">
-        <v>0.343027</v>
+        <v>0.286169</v>
       </c>
       <c r="C735" t="n">
-        <v>0.018919</v>
+        <v>0.02957</v>
       </c>
     </row>
     <row r="736">
@@ -9982,10 +9982,10 @@
         </is>
       </c>
       <c r="B736" t="n">
-        <v>0.344213</v>
+        <v>0.29321</v>
       </c>
       <c r="C736" t="n">
-        <v>0.016216</v>
+        <v>0.026882</v>
       </c>
     </row>
     <row r="737">
@@ -9995,10 +9995,10 @@
         </is>
       </c>
       <c r="B737" t="n">
-        <v>0.380898</v>
+        <v>0.29501</v>
       </c>
       <c r="C737" t="n">
-        <v>0.013514</v>
+        <v>0.024194</v>
       </c>
     </row>
     <row r="738">
@@ -10008,10 +10008,10 @@
         </is>
       </c>
       <c r="B738" t="n">
-        <v>0.392498</v>
+        <v>0.33484</v>
       </c>
       <c r="C738" t="n">
-        <v>0.010811</v>
+        <v>0.021505</v>
       </c>
     </row>
     <row r="739">
@@ -10021,10 +10021,10 @@
         </is>
       </c>
       <c r="B739" t="n">
-        <v>0.439975</v>
+        <v>0.339735</v>
       </c>
       <c r="C739" t="n">
-        <v>0.008108000000000001</v>
+        <v>0.018817</v>
       </c>
     </row>
     <row r="740">
@@ -10034,10 +10034,10 @@
         </is>
       </c>
       <c r="B740" t="n">
-        <v>0.635779</v>
+        <v>0.340999</v>
       </c>
       <c r="C740" t="n">
-        <v>0.005405</v>
+        <v>0.016129</v>
       </c>
     </row>
     <row r="741">
@@ -10047,10 +10047,62 @@
         </is>
       </c>
       <c r="B741" t="n">
-        <v>0.67135</v>
+        <v>0.376465</v>
       </c>
       <c r="C741" t="n">
-        <v>0.002703</v>
+        <v>0.013441</v>
+      </c>
+    </row>
+    <row r="742">
+      <c r="A742" t="inlineStr">
+        <is>
+          <t>Adjusted target</t>
+        </is>
+      </c>
+      <c r="B742" t="n">
+        <v>0.391022</v>
+      </c>
+      <c r="C742" t="n">
+        <v>0.010753</v>
+      </c>
+    </row>
+    <row r="743">
+      <c r="A743" t="inlineStr">
+        <is>
+          <t>Adjusted target</t>
+        </is>
+      </c>
+      <c r="B743" t="n">
+        <v>0.435504</v>
+      </c>
+      <c r="C743" t="n">
+        <v>0.008064999999999999</v>
+      </c>
+    </row>
+    <row r="744">
+      <c r="A744" t="inlineStr">
+        <is>
+          <t>Adjusted target</t>
+        </is>
+      </c>
+      <c r="B744" t="n">
+        <v>0.632473</v>
+      </c>
+      <c r="C744" t="n">
+        <v>0.005376</v>
+      </c>
+    </row>
+    <row r="745">
+      <c r="A745" t="inlineStr">
+        <is>
+          <t>Adjusted target</t>
+        </is>
+      </c>
+      <c r="B745" t="n">
+        <v>0.6656029999999999</v>
+      </c>
+      <c r="C745" t="n">
+        <v>0.002688</v>
       </c>
     </row>
   </sheetData>

--- a/vignettes/vignette-1/tail_exceedance_plot_data.xlsx
+++ b/vignettes/vignette-1/tail_exceedance_plot_data.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C745"/>
+  <dimension ref="A1:C759"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -440,7 +440,7 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>5e-06</v>
+        <v>1e-06</v>
       </c>
       <c r="C2" t="n">
         <v>1</v>
@@ -456,7 +456,7 @@
         <v>9.3e-05</v>
       </c>
       <c r="C3" t="n">
-        <v>0.997312</v>
+        <v>0.9973610000000001</v>
       </c>
     </row>
     <row r="4">
@@ -466,10 +466,10 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0.000522</v>
+        <v>0.000441</v>
       </c>
       <c r="C4" t="n">
-        <v>0.994624</v>
+        <v>0.994723</v>
       </c>
     </row>
     <row r="5">
@@ -479,10 +479,10 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>0.000687</v>
+        <v>0.000522</v>
       </c>
       <c r="C5" t="n">
-        <v>0.991935</v>
+        <v>0.992084</v>
       </c>
     </row>
     <row r="6">
@@ -492,10 +492,10 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>0.001141</v>
+        <v>0.001163</v>
       </c>
       <c r="C6" t="n">
-        <v>0.989247</v>
+        <v>0.989446</v>
       </c>
     </row>
     <row r="7">
@@ -508,7 +508,7 @@
         <v>0.001681</v>
       </c>
       <c r="C7" t="n">
-        <v>0.986559</v>
+        <v>0.986807</v>
       </c>
     </row>
     <row r="8">
@@ -521,7 +521,7 @@
         <v>0.00295</v>
       </c>
       <c r="C8" t="n">
-        <v>0.9838710000000001</v>
+        <v>0.984169</v>
       </c>
     </row>
     <row r="9">
@@ -534,7 +534,7 @@
         <v>0.002998</v>
       </c>
       <c r="C9" t="n">
-        <v>0.981183</v>
+        <v>0.98153</v>
       </c>
     </row>
     <row r="10">
@@ -547,7 +547,7 @@
         <v>0.003455</v>
       </c>
       <c r="C10" t="n">
-        <v>0.978495</v>
+        <v>0.978892</v>
       </c>
     </row>
     <row r="11">
@@ -560,7 +560,7 @@
         <v>0.003769</v>
       </c>
       <c r="C11" t="n">
-        <v>0.975806</v>
+        <v>0.976253</v>
       </c>
     </row>
     <row r="12">
@@ -573,7 +573,7 @@
         <v>0.003788</v>
       </c>
       <c r="C12" t="n">
-        <v>0.973118</v>
+        <v>0.973615</v>
       </c>
     </row>
     <row r="13">
@@ -583,10 +583,10 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>0.003948</v>
+        <v>0.004717</v>
       </c>
       <c r="C13" t="n">
-        <v>0.97043</v>
+        <v>0.970976</v>
       </c>
     </row>
     <row r="14">
@@ -596,10 +596,10 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>0.004497</v>
+        <v>0.004779</v>
       </c>
       <c r="C14" t="n">
-        <v>0.967742</v>
+        <v>0.968338</v>
       </c>
     </row>
     <row r="15">
@@ -609,10 +609,10 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>0.004717</v>
+        <v>0.004912</v>
       </c>
       <c r="C15" t="n">
-        <v>0.965054</v>
+        <v>0.965699</v>
       </c>
     </row>
     <row r="16">
@@ -622,10 +622,10 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>0.004912</v>
+        <v>0.005429</v>
       </c>
       <c r="C16" t="n">
-        <v>0.9623660000000001</v>
+        <v>0.9630609999999999</v>
       </c>
     </row>
     <row r="17">
@@ -635,10 +635,10 @@
         </is>
       </c>
       <c r="B17" t="n">
-        <v>0.005429</v>
+        <v>0.005649</v>
       </c>
       <c r="C17" t="n">
-        <v>0.959677</v>
+        <v>0.960422</v>
       </c>
     </row>
     <row r="18">
@@ -651,7 +651,7 @@
         <v>0.00593</v>
       </c>
       <c r="C18" t="n">
-        <v>0.956989</v>
+        <v>0.957784</v>
       </c>
     </row>
     <row r="19">
@@ -661,10 +661,10 @@
         </is>
       </c>
       <c r="B19" t="n">
-        <v>0.0071</v>
+        <v>0.006143</v>
       </c>
       <c r="C19" t="n">
-        <v>0.954301</v>
+        <v>0.955145</v>
       </c>
     </row>
     <row r="20">
@@ -674,10 +674,10 @@
         </is>
       </c>
       <c r="B20" t="n">
-        <v>0.007582</v>
+        <v>0.006394</v>
       </c>
       <c r="C20" t="n">
-        <v>0.951613</v>
+        <v>0.952507</v>
       </c>
     </row>
     <row r="21">
@@ -687,10 +687,10 @@
         </is>
       </c>
       <c r="B21" t="n">
-        <v>0.008029</v>
+        <v>0.006914</v>
       </c>
       <c r="C21" t="n">
-        <v>0.948925</v>
+        <v>0.949868</v>
       </c>
     </row>
     <row r="22">
@@ -700,10 +700,10 @@
         </is>
       </c>
       <c r="B22" t="n">
-        <v>0.008069</v>
+        <v>0.007419</v>
       </c>
       <c r="C22" t="n">
-        <v>0.946237</v>
+        <v>0.94723</v>
       </c>
     </row>
     <row r="23">
@@ -713,10 +713,10 @@
         </is>
       </c>
       <c r="B23" t="n">
-        <v>0.008137999999999999</v>
+        <v>0.007582</v>
       </c>
       <c r="C23" t="n">
-        <v>0.9435480000000001</v>
+        <v>0.944591</v>
       </c>
     </row>
     <row r="24">
@@ -726,10 +726,10 @@
         </is>
       </c>
       <c r="B24" t="n">
-        <v>0.008377000000000001</v>
+        <v>0.008029</v>
       </c>
       <c r="C24" t="n">
-        <v>0.94086</v>
+        <v>0.941953</v>
       </c>
     </row>
     <row r="25">
@@ -739,10 +739,10 @@
         </is>
       </c>
       <c r="B25" t="n">
-        <v>0.008514000000000001</v>
+        <v>0.008069</v>
       </c>
       <c r="C25" t="n">
-        <v>0.938172</v>
+        <v>0.939314</v>
       </c>
     </row>
     <row r="26">
@@ -752,10 +752,10 @@
         </is>
       </c>
       <c r="B26" t="n">
-        <v>0.008593999999999999</v>
+        <v>0.008173</v>
       </c>
       <c r="C26" t="n">
-        <v>0.935484</v>
+        <v>0.936675</v>
       </c>
     </row>
     <row r="27">
@@ -765,10 +765,10 @@
         </is>
       </c>
       <c r="B27" t="n">
-        <v>0.008658000000000001</v>
+        <v>0.008377000000000001</v>
       </c>
       <c r="C27" t="n">
-        <v>0.932796</v>
+        <v>0.934037</v>
       </c>
     </row>
     <row r="28">
@@ -778,10 +778,10 @@
         </is>
       </c>
       <c r="B28" t="n">
-        <v>0.008992</v>
+        <v>0.008593999999999999</v>
       </c>
       <c r="C28" t="n">
-        <v>0.930108</v>
+        <v>0.9313979999999999</v>
       </c>
     </row>
     <row r="29">
@@ -791,10 +791,10 @@
         </is>
       </c>
       <c r="B29" t="n">
-        <v>0.009011</v>
+        <v>0.008658000000000001</v>
       </c>
       <c r="C29" t="n">
-        <v>0.927419</v>
+        <v>0.92876</v>
       </c>
     </row>
     <row r="30">
@@ -804,10 +804,10 @@
         </is>
       </c>
       <c r="B30" t="n">
-        <v>0.009165</v>
+        <v>0.008992</v>
       </c>
       <c r="C30" t="n">
-        <v>0.924731</v>
+        <v>0.926121</v>
       </c>
     </row>
     <row r="31">
@@ -817,10 +817,10 @@
         </is>
       </c>
       <c r="B31" t="n">
-        <v>0.009428000000000001</v>
+        <v>0.009165</v>
       </c>
       <c r="C31" t="n">
-        <v>0.9220429999999999</v>
+        <v>0.9234830000000001</v>
       </c>
     </row>
     <row r="32">
@@ -830,10 +830,10 @@
         </is>
       </c>
       <c r="B32" t="n">
-        <v>0.009578</v>
+        <v>0.009428000000000001</v>
       </c>
       <c r="C32" t="n">
-        <v>0.919355</v>
+        <v>0.920844</v>
       </c>
     </row>
     <row r="33">
@@ -843,10 +843,10 @@
         </is>
       </c>
       <c r="B33" t="n">
-        <v>0.009774</v>
+        <v>0.009578</v>
       </c>
       <c r="C33" t="n">
-        <v>0.916667</v>
+        <v>0.918206</v>
       </c>
     </row>
     <row r="34">
@@ -856,10 +856,10 @@
         </is>
       </c>
       <c r="B34" t="n">
-        <v>0.009811</v>
+        <v>0.009774</v>
       </c>
       <c r="C34" t="n">
-        <v>0.913978</v>
+        <v>0.915567</v>
       </c>
     </row>
     <row r="35">
@@ -869,10 +869,10 @@
         </is>
       </c>
       <c r="B35" t="n">
-        <v>0.010226</v>
+        <v>0.009811</v>
       </c>
       <c r="C35" t="n">
-        <v>0.91129</v>
+        <v>0.912929</v>
       </c>
     </row>
     <row r="36">
@@ -882,10 +882,10 @@
         </is>
       </c>
       <c r="B36" t="n">
-        <v>0.010518</v>
+        <v>0.010226</v>
       </c>
       <c r="C36" t="n">
-        <v>0.908602</v>
+        <v>0.91029</v>
       </c>
     </row>
     <row r="37">
@@ -895,10 +895,10 @@
         </is>
       </c>
       <c r="B37" t="n">
-        <v>0.010554</v>
+        <v>0.010518</v>
       </c>
       <c r="C37" t="n">
-        <v>0.905914</v>
+        <v>0.907652</v>
       </c>
     </row>
     <row r="38">
@@ -908,10 +908,10 @@
         </is>
       </c>
       <c r="B38" t="n">
-        <v>0.010625</v>
+        <v>0.010943</v>
       </c>
       <c r="C38" t="n">
-        <v>0.903226</v>
+        <v>0.905013</v>
       </c>
     </row>
     <row r="39">
@@ -921,10 +921,10 @@
         </is>
       </c>
       <c r="B39" t="n">
-        <v>0.011326</v>
+        <v>0.011156</v>
       </c>
       <c r="C39" t="n">
-        <v>0.9005379999999999</v>
+        <v>0.902375</v>
       </c>
     </row>
     <row r="40">
@@ -934,10 +934,10 @@
         </is>
       </c>
       <c r="B40" t="n">
-        <v>0.01145</v>
+        <v>0.011326</v>
       </c>
       <c r="C40" t="n">
-        <v>0.897849</v>
+        <v>0.899736</v>
       </c>
     </row>
     <row r="41">
@@ -947,10 +947,10 @@
         </is>
       </c>
       <c r="B41" t="n">
-        <v>0.011999</v>
+        <v>0.01145</v>
       </c>
       <c r="C41" t="n">
-        <v>0.895161</v>
+        <v>0.897098</v>
       </c>
     </row>
     <row r="42">
@@ -960,10 +960,10 @@
         </is>
       </c>
       <c r="B42" t="n">
-        <v>0.012035</v>
+        <v>0.012002</v>
       </c>
       <c r="C42" t="n">
-        <v>0.892473</v>
+        <v>0.894459</v>
       </c>
     </row>
     <row r="43">
@@ -973,10 +973,10 @@
         </is>
       </c>
       <c r="B43" t="n">
-        <v>0.012657</v>
+        <v>0.012035</v>
       </c>
       <c r="C43" t="n">
-        <v>0.889785</v>
+        <v>0.891821</v>
       </c>
     </row>
     <row r="44">
@@ -986,10 +986,10 @@
         </is>
       </c>
       <c r="B44" t="n">
-        <v>0.012918</v>
+        <v>0.012747</v>
       </c>
       <c r="C44" t="n">
-        <v>0.887097</v>
+        <v>0.889182</v>
       </c>
     </row>
     <row r="45">
@@ -999,10 +999,10 @@
         </is>
       </c>
       <c r="B45" t="n">
-        <v>0.013023</v>
+        <v>0.012918</v>
       </c>
       <c r="C45" t="n">
-        <v>0.884409</v>
+        <v>0.886544</v>
       </c>
     </row>
     <row r="46">
@@ -1012,10 +1012,10 @@
         </is>
       </c>
       <c r="B46" t="n">
-        <v>0.013054</v>
+        <v>0.013714</v>
       </c>
       <c r="C46" t="n">
-        <v>0.8817199999999999</v>
+        <v>0.8839050000000001</v>
       </c>
     </row>
     <row r="47">
@@ -1025,10 +1025,10 @@
         </is>
       </c>
       <c r="B47" t="n">
-        <v>0.013094</v>
+        <v>0.01393</v>
       </c>
       <c r="C47" t="n">
-        <v>0.879032</v>
+        <v>0.881266</v>
       </c>
     </row>
     <row r="48">
@@ -1038,10 +1038,10 @@
         </is>
       </c>
       <c r="B48" t="n">
-        <v>0.013641</v>
+        <v>0.013971</v>
       </c>
       <c r="C48" t="n">
-        <v>0.876344</v>
+        <v>0.878628</v>
       </c>
     </row>
     <row r="49">
@@ -1051,10 +1051,10 @@
         </is>
       </c>
       <c r="B49" t="n">
-        <v>0.013714</v>
+        <v>0.014018</v>
       </c>
       <c r="C49" t="n">
-        <v>0.873656</v>
+        <v>0.875989</v>
       </c>
     </row>
     <row r="50">
@@ -1064,10 +1064,10 @@
         </is>
       </c>
       <c r="B50" t="n">
-        <v>0.014018</v>
+        <v>0.014481</v>
       </c>
       <c r="C50" t="n">
-        <v>0.870968</v>
+        <v>0.873351</v>
       </c>
     </row>
     <row r="51">
@@ -1077,10 +1077,10 @@
         </is>
       </c>
       <c r="B51" t="n">
-        <v>0.014351</v>
+        <v>0.014731</v>
       </c>
       <c r="C51" t="n">
-        <v>0.8682800000000001</v>
+        <v>0.870712</v>
       </c>
     </row>
     <row r="52">
@@ -1090,10 +1090,10 @@
         </is>
       </c>
       <c r="B52" t="n">
-        <v>0.014731</v>
+        <v>0.014841</v>
       </c>
       <c r="C52" t="n">
-        <v>0.865591</v>
+        <v>0.868074</v>
       </c>
     </row>
     <row r="53">
@@ -1103,10 +1103,10 @@
         </is>
       </c>
       <c r="B53" t="n">
-        <v>0.014841</v>
+        <v>0.01486</v>
       </c>
       <c r="C53" t="n">
-        <v>0.862903</v>
+        <v>0.865435</v>
       </c>
     </row>
     <row r="54">
@@ -1116,10 +1116,10 @@
         </is>
       </c>
       <c r="B54" t="n">
-        <v>0.01486</v>
+        <v>0.015041</v>
       </c>
       <c r="C54" t="n">
-        <v>0.860215</v>
+        <v>0.862797</v>
       </c>
     </row>
     <row r="55">
@@ -1132,7 +1132,7 @@
         <v>0.015107</v>
       </c>
       <c r="C55" t="n">
-        <v>0.857527</v>
+        <v>0.860158</v>
       </c>
     </row>
     <row r="56">
@@ -1145,7 +1145,7 @@
         <v>0.015107</v>
       </c>
       <c r="C56" t="n">
-        <v>0.854839</v>
+        <v>0.8575199999999999</v>
       </c>
     </row>
     <row r="57">
@@ -1155,10 +1155,10 @@
         </is>
       </c>
       <c r="B57" t="n">
-        <v>0.015349</v>
+        <v>0.015553</v>
       </c>
       <c r="C57" t="n">
-        <v>0.852151</v>
+        <v>0.854881</v>
       </c>
     </row>
     <row r="58">
@@ -1168,10 +1168,10 @@
         </is>
       </c>
       <c r="B58" t="n">
-        <v>0.015553</v>
+        <v>0.016031</v>
       </c>
       <c r="C58" t="n">
-        <v>0.8494620000000001</v>
+        <v>0.852243</v>
       </c>
     </row>
     <row r="59">
@@ -1181,10 +1181,10 @@
         </is>
       </c>
       <c r="B59" t="n">
-        <v>0.016031</v>
+        <v>0.016343</v>
       </c>
       <c r="C59" t="n">
-        <v>0.846774</v>
+        <v>0.849604</v>
       </c>
     </row>
     <row r="60">
@@ -1194,10 +1194,10 @@
         </is>
       </c>
       <c r="B60" t="n">
-        <v>0.016343</v>
+        <v>0.016545</v>
       </c>
       <c r="C60" t="n">
-        <v>0.844086</v>
+        <v>0.846966</v>
       </c>
     </row>
     <row r="61">
@@ -1207,10 +1207,10 @@
         </is>
       </c>
       <c r="B61" t="n">
-        <v>0.016545</v>
+        <v>0.017135</v>
       </c>
       <c r="C61" t="n">
-        <v>0.841398</v>
+        <v>0.844327</v>
       </c>
     </row>
     <row r="62">
@@ -1220,10 +1220,10 @@
         </is>
       </c>
       <c r="B62" t="n">
-        <v>0.017135</v>
+        <v>0.017276</v>
       </c>
       <c r="C62" t="n">
-        <v>0.83871</v>
+        <v>0.841689</v>
       </c>
     </row>
     <row r="63">
@@ -1233,10 +1233,10 @@
         </is>
       </c>
       <c r="B63" t="n">
-        <v>0.017276</v>
+        <v>0.017621</v>
       </c>
       <c r="C63" t="n">
-        <v>0.836022</v>
+        <v>0.83905</v>
       </c>
     </row>
     <row r="64">
@@ -1246,10 +1246,10 @@
         </is>
       </c>
       <c r="B64" t="n">
-        <v>0.017776</v>
+        <v>0.017975</v>
       </c>
       <c r="C64" t="n">
-        <v>0.833333</v>
+        <v>0.836412</v>
       </c>
     </row>
     <row r="65">
@@ -1262,7 +1262,7 @@
         <v>0.018505</v>
       </c>
       <c r="C65" t="n">
-        <v>0.830645</v>
+        <v>0.833773</v>
       </c>
     </row>
     <row r="66">
@@ -1272,10 +1272,10 @@
         </is>
       </c>
       <c r="B66" t="n">
-        <v>0.018629</v>
+        <v>0.018757</v>
       </c>
       <c r="C66" t="n">
-        <v>0.8279570000000001</v>
+        <v>0.831135</v>
       </c>
     </row>
     <row r="67">
@@ -1285,10 +1285,10 @@
         </is>
       </c>
       <c r="B67" t="n">
-        <v>0.018757</v>
+        <v>0.018801</v>
       </c>
       <c r="C67" t="n">
-        <v>0.825269</v>
+        <v>0.828496</v>
       </c>
     </row>
     <row r="68">
@@ -1298,10 +1298,10 @@
         </is>
       </c>
       <c r="B68" t="n">
-        <v>0.018801</v>
+        <v>0.018847</v>
       </c>
       <c r="C68" t="n">
-        <v>0.822581</v>
+        <v>0.825858</v>
       </c>
     </row>
     <row r="69">
@@ -1311,10 +1311,10 @@
         </is>
       </c>
       <c r="B69" t="n">
-        <v>0.018847</v>
+        <v>0.018931</v>
       </c>
       <c r="C69" t="n">
-        <v>0.819892</v>
+        <v>0.823219</v>
       </c>
     </row>
     <row r="70">
@@ -1324,10 +1324,10 @@
         </is>
       </c>
       <c r="B70" t="n">
-        <v>0.018931</v>
+        <v>0.019352</v>
       </c>
       <c r="C70" t="n">
-        <v>0.817204</v>
+        <v>0.82058</v>
       </c>
     </row>
     <row r="71">
@@ -1337,10 +1337,10 @@
         </is>
       </c>
       <c r="B71" t="n">
-        <v>0.019049</v>
+        <v>0.01962</v>
       </c>
       <c r="C71" t="n">
-        <v>0.814516</v>
+        <v>0.8179419999999999</v>
       </c>
     </row>
     <row r="72">
@@ -1350,10 +1350,10 @@
         </is>
       </c>
       <c r="B72" t="n">
-        <v>0.019463</v>
+        <v>0.019953</v>
       </c>
       <c r="C72" t="n">
-        <v>0.811828</v>
+        <v>0.815303</v>
       </c>
     </row>
     <row r="73">
@@ -1363,10 +1363,10 @@
         </is>
       </c>
       <c r="B73" t="n">
-        <v>0.01962</v>
+        <v>0.020186</v>
       </c>
       <c r="C73" t="n">
-        <v>0.80914</v>
+        <v>0.812665</v>
       </c>
     </row>
     <row r="74">
@@ -1376,10 +1376,10 @@
         </is>
       </c>
       <c r="B74" t="n">
-        <v>0.019953</v>
+        <v>0.020393</v>
       </c>
       <c r="C74" t="n">
-        <v>0.8064519999999999</v>
+        <v>0.810026</v>
       </c>
     </row>
     <row r="75">
@@ -1389,10 +1389,10 @@
         </is>
       </c>
       <c r="B75" t="n">
-        <v>0.020393</v>
+        <v>0.02048</v>
       </c>
       <c r="C75" t="n">
-        <v>0.803763</v>
+        <v>0.807388</v>
       </c>
     </row>
     <row r="76">
@@ -1402,10 +1402,10 @@
         </is>
       </c>
       <c r="B76" t="n">
-        <v>0.02048</v>
+        <v>0.021572</v>
       </c>
       <c r="C76" t="n">
-        <v>0.801075</v>
+        <v>0.804749</v>
       </c>
     </row>
     <row r="77">
@@ -1415,10 +1415,10 @@
         </is>
       </c>
       <c r="B77" t="n">
-        <v>0.020817</v>
+        <v>0.021604</v>
       </c>
       <c r="C77" t="n">
-        <v>0.798387</v>
+        <v>0.802111</v>
       </c>
     </row>
     <row r="78">
@@ -1428,10 +1428,10 @@
         </is>
       </c>
       <c r="B78" t="n">
-        <v>0.021604</v>
+        <v>0.021912</v>
       </c>
       <c r="C78" t="n">
-        <v>0.795699</v>
+        <v>0.799472</v>
       </c>
     </row>
     <row r="79">
@@ -1444,7 +1444,7 @@
         <v>0.021918</v>
       </c>
       <c r="C79" t="n">
-        <v>0.793011</v>
+        <v>0.796834</v>
       </c>
     </row>
     <row r="80">
@@ -1457,7 +1457,7 @@
         <v>0.021962</v>
       </c>
       <c r="C80" t="n">
-        <v>0.790323</v>
+        <v>0.794195</v>
       </c>
     </row>
     <row r="81">
@@ -1470,7 +1470,7 @@
         <v>0.022008</v>
       </c>
       <c r="C81" t="n">
-        <v>0.7876339999999999</v>
+        <v>0.791557</v>
       </c>
     </row>
     <row r="82">
@@ -1483,7 +1483,7 @@
         <v>0.022011</v>
       </c>
       <c r="C82" t="n">
-        <v>0.784946</v>
+        <v>0.788918</v>
       </c>
     </row>
     <row r="83">
@@ -1496,7 +1496,7 @@
         <v>0.022121</v>
       </c>
       <c r="C83" t="n">
-        <v>0.782258</v>
+        <v>0.78628</v>
       </c>
     </row>
     <row r="84">
@@ -1506,10 +1506,10 @@
         </is>
       </c>
       <c r="B84" t="n">
-        <v>0.022324</v>
+        <v>0.022299</v>
       </c>
       <c r="C84" t="n">
-        <v>0.77957</v>
+        <v>0.783641</v>
       </c>
     </row>
     <row r="85">
@@ -1519,10 +1519,10 @@
         </is>
       </c>
       <c r="B85" t="n">
-        <v>0.022543</v>
+        <v>0.022324</v>
       </c>
       <c r="C85" t="n">
-        <v>0.776882</v>
+        <v>0.781003</v>
       </c>
     </row>
     <row r="86">
@@ -1532,10 +1532,10 @@
         </is>
       </c>
       <c r="B86" t="n">
-        <v>0.022891</v>
+        <v>0.022543</v>
       </c>
       <c r="C86" t="n">
-        <v>0.774194</v>
+        <v>0.7783639999999999</v>
       </c>
     </row>
     <row r="87">
@@ -1545,10 +1545,10 @@
         </is>
       </c>
       <c r="B87" t="n">
-        <v>0.023483</v>
+        <v>0.022891</v>
       </c>
       <c r="C87" t="n">
-        <v>0.771505</v>
+        <v>0.775726</v>
       </c>
     </row>
     <row r="88">
@@ -1558,10 +1558,10 @@
         </is>
       </c>
       <c r="B88" t="n">
-        <v>0.023855</v>
+        <v>0.023483</v>
       </c>
       <c r="C88" t="n">
-        <v>0.768817</v>
+        <v>0.773087</v>
       </c>
     </row>
     <row r="89">
@@ -1571,10 +1571,10 @@
         </is>
       </c>
       <c r="B89" t="n">
-        <v>0.023991</v>
+        <v>0.023843</v>
       </c>
       <c r="C89" t="n">
-        <v>0.7661289999999999</v>
+        <v>0.7704490000000001</v>
       </c>
     </row>
     <row r="90">
@@ -1584,10 +1584,10 @@
         </is>
       </c>
       <c r="B90" t="n">
-        <v>0.02408</v>
+        <v>0.023991</v>
       </c>
       <c r="C90" t="n">
-        <v>0.763441</v>
+        <v>0.76781</v>
       </c>
     </row>
     <row r="91">
@@ -1597,10 +1597,10 @@
         </is>
       </c>
       <c r="B91" t="n">
-        <v>0.024556</v>
+        <v>0.02408</v>
       </c>
       <c r="C91" t="n">
-        <v>0.760753</v>
+        <v>0.765172</v>
       </c>
     </row>
     <row r="92">
@@ -1610,10 +1610,10 @@
         </is>
       </c>
       <c r="B92" t="n">
-        <v>0.024703</v>
+        <v>0.024413</v>
       </c>
       <c r="C92" t="n">
-        <v>0.758065</v>
+        <v>0.762533</v>
       </c>
     </row>
     <row r="93">
@@ -1623,10 +1623,10 @@
         </is>
       </c>
       <c r="B93" t="n">
-        <v>0.025311</v>
+        <v>0.024896</v>
       </c>
       <c r="C93" t="n">
-        <v>0.755376</v>
+        <v>0.759894</v>
       </c>
     </row>
     <row r="94">
@@ -1639,7 +1639,7 @@
         <v>0.025327</v>
       </c>
       <c r="C94" t="n">
-        <v>0.752688</v>
+        <v>0.757256</v>
       </c>
     </row>
     <row r="95">
@@ -1649,10 +1649,10 @@
         </is>
       </c>
       <c r="B95" t="n">
-        <v>0.025544</v>
+        <v>0.025416</v>
       </c>
       <c r="C95" t="n">
-        <v>0.75</v>
+        <v>0.754617</v>
       </c>
     </row>
     <row r="96">
@@ -1662,10 +1662,10 @@
         </is>
       </c>
       <c r="B96" t="n">
-        <v>0.025755</v>
+        <v>0.025544</v>
       </c>
       <c r="C96" t="n">
-        <v>0.747312</v>
+        <v>0.751979</v>
       </c>
     </row>
     <row r="97">
@@ -1675,10 +1675,10 @@
         </is>
       </c>
       <c r="B97" t="n">
-        <v>0.025837</v>
+        <v>0.025755</v>
       </c>
       <c r="C97" t="n">
-        <v>0.744624</v>
+        <v>0.74934</v>
       </c>
     </row>
     <row r="98">
@@ -1688,10 +1688,10 @@
         </is>
       </c>
       <c r="B98" t="n">
-        <v>0.026545</v>
+        <v>0.025837</v>
       </c>
       <c r="C98" t="n">
-        <v>0.741935</v>
+        <v>0.746702</v>
       </c>
     </row>
     <row r="99">
@@ -1701,10 +1701,10 @@
         </is>
       </c>
       <c r="B99" t="n">
-        <v>0.027214</v>
+        <v>0.026545</v>
       </c>
       <c r="C99" t="n">
-        <v>0.739247</v>
+        <v>0.744063</v>
       </c>
     </row>
     <row r="100">
@@ -1714,10 +1714,10 @@
         </is>
       </c>
       <c r="B100" t="n">
-        <v>0.027413</v>
+        <v>0.027214</v>
       </c>
       <c r="C100" t="n">
-        <v>0.736559</v>
+        <v>0.741425</v>
       </c>
     </row>
     <row r="101">
@@ -1727,10 +1727,10 @@
         </is>
       </c>
       <c r="B101" t="n">
-        <v>0.028098</v>
+        <v>0.027321</v>
       </c>
       <c r="C101" t="n">
-        <v>0.7338710000000001</v>
+        <v>0.7387860000000001</v>
       </c>
     </row>
     <row r="102">
@@ -1740,10 +1740,10 @@
         </is>
       </c>
       <c r="B102" t="n">
-        <v>0.028186</v>
+        <v>0.027355</v>
       </c>
       <c r="C102" t="n">
-        <v>0.731183</v>
+        <v>0.736148</v>
       </c>
     </row>
     <row r="103">
@@ -1753,10 +1753,10 @@
         </is>
       </c>
       <c r="B103" t="n">
-        <v>0.028398</v>
+        <v>0.028098</v>
       </c>
       <c r="C103" t="n">
-        <v>0.728495</v>
+        <v>0.733509</v>
       </c>
     </row>
     <row r="104">
@@ -1766,10 +1766,10 @@
         </is>
       </c>
       <c r="B104" t="n">
-        <v>0.028421</v>
+        <v>0.028186</v>
       </c>
       <c r="C104" t="n">
-        <v>0.725806</v>
+        <v>0.730871</v>
       </c>
     </row>
     <row r="105">
@@ -1779,10 +1779,10 @@
         </is>
       </c>
       <c r="B105" t="n">
-        <v>0.029071</v>
+        <v>0.028375</v>
       </c>
       <c r="C105" t="n">
-        <v>0.723118</v>
+        <v>0.728232</v>
       </c>
     </row>
     <row r="106">
@@ -1792,10 +1792,10 @@
         </is>
       </c>
       <c r="B106" t="n">
-        <v>0.029588</v>
+        <v>0.029071</v>
       </c>
       <c r="C106" t="n">
-        <v>0.72043</v>
+        <v>0.725594</v>
       </c>
     </row>
     <row r="107">
@@ -1805,10 +1805,10 @@
         </is>
       </c>
       <c r="B107" t="n">
-        <v>0.030158</v>
+        <v>0.029588</v>
       </c>
       <c r="C107" t="n">
-        <v>0.717742</v>
+        <v>0.722955</v>
       </c>
     </row>
     <row r="108">
@@ -1818,10 +1818,10 @@
         </is>
       </c>
       <c r="B108" t="n">
-        <v>0.030201</v>
+        <v>0.029854</v>
       </c>
       <c r="C108" t="n">
-        <v>0.715054</v>
+        <v>0.720317</v>
       </c>
     </row>
     <row r="109">
@@ -1831,10 +1831,10 @@
         </is>
       </c>
       <c r="B109" t="n">
-        <v>0.03027</v>
+        <v>0.030158</v>
       </c>
       <c r="C109" t="n">
-        <v>0.7123660000000001</v>
+        <v>0.717678</v>
       </c>
     </row>
     <row r="110">
@@ -1844,10 +1844,10 @@
         </is>
       </c>
       <c r="B110" t="n">
-        <v>0.030697</v>
+        <v>0.030201</v>
       </c>
       <c r="C110" t="n">
-        <v>0.709677</v>
+        <v>0.71504</v>
       </c>
     </row>
     <row r="111">
@@ -1857,10 +1857,10 @@
         </is>
       </c>
       <c r="B111" t="n">
-        <v>0.030903</v>
+        <v>0.03027</v>
       </c>
       <c r="C111" t="n">
-        <v>0.706989</v>
+        <v>0.712401</v>
       </c>
     </row>
     <row r="112">
@@ -1870,10 +1870,10 @@
         </is>
       </c>
       <c r="B112" t="n">
-        <v>0.031127</v>
+        <v>0.030697</v>
       </c>
       <c r="C112" t="n">
-        <v>0.704301</v>
+        <v>0.709763</v>
       </c>
     </row>
     <row r="113">
@@ -1883,10 +1883,10 @@
         </is>
       </c>
       <c r="B113" t="n">
-        <v>0.031327</v>
+        <v>0.030903</v>
       </c>
       <c r="C113" t="n">
-        <v>0.701613</v>
+        <v>0.707124</v>
       </c>
     </row>
     <row r="114">
@@ -1896,10 +1896,10 @@
         </is>
       </c>
       <c r="B114" t="n">
-        <v>0.031556</v>
+        <v>0.031116</v>
       </c>
       <c r="C114" t="n">
-        <v>0.698925</v>
+        <v>0.704485</v>
       </c>
     </row>
     <row r="115">
@@ -1909,10 +1909,10 @@
         </is>
       </c>
       <c r="B115" t="n">
-        <v>0.031969</v>
+        <v>0.031127</v>
       </c>
       <c r="C115" t="n">
-        <v>0.696237</v>
+        <v>0.701847</v>
       </c>
     </row>
     <row r="116">
@@ -1922,10 +1922,10 @@
         </is>
       </c>
       <c r="B116" t="n">
-        <v>0.032827</v>
+        <v>0.031327</v>
       </c>
       <c r="C116" t="n">
-        <v>0.6935480000000001</v>
+        <v>0.6992080000000001</v>
       </c>
     </row>
     <row r="117">
@@ -1935,10 +1935,10 @@
         </is>
       </c>
       <c r="B117" t="n">
-        <v>0.033315</v>
+        <v>0.031556</v>
       </c>
       <c r="C117" t="n">
-        <v>0.69086</v>
+        <v>0.69657</v>
       </c>
     </row>
     <row r="118">
@@ -1948,10 +1948,10 @@
         </is>
       </c>
       <c r="B118" t="n">
-        <v>0.033373</v>
+        <v>0.031969</v>
       </c>
       <c r="C118" t="n">
-        <v>0.688172</v>
+        <v>0.693931</v>
       </c>
     </row>
     <row r="119">
@@ -1961,10 +1961,10 @@
         </is>
       </c>
       <c r="B119" t="n">
-        <v>0.033481</v>
+        <v>0.032545</v>
       </c>
       <c r="C119" t="n">
-        <v>0.685484</v>
+        <v>0.691293</v>
       </c>
     </row>
     <row r="120">
@@ -1974,10 +1974,10 @@
         </is>
       </c>
       <c r="B120" t="n">
-        <v>0.03374</v>
+        <v>0.032827</v>
       </c>
       <c r="C120" t="n">
-        <v>0.682796</v>
+        <v>0.688654</v>
       </c>
     </row>
     <row r="121">
@@ -1987,10 +1987,10 @@
         </is>
       </c>
       <c r="B121" t="n">
-        <v>0.033774</v>
+        <v>0.033373</v>
       </c>
       <c r="C121" t="n">
-        <v>0.680108</v>
+        <v>0.686016</v>
       </c>
     </row>
     <row r="122">
@@ -2000,10 +2000,10 @@
         </is>
       </c>
       <c r="B122" t="n">
-        <v>0.033884</v>
+        <v>0.033481</v>
       </c>
       <c r="C122" t="n">
-        <v>0.677419</v>
+        <v>0.683377</v>
       </c>
     </row>
     <row r="123">
@@ -2013,10 +2013,10 @@
         </is>
       </c>
       <c r="B123" t="n">
-        <v>0.034047</v>
+        <v>0.033774</v>
       </c>
       <c r="C123" t="n">
-        <v>0.674731</v>
+        <v>0.680739</v>
       </c>
     </row>
     <row r="124">
@@ -2026,10 +2026,10 @@
         </is>
       </c>
       <c r="B124" t="n">
-        <v>0.034274</v>
+        <v>0.033884</v>
       </c>
       <c r="C124" t="n">
-        <v>0.6720429999999999</v>
+        <v>0.6781</v>
       </c>
     </row>
     <row r="125">
@@ -2039,10 +2039,10 @@
         </is>
       </c>
       <c r="B125" t="n">
-        <v>0.035039</v>
+        <v>0.034047</v>
       </c>
       <c r="C125" t="n">
-        <v>0.669355</v>
+        <v>0.675462</v>
       </c>
     </row>
     <row r="126">
@@ -2052,10 +2052,10 @@
         </is>
       </c>
       <c r="B126" t="n">
-        <v>0.035117</v>
+        <v>0.034274</v>
       </c>
       <c r="C126" t="n">
-        <v>0.666667</v>
+        <v>0.6728229999999999</v>
       </c>
     </row>
     <row r="127">
@@ -2065,10 +2065,10 @@
         </is>
       </c>
       <c r="B127" t="n">
-        <v>0.035159</v>
+        <v>0.034573</v>
       </c>
       <c r="C127" t="n">
-        <v>0.663978</v>
+        <v>0.670185</v>
       </c>
     </row>
     <row r="128">
@@ -2078,10 +2078,10 @@
         </is>
       </c>
       <c r="B128" t="n">
-        <v>0.035654</v>
+        <v>0.035039</v>
       </c>
       <c r="C128" t="n">
-        <v>0.66129</v>
+        <v>0.667546</v>
       </c>
     </row>
     <row r="129">
@@ -2091,10 +2091,10 @@
         </is>
       </c>
       <c r="B129" t="n">
-        <v>0.036</v>
+        <v>0.035117</v>
       </c>
       <c r="C129" t="n">
-        <v>0.658602</v>
+        <v>0.6649080000000001</v>
       </c>
     </row>
     <row r="130">
@@ -2104,10 +2104,10 @@
         </is>
       </c>
       <c r="B130" t="n">
-        <v>0.037307</v>
+        <v>0.035159</v>
       </c>
       <c r="C130" t="n">
-        <v>0.655914</v>
+        <v>0.662269</v>
       </c>
     </row>
     <row r="131">
@@ -2117,10 +2117,10 @@
         </is>
       </c>
       <c r="B131" t="n">
-        <v>0.037805</v>
+        <v>0.035374</v>
       </c>
       <c r="C131" t="n">
-        <v>0.653226</v>
+        <v>0.659631</v>
       </c>
     </row>
     <row r="132">
@@ -2130,10 +2130,10 @@
         </is>
       </c>
       <c r="B132" t="n">
-        <v>0.03815</v>
+        <v>0.035654</v>
       </c>
       <c r="C132" t="n">
-        <v>0.6505379999999999</v>
+        <v>0.656992</v>
       </c>
     </row>
     <row r="133">
@@ -2143,10 +2143,10 @@
         </is>
       </c>
       <c r="B133" t="n">
-        <v>0.038316</v>
+        <v>0.036</v>
       </c>
       <c r="C133" t="n">
-        <v>0.647849</v>
+        <v>0.654354</v>
       </c>
     </row>
     <row r="134">
@@ -2156,10 +2156,10 @@
         </is>
       </c>
       <c r="B134" t="n">
-        <v>0.03876</v>
+        <v>0.036242</v>
       </c>
       <c r="C134" t="n">
-        <v>0.645161</v>
+        <v>0.651715</v>
       </c>
     </row>
     <row r="135">
@@ -2169,10 +2169,10 @@
         </is>
       </c>
       <c r="B135" t="n">
-        <v>0.039595</v>
+        <v>0.037307</v>
       </c>
       <c r="C135" t="n">
-        <v>0.642473</v>
+        <v>0.649077</v>
       </c>
     </row>
     <row r="136">
@@ -2182,10 +2182,10 @@
         </is>
       </c>
       <c r="B136" t="n">
-        <v>0.03982</v>
+        <v>0.037805</v>
       </c>
       <c r="C136" t="n">
-        <v>0.639785</v>
+        <v>0.646438</v>
       </c>
     </row>
     <row r="137">
@@ -2195,10 +2195,10 @@
         </is>
       </c>
       <c r="B137" t="n">
-        <v>0.040915</v>
+        <v>0.03815</v>
       </c>
       <c r="C137" t="n">
-        <v>0.637097</v>
+        <v>0.643799</v>
       </c>
     </row>
     <row r="138">
@@ -2208,10 +2208,10 @@
         </is>
       </c>
       <c r="B138" t="n">
-        <v>0.040931</v>
+        <v>0.038316</v>
       </c>
       <c r="C138" t="n">
-        <v>0.634409</v>
+        <v>0.641161</v>
       </c>
     </row>
     <row r="139">
@@ -2221,10 +2221,10 @@
         </is>
       </c>
       <c r="B139" t="n">
-        <v>0.040948</v>
+        <v>0.03876</v>
       </c>
       <c r="C139" t="n">
-        <v>0.6317199999999999</v>
+        <v>0.638522</v>
       </c>
     </row>
     <row r="140">
@@ -2234,10 +2234,10 @@
         </is>
       </c>
       <c r="B140" t="n">
-        <v>0.040975</v>
+        <v>0.039595</v>
       </c>
       <c r="C140" t="n">
-        <v>0.629032</v>
+        <v>0.635884</v>
       </c>
     </row>
     <row r="141">
@@ -2247,10 +2247,10 @@
         </is>
       </c>
       <c r="B141" t="n">
-        <v>0.041132</v>
+        <v>0.03982</v>
       </c>
       <c r="C141" t="n">
-        <v>0.626344</v>
+        <v>0.6332449999999999</v>
       </c>
     </row>
     <row r="142">
@@ -2260,10 +2260,10 @@
         </is>
       </c>
       <c r="B142" t="n">
-        <v>0.041243</v>
+        <v>0.040867</v>
       </c>
       <c r="C142" t="n">
-        <v>0.623656</v>
+        <v>0.630607</v>
       </c>
     </row>
     <row r="143">
@@ -2273,10 +2273,10 @@
         </is>
       </c>
       <c r="B143" t="n">
-        <v>0.041331</v>
+        <v>0.040915</v>
       </c>
       <c r="C143" t="n">
-        <v>0.620968</v>
+        <v>0.627968</v>
       </c>
     </row>
     <row r="144">
@@ -2286,10 +2286,10 @@
         </is>
       </c>
       <c r="B144" t="n">
-        <v>0.041457</v>
+        <v>0.040931</v>
       </c>
       <c r="C144" t="n">
-        <v>0.6182800000000001</v>
+        <v>0.6253300000000001</v>
       </c>
     </row>
     <row r="145">
@@ -2299,10 +2299,10 @@
         </is>
       </c>
       <c r="B145" t="n">
-        <v>0.04197</v>
+        <v>0.040948</v>
       </c>
       <c r="C145" t="n">
-        <v>0.615591</v>
+        <v>0.622691</v>
       </c>
     </row>
     <row r="146">
@@ -2312,10 +2312,10 @@
         </is>
       </c>
       <c r="B146" t="n">
-        <v>0.042735</v>
+        <v>0.041019</v>
       </c>
       <c r="C146" t="n">
-        <v>0.612903</v>
+        <v>0.620053</v>
       </c>
     </row>
     <row r="147">
@@ -2325,10 +2325,10 @@
         </is>
       </c>
       <c r="B147" t="n">
-        <v>0.043144</v>
+        <v>0.041132</v>
       </c>
       <c r="C147" t="n">
-        <v>0.610215</v>
+        <v>0.617414</v>
       </c>
     </row>
     <row r="148">
@@ -2338,10 +2338,10 @@
         </is>
       </c>
       <c r="B148" t="n">
-        <v>0.043468</v>
+        <v>0.041331</v>
       </c>
       <c r="C148" t="n">
-        <v>0.607527</v>
+        <v>0.614776</v>
       </c>
     </row>
     <row r="149">
@@ -2351,10 +2351,10 @@
         </is>
       </c>
       <c r="B149" t="n">
-        <v>0.04427</v>
+        <v>0.041359</v>
       </c>
       <c r="C149" t="n">
-        <v>0.604839</v>
+        <v>0.612137</v>
       </c>
     </row>
     <row r="150">
@@ -2364,10 +2364,10 @@
         </is>
       </c>
       <c r="B150" t="n">
-        <v>0.044556</v>
+        <v>0.04197</v>
       </c>
       <c r="C150" t="n">
-        <v>0.602151</v>
+        <v>0.609499</v>
       </c>
     </row>
     <row r="151">
@@ -2377,10 +2377,10 @@
         </is>
       </c>
       <c r="B151" t="n">
-        <v>0.044571</v>
+        <v>0.042735</v>
       </c>
       <c r="C151" t="n">
-        <v>0.5994620000000001</v>
+        <v>0.60686</v>
       </c>
     </row>
     <row r="152">
@@ -2390,10 +2390,10 @@
         </is>
       </c>
       <c r="B152" t="n">
-        <v>0.044773</v>
+        <v>0.043468</v>
       </c>
       <c r="C152" t="n">
-        <v>0.596774</v>
+        <v>0.604222</v>
       </c>
     </row>
     <row r="153">
@@ -2403,10 +2403,10 @@
         </is>
       </c>
       <c r="B153" t="n">
-        <v>0.046486</v>
+        <v>0.044385</v>
       </c>
       <c r="C153" t="n">
-        <v>0.594086</v>
+        <v>0.601583</v>
       </c>
     </row>
     <row r="154">
@@ -2416,10 +2416,10 @@
         </is>
       </c>
       <c r="B154" t="n">
-        <v>0.046763</v>
+        <v>0.044556</v>
       </c>
       <c r="C154" t="n">
-        <v>0.591398</v>
+        <v>0.5989449999999999</v>
       </c>
     </row>
     <row r="155">
@@ -2429,10 +2429,10 @@
         </is>
       </c>
       <c r="B155" t="n">
-        <v>0.046785</v>
+        <v>0.044571</v>
       </c>
       <c r="C155" t="n">
-        <v>0.58871</v>
+        <v>0.596306</v>
       </c>
     </row>
     <row r="156">
@@ -2442,10 +2442,10 @@
         </is>
       </c>
       <c r="B156" t="n">
-        <v>0.046943</v>
+        <v>0.044773</v>
       </c>
       <c r="C156" t="n">
-        <v>0.586022</v>
+        <v>0.593668</v>
       </c>
     </row>
     <row r="157">
@@ -2455,10 +2455,10 @@
         </is>
       </c>
       <c r="B157" t="n">
-        <v>0.047141</v>
+        <v>0.045962</v>
       </c>
       <c r="C157" t="n">
-        <v>0.583333</v>
+        <v>0.591029</v>
       </c>
     </row>
     <row r="158">
@@ -2468,10 +2468,10 @@
         </is>
       </c>
       <c r="B158" t="n">
-        <v>0.047421</v>
+        <v>0.046486</v>
       </c>
       <c r="C158" t="n">
-        <v>0.580645</v>
+        <v>0.588391</v>
       </c>
     </row>
     <row r="159">
@@ -2481,10 +2481,10 @@
         </is>
       </c>
       <c r="B159" t="n">
-        <v>0.047947</v>
+        <v>0.046763</v>
       </c>
       <c r="C159" t="n">
-        <v>0.5779570000000001</v>
+        <v>0.5857520000000001</v>
       </c>
     </row>
     <row r="160">
@@ -2494,10 +2494,10 @@
         </is>
       </c>
       <c r="B160" t="n">
-        <v>0.048746</v>
+        <v>0.046785</v>
       </c>
       <c r="C160" t="n">
-        <v>0.575269</v>
+        <v>0.583113</v>
       </c>
     </row>
     <row r="161">
@@ -2507,10 +2507,10 @@
         </is>
       </c>
       <c r="B161" t="n">
-        <v>0.049358</v>
+        <v>0.046943</v>
       </c>
       <c r="C161" t="n">
-        <v>0.572581</v>
+        <v>0.580475</v>
       </c>
     </row>
     <row r="162">
@@ -2520,10 +2520,10 @@
         </is>
       </c>
       <c r="B162" t="n">
-        <v>0.049478</v>
+        <v>0.047141</v>
       </c>
       <c r="C162" t="n">
-        <v>0.569892</v>
+        <v>0.577836</v>
       </c>
     </row>
     <row r="163">
@@ -2533,10 +2533,10 @@
         </is>
       </c>
       <c r="B163" t="n">
-        <v>0.049673</v>
+        <v>0.047421</v>
       </c>
       <c r="C163" t="n">
-        <v>0.567204</v>
+        <v>0.575198</v>
       </c>
     </row>
     <row r="164">
@@ -2546,10 +2546,10 @@
         </is>
       </c>
       <c r="B164" t="n">
-        <v>0.049728</v>
+        <v>0.047668</v>
       </c>
       <c r="C164" t="n">
-        <v>0.564516</v>
+        <v>0.572559</v>
       </c>
     </row>
     <row r="165">
@@ -2559,10 +2559,10 @@
         </is>
       </c>
       <c r="B165" t="n">
-        <v>0.051151</v>
+        <v>0.048551</v>
       </c>
       <c r="C165" t="n">
-        <v>0.561828</v>
+        <v>0.569921</v>
       </c>
     </row>
     <row r="166">
@@ -2572,10 +2572,10 @@
         </is>
       </c>
       <c r="B166" t="n">
-        <v>0.051423</v>
+        <v>0.048876</v>
       </c>
       <c r="C166" t="n">
-        <v>0.55914</v>
+        <v>0.567282</v>
       </c>
     </row>
     <row r="167">
@@ -2585,10 +2585,10 @@
         </is>
       </c>
       <c r="B167" t="n">
-        <v>0.051449</v>
+        <v>0.04906</v>
       </c>
       <c r="C167" t="n">
-        <v>0.5564519999999999</v>
+        <v>0.564644</v>
       </c>
     </row>
     <row r="168">
@@ -2598,10 +2598,10 @@
         </is>
       </c>
       <c r="B168" t="n">
-        <v>0.051978</v>
+        <v>0.049358</v>
       </c>
       <c r="C168" t="n">
-        <v>0.553763</v>
+        <v>0.562005</v>
       </c>
     </row>
     <row r="169">
@@ -2611,10 +2611,10 @@
         </is>
       </c>
       <c r="B169" t="n">
-        <v>0.052376</v>
+        <v>0.049478</v>
       </c>
       <c r="C169" t="n">
-        <v>0.551075</v>
+        <v>0.5593669999999999</v>
       </c>
     </row>
     <row r="170">
@@ -2624,10 +2624,10 @@
         </is>
       </c>
       <c r="B170" t="n">
-        <v>0.052398</v>
+        <v>0.049516</v>
       </c>
       <c r="C170" t="n">
-        <v>0.548387</v>
+        <v>0.556728</v>
       </c>
     </row>
     <row r="171">
@@ -2637,10 +2637,10 @@
         </is>
       </c>
       <c r="B171" t="n">
-        <v>0.052526</v>
+        <v>0.049728</v>
       </c>
       <c r="C171" t="n">
-        <v>0.545699</v>
+        <v>0.55409</v>
       </c>
     </row>
     <row r="172">
@@ -2650,10 +2650,10 @@
         </is>
       </c>
       <c r="B172" t="n">
-        <v>0.052682</v>
+        <v>0.049754</v>
       </c>
       <c r="C172" t="n">
-        <v>0.543011</v>
+        <v>0.551451</v>
       </c>
     </row>
     <row r="173">
@@ -2663,10 +2663,10 @@
         </is>
       </c>
       <c r="B173" t="n">
-        <v>0.052941</v>
+        <v>0.051151</v>
       </c>
       <c r="C173" t="n">
-        <v>0.540323</v>
+        <v>0.548813</v>
       </c>
     </row>
     <row r="174">
@@ -2676,10 +2676,10 @@
         </is>
       </c>
       <c r="B174" t="n">
-        <v>0.053316</v>
+        <v>0.051264</v>
       </c>
       <c r="C174" t="n">
-        <v>0.5376339999999999</v>
+        <v>0.546174</v>
       </c>
     </row>
     <row r="175">
@@ -2689,10 +2689,10 @@
         </is>
       </c>
       <c r="B175" t="n">
-        <v>0.05382</v>
+        <v>0.051423</v>
       </c>
       <c r="C175" t="n">
-        <v>0.534946</v>
+        <v>0.543536</v>
       </c>
     </row>
     <row r="176">
@@ -2702,10 +2702,10 @@
         </is>
       </c>
       <c r="B176" t="n">
-        <v>0.05439</v>
+        <v>0.051449</v>
       </c>
       <c r="C176" t="n">
-        <v>0.532258</v>
+        <v>0.540897</v>
       </c>
     </row>
     <row r="177">
@@ -2715,10 +2715,10 @@
         </is>
       </c>
       <c r="B177" t="n">
-        <v>0.054595</v>
+        <v>0.051978</v>
       </c>
       <c r="C177" t="n">
-        <v>0.52957</v>
+        <v>0.538259</v>
       </c>
     </row>
     <row r="178">
@@ -2728,10 +2728,10 @@
         </is>
       </c>
       <c r="B178" t="n">
-        <v>0.05496</v>
+        <v>0.052376</v>
       </c>
       <c r="C178" t="n">
-        <v>0.526882</v>
+        <v>0.53562</v>
       </c>
     </row>
     <row r="179">
@@ -2741,10 +2741,10 @@
         </is>
       </c>
       <c r="B179" t="n">
-        <v>0.0555</v>
+        <v>0.052398</v>
       </c>
       <c r="C179" t="n">
-        <v>0.524194</v>
+        <v>0.532982</v>
       </c>
     </row>
     <row r="180">
@@ -2754,10 +2754,10 @@
         </is>
       </c>
       <c r="B180" t="n">
-        <v>0.055621</v>
+        <v>0.052682</v>
       </c>
       <c r="C180" t="n">
-        <v>0.521505</v>
+        <v>0.530343</v>
       </c>
     </row>
     <row r="181">
@@ -2767,10 +2767,10 @@
         </is>
       </c>
       <c r="B181" t="n">
-        <v>0.056242</v>
+        <v>0.052941</v>
       </c>
       <c r="C181" t="n">
-        <v>0.518817</v>
+        <v>0.527704</v>
       </c>
     </row>
     <row r="182">
@@ -2780,10 +2780,10 @@
         </is>
       </c>
       <c r="B182" t="n">
-        <v>0.056487</v>
+        <v>0.053227</v>
       </c>
       <c r="C182" t="n">
-        <v>0.5161289999999999</v>
+        <v>0.525066</v>
       </c>
     </row>
     <row r="183">
@@ -2793,10 +2793,10 @@
         </is>
       </c>
       <c r="B183" t="n">
-        <v>0.056702</v>
+        <v>0.053316</v>
       </c>
       <c r="C183" t="n">
-        <v>0.513441</v>
+        <v>0.522427</v>
       </c>
     </row>
     <row r="184">
@@ -2806,10 +2806,10 @@
         </is>
       </c>
       <c r="B184" t="n">
-        <v>0.056785</v>
+        <v>0.053555</v>
       </c>
       <c r="C184" t="n">
-        <v>0.510753</v>
+        <v>0.5197889999999999</v>
       </c>
     </row>
     <row r="185">
@@ -2819,10 +2819,10 @@
         </is>
       </c>
       <c r="B185" t="n">
-        <v>0.057135</v>
+        <v>0.05382</v>
       </c>
       <c r="C185" t="n">
-        <v>0.508065</v>
+        <v>0.51715</v>
       </c>
     </row>
     <row r="186">
@@ -2832,10 +2832,10 @@
         </is>
       </c>
       <c r="B186" t="n">
-        <v>0.057253</v>
+        <v>0.05439</v>
       </c>
       <c r="C186" t="n">
-        <v>0.505376</v>
+        <v>0.514512</v>
       </c>
     </row>
     <row r="187">
@@ -2845,10 +2845,10 @@
         </is>
       </c>
       <c r="B187" t="n">
-        <v>0.05854</v>
+        <v>0.054595</v>
       </c>
       <c r="C187" t="n">
-        <v>0.502688</v>
+        <v>0.511873</v>
       </c>
     </row>
     <row r="188">
@@ -2858,10 +2858,10 @@
         </is>
       </c>
       <c r="B188" t="n">
-        <v>0.058836</v>
+        <v>0.05496</v>
       </c>
       <c r="C188" t="n">
-        <v>0.5</v>
+        <v>0.509235</v>
       </c>
     </row>
     <row r="189">
@@ -2871,10 +2871,10 @@
         </is>
       </c>
       <c r="B189" t="n">
-        <v>0.059279</v>
+        <v>0.0555</v>
       </c>
       <c r="C189" t="n">
-        <v>0.497312</v>
+        <v>0.506596</v>
       </c>
     </row>
     <row r="190">
@@ -2884,10 +2884,10 @@
         </is>
       </c>
       <c r="B190" t="n">
-        <v>0.059323</v>
+        <v>0.055621</v>
       </c>
       <c r="C190" t="n">
-        <v>0.494624</v>
+        <v>0.503958</v>
       </c>
     </row>
     <row r="191">
@@ -2897,10 +2897,10 @@
         </is>
       </c>
       <c r="B191" t="n">
-        <v>0.059367</v>
+        <v>0.055736</v>
       </c>
       <c r="C191" t="n">
-        <v>0.491935</v>
+        <v>0.501319</v>
       </c>
     </row>
     <row r="192">
@@ -2910,10 +2910,10 @@
         </is>
       </c>
       <c r="B192" t="n">
-        <v>0.059553</v>
+        <v>0.056242</v>
       </c>
       <c r="C192" t="n">
-        <v>0.489247</v>
+        <v>0.498681</v>
       </c>
     </row>
     <row r="193">
@@ -2923,10 +2923,10 @@
         </is>
       </c>
       <c r="B193" t="n">
-        <v>0.059579</v>
+        <v>0.056433</v>
       </c>
       <c r="C193" t="n">
-        <v>0.486559</v>
+        <v>0.496042</v>
       </c>
     </row>
     <row r="194">
@@ -2936,10 +2936,10 @@
         </is>
       </c>
       <c r="B194" t="n">
-        <v>0.060111</v>
+        <v>0.056487</v>
       </c>
       <c r="C194" t="n">
-        <v>0.483871</v>
+        <v>0.493404</v>
       </c>
     </row>
     <row r="195">
@@ -2949,10 +2949,10 @@
         </is>
       </c>
       <c r="B195" t="n">
-        <v>0.060827</v>
+        <v>0.056702</v>
       </c>
       <c r="C195" t="n">
-        <v>0.481183</v>
+        <v>0.490765</v>
       </c>
     </row>
     <row r="196">
@@ -2962,10 +2962,10 @@
         </is>
       </c>
       <c r="B196" t="n">
-        <v>0.061784</v>
+        <v>0.056785</v>
       </c>
       <c r="C196" t="n">
-        <v>0.478495</v>
+        <v>0.488127</v>
       </c>
     </row>
     <row r="197">
@@ -2975,10 +2975,10 @@
         </is>
       </c>
       <c r="B197" t="n">
-        <v>0.06179</v>
+        <v>0.05854</v>
       </c>
       <c r="C197" t="n">
-        <v>0.475806</v>
+        <v>0.485488</v>
       </c>
     </row>
     <row r="198">
@@ -2988,10 +2988,10 @@
         </is>
       </c>
       <c r="B198" t="n">
-        <v>0.061969</v>
+        <v>0.058745</v>
       </c>
       <c r="C198" t="n">
-        <v>0.473118</v>
+        <v>0.48285</v>
       </c>
     </row>
     <row r="199">
@@ -3001,10 +3001,10 @@
         </is>
       </c>
       <c r="B199" t="n">
-        <v>0.062129</v>
+        <v>0.058836</v>
       </c>
       <c r="C199" t="n">
-        <v>0.47043</v>
+        <v>0.480211</v>
       </c>
     </row>
     <row r="200">
@@ -3014,10 +3014,10 @@
         </is>
       </c>
       <c r="B200" t="n">
-        <v>0.06263299999999999</v>
+        <v>0.059279</v>
       </c>
       <c r="C200" t="n">
-        <v>0.467742</v>
+        <v>0.477573</v>
       </c>
     </row>
     <row r="201">
@@ -3027,10 +3027,10 @@
         </is>
       </c>
       <c r="B201" t="n">
-        <v>0.063808</v>
+        <v>0.059367</v>
       </c>
       <c r="C201" t="n">
-        <v>0.465054</v>
+        <v>0.474934</v>
       </c>
     </row>
     <row r="202">
@@ -3040,10 +3040,10 @@
         </is>
       </c>
       <c r="B202" t="n">
-        <v>0.06464300000000001</v>
+        <v>0.059553</v>
       </c>
       <c r="C202" t="n">
-        <v>0.462366</v>
+        <v>0.472296</v>
       </c>
     </row>
     <row r="203">
@@ -3053,10 +3053,10 @@
         </is>
       </c>
       <c r="B203" t="n">
-        <v>0.06555900000000001</v>
+        <v>0.059579</v>
       </c>
       <c r="C203" t="n">
-        <v>0.459677</v>
+        <v>0.469657</v>
       </c>
     </row>
     <row r="204">
@@ -3066,10 +3066,10 @@
         </is>
       </c>
       <c r="B204" t="n">
-        <v>0.066775</v>
+        <v>0.060111</v>
       </c>
       <c r="C204" t="n">
-        <v>0.456989</v>
+        <v>0.467018</v>
       </c>
     </row>
     <row r="205">
@@ -3079,10 +3079,10 @@
         </is>
       </c>
       <c r="B205" t="n">
-        <v>0.066914</v>
+        <v>0.060827</v>
       </c>
       <c r="C205" t="n">
-        <v>0.454301</v>
+        <v>0.46438</v>
       </c>
     </row>
     <row r="206">
@@ -3092,10 +3092,10 @@
         </is>
       </c>
       <c r="B206" t="n">
-        <v>0.067176</v>
+        <v>0.060882</v>
       </c>
       <c r="C206" t="n">
-        <v>0.451613</v>
+        <v>0.461741</v>
       </c>
     </row>
     <row r="207">
@@ -3105,10 +3105,10 @@
         </is>
       </c>
       <c r="B207" t="n">
-        <v>0.06736399999999999</v>
+        <v>0.061712</v>
       </c>
       <c r="C207" t="n">
-        <v>0.448925</v>
+        <v>0.459103</v>
       </c>
     </row>
     <row r="208">
@@ -3118,10 +3118,10 @@
         </is>
       </c>
       <c r="B208" t="n">
-        <v>0.067555</v>
+        <v>0.061784</v>
       </c>
       <c r="C208" t="n">
-        <v>0.446237</v>
+        <v>0.456464</v>
       </c>
     </row>
     <row r="209">
@@ -3131,10 +3131,10 @@
         </is>
       </c>
       <c r="B209" t="n">
-        <v>0.067604</v>
+        <v>0.06179</v>
       </c>
       <c r="C209" t="n">
-        <v>0.443548</v>
+        <v>0.453826</v>
       </c>
     </row>
     <row r="210">
@@ -3144,10 +3144,10 @@
         </is>
       </c>
       <c r="B210" t="n">
-        <v>0.067644</v>
+        <v>0.061969</v>
       </c>
       <c r="C210" t="n">
-        <v>0.44086</v>
+        <v>0.451187</v>
       </c>
     </row>
     <row r="211">
@@ -3157,10 +3157,10 @@
         </is>
       </c>
       <c r="B211" t="n">
-        <v>0.068111</v>
+        <v>0.062129</v>
       </c>
       <c r="C211" t="n">
-        <v>0.438172</v>
+        <v>0.448549</v>
       </c>
     </row>
     <row r="212">
@@ -3170,10 +3170,10 @@
         </is>
       </c>
       <c r="B212" t="n">
-        <v>0.068601</v>
+        <v>0.062168</v>
       </c>
       <c r="C212" t="n">
-        <v>0.435484</v>
+        <v>0.44591</v>
       </c>
     </row>
     <row r="213">
@@ -3183,10 +3183,10 @@
         </is>
       </c>
       <c r="B213" t="n">
-        <v>0.06904200000000001</v>
+        <v>0.062246</v>
       </c>
       <c r="C213" t="n">
-        <v>0.432796</v>
+        <v>0.443272</v>
       </c>
     </row>
     <row r="214">
@@ -3196,10 +3196,10 @@
         </is>
       </c>
       <c r="B214" t="n">
-        <v>0.06909</v>
+        <v>0.06263299999999999</v>
       </c>
       <c r="C214" t="n">
-        <v>0.430108</v>
+        <v>0.440633</v>
       </c>
     </row>
     <row r="215">
@@ -3209,10 +3209,10 @@
         </is>
       </c>
       <c r="B215" t="n">
-        <v>0.069253</v>
+        <v>0.062844</v>
       </c>
       <c r="C215" t="n">
-        <v>0.427419</v>
+        <v>0.437995</v>
       </c>
     </row>
     <row r="216">
@@ -3222,10 +3222,10 @@
         </is>
       </c>
       <c r="B216" t="n">
-        <v>0.070214</v>
+        <v>0.063808</v>
       </c>
       <c r="C216" t="n">
-        <v>0.424731</v>
+        <v>0.435356</v>
       </c>
     </row>
     <row r="217">
@@ -3235,10 +3235,10 @@
         </is>
       </c>
       <c r="B217" t="n">
-        <v>0.070659</v>
+        <v>0.06464300000000001</v>
       </c>
       <c r="C217" t="n">
-        <v>0.422043</v>
+        <v>0.432718</v>
       </c>
     </row>
     <row r="218">
@@ -3248,10 +3248,10 @@
         </is>
       </c>
       <c r="B218" t="n">
-        <v>0.072684</v>
+        <v>0.06555900000000001</v>
       </c>
       <c r="C218" t="n">
-        <v>0.419355</v>
+        <v>0.430079</v>
       </c>
     </row>
     <row r="219">
@@ -3261,10 +3261,10 @@
         </is>
       </c>
       <c r="B219" t="n">
-        <v>0.072744</v>
+        <v>0.067176</v>
       </c>
       <c r="C219" t="n">
-        <v>0.416667</v>
+        <v>0.427441</v>
       </c>
     </row>
     <row r="220">
@@ -3274,10 +3274,10 @@
         </is>
       </c>
       <c r="B220" t="n">
-        <v>0.07295599999999999</v>
+        <v>0.06736399999999999</v>
       </c>
       <c r="C220" t="n">
-        <v>0.413978</v>
+        <v>0.424802</v>
       </c>
     </row>
     <row r="221">
@@ -3287,10 +3287,10 @@
         </is>
       </c>
       <c r="B221" t="n">
-        <v>0.07331</v>
+        <v>0.067375</v>
       </c>
       <c r="C221" t="n">
-        <v>0.41129</v>
+        <v>0.422164</v>
       </c>
     </row>
     <row r="222">
@@ -3300,10 +3300,10 @@
         </is>
       </c>
       <c r="B222" t="n">
-        <v>0.07380299999999999</v>
+        <v>0.067555</v>
       </c>
       <c r="C222" t="n">
-        <v>0.408602</v>
+        <v>0.419525</v>
       </c>
     </row>
     <row r="223">
@@ -3313,10 +3313,10 @@
         </is>
       </c>
       <c r="B223" t="n">
-        <v>0.07424799999999999</v>
+        <v>0.067604</v>
       </c>
       <c r="C223" t="n">
-        <v>0.405914</v>
+        <v>0.416887</v>
       </c>
     </row>
     <row r="224">
@@ -3326,10 +3326,10 @@
         </is>
       </c>
       <c r="B224" t="n">
-        <v>0.07437100000000001</v>
+        <v>0.067644</v>
       </c>
       <c r="C224" t="n">
-        <v>0.403226</v>
+        <v>0.414248</v>
       </c>
     </row>
     <row r="225">
@@ -3339,10 +3339,10 @@
         </is>
       </c>
       <c r="B225" t="n">
-        <v>0.075876</v>
+        <v>0.068111</v>
       </c>
       <c r="C225" t="n">
-        <v>0.400538</v>
+        <v>0.411609</v>
       </c>
     </row>
     <row r="226">
@@ -3352,10 +3352,10 @@
         </is>
       </c>
       <c r="B226" t="n">
-        <v>0.07708</v>
+        <v>0.068601</v>
       </c>
       <c r="C226" t="n">
-        <v>0.397849</v>
+        <v>0.408971</v>
       </c>
     </row>
     <row r="227">
@@ -3365,10 +3365,10 @@
         </is>
       </c>
       <c r="B227" t="n">
-        <v>0.07757799999999999</v>
+        <v>0.068939</v>
       </c>
       <c r="C227" t="n">
-        <v>0.395161</v>
+        <v>0.406332</v>
       </c>
     </row>
     <row r="228">
@@ -3378,10 +3378,10 @@
         </is>
       </c>
       <c r="B228" t="n">
-        <v>0.07779700000000001</v>
+        <v>0.06909</v>
       </c>
       <c r="C228" t="n">
-        <v>0.392473</v>
+        <v>0.403694</v>
       </c>
     </row>
     <row r="229">
@@ -3391,10 +3391,10 @@
         </is>
       </c>
       <c r="B229" t="n">
-        <v>0.077863</v>
+        <v>0.069253</v>
       </c>
       <c r="C229" t="n">
-        <v>0.389785</v>
+        <v>0.401055</v>
       </c>
     </row>
     <row r="230">
@@ -3404,10 +3404,10 @@
         </is>
       </c>
       <c r="B230" t="n">
-        <v>0.07921499999999999</v>
+        <v>0.070214</v>
       </c>
       <c r="C230" t="n">
-        <v>0.387097</v>
+        <v>0.398417</v>
       </c>
     </row>
     <row r="231">
@@ -3417,10 +3417,10 @@
         </is>
       </c>
       <c r="B231" t="n">
-        <v>0.079239</v>
+        <v>0.070659</v>
       </c>
       <c r="C231" t="n">
-        <v>0.384409</v>
+        <v>0.395778</v>
       </c>
     </row>
     <row r="232">
@@ -3430,10 +3430,10 @@
         </is>
       </c>
       <c r="B232" t="n">
-        <v>0.081758</v>
+        <v>0.071394</v>
       </c>
       <c r="C232" t="n">
-        <v>0.38172</v>
+        <v>0.39314</v>
       </c>
     </row>
     <row r="233">
@@ -3443,10 +3443,10 @@
         </is>
       </c>
       <c r="B233" t="n">
-        <v>0.08192000000000001</v>
+        <v>0.072684</v>
       </c>
       <c r="C233" t="n">
-        <v>0.379032</v>
+        <v>0.390501</v>
       </c>
     </row>
     <row r="234">
@@ -3456,10 +3456,10 @@
         </is>
       </c>
       <c r="B234" t="n">
-        <v>0.082479</v>
+        <v>0.072744</v>
       </c>
       <c r="C234" t="n">
-        <v>0.376344</v>
+        <v>0.387863</v>
       </c>
     </row>
     <row r="235">
@@ -3469,10 +3469,10 @@
         </is>
       </c>
       <c r="B235" t="n">
-        <v>0.08254300000000001</v>
+        <v>0.07295599999999999</v>
       </c>
       <c r="C235" t="n">
-        <v>0.373656</v>
+        <v>0.385224</v>
       </c>
     </row>
     <row r="236">
@@ -3482,10 +3482,10 @@
         </is>
       </c>
       <c r="B236" t="n">
-        <v>0.08294600000000001</v>
+        <v>0.07331</v>
       </c>
       <c r="C236" t="n">
-        <v>0.370968</v>
+        <v>0.382586</v>
       </c>
     </row>
     <row r="237">
@@ -3495,10 +3495,10 @@
         </is>
       </c>
       <c r="B237" t="n">
-        <v>0.08384800000000001</v>
+        <v>0.07380299999999999</v>
       </c>
       <c r="C237" t="n">
-        <v>0.36828</v>
+        <v>0.379947</v>
       </c>
     </row>
     <row r="238">
@@ -3508,10 +3508,10 @@
         </is>
       </c>
       <c r="B238" t="n">
-        <v>0.084221</v>
+        <v>0.07424799999999999</v>
       </c>
       <c r="C238" t="n">
-        <v>0.365591</v>
+        <v>0.377309</v>
       </c>
     </row>
     <row r="239">
@@ -3521,10 +3521,10 @@
         </is>
       </c>
       <c r="B239" t="n">
-        <v>0.08483599999999999</v>
+        <v>0.07437100000000001</v>
       </c>
       <c r="C239" t="n">
-        <v>0.362903</v>
+        <v>0.37467</v>
       </c>
     </row>
     <row r="240">
@@ -3534,10 +3534,10 @@
         </is>
       </c>
       <c r="B240" t="n">
-        <v>0.08586199999999999</v>
+        <v>0.075854</v>
       </c>
       <c r="C240" t="n">
-        <v>0.360215</v>
+        <v>0.372032</v>
       </c>
     </row>
     <row r="241">
@@ -3547,10 +3547,10 @@
         </is>
       </c>
       <c r="B241" t="n">
-        <v>0.087156</v>
+        <v>0.075876</v>
       </c>
       <c r="C241" t="n">
-        <v>0.357527</v>
+        <v>0.369393</v>
       </c>
     </row>
     <row r="242">
@@ -3560,10 +3560,10 @@
         </is>
       </c>
       <c r="B242" t="n">
-        <v>0.08717999999999999</v>
+        <v>0.076543</v>
       </c>
       <c r="C242" t="n">
-        <v>0.354839</v>
+        <v>0.366755</v>
       </c>
     </row>
     <row r="243">
@@ -3573,10 +3573,10 @@
         </is>
       </c>
       <c r="B243" t="n">
-        <v>0.088464</v>
+        <v>0.07708</v>
       </c>
       <c r="C243" t="n">
-        <v>0.352151</v>
+        <v>0.364116</v>
       </c>
     </row>
     <row r="244">
@@ -3586,10 +3586,10 @@
         </is>
       </c>
       <c r="B244" t="n">
-        <v>0.088889</v>
+        <v>0.07757799999999999</v>
       </c>
       <c r="C244" t="n">
-        <v>0.349462</v>
+        <v>0.361478</v>
       </c>
     </row>
     <row r="245">
@@ -3599,10 +3599,10 @@
         </is>
       </c>
       <c r="B245" t="n">
-        <v>0.08917700000000001</v>
+        <v>0.077863</v>
       </c>
       <c r="C245" t="n">
-        <v>0.346774</v>
+        <v>0.358839</v>
       </c>
     </row>
     <row r="246">
@@ -3612,10 +3612,10 @@
         </is>
       </c>
       <c r="B246" t="n">
-        <v>0.089823</v>
+        <v>0.077912</v>
       </c>
       <c r="C246" t="n">
-        <v>0.344086</v>
+        <v>0.356201</v>
       </c>
     </row>
     <row r="247">
@@ -3625,10 +3625,10 @@
         </is>
       </c>
       <c r="B247" t="n">
-        <v>0.090265</v>
+        <v>0.07921499999999999</v>
       </c>
       <c r="C247" t="n">
-        <v>0.341398</v>
+        <v>0.353562</v>
       </c>
     </row>
     <row r="248">
@@ -3638,10 +3638,10 @@
         </is>
       </c>
       <c r="B248" t="n">
-        <v>0.090958</v>
+        <v>0.08092199999999999</v>
       </c>
       <c r="C248" t="n">
-        <v>0.33871</v>
+        <v>0.350923</v>
       </c>
     </row>
     <row r="249">
@@ -3651,10 +3651,10 @@
         </is>
       </c>
       <c r="B249" t="n">
-        <v>0.091434</v>
+        <v>0.081607</v>
       </c>
       <c r="C249" t="n">
-        <v>0.336022</v>
+        <v>0.348285</v>
       </c>
     </row>
     <row r="250">
@@ -3664,10 +3664,10 @@
         </is>
       </c>
       <c r="B250" t="n">
-        <v>0.0929</v>
+        <v>0.081758</v>
       </c>
       <c r="C250" t="n">
-        <v>0.333333</v>
+        <v>0.345646</v>
       </c>
     </row>
     <row r="251">
@@ -3677,10 +3677,10 @@
         </is>
       </c>
       <c r="B251" t="n">
-        <v>0.093237</v>
+        <v>0.08192000000000001</v>
       </c>
       <c r="C251" t="n">
-        <v>0.330645</v>
+        <v>0.343008</v>
       </c>
     </row>
     <row r="252">
@@ -3690,10 +3690,10 @@
         </is>
       </c>
       <c r="B252" t="n">
-        <v>0.095842</v>
+        <v>0.082479</v>
       </c>
       <c r="C252" t="n">
-        <v>0.327957</v>
+        <v>0.340369</v>
       </c>
     </row>
     <row r="253">
@@ -3703,10 +3703,10 @@
         </is>
       </c>
       <c r="B253" t="n">
-        <v>0.09630900000000001</v>
+        <v>0.08254300000000001</v>
       </c>
       <c r="C253" t="n">
-        <v>0.325269</v>
+        <v>0.337731</v>
       </c>
     </row>
     <row r="254">
@@ -3716,10 +3716,10 @@
         </is>
       </c>
       <c r="B254" t="n">
-        <v>0.097923</v>
+        <v>0.082594</v>
       </c>
       <c r="C254" t="n">
-        <v>0.322581</v>
+        <v>0.335092</v>
       </c>
     </row>
     <row r="255">
@@ -3729,10 +3729,10 @@
         </is>
       </c>
       <c r="B255" t="n">
-        <v>0.09847400000000001</v>
+        <v>0.083297</v>
       </c>
       <c r="C255" t="n">
-        <v>0.319892</v>
+        <v>0.332454</v>
       </c>
     </row>
     <row r="256">
@@ -3742,10 +3742,10 @@
         </is>
       </c>
       <c r="B256" t="n">
-        <v>0.099063</v>
+        <v>0.08384800000000001</v>
       </c>
       <c r="C256" t="n">
-        <v>0.317204</v>
+        <v>0.329815</v>
       </c>
     </row>
     <row r="257">
@@ -3755,10 +3755,10 @@
         </is>
       </c>
       <c r="B257" t="n">
-        <v>0.09907299999999999</v>
+        <v>0.084221</v>
       </c>
       <c r="C257" t="n">
-        <v>0.314516</v>
+        <v>0.327177</v>
       </c>
     </row>
     <row r="258">
@@ -3768,10 +3768,10 @@
         </is>
       </c>
       <c r="B258" t="n">
-        <v>0.100571</v>
+        <v>0.08483599999999999</v>
       </c>
       <c r="C258" t="n">
-        <v>0.311828</v>
+        <v>0.324538</v>
       </c>
     </row>
     <row r="259">
@@ -3781,10 +3781,10 @@
         </is>
       </c>
       <c r="B259" t="n">
-        <v>0.101335</v>
+        <v>0.08586199999999999</v>
       </c>
       <c r="C259" t="n">
-        <v>0.30914</v>
+        <v>0.3219</v>
       </c>
     </row>
     <row r="260">
@@ -3794,10 +3794,10 @@
         </is>
       </c>
       <c r="B260" t="n">
-        <v>0.10179</v>
+        <v>0.087156</v>
       </c>
       <c r="C260" t="n">
-        <v>0.306452</v>
+        <v>0.319261</v>
       </c>
     </row>
     <row r="261">
@@ -3807,10 +3807,10 @@
         </is>
       </c>
       <c r="B261" t="n">
-        <v>0.101937</v>
+        <v>0.08717999999999999</v>
       </c>
       <c r="C261" t="n">
-        <v>0.303763</v>
+        <v>0.316623</v>
       </c>
     </row>
     <row r="262">
@@ -3820,10 +3820,10 @@
         </is>
       </c>
       <c r="B262" t="n">
-        <v>0.103451</v>
+        <v>0.08820799999999999</v>
       </c>
       <c r="C262" t="n">
-        <v>0.301075</v>
+        <v>0.313984</v>
       </c>
     </row>
     <row r="263">
@@ -3833,10 +3833,10 @@
         </is>
       </c>
       <c r="B263" t="n">
-        <v>0.103942</v>
+        <v>0.088889</v>
       </c>
       <c r="C263" t="n">
-        <v>0.298387</v>
+        <v>0.311346</v>
       </c>
     </row>
     <row r="264">
@@ -3846,10 +3846,10 @@
         </is>
       </c>
       <c r="B264" t="n">
-        <v>0.10427</v>
+        <v>0.08917700000000001</v>
       </c>
       <c r="C264" t="n">
-        <v>0.295699</v>
+        <v>0.308707</v>
       </c>
     </row>
     <row r="265">
@@ -3859,10 +3859,10 @@
         </is>
       </c>
       <c r="B265" t="n">
-        <v>0.105774</v>
+        <v>0.089823</v>
       </c>
       <c r="C265" t="n">
-        <v>0.293011</v>
+        <v>0.306069</v>
       </c>
     </row>
     <row r="266">
@@ -3872,10 +3872,10 @@
         </is>
       </c>
       <c r="B266" t="n">
-        <v>0.106391</v>
+        <v>0.090265</v>
       </c>
       <c r="C266" t="n">
-        <v>0.290323</v>
+        <v>0.30343</v>
       </c>
     </row>
     <row r="267">
@@ -3885,10 +3885,10 @@
         </is>
       </c>
       <c r="B267" t="n">
-        <v>0.106564</v>
+        <v>0.090348</v>
       </c>
       <c r="C267" t="n">
-        <v>0.287634</v>
+        <v>0.300792</v>
       </c>
     </row>
     <row r="268">
@@ -3898,10 +3898,10 @@
         </is>
       </c>
       <c r="B268" t="n">
-        <v>0.106852</v>
+        <v>0.090809</v>
       </c>
       <c r="C268" t="n">
-        <v>0.284946</v>
+        <v>0.298153</v>
       </c>
     </row>
     <row r="269">
@@ -3911,10 +3911,10 @@
         </is>
       </c>
       <c r="B269" t="n">
-        <v>0.107359</v>
+        <v>0.090958</v>
       </c>
       <c r="C269" t="n">
-        <v>0.282258</v>
+        <v>0.295515</v>
       </c>
     </row>
     <row r="270">
@@ -3924,10 +3924,10 @@
         </is>
       </c>
       <c r="B270" t="n">
-        <v>0.109871</v>
+        <v>0.091434</v>
       </c>
       <c r="C270" t="n">
-        <v>0.27957</v>
+        <v>0.292876</v>
       </c>
     </row>
     <row r="271">
@@ -3937,10 +3937,10 @@
         </is>
       </c>
       <c r="B271" t="n">
-        <v>0.110708</v>
+        <v>0.0929</v>
       </c>
       <c r="C271" t="n">
-        <v>0.276882</v>
+        <v>0.290237</v>
       </c>
     </row>
     <row r="272">
@@ -3950,10 +3950,10 @@
         </is>
       </c>
       <c r="B272" t="n">
-        <v>0.111683</v>
+        <v>0.093237</v>
       </c>
       <c r="C272" t="n">
-        <v>0.274194</v>
+        <v>0.287599</v>
       </c>
     </row>
     <row r="273">
@@ -3963,10 +3963,10 @@
         </is>
       </c>
       <c r="B273" t="n">
-        <v>0.112861</v>
+        <v>0.097923</v>
       </c>
       <c r="C273" t="n">
-        <v>0.271505</v>
+        <v>0.28496</v>
       </c>
     </row>
     <row r="274">
@@ -3976,10 +3976,10 @@
         </is>
       </c>
       <c r="B274" t="n">
-        <v>0.11394</v>
+        <v>0.098237</v>
       </c>
       <c r="C274" t="n">
-        <v>0.268817</v>
+        <v>0.282322</v>
       </c>
     </row>
     <row r="275">
@@ -3989,10 +3989,10 @@
         </is>
       </c>
       <c r="B275" t="n">
-        <v>0.114179</v>
+        <v>0.09847400000000001</v>
       </c>
       <c r="C275" t="n">
-        <v>0.266129</v>
+        <v>0.279683</v>
       </c>
     </row>
     <row r="276">
@@ -4002,10 +4002,10 @@
         </is>
       </c>
       <c r="B276" t="n">
-        <v>0.11468</v>
+        <v>0.09907299999999999</v>
       </c>
       <c r="C276" t="n">
-        <v>0.263441</v>
+        <v>0.277045</v>
       </c>
     </row>
     <row r="277">
@@ -4015,10 +4015,10 @@
         </is>
       </c>
       <c r="B277" t="n">
-        <v>0.117496</v>
+        <v>0.100571</v>
       </c>
       <c r="C277" t="n">
-        <v>0.260753</v>
+        <v>0.274406</v>
       </c>
     </row>
     <row r="278">
@@ -4028,10 +4028,10 @@
         </is>
       </c>
       <c r="B278" t="n">
-        <v>0.117846</v>
+        <v>0.101335</v>
       </c>
       <c r="C278" t="n">
-        <v>0.258065</v>
+        <v>0.271768</v>
       </c>
     </row>
     <row r="279">
@@ -4041,10 +4041,10 @@
         </is>
       </c>
       <c r="B279" t="n">
-        <v>0.119464</v>
+        <v>0.101937</v>
       </c>
       <c r="C279" t="n">
-        <v>0.255376</v>
+        <v>0.269129</v>
       </c>
     </row>
     <row r="280">
@@ -4054,10 +4054,10 @@
         </is>
       </c>
       <c r="B280" t="n">
-        <v>0.120351</v>
+        <v>0.103451</v>
       </c>
       <c r="C280" t="n">
-        <v>0.252688</v>
+        <v>0.266491</v>
       </c>
     </row>
     <row r="281">
@@ -4067,10 +4067,10 @@
         </is>
       </c>
       <c r="B281" t="n">
-        <v>0.120448</v>
+        <v>0.103942</v>
       </c>
       <c r="C281" t="n">
-        <v>0.25</v>
+        <v>0.263852</v>
       </c>
     </row>
     <row r="282">
@@ -4080,10 +4080,10 @@
         </is>
       </c>
       <c r="B282" t="n">
-        <v>0.121637</v>
+        <v>0.10427</v>
       </c>
       <c r="C282" t="n">
-        <v>0.247312</v>
+        <v>0.261214</v>
       </c>
     </row>
     <row r="283">
@@ -4093,10 +4093,10 @@
         </is>
       </c>
       <c r="B283" t="n">
-        <v>0.12397</v>
+        <v>0.105774</v>
       </c>
       <c r="C283" t="n">
-        <v>0.244624</v>
+        <v>0.258575</v>
       </c>
     </row>
     <row r="284">
@@ -4106,10 +4106,10 @@
         </is>
       </c>
       <c r="B284" t="n">
-        <v>0.124167</v>
+        <v>0.106391</v>
       </c>
       <c r="C284" t="n">
-        <v>0.241935</v>
+        <v>0.255937</v>
       </c>
     </row>
     <row r="285">
@@ -4119,10 +4119,10 @@
         </is>
       </c>
       <c r="B285" t="n">
-        <v>0.126891</v>
+        <v>0.106564</v>
       </c>
       <c r="C285" t="n">
-        <v>0.239247</v>
+        <v>0.253298</v>
       </c>
     </row>
     <row r="286">
@@ -4132,10 +4132,10 @@
         </is>
       </c>
       <c r="B286" t="n">
-        <v>0.128021</v>
+        <v>0.106852</v>
       </c>
       <c r="C286" t="n">
-        <v>0.236559</v>
+        <v>0.25066</v>
       </c>
     </row>
     <row r="287">
@@ -4145,10 +4145,10 @@
         </is>
       </c>
       <c r="B287" t="n">
-        <v>0.128976</v>
+        <v>0.107359</v>
       </c>
       <c r="C287" t="n">
-        <v>0.233871</v>
+        <v>0.248021</v>
       </c>
     </row>
     <row r="288">
@@ -4158,10 +4158,10 @@
         </is>
       </c>
       <c r="B288" t="n">
-        <v>0.130439</v>
+        <v>0.110708</v>
       </c>
       <c r="C288" t="n">
-        <v>0.231183</v>
+        <v>0.245383</v>
       </c>
     </row>
     <row r="289">
@@ -4171,10 +4171,10 @@
         </is>
       </c>
       <c r="B289" t="n">
-        <v>0.130821</v>
+        <v>0.111683</v>
       </c>
       <c r="C289" t="n">
-        <v>0.228495</v>
+        <v>0.242744</v>
       </c>
     </row>
     <row r="290">
@@ -4184,10 +4184,10 @@
         </is>
       </c>
       <c r="B290" t="n">
-        <v>0.130947</v>
+        <v>0.112861</v>
       </c>
       <c r="C290" t="n">
-        <v>0.225806</v>
+        <v>0.240106</v>
       </c>
     </row>
     <row r="291">
@@ -4197,10 +4197,10 @@
         </is>
       </c>
       <c r="B291" t="n">
-        <v>0.135669</v>
+        <v>0.113263</v>
       </c>
       <c r="C291" t="n">
-        <v>0.223118</v>
+        <v>0.237467</v>
       </c>
     </row>
     <row r="292">
@@ -4210,10 +4210,10 @@
         </is>
       </c>
       <c r="B292" t="n">
-        <v>0.135827</v>
+        <v>0.11394</v>
       </c>
       <c r="C292" t="n">
-        <v>0.22043</v>
+        <v>0.234828</v>
       </c>
     </row>
     <row r="293">
@@ -4223,10 +4223,10 @@
         </is>
       </c>
       <c r="B293" t="n">
-        <v>0.137057</v>
+        <v>0.114179</v>
       </c>
       <c r="C293" t="n">
-        <v>0.217742</v>
+        <v>0.23219</v>
       </c>
     </row>
     <row r="294">
@@ -4236,10 +4236,10 @@
         </is>
       </c>
       <c r="B294" t="n">
-        <v>0.13733</v>
+        <v>0.11468</v>
       </c>
       <c r="C294" t="n">
-        <v>0.215054</v>
+        <v>0.229551</v>
       </c>
     </row>
     <row r="295">
@@ -4249,10 +4249,10 @@
         </is>
       </c>
       <c r="B295" t="n">
-        <v>0.138762</v>
+        <v>0.115972</v>
       </c>
       <c r="C295" t="n">
-        <v>0.212366</v>
+        <v>0.226913</v>
       </c>
     </row>
     <row r="296">
@@ -4262,10 +4262,10 @@
         </is>
       </c>
       <c r="B296" t="n">
-        <v>0.139275</v>
+        <v>0.117496</v>
       </c>
       <c r="C296" t="n">
-        <v>0.209677</v>
+        <v>0.224274</v>
       </c>
     </row>
     <row r="297">
@@ -4275,10 +4275,10 @@
         </is>
       </c>
       <c r="B297" t="n">
-        <v>0.140029</v>
+        <v>0.117846</v>
       </c>
       <c r="C297" t="n">
-        <v>0.206989</v>
+        <v>0.221636</v>
       </c>
     </row>
     <row r="298">
@@ -4288,10 +4288,10 @@
         </is>
       </c>
       <c r="B298" t="n">
-        <v>0.140099</v>
+        <v>0.119464</v>
       </c>
       <c r="C298" t="n">
-        <v>0.204301</v>
+        <v>0.218997</v>
       </c>
     </row>
     <row r="299">
@@ -4301,10 +4301,10 @@
         </is>
       </c>
       <c r="B299" t="n">
-        <v>0.140214</v>
+        <v>0.120351</v>
       </c>
       <c r="C299" t="n">
-        <v>0.201613</v>
+        <v>0.216359</v>
       </c>
     </row>
     <row r="300">
@@ -4314,10 +4314,10 @@
         </is>
       </c>
       <c r="B300" t="n">
-        <v>0.141591</v>
+        <v>0.120448</v>
       </c>
       <c r="C300" t="n">
-        <v>0.198925</v>
+        <v>0.21372</v>
       </c>
     </row>
     <row r="301">
@@ -4327,10 +4327,10 @@
         </is>
       </c>
       <c r="B301" t="n">
-        <v>0.143233</v>
+        <v>0.121637</v>
       </c>
       <c r="C301" t="n">
-        <v>0.196237</v>
+        <v>0.211082</v>
       </c>
     </row>
     <row r="302">
@@ -4340,10 +4340,10 @@
         </is>
       </c>
       <c r="B302" t="n">
-        <v>0.144579</v>
+        <v>0.12397</v>
       </c>
       <c r="C302" t="n">
-        <v>0.193548</v>
+        <v>0.208443</v>
       </c>
     </row>
     <row r="303">
@@ -4353,10 +4353,10 @@
         </is>
       </c>
       <c r="B303" t="n">
-        <v>0.145008</v>
+        <v>0.124167</v>
       </c>
       <c r="C303" t="n">
-        <v>0.19086</v>
+        <v>0.205805</v>
       </c>
     </row>
     <row r="304">
@@ -4366,10 +4366,10 @@
         </is>
       </c>
       <c r="B304" t="n">
-        <v>0.145291</v>
+        <v>0.126891</v>
       </c>
       <c r="C304" t="n">
-        <v>0.188172</v>
+        <v>0.203166</v>
       </c>
     </row>
     <row r="305">
@@ -4379,10 +4379,10 @@
         </is>
       </c>
       <c r="B305" t="n">
-        <v>0.145554</v>
+        <v>0.128021</v>
       </c>
       <c r="C305" t="n">
-        <v>0.185484</v>
+        <v>0.200528</v>
       </c>
     </row>
     <row r="306">
@@ -4392,10 +4392,10 @@
         </is>
       </c>
       <c r="B306" t="n">
-        <v>0.151419</v>
+        <v>0.128976</v>
       </c>
       <c r="C306" t="n">
-        <v>0.182796</v>
+        <v>0.197889</v>
       </c>
     </row>
     <row r="307">
@@ -4405,10 +4405,10 @@
         </is>
       </c>
       <c r="B307" t="n">
-        <v>0.151465</v>
+        <v>0.130439</v>
       </c>
       <c r="C307" t="n">
-        <v>0.180108</v>
+        <v>0.195251</v>
       </c>
     </row>
     <row r="308">
@@ -4418,10 +4418,10 @@
         </is>
       </c>
       <c r="B308" t="n">
-        <v>0.151822</v>
+        <v>0.130821</v>
       </c>
       <c r="C308" t="n">
-        <v>0.177419</v>
+        <v>0.192612</v>
       </c>
     </row>
     <row r="309">
@@ -4431,10 +4431,10 @@
         </is>
       </c>
       <c r="B309" t="n">
-        <v>0.15511</v>
+        <v>0.130916</v>
       </c>
       <c r="C309" t="n">
-        <v>0.174731</v>
+        <v>0.189974</v>
       </c>
     </row>
     <row r="310">
@@ -4444,10 +4444,10 @@
         </is>
       </c>
       <c r="B310" t="n">
-        <v>0.15559</v>
+        <v>0.131209</v>
       </c>
       <c r="C310" t="n">
-        <v>0.172043</v>
+        <v>0.187335</v>
       </c>
     </row>
     <row r="311">
@@ -4457,10 +4457,10 @@
         </is>
       </c>
       <c r="B311" t="n">
-        <v>0.1565</v>
+        <v>0.135669</v>
       </c>
       <c r="C311" t="n">
-        <v>0.169355</v>
+        <v>0.184697</v>
       </c>
     </row>
     <row r="312">
@@ -4470,10 +4470,10 @@
         </is>
       </c>
       <c r="B312" t="n">
-        <v>0.158503</v>
+        <v>0.135827</v>
       </c>
       <c r="C312" t="n">
-        <v>0.166667</v>
+        <v>0.182058</v>
       </c>
     </row>
     <row r="313">
@@ -4483,10 +4483,10 @@
         </is>
       </c>
       <c r="B313" t="n">
-        <v>0.16241</v>
+        <v>0.137023</v>
       </c>
       <c r="C313" t="n">
-        <v>0.163978</v>
+        <v>0.17942</v>
       </c>
     </row>
     <row r="314">
@@ -4496,10 +4496,10 @@
         </is>
       </c>
       <c r="B314" t="n">
-        <v>0.167126</v>
+        <v>0.13733</v>
       </c>
       <c r="C314" t="n">
-        <v>0.16129</v>
+        <v>0.176781</v>
       </c>
     </row>
     <row r="315">
@@ -4509,10 +4509,10 @@
         </is>
       </c>
       <c r="B315" t="n">
-        <v>0.173105</v>
+        <v>0.138762</v>
       </c>
       <c r="C315" t="n">
-        <v>0.158602</v>
+        <v>0.174142</v>
       </c>
     </row>
     <row r="316">
@@ -4522,10 +4522,10 @@
         </is>
       </c>
       <c r="B316" t="n">
-        <v>0.175601</v>
+        <v>0.139275</v>
       </c>
       <c r="C316" t="n">
-        <v>0.155914</v>
+        <v>0.171504</v>
       </c>
     </row>
     <row r="317">
@@ -4535,10 +4535,10 @@
         </is>
       </c>
       <c r="B317" t="n">
-        <v>0.183042</v>
+        <v>0.140029</v>
       </c>
       <c r="C317" t="n">
-        <v>0.153226</v>
+        <v>0.168865</v>
       </c>
     </row>
     <row r="318">
@@ -4548,10 +4548,10 @@
         </is>
       </c>
       <c r="B318" t="n">
-        <v>0.187612</v>
+        <v>0.140099</v>
       </c>
       <c r="C318" t="n">
-        <v>0.150538</v>
+        <v>0.166227</v>
       </c>
     </row>
     <row r="319">
@@ -4561,10 +4561,10 @@
         </is>
       </c>
       <c r="B319" t="n">
-        <v>0.189387</v>
+        <v>0.140214</v>
       </c>
       <c r="C319" t="n">
-        <v>0.147849</v>
+        <v>0.163588</v>
       </c>
     </row>
     <row r="320">
@@ -4574,10 +4574,10 @@
         </is>
       </c>
       <c r="B320" t="n">
-        <v>0.193249</v>
+        <v>0.141914</v>
       </c>
       <c r="C320" t="n">
-        <v>0.145161</v>
+        <v>0.16095</v>
       </c>
     </row>
     <row r="321">
@@ -4587,10 +4587,10 @@
         </is>
       </c>
       <c r="B321" t="n">
-        <v>0.195388</v>
+        <v>0.144579</v>
       </c>
       <c r="C321" t="n">
-        <v>0.142473</v>
+        <v>0.158311</v>
       </c>
     </row>
     <row r="322">
@@ -4600,10 +4600,10 @@
         </is>
       </c>
       <c r="B322" t="n">
-        <v>0.200683</v>
+        <v>0.145008</v>
       </c>
       <c r="C322" t="n">
-        <v>0.139785</v>
+        <v>0.155673</v>
       </c>
     </row>
     <row r="323">
@@ -4613,10 +4613,10 @@
         </is>
       </c>
       <c r="B323" t="n">
-        <v>0.206803</v>
+        <v>0.145291</v>
       </c>
       <c r="C323" t="n">
-        <v>0.137097</v>
+        <v>0.153034</v>
       </c>
     </row>
     <row r="324">
@@ -4626,10 +4626,10 @@
         </is>
       </c>
       <c r="B324" t="n">
-        <v>0.21126</v>
+        <v>0.145554</v>
       </c>
       <c r="C324" t="n">
-        <v>0.134409</v>
+        <v>0.150396</v>
       </c>
     </row>
     <row r="325">
@@ -4639,10 +4639,10 @@
         </is>
       </c>
       <c r="B325" t="n">
-        <v>0.212282</v>
+        <v>0.151419</v>
       </c>
       <c r="C325" t="n">
-        <v>0.13172</v>
+        <v>0.147757</v>
       </c>
     </row>
     <row r="326">
@@ -4652,10 +4652,10 @@
         </is>
       </c>
       <c r="B326" t="n">
-        <v>0.213977</v>
+        <v>0.151465</v>
       </c>
       <c r="C326" t="n">
-        <v>0.129032</v>
+        <v>0.145119</v>
       </c>
     </row>
     <row r="327">
@@ -4665,10 +4665,10 @@
         </is>
       </c>
       <c r="B327" t="n">
-        <v>0.224095</v>
+        <v>0.151822</v>
       </c>
       <c r="C327" t="n">
-        <v>0.126344</v>
+        <v>0.14248</v>
       </c>
     </row>
     <row r="328">
@@ -4678,10 +4678,10 @@
         </is>
       </c>
       <c r="B328" t="n">
-        <v>0.224293</v>
+        <v>0.15511</v>
       </c>
       <c r="C328" t="n">
-        <v>0.123656</v>
+        <v>0.139842</v>
       </c>
     </row>
     <row r="329">
@@ -4691,10 +4691,10 @@
         </is>
       </c>
       <c r="B329" t="n">
-        <v>0.224867</v>
+        <v>0.15559</v>
       </c>
       <c r="C329" t="n">
-        <v>0.120968</v>
+        <v>0.137203</v>
       </c>
     </row>
     <row r="330">
@@ -4704,10 +4704,10 @@
         </is>
       </c>
       <c r="B330" t="n">
-        <v>0.225383</v>
+        <v>0.155726</v>
       </c>
       <c r="C330" t="n">
-        <v>0.11828</v>
+        <v>0.134565</v>
       </c>
     </row>
     <row r="331">
@@ -4717,10 +4717,10 @@
         </is>
       </c>
       <c r="B331" t="n">
-        <v>0.229443</v>
+        <v>0.156434</v>
       </c>
       <c r="C331" t="n">
-        <v>0.115591</v>
+        <v>0.131926</v>
       </c>
     </row>
     <row r="332">
@@ -4730,10 +4730,10 @@
         </is>
       </c>
       <c r="B332" t="n">
-        <v>0.232768</v>
+        <v>0.158503</v>
       </c>
       <c r="C332" t="n">
-        <v>0.112903</v>
+        <v>0.129288</v>
       </c>
     </row>
     <row r="333">
@@ -4743,10 +4743,10 @@
         </is>
       </c>
       <c r="B333" t="n">
-        <v>0.234669</v>
+        <v>0.16241</v>
       </c>
       <c r="C333" t="n">
-        <v>0.110215</v>
+        <v>0.126649</v>
       </c>
     </row>
     <row r="334">
@@ -4756,10 +4756,10 @@
         </is>
       </c>
       <c r="B334" t="n">
-        <v>0.235662</v>
+        <v>0.167126</v>
       </c>
       <c r="C334" t="n">
-        <v>0.107527</v>
+        <v>0.124011</v>
       </c>
     </row>
     <row r="335">
@@ -4769,10 +4769,10 @@
         </is>
       </c>
       <c r="B335" t="n">
-        <v>0.257813</v>
+        <v>0.172262</v>
       </c>
       <c r="C335" t="n">
-        <v>0.104839</v>
+        <v>0.121372</v>
       </c>
     </row>
     <row r="336">
@@ -4782,10 +4782,10 @@
         </is>
       </c>
       <c r="B336" t="n">
-        <v>0.266114</v>
+        <v>0.183042</v>
       </c>
       <c r="C336" t="n">
-        <v>0.102151</v>
+        <v>0.118734</v>
       </c>
     </row>
     <row r="337">
@@ -4795,10 +4795,10 @@
         </is>
       </c>
       <c r="B337" t="n">
-        <v>0.267301</v>
+        <v>0.187612</v>
       </c>
       <c r="C337" t="n">
-        <v>0.09946199999999999</v>
+        <v>0.116095</v>
       </c>
     </row>
     <row r="338">
@@ -4808,10 +4808,10 @@
         </is>
       </c>
       <c r="B338" t="n">
-        <v>0.273424</v>
+        <v>0.189387</v>
       </c>
       <c r="C338" t="n">
-        <v>0.096774</v>
+        <v>0.113456</v>
       </c>
     </row>
     <row r="339">
@@ -4821,10 +4821,10 @@
         </is>
       </c>
       <c r="B339" t="n">
-        <v>0.274371</v>
+        <v>0.193249</v>
       </c>
       <c r="C339" t="n">
-        <v>0.094086</v>
+        <v>0.110818</v>
       </c>
     </row>
     <row r="340">
@@ -4834,10 +4834,10 @@
         </is>
       </c>
       <c r="B340" t="n">
-        <v>0.279391</v>
+        <v>0.195388</v>
       </c>
       <c r="C340" t="n">
-        <v>0.09139799999999999</v>
+        <v>0.108179</v>
       </c>
     </row>
     <row r="341">
@@ -4847,10 +4847,10 @@
         </is>
       </c>
       <c r="B341" t="n">
-        <v>0.28675</v>
+        <v>0.200683</v>
       </c>
       <c r="C341" t="n">
-        <v>0.08871</v>
+        <v>0.105541</v>
       </c>
     </row>
     <row r="342">
@@ -4860,10 +4860,10 @@
         </is>
       </c>
       <c r="B342" t="n">
-        <v>0.292707</v>
+        <v>0.202141</v>
       </c>
       <c r="C342" t="n">
-        <v>0.086022</v>
+        <v>0.102902</v>
       </c>
     </row>
     <row r="343">
@@ -4873,10 +4873,10 @@
         </is>
       </c>
       <c r="B343" t="n">
-        <v>0.295965</v>
+        <v>0.206803</v>
       </c>
       <c r="C343" t="n">
-        <v>0.083333</v>
+        <v>0.100264</v>
       </c>
     </row>
     <row r="344">
@@ -4886,10 +4886,10 @@
         </is>
       </c>
       <c r="B344" t="n">
-        <v>0.303016</v>
+        <v>0.21126</v>
       </c>
       <c r="C344" t="n">
-        <v>0.08064499999999999</v>
+        <v>0.097625</v>
       </c>
     </row>
     <row r="345">
@@ -4899,10 +4899,10 @@
         </is>
       </c>
       <c r="B345" t="n">
-        <v>0.3031</v>
+        <v>0.212282</v>
       </c>
       <c r="C345" t="n">
-        <v>0.077957</v>
+        <v>0.094987</v>
       </c>
     </row>
     <row r="346">
@@ -4912,10 +4912,10 @@
         </is>
       </c>
       <c r="B346" t="n">
-        <v>0.321789</v>
+        <v>0.213977</v>
       </c>
       <c r="C346" t="n">
-        <v>0.075269</v>
+        <v>0.092348</v>
       </c>
     </row>
     <row r="347">
@@ -4925,10 +4925,10 @@
         </is>
       </c>
       <c r="B347" t="n">
-        <v>0.359445</v>
+        <v>0.224095</v>
       </c>
       <c r="C347" t="n">
-        <v>0.07258100000000001</v>
+        <v>0.08971</v>
       </c>
     </row>
     <row r="348">
@@ -4938,10 +4938,10 @@
         </is>
       </c>
       <c r="B348" t="n">
-        <v>0.359851</v>
+        <v>0.229443</v>
       </c>
       <c r="C348" t="n">
-        <v>0.069892</v>
+        <v>0.087071</v>
       </c>
     </row>
     <row r="349">
@@ -4951,10 +4951,10 @@
         </is>
       </c>
       <c r="B349" t="n">
-        <v>0.363732</v>
+        <v>0.235662</v>
       </c>
       <c r="C349" t="n">
-        <v>0.067204</v>
+        <v>0.08443299999999999</v>
       </c>
     </row>
     <row r="350">
@@ -4964,10 +4964,10 @@
         </is>
       </c>
       <c r="B350" t="n">
-        <v>0.364791</v>
+        <v>0.257813</v>
       </c>
       <c r="C350" t="n">
-        <v>0.064516</v>
+        <v>0.08179400000000001</v>
       </c>
     </row>
     <row r="351">
@@ -4977,10 +4977,10 @@
         </is>
       </c>
       <c r="B351" t="n">
-        <v>0.366962</v>
+        <v>0.267282</v>
       </c>
       <c r="C351" t="n">
-        <v>0.061828</v>
+        <v>0.079156</v>
       </c>
     </row>
     <row r="352">
@@ -4990,10 +4990,10 @@
         </is>
       </c>
       <c r="B352" t="n">
-        <v>0.368203</v>
+        <v>0.279391</v>
       </c>
       <c r="C352" t="n">
-        <v>0.05914</v>
+        <v>0.076517</v>
       </c>
     </row>
     <row r="353">
@@ -5003,10 +5003,10 @@
         </is>
       </c>
       <c r="B353" t="n">
-        <v>0.373316</v>
+        <v>0.286735</v>
       </c>
       <c r="C353" t="n">
-        <v>0.056452</v>
+        <v>0.073879</v>
       </c>
     </row>
     <row r="354">
@@ -5016,10 +5016,10 @@
         </is>
       </c>
       <c r="B354" t="n">
-        <v>0.389014</v>
+        <v>0.28675</v>
       </c>
       <c r="C354" t="n">
-        <v>0.053763</v>
+        <v>0.07124</v>
       </c>
     </row>
     <row r="355">
@@ -5029,10 +5029,10 @@
         </is>
       </c>
       <c r="B355" t="n">
-        <v>0.400164</v>
+        <v>0.292707</v>
       </c>
       <c r="C355" t="n">
-        <v>0.051075</v>
+        <v>0.068602</v>
       </c>
     </row>
     <row r="356">
@@ -5042,10 +5042,10 @@
         </is>
       </c>
       <c r="B356" t="n">
-        <v>0.405497</v>
+        <v>0.303016</v>
       </c>
       <c r="C356" t="n">
-        <v>0.048387</v>
+        <v>0.06596299999999999</v>
       </c>
     </row>
     <row r="357">
@@ -5055,10 +5055,10 @@
         </is>
       </c>
       <c r="B357" t="n">
-        <v>0.40983</v>
+        <v>0.35577</v>
       </c>
       <c r="C357" t="n">
-        <v>0.045699</v>
+        <v>0.06332500000000001</v>
       </c>
     </row>
     <row r="358">
@@ -5068,10 +5068,10 @@
         </is>
       </c>
       <c r="B358" t="n">
-        <v>0.438596</v>
+        <v>0.359445</v>
       </c>
       <c r="C358" t="n">
-        <v>0.043011</v>
+        <v>0.060686</v>
       </c>
     </row>
     <row r="359">
@@ -5081,10 +5081,10 @@
         </is>
       </c>
       <c r="B359" t="n">
-        <v>0.440993</v>
+        <v>0.363732</v>
       </c>
       <c r="C359" t="n">
-        <v>0.040323</v>
+        <v>0.058047</v>
       </c>
     </row>
     <row r="360">
@@ -5094,10 +5094,10 @@
         </is>
       </c>
       <c r="B360" t="n">
-        <v>0.454545</v>
+        <v>0.36468</v>
       </c>
       <c r="C360" t="n">
-        <v>0.037634</v>
+        <v>0.055409</v>
       </c>
     </row>
     <row r="361">
@@ -5107,10 +5107,10 @@
         </is>
       </c>
       <c r="B361" t="n">
-        <v>0.46057</v>
+        <v>0.373827</v>
       </c>
       <c r="C361" t="n">
-        <v>0.034946</v>
+        <v>0.05277</v>
       </c>
     </row>
     <row r="362">
@@ -5120,10 +5120,10 @@
         </is>
       </c>
       <c r="B362" t="n">
-        <v>0.476745</v>
+        <v>0.389014</v>
       </c>
       <c r="C362" t="n">
-        <v>0.032258</v>
+        <v>0.050132</v>
       </c>
     </row>
     <row r="363">
@@ -5133,10 +5133,10 @@
         </is>
       </c>
       <c r="B363" t="n">
-        <v>0.605731</v>
+        <v>0.400164</v>
       </c>
       <c r="C363" t="n">
-        <v>0.02957</v>
+        <v>0.047493</v>
       </c>
     </row>
     <row r="364">
@@ -5146,10 +5146,10 @@
         </is>
       </c>
       <c r="B364" t="n">
-        <v>0.634074</v>
+        <v>0.40983</v>
       </c>
       <c r="C364" t="n">
-        <v>0.026882</v>
+        <v>0.044855</v>
       </c>
     </row>
     <row r="365">
@@ -5159,10 +5159,10 @@
         </is>
       </c>
       <c r="B365" t="n">
-        <v>0.648021</v>
+        <v>0.410903</v>
       </c>
       <c r="C365" t="n">
-        <v>0.024194</v>
+        <v>0.042216</v>
       </c>
     </row>
     <row r="366">
@@ -5172,10 +5172,10 @@
         </is>
       </c>
       <c r="B366" t="n">
-        <v>0.672083</v>
+        <v>0.419404</v>
       </c>
       <c r="C366" t="n">
-        <v>0.021505</v>
+        <v>0.039578</v>
       </c>
     </row>
     <row r="367">
@@ -5185,10 +5185,10 @@
         </is>
       </c>
       <c r="B367" t="n">
-        <v>0.678189</v>
+        <v>0.440642</v>
       </c>
       <c r="C367" t="n">
-        <v>0.018817</v>
+        <v>0.036939</v>
       </c>
     </row>
     <row r="368">
@@ -5198,10 +5198,10 @@
         </is>
       </c>
       <c r="B368" t="n">
-        <v>0.707604</v>
+        <v>0.454545</v>
       </c>
       <c r="C368" t="n">
-        <v>0.016129</v>
+        <v>0.034301</v>
       </c>
     </row>
     <row r="369">
@@ -5211,10 +5211,10 @@
         </is>
       </c>
       <c r="B369" t="n">
-        <v>0.711338</v>
+        <v>0.587794</v>
       </c>
       <c r="C369" t="n">
-        <v>0.013441</v>
+        <v>0.031662</v>
       </c>
     </row>
     <row r="370">
@@ -5224,10 +5224,10 @@
         </is>
       </c>
       <c r="B370" t="n">
-        <v>0.76535</v>
+        <v>0.620194</v>
       </c>
       <c r="C370" t="n">
-        <v>0.010753</v>
+        <v>0.029024</v>
       </c>
     </row>
     <row r="371">
@@ -5237,10 +5237,10 @@
         </is>
       </c>
       <c r="B371" t="n">
-        <v>0.838984</v>
+        <v>0.634074</v>
       </c>
       <c r="C371" t="n">
-        <v>0.008064999999999999</v>
+        <v>0.026385</v>
       </c>
     </row>
     <row r="372">
@@ -5250,10 +5250,10 @@
         </is>
       </c>
       <c r="B372" t="n">
-        <v>1.015082</v>
+        <v>0.648021</v>
       </c>
       <c r="C372" t="n">
-        <v>0.005376</v>
+        <v>0.023747</v>
       </c>
     </row>
     <row r="373">
@@ -5263,101 +5263,101 @@
         </is>
       </c>
       <c r="B373" t="n">
-        <v>1.233322</v>
+        <v>0.672434</v>
       </c>
       <c r="C373" t="n">
-        <v>0.002688</v>
+        <v>0.021108</v>
       </c>
     </row>
     <row r="374">
       <c r="A374" t="inlineStr">
         <is>
-          <t>Adjusted target</t>
+          <t>Raw market</t>
         </is>
       </c>
       <c r="B374" t="n">
-        <v>4e-06</v>
+        <v>0.678189</v>
       </c>
       <c r="C374" t="n">
-        <v>1</v>
+        <v>0.01847</v>
       </c>
     </row>
     <row r="375">
       <c r="A375" t="inlineStr">
         <is>
-          <t>Adjusted target</t>
+          <t>Raw market</t>
         </is>
       </c>
       <c r="B375" t="n">
-        <v>0.000109</v>
+        <v>0.707604</v>
       </c>
       <c r="C375" t="n">
-        <v>0.997312</v>
+        <v>0.015831</v>
       </c>
     </row>
     <row r="376">
       <c r="A376" t="inlineStr">
         <is>
-          <t>Adjusted target</t>
+          <t>Raw market</t>
         </is>
       </c>
       <c r="B376" t="n">
-        <v>0.000516</v>
+        <v>0.711338</v>
       </c>
       <c r="C376" t="n">
-        <v>0.994624</v>
+        <v>0.013193</v>
       </c>
     </row>
     <row r="377">
       <c r="A377" t="inlineStr">
         <is>
-          <t>Adjusted target</t>
+          <t>Raw market</t>
         </is>
       </c>
       <c r="B377" t="n">
-        <v>0.000518</v>
+        <v>0.76535</v>
       </c>
       <c r="C377" t="n">
-        <v>0.991935</v>
+        <v>0.010554</v>
       </c>
     </row>
     <row r="378">
       <c r="A378" t="inlineStr">
         <is>
-          <t>Adjusted target</t>
+          <t>Raw market</t>
         </is>
       </c>
       <c r="B378" t="n">
-        <v>0.000928</v>
+        <v>0.838984</v>
       </c>
       <c r="C378" t="n">
-        <v>0.989247</v>
+        <v>0.007915999999999999</v>
       </c>
     </row>
     <row r="379">
       <c r="A379" t="inlineStr">
         <is>
-          <t>Adjusted target</t>
+          <t>Raw market</t>
         </is>
       </c>
       <c r="B379" t="n">
-        <v>0.00168</v>
+        <v>1.015082</v>
       </c>
       <c r="C379" t="n">
-        <v>0.986559</v>
+        <v>0.005277</v>
       </c>
     </row>
     <row r="380">
       <c r="A380" t="inlineStr">
         <is>
-          <t>Adjusted target</t>
+          <t>Raw market</t>
         </is>
       </c>
       <c r="B380" t="n">
-        <v>0.001819</v>
+        <v>2.37737</v>
       </c>
       <c r="C380" t="n">
-        <v>0.9838710000000001</v>
+        <v>0.002639</v>
       </c>
     </row>
     <row r="381">
@@ -5367,10 +5367,10 @@
         </is>
       </c>
       <c r="B381" t="n">
-        <v>0.001962</v>
+        <v>1e-06</v>
       </c>
       <c r="C381" t="n">
-        <v>0.981183</v>
+        <v>1</v>
       </c>
     </row>
     <row r="382">
@@ -5380,10 +5380,10 @@
         </is>
       </c>
       <c r="B382" t="n">
-        <v>0.001972</v>
+        <v>0.000108</v>
       </c>
       <c r="C382" t="n">
-        <v>0.978495</v>
+        <v>0.9973610000000001</v>
       </c>
     </row>
     <row r="383">
@@ -5393,10 +5393,10 @@
         </is>
       </c>
       <c r="B383" t="n">
-        <v>0.002441</v>
+        <v>0.000301</v>
       </c>
       <c r="C383" t="n">
-        <v>0.975806</v>
+        <v>0.994723</v>
       </c>
     </row>
     <row r="384">
@@ -5406,10 +5406,10 @@
         </is>
       </c>
       <c r="B384" t="n">
-        <v>0.002742</v>
+        <v>0.000517</v>
       </c>
       <c r="C384" t="n">
-        <v>0.973118</v>
+        <v>0.992084</v>
       </c>
     </row>
     <row r="385">
@@ -5419,10 +5419,10 @@
         </is>
       </c>
       <c r="B385" t="n">
-        <v>0.003089</v>
+        <v>0.000993</v>
       </c>
       <c r="C385" t="n">
-        <v>0.97043</v>
+        <v>0.989446</v>
       </c>
     </row>
     <row r="386">
@@ -5432,10 +5432,10 @@
         </is>
       </c>
       <c r="B386" t="n">
-        <v>0.003482</v>
+        <v>0.001625</v>
       </c>
       <c r="C386" t="n">
-        <v>0.967742</v>
+        <v>0.986807</v>
       </c>
     </row>
     <row r="387">
@@ -5445,10 +5445,10 @@
         </is>
       </c>
       <c r="B387" t="n">
-        <v>0.003899</v>
+        <v>0.001915</v>
       </c>
       <c r="C387" t="n">
-        <v>0.965054</v>
+        <v>0.984169</v>
       </c>
     </row>
     <row r="388">
@@ -5458,10 +5458,10 @@
         </is>
       </c>
       <c r="B388" t="n">
-        <v>0.00401</v>
+        <v>0.00195</v>
       </c>
       <c r="C388" t="n">
-        <v>0.9623660000000001</v>
+        <v>0.98153</v>
       </c>
     </row>
     <row r="389">
@@ -5471,10 +5471,10 @@
         </is>
       </c>
       <c r="B389" t="n">
-        <v>0.004228</v>
+        <v>0.002083</v>
       </c>
       <c r="C389" t="n">
-        <v>0.959677</v>
+        <v>0.978892</v>
       </c>
     </row>
     <row r="390">
@@ -5484,10 +5484,10 @@
         </is>
       </c>
       <c r="B390" t="n">
-        <v>0.004293</v>
+        <v>0.002689</v>
       </c>
       <c r="C390" t="n">
-        <v>0.956989</v>
+        <v>0.976253</v>
       </c>
     </row>
     <row r="391">
@@ -5497,10 +5497,10 @@
         </is>
       </c>
       <c r="B391" t="n">
-        <v>0.004348</v>
+        <v>0.002826</v>
       </c>
       <c r="C391" t="n">
-        <v>0.954301</v>
+        <v>0.973615</v>
       </c>
     </row>
     <row r="392">
@@ -5510,10 +5510,10 @@
         </is>
       </c>
       <c r="B392" t="n">
-        <v>0.004526</v>
+        <v>0.003056</v>
       </c>
       <c r="C392" t="n">
-        <v>0.951613</v>
+        <v>0.970976</v>
       </c>
     </row>
     <row r="393">
@@ -5523,10 +5523,10 @@
         </is>
       </c>
       <c r="B393" t="n">
-        <v>0.004821</v>
+        <v>0.003365</v>
       </c>
       <c r="C393" t="n">
-        <v>0.948925</v>
+        <v>0.968338</v>
       </c>
     </row>
     <row r="394">
@@ -5536,10 +5536,10 @@
         </is>
       </c>
       <c r="B394" t="n">
-        <v>0.004851</v>
+        <v>0.003619</v>
       </c>
       <c r="C394" t="n">
-        <v>0.946237</v>
+        <v>0.965699</v>
       </c>
     </row>
     <row r="395">
@@ -5549,10 +5549,10 @@
         </is>
       </c>
       <c r="B395" t="n">
-        <v>0.004851</v>
+        <v>0.004103</v>
       </c>
       <c r="C395" t="n">
-        <v>0.9435480000000001</v>
+        <v>0.9630609999999999</v>
       </c>
     </row>
     <row r="396">
@@ -5562,10 +5562,10 @@
         </is>
       </c>
       <c r="B396" t="n">
-        <v>0.005005</v>
+        <v>0.0042</v>
       </c>
       <c r="C396" t="n">
-        <v>0.94086</v>
+        <v>0.960422</v>
       </c>
     </row>
     <row r="397">
@@ -5575,10 +5575,10 @@
         </is>
       </c>
       <c r="B397" t="n">
-        <v>0.005028</v>
+        <v>0.004267</v>
       </c>
       <c r="C397" t="n">
-        <v>0.938172</v>
+        <v>0.957784</v>
       </c>
     </row>
     <row r="398">
@@ -5588,10 +5588,10 @@
         </is>
       </c>
       <c r="B398" t="n">
-        <v>0.005148</v>
+        <v>0.004338</v>
       </c>
       <c r="C398" t="n">
-        <v>0.935484</v>
+        <v>0.955145</v>
       </c>
     </row>
     <row r="399">
@@ -5601,10 +5601,10 @@
         </is>
       </c>
       <c r="B399" t="n">
-        <v>0.005302</v>
+        <v>0.004453</v>
       </c>
       <c r="C399" t="n">
-        <v>0.932796</v>
+        <v>0.952507</v>
       </c>
     </row>
     <row r="400">
@@ -5614,10 +5614,10 @@
         </is>
       </c>
       <c r="B400" t="n">
-        <v>0.005401</v>
+        <v>0.004747</v>
       </c>
       <c r="C400" t="n">
-        <v>0.930108</v>
+        <v>0.949868</v>
       </c>
     </row>
     <row r="401">
@@ -5627,10 +5627,10 @@
         </is>
       </c>
       <c r="B401" t="n">
-        <v>0.005836</v>
+        <v>0.004779</v>
       </c>
       <c r="C401" t="n">
-        <v>0.927419</v>
+        <v>0.94723</v>
       </c>
     </row>
     <row r="402">
@@ -5640,10 +5640,10 @@
         </is>
       </c>
       <c r="B402" t="n">
-        <v>0.005879</v>
+        <v>0.004802</v>
       </c>
       <c r="C402" t="n">
-        <v>0.924731</v>
+        <v>0.944591</v>
       </c>
     </row>
     <row r="403">
@@ -5653,10 +5653,10 @@
         </is>
       </c>
       <c r="B403" t="n">
-        <v>0.005881</v>
+        <v>0.005033</v>
       </c>
       <c r="C403" t="n">
-        <v>0.9220429999999999</v>
+        <v>0.941953</v>
       </c>
     </row>
     <row r="404">
@@ -5666,10 +5666,10 @@
         </is>
       </c>
       <c r="B404" t="n">
-        <v>0.006012</v>
+        <v>0.005286</v>
       </c>
       <c r="C404" t="n">
-        <v>0.919355</v>
+        <v>0.939314</v>
       </c>
     </row>
     <row r="405">
@@ -5679,10 +5679,10 @@
         </is>
       </c>
       <c r="B405" t="n">
-        <v>0.007077</v>
+        <v>0.005559</v>
       </c>
       <c r="C405" t="n">
-        <v>0.916667</v>
+        <v>0.936675</v>
       </c>
     </row>
     <row r="406">
@@ -5692,10 +5692,10 @@
         </is>
       </c>
       <c r="B406" t="n">
-        <v>0.007592</v>
+        <v>0.005712</v>
       </c>
       <c r="C406" t="n">
-        <v>0.913978</v>
+        <v>0.934037</v>
       </c>
     </row>
     <row r="407">
@@ -5705,10 +5705,10 @@
         </is>
       </c>
       <c r="B407" t="n">
-        <v>0.007821</v>
+        <v>0.005745</v>
       </c>
       <c r="C407" t="n">
-        <v>0.91129</v>
+        <v>0.9313979999999999</v>
       </c>
     </row>
     <row r="408">
@@ -5718,10 +5718,10 @@
         </is>
       </c>
       <c r="B408" t="n">
-        <v>0.008194999999999999</v>
+        <v>0.005887</v>
       </c>
       <c r="C408" t="n">
-        <v>0.908602</v>
+        <v>0.92876</v>
       </c>
     </row>
     <row r="409">
@@ -5731,10 +5731,10 @@
         </is>
       </c>
       <c r="B409" t="n">
-        <v>0.008689000000000001</v>
+        <v>0.006738</v>
       </c>
       <c r="C409" t="n">
-        <v>0.905914</v>
+        <v>0.926121</v>
       </c>
     </row>
     <row r="410">
@@ -5744,10 +5744,10 @@
         </is>
       </c>
       <c r="B410" t="n">
-        <v>0.008987999999999999</v>
+        <v>0.0069</v>
       </c>
       <c r="C410" t="n">
-        <v>0.903226</v>
+        <v>0.9234830000000001</v>
       </c>
     </row>
     <row r="411">
@@ -5757,10 +5757,10 @@
         </is>
       </c>
       <c r="B411" t="n">
-        <v>0.009497999999999999</v>
+        <v>0.007769</v>
       </c>
       <c r="C411" t="n">
-        <v>0.9005379999999999</v>
+        <v>0.920844</v>
       </c>
     </row>
     <row r="412">
@@ -5770,10 +5770,10 @@
         </is>
       </c>
       <c r="B412" t="n">
-        <v>0.009976</v>
+        <v>0.008177</v>
       </c>
       <c r="C412" t="n">
-        <v>0.897849</v>
+        <v>0.918206</v>
       </c>
     </row>
     <row r="413">
@@ -5783,10 +5783,10 @@
         </is>
       </c>
       <c r="B413" t="n">
-        <v>0.009979</v>
+        <v>0.008243</v>
       </c>
       <c r="C413" t="n">
-        <v>0.895161</v>
+        <v>0.915567</v>
       </c>
     </row>
     <row r="414">
@@ -5796,10 +5796,10 @@
         </is>
       </c>
       <c r="B414" t="n">
-        <v>0.010052</v>
+        <v>0.008603</v>
       </c>
       <c r="C414" t="n">
-        <v>0.892473</v>
+        <v>0.912929</v>
       </c>
     </row>
     <row r="415">
@@ -5809,10 +5809,10 @@
         </is>
       </c>
       <c r="B415" t="n">
-        <v>0.010053</v>
+        <v>0.008626</v>
       </c>
       <c r="C415" t="n">
-        <v>0.889785</v>
+        <v>0.91029</v>
       </c>
     </row>
     <row r="416">
@@ -5822,10 +5822,10 @@
         </is>
       </c>
       <c r="B416" t="n">
-        <v>0.010311</v>
+        <v>0.008701</v>
       </c>
       <c r="C416" t="n">
-        <v>0.887097</v>
+        <v>0.907652</v>
       </c>
     </row>
     <row r="417">
@@ -5835,10 +5835,10 @@
         </is>
       </c>
       <c r="B417" t="n">
-        <v>0.010334</v>
+        <v>0.008722000000000001</v>
       </c>
       <c r="C417" t="n">
-        <v>0.884409</v>
+        <v>0.905013</v>
       </c>
     </row>
     <row r="418">
@@ -5848,10 +5848,10 @@
         </is>
       </c>
       <c r="B418" t="n">
-        <v>0.010409</v>
+        <v>0.008932000000000001</v>
       </c>
       <c r="C418" t="n">
-        <v>0.8817199999999999</v>
+        <v>0.902375</v>
       </c>
     </row>
     <row r="419">
@@ -5861,10 +5861,10 @@
         </is>
       </c>
       <c r="B419" t="n">
-        <v>0.010718</v>
+        <v>0.009009</v>
       </c>
       <c r="C419" t="n">
-        <v>0.879032</v>
+        <v>0.899736</v>
       </c>
     </row>
     <row r="420">
@@ -5874,10 +5874,10 @@
         </is>
       </c>
       <c r="B420" t="n">
-        <v>0.010802</v>
+        <v>0.009431</v>
       </c>
       <c r="C420" t="n">
-        <v>0.876344</v>
+        <v>0.897098</v>
       </c>
     </row>
     <row r="421">
@@ -5887,10 +5887,10 @@
         </is>
       </c>
       <c r="B421" t="n">
-        <v>0.011107</v>
+        <v>0.009752</v>
       </c>
       <c r="C421" t="n">
-        <v>0.873656</v>
+        <v>0.894459</v>
       </c>
     </row>
     <row r="422">
@@ -5900,10 +5900,10 @@
         </is>
       </c>
       <c r="B422" t="n">
-        <v>0.01117</v>
+        <v>0.009863</v>
       </c>
       <c r="C422" t="n">
-        <v>0.870968</v>
+        <v>0.891821</v>
       </c>
     </row>
     <row r="423">
@@ -5913,10 +5913,10 @@
         </is>
       </c>
       <c r="B423" t="n">
-        <v>0.011719</v>
+        <v>0.009897</v>
       </c>
       <c r="C423" t="n">
-        <v>0.8682800000000001</v>
+        <v>0.889182</v>
       </c>
     </row>
     <row r="424">
@@ -5926,10 +5926,10 @@
         </is>
       </c>
       <c r="B424" t="n">
-        <v>0.012012</v>
+        <v>0.009959000000000001</v>
       </c>
       <c r="C424" t="n">
-        <v>0.865591</v>
+        <v>0.886544</v>
       </c>
     </row>
     <row r="425">
@@ -5939,10 +5939,10 @@
         </is>
       </c>
       <c r="B425" t="n">
-        <v>0.012114</v>
+        <v>0.010057</v>
       </c>
       <c r="C425" t="n">
-        <v>0.862903</v>
+        <v>0.8839050000000001</v>
       </c>
     </row>
     <row r="426">
@@ -5952,10 +5952,10 @@
         </is>
       </c>
       <c r="B426" t="n">
-        <v>0.012221</v>
+        <v>0.010249</v>
       </c>
       <c r="C426" t="n">
-        <v>0.860215</v>
+        <v>0.881266</v>
       </c>
     </row>
     <row r="427">
@@ -5965,10 +5965,10 @@
         </is>
       </c>
       <c r="B427" t="n">
-        <v>0.012295</v>
+        <v>0.010604</v>
       </c>
       <c r="C427" t="n">
-        <v>0.857527</v>
+        <v>0.878628</v>
       </c>
     </row>
     <row r="428">
@@ -5978,10 +5978,10 @@
         </is>
       </c>
       <c r="B428" t="n">
-        <v>0.012708</v>
+        <v>0.010697</v>
       </c>
       <c r="C428" t="n">
-        <v>0.854839</v>
+        <v>0.875989</v>
       </c>
     </row>
     <row r="429">
@@ -5991,10 +5991,10 @@
         </is>
       </c>
       <c r="B429" t="n">
-        <v>0.013049</v>
+        <v>0.010729</v>
       </c>
       <c r="C429" t="n">
-        <v>0.852151</v>
+        <v>0.873351</v>
       </c>
     </row>
     <row r="430">
@@ -6004,10 +6004,10 @@
         </is>
       </c>
       <c r="B430" t="n">
-        <v>0.013127</v>
+        <v>0.01095</v>
       </c>
       <c r="C430" t="n">
-        <v>0.8494620000000001</v>
+        <v>0.870712</v>
       </c>
     </row>
     <row r="431">
@@ -6017,10 +6017,10 @@
         </is>
       </c>
       <c r="B431" t="n">
-        <v>0.013221</v>
+        <v>0.011538</v>
       </c>
       <c r="C431" t="n">
-        <v>0.846774</v>
+        <v>0.868074</v>
       </c>
     </row>
     <row r="432">
@@ -6030,10 +6030,10 @@
         </is>
       </c>
       <c r="B432" t="n">
-        <v>0.013223</v>
+        <v>0.01184</v>
       </c>
       <c r="C432" t="n">
-        <v>0.844086</v>
+        <v>0.865435</v>
       </c>
     </row>
     <row r="433">
@@ -6043,10 +6043,10 @@
         </is>
       </c>
       <c r="B433" t="n">
-        <v>0.014012</v>
+        <v>0.011961</v>
       </c>
       <c r="C433" t="n">
-        <v>0.841398</v>
+        <v>0.862797</v>
       </c>
     </row>
     <row r="434">
@@ -6056,10 +6056,10 @@
         </is>
       </c>
       <c r="B434" t="n">
-        <v>0.014434</v>
+        <v>0.012029</v>
       </c>
       <c r="C434" t="n">
-        <v>0.83871</v>
+        <v>0.860158</v>
       </c>
     </row>
     <row r="435">
@@ -6069,10 +6069,10 @@
         </is>
       </c>
       <c r="B435" t="n">
-        <v>0.01444</v>
+        <v>0.012123</v>
       </c>
       <c r="C435" t="n">
-        <v>0.836022</v>
+        <v>0.8575199999999999</v>
       </c>
     </row>
     <row r="436">
@@ -6082,10 +6082,10 @@
         </is>
       </c>
       <c r="B436" t="n">
-        <v>0.014533</v>
+        <v>0.012358</v>
       </c>
       <c r="C436" t="n">
-        <v>0.833333</v>
+        <v>0.854881</v>
       </c>
     </row>
     <row r="437">
@@ -6095,10 +6095,10 @@
         </is>
       </c>
       <c r="B437" t="n">
-        <v>0.014586</v>
+        <v>0.012648</v>
       </c>
       <c r="C437" t="n">
-        <v>0.830645</v>
+        <v>0.852243</v>
       </c>
     </row>
     <row r="438">
@@ -6108,10 +6108,10 @@
         </is>
       </c>
       <c r="B438" t="n">
-        <v>0.014879</v>
+        <v>0.012936</v>
       </c>
       <c r="C438" t="n">
-        <v>0.8279570000000001</v>
+        <v>0.849604</v>
       </c>
     </row>
     <row r="439">
@@ -6121,10 +6121,10 @@
         </is>
       </c>
       <c r="B439" t="n">
-        <v>0.015032</v>
+        <v>0.01305</v>
       </c>
       <c r="C439" t="n">
-        <v>0.825269</v>
+        <v>0.846966</v>
       </c>
     </row>
     <row r="440">
@@ -6134,10 +6134,10 @@
         </is>
       </c>
       <c r="B440" t="n">
-        <v>0.015315</v>
+        <v>0.013176</v>
       </c>
       <c r="C440" t="n">
-        <v>0.822581</v>
+        <v>0.844327</v>
       </c>
     </row>
     <row r="441">
@@ -6147,10 +6147,10 @@
         </is>
       </c>
       <c r="B441" t="n">
-        <v>0.015429</v>
+        <v>0.014337</v>
       </c>
       <c r="C441" t="n">
-        <v>0.819892</v>
+        <v>0.841689</v>
       </c>
     </row>
     <row r="442">
@@ -6160,10 +6160,10 @@
         </is>
       </c>
       <c r="B442" t="n">
-        <v>0.015639</v>
+        <v>0.014373</v>
       </c>
       <c r="C442" t="n">
-        <v>0.817204</v>
+        <v>0.83905</v>
       </c>
     </row>
     <row r="443">
@@ -6173,10 +6173,10 @@
         </is>
       </c>
       <c r="B443" t="n">
-        <v>0.015977</v>
+        <v>0.0145</v>
       </c>
       <c r="C443" t="n">
-        <v>0.814516</v>
+        <v>0.836412</v>
       </c>
     </row>
     <row r="444">
@@ -6186,10 +6186,10 @@
         </is>
       </c>
       <c r="B444" t="n">
-        <v>0.015996</v>
+        <v>0.014646</v>
       </c>
       <c r="C444" t="n">
-        <v>0.811828</v>
+        <v>0.833773</v>
       </c>
     </row>
     <row r="445">
@@ -6199,10 +6199,10 @@
         </is>
       </c>
       <c r="B445" t="n">
-        <v>0.016054</v>
+        <v>0.014989</v>
       </c>
       <c r="C445" t="n">
-        <v>0.80914</v>
+        <v>0.831135</v>
       </c>
     </row>
     <row r="446">
@@ -6212,10 +6212,10 @@
         </is>
       </c>
       <c r="B446" t="n">
-        <v>0.01606</v>
+        <v>0.015165</v>
       </c>
       <c r="C446" t="n">
-        <v>0.8064519999999999</v>
+        <v>0.828496</v>
       </c>
     </row>
     <row r="447">
@@ -6225,10 +6225,10 @@
         </is>
       </c>
       <c r="B447" t="n">
-        <v>0.016241</v>
+        <v>0.015339</v>
       </c>
       <c r="C447" t="n">
-        <v>0.803763</v>
+        <v>0.825858</v>
       </c>
     </row>
     <row r="448">
@@ -6238,10 +6238,10 @@
         </is>
       </c>
       <c r="B448" t="n">
-        <v>0.01629</v>
+        <v>0.015456</v>
       </c>
       <c r="C448" t="n">
-        <v>0.801075</v>
+        <v>0.823219</v>
       </c>
     </row>
     <row r="449">
@@ -6251,10 +6251,10 @@
         </is>
       </c>
       <c r="B449" t="n">
-        <v>0.016939</v>
+        <v>0.015877</v>
       </c>
       <c r="C449" t="n">
-        <v>0.798387</v>
+        <v>0.82058</v>
       </c>
     </row>
     <row r="450">
@@ -6264,10 +6264,10 @@
         </is>
       </c>
       <c r="B450" t="n">
-        <v>0.01702</v>
+        <v>0.016034</v>
       </c>
       <c r="C450" t="n">
-        <v>0.795699</v>
+        <v>0.8179419999999999</v>
       </c>
     </row>
     <row r="451">
@@ -6277,10 +6277,10 @@
         </is>
       </c>
       <c r="B451" t="n">
-        <v>0.017278</v>
+        <v>0.016134</v>
       </c>
       <c r="C451" t="n">
-        <v>0.793011</v>
+        <v>0.815303</v>
       </c>
     </row>
     <row r="452">
@@ -6290,10 +6290,10 @@
         </is>
       </c>
       <c r="B452" t="n">
-        <v>0.017641</v>
+        <v>0.016241</v>
       </c>
       <c r="C452" t="n">
-        <v>0.790323</v>
+        <v>0.812665</v>
       </c>
     </row>
     <row r="453">
@@ -6303,10 +6303,10 @@
         </is>
       </c>
       <c r="B453" t="n">
-        <v>0.018482</v>
+        <v>0.016568</v>
       </c>
       <c r="C453" t="n">
-        <v>0.7876339999999999</v>
+        <v>0.810026</v>
       </c>
     </row>
     <row r="454">
@@ -6316,10 +6316,10 @@
         </is>
       </c>
       <c r="B454" t="n">
-        <v>0.018657</v>
+        <v>0.016647</v>
       </c>
       <c r="C454" t="n">
-        <v>0.784946</v>
+        <v>0.807388</v>
       </c>
     </row>
     <row r="455">
@@ -6329,10 +6329,10 @@
         </is>
       </c>
       <c r="B455" t="n">
-        <v>0.018675</v>
+        <v>0.01674</v>
       </c>
       <c r="C455" t="n">
-        <v>0.782258</v>
+        <v>0.804749</v>
       </c>
     </row>
     <row r="456">
@@ -6342,10 +6342,10 @@
         </is>
       </c>
       <c r="B456" t="n">
-        <v>0.018906</v>
+        <v>0.017067</v>
       </c>
       <c r="C456" t="n">
-        <v>0.77957</v>
+        <v>0.802111</v>
       </c>
     </row>
     <row r="457">
@@ -6355,10 +6355,10 @@
         </is>
       </c>
       <c r="B457" t="n">
-        <v>0.018959</v>
+        <v>0.017324</v>
       </c>
       <c r="C457" t="n">
-        <v>0.776882</v>
+        <v>0.799472</v>
       </c>
     </row>
     <row r="458">
@@ -6368,10 +6368,10 @@
         </is>
       </c>
       <c r="B458" t="n">
-        <v>0.019553</v>
+        <v>0.018026</v>
       </c>
       <c r="C458" t="n">
-        <v>0.774194</v>
+        <v>0.796834</v>
       </c>
     </row>
     <row r="459">
@@ -6381,10 +6381,10 @@
         </is>
       </c>
       <c r="B459" t="n">
-        <v>0.020013</v>
+        <v>0.018096</v>
       </c>
       <c r="C459" t="n">
-        <v>0.771505</v>
+        <v>0.794195</v>
       </c>
     </row>
     <row r="460">
@@ -6394,10 +6394,10 @@
         </is>
       </c>
       <c r="B460" t="n">
-        <v>0.020021</v>
+        <v>0.018405</v>
       </c>
       <c r="C460" t="n">
-        <v>0.768817</v>
+        <v>0.791557</v>
       </c>
     </row>
     <row r="461">
@@ -6407,10 +6407,10 @@
         </is>
       </c>
       <c r="B461" t="n">
-        <v>0.020081</v>
+        <v>0.018553</v>
       </c>
       <c r="C461" t="n">
-        <v>0.7661289999999999</v>
+        <v>0.788918</v>
       </c>
     </row>
     <row r="462">
@@ -6420,10 +6420,10 @@
         </is>
       </c>
       <c r="B462" t="n">
-        <v>0.020247</v>
+        <v>0.018661</v>
       </c>
       <c r="C462" t="n">
-        <v>0.763441</v>
+        <v>0.78628</v>
       </c>
     </row>
     <row r="463">
@@ -6433,10 +6433,10 @@
         </is>
       </c>
       <c r="B463" t="n">
-        <v>0.020568</v>
+        <v>0.018819</v>
       </c>
       <c r="C463" t="n">
-        <v>0.760753</v>
+        <v>0.783641</v>
       </c>
     </row>
     <row r="464">
@@ -6446,10 +6446,10 @@
         </is>
       </c>
       <c r="B464" t="n">
-        <v>0.020691</v>
+        <v>0.019232</v>
       </c>
       <c r="C464" t="n">
-        <v>0.758065</v>
+        <v>0.781003</v>
       </c>
     </row>
     <row r="465">
@@ -6459,10 +6459,10 @@
         </is>
       </c>
       <c r="B465" t="n">
-        <v>0.021237</v>
+        <v>0.019269</v>
       </c>
       <c r="C465" t="n">
-        <v>0.755376</v>
+        <v>0.7783639999999999</v>
       </c>
     </row>
     <row r="466">
@@ -6472,10 +6472,10 @@
         </is>
       </c>
       <c r="B466" t="n">
-        <v>0.02134</v>
+        <v>0.01996</v>
       </c>
       <c r="C466" t="n">
-        <v>0.752688</v>
+        <v>0.775726</v>
       </c>
     </row>
     <row r="467">
@@ -6485,10 +6485,10 @@
         </is>
       </c>
       <c r="B467" t="n">
-        <v>0.021451</v>
+        <v>0.020233</v>
       </c>
       <c r="C467" t="n">
-        <v>0.75</v>
+        <v>0.773087</v>
       </c>
     </row>
     <row r="468">
@@ -6498,10 +6498,10 @@
         </is>
       </c>
       <c r="B468" t="n">
-        <v>0.022102</v>
+        <v>0.020452</v>
       </c>
       <c r="C468" t="n">
-        <v>0.747312</v>
+        <v>0.7704490000000001</v>
       </c>
     </row>
     <row r="469">
@@ -6511,10 +6511,10 @@
         </is>
       </c>
       <c r="B469" t="n">
-        <v>0.022713</v>
+        <v>0.020567</v>
       </c>
       <c r="C469" t="n">
-        <v>0.744624</v>
+        <v>0.76781</v>
       </c>
     </row>
     <row r="470">
@@ -6524,10 +6524,10 @@
         </is>
       </c>
       <c r="B470" t="n">
-        <v>0.022756</v>
+        <v>0.021014</v>
       </c>
       <c r="C470" t="n">
-        <v>0.741935</v>
+        <v>0.765172</v>
       </c>
     </row>
     <row r="471">
@@ -6537,10 +6537,10 @@
         </is>
       </c>
       <c r="B471" t="n">
-        <v>0.023298</v>
+        <v>0.021171</v>
       </c>
       <c r="C471" t="n">
-        <v>0.739247</v>
+        <v>0.762533</v>
       </c>
     </row>
     <row r="472">
@@ -6550,10 +6550,10 @@
         </is>
       </c>
       <c r="B472" t="n">
-        <v>0.024539</v>
+        <v>0.021612</v>
       </c>
       <c r="C472" t="n">
-        <v>0.736559</v>
+        <v>0.759894</v>
       </c>
     </row>
     <row r="473">
@@ -6563,10 +6563,10 @@
         </is>
       </c>
       <c r="B473" t="n">
-        <v>0.024619</v>
+        <v>0.022012</v>
       </c>
       <c r="C473" t="n">
-        <v>0.7338710000000001</v>
+        <v>0.757256</v>
       </c>
     </row>
     <row r="474">
@@ -6576,10 +6576,10 @@
         </is>
       </c>
       <c r="B474" t="n">
-        <v>0.024658</v>
+        <v>0.022137</v>
       </c>
       <c r="C474" t="n">
-        <v>0.731183</v>
+        <v>0.754617</v>
       </c>
     </row>
     <row r="475">
@@ -6589,10 +6589,10 @@
         </is>
       </c>
       <c r="B475" t="n">
-        <v>0.025112</v>
+        <v>0.0222</v>
       </c>
       <c r="C475" t="n">
-        <v>0.728495</v>
+        <v>0.751979</v>
       </c>
     </row>
     <row r="476">
@@ -6602,10 +6602,10 @@
         </is>
       </c>
       <c r="B476" t="n">
-        <v>0.025337</v>
+        <v>0.022517</v>
       </c>
       <c r="C476" t="n">
-        <v>0.725806</v>
+        <v>0.74934</v>
       </c>
     </row>
     <row r="477">
@@ -6615,10 +6615,10 @@
         </is>
       </c>
       <c r="B477" t="n">
-        <v>0.02597</v>
+        <v>0.023844</v>
       </c>
       <c r="C477" t="n">
-        <v>0.723118</v>
+        <v>0.746702</v>
       </c>
     </row>
     <row r="478">
@@ -6628,10 +6628,10 @@
         </is>
       </c>
       <c r="B478" t="n">
-        <v>0.026507</v>
+        <v>0.024006</v>
       </c>
       <c r="C478" t="n">
-        <v>0.72043</v>
+        <v>0.744063</v>
       </c>
     </row>
     <row r="479">
@@ -6641,10 +6641,10 @@
         </is>
       </c>
       <c r="B479" t="n">
-        <v>0.026606</v>
+        <v>0.02409</v>
       </c>
       <c r="C479" t="n">
-        <v>0.717742</v>
+        <v>0.741425</v>
       </c>
     </row>
     <row r="480">
@@ -6654,10 +6654,10 @@
         </is>
       </c>
       <c r="B480" t="n">
-        <v>0.026654</v>
+        <v>0.024093</v>
       </c>
       <c r="C480" t="n">
-        <v>0.715054</v>
+        <v>0.7387860000000001</v>
       </c>
     </row>
     <row r="481">
@@ -6667,10 +6667,10 @@
         </is>
       </c>
       <c r="B481" t="n">
-        <v>0.026731</v>
+        <v>0.02426</v>
       </c>
       <c r="C481" t="n">
-        <v>0.7123660000000001</v>
+        <v>0.736148</v>
       </c>
     </row>
     <row r="482">
@@ -6680,10 +6680,10 @@
         </is>
       </c>
       <c r="B482" t="n">
-        <v>0.026955</v>
+        <v>0.024327</v>
       </c>
       <c r="C482" t="n">
-        <v>0.709677</v>
+        <v>0.733509</v>
       </c>
     </row>
     <row r="483">
@@ -6693,10 +6693,10 @@
         </is>
       </c>
       <c r="B483" t="n">
-        <v>0.027299</v>
+        <v>0.024474</v>
       </c>
       <c r="C483" t="n">
-        <v>0.706989</v>
+        <v>0.730871</v>
       </c>
     </row>
     <row r="484">
@@ -6706,10 +6706,10 @@
         </is>
       </c>
       <c r="B484" t="n">
-        <v>0.027394</v>
+        <v>0.024858</v>
       </c>
       <c r="C484" t="n">
-        <v>0.704301</v>
+        <v>0.728232</v>
       </c>
     </row>
     <row r="485">
@@ -6719,10 +6719,10 @@
         </is>
       </c>
       <c r="B485" t="n">
-        <v>0.027557</v>
+        <v>0.024904</v>
       </c>
       <c r="C485" t="n">
-        <v>0.701613</v>
+        <v>0.725594</v>
       </c>
     </row>
     <row r="486">
@@ -6732,10 +6732,10 @@
         </is>
       </c>
       <c r="B486" t="n">
-        <v>0.027802</v>
+        <v>0.025167</v>
       </c>
       <c r="C486" t="n">
-        <v>0.698925</v>
+        <v>0.722955</v>
       </c>
     </row>
     <row r="487">
@@ -6745,10 +6745,10 @@
         </is>
       </c>
       <c r="B487" t="n">
-        <v>0.027829</v>
+        <v>0.02527</v>
       </c>
       <c r="C487" t="n">
-        <v>0.696237</v>
+        <v>0.720317</v>
       </c>
     </row>
     <row r="488">
@@ -6758,10 +6758,10 @@
         </is>
       </c>
       <c r="B488" t="n">
-        <v>0.028126</v>
+        <v>0.02542</v>
       </c>
       <c r="C488" t="n">
-        <v>0.6935480000000001</v>
+        <v>0.717678</v>
       </c>
     </row>
     <row r="489">
@@ -6771,10 +6771,10 @@
         </is>
       </c>
       <c r="B489" t="n">
-        <v>0.028233</v>
+        <v>0.025651</v>
       </c>
       <c r="C489" t="n">
-        <v>0.69086</v>
+        <v>0.71504</v>
       </c>
     </row>
     <row r="490">
@@ -6784,10 +6784,10 @@
         </is>
       </c>
       <c r="B490" t="n">
-        <v>0.028688</v>
+        <v>0.025846</v>
       </c>
       <c r="C490" t="n">
-        <v>0.688172</v>
+        <v>0.712401</v>
       </c>
     </row>
     <row r="491">
@@ -6797,10 +6797,10 @@
         </is>
       </c>
       <c r="B491" t="n">
-        <v>0.029113</v>
+        <v>0.026201</v>
       </c>
       <c r="C491" t="n">
-        <v>0.685484</v>
+        <v>0.709763</v>
       </c>
     </row>
     <row r="492">
@@ -6810,10 +6810,10 @@
         </is>
       </c>
       <c r="B492" t="n">
-        <v>0.029344</v>
+        <v>0.026241</v>
       </c>
       <c r="C492" t="n">
-        <v>0.682796</v>
+        <v>0.707124</v>
       </c>
     </row>
     <row r="493">
@@ -6823,10 +6823,10 @@
         </is>
       </c>
       <c r="B493" t="n">
-        <v>0.029523</v>
+        <v>0.026521</v>
       </c>
       <c r="C493" t="n">
-        <v>0.680108</v>
+        <v>0.704485</v>
       </c>
     </row>
     <row r="494">
@@ -6836,10 +6836,10 @@
         </is>
       </c>
       <c r="B494" t="n">
-        <v>0.030226</v>
+        <v>0.026869</v>
       </c>
       <c r="C494" t="n">
-        <v>0.677419</v>
+        <v>0.701847</v>
       </c>
     </row>
     <row r="495">
@@ -6849,10 +6849,10 @@
         </is>
       </c>
       <c r="B495" t="n">
-        <v>0.030764</v>
+        <v>0.026981</v>
       </c>
       <c r="C495" t="n">
-        <v>0.674731</v>
+        <v>0.6992080000000001</v>
       </c>
     </row>
     <row r="496">
@@ -6862,10 +6862,10 @@
         </is>
       </c>
       <c r="B496" t="n">
-        <v>0.031026</v>
+        <v>0.027174</v>
       </c>
       <c r="C496" t="n">
-        <v>0.6720429999999999</v>
+        <v>0.69657</v>
       </c>
     </row>
     <row r="497">
@@ -6875,10 +6875,10 @@
         </is>
       </c>
       <c r="B497" t="n">
-        <v>0.031377</v>
+        <v>0.027193</v>
       </c>
       <c r="C497" t="n">
-        <v>0.669355</v>
+        <v>0.693931</v>
       </c>
     </row>
     <row r="498">
@@ -6888,10 +6888,10 @@
         </is>
       </c>
       <c r="B498" t="n">
-        <v>0.031405</v>
+        <v>0.027564</v>
       </c>
       <c r="C498" t="n">
-        <v>0.666667</v>
+        <v>0.691293</v>
       </c>
     </row>
     <row r="499">
@@ -6901,10 +6901,10 @@
         </is>
       </c>
       <c r="B499" t="n">
-        <v>0.032166</v>
+        <v>0.02784</v>
       </c>
       <c r="C499" t="n">
-        <v>0.663978</v>
+        <v>0.688654</v>
       </c>
     </row>
     <row r="500">
@@ -6914,10 +6914,10 @@
         </is>
       </c>
       <c r="B500" t="n">
-        <v>0.032324</v>
+        <v>0.028032</v>
       </c>
       <c r="C500" t="n">
-        <v>0.66129</v>
+        <v>0.686016</v>
       </c>
     </row>
     <row r="501">
@@ -6927,10 +6927,10 @@
         </is>
       </c>
       <c r="B501" t="n">
-        <v>0.032462</v>
+        <v>0.028097</v>
       </c>
       <c r="C501" t="n">
-        <v>0.658602</v>
+        <v>0.683377</v>
       </c>
     </row>
     <row r="502">
@@ -6940,10 +6940,10 @@
         </is>
       </c>
       <c r="B502" t="n">
-        <v>0.0325</v>
+        <v>0.028448</v>
       </c>
       <c r="C502" t="n">
-        <v>0.655914</v>
+        <v>0.680739</v>
       </c>
     </row>
     <row r="503">
@@ -6953,10 +6953,10 @@
         </is>
       </c>
       <c r="B503" t="n">
-        <v>0.033033</v>
+        <v>0.028601</v>
       </c>
       <c r="C503" t="n">
-        <v>0.653226</v>
+        <v>0.6781</v>
       </c>
     </row>
     <row r="504">
@@ -6966,10 +6966,10 @@
         </is>
       </c>
       <c r="B504" t="n">
-        <v>0.033269</v>
+        <v>0.028767</v>
       </c>
       <c r="C504" t="n">
-        <v>0.6505379999999999</v>
+        <v>0.675462</v>
       </c>
     </row>
     <row r="505">
@@ -6979,10 +6979,10 @@
         </is>
       </c>
       <c r="B505" t="n">
-        <v>0.033374</v>
+        <v>0.029003</v>
       </c>
       <c r="C505" t="n">
-        <v>0.647849</v>
+        <v>0.6728229999999999</v>
       </c>
     </row>
     <row r="506">
@@ -6992,10 +6992,10 @@
         </is>
       </c>
       <c r="B506" t="n">
-        <v>0.033578</v>
+        <v>0.02936</v>
       </c>
       <c r="C506" t="n">
-        <v>0.645161</v>
+        <v>0.670185</v>
       </c>
     </row>
     <row r="507">
@@ -7005,10 +7005,10 @@
         </is>
       </c>
       <c r="B507" t="n">
-        <v>0.033622</v>
+        <v>0.030183</v>
       </c>
       <c r="C507" t="n">
-        <v>0.642473</v>
+        <v>0.667546</v>
       </c>
     </row>
     <row r="508">
@@ -7018,10 +7018,10 @@
         </is>
       </c>
       <c r="B508" t="n">
-        <v>0.033839</v>
+        <v>0.030682</v>
       </c>
       <c r="C508" t="n">
-        <v>0.639785</v>
+        <v>0.6649080000000001</v>
       </c>
     </row>
     <row r="509">
@@ -7031,10 +7031,10 @@
         </is>
       </c>
       <c r="B509" t="n">
-        <v>0.033871</v>
+        <v>0.030825</v>
       </c>
       <c r="C509" t="n">
-        <v>0.637097</v>
+        <v>0.662269</v>
       </c>
     </row>
     <row r="510">
@@ -7044,10 +7044,10 @@
         </is>
       </c>
       <c r="B510" t="n">
-        <v>0.034273</v>
+        <v>0.03131</v>
       </c>
       <c r="C510" t="n">
-        <v>0.634409</v>
+        <v>0.659631</v>
       </c>
     </row>
     <row r="511">
@@ -7057,10 +7057,10 @@
         </is>
       </c>
       <c r="B511" t="n">
-        <v>0.034391</v>
+        <v>0.031497</v>
       </c>
       <c r="C511" t="n">
-        <v>0.6317199999999999</v>
+        <v>0.656992</v>
       </c>
     </row>
     <row r="512">
@@ -7070,10 +7070,10 @@
         </is>
       </c>
       <c r="B512" t="n">
-        <v>0.03441</v>
+        <v>0.03168</v>
       </c>
       <c r="C512" t="n">
-        <v>0.629032</v>
+        <v>0.654354</v>
       </c>
     </row>
     <row r="513">
@@ -7083,10 +7083,10 @@
         </is>
       </c>
       <c r="B513" t="n">
-        <v>0.035435</v>
+        <v>0.032162</v>
       </c>
       <c r="C513" t="n">
-        <v>0.626344</v>
+        <v>0.651715</v>
       </c>
     </row>
     <row r="514">
@@ -7096,10 +7096,10 @@
         </is>
       </c>
       <c r="B514" t="n">
-        <v>0.035462</v>
+        <v>0.03241</v>
       </c>
       <c r="C514" t="n">
-        <v>0.623656</v>
+        <v>0.649077</v>
       </c>
     </row>
     <row r="515">
@@ -7109,10 +7109,10 @@
         </is>
       </c>
       <c r="B515" t="n">
-        <v>0.035906</v>
+        <v>0.032441</v>
       </c>
       <c r="C515" t="n">
-        <v>0.620968</v>
+        <v>0.646438</v>
       </c>
     </row>
     <row r="516">
@@ -7122,10 +7122,10 @@
         </is>
       </c>
       <c r="B516" t="n">
-        <v>0.036355</v>
+        <v>0.032711</v>
       </c>
       <c r="C516" t="n">
-        <v>0.6182800000000001</v>
+        <v>0.643799</v>
       </c>
     </row>
     <row r="517">
@@ -7135,10 +7135,10 @@
         </is>
       </c>
       <c r="B517" t="n">
-        <v>0.036545</v>
+        <v>0.032953</v>
       </c>
       <c r="C517" t="n">
-        <v>0.615591</v>
+        <v>0.641161</v>
       </c>
     </row>
     <row r="518">
@@ -7148,10 +7148,10 @@
         </is>
       </c>
       <c r="B518" t="n">
-        <v>0.037726</v>
+        <v>0.033124</v>
       </c>
       <c r="C518" t="n">
-        <v>0.612903</v>
+        <v>0.638522</v>
       </c>
     </row>
     <row r="519">
@@ -7161,10 +7161,10 @@
         </is>
       </c>
       <c r="B519" t="n">
-        <v>0.037942</v>
+        <v>0.033147</v>
       </c>
       <c r="C519" t="n">
-        <v>0.610215</v>
+        <v>0.635884</v>
       </c>
     </row>
     <row r="520">
@@ -7174,10 +7174,10 @@
         </is>
       </c>
       <c r="B520" t="n">
-        <v>0.038228</v>
+        <v>0.033362</v>
       </c>
       <c r="C520" t="n">
-        <v>0.607527</v>
+        <v>0.6332449999999999</v>
       </c>
     </row>
     <row r="521">
@@ -7187,10 +7187,10 @@
         </is>
       </c>
       <c r="B521" t="n">
-        <v>0.038746</v>
+        <v>0.033735</v>
       </c>
       <c r="C521" t="n">
-        <v>0.604839</v>
+        <v>0.630607</v>
       </c>
     </row>
     <row r="522">
@@ -7200,10 +7200,10 @@
         </is>
       </c>
       <c r="B522" t="n">
-        <v>0.038784</v>
+        <v>0.033893</v>
       </c>
       <c r="C522" t="n">
-        <v>0.602151</v>
+        <v>0.627968</v>
       </c>
     </row>
     <row r="523">
@@ -7213,10 +7213,10 @@
         </is>
       </c>
       <c r="B523" t="n">
-        <v>0.038921</v>
+        <v>0.034046</v>
       </c>
       <c r="C523" t="n">
-        <v>0.5994620000000001</v>
+        <v>0.6253300000000001</v>
       </c>
     </row>
     <row r="524">
@@ -7226,10 +7226,10 @@
         </is>
       </c>
       <c r="B524" t="n">
-        <v>0.039017</v>
+        <v>0.034233</v>
       </c>
       <c r="C524" t="n">
-        <v>0.596774</v>
+        <v>0.622691</v>
       </c>
     </row>
     <row r="525">
@@ -7239,10 +7239,10 @@
         </is>
       </c>
       <c r="B525" t="n">
-        <v>0.039186</v>
+        <v>0.034405</v>
       </c>
       <c r="C525" t="n">
-        <v>0.594086</v>
+        <v>0.620053</v>
       </c>
     </row>
     <row r="526">
@@ -7252,10 +7252,10 @@
         </is>
       </c>
       <c r="B526" t="n">
-        <v>0.03923</v>
+        <v>0.034556</v>
       </c>
       <c r="C526" t="n">
-        <v>0.591398</v>
+        <v>0.617414</v>
       </c>
     </row>
     <row r="527">
@@ -7265,10 +7265,10 @@
         </is>
       </c>
       <c r="B527" t="n">
-        <v>0.039391</v>
+        <v>0.034569</v>
       </c>
       <c r="C527" t="n">
-        <v>0.58871</v>
+        <v>0.614776</v>
       </c>
     </row>
     <row r="528">
@@ -7278,10 +7278,10 @@
         </is>
       </c>
       <c r="B528" t="n">
-        <v>0.039653</v>
+        <v>0.035056</v>
       </c>
       <c r="C528" t="n">
-        <v>0.586022</v>
+        <v>0.612137</v>
       </c>
     </row>
     <row r="529">
@@ -7291,10 +7291,10 @@
         </is>
       </c>
       <c r="B529" t="n">
-        <v>0.039713</v>
+        <v>0.035138</v>
       </c>
       <c r="C529" t="n">
-        <v>0.583333</v>
+        <v>0.609499</v>
       </c>
     </row>
     <row r="530">
@@ -7304,10 +7304,10 @@
         </is>
       </c>
       <c r="B530" t="n">
-        <v>0.039806</v>
+        <v>0.035966</v>
       </c>
       <c r="C530" t="n">
-        <v>0.580645</v>
+        <v>0.60686</v>
       </c>
     </row>
     <row r="531">
@@ -7317,10 +7317,10 @@
         </is>
       </c>
       <c r="B531" t="n">
-        <v>0.039838</v>
+        <v>0.036415</v>
       </c>
       <c r="C531" t="n">
-        <v>0.5779570000000001</v>
+        <v>0.604222</v>
       </c>
     </row>
     <row r="532">
@@ -7330,10 +7330,10 @@
         </is>
       </c>
       <c r="B532" t="n">
-        <v>0.040034</v>
+        <v>0.03646</v>
       </c>
       <c r="C532" t="n">
-        <v>0.575269</v>
+        <v>0.601583</v>
       </c>
     </row>
     <row r="533">
@@ -7343,10 +7343,10 @@
         </is>
       </c>
       <c r="B533" t="n">
-        <v>0.040426</v>
+        <v>0.037085</v>
       </c>
       <c r="C533" t="n">
-        <v>0.572581</v>
+        <v>0.5989449999999999</v>
       </c>
     </row>
     <row r="534">
@@ -7356,10 +7356,10 @@
         </is>
       </c>
       <c r="B534" t="n">
-        <v>0.040511</v>
+        <v>0.037103</v>
       </c>
       <c r="C534" t="n">
-        <v>0.569892</v>
+        <v>0.596306</v>
       </c>
     </row>
     <row r="535">
@@ -7369,10 +7369,10 @@
         </is>
       </c>
       <c r="B535" t="n">
-        <v>0.040661</v>
+        <v>0.037392</v>
       </c>
       <c r="C535" t="n">
-        <v>0.567204</v>
+        <v>0.593668</v>
       </c>
     </row>
     <row r="536">
@@ -7382,10 +7382,10 @@
         </is>
       </c>
       <c r="B536" t="n">
-        <v>0.041277</v>
+        <v>0.037531</v>
       </c>
       <c r="C536" t="n">
-        <v>0.564516</v>
+        <v>0.591029</v>
       </c>
     </row>
     <row r="537">
@@ -7395,10 +7395,10 @@
         </is>
       </c>
       <c r="B537" t="n">
-        <v>0.041278</v>
+        <v>0.037797</v>
       </c>
       <c r="C537" t="n">
-        <v>0.561828</v>
+        <v>0.588391</v>
       </c>
     </row>
     <row r="538">
@@ -7408,10 +7408,10 @@
         </is>
       </c>
       <c r="B538" t="n">
-        <v>0.041563</v>
+        <v>0.03782</v>
       </c>
       <c r="C538" t="n">
-        <v>0.55914</v>
+        <v>0.5857520000000001</v>
       </c>
     </row>
     <row r="539">
@@ -7421,10 +7421,10 @@
         </is>
       </c>
       <c r="B539" t="n">
-        <v>0.041683</v>
+        <v>0.038134</v>
       </c>
       <c r="C539" t="n">
-        <v>0.5564519999999999</v>
+        <v>0.583113</v>
       </c>
     </row>
     <row r="540">
@@ -7434,10 +7434,10 @@
         </is>
       </c>
       <c r="B540" t="n">
-        <v>0.042112</v>
+        <v>0.038674</v>
       </c>
       <c r="C540" t="n">
-        <v>0.553763</v>
+        <v>0.580475</v>
       </c>
     </row>
     <row r="541">
@@ -7447,10 +7447,10 @@
         </is>
       </c>
       <c r="B541" t="n">
-        <v>0.042278</v>
+        <v>0.038772</v>
       </c>
       <c r="C541" t="n">
-        <v>0.551075</v>
+        <v>0.577836</v>
       </c>
     </row>
     <row r="542">
@@ -7460,10 +7460,10 @@
         </is>
       </c>
       <c r="B542" t="n">
-        <v>0.043166</v>
+        <v>0.038909</v>
       </c>
       <c r="C542" t="n">
-        <v>0.548387</v>
+        <v>0.575198</v>
       </c>
     </row>
     <row r="543">
@@ -7473,10 +7473,10 @@
         </is>
       </c>
       <c r="B543" t="n">
-        <v>0.043336</v>
+        <v>0.038915</v>
       </c>
       <c r="C543" t="n">
-        <v>0.545699</v>
+        <v>0.572559</v>
       </c>
     </row>
     <row r="544">
@@ -7486,10 +7486,10 @@
         </is>
       </c>
       <c r="B544" t="n">
-        <v>0.043456</v>
+        <v>0.039123</v>
       </c>
       <c r="C544" t="n">
-        <v>0.543011</v>
+        <v>0.569921</v>
       </c>
     </row>
     <row r="545">
@@ -7499,10 +7499,10 @@
         </is>
       </c>
       <c r="B545" t="n">
-        <v>0.04379</v>
+        <v>0.039153</v>
       </c>
       <c r="C545" t="n">
-        <v>0.540323</v>
+        <v>0.567282</v>
       </c>
     </row>
     <row r="546">
@@ -7512,10 +7512,10 @@
         </is>
       </c>
       <c r="B546" t="n">
-        <v>0.045214</v>
+        <v>0.039155</v>
       </c>
       <c r="C546" t="n">
-        <v>0.5376339999999999</v>
+        <v>0.564644</v>
       </c>
     </row>
     <row r="547">
@@ -7525,10 +7525,10 @@
         </is>
       </c>
       <c r="B547" t="n">
-        <v>0.045707</v>
+        <v>0.039488</v>
       </c>
       <c r="C547" t="n">
-        <v>0.534946</v>
+        <v>0.562005</v>
       </c>
     </row>
     <row r="548">
@@ -7538,10 +7538,10 @@
         </is>
       </c>
       <c r="B548" t="n">
-        <v>0.046088</v>
+        <v>0.039677</v>
       </c>
       <c r="C548" t="n">
-        <v>0.532258</v>
+        <v>0.5593669999999999</v>
       </c>
     </row>
     <row r="549">
@@ -7551,10 +7551,10 @@
         </is>
       </c>
       <c r="B549" t="n">
-        <v>0.046113</v>
+        <v>0.039729</v>
       </c>
       <c r="C549" t="n">
-        <v>0.52957</v>
+        <v>0.556728</v>
       </c>
     </row>
     <row r="550">
@@ -7564,10 +7564,10 @@
         </is>
       </c>
       <c r="B550" t="n">
-        <v>0.046333</v>
+        <v>0.039946</v>
       </c>
       <c r="C550" t="n">
-        <v>0.526882</v>
+        <v>0.55409</v>
       </c>
     </row>
     <row r="551">
@@ -7577,10 +7577,10 @@
         </is>
       </c>
       <c r="B551" t="n">
-        <v>0.046711</v>
+        <v>0.039995</v>
       </c>
       <c r="C551" t="n">
-        <v>0.524194</v>
+        <v>0.551451</v>
       </c>
     </row>
     <row r="552">
@@ -7590,10 +7590,10 @@
         </is>
       </c>
       <c r="B552" t="n">
-        <v>0.047726</v>
+        <v>0.040011</v>
       </c>
       <c r="C552" t="n">
-        <v>0.521505</v>
+        <v>0.548813</v>
       </c>
     </row>
     <row r="553">
@@ -7603,10 +7603,10 @@
         </is>
       </c>
       <c r="B553" t="n">
-        <v>0.048001</v>
+        <v>0.040471</v>
       </c>
       <c r="C553" t="n">
-        <v>0.518817</v>
+        <v>0.546174</v>
       </c>
     </row>
     <row r="554">
@@ -7616,10 +7616,10 @@
         </is>
       </c>
       <c r="B554" t="n">
-        <v>0.04889</v>
+        <v>0.040576</v>
       </c>
       <c r="C554" t="n">
-        <v>0.5161289999999999</v>
+        <v>0.543536</v>
       </c>
     </row>
     <row r="555">
@@ -7629,10 +7629,10 @@
         </is>
       </c>
       <c r="B555" t="n">
-        <v>0.049282</v>
+        <v>0.040639</v>
       </c>
       <c r="C555" t="n">
-        <v>0.513441</v>
+        <v>0.540897</v>
       </c>
     </row>
     <row r="556">
@@ -7642,10 +7642,10 @@
         </is>
       </c>
       <c r="B556" t="n">
-        <v>0.050628</v>
+        <v>0.040924</v>
       </c>
       <c r="C556" t="n">
-        <v>0.510753</v>
+        <v>0.538259</v>
       </c>
     </row>
     <row r="557">
@@ -7655,10 +7655,10 @@
         </is>
       </c>
       <c r="B557" t="n">
-        <v>0.050703</v>
+        <v>0.041079</v>
       </c>
       <c r="C557" t="n">
-        <v>0.508065</v>
+        <v>0.53562</v>
       </c>
     </row>
     <row r="558">
@@ -7668,10 +7668,10 @@
         </is>
       </c>
       <c r="B558" t="n">
-        <v>0.050846</v>
+        <v>0.041379</v>
       </c>
       <c r="C558" t="n">
-        <v>0.505376</v>
+        <v>0.532982</v>
       </c>
     </row>
     <row r="559">
@@ -7681,10 +7681,10 @@
         </is>
       </c>
       <c r="B559" t="n">
-        <v>0.050946</v>
+        <v>0.04219</v>
       </c>
       <c r="C559" t="n">
-        <v>0.502688</v>
+        <v>0.530343</v>
       </c>
     </row>
     <row r="560">
@@ -7694,10 +7694,10 @@
         </is>
       </c>
       <c r="B560" t="n">
-        <v>0.051117</v>
+        <v>0.042716</v>
       </c>
       <c r="C560" t="n">
-        <v>0.5</v>
+        <v>0.527704</v>
       </c>
     </row>
     <row r="561">
@@ -7707,10 +7707,10 @@
         </is>
       </c>
       <c r="B561" t="n">
-        <v>0.051538</v>
+        <v>0.042834</v>
       </c>
       <c r="C561" t="n">
-        <v>0.497312</v>
+        <v>0.525066</v>
       </c>
     </row>
     <row r="562">
@@ -7720,10 +7720,10 @@
         </is>
       </c>
       <c r="B562" t="n">
-        <v>0.052018</v>
+        <v>0.042876</v>
       </c>
       <c r="C562" t="n">
-        <v>0.494624</v>
+        <v>0.522427</v>
       </c>
     </row>
     <row r="563">
@@ -7733,10 +7733,10 @@
         </is>
       </c>
       <c r="B563" t="n">
-        <v>0.052564</v>
+        <v>0.04324</v>
       </c>
       <c r="C563" t="n">
-        <v>0.491935</v>
+        <v>0.5197889999999999</v>
       </c>
     </row>
     <row r="564">
@@ -7746,10 +7746,10 @@
         </is>
       </c>
       <c r="B564" t="n">
-        <v>0.053229</v>
+        <v>0.043751</v>
       </c>
       <c r="C564" t="n">
-        <v>0.489247</v>
+        <v>0.51715</v>
       </c>
     </row>
     <row r="565">
@@ -7759,10 +7759,10 @@
         </is>
       </c>
       <c r="B565" t="n">
-        <v>0.05329</v>
+        <v>0.044248</v>
       </c>
       <c r="C565" t="n">
-        <v>0.486559</v>
+        <v>0.514512</v>
       </c>
     </row>
     <row r="566">
@@ -7772,10 +7772,10 @@
         </is>
       </c>
       <c r="B566" t="n">
-        <v>0.053407</v>
+        <v>0.044292</v>
       </c>
       <c r="C566" t="n">
-        <v>0.483871</v>
+        <v>0.511873</v>
       </c>
     </row>
     <row r="567">
@@ -7785,10 +7785,10 @@
         </is>
       </c>
       <c r="B567" t="n">
-        <v>0.053529</v>
+        <v>0.044573</v>
       </c>
       <c r="C567" t="n">
-        <v>0.481183</v>
+        <v>0.509235</v>
       </c>
     </row>
     <row r="568">
@@ -7798,10 +7798,10 @@
         </is>
       </c>
       <c r="B568" t="n">
-        <v>0.053665</v>
+        <v>0.044953</v>
       </c>
       <c r="C568" t="n">
-        <v>0.478495</v>
+        <v>0.506596</v>
       </c>
     </row>
     <row r="569">
@@ -7811,10 +7811,10 @@
         </is>
       </c>
       <c r="B569" t="n">
-        <v>0.054147</v>
+        <v>0.045333</v>
       </c>
       <c r="C569" t="n">
-        <v>0.475806</v>
+        <v>0.503958</v>
       </c>
     </row>
     <row r="570">
@@ -7824,10 +7824,10 @@
         </is>
       </c>
       <c r="B570" t="n">
-        <v>0.054165</v>
+        <v>0.045758</v>
       </c>
       <c r="C570" t="n">
-        <v>0.473118</v>
+        <v>0.501319</v>
       </c>
     </row>
     <row r="571">
@@ -7837,10 +7837,10 @@
         </is>
       </c>
       <c r="B571" t="n">
-        <v>0.054577</v>
+        <v>0.0458</v>
       </c>
       <c r="C571" t="n">
-        <v>0.47043</v>
+        <v>0.498681</v>
       </c>
     </row>
     <row r="572">
@@ -7850,10 +7850,10 @@
         </is>
       </c>
       <c r="B572" t="n">
-        <v>0.055014</v>
+        <v>0.045899</v>
       </c>
       <c r="C572" t="n">
-        <v>0.467742</v>
+        <v>0.496042</v>
       </c>
     </row>
     <row r="573">
@@ -7863,10 +7863,10 @@
         </is>
       </c>
       <c r="B573" t="n">
-        <v>0.055491</v>
+        <v>0.046171</v>
       </c>
       <c r="C573" t="n">
-        <v>0.465054</v>
+        <v>0.493404</v>
       </c>
     </row>
     <row r="574">
@@ -7876,10 +7876,10 @@
         </is>
       </c>
       <c r="B574" t="n">
-        <v>0.0559</v>
+        <v>0.046645</v>
       </c>
       <c r="C574" t="n">
-        <v>0.462366</v>
+        <v>0.490765</v>
       </c>
     </row>
     <row r="575">
@@ -7889,10 +7889,10 @@
         </is>
       </c>
       <c r="B575" t="n">
-        <v>0.056646</v>
+        <v>0.047597</v>
       </c>
       <c r="C575" t="n">
-        <v>0.459677</v>
+        <v>0.488127</v>
       </c>
     </row>
     <row r="576">
@@ -7902,10 +7902,10 @@
         </is>
       </c>
       <c r="B576" t="n">
-        <v>0.056855</v>
+        <v>0.047631</v>
       </c>
       <c r="C576" t="n">
-        <v>0.456989</v>
+        <v>0.485488</v>
       </c>
     </row>
     <row r="577">
@@ -7915,10 +7915,10 @@
         </is>
       </c>
       <c r="B577" t="n">
-        <v>0.057529</v>
+        <v>0.048018</v>
       </c>
       <c r="C577" t="n">
-        <v>0.454301</v>
+        <v>0.48285</v>
       </c>
     </row>
     <row r="578">
@@ -7928,10 +7928,10 @@
         </is>
       </c>
       <c r="B578" t="n">
-        <v>0.058143</v>
+        <v>0.048495</v>
       </c>
       <c r="C578" t="n">
-        <v>0.451613</v>
+        <v>0.480211</v>
       </c>
     </row>
     <row r="579">
@@ -7941,10 +7941,10 @@
         </is>
       </c>
       <c r="B579" t="n">
-        <v>0.058284</v>
+        <v>0.048806</v>
       </c>
       <c r="C579" t="n">
-        <v>0.448925</v>
+        <v>0.477573</v>
       </c>
     </row>
     <row r="580">
@@ -7954,10 +7954,10 @@
         </is>
       </c>
       <c r="B580" t="n">
-        <v>0.061075</v>
+        <v>0.049017</v>
       </c>
       <c r="C580" t="n">
-        <v>0.446237</v>
+        <v>0.474934</v>
       </c>
     </row>
     <row r="581">
@@ -7967,10 +7967,10 @@
         </is>
       </c>
       <c r="B581" t="n">
-        <v>0.062133</v>
+        <v>0.049824</v>
       </c>
       <c r="C581" t="n">
-        <v>0.443548</v>
+        <v>0.472296</v>
       </c>
     </row>
     <row r="582">
@@ -7980,10 +7980,10 @@
         </is>
       </c>
       <c r="B582" t="n">
-        <v>0.062734</v>
+        <v>0.050619</v>
       </c>
       <c r="C582" t="n">
-        <v>0.44086</v>
+        <v>0.469657</v>
       </c>
     </row>
     <row r="583">
@@ -7993,10 +7993,10 @@
         </is>
       </c>
       <c r="B583" t="n">
-        <v>0.06347899999999999</v>
+        <v>0.050743</v>
       </c>
       <c r="C583" t="n">
-        <v>0.438172</v>
+        <v>0.467018</v>
       </c>
     </row>
     <row r="584">
@@ -8006,10 +8006,10 @@
         </is>
       </c>
       <c r="B584" t="n">
-        <v>0.06355</v>
+        <v>0.050915</v>
       </c>
       <c r="C584" t="n">
-        <v>0.435484</v>
+        <v>0.46438</v>
       </c>
     </row>
     <row r="585">
@@ -8019,10 +8019,10 @@
         </is>
       </c>
       <c r="B585" t="n">
-        <v>0.06367200000000001</v>
+        <v>0.051171</v>
       </c>
       <c r="C585" t="n">
-        <v>0.432796</v>
+        <v>0.461741</v>
       </c>
     </row>
     <row r="586">
@@ -8032,10 +8032,10 @@
         </is>
       </c>
       <c r="B586" t="n">
-        <v>0.063774</v>
+        <v>0.051247</v>
       </c>
       <c r="C586" t="n">
-        <v>0.430108</v>
+        <v>0.459103</v>
       </c>
     </row>
     <row r="587">
@@ -8045,10 +8045,10 @@
         </is>
       </c>
       <c r="B587" t="n">
-        <v>0.06392100000000001</v>
+        <v>0.051692</v>
       </c>
       <c r="C587" t="n">
-        <v>0.427419</v>
+        <v>0.456464</v>
       </c>
     </row>
     <row r="588">
@@ -8058,10 +8058,10 @@
         </is>
       </c>
       <c r="B588" t="n">
-        <v>0.064072</v>
+        <v>0.051756</v>
       </c>
       <c r="C588" t="n">
-        <v>0.424731</v>
+        <v>0.453826</v>
       </c>
     </row>
     <row r="589">
@@ -8071,10 +8071,10 @@
         </is>
       </c>
       <c r="B589" t="n">
-        <v>0.06422700000000001</v>
+        <v>0.052558</v>
       </c>
       <c r="C589" t="n">
-        <v>0.422043</v>
+        <v>0.451187</v>
       </c>
     </row>
     <row r="590">
@@ -8084,10 +8084,10 @@
         </is>
       </c>
       <c r="B590" t="n">
-        <v>0.065222</v>
+        <v>0.052806</v>
       </c>
       <c r="C590" t="n">
-        <v>0.419355</v>
+        <v>0.448549</v>
       </c>
     </row>
     <row r="591">
@@ -8097,10 +8097,10 @@
         </is>
       </c>
       <c r="B591" t="n">
-        <v>0.06547600000000001</v>
+        <v>0.052851</v>
       </c>
       <c r="C591" t="n">
-        <v>0.416667</v>
+        <v>0.44591</v>
       </c>
     </row>
     <row r="592">
@@ -8110,10 +8110,10 @@
         </is>
       </c>
       <c r="B592" t="n">
-        <v>0.06558700000000001</v>
+        <v>0.052953</v>
       </c>
       <c r="C592" t="n">
-        <v>0.413978</v>
+        <v>0.443272</v>
       </c>
     </row>
     <row r="593">
@@ -8123,10 +8123,10 @@
         </is>
       </c>
       <c r="B593" t="n">
-        <v>0.067699</v>
+        <v>0.052966</v>
       </c>
       <c r="C593" t="n">
-        <v>0.41129</v>
+        <v>0.440633</v>
       </c>
     </row>
     <row r="594">
@@ -8136,10 +8136,10 @@
         </is>
       </c>
       <c r="B594" t="n">
-        <v>0.068151</v>
+        <v>0.053108</v>
       </c>
       <c r="C594" t="n">
-        <v>0.408602</v>
+        <v>0.437995</v>
       </c>
     </row>
     <row r="595">
@@ -8149,10 +8149,10 @@
         </is>
       </c>
       <c r="B595" t="n">
-        <v>0.068244</v>
+        <v>0.053347</v>
       </c>
       <c r="C595" t="n">
-        <v>0.405914</v>
+        <v>0.435356</v>
       </c>
     </row>
     <row r="596">
@@ -8162,10 +8162,10 @@
         </is>
       </c>
       <c r="B596" t="n">
-        <v>0.068412</v>
+        <v>0.053637</v>
       </c>
       <c r="C596" t="n">
-        <v>0.403226</v>
+        <v>0.432718</v>
       </c>
     </row>
     <row r="597">
@@ -8175,10 +8175,10 @@
         </is>
       </c>
       <c r="B597" t="n">
-        <v>0.06931</v>
+        <v>0.05395</v>
       </c>
       <c r="C597" t="n">
-        <v>0.400538</v>
+        <v>0.430079</v>
       </c>
     </row>
     <row r="598">
@@ -8188,10 +8188,10 @@
         </is>
       </c>
       <c r="B598" t="n">
-        <v>0.069476</v>
+        <v>0.054049</v>
       </c>
       <c r="C598" t="n">
-        <v>0.397849</v>
+        <v>0.427441</v>
       </c>
     </row>
     <row r="599">
@@ -8201,10 +8201,10 @@
         </is>
       </c>
       <c r="B599" t="n">
-        <v>0.069582</v>
+        <v>0.055818</v>
       </c>
       <c r="C599" t="n">
-        <v>0.395161</v>
+        <v>0.424802</v>
       </c>
     </row>
     <row r="600">
@@ -8214,10 +8214,10 @@
         </is>
       </c>
       <c r="B600" t="n">
-        <v>0.069697</v>
+        <v>0.056125</v>
       </c>
       <c r="C600" t="n">
-        <v>0.392473</v>
+        <v>0.422164</v>
       </c>
     </row>
     <row r="601">
@@ -8227,10 +8227,10 @@
         </is>
       </c>
       <c r="B601" t="n">
-        <v>0.069782</v>
+        <v>0.056418</v>
       </c>
       <c r="C601" t="n">
-        <v>0.389785</v>
+        <v>0.419525</v>
       </c>
     </row>
     <row r="602">
@@ -8240,10 +8240,10 @@
         </is>
       </c>
       <c r="B602" t="n">
-        <v>0.070008</v>
+        <v>0.057111</v>
       </c>
       <c r="C602" t="n">
-        <v>0.387097</v>
+        <v>0.416887</v>
       </c>
     </row>
     <row r="603">
@@ -8253,10 +8253,10 @@
         </is>
       </c>
       <c r="B603" t="n">
-        <v>0.070483</v>
+        <v>0.057387</v>
       </c>
       <c r="C603" t="n">
-        <v>0.384409</v>
+        <v>0.414248</v>
       </c>
     </row>
     <row r="604">
@@ -8266,10 +8266,10 @@
         </is>
       </c>
       <c r="B604" t="n">
-        <v>0.07058200000000001</v>
+        <v>0.057824</v>
       </c>
       <c r="C604" t="n">
-        <v>0.38172</v>
+        <v>0.411609</v>
       </c>
     </row>
     <row r="605">
@@ -8279,10 +8279,10 @@
         </is>
       </c>
       <c r="B605" t="n">
-        <v>0.070634</v>
+        <v>0.058699</v>
       </c>
       <c r="C605" t="n">
-        <v>0.379032</v>
+        <v>0.408971</v>
       </c>
     </row>
     <row r="606">
@@ -8292,10 +8292,10 @@
         </is>
       </c>
       <c r="B606" t="n">
-        <v>0.070712</v>
+        <v>0.060458</v>
       </c>
       <c r="C606" t="n">
-        <v>0.376344</v>
+        <v>0.406332</v>
       </c>
     </row>
     <row r="607">
@@ -8305,10 +8305,10 @@
         </is>
       </c>
       <c r="B607" t="n">
-        <v>0.07160900000000001</v>
+        <v>0.060801</v>
       </c>
       <c r="C607" t="n">
-        <v>0.373656</v>
+        <v>0.403694</v>
       </c>
     </row>
     <row r="608">
@@ -8318,10 +8318,10 @@
         </is>
       </c>
       <c r="B608" t="n">
-        <v>0.07201200000000001</v>
+        <v>0.060996</v>
       </c>
       <c r="C608" t="n">
-        <v>0.370968</v>
+        <v>0.401055</v>
       </c>
     </row>
     <row r="609">
@@ -8331,10 +8331,10 @@
         </is>
       </c>
       <c r="B609" t="n">
-        <v>0.072146</v>
+        <v>0.062293</v>
       </c>
       <c r="C609" t="n">
-        <v>0.36828</v>
+        <v>0.398417</v>
       </c>
     </row>
     <row r="610">
@@ -8344,10 +8344,10 @@
         </is>
       </c>
       <c r="B610" t="n">
-        <v>0.07244399999999999</v>
+        <v>0.062308</v>
       </c>
       <c r="C610" t="n">
-        <v>0.365591</v>
+        <v>0.395778</v>
       </c>
     </row>
     <row r="611">
@@ -8357,10 +8357,10 @@
         </is>
       </c>
       <c r="B611" t="n">
-        <v>0.072625</v>
+        <v>0.06250600000000001</v>
       </c>
       <c r="C611" t="n">
-        <v>0.362903</v>
+        <v>0.39314</v>
       </c>
     </row>
     <row r="612">
@@ -8370,10 +8370,10 @@
         </is>
       </c>
       <c r="B612" t="n">
-        <v>0.072738</v>
+        <v>0.06268799999999999</v>
       </c>
       <c r="C612" t="n">
-        <v>0.360215</v>
+        <v>0.390501</v>
       </c>
     </row>
     <row r="613">
@@ -8383,10 +8383,10 @@
         </is>
       </c>
       <c r="B613" t="n">
-        <v>0.073739</v>
+        <v>0.06293700000000001</v>
       </c>
       <c r="C613" t="n">
-        <v>0.357527</v>
+        <v>0.387863</v>
       </c>
     </row>
     <row r="614">
@@ -8396,10 +8396,10 @@
         </is>
       </c>
       <c r="B614" t="n">
-        <v>0.073985</v>
+        <v>0.063111</v>
       </c>
       <c r="C614" t="n">
-        <v>0.354839</v>
+        <v>0.385224</v>
       </c>
     </row>
     <row r="615">
@@ -8409,10 +8409,10 @@
         </is>
       </c>
       <c r="B615" t="n">
-        <v>0.074637</v>
+        <v>0.06339400000000001</v>
       </c>
       <c r="C615" t="n">
-        <v>0.352151</v>
+        <v>0.382586</v>
       </c>
     </row>
     <row r="616">
@@ -8422,10 +8422,10 @@
         </is>
       </c>
       <c r="B616" t="n">
-        <v>0.075277</v>
+        <v>0.063467</v>
       </c>
       <c r="C616" t="n">
-        <v>0.349462</v>
+        <v>0.379947</v>
       </c>
     </row>
     <row r="617">
@@ -8435,10 +8435,10 @@
         </is>
       </c>
       <c r="B617" t="n">
-        <v>0.075353</v>
+        <v>0.06383800000000001</v>
       </c>
       <c r="C617" t="n">
-        <v>0.346774</v>
+        <v>0.377309</v>
       </c>
     </row>
     <row r="618">
@@ -8448,10 +8448,10 @@
         </is>
       </c>
       <c r="B618" t="n">
-        <v>0.075672</v>
+        <v>0.06404600000000001</v>
       </c>
       <c r="C618" t="n">
-        <v>0.344086</v>
+        <v>0.37467</v>
       </c>
     </row>
     <row r="619">
@@ -8461,10 +8461,10 @@
         </is>
       </c>
       <c r="B619" t="n">
-        <v>0.075724</v>
+        <v>0.064246</v>
       </c>
       <c r="C619" t="n">
-        <v>0.341398</v>
+        <v>0.372032</v>
       </c>
     </row>
     <row r="620">
@@ -8474,10 +8474,10 @@
         </is>
       </c>
       <c r="B620" t="n">
-        <v>0.07589</v>
+        <v>0.064315</v>
       </c>
       <c r="C620" t="n">
-        <v>0.33871</v>
+        <v>0.369393</v>
       </c>
     </row>
     <row r="621">
@@ -8487,10 +8487,10 @@
         </is>
       </c>
       <c r="B621" t="n">
-        <v>0.076736</v>
+        <v>0.064414</v>
       </c>
       <c r="C621" t="n">
-        <v>0.336022</v>
+        <v>0.366755</v>
       </c>
     </row>
     <row r="622">
@@ -8500,10 +8500,10 @@
         </is>
       </c>
       <c r="B622" t="n">
-        <v>0.07705099999999999</v>
+        <v>0.064482</v>
       </c>
       <c r="C622" t="n">
-        <v>0.333333</v>
+        <v>0.364116</v>
       </c>
     </row>
     <row r="623">
@@ -8513,10 +8513,10 @@
         </is>
       </c>
       <c r="B623" t="n">
-        <v>0.07832500000000001</v>
+        <v>0.065289</v>
       </c>
       <c r="C623" t="n">
-        <v>0.330645</v>
+        <v>0.361478</v>
       </c>
     </row>
     <row r="624">
@@ -8526,10 +8526,10 @@
         </is>
       </c>
       <c r="B624" t="n">
-        <v>0.07935</v>
+        <v>0.06533700000000001</v>
       </c>
       <c r="C624" t="n">
-        <v>0.327957</v>
+        <v>0.358839</v>
       </c>
     </row>
     <row r="625">
@@ -8539,10 +8539,10 @@
         </is>
       </c>
       <c r="B625" t="n">
-        <v>0.07962</v>
+        <v>0.06553299999999999</v>
       </c>
       <c r="C625" t="n">
-        <v>0.325269</v>
+        <v>0.356201</v>
       </c>
     </row>
     <row r="626">
@@ -8552,10 +8552,10 @@
         </is>
       </c>
       <c r="B626" t="n">
-        <v>0.080682</v>
+        <v>0.065595</v>
       </c>
       <c r="C626" t="n">
-        <v>0.322581</v>
+        <v>0.353562</v>
       </c>
     </row>
     <row r="627">
@@ -8565,10 +8565,10 @@
         </is>
       </c>
       <c r="B627" t="n">
-        <v>0.081625</v>
+        <v>0.06633500000000001</v>
       </c>
       <c r="C627" t="n">
-        <v>0.319892</v>
+        <v>0.350923</v>
       </c>
     </row>
     <row r="628">
@@ -8578,10 +8578,10 @@
         </is>
       </c>
       <c r="B628" t="n">
-        <v>0.081983</v>
+        <v>0.066376</v>
       </c>
       <c r="C628" t="n">
-        <v>0.317204</v>
+        <v>0.348285</v>
       </c>
     </row>
     <row r="629">
@@ -8591,10 +8591,10 @@
         </is>
       </c>
       <c r="B629" t="n">
-        <v>0.084212</v>
+        <v>0.066542</v>
       </c>
       <c r="C629" t="n">
-        <v>0.314516</v>
+        <v>0.345646</v>
       </c>
     </row>
     <row r="630">
@@ -8604,10 +8604,10 @@
         </is>
       </c>
       <c r="B630" t="n">
-        <v>0.084313</v>
+        <v>0.06743300000000001</v>
       </c>
       <c r="C630" t="n">
-        <v>0.311828</v>
+        <v>0.343008</v>
       </c>
     </row>
     <row r="631">
@@ -8617,10 +8617,10 @@
         </is>
       </c>
       <c r="B631" t="n">
-        <v>0.084507</v>
+        <v>0.06763</v>
       </c>
       <c r="C631" t="n">
-        <v>0.30914</v>
+        <v>0.340369</v>
       </c>
     </row>
     <row r="632">
@@ -8630,10 +8630,10 @@
         </is>
       </c>
       <c r="B632" t="n">
-        <v>0.085103</v>
+        <v>0.068096</v>
       </c>
       <c r="C632" t="n">
-        <v>0.306452</v>
+        <v>0.337731</v>
       </c>
     </row>
     <row r="633">
@@ -8643,10 +8643,10 @@
         </is>
       </c>
       <c r="B633" t="n">
-        <v>0.085295</v>
+        <v>0.06876500000000001</v>
       </c>
       <c r="C633" t="n">
-        <v>0.303763</v>
+        <v>0.335092</v>
       </c>
     </row>
     <row r="634">
@@ -8656,10 +8656,10 @@
         </is>
       </c>
       <c r="B634" t="n">
-        <v>0.085727</v>
+        <v>0.069602</v>
       </c>
       <c r="C634" t="n">
-        <v>0.301075</v>
+        <v>0.332454</v>
       </c>
     </row>
     <row r="635">
@@ -8669,10 +8669,10 @@
         </is>
       </c>
       <c r="B635" t="n">
-        <v>0.085993</v>
+        <v>0.06992900000000001</v>
       </c>
       <c r="C635" t="n">
-        <v>0.298387</v>
+        <v>0.329815</v>
       </c>
     </row>
     <row r="636">
@@ -8682,10 +8682,10 @@
         </is>
       </c>
       <c r="B636" t="n">
-        <v>0.08623400000000001</v>
+        <v>0.06995700000000001</v>
       </c>
       <c r="C636" t="n">
-        <v>0.295699</v>
+        <v>0.327177</v>
       </c>
     </row>
     <row r="637">
@@ -8695,10 +8695,10 @@
         </is>
       </c>
       <c r="B637" t="n">
-        <v>0.08643000000000001</v>
+        <v>0.070106</v>
       </c>
       <c r="C637" t="n">
-        <v>0.293011</v>
+        <v>0.324538</v>
       </c>
     </row>
     <row r="638">
@@ -8708,10 +8708,10 @@
         </is>
       </c>
       <c r="B638" t="n">
-        <v>0.08701</v>
+        <v>0.071354</v>
       </c>
       <c r="C638" t="n">
-        <v>0.290323</v>
+        <v>0.3219</v>
       </c>
     </row>
     <row r="639">
@@ -8721,10 +8721,10 @@
         </is>
       </c>
       <c r="B639" t="n">
-        <v>0.087683</v>
+        <v>0.07140199999999999</v>
       </c>
       <c r="C639" t="n">
-        <v>0.287634</v>
+        <v>0.319261</v>
       </c>
     </row>
     <row r="640">
@@ -8734,10 +8734,10 @@
         </is>
       </c>
       <c r="B640" t="n">
-        <v>0.087899</v>
+        <v>0.07191</v>
       </c>
       <c r="C640" t="n">
-        <v>0.284946</v>
+        <v>0.316623</v>
       </c>
     </row>
     <row r="641">
@@ -8747,10 +8747,10 @@
         </is>
       </c>
       <c r="B641" t="n">
-        <v>0.08860800000000001</v>
+        <v>0.0721</v>
       </c>
       <c r="C641" t="n">
-        <v>0.282258</v>
+        <v>0.313984</v>
       </c>
     </row>
     <row r="642">
@@ -8760,10 +8760,10 @@
         </is>
       </c>
       <c r="B642" t="n">
-        <v>0.08905200000000001</v>
+        <v>0.072242</v>
       </c>
       <c r="C642" t="n">
-        <v>0.27957</v>
+        <v>0.311346</v>
       </c>
     </row>
     <row r="643">
@@ -8773,10 +8773,10 @@
         </is>
       </c>
       <c r="B643" t="n">
-        <v>0.08945699999999999</v>
+        <v>0.07230499999999999</v>
       </c>
       <c r="C643" t="n">
-        <v>0.276882</v>
+        <v>0.308707</v>
       </c>
     </row>
     <row r="644">
@@ -8786,10 +8786,10 @@
         </is>
       </c>
       <c r="B644" t="n">
-        <v>0.089564</v>
+        <v>0.07351199999999999</v>
       </c>
       <c r="C644" t="n">
-        <v>0.274194</v>
+        <v>0.306069</v>
       </c>
     </row>
     <row r="645">
@@ -8799,10 +8799,10 @@
         </is>
       </c>
       <c r="B645" t="n">
-        <v>0.08956500000000001</v>
+        <v>0.074277</v>
       </c>
       <c r="C645" t="n">
-        <v>0.271505</v>
+        <v>0.30343</v>
       </c>
     </row>
     <row r="646">
@@ -8812,10 +8812,10 @@
         </is>
       </c>
       <c r="B646" t="n">
-        <v>0.089714</v>
+        <v>0.074363</v>
       </c>
       <c r="C646" t="n">
-        <v>0.268817</v>
+        <v>0.300792</v>
       </c>
     </row>
     <row r="647">
@@ -8825,10 +8825,10 @@
         </is>
       </c>
       <c r="B647" t="n">
-        <v>0.091044</v>
+        <v>0.074653</v>
       </c>
       <c r="C647" t="n">
-        <v>0.266129</v>
+        <v>0.298153</v>
       </c>
     </row>
     <row r="648">
@@ -8838,10 +8838,10 @@
         </is>
       </c>
       <c r="B648" t="n">
-        <v>0.091164</v>
+        <v>0.074903</v>
       </c>
       <c r="C648" t="n">
-        <v>0.263441</v>
+        <v>0.295515</v>
       </c>
     </row>
     <row r="649">
@@ -8851,10 +8851,10 @@
         </is>
       </c>
       <c r="B649" t="n">
-        <v>0.091839</v>
+        <v>0.075792</v>
       </c>
       <c r="C649" t="n">
-        <v>0.260753</v>
+        <v>0.292876</v>
       </c>
     </row>
     <row r="650">
@@ -8864,10 +8864,10 @@
         </is>
       </c>
       <c r="B650" t="n">
-        <v>0.09277100000000001</v>
+        <v>0.077958</v>
       </c>
       <c r="C650" t="n">
-        <v>0.258065</v>
+        <v>0.290237</v>
       </c>
     </row>
     <row r="651">
@@ -8877,10 +8877,10 @@
         </is>
       </c>
       <c r="B651" t="n">
-        <v>0.09286</v>
+        <v>0.078574</v>
       </c>
       <c r="C651" t="n">
-        <v>0.255376</v>
+        <v>0.287599</v>
       </c>
     </row>
     <row r="652">
@@ -8890,10 +8890,10 @@
         </is>
       </c>
       <c r="B652" t="n">
-        <v>0.094002</v>
+        <v>0.079247</v>
       </c>
       <c r="C652" t="n">
-        <v>0.252688</v>
+        <v>0.28496</v>
       </c>
     </row>
     <row r="653">
@@ -8903,10 +8903,10 @@
         </is>
       </c>
       <c r="B653" t="n">
-        <v>0.09490700000000001</v>
+        <v>0.080038</v>
       </c>
       <c r="C653" t="n">
-        <v>0.25</v>
+        <v>0.282322</v>
       </c>
     </row>
     <row r="654">
@@ -8916,10 +8916,10 @@
         </is>
       </c>
       <c r="B654" t="n">
-        <v>0.09661</v>
+        <v>0.08017199999999999</v>
       </c>
       <c r="C654" t="n">
-        <v>0.247312</v>
+        <v>0.279683</v>
       </c>
     </row>
     <row r="655">
@@ -8929,10 +8929,10 @@
         </is>
       </c>
       <c r="B655" t="n">
-        <v>0.097039</v>
+        <v>0.080709</v>
       </c>
       <c r="C655" t="n">
-        <v>0.244624</v>
+        <v>0.277045</v>
       </c>
     </row>
     <row r="656">
@@ -8942,10 +8942,10 @@
         </is>
       </c>
       <c r="B656" t="n">
-        <v>0.097856</v>
+        <v>0.081867</v>
       </c>
       <c r="C656" t="n">
-        <v>0.241935</v>
+        <v>0.274406</v>
       </c>
     </row>
     <row r="657">
@@ -8955,10 +8955,10 @@
         </is>
       </c>
       <c r="B657" t="n">
-        <v>0.09825</v>
+        <v>0.08254400000000001</v>
       </c>
       <c r="C657" t="n">
-        <v>0.239247</v>
+        <v>0.271768</v>
       </c>
     </row>
     <row r="658">
@@ -8968,10 +8968,10 @@
         </is>
       </c>
       <c r="B658" t="n">
-        <v>0.099144</v>
+        <v>0.082756</v>
       </c>
       <c r="C658" t="n">
-        <v>0.236559</v>
+        <v>0.269129</v>
       </c>
     </row>
     <row r="659">
@@ -8981,10 +8981,10 @@
         </is>
       </c>
       <c r="B659" t="n">
-        <v>0.099574</v>
+        <v>0.083689</v>
       </c>
       <c r="C659" t="n">
-        <v>0.233871</v>
+        <v>0.266491</v>
       </c>
     </row>
     <row r="660">
@@ -8994,10 +8994,10 @@
         </is>
       </c>
       <c r="B660" t="n">
-        <v>0.100559</v>
+        <v>0.084078</v>
       </c>
       <c r="C660" t="n">
-        <v>0.231183</v>
+        <v>0.263852</v>
       </c>
     </row>
     <row r="661">
@@ -9007,10 +9007,10 @@
         </is>
       </c>
       <c r="B661" t="n">
-        <v>0.101179</v>
+        <v>0.084255</v>
       </c>
       <c r="C661" t="n">
-        <v>0.228495</v>
+        <v>0.261214</v>
       </c>
     </row>
     <row r="662">
@@ -9020,10 +9020,10 @@
         </is>
       </c>
       <c r="B662" t="n">
-        <v>0.101564</v>
+        <v>0.084591</v>
       </c>
       <c r="C662" t="n">
-        <v>0.225806</v>
+        <v>0.258575</v>
       </c>
     </row>
     <row r="663">
@@ -9033,10 +9033,10 @@
         </is>
       </c>
       <c r="B663" t="n">
-        <v>0.101911</v>
+        <v>0.08499900000000001</v>
       </c>
       <c r="C663" t="n">
-        <v>0.223118</v>
+        <v>0.255937</v>
       </c>
     </row>
     <row r="664">
@@ -9046,10 +9046,10 @@
         </is>
       </c>
       <c r="B664" t="n">
-        <v>0.101967</v>
+        <v>0.085302</v>
       </c>
       <c r="C664" t="n">
-        <v>0.22043</v>
+        <v>0.253298</v>
       </c>
     </row>
     <row r="665">
@@ -9059,10 +9059,10 @@
         </is>
       </c>
       <c r="B665" t="n">
-        <v>0.103645</v>
+        <v>0.08569599999999999</v>
       </c>
       <c r="C665" t="n">
-        <v>0.217742</v>
+        <v>0.25066</v>
       </c>
     </row>
     <row r="666">
@@ -9072,10 +9072,10 @@
         </is>
       </c>
       <c r="B666" t="n">
-        <v>0.104232</v>
+        <v>0.086089</v>
       </c>
       <c r="C666" t="n">
-        <v>0.215054</v>
+        <v>0.248021</v>
       </c>
     </row>
     <row r="667">
@@ -9085,10 +9085,10 @@
         </is>
       </c>
       <c r="B667" t="n">
-        <v>0.105014</v>
+        <v>0.086158</v>
       </c>
       <c r="C667" t="n">
-        <v>0.212366</v>
+        <v>0.245383</v>
       </c>
     </row>
     <row r="668">
@@ -9098,10 +9098,10 @@
         </is>
       </c>
       <c r="B668" t="n">
-        <v>0.105229</v>
+        <v>0.086745</v>
       </c>
       <c r="C668" t="n">
-        <v>0.209677</v>
+        <v>0.242744</v>
       </c>
     </row>
     <row r="669">
@@ -9111,10 +9111,10 @@
         </is>
       </c>
       <c r="B669" t="n">
-        <v>0.105369</v>
+        <v>0.087252</v>
       </c>
       <c r="C669" t="n">
-        <v>0.206989</v>
+        <v>0.240106</v>
       </c>
     </row>
     <row r="670">
@@ -9124,10 +9124,10 @@
         </is>
       </c>
       <c r="B670" t="n">
-        <v>0.106591</v>
+        <v>0.087782</v>
       </c>
       <c r="C670" t="n">
-        <v>0.204301</v>
+        <v>0.237467</v>
       </c>
     </row>
     <row r="671">
@@ -9137,10 +9137,10 @@
         </is>
       </c>
       <c r="B671" t="n">
-        <v>0.110929</v>
+        <v>0.087934</v>
       </c>
       <c r="C671" t="n">
-        <v>0.201613</v>
+        <v>0.234828</v>
       </c>
     </row>
     <row r="672">
@@ -9150,10 +9150,10 @@
         </is>
       </c>
       <c r="B672" t="n">
-        <v>0.113882</v>
+        <v>0.088393</v>
       </c>
       <c r="C672" t="n">
-        <v>0.198925</v>
+        <v>0.23219</v>
       </c>
     </row>
     <row r="673">
@@ -9163,10 +9163,10 @@
         </is>
       </c>
       <c r="B673" t="n">
-        <v>0.114167</v>
+        <v>0.088908</v>
       </c>
       <c r="C673" t="n">
-        <v>0.196237</v>
+        <v>0.229551</v>
       </c>
     </row>
     <row r="674">
@@ -9176,10 +9176,10 @@
         </is>
       </c>
       <c r="B674" t="n">
-        <v>0.115454</v>
+        <v>0.089102</v>
       </c>
       <c r="C674" t="n">
-        <v>0.193548</v>
+        <v>0.226913</v>
       </c>
     </row>
     <row r="675">
@@ -9189,10 +9189,10 @@
         </is>
       </c>
       <c r="B675" t="n">
-        <v>0.116249</v>
+        <v>0.089891</v>
       </c>
       <c r="C675" t="n">
-        <v>0.19086</v>
+        <v>0.224274</v>
       </c>
     </row>
     <row r="676">
@@ -9202,10 +9202,10 @@
         </is>
       </c>
       <c r="B676" t="n">
-        <v>0.1177</v>
+        <v>0.090933</v>
       </c>
       <c r="C676" t="n">
-        <v>0.188172</v>
+        <v>0.221636</v>
       </c>
     </row>
     <row r="677">
@@ -9215,10 +9215,10 @@
         </is>
       </c>
       <c r="B677" t="n">
-        <v>0.117744</v>
+        <v>0.091527</v>
       </c>
       <c r="C677" t="n">
-        <v>0.185484</v>
+        <v>0.218997</v>
       </c>
     </row>
     <row r="678">
@@ -9228,10 +9228,10 @@
         </is>
       </c>
       <c r="B678" t="n">
-        <v>0.12079</v>
+        <v>0.091528</v>
       </c>
       <c r="C678" t="n">
-        <v>0.182796</v>
+        <v>0.216359</v>
       </c>
     </row>
     <row r="679">
@@ -9241,10 +9241,10 @@
         </is>
       </c>
       <c r="B679" t="n">
-        <v>0.120819</v>
+        <v>0.09218999999999999</v>
       </c>
       <c r="C679" t="n">
-        <v>0.180108</v>
+        <v>0.21372</v>
       </c>
     </row>
     <row r="680">
@@ -9254,10 +9254,10 @@
         </is>
       </c>
       <c r="B680" t="n">
-        <v>0.121756</v>
+        <v>0.09333</v>
       </c>
       <c r="C680" t="n">
-        <v>0.177419</v>
+        <v>0.211082</v>
       </c>
     </row>
     <row r="681">
@@ -9267,10 +9267,10 @@
         </is>
       </c>
       <c r="B681" t="n">
-        <v>0.122035</v>
+        <v>0.09348099999999999</v>
       </c>
       <c r="C681" t="n">
-        <v>0.174731</v>
+        <v>0.208443</v>
       </c>
     </row>
     <row r="682">
@@ -9280,10 +9280,10 @@
         </is>
       </c>
       <c r="B682" t="n">
-        <v>0.1229</v>
+        <v>0.094362</v>
       </c>
       <c r="C682" t="n">
-        <v>0.172043</v>
+        <v>0.205805</v>
       </c>
     </row>
     <row r="683">
@@ -9293,10 +9293,10 @@
         </is>
       </c>
       <c r="B683" t="n">
-        <v>0.123834</v>
+        <v>0.09581099999999999</v>
       </c>
       <c r="C683" t="n">
-        <v>0.169355</v>
+        <v>0.203166</v>
       </c>
     </row>
     <row r="684">
@@ -9306,10 +9306,10 @@
         </is>
       </c>
       <c r="B684" t="n">
-        <v>0.126745</v>
+        <v>0.095817</v>
       </c>
       <c r="C684" t="n">
-        <v>0.166667</v>
+        <v>0.200528</v>
       </c>
     </row>
     <row r="685">
@@ -9319,10 +9319,10 @@
         </is>
       </c>
       <c r="B685" t="n">
-        <v>0.126914</v>
+        <v>0.097037</v>
       </c>
       <c r="C685" t="n">
-        <v>0.163978</v>
+        <v>0.197889</v>
       </c>
     </row>
     <row r="686">
@@ -9332,10 +9332,10 @@
         </is>
       </c>
       <c r="B686" t="n">
-        <v>0.128783</v>
+        <v>0.09739200000000001</v>
       </c>
       <c r="C686" t="n">
-        <v>0.16129</v>
+        <v>0.195251</v>
       </c>
     </row>
     <row r="687">
@@ -9345,10 +9345,10 @@
         </is>
       </c>
       <c r="B687" t="n">
-        <v>0.128901</v>
+        <v>0.097444</v>
       </c>
       <c r="C687" t="n">
-        <v>0.158602</v>
+        <v>0.192612</v>
       </c>
     </row>
     <row r="688">
@@ -9358,10 +9358,10 @@
         </is>
       </c>
       <c r="B688" t="n">
-        <v>0.129603</v>
+        <v>0.100083</v>
       </c>
       <c r="C688" t="n">
-        <v>0.155914</v>
+        <v>0.189974</v>
       </c>
     </row>
     <row r="689">
@@ -9371,10 +9371,10 @@
         </is>
       </c>
       <c r="B689" t="n">
-        <v>0.130131</v>
+        <v>0.101159</v>
       </c>
       <c r="C689" t="n">
-        <v>0.153226</v>
+        <v>0.187335</v>
       </c>
     </row>
     <row r="690">
@@ -9384,10 +9384,10 @@
         </is>
       </c>
       <c r="B690" t="n">
-        <v>0.132068</v>
+        <v>0.101343</v>
       </c>
       <c r="C690" t="n">
-        <v>0.150538</v>
+        <v>0.184697</v>
       </c>
     </row>
     <row r="691">
@@ -9397,10 +9397,10 @@
         </is>
       </c>
       <c r="B691" t="n">
-        <v>0.132159</v>
+        <v>0.10242</v>
       </c>
       <c r="C691" t="n">
-        <v>0.147849</v>
+        <v>0.182058</v>
       </c>
     </row>
     <row r="692">
@@ -9410,10 +9410,10 @@
         </is>
       </c>
       <c r="B692" t="n">
-        <v>0.133451</v>
+        <v>0.103598</v>
       </c>
       <c r="C692" t="n">
-        <v>0.145161</v>
+        <v>0.17942</v>
       </c>
     </row>
     <row r="693">
@@ -9423,10 +9423,10 @@
         </is>
       </c>
       <c r="B693" t="n">
-        <v>0.133596</v>
+        <v>0.103805</v>
       </c>
       <c r="C693" t="n">
-        <v>0.142473</v>
+        <v>0.176781</v>
       </c>
     </row>
     <row r="694">
@@ -9436,10 +9436,10 @@
         </is>
       </c>
       <c r="B694" t="n">
-        <v>0.133836</v>
+        <v>0.104884</v>
       </c>
       <c r="C694" t="n">
-        <v>0.139785</v>
+        <v>0.174142</v>
       </c>
     </row>
     <row r="695">
@@ -9449,10 +9449,10 @@
         </is>
       </c>
       <c r="B695" t="n">
-        <v>0.134258</v>
+        <v>0.105888</v>
       </c>
       <c r="C695" t="n">
-        <v>0.137097</v>
+        <v>0.171504</v>
       </c>
     </row>
     <row r="696">
@@ -9462,10 +9462,10 @@
         </is>
       </c>
       <c r="B696" t="n">
-        <v>0.134443</v>
+        <v>0.109171</v>
       </c>
       <c r="C696" t="n">
-        <v>0.134409</v>
+        <v>0.168865</v>
       </c>
     </row>
     <row r="697">
@@ -9475,10 +9475,10 @@
         </is>
       </c>
       <c r="B697" t="n">
-        <v>0.134772</v>
+        <v>0.1104</v>
       </c>
       <c r="C697" t="n">
-        <v>0.13172</v>
+        <v>0.166227</v>
       </c>
     </row>
     <row r="698">
@@ -9488,10 +9488,10 @@
         </is>
       </c>
       <c r="B698" t="n">
-        <v>0.134931</v>
+        <v>0.113128</v>
       </c>
       <c r="C698" t="n">
-        <v>0.129032</v>
+        <v>0.163588</v>
       </c>
     </row>
     <row r="699">
@@ -9501,10 +9501,10 @@
         </is>
       </c>
       <c r="B699" t="n">
-        <v>0.13504</v>
+        <v>0.113228</v>
       </c>
       <c r="C699" t="n">
-        <v>0.126344</v>
+        <v>0.16095</v>
       </c>
     </row>
     <row r="700">
@@ -9514,10 +9514,10 @@
         </is>
       </c>
       <c r="B700" t="n">
-        <v>0.136667</v>
+        <v>0.114436</v>
       </c>
       <c r="C700" t="n">
-        <v>0.123656</v>
+        <v>0.158311</v>
       </c>
     </row>
     <row r="701">
@@ -9527,10 +9527,10 @@
         </is>
       </c>
       <c r="B701" t="n">
-        <v>0.138716</v>
+        <v>0.115489</v>
       </c>
       <c r="C701" t="n">
-        <v>0.120968</v>
+        <v>0.155673</v>
       </c>
     </row>
     <row r="702">
@@ -9540,10 +9540,10 @@
         </is>
       </c>
       <c r="B702" t="n">
-        <v>0.139686</v>
+        <v>0.115936</v>
       </c>
       <c r="C702" t="n">
-        <v>0.11828</v>
+        <v>0.153034</v>
       </c>
     </row>
     <row r="703">
@@ -9553,10 +9553,10 @@
         </is>
       </c>
       <c r="B703" t="n">
-        <v>0.139823</v>
+        <v>0.11625</v>
       </c>
       <c r="C703" t="n">
-        <v>0.115591</v>
+        <v>0.150396</v>
       </c>
     </row>
     <row r="704">
@@ -9566,10 +9566,10 @@
         </is>
       </c>
       <c r="B704" t="n">
-        <v>0.152344</v>
+        <v>0.117243</v>
       </c>
       <c r="C704" t="n">
-        <v>0.112903</v>
+        <v>0.147757</v>
       </c>
     </row>
     <row r="705">
@@ -9579,10 +9579,10 @@
         </is>
       </c>
       <c r="B705" t="n">
-        <v>0.158002</v>
+        <v>0.120061</v>
       </c>
       <c r="C705" t="n">
-        <v>0.110215</v>
+        <v>0.145119</v>
       </c>
     </row>
     <row r="706">
@@ -9592,10 +9592,10 @@
         </is>
       </c>
       <c r="B706" t="n">
-        <v>0.158281</v>
+        <v>0.12104</v>
       </c>
       <c r="C706" t="n">
-        <v>0.107527</v>
+        <v>0.14248</v>
       </c>
     </row>
     <row r="707">
@@ -9605,10 +9605,10 @@
         </is>
       </c>
       <c r="B707" t="n">
-        <v>0.159143</v>
+        <v>0.121096</v>
       </c>
       <c r="C707" t="n">
-        <v>0.104839</v>
+        <v>0.139842</v>
       </c>
     </row>
     <row r="708">
@@ -9618,10 +9618,10 @@
         </is>
       </c>
       <c r="B708" t="n">
-        <v>0.159726</v>
+        <v>0.121925</v>
       </c>
       <c r="C708" t="n">
-        <v>0.102151</v>
+        <v>0.137203</v>
       </c>
     </row>
     <row r="709">
@@ -9631,10 +9631,10 @@
         </is>
       </c>
       <c r="B709" t="n">
-        <v>0.159861</v>
+        <v>0.122277</v>
       </c>
       <c r="C709" t="n">
-        <v>0.09946199999999999</v>
+        <v>0.134565</v>
       </c>
     </row>
     <row r="710">
@@ -9644,10 +9644,10 @@
         </is>
       </c>
       <c r="B710" t="n">
-        <v>0.16141</v>
+        <v>0.125319</v>
       </c>
       <c r="C710" t="n">
-        <v>0.096774</v>
+        <v>0.131926</v>
       </c>
     </row>
     <row r="711">
@@ -9657,10 +9657,10 @@
         </is>
       </c>
       <c r="B711" t="n">
-        <v>0.169525</v>
+        <v>0.126292</v>
       </c>
       <c r="C711" t="n">
-        <v>0.094086</v>
+        <v>0.129288</v>
       </c>
     </row>
     <row r="712">
@@ -9670,10 +9670,10 @@
         </is>
       </c>
       <c r="B712" t="n">
-        <v>0.170376</v>
+        <v>0.127738</v>
       </c>
       <c r="C712" t="n">
-        <v>0.09139799999999999</v>
+        <v>0.126649</v>
       </c>
     </row>
     <row r="713">
@@ -9683,10 +9683,10 @@
         </is>
       </c>
       <c r="B713" t="n">
-        <v>0.171855</v>
+        <v>0.128052</v>
       </c>
       <c r="C713" t="n">
-        <v>0.08871</v>
+        <v>0.124011</v>
       </c>
     </row>
     <row r="714">
@@ -9696,10 +9696,10 @@
         </is>
       </c>
       <c r="B714" t="n">
-        <v>0.173539</v>
+        <v>0.128094</v>
       </c>
       <c r="C714" t="n">
-        <v>0.086022</v>
+        <v>0.121372</v>
       </c>
     </row>
     <row r="715">
@@ -9709,10 +9709,10 @@
         </is>
       </c>
       <c r="B715" t="n">
-        <v>0.174208</v>
+        <v>0.128592</v>
       </c>
       <c r="C715" t="n">
-        <v>0.083333</v>
+        <v>0.118734</v>
       </c>
     </row>
     <row r="716">
@@ -9722,10 +9722,10 @@
         </is>
       </c>
       <c r="B716" t="n">
-        <v>0.178201</v>
+        <v>0.130809</v>
       </c>
       <c r="C716" t="n">
-        <v>0.08064499999999999</v>
+        <v>0.116095</v>
       </c>
     </row>
     <row r="717">
@@ -9735,10 +9735,10 @@
         </is>
       </c>
       <c r="B717" t="n">
-        <v>0.180948</v>
+        <v>0.131556</v>
       </c>
       <c r="C717" t="n">
-        <v>0.077957</v>
+        <v>0.113456</v>
       </c>
     </row>
     <row r="718">
@@ -9748,10 +9748,10 @@
         </is>
       </c>
       <c r="B718" t="n">
-        <v>0.185535</v>
+        <v>0.13259</v>
       </c>
       <c r="C718" t="n">
-        <v>0.075269</v>
+        <v>0.110818</v>
       </c>
     </row>
     <row r="719">
@@ -9761,10 +9761,10 @@
         </is>
       </c>
       <c r="B719" t="n">
-        <v>0.18592</v>
+        <v>0.132761</v>
       </c>
       <c r="C719" t="n">
-        <v>0.07258100000000001</v>
+        <v>0.108179</v>
       </c>
     </row>
     <row r="720">
@@ -9774,10 +9774,10 @@
         </is>
       </c>
       <c r="B720" t="n">
-        <v>0.186413</v>
+        <v>0.132941</v>
       </c>
       <c r="C720" t="n">
-        <v>0.069892</v>
+        <v>0.105541</v>
       </c>
     </row>
     <row r="721">
@@ -9787,10 +9787,10 @@
         </is>
       </c>
       <c r="B721" t="n">
-        <v>0.189976</v>
+        <v>0.133128</v>
       </c>
       <c r="C721" t="n">
-        <v>0.067204</v>
+        <v>0.102902</v>
       </c>
     </row>
     <row r="722">
@@ -9800,10 +9800,10 @@
         </is>
       </c>
       <c r="B722" t="n">
-        <v>0.190804</v>
+        <v>0.13327</v>
       </c>
       <c r="C722" t="n">
-        <v>0.064516</v>
+        <v>0.100264</v>
       </c>
     </row>
     <row r="723">
@@ -9813,10 +9813,10 @@
         </is>
       </c>
       <c r="B723" t="n">
-        <v>0.194014</v>
+        <v>0.133815</v>
       </c>
       <c r="C723" t="n">
-        <v>0.061828</v>
+        <v>0.097625</v>
       </c>
     </row>
     <row r="724">
@@ -9826,10 +9826,10 @@
         </is>
       </c>
       <c r="B724" t="n">
-        <v>0.21152</v>
+        <v>0.133895</v>
       </c>
       <c r="C724" t="n">
-        <v>0.05914</v>
+        <v>0.094987</v>
       </c>
     </row>
     <row r="725">
@@ -9839,10 +9839,10 @@
         </is>
       </c>
       <c r="B725" t="n">
-        <v>0.214346</v>
+        <v>0.138455</v>
       </c>
       <c r="C725" t="n">
-        <v>0.056452</v>
+        <v>0.092348</v>
       </c>
     </row>
     <row r="726">
@@ -9852,10 +9852,10 @@
         </is>
       </c>
       <c r="B726" t="n">
-        <v>0.217108</v>
+        <v>0.138506</v>
       </c>
       <c r="C726" t="n">
-        <v>0.053763</v>
+        <v>0.08971</v>
       </c>
     </row>
     <row r="727">
@@ -9865,10 +9865,10 @@
         </is>
       </c>
       <c r="B727" t="n">
-        <v>0.219344</v>
+        <v>0.145445</v>
       </c>
       <c r="C727" t="n">
-        <v>0.051075</v>
+        <v>0.087071</v>
       </c>
     </row>
     <row r="728">
@@ -9878,10 +9878,10 @@
         </is>
       </c>
       <c r="B728" t="n">
-        <v>0.221036</v>
+        <v>0.153444</v>
       </c>
       <c r="C728" t="n">
-        <v>0.048387</v>
+        <v>0.08443299999999999</v>
       </c>
     </row>
     <row r="729">
@@ -9891,10 +9891,10 @@
         </is>
       </c>
       <c r="B729" t="n">
-        <v>0.227698</v>
+        <v>0.157043</v>
       </c>
       <c r="C729" t="n">
-        <v>0.045699</v>
+        <v>0.08179400000000001</v>
       </c>
     </row>
     <row r="730">
@@ -9904,10 +9904,10 @@
         </is>
       </c>
       <c r="B730" t="n">
-        <v>0.228679</v>
+        <v>0.157661</v>
       </c>
       <c r="C730" t="n">
-        <v>0.043011</v>
+        <v>0.079156</v>
       </c>
     </row>
     <row r="731">
@@ -9917,10 +9917,10 @@
         </is>
       </c>
       <c r="B731" t="n">
-        <v>0.231609</v>
+        <v>0.158875</v>
       </c>
       <c r="C731" t="n">
-        <v>0.040323</v>
+        <v>0.076517</v>
       </c>
     </row>
     <row r="732">
@@ -9930,10 +9930,10 @@
         </is>
       </c>
       <c r="B732" t="n">
-        <v>0.239083</v>
+        <v>0.161055</v>
       </c>
       <c r="C732" t="n">
-        <v>0.037634</v>
+        <v>0.073879</v>
       </c>
     </row>
     <row r="733">
@@ -9943,10 +9943,10 @@
         </is>
       </c>
       <c r="B733" t="n">
-        <v>0.249958</v>
+        <v>0.161699</v>
       </c>
       <c r="C733" t="n">
-        <v>0.034946</v>
+        <v>0.07124</v>
       </c>
     </row>
     <row r="734">
@@ -9956,10 +9956,10 @@
         </is>
       </c>
       <c r="B734" t="n">
-        <v>0.255318</v>
+        <v>0.165547</v>
       </c>
       <c r="C734" t="n">
-        <v>0.032258</v>
+        <v>0.068602</v>
       </c>
     </row>
     <row r="735">
@@ -9969,10 +9969,10 @@
         </is>
       </c>
       <c r="B735" t="n">
-        <v>0.286169</v>
+        <v>0.168252</v>
       </c>
       <c r="C735" t="n">
-        <v>0.02957</v>
+        <v>0.06596299999999999</v>
       </c>
     </row>
     <row r="736">
@@ -9982,10 +9982,10 @@
         </is>
       </c>
       <c r="B736" t="n">
-        <v>0.29321</v>
+        <v>0.16997</v>
       </c>
       <c r="C736" t="n">
-        <v>0.026882</v>
+        <v>0.06332500000000001</v>
       </c>
     </row>
     <row r="737">
@@ -9995,10 +9995,10 @@
         </is>
       </c>
       <c r="B737" t="n">
-        <v>0.29501</v>
+        <v>0.170729</v>
       </c>
       <c r="C737" t="n">
-        <v>0.024194</v>
+        <v>0.060686</v>
       </c>
     </row>
     <row r="738">
@@ -10008,10 +10008,10 @@
         </is>
       </c>
       <c r="B738" t="n">
-        <v>0.33484</v>
+        <v>0.172047</v>
       </c>
       <c r="C738" t="n">
-        <v>0.021505</v>
+        <v>0.058047</v>
       </c>
     </row>
     <row r="739">
@@ -10021,10 +10021,10 @@
         </is>
       </c>
       <c r="B739" t="n">
-        <v>0.339735</v>
+        <v>0.173745</v>
       </c>
       <c r="C739" t="n">
-        <v>0.018817</v>
+        <v>0.055409</v>
       </c>
     </row>
     <row r="740">
@@ -10034,10 +10034,10 @@
         </is>
       </c>
       <c r="B740" t="n">
-        <v>0.340999</v>
+        <v>0.183189</v>
       </c>
       <c r="C740" t="n">
-        <v>0.016129</v>
+        <v>0.05277</v>
       </c>
     </row>
     <row r="741">
@@ -10047,10 +10047,10 @@
         </is>
       </c>
       <c r="B741" t="n">
-        <v>0.376465</v>
+        <v>0.186865</v>
       </c>
       <c r="C741" t="n">
-        <v>0.013441</v>
+        <v>0.050132</v>
       </c>
     </row>
     <row r="742">
@@ -10060,10 +10060,10 @@
         </is>
       </c>
       <c r="B742" t="n">
-        <v>0.391022</v>
+        <v>0.189108</v>
       </c>
       <c r="C742" t="n">
-        <v>0.010753</v>
+        <v>0.047493</v>
       </c>
     </row>
     <row r="743">
@@ -10073,10 +10073,10 @@
         </is>
       </c>
       <c r="B743" t="n">
-        <v>0.435504</v>
+        <v>0.189862</v>
       </c>
       <c r="C743" t="n">
-        <v>0.008064999999999999</v>
+        <v>0.044855</v>
       </c>
     </row>
     <row r="744">
@@ -10086,10 +10086,10 @@
         </is>
       </c>
       <c r="B744" t="n">
-        <v>0.632473</v>
+        <v>0.19512</v>
       </c>
       <c r="C744" t="n">
-        <v>0.005376</v>
+        <v>0.042216</v>
       </c>
     </row>
     <row r="745">
@@ -10099,10 +10099,192 @@
         </is>
       </c>
       <c r="B745" t="n">
-        <v>0.6656029999999999</v>
+        <v>0.200625</v>
       </c>
       <c r="C745" t="n">
-        <v>0.002688</v>
+        <v>0.039578</v>
+      </c>
+    </row>
+    <row r="746">
+      <c r="A746" t="inlineStr">
+        <is>
+          <t>Adjusted target</t>
+        </is>
+      </c>
+      <c r="B746" t="n">
+        <v>0.203039</v>
+      </c>
+      <c r="C746" t="n">
+        <v>0.036939</v>
+      </c>
+    </row>
+    <row r="747">
+      <c r="A747" t="inlineStr">
+        <is>
+          <t>Adjusted target</t>
+        </is>
+      </c>
+      <c r="B747" t="n">
+        <v>0.207801</v>
+      </c>
+      <c r="C747" t="n">
+        <v>0.034301</v>
+      </c>
+    </row>
+    <row r="748">
+      <c r="A748" t="inlineStr">
+        <is>
+          <t>Adjusted target</t>
+        </is>
+      </c>
+      <c r="B748" t="n">
+        <v>0.213063</v>
+      </c>
+      <c r="C748" t="n">
+        <v>0.031662</v>
+      </c>
+    </row>
+    <row r="749">
+      <c r="A749" t="inlineStr">
+        <is>
+          <t>Adjusted target</t>
+        </is>
+      </c>
+      <c r="B749" t="n">
+        <v>0.220211</v>
+      </c>
+      <c r="C749" t="n">
+        <v>0.029024</v>
+      </c>
+    </row>
+    <row r="750">
+      <c r="A750" t="inlineStr">
+        <is>
+          <t>Adjusted target</t>
+        </is>
+      </c>
+      <c r="B750" t="n">
+        <v>0.2314</v>
+      </c>
+      <c r="C750" t="n">
+        <v>0.026385</v>
+      </c>
+    </row>
+    <row r="751">
+      <c r="A751" t="inlineStr">
+        <is>
+          <t>Adjusted target</t>
+        </is>
+      </c>
+      <c r="B751" t="n">
+        <v>0.244745</v>
+      </c>
+      <c r="C751" t="n">
+        <v>0.023747</v>
+      </c>
+    </row>
+    <row r="752">
+      <c r="A752" t="inlineStr">
+        <is>
+          <t>Adjusted target</t>
+        </is>
+      </c>
+      <c r="B752" t="n">
+        <v>0.250994</v>
+      </c>
+      <c r="C752" t="n">
+        <v>0.021108</v>
+      </c>
+    </row>
+    <row r="753">
+      <c r="A753" t="inlineStr">
+        <is>
+          <t>Adjusted target</t>
+        </is>
+      </c>
+      <c r="B753" t="n">
+        <v>0.277456</v>
+      </c>
+      <c r="C753" t="n">
+        <v>0.01847</v>
+      </c>
+    </row>
+    <row r="754">
+      <c r="A754" t="inlineStr">
+        <is>
+          <t>Adjusted target</t>
+        </is>
+      </c>
+      <c r="B754" t="n">
+        <v>0.279457</v>
+      </c>
+      <c r="C754" t="n">
+        <v>0.015831</v>
+      </c>
+    </row>
+    <row r="755">
+      <c r="A755" t="inlineStr">
+        <is>
+          <t>Adjusted target</t>
+        </is>
+      </c>
+      <c r="B755" t="n">
+        <v>0.307116</v>
+      </c>
+      <c r="C755" t="n">
+        <v>0.013193</v>
+      </c>
+    </row>
+    <row r="756">
+      <c r="A756" t="inlineStr">
+        <is>
+          <t>Adjusted target</t>
+        </is>
+      </c>
+      <c r="B756" t="n">
+        <v>0.320037</v>
+      </c>
+      <c r="C756" t="n">
+        <v>0.010554</v>
+      </c>
+    </row>
+    <row r="757">
+      <c r="A757" t="inlineStr">
+        <is>
+          <t>Adjusted target</t>
+        </is>
+      </c>
+      <c r="B757" t="n">
+        <v>0.360489</v>
+      </c>
+      <c r="C757" t="n">
+        <v>0.007915999999999999</v>
+      </c>
+    </row>
+    <row r="758">
+      <c r="A758" t="inlineStr">
+        <is>
+          <t>Adjusted target</t>
+        </is>
+      </c>
+      <c r="B758" t="n">
+        <v>0.375924</v>
+      </c>
+      <c r="C758" t="n">
+        <v>0.005277</v>
+      </c>
+    </row>
+    <row r="759">
+      <c r="A759" t="inlineStr">
+        <is>
+          <t>Adjusted target</t>
+        </is>
+      </c>
+      <c r="B759" t="n">
+        <v>0.422116</v>
+      </c>
+      <c r="C759" t="n">
+        <v>0.002639</v>
       </c>
     </row>
   </sheetData>

--- a/vignettes/vignette-1/tail_exceedance_plot_data.xlsx
+++ b/vignettes/vignette-1/tail_exceedance_plot_data.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C759"/>
+  <dimension ref="A1:C753"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -456,7 +456,7 @@
         <v>9.3e-05</v>
       </c>
       <c r="C3" t="n">
-        <v>0.9973610000000001</v>
+        <v>0.99734</v>
       </c>
     </row>
     <row r="4">
@@ -469,7 +469,7 @@
         <v>0.000441</v>
       </c>
       <c r="C4" t="n">
-        <v>0.994723</v>
+        <v>0.994681</v>
       </c>
     </row>
     <row r="5">
@@ -482,7 +482,7 @@
         <v>0.000522</v>
       </c>
       <c r="C5" t="n">
-        <v>0.992084</v>
+        <v>0.992021</v>
       </c>
     </row>
     <row r="6">
@@ -495,7 +495,7 @@
         <v>0.001163</v>
       </c>
       <c r="C6" t="n">
-        <v>0.989446</v>
+        <v>0.989362</v>
       </c>
     </row>
     <row r="7">
@@ -508,7 +508,7 @@
         <v>0.001681</v>
       </c>
       <c r="C7" t="n">
-        <v>0.986807</v>
+        <v>0.986702</v>
       </c>
     </row>
     <row r="8">
@@ -521,7 +521,7 @@
         <v>0.00295</v>
       </c>
       <c r="C8" t="n">
-        <v>0.984169</v>
+        <v>0.984043</v>
       </c>
     </row>
     <row r="9">
@@ -534,7 +534,7 @@
         <v>0.002998</v>
       </c>
       <c r="C9" t="n">
-        <v>0.98153</v>
+        <v>0.981383</v>
       </c>
     </row>
     <row r="10">
@@ -547,7 +547,7 @@
         <v>0.003455</v>
       </c>
       <c r="C10" t="n">
-        <v>0.978892</v>
+        <v>0.978723</v>
       </c>
     </row>
     <row r="11">
@@ -560,7 +560,7 @@
         <v>0.003769</v>
       </c>
       <c r="C11" t="n">
-        <v>0.976253</v>
+        <v>0.976064</v>
       </c>
     </row>
     <row r="12">
@@ -573,7 +573,7 @@
         <v>0.003788</v>
       </c>
       <c r="C12" t="n">
-        <v>0.973615</v>
+        <v>0.973404</v>
       </c>
     </row>
     <row r="13">
@@ -586,7 +586,7 @@
         <v>0.004717</v>
       </c>
       <c r="C13" t="n">
-        <v>0.970976</v>
+        <v>0.970745</v>
       </c>
     </row>
     <row r="14">
@@ -599,7 +599,7 @@
         <v>0.004779</v>
       </c>
       <c r="C14" t="n">
-        <v>0.968338</v>
+        <v>0.968085</v>
       </c>
     </row>
     <row r="15">
@@ -612,7 +612,7 @@
         <v>0.004912</v>
       </c>
       <c r="C15" t="n">
-        <v>0.965699</v>
+        <v>0.965426</v>
       </c>
     </row>
     <row r="16">
@@ -625,7 +625,7 @@
         <v>0.005429</v>
       </c>
       <c r="C16" t="n">
-        <v>0.9630609999999999</v>
+        <v>0.962766</v>
       </c>
     </row>
     <row r="17">
@@ -638,7 +638,7 @@
         <v>0.005649</v>
       </c>
       <c r="C17" t="n">
-        <v>0.960422</v>
+        <v>0.960106</v>
       </c>
     </row>
     <row r="18">
@@ -651,7 +651,7 @@
         <v>0.00593</v>
       </c>
       <c r="C18" t="n">
-        <v>0.957784</v>
+        <v>0.957447</v>
       </c>
     </row>
     <row r="19">
@@ -664,7 +664,7 @@
         <v>0.006143</v>
       </c>
       <c r="C19" t="n">
-        <v>0.955145</v>
+        <v>0.9547870000000001</v>
       </c>
     </row>
     <row r="20">
@@ -677,7 +677,7 @@
         <v>0.006394</v>
       </c>
       <c r="C20" t="n">
-        <v>0.952507</v>
+        <v>0.952128</v>
       </c>
     </row>
     <row r="21">
@@ -690,7 +690,7 @@
         <v>0.006914</v>
       </c>
       <c r="C21" t="n">
-        <v>0.949868</v>
+        <v>0.949468</v>
       </c>
     </row>
     <row r="22">
@@ -703,7 +703,7 @@
         <v>0.007419</v>
       </c>
       <c r="C22" t="n">
-        <v>0.94723</v>
+        <v>0.946809</v>
       </c>
     </row>
     <row r="23">
@@ -716,7 +716,7 @@
         <v>0.007582</v>
       </c>
       <c r="C23" t="n">
-        <v>0.944591</v>
+        <v>0.944149</v>
       </c>
     </row>
     <row r="24">
@@ -729,7 +729,7 @@
         <v>0.008029</v>
       </c>
       <c r="C24" t="n">
-        <v>0.941953</v>
+        <v>0.941489</v>
       </c>
     </row>
     <row r="25">
@@ -742,7 +742,7 @@
         <v>0.008069</v>
       </c>
       <c r="C25" t="n">
-        <v>0.939314</v>
+        <v>0.9388300000000001</v>
       </c>
     </row>
     <row r="26">
@@ -755,7 +755,7 @@
         <v>0.008173</v>
       </c>
       <c r="C26" t="n">
-        <v>0.936675</v>
+        <v>0.9361699999999999</v>
       </c>
     </row>
     <row r="27">
@@ -768,7 +768,7 @@
         <v>0.008377000000000001</v>
       </c>
       <c r="C27" t="n">
-        <v>0.934037</v>
+        <v>0.933511</v>
       </c>
     </row>
     <row r="28">
@@ -781,7 +781,7 @@
         <v>0.008593999999999999</v>
       </c>
       <c r="C28" t="n">
-        <v>0.9313979999999999</v>
+        <v>0.930851</v>
       </c>
     </row>
     <row r="29">
@@ -794,7 +794,7 @@
         <v>0.008658000000000001</v>
       </c>
       <c r="C29" t="n">
-        <v>0.92876</v>
+        <v>0.928191</v>
       </c>
     </row>
     <row r="30">
@@ -807,7 +807,7 @@
         <v>0.008992</v>
       </c>
       <c r="C30" t="n">
-        <v>0.926121</v>
+        <v>0.925532</v>
       </c>
     </row>
     <row r="31">
@@ -820,7 +820,7 @@
         <v>0.009165</v>
       </c>
       <c r="C31" t="n">
-        <v>0.9234830000000001</v>
+        <v>0.922872</v>
       </c>
     </row>
     <row r="32">
@@ -833,7 +833,7 @@
         <v>0.009428000000000001</v>
       </c>
       <c r="C32" t="n">
-        <v>0.920844</v>
+        <v>0.9202129999999999</v>
       </c>
     </row>
     <row r="33">
@@ -846,7 +846,7 @@
         <v>0.009578</v>
       </c>
       <c r="C33" t="n">
-        <v>0.918206</v>
+        <v>0.917553</v>
       </c>
     </row>
     <row r="34">
@@ -859,7 +859,7 @@
         <v>0.009774</v>
       </c>
       <c r="C34" t="n">
-        <v>0.915567</v>
+        <v>0.914894</v>
       </c>
     </row>
     <row r="35">
@@ -872,7 +872,7 @@
         <v>0.009811</v>
       </c>
       <c r="C35" t="n">
-        <v>0.912929</v>
+        <v>0.912234</v>
       </c>
     </row>
     <row r="36">
@@ -885,7 +885,7 @@
         <v>0.010226</v>
       </c>
       <c r="C36" t="n">
-        <v>0.91029</v>
+        <v>0.909574</v>
       </c>
     </row>
     <row r="37">
@@ -898,7 +898,7 @@
         <v>0.010518</v>
       </c>
       <c r="C37" t="n">
-        <v>0.907652</v>
+        <v>0.906915</v>
       </c>
     </row>
     <row r="38">
@@ -911,7 +911,7 @@
         <v>0.010943</v>
       </c>
       <c r="C38" t="n">
-        <v>0.905013</v>
+        <v>0.904255</v>
       </c>
     </row>
     <row r="39">
@@ -924,7 +924,7 @@
         <v>0.011156</v>
       </c>
       <c r="C39" t="n">
-        <v>0.902375</v>
+        <v>0.901596</v>
       </c>
     </row>
     <row r="40">
@@ -937,7 +937,7 @@
         <v>0.011326</v>
       </c>
       <c r="C40" t="n">
-        <v>0.899736</v>
+        <v>0.898936</v>
       </c>
     </row>
     <row r="41">
@@ -950,7 +950,7 @@
         <v>0.01145</v>
       </c>
       <c r="C41" t="n">
-        <v>0.897098</v>
+        <v>0.896277</v>
       </c>
     </row>
     <row r="42">
@@ -963,7 +963,7 @@
         <v>0.012002</v>
       </c>
       <c r="C42" t="n">
-        <v>0.894459</v>
+        <v>0.893617</v>
       </c>
     </row>
     <row r="43">
@@ -976,7 +976,7 @@
         <v>0.012035</v>
       </c>
       <c r="C43" t="n">
-        <v>0.891821</v>
+        <v>0.890957</v>
       </c>
     </row>
     <row r="44">
@@ -989,7 +989,7 @@
         <v>0.012747</v>
       </c>
       <c r="C44" t="n">
-        <v>0.889182</v>
+        <v>0.888298</v>
       </c>
     </row>
     <row r="45">
@@ -1002,7 +1002,7 @@
         <v>0.012918</v>
       </c>
       <c r="C45" t="n">
-        <v>0.886544</v>
+        <v>0.885638</v>
       </c>
     </row>
     <row r="46">
@@ -1015,7 +1015,7 @@
         <v>0.013714</v>
       </c>
       <c r="C46" t="n">
-        <v>0.8839050000000001</v>
+        <v>0.882979</v>
       </c>
     </row>
     <row r="47">
@@ -1028,7 +1028,7 @@
         <v>0.01393</v>
       </c>
       <c r="C47" t="n">
-        <v>0.881266</v>
+        <v>0.880319</v>
       </c>
     </row>
     <row r="48">
@@ -1041,7 +1041,7 @@
         <v>0.013971</v>
       </c>
       <c r="C48" t="n">
-        <v>0.878628</v>
+        <v>0.87766</v>
       </c>
     </row>
     <row r="49">
@@ -1054,7 +1054,7 @@
         <v>0.014018</v>
       </c>
       <c r="C49" t="n">
-        <v>0.875989</v>
+        <v>0.875</v>
       </c>
     </row>
     <row r="50">
@@ -1067,7 +1067,7 @@
         <v>0.014481</v>
       </c>
       <c r="C50" t="n">
-        <v>0.873351</v>
+        <v>0.87234</v>
       </c>
     </row>
     <row r="51">
@@ -1080,7 +1080,7 @@
         <v>0.014731</v>
       </c>
       <c r="C51" t="n">
-        <v>0.870712</v>
+        <v>0.869681</v>
       </c>
     </row>
     <row r="52">
@@ -1093,7 +1093,7 @@
         <v>0.014841</v>
       </c>
       <c r="C52" t="n">
-        <v>0.868074</v>
+        <v>0.867021</v>
       </c>
     </row>
     <row r="53">
@@ -1106,7 +1106,7 @@
         <v>0.01486</v>
       </c>
       <c r="C53" t="n">
-        <v>0.865435</v>
+        <v>0.864362</v>
       </c>
     </row>
     <row r="54">
@@ -1119,7 +1119,7 @@
         <v>0.015041</v>
       </c>
       <c r="C54" t="n">
-        <v>0.862797</v>
+        <v>0.861702</v>
       </c>
     </row>
     <row r="55">
@@ -1132,7 +1132,7 @@
         <v>0.015107</v>
       </c>
       <c r="C55" t="n">
-        <v>0.860158</v>
+        <v>0.859043</v>
       </c>
     </row>
     <row r="56">
@@ -1145,7 +1145,7 @@
         <v>0.015107</v>
       </c>
       <c r="C56" t="n">
-        <v>0.8575199999999999</v>
+        <v>0.856383</v>
       </c>
     </row>
     <row r="57">
@@ -1158,7 +1158,7 @@
         <v>0.015553</v>
       </c>
       <c r="C57" t="n">
-        <v>0.854881</v>
+        <v>0.853723</v>
       </c>
     </row>
     <row r="58">
@@ -1171,7 +1171,7 @@
         <v>0.016031</v>
       </c>
       <c r="C58" t="n">
-        <v>0.852243</v>
+        <v>0.851064</v>
       </c>
     </row>
     <row r="59">
@@ -1184,7 +1184,7 @@
         <v>0.016343</v>
       </c>
       <c r="C59" t="n">
-        <v>0.849604</v>
+        <v>0.848404</v>
       </c>
     </row>
     <row r="60">
@@ -1197,7 +1197,7 @@
         <v>0.016545</v>
       </c>
       <c r="C60" t="n">
-        <v>0.846966</v>
+        <v>0.845745</v>
       </c>
     </row>
     <row r="61">
@@ -1210,7 +1210,7 @@
         <v>0.017135</v>
       </c>
       <c r="C61" t="n">
-        <v>0.844327</v>
+        <v>0.843085</v>
       </c>
     </row>
     <row r="62">
@@ -1223,7 +1223,7 @@
         <v>0.017276</v>
       </c>
       <c r="C62" t="n">
-        <v>0.841689</v>
+        <v>0.840426</v>
       </c>
     </row>
     <row r="63">
@@ -1236,7 +1236,7 @@
         <v>0.017621</v>
       </c>
       <c r="C63" t="n">
-        <v>0.83905</v>
+        <v>0.837766</v>
       </c>
     </row>
     <row r="64">
@@ -1249,7 +1249,7 @@
         <v>0.017975</v>
       </c>
       <c r="C64" t="n">
-        <v>0.836412</v>
+        <v>0.835106</v>
       </c>
     </row>
     <row r="65">
@@ -1259,10 +1259,10 @@
         </is>
       </c>
       <c r="B65" t="n">
-        <v>0.018505</v>
+        <v>0.018257</v>
       </c>
       <c r="C65" t="n">
-        <v>0.833773</v>
+        <v>0.832447</v>
       </c>
     </row>
     <row r="66">
@@ -1272,10 +1272,10 @@
         </is>
       </c>
       <c r="B66" t="n">
-        <v>0.018757</v>
+        <v>0.018505</v>
       </c>
       <c r="C66" t="n">
-        <v>0.831135</v>
+        <v>0.8297870000000001</v>
       </c>
     </row>
     <row r="67">
@@ -1285,10 +1285,10 @@
         </is>
       </c>
       <c r="B67" t="n">
-        <v>0.018801</v>
+        <v>0.018757</v>
       </c>
       <c r="C67" t="n">
-        <v>0.828496</v>
+        <v>0.827128</v>
       </c>
     </row>
     <row r="68">
@@ -1298,10 +1298,10 @@
         </is>
       </c>
       <c r="B68" t="n">
-        <v>0.018847</v>
+        <v>0.018801</v>
       </c>
       <c r="C68" t="n">
-        <v>0.825858</v>
+        <v>0.824468</v>
       </c>
     </row>
     <row r="69">
@@ -1311,10 +1311,10 @@
         </is>
       </c>
       <c r="B69" t="n">
-        <v>0.018931</v>
+        <v>0.018847</v>
       </c>
       <c r="C69" t="n">
-        <v>0.823219</v>
+        <v>0.821809</v>
       </c>
     </row>
     <row r="70">
@@ -1324,10 +1324,10 @@
         </is>
       </c>
       <c r="B70" t="n">
-        <v>0.019352</v>
+        <v>0.018931</v>
       </c>
       <c r="C70" t="n">
-        <v>0.82058</v>
+        <v>0.819149</v>
       </c>
     </row>
     <row r="71">
@@ -1337,10 +1337,10 @@
         </is>
       </c>
       <c r="B71" t="n">
-        <v>0.01962</v>
+        <v>0.019352</v>
       </c>
       <c r="C71" t="n">
-        <v>0.8179419999999999</v>
+        <v>0.816489</v>
       </c>
     </row>
     <row r="72">
@@ -1350,10 +1350,10 @@
         </is>
       </c>
       <c r="B72" t="n">
-        <v>0.019953</v>
+        <v>0.01962</v>
       </c>
       <c r="C72" t="n">
-        <v>0.815303</v>
+        <v>0.8138300000000001</v>
       </c>
     </row>
     <row r="73">
@@ -1363,10 +1363,10 @@
         </is>
       </c>
       <c r="B73" t="n">
-        <v>0.020186</v>
+        <v>0.019953</v>
       </c>
       <c r="C73" t="n">
-        <v>0.812665</v>
+        <v>0.8111699999999999</v>
       </c>
     </row>
     <row r="74">
@@ -1376,10 +1376,10 @@
         </is>
       </c>
       <c r="B74" t="n">
-        <v>0.020393</v>
+        <v>0.020186</v>
       </c>
       <c r="C74" t="n">
-        <v>0.810026</v>
+        <v>0.808511</v>
       </c>
     </row>
     <row r="75">
@@ -1389,10 +1389,10 @@
         </is>
       </c>
       <c r="B75" t="n">
-        <v>0.02048</v>
+        <v>0.020393</v>
       </c>
       <c r="C75" t="n">
-        <v>0.807388</v>
+        <v>0.805851</v>
       </c>
     </row>
     <row r="76">
@@ -1402,10 +1402,10 @@
         </is>
       </c>
       <c r="B76" t="n">
-        <v>0.021572</v>
+        <v>0.02048</v>
       </c>
       <c r="C76" t="n">
-        <v>0.804749</v>
+        <v>0.803191</v>
       </c>
     </row>
     <row r="77">
@@ -1415,10 +1415,10 @@
         </is>
       </c>
       <c r="B77" t="n">
-        <v>0.021604</v>
+        <v>0.021572</v>
       </c>
       <c r="C77" t="n">
-        <v>0.802111</v>
+        <v>0.800532</v>
       </c>
     </row>
     <row r="78">
@@ -1428,10 +1428,10 @@
         </is>
       </c>
       <c r="B78" t="n">
-        <v>0.021912</v>
+        <v>0.021604</v>
       </c>
       <c r="C78" t="n">
-        <v>0.799472</v>
+        <v>0.797872</v>
       </c>
     </row>
     <row r="79">
@@ -1441,10 +1441,10 @@
         </is>
       </c>
       <c r="B79" t="n">
-        <v>0.021918</v>
+        <v>0.021912</v>
       </c>
       <c r="C79" t="n">
-        <v>0.796834</v>
+        <v>0.7952129999999999</v>
       </c>
     </row>
     <row r="80">
@@ -1454,10 +1454,10 @@
         </is>
       </c>
       <c r="B80" t="n">
-        <v>0.021962</v>
+        <v>0.021918</v>
       </c>
       <c r="C80" t="n">
-        <v>0.794195</v>
+        <v>0.792553</v>
       </c>
     </row>
     <row r="81">
@@ -1467,10 +1467,10 @@
         </is>
       </c>
       <c r="B81" t="n">
-        <v>0.022008</v>
+        <v>0.021962</v>
       </c>
       <c r="C81" t="n">
-        <v>0.791557</v>
+        <v>0.789894</v>
       </c>
     </row>
     <row r="82">
@@ -1480,10 +1480,10 @@
         </is>
       </c>
       <c r="B82" t="n">
-        <v>0.022011</v>
+        <v>0.022008</v>
       </c>
       <c r="C82" t="n">
-        <v>0.788918</v>
+        <v>0.787234</v>
       </c>
     </row>
     <row r="83">
@@ -1493,10 +1493,10 @@
         </is>
       </c>
       <c r="B83" t="n">
-        <v>0.022121</v>
+        <v>0.022011</v>
       </c>
       <c r="C83" t="n">
-        <v>0.78628</v>
+        <v>0.784574</v>
       </c>
     </row>
     <row r="84">
@@ -1506,10 +1506,10 @@
         </is>
       </c>
       <c r="B84" t="n">
-        <v>0.022299</v>
+        <v>0.022121</v>
       </c>
       <c r="C84" t="n">
-        <v>0.783641</v>
+        <v>0.781915</v>
       </c>
     </row>
     <row r="85">
@@ -1519,10 +1519,10 @@
         </is>
       </c>
       <c r="B85" t="n">
-        <v>0.022324</v>
+        <v>0.022299</v>
       </c>
       <c r="C85" t="n">
-        <v>0.781003</v>
+        <v>0.779255</v>
       </c>
     </row>
     <row r="86">
@@ -1532,10 +1532,10 @@
         </is>
       </c>
       <c r="B86" t="n">
-        <v>0.022543</v>
+        <v>0.022324</v>
       </c>
       <c r="C86" t="n">
-        <v>0.7783639999999999</v>
+        <v>0.776596</v>
       </c>
     </row>
     <row r="87">
@@ -1545,10 +1545,10 @@
         </is>
       </c>
       <c r="B87" t="n">
-        <v>0.022891</v>
+        <v>0.022543</v>
       </c>
       <c r="C87" t="n">
-        <v>0.775726</v>
+        <v>0.773936</v>
       </c>
     </row>
     <row r="88">
@@ -1558,10 +1558,10 @@
         </is>
       </c>
       <c r="B88" t="n">
-        <v>0.023483</v>
+        <v>0.022891</v>
       </c>
       <c r="C88" t="n">
-        <v>0.773087</v>
+        <v>0.771277</v>
       </c>
     </row>
     <row r="89">
@@ -1571,10 +1571,10 @@
         </is>
       </c>
       <c r="B89" t="n">
-        <v>0.023843</v>
+        <v>0.023483</v>
       </c>
       <c r="C89" t="n">
-        <v>0.7704490000000001</v>
+        <v>0.768617</v>
       </c>
     </row>
     <row r="90">
@@ -1584,10 +1584,10 @@
         </is>
       </c>
       <c r="B90" t="n">
-        <v>0.023991</v>
+        <v>0.023843</v>
       </c>
       <c r="C90" t="n">
-        <v>0.76781</v>
+        <v>0.765957</v>
       </c>
     </row>
     <row r="91">
@@ -1597,10 +1597,10 @@
         </is>
       </c>
       <c r="B91" t="n">
-        <v>0.02408</v>
+        <v>0.023991</v>
       </c>
       <c r="C91" t="n">
-        <v>0.765172</v>
+        <v>0.763298</v>
       </c>
     </row>
     <row r="92">
@@ -1610,10 +1610,10 @@
         </is>
       </c>
       <c r="B92" t="n">
-        <v>0.024413</v>
+        <v>0.02408</v>
       </c>
       <c r="C92" t="n">
-        <v>0.762533</v>
+        <v>0.760638</v>
       </c>
     </row>
     <row r="93">
@@ -1623,10 +1623,10 @@
         </is>
       </c>
       <c r="B93" t="n">
-        <v>0.024896</v>
+        <v>0.024413</v>
       </c>
       <c r="C93" t="n">
-        <v>0.759894</v>
+        <v>0.757979</v>
       </c>
     </row>
     <row r="94">
@@ -1636,10 +1636,10 @@
         </is>
       </c>
       <c r="B94" t="n">
-        <v>0.025327</v>
+        <v>0.024896</v>
       </c>
       <c r="C94" t="n">
-        <v>0.757256</v>
+        <v>0.755319</v>
       </c>
     </row>
     <row r="95">
@@ -1649,10 +1649,10 @@
         </is>
       </c>
       <c r="B95" t="n">
-        <v>0.025416</v>
+        <v>0.025327</v>
       </c>
       <c r="C95" t="n">
-        <v>0.754617</v>
+        <v>0.75266</v>
       </c>
     </row>
     <row r="96">
@@ -1662,10 +1662,10 @@
         </is>
       </c>
       <c r="B96" t="n">
-        <v>0.025544</v>
+        <v>0.025416</v>
       </c>
       <c r="C96" t="n">
-        <v>0.751979</v>
+        <v>0.75</v>
       </c>
     </row>
     <row r="97">
@@ -1675,10 +1675,10 @@
         </is>
       </c>
       <c r="B97" t="n">
-        <v>0.025755</v>
+        <v>0.025544</v>
       </c>
       <c r="C97" t="n">
-        <v>0.74934</v>
+        <v>0.74734</v>
       </c>
     </row>
     <row r="98">
@@ -1688,10 +1688,10 @@
         </is>
       </c>
       <c r="B98" t="n">
-        <v>0.025837</v>
+        <v>0.025755</v>
       </c>
       <c r="C98" t="n">
-        <v>0.746702</v>
+        <v>0.744681</v>
       </c>
     </row>
     <row r="99">
@@ -1704,7 +1704,7 @@
         <v>0.026545</v>
       </c>
       <c r="C99" t="n">
-        <v>0.744063</v>
+        <v>0.742021</v>
       </c>
     </row>
     <row r="100">
@@ -1717,7 +1717,7 @@
         <v>0.027214</v>
       </c>
       <c r="C100" t="n">
-        <v>0.741425</v>
+        <v>0.739362</v>
       </c>
     </row>
     <row r="101">
@@ -1730,7 +1730,7 @@
         <v>0.027321</v>
       </c>
       <c r="C101" t="n">
-        <v>0.7387860000000001</v>
+        <v>0.736702</v>
       </c>
     </row>
     <row r="102">
@@ -1743,7 +1743,7 @@
         <v>0.027355</v>
       </c>
       <c r="C102" t="n">
-        <v>0.736148</v>
+        <v>0.734043</v>
       </c>
     </row>
     <row r="103">
@@ -1756,7 +1756,7 @@
         <v>0.028098</v>
       </c>
       <c r="C103" t="n">
-        <v>0.733509</v>
+        <v>0.731383</v>
       </c>
     </row>
     <row r="104">
@@ -1769,7 +1769,7 @@
         <v>0.028186</v>
       </c>
       <c r="C104" t="n">
-        <v>0.730871</v>
+        <v>0.728723</v>
       </c>
     </row>
     <row r="105">
@@ -1782,7 +1782,7 @@
         <v>0.028375</v>
       </c>
       <c r="C105" t="n">
-        <v>0.728232</v>
+        <v>0.726064</v>
       </c>
     </row>
     <row r="106">
@@ -1795,7 +1795,7 @@
         <v>0.029071</v>
       </c>
       <c r="C106" t="n">
-        <v>0.725594</v>
+        <v>0.723404</v>
       </c>
     </row>
     <row r="107">
@@ -1808,7 +1808,7 @@
         <v>0.029588</v>
       </c>
       <c r="C107" t="n">
-        <v>0.722955</v>
+        <v>0.720745</v>
       </c>
     </row>
     <row r="108">
@@ -1821,7 +1821,7 @@
         <v>0.029854</v>
       </c>
       <c r="C108" t="n">
-        <v>0.720317</v>
+        <v>0.718085</v>
       </c>
     </row>
     <row r="109">
@@ -1834,7 +1834,7 @@
         <v>0.030158</v>
       </c>
       <c r="C109" t="n">
-        <v>0.717678</v>
+        <v>0.715426</v>
       </c>
     </row>
     <row r="110">
@@ -1847,7 +1847,7 @@
         <v>0.030201</v>
       </c>
       <c r="C110" t="n">
-        <v>0.71504</v>
+        <v>0.712766</v>
       </c>
     </row>
     <row r="111">
@@ -1860,7 +1860,7 @@
         <v>0.03027</v>
       </c>
       <c r="C111" t="n">
-        <v>0.712401</v>
+        <v>0.710106</v>
       </c>
     </row>
     <row r="112">
@@ -1873,7 +1873,7 @@
         <v>0.030697</v>
       </c>
       <c r="C112" t="n">
-        <v>0.709763</v>
+        <v>0.707447</v>
       </c>
     </row>
     <row r="113">
@@ -1886,7 +1886,7 @@
         <v>0.030903</v>
       </c>
       <c r="C113" t="n">
-        <v>0.707124</v>
+        <v>0.7047870000000001</v>
       </c>
     </row>
     <row r="114">
@@ -1899,7 +1899,7 @@
         <v>0.031116</v>
       </c>
       <c r="C114" t="n">
-        <v>0.704485</v>
+        <v>0.702128</v>
       </c>
     </row>
     <row r="115">
@@ -1912,7 +1912,7 @@
         <v>0.031127</v>
       </c>
       <c r="C115" t="n">
-        <v>0.701847</v>
+        <v>0.699468</v>
       </c>
     </row>
     <row r="116">
@@ -1925,7 +1925,7 @@
         <v>0.031327</v>
       </c>
       <c r="C116" t="n">
-        <v>0.6992080000000001</v>
+        <v>0.696809</v>
       </c>
     </row>
     <row r="117">
@@ -1938,7 +1938,7 @@
         <v>0.031556</v>
       </c>
       <c r="C117" t="n">
-        <v>0.69657</v>
+        <v>0.694149</v>
       </c>
     </row>
     <row r="118">
@@ -1951,7 +1951,7 @@
         <v>0.031969</v>
       </c>
       <c r="C118" t="n">
-        <v>0.693931</v>
+        <v>0.691489</v>
       </c>
     </row>
     <row r="119">
@@ -1964,7 +1964,7 @@
         <v>0.032545</v>
       </c>
       <c r="C119" t="n">
-        <v>0.691293</v>
+        <v>0.6888300000000001</v>
       </c>
     </row>
     <row r="120">
@@ -1977,7 +1977,7 @@
         <v>0.032827</v>
       </c>
       <c r="C120" t="n">
-        <v>0.688654</v>
+        <v>0.6861699999999999</v>
       </c>
     </row>
     <row r="121">
@@ -1987,10 +1987,10 @@
         </is>
       </c>
       <c r="B121" t="n">
-        <v>0.033373</v>
+        <v>0.033481</v>
       </c>
       <c r="C121" t="n">
-        <v>0.686016</v>
+        <v>0.683511</v>
       </c>
     </row>
     <row r="122">
@@ -2000,10 +2000,10 @@
         </is>
       </c>
       <c r="B122" t="n">
-        <v>0.033481</v>
+        <v>0.033774</v>
       </c>
       <c r="C122" t="n">
-        <v>0.683377</v>
+        <v>0.680851</v>
       </c>
     </row>
     <row r="123">
@@ -2013,10 +2013,10 @@
         </is>
       </c>
       <c r="B123" t="n">
-        <v>0.033774</v>
+        <v>0.033884</v>
       </c>
       <c r="C123" t="n">
-        <v>0.680739</v>
+        <v>0.678191</v>
       </c>
     </row>
     <row r="124">
@@ -2026,10 +2026,10 @@
         </is>
       </c>
       <c r="B124" t="n">
-        <v>0.033884</v>
+        <v>0.034047</v>
       </c>
       <c r="C124" t="n">
-        <v>0.6781</v>
+        <v>0.675532</v>
       </c>
     </row>
     <row r="125">
@@ -2039,10 +2039,10 @@
         </is>
       </c>
       <c r="B125" t="n">
-        <v>0.034047</v>
+        <v>0.034274</v>
       </c>
       <c r="C125" t="n">
-        <v>0.675462</v>
+        <v>0.672872</v>
       </c>
     </row>
     <row r="126">
@@ -2052,10 +2052,10 @@
         </is>
       </c>
       <c r="B126" t="n">
-        <v>0.034274</v>
+        <v>0.034573</v>
       </c>
       <c r="C126" t="n">
-        <v>0.6728229999999999</v>
+        <v>0.6702129999999999</v>
       </c>
     </row>
     <row r="127">
@@ -2065,10 +2065,10 @@
         </is>
       </c>
       <c r="B127" t="n">
-        <v>0.034573</v>
+        <v>0.035039</v>
       </c>
       <c r="C127" t="n">
-        <v>0.670185</v>
+        <v>0.667553</v>
       </c>
     </row>
     <row r="128">
@@ -2078,10 +2078,10 @@
         </is>
       </c>
       <c r="B128" t="n">
-        <v>0.035039</v>
+        <v>0.035117</v>
       </c>
       <c r="C128" t="n">
-        <v>0.667546</v>
+        <v>0.664894</v>
       </c>
     </row>
     <row r="129">
@@ -2091,10 +2091,10 @@
         </is>
       </c>
       <c r="B129" t="n">
-        <v>0.035117</v>
+        <v>0.035159</v>
       </c>
       <c r="C129" t="n">
-        <v>0.6649080000000001</v>
+        <v>0.662234</v>
       </c>
     </row>
     <row r="130">
@@ -2104,10 +2104,10 @@
         </is>
       </c>
       <c r="B130" t="n">
-        <v>0.035159</v>
+        <v>0.035374</v>
       </c>
       <c r="C130" t="n">
-        <v>0.662269</v>
+        <v>0.659574</v>
       </c>
     </row>
     <row r="131">
@@ -2117,10 +2117,10 @@
         </is>
       </c>
       <c r="B131" t="n">
-        <v>0.035374</v>
+        <v>0.035654</v>
       </c>
       <c r="C131" t="n">
-        <v>0.659631</v>
+        <v>0.656915</v>
       </c>
     </row>
     <row r="132">
@@ -2130,10 +2130,10 @@
         </is>
       </c>
       <c r="B132" t="n">
-        <v>0.035654</v>
+        <v>0.036</v>
       </c>
       <c r="C132" t="n">
-        <v>0.656992</v>
+        <v>0.654255</v>
       </c>
     </row>
     <row r="133">
@@ -2143,10 +2143,10 @@
         </is>
       </c>
       <c r="B133" t="n">
-        <v>0.036</v>
+        <v>0.036242</v>
       </c>
       <c r="C133" t="n">
-        <v>0.654354</v>
+        <v>0.651596</v>
       </c>
     </row>
     <row r="134">
@@ -2156,10 +2156,10 @@
         </is>
       </c>
       <c r="B134" t="n">
-        <v>0.036242</v>
+        <v>0.037307</v>
       </c>
       <c r="C134" t="n">
-        <v>0.651715</v>
+        <v>0.648936</v>
       </c>
     </row>
     <row r="135">
@@ -2169,10 +2169,10 @@
         </is>
       </c>
       <c r="B135" t="n">
-        <v>0.037307</v>
+        <v>0.037431</v>
       </c>
       <c r="C135" t="n">
-        <v>0.649077</v>
+        <v>0.646277</v>
       </c>
     </row>
     <row r="136">
@@ -2185,7 +2185,7 @@
         <v>0.037805</v>
       </c>
       <c r="C136" t="n">
-        <v>0.646438</v>
+        <v>0.643617</v>
       </c>
     </row>
     <row r="137">
@@ -2198,7 +2198,7 @@
         <v>0.03815</v>
       </c>
       <c r="C137" t="n">
-        <v>0.643799</v>
+        <v>0.640957</v>
       </c>
     </row>
     <row r="138">
@@ -2211,7 +2211,7 @@
         <v>0.038316</v>
       </c>
       <c r="C138" t="n">
-        <v>0.641161</v>
+        <v>0.638298</v>
       </c>
     </row>
     <row r="139">
@@ -2224,7 +2224,7 @@
         <v>0.03876</v>
       </c>
       <c r="C139" t="n">
-        <v>0.638522</v>
+        <v>0.635638</v>
       </c>
     </row>
     <row r="140">
@@ -2237,7 +2237,7 @@
         <v>0.039595</v>
       </c>
       <c r="C140" t="n">
-        <v>0.635884</v>
+        <v>0.632979</v>
       </c>
     </row>
     <row r="141">
@@ -2250,7 +2250,7 @@
         <v>0.03982</v>
       </c>
       <c r="C141" t="n">
-        <v>0.6332449999999999</v>
+        <v>0.630319</v>
       </c>
     </row>
     <row r="142">
@@ -2263,7 +2263,7 @@
         <v>0.040867</v>
       </c>
       <c r="C142" t="n">
-        <v>0.630607</v>
+        <v>0.62766</v>
       </c>
     </row>
     <row r="143">
@@ -2276,7 +2276,7 @@
         <v>0.040915</v>
       </c>
       <c r="C143" t="n">
-        <v>0.627968</v>
+        <v>0.625</v>
       </c>
     </row>
     <row r="144">
@@ -2289,7 +2289,7 @@
         <v>0.040931</v>
       </c>
       <c r="C144" t="n">
-        <v>0.6253300000000001</v>
+        <v>0.62234</v>
       </c>
     </row>
     <row r="145">
@@ -2302,7 +2302,7 @@
         <v>0.040948</v>
       </c>
       <c r="C145" t="n">
-        <v>0.622691</v>
+        <v>0.619681</v>
       </c>
     </row>
     <row r="146">
@@ -2315,7 +2315,7 @@
         <v>0.041019</v>
       </c>
       <c r="C146" t="n">
-        <v>0.620053</v>
+        <v>0.617021</v>
       </c>
     </row>
     <row r="147">
@@ -2328,7 +2328,7 @@
         <v>0.041132</v>
       </c>
       <c r="C147" t="n">
-        <v>0.617414</v>
+        <v>0.614362</v>
       </c>
     </row>
     <row r="148">
@@ -2341,7 +2341,7 @@
         <v>0.041331</v>
       </c>
       <c r="C148" t="n">
-        <v>0.614776</v>
+        <v>0.611702</v>
       </c>
     </row>
     <row r="149">
@@ -2354,7 +2354,7 @@
         <v>0.041359</v>
       </c>
       <c r="C149" t="n">
-        <v>0.612137</v>
+        <v>0.609043</v>
       </c>
     </row>
     <row r="150">
@@ -2367,7 +2367,7 @@
         <v>0.04197</v>
       </c>
       <c r="C150" t="n">
-        <v>0.609499</v>
+        <v>0.606383</v>
       </c>
     </row>
     <row r="151">
@@ -2380,7 +2380,7 @@
         <v>0.042735</v>
       </c>
       <c r="C151" t="n">
-        <v>0.60686</v>
+        <v>0.603723</v>
       </c>
     </row>
     <row r="152">
@@ -2393,7 +2393,7 @@
         <v>0.043468</v>
       </c>
       <c r="C152" t="n">
-        <v>0.604222</v>
+        <v>0.601064</v>
       </c>
     </row>
     <row r="153">
@@ -2406,7 +2406,7 @@
         <v>0.044385</v>
       </c>
       <c r="C153" t="n">
-        <v>0.601583</v>
+        <v>0.598404</v>
       </c>
     </row>
     <row r="154">
@@ -2419,7 +2419,7 @@
         <v>0.044556</v>
       </c>
       <c r="C154" t="n">
-        <v>0.5989449999999999</v>
+        <v>0.595745</v>
       </c>
     </row>
     <row r="155">
@@ -2432,7 +2432,7 @@
         <v>0.044571</v>
       </c>
       <c r="C155" t="n">
-        <v>0.596306</v>
+        <v>0.593085</v>
       </c>
     </row>
     <row r="156">
@@ -2445,7 +2445,7 @@
         <v>0.044773</v>
       </c>
       <c r="C156" t="n">
-        <v>0.593668</v>
+        <v>0.590426</v>
       </c>
     </row>
     <row r="157">
@@ -2458,7 +2458,7 @@
         <v>0.045962</v>
       </c>
       <c r="C157" t="n">
-        <v>0.591029</v>
+        <v>0.587766</v>
       </c>
     </row>
     <row r="158">
@@ -2471,7 +2471,7 @@
         <v>0.046486</v>
       </c>
       <c r="C158" t="n">
-        <v>0.588391</v>
+        <v>0.585106</v>
       </c>
     </row>
     <row r="159">
@@ -2484,7 +2484,7 @@
         <v>0.046763</v>
       </c>
       <c r="C159" t="n">
-        <v>0.5857520000000001</v>
+        <v>0.582447</v>
       </c>
     </row>
     <row r="160">
@@ -2497,7 +2497,7 @@
         <v>0.046785</v>
       </c>
       <c r="C160" t="n">
-        <v>0.583113</v>
+        <v>0.5797870000000001</v>
       </c>
     </row>
     <row r="161">
@@ -2510,7 +2510,7 @@
         <v>0.046943</v>
       </c>
       <c r="C161" t="n">
-        <v>0.580475</v>
+        <v>0.577128</v>
       </c>
     </row>
     <row r="162">
@@ -2523,7 +2523,7 @@
         <v>0.047141</v>
       </c>
       <c r="C162" t="n">
-        <v>0.577836</v>
+        <v>0.574468</v>
       </c>
     </row>
     <row r="163">
@@ -2536,7 +2536,7 @@
         <v>0.047421</v>
       </c>
       <c r="C163" t="n">
-        <v>0.575198</v>
+        <v>0.571809</v>
       </c>
     </row>
     <row r="164">
@@ -2546,10 +2546,10 @@
         </is>
       </c>
       <c r="B164" t="n">
-        <v>0.047668</v>
+        <v>0.048551</v>
       </c>
       <c r="C164" t="n">
-        <v>0.572559</v>
+        <v>0.569149</v>
       </c>
     </row>
     <row r="165">
@@ -2559,10 +2559,10 @@
         </is>
       </c>
       <c r="B165" t="n">
-        <v>0.048551</v>
+        <v>0.04906</v>
       </c>
       <c r="C165" t="n">
-        <v>0.569921</v>
+        <v>0.566489</v>
       </c>
     </row>
     <row r="166">
@@ -2572,10 +2572,10 @@
         </is>
       </c>
       <c r="B166" t="n">
-        <v>0.048876</v>
+        <v>0.049358</v>
       </c>
       <c r="C166" t="n">
-        <v>0.567282</v>
+        <v>0.5638300000000001</v>
       </c>
     </row>
     <row r="167">
@@ -2585,10 +2585,10 @@
         </is>
       </c>
       <c r="B167" t="n">
-        <v>0.04906</v>
+        <v>0.049478</v>
       </c>
       <c r="C167" t="n">
-        <v>0.564644</v>
+        <v>0.5611699999999999</v>
       </c>
     </row>
     <row r="168">
@@ -2598,10 +2598,10 @@
         </is>
       </c>
       <c r="B168" t="n">
-        <v>0.049358</v>
+        <v>0.049516</v>
       </c>
       <c r="C168" t="n">
-        <v>0.562005</v>
+        <v>0.558511</v>
       </c>
     </row>
     <row r="169">
@@ -2611,10 +2611,10 @@
         </is>
       </c>
       <c r="B169" t="n">
-        <v>0.049478</v>
+        <v>0.049728</v>
       </c>
       <c r="C169" t="n">
-        <v>0.5593669999999999</v>
+        <v>0.555851</v>
       </c>
     </row>
     <row r="170">
@@ -2624,10 +2624,10 @@
         </is>
       </c>
       <c r="B170" t="n">
-        <v>0.049516</v>
+        <v>0.049754</v>
       </c>
       <c r="C170" t="n">
-        <v>0.556728</v>
+        <v>0.553191</v>
       </c>
     </row>
     <row r="171">
@@ -2637,10 +2637,10 @@
         </is>
       </c>
       <c r="B171" t="n">
-        <v>0.049728</v>
+        <v>0.051151</v>
       </c>
       <c r="C171" t="n">
-        <v>0.55409</v>
+        <v>0.550532</v>
       </c>
     </row>
     <row r="172">
@@ -2650,10 +2650,10 @@
         </is>
       </c>
       <c r="B172" t="n">
-        <v>0.049754</v>
+        <v>0.051264</v>
       </c>
       <c r="C172" t="n">
-        <v>0.551451</v>
+        <v>0.547872</v>
       </c>
     </row>
     <row r="173">
@@ -2663,10 +2663,10 @@
         </is>
       </c>
       <c r="B173" t="n">
-        <v>0.051151</v>
+        <v>0.051423</v>
       </c>
       <c r="C173" t="n">
-        <v>0.548813</v>
+        <v>0.5452129999999999</v>
       </c>
     </row>
     <row r="174">
@@ -2676,10 +2676,10 @@
         </is>
       </c>
       <c r="B174" t="n">
-        <v>0.051264</v>
+        <v>0.051449</v>
       </c>
       <c r="C174" t="n">
-        <v>0.546174</v>
+        <v>0.542553</v>
       </c>
     </row>
     <row r="175">
@@ -2689,10 +2689,10 @@
         </is>
       </c>
       <c r="B175" t="n">
-        <v>0.051423</v>
+        <v>0.051978</v>
       </c>
       <c r="C175" t="n">
-        <v>0.543536</v>
+        <v>0.539894</v>
       </c>
     </row>
     <row r="176">
@@ -2702,10 +2702,10 @@
         </is>
       </c>
       <c r="B176" t="n">
-        <v>0.051449</v>
+        <v>0.052376</v>
       </c>
       <c r="C176" t="n">
-        <v>0.540897</v>
+        <v>0.537234</v>
       </c>
     </row>
     <row r="177">
@@ -2715,10 +2715,10 @@
         </is>
       </c>
       <c r="B177" t="n">
-        <v>0.051978</v>
+        <v>0.052398</v>
       </c>
       <c r="C177" t="n">
-        <v>0.538259</v>
+        <v>0.534574</v>
       </c>
     </row>
     <row r="178">
@@ -2728,10 +2728,10 @@
         </is>
       </c>
       <c r="B178" t="n">
-        <v>0.052376</v>
+        <v>0.052682</v>
       </c>
       <c r="C178" t="n">
-        <v>0.53562</v>
+        <v>0.531915</v>
       </c>
     </row>
     <row r="179">
@@ -2741,10 +2741,10 @@
         </is>
       </c>
       <c r="B179" t="n">
-        <v>0.052398</v>
+        <v>0.052941</v>
       </c>
       <c r="C179" t="n">
-        <v>0.532982</v>
+        <v>0.529255</v>
       </c>
     </row>
     <row r="180">
@@ -2754,10 +2754,10 @@
         </is>
       </c>
       <c r="B180" t="n">
-        <v>0.052682</v>
+        <v>0.053227</v>
       </c>
       <c r="C180" t="n">
-        <v>0.530343</v>
+        <v>0.526596</v>
       </c>
     </row>
     <row r="181">
@@ -2767,10 +2767,10 @@
         </is>
       </c>
       <c r="B181" t="n">
-        <v>0.052941</v>
+        <v>0.053316</v>
       </c>
       <c r="C181" t="n">
-        <v>0.527704</v>
+        <v>0.523936</v>
       </c>
     </row>
     <row r="182">
@@ -2780,10 +2780,10 @@
         </is>
       </c>
       <c r="B182" t="n">
-        <v>0.053227</v>
+        <v>0.053555</v>
       </c>
       <c r="C182" t="n">
-        <v>0.525066</v>
+        <v>0.521277</v>
       </c>
     </row>
     <row r="183">
@@ -2793,10 +2793,10 @@
         </is>
       </c>
       <c r="B183" t="n">
-        <v>0.053316</v>
+        <v>0.05382</v>
       </c>
       <c r="C183" t="n">
-        <v>0.522427</v>
+        <v>0.518617</v>
       </c>
     </row>
     <row r="184">
@@ -2806,10 +2806,10 @@
         </is>
       </c>
       <c r="B184" t="n">
-        <v>0.053555</v>
+        <v>0.05439</v>
       </c>
       <c r="C184" t="n">
-        <v>0.5197889999999999</v>
+        <v>0.515957</v>
       </c>
     </row>
     <row r="185">
@@ -2819,10 +2819,10 @@
         </is>
       </c>
       <c r="B185" t="n">
-        <v>0.05382</v>
+        <v>0.054595</v>
       </c>
       <c r="C185" t="n">
-        <v>0.51715</v>
+        <v>0.513298</v>
       </c>
     </row>
     <row r="186">
@@ -2832,10 +2832,10 @@
         </is>
       </c>
       <c r="B186" t="n">
-        <v>0.05439</v>
+        <v>0.05496</v>
       </c>
       <c r="C186" t="n">
-        <v>0.514512</v>
+        <v>0.510638</v>
       </c>
     </row>
     <row r="187">
@@ -2845,10 +2845,10 @@
         </is>
       </c>
       <c r="B187" t="n">
-        <v>0.054595</v>
+        <v>0.0555</v>
       </c>
       <c r="C187" t="n">
-        <v>0.511873</v>
+        <v>0.507979</v>
       </c>
     </row>
     <row r="188">
@@ -2858,10 +2858,10 @@
         </is>
       </c>
       <c r="B188" t="n">
-        <v>0.05496</v>
+        <v>0.055621</v>
       </c>
       <c r="C188" t="n">
-        <v>0.509235</v>
+        <v>0.505319</v>
       </c>
     </row>
     <row r="189">
@@ -2871,10 +2871,10 @@
         </is>
       </c>
       <c r="B189" t="n">
-        <v>0.0555</v>
+        <v>0.055736</v>
       </c>
       <c r="C189" t="n">
-        <v>0.506596</v>
+        <v>0.50266</v>
       </c>
     </row>
     <row r="190">
@@ -2884,10 +2884,10 @@
         </is>
       </c>
       <c r="B190" t="n">
-        <v>0.055621</v>
+        <v>0.056242</v>
       </c>
       <c r="C190" t="n">
-        <v>0.503958</v>
+        <v>0.5</v>
       </c>
     </row>
     <row r="191">
@@ -2897,10 +2897,10 @@
         </is>
       </c>
       <c r="B191" t="n">
-        <v>0.055736</v>
+        <v>0.056433</v>
       </c>
       <c r="C191" t="n">
-        <v>0.501319</v>
+        <v>0.49734</v>
       </c>
     </row>
     <row r="192">
@@ -2910,10 +2910,10 @@
         </is>
       </c>
       <c r="B192" t="n">
-        <v>0.056242</v>
+        <v>0.056487</v>
       </c>
       <c r="C192" t="n">
-        <v>0.498681</v>
+        <v>0.494681</v>
       </c>
     </row>
     <row r="193">
@@ -2923,10 +2923,10 @@
         </is>
       </c>
       <c r="B193" t="n">
-        <v>0.056433</v>
+        <v>0.056702</v>
       </c>
       <c r="C193" t="n">
-        <v>0.496042</v>
+        <v>0.492021</v>
       </c>
     </row>
     <row r="194">
@@ -2936,10 +2936,10 @@
         </is>
       </c>
       <c r="B194" t="n">
-        <v>0.056487</v>
+        <v>0.056785</v>
       </c>
       <c r="C194" t="n">
-        <v>0.493404</v>
+        <v>0.489362</v>
       </c>
     </row>
     <row r="195">
@@ -2949,10 +2949,10 @@
         </is>
       </c>
       <c r="B195" t="n">
-        <v>0.056702</v>
+        <v>0.05854</v>
       </c>
       <c r="C195" t="n">
-        <v>0.490765</v>
+        <v>0.486702</v>
       </c>
     </row>
     <row r="196">
@@ -2962,10 +2962,10 @@
         </is>
       </c>
       <c r="B196" t="n">
-        <v>0.056785</v>
+        <v>0.058745</v>
       </c>
       <c r="C196" t="n">
-        <v>0.488127</v>
+        <v>0.484043</v>
       </c>
     </row>
     <row r="197">
@@ -2975,10 +2975,10 @@
         </is>
       </c>
       <c r="B197" t="n">
-        <v>0.05854</v>
+        <v>0.058836</v>
       </c>
       <c r="C197" t="n">
-        <v>0.485488</v>
+        <v>0.481383</v>
       </c>
     </row>
     <row r="198">
@@ -2988,10 +2988,10 @@
         </is>
       </c>
       <c r="B198" t="n">
-        <v>0.058745</v>
+        <v>0.059279</v>
       </c>
       <c r="C198" t="n">
-        <v>0.48285</v>
+        <v>0.478723</v>
       </c>
     </row>
     <row r="199">
@@ -3001,10 +3001,10 @@
         </is>
       </c>
       <c r="B199" t="n">
-        <v>0.058836</v>
+        <v>0.059367</v>
       </c>
       <c r="C199" t="n">
-        <v>0.480211</v>
+        <v>0.476064</v>
       </c>
     </row>
     <row r="200">
@@ -3014,10 +3014,10 @@
         </is>
       </c>
       <c r="B200" t="n">
-        <v>0.059279</v>
+        <v>0.059553</v>
       </c>
       <c r="C200" t="n">
-        <v>0.477573</v>
+        <v>0.473404</v>
       </c>
     </row>
     <row r="201">
@@ -3027,10 +3027,10 @@
         </is>
       </c>
       <c r="B201" t="n">
-        <v>0.059367</v>
+        <v>0.059579</v>
       </c>
       <c r="C201" t="n">
-        <v>0.474934</v>
+        <v>0.470745</v>
       </c>
     </row>
     <row r="202">
@@ -3040,10 +3040,10 @@
         </is>
       </c>
       <c r="B202" t="n">
-        <v>0.059553</v>
+        <v>0.060111</v>
       </c>
       <c r="C202" t="n">
-        <v>0.472296</v>
+        <v>0.468085</v>
       </c>
     </row>
     <row r="203">
@@ -3053,10 +3053,10 @@
         </is>
       </c>
       <c r="B203" t="n">
-        <v>0.059579</v>
+        <v>0.060827</v>
       </c>
       <c r="C203" t="n">
-        <v>0.469657</v>
+        <v>0.465426</v>
       </c>
     </row>
     <row r="204">
@@ -3066,10 +3066,10 @@
         </is>
       </c>
       <c r="B204" t="n">
-        <v>0.060111</v>
+        <v>0.060882</v>
       </c>
       <c r="C204" t="n">
-        <v>0.467018</v>
+        <v>0.462766</v>
       </c>
     </row>
     <row r="205">
@@ -3079,10 +3079,10 @@
         </is>
       </c>
       <c r="B205" t="n">
-        <v>0.060827</v>
+        <v>0.061712</v>
       </c>
       <c r="C205" t="n">
-        <v>0.46438</v>
+        <v>0.460106</v>
       </c>
     </row>
     <row r="206">
@@ -3092,10 +3092,10 @@
         </is>
       </c>
       <c r="B206" t="n">
-        <v>0.060882</v>
+        <v>0.061784</v>
       </c>
       <c r="C206" t="n">
-        <v>0.461741</v>
+        <v>0.457447</v>
       </c>
     </row>
     <row r="207">
@@ -3105,10 +3105,10 @@
         </is>
       </c>
       <c r="B207" t="n">
-        <v>0.061712</v>
+        <v>0.06179</v>
       </c>
       <c r="C207" t="n">
-        <v>0.459103</v>
+        <v>0.454787</v>
       </c>
     </row>
     <row r="208">
@@ -3118,10 +3118,10 @@
         </is>
       </c>
       <c r="B208" t="n">
-        <v>0.061784</v>
+        <v>0.061969</v>
       </c>
       <c r="C208" t="n">
-        <v>0.456464</v>
+        <v>0.452128</v>
       </c>
     </row>
     <row r="209">
@@ -3131,10 +3131,10 @@
         </is>
       </c>
       <c r="B209" t="n">
-        <v>0.06179</v>
+        <v>0.062129</v>
       </c>
       <c r="C209" t="n">
-        <v>0.453826</v>
+        <v>0.449468</v>
       </c>
     </row>
     <row r="210">
@@ -3144,10 +3144,10 @@
         </is>
       </c>
       <c r="B210" t="n">
-        <v>0.061969</v>
+        <v>0.062168</v>
       </c>
       <c r="C210" t="n">
-        <v>0.451187</v>
+        <v>0.446809</v>
       </c>
     </row>
     <row r="211">
@@ -3157,10 +3157,10 @@
         </is>
       </c>
       <c r="B211" t="n">
-        <v>0.062129</v>
+        <v>0.062246</v>
       </c>
       <c r="C211" t="n">
-        <v>0.448549</v>
+        <v>0.444149</v>
       </c>
     </row>
     <row r="212">
@@ -3170,10 +3170,10 @@
         </is>
       </c>
       <c r="B212" t="n">
-        <v>0.062168</v>
+        <v>0.06263299999999999</v>
       </c>
       <c r="C212" t="n">
-        <v>0.44591</v>
+        <v>0.441489</v>
       </c>
     </row>
     <row r="213">
@@ -3183,10 +3183,10 @@
         </is>
       </c>
       <c r="B213" t="n">
-        <v>0.062246</v>
+        <v>0.062844</v>
       </c>
       <c r="C213" t="n">
-        <v>0.443272</v>
+        <v>0.43883</v>
       </c>
     </row>
     <row r="214">
@@ -3196,10 +3196,10 @@
         </is>
       </c>
       <c r="B214" t="n">
-        <v>0.06263299999999999</v>
+        <v>0.063808</v>
       </c>
       <c r="C214" t="n">
-        <v>0.440633</v>
+        <v>0.43617</v>
       </c>
     </row>
     <row r="215">
@@ -3209,10 +3209,10 @@
         </is>
       </c>
       <c r="B215" t="n">
-        <v>0.062844</v>
+        <v>0.06464300000000001</v>
       </c>
       <c r="C215" t="n">
-        <v>0.437995</v>
+        <v>0.433511</v>
       </c>
     </row>
     <row r="216">
@@ -3222,10 +3222,10 @@
         </is>
       </c>
       <c r="B216" t="n">
-        <v>0.063808</v>
+        <v>0.064842</v>
       </c>
       <c r="C216" t="n">
-        <v>0.435356</v>
+        <v>0.430851</v>
       </c>
     </row>
     <row r="217">
@@ -3235,10 +3235,10 @@
         </is>
       </c>
       <c r="B217" t="n">
-        <v>0.06464300000000001</v>
+        <v>0.06555900000000001</v>
       </c>
       <c r="C217" t="n">
-        <v>0.432718</v>
+        <v>0.428191</v>
       </c>
     </row>
     <row r="218">
@@ -3248,10 +3248,10 @@
         </is>
       </c>
       <c r="B218" t="n">
-        <v>0.06555900000000001</v>
+        <v>0.067176</v>
       </c>
       <c r="C218" t="n">
-        <v>0.430079</v>
+        <v>0.425532</v>
       </c>
     </row>
     <row r="219">
@@ -3261,10 +3261,10 @@
         </is>
       </c>
       <c r="B219" t="n">
-        <v>0.067176</v>
+        <v>0.06736399999999999</v>
       </c>
       <c r="C219" t="n">
-        <v>0.427441</v>
+        <v>0.422872</v>
       </c>
     </row>
     <row r="220">
@@ -3274,10 +3274,10 @@
         </is>
       </c>
       <c r="B220" t="n">
-        <v>0.06736399999999999</v>
+        <v>0.067375</v>
       </c>
       <c r="C220" t="n">
-        <v>0.424802</v>
+        <v>0.420213</v>
       </c>
     </row>
     <row r="221">
@@ -3287,10 +3287,10 @@
         </is>
       </c>
       <c r="B221" t="n">
-        <v>0.067375</v>
+        <v>0.067555</v>
       </c>
       <c r="C221" t="n">
-        <v>0.422164</v>
+        <v>0.417553</v>
       </c>
     </row>
     <row r="222">
@@ -3300,10 +3300,10 @@
         </is>
       </c>
       <c r="B222" t="n">
-        <v>0.067555</v>
+        <v>0.067604</v>
       </c>
       <c r="C222" t="n">
-        <v>0.419525</v>
+        <v>0.414894</v>
       </c>
     </row>
     <row r="223">
@@ -3313,10 +3313,10 @@
         </is>
       </c>
       <c r="B223" t="n">
-        <v>0.067604</v>
+        <v>0.067644</v>
       </c>
       <c r="C223" t="n">
-        <v>0.416887</v>
+        <v>0.412234</v>
       </c>
     </row>
     <row r="224">
@@ -3326,10 +3326,10 @@
         </is>
       </c>
       <c r="B224" t="n">
-        <v>0.067644</v>
+        <v>0.068111</v>
       </c>
       <c r="C224" t="n">
-        <v>0.414248</v>
+        <v>0.409574</v>
       </c>
     </row>
     <row r="225">
@@ -3339,10 +3339,10 @@
         </is>
       </c>
       <c r="B225" t="n">
-        <v>0.068111</v>
+        <v>0.068601</v>
       </c>
       <c r="C225" t="n">
-        <v>0.411609</v>
+        <v>0.406915</v>
       </c>
     </row>
     <row r="226">
@@ -3352,10 +3352,10 @@
         </is>
       </c>
       <c r="B226" t="n">
-        <v>0.068601</v>
+        <v>0.068939</v>
       </c>
       <c r="C226" t="n">
-        <v>0.408971</v>
+        <v>0.404255</v>
       </c>
     </row>
     <row r="227">
@@ -3365,10 +3365,10 @@
         </is>
       </c>
       <c r="B227" t="n">
-        <v>0.068939</v>
+        <v>0.06909</v>
       </c>
       <c r="C227" t="n">
-        <v>0.406332</v>
+        <v>0.401596</v>
       </c>
     </row>
     <row r="228">
@@ -3378,10 +3378,10 @@
         </is>
       </c>
       <c r="B228" t="n">
-        <v>0.06909</v>
+        <v>0.069253</v>
       </c>
       <c r="C228" t="n">
-        <v>0.403694</v>
+        <v>0.398936</v>
       </c>
     </row>
     <row r="229">
@@ -3391,10 +3391,10 @@
         </is>
       </c>
       <c r="B229" t="n">
-        <v>0.069253</v>
+        <v>0.070214</v>
       </c>
       <c r="C229" t="n">
-        <v>0.401055</v>
+        <v>0.396277</v>
       </c>
     </row>
     <row r="230">
@@ -3404,10 +3404,10 @@
         </is>
       </c>
       <c r="B230" t="n">
-        <v>0.070214</v>
+        <v>0.070659</v>
       </c>
       <c r="C230" t="n">
-        <v>0.398417</v>
+        <v>0.393617</v>
       </c>
     </row>
     <row r="231">
@@ -3417,10 +3417,10 @@
         </is>
       </c>
       <c r="B231" t="n">
-        <v>0.070659</v>
+        <v>0.071394</v>
       </c>
       <c r="C231" t="n">
-        <v>0.395778</v>
+        <v>0.390957</v>
       </c>
     </row>
     <row r="232">
@@ -3430,10 +3430,10 @@
         </is>
       </c>
       <c r="B232" t="n">
-        <v>0.071394</v>
+        <v>0.072684</v>
       </c>
       <c r="C232" t="n">
-        <v>0.39314</v>
+        <v>0.388298</v>
       </c>
     </row>
     <row r="233">
@@ -3443,10 +3443,10 @@
         </is>
       </c>
       <c r="B233" t="n">
-        <v>0.072684</v>
+        <v>0.072744</v>
       </c>
       <c r="C233" t="n">
-        <v>0.390501</v>
+        <v>0.385638</v>
       </c>
     </row>
     <row r="234">
@@ -3456,10 +3456,10 @@
         </is>
       </c>
       <c r="B234" t="n">
-        <v>0.072744</v>
+        <v>0.07295599999999999</v>
       </c>
       <c r="C234" t="n">
-        <v>0.387863</v>
+        <v>0.382979</v>
       </c>
     </row>
     <row r="235">
@@ -3469,10 +3469,10 @@
         </is>
       </c>
       <c r="B235" t="n">
-        <v>0.07295599999999999</v>
+        <v>0.07331</v>
       </c>
       <c r="C235" t="n">
-        <v>0.385224</v>
+        <v>0.380319</v>
       </c>
     </row>
     <row r="236">
@@ -3482,10 +3482,10 @@
         </is>
       </c>
       <c r="B236" t="n">
-        <v>0.07331</v>
+        <v>0.07380299999999999</v>
       </c>
       <c r="C236" t="n">
-        <v>0.382586</v>
+        <v>0.37766</v>
       </c>
     </row>
     <row r="237">
@@ -3495,10 +3495,10 @@
         </is>
       </c>
       <c r="B237" t="n">
-        <v>0.07380299999999999</v>
+        <v>0.07424799999999999</v>
       </c>
       <c r="C237" t="n">
-        <v>0.379947</v>
+        <v>0.375</v>
       </c>
     </row>
     <row r="238">
@@ -3508,10 +3508,10 @@
         </is>
       </c>
       <c r="B238" t="n">
-        <v>0.07424799999999999</v>
+        <v>0.07437100000000001</v>
       </c>
       <c r="C238" t="n">
-        <v>0.377309</v>
+        <v>0.37234</v>
       </c>
     </row>
     <row r="239">
@@ -3521,10 +3521,10 @@
         </is>
       </c>
       <c r="B239" t="n">
-        <v>0.07437100000000001</v>
+        <v>0.075854</v>
       </c>
       <c r="C239" t="n">
-        <v>0.37467</v>
+        <v>0.369681</v>
       </c>
     </row>
     <row r="240">
@@ -3534,10 +3534,10 @@
         </is>
       </c>
       <c r="B240" t="n">
-        <v>0.075854</v>
+        <v>0.075876</v>
       </c>
       <c r="C240" t="n">
-        <v>0.372032</v>
+        <v>0.367021</v>
       </c>
     </row>
     <row r="241">
@@ -3547,10 +3547,10 @@
         </is>
       </c>
       <c r="B241" t="n">
-        <v>0.075876</v>
+        <v>0.076543</v>
       </c>
       <c r="C241" t="n">
-        <v>0.369393</v>
+        <v>0.364362</v>
       </c>
     </row>
     <row r="242">
@@ -3560,10 +3560,10 @@
         </is>
       </c>
       <c r="B242" t="n">
-        <v>0.076543</v>
+        <v>0.07708</v>
       </c>
       <c r="C242" t="n">
-        <v>0.366755</v>
+        <v>0.361702</v>
       </c>
     </row>
     <row r="243">
@@ -3573,10 +3573,10 @@
         </is>
       </c>
       <c r="B243" t="n">
-        <v>0.07708</v>
+        <v>0.07757799999999999</v>
       </c>
       <c r="C243" t="n">
-        <v>0.364116</v>
+        <v>0.359043</v>
       </c>
     </row>
     <row r="244">
@@ -3586,10 +3586,10 @@
         </is>
       </c>
       <c r="B244" t="n">
-        <v>0.07757799999999999</v>
+        <v>0.077863</v>
       </c>
       <c r="C244" t="n">
-        <v>0.361478</v>
+        <v>0.356383</v>
       </c>
     </row>
     <row r="245">
@@ -3599,10 +3599,10 @@
         </is>
       </c>
       <c r="B245" t="n">
-        <v>0.077863</v>
+        <v>0.077912</v>
       </c>
       <c r="C245" t="n">
-        <v>0.358839</v>
+        <v>0.353723</v>
       </c>
     </row>
     <row r="246">
@@ -3612,10 +3612,10 @@
         </is>
       </c>
       <c r="B246" t="n">
-        <v>0.077912</v>
+        <v>0.078084</v>
       </c>
       <c r="C246" t="n">
-        <v>0.356201</v>
+        <v>0.351064</v>
       </c>
     </row>
     <row r="247">
@@ -3628,7 +3628,7 @@
         <v>0.07921499999999999</v>
       </c>
       <c r="C247" t="n">
-        <v>0.353562</v>
+        <v>0.348404</v>
       </c>
     </row>
     <row r="248">
@@ -3641,7 +3641,7 @@
         <v>0.08092199999999999</v>
       </c>
       <c r="C248" t="n">
-        <v>0.350923</v>
+        <v>0.345745</v>
       </c>
     </row>
     <row r="249">
@@ -3654,7 +3654,7 @@
         <v>0.081607</v>
       </c>
       <c r="C249" t="n">
-        <v>0.348285</v>
+        <v>0.343085</v>
       </c>
     </row>
     <row r="250">
@@ -3667,7 +3667,7 @@
         <v>0.081758</v>
       </c>
       <c r="C250" t="n">
-        <v>0.345646</v>
+        <v>0.340426</v>
       </c>
     </row>
     <row r="251">
@@ -3680,7 +3680,7 @@
         <v>0.08192000000000001</v>
       </c>
       <c r="C251" t="n">
-        <v>0.343008</v>
+        <v>0.337766</v>
       </c>
     </row>
     <row r="252">
@@ -3693,7 +3693,7 @@
         <v>0.082479</v>
       </c>
       <c r="C252" t="n">
-        <v>0.340369</v>
+        <v>0.335106</v>
       </c>
     </row>
     <row r="253">
@@ -3706,7 +3706,7 @@
         <v>0.08254300000000001</v>
       </c>
       <c r="C253" t="n">
-        <v>0.337731</v>
+        <v>0.332447</v>
       </c>
     </row>
     <row r="254">
@@ -3719,7 +3719,7 @@
         <v>0.082594</v>
       </c>
       <c r="C254" t="n">
-        <v>0.335092</v>
+        <v>0.329787</v>
       </c>
     </row>
     <row r="255">
@@ -3732,7 +3732,7 @@
         <v>0.083297</v>
       </c>
       <c r="C255" t="n">
-        <v>0.332454</v>
+        <v>0.327128</v>
       </c>
     </row>
     <row r="256">
@@ -3742,10 +3742,10 @@
         </is>
       </c>
       <c r="B256" t="n">
-        <v>0.08384800000000001</v>
+        <v>0.083664</v>
       </c>
       <c r="C256" t="n">
-        <v>0.329815</v>
+        <v>0.324468</v>
       </c>
     </row>
     <row r="257">
@@ -3755,10 +3755,10 @@
         </is>
       </c>
       <c r="B257" t="n">
-        <v>0.084221</v>
+        <v>0.08384800000000001</v>
       </c>
       <c r="C257" t="n">
-        <v>0.327177</v>
+        <v>0.321809</v>
       </c>
     </row>
     <row r="258">
@@ -3768,10 +3768,10 @@
         </is>
       </c>
       <c r="B258" t="n">
-        <v>0.08483599999999999</v>
+        <v>0.084221</v>
       </c>
       <c r="C258" t="n">
-        <v>0.324538</v>
+        <v>0.319149</v>
       </c>
     </row>
     <row r="259">
@@ -3781,10 +3781,10 @@
         </is>
       </c>
       <c r="B259" t="n">
-        <v>0.08586199999999999</v>
+        <v>0.08483599999999999</v>
       </c>
       <c r="C259" t="n">
-        <v>0.3219</v>
+        <v>0.316489</v>
       </c>
     </row>
     <row r="260">
@@ -3794,10 +3794,10 @@
         </is>
       </c>
       <c r="B260" t="n">
-        <v>0.087156</v>
+        <v>0.08586199999999999</v>
       </c>
       <c r="C260" t="n">
-        <v>0.319261</v>
+        <v>0.31383</v>
       </c>
     </row>
     <row r="261">
@@ -3807,10 +3807,10 @@
         </is>
       </c>
       <c r="B261" t="n">
-        <v>0.08717999999999999</v>
+        <v>0.087156</v>
       </c>
       <c r="C261" t="n">
-        <v>0.316623</v>
+        <v>0.31117</v>
       </c>
     </row>
     <row r="262">
@@ -3820,10 +3820,10 @@
         </is>
       </c>
       <c r="B262" t="n">
-        <v>0.08820799999999999</v>
+        <v>0.08717999999999999</v>
       </c>
       <c r="C262" t="n">
-        <v>0.313984</v>
+        <v>0.308511</v>
       </c>
     </row>
     <row r="263">
@@ -3833,10 +3833,10 @@
         </is>
       </c>
       <c r="B263" t="n">
-        <v>0.088889</v>
+        <v>0.08820799999999999</v>
       </c>
       <c r="C263" t="n">
-        <v>0.311346</v>
+        <v>0.305851</v>
       </c>
     </row>
     <row r="264">
@@ -3846,10 +3846,10 @@
         </is>
       </c>
       <c r="B264" t="n">
-        <v>0.08917700000000001</v>
+        <v>0.088889</v>
       </c>
       <c r="C264" t="n">
-        <v>0.308707</v>
+        <v>0.303191</v>
       </c>
     </row>
     <row r="265">
@@ -3859,10 +3859,10 @@
         </is>
       </c>
       <c r="B265" t="n">
-        <v>0.089823</v>
+        <v>0.08917700000000001</v>
       </c>
       <c r="C265" t="n">
-        <v>0.306069</v>
+        <v>0.300532</v>
       </c>
     </row>
     <row r="266">
@@ -3872,10 +3872,10 @@
         </is>
       </c>
       <c r="B266" t="n">
-        <v>0.090265</v>
+        <v>0.089823</v>
       </c>
       <c r="C266" t="n">
-        <v>0.30343</v>
+        <v>0.297872</v>
       </c>
     </row>
     <row r="267">
@@ -3885,10 +3885,10 @@
         </is>
       </c>
       <c r="B267" t="n">
-        <v>0.090348</v>
+        <v>0.090265</v>
       </c>
       <c r="C267" t="n">
-        <v>0.300792</v>
+        <v>0.295213</v>
       </c>
     </row>
     <row r="268">
@@ -3898,10 +3898,10 @@
         </is>
       </c>
       <c r="B268" t="n">
-        <v>0.090809</v>
+        <v>0.090348</v>
       </c>
       <c r="C268" t="n">
-        <v>0.298153</v>
+        <v>0.292553</v>
       </c>
     </row>
     <row r="269">
@@ -3911,10 +3911,10 @@
         </is>
       </c>
       <c r="B269" t="n">
-        <v>0.090958</v>
+        <v>0.090809</v>
       </c>
       <c r="C269" t="n">
-        <v>0.295515</v>
+        <v>0.289894</v>
       </c>
     </row>
     <row r="270">
@@ -3924,10 +3924,10 @@
         </is>
       </c>
       <c r="B270" t="n">
-        <v>0.091434</v>
+        <v>0.090958</v>
       </c>
       <c r="C270" t="n">
-        <v>0.292876</v>
+        <v>0.287234</v>
       </c>
     </row>
     <row r="271">
@@ -3937,10 +3937,10 @@
         </is>
       </c>
       <c r="B271" t="n">
-        <v>0.0929</v>
+        <v>0.091434</v>
       </c>
       <c r="C271" t="n">
-        <v>0.290237</v>
+        <v>0.284574</v>
       </c>
     </row>
     <row r="272">
@@ -3950,10 +3950,10 @@
         </is>
       </c>
       <c r="B272" t="n">
-        <v>0.093237</v>
+        <v>0.0929</v>
       </c>
       <c r="C272" t="n">
-        <v>0.287599</v>
+        <v>0.281915</v>
       </c>
     </row>
     <row r="273">
@@ -3963,10 +3963,10 @@
         </is>
       </c>
       <c r="B273" t="n">
-        <v>0.097923</v>
+        <v>0.093237</v>
       </c>
       <c r="C273" t="n">
-        <v>0.28496</v>
+        <v>0.279255</v>
       </c>
     </row>
     <row r="274">
@@ -3976,10 +3976,10 @@
         </is>
       </c>
       <c r="B274" t="n">
-        <v>0.098237</v>
+        <v>0.097923</v>
       </c>
       <c r="C274" t="n">
-        <v>0.282322</v>
+        <v>0.276596</v>
       </c>
     </row>
     <row r="275">
@@ -3989,10 +3989,10 @@
         </is>
       </c>
       <c r="B275" t="n">
-        <v>0.09847400000000001</v>
+        <v>0.098237</v>
       </c>
       <c r="C275" t="n">
-        <v>0.279683</v>
+        <v>0.273936</v>
       </c>
     </row>
     <row r="276">
@@ -4002,10 +4002,10 @@
         </is>
       </c>
       <c r="B276" t="n">
-        <v>0.09907299999999999</v>
+        <v>0.09847400000000001</v>
       </c>
       <c r="C276" t="n">
-        <v>0.277045</v>
+        <v>0.271277</v>
       </c>
     </row>
     <row r="277">
@@ -4015,10 +4015,10 @@
         </is>
       </c>
       <c r="B277" t="n">
-        <v>0.100571</v>
+        <v>0.09907299999999999</v>
       </c>
       <c r="C277" t="n">
-        <v>0.274406</v>
+        <v>0.268617</v>
       </c>
     </row>
     <row r="278">
@@ -4028,10 +4028,10 @@
         </is>
       </c>
       <c r="B278" t="n">
-        <v>0.101335</v>
+        <v>0.09943399999999999</v>
       </c>
       <c r="C278" t="n">
-        <v>0.271768</v>
+        <v>0.265957</v>
       </c>
     </row>
     <row r="279">
@@ -4041,10 +4041,10 @@
         </is>
       </c>
       <c r="B279" t="n">
-        <v>0.101937</v>
+        <v>0.100571</v>
       </c>
       <c r="C279" t="n">
-        <v>0.269129</v>
+        <v>0.263298</v>
       </c>
     </row>
     <row r="280">
@@ -4054,10 +4054,10 @@
         </is>
       </c>
       <c r="B280" t="n">
-        <v>0.103451</v>
+        <v>0.101335</v>
       </c>
       <c r="C280" t="n">
-        <v>0.266491</v>
+        <v>0.260638</v>
       </c>
     </row>
     <row r="281">
@@ -4067,10 +4067,10 @@
         </is>
       </c>
       <c r="B281" t="n">
-        <v>0.103942</v>
+        <v>0.103451</v>
       </c>
       <c r="C281" t="n">
-        <v>0.263852</v>
+        <v>0.257979</v>
       </c>
     </row>
     <row r="282">
@@ -4080,10 +4080,10 @@
         </is>
       </c>
       <c r="B282" t="n">
-        <v>0.10427</v>
+        <v>0.103942</v>
       </c>
       <c r="C282" t="n">
-        <v>0.261214</v>
+        <v>0.255319</v>
       </c>
     </row>
     <row r="283">
@@ -4093,10 +4093,10 @@
         </is>
       </c>
       <c r="B283" t="n">
-        <v>0.105774</v>
+        <v>0.10427</v>
       </c>
       <c r="C283" t="n">
-        <v>0.258575</v>
+        <v>0.25266</v>
       </c>
     </row>
     <row r="284">
@@ -4106,10 +4106,10 @@
         </is>
       </c>
       <c r="B284" t="n">
-        <v>0.106391</v>
+        <v>0.105774</v>
       </c>
       <c r="C284" t="n">
-        <v>0.255937</v>
+        <v>0.25</v>
       </c>
     </row>
     <row r="285">
@@ -4119,10 +4119,10 @@
         </is>
       </c>
       <c r="B285" t="n">
-        <v>0.106564</v>
+        <v>0.106391</v>
       </c>
       <c r="C285" t="n">
-        <v>0.253298</v>
+        <v>0.24734</v>
       </c>
     </row>
     <row r="286">
@@ -4132,10 +4132,10 @@
         </is>
       </c>
       <c r="B286" t="n">
-        <v>0.106852</v>
+        <v>0.106564</v>
       </c>
       <c r="C286" t="n">
-        <v>0.25066</v>
+        <v>0.244681</v>
       </c>
     </row>
     <row r="287">
@@ -4145,10 +4145,10 @@
         </is>
       </c>
       <c r="B287" t="n">
-        <v>0.107359</v>
+        <v>0.106852</v>
       </c>
       <c r="C287" t="n">
-        <v>0.248021</v>
+        <v>0.242021</v>
       </c>
     </row>
     <row r="288">
@@ -4158,10 +4158,10 @@
         </is>
       </c>
       <c r="B288" t="n">
-        <v>0.110708</v>
+        <v>0.107359</v>
       </c>
       <c r="C288" t="n">
-        <v>0.245383</v>
+        <v>0.239362</v>
       </c>
     </row>
     <row r="289">
@@ -4171,10 +4171,10 @@
         </is>
       </c>
       <c r="B289" t="n">
-        <v>0.111683</v>
+        <v>0.110708</v>
       </c>
       <c r="C289" t="n">
-        <v>0.242744</v>
+        <v>0.236702</v>
       </c>
     </row>
     <row r="290">
@@ -4184,10 +4184,10 @@
         </is>
       </c>
       <c r="B290" t="n">
-        <v>0.112861</v>
+        <v>0.111683</v>
       </c>
       <c r="C290" t="n">
-        <v>0.240106</v>
+        <v>0.234043</v>
       </c>
     </row>
     <row r="291">
@@ -4197,10 +4197,10 @@
         </is>
       </c>
       <c r="B291" t="n">
-        <v>0.113263</v>
+        <v>0.112861</v>
       </c>
       <c r="C291" t="n">
-        <v>0.237467</v>
+        <v>0.231383</v>
       </c>
     </row>
     <row r="292">
@@ -4213,7 +4213,7 @@
         <v>0.11394</v>
       </c>
       <c r="C292" t="n">
-        <v>0.234828</v>
+        <v>0.228723</v>
       </c>
     </row>
     <row r="293">
@@ -4226,7 +4226,7 @@
         <v>0.114179</v>
       </c>
       <c r="C293" t="n">
-        <v>0.23219</v>
+        <v>0.226064</v>
       </c>
     </row>
     <row r="294">
@@ -4239,7 +4239,7 @@
         <v>0.11468</v>
       </c>
       <c r="C294" t="n">
-        <v>0.229551</v>
+        <v>0.223404</v>
       </c>
     </row>
     <row r="295">
@@ -4252,7 +4252,7 @@
         <v>0.115972</v>
       </c>
       <c r="C295" t="n">
-        <v>0.226913</v>
+        <v>0.220745</v>
       </c>
     </row>
     <row r="296">
@@ -4265,7 +4265,7 @@
         <v>0.117496</v>
       </c>
       <c r="C296" t="n">
-        <v>0.224274</v>
+        <v>0.218085</v>
       </c>
     </row>
     <row r="297">
@@ -4278,7 +4278,7 @@
         <v>0.117846</v>
       </c>
       <c r="C297" t="n">
-        <v>0.221636</v>
+        <v>0.215426</v>
       </c>
     </row>
     <row r="298">
@@ -4291,7 +4291,7 @@
         <v>0.119464</v>
       </c>
       <c r="C298" t="n">
-        <v>0.218997</v>
+        <v>0.212766</v>
       </c>
     </row>
     <row r="299">
@@ -4304,7 +4304,7 @@
         <v>0.120351</v>
       </c>
       <c r="C299" t="n">
-        <v>0.216359</v>
+        <v>0.210106</v>
       </c>
     </row>
     <row r="300">
@@ -4317,7 +4317,7 @@
         <v>0.120448</v>
       </c>
       <c r="C300" t="n">
-        <v>0.21372</v>
+        <v>0.207447</v>
       </c>
     </row>
     <row r="301">
@@ -4330,7 +4330,7 @@
         <v>0.121637</v>
       </c>
       <c r="C301" t="n">
-        <v>0.211082</v>
+        <v>0.204787</v>
       </c>
     </row>
     <row r="302">
@@ -4343,7 +4343,7 @@
         <v>0.12397</v>
       </c>
       <c r="C302" t="n">
-        <v>0.208443</v>
+        <v>0.202128</v>
       </c>
     </row>
     <row r="303">
@@ -4356,7 +4356,7 @@
         <v>0.124167</v>
       </c>
       <c r="C303" t="n">
-        <v>0.205805</v>
+        <v>0.199468</v>
       </c>
     </row>
     <row r="304">
@@ -4369,7 +4369,7 @@
         <v>0.126891</v>
       </c>
       <c r="C304" t="n">
-        <v>0.203166</v>
+        <v>0.196809</v>
       </c>
     </row>
     <row r="305">
@@ -4382,7 +4382,7 @@
         <v>0.128021</v>
       </c>
       <c r="C305" t="n">
-        <v>0.200528</v>
+        <v>0.194149</v>
       </c>
     </row>
     <row r="306">
@@ -4395,7 +4395,7 @@
         <v>0.128976</v>
       </c>
       <c r="C306" t="n">
-        <v>0.197889</v>
+        <v>0.191489</v>
       </c>
     </row>
     <row r="307">
@@ -4408,7 +4408,7 @@
         <v>0.130439</v>
       </c>
       <c r="C307" t="n">
-        <v>0.195251</v>
+        <v>0.18883</v>
       </c>
     </row>
     <row r="308">
@@ -4421,7 +4421,7 @@
         <v>0.130821</v>
       </c>
       <c r="C308" t="n">
-        <v>0.192612</v>
+        <v>0.18617</v>
       </c>
     </row>
     <row r="309">
@@ -4434,7 +4434,7 @@
         <v>0.130916</v>
       </c>
       <c r="C309" t="n">
-        <v>0.189974</v>
+        <v>0.183511</v>
       </c>
     </row>
     <row r="310">
@@ -4444,10 +4444,10 @@
         </is>
       </c>
       <c r="B310" t="n">
-        <v>0.131209</v>
+        <v>0.135669</v>
       </c>
       <c r="C310" t="n">
-        <v>0.187335</v>
+        <v>0.180851</v>
       </c>
     </row>
     <row r="311">
@@ -4457,10 +4457,10 @@
         </is>
       </c>
       <c r="B311" t="n">
-        <v>0.135669</v>
+        <v>0.135827</v>
       </c>
       <c r="C311" t="n">
-        <v>0.184697</v>
+        <v>0.178191</v>
       </c>
     </row>
     <row r="312">
@@ -4470,10 +4470,10 @@
         </is>
       </c>
       <c r="B312" t="n">
-        <v>0.135827</v>
+        <v>0.137023</v>
       </c>
       <c r="C312" t="n">
-        <v>0.182058</v>
+        <v>0.175532</v>
       </c>
     </row>
     <row r="313">
@@ -4483,10 +4483,10 @@
         </is>
       </c>
       <c r="B313" t="n">
-        <v>0.137023</v>
+        <v>0.13733</v>
       </c>
       <c r="C313" t="n">
-        <v>0.17942</v>
+        <v>0.172872</v>
       </c>
     </row>
     <row r="314">
@@ -4496,10 +4496,10 @@
         </is>
       </c>
       <c r="B314" t="n">
-        <v>0.13733</v>
+        <v>0.138762</v>
       </c>
       <c r="C314" t="n">
-        <v>0.176781</v>
+        <v>0.170213</v>
       </c>
     </row>
     <row r="315">
@@ -4509,10 +4509,10 @@
         </is>
       </c>
       <c r="B315" t="n">
-        <v>0.138762</v>
+        <v>0.139275</v>
       </c>
       <c r="C315" t="n">
-        <v>0.174142</v>
+        <v>0.167553</v>
       </c>
     </row>
     <row r="316">
@@ -4522,10 +4522,10 @@
         </is>
       </c>
       <c r="B316" t="n">
-        <v>0.139275</v>
+        <v>0.140029</v>
       </c>
       <c r="C316" t="n">
-        <v>0.171504</v>
+        <v>0.164894</v>
       </c>
     </row>
     <row r="317">
@@ -4535,10 +4535,10 @@
         </is>
       </c>
       <c r="B317" t="n">
-        <v>0.140029</v>
+        <v>0.140099</v>
       </c>
       <c r="C317" t="n">
-        <v>0.168865</v>
+        <v>0.162234</v>
       </c>
     </row>
     <row r="318">
@@ -4548,10 +4548,10 @@
         </is>
       </c>
       <c r="B318" t="n">
-        <v>0.140099</v>
+        <v>0.140214</v>
       </c>
       <c r="C318" t="n">
-        <v>0.166227</v>
+        <v>0.159574</v>
       </c>
     </row>
     <row r="319">
@@ -4561,10 +4561,10 @@
         </is>
       </c>
       <c r="B319" t="n">
-        <v>0.140214</v>
+        <v>0.141914</v>
       </c>
       <c r="C319" t="n">
-        <v>0.163588</v>
+        <v>0.156915</v>
       </c>
     </row>
     <row r="320">
@@ -4574,10 +4574,10 @@
         </is>
       </c>
       <c r="B320" t="n">
-        <v>0.141914</v>
+        <v>0.144579</v>
       </c>
       <c r="C320" t="n">
-        <v>0.16095</v>
+        <v>0.154255</v>
       </c>
     </row>
     <row r="321">
@@ -4587,10 +4587,10 @@
         </is>
       </c>
       <c r="B321" t="n">
-        <v>0.144579</v>
+        <v>0.145008</v>
       </c>
       <c r="C321" t="n">
-        <v>0.158311</v>
+        <v>0.151596</v>
       </c>
     </row>
     <row r="322">
@@ -4600,10 +4600,10 @@
         </is>
       </c>
       <c r="B322" t="n">
-        <v>0.145008</v>
+        <v>0.145291</v>
       </c>
       <c r="C322" t="n">
-        <v>0.155673</v>
+        <v>0.148936</v>
       </c>
     </row>
     <row r="323">
@@ -4613,10 +4613,10 @@
         </is>
       </c>
       <c r="B323" t="n">
-        <v>0.145291</v>
+        <v>0.145554</v>
       </c>
       <c r="C323" t="n">
-        <v>0.153034</v>
+        <v>0.146277</v>
       </c>
     </row>
     <row r="324">
@@ -4626,10 +4626,10 @@
         </is>
       </c>
       <c r="B324" t="n">
-        <v>0.145554</v>
+        <v>0.151419</v>
       </c>
       <c r="C324" t="n">
-        <v>0.150396</v>
+        <v>0.143617</v>
       </c>
     </row>
     <row r="325">
@@ -4639,10 +4639,10 @@
         </is>
       </c>
       <c r="B325" t="n">
-        <v>0.151419</v>
+        <v>0.151465</v>
       </c>
       <c r="C325" t="n">
-        <v>0.147757</v>
+        <v>0.140957</v>
       </c>
     </row>
     <row r="326">
@@ -4652,10 +4652,10 @@
         </is>
       </c>
       <c r="B326" t="n">
-        <v>0.151465</v>
+        <v>0.151822</v>
       </c>
       <c r="C326" t="n">
-        <v>0.145119</v>
+        <v>0.138298</v>
       </c>
     </row>
     <row r="327">
@@ -4665,10 +4665,10 @@
         </is>
       </c>
       <c r="B327" t="n">
-        <v>0.151822</v>
+        <v>0.15511</v>
       </c>
       <c r="C327" t="n">
-        <v>0.14248</v>
+        <v>0.135638</v>
       </c>
     </row>
     <row r="328">
@@ -4678,10 +4678,10 @@
         </is>
       </c>
       <c r="B328" t="n">
-        <v>0.15511</v>
+        <v>0.15559</v>
       </c>
       <c r="C328" t="n">
-        <v>0.139842</v>
+        <v>0.132979</v>
       </c>
     </row>
     <row r="329">
@@ -4691,10 +4691,10 @@
         </is>
       </c>
       <c r="B329" t="n">
-        <v>0.15559</v>
+        <v>0.155726</v>
       </c>
       <c r="C329" t="n">
-        <v>0.137203</v>
+        <v>0.130319</v>
       </c>
     </row>
     <row r="330">
@@ -4704,10 +4704,10 @@
         </is>
       </c>
       <c r="B330" t="n">
-        <v>0.155726</v>
+        <v>0.156434</v>
       </c>
       <c r="C330" t="n">
-        <v>0.134565</v>
+        <v>0.12766</v>
       </c>
     </row>
     <row r="331">
@@ -4717,10 +4717,10 @@
         </is>
       </c>
       <c r="B331" t="n">
-        <v>0.156434</v>
+        <v>0.158503</v>
       </c>
       <c r="C331" t="n">
-        <v>0.131926</v>
+        <v>0.125</v>
       </c>
     </row>
     <row r="332">
@@ -4730,10 +4730,10 @@
         </is>
       </c>
       <c r="B332" t="n">
-        <v>0.158503</v>
+        <v>0.16241</v>
       </c>
       <c r="C332" t="n">
-        <v>0.129288</v>
+        <v>0.12234</v>
       </c>
     </row>
     <row r="333">
@@ -4743,10 +4743,10 @@
         </is>
       </c>
       <c r="B333" t="n">
-        <v>0.16241</v>
+        <v>0.167126</v>
       </c>
       <c r="C333" t="n">
-        <v>0.126649</v>
+        <v>0.119681</v>
       </c>
     </row>
     <row r="334">
@@ -4756,10 +4756,10 @@
         </is>
       </c>
       <c r="B334" t="n">
-        <v>0.167126</v>
+        <v>0.172262</v>
       </c>
       <c r="C334" t="n">
-        <v>0.124011</v>
+        <v>0.117021</v>
       </c>
     </row>
     <row r="335">
@@ -4769,10 +4769,10 @@
         </is>
       </c>
       <c r="B335" t="n">
-        <v>0.172262</v>
+        <v>0.183042</v>
       </c>
       <c r="C335" t="n">
-        <v>0.121372</v>
+        <v>0.114362</v>
       </c>
     </row>
     <row r="336">
@@ -4782,10 +4782,10 @@
         </is>
       </c>
       <c r="B336" t="n">
-        <v>0.183042</v>
+        <v>0.187612</v>
       </c>
       <c r="C336" t="n">
-        <v>0.118734</v>
+        <v>0.111702</v>
       </c>
     </row>
     <row r="337">
@@ -4795,10 +4795,10 @@
         </is>
       </c>
       <c r="B337" t="n">
-        <v>0.187612</v>
+        <v>0.189387</v>
       </c>
       <c r="C337" t="n">
-        <v>0.116095</v>
+        <v>0.109043</v>
       </c>
     </row>
     <row r="338">
@@ -4808,10 +4808,10 @@
         </is>
       </c>
       <c r="B338" t="n">
-        <v>0.189387</v>
+        <v>0.193249</v>
       </c>
       <c r="C338" t="n">
-        <v>0.113456</v>
+        <v>0.106383</v>
       </c>
     </row>
     <row r="339">
@@ -4821,10 +4821,10 @@
         </is>
       </c>
       <c r="B339" t="n">
-        <v>0.193249</v>
+        <v>0.195388</v>
       </c>
       <c r="C339" t="n">
-        <v>0.110818</v>
+        <v>0.103723</v>
       </c>
     </row>
     <row r="340">
@@ -4834,10 +4834,10 @@
         </is>
       </c>
       <c r="B340" t="n">
-        <v>0.195388</v>
+        <v>0.200683</v>
       </c>
       <c r="C340" t="n">
-        <v>0.108179</v>
+        <v>0.101064</v>
       </c>
     </row>
     <row r="341">
@@ -4847,10 +4847,10 @@
         </is>
       </c>
       <c r="B341" t="n">
-        <v>0.200683</v>
+        <v>0.202141</v>
       </c>
       <c r="C341" t="n">
-        <v>0.105541</v>
+        <v>0.09840400000000001</v>
       </c>
     </row>
     <row r="342">
@@ -4860,10 +4860,10 @@
         </is>
       </c>
       <c r="B342" t="n">
-        <v>0.202141</v>
+        <v>0.206803</v>
       </c>
       <c r="C342" t="n">
-        <v>0.102902</v>
+        <v>0.095745</v>
       </c>
     </row>
     <row r="343">
@@ -4873,10 +4873,10 @@
         </is>
       </c>
       <c r="B343" t="n">
-        <v>0.206803</v>
+        <v>0.21126</v>
       </c>
       <c r="C343" t="n">
-        <v>0.100264</v>
+        <v>0.093085</v>
       </c>
     </row>
     <row r="344">
@@ -4886,10 +4886,10 @@
         </is>
       </c>
       <c r="B344" t="n">
-        <v>0.21126</v>
+        <v>0.212282</v>
       </c>
       <c r="C344" t="n">
-        <v>0.097625</v>
+        <v>0.09042600000000001</v>
       </c>
     </row>
     <row r="345">
@@ -4899,10 +4899,10 @@
         </is>
       </c>
       <c r="B345" t="n">
-        <v>0.212282</v>
+        <v>0.213977</v>
       </c>
       <c r="C345" t="n">
-        <v>0.094987</v>
+        <v>0.087766</v>
       </c>
     </row>
     <row r="346">
@@ -4912,10 +4912,10 @@
         </is>
       </c>
       <c r="B346" t="n">
-        <v>0.213977</v>
+        <v>0.224095</v>
       </c>
       <c r="C346" t="n">
-        <v>0.092348</v>
+        <v>0.085106</v>
       </c>
     </row>
     <row r="347">
@@ -4925,10 +4925,10 @@
         </is>
       </c>
       <c r="B347" t="n">
-        <v>0.224095</v>
+        <v>0.229443</v>
       </c>
       <c r="C347" t="n">
-        <v>0.08971</v>
+        <v>0.08244700000000001</v>
       </c>
     </row>
     <row r="348">
@@ -4938,10 +4938,10 @@
         </is>
       </c>
       <c r="B348" t="n">
-        <v>0.229443</v>
+        <v>0.235662</v>
       </c>
       <c r="C348" t="n">
-        <v>0.087071</v>
+        <v>0.079787</v>
       </c>
     </row>
     <row r="349">
@@ -4951,10 +4951,10 @@
         </is>
       </c>
       <c r="B349" t="n">
-        <v>0.235662</v>
+        <v>0.245733</v>
       </c>
       <c r="C349" t="n">
-        <v>0.08443299999999999</v>
+        <v>0.077128</v>
       </c>
     </row>
     <row r="350">
@@ -4967,7 +4967,7 @@
         <v>0.257813</v>
       </c>
       <c r="C350" t="n">
-        <v>0.08179400000000001</v>
+        <v>0.07446800000000001</v>
       </c>
     </row>
     <row r="351">
@@ -4977,10 +4977,10 @@
         </is>
       </c>
       <c r="B351" t="n">
-        <v>0.267282</v>
+        <v>0.279391</v>
       </c>
       <c r="C351" t="n">
-        <v>0.079156</v>
+        <v>0.071809</v>
       </c>
     </row>
     <row r="352">
@@ -4990,10 +4990,10 @@
         </is>
       </c>
       <c r="B352" t="n">
-        <v>0.279391</v>
+        <v>0.286735</v>
       </c>
       <c r="C352" t="n">
-        <v>0.076517</v>
+        <v>0.069149</v>
       </c>
     </row>
     <row r="353">
@@ -5003,10 +5003,10 @@
         </is>
       </c>
       <c r="B353" t="n">
-        <v>0.286735</v>
+        <v>0.28675</v>
       </c>
       <c r="C353" t="n">
-        <v>0.073879</v>
+        <v>0.06648900000000001</v>
       </c>
     </row>
     <row r="354">
@@ -5016,10 +5016,10 @@
         </is>
       </c>
       <c r="B354" t="n">
-        <v>0.28675</v>
+        <v>0.292707</v>
       </c>
       <c r="C354" t="n">
-        <v>0.07124</v>
+        <v>0.06383</v>
       </c>
     </row>
     <row r="355">
@@ -5029,10 +5029,10 @@
         </is>
       </c>
       <c r="B355" t="n">
-        <v>0.292707</v>
+        <v>0.303016</v>
       </c>
       <c r="C355" t="n">
-        <v>0.068602</v>
+        <v>0.06117</v>
       </c>
     </row>
     <row r="356">
@@ -5042,10 +5042,10 @@
         </is>
       </c>
       <c r="B356" t="n">
-        <v>0.303016</v>
+        <v>0.35577</v>
       </c>
       <c r="C356" t="n">
-        <v>0.06596299999999999</v>
+        <v>0.058511</v>
       </c>
     </row>
     <row r="357">
@@ -5055,10 +5055,10 @@
         </is>
       </c>
       <c r="B357" t="n">
-        <v>0.35577</v>
+        <v>0.359445</v>
       </c>
       <c r="C357" t="n">
-        <v>0.06332500000000001</v>
+        <v>0.055851</v>
       </c>
     </row>
     <row r="358">
@@ -5068,10 +5068,10 @@
         </is>
       </c>
       <c r="B358" t="n">
-        <v>0.359445</v>
+        <v>0.363732</v>
       </c>
       <c r="C358" t="n">
-        <v>0.060686</v>
+        <v>0.053191</v>
       </c>
     </row>
     <row r="359">
@@ -5081,10 +5081,10 @@
         </is>
       </c>
       <c r="B359" t="n">
-        <v>0.363732</v>
+        <v>0.36468</v>
       </c>
       <c r="C359" t="n">
-        <v>0.058047</v>
+        <v>0.050532</v>
       </c>
     </row>
     <row r="360">
@@ -5094,10 +5094,10 @@
         </is>
       </c>
       <c r="B360" t="n">
-        <v>0.36468</v>
+        <v>0.373827</v>
       </c>
       <c r="C360" t="n">
-        <v>0.055409</v>
+        <v>0.047872</v>
       </c>
     </row>
     <row r="361">
@@ -5107,10 +5107,10 @@
         </is>
       </c>
       <c r="B361" t="n">
-        <v>0.373827</v>
+        <v>0.389014</v>
       </c>
       <c r="C361" t="n">
-        <v>0.05277</v>
+        <v>0.045213</v>
       </c>
     </row>
     <row r="362">
@@ -5120,10 +5120,10 @@
         </is>
       </c>
       <c r="B362" t="n">
-        <v>0.389014</v>
+        <v>0.400164</v>
       </c>
       <c r="C362" t="n">
-        <v>0.050132</v>
+        <v>0.042553</v>
       </c>
     </row>
     <row r="363">
@@ -5133,10 +5133,10 @@
         </is>
       </c>
       <c r="B363" t="n">
-        <v>0.400164</v>
+        <v>0.40983</v>
       </c>
       <c r="C363" t="n">
-        <v>0.047493</v>
+        <v>0.039894</v>
       </c>
     </row>
     <row r="364">
@@ -5146,10 +5146,10 @@
         </is>
       </c>
       <c r="B364" t="n">
-        <v>0.40983</v>
+        <v>0.410903</v>
       </c>
       <c r="C364" t="n">
-        <v>0.044855</v>
+        <v>0.037234</v>
       </c>
     </row>
     <row r="365">
@@ -5159,10 +5159,10 @@
         </is>
       </c>
       <c r="B365" t="n">
-        <v>0.410903</v>
+        <v>0.419404</v>
       </c>
       <c r="C365" t="n">
-        <v>0.042216</v>
+        <v>0.034574</v>
       </c>
     </row>
     <row r="366">
@@ -5172,10 +5172,10 @@
         </is>
       </c>
       <c r="B366" t="n">
-        <v>0.419404</v>
+        <v>0.440642</v>
       </c>
       <c r="C366" t="n">
-        <v>0.039578</v>
+        <v>0.031915</v>
       </c>
     </row>
     <row r="367">
@@ -5185,10 +5185,10 @@
         </is>
       </c>
       <c r="B367" t="n">
-        <v>0.440642</v>
+        <v>0.454545</v>
       </c>
       <c r="C367" t="n">
-        <v>0.036939</v>
+        <v>0.029255</v>
       </c>
     </row>
     <row r="368">
@@ -5198,10 +5198,10 @@
         </is>
       </c>
       <c r="B368" t="n">
-        <v>0.454545</v>
+        <v>0.587794</v>
       </c>
       <c r="C368" t="n">
-        <v>0.034301</v>
+        <v>0.026596</v>
       </c>
     </row>
     <row r="369">
@@ -5211,10 +5211,10 @@
         </is>
       </c>
       <c r="B369" t="n">
-        <v>0.587794</v>
+        <v>0.620194</v>
       </c>
       <c r="C369" t="n">
-        <v>0.031662</v>
+        <v>0.023936</v>
       </c>
     </row>
     <row r="370">
@@ -5224,10 +5224,10 @@
         </is>
       </c>
       <c r="B370" t="n">
-        <v>0.620194</v>
+        <v>0.634074</v>
       </c>
       <c r="C370" t="n">
-        <v>0.029024</v>
+        <v>0.021277</v>
       </c>
     </row>
     <row r="371">
@@ -5237,10 +5237,10 @@
         </is>
       </c>
       <c r="B371" t="n">
-        <v>0.634074</v>
+        <v>0.672434</v>
       </c>
       <c r="C371" t="n">
-        <v>0.026385</v>
+        <v>0.018617</v>
       </c>
     </row>
     <row r="372">
@@ -5250,10 +5250,10 @@
         </is>
       </c>
       <c r="B372" t="n">
-        <v>0.648021</v>
+        <v>0.678189</v>
       </c>
       <c r="C372" t="n">
-        <v>0.023747</v>
+        <v>0.015957</v>
       </c>
     </row>
     <row r="373">
@@ -5263,10 +5263,10 @@
         </is>
       </c>
       <c r="B373" t="n">
-        <v>0.672434</v>
+        <v>0.707604</v>
       </c>
       <c r="C373" t="n">
-        <v>0.021108</v>
+        <v>0.013298</v>
       </c>
     </row>
     <row r="374">
@@ -5276,10 +5276,10 @@
         </is>
       </c>
       <c r="B374" t="n">
-        <v>0.678189</v>
+        <v>0.711338</v>
       </c>
       <c r="C374" t="n">
-        <v>0.01847</v>
+        <v>0.010638</v>
       </c>
     </row>
     <row r="375">
@@ -5289,10 +5289,10 @@
         </is>
       </c>
       <c r="B375" t="n">
-        <v>0.707604</v>
+        <v>0.76535</v>
       </c>
       <c r="C375" t="n">
-        <v>0.015831</v>
+        <v>0.007979</v>
       </c>
     </row>
     <row r="376">
@@ -5302,10 +5302,10 @@
         </is>
       </c>
       <c r="B376" t="n">
-        <v>0.711338</v>
+        <v>0.838984</v>
       </c>
       <c r="C376" t="n">
-        <v>0.013193</v>
+        <v>0.005319</v>
       </c>
     </row>
     <row r="377">
@@ -5315,49 +5315,49 @@
         </is>
       </c>
       <c r="B377" t="n">
-        <v>0.76535</v>
+        <v>1.015082</v>
       </c>
       <c r="C377" t="n">
-        <v>0.010554</v>
+        <v>0.00266</v>
       </c>
     </row>
     <row r="378">
       <c r="A378" t="inlineStr">
         <is>
-          <t>Raw market</t>
+          <t>Adjusted target</t>
         </is>
       </c>
       <c r="B378" t="n">
-        <v>0.838984</v>
+        <v>1e-06</v>
       </c>
       <c r="C378" t="n">
-        <v>0.007915999999999999</v>
+        <v>1</v>
       </c>
     </row>
     <row r="379">
       <c r="A379" t="inlineStr">
         <is>
-          <t>Raw market</t>
+          <t>Adjusted target</t>
         </is>
       </c>
       <c r="B379" t="n">
-        <v>1.015082</v>
+        <v>0.000102</v>
       </c>
       <c r="C379" t="n">
-        <v>0.005277</v>
+        <v>0.99734</v>
       </c>
     </row>
     <row r="380">
       <c r="A380" t="inlineStr">
         <is>
-          <t>Raw market</t>
+          <t>Adjusted target</t>
         </is>
       </c>
       <c r="B380" t="n">
-        <v>2.37737</v>
+        <v>0.000307</v>
       </c>
       <c r="C380" t="n">
-        <v>0.002639</v>
+        <v>0.994681</v>
       </c>
     </row>
     <row r="381">
@@ -5367,10 +5367,10 @@
         </is>
       </c>
       <c r="B381" t="n">
-        <v>1e-06</v>
+        <v>0.000503</v>
       </c>
       <c r="C381" t="n">
-        <v>1</v>
+        <v>0.992021</v>
       </c>
     </row>
     <row r="382">
@@ -5380,10 +5380,10 @@
         </is>
       </c>
       <c r="B382" t="n">
-        <v>0.000108</v>
+        <v>0.00102</v>
       </c>
       <c r="C382" t="n">
-        <v>0.9973610000000001</v>
+        <v>0.989362</v>
       </c>
     </row>
     <row r="383">
@@ -5393,10 +5393,10 @@
         </is>
       </c>
       <c r="B383" t="n">
-        <v>0.000301</v>
+        <v>0.001631</v>
       </c>
       <c r="C383" t="n">
-        <v>0.994723</v>
+        <v>0.986702</v>
       </c>
     </row>
     <row r="384">
@@ -5406,10 +5406,10 @@
         </is>
       </c>
       <c r="B384" t="n">
-        <v>0.000517</v>
+        <v>0.001849</v>
       </c>
       <c r="C384" t="n">
-        <v>0.992084</v>
+        <v>0.984043</v>
       </c>
     </row>
     <row r="385">
@@ -5419,10 +5419,10 @@
         </is>
       </c>
       <c r="B385" t="n">
-        <v>0.000993</v>
+        <v>0.001885</v>
       </c>
       <c r="C385" t="n">
-        <v>0.989446</v>
+        <v>0.981383</v>
       </c>
     </row>
     <row r="386">
@@ -5432,10 +5432,10 @@
         </is>
       </c>
       <c r="B386" t="n">
-        <v>0.001625</v>
+        <v>0.002077</v>
       </c>
       <c r="C386" t="n">
-        <v>0.986807</v>
+        <v>0.978723</v>
       </c>
     </row>
     <row r="387">
@@ -5445,10 +5445,10 @@
         </is>
       </c>
       <c r="B387" t="n">
-        <v>0.001915</v>
+        <v>0.002655</v>
       </c>
       <c r="C387" t="n">
-        <v>0.984169</v>
+        <v>0.976064</v>
       </c>
     </row>
     <row r="388">
@@ -5458,10 +5458,10 @@
         </is>
       </c>
       <c r="B388" t="n">
-        <v>0.00195</v>
+        <v>0.002798</v>
       </c>
       <c r="C388" t="n">
-        <v>0.98153</v>
+        <v>0.973404</v>
       </c>
     </row>
     <row r="389">
@@ -5471,10 +5471,10 @@
         </is>
       </c>
       <c r="B389" t="n">
-        <v>0.002083</v>
+        <v>0.003129</v>
       </c>
       <c r="C389" t="n">
-        <v>0.978892</v>
+        <v>0.970745</v>
       </c>
     </row>
     <row r="390">
@@ -5484,10 +5484,10 @@
         </is>
       </c>
       <c r="B390" t="n">
-        <v>0.002689</v>
+        <v>0.003421</v>
       </c>
       <c r="C390" t="n">
-        <v>0.976253</v>
+        <v>0.968085</v>
       </c>
     </row>
     <row r="391">
@@ -5497,10 +5497,10 @@
         </is>
       </c>
       <c r="B391" t="n">
-        <v>0.002826</v>
+        <v>0.004014</v>
       </c>
       <c r="C391" t="n">
-        <v>0.973615</v>
+        <v>0.965426</v>
       </c>
     </row>
     <row r="392">
@@ -5510,10 +5510,10 @@
         </is>
       </c>
       <c r="B392" t="n">
-        <v>0.003056</v>
+        <v>0.004049</v>
       </c>
       <c r="C392" t="n">
-        <v>0.970976</v>
+        <v>0.962766</v>
       </c>
     </row>
     <row r="393">
@@ -5523,10 +5523,10 @@
         </is>
       </c>
       <c r="B393" t="n">
-        <v>0.003365</v>
+        <v>0.004162</v>
       </c>
       <c r="C393" t="n">
-        <v>0.968338</v>
+        <v>0.960106</v>
       </c>
     </row>
     <row r="394">
@@ -5536,10 +5536,10 @@
         </is>
       </c>
       <c r="B394" t="n">
-        <v>0.003619</v>
+        <v>0.004376</v>
       </c>
       <c r="C394" t="n">
-        <v>0.965699</v>
+        <v>0.957447</v>
       </c>
     </row>
     <row r="395">
@@ -5549,10 +5549,10 @@
         </is>
       </c>
       <c r="B395" t="n">
-        <v>0.004103</v>
+        <v>0.004698</v>
       </c>
       <c r="C395" t="n">
-        <v>0.9630609999999999</v>
+        <v>0.9547870000000001</v>
       </c>
     </row>
     <row r="396">
@@ -5562,10 +5562,10 @@
         </is>
       </c>
       <c r="B396" t="n">
-        <v>0.0042</v>
+        <v>0.004715</v>
       </c>
       <c r="C396" t="n">
-        <v>0.960422</v>
+        <v>0.952128</v>
       </c>
     </row>
     <row r="397">
@@ -5575,10 +5575,10 @@
         </is>
       </c>
       <c r="B397" t="n">
-        <v>0.004267</v>
+        <v>0.004717</v>
       </c>
       <c r="C397" t="n">
-        <v>0.957784</v>
+        <v>0.949468</v>
       </c>
     </row>
     <row r="398">
@@ -5588,10 +5588,10 @@
         </is>
       </c>
       <c r="B398" t="n">
-        <v>0.004338</v>
+        <v>0.004792</v>
       </c>
       <c r="C398" t="n">
-        <v>0.955145</v>
+        <v>0.946809</v>
       </c>
     </row>
     <row r="399">
@@ -5601,10 +5601,10 @@
         </is>
       </c>
       <c r="B399" t="n">
-        <v>0.004453</v>
+        <v>0.004927</v>
       </c>
       <c r="C399" t="n">
-        <v>0.952507</v>
+        <v>0.944149</v>
       </c>
     </row>
     <row r="400">
@@ -5614,10 +5614,10 @@
         </is>
       </c>
       <c r="B400" t="n">
-        <v>0.004747</v>
+        <v>0.005237</v>
       </c>
       <c r="C400" t="n">
-        <v>0.949868</v>
+        <v>0.941489</v>
       </c>
     </row>
     <row r="401">
@@ -5627,10 +5627,10 @@
         </is>
       </c>
       <c r="B401" t="n">
-        <v>0.004779</v>
+        <v>0.00539</v>
       </c>
       <c r="C401" t="n">
-        <v>0.94723</v>
+        <v>0.9388300000000001</v>
       </c>
     </row>
     <row r="402">
@@ -5640,10 +5640,10 @@
         </is>
       </c>
       <c r="B402" t="n">
-        <v>0.004802</v>
+        <v>0.005401</v>
       </c>
       <c r="C402" t="n">
-        <v>0.944591</v>
+        <v>0.9361699999999999</v>
       </c>
     </row>
     <row r="403">
@@ -5653,10 +5653,10 @@
         </is>
       </c>
       <c r="B403" t="n">
-        <v>0.005033</v>
+        <v>0.005853</v>
       </c>
       <c r="C403" t="n">
-        <v>0.941953</v>
+        <v>0.933511</v>
       </c>
     </row>
     <row r="404">
@@ -5666,10 +5666,10 @@
         </is>
       </c>
       <c r="B404" t="n">
-        <v>0.005286</v>
+        <v>0.005855</v>
       </c>
       <c r="C404" t="n">
-        <v>0.939314</v>
+        <v>0.930851</v>
       </c>
     </row>
     <row r="405">
@@ -5679,10 +5679,10 @@
         </is>
       </c>
       <c r="B405" t="n">
-        <v>0.005559</v>
+        <v>0.006366</v>
       </c>
       <c r="C405" t="n">
-        <v>0.936675</v>
+        <v>0.928191</v>
       </c>
     </row>
     <row r="406">
@@ -5692,10 +5692,10 @@
         </is>
       </c>
       <c r="B406" t="n">
-        <v>0.005712</v>
+        <v>0.006759</v>
       </c>
       <c r="C406" t="n">
-        <v>0.934037</v>
+        <v>0.925532</v>
       </c>
     </row>
     <row r="407">
@@ -5705,10 +5705,10 @@
         </is>
       </c>
       <c r="B407" t="n">
-        <v>0.005745</v>
+        <v>0.007556</v>
       </c>
       <c r="C407" t="n">
-        <v>0.9313979999999999</v>
+        <v>0.922872</v>
       </c>
     </row>
     <row r="408">
@@ -5718,10 +5718,10 @@
         </is>
       </c>
       <c r="B408" t="n">
-        <v>0.005887</v>
+        <v>0.007887</v>
       </c>
       <c r="C408" t="n">
-        <v>0.92876</v>
+        <v>0.9202129999999999</v>
       </c>
     </row>
     <row r="409">
@@ -5731,10 +5731,10 @@
         </is>
       </c>
       <c r="B409" t="n">
-        <v>0.006738</v>
+        <v>0.008090999999999999</v>
       </c>
       <c r="C409" t="n">
-        <v>0.926121</v>
+        <v>0.917553</v>
       </c>
     </row>
     <row r="410">
@@ -5744,10 +5744,10 @@
         </is>
       </c>
       <c r="B410" t="n">
-        <v>0.0069</v>
+        <v>0.008198</v>
       </c>
       <c r="C410" t="n">
-        <v>0.9234830000000001</v>
+        <v>0.914894</v>
       </c>
     </row>
     <row r="411">
@@ -5757,10 +5757,10 @@
         </is>
       </c>
       <c r="B411" t="n">
-        <v>0.007769</v>
+        <v>0.008213</v>
       </c>
       <c r="C411" t="n">
-        <v>0.920844</v>
+        <v>0.912234</v>
       </c>
     </row>
     <row r="412">
@@ -5770,10 +5770,10 @@
         </is>
       </c>
       <c r="B412" t="n">
-        <v>0.008177</v>
+        <v>0.008325000000000001</v>
       </c>
       <c r="C412" t="n">
-        <v>0.918206</v>
+        <v>0.909574</v>
       </c>
     </row>
     <row r="413">
@@ -5783,10 +5783,10 @@
         </is>
       </c>
       <c r="B413" t="n">
-        <v>0.008243</v>
+        <v>0.008584</v>
       </c>
       <c r="C413" t="n">
-        <v>0.915567</v>
+        <v>0.906915</v>
       </c>
     </row>
     <row r="414">
@@ -5796,10 +5796,10 @@
         </is>
       </c>
       <c r="B414" t="n">
-        <v>0.008603</v>
+        <v>0.008670000000000001</v>
       </c>
       <c r="C414" t="n">
-        <v>0.912929</v>
+        <v>0.904255</v>
       </c>
     </row>
     <row r="415">
@@ -5809,10 +5809,10 @@
         </is>
       </c>
       <c r="B415" t="n">
-        <v>0.008626</v>
+        <v>0.008696000000000001</v>
       </c>
       <c r="C415" t="n">
-        <v>0.91029</v>
+        <v>0.901596</v>
       </c>
     </row>
     <row r="416">
@@ -5822,10 +5822,10 @@
         </is>
       </c>
       <c r="B416" t="n">
-        <v>0.008701</v>
+        <v>0.008838</v>
       </c>
       <c r="C416" t="n">
-        <v>0.907652</v>
+        <v>0.898936</v>
       </c>
     </row>
     <row r="417">
@@ -5835,10 +5835,10 @@
         </is>
       </c>
       <c r="B417" t="n">
-        <v>0.008722000000000001</v>
+        <v>0.009552</v>
       </c>
       <c r="C417" t="n">
-        <v>0.905013</v>
+        <v>0.896277</v>
       </c>
     </row>
     <row r="418">
@@ -5848,10 +5848,10 @@
         </is>
       </c>
       <c r="B418" t="n">
-        <v>0.008932000000000001</v>
+        <v>0.009578</v>
       </c>
       <c r="C418" t="n">
-        <v>0.902375</v>
+        <v>0.893617</v>
       </c>
     </row>
     <row r="419">
@@ -5861,10 +5861,10 @@
         </is>
       </c>
       <c r="B419" t="n">
-        <v>0.009009</v>
+        <v>0.009582</v>
       </c>
       <c r="C419" t="n">
-        <v>0.899736</v>
+        <v>0.890957</v>
       </c>
     </row>
     <row r="420">
@@ -5874,10 +5874,10 @@
         </is>
       </c>
       <c r="B420" t="n">
-        <v>0.009431</v>
+        <v>0.00971</v>
       </c>
       <c r="C420" t="n">
-        <v>0.897098</v>
+        <v>0.888298</v>
       </c>
     </row>
     <row r="421">
@@ -5887,10 +5887,10 @@
         </is>
       </c>
       <c r="B421" t="n">
-        <v>0.009752</v>
+        <v>0.009842999999999999</v>
       </c>
       <c r="C421" t="n">
-        <v>0.894459</v>
+        <v>0.885638</v>
       </c>
     </row>
     <row r="422">
@@ -5900,10 +5900,10 @@
         </is>
       </c>
       <c r="B422" t="n">
-        <v>0.009863</v>
+        <v>0.009845</v>
       </c>
       <c r="C422" t="n">
-        <v>0.891821</v>
+        <v>0.882979</v>
       </c>
     </row>
     <row r="423">
@@ -5913,10 +5913,10 @@
         </is>
       </c>
       <c r="B423" t="n">
-        <v>0.009897</v>
+        <v>0.009894</v>
       </c>
       <c r="C423" t="n">
-        <v>0.889182</v>
+        <v>0.880319</v>
       </c>
     </row>
     <row r="424">
@@ -5926,10 +5926,10 @@
         </is>
       </c>
       <c r="B424" t="n">
-        <v>0.009959000000000001</v>
+        <v>0.010175</v>
       </c>
       <c r="C424" t="n">
-        <v>0.886544</v>
+        <v>0.87766</v>
       </c>
     </row>
     <row r="425">
@@ -5939,10 +5939,10 @@
         </is>
       </c>
       <c r="B425" t="n">
-        <v>0.010057</v>
+        <v>0.010302</v>
       </c>
       <c r="C425" t="n">
-        <v>0.8839050000000001</v>
+        <v>0.875</v>
       </c>
     </row>
     <row r="426">
@@ -5952,10 +5952,10 @@
         </is>
       </c>
       <c r="B426" t="n">
-        <v>0.010249</v>
+        <v>0.010501</v>
       </c>
       <c r="C426" t="n">
-        <v>0.881266</v>
+        <v>0.87234</v>
       </c>
     </row>
     <row r="427">
@@ -5965,10 +5965,10 @@
         </is>
       </c>
       <c r="B427" t="n">
-        <v>0.010604</v>
+        <v>0.010995</v>
       </c>
       <c r="C427" t="n">
-        <v>0.878628</v>
+        <v>0.869681</v>
       </c>
     </row>
     <row r="428">
@@ -5978,10 +5978,10 @@
         </is>
       </c>
       <c r="B428" t="n">
-        <v>0.010697</v>
+        <v>0.011579</v>
       </c>
       <c r="C428" t="n">
-        <v>0.875989</v>
+        <v>0.867021</v>
       </c>
     </row>
     <row r="429">
@@ -5991,10 +5991,10 @@
         </is>
       </c>
       <c r="B429" t="n">
-        <v>0.010729</v>
+        <v>0.011742</v>
       </c>
       <c r="C429" t="n">
-        <v>0.873351</v>
+        <v>0.864362</v>
       </c>
     </row>
     <row r="430">
@@ -6004,10 +6004,10 @@
         </is>
       </c>
       <c r="B430" t="n">
-        <v>0.01095</v>
+        <v>0.011898</v>
       </c>
       <c r="C430" t="n">
-        <v>0.870712</v>
+        <v>0.861702</v>
       </c>
     </row>
     <row r="431">
@@ -6017,10 +6017,10 @@
         </is>
       </c>
       <c r="B431" t="n">
-        <v>0.011538</v>
+        <v>0.011942</v>
       </c>
       <c r="C431" t="n">
-        <v>0.868074</v>
+        <v>0.859043</v>
       </c>
     </row>
     <row r="432">
@@ -6030,10 +6030,10 @@
         </is>
       </c>
       <c r="B432" t="n">
-        <v>0.01184</v>
+        <v>0.012238</v>
       </c>
       <c r="C432" t="n">
-        <v>0.865435</v>
+        <v>0.856383</v>
       </c>
     </row>
     <row r="433">
@@ -6043,10 +6043,10 @@
         </is>
       </c>
       <c r="B433" t="n">
-        <v>0.011961</v>
+        <v>0.012288</v>
       </c>
       <c r="C433" t="n">
-        <v>0.862797</v>
+        <v>0.853723</v>
       </c>
     </row>
     <row r="434">
@@ -6056,10 +6056,10 @@
         </is>
       </c>
       <c r="B434" t="n">
-        <v>0.012029</v>
+        <v>0.012637</v>
       </c>
       <c r="C434" t="n">
-        <v>0.860158</v>
+        <v>0.851064</v>
       </c>
     </row>
     <row r="435">
@@ -6069,10 +6069,10 @@
         </is>
       </c>
       <c r="B435" t="n">
-        <v>0.012123</v>
+        <v>0.012911</v>
       </c>
       <c r="C435" t="n">
-        <v>0.8575199999999999</v>
+        <v>0.848404</v>
       </c>
     </row>
     <row r="436">
@@ -6082,10 +6082,10 @@
         </is>
       </c>
       <c r="B436" t="n">
-        <v>0.012358</v>
+        <v>0.01311</v>
       </c>
       <c r="C436" t="n">
-        <v>0.854881</v>
+        <v>0.845745</v>
       </c>
     </row>
     <row r="437">
@@ -6095,10 +6095,10 @@
         </is>
       </c>
       <c r="B437" t="n">
-        <v>0.012648</v>
+        <v>0.013435</v>
       </c>
       <c r="C437" t="n">
-        <v>0.852243</v>
+        <v>0.843085</v>
       </c>
     </row>
     <row r="438">
@@ -6108,10 +6108,10 @@
         </is>
       </c>
       <c r="B438" t="n">
-        <v>0.012936</v>
+        <v>0.01364</v>
       </c>
       <c r="C438" t="n">
-        <v>0.849604</v>
+        <v>0.840426</v>
       </c>
     </row>
     <row r="439">
@@ -6121,10 +6121,10 @@
         </is>
       </c>
       <c r="B439" t="n">
-        <v>0.01305</v>
+        <v>0.013653</v>
       </c>
       <c r="C439" t="n">
-        <v>0.846966</v>
+        <v>0.837766</v>
       </c>
     </row>
     <row r="440">
@@ -6134,10 +6134,10 @@
         </is>
       </c>
       <c r="B440" t="n">
-        <v>0.013176</v>
+        <v>0.014212</v>
       </c>
       <c r="C440" t="n">
-        <v>0.844327</v>
+        <v>0.835106</v>
       </c>
     </row>
     <row r="441">
@@ -6147,10 +6147,10 @@
         </is>
       </c>
       <c r="B441" t="n">
-        <v>0.014337</v>
+        <v>0.014219</v>
       </c>
       <c r="C441" t="n">
-        <v>0.841689</v>
+        <v>0.832447</v>
       </c>
     </row>
     <row r="442">
@@ -6160,10 +6160,10 @@
         </is>
       </c>
       <c r="B442" t="n">
-        <v>0.014373</v>
+        <v>0.014468</v>
       </c>
       <c r="C442" t="n">
-        <v>0.83905</v>
+        <v>0.8297870000000001</v>
       </c>
     </row>
     <row r="443">
@@ -6173,10 +6173,10 @@
         </is>
       </c>
       <c r="B443" t="n">
-        <v>0.0145</v>
+        <v>0.014515</v>
       </c>
       <c r="C443" t="n">
-        <v>0.836412</v>
+        <v>0.827128</v>
       </c>
     </row>
     <row r="444">
@@ -6186,10 +6186,10 @@
         </is>
       </c>
       <c r="B444" t="n">
-        <v>0.014646</v>
+        <v>0.01482</v>
       </c>
       <c r="C444" t="n">
-        <v>0.833773</v>
+        <v>0.824468</v>
       </c>
     </row>
     <row r="445">
@@ -6199,10 +6199,10 @@
         </is>
       </c>
       <c r="B445" t="n">
-        <v>0.014989</v>
+        <v>0.015057</v>
       </c>
       <c r="C445" t="n">
-        <v>0.831135</v>
+        <v>0.821809</v>
       </c>
     </row>
     <row r="446">
@@ -6212,10 +6212,10 @@
         </is>
       </c>
       <c r="B446" t="n">
-        <v>0.015165</v>
+        <v>0.015242</v>
       </c>
       <c r="C446" t="n">
-        <v>0.828496</v>
+        <v>0.819149</v>
       </c>
     </row>
     <row r="447">
@@ -6225,10 +6225,10 @@
         </is>
       </c>
       <c r="B447" t="n">
-        <v>0.015339</v>
+        <v>0.015551</v>
       </c>
       <c r="C447" t="n">
-        <v>0.825858</v>
+        <v>0.816489</v>
       </c>
     </row>
     <row r="448">
@@ -6238,10 +6238,10 @@
         </is>
       </c>
       <c r="B448" t="n">
-        <v>0.015456</v>
+        <v>0.015605</v>
       </c>
       <c r="C448" t="n">
-        <v>0.823219</v>
+        <v>0.8138300000000001</v>
       </c>
     </row>
     <row r="449">
@@ -6251,10 +6251,10 @@
         </is>
       </c>
       <c r="B449" t="n">
-        <v>0.015877</v>
+        <v>0.015807</v>
       </c>
       <c r="C449" t="n">
-        <v>0.82058</v>
+        <v>0.8111699999999999</v>
       </c>
     </row>
     <row r="450">
@@ -6264,10 +6264,10 @@
         </is>
       </c>
       <c r="B450" t="n">
-        <v>0.016034</v>
+        <v>0.015812</v>
       </c>
       <c r="C450" t="n">
-        <v>0.8179419999999999</v>
+        <v>0.808511</v>
       </c>
     </row>
     <row r="451">
@@ -6277,10 +6277,10 @@
         </is>
       </c>
       <c r="B451" t="n">
-        <v>0.016134</v>
+        <v>0.016268</v>
       </c>
       <c r="C451" t="n">
-        <v>0.815303</v>
+        <v>0.805851</v>
       </c>
     </row>
     <row r="452">
@@ -6290,10 +6290,10 @@
         </is>
       </c>
       <c r="B452" t="n">
-        <v>0.016241</v>
+        <v>0.016444</v>
       </c>
       <c r="C452" t="n">
-        <v>0.812665</v>
+        <v>0.803191</v>
       </c>
     </row>
     <row r="453">
@@ -6303,10 +6303,10 @@
         </is>
       </c>
       <c r="B453" t="n">
-        <v>0.016568</v>
+        <v>0.016539</v>
       </c>
       <c r="C453" t="n">
-        <v>0.810026</v>
+        <v>0.800532</v>
       </c>
     </row>
     <row r="454">
@@ -6316,10 +6316,10 @@
         </is>
       </c>
       <c r="B454" t="n">
-        <v>0.016647</v>
+        <v>0.017115</v>
       </c>
       <c r="C454" t="n">
-        <v>0.807388</v>
+        <v>0.797872</v>
       </c>
     </row>
     <row r="455">
@@ -6329,10 +6329,10 @@
         </is>
       </c>
       <c r="B455" t="n">
-        <v>0.01674</v>
+        <v>0.017277</v>
       </c>
       <c r="C455" t="n">
-        <v>0.804749</v>
+        <v>0.7952129999999999</v>
       </c>
     </row>
     <row r="456">
@@ -6342,10 +6342,10 @@
         </is>
       </c>
       <c r="B456" t="n">
-        <v>0.017067</v>
+        <v>0.017338</v>
       </c>
       <c r="C456" t="n">
-        <v>0.802111</v>
+        <v>0.792553</v>
       </c>
     </row>
     <row r="457">
@@ -6355,10 +6355,10 @@
         </is>
       </c>
       <c r="B457" t="n">
-        <v>0.017324</v>
+        <v>0.017858</v>
       </c>
       <c r="C457" t="n">
-        <v>0.799472</v>
+        <v>0.789894</v>
       </c>
     </row>
     <row r="458">
@@ -6368,10 +6368,10 @@
         </is>
       </c>
       <c r="B458" t="n">
-        <v>0.018026</v>
+        <v>0.017967</v>
       </c>
       <c r="C458" t="n">
-        <v>0.796834</v>
+        <v>0.787234</v>
       </c>
     </row>
     <row r="459">
@@ -6381,10 +6381,10 @@
         </is>
       </c>
       <c r="B459" t="n">
-        <v>0.018096</v>
+        <v>0.01822</v>
       </c>
       <c r="C459" t="n">
-        <v>0.794195</v>
+        <v>0.784574</v>
       </c>
     </row>
     <row r="460">
@@ -6394,10 +6394,10 @@
         </is>
       </c>
       <c r="B460" t="n">
-        <v>0.018405</v>
+        <v>0.018507</v>
       </c>
       <c r="C460" t="n">
-        <v>0.791557</v>
+        <v>0.781915</v>
       </c>
     </row>
     <row r="461">
@@ -6407,10 +6407,10 @@
         </is>
       </c>
       <c r="B461" t="n">
-        <v>0.018553</v>
+        <v>0.018573</v>
       </c>
       <c r="C461" t="n">
-        <v>0.788918</v>
+        <v>0.779255</v>
       </c>
     </row>
     <row r="462">
@@ -6420,10 +6420,10 @@
         </is>
       </c>
       <c r="B462" t="n">
-        <v>0.018661</v>
+        <v>0.018744</v>
       </c>
       <c r="C462" t="n">
-        <v>0.78628</v>
+        <v>0.776596</v>
       </c>
     </row>
     <row r="463">
@@ -6433,10 +6433,10 @@
         </is>
       </c>
       <c r="B463" t="n">
-        <v>0.018819</v>
+        <v>0.018963</v>
       </c>
       <c r="C463" t="n">
-        <v>0.783641</v>
+        <v>0.773936</v>
       </c>
     </row>
     <row r="464">
@@ -6446,10 +6446,10 @@
         </is>
       </c>
       <c r="B464" t="n">
-        <v>0.019232</v>
+        <v>0.019795</v>
       </c>
       <c r="C464" t="n">
-        <v>0.781003</v>
+        <v>0.771277</v>
       </c>
     </row>
     <row r="465">
@@ -6459,10 +6459,10 @@
         </is>
       </c>
       <c r="B465" t="n">
-        <v>0.019269</v>
+        <v>0.020081</v>
       </c>
       <c r="C465" t="n">
-        <v>0.7783639999999999</v>
+        <v>0.768617</v>
       </c>
     </row>
     <row r="466">
@@ -6472,10 +6472,10 @@
         </is>
       </c>
       <c r="B466" t="n">
-        <v>0.01996</v>
+        <v>0.020394</v>
       </c>
       <c r="C466" t="n">
-        <v>0.775726</v>
+        <v>0.765957</v>
       </c>
     </row>
     <row r="467">
@@ -6485,10 +6485,10 @@
         </is>
       </c>
       <c r="B467" t="n">
-        <v>0.020233</v>
+        <v>0.021001</v>
       </c>
       <c r="C467" t="n">
-        <v>0.773087</v>
+        <v>0.763298</v>
       </c>
     </row>
     <row r="468">
@@ -6498,10 +6498,10 @@
         </is>
       </c>
       <c r="B468" t="n">
-        <v>0.020452</v>
+        <v>0.021092</v>
       </c>
       <c r="C468" t="n">
-        <v>0.7704490000000001</v>
+        <v>0.760638</v>
       </c>
     </row>
     <row r="469">
@@ -6511,10 +6511,10 @@
         </is>
       </c>
       <c r="B469" t="n">
-        <v>0.020567</v>
+        <v>0.021381</v>
       </c>
       <c r="C469" t="n">
-        <v>0.76781</v>
+        <v>0.757979</v>
       </c>
     </row>
     <row r="470">
@@ -6524,10 +6524,10 @@
         </is>
       </c>
       <c r="B470" t="n">
-        <v>0.021014</v>
+        <v>0.021441</v>
       </c>
       <c r="C470" t="n">
-        <v>0.765172</v>
+        <v>0.755319</v>
       </c>
     </row>
     <row r="471">
@@ -6537,10 +6537,10 @@
         </is>
       </c>
       <c r="B471" t="n">
-        <v>0.021171</v>
+        <v>0.02146</v>
       </c>
       <c r="C471" t="n">
-        <v>0.762533</v>
+        <v>0.75266</v>
       </c>
     </row>
     <row r="472">
@@ -6550,10 +6550,10 @@
         </is>
       </c>
       <c r="B472" t="n">
-        <v>0.021612</v>
+        <v>0.021512</v>
       </c>
       <c r="C472" t="n">
-        <v>0.759894</v>
+        <v>0.75</v>
       </c>
     </row>
     <row r="473">
@@ -6563,10 +6563,10 @@
         </is>
       </c>
       <c r="B473" t="n">
-        <v>0.022012</v>
+        <v>0.022551</v>
       </c>
       <c r="C473" t="n">
-        <v>0.757256</v>
+        <v>0.74734</v>
       </c>
     </row>
     <row r="474">
@@ -6576,10 +6576,10 @@
         </is>
       </c>
       <c r="B474" t="n">
-        <v>0.022137</v>
+        <v>0.022662</v>
       </c>
       <c r="C474" t="n">
-        <v>0.754617</v>
+        <v>0.744681</v>
       </c>
     </row>
     <row r="475">
@@ -6589,10 +6589,10 @@
         </is>
       </c>
       <c r="B475" t="n">
-        <v>0.0222</v>
+        <v>0.022744</v>
       </c>
       <c r="C475" t="n">
-        <v>0.751979</v>
+        <v>0.742021</v>
       </c>
     </row>
     <row r="476">
@@ -6602,10 +6602,10 @@
         </is>
       </c>
       <c r="B476" t="n">
-        <v>0.022517</v>
+        <v>0.023153</v>
       </c>
       <c r="C476" t="n">
-        <v>0.74934</v>
+        <v>0.739362</v>
       </c>
     </row>
     <row r="477">
@@ -6615,10 +6615,10 @@
         </is>
       </c>
       <c r="B477" t="n">
-        <v>0.023844</v>
+        <v>0.023212</v>
       </c>
       <c r="C477" t="n">
-        <v>0.746702</v>
+        <v>0.736702</v>
       </c>
     </row>
     <row r="478">
@@ -6628,10 +6628,10 @@
         </is>
       </c>
       <c r="B478" t="n">
-        <v>0.024006</v>
+        <v>0.023288</v>
       </c>
       <c r="C478" t="n">
-        <v>0.744063</v>
+        <v>0.734043</v>
       </c>
     </row>
     <row r="479">
@@ -6641,10 +6641,10 @@
         </is>
       </c>
       <c r="B479" t="n">
-        <v>0.02409</v>
+        <v>0.023356</v>
       </c>
       <c r="C479" t="n">
-        <v>0.741425</v>
+        <v>0.731383</v>
       </c>
     </row>
     <row r="480">
@@ -6654,10 +6654,10 @@
         </is>
       </c>
       <c r="B480" t="n">
-        <v>0.024093</v>
+        <v>0.023722</v>
       </c>
       <c r="C480" t="n">
-        <v>0.7387860000000001</v>
+        <v>0.728723</v>
       </c>
     </row>
     <row r="481">
@@ -6667,10 +6667,10 @@
         </is>
       </c>
       <c r="B481" t="n">
-        <v>0.02426</v>
+        <v>0.024008</v>
       </c>
       <c r="C481" t="n">
-        <v>0.736148</v>
+        <v>0.726064</v>
       </c>
     </row>
     <row r="482">
@@ -6680,10 +6680,10 @@
         </is>
       </c>
       <c r="B482" t="n">
-        <v>0.024327</v>
+        <v>0.024171</v>
       </c>
       <c r="C482" t="n">
-        <v>0.733509</v>
+        <v>0.723404</v>
       </c>
     </row>
     <row r="483">
@@ -6693,10 +6693,10 @@
         </is>
       </c>
       <c r="B483" t="n">
-        <v>0.024474</v>
+        <v>0.024785</v>
       </c>
       <c r="C483" t="n">
-        <v>0.730871</v>
+        <v>0.720745</v>
       </c>
     </row>
     <row r="484">
@@ -6706,10 +6706,10 @@
         </is>
       </c>
       <c r="B484" t="n">
-        <v>0.024858</v>
+        <v>0.024827</v>
       </c>
       <c r="C484" t="n">
-        <v>0.728232</v>
+        <v>0.718085</v>
       </c>
     </row>
     <row r="485">
@@ -6719,10 +6719,10 @@
         </is>
       </c>
       <c r="B485" t="n">
-        <v>0.024904</v>
+        <v>0.024936</v>
       </c>
       <c r="C485" t="n">
-        <v>0.725594</v>
+        <v>0.715426</v>
       </c>
     </row>
     <row r="486">
@@ -6732,10 +6732,10 @@
         </is>
       </c>
       <c r="B486" t="n">
-        <v>0.025167</v>
+        <v>0.024967</v>
       </c>
       <c r="C486" t="n">
-        <v>0.722955</v>
+        <v>0.712766</v>
       </c>
     </row>
     <row r="487">
@@ -6745,10 +6745,10 @@
         </is>
       </c>
       <c r="B487" t="n">
-        <v>0.02527</v>
+        <v>0.025068</v>
       </c>
       <c r="C487" t="n">
-        <v>0.720317</v>
+        <v>0.710106</v>
       </c>
     </row>
     <row r="488">
@@ -6758,10 +6758,10 @@
         </is>
       </c>
       <c r="B488" t="n">
-        <v>0.02542</v>
+        <v>0.025482</v>
       </c>
       <c r="C488" t="n">
-        <v>0.717678</v>
+        <v>0.707447</v>
       </c>
     </row>
     <row r="489">
@@ -6771,10 +6771,10 @@
         </is>
       </c>
       <c r="B489" t="n">
-        <v>0.025651</v>
+        <v>0.025736</v>
       </c>
       <c r="C489" t="n">
-        <v>0.71504</v>
+        <v>0.7047870000000001</v>
       </c>
     </row>
     <row r="490">
@@ -6784,10 +6784,10 @@
         </is>
       </c>
       <c r="B490" t="n">
-        <v>0.025846</v>
+        <v>0.025958</v>
       </c>
       <c r="C490" t="n">
-        <v>0.712401</v>
+        <v>0.702128</v>
       </c>
     </row>
     <row r="491">
@@ -6797,10 +6797,10 @@
         </is>
       </c>
       <c r="B491" t="n">
-        <v>0.026201</v>
+        <v>0.026223</v>
       </c>
       <c r="C491" t="n">
-        <v>0.709763</v>
+        <v>0.699468</v>
       </c>
     </row>
     <row r="492">
@@ -6810,10 +6810,10 @@
         </is>
       </c>
       <c r="B492" t="n">
-        <v>0.026241</v>
+        <v>0.026672</v>
       </c>
       <c r="C492" t="n">
-        <v>0.707124</v>
+        <v>0.696809</v>
       </c>
     </row>
     <row r="493">
@@ -6823,10 +6823,10 @@
         </is>
       </c>
       <c r="B493" t="n">
-        <v>0.026521</v>
+        <v>0.026682</v>
       </c>
       <c r="C493" t="n">
-        <v>0.704485</v>
+        <v>0.694149</v>
       </c>
     </row>
     <row r="494">
@@ -6836,10 +6836,10 @@
         </is>
       </c>
       <c r="B494" t="n">
-        <v>0.026869</v>
+        <v>0.026685</v>
       </c>
       <c r="C494" t="n">
-        <v>0.701847</v>
+        <v>0.691489</v>
       </c>
     </row>
     <row r="495">
@@ -6849,10 +6849,10 @@
         </is>
       </c>
       <c r="B495" t="n">
-        <v>0.026981</v>
+        <v>0.026725</v>
       </c>
       <c r="C495" t="n">
-        <v>0.6992080000000001</v>
+        <v>0.6888300000000001</v>
       </c>
     </row>
     <row r="496">
@@ -6862,10 +6862,10 @@
         </is>
       </c>
       <c r="B496" t="n">
-        <v>0.027174</v>
+        <v>0.026811</v>
       </c>
       <c r="C496" t="n">
-        <v>0.69657</v>
+        <v>0.6861699999999999</v>
       </c>
     </row>
     <row r="497">
@@ -6875,10 +6875,10 @@
         </is>
       </c>
       <c r="B497" t="n">
-        <v>0.027193</v>
+        <v>0.027014</v>
       </c>
       <c r="C497" t="n">
-        <v>0.693931</v>
+        <v>0.683511</v>
       </c>
     </row>
     <row r="498">
@@ -6888,10 +6888,10 @@
         </is>
       </c>
       <c r="B498" t="n">
-        <v>0.027564</v>
+        <v>0.027315</v>
       </c>
       <c r="C498" t="n">
-        <v>0.691293</v>
+        <v>0.680851</v>
       </c>
     </row>
     <row r="499">
@@ -6901,10 +6901,10 @@
         </is>
       </c>
       <c r="B499" t="n">
-        <v>0.02784</v>
+        <v>0.027652</v>
       </c>
       <c r="C499" t="n">
-        <v>0.688654</v>
+        <v>0.678191</v>
       </c>
     </row>
     <row r="500">
@@ -6914,10 +6914,10 @@
         </is>
       </c>
       <c r="B500" t="n">
-        <v>0.028032</v>
+        <v>0.028331</v>
       </c>
       <c r="C500" t="n">
-        <v>0.686016</v>
+        <v>0.675532</v>
       </c>
     </row>
     <row r="501">
@@ -6927,10 +6927,10 @@
         </is>
       </c>
       <c r="B501" t="n">
-        <v>0.028097</v>
+        <v>0.028362</v>
       </c>
       <c r="C501" t="n">
-        <v>0.683377</v>
+        <v>0.672872</v>
       </c>
     </row>
     <row r="502">
@@ -6940,10 +6940,10 @@
         </is>
       </c>
       <c r="B502" t="n">
-        <v>0.028448</v>
+        <v>0.028919</v>
       </c>
       <c r="C502" t="n">
-        <v>0.680739</v>
+        <v>0.6702129999999999</v>
       </c>
     </row>
     <row r="503">
@@ -6953,10 +6953,10 @@
         </is>
       </c>
       <c r="B503" t="n">
-        <v>0.028601</v>
+        <v>0.029011</v>
       </c>
       <c r="C503" t="n">
-        <v>0.6781</v>
+        <v>0.667553</v>
       </c>
     </row>
     <row r="504">
@@ -6966,10 +6966,10 @@
         </is>
       </c>
       <c r="B504" t="n">
-        <v>0.028767</v>
+        <v>0.029333</v>
       </c>
       <c r="C504" t="n">
-        <v>0.675462</v>
+        <v>0.664894</v>
       </c>
     </row>
     <row r="505">
@@ -6979,10 +6979,10 @@
         </is>
       </c>
       <c r="B505" t="n">
-        <v>0.029003</v>
+        <v>0.029651</v>
       </c>
       <c r="C505" t="n">
-        <v>0.6728229999999999</v>
+        <v>0.662234</v>
       </c>
     </row>
     <row r="506">
@@ -6992,10 +6992,10 @@
         </is>
       </c>
       <c r="B506" t="n">
-        <v>0.02936</v>
+        <v>0.030432</v>
       </c>
       <c r="C506" t="n">
-        <v>0.670185</v>
+        <v>0.659574</v>
       </c>
     </row>
     <row r="507">
@@ -7005,10 +7005,10 @@
         </is>
       </c>
       <c r="B507" t="n">
-        <v>0.030183</v>
+        <v>0.030582</v>
       </c>
       <c r="C507" t="n">
-        <v>0.667546</v>
+        <v>0.656915</v>
       </c>
     </row>
     <row r="508">
@@ -7018,10 +7018,10 @@
         </is>
       </c>
       <c r="B508" t="n">
-        <v>0.030682</v>
+        <v>0.03084</v>
       </c>
       <c r="C508" t="n">
-        <v>0.6649080000000001</v>
+        <v>0.654255</v>
       </c>
     </row>
     <row r="509">
@@ -7031,10 +7031,10 @@
         </is>
       </c>
       <c r="B509" t="n">
-        <v>0.030825</v>
+        <v>0.03103</v>
       </c>
       <c r="C509" t="n">
-        <v>0.662269</v>
+        <v>0.651596</v>
       </c>
     </row>
     <row r="510">
@@ -7044,10 +7044,10 @@
         </is>
       </c>
       <c r="B510" t="n">
-        <v>0.03131</v>
+        <v>0.031347</v>
       </c>
       <c r="C510" t="n">
-        <v>0.659631</v>
+        <v>0.648936</v>
       </c>
     </row>
     <row r="511">
@@ -7057,10 +7057,10 @@
         </is>
       </c>
       <c r="B511" t="n">
-        <v>0.031497</v>
+        <v>0.031635</v>
       </c>
       <c r="C511" t="n">
-        <v>0.656992</v>
+        <v>0.646277</v>
       </c>
     </row>
     <row r="512">
@@ -7070,10 +7070,10 @@
         </is>
       </c>
       <c r="B512" t="n">
-        <v>0.03168</v>
+        <v>0.032457</v>
       </c>
       <c r="C512" t="n">
-        <v>0.654354</v>
+        <v>0.643617</v>
       </c>
     </row>
     <row r="513">
@@ -7083,10 +7083,10 @@
         </is>
       </c>
       <c r="B513" t="n">
-        <v>0.032162</v>
+        <v>0.03256</v>
       </c>
       <c r="C513" t="n">
-        <v>0.651715</v>
+        <v>0.640957</v>
       </c>
     </row>
     <row r="514">
@@ -7096,10 +7096,10 @@
         </is>
       </c>
       <c r="B514" t="n">
-        <v>0.03241</v>
+        <v>0.032611</v>
       </c>
       <c r="C514" t="n">
-        <v>0.649077</v>
+        <v>0.638298</v>
       </c>
     </row>
     <row r="515">
@@ -7109,10 +7109,10 @@
         </is>
       </c>
       <c r="B515" t="n">
-        <v>0.032441</v>
+        <v>0.032657</v>
       </c>
       <c r="C515" t="n">
-        <v>0.646438</v>
+        <v>0.635638</v>
       </c>
     </row>
     <row r="516">
@@ -7122,10 +7122,10 @@
         </is>
       </c>
       <c r="B516" t="n">
-        <v>0.032711</v>
+        <v>0.032713</v>
       </c>
       <c r="C516" t="n">
-        <v>0.643799</v>
+        <v>0.632979</v>
       </c>
     </row>
     <row r="517">
@@ -7135,10 +7135,10 @@
         </is>
       </c>
       <c r="B517" t="n">
-        <v>0.032953</v>
+        <v>0.03296</v>
       </c>
       <c r="C517" t="n">
-        <v>0.641161</v>
+        <v>0.630319</v>
       </c>
     </row>
     <row r="518">
@@ -7148,10 +7148,10 @@
         </is>
       </c>
       <c r="B518" t="n">
-        <v>0.033124</v>
+        <v>0.033098</v>
       </c>
       <c r="C518" t="n">
-        <v>0.638522</v>
+        <v>0.62766</v>
       </c>
     </row>
     <row r="519">
@@ -7161,10 +7161,10 @@
         </is>
       </c>
       <c r="B519" t="n">
-        <v>0.033147</v>
+        <v>0.033505</v>
       </c>
       <c r="C519" t="n">
-        <v>0.635884</v>
+        <v>0.625</v>
       </c>
     </row>
     <row r="520">
@@ -7174,10 +7174,10 @@
         </is>
       </c>
       <c r="B520" t="n">
-        <v>0.033362</v>
+        <v>0.033512</v>
       </c>
       <c r="C520" t="n">
-        <v>0.6332449999999999</v>
+        <v>0.62234</v>
       </c>
     </row>
     <row r="521">
@@ -7187,10 +7187,10 @@
         </is>
       </c>
       <c r="B521" t="n">
-        <v>0.033735</v>
+        <v>0.033831</v>
       </c>
       <c r="C521" t="n">
-        <v>0.630607</v>
+        <v>0.619681</v>
       </c>
     </row>
     <row r="522">
@@ -7200,10 +7200,10 @@
         </is>
       </c>
       <c r="B522" t="n">
-        <v>0.033893</v>
+        <v>0.033849</v>
       </c>
       <c r="C522" t="n">
-        <v>0.627968</v>
+        <v>0.617021</v>
       </c>
     </row>
     <row r="523">
@@ -7213,10 +7213,10 @@
         </is>
       </c>
       <c r="B523" t="n">
-        <v>0.034046</v>
+        <v>0.03407</v>
       </c>
       <c r="C523" t="n">
-        <v>0.6253300000000001</v>
+        <v>0.614362</v>
       </c>
     </row>
     <row r="524">
@@ -7226,10 +7226,10 @@
         </is>
       </c>
       <c r="B524" t="n">
-        <v>0.034233</v>
+        <v>0.034308</v>
       </c>
       <c r="C524" t="n">
-        <v>0.622691</v>
+        <v>0.611702</v>
       </c>
     </row>
     <row r="525">
@@ -7239,10 +7239,10 @@
         </is>
       </c>
       <c r="B525" t="n">
-        <v>0.034405</v>
+        <v>0.034363</v>
       </c>
       <c r="C525" t="n">
-        <v>0.620053</v>
+        <v>0.609043</v>
       </c>
     </row>
     <row r="526">
@@ -7252,10 +7252,10 @@
         </is>
       </c>
       <c r="B526" t="n">
-        <v>0.034556</v>
+        <v>0.034589</v>
       </c>
       <c r="C526" t="n">
-        <v>0.617414</v>
+        <v>0.606383</v>
       </c>
     </row>
     <row r="527">
@@ -7265,10 +7265,10 @@
         </is>
       </c>
       <c r="B527" t="n">
-        <v>0.034569</v>
+        <v>0.034846</v>
       </c>
       <c r="C527" t="n">
-        <v>0.614776</v>
+        <v>0.603723</v>
       </c>
     </row>
     <row r="528">
@@ -7278,10 +7278,10 @@
         </is>
       </c>
       <c r="B528" t="n">
-        <v>0.035056</v>
+        <v>0.035044</v>
       </c>
       <c r="C528" t="n">
-        <v>0.612137</v>
+        <v>0.601064</v>
       </c>
     </row>
     <row r="529">
@@ -7291,10 +7291,10 @@
         </is>
       </c>
       <c r="B529" t="n">
-        <v>0.035138</v>
+        <v>0.035505</v>
       </c>
       <c r="C529" t="n">
-        <v>0.609499</v>
+        <v>0.598404</v>
       </c>
     </row>
     <row r="530">
@@ -7304,10 +7304,10 @@
         </is>
       </c>
       <c r="B530" t="n">
-        <v>0.035966</v>
+        <v>0.035755</v>
       </c>
       <c r="C530" t="n">
-        <v>0.60686</v>
+        <v>0.595745</v>
       </c>
     </row>
     <row r="531">
@@ -7317,10 +7317,10 @@
         </is>
       </c>
       <c r="B531" t="n">
-        <v>0.036415</v>
+        <v>0.036053</v>
       </c>
       <c r="C531" t="n">
-        <v>0.604222</v>
+        <v>0.593085</v>
       </c>
     </row>
     <row r="532">
@@ -7330,10 +7330,10 @@
         </is>
       </c>
       <c r="B532" t="n">
-        <v>0.03646</v>
+        <v>0.036614</v>
       </c>
       <c r="C532" t="n">
-        <v>0.601583</v>
+        <v>0.590426</v>
       </c>
     </row>
     <row r="533">
@@ -7343,10 +7343,10 @@
         </is>
       </c>
       <c r="B533" t="n">
-        <v>0.037085</v>
+        <v>0.036735</v>
       </c>
       <c r="C533" t="n">
-        <v>0.5989449999999999</v>
+        <v>0.587766</v>
       </c>
     </row>
     <row r="534">
@@ -7356,10 +7356,10 @@
         </is>
       </c>
       <c r="B534" t="n">
-        <v>0.037103</v>
+        <v>0.03694</v>
       </c>
       <c r="C534" t="n">
-        <v>0.596306</v>
+        <v>0.585106</v>
       </c>
     </row>
     <row r="535">
@@ -7369,10 +7369,10 @@
         </is>
       </c>
       <c r="B535" t="n">
-        <v>0.037392</v>
+        <v>0.03736</v>
       </c>
       <c r="C535" t="n">
-        <v>0.593668</v>
+        <v>0.582447</v>
       </c>
     </row>
     <row r="536">
@@ -7382,10 +7382,10 @@
         </is>
       </c>
       <c r="B536" t="n">
-        <v>0.037531</v>
+        <v>0.037384</v>
       </c>
       <c r="C536" t="n">
-        <v>0.591029</v>
+        <v>0.5797870000000001</v>
       </c>
     </row>
     <row r="537">
@@ -7395,10 +7395,10 @@
         </is>
       </c>
       <c r="B537" t="n">
-        <v>0.037797</v>
+        <v>0.037424</v>
       </c>
       <c r="C537" t="n">
-        <v>0.588391</v>
+        <v>0.577128</v>
       </c>
     </row>
     <row r="538">
@@ -7408,10 +7408,10 @@
         </is>
       </c>
       <c r="B538" t="n">
-        <v>0.03782</v>
+        <v>0.037477</v>
       </c>
       <c r="C538" t="n">
-        <v>0.5857520000000001</v>
+        <v>0.574468</v>
       </c>
     </row>
     <row r="539">
@@ -7421,10 +7421,10 @@
         </is>
       </c>
       <c r="B539" t="n">
-        <v>0.038134</v>
+        <v>0.037512</v>
       </c>
       <c r="C539" t="n">
-        <v>0.583113</v>
+        <v>0.571809</v>
       </c>
     </row>
     <row r="540">
@@ -7434,10 +7434,10 @@
         </is>
       </c>
       <c r="B540" t="n">
-        <v>0.038674</v>
+        <v>0.037789</v>
       </c>
       <c r="C540" t="n">
-        <v>0.580475</v>
+        <v>0.569149</v>
       </c>
     </row>
     <row r="541">
@@ -7447,10 +7447,10 @@
         </is>
       </c>
       <c r="B541" t="n">
-        <v>0.038772</v>
+        <v>0.037817</v>
       </c>
       <c r="C541" t="n">
-        <v>0.577836</v>
+        <v>0.566489</v>
       </c>
     </row>
     <row r="542">
@@ -7460,10 +7460,10 @@
         </is>
       </c>
       <c r="B542" t="n">
-        <v>0.038909</v>
+        <v>0.037854</v>
       </c>
       <c r="C542" t="n">
-        <v>0.575198</v>
+        <v>0.5638300000000001</v>
       </c>
     </row>
     <row r="543">
@@ -7473,10 +7473,10 @@
         </is>
       </c>
       <c r="B543" t="n">
-        <v>0.038915</v>
+        <v>0.038305</v>
       </c>
       <c r="C543" t="n">
-        <v>0.572559</v>
+        <v>0.5611699999999999</v>
       </c>
     </row>
     <row r="544">
@@ -7486,10 +7486,10 @@
         </is>
       </c>
       <c r="B544" t="n">
-        <v>0.039123</v>
+        <v>0.038561</v>
       </c>
       <c r="C544" t="n">
-        <v>0.569921</v>
+        <v>0.558511</v>
       </c>
     </row>
     <row r="545">
@@ -7499,10 +7499,10 @@
         </is>
       </c>
       <c r="B545" t="n">
-        <v>0.039153</v>
+        <v>0.038598</v>
       </c>
       <c r="C545" t="n">
-        <v>0.567282</v>
+        <v>0.555851</v>
       </c>
     </row>
     <row r="546">
@@ -7512,10 +7512,10 @@
         </is>
       </c>
       <c r="B546" t="n">
-        <v>0.039155</v>
+        <v>0.038709</v>
       </c>
       <c r="C546" t="n">
-        <v>0.564644</v>
+        <v>0.553191</v>
       </c>
     </row>
     <row r="547">
@@ -7525,10 +7525,10 @@
         </is>
       </c>
       <c r="B547" t="n">
-        <v>0.039488</v>
+        <v>0.038758</v>
       </c>
       <c r="C547" t="n">
-        <v>0.562005</v>
+        <v>0.550532</v>
       </c>
     </row>
     <row r="548">
@@ -7538,10 +7538,10 @@
         </is>
       </c>
       <c r="B548" t="n">
-        <v>0.039677</v>
+        <v>0.038812</v>
       </c>
       <c r="C548" t="n">
-        <v>0.5593669999999999</v>
+        <v>0.547872</v>
       </c>
     </row>
     <row r="549">
@@ -7551,10 +7551,10 @@
         </is>
       </c>
       <c r="B549" t="n">
-        <v>0.039729</v>
+        <v>0.039104</v>
       </c>
       <c r="C549" t="n">
-        <v>0.556728</v>
+        <v>0.5452129999999999</v>
       </c>
     </row>
     <row r="550">
@@ -7564,10 +7564,10 @@
         </is>
       </c>
       <c r="B550" t="n">
-        <v>0.039946</v>
+        <v>0.039326</v>
       </c>
       <c r="C550" t="n">
-        <v>0.55409</v>
+        <v>0.542553</v>
       </c>
     </row>
     <row r="551">
@@ -7577,10 +7577,10 @@
         </is>
       </c>
       <c r="B551" t="n">
-        <v>0.039995</v>
+        <v>0.039507</v>
       </c>
       <c r="C551" t="n">
-        <v>0.551451</v>
+        <v>0.539894</v>
       </c>
     </row>
     <row r="552">
@@ -7590,10 +7590,10 @@
         </is>
       </c>
       <c r="B552" t="n">
-        <v>0.040011</v>
+        <v>0.04032</v>
       </c>
       <c r="C552" t="n">
-        <v>0.548813</v>
+        <v>0.537234</v>
       </c>
     </row>
     <row r="553">
@@ -7603,10 +7603,10 @@
         </is>
       </c>
       <c r="B553" t="n">
-        <v>0.040471</v>
+        <v>0.041106</v>
       </c>
       <c r="C553" t="n">
-        <v>0.546174</v>
+        <v>0.534574</v>
       </c>
     </row>
     <row r="554">
@@ -7616,10 +7616,10 @@
         </is>
       </c>
       <c r="B554" t="n">
-        <v>0.040576</v>
+        <v>0.041151</v>
       </c>
       <c r="C554" t="n">
-        <v>0.543536</v>
+        <v>0.531915</v>
       </c>
     </row>
     <row r="555">
@@ -7629,10 +7629,10 @@
         </is>
       </c>
       <c r="B555" t="n">
-        <v>0.040639</v>
+        <v>0.041223</v>
       </c>
       <c r="C555" t="n">
-        <v>0.540897</v>
+        <v>0.529255</v>
       </c>
     </row>
     <row r="556">
@@ -7642,10 +7642,10 @@
         </is>
       </c>
       <c r="B556" t="n">
-        <v>0.040924</v>
+        <v>0.041289</v>
       </c>
       <c r="C556" t="n">
-        <v>0.538259</v>
+        <v>0.526596</v>
       </c>
     </row>
     <row r="557">
@@ -7655,10 +7655,10 @@
         </is>
       </c>
       <c r="B557" t="n">
-        <v>0.041079</v>
+        <v>0.041439</v>
       </c>
       <c r="C557" t="n">
-        <v>0.53562</v>
+        <v>0.523936</v>
       </c>
     </row>
     <row r="558">
@@ -7668,10 +7668,10 @@
         </is>
       </c>
       <c r="B558" t="n">
-        <v>0.041379</v>
+        <v>0.041725</v>
       </c>
       <c r="C558" t="n">
-        <v>0.532982</v>
+        <v>0.521277</v>
       </c>
     </row>
     <row r="559">
@@ -7681,10 +7681,10 @@
         </is>
       </c>
       <c r="B559" t="n">
-        <v>0.04219</v>
+        <v>0.041859</v>
       </c>
       <c r="C559" t="n">
-        <v>0.530343</v>
+        <v>0.518617</v>
       </c>
     </row>
     <row r="560">
@@ -7694,10 +7694,10 @@
         </is>
       </c>
       <c r="B560" t="n">
-        <v>0.042716</v>
+        <v>0.04222</v>
       </c>
       <c r="C560" t="n">
-        <v>0.527704</v>
+        <v>0.515957</v>
       </c>
     </row>
     <row r="561">
@@ -7707,10 +7707,10 @@
         </is>
       </c>
       <c r="B561" t="n">
-        <v>0.042834</v>
+        <v>0.042501</v>
       </c>
       <c r="C561" t="n">
-        <v>0.525066</v>
+        <v>0.513298</v>
       </c>
     </row>
     <row r="562">
@@ -7720,10 +7720,10 @@
         </is>
       </c>
       <c r="B562" t="n">
-        <v>0.042876</v>
+        <v>0.042556</v>
       </c>
       <c r="C562" t="n">
-        <v>0.522427</v>
+        <v>0.510638</v>
       </c>
     </row>
     <row r="563">
@@ -7733,10 +7733,10 @@
         </is>
       </c>
       <c r="B563" t="n">
-        <v>0.04324</v>
+        <v>0.042656</v>
       </c>
       <c r="C563" t="n">
-        <v>0.5197889999999999</v>
+        <v>0.507979</v>
       </c>
     </row>
     <row r="564">
@@ -7746,10 +7746,10 @@
         </is>
       </c>
       <c r="B564" t="n">
-        <v>0.043751</v>
+        <v>0.043746</v>
       </c>
       <c r="C564" t="n">
-        <v>0.51715</v>
+        <v>0.505319</v>
       </c>
     </row>
     <row r="565">
@@ -7759,10 +7759,10 @@
         </is>
       </c>
       <c r="B565" t="n">
-        <v>0.044248</v>
+        <v>0.044096</v>
       </c>
       <c r="C565" t="n">
-        <v>0.514512</v>
+        <v>0.50266</v>
       </c>
     </row>
     <row r="566">
@@ -7772,10 +7772,10 @@
         </is>
       </c>
       <c r="B566" t="n">
-        <v>0.044292</v>
+        <v>0.04418</v>
       </c>
       <c r="C566" t="n">
-        <v>0.511873</v>
+        <v>0.5</v>
       </c>
     </row>
     <row r="567">
@@ -7785,10 +7785,10 @@
         </is>
       </c>
       <c r="B567" t="n">
-        <v>0.044573</v>
+        <v>0.044394</v>
       </c>
       <c r="C567" t="n">
-        <v>0.509235</v>
+        <v>0.49734</v>
       </c>
     </row>
     <row r="568">
@@ -7798,10 +7798,10 @@
         </is>
       </c>
       <c r="B568" t="n">
-        <v>0.044953</v>
+        <v>0.044743</v>
       </c>
       <c r="C568" t="n">
-        <v>0.506596</v>
+        <v>0.494681</v>
       </c>
     </row>
     <row r="569">
@@ -7811,10 +7811,10 @@
         </is>
       </c>
       <c r="B569" t="n">
-        <v>0.045333</v>
+        <v>0.046063</v>
       </c>
       <c r="C569" t="n">
-        <v>0.503958</v>
+        <v>0.492021</v>
       </c>
     </row>
     <row r="570">
@@ -7824,10 +7824,10 @@
         </is>
       </c>
       <c r="B570" t="n">
-        <v>0.045758</v>
+        <v>0.046069</v>
       </c>
       <c r="C570" t="n">
-        <v>0.501319</v>
+        <v>0.489362</v>
       </c>
     </row>
     <row r="571">
@@ -7837,10 +7837,10 @@
         </is>
       </c>
       <c r="B571" t="n">
-        <v>0.0458</v>
+        <v>0.046333</v>
       </c>
       <c r="C571" t="n">
-        <v>0.498681</v>
+        <v>0.486702</v>
       </c>
     </row>
     <row r="572">
@@ -7850,10 +7850,10 @@
         </is>
       </c>
       <c r="B572" t="n">
-        <v>0.045899</v>
+        <v>0.046381</v>
       </c>
       <c r="C572" t="n">
-        <v>0.496042</v>
+        <v>0.484043</v>
       </c>
     </row>
     <row r="573">
@@ -7863,10 +7863,10 @@
         </is>
       </c>
       <c r="B573" t="n">
-        <v>0.046171</v>
+        <v>0.046489</v>
       </c>
       <c r="C573" t="n">
-        <v>0.493404</v>
+        <v>0.481383</v>
       </c>
     </row>
     <row r="574">
@@ -7876,10 +7876,10 @@
         </is>
       </c>
       <c r="B574" t="n">
-        <v>0.046645</v>
+        <v>0.047133</v>
       </c>
       <c r="C574" t="n">
-        <v>0.490765</v>
+        <v>0.478723</v>
       </c>
     </row>
     <row r="575">
@@ -7889,10 +7889,10 @@
         </is>
       </c>
       <c r="B575" t="n">
-        <v>0.047597</v>
+        <v>0.047557</v>
       </c>
       <c r="C575" t="n">
-        <v>0.488127</v>
+        <v>0.476064</v>
       </c>
     </row>
     <row r="576">
@@ -7902,10 +7902,10 @@
         </is>
       </c>
       <c r="B576" t="n">
-        <v>0.047631</v>
+        <v>0.047665</v>
       </c>
       <c r="C576" t="n">
-        <v>0.485488</v>
+        <v>0.473404</v>
       </c>
     </row>
     <row r="577">
@@ -7915,10 +7915,10 @@
         </is>
       </c>
       <c r="B577" t="n">
-        <v>0.048018</v>
+        <v>0.047694</v>
       </c>
       <c r="C577" t="n">
-        <v>0.48285</v>
+        <v>0.470745</v>
       </c>
     </row>
     <row r="578">
@@ -7928,10 +7928,10 @@
         </is>
       </c>
       <c r="B578" t="n">
-        <v>0.048495</v>
+        <v>0.048177</v>
       </c>
       <c r="C578" t="n">
-        <v>0.480211</v>
+        <v>0.468085</v>
       </c>
     </row>
     <row r="579">
@@ -7941,10 +7941,10 @@
         </is>
       </c>
       <c r="B579" t="n">
-        <v>0.048806</v>
+        <v>0.048363</v>
       </c>
       <c r="C579" t="n">
-        <v>0.477573</v>
+        <v>0.465426</v>
       </c>
     </row>
     <row r="580">
@@ -7954,10 +7954,10 @@
         </is>
       </c>
       <c r="B580" t="n">
-        <v>0.049017</v>
+        <v>0.04874</v>
       </c>
       <c r="C580" t="n">
-        <v>0.474934</v>
+        <v>0.462766</v>
       </c>
     </row>
     <row r="581">
@@ -7967,10 +7967,10 @@
         </is>
       </c>
       <c r="B581" t="n">
-        <v>0.049824</v>
+        <v>0.049562</v>
       </c>
       <c r="C581" t="n">
-        <v>0.472296</v>
+        <v>0.460106</v>
       </c>
     </row>
     <row r="582">
@@ -7980,10 +7980,10 @@
         </is>
       </c>
       <c r="B582" t="n">
-        <v>0.050619</v>
+        <v>0.04982</v>
       </c>
       <c r="C582" t="n">
-        <v>0.469657</v>
+        <v>0.457447</v>
       </c>
     </row>
     <row r="583">
@@ -7993,10 +7993,10 @@
         </is>
       </c>
       <c r="B583" t="n">
-        <v>0.050743</v>
+        <v>0.050252</v>
       </c>
       <c r="C583" t="n">
-        <v>0.467018</v>
+        <v>0.454787</v>
       </c>
     </row>
     <row r="584">
@@ -8006,10 +8006,10 @@
         </is>
       </c>
       <c r="B584" t="n">
-        <v>0.050915</v>
+        <v>0.050856</v>
       </c>
       <c r="C584" t="n">
-        <v>0.46438</v>
+        <v>0.452128</v>
       </c>
     </row>
     <row r="585">
@@ -8019,10 +8019,10 @@
         </is>
       </c>
       <c r="B585" t="n">
-        <v>0.051171</v>
+        <v>0.050865</v>
       </c>
       <c r="C585" t="n">
-        <v>0.461741</v>
+        <v>0.449468</v>
       </c>
     </row>
     <row r="586">
@@ -8032,10 +8032,10 @@
         </is>
       </c>
       <c r="B586" t="n">
-        <v>0.051247</v>
+        <v>0.051296</v>
       </c>
       <c r="C586" t="n">
-        <v>0.459103</v>
+        <v>0.446809</v>
       </c>
     </row>
     <row r="587">
@@ -8045,10 +8045,10 @@
         </is>
       </c>
       <c r="B587" t="n">
-        <v>0.051692</v>
+        <v>0.051428</v>
       </c>
       <c r="C587" t="n">
-        <v>0.456464</v>
+        <v>0.444149</v>
       </c>
     </row>
     <row r="588">
@@ -8058,10 +8058,10 @@
         </is>
       </c>
       <c r="B588" t="n">
-        <v>0.051756</v>
+        <v>0.051806</v>
       </c>
       <c r="C588" t="n">
-        <v>0.453826</v>
+        <v>0.441489</v>
       </c>
     </row>
     <row r="589">
@@ -8071,10 +8071,10 @@
         </is>
       </c>
       <c r="B589" t="n">
-        <v>0.052558</v>
+        <v>0.051997</v>
       </c>
       <c r="C589" t="n">
-        <v>0.451187</v>
+        <v>0.43883</v>
       </c>
     </row>
     <row r="590">
@@ -8084,10 +8084,10 @@
         </is>
       </c>
       <c r="B590" t="n">
-        <v>0.052806</v>
+        <v>0.052056</v>
       </c>
       <c r="C590" t="n">
-        <v>0.448549</v>
+        <v>0.43617</v>
       </c>
     </row>
     <row r="591">
@@ -8097,10 +8097,10 @@
         </is>
       </c>
       <c r="B591" t="n">
-        <v>0.052851</v>
+        <v>0.052131</v>
       </c>
       <c r="C591" t="n">
-        <v>0.44591</v>
+        <v>0.433511</v>
       </c>
     </row>
     <row r="592">
@@ -8110,10 +8110,10 @@
         </is>
       </c>
       <c r="B592" t="n">
-        <v>0.052953</v>
+        <v>0.052233</v>
       </c>
       <c r="C592" t="n">
-        <v>0.443272</v>
+        <v>0.430851</v>
       </c>
     </row>
     <row r="593">
@@ -8123,10 +8123,10 @@
         </is>
       </c>
       <c r="B593" t="n">
-        <v>0.052966</v>
+        <v>0.053396</v>
       </c>
       <c r="C593" t="n">
-        <v>0.440633</v>
+        <v>0.428191</v>
       </c>
     </row>
     <row r="594">
@@ -8136,10 +8136,10 @@
         </is>
       </c>
       <c r="B594" t="n">
-        <v>0.053108</v>
+        <v>0.053713</v>
       </c>
       <c r="C594" t="n">
-        <v>0.437995</v>
+        <v>0.425532</v>
       </c>
     </row>
     <row r="595">
@@ -8149,10 +8149,10 @@
         </is>
       </c>
       <c r="B595" t="n">
-        <v>0.053347</v>
+        <v>0.054187</v>
       </c>
       <c r="C595" t="n">
-        <v>0.435356</v>
+        <v>0.422872</v>
       </c>
     </row>
     <row r="596">
@@ -8162,10 +8162,10 @@
         </is>
       </c>
       <c r="B596" t="n">
-        <v>0.053637</v>
+        <v>0.054452</v>
       </c>
       <c r="C596" t="n">
-        <v>0.432718</v>
+        <v>0.420213</v>
       </c>
     </row>
     <row r="597">
@@ -8175,10 +8175,10 @@
         </is>
       </c>
       <c r="B597" t="n">
-        <v>0.05395</v>
+        <v>0.054472</v>
       </c>
       <c r="C597" t="n">
-        <v>0.430079</v>
+        <v>0.417553</v>
       </c>
     </row>
     <row r="598">
@@ -8188,10 +8188,10 @@
         </is>
       </c>
       <c r="B598" t="n">
-        <v>0.054049</v>
+        <v>0.056192</v>
       </c>
       <c r="C598" t="n">
-        <v>0.427441</v>
+        <v>0.414894</v>
       </c>
     </row>
     <row r="599">
@@ -8201,10 +8201,10 @@
         </is>
       </c>
       <c r="B599" t="n">
-        <v>0.055818</v>
+        <v>0.056663</v>
       </c>
       <c r="C599" t="n">
-        <v>0.424802</v>
+        <v>0.412234</v>
       </c>
     </row>
     <row r="600">
@@ -8214,10 +8214,10 @@
         </is>
       </c>
       <c r="B600" t="n">
-        <v>0.056125</v>
+        <v>0.056973</v>
       </c>
       <c r="C600" t="n">
-        <v>0.422164</v>
+        <v>0.409574</v>
       </c>
     </row>
     <row r="601">
@@ -8227,10 +8227,10 @@
         </is>
       </c>
       <c r="B601" t="n">
-        <v>0.056418</v>
+        <v>0.058612</v>
       </c>
       <c r="C601" t="n">
-        <v>0.419525</v>
+        <v>0.406915</v>
       </c>
     </row>
     <row r="602">
@@ -8240,10 +8240,10 @@
         </is>
       </c>
       <c r="B602" t="n">
-        <v>0.057111</v>
+        <v>0.058652</v>
       </c>
       <c r="C602" t="n">
-        <v>0.416887</v>
+        <v>0.404255</v>
       </c>
     </row>
     <row r="603">
@@ -8253,10 +8253,10 @@
         </is>
       </c>
       <c r="B603" t="n">
-        <v>0.057387</v>
+        <v>0.059429</v>
       </c>
       <c r="C603" t="n">
-        <v>0.414248</v>
+        <v>0.401596</v>
       </c>
     </row>
     <row r="604">
@@ -8266,10 +8266,10 @@
         </is>
       </c>
       <c r="B604" t="n">
-        <v>0.057824</v>
+        <v>0.059609</v>
       </c>
       <c r="C604" t="n">
-        <v>0.411609</v>
+        <v>0.398936</v>
       </c>
     </row>
     <row r="605">
@@ -8279,10 +8279,10 @@
         </is>
       </c>
       <c r="B605" t="n">
-        <v>0.058699</v>
+        <v>0.060035</v>
       </c>
       <c r="C605" t="n">
-        <v>0.408971</v>
+        <v>0.396277</v>
       </c>
     </row>
     <row r="606">
@@ -8292,10 +8292,10 @@
         </is>
       </c>
       <c r="B606" t="n">
-        <v>0.060458</v>
+        <v>0.060241</v>
       </c>
       <c r="C606" t="n">
-        <v>0.406332</v>
+        <v>0.393617</v>
       </c>
     </row>
     <row r="607">
@@ -8305,10 +8305,10 @@
         </is>
       </c>
       <c r="B607" t="n">
-        <v>0.060801</v>
+        <v>0.060491</v>
       </c>
       <c r="C607" t="n">
-        <v>0.403694</v>
+        <v>0.390957</v>
       </c>
     </row>
     <row r="608">
@@ -8318,10 +8318,10 @@
         </is>
       </c>
       <c r="B608" t="n">
-        <v>0.060996</v>
+        <v>0.061036</v>
       </c>
       <c r="C608" t="n">
-        <v>0.401055</v>
+        <v>0.388298</v>
       </c>
     </row>
     <row r="609">
@@ -8331,10 +8331,10 @@
         </is>
       </c>
       <c r="B609" t="n">
-        <v>0.062293</v>
+        <v>0.061192</v>
       </c>
       <c r="C609" t="n">
-        <v>0.398417</v>
+        <v>0.385638</v>
       </c>
     </row>
     <row r="610">
@@ -8344,10 +8344,10 @@
         </is>
       </c>
       <c r="B610" t="n">
-        <v>0.062308</v>
+        <v>0.061397</v>
       </c>
       <c r="C610" t="n">
-        <v>0.395778</v>
+        <v>0.382979</v>
       </c>
     </row>
     <row r="611">
@@ -8357,10 +8357,10 @@
         </is>
       </c>
       <c r="B611" t="n">
-        <v>0.06250600000000001</v>
+        <v>0.061607</v>
       </c>
       <c r="C611" t="n">
-        <v>0.39314</v>
+        <v>0.380319</v>
       </c>
     </row>
     <row r="612">
@@ -8370,10 +8370,10 @@
         </is>
       </c>
       <c r="B612" t="n">
-        <v>0.06268799999999999</v>
+        <v>0.061785</v>
       </c>
       <c r="C612" t="n">
-        <v>0.390501</v>
+        <v>0.37766</v>
       </c>
     </row>
     <row r="613">
@@ -8383,10 +8383,10 @@
         </is>
       </c>
       <c r="B613" t="n">
-        <v>0.06293700000000001</v>
+        <v>0.061976</v>
       </c>
       <c r="C613" t="n">
-        <v>0.387863</v>
+        <v>0.375</v>
       </c>
     </row>
     <row r="614">
@@ -8396,10 +8396,10 @@
         </is>
       </c>
       <c r="B614" t="n">
-        <v>0.063111</v>
+        <v>0.062158</v>
       </c>
       <c r="C614" t="n">
-        <v>0.385224</v>
+        <v>0.37234</v>
       </c>
     </row>
     <row r="615">
@@ -8409,10 +8409,10 @@
         </is>
       </c>
       <c r="B615" t="n">
-        <v>0.06339400000000001</v>
+        <v>0.062285</v>
       </c>
       <c r="C615" t="n">
-        <v>0.382586</v>
+        <v>0.369681</v>
       </c>
     </row>
     <row r="616">
@@ -8422,10 +8422,10 @@
         </is>
       </c>
       <c r="B616" t="n">
-        <v>0.063467</v>
+        <v>0.06265900000000001</v>
       </c>
       <c r="C616" t="n">
-        <v>0.379947</v>
+        <v>0.367021</v>
       </c>
     </row>
     <row r="617">
@@ -8435,10 +8435,10 @@
         </is>
       </c>
       <c r="B617" t="n">
-        <v>0.06383800000000001</v>
+        <v>0.062987</v>
       </c>
       <c r="C617" t="n">
-        <v>0.377309</v>
+        <v>0.364362</v>
       </c>
     </row>
     <row r="618">
@@ -8448,10 +8448,10 @@
         </is>
       </c>
       <c r="B618" t="n">
-        <v>0.06404600000000001</v>
+        <v>0.06304899999999999</v>
       </c>
       <c r="C618" t="n">
-        <v>0.37467</v>
+        <v>0.361702</v>
       </c>
     </row>
     <row r="619">
@@ -8461,10 +8461,10 @@
         </is>
       </c>
       <c r="B619" t="n">
-        <v>0.064246</v>
+        <v>0.063262</v>
       </c>
       <c r="C619" t="n">
-        <v>0.372032</v>
+        <v>0.359043</v>
       </c>
     </row>
     <row r="620">
@@ -8474,10 +8474,10 @@
         </is>
       </c>
       <c r="B620" t="n">
-        <v>0.064315</v>
+        <v>0.063774</v>
       </c>
       <c r="C620" t="n">
-        <v>0.369393</v>
+        <v>0.356383</v>
       </c>
     </row>
     <row r="621">
@@ -8487,10 +8487,10 @@
         </is>
       </c>
       <c r="B621" t="n">
-        <v>0.064414</v>
+        <v>0.064138</v>
       </c>
       <c r="C621" t="n">
-        <v>0.366755</v>
+        <v>0.353723</v>
       </c>
     </row>
     <row r="622">
@@ -8503,7 +8503,7 @@
         <v>0.064482</v>
       </c>
       <c r="C622" t="n">
-        <v>0.364116</v>
+        <v>0.351064</v>
       </c>
     </row>
     <row r="623">
@@ -8513,10 +8513,10 @@
         </is>
       </c>
       <c r="B623" t="n">
-        <v>0.065289</v>
+        <v>0.064771</v>
       </c>
       <c r="C623" t="n">
-        <v>0.361478</v>
+        <v>0.348404</v>
       </c>
     </row>
     <row r="624">
@@ -8526,10 +8526,10 @@
         </is>
       </c>
       <c r="B624" t="n">
-        <v>0.06533700000000001</v>
+        <v>0.065068</v>
       </c>
       <c r="C624" t="n">
-        <v>0.358839</v>
+        <v>0.345745</v>
       </c>
     </row>
     <row r="625">
@@ -8539,10 +8539,10 @@
         </is>
       </c>
       <c r="B625" t="n">
-        <v>0.06553299999999999</v>
+        <v>0.06586699999999999</v>
       </c>
       <c r="C625" t="n">
-        <v>0.356201</v>
+        <v>0.343085</v>
       </c>
     </row>
     <row r="626">
@@ -8552,10 +8552,10 @@
         </is>
       </c>
       <c r="B626" t="n">
-        <v>0.065595</v>
+        <v>0.06605</v>
       </c>
       <c r="C626" t="n">
-        <v>0.353562</v>
+        <v>0.340426</v>
       </c>
     </row>
     <row r="627">
@@ -8565,10 +8565,10 @@
         </is>
       </c>
       <c r="B627" t="n">
-        <v>0.06633500000000001</v>
+        <v>0.066358</v>
       </c>
       <c r="C627" t="n">
-        <v>0.350923</v>
+        <v>0.337766</v>
       </c>
     </row>
     <row r="628">
@@ -8578,10 +8578,10 @@
         </is>
       </c>
       <c r="B628" t="n">
-        <v>0.066376</v>
+        <v>0.066555</v>
       </c>
       <c r="C628" t="n">
-        <v>0.348285</v>
+        <v>0.335106</v>
       </c>
     </row>
     <row r="629">
@@ -8591,10 +8591,10 @@
         </is>
       </c>
       <c r="B629" t="n">
-        <v>0.066542</v>
+        <v>0.06693300000000001</v>
       </c>
       <c r="C629" t="n">
-        <v>0.345646</v>
+        <v>0.332447</v>
       </c>
     </row>
     <row r="630">
@@ -8604,10 +8604,10 @@
         </is>
       </c>
       <c r="B630" t="n">
-        <v>0.06743300000000001</v>
+        <v>0.067597</v>
       </c>
       <c r="C630" t="n">
-        <v>0.343008</v>
+        <v>0.329787</v>
       </c>
     </row>
     <row r="631">
@@ -8617,10 +8617,10 @@
         </is>
       </c>
       <c r="B631" t="n">
-        <v>0.06763</v>
+        <v>0.067853</v>
       </c>
       <c r="C631" t="n">
-        <v>0.340369</v>
+        <v>0.327128</v>
       </c>
     </row>
     <row r="632">
@@ -8630,10 +8630,10 @@
         </is>
       </c>
       <c r="B632" t="n">
-        <v>0.068096</v>
+        <v>0.067968</v>
       </c>
       <c r="C632" t="n">
-        <v>0.337731</v>
+        <v>0.324468</v>
       </c>
     </row>
     <row r="633">
@@ -8643,10 +8643,10 @@
         </is>
       </c>
       <c r="B633" t="n">
-        <v>0.06876500000000001</v>
+        <v>0.068048</v>
       </c>
       <c r="C633" t="n">
-        <v>0.335092</v>
+        <v>0.321809</v>
       </c>
     </row>
     <row r="634">
@@ -8656,10 +8656,10 @@
         </is>
       </c>
       <c r="B634" t="n">
-        <v>0.069602</v>
+        <v>0.069186</v>
       </c>
       <c r="C634" t="n">
-        <v>0.332454</v>
+        <v>0.319149</v>
       </c>
     </row>
     <row r="635">
@@ -8669,10 +8669,10 @@
         </is>
       </c>
       <c r="B635" t="n">
-        <v>0.06992900000000001</v>
+        <v>0.06936199999999999</v>
       </c>
       <c r="C635" t="n">
-        <v>0.329815</v>
+        <v>0.316489</v>
       </c>
     </row>
     <row r="636">
@@ -8682,10 +8682,10 @@
         </is>
       </c>
       <c r="B636" t="n">
-        <v>0.06995700000000001</v>
+        <v>0.07008300000000001</v>
       </c>
       <c r="C636" t="n">
-        <v>0.327177</v>
+        <v>0.31383</v>
       </c>
     </row>
     <row r="637">
@@ -8695,10 +8695,10 @@
         </is>
       </c>
       <c r="B637" t="n">
-        <v>0.070106</v>
+        <v>0.070171</v>
       </c>
       <c r="C637" t="n">
-        <v>0.324538</v>
+        <v>0.31117</v>
       </c>
     </row>
     <row r="638">
@@ -8708,10 +8708,10 @@
         </is>
       </c>
       <c r="B638" t="n">
-        <v>0.071354</v>
+        <v>0.07036100000000001</v>
       </c>
       <c r="C638" t="n">
-        <v>0.3219</v>
+        <v>0.308511</v>
       </c>
     </row>
     <row r="639">
@@ -8721,10 +8721,10 @@
         </is>
       </c>
       <c r="B639" t="n">
-        <v>0.07140199999999999</v>
+        <v>0.07054299999999999</v>
       </c>
       <c r="C639" t="n">
-        <v>0.319261</v>
+        <v>0.305851</v>
       </c>
     </row>
     <row r="640">
@@ -8734,10 +8734,10 @@
         </is>
       </c>
       <c r="B640" t="n">
-        <v>0.07191</v>
+        <v>0.071228</v>
       </c>
       <c r="C640" t="n">
-        <v>0.316623</v>
+        <v>0.303191</v>
       </c>
     </row>
     <row r="641">
@@ -8747,10 +8747,10 @@
         </is>
       </c>
       <c r="B641" t="n">
-        <v>0.0721</v>
+        <v>0.071787</v>
       </c>
       <c r="C641" t="n">
-        <v>0.313984</v>
+        <v>0.300532</v>
       </c>
     </row>
     <row r="642">
@@ -8760,10 +8760,10 @@
         </is>
       </c>
       <c r="B642" t="n">
-        <v>0.072242</v>
+        <v>0.07258299999999999</v>
       </c>
       <c r="C642" t="n">
-        <v>0.311346</v>
+        <v>0.297872</v>
       </c>
     </row>
     <row r="643">
@@ -8773,10 +8773,10 @@
         </is>
       </c>
       <c r="B643" t="n">
-        <v>0.07230499999999999</v>
+        <v>0.072865</v>
       </c>
       <c r="C643" t="n">
-        <v>0.308707</v>
+        <v>0.295213</v>
       </c>
     </row>
     <row r="644">
@@ -8786,10 +8786,10 @@
         </is>
       </c>
       <c r="B644" t="n">
-        <v>0.07351199999999999</v>
+        <v>0.073088</v>
       </c>
       <c r="C644" t="n">
-        <v>0.306069</v>
+        <v>0.292553</v>
       </c>
     </row>
     <row r="645">
@@ -8799,10 +8799,10 @@
         </is>
       </c>
       <c r="B645" t="n">
-        <v>0.074277</v>
+        <v>0.074283</v>
       </c>
       <c r="C645" t="n">
-        <v>0.30343</v>
+        <v>0.289894</v>
       </c>
     </row>
     <row r="646">
@@ -8812,10 +8812,10 @@
         </is>
       </c>
       <c r="B646" t="n">
-        <v>0.074363</v>
+        <v>0.07442600000000001</v>
       </c>
       <c r="C646" t="n">
-        <v>0.300792</v>
+        <v>0.287234</v>
       </c>
     </row>
     <row r="647">
@@ -8825,10 +8825,10 @@
         </is>
       </c>
       <c r="B647" t="n">
-        <v>0.074653</v>
+        <v>0.07463400000000001</v>
       </c>
       <c r="C647" t="n">
-        <v>0.298153</v>
+        <v>0.284574</v>
       </c>
     </row>
     <row r="648">
@@ -8838,10 +8838,10 @@
         </is>
       </c>
       <c r="B648" t="n">
-        <v>0.074903</v>
+        <v>0.074896</v>
       </c>
       <c r="C648" t="n">
-        <v>0.295515</v>
+        <v>0.281915</v>
       </c>
     </row>
     <row r="649">
@@ -8851,10 +8851,10 @@
         </is>
       </c>
       <c r="B649" t="n">
-        <v>0.075792</v>
+        <v>0.07623099999999999</v>
       </c>
       <c r="C649" t="n">
-        <v>0.292876</v>
+        <v>0.279255</v>
       </c>
     </row>
     <row r="650">
@@ -8864,10 +8864,10 @@
         </is>
       </c>
       <c r="B650" t="n">
-        <v>0.077958</v>
+        <v>0.076753</v>
       </c>
       <c r="C650" t="n">
-        <v>0.290237</v>
+        <v>0.276596</v>
       </c>
     </row>
     <row r="651">
@@ -8877,10 +8877,10 @@
         </is>
       </c>
       <c r="B651" t="n">
-        <v>0.078574</v>
+        <v>0.076774</v>
       </c>
       <c r="C651" t="n">
-        <v>0.287599</v>
+        <v>0.273936</v>
       </c>
     </row>
     <row r="652">
@@ -8890,10 +8890,10 @@
         </is>
       </c>
       <c r="B652" t="n">
-        <v>0.079247</v>
+        <v>0.079154</v>
       </c>
       <c r="C652" t="n">
-        <v>0.28496</v>
+        <v>0.271277</v>
       </c>
     </row>
     <row r="653">
@@ -8903,10 +8903,10 @@
         </is>
       </c>
       <c r="B653" t="n">
-        <v>0.080038</v>
+        <v>0.079251</v>
       </c>
       <c r="C653" t="n">
-        <v>0.282322</v>
+        <v>0.268617</v>
       </c>
     </row>
     <row r="654">
@@ -8916,10 +8916,10 @@
         </is>
       </c>
       <c r="B654" t="n">
-        <v>0.08017199999999999</v>
+        <v>0.080453</v>
       </c>
       <c r="C654" t="n">
-        <v>0.279683</v>
+        <v>0.265957</v>
       </c>
     </row>
     <row r="655">
@@ -8929,10 +8929,10 @@
         </is>
       </c>
       <c r="B655" t="n">
-        <v>0.080709</v>
+        <v>0.080677</v>
       </c>
       <c r="C655" t="n">
-        <v>0.277045</v>
+        <v>0.263298</v>
       </c>
     </row>
     <row r="656">
@@ -8942,10 +8942,10 @@
         </is>
       </c>
       <c r="B656" t="n">
-        <v>0.081867</v>
+        <v>0.08074199999999999</v>
       </c>
       <c r="C656" t="n">
-        <v>0.274406</v>
+        <v>0.260638</v>
       </c>
     </row>
     <row r="657">
@@ -8955,10 +8955,10 @@
         </is>
       </c>
       <c r="B657" t="n">
-        <v>0.08254400000000001</v>
+        <v>0.080849</v>
       </c>
       <c r="C657" t="n">
-        <v>0.271768</v>
+        <v>0.257979</v>
       </c>
     </row>
     <row r="658">
@@ -8968,10 +8968,10 @@
         </is>
       </c>
       <c r="B658" t="n">
-        <v>0.082756</v>
+        <v>0.082042</v>
       </c>
       <c r="C658" t="n">
-        <v>0.269129</v>
+        <v>0.255319</v>
       </c>
     </row>
     <row r="659">
@@ -8981,10 +8981,10 @@
         </is>
       </c>
       <c r="B659" t="n">
-        <v>0.083689</v>
+        <v>0.08221299999999999</v>
       </c>
       <c r="C659" t="n">
-        <v>0.266491</v>
+        <v>0.25266</v>
       </c>
     </row>
     <row r="660">
@@ -8994,10 +8994,10 @@
         </is>
       </c>
       <c r="B660" t="n">
-        <v>0.084078</v>
+        <v>0.08289100000000001</v>
       </c>
       <c r="C660" t="n">
-        <v>0.263852</v>
+        <v>0.25</v>
       </c>
     </row>
     <row r="661">
@@ -9007,10 +9007,10 @@
         </is>
       </c>
       <c r="B661" t="n">
-        <v>0.084255</v>
+        <v>0.082899</v>
       </c>
       <c r="C661" t="n">
-        <v>0.261214</v>
+        <v>0.24734</v>
       </c>
     </row>
     <row r="662">
@@ -9020,10 +9020,10 @@
         </is>
       </c>
       <c r="B662" t="n">
-        <v>0.084591</v>
+        <v>0.08323999999999999</v>
       </c>
       <c r="C662" t="n">
-        <v>0.258575</v>
+        <v>0.244681</v>
       </c>
     </row>
     <row r="663">
@@ -9033,10 +9033,10 @@
         </is>
       </c>
       <c r="B663" t="n">
-        <v>0.08499900000000001</v>
+        <v>0.084049</v>
       </c>
       <c r="C663" t="n">
-        <v>0.255937</v>
+        <v>0.242021</v>
       </c>
     </row>
     <row r="664">
@@ -9046,10 +9046,10 @@
         </is>
       </c>
       <c r="B664" t="n">
-        <v>0.085302</v>
+        <v>0.08409</v>
       </c>
       <c r="C664" t="n">
-        <v>0.253298</v>
+        <v>0.239362</v>
       </c>
     </row>
     <row r="665">
@@ -9059,10 +9059,10 @@
         </is>
       </c>
       <c r="B665" t="n">
-        <v>0.08569599999999999</v>
+        <v>0.084401</v>
       </c>
       <c r="C665" t="n">
-        <v>0.25066</v>
+        <v>0.236702</v>
       </c>
     </row>
     <row r="666">
@@ -9072,10 +9072,10 @@
         </is>
       </c>
       <c r="B666" t="n">
-        <v>0.086089</v>
+        <v>0.084886</v>
       </c>
       <c r="C666" t="n">
-        <v>0.248021</v>
+        <v>0.234043</v>
       </c>
     </row>
     <row r="667">
@@ -9085,10 +9085,10 @@
         </is>
       </c>
       <c r="B667" t="n">
-        <v>0.086158</v>
+        <v>0.08602600000000001</v>
       </c>
       <c r="C667" t="n">
-        <v>0.245383</v>
+        <v>0.231383</v>
       </c>
     </row>
     <row r="668">
@@ -9098,10 +9098,10 @@
         </is>
       </c>
       <c r="B668" t="n">
-        <v>0.086745</v>
+        <v>0.086852</v>
       </c>
       <c r="C668" t="n">
-        <v>0.242744</v>
+        <v>0.228723</v>
       </c>
     </row>
     <row r="669">
@@ -9111,10 +9111,10 @@
         </is>
       </c>
       <c r="B669" t="n">
-        <v>0.087252</v>
+        <v>0.0873</v>
       </c>
       <c r="C669" t="n">
-        <v>0.240106</v>
+        <v>0.226064</v>
       </c>
     </row>
     <row r="670">
@@ -9124,10 +9124,10 @@
         </is>
       </c>
       <c r="B670" t="n">
-        <v>0.087782</v>
+        <v>0.087301</v>
       </c>
       <c r="C670" t="n">
-        <v>0.237467</v>
+        <v>0.223404</v>
       </c>
     </row>
     <row r="671">
@@ -9137,10 +9137,10 @@
         </is>
       </c>
       <c r="B671" t="n">
-        <v>0.087934</v>
+        <v>0.087466</v>
       </c>
       <c r="C671" t="n">
-        <v>0.234828</v>
+        <v>0.220745</v>
       </c>
     </row>
     <row r="672">
@@ -9150,10 +9150,10 @@
         </is>
       </c>
       <c r="B672" t="n">
-        <v>0.088393</v>
+        <v>0.08747099999999999</v>
       </c>
       <c r="C672" t="n">
-        <v>0.23219</v>
+        <v>0.218085</v>
       </c>
     </row>
     <row r="673">
@@ -9163,10 +9163,10 @@
         </is>
       </c>
       <c r="B673" t="n">
-        <v>0.088908</v>
+        <v>0.08803900000000001</v>
       </c>
       <c r="C673" t="n">
-        <v>0.229551</v>
+        <v>0.215426</v>
       </c>
     </row>
     <row r="674">
@@ -9176,10 +9176,10 @@
         </is>
       </c>
       <c r="B674" t="n">
-        <v>0.089102</v>
+        <v>0.088073</v>
       </c>
       <c r="C674" t="n">
-        <v>0.226913</v>
+        <v>0.212766</v>
       </c>
     </row>
     <row r="675">
@@ -9189,10 +9189,10 @@
         </is>
       </c>
       <c r="B675" t="n">
-        <v>0.089891</v>
+        <v>0.090269</v>
       </c>
       <c r="C675" t="n">
-        <v>0.224274</v>
+        <v>0.210106</v>
       </c>
     </row>
     <row r="676">
@@ -9202,10 +9202,10 @@
         </is>
       </c>
       <c r="B676" t="n">
-        <v>0.090933</v>
+        <v>0.09045</v>
       </c>
       <c r="C676" t="n">
-        <v>0.221636</v>
+        <v>0.207447</v>
       </c>
     </row>
     <row r="677">
@@ -9215,10 +9215,10 @@
         </is>
       </c>
       <c r="B677" t="n">
-        <v>0.091527</v>
+        <v>0.091068</v>
       </c>
       <c r="C677" t="n">
-        <v>0.218997</v>
+        <v>0.204787</v>
       </c>
     </row>
     <row r="678">
@@ -9228,10 +9228,10 @@
         </is>
       </c>
       <c r="B678" t="n">
-        <v>0.091528</v>
+        <v>0.091833</v>
       </c>
       <c r="C678" t="n">
-        <v>0.216359</v>
+        <v>0.202128</v>
       </c>
     </row>
     <row r="679">
@@ -9241,10 +9241,10 @@
         </is>
       </c>
       <c r="B679" t="n">
-        <v>0.09218999999999999</v>
+        <v>0.09188300000000001</v>
       </c>
       <c r="C679" t="n">
-        <v>0.21372</v>
+        <v>0.199468</v>
       </c>
     </row>
     <row r="680">
@@ -9254,10 +9254,10 @@
         </is>
       </c>
       <c r="B680" t="n">
-        <v>0.09333</v>
+        <v>0.09278699999999999</v>
       </c>
       <c r="C680" t="n">
-        <v>0.211082</v>
+        <v>0.196809</v>
       </c>
     </row>
     <row r="681">
@@ -9267,10 +9267,10 @@
         </is>
       </c>
       <c r="B681" t="n">
-        <v>0.09348099999999999</v>
+        <v>0.093709</v>
       </c>
       <c r="C681" t="n">
-        <v>0.208443</v>
+        <v>0.194149</v>
       </c>
     </row>
     <row r="682">
@@ -9280,10 +9280,10 @@
         </is>
       </c>
       <c r="B682" t="n">
-        <v>0.094362</v>
+        <v>0.094194</v>
       </c>
       <c r="C682" t="n">
-        <v>0.205805</v>
+        <v>0.191489</v>
       </c>
     </row>
     <row r="683">
@@ -9293,10 +9293,10 @@
         </is>
       </c>
       <c r="B683" t="n">
-        <v>0.09581099999999999</v>
+        <v>0.09460499999999999</v>
       </c>
       <c r="C683" t="n">
-        <v>0.203166</v>
+        <v>0.18883</v>
       </c>
     </row>
     <row r="684">
@@ -9306,10 +9306,10 @@
         </is>
       </c>
       <c r="B684" t="n">
-        <v>0.095817</v>
+        <v>0.095223</v>
       </c>
       <c r="C684" t="n">
-        <v>0.200528</v>
+        <v>0.18617</v>
       </c>
     </row>
     <row r="685">
@@ -9319,10 +9319,10 @@
         </is>
       </c>
       <c r="B685" t="n">
-        <v>0.097037</v>
+        <v>0.09707200000000001</v>
       </c>
       <c r="C685" t="n">
-        <v>0.197889</v>
+        <v>0.183511</v>
       </c>
     </row>
     <row r="686">
@@ -9332,10 +9332,10 @@
         </is>
       </c>
       <c r="B686" t="n">
-        <v>0.09739200000000001</v>
+        <v>0.09715</v>
       </c>
       <c r="C686" t="n">
-        <v>0.195251</v>
+        <v>0.180851</v>
       </c>
     </row>
     <row r="687">
@@ -9345,10 +9345,10 @@
         </is>
       </c>
       <c r="B687" t="n">
-        <v>0.097444</v>
+        <v>0.100291</v>
       </c>
       <c r="C687" t="n">
-        <v>0.192612</v>
+        <v>0.178191</v>
       </c>
     </row>
     <row r="688">
@@ -9358,10 +9358,10 @@
         </is>
       </c>
       <c r="B688" t="n">
-        <v>0.100083</v>
+        <v>0.101921</v>
       </c>
       <c r="C688" t="n">
-        <v>0.189974</v>
+        <v>0.175532</v>
       </c>
     </row>
     <row r="689">
@@ -9371,10 +9371,10 @@
         </is>
       </c>
       <c r="B689" t="n">
-        <v>0.101159</v>
+        <v>0.102166</v>
       </c>
       <c r="C689" t="n">
-        <v>0.187335</v>
+        <v>0.172872</v>
       </c>
     </row>
     <row r="690">
@@ -9384,10 +9384,10 @@
         </is>
       </c>
       <c r="B690" t="n">
-        <v>0.101343</v>
+        <v>0.104146</v>
       </c>
       <c r="C690" t="n">
-        <v>0.184697</v>
+        <v>0.170213</v>
       </c>
     </row>
     <row r="691">
@@ -9397,10 +9397,10 @@
         </is>
       </c>
       <c r="B691" t="n">
-        <v>0.10242</v>
+        <v>0.104443</v>
       </c>
       <c r="C691" t="n">
-        <v>0.182058</v>
+        <v>0.167553</v>
       </c>
     </row>
     <row r="692">
@@ -9410,10 +9410,10 @@
         </is>
       </c>
       <c r="B692" t="n">
-        <v>0.103598</v>
+        <v>0.105048</v>
       </c>
       <c r="C692" t="n">
-        <v>0.17942</v>
+        <v>0.164894</v>
       </c>
     </row>
     <row r="693">
@@ -9423,10 +9423,10 @@
         </is>
       </c>
       <c r="B693" t="n">
-        <v>0.103805</v>
+        <v>0.106714</v>
       </c>
       <c r="C693" t="n">
-        <v>0.176781</v>
+        <v>0.162234</v>
       </c>
     </row>
     <row r="694">
@@ -9436,10 +9436,10 @@
         </is>
       </c>
       <c r="B694" t="n">
-        <v>0.104884</v>
+        <v>0.106849</v>
       </c>
       <c r="C694" t="n">
-        <v>0.174142</v>
+        <v>0.159574</v>
       </c>
     </row>
     <row r="695">
@@ -9449,10 +9449,10 @@
         </is>
       </c>
       <c r="B695" t="n">
-        <v>0.105888</v>
+        <v>0.108285</v>
       </c>
       <c r="C695" t="n">
-        <v>0.171504</v>
+        <v>0.156915</v>
       </c>
     </row>
     <row r="696">
@@ -9462,10 +9462,10 @@
         </is>
       </c>
       <c r="B696" t="n">
-        <v>0.109171</v>
+        <v>0.109845</v>
       </c>
       <c r="C696" t="n">
-        <v>0.168865</v>
+        <v>0.154255</v>
       </c>
     </row>
     <row r="697">
@@ -9475,10 +9475,10 @@
         </is>
       </c>
       <c r="B697" t="n">
-        <v>0.1104</v>
+        <v>0.110587</v>
       </c>
       <c r="C697" t="n">
-        <v>0.166227</v>
+        <v>0.151596</v>
       </c>
     </row>
     <row r="698">
@@ -9488,10 +9488,10 @@
         </is>
       </c>
       <c r="B698" t="n">
-        <v>0.113128</v>
+        <v>0.111572</v>
       </c>
       <c r="C698" t="n">
-        <v>0.163588</v>
+        <v>0.148936</v>
       </c>
     </row>
     <row r="699">
@@ -9501,10 +9501,10 @@
         </is>
       </c>
       <c r="B699" t="n">
-        <v>0.113228</v>
+        <v>0.113289</v>
       </c>
       <c r="C699" t="n">
-        <v>0.16095</v>
+        <v>0.146277</v>
       </c>
     </row>
     <row r="700">
@@ -9514,10 +9514,10 @@
         </is>
       </c>
       <c r="B700" t="n">
-        <v>0.114436</v>
+        <v>0.114655</v>
       </c>
       <c r="C700" t="n">
-        <v>0.158311</v>
+        <v>0.143617</v>
       </c>
     </row>
     <row r="701">
@@ -9527,10 +9527,10 @@
         </is>
       </c>
       <c r="B701" t="n">
-        <v>0.115489</v>
+        <v>0.115883</v>
       </c>
       <c r="C701" t="n">
-        <v>0.155673</v>
+        <v>0.140957</v>
       </c>
     </row>
     <row r="702">
@@ -9540,10 +9540,10 @@
         </is>
       </c>
       <c r="B702" t="n">
-        <v>0.115936</v>
+        <v>0.116057</v>
       </c>
       <c r="C702" t="n">
-        <v>0.153034</v>
+        <v>0.138298</v>
       </c>
     </row>
     <row r="703">
@@ -9553,10 +9553,10 @@
         </is>
       </c>
       <c r="B703" t="n">
-        <v>0.11625</v>
+        <v>0.116307</v>
       </c>
       <c r="C703" t="n">
-        <v>0.150396</v>
+        <v>0.135638</v>
       </c>
     </row>
     <row r="704">
@@ -9566,10 +9566,10 @@
         </is>
       </c>
       <c r="B704" t="n">
-        <v>0.117243</v>
+        <v>0.117176</v>
       </c>
       <c r="C704" t="n">
-        <v>0.147757</v>
+        <v>0.132979</v>
       </c>
     </row>
     <row r="705">
@@ -9579,10 +9579,10 @@
         </is>
       </c>
       <c r="B705" t="n">
-        <v>0.120061</v>
+        <v>0.117591</v>
       </c>
       <c r="C705" t="n">
-        <v>0.145119</v>
+        <v>0.130319</v>
       </c>
     </row>
     <row r="706">
@@ -9592,10 +9592,10 @@
         </is>
       </c>
       <c r="B706" t="n">
-        <v>0.12104</v>
+        <v>0.11767</v>
       </c>
       <c r="C706" t="n">
-        <v>0.14248</v>
+        <v>0.12766</v>
       </c>
     </row>
     <row r="707">
@@ -9605,10 +9605,10 @@
         </is>
       </c>
       <c r="B707" t="n">
-        <v>0.121096</v>
+        <v>0.118465</v>
       </c>
       <c r="C707" t="n">
-        <v>0.139842</v>
+        <v>0.125</v>
       </c>
     </row>
     <row r="708">
@@ -9618,10 +9618,10 @@
         </is>
       </c>
       <c r="B708" t="n">
-        <v>0.121925</v>
+        <v>0.119059</v>
       </c>
       <c r="C708" t="n">
-        <v>0.137203</v>
+        <v>0.12234</v>
       </c>
     </row>
     <row r="709">
@@ -9631,10 +9631,10 @@
         </is>
       </c>
       <c r="B709" t="n">
-        <v>0.122277</v>
+        <v>0.121802</v>
       </c>
       <c r="C709" t="n">
-        <v>0.134565</v>
+        <v>0.119681</v>
       </c>
     </row>
     <row r="710">
@@ -9644,10 +9644,10 @@
         </is>
       </c>
       <c r="B710" t="n">
-        <v>0.125319</v>
+        <v>0.122267</v>
       </c>
       <c r="C710" t="n">
-        <v>0.131926</v>
+        <v>0.117021</v>
       </c>
     </row>
     <row r="711">
@@ -9657,10 +9657,10 @@
         </is>
       </c>
       <c r="B711" t="n">
-        <v>0.126292</v>
+        <v>0.12304</v>
       </c>
       <c r="C711" t="n">
-        <v>0.129288</v>
+        <v>0.114362</v>
       </c>
     </row>
     <row r="712">
@@ -9670,10 +9670,10 @@
         </is>
       </c>
       <c r="B712" t="n">
-        <v>0.127738</v>
+        <v>0.125468</v>
       </c>
       <c r="C712" t="n">
-        <v>0.126649</v>
+        <v>0.111702</v>
       </c>
     </row>
     <row r="713">
@@ -9683,10 +9683,10 @@
         </is>
       </c>
       <c r="B713" t="n">
-        <v>0.128052</v>
+        <v>0.126527</v>
       </c>
       <c r="C713" t="n">
-        <v>0.124011</v>
+        <v>0.109043</v>
       </c>
     </row>
     <row r="714">
@@ -9696,10 +9696,10 @@
         </is>
       </c>
       <c r="B714" t="n">
-        <v>0.128094</v>
+        <v>0.127412</v>
       </c>
       <c r="C714" t="n">
-        <v>0.121372</v>
+        <v>0.106383</v>
       </c>
     </row>
     <row r="715">
@@ -9709,10 +9709,10 @@
         </is>
       </c>
       <c r="B715" t="n">
-        <v>0.128592</v>
+        <v>0.127703</v>
       </c>
       <c r="C715" t="n">
-        <v>0.118734</v>
+        <v>0.103723</v>
       </c>
     </row>
     <row r="716">
@@ -9722,10 +9722,10 @@
         </is>
       </c>
       <c r="B716" t="n">
-        <v>0.130809</v>
+        <v>0.129269</v>
       </c>
       <c r="C716" t="n">
-        <v>0.116095</v>
+        <v>0.101064</v>
       </c>
     </row>
     <row r="717">
@@ -9735,10 +9735,10 @@
         </is>
       </c>
       <c r="B717" t="n">
-        <v>0.131556</v>
+        <v>0.130597</v>
       </c>
       <c r="C717" t="n">
-        <v>0.113456</v>
+        <v>0.09840400000000001</v>
       </c>
     </row>
     <row r="718">
@@ -9748,10 +9748,10 @@
         </is>
       </c>
       <c r="B718" t="n">
-        <v>0.13259</v>
+        <v>0.131202</v>
       </c>
       <c r="C718" t="n">
-        <v>0.110818</v>
+        <v>0.095745</v>
       </c>
     </row>
     <row r="719">
@@ -9761,10 +9761,10 @@
         </is>
       </c>
       <c r="B719" t="n">
-        <v>0.132761</v>
+        <v>0.131362</v>
       </c>
       <c r="C719" t="n">
-        <v>0.108179</v>
+        <v>0.093085</v>
       </c>
     </row>
     <row r="720">
@@ -9774,10 +9774,10 @@
         </is>
       </c>
       <c r="B720" t="n">
-        <v>0.132941</v>
+        <v>0.132383</v>
       </c>
       <c r="C720" t="n">
-        <v>0.105541</v>
+        <v>0.09042600000000001</v>
       </c>
     </row>
     <row r="721">
@@ -9787,10 +9787,10 @@
         </is>
       </c>
       <c r="B721" t="n">
-        <v>0.133128</v>
+        <v>0.13263</v>
       </c>
       <c r="C721" t="n">
-        <v>0.102902</v>
+        <v>0.087766</v>
       </c>
     </row>
     <row r="722">
@@ -9800,10 +9800,10 @@
         </is>
       </c>
       <c r="B722" t="n">
-        <v>0.13327</v>
+        <v>0.136914</v>
       </c>
       <c r="C722" t="n">
-        <v>0.100264</v>
+        <v>0.085106</v>
       </c>
     </row>
     <row r="723">
@@ -9813,10 +9813,10 @@
         </is>
       </c>
       <c r="B723" t="n">
-        <v>0.133815</v>
+        <v>0.143549</v>
       </c>
       <c r="C723" t="n">
-        <v>0.097625</v>
+        <v>0.08244700000000001</v>
       </c>
     </row>
     <row r="724">
@@ -9826,10 +9826,10 @@
         </is>
       </c>
       <c r="B724" t="n">
-        <v>0.133895</v>
+        <v>0.144253</v>
       </c>
       <c r="C724" t="n">
-        <v>0.094987</v>
+        <v>0.079787</v>
       </c>
     </row>
     <row r="725">
@@ -9839,10 +9839,10 @@
         </is>
       </c>
       <c r="B725" t="n">
-        <v>0.138455</v>
+        <v>0.149441</v>
       </c>
       <c r="C725" t="n">
-        <v>0.092348</v>
+        <v>0.077128</v>
       </c>
     </row>
     <row r="726">
@@ -9852,10 +9852,10 @@
         </is>
       </c>
       <c r="B726" t="n">
-        <v>0.138506</v>
+        <v>0.150255</v>
       </c>
       <c r="C726" t="n">
-        <v>0.08971</v>
+        <v>0.07446800000000001</v>
       </c>
     </row>
     <row r="727">
@@ -9865,10 +9865,10 @@
         </is>
       </c>
       <c r="B727" t="n">
-        <v>0.145445</v>
+        <v>0.152307</v>
       </c>
       <c r="C727" t="n">
-        <v>0.087071</v>
+        <v>0.071809</v>
       </c>
     </row>
     <row r="728">
@@ -9878,10 +9878,10 @@
         </is>
       </c>
       <c r="B728" t="n">
-        <v>0.153444</v>
+        <v>0.15474</v>
       </c>
       <c r="C728" t="n">
-        <v>0.08443299999999999</v>
+        <v>0.069149</v>
       </c>
     </row>
     <row r="729">
@@ -9891,10 +9891,10 @@
         </is>
       </c>
       <c r="B729" t="n">
-        <v>0.157043</v>
+        <v>0.156823</v>
       </c>
       <c r="C729" t="n">
-        <v>0.08179400000000001</v>
+        <v>0.06648900000000001</v>
       </c>
     </row>
     <row r="730">
@@ -9904,10 +9904,10 @@
         </is>
       </c>
       <c r="B730" t="n">
-        <v>0.157661</v>
+        <v>0.157804</v>
       </c>
       <c r="C730" t="n">
-        <v>0.079156</v>
+        <v>0.06383</v>
       </c>
     </row>
     <row r="731">
@@ -9917,10 +9917,10 @@
         </is>
       </c>
       <c r="B731" t="n">
-        <v>0.158875</v>
+        <v>0.159124</v>
       </c>
       <c r="C731" t="n">
-        <v>0.076517</v>
+        <v>0.06117</v>
       </c>
     </row>
     <row r="732">
@@ -9930,10 +9930,10 @@
         </is>
       </c>
       <c r="B732" t="n">
-        <v>0.161055</v>
+        <v>0.162965</v>
       </c>
       <c r="C732" t="n">
-        <v>0.073879</v>
+        <v>0.058511</v>
       </c>
     </row>
     <row r="733">
@@ -9943,10 +9943,10 @@
         </is>
       </c>
       <c r="B733" t="n">
-        <v>0.161699</v>
+        <v>0.164139</v>
       </c>
       <c r="C733" t="n">
-        <v>0.07124</v>
+        <v>0.055851</v>
       </c>
     </row>
     <row r="734">
@@ -9956,10 +9956,10 @@
         </is>
       </c>
       <c r="B734" t="n">
-        <v>0.165547</v>
+        <v>0.166078</v>
       </c>
       <c r="C734" t="n">
-        <v>0.068602</v>
+        <v>0.053191</v>
       </c>
     </row>
     <row r="735">
@@ -9969,10 +9969,10 @@
         </is>
       </c>
       <c r="B735" t="n">
-        <v>0.168252</v>
+        <v>0.169314</v>
       </c>
       <c r="C735" t="n">
-        <v>0.06596299999999999</v>
+        <v>0.050532</v>
       </c>
     </row>
     <row r="736">
@@ -9982,10 +9982,10 @@
         </is>
       </c>
       <c r="B736" t="n">
-        <v>0.16997</v>
+        <v>0.172443</v>
       </c>
       <c r="C736" t="n">
-        <v>0.06332500000000001</v>
+        <v>0.047872</v>
       </c>
     </row>
     <row r="737">
@@ -9995,10 +9995,10 @@
         </is>
       </c>
       <c r="B737" t="n">
-        <v>0.170729</v>
+        <v>0.174893</v>
       </c>
       <c r="C737" t="n">
-        <v>0.060686</v>
+        <v>0.045213</v>
       </c>
     </row>
     <row r="738">
@@ -10008,10 +10008,10 @@
         </is>
       </c>
       <c r="B738" t="n">
-        <v>0.172047</v>
+        <v>0.17575</v>
       </c>
       <c r="C738" t="n">
-        <v>0.058047</v>
+        <v>0.042553</v>
       </c>
     </row>
     <row r="739">
@@ -10021,10 +10021,10 @@
         </is>
       </c>
       <c r="B739" t="n">
-        <v>0.173745</v>
+        <v>0.177768</v>
       </c>
       <c r="C739" t="n">
-        <v>0.055409</v>
+        <v>0.039894</v>
       </c>
     </row>
     <row r="740">
@@ -10034,10 +10034,10 @@
         </is>
       </c>
       <c r="B740" t="n">
-        <v>0.183189</v>
+        <v>0.188087</v>
       </c>
       <c r="C740" t="n">
-        <v>0.05277</v>
+        <v>0.037234</v>
       </c>
     </row>
     <row r="741">
@@ -10047,10 +10047,10 @@
         </is>
       </c>
       <c r="B741" t="n">
-        <v>0.186865</v>
+        <v>0.191645</v>
       </c>
       <c r="C741" t="n">
-        <v>0.050132</v>
+        <v>0.034574</v>
       </c>
     </row>
     <row r="742">
@@ -10060,10 +10060,10 @@
         </is>
       </c>
       <c r="B742" t="n">
-        <v>0.189108</v>
+        <v>0.196529</v>
       </c>
       <c r="C742" t="n">
-        <v>0.047493</v>
+        <v>0.031915</v>
       </c>
     </row>
     <row r="743">
@@ -10073,10 +10073,10 @@
         </is>
       </c>
       <c r="B743" t="n">
-        <v>0.189862</v>
+        <v>0.202009</v>
       </c>
       <c r="C743" t="n">
-        <v>0.044855</v>
+        <v>0.029255</v>
       </c>
     </row>
     <row r="744">
@@ -10086,10 +10086,10 @@
         </is>
       </c>
       <c r="B744" t="n">
-        <v>0.19512</v>
+        <v>0.211973</v>
       </c>
       <c r="C744" t="n">
-        <v>0.042216</v>
+        <v>0.026596</v>
       </c>
     </row>
     <row r="745">
@@ -10099,10 +10099,10 @@
         </is>
       </c>
       <c r="B745" t="n">
-        <v>0.200625</v>
+        <v>0.222911</v>
       </c>
       <c r="C745" t="n">
-        <v>0.039578</v>
+        <v>0.023936</v>
       </c>
     </row>
     <row r="746">
@@ -10112,10 +10112,10 @@
         </is>
       </c>
       <c r="B746" t="n">
-        <v>0.203039</v>
+        <v>0.223629</v>
       </c>
       <c r="C746" t="n">
-        <v>0.036939</v>
+        <v>0.021277</v>
       </c>
     </row>
     <row r="747">
@@ -10125,10 +10125,10 @@
         </is>
       </c>
       <c r="B747" t="n">
-        <v>0.207801</v>
+        <v>0.230509</v>
       </c>
       <c r="C747" t="n">
-        <v>0.034301</v>
+        <v>0.018617</v>
       </c>
     </row>
     <row r="748">
@@ -10138,10 +10138,10 @@
         </is>
       </c>
       <c r="B748" t="n">
-        <v>0.213063</v>
+        <v>0.247289</v>
       </c>
       <c r="C748" t="n">
-        <v>0.031662</v>
+        <v>0.015957</v>
       </c>
     </row>
     <row r="749">
@@ -10151,10 +10151,10 @@
         </is>
       </c>
       <c r="B749" t="n">
-        <v>0.220211</v>
+        <v>0.276518</v>
       </c>
       <c r="C749" t="n">
-        <v>0.029024</v>
+        <v>0.013298</v>
       </c>
     </row>
     <row r="750">
@@ -10164,10 +10164,10 @@
         </is>
       </c>
       <c r="B750" t="n">
-        <v>0.2314</v>
+        <v>0.277584</v>
       </c>
       <c r="C750" t="n">
-        <v>0.026385</v>
+        <v>0.010638</v>
       </c>
     </row>
     <row r="751">
@@ -10177,10 +10177,10 @@
         </is>
       </c>
       <c r="B751" t="n">
-        <v>0.244745</v>
+        <v>0.3128</v>
       </c>
       <c r="C751" t="n">
-        <v>0.023747</v>
+        <v>0.007979</v>
       </c>
     </row>
     <row r="752">
@@ -10190,10 +10190,10 @@
         </is>
       </c>
       <c r="B752" t="n">
-        <v>0.250994</v>
+        <v>0.347132</v>
       </c>
       <c r="C752" t="n">
-        <v>0.021108</v>
+        <v>0.005319</v>
       </c>
     </row>
     <row r="753">
@@ -10203,88 +10203,10 @@
         </is>
       </c>
       <c r="B753" t="n">
-        <v>0.277456</v>
+        <v>0.403327</v>
       </c>
       <c r="C753" t="n">
-        <v>0.01847</v>
-      </c>
-    </row>
-    <row r="754">
-      <c r="A754" t="inlineStr">
-        <is>
-          <t>Adjusted target</t>
-        </is>
-      </c>
-      <c r="B754" t="n">
-        <v>0.279457</v>
-      </c>
-      <c r="C754" t="n">
-        <v>0.015831</v>
-      </c>
-    </row>
-    <row r="755">
-      <c r="A755" t="inlineStr">
-        <is>
-          <t>Adjusted target</t>
-        </is>
-      </c>
-      <c r="B755" t="n">
-        <v>0.307116</v>
-      </c>
-      <c r="C755" t="n">
-        <v>0.013193</v>
-      </c>
-    </row>
-    <row r="756">
-      <c r="A756" t="inlineStr">
-        <is>
-          <t>Adjusted target</t>
-        </is>
-      </c>
-      <c r="B756" t="n">
-        <v>0.320037</v>
-      </c>
-      <c r="C756" t="n">
-        <v>0.010554</v>
-      </c>
-    </row>
-    <row r="757">
-      <c r="A757" t="inlineStr">
-        <is>
-          <t>Adjusted target</t>
-        </is>
-      </c>
-      <c r="B757" t="n">
-        <v>0.360489</v>
-      </c>
-      <c r="C757" t="n">
-        <v>0.007915999999999999</v>
-      </c>
-    </row>
-    <row r="758">
-      <c r="A758" t="inlineStr">
-        <is>
-          <t>Adjusted target</t>
-        </is>
-      </c>
-      <c r="B758" t="n">
-        <v>0.375924</v>
-      </c>
-      <c r="C758" t="n">
-        <v>0.005277</v>
-      </c>
-    </row>
-    <row r="759">
-      <c r="A759" t="inlineStr">
-        <is>
-          <t>Adjusted target</t>
-        </is>
-      </c>
-      <c r="B759" t="n">
-        <v>0.422116</v>
-      </c>
-      <c r="C759" t="n">
-        <v>0.002639</v>
+        <v>0.00266</v>
       </c>
     </row>
   </sheetData>

--- a/vignettes/vignette-1/tail_exceedance_plot_data.xlsx
+++ b/vignettes/vignette-1/tail_exceedance_plot_data.xlsx
@@ -5341,7 +5341,7 @@
         </is>
       </c>
       <c r="B379" t="n">
-        <v>0.000102</v>
+        <v>0.000103</v>
       </c>
       <c r="C379" t="n">
         <v>0.99734</v>
@@ -5354,7 +5354,7 @@
         </is>
       </c>
       <c r="B380" t="n">
-        <v>0.000307</v>
+        <v>0.000309</v>
       </c>
       <c r="C380" t="n">
         <v>0.994681</v>
@@ -5367,7 +5367,7 @@
         </is>
       </c>
       <c r="B381" t="n">
-        <v>0.000503</v>
+        <v>0.000504</v>
       </c>
       <c r="C381" t="n">
         <v>0.992021</v>
@@ -5380,7 +5380,7 @@
         </is>
       </c>
       <c r="B382" t="n">
-        <v>0.00102</v>
+        <v>0.001023</v>
       </c>
       <c r="C382" t="n">
         <v>0.989362</v>
@@ -5393,7 +5393,7 @@
         </is>
       </c>
       <c r="B383" t="n">
-        <v>0.001631</v>
+        <v>0.001641</v>
       </c>
       <c r="C383" t="n">
         <v>0.986702</v>
@@ -5406,7 +5406,7 @@
         </is>
       </c>
       <c r="B384" t="n">
-        <v>0.001849</v>
+        <v>0.001859</v>
       </c>
       <c r="C384" t="n">
         <v>0.984043</v>
@@ -5419,7 +5419,7 @@
         </is>
       </c>
       <c r="B385" t="n">
-        <v>0.001885</v>
+        <v>0.001898</v>
       </c>
       <c r="C385" t="n">
         <v>0.981383</v>
@@ -5432,7 +5432,7 @@
         </is>
       </c>
       <c r="B386" t="n">
-        <v>0.002077</v>
+        <v>0.002107</v>
       </c>
       <c r="C386" t="n">
         <v>0.978723</v>
@@ -5445,7 +5445,7 @@
         </is>
       </c>
       <c r="B387" t="n">
-        <v>0.002655</v>
+        <v>0.002675</v>
       </c>
       <c r="C387" t="n">
         <v>0.976064</v>
@@ -5458,7 +5458,7 @@
         </is>
       </c>
       <c r="B388" t="n">
-        <v>0.002798</v>
+        <v>0.002829</v>
       </c>
       <c r="C388" t="n">
         <v>0.973404</v>
@@ -5471,7 +5471,7 @@
         </is>
       </c>
       <c r="B389" t="n">
-        <v>0.003129</v>
+        <v>0.003139</v>
       </c>
       <c r="C389" t="n">
         <v>0.970745</v>
@@ -5484,7 +5484,7 @@
         </is>
       </c>
       <c r="B390" t="n">
-        <v>0.003421</v>
+        <v>0.003453</v>
       </c>
       <c r="C390" t="n">
         <v>0.968085</v>
@@ -5497,7 +5497,7 @@
         </is>
       </c>
       <c r="B391" t="n">
-        <v>0.004014</v>
+        <v>0.004067</v>
       </c>
       <c r="C391" t="n">
         <v>0.965426</v>
@@ -5510,7 +5510,7 @@
         </is>
       </c>
       <c r="B392" t="n">
-        <v>0.004049</v>
+        <v>0.004152</v>
       </c>
       <c r="C392" t="n">
         <v>0.962766</v>
@@ -5523,7 +5523,7 @@
         </is>
       </c>
       <c r="B393" t="n">
-        <v>0.004162</v>
+        <v>0.004202</v>
       </c>
       <c r="C393" t="n">
         <v>0.960106</v>
@@ -5536,7 +5536,7 @@
         </is>
       </c>
       <c r="B394" t="n">
-        <v>0.004376</v>
+        <v>0.004379</v>
       </c>
       <c r="C394" t="n">
         <v>0.957447</v>
@@ -5549,7 +5549,7 @@
         </is>
       </c>
       <c r="B395" t="n">
-        <v>0.004698</v>
+        <v>0.004727</v>
       </c>
       <c r="C395" t="n">
         <v>0.9547870000000001</v>
@@ -5562,7 +5562,7 @@
         </is>
       </c>
       <c r="B396" t="n">
-        <v>0.004715</v>
+        <v>0.004757</v>
       </c>
       <c r="C396" t="n">
         <v>0.952128</v>
@@ -5575,7 +5575,7 @@
         </is>
       </c>
       <c r="B397" t="n">
-        <v>0.004717</v>
+        <v>0.004764</v>
       </c>
       <c r="C397" t="n">
         <v>0.949468</v>
@@ -5588,7 +5588,7 @@
         </is>
       </c>
       <c r="B398" t="n">
-        <v>0.004792</v>
+        <v>0.004905</v>
       </c>
       <c r="C398" t="n">
         <v>0.946809</v>
@@ -5601,7 +5601,7 @@
         </is>
       </c>
       <c r="B399" t="n">
-        <v>0.004927</v>
+        <v>0.005007</v>
       </c>
       <c r="C399" t="n">
         <v>0.944149</v>
@@ -5614,7 +5614,7 @@
         </is>
       </c>
       <c r="B400" t="n">
-        <v>0.005237</v>
+        <v>0.005256</v>
       </c>
       <c r="C400" t="n">
         <v>0.941489</v>
@@ -5627,7 +5627,7 @@
         </is>
       </c>
       <c r="B401" t="n">
-        <v>0.00539</v>
+        <v>0.00542</v>
       </c>
       <c r="C401" t="n">
         <v>0.9388300000000001</v>
@@ -5640,7 +5640,7 @@
         </is>
       </c>
       <c r="B402" t="n">
-        <v>0.005401</v>
+        <v>0.005443</v>
       </c>
       <c r="C402" t="n">
         <v>0.9361699999999999</v>
@@ -5653,7 +5653,7 @@
         </is>
       </c>
       <c r="B403" t="n">
-        <v>0.005853</v>
+        <v>0.005882</v>
       </c>
       <c r="C403" t="n">
         <v>0.933511</v>
@@ -5666,7 +5666,7 @@
         </is>
       </c>
       <c r="B404" t="n">
-        <v>0.005855</v>
+        <v>0.00589</v>
       </c>
       <c r="C404" t="n">
         <v>0.930851</v>
@@ -5679,7 +5679,7 @@
         </is>
       </c>
       <c r="B405" t="n">
-        <v>0.006366</v>
+        <v>0.006552</v>
       </c>
       <c r="C405" t="n">
         <v>0.928191</v>
@@ -5692,7 +5692,7 @@
         </is>
       </c>
       <c r="B406" t="n">
-        <v>0.006759</v>
+        <v>0.006779</v>
       </c>
       <c r="C406" t="n">
         <v>0.925532</v>
@@ -5705,7 +5705,7 @@
         </is>
       </c>
       <c r="B407" t="n">
-        <v>0.007556</v>
+        <v>0.007579</v>
       </c>
       <c r="C407" t="n">
         <v>0.922872</v>
@@ -5718,7 +5718,7 @@
         </is>
       </c>
       <c r="B408" t="n">
-        <v>0.007887</v>
+        <v>0.007972999999999999</v>
       </c>
       <c r="C408" t="n">
         <v>0.9202129999999999</v>
@@ -5731,7 +5731,7 @@
         </is>
       </c>
       <c r="B409" t="n">
-        <v>0.008090999999999999</v>
+        <v>0.008101000000000001</v>
       </c>
       <c r="C409" t="n">
         <v>0.917553</v>
@@ -5744,7 +5744,7 @@
         </is>
       </c>
       <c r="B410" t="n">
-        <v>0.008198</v>
+        <v>0.008219000000000001</v>
       </c>
       <c r="C410" t="n">
         <v>0.914894</v>
@@ -5757,7 +5757,7 @@
         </is>
       </c>
       <c r="B411" t="n">
-        <v>0.008213</v>
+        <v>0.008285000000000001</v>
       </c>
       <c r="C411" t="n">
         <v>0.912234</v>
@@ -5770,7 +5770,7 @@
         </is>
       </c>
       <c r="B412" t="n">
-        <v>0.008325000000000001</v>
+        <v>0.008363000000000001</v>
       </c>
       <c r="C412" t="n">
         <v>0.909574</v>
@@ -5783,7 +5783,7 @@
         </is>
       </c>
       <c r="B413" t="n">
-        <v>0.008584</v>
+        <v>0.008595999999999999</v>
       </c>
       <c r="C413" t="n">
         <v>0.906915</v>
@@ -5796,7 +5796,7 @@
         </is>
       </c>
       <c r="B414" t="n">
-        <v>0.008670000000000001</v>
+        <v>0.008699</v>
       </c>
       <c r="C414" t="n">
         <v>0.904255</v>
@@ -5809,7 +5809,7 @@
         </is>
       </c>
       <c r="B415" t="n">
-        <v>0.008696000000000001</v>
+        <v>0.008798</v>
       </c>
       <c r="C415" t="n">
         <v>0.901596</v>
@@ -5822,7 +5822,7 @@
         </is>
       </c>
       <c r="B416" t="n">
-        <v>0.008838</v>
+        <v>0.008947</v>
       </c>
       <c r="C416" t="n">
         <v>0.898936</v>
@@ -5835,7 +5835,7 @@
         </is>
       </c>
       <c r="B417" t="n">
-        <v>0.009552</v>
+        <v>0.009594999999999999</v>
       </c>
       <c r="C417" t="n">
         <v>0.896277</v>
@@ -5848,7 +5848,7 @@
         </is>
       </c>
       <c r="B418" t="n">
-        <v>0.009578</v>
+        <v>0.009639</v>
       </c>
       <c r="C418" t="n">
         <v>0.893617</v>
@@ -5861,7 +5861,7 @@
         </is>
       </c>
       <c r="B419" t="n">
-        <v>0.009582</v>
+        <v>0.009733</v>
       </c>
       <c r="C419" t="n">
         <v>0.890957</v>
@@ -5874,7 +5874,7 @@
         </is>
       </c>
       <c r="B420" t="n">
-        <v>0.00971</v>
+        <v>0.009756000000000001</v>
       </c>
       <c r="C420" t="n">
         <v>0.888298</v>
@@ -5887,7 +5887,7 @@
         </is>
       </c>
       <c r="B421" t="n">
-        <v>0.009842999999999999</v>
+        <v>0.010005</v>
       </c>
       <c r="C421" t="n">
         <v>0.885638</v>
@@ -5900,7 +5900,7 @@
         </is>
       </c>
       <c r="B422" t="n">
-        <v>0.009845</v>
+        <v>0.010012</v>
       </c>
       <c r="C422" t="n">
         <v>0.882979</v>
@@ -5913,7 +5913,7 @@
         </is>
       </c>
       <c r="B423" t="n">
-        <v>0.009894</v>
+        <v>0.010057</v>
       </c>
       <c r="C423" t="n">
         <v>0.880319</v>
@@ -5926,7 +5926,7 @@
         </is>
       </c>
       <c r="B424" t="n">
-        <v>0.010175</v>
+        <v>0.010209</v>
       </c>
       <c r="C424" t="n">
         <v>0.87766</v>
@@ -5939,7 +5939,7 @@
         </is>
       </c>
       <c r="B425" t="n">
-        <v>0.010302</v>
+        <v>0.010345</v>
       </c>
       <c r="C425" t="n">
         <v>0.875</v>
@@ -5952,7 +5952,7 @@
         </is>
       </c>
       <c r="B426" t="n">
-        <v>0.010501</v>
+        <v>0.010564</v>
       </c>
       <c r="C426" t="n">
         <v>0.87234</v>
@@ -5965,7 +5965,7 @@
         </is>
       </c>
       <c r="B427" t="n">
-        <v>0.010995</v>
+        <v>0.01106</v>
       </c>
       <c r="C427" t="n">
         <v>0.869681</v>
@@ -5978,7 +5978,7 @@
         </is>
       </c>
       <c r="B428" t="n">
-        <v>0.011579</v>
+        <v>0.011615</v>
       </c>
       <c r="C428" t="n">
         <v>0.867021</v>
@@ -5991,7 +5991,7 @@
         </is>
       </c>
       <c r="B429" t="n">
-        <v>0.011742</v>
+        <v>0.011819</v>
       </c>
       <c r="C429" t="n">
         <v>0.864362</v>
@@ -6004,7 +6004,7 @@
         </is>
       </c>
       <c r="B430" t="n">
-        <v>0.011898</v>
+        <v>0.011921</v>
       </c>
       <c r="C430" t="n">
         <v>0.861702</v>
@@ -6017,7 +6017,7 @@
         </is>
       </c>
       <c r="B431" t="n">
-        <v>0.011942</v>
+        <v>0.012221</v>
       </c>
       <c r="C431" t="n">
         <v>0.859043</v>
@@ -6030,7 +6030,7 @@
         </is>
       </c>
       <c r="B432" t="n">
-        <v>0.012238</v>
+        <v>0.012257</v>
       </c>
       <c r="C432" t="n">
         <v>0.856383</v>
@@ -6043,7 +6043,7 @@
         </is>
       </c>
       <c r="B433" t="n">
-        <v>0.012288</v>
+        <v>0.012328</v>
       </c>
       <c r="C433" t="n">
         <v>0.853723</v>
@@ -6056,7 +6056,7 @@
         </is>
       </c>
       <c r="B434" t="n">
-        <v>0.012637</v>
+        <v>0.012916</v>
       </c>
       <c r="C434" t="n">
         <v>0.851064</v>
@@ -6069,7 +6069,7 @@
         </is>
       </c>
       <c r="B435" t="n">
-        <v>0.012911</v>
+        <v>0.012968</v>
       </c>
       <c r="C435" t="n">
         <v>0.848404</v>
@@ -6082,7 +6082,7 @@
         </is>
       </c>
       <c r="B436" t="n">
-        <v>0.01311</v>
+        <v>0.013139</v>
       </c>
       <c r="C436" t="n">
         <v>0.845745</v>
@@ -6095,7 +6095,7 @@
         </is>
       </c>
       <c r="B437" t="n">
-        <v>0.013435</v>
+        <v>0.013563</v>
       </c>
       <c r="C437" t="n">
         <v>0.843085</v>
@@ -6108,7 +6108,7 @@
         </is>
       </c>
       <c r="B438" t="n">
-        <v>0.01364</v>
+        <v>0.013722</v>
       </c>
       <c r="C438" t="n">
         <v>0.840426</v>
@@ -6121,7 +6121,7 @@
         </is>
       </c>
       <c r="B439" t="n">
-        <v>0.013653</v>
+        <v>0.013765</v>
       </c>
       <c r="C439" t="n">
         <v>0.837766</v>
@@ -6134,7 +6134,7 @@
         </is>
       </c>
       <c r="B440" t="n">
-        <v>0.014212</v>
+        <v>0.014247</v>
       </c>
       <c r="C440" t="n">
         <v>0.835106</v>
@@ -6147,7 +6147,7 @@
         </is>
       </c>
       <c r="B441" t="n">
-        <v>0.014219</v>
+        <v>0.014346</v>
       </c>
       <c r="C441" t="n">
         <v>0.832447</v>
@@ -6160,7 +6160,7 @@
         </is>
       </c>
       <c r="B442" t="n">
-        <v>0.014468</v>
+        <v>0.014559</v>
       </c>
       <c r="C442" t="n">
         <v>0.8297870000000001</v>
@@ -6173,7 +6173,7 @@
         </is>
       </c>
       <c r="B443" t="n">
-        <v>0.014515</v>
+        <v>0.014872</v>
       </c>
       <c r="C443" t="n">
         <v>0.827128</v>
@@ -6186,7 +6186,7 @@
         </is>
       </c>
       <c r="B444" t="n">
-        <v>0.01482</v>
+        <v>0.015136</v>
       </c>
       <c r="C444" t="n">
         <v>0.824468</v>
@@ -6199,7 +6199,7 @@
         </is>
       </c>
       <c r="B445" t="n">
-        <v>0.015057</v>
+        <v>0.015375</v>
       </c>
       <c r="C445" t="n">
         <v>0.821809</v>
@@ -6212,7 +6212,7 @@
         </is>
       </c>
       <c r="B446" t="n">
-        <v>0.015242</v>
+        <v>0.015533</v>
       </c>
       <c r="C446" t="n">
         <v>0.819149</v>
@@ -6225,7 +6225,7 @@
         </is>
       </c>
       <c r="B447" t="n">
-        <v>0.015551</v>
+        <v>0.015621</v>
       </c>
       <c r="C447" t="n">
         <v>0.816489</v>
@@ -6238,7 +6238,7 @@
         </is>
       </c>
       <c r="B448" t="n">
-        <v>0.015605</v>
+        <v>0.015719</v>
       </c>
       <c r="C448" t="n">
         <v>0.8138300000000001</v>
@@ -6251,7 +6251,7 @@
         </is>
       </c>
       <c r="B449" t="n">
-        <v>0.015807</v>
+        <v>0.015834</v>
       </c>
       <c r="C449" t="n">
         <v>0.8111699999999999</v>
@@ -6264,7 +6264,7 @@
         </is>
       </c>
       <c r="B450" t="n">
-        <v>0.015812</v>
+        <v>0.015849</v>
       </c>
       <c r="C450" t="n">
         <v>0.808511</v>
@@ -6277,7 +6277,7 @@
         </is>
       </c>
       <c r="B451" t="n">
-        <v>0.016268</v>
+        <v>0.016375</v>
       </c>
       <c r="C451" t="n">
         <v>0.805851</v>
@@ -6290,7 +6290,7 @@
         </is>
       </c>
       <c r="B452" t="n">
-        <v>0.016444</v>
+        <v>0.016566</v>
       </c>
       <c r="C452" t="n">
         <v>0.803191</v>
@@ -6303,7 +6303,7 @@
         </is>
       </c>
       <c r="B453" t="n">
-        <v>0.016539</v>
+        <v>0.016636</v>
       </c>
       <c r="C453" t="n">
         <v>0.800532</v>
@@ -6316,7 +6316,7 @@
         </is>
       </c>
       <c r="B454" t="n">
-        <v>0.017115</v>
+        <v>0.017188</v>
       </c>
       <c r="C454" t="n">
         <v>0.797872</v>
@@ -6329,7 +6329,7 @@
         </is>
       </c>
       <c r="B455" t="n">
-        <v>0.017277</v>
+        <v>0.017342</v>
       </c>
       <c r="C455" t="n">
         <v>0.7952129999999999</v>
@@ -6342,7 +6342,7 @@
         </is>
       </c>
       <c r="B456" t="n">
-        <v>0.017338</v>
+        <v>0.017487</v>
       </c>
       <c r="C456" t="n">
         <v>0.792553</v>
@@ -6355,7 +6355,7 @@
         </is>
       </c>
       <c r="B457" t="n">
-        <v>0.017858</v>
+        <v>0.017958</v>
       </c>
       <c r="C457" t="n">
         <v>0.789894</v>
@@ -6368,7 +6368,7 @@
         </is>
       </c>
       <c r="B458" t="n">
-        <v>0.017967</v>
+        <v>0.018059</v>
       </c>
       <c r="C458" t="n">
         <v>0.787234</v>
@@ -6381,7 +6381,7 @@
         </is>
       </c>
       <c r="B459" t="n">
-        <v>0.01822</v>
+        <v>0.018334</v>
       </c>
       <c r="C459" t="n">
         <v>0.784574</v>
@@ -6394,7 +6394,7 @@
         </is>
       </c>
       <c r="B460" t="n">
-        <v>0.018507</v>
+        <v>0.01853</v>
       </c>
       <c r="C460" t="n">
         <v>0.781915</v>
@@ -6407,7 +6407,7 @@
         </is>
       </c>
       <c r="B461" t="n">
-        <v>0.018573</v>
+        <v>0.018599</v>
       </c>
       <c r="C461" t="n">
         <v>0.779255</v>
@@ -6420,7 +6420,7 @@
         </is>
       </c>
       <c r="B462" t="n">
-        <v>0.018744</v>
+        <v>0.01895</v>
       </c>
       <c r="C462" t="n">
         <v>0.776596</v>
@@ -6433,7 +6433,7 @@
         </is>
       </c>
       <c r="B463" t="n">
-        <v>0.018963</v>
+        <v>0.019085</v>
       </c>
       <c r="C463" t="n">
         <v>0.773936</v>
@@ -6446,7 +6446,7 @@
         </is>
       </c>
       <c r="B464" t="n">
-        <v>0.019795</v>
+        <v>0.019822</v>
       </c>
       <c r="C464" t="n">
         <v>0.771277</v>
@@ -6459,7 +6459,7 @@
         </is>
       </c>
       <c r="B465" t="n">
-        <v>0.020081</v>
+        <v>0.020147</v>
       </c>
       <c r="C465" t="n">
         <v>0.768617</v>
@@ -6472,7 +6472,7 @@
         </is>
       </c>
       <c r="B466" t="n">
-        <v>0.020394</v>
+        <v>0.020656</v>
       </c>
       <c r="C466" t="n">
         <v>0.765957</v>
@@ -6485,7 +6485,7 @@
         </is>
       </c>
       <c r="B467" t="n">
-        <v>0.021001</v>
+        <v>0.021044</v>
       </c>
       <c r="C467" t="n">
         <v>0.763298</v>
@@ -6498,7 +6498,7 @@
         </is>
       </c>
       <c r="B468" t="n">
-        <v>0.021092</v>
+        <v>0.021199</v>
       </c>
       <c r="C468" t="n">
         <v>0.760638</v>
@@ -6511,7 +6511,7 @@
         </is>
       </c>
       <c r="B469" t="n">
-        <v>0.021381</v>
+        <v>0.021496</v>
       </c>
       <c r="C469" t="n">
         <v>0.757979</v>
@@ -6524,7 +6524,7 @@
         </is>
       </c>
       <c r="B470" t="n">
-        <v>0.021441</v>
+        <v>0.021614</v>
       </c>
       <c r="C470" t="n">
         <v>0.755319</v>
@@ -6537,7 +6537,7 @@
         </is>
       </c>
       <c r="B471" t="n">
-        <v>0.02146</v>
+        <v>0.021635</v>
       </c>
       <c r="C471" t="n">
         <v>0.75266</v>
@@ -6550,7 +6550,7 @@
         </is>
       </c>
       <c r="B472" t="n">
-        <v>0.021512</v>
+        <v>0.021716</v>
       </c>
       <c r="C472" t="n">
         <v>0.75</v>
@@ -6563,7 +6563,7 @@
         </is>
       </c>
       <c r="B473" t="n">
-        <v>0.022551</v>
+        <v>0.022799</v>
       </c>
       <c r="C473" t="n">
         <v>0.74734</v>
@@ -6576,7 +6576,7 @@
         </is>
       </c>
       <c r="B474" t="n">
-        <v>0.022662</v>
+        <v>0.022832</v>
       </c>
       <c r="C474" t="n">
         <v>0.744681</v>
@@ -6589,7 +6589,7 @@
         </is>
       </c>
       <c r="B475" t="n">
-        <v>0.022744</v>
+        <v>0.022946</v>
       </c>
       <c r="C475" t="n">
         <v>0.742021</v>
@@ -6602,7 +6602,7 @@
         </is>
       </c>
       <c r="B476" t="n">
-        <v>0.023153</v>
+        <v>0.023224</v>
       </c>
       <c r="C476" t="n">
         <v>0.739362</v>
@@ -6615,7 +6615,7 @@
         </is>
       </c>
       <c r="B477" t="n">
-        <v>0.023212</v>
+        <v>0.023291</v>
       </c>
       <c r="C477" t="n">
         <v>0.736702</v>
@@ -6628,7 +6628,7 @@
         </is>
       </c>
       <c r="B478" t="n">
-        <v>0.023288</v>
+        <v>0.023574</v>
       </c>
       <c r="C478" t="n">
         <v>0.734043</v>
@@ -6641,7 +6641,7 @@
         </is>
       </c>
       <c r="B479" t="n">
-        <v>0.023356</v>
+        <v>0.023792</v>
       </c>
       <c r="C479" t="n">
         <v>0.731383</v>
@@ -6654,7 +6654,7 @@
         </is>
       </c>
       <c r="B480" t="n">
-        <v>0.023722</v>
+        <v>0.023874</v>
       </c>
       <c r="C480" t="n">
         <v>0.728723</v>
@@ -6667,7 +6667,7 @@
         </is>
       </c>
       <c r="B481" t="n">
-        <v>0.024008</v>
+        <v>0.024054</v>
       </c>
       <c r="C481" t="n">
         <v>0.726064</v>
@@ -6680,7 +6680,7 @@
         </is>
       </c>
       <c r="B482" t="n">
-        <v>0.024171</v>
+        <v>0.024441</v>
       </c>
       <c r="C482" t="n">
         <v>0.723404</v>
@@ -6693,7 +6693,7 @@
         </is>
       </c>
       <c r="B483" t="n">
-        <v>0.024785</v>
+        <v>0.024979</v>
       </c>
       <c r="C483" t="n">
         <v>0.720745</v>
@@ -6706,7 +6706,7 @@
         </is>
       </c>
       <c r="B484" t="n">
-        <v>0.024827</v>
+        <v>0.025105</v>
       </c>
       <c r="C484" t="n">
         <v>0.718085</v>
@@ -6719,7 +6719,7 @@
         </is>
       </c>
       <c r="B485" t="n">
-        <v>0.024936</v>
+        <v>0.025163</v>
       </c>
       <c r="C485" t="n">
         <v>0.715426</v>
@@ -6732,7 +6732,7 @@
         </is>
       </c>
       <c r="B486" t="n">
-        <v>0.024967</v>
+        <v>0.0252</v>
       </c>
       <c r="C486" t="n">
         <v>0.712766</v>
@@ -6745,7 +6745,7 @@
         </is>
       </c>
       <c r="B487" t="n">
-        <v>0.025068</v>
+        <v>0.025374</v>
       </c>
       <c r="C487" t="n">
         <v>0.710106</v>
@@ -6758,7 +6758,7 @@
         </is>
       </c>
       <c r="B488" t="n">
-        <v>0.025482</v>
+        <v>0.025579</v>
       </c>
       <c r="C488" t="n">
         <v>0.707447</v>
@@ -6771,7 +6771,7 @@
         </is>
       </c>
       <c r="B489" t="n">
-        <v>0.025736</v>
+        <v>0.025993</v>
       </c>
       <c r="C489" t="n">
         <v>0.7047870000000001</v>
@@ -6784,7 +6784,7 @@
         </is>
       </c>
       <c r="B490" t="n">
-        <v>0.025958</v>
+        <v>0.026113</v>
       </c>
       <c r="C490" t="n">
         <v>0.702128</v>
@@ -6797,7 +6797,7 @@
         </is>
       </c>
       <c r="B491" t="n">
-        <v>0.026223</v>
+        <v>0.026293</v>
       </c>
       <c r="C491" t="n">
         <v>0.699468</v>
@@ -6810,7 +6810,7 @@
         </is>
       </c>
       <c r="B492" t="n">
-        <v>0.026672</v>
+        <v>0.026753</v>
       </c>
       <c r="C492" t="n">
         <v>0.696809</v>
@@ -6823,7 +6823,7 @@
         </is>
       </c>
       <c r="B493" t="n">
-        <v>0.026682</v>
+        <v>0.026797</v>
       </c>
       <c r="C493" t="n">
         <v>0.694149</v>
@@ -6836,7 +6836,7 @@
         </is>
       </c>
       <c r="B494" t="n">
-        <v>0.026685</v>
+        <v>0.026823</v>
       </c>
       <c r="C494" t="n">
         <v>0.691489</v>
@@ -6849,7 +6849,7 @@
         </is>
       </c>
       <c r="B495" t="n">
-        <v>0.026725</v>
+        <v>0.026901</v>
       </c>
       <c r="C495" t="n">
         <v>0.6888300000000001</v>
@@ -6862,7 +6862,7 @@
         </is>
       </c>
       <c r="B496" t="n">
-        <v>0.026811</v>
+        <v>0.026916</v>
       </c>
       <c r="C496" t="n">
         <v>0.6861699999999999</v>
@@ -6875,7 +6875,7 @@
         </is>
       </c>
       <c r="B497" t="n">
-        <v>0.027014</v>
+        <v>0.027315</v>
       </c>
       <c r="C497" t="n">
         <v>0.683511</v>
@@ -6888,7 +6888,7 @@
         </is>
       </c>
       <c r="B498" t="n">
-        <v>0.027315</v>
+        <v>0.027458</v>
       </c>
       <c r="C498" t="n">
         <v>0.680851</v>
@@ -6901,7 +6901,7 @@
         </is>
       </c>
       <c r="B499" t="n">
-        <v>0.027652</v>
+        <v>0.027772</v>
       </c>
       <c r="C499" t="n">
         <v>0.678191</v>
@@ -6914,7 +6914,7 @@
         </is>
       </c>
       <c r="B500" t="n">
-        <v>0.028331</v>
+        <v>0.028383</v>
       </c>
       <c r="C500" t="n">
         <v>0.675532</v>
@@ -6927,7 +6927,7 @@
         </is>
       </c>
       <c r="B501" t="n">
-        <v>0.028362</v>
+        <v>0.028621</v>
       </c>
       <c r="C501" t="n">
         <v>0.672872</v>
@@ -6940,7 +6940,7 @@
         </is>
       </c>
       <c r="B502" t="n">
-        <v>0.028919</v>
+        <v>0.029165</v>
       </c>
       <c r="C502" t="n">
         <v>0.6702129999999999</v>
@@ -6953,7 +6953,7 @@
         </is>
       </c>
       <c r="B503" t="n">
-        <v>0.029011</v>
+        <v>0.029357</v>
       </c>
       <c r="C503" t="n">
         <v>0.667553</v>
@@ -6966,7 +6966,7 @@
         </is>
       </c>
       <c r="B504" t="n">
-        <v>0.029333</v>
+        <v>0.029654</v>
       </c>
       <c r="C504" t="n">
         <v>0.664894</v>
@@ -6979,7 +6979,7 @@
         </is>
       </c>
       <c r="B505" t="n">
-        <v>0.029651</v>
+        <v>0.029681</v>
       </c>
       <c r="C505" t="n">
         <v>0.662234</v>
@@ -6992,7 +6992,7 @@
         </is>
       </c>
       <c r="B506" t="n">
-        <v>0.030432</v>
+        <v>0.030513</v>
       </c>
       <c r="C506" t="n">
         <v>0.659574</v>
@@ -7005,7 +7005,7 @@
         </is>
       </c>
       <c r="B507" t="n">
-        <v>0.030582</v>
+        <v>0.030651</v>
       </c>
       <c r="C507" t="n">
         <v>0.656915</v>
@@ -7018,7 +7018,7 @@
         </is>
       </c>
       <c r="B508" t="n">
-        <v>0.03084</v>
+        <v>0.031091</v>
       </c>
       <c r="C508" t="n">
         <v>0.654255</v>
@@ -7031,7 +7031,7 @@
         </is>
       </c>
       <c r="B509" t="n">
-        <v>0.03103</v>
+        <v>0.03114</v>
       </c>
       <c r="C509" t="n">
         <v>0.651596</v>
@@ -7044,7 +7044,7 @@
         </is>
       </c>
       <c r="B510" t="n">
-        <v>0.031347</v>
+        <v>0.031548</v>
       </c>
       <c r="C510" t="n">
         <v>0.648936</v>
@@ -7057,7 +7057,7 @@
         </is>
       </c>
       <c r="B511" t="n">
-        <v>0.031635</v>
+        <v>0.031711</v>
       </c>
       <c r="C511" t="n">
         <v>0.646277</v>
@@ -7070,7 +7070,7 @@
         </is>
       </c>
       <c r="B512" t="n">
-        <v>0.032457</v>
+        <v>0.03257</v>
       </c>
       <c r="C512" t="n">
         <v>0.643617</v>
@@ -7083,7 +7083,7 @@
         </is>
       </c>
       <c r="B513" t="n">
-        <v>0.03256</v>
+        <v>0.032661</v>
       </c>
       <c r="C513" t="n">
         <v>0.640957</v>
@@ -7096,7 +7096,7 @@
         </is>
       </c>
       <c r="B514" t="n">
-        <v>0.032611</v>
+        <v>0.032768</v>
       </c>
       <c r="C514" t="n">
         <v>0.638298</v>
@@ -7109,7 +7109,7 @@
         </is>
       </c>
       <c r="B515" t="n">
-        <v>0.032657</v>
+        <v>0.032826</v>
       </c>
       <c r="C515" t="n">
         <v>0.635638</v>
@@ -7122,7 +7122,7 @@
         </is>
       </c>
       <c r="B516" t="n">
-        <v>0.032713</v>
+        <v>0.032885</v>
       </c>
       <c r="C516" t="n">
         <v>0.632979</v>
@@ -7135,7 +7135,7 @@
         </is>
       </c>
       <c r="B517" t="n">
-        <v>0.03296</v>
+        <v>0.033177</v>
       </c>
       <c r="C517" t="n">
         <v>0.630319</v>
@@ -7148,7 +7148,7 @@
         </is>
       </c>
       <c r="B518" t="n">
-        <v>0.033098</v>
+        <v>0.033253</v>
       </c>
       <c r="C518" t="n">
         <v>0.62766</v>
@@ -7161,7 +7161,7 @@
         </is>
       </c>
       <c r="B519" t="n">
-        <v>0.033505</v>
+        <v>0.033656</v>
       </c>
       <c r="C519" t="n">
         <v>0.625</v>
@@ -7174,7 +7174,7 @@
         </is>
       </c>
       <c r="B520" t="n">
-        <v>0.033512</v>
+        <v>0.033976</v>
       </c>
       <c r="C520" t="n">
         <v>0.62234</v>
@@ -7187,7 +7187,7 @@
         </is>
       </c>
       <c r="B521" t="n">
-        <v>0.033831</v>
+        <v>0.034025</v>
       </c>
       <c r="C521" t="n">
         <v>0.619681</v>
@@ -7200,7 +7200,7 @@
         </is>
       </c>
       <c r="B522" t="n">
-        <v>0.033849</v>
+        <v>0.034262</v>
       </c>
       <c r="C522" t="n">
         <v>0.617021</v>
@@ -7213,7 +7213,7 @@
         </is>
       </c>
       <c r="B523" t="n">
-        <v>0.03407</v>
+        <v>0.034279</v>
       </c>
       <c r="C523" t="n">
         <v>0.614362</v>
@@ -7226,7 +7226,7 @@
         </is>
       </c>
       <c r="B524" t="n">
-        <v>0.034308</v>
+        <v>0.034358</v>
       </c>
       <c r="C524" t="n">
         <v>0.611702</v>
@@ -7239,7 +7239,7 @@
         </is>
       </c>
       <c r="B525" t="n">
-        <v>0.034363</v>
+        <v>0.03454</v>
       </c>
       <c r="C525" t="n">
         <v>0.609043</v>
@@ -7252,7 +7252,7 @@
         </is>
       </c>
       <c r="B526" t="n">
-        <v>0.034589</v>
+        <v>0.034785</v>
       </c>
       <c r="C526" t="n">
         <v>0.606383</v>
@@ -7265,7 +7265,7 @@
         </is>
       </c>
       <c r="B527" t="n">
-        <v>0.034846</v>
+        <v>0.035007</v>
       </c>
       <c r="C527" t="n">
         <v>0.603723</v>
@@ -7278,7 +7278,7 @@
         </is>
       </c>
       <c r="B528" t="n">
-        <v>0.035044</v>
+        <v>0.035267</v>
       </c>
       <c r="C528" t="n">
         <v>0.601064</v>
@@ -7291,7 +7291,7 @@
         </is>
       </c>
       <c r="B529" t="n">
-        <v>0.035505</v>
+        <v>0.035602</v>
       </c>
       <c r="C529" t="n">
         <v>0.598404</v>
@@ -7304,7 +7304,7 @@
         </is>
       </c>
       <c r="B530" t="n">
-        <v>0.035755</v>
+        <v>0.035957</v>
       </c>
       <c r="C530" t="n">
         <v>0.595745</v>
@@ -7317,7 +7317,7 @@
         </is>
       </c>
       <c r="B531" t="n">
-        <v>0.036053</v>
+        <v>0.036431</v>
       </c>
       <c r="C531" t="n">
         <v>0.593085</v>
@@ -7330,7 +7330,7 @@
         </is>
       </c>
       <c r="B532" t="n">
-        <v>0.036614</v>
+        <v>0.037036</v>
       </c>
       <c r="C532" t="n">
         <v>0.590426</v>
@@ -7343,7 +7343,7 @@
         </is>
       </c>
       <c r="B533" t="n">
-        <v>0.036735</v>
+        <v>0.037079</v>
       </c>
       <c r="C533" t="n">
         <v>0.587766</v>
@@ -7356,7 +7356,7 @@
         </is>
       </c>
       <c r="B534" t="n">
-        <v>0.03694</v>
+        <v>0.037112</v>
       </c>
       <c r="C534" t="n">
         <v>0.585106</v>
@@ -7369,7 +7369,7 @@
         </is>
       </c>
       <c r="B535" t="n">
-        <v>0.03736</v>
+        <v>0.037437</v>
       </c>
       <c r="C535" t="n">
         <v>0.582447</v>
@@ -7382,7 +7382,7 @@
         </is>
       </c>
       <c r="B536" t="n">
-        <v>0.037384</v>
+        <v>0.037486</v>
       </c>
       <c r="C536" t="n">
         <v>0.5797870000000001</v>
@@ -7395,7 +7395,7 @@
         </is>
       </c>
       <c r="B537" t="n">
-        <v>0.037424</v>
+        <v>0.037751</v>
       </c>
       <c r="C537" t="n">
         <v>0.577128</v>
@@ -7408,7 +7408,7 @@
         </is>
       </c>
       <c r="B538" t="n">
-        <v>0.037477</v>
+        <v>0.03778</v>
       </c>
       <c r="C538" t="n">
         <v>0.574468</v>
@@ -7421,7 +7421,7 @@
         </is>
       </c>
       <c r="B539" t="n">
-        <v>0.037512</v>
+        <v>0.037786</v>
       </c>
       <c r="C539" t="n">
         <v>0.571809</v>
@@ -7434,7 +7434,7 @@
         </is>
       </c>
       <c r="B540" t="n">
-        <v>0.037789</v>
+        <v>0.038034</v>
       </c>
       <c r="C540" t="n">
         <v>0.569149</v>
@@ -7447,7 +7447,7 @@
         </is>
       </c>
       <c r="B541" t="n">
-        <v>0.037817</v>
+        <v>0.038055</v>
       </c>
       <c r="C541" t="n">
         <v>0.566489</v>
@@ -7460,7 +7460,7 @@
         </is>
       </c>
       <c r="B542" t="n">
-        <v>0.037854</v>
+        <v>0.038074</v>
       </c>
       <c r="C542" t="n">
         <v>0.5638300000000001</v>
@@ -7473,7 +7473,7 @@
         </is>
       </c>
       <c r="B543" t="n">
-        <v>0.038305</v>
+        <v>0.038555</v>
       </c>
       <c r="C543" t="n">
         <v>0.5611699999999999</v>
@@ -7486,7 +7486,7 @@
         </is>
       </c>
       <c r="B544" t="n">
-        <v>0.038561</v>
+        <v>0.038801</v>
       </c>
       <c r="C544" t="n">
         <v>0.558511</v>
@@ -7499,7 +7499,7 @@
         </is>
       </c>
       <c r="B545" t="n">
-        <v>0.038598</v>
+        <v>0.038806</v>
       </c>
       <c r="C545" t="n">
         <v>0.555851</v>
@@ -7512,7 +7512,7 @@
         </is>
       </c>
       <c r="B546" t="n">
-        <v>0.038709</v>
+        <v>0.038976</v>
       </c>
       <c r="C546" t="n">
         <v>0.553191</v>
@@ -7525,7 +7525,7 @@
         </is>
       </c>
       <c r="B547" t="n">
-        <v>0.038758</v>
+        <v>0.038998</v>
       </c>
       <c r="C547" t="n">
         <v>0.550532</v>
@@ -7538,7 +7538,7 @@
         </is>
       </c>
       <c r="B548" t="n">
-        <v>0.038812</v>
+        <v>0.039036</v>
       </c>
       <c r="C548" t="n">
         <v>0.547872</v>
@@ -7551,7 +7551,7 @@
         </is>
       </c>
       <c r="B549" t="n">
-        <v>0.039104</v>
+        <v>0.039362</v>
       </c>
       <c r="C549" t="n">
         <v>0.5452129999999999</v>
@@ -7564,7 +7564,7 @@
         </is>
       </c>
       <c r="B550" t="n">
-        <v>0.039326</v>
+        <v>0.039523</v>
       </c>
       <c r="C550" t="n">
         <v>0.542553</v>
@@ -7577,7 +7577,7 @@
         </is>
       </c>
       <c r="B551" t="n">
-        <v>0.039507</v>
+        <v>0.039742</v>
       </c>
       <c r="C551" t="n">
         <v>0.539894</v>
@@ -7590,7 +7590,7 @@
         </is>
       </c>
       <c r="B552" t="n">
-        <v>0.04032</v>
+        <v>0.040422</v>
       </c>
       <c r="C552" t="n">
         <v>0.537234</v>
@@ -7603,7 +7603,7 @@
         </is>
       </c>
       <c r="B553" t="n">
-        <v>0.041106</v>
+        <v>0.041295</v>
       </c>
       <c r="C553" t="n">
         <v>0.534574</v>
@@ -7616,7 +7616,7 @@
         </is>
       </c>
       <c r="B554" t="n">
-        <v>0.041151</v>
+        <v>0.041335</v>
       </c>
       <c r="C554" t="n">
         <v>0.531915</v>
@@ -7629,7 +7629,7 @@
         </is>
       </c>
       <c r="B555" t="n">
-        <v>0.041223</v>
+        <v>0.041513</v>
       </c>
       <c r="C555" t="n">
         <v>0.529255</v>
@@ -7642,7 +7642,7 @@
         </is>
       </c>
       <c r="B556" t="n">
-        <v>0.041289</v>
+        <v>0.041657</v>
       </c>
       <c r="C556" t="n">
         <v>0.526596</v>
@@ -7655,7 +7655,7 @@
         </is>
       </c>
       <c r="B557" t="n">
-        <v>0.041439</v>
+        <v>0.041738</v>
       </c>
       <c r="C557" t="n">
         <v>0.523936</v>
@@ -7668,7 +7668,7 @@
         </is>
       </c>
       <c r="B558" t="n">
-        <v>0.041725</v>
+        <v>0.042055</v>
       </c>
       <c r="C558" t="n">
         <v>0.521277</v>
@@ -7681,7 +7681,7 @@
         </is>
       </c>
       <c r="B559" t="n">
-        <v>0.041859</v>
+        <v>0.042323</v>
       </c>
       <c r="C559" t="n">
         <v>0.518617</v>
@@ -7694,7 +7694,7 @@
         </is>
       </c>
       <c r="B560" t="n">
-        <v>0.04222</v>
+        <v>0.042331</v>
       </c>
       <c r="C560" t="n">
         <v>0.515957</v>
@@ -7707,7 +7707,7 @@
         </is>
       </c>
       <c r="B561" t="n">
-        <v>0.042501</v>
+        <v>0.042796</v>
       </c>
       <c r="C561" t="n">
         <v>0.513298</v>
@@ -7720,7 +7720,7 @@
         </is>
       </c>
       <c r="B562" t="n">
-        <v>0.042556</v>
+        <v>0.042848</v>
       </c>
       <c r="C562" t="n">
         <v>0.510638</v>
@@ -7733,7 +7733,7 @@
         </is>
       </c>
       <c r="B563" t="n">
-        <v>0.042656</v>
+        <v>0.043897</v>
       </c>
       <c r="C563" t="n">
         <v>0.507979</v>
@@ -7746,7 +7746,7 @@
         </is>
       </c>
       <c r="B564" t="n">
-        <v>0.043746</v>
+        <v>0.044517</v>
       </c>
       <c r="C564" t="n">
         <v>0.505319</v>
@@ -7759,7 +7759,7 @@
         </is>
       </c>
       <c r="B565" t="n">
-        <v>0.044096</v>
+        <v>0.044604</v>
       </c>
       <c r="C565" t="n">
         <v>0.50266</v>
@@ -7772,7 +7772,7 @@
         </is>
       </c>
       <c r="B566" t="n">
-        <v>0.04418</v>
+        <v>0.044792</v>
       </c>
       <c r="C566" t="n">
         <v>0.5</v>
@@ -7785,7 +7785,7 @@
         </is>
       </c>
       <c r="B567" t="n">
-        <v>0.044394</v>
+        <v>0.04488</v>
       </c>
       <c r="C567" t="n">
         <v>0.49734</v>
@@ -7798,7 +7798,7 @@
         </is>
       </c>
       <c r="B568" t="n">
-        <v>0.044743</v>
+        <v>0.045184</v>
       </c>
       <c r="C568" t="n">
         <v>0.494681</v>
@@ -7811,7 +7811,7 @@
         </is>
       </c>
       <c r="B569" t="n">
-        <v>0.046063</v>
+        <v>0.046119</v>
       </c>
       <c r="C569" t="n">
         <v>0.492021</v>
@@ -7824,7 +7824,7 @@
         </is>
       </c>
       <c r="B570" t="n">
-        <v>0.046069</v>
+        <v>0.046334</v>
       </c>
       <c r="C570" t="n">
         <v>0.489362</v>
@@ -7837,7 +7837,7 @@
         </is>
       </c>
       <c r="B571" t="n">
-        <v>0.046333</v>
+        <v>0.046481</v>
       </c>
       <c r="C571" t="n">
         <v>0.486702</v>
@@ -7850,7 +7850,7 @@
         </is>
       </c>
       <c r="B572" t="n">
-        <v>0.046381</v>
+        <v>0.046566</v>
       </c>
       <c r="C572" t="n">
         <v>0.484043</v>
@@ -7863,7 +7863,7 @@
         </is>
       </c>
       <c r="B573" t="n">
-        <v>0.046489</v>
+        <v>0.046595</v>
       </c>
       <c r="C573" t="n">
         <v>0.481383</v>
@@ -7876,7 +7876,7 @@
         </is>
       </c>
       <c r="B574" t="n">
-        <v>0.047133</v>
+        <v>0.0477</v>
       </c>
       <c r="C574" t="n">
         <v>0.478723</v>
@@ -7889,7 +7889,7 @@
         </is>
       </c>
       <c r="B575" t="n">
-        <v>0.047557</v>
+        <v>0.047706</v>
       </c>
       <c r="C575" t="n">
         <v>0.476064</v>
@@ -7902,7 +7902,7 @@
         </is>
       </c>
       <c r="B576" t="n">
-        <v>0.047665</v>
+        <v>0.047948</v>
       </c>
       <c r="C576" t="n">
         <v>0.473404</v>
@@ -7915,7 +7915,7 @@
         </is>
       </c>
       <c r="B577" t="n">
-        <v>0.047694</v>
+        <v>0.048396</v>
       </c>
       <c r="C577" t="n">
         <v>0.470745</v>
@@ -7928,7 +7928,7 @@
         </is>
       </c>
       <c r="B578" t="n">
-        <v>0.048177</v>
+        <v>0.048527</v>
       </c>
       <c r="C578" t="n">
         <v>0.468085</v>
@@ -7941,7 +7941,7 @@
         </is>
       </c>
       <c r="B579" t="n">
-        <v>0.048363</v>
+        <v>0.048587</v>
       </c>
       <c r="C579" t="n">
         <v>0.465426</v>
@@ -7954,7 +7954,7 @@
         </is>
       </c>
       <c r="B580" t="n">
-        <v>0.04874</v>
+        <v>0.048976</v>
       </c>
       <c r="C580" t="n">
         <v>0.462766</v>
@@ -7967,7 +7967,7 @@
         </is>
       </c>
       <c r="B581" t="n">
-        <v>0.049562</v>
+        <v>0.049931</v>
       </c>
       <c r="C581" t="n">
         <v>0.460106</v>
@@ -7980,7 +7980,7 @@
         </is>
       </c>
       <c r="B582" t="n">
-        <v>0.04982</v>
+        <v>0.050274</v>
       </c>
       <c r="C582" t="n">
         <v>0.457447</v>
@@ -7993,7 +7993,7 @@
         </is>
       </c>
       <c r="B583" t="n">
-        <v>0.050252</v>
+        <v>0.050554</v>
       </c>
       <c r="C583" t="n">
         <v>0.454787</v>
@@ -8006,7 +8006,7 @@
         </is>
       </c>
       <c r="B584" t="n">
-        <v>0.050856</v>
+        <v>0.050986</v>
       </c>
       <c r="C584" t="n">
         <v>0.452128</v>
@@ -8019,7 +8019,7 @@
         </is>
       </c>
       <c r="B585" t="n">
-        <v>0.050865</v>
+        <v>0.051099</v>
       </c>
       <c r="C585" t="n">
         <v>0.449468</v>
@@ -8032,7 +8032,7 @@
         </is>
       </c>
       <c r="B586" t="n">
-        <v>0.051296</v>
+        <v>0.051498</v>
       </c>
       <c r="C586" t="n">
         <v>0.446809</v>
@@ -8045,7 +8045,7 @@
         </is>
       </c>
       <c r="B587" t="n">
-        <v>0.051428</v>
+        <v>0.051636</v>
       </c>
       <c r="C587" t="n">
         <v>0.444149</v>
@@ -8058,7 +8058,7 @@
         </is>
       </c>
       <c r="B588" t="n">
-        <v>0.051806</v>
+        <v>0.05196</v>
       </c>
       <c r="C588" t="n">
         <v>0.441489</v>
@@ -8071,7 +8071,7 @@
         </is>
       </c>
       <c r="B589" t="n">
-        <v>0.051997</v>
+        <v>0.052149</v>
       </c>
       <c r="C589" t="n">
         <v>0.43883</v>
@@ -8084,7 +8084,7 @@
         </is>
       </c>
       <c r="B590" t="n">
-        <v>0.052056</v>
+        <v>0.052174</v>
       </c>
       <c r="C590" t="n">
         <v>0.43617</v>
@@ -8097,7 +8097,7 @@
         </is>
       </c>
       <c r="B591" t="n">
-        <v>0.052131</v>
+        <v>0.052306</v>
       </c>
       <c r="C591" t="n">
         <v>0.433511</v>
@@ -8110,7 +8110,7 @@
         </is>
       </c>
       <c r="B592" t="n">
-        <v>0.052233</v>
+        <v>0.052566</v>
       </c>
       <c r="C592" t="n">
         <v>0.430851</v>
@@ -8123,7 +8123,7 @@
         </is>
       </c>
       <c r="B593" t="n">
-        <v>0.053396</v>
+        <v>0.053421</v>
       </c>
       <c r="C593" t="n">
         <v>0.428191</v>
@@ -8136,7 +8136,7 @@
         </is>
       </c>
       <c r="B594" t="n">
-        <v>0.053713</v>
+        <v>0.054249</v>
       </c>
       <c r="C594" t="n">
         <v>0.425532</v>
@@ -8149,7 +8149,7 @@
         </is>
       </c>
       <c r="B595" t="n">
-        <v>0.054187</v>
+        <v>0.054469</v>
       </c>
       <c r="C595" t="n">
         <v>0.422872</v>
@@ -8162,7 +8162,7 @@
         </is>
       </c>
       <c r="B596" t="n">
-        <v>0.054452</v>
+        <v>0.054647</v>
       </c>
       <c r="C596" t="n">
         <v>0.420213</v>
@@ -8175,7 +8175,7 @@
         </is>
       </c>
       <c r="B597" t="n">
-        <v>0.054472</v>
+        <v>0.054803</v>
       </c>
       <c r="C597" t="n">
         <v>0.417553</v>
@@ -8188,7 +8188,7 @@
         </is>
       </c>
       <c r="B598" t="n">
-        <v>0.056192</v>
+        <v>0.05631</v>
       </c>
       <c r="C598" t="n">
         <v>0.414894</v>
@@ -8201,7 +8201,7 @@
         </is>
       </c>
       <c r="B599" t="n">
-        <v>0.056663</v>
+        <v>0.057265</v>
       </c>
       <c r="C599" t="n">
         <v>0.412234</v>
@@ -8214,7 +8214,7 @@
         </is>
       </c>
       <c r="B600" t="n">
-        <v>0.056973</v>
+        <v>0.057486</v>
       </c>
       <c r="C600" t="n">
         <v>0.409574</v>
@@ -8227,7 +8227,7 @@
         </is>
       </c>
       <c r="B601" t="n">
-        <v>0.058612</v>
+        <v>0.059105</v>
       </c>
       <c r="C601" t="n">
         <v>0.406915</v>
@@ -8240,7 +8240,7 @@
         </is>
       </c>
       <c r="B602" t="n">
-        <v>0.058652</v>
+        <v>0.059106</v>
       </c>
       <c r="C602" t="n">
         <v>0.404255</v>
@@ -8253,7 +8253,7 @@
         </is>
       </c>
       <c r="B603" t="n">
-        <v>0.059429</v>
+        <v>0.059827</v>
       </c>
       <c r="C603" t="n">
         <v>0.401596</v>
@@ -8266,7 +8266,7 @@
         </is>
       </c>
       <c r="B604" t="n">
-        <v>0.059609</v>
+        <v>0.059954</v>
       </c>
       <c r="C604" t="n">
         <v>0.398936</v>
@@ -8279,7 +8279,7 @@
         </is>
       </c>
       <c r="B605" t="n">
-        <v>0.060035</v>
+        <v>0.06015</v>
       </c>
       <c r="C605" t="n">
         <v>0.396277</v>
@@ -8292,7 +8292,7 @@
         </is>
       </c>
       <c r="B606" t="n">
-        <v>0.060241</v>
+        <v>0.060828</v>
       </c>
       <c r="C606" t="n">
         <v>0.393617</v>
@@ -8305,7 +8305,7 @@
         </is>
       </c>
       <c r="B607" t="n">
-        <v>0.060491</v>
+        <v>0.060973</v>
       </c>
       <c r="C607" t="n">
         <v>0.390957</v>
@@ -8318,7 +8318,7 @@
         </is>
       </c>
       <c r="B608" t="n">
-        <v>0.061036</v>
+        <v>0.061492</v>
       </c>
       <c r="C608" t="n">
         <v>0.388298</v>
@@ -8331,7 +8331,7 @@
         </is>
       </c>
       <c r="B609" t="n">
-        <v>0.061192</v>
+        <v>0.061675</v>
       </c>
       <c r="C609" t="n">
         <v>0.385638</v>
@@ -8344,7 +8344,7 @@
         </is>
       </c>
       <c r="B610" t="n">
-        <v>0.061397</v>
+        <v>0.061698</v>
       </c>
       <c r="C610" t="n">
         <v>0.382979</v>
@@ -8357,7 +8357,7 @@
         </is>
       </c>
       <c r="B611" t="n">
-        <v>0.061607</v>
+        <v>0.061947</v>
       </c>
       <c r="C611" t="n">
         <v>0.380319</v>
@@ -8370,7 +8370,7 @@
         </is>
       </c>
       <c r="B612" t="n">
-        <v>0.061785</v>
+        <v>0.062155</v>
       </c>
       <c r="C612" t="n">
         <v>0.37766</v>
@@ -8383,7 +8383,7 @@
         </is>
       </c>
       <c r="B613" t="n">
-        <v>0.061976</v>
+        <v>0.06267399999999999</v>
       </c>
       <c r="C613" t="n">
         <v>0.375</v>
@@ -8396,7 +8396,7 @@
         </is>
       </c>
       <c r="B614" t="n">
-        <v>0.062158</v>
+        <v>0.06274</v>
       </c>
       <c r="C614" t="n">
         <v>0.37234</v>
@@ -8409,7 +8409,7 @@
         </is>
       </c>
       <c r="B615" t="n">
-        <v>0.062285</v>
+        <v>0.062892</v>
       </c>
       <c r="C615" t="n">
         <v>0.369681</v>
@@ -8422,7 +8422,7 @@
         </is>
       </c>
       <c r="B616" t="n">
-        <v>0.06265900000000001</v>
+        <v>0.06310499999999999</v>
       </c>
       <c r="C616" t="n">
         <v>0.367021</v>
@@ -8435,7 +8435,7 @@
         </is>
       </c>
       <c r="B617" t="n">
-        <v>0.062987</v>
+        <v>0.063152</v>
       </c>
       <c r="C617" t="n">
         <v>0.364362</v>
@@ -8448,7 +8448,7 @@
         </is>
       </c>
       <c r="B618" t="n">
-        <v>0.06304899999999999</v>
+        <v>0.06340700000000001</v>
       </c>
       <c r="C618" t="n">
         <v>0.361702</v>
@@ -8461,7 +8461,7 @@
         </is>
       </c>
       <c r="B619" t="n">
-        <v>0.063262</v>
+        <v>0.063926</v>
       </c>
       <c r="C619" t="n">
         <v>0.359043</v>
@@ -8474,7 +8474,7 @@
         </is>
       </c>
       <c r="B620" t="n">
-        <v>0.063774</v>
+        <v>0.064183</v>
       </c>
       <c r="C620" t="n">
         <v>0.356383</v>
@@ -8487,7 +8487,7 @@
         </is>
       </c>
       <c r="B621" t="n">
-        <v>0.064138</v>
+        <v>0.064622</v>
       </c>
       <c r="C621" t="n">
         <v>0.353723</v>
@@ -8500,7 +8500,7 @@
         </is>
       </c>
       <c r="B622" t="n">
-        <v>0.064482</v>
+        <v>0.065391</v>
       </c>
       <c r="C622" t="n">
         <v>0.351064</v>
@@ -8513,7 +8513,7 @@
         </is>
       </c>
       <c r="B623" t="n">
-        <v>0.064771</v>
+        <v>0.06565799999999999</v>
       </c>
       <c r="C623" t="n">
         <v>0.348404</v>
@@ -8526,7 +8526,7 @@
         </is>
       </c>
       <c r="B624" t="n">
-        <v>0.065068</v>
+        <v>0.06615699999999999</v>
       </c>
       <c r="C624" t="n">
         <v>0.345745</v>
@@ -8539,7 +8539,7 @@
         </is>
       </c>
       <c r="B625" t="n">
-        <v>0.06586699999999999</v>
+        <v>0.066275</v>
       </c>
       <c r="C625" t="n">
         <v>0.343085</v>
@@ -8552,7 +8552,7 @@
         </is>
       </c>
       <c r="B626" t="n">
-        <v>0.06605</v>
+        <v>0.06665699999999999</v>
       </c>
       <c r="C626" t="n">
         <v>0.340426</v>
@@ -8565,7 +8565,7 @@
         </is>
       </c>
       <c r="B627" t="n">
-        <v>0.066358</v>
+        <v>0.066718</v>
       </c>
       <c r="C627" t="n">
         <v>0.337766</v>
@@ -8578,7 +8578,7 @@
         </is>
       </c>
       <c r="B628" t="n">
-        <v>0.066555</v>
+        <v>0.066894</v>
       </c>
       <c r="C628" t="n">
         <v>0.335106</v>
@@ -8591,7 +8591,7 @@
         </is>
       </c>
       <c r="B629" t="n">
-        <v>0.06693300000000001</v>
+        <v>0.068062</v>
       </c>
       <c r="C629" t="n">
         <v>0.332447</v>
@@ -8604,7 +8604,7 @@
         </is>
       </c>
       <c r="B630" t="n">
-        <v>0.067597</v>
+        <v>0.06837699999999999</v>
       </c>
       <c r="C630" t="n">
         <v>0.329787</v>
@@ -8617,7 +8617,7 @@
         </is>
       </c>
       <c r="B631" t="n">
-        <v>0.067853</v>
+        <v>0.06851</v>
       </c>
       <c r="C631" t="n">
         <v>0.327128</v>
@@ -8630,7 +8630,7 @@
         </is>
       </c>
       <c r="B632" t="n">
-        <v>0.067968</v>
+        <v>0.068568</v>
       </c>
       <c r="C632" t="n">
         <v>0.324468</v>
@@ -8643,7 +8643,7 @@
         </is>
       </c>
       <c r="B633" t="n">
-        <v>0.068048</v>
+        <v>0.06929299999999999</v>
       </c>
       <c r="C633" t="n">
         <v>0.321809</v>
@@ -8656,7 +8656,7 @@
         </is>
       </c>
       <c r="B634" t="n">
-        <v>0.069186</v>
+        <v>0.06981</v>
       </c>
       <c r="C634" t="n">
         <v>0.319149</v>
@@ -8669,7 +8669,7 @@
         </is>
       </c>
       <c r="B635" t="n">
-        <v>0.06936199999999999</v>
+        <v>0.06990399999999999</v>
       </c>
       <c r="C635" t="n">
         <v>0.316489</v>
@@ -8682,7 +8682,7 @@
         </is>
       </c>
       <c r="B636" t="n">
-        <v>0.07008300000000001</v>
+        <v>0.070462</v>
       </c>
       <c r="C636" t="n">
         <v>0.31383</v>
@@ -8695,7 +8695,7 @@
         </is>
       </c>
       <c r="B637" t="n">
-        <v>0.070171</v>
+        <v>0.07062</v>
       </c>
       <c r="C637" t="n">
         <v>0.31117</v>
@@ -8708,7 +8708,7 @@
         </is>
       </c>
       <c r="B638" t="n">
-        <v>0.07036100000000001</v>
+        <v>0.070713</v>
       </c>
       <c r="C638" t="n">
         <v>0.308511</v>
@@ -8721,7 +8721,7 @@
         </is>
       </c>
       <c r="B639" t="n">
-        <v>0.07054299999999999</v>
+        <v>0.07081899999999999</v>
       </c>
       <c r="C639" t="n">
         <v>0.305851</v>
@@ -8734,7 +8734,7 @@
         </is>
       </c>
       <c r="B640" t="n">
-        <v>0.071228</v>
+        <v>0.071283</v>
       </c>
       <c r="C640" t="n">
         <v>0.303191</v>
@@ -8747,7 +8747,7 @@
         </is>
       </c>
       <c r="B641" t="n">
-        <v>0.071787</v>
+        <v>0.072476</v>
       </c>
       <c r="C641" t="n">
         <v>0.300532</v>
@@ -8760,7 +8760,7 @@
         </is>
       </c>
       <c r="B642" t="n">
-        <v>0.07258299999999999</v>
+        <v>0.07283100000000001</v>
       </c>
       <c r="C642" t="n">
         <v>0.297872</v>
@@ -8773,7 +8773,7 @@
         </is>
       </c>
       <c r="B643" t="n">
-        <v>0.072865</v>
+        <v>0.073282</v>
       </c>
       <c r="C643" t="n">
         <v>0.295213</v>
@@ -8786,7 +8786,7 @@
         </is>
       </c>
       <c r="B644" t="n">
-        <v>0.073088</v>
+        <v>0.073453</v>
       </c>
       <c r="C644" t="n">
         <v>0.292553</v>
@@ -8799,7 +8799,7 @@
         </is>
       </c>
       <c r="B645" t="n">
-        <v>0.074283</v>
+        <v>0.074906</v>
       </c>
       <c r="C645" t="n">
         <v>0.289894</v>
@@ -8812,7 +8812,7 @@
         </is>
       </c>
       <c r="B646" t="n">
-        <v>0.07442600000000001</v>
+        <v>0.075296</v>
       </c>
       <c r="C646" t="n">
         <v>0.287234</v>
@@ -8825,7 +8825,7 @@
         </is>
       </c>
       <c r="B647" t="n">
-        <v>0.07463400000000001</v>
+        <v>0.075886</v>
       </c>
       <c r="C647" t="n">
         <v>0.284574</v>
@@ -8838,7 +8838,7 @@
         </is>
       </c>
       <c r="B648" t="n">
-        <v>0.074896</v>
+        <v>0.07615</v>
       </c>
       <c r="C648" t="n">
         <v>0.281915</v>
@@ -8851,7 +8851,7 @@
         </is>
       </c>
       <c r="B649" t="n">
-        <v>0.07623099999999999</v>
+        <v>0.076526</v>
       </c>
       <c r="C649" t="n">
         <v>0.279255</v>
@@ -8864,7 +8864,7 @@
         </is>
       </c>
       <c r="B650" t="n">
-        <v>0.076753</v>
+        <v>0.076887</v>
       </c>
       <c r="C650" t="n">
         <v>0.276596</v>
@@ -8877,7 +8877,7 @@
         </is>
       </c>
       <c r="B651" t="n">
-        <v>0.076774</v>
+        <v>0.07710500000000001</v>
       </c>
       <c r="C651" t="n">
         <v>0.273936</v>
@@ -8890,7 +8890,7 @@
         </is>
       </c>
       <c r="B652" t="n">
-        <v>0.079154</v>
+        <v>0.07987900000000001</v>
       </c>
       <c r="C652" t="n">
         <v>0.271277</v>
@@ -8903,7 +8903,7 @@
         </is>
       </c>
       <c r="B653" t="n">
-        <v>0.079251</v>
+        <v>0.08000699999999999</v>
       </c>
       <c r="C653" t="n">
         <v>0.268617</v>
@@ -8916,7 +8916,7 @@
         </is>
       </c>
       <c r="B654" t="n">
-        <v>0.080453</v>
+        <v>0.08071399999999999</v>
       </c>
       <c r="C654" t="n">
         <v>0.265957</v>
@@ -8929,7 +8929,7 @@
         </is>
       </c>
       <c r="B655" t="n">
-        <v>0.080677</v>
+        <v>0.080946</v>
       </c>
       <c r="C655" t="n">
         <v>0.263298</v>
@@ -8942,7 +8942,7 @@
         </is>
       </c>
       <c r="B656" t="n">
-        <v>0.08074199999999999</v>
+        <v>0.08137900000000001</v>
       </c>
       <c r="C656" t="n">
         <v>0.260638</v>
@@ -8955,7 +8955,7 @@
         </is>
       </c>
       <c r="B657" t="n">
-        <v>0.080849</v>
+        <v>0.08161499999999999</v>
       </c>
       <c r="C657" t="n">
         <v>0.257979</v>
@@ -8968,7 +8968,7 @@
         </is>
       </c>
       <c r="B658" t="n">
-        <v>0.082042</v>
+        <v>0.0824</v>
       </c>
       <c r="C658" t="n">
         <v>0.255319</v>
@@ -8981,7 +8981,7 @@
         </is>
       </c>
       <c r="B659" t="n">
-        <v>0.08221299999999999</v>
+        <v>0.083053</v>
       </c>
       <c r="C659" t="n">
         <v>0.25266</v>
@@ -8994,7 +8994,7 @@
         </is>
       </c>
       <c r="B660" t="n">
-        <v>0.08289100000000001</v>
+        <v>0.083201</v>
       </c>
       <c r="C660" t="n">
         <v>0.25</v>
@@ -9007,7 +9007,7 @@
         </is>
       </c>
       <c r="B661" t="n">
-        <v>0.082899</v>
+        <v>0.08387500000000001</v>
       </c>
       <c r="C661" t="n">
         <v>0.24734</v>
@@ -9020,7 +9020,7 @@
         </is>
       </c>
       <c r="B662" t="n">
-        <v>0.08323999999999999</v>
+        <v>0.0843</v>
       </c>
       <c r="C662" t="n">
         <v>0.244681</v>
@@ -9033,7 +9033,7 @@
         </is>
       </c>
       <c r="B663" t="n">
-        <v>0.084049</v>
+        <v>0.084425</v>
       </c>
       <c r="C663" t="n">
         <v>0.242021</v>
@@ -9046,7 +9046,7 @@
         </is>
       </c>
       <c r="B664" t="n">
-        <v>0.08409</v>
+        <v>0.08463</v>
       </c>
       <c r="C664" t="n">
         <v>0.239362</v>
@@ -9059,7 +9059,7 @@
         </is>
       </c>
       <c r="B665" t="n">
-        <v>0.084401</v>
+        <v>0.085004</v>
       </c>
       <c r="C665" t="n">
         <v>0.236702</v>
@@ -9072,7 +9072,7 @@
         </is>
       </c>
       <c r="B666" t="n">
-        <v>0.084886</v>
+        <v>0.085185</v>
       </c>
       <c r="C666" t="n">
         <v>0.234043</v>
@@ -9085,7 +9085,7 @@
         </is>
       </c>
       <c r="B667" t="n">
-        <v>0.08602600000000001</v>
+        <v>0.086906</v>
       </c>
       <c r="C667" t="n">
         <v>0.231383</v>
@@ -9098,7 +9098,7 @@
         </is>
       </c>
       <c r="B668" t="n">
-        <v>0.086852</v>
+        <v>0.08698599999999999</v>
       </c>
       <c r="C668" t="n">
         <v>0.228723</v>
@@ -9111,7 +9111,7 @@
         </is>
       </c>
       <c r="B669" t="n">
-        <v>0.0873</v>
+        <v>0.087474</v>
       </c>
       <c r="C669" t="n">
         <v>0.226064</v>
@@ -9124,7 +9124,7 @@
         </is>
       </c>
       <c r="B670" t="n">
-        <v>0.087301</v>
+        <v>0.087716</v>
       </c>
       <c r="C670" t="n">
         <v>0.223404</v>
@@ -9137,7 +9137,7 @@
         </is>
       </c>
       <c r="B671" t="n">
-        <v>0.087466</v>
+        <v>0.08802</v>
       </c>
       <c r="C671" t="n">
         <v>0.220745</v>
@@ -9150,7 +9150,7 @@
         </is>
       </c>
       <c r="B672" t="n">
-        <v>0.08747099999999999</v>
+        <v>0.088958</v>
       </c>
       <c r="C672" t="n">
         <v>0.218085</v>
@@ -9163,7 +9163,7 @@
         </is>
       </c>
       <c r="B673" t="n">
-        <v>0.08803900000000001</v>
+        <v>0.089104</v>
       </c>
       <c r="C673" t="n">
         <v>0.215426</v>
@@ -9176,7 +9176,7 @@
         </is>
       </c>
       <c r="B674" t="n">
-        <v>0.088073</v>
+        <v>0.089249</v>
       </c>
       <c r="C674" t="n">
         <v>0.212766</v>
@@ -9189,7 +9189,7 @@
         </is>
       </c>
       <c r="B675" t="n">
-        <v>0.090269</v>
+        <v>0.09063499999999999</v>
       </c>
       <c r="C675" t="n">
         <v>0.210106</v>
@@ -9202,7 +9202,7 @@
         </is>
       </c>
       <c r="B676" t="n">
-        <v>0.09045</v>
+        <v>0.090902</v>
       </c>
       <c r="C676" t="n">
         <v>0.207447</v>
@@ -9215,7 +9215,7 @@
         </is>
       </c>
       <c r="B677" t="n">
-        <v>0.091068</v>
+        <v>0.091964</v>
       </c>
       <c r="C677" t="n">
         <v>0.204787</v>
@@ -9228,7 +9228,7 @@
         </is>
       </c>
       <c r="B678" t="n">
-        <v>0.091833</v>
+        <v>0.092474</v>
       </c>
       <c r="C678" t="n">
         <v>0.202128</v>
@@ -9241,7 +9241,7 @@
         </is>
       </c>
       <c r="B679" t="n">
-        <v>0.09188300000000001</v>
+        <v>0.09306499999999999</v>
       </c>
       <c r="C679" t="n">
         <v>0.199468</v>
@@ -9254,7 +9254,7 @@
         </is>
       </c>
       <c r="B680" t="n">
-        <v>0.09278699999999999</v>
+        <v>0.094267</v>
       </c>
       <c r="C680" t="n">
         <v>0.196809</v>
@@ -9267,7 +9267,7 @@
         </is>
       </c>
       <c r="B681" t="n">
-        <v>0.093709</v>
+        <v>0.094307</v>
       </c>
       <c r="C681" t="n">
         <v>0.194149</v>
@@ -9280,7 +9280,7 @@
         </is>
       </c>
       <c r="B682" t="n">
-        <v>0.094194</v>
+        <v>0.09436799999999999</v>
       </c>
       <c r="C682" t="n">
         <v>0.191489</v>
@@ -9293,7 +9293,7 @@
         </is>
       </c>
       <c r="B683" t="n">
-        <v>0.09460499999999999</v>
+        <v>0.094981</v>
       </c>
       <c r="C683" t="n">
         <v>0.18883</v>
@@ -9306,7 +9306,7 @@
         </is>
       </c>
       <c r="B684" t="n">
-        <v>0.095223</v>
+        <v>0.09550500000000001</v>
       </c>
       <c r="C684" t="n">
         <v>0.18617</v>
@@ -9319,7 +9319,7 @@
         </is>
       </c>
       <c r="B685" t="n">
-        <v>0.09707200000000001</v>
+        <v>0.097443</v>
       </c>
       <c r="C685" t="n">
         <v>0.183511</v>
@@ -9332,7 +9332,7 @@
         </is>
       </c>
       <c r="B686" t="n">
-        <v>0.09715</v>
+        <v>0.097576</v>
       </c>
       <c r="C686" t="n">
         <v>0.180851</v>
@@ -9345,7 +9345,7 @@
         </is>
       </c>
       <c r="B687" t="n">
-        <v>0.100291</v>
+        <v>0.10056</v>
       </c>
       <c r="C687" t="n">
         <v>0.178191</v>
@@ -9358,7 +9358,7 @@
         </is>
       </c>
       <c r="B688" t="n">
-        <v>0.101921</v>
+        <v>0.102206</v>
       </c>
       <c r="C688" t="n">
         <v>0.175532</v>
@@ -9371,7 +9371,7 @@
         </is>
       </c>
       <c r="B689" t="n">
-        <v>0.102166</v>
+        <v>0.103992</v>
       </c>
       <c r="C689" t="n">
         <v>0.172872</v>
@@ -9384,7 +9384,7 @@
         </is>
       </c>
       <c r="B690" t="n">
-        <v>0.104146</v>
+        <v>0.104526</v>
       </c>
       <c r="C690" t="n">
         <v>0.170213</v>
@@ -9397,7 +9397,7 @@
         </is>
       </c>
       <c r="B691" t="n">
-        <v>0.104443</v>
+        <v>0.105089</v>
       </c>
       <c r="C691" t="n">
         <v>0.167553</v>
@@ -9410,7 +9410,7 @@
         </is>
       </c>
       <c r="B692" t="n">
-        <v>0.105048</v>
+        <v>0.105283</v>
       </c>
       <c r="C692" t="n">
         <v>0.164894</v>
@@ -9423,7 +9423,7 @@
         </is>
       </c>
       <c r="B693" t="n">
-        <v>0.106714</v>
+        <v>0.107938</v>
       </c>
       <c r="C693" t="n">
         <v>0.162234</v>
@@ -9436,7 +9436,7 @@
         </is>
       </c>
       <c r="B694" t="n">
-        <v>0.106849</v>
+        <v>0.108433</v>
       </c>
       <c r="C694" t="n">
         <v>0.159574</v>
@@ -9449,7 +9449,7 @@
         </is>
       </c>
       <c r="B695" t="n">
-        <v>0.108285</v>
+        <v>0.108788</v>
       </c>
       <c r="C695" t="n">
         <v>0.156915</v>
@@ -9462,7 +9462,7 @@
         </is>
       </c>
       <c r="B696" t="n">
-        <v>0.109845</v>
+        <v>0.110905</v>
       </c>
       <c r="C696" t="n">
         <v>0.154255</v>
@@ -9475,7 +9475,7 @@
         </is>
       </c>
       <c r="B697" t="n">
-        <v>0.110587</v>
+        <v>0.111574</v>
       </c>
       <c r="C697" t="n">
         <v>0.151596</v>
@@ -9488,7 +9488,7 @@
         </is>
       </c>
       <c r="B698" t="n">
-        <v>0.111572</v>
+        <v>0.112195</v>
       </c>
       <c r="C698" t="n">
         <v>0.148936</v>
@@ -9501,7 +9501,7 @@
         </is>
       </c>
       <c r="B699" t="n">
-        <v>0.113289</v>
+        <v>0.113543</v>
       </c>
       <c r="C699" t="n">
         <v>0.146277</v>
@@ -9514,7 +9514,7 @@
         </is>
       </c>
       <c r="B700" t="n">
-        <v>0.114655</v>
+        <v>0.114797</v>
       </c>
       <c r="C700" t="n">
         <v>0.143617</v>
@@ -9527,7 +9527,7 @@
         </is>
       </c>
       <c r="B701" t="n">
-        <v>0.115883</v>
+        <v>0.116567</v>
       </c>
       <c r="C701" t="n">
         <v>0.140957</v>
@@ -9540,7 +9540,7 @@
         </is>
       </c>
       <c r="B702" t="n">
-        <v>0.116057</v>
+        <v>0.116761</v>
       </c>
       <c r="C702" t="n">
         <v>0.138298</v>
@@ -9553,7 +9553,7 @@
         </is>
       </c>
       <c r="B703" t="n">
-        <v>0.116307</v>
+        <v>0.117243</v>
       </c>
       <c r="C703" t="n">
         <v>0.135638</v>
@@ -9566,7 +9566,7 @@
         </is>
       </c>
       <c r="B704" t="n">
-        <v>0.117176</v>
+        <v>0.117797</v>
       </c>
       <c r="C704" t="n">
         <v>0.132979</v>
@@ -9579,7 +9579,7 @@
         </is>
       </c>
       <c r="B705" t="n">
-        <v>0.117591</v>
+        <v>0.118039</v>
       </c>
       <c r="C705" t="n">
         <v>0.130319</v>
@@ -9592,7 +9592,7 @@
         </is>
       </c>
       <c r="B706" t="n">
-        <v>0.11767</v>
+        <v>0.119262</v>
       </c>
       <c r="C706" t="n">
         <v>0.12766</v>
@@ -9605,7 +9605,7 @@
         </is>
       </c>
       <c r="B707" t="n">
-        <v>0.118465</v>
+        <v>0.119439</v>
       </c>
       <c r="C707" t="n">
         <v>0.125</v>
@@ -9618,7 +9618,7 @@
         </is>
       </c>
       <c r="B708" t="n">
-        <v>0.119059</v>
+        <v>0.119873</v>
       </c>
       <c r="C708" t="n">
         <v>0.12234</v>
@@ -9631,7 +9631,7 @@
         </is>
       </c>
       <c r="B709" t="n">
-        <v>0.121802</v>
+        <v>0.122986</v>
       </c>
       <c r="C709" t="n">
         <v>0.119681</v>
@@ -9644,7 +9644,7 @@
         </is>
       </c>
       <c r="B710" t="n">
-        <v>0.122267</v>
+        <v>0.12344</v>
       </c>
       <c r="C710" t="n">
         <v>0.117021</v>
@@ -9657,7 +9657,7 @@
         </is>
       </c>
       <c r="B711" t="n">
-        <v>0.12304</v>
+        <v>0.124248</v>
       </c>
       <c r="C711" t="n">
         <v>0.114362</v>
@@ -9670,7 +9670,7 @@
         </is>
       </c>
       <c r="B712" t="n">
-        <v>0.125468</v>
+        <v>0.126154</v>
       </c>
       <c r="C712" t="n">
         <v>0.111702</v>
@@ -9683,7 +9683,7 @@
         </is>
       </c>
       <c r="B713" t="n">
-        <v>0.126527</v>
+        <v>0.12781</v>
       </c>
       <c r="C713" t="n">
         <v>0.109043</v>
@@ -9696,7 +9696,7 @@
         </is>
       </c>
       <c r="B714" t="n">
-        <v>0.127412</v>
+        <v>0.127819</v>
       </c>
       <c r="C714" t="n">
         <v>0.106383</v>
@@ -9709,7 +9709,7 @@
         </is>
       </c>
       <c r="B715" t="n">
-        <v>0.127703</v>
+        <v>0.128916</v>
       </c>
       <c r="C715" t="n">
         <v>0.103723</v>
@@ -9722,7 +9722,7 @@
         </is>
       </c>
       <c r="B716" t="n">
-        <v>0.129269</v>
+        <v>0.130024</v>
       </c>
       <c r="C716" t="n">
         <v>0.101064</v>
@@ -9735,7 +9735,7 @@
         </is>
       </c>
       <c r="B717" t="n">
-        <v>0.130597</v>
+        <v>0.130967</v>
       </c>
       <c r="C717" t="n">
         <v>0.09840400000000001</v>
@@ -9748,7 +9748,7 @@
         </is>
       </c>
       <c r="B718" t="n">
-        <v>0.131202</v>
+        <v>0.131323</v>
       </c>
       <c r="C718" t="n">
         <v>0.095745</v>
@@ -9761,7 +9761,7 @@
         </is>
       </c>
       <c r="B719" t="n">
-        <v>0.131362</v>
+        <v>0.13169</v>
       </c>
       <c r="C719" t="n">
         <v>0.093085</v>
@@ -9774,7 +9774,7 @@
         </is>
       </c>
       <c r="B720" t="n">
-        <v>0.132383</v>
+        <v>0.133358</v>
       </c>
       <c r="C720" t="n">
         <v>0.09042600000000001</v>
@@ -9787,7 +9787,7 @@
         </is>
       </c>
       <c r="B721" t="n">
-        <v>0.13263</v>
+        <v>0.133507</v>
       </c>
       <c r="C721" t="n">
         <v>0.087766</v>
@@ -9800,7 +9800,7 @@
         </is>
       </c>
       <c r="B722" t="n">
-        <v>0.136914</v>
+        <v>0.137073</v>
       </c>
       <c r="C722" t="n">
         <v>0.085106</v>
@@ -9813,7 +9813,7 @@
         </is>
       </c>
       <c r="B723" t="n">
-        <v>0.143549</v>
+        <v>0.146166</v>
       </c>
       <c r="C723" t="n">
         <v>0.08244700000000001</v>
@@ -9826,7 +9826,7 @@
         </is>
       </c>
       <c r="B724" t="n">
-        <v>0.144253</v>
+        <v>0.147565</v>
       </c>
       <c r="C724" t="n">
         <v>0.079787</v>
@@ -9839,7 +9839,7 @@
         </is>
       </c>
       <c r="B725" t="n">
-        <v>0.149441</v>
+        <v>0.149889</v>
       </c>
       <c r="C725" t="n">
         <v>0.077128</v>
@@ -9852,7 +9852,7 @@
         </is>
       </c>
       <c r="B726" t="n">
-        <v>0.150255</v>
+        <v>0.151093</v>
       </c>
       <c r="C726" t="n">
         <v>0.07446800000000001</v>
@@ -9865,7 +9865,7 @@
         </is>
       </c>
       <c r="B727" t="n">
-        <v>0.152307</v>
+        <v>0.152887</v>
       </c>
       <c r="C727" t="n">
         <v>0.071809</v>
@@ -9878,7 +9878,7 @@
         </is>
       </c>
       <c r="B728" t="n">
-        <v>0.15474</v>
+        <v>0.158037</v>
       </c>
       <c r="C728" t="n">
         <v>0.069149</v>
@@ -9891,7 +9891,7 @@
         </is>
       </c>
       <c r="B729" t="n">
-        <v>0.156823</v>
+        <v>0.158408</v>
       </c>
       <c r="C729" t="n">
         <v>0.06648900000000001</v>
@@ -9904,7 +9904,7 @@
         </is>
       </c>
       <c r="B730" t="n">
-        <v>0.157804</v>
+        <v>0.159013</v>
       </c>
       <c r="C730" t="n">
         <v>0.06383</v>
@@ -9917,7 +9917,7 @@
         </is>
       </c>
       <c r="B731" t="n">
-        <v>0.159124</v>
+        <v>0.16111</v>
       </c>
       <c r="C731" t="n">
         <v>0.06117</v>
@@ -9930,7 +9930,7 @@
         </is>
       </c>
       <c r="B732" t="n">
-        <v>0.162965</v>
+        <v>0.163852</v>
       </c>
       <c r="C732" t="n">
         <v>0.058511</v>
@@ -9943,7 +9943,7 @@
         </is>
       </c>
       <c r="B733" t="n">
-        <v>0.164139</v>
+        <v>0.165874</v>
       </c>
       <c r="C733" t="n">
         <v>0.055851</v>
@@ -9956,7 +9956,7 @@
         </is>
       </c>
       <c r="B734" t="n">
-        <v>0.166078</v>
+        <v>0.166506</v>
       </c>
       <c r="C734" t="n">
         <v>0.053191</v>
@@ -9969,7 +9969,7 @@
         </is>
       </c>
       <c r="B735" t="n">
-        <v>0.169314</v>
+        <v>0.169646</v>
       </c>
       <c r="C735" t="n">
         <v>0.050532</v>
@@ -9982,7 +9982,7 @@
         </is>
       </c>
       <c r="B736" t="n">
-        <v>0.172443</v>
+        <v>0.174797</v>
       </c>
       <c r="C736" t="n">
         <v>0.047872</v>
@@ -9995,7 +9995,7 @@
         </is>
       </c>
       <c r="B737" t="n">
-        <v>0.174893</v>
+        <v>0.17631</v>
       </c>
       <c r="C737" t="n">
         <v>0.045213</v>
@@ -10008,7 +10008,7 @@
         </is>
       </c>
       <c r="B738" t="n">
-        <v>0.17575</v>
+        <v>0.178845</v>
       </c>
       <c r="C738" t="n">
         <v>0.042553</v>
@@ -10021,7 +10021,7 @@
         </is>
       </c>
       <c r="B739" t="n">
-        <v>0.177768</v>
+        <v>0.180465</v>
       </c>
       <c r="C739" t="n">
         <v>0.039894</v>
@@ -10034,7 +10034,7 @@
         </is>
       </c>
       <c r="B740" t="n">
-        <v>0.188087</v>
+        <v>0.18879</v>
       </c>
       <c r="C740" t="n">
         <v>0.037234</v>
@@ -10047,7 +10047,7 @@
         </is>
       </c>
       <c r="B741" t="n">
-        <v>0.191645</v>
+        <v>0.193711</v>
       </c>
       <c r="C741" t="n">
         <v>0.034574</v>
@@ -10060,7 +10060,7 @@
         </is>
       </c>
       <c r="B742" t="n">
-        <v>0.196529</v>
+        <v>0.202325</v>
       </c>
       <c r="C742" t="n">
         <v>0.031915</v>
@@ -10073,7 +10073,7 @@
         </is>
       </c>
       <c r="B743" t="n">
-        <v>0.202009</v>
+        <v>0.206049</v>
       </c>
       <c r="C743" t="n">
         <v>0.029255</v>
@@ -10086,7 +10086,7 @@
         </is>
       </c>
       <c r="B744" t="n">
-        <v>0.211973</v>
+        <v>0.215387</v>
       </c>
       <c r="C744" t="n">
         <v>0.026596</v>
@@ -10099,7 +10099,7 @@
         </is>
       </c>
       <c r="B745" t="n">
-        <v>0.222911</v>
+        <v>0.223697</v>
       </c>
       <c r="C745" t="n">
         <v>0.023936</v>
@@ -10112,7 +10112,7 @@
         </is>
       </c>
       <c r="B746" t="n">
-        <v>0.223629</v>
+        <v>0.225171</v>
       </c>
       <c r="C746" t="n">
         <v>0.021277</v>
@@ -10125,7 +10125,7 @@
         </is>
       </c>
       <c r="B747" t="n">
-        <v>0.230509</v>
+        <v>0.232207</v>
       </c>
       <c r="C747" t="n">
         <v>0.018617</v>
@@ -10138,7 +10138,7 @@
         </is>
       </c>
       <c r="B748" t="n">
-        <v>0.247289</v>
+        <v>0.248446</v>
       </c>
       <c r="C748" t="n">
         <v>0.015957</v>
@@ -10151,7 +10151,7 @@
         </is>
       </c>
       <c r="B749" t="n">
-        <v>0.276518</v>
+        <v>0.278184</v>
       </c>
       <c r="C749" t="n">
         <v>0.013298</v>
@@ -10164,7 +10164,7 @@
         </is>
       </c>
       <c r="B750" t="n">
-        <v>0.277584</v>
+        <v>0.279905</v>
       </c>
       <c r="C750" t="n">
         <v>0.010638</v>
@@ -10177,7 +10177,7 @@
         </is>
       </c>
       <c r="B751" t="n">
-        <v>0.3128</v>
+        <v>0.313884</v>
       </c>
       <c r="C751" t="n">
         <v>0.007979</v>
@@ -10190,7 +10190,7 @@
         </is>
       </c>
       <c r="B752" t="n">
-        <v>0.347132</v>
+        <v>0.351465</v>
       </c>
       <c r="C752" t="n">
         <v>0.005319</v>
@@ -10203,7 +10203,7 @@
         </is>
       </c>
       <c r="B753" t="n">
-        <v>0.403327</v>
+        <v>0.407638</v>
       </c>
       <c r="C753" t="n">
         <v>0.00266</v>

--- a/vignettes/vignette-1/tail_exceedance_plot_data.xlsx
+++ b/vignettes/vignette-1/tail_exceedance_plot_data.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C753"/>
+  <dimension ref="A1:C759"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -456,7 +456,7 @@
         <v>9.3e-05</v>
       </c>
       <c r="C3" t="n">
-        <v>0.99734</v>
+        <v>0.9973610000000001</v>
       </c>
     </row>
     <row r="4">
@@ -469,7 +469,7 @@
         <v>0.000441</v>
       </c>
       <c r="C4" t="n">
-        <v>0.994681</v>
+        <v>0.994723</v>
       </c>
     </row>
     <row r="5">
@@ -482,7 +482,7 @@
         <v>0.000522</v>
       </c>
       <c r="C5" t="n">
-        <v>0.992021</v>
+        <v>0.992084</v>
       </c>
     </row>
     <row r="6">
@@ -495,7 +495,7 @@
         <v>0.001163</v>
       </c>
       <c r="C6" t="n">
-        <v>0.989362</v>
+        <v>0.989446</v>
       </c>
     </row>
     <row r="7">
@@ -508,7 +508,7 @@
         <v>0.001681</v>
       </c>
       <c r="C7" t="n">
-        <v>0.986702</v>
+        <v>0.986807</v>
       </c>
     </row>
     <row r="8">
@@ -521,7 +521,7 @@
         <v>0.00295</v>
       </c>
       <c r="C8" t="n">
-        <v>0.984043</v>
+        <v>0.984169</v>
       </c>
     </row>
     <row r="9">
@@ -534,7 +534,7 @@
         <v>0.002998</v>
       </c>
       <c r="C9" t="n">
-        <v>0.981383</v>
+        <v>0.98153</v>
       </c>
     </row>
     <row r="10">
@@ -547,7 +547,7 @@
         <v>0.003455</v>
       </c>
       <c r="C10" t="n">
-        <v>0.978723</v>
+        <v>0.978892</v>
       </c>
     </row>
     <row r="11">
@@ -560,7 +560,7 @@
         <v>0.003769</v>
       </c>
       <c r="C11" t="n">
-        <v>0.976064</v>
+        <v>0.976253</v>
       </c>
     </row>
     <row r="12">
@@ -573,7 +573,7 @@
         <v>0.003788</v>
       </c>
       <c r="C12" t="n">
-        <v>0.973404</v>
+        <v>0.973615</v>
       </c>
     </row>
     <row r="13">
@@ -586,7 +586,7 @@
         <v>0.004717</v>
       </c>
       <c r="C13" t="n">
-        <v>0.970745</v>
+        <v>0.970976</v>
       </c>
     </row>
     <row r="14">
@@ -599,7 +599,7 @@
         <v>0.004779</v>
       </c>
       <c r="C14" t="n">
-        <v>0.968085</v>
+        <v>0.968338</v>
       </c>
     </row>
     <row r="15">
@@ -612,7 +612,7 @@
         <v>0.004912</v>
       </c>
       <c r="C15" t="n">
-        <v>0.965426</v>
+        <v>0.965699</v>
       </c>
     </row>
     <row r="16">
@@ -625,7 +625,7 @@
         <v>0.005429</v>
       </c>
       <c r="C16" t="n">
-        <v>0.962766</v>
+        <v>0.9630609999999999</v>
       </c>
     </row>
     <row r="17">
@@ -638,7 +638,7 @@
         <v>0.005649</v>
       </c>
       <c r="C17" t="n">
-        <v>0.960106</v>
+        <v>0.960422</v>
       </c>
     </row>
     <row r="18">
@@ -651,7 +651,7 @@
         <v>0.00593</v>
       </c>
       <c r="C18" t="n">
-        <v>0.957447</v>
+        <v>0.957784</v>
       </c>
     </row>
     <row r="19">
@@ -664,7 +664,7 @@
         <v>0.006143</v>
       </c>
       <c r="C19" t="n">
-        <v>0.9547870000000001</v>
+        <v>0.955145</v>
       </c>
     </row>
     <row r="20">
@@ -677,7 +677,7 @@
         <v>0.006394</v>
       </c>
       <c r="C20" t="n">
-        <v>0.952128</v>
+        <v>0.952507</v>
       </c>
     </row>
     <row r="21">
@@ -690,7 +690,7 @@
         <v>0.006914</v>
       </c>
       <c r="C21" t="n">
-        <v>0.949468</v>
+        <v>0.949868</v>
       </c>
     </row>
     <row r="22">
@@ -703,7 +703,7 @@
         <v>0.007419</v>
       </c>
       <c r="C22" t="n">
-        <v>0.946809</v>
+        <v>0.94723</v>
       </c>
     </row>
     <row r="23">
@@ -716,7 +716,7 @@
         <v>0.007582</v>
       </c>
       <c r="C23" t="n">
-        <v>0.944149</v>
+        <v>0.944591</v>
       </c>
     </row>
     <row r="24">
@@ -729,7 +729,7 @@
         <v>0.008029</v>
       </c>
       <c r="C24" t="n">
-        <v>0.941489</v>
+        <v>0.941953</v>
       </c>
     </row>
     <row r="25">
@@ -742,7 +742,7 @@
         <v>0.008069</v>
       </c>
       <c r="C25" t="n">
-        <v>0.9388300000000001</v>
+        <v>0.939314</v>
       </c>
     </row>
     <row r="26">
@@ -755,7 +755,7 @@
         <v>0.008173</v>
       </c>
       <c r="C26" t="n">
-        <v>0.9361699999999999</v>
+        <v>0.936675</v>
       </c>
     </row>
     <row r="27">
@@ -768,7 +768,7 @@
         <v>0.008377000000000001</v>
       </c>
       <c r="C27" t="n">
-        <v>0.933511</v>
+        <v>0.934037</v>
       </c>
     </row>
     <row r="28">
@@ -781,7 +781,7 @@
         <v>0.008593999999999999</v>
       </c>
       <c r="C28" t="n">
-        <v>0.930851</v>
+        <v>0.9313979999999999</v>
       </c>
     </row>
     <row r="29">
@@ -794,7 +794,7 @@
         <v>0.008658000000000001</v>
       </c>
       <c r="C29" t="n">
-        <v>0.928191</v>
+        <v>0.92876</v>
       </c>
     </row>
     <row r="30">
@@ -807,7 +807,7 @@
         <v>0.008992</v>
       </c>
       <c r="C30" t="n">
-        <v>0.925532</v>
+        <v>0.926121</v>
       </c>
     </row>
     <row r="31">
@@ -820,7 +820,7 @@
         <v>0.009165</v>
       </c>
       <c r="C31" t="n">
-        <v>0.922872</v>
+        <v>0.9234830000000001</v>
       </c>
     </row>
     <row r="32">
@@ -833,7 +833,7 @@
         <v>0.009428000000000001</v>
       </c>
       <c r="C32" t="n">
-        <v>0.9202129999999999</v>
+        <v>0.920844</v>
       </c>
     </row>
     <row r="33">
@@ -846,7 +846,7 @@
         <v>0.009578</v>
       </c>
       <c r="C33" t="n">
-        <v>0.917553</v>
+        <v>0.918206</v>
       </c>
     </row>
     <row r="34">
@@ -859,7 +859,7 @@
         <v>0.009774</v>
       </c>
       <c r="C34" t="n">
-        <v>0.914894</v>
+        <v>0.915567</v>
       </c>
     </row>
     <row r="35">
@@ -872,7 +872,7 @@
         <v>0.009811</v>
       </c>
       <c r="C35" t="n">
-        <v>0.912234</v>
+        <v>0.912929</v>
       </c>
     </row>
     <row r="36">
@@ -885,7 +885,7 @@
         <v>0.010226</v>
       </c>
       <c r="C36" t="n">
-        <v>0.909574</v>
+        <v>0.91029</v>
       </c>
     </row>
     <row r="37">
@@ -898,7 +898,7 @@
         <v>0.010518</v>
       </c>
       <c r="C37" t="n">
-        <v>0.906915</v>
+        <v>0.907652</v>
       </c>
     </row>
     <row r="38">
@@ -911,7 +911,7 @@
         <v>0.010943</v>
       </c>
       <c r="C38" t="n">
-        <v>0.904255</v>
+        <v>0.905013</v>
       </c>
     </row>
     <row r="39">
@@ -924,7 +924,7 @@
         <v>0.011156</v>
       </c>
       <c r="C39" t="n">
-        <v>0.901596</v>
+        <v>0.902375</v>
       </c>
     </row>
     <row r="40">
@@ -937,7 +937,7 @@
         <v>0.011326</v>
       </c>
       <c r="C40" t="n">
-        <v>0.898936</v>
+        <v>0.899736</v>
       </c>
     </row>
     <row r="41">
@@ -950,7 +950,7 @@
         <v>0.01145</v>
       </c>
       <c r="C41" t="n">
-        <v>0.896277</v>
+        <v>0.897098</v>
       </c>
     </row>
     <row r="42">
@@ -963,7 +963,7 @@
         <v>0.012002</v>
       </c>
       <c r="C42" t="n">
-        <v>0.893617</v>
+        <v>0.894459</v>
       </c>
     </row>
     <row r="43">
@@ -976,7 +976,7 @@
         <v>0.012035</v>
       </c>
       <c r="C43" t="n">
-        <v>0.890957</v>
+        <v>0.891821</v>
       </c>
     </row>
     <row r="44">
@@ -989,7 +989,7 @@
         <v>0.012747</v>
       </c>
       <c r="C44" t="n">
-        <v>0.888298</v>
+        <v>0.889182</v>
       </c>
     </row>
     <row r="45">
@@ -1002,7 +1002,7 @@
         <v>0.012918</v>
       </c>
       <c r="C45" t="n">
-        <v>0.885638</v>
+        <v>0.886544</v>
       </c>
     </row>
     <row r="46">
@@ -1015,7 +1015,7 @@
         <v>0.013714</v>
       </c>
       <c r="C46" t="n">
-        <v>0.882979</v>
+        <v>0.8839050000000001</v>
       </c>
     </row>
     <row r="47">
@@ -1028,7 +1028,7 @@
         <v>0.01393</v>
       </c>
       <c r="C47" t="n">
-        <v>0.880319</v>
+        <v>0.881266</v>
       </c>
     </row>
     <row r="48">
@@ -1041,7 +1041,7 @@
         <v>0.013971</v>
       </c>
       <c r="C48" t="n">
-        <v>0.87766</v>
+        <v>0.878628</v>
       </c>
     </row>
     <row r="49">
@@ -1054,7 +1054,7 @@
         <v>0.014018</v>
       </c>
       <c r="C49" t="n">
-        <v>0.875</v>
+        <v>0.875989</v>
       </c>
     </row>
     <row r="50">
@@ -1064,10 +1064,10 @@
         </is>
       </c>
       <c r="B50" t="n">
-        <v>0.014481</v>
+        <v>0.01417</v>
       </c>
       <c r="C50" t="n">
-        <v>0.87234</v>
+        <v>0.873351</v>
       </c>
     </row>
     <row r="51">
@@ -1077,10 +1077,10 @@
         </is>
       </c>
       <c r="B51" t="n">
-        <v>0.014731</v>
+        <v>0.014481</v>
       </c>
       <c r="C51" t="n">
-        <v>0.869681</v>
+        <v>0.870712</v>
       </c>
     </row>
     <row r="52">
@@ -1090,10 +1090,10 @@
         </is>
       </c>
       <c r="B52" t="n">
-        <v>0.014841</v>
+        <v>0.014731</v>
       </c>
       <c r="C52" t="n">
-        <v>0.867021</v>
+        <v>0.868074</v>
       </c>
     </row>
     <row r="53">
@@ -1103,10 +1103,10 @@
         </is>
       </c>
       <c r="B53" t="n">
-        <v>0.01486</v>
+        <v>0.014841</v>
       </c>
       <c r="C53" t="n">
-        <v>0.864362</v>
+        <v>0.865435</v>
       </c>
     </row>
     <row r="54">
@@ -1116,10 +1116,10 @@
         </is>
       </c>
       <c r="B54" t="n">
-        <v>0.015041</v>
+        <v>0.01486</v>
       </c>
       <c r="C54" t="n">
-        <v>0.861702</v>
+        <v>0.862797</v>
       </c>
     </row>
     <row r="55">
@@ -1129,10 +1129,10 @@
         </is>
       </c>
       <c r="B55" t="n">
-        <v>0.015107</v>
+        <v>0.015041</v>
       </c>
       <c r="C55" t="n">
-        <v>0.859043</v>
+        <v>0.860158</v>
       </c>
     </row>
     <row r="56">
@@ -1145,7 +1145,7 @@
         <v>0.015107</v>
       </c>
       <c r="C56" t="n">
-        <v>0.856383</v>
+        <v>0.8575199999999999</v>
       </c>
     </row>
     <row r="57">
@@ -1155,10 +1155,10 @@
         </is>
       </c>
       <c r="B57" t="n">
-        <v>0.015553</v>
+        <v>0.015107</v>
       </c>
       <c r="C57" t="n">
-        <v>0.853723</v>
+        <v>0.854881</v>
       </c>
     </row>
     <row r="58">
@@ -1168,10 +1168,10 @@
         </is>
       </c>
       <c r="B58" t="n">
-        <v>0.016031</v>
+        <v>0.015553</v>
       </c>
       <c r="C58" t="n">
-        <v>0.851064</v>
+        <v>0.852243</v>
       </c>
     </row>
     <row r="59">
@@ -1181,10 +1181,10 @@
         </is>
       </c>
       <c r="B59" t="n">
-        <v>0.016343</v>
+        <v>0.016031</v>
       </c>
       <c r="C59" t="n">
-        <v>0.848404</v>
+        <v>0.849604</v>
       </c>
     </row>
     <row r="60">
@@ -1194,10 +1194,10 @@
         </is>
       </c>
       <c r="B60" t="n">
-        <v>0.016545</v>
+        <v>0.016343</v>
       </c>
       <c r="C60" t="n">
-        <v>0.845745</v>
+        <v>0.846966</v>
       </c>
     </row>
     <row r="61">
@@ -1207,10 +1207,10 @@
         </is>
       </c>
       <c r="B61" t="n">
-        <v>0.017135</v>
+        <v>0.016545</v>
       </c>
       <c r="C61" t="n">
-        <v>0.843085</v>
+        <v>0.844327</v>
       </c>
     </row>
     <row r="62">
@@ -1220,10 +1220,10 @@
         </is>
       </c>
       <c r="B62" t="n">
-        <v>0.017276</v>
+        <v>0.017135</v>
       </c>
       <c r="C62" t="n">
-        <v>0.840426</v>
+        <v>0.841689</v>
       </c>
     </row>
     <row r="63">
@@ -1233,10 +1233,10 @@
         </is>
       </c>
       <c r="B63" t="n">
-        <v>0.017621</v>
+        <v>0.017276</v>
       </c>
       <c r="C63" t="n">
-        <v>0.837766</v>
+        <v>0.83905</v>
       </c>
     </row>
     <row r="64">
@@ -1246,10 +1246,10 @@
         </is>
       </c>
       <c r="B64" t="n">
-        <v>0.017975</v>
+        <v>0.017621</v>
       </c>
       <c r="C64" t="n">
-        <v>0.835106</v>
+        <v>0.836412</v>
       </c>
     </row>
     <row r="65">
@@ -1259,10 +1259,10 @@
         </is>
       </c>
       <c r="B65" t="n">
-        <v>0.018257</v>
+        <v>0.017975</v>
       </c>
       <c r="C65" t="n">
-        <v>0.832447</v>
+        <v>0.833773</v>
       </c>
     </row>
     <row r="66">
@@ -1272,10 +1272,10 @@
         </is>
       </c>
       <c r="B66" t="n">
-        <v>0.018505</v>
+        <v>0.018257</v>
       </c>
       <c r="C66" t="n">
-        <v>0.8297870000000001</v>
+        <v>0.831135</v>
       </c>
     </row>
     <row r="67">
@@ -1285,10 +1285,10 @@
         </is>
       </c>
       <c r="B67" t="n">
-        <v>0.018757</v>
+        <v>0.018505</v>
       </c>
       <c r="C67" t="n">
-        <v>0.827128</v>
+        <v>0.828496</v>
       </c>
     </row>
     <row r="68">
@@ -1298,10 +1298,10 @@
         </is>
       </c>
       <c r="B68" t="n">
-        <v>0.018801</v>
+        <v>0.018757</v>
       </c>
       <c r="C68" t="n">
-        <v>0.824468</v>
+        <v>0.825858</v>
       </c>
     </row>
     <row r="69">
@@ -1311,10 +1311,10 @@
         </is>
       </c>
       <c r="B69" t="n">
-        <v>0.018847</v>
+        <v>0.018801</v>
       </c>
       <c r="C69" t="n">
-        <v>0.821809</v>
+        <v>0.823219</v>
       </c>
     </row>
     <row r="70">
@@ -1324,10 +1324,10 @@
         </is>
       </c>
       <c r="B70" t="n">
-        <v>0.018931</v>
+        <v>0.018847</v>
       </c>
       <c r="C70" t="n">
-        <v>0.819149</v>
+        <v>0.82058</v>
       </c>
     </row>
     <row r="71">
@@ -1337,10 +1337,10 @@
         </is>
       </c>
       <c r="B71" t="n">
-        <v>0.019352</v>
+        <v>0.018931</v>
       </c>
       <c r="C71" t="n">
-        <v>0.816489</v>
+        <v>0.8179419999999999</v>
       </c>
     </row>
     <row r="72">
@@ -1350,10 +1350,10 @@
         </is>
       </c>
       <c r="B72" t="n">
-        <v>0.01962</v>
+        <v>0.019352</v>
       </c>
       <c r="C72" t="n">
-        <v>0.8138300000000001</v>
+        <v>0.815303</v>
       </c>
     </row>
     <row r="73">
@@ -1363,10 +1363,10 @@
         </is>
       </c>
       <c r="B73" t="n">
-        <v>0.019953</v>
+        <v>0.01962</v>
       </c>
       <c r="C73" t="n">
-        <v>0.8111699999999999</v>
+        <v>0.812665</v>
       </c>
     </row>
     <row r="74">
@@ -1376,10 +1376,10 @@
         </is>
       </c>
       <c r="B74" t="n">
-        <v>0.020186</v>
+        <v>0.019953</v>
       </c>
       <c r="C74" t="n">
-        <v>0.808511</v>
+        <v>0.810026</v>
       </c>
     </row>
     <row r="75">
@@ -1389,10 +1389,10 @@
         </is>
       </c>
       <c r="B75" t="n">
-        <v>0.020393</v>
+        <v>0.020186</v>
       </c>
       <c r="C75" t="n">
-        <v>0.805851</v>
+        <v>0.807388</v>
       </c>
     </row>
     <row r="76">
@@ -1402,10 +1402,10 @@
         </is>
       </c>
       <c r="B76" t="n">
-        <v>0.02048</v>
+        <v>0.020393</v>
       </c>
       <c r="C76" t="n">
-        <v>0.803191</v>
+        <v>0.804749</v>
       </c>
     </row>
     <row r="77">
@@ -1415,10 +1415,10 @@
         </is>
       </c>
       <c r="B77" t="n">
-        <v>0.021572</v>
+        <v>0.02048</v>
       </c>
       <c r="C77" t="n">
-        <v>0.800532</v>
+        <v>0.802111</v>
       </c>
     </row>
     <row r="78">
@@ -1428,10 +1428,10 @@
         </is>
       </c>
       <c r="B78" t="n">
-        <v>0.021604</v>
+        <v>0.021572</v>
       </c>
       <c r="C78" t="n">
-        <v>0.797872</v>
+        <v>0.799472</v>
       </c>
     </row>
     <row r="79">
@@ -1441,10 +1441,10 @@
         </is>
       </c>
       <c r="B79" t="n">
-        <v>0.021912</v>
+        <v>0.021604</v>
       </c>
       <c r="C79" t="n">
-        <v>0.7952129999999999</v>
+        <v>0.796834</v>
       </c>
     </row>
     <row r="80">
@@ -1454,10 +1454,10 @@
         </is>
       </c>
       <c r="B80" t="n">
-        <v>0.021918</v>
+        <v>0.021912</v>
       </c>
       <c r="C80" t="n">
-        <v>0.792553</v>
+        <v>0.794195</v>
       </c>
     </row>
     <row r="81">
@@ -1467,10 +1467,10 @@
         </is>
       </c>
       <c r="B81" t="n">
-        <v>0.021962</v>
+        <v>0.021918</v>
       </c>
       <c r="C81" t="n">
-        <v>0.789894</v>
+        <v>0.791557</v>
       </c>
     </row>
     <row r="82">
@@ -1480,10 +1480,10 @@
         </is>
       </c>
       <c r="B82" t="n">
-        <v>0.022008</v>
+        <v>0.021962</v>
       </c>
       <c r="C82" t="n">
-        <v>0.787234</v>
+        <v>0.788918</v>
       </c>
     </row>
     <row r="83">
@@ -1493,10 +1493,10 @@
         </is>
       </c>
       <c r="B83" t="n">
-        <v>0.022011</v>
+        <v>0.022008</v>
       </c>
       <c r="C83" t="n">
-        <v>0.784574</v>
+        <v>0.78628</v>
       </c>
     </row>
     <row r="84">
@@ -1506,10 +1506,10 @@
         </is>
       </c>
       <c r="B84" t="n">
-        <v>0.022121</v>
+        <v>0.022011</v>
       </c>
       <c r="C84" t="n">
-        <v>0.781915</v>
+        <v>0.783641</v>
       </c>
     </row>
     <row r="85">
@@ -1519,10 +1519,10 @@
         </is>
       </c>
       <c r="B85" t="n">
-        <v>0.022299</v>
+        <v>0.022121</v>
       </c>
       <c r="C85" t="n">
-        <v>0.779255</v>
+        <v>0.781003</v>
       </c>
     </row>
     <row r="86">
@@ -1532,10 +1532,10 @@
         </is>
       </c>
       <c r="B86" t="n">
-        <v>0.022324</v>
+        <v>0.022299</v>
       </c>
       <c r="C86" t="n">
-        <v>0.776596</v>
+        <v>0.7783639999999999</v>
       </c>
     </row>
     <row r="87">
@@ -1545,10 +1545,10 @@
         </is>
       </c>
       <c r="B87" t="n">
-        <v>0.022543</v>
+        <v>0.022324</v>
       </c>
       <c r="C87" t="n">
-        <v>0.773936</v>
+        <v>0.775726</v>
       </c>
     </row>
     <row r="88">
@@ -1558,10 +1558,10 @@
         </is>
       </c>
       <c r="B88" t="n">
-        <v>0.022891</v>
+        <v>0.022543</v>
       </c>
       <c r="C88" t="n">
-        <v>0.771277</v>
+        <v>0.773087</v>
       </c>
     </row>
     <row r="89">
@@ -1571,10 +1571,10 @@
         </is>
       </c>
       <c r="B89" t="n">
-        <v>0.023483</v>
+        <v>0.022891</v>
       </c>
       <c r="C89" t="n">
-        <v>0.768617</v>
+        <v>0.7704490000000001</v>
       </c>
     </row>
     <row r="90">
@@ -1584,10 +1584,10 @@
         </is>
       </c>
       <c r="B90" t="n">
-        <v>0.023843</v>
+        <v>0.023483</v>
       </c>
       <c r="C90" t="n">
-        <v>0.765957</v>
+        <v>0.76781</v>
       </c>
     </row>
     <row r="91">
@@ -1597,10 +1597,10 @@
         </is>
       </c>
       <c r="B91" t="n">
-        <v>0.023991</v>
+        <v>0.023843</v>
       </c>
       <c r="C91" t="n">
-        <v>0.763298</v>
+        <v>0.765172</v>
       </c>
     </row>
     <row r="92">
@@ -1610,10 +1610,10 @@
         </is>
       </c>
       <c r="B92" t="n">
-        <v>0.02408</v>
+        <v>0.023991</v>
       </c>
       <c r="C92" t="n">
-        <v>0.760638</v>
+        <v>0.762533</v>
       </c>
     </row>
     <row r="93">
@@ -1623,10 +1623,10 @@
         </is>
       </c>
       <c r="B93" t="n">
-        <v>0.024413</v>
+        <v>0.02408</v>
       </c>
       <c r="C93" t="n">
-        <v>0.757979</v>
+        <v>0.759894</v>
       </c>
     </row>
     <row r="94">
@@ -1636,10 +1636,10 @@
         </is>
       </c>
       <c r="B94" t="n">
-        <v>0.024896</v>
+        <v>0.024413</v>
       </c>
       <c r="C94" t="n">
-        <v>0.755319</v>
+        <v>0.757256</v>
       </c>
     </row>
     <row r="95">
@@ -1649,10 +1649,10 @@
         </is>
       </c>
       <c r="B95" t="n">
-        <v>0.025327</v>
+        <v>0.024896</v>
       </c>
       <c r="C95" t="n">
-        <v>0.75266</v>
+        <v>0.754617</v>
       </c>
     </row>
     <row r="96">
@@ -1662,10 +1662,10 @@
         </is>
       </c>
       <c r="B96" t="n">
-        <v>0.025416</v>
+        <v>0.025327</v>
       </c>
       <c r="C96" t="n">
-        <v>0.75</v>
+        <v>0.751979</v>
       </c>
     </row>
     <row r="97">
@@ -1675,10 +1675,10 @@
         </is>
       </c>
       <c r="B97" t="n">
-        <v>0.025544</v>
+        <v>0.025416</v>
       </c>
       <c r="C97" t="n">
-        <v>0.74734</v>
+        <v>0.74934</v>
       </c>
     </row>
     <row r="98">
@@ -1688,10 +1688,10 @@
         </is>
       </c>
       <c r="B98" t="n">
-        <v>0.025755</v>
+        <v>0.025544</v>
       </c>
       <c r="C98" t="n">
-        <v>0.744681</v>
+        <v>0.746702</v>
       </c>
     </row>
     <row r="99">
@@ -1701,10 +1701,10 @@
         </is>
       </c>
       <c r="B99" t="n">
-        <v>0.026545</v>
+        <v>0.025755</v>
       </c>
       <c r="C99" t="n">
-        <v>0.742021</v>
+        <v>0.744063</v>
       </c>
     </row>
     <row r="100">
@@ -1714,10 +1714,10 @@
         </is>
       </c>
       <c r="B100" t="n">
-        <v>0.027214</v>
+        <v>0.026545</v>
       </c>
       <c r="C100" t="n">
-        <v>0.739362</v>
+        <v>0.741425</v>
       </c>
     </row>
     <row r="101">
@@ -1727,10 +1727,10 @@
         </is>
       </c>
       <c r="B101" t="n">
-        <v>0.027321</v>
+        <v>0.027214</v>
       </c>
       <c r="C101" t="n">
-        <v>0.736702</v>
+        <v>0.7387860000000001</v>
       </c>
     </row>
     <row r="102">
@@ -1740,10 +1740,10 @@
         </is>
       </c>
       <c r="B102" t="n">
-        <v>0.027355</v>
+        <v>0.027321</v>
       </c>
       <c r="C102" t="n">
-        <v>0.734043</v>
+        <v>0.736148</v>
       </c>
     </row>
     <row r="103">
@@ -1753,10 +1753,10 @@
         </is>
       </c>
       <c r="B103" t="n">
-        <v>0.028098</v>
+        <v>0.027355</v>
       </c>
       <c r="C103" t="n">
-        <v>0.731383</v>
+        <v>0.733509</v>
       </c>
     </row>
     <row r="104">
@@ -1766,10 +1766,10 @@
         </is>
       </c>
       <c r="B104" t="n">
-        <v>0.028186</v>
+        <v>0.028098</v>
       </c>
       <c r="C104" t="n">
-        <v>0.728723</v>
+        <v>0.730871</v>
       </c>
     </row>
     <row r="105">
@@ -1779,10 +1779,10 @@
         </is>
       </c>
       <c r="B105" t="n">
-        <v>0.028375</v>
+        <v>0.028186</v>
       </c>
       <c r="C105" t="n">
-        <v>0.726064</v>
+        <v>0.728232</v>
       </c>
     </row>
     <row r="106">
@@ -1792,10 +1792,10 @@
         </is>
       </c>
       <c r="B106" t="n">
-        <v>0.029071</v>
+        <v>0.028375</v>
       </c>
       <c r="C106" t="n">
-        <v>0.723404</v>
+        <v>0.725594</v>
       </c>
     </row>
     <row r="107">
@@ -1805,10 +1805,10 @@
         </is>
       </c>
       <c r="B107" t="n">
-        <v>0.029588</v>
+        <v>0.029046</v>
       </c>
       <c r="C107" t="n">
-        <v>0.720745</v>
+        <v>0.722955</v>
       </c>
     </row>
     <row r="108">
@@ -1818,10 +1818,10 @@
         </is>
       </c>
       <c r="B108" t="n">
-        <v>0.029854</v>
+        <v>0.029071</v>
       </c>
       <c r="C108" t="n">
-        <v>0.718085</v>
+        <v>0.720317</v>
       </c>
     </row>
     <row r="109">
@@ -1831,10 +1831,10 @@
         </is>
       </c>
       <c r="B109" t="n">
-        <v>0.030158</v>
+        <v>0.029588</v>
       </c>
       <c r="C109" t="n">
-        <v>0.715426</v>
+        <v>0.717678</v>
       </c>
     </row>
     <row r="110">
@@ -1844,10 +1844,10 @@
         </is>
       </c>
       <c r="B110" t="n">
-        <v>0.030201</v>
+        <v>0.029854</v>
       </c>
       <c r="C110" t="n">
-        <v>0.712766</v>
+        <v>0.71504</v>
       </c>
     </row>
     <row r="111">
@@ -1857,10 +1857,10 @@
         </is>
       </c>
       <c r="B111" t="n">
-        <v>0.03027</v>
+        <v>0.030158</v>
       </c>
       <c r="C111" t="n">
-        <v>0.710106</v>
+        <v>0.712401</v>
       </c>
     </row>
     <row r="112">
@@ -1870,10 +1870,10 @@
         </is>
       </c>
       <c r="B112" t="n">
-        <v>0.030697</v>
+        <v>0.030201</v>
       </c>
       <c r="C112" t="n">
-        <v>0.707447</v>
+        <v>0.709763</v>
       </c>
     </row>
     <row r="113">
@@ -1883,10 +1883,10 @@
         </is>
       </c>
       <c r="B113" t="n">
-        <v>0.030903</v>
+        <v>0.03027</v>
       </c>
       <c r="C113" t="n">
-        <v>0.7047870000000001</v>
+        <v>0.707124</v>
       </c>
     </row>
     <row r="114">
@@ -1896,10 +1896,10 @@
         </is>
       </c>
       <c r="B114" t="n">
-        <v>0.031116</v>
+        <v>0.030697</v>
       </c>
       <c r="C114" t="n">
-        <v>0.702128</v>
+        <v>0.704485</v>
       </c>
     </row>
     <row r="115">
@@ -1909,10 +1909,10 @@
         </is>
       </c>
       <c r="B115" t="n">
-        <v>0.031127</v>
+        <v>0.030903</v>
       </c>
       <c r="C115" t="n">
-        <v>0.699468</v>
+        <v>0.701847</v>
       </c>
     </row>
     <row r="116">
@@ -1922,10 +1922,10 @@
         </is>
       </c>
       <c r="B116" t="n">
-        <v>0.031327</v>
+        <v>0.031116</v>
       </c>
       <c r="C116" t="n">
-        <v>0.696809</v>
+        <v>0.6992080000000001</v>
       </c>
     </row>
     <row r="117">
@@ -1935,10 +1935,10 @@
         </is>
       </c>
       <c r="B117" t="n">
-        <v>0.031556</v>
+        <v>0.031127</v>
       </c>
       <c r="C117" t="n">
-        <v>0.694149</v>
+        <v>0.69657</v>
       </c>
     </row>
     <row r="118">
@@ -1948,10 +1948,10 @@
         </is>
       </c>
       <c r="B118" t="n">
-        <v>0.031969</v>
+        <v>0.031327</v>
       </c>
       <c r="C118" t="n">
-        <v>0.691489</v>
+        <v>0.693931</v>
       </c>
     </row>
     <row r="119">
@@ -1961,10 +1961,10 @@
         </is>
       </c>
       <c r="B119" t="n">
-        <v>0.032545</v>
+        <v>0.031556</v>
       </c>
       <c r="C119" t="n">
-        <v>0.6888300000000001</v>
+        <v>0.691293</v>
       </c>
     </row>
     <row r="120">
@@ -1974,10 +1974,10 @@
         </is>
       </c>
       <c r="B120" t="n">
-        <v>0.032827</v>
+        <v>0.031969</v>
       </c>
       <c r="C120" t="n">
-        <v>0.6861699999999999</v>
+        <v>0.688654</v>
       </c>
     </row>
     <row r="121">
@@ -1987,10 +1987,10 @@
         </is>
       </c>
       <c r="B121" t="n">
-        <v>0.033481</v>
+        <v>0.032545</v>
       </c>
       <c r="C121" t="n">
-        <v>0.683511</v>
+        <v>0.686016</v>
       </c>
     </row>
     <row r="122">
@@ -2000,10 +2000,10 @@
         </is>
       </c>
       <c r="B122" t="n">
-        <v>0.033774</v>
+        <v>0.032827</v>
       </c>
       <c r="C122" t="n">
-        <v>0.680851</v>
+        <v>0.683377</v>
       </c>
     </row>
     <row r="123">
@@ -2013,10 +2013,10 @@
         </is>
       </c>
       <c r="B123" t="n">
-        <v>0.033884</v>
+        <v>0.033481</v>
       </c>
       <c r="C123" t="n">
-        <v>0.678191</v>
+        <v>0.680739</v>
       </c>
     </row>
     <row r="124">
@@ -2026,10 +2026,10 @@
         </is>
       </c>
       <c r="B124" t="n">
-        <v>0.034047</v>
+        <v>0.033774</v>
       </c>
       <c r="C124" t="n">
-        <v>0.675532</v>
+        <v>0.6781</v>
       </c>
     </row>
     <row r="125">
@@ -2039,10 +2039,10 @@
         </is>
       </c>
       <c r="B125" t="n">
-        <v>0.034274</v>
+        <v>0.033884</v>
       </c>
       <c r="C125" t="n">
-        <v>0.672872</v>
+        <v>0.675462</v>
       </c>
     </row>
     <row r="126">
@@ -2052,10 +2052,10 @@
         </is>
       </c>
       <c r="B126" t="n">
-        <v>0.034573</v>
+        <v>0.034047</v>
       </c>
       <c r="C126" t="n">
-        <v>0.6702129999999999</v>
+        <v>0.6728229999999999</v>
       </c>
     </row>
     <row r="127">
@@ -2065,10 +2065,10 @@
         </is>
       </c>
       <c r="B127" t="n">
-        <v>0.035039</v>
+        <v>0.034274</v>
       </c>
       <c r="C127" t="n">
-        <v>0.667553</v>
+        <v>0.670185</v>
       </c>
     </row>
     <row r="128">
@@ -2078,10 +2078,10 @@
         </is>
       </c>
       <c r="B128" t="n">
-        <v>0.035117</v>
+        <v>0.034573</v>
       </c>
       <c r="C128" t="n">
-        <v>0.664894</v>
+        <v>0.667546</v>
       </c>
     </row>
     <row r="129">
@@ -2091,10 +2091,10 @@
         </is>
       </c>
       <c r="B129" t="n">
-        <v>0.035159</v>
+        <v>0.035039</v>
       </c>
       <c r="C129" t="n">
-        <v>0.662234</v>
+        <v>0.6649080000000001</v>
       </c>
     </row>
     <row r="130">
@@ -2104,10 +2104,10 @@
         </is>
       </c>
       <c r="B130" t="n">
-        <v>0.035374</v>
+        <v>0.035117</v>
       </c>
       <c r="C130" t="n">
-        <v>0.659574</v>
+        <v>0.662269</v>
       </c>
     </row>
     <row r="131">
@@ -2117,10 +2117,10 @@
         </is>
       </c>
       <c r="B131" t="n">
-        <v>0.035654</v>
+        <v>0.035159</v>
       </c>
       <c r="C131" t="n">
-        <v>0.656915</v>
+        <v>0.659631</v>
       </c>
     </row>
     <row r="132">
@@ -2130,10 +2130,10 @@
         </is>
       </c>
       <c r="B132" t="n">
-        <v>0.036</v>
+        <v>0.035374</v>
       </c>
       <c r="C132" t="n">
-        <v>0.654255</v>
+        <v>0.656992</v>
       </c>
     </row>
     <row r="133">
@@ -2143,10 +2143,10 @@
         </is>
       </c>
       <c r="B133" t="n">
-        <v>0.036242</v>
+        <v>0.035654</v>
       </c>
       <c r="C133" t="n">
-        <v>0.651596</v>
+        <v>0.654354</v>
       </c>
     </row>
     <row r="134">
@@ -2156,10 +2156,10 @@
         </is>
       </c>
       <c r="B134" t="n">
-        <v>0.037307</v>
+        <v>0.036</v>
       </c>
       <c r="C134" t="n">
-        <v>0.648936</v>
+        <v>0.651715</v>
       </c>
     </row>
     <row r="135">
@@ -2169,10 +2169,10 @@
         </is>
       </c>
       <c r="B135" t="n">
-        <v>0.037431</v>
+        <v>0.036242</v>
       </c>
       <c r="C135" t="n">
-        <v>0.646277</v>
+        <v>0.649077</v>
       </c>
     </row>
     <row r="136">
@@ -2182,10 +2182,10 @@
         </is>
       </c>
       <c r="B136" t="n">
-        <v>0.037805</v>
+        <v>0.037307</v>
       </c>
       <c r="C136" t="n">
-        <v>0.643617</v>
+        <v>0.646438</v>
       </c>
     </row>
     <row r="137">
@@ -2195,10 +2195,10 @@
         </is>
       </c>
       <c r="B137" t="n">
-        <v>0.03815</v>
+        <v>0.037431</v>
       </c>
       <c r="C137" t="n">
-        <v>0.640957</v>
+        <v>0.643799</v>
       </c>
     </row>
     <row r="138">
@@ -2208,10 +2208,10 @@
         </is>
       </c>
       <c r="B138" t="n">
-        <v>0.038316</v>
+        <v>0.037805</v>
       </c>
       <c r="C138" t="n">
-        <v>0.638298</v>
+        <v>0.641161</v>
       </c>
     </row>
     <row r="139">
@@ -2221,10 +2221,10 @@
         </is>
       </c>
       <c r="B139" t="n">
-        <v>0.03876</v>
+        <v>0.03815</v>
       </c>
       <c r="C139" t="n">
-        <v>0.635638</v>
+        <v>0.638522</v>
       </c>
     </row>
     <row r="140">
@@ -2234,10 +2234,10 @@
         </is>
       </c>
       <c r="B140" t="n">
-        <v>0.039595</v>
+        <v>0.038316</v>
       </c>
       <c r="C140" t="n">
-        <v>0.632979</v>
+        <v>0.635884</v>
       </c>
     </row>
     <row r="141">
@@ -2247,10 +2247,10 @@
         </is>
       </c>
       <c r="B141" t="n">
-        <v>0.03982</v>
+        <v>0.03876</v>
       </c>
       <c r="C141" t="n">
-        <v>0.630319</v>
+        <v>0.6332449999999999</v>
       </c>
     </row>
     <row r="142">
@@ -2260,10 +2260,10 @@
         </is>
       </c>
       <c r="B142" t="n">
-        <v>0.040867</v>
+        <v>0.039595</v>
       </c>
       <c r="C142" t="n">
-        <v>0.62766</v>
+        <v>0.630607</v>
       </c>
     </row>
     <row r="143">
@@ -2273,10 +2273,10 @@
         </is>
       </c>
       <c r="B143" t="n">
-        <v>0.040915</v>
+        <v>0.03982</v>
       </c>
       <c r="C143" t="n">
-        <v>0.625</v>
+        <v>0.627968</v>
       </c>
     </row>
     <row r="144">
@@ -2286,10 +2286,10 @@
         </is>
       </c>
       <c r="B144" t="n">
-        <v>0.040931</v>
+        <v>0.040867</v>
       </c>
       <c r="C144" t="n">
-        <v>0.62234</v>
+        <v>0.6253300000000001</v>
       </c>
     </row>
     <row r="145">
@@ -2299,10 +2299,10 @@
         </is>
       </c>
       <c r="B145" t="n">
-        <v>0.040948</v>
+        <v>0.040915</v>
       </c>
       <c r="C145" t="n">
-        <v>0.619681</v>
+        <v>0.622691</v>
       </c>
     </row>
     <row r="146">
@@ -2312,10 +2312,10 @@
         </is>
       </c>
       <c r="B146" t="n">
-        <v>0.041019</v>
+        <v>0.040931</v>
       </c>
       <c r="C146" t="n">
-        <v>0.617021</v>
+        <v>0.620053</v>
       </c>
     </row>
     <row r="147">
@@ -2325,10 +2325,10 @@
         </is>
       </c>
       <c r="B147" t="n">
-        <v>0.041132</v>
+        <v>0.040948</v>
       </c>
       <c r="C147" t="n">
-        <v>0.614362</v>
+        <v>0.617414</v>
       </c>
     </row>
     <row r="148">
@@ -2338,10 +2338,10 @@
         </is>
       </c>
       <c r="B148" t="n">
-        <v>0.041331</v>
+        <v>0.041019</v>
       </c>
       <c r="C148" t="n">
-        <v>0.611702</v>
+        <v>0.614776</v>
       </c>
     </row>
     <row r="149">
@@ -2351,10 +2351,10 @@
         </is>
       </c>
       <c r="B149" t="n">
-        <v>0.041359</v>
+        <v>0.041132</v>
       </c>
       <c r="C149" t="n">
-        <v>0.609043</v>
+        <v>0.612137</v>
       </c>
     </row>
     <row r="150">
@@ -2364,10 +2364,10 @@
         </is>
       </c>
       <c r="B150" t="n">
-        <v>0.04197</v>
+        <v>0.041331</v>
       </c>
       <c r="C150" t="n">
-        <v>0.606383</v>
+        <v>0.609499</v>
       </c>
     </row>
     <row r="151">
@@ -2377,10 +2377,10 @@
         </is>
       </c>
       <c r="B151" t="n">
-        <v>0.042735</v>
+        <v>0.041359</v>
       </c>
       <c r="C151" t="n">
-        <v>0.603723</v>
+        <v>0.60686</v>
       </c>
     </row>
     <row r="152">
@@ -2390,10 +2390,10 @@
         </is>
       </c>
       <c r="B152" t="n">
-        <v>0.043468</v>
+        <v>0.04197</v>
       </c>
       <c r="C152" t="n">
-        <v>0.601064</v>
+        <v>0.604222</v>
       </c>
     </row>
     <row r="153">
@@ -2403,10 +2403,10 @@
         </is>
       </c>
       <c r="B153" t="n">
-        <v>0.044385</v>
+        <v>0.042735</v>
       </c>
       <c r="C153" t="n">
-        <v>0.598404</v>
+        <v>0.601583</v>
       </c>
     </row>
     <row r="154">
@@ -2416,10 +2416,10 @@
         </is>
       </c>
       <c r="B154" t="n">
-        <v>0.044556</v>
+        <v>0.043468</v>
       </c>
       <c r="C154" t="n">
-        <v>0.595745</v>
+        <v>0.5989449999999999</v>
       </c>
     </row>
     <row r="155">
@@ -2429,10 +2429,10 @@
         </is>
       </c>
       <c r="B155" t="n">
-        <v>0.044571</v>
+        <v>0.044385</v>
       </c>
       <c r="C155" t="n">
-        <v>0.593085</v>
+        <v>0.596306</v>
       </c>
     </row>
     <row r="156">
@@ -2442,10 +2442,10 @@
         </is>
       </c>
       <c r="B156" t="n">
-        <v>0.044773</v>
+        <v>0.044556</v>
       </c>
       <c r="C156" t="n">
-        <v>0.590426</v>
+        <v>0.593668</v>
       </c>
     </row>
     <row r="157">
@@ -2455,10 +2455,10 @@
         </is>
       </c>
       <c r="B157" t="n">
-        <v>0.045962</v>
+        <v>0.044571</v>
       </c>
       <c r="C157" t="n">
-        <v>0.587766</v>
+        <v>0.591029</v>
       </c>
     </row>
     <row r="158">
@@ -2468,10 +2468,10 @@
         </is>
       </c>
       <c r="B158" t="n">
-        <v>0.046486</v>
+        <v>0.044773</v>
       </c>
       <c r="C158" t="n">
-        <v>0.585106</v>
+        <v>0.588391</v>
       </c>
     </row>
     <row r="159">
@@ -2481,10 +2481,10 @@
         </is>
       </c>
       <c r="B159" t="n">
-        <v>0.046763</v>
+        <v>0.045962</v>
       </c>
       <c r="C159" t="n">
-        <v>0.582447</v>
+        <v>0.5857520000000001</v>
       </c>
     </row>
     <row r="160">
@@ -2494,10 +2494,10 @@
         </is>
       </c>
       <c r="B160" t="n">
-        <v>0.046785</v>
+        <v>0.046486</v>
       </c>
       <c r="C160" t="n">
-        <v>0.5797870000000001</v>
+        <v>0.583113</v>
       </c>
     </row>
     <row r="161">
@@ -2507,10 +2507,10 @@
         </is>
       </c>
       <c r="B161" t="n">
-        <v>0.046943</v>
+        <v>0.046763</v>
       </c>
       <c r="C161" t="n">
-        <v>0.577128</v>
+        <v>0.580475</v>
       </c>
     </row>
     <row r="162">
@@ -2520,10 +2520,10 @@
         </is>
       </c>
       <c r="B162" t="n">
-        <v>0.047141</v>
+        <v>0.046785</v>
       </c>
       <c r="C162" t="n">
-        <v>0.574468</v>
+        <v>0.577836</v>
       </c>
     </row>
     <row r="163">
@@ -2533,10 +2533,10 @@
         </is>
       </c>
       <c r="B163" t="n">
-        <v>0.047421</v>
+        <v>0.046943</v>
       </c>
       <c r="C163" t="n">
-        <v>0.571809</v>
+        <v>0.575198</v>
       </c>
     </row>
     <row r="164">
@@ -2546,10 +2546,10 @@
         </is>
       </c>
       <c r="B164" t="n">
-        <v>0.048551</v>
+        <v>0.047141</v>
       </c>
       <c r="C164" t="n">
-        <v>0.569149</v>
+        <v>0.572559</v>
       </c>
     </row>
     <row r="165">
@@ -2559,10 +2559,10 @@
         </is>
       </c>
       <c r="B165" t="n">
-        <v>0.04906</v>
+        <v>0.047421</v>
       </c>
       <c r="C165" t="n">
-        <v>0.566489</v>
+        <v>0.569921</v>
       </c>
     </row>
     <row r="166">
@@ -2572,10 +2572,10 @@
         </is>
       </c>
       <c r="B166" t="n">
-        <v>0.049358</v>
+        <v>0.048551</v>
       </c>
       <c r="C166" t="n">
-        <v>0.5638300000000001</v>
+        <v>0.567282</v>
       </c>
     </row>
     <row r="167">
@@ -2585,10 +2585,10 @@
         </is>
       </c>
       <c r="B167" t="n">
-        <v>0.049478</v>
+        <v>0.04906</v>
       </c>
       <c r="C167" t="n">
-        <v>0.5611699999999999</v>
+        <v>0.564644</v>
       </c>
     </row>
     <row r="168">
@@ -2598,10 +2598,10 @@
         </is>
       </c>
       <c r="B168" t="n">
-        <v>0.049516</v>
+        <v>0.049358</v>
       </c>
       <c r="C168" t="n">
-        <v>0.558511</v>
+        <v>0.562005</v>
       </c>
     </row>
     <row r="169">
@@ -2611,10 +2611,10 @@
         </is>
       </c>
       <c r="B169" t="n">
-        <v>0.049728</v>
+        <v>0.049478</v>
       </c>
       <c r="C169" t="n">
-        <v>0.555851</v>
+        <v>0.5593669999999999</v>
       </c>
     </row>
     <row r="170">
@@ -2624,10 +2624,10 @@
         </is>
       </c>
       <c r="B170" t="n">
-        <v>0.049754</v>
+        <v>0.049516</v>
       </c>
       <c r="C170" t="n">
-        <v>0.553191</v>
+        <v>0.556728</v>
       </c>
     </row>
     <row r="171">
@@ -2637,10 +2637,10 @@
         </is>
       </c>
       <c r="B171" t="n">
-        <v>0.051151</v>
+        <v>0.049728</v>
       </c>
       <c r="C171" t="n">
-        <v>0.550532</v>
+        <v>0.55409</v>
       </c>
     </row>
     <row r="172">
@@ -2650,10 +2650,10 @@
         </is>
       </c>
       <c r="B172" t="n">
-        <v>0.051264</v>
+        <v>0.049754</v>
       </c>
       <c r="C172" t="n">
-        <v>0.547872</v>
+        <v>0.551451</v>
       </c>
     </row>
     <row r="173">
@@ -2663,10 +2663,10 @@
         </is>
       </c>
       <c r="B173" t="n">
-        <v>0.051423</v>
+        <v>0.051151</v>
       </c>
       <c r="C173" t="n">
-        <v>0.5452129999999999</v>
+        <v>0.548813</v>
       </c>
     </row>
     <row r="174">
@@ -2676,10 +2676,10 @@
         </is>
       </c>
       <c r="B174" t="n">
-        <v>0.051449</v>
+        <v>0.051264</v>
       </c>
       <c r="C174" t="n">
-        <v>0.542553</v>
+        <v>0.546174</v>
       </c>
     </row>
     <row r="175">
@@ -2689,10 +2689,10 @@
         </is>
       </c>
       <c r="B175" t="n">
-        <v>0.051978</v>
+        <v>0.051423</v>
       </c>
       <c r="C175" t="n">
-        <v>0.539894</v>
+        <v>0.543536</v>
       </c>
     </row>
     <row r="176">
@@ -2702,10 +2702,10 @@
         </is>
       </c>
       <c r="B176" t="n">
-        <v>0.052376</v>
+        <v>0.051449</v>
       </c>
       <c r="C176" t="n">
-        <v>0.537234</v>
+        <v>0.540897</v>
       </c>
     </row>
     <row r="177">
@@ -2715,10 +2715,10 @@
         </is>
       </c>
       <c r="B177" t="n">
-        <v>0.052398</v>
+        <v>0.051978</v>
       </c>
       <c r="C177" t="n">
-        <v>0.534574</v>
+        <v>0.538259</v>
       </c>
     </row>
     <row r="178">
@@ -2728,10 +2728,10 @@
         </is>
       </c>
       <c r="B178" t="n">
-        <v>0.052682</v>
+        <v>0.052376</v>
       </c>
       <c r="C178" t="n">
-        <v>0.531915</v>
+        <v>0.53562</v>
       </c>
     </row>
     <row r="179">
@@ -2741,10 +2741,10 @@
         </is>
       </c>
       <c r="B179" t="n">
-        <v>0.052941</v>
+        <v>0.052398</v>
       </c>
       <c r="C179" t="n">
-        <v>0.529255</v>
+        <v>0.532982</v>
       </c>
     </row>
     <row r="180">
@@ -2754,10 +2754,10 @@
         </is>
       </c>
       <c r="B180" t="n">
-        <v>0.053227</v>
+        <v>0.052682</v>
       </c>
       <c r="C180" t="n">
-        <v>0.526596</v>
+        <v>0.530343</v>
       </c>
     </row>
     <row r="181">
@@ -2767,10 +2767,10 @@
         </is>
       </c>
       <c r="B181" t="n">
-        <v>0.053316</v>
+        <v>0.052941</v>
       </c>
       <c r="C181" t="n">
-        <v>0.523936</v>
+        <v>0.527704</v>
       </c>
     </row>
     <row r="182">
@@ -2780,10 +2780,10 @@
         </is>
       </c>
       <c r="B182" t="n">
-        <v>0.053555</v>
+        <v>0.053227</v>
       </c>
       <c r="C182" t="n">
-        <v>0.521277</v>
+        <v>0.525066</v>
       </c>
     </row>
     <row r="183">
@@ -2793,10 +2793,10 @@
         </is>
       </c>
       <c r="B183" t="n">
-        <v>0.05382</v>
+        <v>0.053316</v>
       </c>
       <c r="C183" t="n">
-        <v>0.518617</v>
+        <v>0.522427</v>
       </c>
     </row>
     <row r="184">
@@ -2806,10 +2806,10 @@
         </is>
       </c>
       <c r="B184" t="n">
-        <v>0.05439</v>
+        <v>0.053555</v>
       </c>
       <c r="C184" t="n">
-        <v>0.515957</v>
+        <v>0.5197889999999999</v>
       </c>
     </row>
     <row r="185">
@@ -2819,10 +2819,10 @@
         </is>
       </c>
       <c r="B185" t="n">
-        <v>0.054595</v>
+        <v>0.05382</v>
       </c>
       <c r="C185" t="n">
-        <v>0.513298</v>
+        <v>0.51715</v>
       </c>
     </row>
     <row r="186">
@@ -2832,10 +2832,10 @@
         </is>
       </c>
       <c r="B186" t="n">
-        <v>0.05496</v>
+        <v>0.05439</v>
       </c>
       <c r="C186" t="n">
-        <v>0.510638</v>
+        <v>0.514512</v>
       </c>
     </row>
     <row r="187">
@@ -2845,10 +2845,10 @@
         </is>
       </c>
       <c r="B187" t="n">
-        <v>0.0555</v>
+        <v>0.054595</v>
       </c>
       <c r="C187" t="n">
-        <v>0.507979</v>
+        <v>0.511873</v>
       </c>
     </row>
     <row r="188">
@@ -2858,10 +2858,10 @@
         </is>
       </c>
       <c r="B188" t="n">
-        <v>0.055621</v>
+        <v>0.05496</v>
       </c>
       <c r="C188" t="n">
-        <v>0.505319</v>
+        <v>0.509235</v>
       </c>
     </row>
     <row r="189">
@@ -2871,10 +2871,10 @@
         </is>
       </c>
       <c r="B189" t="n">
-        <v>0.055736</v>
+        <v>0.0555</v>
       </c>
       <c r="C189" t="n">
-        <v>0.50266</v>
+        <v>0.506596</v>
       </c>
     </row>
     <row r="190">
@@ -2884,10 +2884,10 @@
         </is>
       </c>
       <c r="B190" t="n">
-        <v>0.056242</v>
+        <v>0.055621</v>
       </c>
       <c r="C190" t="n">
-        <v>0.5</v>
+        <v>0.503958</v>
       </c>
     </row>
     <row r="191">
@@ -2897,10 +2897,10 @@
         </is>
       </c>
       <c r="B191" t="n">
-        <v>0.056433</v>
+        <v>0.055736</v>
       </c>
       <c r="C191" t="n">
-        <v>0.49734</v>
+        <v>0.501319</v>
       </c>
     </row>
     <row r="192">
@@ -2910,10 +2910,10 @@
         </is>
       </c>
       <c r="B192" t="n">
-        <v>0.056487</v>
+        <v>0.056242</v>
       </c>
       <c r="C192" t="n">
-        <v>0.494681</v>
+        <v>0.498681</v>
       </c>
     </row>
     <row r="193">
@@ -2923,10 +2923,10 @@
         </is>
       </c>
       <c r="B193" t="n">
-        <v>0.056702</v>
+        <v>0.056433</v>
       </c>
       <c r="C193" t="n">
-        <v>0.492021</v>
+        <v>0.496042</v>
       </c>
     </row>
     <row r="194">
@@ -2936,10 +2936,10 @@
         </is>
       </c>
       <c r="B194" t="n">
-        <v>0.056785</v>
+        <v>0.056487</v>
       </c>
       <c r="C194" t="n">
-        <v>0.489362</v>
+        <v>0.493404</v>
       </c>
     </row>
     <row r="195">
@@ -2949,10 +2949,10 @@
         </is>
       </c>
       <c r="B195" t="n">
-        <v>0.05854</v>
+        <v>0.056702</v>
       </c>
       <c r="C195" t="n">
-        <v>0.486702</v>
+        <v>0.490765</v>
       </c>
     </row>
     <row r="196">
@@ -2962,10 +2962,10 @@
         </is>
       </c>
       <c r="B196" t="n">
-        <v>0.058745</v>
+        <v>0.056785</v>
       </c>
       <c r="C196" t="n">
-        <v>0.484043</v>
+        <v>0.488127</v>
       </c>
     </row>
     <row r="197">
@@ -2975,10 +2975,10 @@
         </is>
       </c>
       <c r="B197" t="n">
-        <v>0.058836</v>
+        <v>0.05854</v>
       </c>
       <c r="C197" t="n">
-        <v>0.481383</v>
+        <v>0.485488</v>
       </c>
     </row>
     <row r="198">
@@ -2988,10 +2988,10 @@
         </is>
       </c>
       <c r="B198" t="n">
-        <v>0.059279</v>
+        <v>0.058745</v>
       </c>
       <c r="C198" t="n">
-        <v>0.478723</v>
+        <v>0.48285</v>
       </c>
     </row>
     <row r="199">
@@ -3001,10 +3001,10 @@
         </is>
       </c>
       <c r="B199" t="n">
-        <v>0.059367</v>
+        <v>0.058836</v>
       </c>
       <c r="C199" t="n">
-        <v>0.476064</v>
+        <v>0.480211</v>
       </c>
     </row>
     <row r="200">
@@ -3014,10 +3014,10 @@
         </is>
       </c>
       <c r="B200" t="n">
-        <v>0.059553</v>
+        <v>0.059279</v>
       </c>
       <c r="C200" t="n">
-        <v>0.473404</v>
+        <v>0.477573</v>
       </c>
     </row>
     <row r="201">
@@ -3027,10 +3027,10 @@
         </is>
       </c>
       <c r="B201" t="n">
-        <v>0.059579</v>
+        <v>0.059367</v>
       </c>
       <c r="C201" t="n">
-        <v>0.470745</v>
+        <v>0.474934</v>
       </c>
     </row>
     <row r="202">
@@ -3040,10 +3040,10 @@
         </is>
       </c>
       <c r="B202" t="n">
-        <v>0.060111</v>
+        <v>0.059553</v>
       </c>
       <c r="C202" t="n">
-        <v>0.468085</v>
+        <v>0.472296</v>
       </c>
     </row>
     <row r="203">
@@ -3053,10 +3053,10 @@
         </is>
       </c>
       <c r="B203" t="n">
-        <v>0.060827</v>
+        <v>0.059579</v>
       </c>
       <c r="C203" t="n">
-        <v>0.465426</v>
+        <v>0.469657</v>
       </c>
     </row>
     <row r="204">
@@ -3066,10 +3066,10 @@
         </is>
       </c>
       <c r="B204" t="n">
-        <v>0.060882</v>
+        <v>0.060111</v>
       </c>
       <c r="C204" t="n">
-        <v>0.462766</v>
+        <v>0.467018</v>
       </c>
     </row>
     <row r="205">
@@ -3079,10 +3079,10 @@
         </is>
       </c>
       <c r="B205" t="n">
-        <v>0.061712</v>
+        <v>0.060827</v>
       </c>
       <c r="C205" t="n">
-        <v>0.460106</v>
+        <v>0.46438</v>
       </c>
     </row>
     <row r="206">
@@ -3092,10 +3092,10 @@
         </is>
       </c>
       <c r="B206" t="n">
-        <v>0.061784</v>
+        <v>0.060882</v>
       </c>
       <c r="C206" t="n">
-        <v>0.457447</v>
+        <v>0.461741</v>
       </c>
     </row>
     <row r="207">
@@ -3105,10 +3105,10 @@
         </is>
       </c>
       <c r="B207" t="n">
-        <v>0.06179</v>
+        <v>0.061712</v>
       </c>
       <c r="C207" t="n">
-        <v>0.454787</v>
+        <v>0.459103</v>
       </c>
     </row>
     <row r="208">
@@ -3118,10 +3118,10 @@
         </is>
       </c>
       <c r="B208" t="n">
-        <v>0.061969</v>
+        <v>0.061784</v>
       </c>
       <c r="C208" t="n">
-        <v>0.452128</v>
+        <v>0.456464</v>
       </c>
     </row>
     <row r="209">
@@ -3131,10 +3131,10 @@
         </is>
       </c>
       <c r="B209" t="n">
-        <v>0.062129</v>
+        <v>0.06179</v>
       </c>
       <c r="C209" t="n">
-        <v>0.449468</v>
+        <v>0.453826</v>
       </c>
     </row>
     <row r="210">
@@ -3144,10 +3144,10 @@
         </is>
       </c>
       <c r="B210" t="n">
-        <v>0.062168</v>
+        <v>0.061969</v>
       </c>
       <c r="C210" t="n">
-        <v>0.446809</v>
+        <v>0.451187</v>
       </c>
     </row>
     <row r="211">
@@ -3157,10 +3157,10 @@
         </is>
       </c>
       <c r="B211" t="n">
-        <v>0.062246</v>
+        <v>0.062129</v>
       </c>
       <c r="C211" t="n">
-        <v>0.444149</v>
+        <v>0.448549</v>
       </c>
     </row>
     <row r="212">
@@ -3170,10 +3170,10 @@
         </is>
       </c>
       <c r="B212" t="n">
-        <v>0.06263299999999999</v>
+        <v>0.062168</v>
       </c>
       <c r="C212" t="n">
-        <v>0.441489</v>
+        <v>0.44591</v>
       </c>
     </row>
     <row r="213">
@@ -3183,10 +3183,10 @@
         </is>
       </c>
       <c r="B213" t="n">
-        <v>0.062844</v>
+        <v>0.062246</v>
       </c>
       <c r="C213" t="n">
-        <v>0.43883</v>
+        <v>0.443272</v>
       </c>
     </row>
     <row r="214">
@@ -3196,10 +3196,10 @@
         </is>
       </c>
       <c r="B214" t="n">
-        <v>0.063808</v>
+        <v>0.06263299999999999</v>
       </c>
       <c r="C214" t="n">
-        <v>0.43617</v>
+        <v>0.440633</v>
       </c>
     </row>
     <row r="215">
@@ -3209,10 +3209,10 @@
         </is>
       </c>
       <c r="B215" t="n">
-        <v>0.06464300000000001</v>
+        <v>0.062844</v>
       </c>
       <c r="C215" t="n">
-        <v>0.433511</v>
+        <v>0.437995</v>
       </c>
     </row>
     <row r="216">
@@ -3222,10 +3222,10 @@
         </is>
       </c>
       <c r="B216" t="n">
-        <v>0.064842</v>
+        <v>0.063808</v>
       </c>
       <c r="C216" t="n">
-        <v>0.430851</v>
+        <v>0.435356</v>
       </c>
     </row>
     <row r="217">
@@ -3235,10 +3235,10 @@
         </is>
       </c>
       <c r="B217" t="n">
-        <v>0.06555900000000001</v>
+        <v>0.06464300000000001</v>
       </c>
       <c r="C217" t="n">
-        <v>0.428191</v>
+        <v>0.432718</v>
       </c>
     </row>
     <row r="218">
@@ -3248,10 +3248,10 @@
         </is>
       </c>
       <c r="B218" t="n">
-        <v>0.067176</v>
+        <v>0.064842</v>
       </c>
       <c r="C218" t="n">
-        <v>0.425532</v>
+        <v>0.430079</v>
       </c>
     </row>
     <row r="219">
@@ -3261,10 +3261,10 @@
         </is>
       </c>
       <c r="B219" t="n">
-        <v>0.06736399999999999</v>
+        <v>0.06555900000000001</v>
       </c>
       <c r="C219" t="n">
-        <v>0.422872</v>
+        <v>0.427441</v>
       </c>
     </row>
     <row r="220">
@@ -3274,10 +3274,10 @@
         </is>
       </c>
       <c r="B220" t="n">
-        <v>0.067375</v>
+        <v>0.067176</v>
       </c>
       <c r="C220" t="n">
-        <v>0.420213</v>
+        <v>0.424802</v>
       </c>
     </row>
     <row r="221">
@@ -3287,10 +3287,10 @@
         </is>
       </c>
       <c r="B221" t="n">
-        <v>0.067555</v>
+        <v>0.06736399999999999</v>
       </c>
       <c r="C221" t="n">
-        <v>0.417553</v>
+        <v>0.422164</v>
       </c>
     </row>
     <row r="222">
@@ -3300,10 +3300,10 @@
         </is>
       </c>
       <c r="B222" t="n">
-        <v>0.067604</v>
+        <v>0.067375</v>
       </c>
       <c r="C222" t="n">
-        <v>0.414894</v>
+        <v>0.419525</v>
       </c>
     </row>
     <row r="223">
@@ -3313,10 +3313,10 @@
         </is>
       </c>
       <c r="B223" t="n">
-        <v>0.067644</v>
+        <v>0.067555</v>
       </c>
       <c r="C223" t="n">
-        <v>0.412234</v>
+        <v>0.416887</v>
       </c>
     </row>
     <row r="224">
@@ -3326,10 +3326,10 @@
         </is>
       </c>
       <c r="B224" t="n">
-        <v>0.068111</v>
+        <v>0.067604</v>
       </c>
       <c r="C224" t="n">
-        <v>0.409574</v>
+        <v>0.414248</v>
       </c>
     </row>
     <row r="225">
@@ -3339,10 +3339,10 @@
         </is>
       </c>
       <c r="B225" t="n">
-        <v>0.068601</v>
+        <v>0.067644</v>
       </c>
       <c r="C225" t="n">
-        <v>0.406915</v>
+        <v>0.411609</v>
       </c>
     </row>
     <row r="226">
@@ -3352,10 +3352,10 @@
         </is>
       </c>
       <c r="B226" t="n">
-        <v>0.068939</v>
+        <v>0.068111</v>
       </c>
       <c r="C226" t="n">
-        <v>0.404255</v>
+        <v>0.408971</v>
       </c>
     </row>
     <row r="227">
@@ -3365,10 +3365,10 @@
         </is>
       </c>
       <c r="B227" t="n">
-        <v>0.06909</v>
+        <v>0.068601</v>
       </c>
       <c r="C227" t="n">
-        <v>0.401596</v>
+        <v>0.406332</v>
       </c>
     </row>
     <row r="228">
@@ -3378,10 +3378,10 @@
         </is>
       </c>
       <c r="B228" t="n">
-        <v>0.069253</v>
+        <v>0.068939</v>
       </c>
       <c r="C228" t="n">
-        <v>0.398936</v>
+        <v>0.403694</v>
       </c>
     </row>
     <row r="229">
@@ -3391,10 +3391,10 @@
         </is>
       </c>
       <c r="B229" t="n">
-        <v>0.070214</v>
+        <v>0.06909</v>
       </c>
       <c r="C229" t="n">
-        <v>0.396277</v>
+        <v>0.401055</v>
       </c>
     </row>
     <row r="230">
@@ -3404,10 +3404,10 @@
         </is>
       </c>
       <c r="B230" t="n">
-        <v>0.070659</v>
+        <v>0.069253</v>
       </c>
       <c r="C230" t="n">
-        <v>0.393617</v>
+        <v>0.398417</v>
       </c>
     </row>
     <row r="231">
@@ -3417,10 +3417,10 @@
         </is>
       </c>
       <c r="B231" t="n">
-        <v>0.071394</v>
+        <v>0.070214</v>
       </c>
       <c r="C231" t="n">
-        <v>0.390957</v>
+        <v>0.395778</v>
       </c>
     </row>
     <row r="232">
@@ -3430,10 +3430,10 @@
         </is>
       </c>
       <c r="B232" t="n">
-        <v>0.072684</v>
+        <v>0.070659</v>
       </c>
       <c r="C232" t="n">
-        <v>0.388298</v>
+        <v>0.39314</v>
       </c>
     </row>
     <row r="233">
@@ -3443,10 +3443,10 @@
         </is>
       </c>
       <c r="B233" t="n">
-        <v>0.072744</v>
+        <v>0.071394</v>
       </c>
       <c r="C233" t="n">
-        <v>0.385638</v>
+        <v>0.390501</v>
       </c>
     </row>
     <row r="234">
@@ -3456,10 +3456,10 @@
         </is>
       </c>
       <c r="B234" t="n">
-        <v>0.07295599999999999</v>
+        <v>0.072684</v>
       </c>
       <c r="C234" t="n">
-        <v>0.382979</v>
+        <v>0.387863</v>
       </c>
     </row>
     <row r="235">
@@ -3469,10 +3469,10 @@
         </is>
       </c>
       <c r="B235" t="n">
-        <v>0.07331</v>
+        <v>0.072744</v>
       </c>
       <c r="C235" t="n">
-        <v>0.380319</v>
+        <v>0.385224</v>
       </c>
     </row>
     <row r="236">
@@ -3482,10 +3482,10 @@
         </is>
       </c>
       <c r="B236" t="n">
-        <v>0.07380299999999999</v>
+        <v>0.07295599999999999</v>
       </c>
       <c r="C236" t="n">
-        <v>0.37766</v>
+        <v>0.382586</v>
       </c>
     </row>
     <row r="237">
@@ -3495,10 +3495,10 @@
         </is>
       </c>
       <c r="B237" t="n">
-        <v>0.07424799999999999</v>
+        <v>0.07331</v>
       </c>
       <c r="C237" t="n">
-        <v>0.375</v>
+        <v>0.379947</v>
       </c>
     </row>
     <row r="238">
@@ -3508,10 +3508,10 @@
         </is>
       </c>
       <c r="B238" t="n">
-        <v>0.07437100000000001</v>
+        <v>0.07380299999999999</v>
       </c>
       <c r="C238" t="n">
-        <v>0.37234</v>
+        <v>0.377309</v>
       </c>
     </row>
     <row r="239">
@@ -3521,10 +3521,10 @@
         </is>
       </c>
       <c r="B239" t="n">
-        <v>0.075854</v>
+        <v>0.07424799999999999</v>
       </c>
       <c r="C239" t="n">
-        <v>0.369681</v>
+        <v>0.37467</v>
       </c>
     </row>
     <row r="240">
@@ -3534,10 +3534,10 @@
         </is>
       </c>
       <c r="B240" t="n">
-        <v>0.075876</v>
+        <v>0.07437100000000001</v>
       </c>
       <c r="C240" t="n">
-        <v>0.367021</v>
+        <v>0.372032</v>
       </c>
     </row>
     <row r="241">
@@ -3547,10 +3547,10 @@
         </is>
       </c>
       <c r="B241" t="n">
-        <v>0.076543</v>
+        <v>0.075854</v>
       </c>
       <c r="C241" t="n">
-        <v>0.364362</v>
+        <v>0.369393</v>
       </c>
     </row>
     <row r="242">
@@ -3560,10 +3560,10 @@
         </is>
       </c>
       <c r="B242" t="n">
-        <v>0.07708</v>
+        <v>0.075876</v>
       </c>
       <c r="C242" t="n">
-        <v>0.361702</v>
+        <v>0.366755</v>
       </c>
     </row>
     <row r="243">
@@ -3573,10 +3573,10 @@
         </is>
       </c>
       <c r="B243" t="n">
-        <v>0.07757799999999999</v>
+        <v>0.076543</v>
       </c>
       <c r="C243" t="n">
-        <v>0.359043</v>
+        <v>0.364116</v>
       </c>
     </row>
     <row r="244">
@@ -3586,10 +3586,10 @@
         </is>
       </c>
       <c r="B244" t="n">
-        <v>0.077863</v>
+        <v>0.07708</v>
       </c>
       <c r="C244" t="n">
-        <v>0.356383</v>
+        <v>0.361478</v>
       </c>
     </row>
     <row r="245">
@@ -3599,10 +3599,10 @@
         </is>
       </c>
       <c r="B245" t="n">
-        <v>0.077912</v>
+        <v>0.07757799999999999</v>
       </c>
       <c r="C245" t="n">
-        <v>0.353723</v>
+        <v>0.358839</v>
       </c>
     </row>
     <row r="246">
@@ -3612,10 +3612,10 @@
         </is>
       </c>
       <c r="B246" t="n">
-        <v>0.078084</v>
+        <v>0.077863</v>
       </c>
       <c r="C246" t="n">
-        <v>0.351064</v>
+        <v>0.356201</v>
       </c>
     </row>
     <row r="247">
@@ -3625,10 +3625,10 @@
         </is>
       </c>
       <c r="B247" t="n">
-        <v>0.07921499999999999</v>
+        <v>0.077912</v>
       </c>
       <c r="C247" t="n">
-        <v>0.348404</v>
+        <v>0.353562</v>
       </c>
     </row>
     <row r="248">
@@ -3638,10 +3638,10 @@
         </is>
       </c>
       <c r="B248" t="n">
-        <v>0.08092199999999999</v>
+        <v>0.078084</v>
       </c>
       <c r="C248" t="n">
-        <v>0.345745</v>
+        <v>0.350923</v>
       </c>
     </row>
     <row r="249">
@@ -3651,10 +3651,10 @@
         </is>
       </c>
       <c r="B249" t="n">
-        <v>0.081607</v>
+        <v>0.07921499999999999</v>
       </c>
       <c r="C249" t="n">
-        <v>0.343085</v>
+        <v>0.348285</v>
       </c>
     </row>
     <row r="250">
@@ -3664,10 +3664,10 @@
         </is>
       </c>
       <c r="B250" t="n">
-        <v>0.081758</v>
+        <v>0.08092199999999999</v>
       </c>
       <c r="C250" t="n">
-        <v>0.340426</v>
+        <v>0.345646</v>
       </c>
     </row>
     <row r="251">
@@ -3677,10 +3677,10 @@
         </is>
       </c>
       <c r="B251" t="n">
-        <v>0.08192000000000001</v>
+        <v>0.081607</v>
       </c>
       <c r="C251" t="n">
-        <v>0.337766</v>
+        <v>0.343008</v>
       </c>
     </row>
     <row r="252">
@@ -3690,10 +3690,10 @@
         </is>
       </c>
       <c r="B252" t="n">
-        <v>0.082479</v>
+        <v>0.081758</v>
       </c>
       <c r="C252" t="n">
-        <v>0.335106</v>
+        <v>0.340369</v>
       </c>
     </row>
     <row r="253">
@@ -3703,10 +3703,10 @@
         </is>
       </c>
       <c r="B253" t="n">
-        <v>0.08254300000000001</v>
+        <v>0.08192000000000001</v>
       </c>
       <c r="C253" t="n">
-        <v>0.332447</v>
+        <v>0.337731</v>
       </c>
     </row>
     <row r="254">
@@ -3716,10 +3716,10 @@
         </is>
       </c>
       <c r="B254" t="n">
-        <v>0.082594</v>
+        <v>0.082479</v>
       </c>
       <c r="C254" t="n">
-        <v>0.329787</v>
+        <v>0.335092</v>
       </c>
     </row>
     <row r="255">
@@ -3729,10 +3729,10 @@
         </is>
       </c>
       <c r="B255" t="n">
-        <v>0.083297</v>
+        <v>0.08254300000000001</v>
       </c>
       <c r="C255" t="n">
-        <v>0.327128</v>
+        <v>0.332454</v>
       </c>
     </row>
     <row r="256">
@@ -3742,10 +3742,10 @@
         </is>
       </c>
       <c r="B256" t="n">
-        <v>0.083664</v>
+        <v>0.082594</v>
       </c>
       <c r="C256" t="n">
-        <v>0.324468</v>
+        <v>0.329815</v>
       </c>
     </row>
     <row r="257">
@@ -3755,10 +3755,10 @@
         </is>
       </c>
       <c r="B257" t="n">
-        <v>0.08384800000000001</v>
+        <v>0.083297</v>
       </c>
       <c r="C257" t="n">
-        <v>0.321809</v>
+        <v>0.327177</v>
       </c>
     </row>
     <row r="258">
@@ -3768,10 +3768,10 @@
         </is>
       </c>
       <c r="B258" t="n">
-        <v>0.084221</v>
+        <v>0.083664</v>
       </c>
       <c r="C258" t="n">
-        <v>0.319149</v>
+        <v>0.324538</v>
       </c>
     </row>
     <row r="259">
@@ -3781,10 +3781,10 @@
         </is>
       </c>
       <c r="B259" t="n">
-        <v>0.08483599999999999</v>
+        <v>0.08384800000000001</v>
       </c>
       <c r="C259" t="n">
-        <v>0.316489</v>
+        <v>0.3219</v>
       </c>
     </row>
     <row r="260">
@@ -3794,10 +3794,10 @@
         </is>
       </c>
       <c r="B260" t="n">
-        <v>0.08586199999999999</v>
+        <v>0.084221</v>
       </c>
       <c r="C260" t="n">
-        <v>0.31383</v>
+        <v>0.319261</v>
       </c>
     </row>
     <row r="261">
@@ -3807,10 +3807,10 @@
         </is>
       </c>
       <c r="B261" t="n">
-        <v>0.087156</v>
+        <v>0.08483599999999999</v>
       </c>
       <c r="C261" t="n">
-        <v>0.31117</v>
+        <v>0.316623</v>
       </c>
     </row>
     <row r="262">
@@ -3820,10 +3820,10 @@
         </is>
       </c>
       <c r="B262" t="n">
-        <v>0.08717999999999999</v>
+        <v>0.08586199999999999</v>
       </c>
       <c r="C262" t="n">
-        <v>0.308511</v>
+        <v>0.313984</v>
       </c>
     </row>
     <row r="263">
@@ -3833,10 +3833,10 @@
         </is>
       </c>
       <c r="B263" t="n">
-        <v>0.08820799999999999</v>
+        <v>0.087156</v>
       </c>
       <c r="C263" t="n">
-        <v>0.305851</v>
+        <v>0.311346</v>
       </c>
     </row>
     <row r="264">
@@ -3846,10 +3846,10 @@
         </is>
       </c>
       <c r="B264" t="n">
-        <v>0.088889</v>
+        <v>0.08717999999999999</v>
       </c>
       <c r="C264" t="n">
-        <v>0.303191</v>
+        <v>0.308707</v>
       </c>
     </row>
     <row r="265">
@@ -3859,10 +3859,10 @@
         </is>
       </c>
       <c r="B265" t="n">
-        <v>0.08917700000000001</v>
+        <v>0.08820799999999999</v>
       </c>
       <c r="C265" t="n">
-        <v>0.300532</v>
+        <v>0.306069</v>
       </c>
     </row>
     <row r="266">
@@ -3872,10 +3872,10 @@
         </is>
       </c>
       <c r="B266" t="n">
-        <v>0.089823</v>
+        <v>0.088889</v>
       </c>
       <c r="C266" t="n">
-        <v>0.297872</v>
+        <v>0.30343</v>
       </c>
     </row>
     <row r="267">
@@ -3885,10 +3885,10 @@
         </is>
       </c>
       <c r="B267" t="n">
-        <v>0.090265</v>
+        <v>0.08917700000000001</v>
       </c>
       <c r="C267" t="n">
-        <v>0.295213</v>
+        <v>0.300792</v>
       </c>
     </row>
     <row r="268">
@@ -3898,10 +3898,10 @@
         </is>
       </c>
       <c r="B268" t="n">
-        <v>0.090348</v>
+        <v>0.089823</v>
       </c>
       <c r="C268" t="n">
-        <v>0.292553</v>
+        <v>0.298153</v>
       </c>
     </row>
     <row r="269">
@@ -3911,10 +3911,10 @@
         </is>
       </c>
       <c r="B269" t="n">
-        <v>0.090809</v>
+        <v>0.090265</v>
       </c>
       <c r="C269" t="n">
-        <v>0.289894</v>
+        <v>0.295515</v>
       </c>
     </row>
     <row r="270">
@@ -3924,10 +3924,10 @@
         </is>
       </c>
       <c r="B270" t="n">
-        <v>0.090958</v>
+        <v>0.090348</v>
       </c>
       <c r="C270" t="n">
-        <v>0.287234</v>
+        <v>0.292876</v>
       </c>
     </row>
     <row r="271">
@@ -3937,10 +3937,10 @@
         </is>
       </c>
       <c r="B271" t="n">
-        <v>0.091434</v>
+        <v>0.090809</v>
       </c>
       <c r="C271" t="n">
-        <v>0.284574</v>
+        <v>0.290237</v>
       </c>
     </row>
     <row r="272">
@@ -3950,10 +3950,10 @@
         </is>
       </c>
       <c r="B272" t="n">
-        <v>0.0929</v>
+        <v>0.090958</v>
       </c>
       <c r="C272" t="n">
-        <v>0.281915</v>
+        <v>0.287599</v>
       </c>
     </row>
     <row r="273">
@@ -3963,10 +3963,10 @@
         </is>
       </c>
       <c r="B273" t="n">
-        <v>0.093237</v>
+        <v>0.091434</v>
       </c>
       <c r="C273" t="n">
-        <v>0.279255</v>
+        <v>0.28496</v>
       </c>
     </row>
     <row r="274">
@@ -3976,10 +3976,10 @@
         </is>
       </c>
       <c r="B274" t="n">
-        <v>0.097923</v>
+        <v>0.0929</v>
       </c>
       <c r="C274" t="n">
-        <v>0.276596</v>
+        <v>0.282322</v>
       </c>
     </row>
     <row r="275">
@@ -3989,10 +3989,10 @@
         </is>
       </c>
       <c r="B275" t="n">
-        <v>0.098237</v>
+        <v>0.093237</v>
       </c>
       <c r="C275" t="n">
-        <v>0.273936</v>
+        <v>0.279683</v>
       </c>
     </row>
     <row r="276">
@@ -4002,10 +4002,10 @@
         </is>
       </c>
       <c r="B276" t="n">
-        <v>0.09847400000000001</v>
+        <v>0.097923</v>
       </c>
       <c r="C276" t="n">
-        <v>0.271277</v>
+        <v>0.277045</v>
       </c>
     </row>
     <row r="277">
@@ -4015,10 +4015,10 @@
         </is>
       </c>
       <c r="B277" t="n">
-        <v>0.09907299999999999</v>
+        <v>0.098237</v>
       </c>
       <c r="C277" t="n">
-        <v>0.268617</v>
+        <v>0.274406</v>
       </c>
     </row>
     <row r="278">
@@ -4028,10 +4028,10 @@
         </is>
       </c>
       <c r="B278" t="n">
-        <v>0.09943399999999999</v>
+        <v>0.09847400000000001</v>
       </c>
       <c r="C278" t="n">
-        <v>0.265957</v>
+        <v>0.271768</v>
       </c>
     </row>
     <row r="279">
@@ -4041,10 +4041,10 @@
         </is>
       </c>
       <c r="B279" t="n">
-        <v>0.100571</v>
+        <v>0.09907299999999999</v>
       </c>
       <c r="C279" t="n">
-        <v>0.263298</v>
+        <v>0.269129</v>
       </c>
     </row>
     <row r="280">
@@ -4054,10 +4054,10 @@
         </is>
       </c>
       <c r="B280" t="n">
-        <v>0.101335</v>
+        <v>0.09943399999999999</v>
       </c>
       <c r="C280" t="n">
-        <v>0.260638</v>
+        <v>0.266491</v>
       </c>
     </row>
     <row r="281">
@@ -4067,10 +4067,10 @@
         </is>
       </c>
       <c r="B281" t="n">
-        <v>0.103451</v>
+        <v>0.100571</v>
       </c>
       <c r="C281" t="n">
-        <v>0.257979</v>
+        <v>0.263852</v>
       </c>
     </row>
     <row r="282">
@@ -4080,10 +4080,10 @@
         </is>
       </c>
       <c r="B282" t="n">
-        <v>0.103942</v>
+        <v>0.101335</v>
       </c>
       <c r="C282" t="n">
-        <v>0.255319</v>
+        <v>0.261214</v>
       </c>
     </row>
     <row r="283">
@@ -4093,10 +4093,10 @@
         </is>
       </c>
       <c r="B283" t="n">
-        <v>0.10427</v>
+        <v>0.103451</v>
       </c>
       <c r="C283" t="n">
-        <v>0.25266</v>
+        <v>0.258575</v>
       </c>
     </row>
     <row r="284">
@@ -4106,10 +4106,10 @@
         </is>
       </c>
       <c r="B284" t="n">
-        <v>0.105774</v>
+        <v>0.103942</v>
       </c>
       <c r="C284" t="n">
-        <v>0.25</v>
+        <v>0.255937</v>
       </c>
     </row>
     <row r="285">
@@ -4119,10 +4119,10 @@
         </is>
       </c>
       <c r="B285" t="n">
-        <v>0.106391</v>
+        <v>0.10427</v>
       </c>
       <c r="C285" t="n">
-        <v>0.24734</v>
+        <v>0.253298</v>
       </c>
     </row>
     <row r="286">
@@ -4132,10 +4132,10 @@
         </is>
       </c>
       <c r="B286" t="n">
-        <v>0.106564</v>
+        <v>0.105774</v>
       </c>
       <c r="C286" t="n">
-        <v>0.244681</v>
+        <v>0.25066</v>
       </c>
     </row>
     <row r="287">
@@ -4145,10 +4145,10 @@
         </is>
       </c>
       <c r="B287" t="n">
-        <v>0.106852</v>
+        <v>0.106391</v>
       </c>
       <c r="C287" t="n">
-        <v>0.242021</v>
+        <v>0.248021</v>
       </c>
     </row>
     <row r="288">
@@ -4158,10 +4158,10 @@
         </is>
       </c>
       <c r="B288" t="n">
-        <v>0.107359</v>
+        <v>0.106564</v>
       </c>
       <c r="C288" t="n">
-        <v>0.239362</v>
+        <v>0.245383</v>
       </c>
     </row>
     <row r="289">
@@ -4171,10 +4171,10 @@
         </is>
       </c>
       <c r="B289" t="n">
-        <v>0.110708</v>
+        <v>0.106852</v>
       </c>
       <c r="C289" t="n">
-        <v>0.236702</v>
+        <v>0.242744</v>
       </c>
     </row>
     <row r="290">
@@ -4184,10 +4184,10 @@
         </is>
       </c>
       <c r="B290" t="n">
-        <v>0.111683</v>
+        <v>0.107359</v>
       </c>
       <c r="C290" t="n">
-        <v>0.234043</v>
+        <v>0.240106</v>
       </c>
     </row>
     <row r="291">
@@ -4197,10 +4197,10 @@
         </is>
       </c>
       <c r="B291" t="n">
-        <v>0.112861</v>
+        <v>0.110708</v>
       </c>
       <c r="C291" t="n">
-        <v>0.231383</v>
+        <v>0.237467</v>
       </c>
     </row>
     <row r="292">
@@ -4210,10 +4210,10 @@
         </is>
       </c>
       <c r="B292" t="n">
-        <v>0.11394</v>
+        <v>0.111683</v>
       </c>
       <c r="C292" t="n">
-        <v>0.228723</v>
+        <v>0.234828</v>
       </c>
     </row>
     <row r="293">
@@ -4223,10 +4223,10 @@
         </is>
       </c>
       <c r="B293" t="n">
-        <v>0.114179</v>
+        <v>0.112861</v>
       </c>
       <c r="C293" t="n">
-        <v>0.226064</v>
+        <v>0.23219</v>
       </c>
     </row>
     <row r="294">
@@ -4236,10 +4236,10 @@
         </is>
       </c>
       <c r="B294" t="n">
-        <v>0.11468</v>
+        <v>0.11394</v>
       </c>
       <c r="C294" t="n">
-        <v>0.223404</v>
+        <v>0.229551</v>
       </c>
     </row>
     <row r="295">
@@ -4249,10 +4249,10 @@
         </is>
       </c>
       <c r="B295" t="n">
-        <v>0.115972</v>
+        <v>0.114179</v>
       </c>
       <c r="C295" t="n">
-        <v>0.220745</v>
+        <v>0.226913</v>
       </c>
     </row>
     <row r="296">
@@ -4262,10 +4262,10 @@
         </is>
       </c>
       <c r="B296" t="n">
-        <v>0.117496</v>
+        <v>0.11468</v>
       </c>
       <c r="C296" t="n">
-        <v>0.218085</v>
+        <v>0.224274</v>
       </c>
     </row>
     <row r="297">
@@ -4275,10 +4275,10 @@
         </is>
       </c>
       <c r="B297" t="n">
-        <v>0.117846</v>
+        <v>0.115972</v>
       </c>
       <c r="C297" t="n">
-        <v>0.215426</v>
+        <v>0.221636</v>
       </c>
     </row>
     <row r="298">
@@ -4288,10 +4288,10 @@
         </is>
       </c>
       <c r="B298" t="n">
-        <v>0.119464</v>
+        <v>0.117496</v>
       </c>
       <c r="C298" t="n">
-        <v>0.212766</v>
+        <v>0.218997</v>
       </c>
     </row>
     <row r="299">
@@ -4301,10 +4301,10 @@
         </is>
       </c>
       <c r="B299" t="n">
-        <v>0.120351</v>
+        <v>0.117846</v>
       </c>
       <c r="C299" t="n">
-        <v>0.210106</v>
+        <v>0.216359</v>
       </c>
     </row>
     <row r="300">
@@ -4314,10 +4314,10 @@
         </is>
       </c>
       <c r="B300" t="n">
-        <v>0.120448</v>
+        <v>0.119464</v>
       </c>
       <c r="C300" t="n">
-        <v>0.207447</v>
+        <v>0.21372</v>
       </c>
     </row>
     <row r="301">
@@ -4327,10 +4327,10 @@
         </is>
       </c>
       <c r="B301" t="n">
-        <v>0.121637</v>
+        <v>0.120351</v>
       </c>
       <c r="C301" t="n">
-        <v>0.204787</v>
+        <v>0.211082</v>
       </c>
     </row>
     <row r="302">
@@ -4340,10 +4340,10 @@
         </is>
       </c>
       <c r="B302" t="n">
-        <v>0.12397</v>
+        <v>0.120448</v>
       </c>
       <c r="C302" t="n">
-        <v>0.202128</v>
+        <v>0.208443</v>
       </c>
     </row>
     <row r="303">
@@ -4353,10 +4353,10 @@
         </is>
       </c>
       <c r="B303" t="n">
-        <v>0.124167</v>
+        <v>0.121637</v>
       </c>
       <c r="C303" t="n">
-        <v>0.199468</v>
+        <v>0.205805</v>
       </c>
     </row>
     <row r="304">
@@ -4366,10 +4366,10 @@
         </is>
       </c>
       <c r="B304" t="n">
-        <v>0.126891</v>
+        <v>0.12397</v>
       </c>
       <c r="C304" t="n">
-        <v>0.196809</v>
+        <v>0.203166</v>
       </c>
     </row>
     <row r="305">
@@ -4379,10 +4379,10 @@
         </is>
       </c>
       <c r="B305" t="n">
-        <v>0.128021</v>
+        <v>0.124167</v>
       </c>
       <c r="C305" t="n">
-        <v>0.194149</v>
+        <v>0.200528</v>
       </c>
     </row>
     <row r="306">
@@ -4392,10 +4392,10 @@
         </is>
       </c>
       <c r="B306" t="n">
-        <v>0.128976</v>
+        <v>0.126891</v>
       </c>
       <c r="C306" t="n">
-        <v>0.191489</v>
+        <v>0.197889</v>
       </c>
     </row>
     <row r="307">
@@ -4405,10 +4405,10 @@
         </is>
       </c>
       <c r="B307" t="n">
-        <v>0.130439</v>
+        <v>0.128021</v>
       </c>
       <c r="C307" t="n">
-        <v>0.18883</v>
+        <v>0.195251</v>
       </c>
     </row>
     <row r="308">
@@ -4418,10 +4418,10 @@
         </is>
       </c>
       <c r="B308" t="n">
-        <v>0.130821</v>
+        <v>0.128976</v>
       </c>
       <c r="C308" t="n">
-        <v>0.18617</v>
+        <v>0.192612</v>
       </c>
     </row>
     <row r="309">
@@ -4431,10 +4431,10 @@
         </is>
       </c>
       <c r="B309" t="n">
-        <v>0.130916</v>
+        <v>0.130439</v>
       </c>
       <c r="C309" t="n">
-        <v>0.183511</v>
+        <v>0.189974</v>
       </c>
     </row>
     <row r="310">
@@ -4444,10 +4444,10 @@
         </is>
       </c>
       <c r="B310" t="n">
-        <v>0.135669</v>
+        <v>0.130821</v>
       </c>
       <c r="C310" t="n">
-        <v>0.180851</v>
+        <v>0.187335</v>
       </c>
     </row>
     <row r="311">
@@ -4457,10 +4457,10 @@
         </is>
       </c>
       <c r="B311" t="n">
-        <v>0.135827</v>
+        <v>0.130916</v>
       </c>
       <c r="C311" t="n">
-        <v>0.178191</v>
+        <v>0.184697</v>
       </c>
     </row>
     <row r="312">
@@ -4470,10 +4470,10 @@
         </is>
       </c>
       <c r="B312" t="n">
-        <v>0.137023</v>
+        <v>0.135669</v>
       </c>
       <c r="C312" t="n">
-        <v>0.175532</v>
+        <v>0.182058</v>
       </c>
     </row>
     <row r="313">
@@ -4483,10 +4483,10 @@
         </is>
       </c>
       <c r="B313" t="n">
-        <v>0.13733</v>
+        <v>0.135827</v>
       </c>
       <c r="C313" t="n">
-        <v>0.172872</v>
+        <v>0.17942</v>
       </c>
     </row>
     <row r="314">
@@ -4496,10 +4496,10 @@
         </is>
       </c>
       <c r="B314" t="n">
-        <v>0.138762</v>
+        <v>0.137023</v>
       </c>
       <c r="C314" t="n">
-        <v>0.170213</v>
+        <v>0.176781</v>
       </c>
     </row>
     <row r="315">
@@ -4509,10 +4509,10 @@
         </is>
       </c>
       <c r="B315" t="n">
-        <v>0.139275</v>
+        <v>0.13733</v>
       </c>
       <c r="C315" t="n">
-        <v>0.167553</v>
+        <v>0.174142</v>
       </c>
     </row>
     <row r="316">
@@ -4522,10 +4522,10 @@
         </is>
       </c>
       <c r="B316" t="n">
-        <v>0.140029</v>
+        <v>0.138762</v>
       </c>
       <c r="C316" t="n">
-        <v>0.164894</v>
+        <v>0.171504</v>
       </c>
     </row>
     <row r="317">
@@ -4535,10 +4535,10 @@
         </is>
       </c>
       <c r="B317" t="n">
-        <v>0.140099</v>
+        <v>0.139275</v>
       </c>
       <c r="C317" t="n">
-        <v>0.162234</v>
+        <v>0.168865</v>
       </c>
     </row>
     <row r="318">
@@ -4548,10 +4548,10 @@
         </is>
       </c>
       <c r="B318" t="n">
-        <v>0.140214</v>
+        <v>0.140029</v>
       </c>
       <c r="C318" t="n">
-        <v>0.159574</v>
+        <v>0.166227</v>
       </c>
     </row>
     <row r="319">
@@ -4561,10 +4561,10 @@
         </is>
       </c>
       <c r="B319" t="n">
-        <v>0.141914</v>
+        <v>0.140099</v>
       </c>
       <c r="C319" t="n">
-        <v>0.156915</v>
+        <v>0.163588</v>
       </c>
     </row>
     <row r="320">
@@ -4574,10 +4574,10 @@
         </is>
       </c>
       <c r="B320" t="n">
-        <v>0.144579</v>
+        <v>0.140214</v>
       </c>
       <c r="C320" t="n">
-        <v>0.154255</v>
+        <v>0.16095</v>
       </c>
     </row>
     <row r="321">
@@ -4587,10 +4587,10 @@
         </is>
       </c>
       <c r="B321" t="n">
-        <v>0.145008</v>
+        <v>0.141914</v>
       </c>
       <c r="C321" t="n">
-        <v>0.151596</v>
+        <v>0.158311</v>
       </c>
     </row>
     <row r="322">
@@ -4600,10 +4600,10 @@
         </is>
       </c>
       <c r="B322" t="n">
-        <v>0.145291</v>
+        <v>0.144579</v>
       </c>
       <c r="C322" t="n">
-        <v>0.148936</v>
+        <v>0.155673</v>
       </c>
     </row>
     <row r="323">
@@ -4613,10 +4613,10 @@
         </is>
       </c>
       <c r="B323" t="n">
-        <v>0.145554</v>
+        <v>0.145008</v>
       </c>
       <c r="C323" t="n">
-        <v>0.146277</v>
+        <v>0.153034</v>
       </c>
     </row>
     <row r="324">
@@ -4626,10 +4626,10 @@
         </is>
       </c>
       <c r="B324" t="n">
-        <v>0.151419</v>
+        <v>0.145291</v>
       </c>
       <c r="C324" t="n">
-        <v>0.143617</v>
+        <v>0.150396</v>
       </c>
     </row>
     <row r="325">
@@ -4639,10 +4639,10 @@
         </is>
       </c>
       <c r="B325" t="n">
-        <v>0.151465</v>
+        <v>0.145554</v>
       </c>
       <c r="C325" t="n">
-        <v>0.140957</v>
+        <v>0.147757</v>
       </c>
     </row>
     <row r="326">
@@ -4652,10 +4652,10 @@
         </is>
       </c>
       <c r="B326" t="n">
-        <v>0.151822</v>
+        <v>0.151419</v>
       </c>
       <c r="C326" t="n">
-        <v>0.138298</v>
+        <v>0.145119</v>
       </c>
     </row>
     <row r="327">
@@ -4665,10 +4665,10 @@
         </is>
       </c>
       <c r="B327" t="n">
-        <v>0.15511</v>
+        <v>0.151465</v>
       </c>
       <c r="C327" t="n">
-        <v>0.135638</v>
+        <v>0.14248</v>
       </c>
     </row>
     <row r="328">
@@ -4678,10 +4678,10 @@
         </is>
       </c>
       <c r="B328" t="n">
-        <v>0.15559</v>
+        <v>0.151822</v>
       </c>
       <c r="C328" t="n">
-        <v>0.132979</v>
+        <v>0.139842</v>
       </c>
     </row>
     <row r="329">
@@ -4691,10 +4691,10 @@
         </is>
       </c>
       <c r="B329" t="n">
-        <v>0.155726</v>
+        <v>0.15511</v>
       </c>
       <c r="C329" t="n">
-        <v>0.130319</v>
+        <v>0.137203</v>
       </c>
     </row>
     <row r="330">
@@ -4704,10 +4704,10 @@
         </is>
       </c>
       <c r="B330" t="n">
-        <v>0.156434</v>
+        <v>0.15559</v>
       </c>
       <c r="C330" t="n">
-        <v>0.12766</v>
+        <v>0.134565</v>
       </c>
     </row>
     <row r="331">
@@ -4717,10 +4717,10 @@
         </is>
       </c>
       <c r="B331" t="n">
-        <v>0.158503</v>
+        <v>0.155726</v>
       </c>
       <c r="C331" t="n">
-        <v>0.125</v>
+        <v>0.131926</v>
       </c>
     </row>
     <row r="332">
@@ -4730,10 +4730,10 @@
         </is>
       </c>
       <c r="B332" t="n">
-        <v>0.16241</v>
+        <v>0.156434</v>
       </c>
       <c r="C332" t="n">
-        <v>0.12234</v>
+        <v>0.129288</v>
       </c>
     </row>
     <row r="333">
@@ -4743,10 +4743,10 @@
         </is>
       </c>
       <c r="B333" t="n">
-        <v>0.167126</v>
+        <v>0.158503</v>
       </c>
       <c r="C333" t="n">
-        <v>0.119681</v>
+        <v>0.126649</v>
       </c>
     </row>
     <row r="334">
@@ -4756,10 +4756,10 @@
         </is>
       </c>
       <c r="B334" t="n">
-        <v>0.172262</v>
+        <v>0.16241</v>
       </c>
       <c r="C334" t="n">
-        <v>0.117021</v>
+        <v>0.124011</v>
       </c>
     </row>
     <row r="335">
@@ -4769,10 +4769,10 @@
         </is>
       </c>
       <c r="B335" t="n">
-        <v>0.183042</v>
+        <v>0.167126</v>
       </c>
       <c r="C335" t="n">
-        <v>0.114362</v>
+        <v>0.121372</v>
       </c>
     </row>
     <row r="336">
@@ -4782,10 +4782,10 @@
         </is>
       </c>
       <c r="B336" t="n">
-        <v>0.187612</v>
+        <v>0.172262</v>
       </c>
       <c r="C336" t="n">
-        <v>0.111702</v>
+        <v>0.118734</v>
       </c>
     </row>
     <row r="337">
@@ -4795,10 +4795,10 @@
         </is>
       </c>
       <c r="B337" t="n">
-        <v>0.189387</v>
+        <v>0.179571</v>
       </c>
       <c r="C337" t="n">
-        <v>0.109043</v>
+        <v>0.116095</v>
       </c>
     </row>
     <row r="338">
@@ -4808,10 +4808,10 @@
         </is>
       </c>
       <c r="B338" t="n">
-        <v>0.193249</v>
+        <v>0.183042</v>
       </c>
       <c r="C338" t="n">
-        <v>0.106383</v>
+        <v>0.113456</v>
       </c>
     </row>
     <row r="339">
@@ -4821,10 +4821,10 @@
         </is>
       </c>
       <c r="B339" t="n">
-        <v>0.195388</v>
+        <v>0.187612</v>
       </c>
       <c r="C339" t="n">
-        <v>0.103723</v>
+        <v>0.110818</v>
       </c>
     </row>
     <row r="340">
@@ -4834,10 +4834,10 @@
         </is>
       </c>
       <c r="B340" t="n">
-        <v>0.200683</v>
+        <v>0.189387</v>
       </c>
       <c r="C340" t="n">
-        <v>0.101064</v>
+        <v>0.108179</v>
       </c>
     </row>
     <row r="341">
@@ -4847,10 +4847,10 @@
         </is>
       </c>
       <c r="B341" t="n">
-        <v>0.202141</v>
+        <v>0.193249</v>
       </c>
       <c r="C341" t="n">
-        <v>0.09840400000000001</v>
+        <v>0.105541</v>
       </c>
     </row>
     <row r="342">
@@ -4860,10 +4860,10 @@
         </is>
       </c>
       <c r="B342" t="n">
-        <v>0.206803</v>
+        <v>0.195388</v>
       </c>
       <c r="C342" t="n">
-        <v>0.095745</v>
+        <v>0.102902</v>
       </c>
     </row>
     <row r="343">
@@ -4873,10 +4873,10 @@
         </is>
       </c>
       <c r="B343" t="n">
-        <v>0.21126</v>
+        <v>0.200683</v>
       </c>
       <c r="C343" t="n">
-        <v>0.093085</v>
+        <v>0.100264</v>
       </c>
     </row>
     <row r="344">
@@ -4886,10 +4886,10 @@
         </is>
       </c>
       <c r="B344" t="n">
-        <v>0.212282</v>
+        <v>0.202141</v>
       </c>
       <c r="C344" t="n">
-        <v>0.09042600000000001</v>
+        <v>0.097625</v>
       </c>
     </row>
     <row r="345">
@@ -4899,10 +4899,10 @@
         </is>
       </c>
       <c r="B345" t="n">
-        <v>0.213977</v>
+        <v>0.206803</v>
       </c>
       <c r="C345" t="n">
-        <v>0.087766</v>
+        <v>0.094987</v>
       </c>
     </row>
     <row r="346">
@@ -4912,10 +4912,10 @@
         </is>
       </c>
       <c r="B346" t="n">
-        <v>0.224095</v>
+        <v>0.21126</v>
       </c>
       <c r="C346" t="n">
-        <v>0.085106</v>
+        <v>0.092348</v>
       </c>
     </row>
     <row r="347">
@@ -4925,10 +4925,10 @@
         </is>
       </c>
       <c r="B347" t="n">
-        <v>0.229443</v>
+        <v>0.212282</v>
       </c>
       <c r="C347" t="n">
-        <v>0.08244700000000001</v>
+        <v>0.08971</v>
       </c>
     </row>
     <row r="348">
@@ -4938,10 +4938,10 @@
         </is>
       </c>
       <c r="B348" t="n">
-        <v>0.235662</v>
+        <v>0.213977</v>
       </c>
       <c r="C348" t="n">
-        <v>0.079787</v>
+        <v>0.087071</v>
       </c>
     </row>
     <row r="349">
@@ -4951,10 +4951,10 @@
         </is>
       </c>
       <c r="B349" t="n">
-        <v>0.245733</v>
+        <v>0.224095</v>
       </c>
       <c r="C349" t="n">
-        <v>0.077128</v>
+        <v>0.08443299999999999</v>
       </c>
     </row>
     <row r="350">
@@ -4964,10 +4964,10 @@
         </is>
       </c>
       <c r="B350" t="n">
-        <v>0.257813</v>
+        <v>0.229443</v>
       </c>
       <c r="C350" t="n">
-        <v>0.07446800000000001</v>
+        <v>0.08179400000000001</v>
       </c>
     </row>
     <row r="351">
@@ -4977,10 +4977,10 @@
         </is>
       </c>
       <c r="B351" t="n">
-        <v>0.279391</v>
+        <v>0.235662</v>
       </c>
       <c r="C351" t="n">
-        <v>0.071809</v>
+        <v>0.079156</v>
       </c>
     </row>
     <row r="352">
@@ -4990,10 +4990,10 @@
         </is>
       </c>
       <c r="B352" t="n">
-        <v>0.286735</v>
+        <v>0.245733</v>
       </c>
       <c r="C352" t="n">
-        <v>0.069149</v>
+        <v>0.076517</v>
       </c>
     </row>
     <row r="353">
@@ -5003,10 +5003,10 @@
         </is>
       </c>
       <c r="B353" t="n">
-        <v>0.28675</v>
+        <v>0.257813</v>
       </c>
       <c r="C353" t="n">
-        <v>0.06648900000000001</v>
+        <v>0.073879</v>
       </c>
     </row>
     <row r="354">
@@ -5016,10 +5016,10 @@
         </is>
       </c>
       <c r="B354" t="n">
-        <v>0.292707</v>
+        <v>0.279391</v>
       </c>
       <c r="C354" t="n">
-        <v>0.06383</v>
+        <v>0.07124</v>
       </c>
     </row>
     <row r="355">
@@ -5029,10 +5029,10 @@
         </is>
       </c>
       <c r="B355" t="n">
-        <v>0.303016</v>
+        <v>0.286735</v>
       </c>
       <c r="C355" t="n">
-        <v>0.06117</v>
+        <v>0.068602</v>
       </c>
     </row>
     <row r="356">
@@ -5042,10 +5042,10 @@
         </is>
       </c>
       <c r="B356" t="n">
-        <v>0.35577</v>
+        <v>0.28675</v>
       </c>
       <c r="C356" t="n">
-        <v>0.058511</v>
+        <v>0.06596299999999999</v>
       </c>
     </row>
     <row r="357">
@@ -5055,10 +5055,10 @@
         </is>
       </c>
       <c r="B357" t="n">
-        <v>0.359445</v>
+        <v>0.292707</v>
       </c>
       <c r="C357" t="n">
-        <v>0.055851</v>
+        <v>0.06332500000000001</v>
       </c>
     </row>
     <row r="358">
@@ -5068,10 +5068,10 @@
         </is>
       </c>
       <c r="B358" t="n">
-        <v>0.363732</v>
+        <v>0.303016</v>
       </c>
       <c r="C358" t="n">
-        <v>0.053191</v>
+        <v>0.060686</v>
       </c>
     </row>
     <row r="359">
@@ -5081,10 +5081,10 @@
         </is>
       </c>
       <c r="B359" t="n">
-        <v>0.36468</v>
+        <v>0.35577</v>
       </c>
       <c r="C359" t="n">
-        <v>0.050532</v>
+        <v>0.058047</v>
       </c>
     </row>
     <row r="360">
@@ -5094,10 +5094,10 @@
         </is>
       </c>
       <c r="B360" t="n">
-        <v>0.373827</v>
+        <v>0.359445</v>
       </c>
       <c r="C360" t="n">
-        <v>0.047872</v>
+        <v>0.055409</v>
       </c>
     </row>
     <row r="361">
@@ -5107,10 +5107,10 @@
         </is>
       </c>
       <c r="B361" t="n">
-        <v>0.389014</v>
+        <v>0.363732</v>
       </c>
       <c r="C361" t="n">
-        <v>0.045213</v>
+        <v>0.05277</v>
       </c>
     </row>
     <row r="362">
@@ -5120,10 +5120,10 @@
         </is>
       </c>
       <c r="B362" t="n">
-        <v>0.400164</v>
+        <v>0.36468</v>
       </c>
       <c r="C362" t="n">
-        <v>0.042553</v>
+        <v>0.050132</v>
       </c>
     </row>
     <row r="363">
@@ -5133,10 +5133,10 @@
         </is>
       </c>
       <c r="B363" t="n">
-        <v>0.40983</v>
+        <v>0.373827</v>
       </c>
       <c r="C363" t="n">
-        <v>0.039894</v>
+        <v>0.047493</v>
       </c>
     </row>
     <row r="364">
@@ -5146,10 +5146,10 @@
         </is>
       </c>
       <c r="B364" t="n">
-        <v>0.410903</v>
+        <v>0.389014</v>
       </c>
       <c r="C364" t="n">
-        <v>0.037234</v>
+        <v>0.044855</v>
       </c>
     </row>
     <row r="365">
@@ -5159,10 +5159,10 @@
         </is>
       </c>
       <c r="B365" t="n">
-        <v>0.419404</v>
+        <v>0.400164</v>
       </c>
       <c r="C365" t="n">
-        <v>0.034574</v>
+        <v>0.042216</v>
       </c>
     </row>
     <row r="366">
@@ -5172,10 +5172,10 @@
         </is>
       </c>
       <c r="B366" t="n">
-        <v>0.440642</v>
+        <v>0.40983</v>
       </c>
       <c r="C366" t="n">
-        <v>0.031915</v>
+        <v>0.039578</v>
       </c>
     </row>
     <row r="367">
@@ -5185,10 +5185,10 @@
         </is>
       </c>
       <c r="B367" t="n">
-        <v>0.454545</v>
+        <v>0.410903</v>
       </c>
       <c r="C367" t="n">
-        <v>0.029255</v>
+        <v>0.036939</v>
       </c>
     </row>
     <row r="368">
@@ -5198,10 +5198,10 @@
         </is>
       </c>
       <c r="B368" t="n">
-        <v>0.587794</v>
+        <v>0.419404</v>
       </c>
       <c r="C368" t="n">
-        <v>0.026596</v>
+        <v>0.034301</v>
       </c>
     </row>
     <row r="369">
@@ -5211,10 +5211,10 @@
         </is>
       </c>
       <c r="B369" t="n">
-        <v>0.620194</v>
+        <v>0.440642</v>
       </c>
       <c r="C369" t="n">
-        <v>0.023936</v>
+        <v>0.031662</v>
       </c>
     </row>
     <row r="370">
@@ -5224,10 +5224,10 @@
         </is>
       </c>
       <c r="B370" t="n">
-        <v>0.634074</v>
+        <v>0.454545</v>
       </c>
       <c r="C370" t="n">
-        <v>0.021277</v>
+        <v>0.029024</v>
       </c>
     </row>
     <row r="371">
@@ -5237,10 +5237,10 @@
         </is>
       </c>
       <c r="B371" t="n">
-        <v>0.672434</v>
+        <v>0.587794</v>
       </c>
       <c r="C371" t="n">
-        <v>0.018617</v>
+        <v>0.026385</v>
       </c>
     </row>
     <row r="372">
@@ -5250,10 +5250,10 @@
         </is>
       </c>
       <c r="B372" t="n">
-        <v>0.678189</v>
+        <v>0.620194</v>
       </c>
       <c r="C372" t="n">
-        <v>0.015957</v>
+        <v>0.023747</v>
       </c>
     </row>
     <row r="373">
@@ -5263,10 +5263,10 @@
         </is>
       </c>
       <c r="B373" t="n">
-        <v>0.707604</v>
+        <v>0.634074</v>
       </c>
       <c r="C373" t="n">
-        <v>0.013298</v>
+        <v>0.021108</v>
       </c>
     </row>
     <row r="374">
@@ -5276,10 +5276,10 @@
         </is>
       </c>
       <c r="B374" t="n">
-        <v>0.711338</v>
+        <v>0.672434</v>
       </c>
       <c r="C374" t="n">
-        <v>0.010638</v>
+        <v>0.01847</v>
       </c>
     </row>
     <row r="375">
@@ -5289,10 +5289,10 @@
         </is>
       </c>
       <c r="B375" t="n">
-        <v>0.76535</v>
+        <v>0.678189</v>
       </c>
       <c r="C375" t="n">
-        <v>0.007979</v>
+        <v>0.015831</v>
       </c>
     </row>
     <row r="376">
@@ -5302,10 +5302,10 @@
         </is>
       </c>
       <c r="B376" t="n">
-        <v>0.838984</v>
+        <v>0.707604</v>
       </c>
       <c r="C376" t="n">
-        <v>0.005319</v>
+        <v>0.013193</v>
       </c>
     </row>
     <row r="377">
@@ -5315,49 +5315,49 @@
         </is>
       </c>
       <c r="B377" t="n">
-        <v>1.015082</v>
+        <v>0.711338</v>
       </c>
       <c r="C377" t="n">
-        <v>0.00266</v>
+        <v>0.010554</v>
       </c>
     </row>
     <row r="378">
       <c r="A378" t="inlineStr">
         <is>
-          <t>Adjusted target</t>
+          <t>Raw market</t>
         </is>
       </c>
       <c r="B378" t="n">
-        <v>1e-06</v>
+        <v>0.76535</v>
       </c>
       <c r="C378" t="n">
-        <v>1</v>
+        <v>0.007915999999999999</v>
       </c>
     </row>
     <row r="379">
       <c r="A379" t="inlineStr">
         <is>
-          <t>Adjusted target</t>
+          <t>Raw market</t>
         </is>
       </c>
       <c r="B379" t="n">
-        <v>0.000103</v>
+        <v>0.838984</v>
       </c>
       <c r="C379" t="n">
-        <v>0.99734</v>
+        <v>0.005277</v>
       </c>
     </row>
     <row r="380">
       <c r="A380" t="inlineStr">
         <is>
-          <t>Adjusted target</t>
+          <t>Raw market</t>
         </is>
       </c>
       <c r="B380" t="n">
-        <v>0.000309</v>
+        <v>1.015082</v>
       </c>
       <c r="C380" t="n">
-        <v>0.994681</v>
+        <v>0.002639</v>
       </c>
     </row>
     <row r="381">
@@ -5367,10 +5367,10 @@
         </is>
       </c>
       <c r="B381" t="n">
-        <v>0.000504</v>
+        <v>2e-06</v>
       </c>
       <c r="C381" t="n">
-        <v>0.992021</v>
+        <v>1</v>
       </c>
     </row>
     <row r="382">
@@ -5380,10 +5380,10 @@
         </is>
       </c>
       <c r="B382" t="n">
-        <v>0.001023</v>
+        <v>0.000116</v>
       </c>
       <c r="C382" t="n">
-        <v>0.989362</v>
+        <v>0.9973610000000001</v>
       </c>
     </row>
     <row r="383">
@@ -5393,10 +5393,10 @@
         </is>
       </c>
       <c r="B383" t="n">
-        <v>0.001641</v>
+        <v>0.000336</v>
       </c>
       <c r="C383" t="n">
-        <v>0.986702</v>
+        <v>0.994723</v>
       </c>
     </row>
     <row r="384">
@@ -5406,10 +5406,10 @@
         </is>
       </c>
       <c r="B384" t="n">
-        <v>0.001859</v>
+        <v>0.000546</v>
       </c>
       <c r="C384" t="n">
-        <v>0.984043</v>
+        <v>0.992084</v>
       </c>
     </row>
     <row r="385">
@@ -5419,10 +5419,10 @@
         </is>
       </c>
       <c r="B385" t="n">
-        <v>0.001898</v>
+        <v>0.001107</v>
       </c>
       <c r="C385" t="n">
-        <v>0.981383</v>
+        <v>0.989446</v>
       </c>
     </row>
     <row r="386">
@@ -5432,10 +5432,10 @@
         </is>
       </c>
       <c r="B386" t="n">
-        <v>0.002107</v>
+        <v>0.001722</v>
       </c>
       <c r="C386" t="n">
-        <v>0.978723</v>
+        <v>0.986807</v>
       </c>
     </row>
     <row r="387">
@@ -5445,10 +5445,10 @@
         </is>
       </c>
       <c r="B387" t="n">
-        <v>0.002675</v>
+        <v>0.00211</v>
       </c>
       <c r="C387" t="n">
-        <v>0.976064</v>
+        <v>0.984169</v>
       </c>
     </row>
     <row r="388">
@@ -5458,10 +5458,10 @@
         </is>
       </c>
       <c r="B388" t="n">
-        <v>0.002829</v>
+        <v>0.002121</v>
       </c>
       <c r="C388" t="n">
-        <v>0.973404</v>
+        <v>0.98153</v>
       </c>
     </row>
     <row r="389">
@@ -5471,10 +5471,10 @@
         </is>
       </c>
       <c r="B389" t="n">
-        <v>0.003139</v>
+        <v>0.002279</v>
       </c>
       <c r="C389" t="n">
-        <v>0.970745</v>
+        <v>0.978892</v>
       </c>
     </row>
     <row r="390">
@@ -5484,10 +5484,10 @@
         </is>
       </c>
       <c r="B390" t="n">
-        <v>0.003453</v>
+        <v>0.003079</v>
       </c>
       <c r="C390" t="n">
-        <v>0.968085</v>
+        <v>0.976253</v>
       </c>
     </row>
     <row r="391">
@@ -5497,10 +5497,10 @@
         </is>
       </c>
       <c r="B391" t="n">
-        <v>0.004067</v>
+        <v>0.00312</v>
       </c>
       <c r="C391" t="n">
-        <v>0.965426</v>
+        <v>0.973615</v>
       </c>
     </row>
     <row r="392">
@@ -5510,10 +5510,10 @@
         </is>
       </c>
       <c r="B392" t="n">
-        <v>0.004152</v>
+        <v>0.00341</v>
       </c>
       <c r="C392" t="n">
-        <v>0.962766</v>
+        <v>0.970976</v>
       </c>
     </row>
     <row r="393">
@@ -5523,10 +5523,10 @@
         </is>
       </c>
       <c r="B393" t="n">
-        <v>0.004202</v>
+        <v>0.003543</v>
       </c>
       <c r="C393" t="n">
-        <v>0.960106</v>
+        <v>0.968338</v>
       </c>
     </row>
     <row r="394">
@@ -5536,10 +5536,10 @@
         </is>
       </c>
       <c r="B394" t="n">
-        <v>0.004379</v>
+        <v>0.004494</v>
       </c>
       <c r="C394" t="n">
-        <v>0.957447</v>
+        <v>0.965699</v>
       </c>
     </row>
     <row r="395">
@@ -5549,10 +5549,10 @@
         </is>
       </c>
       <c r="B395" t="n">
-        <v>0.004727</v>
+        <v>0.004551</v>
       </c>
       <c r="C395" t="n">
-        <v>0.9547870000000001</v>
+        <v>0.9630609999999999</v>
       </c>
     </row>
     <row r="396">
@@ -5562,10 +5562,10 @@
         </is>
       </c>
       <c r="B396" t="n">
-        <v>0.004757</v>
+        <v>0.004861</v>
       </c>
       <c r="C396" t="n">
-        <v>0.952128</v>
+        <v>0.960422</v>
       </c>
     </row>
     <row r="397">
@@ -5575,10 +5575,10 @@
         </is>
       </c>
       <c r="B397" t="n">
-        <v>0.004764</v>
+        <v>0.004916</v>
       </c>
       <c r="C397" t="n">
-        <v>0.949468</v>
+        <v>0.957784</v>
       </c>
     </row>
     <row r="398">
@@ -5588,10 +5588,10 @@
         </is>
       </c>
       <c r="B398" t="n">
-        <v>0.004905</v>
+        <v>0.00504</v>
       </c>
       <c r="C398" t="n">
-        <v>0.946809</v>
+        <v>0.955145</v>
       </c>
     </row>
     <row r="399">
@@ -5601,10 +5601,10 @@
         </is>
       </c>
       <c r="B399" t="n">
-        <v>0.005007</v>
+        <v>0.005114</v>
       </c>
       <c r="C399" t="n">
-        <v>0.944149</v>
+        <v>0.952507</v>
       </c>
     </row>
     <row r="400">
@@ -5614,10 +5614,10 @@
         </is>
       </c>
       <c r="B400" t="n">
-        <v>0.005256</v>
+        <v>0.005212</v>
       </c>
       <c r="C400" t="n">
-        <v>0.941489</v>
+        <v>0.949868</v>
       </c>
     </row>
     <row r="401">
@@ -5627,10 +5627,10 @@
         </is>
       </c>
       <c r="B401" t="n">
-        <v>0.00542</v>
+        <v>0.005249</v>
       </c>
       <c r="C401" t="n">
-        <v>0.9388300000000001</v>
+        <v>0.94723</v>
       </c>
     </row>
     <row r="402">
@@ -5640,10 +5640,10 @@
         </is>
       </c>
       <c r="B402" t="n">
-        <v>0.005443</v>
+        <v>0.005568</v>
       </c>
       <c r="C402" t="n">
-        <v>0.9361699999999999</v>
+        <v>0.944591</v>
       </c>
     </row>
     <row r="403">
@@ -5653,10 +5653,10 @@
         </is>
       </c>
       <c r="B403" t="n">
-        <v>0.005882</v>
+        <v>0.005569</v>
       </c>
       <c r="C403" t="n">
-        <v>0.933511</v>
+        <v>0.941953</v>
       </c>
     </row>
     <row r="404">
@@ -5666,10 +5666,10 @@
         </is>
       </c>
       <c r="B404" t="n">
-        <v>0.00589</v>
+        <v>0.005738</v>
       </c>
       <c r="C404" t="n">
-        <v>0.930851</v>
+        <v>0.939314</v>
       </c>
     </row>
     <row r="405">
@@ -5679,10 +5679,10 @@
         </is>
       </c>
       <c r="B405" t="n">
-        <v>0.006552</v>
+        <v>0.006223</v>
       </c>
       <c r="C405" t="n">
-        <v>0.928191</v>
+        <v>0.936675</v>
       </c>
     </row>
     <row r="406">
@@ -5692,10 +5692,10 @@
         </is>
       </c>
       <c r="B406" t="n">
-        <v>0.006779</v>
+        <v>0.00651</v>
       </c>
       <c r="C406" t="n">
-        <v>0.925532</v>
+        <v>0.934037</v>
       </c>
     </row>
     <row r="407">
@@ -5705,10 +5705,10 @@
         </is>
       </c>
       <c r="B407" t="n">
-        <v>0.007579</v>
+        <v>0.006604</v>
       </c>
       <c r="C407" t="n">
-        <v>0.922872</v>
+        <v>0.9313979999999999</v>
       </c>
     </row>
     <row r="408">
@@ -5718,10 +5718,10 @@
         </is>
       </c>
       <c r="B408" t="n">
-        <v>0.007972999999999999</v>
+        <v>0.007292</v>
       </c>
       <c r="C408" t="n">
-        <v>0.9202129999999999</v>
+        <v>0.92876</v>
       </c>
     </row>
     <row r="409">
@@ -5731,10 +5731,10 @@
         </is>
       </c>
       <c r="B409" t="n">
-        <v>0.008101000000000001</v>
+        <v>0.008134000000000001</v>
       </c>
       <c r="C409" t="n">
-        <v>0.917553</v>
+        <v>0.926121</v>
       </c>
     </row>
     <row r="410">
@@ -5744,10 +5744,10 @@
         </is>
       </c>
       <c r="B410" t="n">
-        <v>0.008219000000000001</v>
+        <v>0.008196</v>
       </c>
       <c r="C410" t="n">
-        <v>0.914894</v>
+        <v>0.9234830000000001</v>
       </c>
     </row>
     <row r="411">
@@ -5757,10 +5757,10 @@
         </is>
       </c>
       <c r="B411" t="n">
-        <v>0.008285000000000001</v>
+        <v>0.008433</v>
       </c>
       <c r="C411" t="n">
-        <v>0.912234</v>
+        <v>0.920844</v>
       </c>
     </row>
     <row r="412">
@@ -5770,10 +5770,10 @@
         </is>
       </c>
       <c r="B412" t="n">
-        <v>0.008363000000000001</v>
+        <v>0.008607999999999999</v>
       </c>
       <c r="C412" t="n">
-        <v>0.909574</v>
+        <v>0.918206</v>
       </c>
     </row>
     <row r="413">
@@ -5783,10 +5783,10 @@
         </is>
       </c>
       <c r="B413" t="n">
-        <v>0.008595999999999999</v>
+        <v>0.008881999999999999</v>
       </c>
       <c r="C413" t="n">
-        <v>0.906915</v>
+        <v>0.915567</v>
       </c>
     </row>
     <row r="414">
@@ -5796,10 +5796,10 @@
         </is>
       </c>
       <c r="B414" t="n">
-        <v>0.008699</v>
+        <v>0.008884</v>
       </c>
       <c r="C414" t="n">
-        <v>0.904255</v>
+        <v>0.912929</v>
       </c>
     </row>
     <row r="415">
@@ -5809,10 +5809,10 @@
         </is>
       </c>
       <c r="B415" t="n">
-        <v>0.008798</v>
+        <v>0.009292</v>
       </c>
       <c r="C415" t="n">
-        <v>0.901596</v>
+        <v>0.91029</v>
       </c>
     </row>
     <row r="416">
@@ -5822,10 +5822,10 @@
         </is>
       </c>
       <c r="B416" t="n">
-        <v>0.008947</v>
+        <v>0.009342</v>
       </c>
       <c r="C416" t="n">
-        <v>0.898936</v>
+        <v>0.907652</v>
       </c>
     </row>
     <row r="417">
@@ -5835,10 +5835,10 @@
         </is>
       </c>
       <c r="B417" t="n">
-        <v>0.009594999999999999</v>
+        <v>0.009375</v>
       </c>
       <c r="C417" t="n">
-        <v>0.896277</v>
+        <v>0.905013</v>
       </c>
     </row>
     <row r="418">
@@ -5848,10 +5848,10 @@
         </is>
       </c>
       <c r="B418" t="n">
-        <v>0.009639</v>
+        <v>0.010007</v>
       </c>
       <c r="C418" t="n">
-        <v>0.893617</v>
+        <v>0.902375</v>
       </c>
     </row>
     <row r="419">
@@ -5861,10 +5861,10 @@
         </is>
       </c>
       <c r="B419" t="n">
-        <v>0.009733</v>
+        <v>0.010135</v>
       </c>
       <c r="C419" t="n">
-        <v>0.890957</v>
+        <v>0.899736</v>
       </c>
     </row>
     <row r="420">
@@ -5874,10 +5874,10 @@
         </is>
       </c>
       <c r="B420" t="n">
-        <v>0.009756000000000001</v>
+        <v>0.01014</v>
       </c>
       <c r="C420" t="n">
-        <v>0.888298</v>
+        <v>0.897098</v>
       </c>
     </row>
     <row r="421">
@@ -5887,10 +5887,10 @@
         </is>
       </c>
       <c r="B421" t="n">
-        <v>0.010005</v>
+        <v>0.010301</v>
       </c>
       <c r="C421" t="n">
-        <v>0.885638</v>
+        <v>0.894459</v>
       </c>
     </row>
     <row r="422">
@@ -5900,10 +5900,10 @@
         </is>
       </c>
       <c r="B422" t="n">
-        <v>0.010012</v>
+        <v>0.010561</v>
       </c>
       <c r="C422" t="n">
-        <v>0.882979</v>
+        <v>0.891821</v>
       </c>
     </row>
     <row r="423">
@@ -5913,10 +5913,10 @@
         </is>
       </c>
       <c r="B423" t="n">
-        <v>0.010057</v>
+        <v>0.010866</v>
       </c>
       <c r="C423" t="n">
-        <v>0.880319</v>
+        <v>0.889182</v>
       </c>
     </row>
     <row r="424">
@@ -5926,10 +5926,10 @@
         </is>
       </c>
       <c r="B424" t="n">
-        <v>0.010209</v>
+        <v>0.011201</v>
       </c>
       <c r="C424" t="n">
-        <v>0.87766</v>
+        <v>0.886544</v>
       </c>
     </row>
     <row r="425">
@@ -5939,10 +5939,10 @@
         </is>
       </c>
       <c r="B425" t="n">
-        <v>0.010345</v>
+        <v>0.011302</v>
       </c>
       <c r="C425" t="n">
-        <v>0.875</v>
+        <v>0.8839050000000001</v>
       </c>
     </row>
     <row r="426">
@@ -5952,10 +5952,10 @@
         </is>
       </c>
       <c r="B426" t="n">
-        <v>0.010564</v>
+        <v>0.011417</v>
       </c>
       <c r="C426" t="n">
-        <v>0.87234</v>
+        <v>0.881266</v>
       </c>
     </row>
     <row r="427">
@@ -5965,10 +5965,10 @@
         </is>
       </c>
       <c r="B427" t="n">
-        <v>0.01106</v>
+        <v>0.011456</v>
       </c>
       <c r="C427" t="n">
-        <v>0.869681</v>
+        <v>0.878628</v>
       </c>
     </row>
     <row r="428">
@@ -5978,10 +5978,10 @@
         </is>
       </c>
       <c r="B428" t="n">
-        <v>0.011615</v>
+        <v>0.011855</v>
       </c>
       <c r="C428" t="n">
-        <v>0.867021</v>
+        <v>0.875989</v>
       </c>
     </row>
     <row r="429">
@@ -5991,10 +5991,10 @@
         </is>
       </c>
       <c r="B429" t="n">
-        <v>0.011819</v>
+        <v>0.01205</v>
       </c>
       <c r="C429" t="n">
-        <v>0.864362</v>
+        <v>0.873351</v>
       </c>
     </row>
     <row r="430">
@@ -6004,10 +6004,10 @@
         </is>
       </c>
       <c r="B430" t="n">
-        <v>0.011921</v>
+        <v>0.012327</v>
       </c>
       <c r="C430" t="n">
-        <v>0.861702</v>
+        <v>0.870712</v>
       </c>
     </row>
     <row r="431">
@@ -6017,10 +6017,10 @@
         </is>
       </c>
       <c r="B431" t="n">
-        <v>0.012221</v>
+        <v>0.012618</v>
       </c>
       <c r="C431" t="n">
-        <v>0.859043</v>
+        <v>0.868074</v>
       </c>
     </row>
     <row r="432">
@@ -6030,10 +6030,10 @@
         </is>
       </c>
       <c r="B432" t="n">
-        <v>0.012257</v>
+        <v>0.012623</v>
       </c>
       <c r="C432" t="n">
-        <v>0.856383</v>
+        <v>0.865435</v>
       </c>
     </row>
     <row r="433">
@@ -6043,10 +6043,10 @@
         </is>
       </c>
       <c r="B433" t="n">
-        <v>0.012328</v>
+        <v>0.012751</v>
       </c>
       <c r="C433" t="n">
-        <v>0.853723</v>
+        <v>0.862797</v>
       </c>
     </row>
     <row r="434">
@@ -6056,10 +6056,10 @@
         </is>
       </c>
       <c r="B434" t="n">
-        <v>0.012916</v>
+        <v>0.012816</v>
       </c>
       <c r="C434" t="n">
-        <v>0.851064</v>
+        <v>0.860158</v>
       </c>
     </row>
     <row r="435">
@@ -6069,10 +6069,10 @@
         </is>
       </c>
       <c r="B435" t="n">
-        <v>0.012968</v>
+        <v>0.013068</v>
       </c>
       <c r="C435" t="n">
-        <v>0.848404</v>
+        <v>0.8575199999999999</v>
       </c>
     </row>
     <row r="436">
@@ -6082,10 +6082,10 @@
         </is>
       </c>
       <c r="B436" t="n">
-        <v>0.013139</v>
+        <v>0.013098</v>
       </c>
       <c r="C436" t="n">
-        <v>0.845745</v>
+        <v>0.854881</v>
       </c>
     </row>
     <row r="437">
@@ -6095,10 +6095,10 @@
         </is>
       </c>
       <c r="B437" t="n">
-        <v>0.013563</v>
+        <v>0.0134</v>
       </c>
       <c r="C437" t="n">
-        <v>0.843085</v>
+        <v>0.852243</v>
       </c>
     </row>
     <row r="438">
@@ -6108,10 +6108,10 @@
         </is>
       </c>
       <c r="B438" t="n">
-        <v>0.013722</v>
+        <v>0.013608</v>
       </c>
       <c r="C438" t="n">
-        <v>0.840426</v>
+        <v>0.849604</v>
       </c>
     </row>
     <row r="439">
@@ -6121,10 +6121,10 @@
         </is>
       </c>
       <c r="B439" t="n">
-        <v>0.013765</v>
+        <v>0.013991</v>
       </c>
       <c r="C439" t="n">
-        <v>0.837766</v>
+        <v>0.846966</v>
       </c>
     </row>
     <row r="440">
@@ -6134,10 +6134,10 @@
         </is>
       </c>
       <c r="B440" t="n">
-        <v>0.014247</v>
+        <v>0.015068</v>
       </c>
       <c r="C440" t="n">
-        <v>0.835106</v>
+        <v>0.844327</v>
       </c>
     </row>
     <row r="441">
@@ -6147,10 +6147,10 @@
         </is>
       </c>
       <c r="B441" t="n">
-        <v>0.014346</v>
+        <v>0.015336</v>
       </c>
       <c r="C441" t="n">
-        <v>0.832447</v>
+        <v>0.841689</v>
       </c>
     </row>
     <row r="442">
@@ -6160,10 +6160,10 @@
         </is>
       </c>
       <c r="B442" t="n">
-        <v>0.014559</v>
+        <v>0.015375</v>
       </c>
       <c r="C442" t="n">
-        <v>0.8297870000000001</v>
+        <v>0.83905</v>
       </c>
     </row>
     <row r="443">
@@ -6173,10 +6173,10 @@
         </is>
       </c>
       <c r="B443" t="n">
-        <v>0.014872</v>
+        <v>0.015656</v>
       </c>
       <c r="C443" t="n">
-        <v>0.827128</v>
+        <v>0.836412</v>
       </c>
     </row>
     <row r="444">
@@ -6186,10 +6186,10 @@
         </is>
       </c>
       <c r="B444" t="n">
-        <v>0.015136</v>
+        <v>0.015695</v>
       </c>
       <c r="C444" t="n">
-        <v>0.824468</v>
+        <v>0.833773</v>
       </c>
     </row>
     <row r="445">
@@ -6199,10 +6199,10 @@
         </is>
       </c>
       <c r="B445" t="n">
-        <v>0.015375</v>
+        <v>0.015703</v>
       </c>
       <c r="C445" t="n">
-        <v>0.821809</v>
+        <v>0.831135</v>
       </c>
     </row>
     <row r="446">
@@ -6212,10 +6212,10 @@
         </is>
       </c>
       <c r="B446" t="n">
-        <v>0.015533</v>
+        <v>0.016145</v>
       </c>
       <c r="C446" t="n">
-        <v>0.819149</v>
+        <v>0.828496</v>
       </c>
     </row>
     <row r="447">
@@ -6225,10 +6225,10 @@
         </is>
       </c>
       <c r="B447" t="n">
-        <v>0.015621</v>
+        <v>0.016489</v>
       </c>
       <c r="C447" t="n">
-        <v>0.816489</v>
+        <v>0.825858</v>
       </c>
     </row>
     <row r="448">
@@ -6238,10 +6238,10 @@
         </is>
       </c>
       <c r="B448" t="n">
-        <v>0.015719</v>
+        <v>0.016774</v>
       </c>
       <c r="C448" t="n">
-        <v>0.8138300000000001</v>
+        <v>0.823219</v>
       </c>
     </row>
     <row r="449">
@@ -6251,10 +6251,10 @@
         </is>
       </c>
       <c r="B449" t="n">
-        <v>0.015834</v>
+        <v>0.016843</v>
       </c>
       <c r="C449" t="n">
-        <v>0.8111699999999999</v>
+        <v>0.82058</v>
       </c>
     </row>
     <row r="450">
@@ -6264,10 +6264,10 @@
         </is>
       </c>
       <c r="B450" t="n">
-        <v>0.015849</v>
+        <v>0.01697</v>
       </c>
       <c r="C450" t="n">
-        <v>0.808511</v>
+        <v>0.8179419999999999</v>
       </c>
     </row>
     <row r="451">
@@ -6277,10 +6277,10 @@
         </is>
       </c>
       <c r="B451" t="n">
-        <v>0.016375</v>
+        <v>0.01709</v>
       </c>
       <c r="C451" t="n">
-        <v>0.805851</v>
+        <v>0.815303</v>
       </c>
     </row>
     <row r="452">
@@ -6290,10 +6290,10 @@
         </is>
       </c>
       <c r="B452" t="n">
-        <v>0.016566</v>
+        <v>0.0173</v>
       </c>
       <c r="C452" t="n">
-        <v>0.803191</v>
+        <v>0.812665</v>
       </c>
     </row>
     <row r="453">
@@ -6303,10 +6303,10 @@
         </is>
       </c>
       <c r="B453" t="n">
-        <v>0.016636</v>
+        <v>0.017478</v>
       </c>
       <c r="C453" t="n">
-        <v>0.800532</v>
+        <v>0.810026</v>
       </c>
     </row>
     <row r="454">
@@ -6316,10 +6316,10 @@
         </is>
       </c>
       <c r="B454" t="n">
-        <v>0.017188</v>
+        <v>0.017808</v>
       </c>
       <c r="C454" t="n">
-        <v>0.797872</v>
+        <v>0.807388</v>
       </c>
     </row>
     <row r="455">
@@ -6329,10 +6329,10 @@
         </is>
       </c>
       <c r="B455" t="n">
-        <v>0.017342</v>
+        <v>0.018065</v>
       </c>
       <c r="C455" t="n">
-        <v>0.7952129999999999</v>
+        <v>0.804749</v>
       </c>
     </row>
     <row r="456">
@@ -6342,10 +6342,10 @@
         </is>
       </c>
       <c r="B456" t="n">
-        <v>0.017487</v>
+        <v>0.01814</v>
       </c>
       <c r="C456" t="n">
-        <v>0.792553</v>
+        <v>0.802111</v>
       </c>
     </row>
     <row r="457">
@@ -6355,10 +6355,10 @@
         </is>
       </c>
       <c r="B457" t="n">
-        <v>0.017958</v>
+        <v>0.018332</v>
       </c>
       <c r="C457" t="n">
-        <v>0.789894</v>
+        <v>0.799472</v>
       </c>
     </row>
     <row r="458">
@@ -6368,10 +6368,10 @@
         </is>
       </c>
       <c r="B458" t="n">
-        <v>0.018059</v>
+        <v>0.01893</v>
       </c>
       <c r="C458" t="n">
-        <v>0.787234</v>
+        <v>0.796834</v>
       </c>
     </row>
     <row r="459">
@@ -6381,10 +6381,10 @@
         </is>
       </c>
       <c r="B459" t="n">
-        <v>0.018334</v>
+        <v>0.019017</v>
       </c>
       <c r="C459" t="n">
-        <v>0.784574</v>
+        <v>0.794195</v>
       </c>
     </row>
     <row r="460">
@@ -6394,10 +6394,10 @@
         </is>
       </c>
       <c r="B460" t="n">
-        <v>0.01853</v>
+        <v>0.019053</v>
       </c>
       <c r="C460" t="n">
-        <v>0.781915</v>
+        <v>0.791557</v>
       </c>
     </row>
     <row r="461">
@@ -6407,10 +6407,10 @@
         </is>
       </c>
       <c r="B461" t="n">
-        <v>0.018599</v>
+        <v>0.019106</v>
       </c>
       <c r="C461" t="n">
-        <v>0.779255</v>
+        <v>0.788918</v>
       </c>
     </row>
     <row r="462">
@@ -6420,10 +6420,10 @@
         </is>
       </c>
       <c r="B462" t="n">
-        <v>0.01895</v>
+        <v>0.019445</v>
       </c>
       <c r="C462" t="n">
-        <v>0.776596</v>
+        <v>0.78628</v>
       </c>
     </row>
     <row r="463">
@@ -6433,10 +6433,10 @@
         </is>
       </c>
       <c r="B463" t="n">
-        <v>0.019085</v>
+        <v>0.019672</v>
       </c>
       <c r="C463" t="n">
-        <v>0.773936</v>
+        <v>0.783641</v>
       </c>
     </row>
     <row r="464">
@@ -6446,10 +6446,10 @@
         </is>
       </c>
       <c r="B464" t="n">
-        <v>0.019822</v>
+        <v>0.019993</v>
       </c>
       <c r="C464" t="n">
-        <v>0.771277</v>
+        <v>0.781003</v>
       </c>
     </row>
     <row r="465">
@@ -6459,10 +6459,10 @@
         </is>
       </c>
       <c r="B465" t="n">
-        <v>0.020147</v>
+        <v>0.020675</v>
       </c>
       <c r="C465" t="n">
-        <v>0.768617</v>
+        <v>0.7783639999999999</v>
       </c>
     </row>
     <row r="466">
@@ -6472,10 +6472,10 @@
         </is>
       </c>
       <c r="B466" t="n">
-        <v>0.020656</v>
+        <v>0.020863</v>
       </c>
       <c r="C466" t="n">
-        <v>0.765957</v>
+        <v>0.775726</v>
       </c>
     </row>
     <row r="467">
@@ -6485,10 +6485,10 @@
         </is>
       </c>
       <c r="B467" t="n">
-        <v>0.021044</v>
+        <v>0.02097</v>
       </c>
       <c r="C467" t="n">
-        <v>0.763298</v>
+        <v>0.773087</v>
       </c>
     </row>
     <row r="468">
@@ -6498,10 +6498,10 @@
         </is>
       </c>
       <c r="B468" t="n">
-        <v>0.021199</v>
+        <v>0.021295</v>
       </c>
       <c r="C468" t="n">
-        <v>0.760638</v>
+        <v>0.7704490000000001</v>
       </c>
     </row>
     <row r="469">
@@ -6511,10 +6511,10 @@
         </is>
       </c>
       <c r="B469" t="n">
-        <v>0.021496</v>
+        <v>0.021695</v>
       </c>
       <c r="C469" t="n">
-        <v>0.757979</v>
+        <v>0.76781</v>
       </c>
     </row>
     <row r="470">
@@ -6524,10 +6524,10 @@
         </is>
       </c>
       <c r="B470" t="n">
-        <v>0.021614</v>
+        <v>0.021979</v>
       </c>
       <c r="C470" t="n">
-        <v>0.755319</v>
+        <v>0.765172</v>
       </c>
     </row>
     <row r="471">
@@ -6537,10 +6537,10 @@
         </is>
       </c>
       <c r="B471" t="n">
-        <v>0.021635</v>
+        <v>0.022548</v>
       </c>
       <c r="C471" t="n">
-        <v>0.75266</v>
+        <v>0.762533</v>
       </c>
     </row>
     <row r="472">
@@ -6550,10 +6550,10 @@
         </is>
       </c>
       <c r="B472" t="n">
-        <v>0.021716</v>
+        <v>0.023039</v>
       </c>
       <c r="C472" t="n">
-        <v>0.75</v>
+        <v>0.759894</v>
       </c>
     </row>
     <row r="473">
@@ -6563,10 +6563,10 @@
         </is>
       </c>
       <c r="B473" t="n">
-        <v>0.022799</v>
+        <v>0.024101</v>
       </c>
       <c r="C473" t="n">
-        <v>0.74734</v>
+        <v>0.757256</v>
       </c>
     </row>
     <row r="474">
@@ -6576,10 +6576,10 @@
         </is>
       </c>
       <c r="B474" t="n">
-        <v>0.022832</v>
+        <v>0.024145</v>
       </c>
       <c r="C474" t="n">
-        <v>0.744681</v>
+        <v>0.754617</v>
       </c>
     </row>
     <row r="475">
@@ -6589,10 +6589,10 @@
         </is>
       </c>
       <c r="B475" t="n">
-        <v>0.022946</v>
+        <v>0.024241</v>
       </c>
       <c r="C475" t="n">
-        <v>0.742021</v>
+        <v>0.751979</v>
       </c>
     </row>
     <row r="476">
@@ -6602,10 +6602,10 @@
         </is>
       </c>
       <c r="B476" t="n">
-        <v>0.023224</v>
+        <v>0.024526</v>
       </c>
       <c r="C476" t="n">
-        <v>0.739362</v>
+        <v>0.74934</v>
       </c>
     </row>
     <row r="477">
@@ -6615,10 +6615,10 @@
         </is>
       </c>
       <c r="B477" t="n">
-        <v>0.023291</v>
+        <v>0.024843</v>
       </c>
       <c r="C477" t="n">
-        <v>0.736702</v>
+        <v>0.746702</v>
       </c>
     </row>
     <row r="478">
@@ -6628,10 +6628,10 @@
         </is>
       </c>
       <c r="B478" t="n">
-        <v>0.023574</v>
+        <v>0.025216</v>
       </c>
       <c r="C478" t="n">
-        <v>0.734043</v>
+        <v>0.744063</v>
       </c>
     </row>
     <row r="479">
@@ -6641,10 +6641,10 @@
         </is>
       </c>
       <c r="B479" t="n">
-        <v>0.023792</v>
+        <v>0.025284</v>
       </c>
       <c r="C479" t="n">
-        <v>0.731383</v>
+        <v>0.741425</v>
       </c>
     </row>
     <row r="480">
@@ -6654,10 +6654,10 @@
         </is>
       </c>
       <c r="B480" t="n">
-        <v>0.023874</v>
+        <v>0.025313</v>
       </c>
       <c r="C480" t="n">
-        <v>0.728723</v>
+        <v>0.7387860000000001</v>
       </c>
     </row>
     <row r="481">
@@ -6667,10 +6667,10 @@
         </is>
       </c>
       <c r="B481" t="n">
-        <v>0.024054</v>
+        <v>0.025698</v>
       </c>
       <c r="C481" t="n">
-        <v>0.726064</v>
+        <v>0.736148</v>
       </c>
     </row>
     <row r="482">
@@ -6680,10 +6680,10 @@
         </is>
       </c>
       <c r="B482" t="n">
-        <v>0.024441</v>
+        <v>0.025774</v>
       </c>
       <c r="C482" t="n">
-        <v>0.723404</v>
+        <v>0.733509</v>
       </c>
     </row>
     <row r="483">
@@ -6693,10 +6693,10 @@
         </is>
       </c>
       <c r="B483" t="n">
-        <v>0.024979</v>
+        <v>0.026152</v>
       </c>
       <c r="C483" t="n">
-        <v>0.720745</v>
+        <v>0.730871</v>
       </c>
     </row>
     <row r="484">
@@ -6706,10 +6706,10 @@
         </is>
       </c>
       <c r="B484" t="n">
-        <v>0.025105</v>
+        <v>0.0266</v>
       </c>
       <c r="C484" t="n">
-        <v>0.718085</v>
+        <v>0.728232</v>
       </c>
     </row>
     <row r="485">
@@ -6719,10 +6719,10 @@
         </is>
       </c>
       <c r="B485" t="n">
-        <v>0.025163</v>
+        <v>0.027307</v>
       </c>
       <c r="C485" t="n">
-        <v>0.715426</v>
+        <v>0.725594</v>
       </c>
     </row>
     <row r="486">
@@ -6732,10 +6732,10 @@
         </is>
       </c>
       <c r="B486" t="n">
-        <v>0.0252</v>
+        <v>0.027503</v>
       </c>
       <c r="C486" t="n">
-        <v>0.712766</v>
+        <v>0.722955</v>
       </c>
     </row>
     <row r="487">
@@ -6745,10 +6745,10 @@
         </is>
       </c>
       <c r="B487" t="n">
-        <v>0.025374</v>
+        <v>0.027753</v>
       </c>
       <c r="C487" t="n">
-        <v>0.710106</v>
+        <v>0.720317</v>
       </c>
     </row>
     <row r="488">
@@ -6758,10 +6758,10 @@
         </is>
       </c>
       <c r="B488" t="n">
-        <v>0.025579</v>
+        <v>0.027865</v>
       </c>
       <c r="C488" t="n">
-        <v>0.707447</v>
+        <v>0.717678</v>
       </c>
     </row>
     <row r="489">
@@ -6771,10 +6771,10 @@
         </is>
       </c>
       <c r="B489" t="n">
-        <v>0.025993</v>
+        <v>0.027894</v>
       </c>
       <c r="C489" t="n">
-        <v>0.7047870000000001</v>
+        <v>0.71504</v>
       </c>
     </row>
     <row r="490">
@@ -6784,10 +6784,10 @@
         </is>
       </c>
       <c r="B490" t="n">
-        <v>0.026113</v>
+        <v>0.027903</v>
       </c>
       <c r="C490" t="n">
-        <v>0.702128</v>
+        <v>0.712401</v>
       </c>
     </row>
     <row r="491">
@@ -6797,10 +6797,10 @@
         </is>
       </c>
       <c r="B491" t="n">
-        <v>0.026293</v>
+        <v>0.027908</v>
       </c>
       <c r="C491" t="n">
-        <v>0.699468</v>
+        <v>0.709763</v>
       </c>
     </row>
     <row r="492">
@@ -6810,10 +6810,10 @@
         </is>
       </c>
       <c r="B492" t="n">
-        <v>0.026753</v>
+        <v>0.028124</v>
       </c>
       <c r="C492" t="n">
-        <v>0.696809</v>
+        <v>0.707124</v>
       </c>
     </row>
     <row r="493">
@@ -6823,10 +6823,10 @@
         </is>
       </c>
       <c r="B493" t="n">
-        <v>0.026797</v>
+        <v>0.028198</v>
       </c>
       <c r="C493" t="n">
-        <v>0.694149</v>
+        <v>0.704485</v>
       </c>
     </row>
     <row r="494">
@@ -6836,10 +6836,10 @@
         </is>
       </c>
       <c r="B494" t="n">
-        <v>0.026823</v>
+        <v>0.028394</v>
       </c>
       <c r="C494" t="n">
-        <v>0.691489</v>
+        <v>0.701847</v>
       </c>
     </row>
     <row r="495">
@@ -6849,10 +6849,10 @@
         </is>
       </c>
       <c r="B495" t="n">
-        <v>0.026901</v>
+        <v>0.028776</v>
       </c>
       <c r="C495" t="n">
-        <v>0.6888300000000001</v>
+        <v>0.6992080000000001</v>
       </c>
     </row>
     <row r="496">
@@ -6862,10 +6862,10 @@
         </is>
       </c>
       <c r="B496" t="n">
-        <v>0.026916</v>
+        <v>0.029099</v>
       </c>
       <c r="C496" t="n">
-        <v>0.6861699999999999</v>
+        <v>0.69657</v>
       </c>
     </row>
     <row r="497">
@@ -6875,10 +6875,10 @@
         </is>
       </c>
       <c r="B497" t="n">
-        <v>0.027315</v>
+        <v>0.029319</v>
       </c>
       <c r="C497" t="n">
-        <v>0.683511</v>
+        <v>0.693931</v>
       </c>
     </row>
     <row r="498">
@@ -6888,10 +6888,10 @@
         </is>
       </c>
       <c r="B498" t="n">
-        <v>0.027458</v>
+        <v>0.02965</v>
       </c>
       <c r="C498" t="n">
-        <v>0.680851</v>
+        <v>0.691293</v>
       </c>
     </row>
     <row r="499">
@@ -6901,10 +6901,10 @@
         </is>
       </c>
       <c r="B499" t="n">
-        <v>0.027772</v>
+        <v>0.029793</v>
       </c>
       <c r="C499" t="n">
-        <v>0.678191</v>
+        <v>0.688654</v>
       </c>
     </row>
     <row r="500">
@@ -6914,10 +6914,10 @@
         </is>
       </c>
       <c r="B500" t="n">
-        <v>0.028383</v>
+        <v>0.03004</v>
       </c>
       <c r="C500" t="n">
-        <v>0.675532</v>
+        <v>0.686016</v>
       </c>
     </row>
     <row r="501">
@@ -6927,10 +6927,10 @@
         </is>
       </c>
       <c r="B501" t="n">
-        <v>0.028621</v>
+        <v>0.030355</v>
       </c>
       <c r="C501" t="n">
-        <v>0.672872</v>
+        <v>0.683377</v>
       </c>
     </row>
     <row r="502">
@@ -6940,10 +6940,10 @@
         </is>
       </c>
       <c r="B502" t="n">
-        <v>0.029165</v>
+        <v>0.030366</v>
       </c>
       <c r="C502" t="n">
-        <v>0.6702129999999999</v>
+        <v>0.680739</v>
       </c>
     </row>
     <row r="503">
@@ -6953,10 +6953,10 @@
         </is>
       </c>
       <c r="B503" t="n">
-        <v>0.029357</v>
+        <v>0.030519</v>
       </c>
       <c r="C503" t="n">
-        <v>0.667553</v>
+        <v>0.6781</v>
       </c>
     </row>
     <row r="504">
@@ -6966,10 +6966,10 @@
         </is>
       </c>
       <c r="B504" t="n">
-        <v>0.029654</v>
+        <v>0.030911</v>
       </c>
       <c r="C504" t="n">
-        <v>0.664894</v>
+        <v>0.675462</v>
       </c>
     </row>
     <row r="505">
@@ -6979,10 +6979,10 @@
         </is>
       </c>
       <c r="B505" t="n">
-        <v>0.029681</v>
+        <v>0.031097</v>
       </c>
       <c r="C505" t="n">
-        <v>0.662234</v>
+        <v>0.6728229999999999</v>
       </c>
     </row>
     <row r="506">
@@ -6992,10 +6992,10 @@
         </is>
       </c>
       <c r="B506" t="n">
-        <v>0.030513</v>
+        <v>0.031436</v>
       </c>
       <c r="C506" t="n">
-        <v>0.659574</v>
+        <v>0.670185</v>
       </c>
     </row>
     <row r="507">
@@ -7005,10 +7005,10 @@
         </is>
       </c>
       <c r="B507" t="n">
-        <v>0.030651</v>
+        <v>0.031779</v>
       </c>
       <c r="C507" t="n">
-        <v>0.656915</v>
+        <v>0.667546</v>
       </c>
     </row>
     <row r="508">
@@ -7018,10 +7018,10 @@
         </is>
       </c>
       <c r="B508" t="n">
-        <v>0.031091</v>
+        <v>0.032816</v>
       </c>
       <c r="C508" t="n">
-        <v>0.654255</v>
+        <v>0.6649080000000001</v>
       </c>
     </row>
     <row r="509">
@@ -7031,10 +7031,10 @@
         </is>
       </c>
       <c r="B509" t="n">
-        <v>0.03114</v>
+        <v>0.032838</v>
       </c>
       <c r="C509" t="n">
-        <v>0.651596</v>
+        <v>0.662269</v>
       </c>
     </row>
     <row r="510">
@@ -7044,10 +7044,10 @@
         </is>
       </c>
       <c r="B510" t="n">
-        <v>0.031548</v>
+        <v>0.032872</v>
       </c>
       <c r="C510" t="n">
-        <v>0.648936</v>
+        <v>0.659631</v>
       </c>
     </row>
     <row r="511">
@@ -7057,10 +7057,10 @@
         </is>
       </c>
       <c r="B511" t="n">
-        <v>0.031711</v>
+        <v>0.03302</v>
       </c>
       <c r="C511" t="n">
-        <v>0.646277</v>
+        <v>0.656992</v>
       </c>
     </row>
     <row r="512">
@@ -7070,10 +7070,10 @@
         </is>
       </c>
       <c r="B512" t="n">
-        <v>0.03257</v>
+        <v>0.033951</v>
       </c>
       <c r="C512" t="n">
-        <v>0.643617</v>
+        <v>0.654354</v>
       </c>
     </row>
     <row r="513">
@@ -7083,10 +7083,10 @@
         </is>
       </c>
       <c r="B513" t="n">
-        <v>0.032661</v>
+        <v>0.033987</v>
       </c>
       <c r="C513" t="n">
-        <v>0.640957</v>
+        <v>0.651715</v>
       </c>
     </row>
     <row r="514">
@@ -7096,10 +7096,10 @@
         </is>
       </c>
       <c r="B514" t="n">
-        <v>0.032768</v>
+        <v>0.034062</v>
       </c>
       <c r="C514" t="n">
-        <v>0.638298</v>
+        <v>0.649077</v>
       </c>
     </row>
     <row r="515">
@@ -7109,10 +7109,10 @@
         </is>
       </c>
       <c r="B515" t="n">
-        <v>0.032826</v>
+        <v>0.034303</v>
       </c>
       <c r="C515" t="n">
-        <v>0.635638</v>
+        <v>0.646438</v>
       </c>
     </row>
     <row r="516">
@@ -7122,10 +7122,10 @@
         </is>
       </c>
       <c r="B516" t="n">
-        <v>0.032885</v>
+        <v>0.034487</v>
       </c>
       <c r="C516" t="n">
-        <v>0.632979</v>
+        <v>0.643799</v>
       </c>
     </row>
     <row r="517">
@@ -7135,10 +7135,10 @@
         </is>
       </c>
       <c r="B517" t="n">
-        <v>0.033177</v>
+        <v>0.034515</v>
       </c>
       <c r="C517" t="n">
-        <v>0.630319</v>
+        <v>0.641161</v>
       </c>
     </row>
     <row r="518">
@@ -7148,10 +7148,10 @@
         </is>
       </c>
       <c r="B518" t="n">
-        <v>0.033253</v>
+        <v>0.034933</v>
       </c>
       <c r="C518" t="n">
-        <v>0.62766</v>
+        <v>0.638522</v>
       </c>
     </row>
     <row r="519">
@@ -7161,10 +7161,10 @@
         </is>
       </c>
       <c r="B519" t="n">
-        <v>0.033656</v>
+        <v>0.035141</v>
       </c>
       <c r="C519" t="n">
-        <v>0.625</v>
+        <v>0.635884</v>
       </c>
     </row>
     <row r="520">
@@ -7174,10 +7174,10 @@
         </is>
       </c>
       <c r="B520" t="n">
-        <v>0.033976</v>
+        <v>0.035145</v>
       </c>
       <c r="C520" t="n">
-        <v>0.62234</v>
+        <v>0.6332449999999999</v>
       </c>
     </row>
     <row r="521">
@@ -7187,10 +7187,10 @@
         </is>
       </c>
       <c r="B521" t="n">
-        <v>0.034025</v>
+        <v>0.035148</v>
       </c>
       <c r="C521" t="n">
-        <v>0.619681</v>
+        <v>0.630607</v>
       </c>
     </row>
     <row r="522">
@@ -7200,10 +7200,10 @@
         </is>
       </c>
       <c r="B522" t="n">
-        <v>0.034262</v>
+        <v>0.035942</v>
       </c>
       <c r="C522" t="n">
-        <v>0.617021</v>
+        <v>0.627968</v>
       </c>
     </row>
     <row r="523">
@@ -7213,10 +7213,10 @@
         </is>
       </c>
       <c r="B523" t="n">
-        <v>0.034279</v>
+        <v>0.036</v>
       </c>
       <c r="C523" t="n">
-        <v>0.614362</v>
+        <v>0.6253300000000001</v>
       </c>
     </row>
     <row r="524">
@@ -7226,10 +7226,10 @@
         </is>
       </c>
       <c r="B524" t="n">
-        <v>0.034358</v>
+        <v>0.036685</v>
       </c>
       <c r="C524" t="n">
-        <v>0.611702</v>
+        <v>0.622691</v>
       </c>
     </row>
     <row r="525">
@@ -7239,10 +7239,10 @@
         </is>
       </c>
       <c r="B525" t="n">
-        <v>0.03454</v>
+        <v>0.037036</v>
       </c>
       <c r="C525" t="n">
-        <v>0.609043</v>
+        <v>0.620053</v>
       </c>
     </row>
     <row r="526">
@@ -7252,10 +7252,10 @@
         </is>
       </c>
       <c r="B526" t="n">
-        <v>0.034785</v>
+        <v>0.037314</v>
       </c>
       <c r="C526" t="n">
-        <v>0.606383</v>
+        <v>0.617414</v>
       </c>
     </row>
     <row r="527">
@@ -7265,10 +7265,10 @@
         </is>
       </c>
       <c r="B527" t="n">
-        <v>0.035007</v>
+        <v>0.037796</v>
       </c>
       <c r="C527" t="n">
-        <v>0.603723</v>
+        <v>0.614776</v>
       </c>
     </row>
     <row r="528">
@@ -7278,10 +7278,10 @@
         </is>
       </c>
       <c r="B528" t="n">
-        <v>0.035267</v>
+        <v>0.038005</v>
       </c>
       <c r="C528" t="n">
-        <v>0.601064</v>
+        <v>0.612137</v>
       </c>
     </row>
     <row r="529">
@@ -7291,10 +7291,10 @@
         </is>
       </c>
       <c r="B529" t="n">
-        <v>0.035602</v>
+        <v>0.038265</v>
       </c>
       <c r="C529" t="n">
-        <v>0.598404</v>
+        <v>0.609499</v>
       </c>
     </row>
     <row r="530">
@@ -7304,10 +7304,10 @@
         </is>
       </c>
       <c r="B530" t="n">
-        <v>0.035957</v>
+        <v>0.038466</v>
       </c>
       <c r="C530" t="n">
-        <v>0.595745</v>
+        <v>0.60686</v>
       </c>
     </row>
     <row r="531">
@@ -7317,10 +7317,10 @@
         </is>
       </c>
       <c r="B531" t="n">
-        <v>0.036431</v>
+        <v>0.038821</v>
       </c>
       <c r="C531" t="n">
-        <v>0.593085</v>
+        <v>0.604222</v>
       </c>
     </row>
     <row r="532">
@@ -7330,10 +7330,10 @@
         </is>
       </c>
       <c r="B532" t="n">
-        <v>0.037036</v>
+        <v>0.039013</v>
       </c>
       <c r="C532" t="n">
-        <v>0.590426</v>
+        <v>0.601583</v>
       </c>
     </row>
     <row r="533">
@@ -7343,10 +7343,10 @@
         </is>
       </c>
       <c r="B533" t="n">
-        <v>0.037079</v>
+        <v>0.039064</v>
       </c>
       <c r="C533" t="n">
-        <v>0.587766</v>
+        <v>0.5989449999999999</v>
       </c>
     </row>
     <row r="534">
@@ -7356,10 +7356,10 @@
         </is>
       </c>
       <c r="B534" t="n">
-        <v>0.037112</v>
+        <v>0.039142</v>
       </c>
       <c r="C534" t="n">
-        <v>0.585106</v>
+        <v>0.596306</v>
       </c>
     </row>
     <row r="535">
@@ -7369,10 +7369,10 @@
         </is>
       </c>
       <c r="B535" t="n">
-        <v>0.037437</v>
+        <v>0.039338</v>
       </c>
       <c r="C535" t="n">
-        <v>0.582447</v>
+        <v>0.593668</v>
       </c>
     </row>
     <row r="536">
@@ -7382,10 +7382,10 @@
         </is>
       </c>
       <c r="B536" t="n">
-        <v>0.037486</v>
+        <v>0.039669</v>
       </c>
       <c r="C536" t="n">
-        <v>0.5797870000000001</v>
+        <v>0.591029</v>
       </c>
     </row>
     <row r="537">
@@ -7395,10 +7395,10 @@
         </is>
       </c>
       <c r="B537" t="n">
-        <v>0.037751</v>
+        <v>0.039782</v>
       </c>
       <c r="C537" t="n">
-        <v>0.577128</v>
+        <v>0.588391</v>
       </c>
     </row>
     <row r="538">
@@ -7408,10 +7408,10 @@
         </is>
       </c>
       <c r="B538" t="n">
-        <v>0.03778</v>
+        <v>0.039782</v>
       </c>
       <c r="C538" t="n">
-        <v>0.574468</v>
+        <v>0.5857520000000001</v>
       </c>
     </row>
     <row r="539">
@@ -7421,10 +7421,10 @@
         </is>
       </c>
       <c r="B539" t="n">
-        <v>0.037786</v>
+        <v>0.040328</v>
       </c>
       <c r="C539" t="n">
-        <v>0.571809</v>
+        <v>0.583113</v>
       </c>
     </row>
     <row r="540">
@@ -7434,10 +7434,10 @@
         </is>
       </c>
       <c r="B540" t="n">
-        <v>0.038034</v>
+        <v>0.041065</v>
       </c>
       <c r="C540" t="n">
-        <v>0.569149</v>
+        <v>0.580475</v>
       </c>
     </row>
     <row r="541">
@@ -7447,10 +7447,10 @@
         </is>
       </c>
       <c r="B541" t="n">
-        <v>0.038055</v>
+        <v>0.041301</v>
       </c>
       <c r="C541" t="n">
-        <v>0.566489</v>
+        <v>0.577836</v>
       </c>
     </row>
     <row r="542">
@@ -7460,10 +7460,10 @@
         </is>
       </c>
       <c r="B542" t="n">
-        <v>0.038074</v>
+        <v>0.041598</v>
       </c>
       <c r="C542" t="n">
-        <v>0.5638300000000001</v>
+        <v>0.575198</v>
       </c>
     </row>
     <row r="543">
@@ -7473,10 +7473,10 @@
         </is>
       </c>
       <c r="B543" t="n">
-        <v>0.038555</v>
+        <v>0.041685</v>
       </c>
       <c r="C543" t="n">
-        <v>0.5611699999999999</v>
+        <v>0.572559</v>
       </c>
     </row>
     <row r="544">
@@ -7486,10 +7486,10 @@
         </is>
       </c>
       <c r="B544" t="n">
-        <v>0.038801</v>
+        <v>0.041722</v>
       </c>
       <c r="C544" t="n">
-        <v>0.558511</v>
+        <v>0.569921</v>
       </c>
     </row>
     <row r="545">
@@ -7499,10 +7499,10 @@
         </is>
       </c>
       <c r="B545" t="n">
-        <v>0.038806</v>
+        <v>0.042018</v>
       </c>
       <c r="C545" t="n">
-        <v>0.555851</v>
+        <v>0.567282</v>
       </c>
     </row>
     <row r="546">
@@ -7512,10 +7512,10 @@
         </is>
       </c>
       <c r="B546" t="n">
-        <v>0.038976</v>
+        <v>0.042255</v>
       </c>
       <c r="C546" t="n">
-        <v>0.553191</v>
+        <v>0.564644</v>
       </c>
     </row>
     <row r="547">
@@ -7525,10 +7525,10 @@
         </is>
       </c>
       <c r="B547" t="n">
-        <v>0.038998</v>
+        <v>0.042901</v>
       </c>
       <c r="C547" t="n">
-        <v>0.550532</v>
+        <v>0.562005</v>
       </c>
     </row>
     <row r="548">
@@ -7538,10 +7538,10 @@
         </is>
       </c>
       <c r="B548" t="n">
-        <v>0.039036</v>
+        <v>0.042941</v>
       </c>
       <c r="C548" t="n">
-        <v>0.547872</v>
+        <v>0.5593669999999999</v>
       </c>
     </row>
     <row r="549">
@@ -7551,10 +7551,10 @@
         </is>
       </c>
       <c r="B549" t="n">
-        <v>0.039362</v>
+        <v>0.043133</v>
       </c>
       <c r="C549" t="n">
-        <v>0.5452129999999999</v>
+        <v>0.556728</v>
       </c>
     </row>
     <row r="550">
@@ -7564,10 +7564,10 @@
         </is>
       </c>
       <c r="B550" t="n">
-        <v>0.039523</v>
+        <v>0.043233</v>
       </c>
       <c r="C550" t="n">
-        <v>0.542553</v>
+        <v>0.55409</v>
       </c>
     </row>
     <row r="551">
@@ -7577,10 +7577,10 @@
         </is>
       </c>
       <c r="B551" t="n">
-        <v>0.039742</v>
+        <v>0.043273</v>
       </c>
       <c r="C551" t="n">
-        <v>0.539894</v>
+        <v>0.551451</v>
       </c>
     </row>
     <row r="552">
@@ -7590,10 +7590,10 @@
         </is>
       </c>
       <c r="B552" t="n">
-        <v>0.040422</v>
+        <v>0.043302</v>
       </c>
       <c r="C552" t="n">
-        <v>0.537234</v>
+        <v>0.548813</v>
       </c>
     </row>
     <row r="553">
@@ -7603,10 +7603,10 @@
         </is>
       </c>
       <c r="B553" t="n">
-        <v>0.041295</v>
+        <v>0.04334</v>
       </c>
       <c r="C553" t="n">
-        <v>0.534574</v>
+        <v>0.546174</v>
       </c>
     </row>
     <row r="554">
@@ -7616,10 +7616,10 @@
         </is>
       </c>
       <c r="B554" t="n">
-        <v>0.041335</v>
+        <v>0.043754</v>
       </c>
       <c r="C554" t="n">
-        <v>0.531915</v>
+        <v>0.543536</v>
       </c>
     </row>
     <row r="555">
@@ -7629,10 +7629,10 @@
         </is>
       </c>
       <c r="B555" t="n">
-        <v>0.041513</v>
+        <v>0.044035</v>
       </c>
       <c r="C555" t="n">
-        <v>0.529255</v>
+        <v>0.540897</v>
       </c>
     </row>
     <row r="556">
@@ -7642,10 +7642,10 @@
         </is>
       </c>
       <c r="B556" t="n">
-        <v>0.041657</v>
+        <v>0.044195</v>
       </c>
       <c r="C556" t="n">
-        <v>0.526596</v>
+        <v>0.538259</v>
       </c>
     </row>
     <row r="557">
@@ -7655,10 +7655,10 @@
         </is>
       </c>
       <c r="B557" t="n">
-        <v>0.041738</v>
+        <v>0.044566</v>
       </c>
       <c r="C557" t="n">
-        <v>0.523936</v>
+        <v>0.53562</v>
       </c>
     </row>
     <row r="558">
@@ -7668,10 +7668,10 @@
         </is>
       </c>
       <c r="B558" t="n">
-        <v>0.042055</v>
+        <v>0.045058</v>
       </c>
       <c r="C558" t="n">
-        <v>0.521277</v>
+        <v>0.532982</v>
       </c>
     </row>
     <row r="559">
@@ -7681,10 +7681,10 @@
         </is>
       </c>
       <c r="B559" t="n">
-        <v>0.042323</v>
+        <v>0.04509</v>
       </c>
       <c r="C559" t="n">
-        <v>0.518617</v>
+        <v>0.530343</v>
       </c>
     </row>
     <row r="560">
@@ -7694,10 +7694,10 @@
         </is>
       </c>
       <c r="B560" t="n">
-        <v>0.042331</v>
+        <v>0.045484</v>
       </c>
       <c r="C560" t="n">
-        <v>0.515957</v>
+        <v>0.527704</v>
       </c>
     </row>
     <row r="561">
@@ -7707,10 +7707,10 @@
         </is>
       </c>
       <c r="B561" t="n">
-        <v>0.042796</v>
+        <v>0.045773</v>
       </c>
       <c r="C561" t="n">
-        <v>0.513298</v>
+        <v>0.525066</v>
       </c>
     </row>
     <row r="562">
@@ -7720,10 +7720,10 @@
         </is>
       </c>
       <c r="B562" t="n">
-        <v>0.042848</v>
+        <v>0.045904</v>
       </c>
       <c r="C562" t="n">
-        <v>0.510638</v>
+        <v>0.522427</v>
       </c>
     </row>
     <row r="563">
@@ -7733,10 +7733,10 @@
         </is>
       </c>
       <c r="B563" t="n">
-        <v>0.043897</v>
+        <v>0.04667</v>
       </c>
       <c r="C563" t="n">
-        <v>0.507979</v>
+        <v>0.5197889999999999</v>
       </c>
     </row>
     <row r="564">
@@ -7746,10 +7746,10 @@
         </is>
       </c>
       <c r="B564" t="n">
-        <v>0.044517</v>
+        <v>0.047614</v>
       </c>
       <c r="C564" t="n">
-        <v>0.505319</v>
+        <v>0.51715</v>
       </c>
     </row>
     <row r="565">
@@ -7759,10 +7759,10 @@
         </is>
       </c>
       <c r="B565" t="n">
-        <v>0.044604</v>
+        <v>0.047796</v>
       </c>
       <c r="C565" t="n">
-        <v>0.50266</v>
+        <v>0.514512</v>
       </c>
     </row>
     <row r="566">
@@ -7772,10 +7772,10 @@
         </is>
       </c>
       <c r="B566" t="n">
-        <v>0.044792</v>
+        <v>0.04799</v>
       </c>
       <c r="C566" t="n">
-        <v>0.5</v>
+        <v>0.511873</v>
       </c>
     </row>
     <row r="567">
@@ -7785,10 +7785,10 @@
         </is>
       </c>
       <c r="B567" t="n">
-        <v>0.04488</v>
+        <v>0.048249</v>
       </c>
       <c r="C567" t="n">
-        <v>0.49734</v>
+        <v>0.509235</v>
       </c>
     </row>
     <row r="568">
@@ -7798,10 +7798,10 @@
         </is>
       </c>
       <c r="B568" t="n">
-        <v>0.045184</v>
+        <v>0.048291</v>
       </c>
       <c r="C568" t="n">
-        <v>0.494681</v>
+        <v>0.506596</v>
       </c>
     </row>
     <row r="569">
@@ -7811,10 +7811,10 @@
         </is>
       </c>
       <c r="B569" t="n">
-        <v>0.046119</v>
+        <v>0.048355</v>
       </c>
       <c r="C569" t="n">
-        <v>0.492021</v>
+        <v>0.503958</v>
       </c>
     </row>
     <row r="570">
@@ -7824,10 +7824,10 @@
         </is>
       </c>
       <c r="B570" t="n">
-        <v>0.046334</v>
+        <v>0.048734</v>
       </c>
       <c r="C570" t="n">
-        <v>0.489362</v>
+        <v>0.501319</v>
       </c>
     </row>
     <row r="571">
@@ -7837,10 +7837,10 @@
         </is>
       </c>
       <c r="B571" t="n">
-        <v>0.046481</v>
+        <v>0.049271</v>
       </c>
       <c r="C571" t="n">
-        <v>0.486702</v>
+        <v>0.498681</v>
       </c>
     </row>
     <row r="572">
@@ -7850,10 +7850,10 @@
         </is>
       </c>
       <c r="B572" t="n">
-        <v>0.046566</v>
+        <v>0.04965</v>
       </c>
       <c r="C572" t="n">
-        <v>0.484043</v>
+        <v>0.496042</v>
       </c>
     </row>
     <row r="573">
@@ -7863,10 +7863,10 @@
         </is>
       </c>
       <c r="B573" t="n">
-        <v>0.046595</v>
+        <v>0.050794</v>
       </c>
       <c r="C573" t="n">
-        <v>0.481383</v>
+        <v>0.493404</v>
       </c>
     </row>
     <row r="574">
@@ -7876,10 +7876,10 @@
         </is>
       </c>
       <c r="B574" t="n">
-        <v>0.0477</v>
+        <v>0.051071</v>
       </c>
       <c r="C574" t="n">
-        <v>0.478723</v>
+        <v>0.490765</v>
       </c>
     </row>
     <row r="575">
@@ -7889,10 +7889,10 @@
         </is>
       </c>
       <c r="B575" t="n">
-        <v>0.047706</v>
+        <v>0.051169</v>
       </c>
       <c r="C575" t="n">
-        <v>0.476064</v>
+        <v>0.488127</v>
       </c>
     </row>
     <row r="576">
@@ -7902,10 +7902,10 @@
         </is>
       </c>
       <c r="B576" t="n">
-        <v>0.047948</v>
+        <v>0.051203</v>
       </c>
       <c r="C576" t="n">
-        <v>0.473404</v>
+        <v>0.485488</v>
       </c>
     </row>
     <row r="577">
@@ -7915,10 +7915,10 @@
         </is>
       </c>
       <c r="B577" t="n">
-        <v>0.048396</v>
+        <v>0.051866</v>
       </c>
       <c r="C577" t="n">
-        <v>0.470745</v>
+        <v>0.48285</v>
       </c>
     </row>
     <row r="578">
@@ -7928,10 +7928,10 @@
         </is>
       </c>
       <c r="B578" t="n">
-        <v>0.048527</v>
+        <v>0.0526</v>
       </c>
       <c r="C578" t="n">
-        <v>0.468085</v>
+        <v>0.480211</v>
       </c>
     </row>
     <row r="579">
@@ -7941,10 +7941,10 @@
         </is>
       </c>
       <c r="B579" t="n">
-        <v>0.048587</v>
+        <v>0.052799</v>
       </c>
       <c r="C579" t="n">
-        <v>0.465426</v>
+        <v>0.477573</v>
       </c>
     </row>
     <row r="580">
@@ -7954,10 +7954,10 @@
         </is>
       </c>
       <c r="B580" t="n">
-        <v>0.048976</v>
+        <v>0.053378</v>
       </c>
       <c r="C580" t="n">
-        <v>0.462766</v>
+        <v>0.474934</v>
       </c>
     </row>
     <row r="581">
@@ -7967,10 +7967,10 @@
         </is>
       </c>
       <c r="B581" t="n">
-        <v>0.049931</v>
+        <v>0.053381</v>
       </c>
       <c r="C581" t="n">
-        <v>0.460106</v>
+        <v>0.472296</v>
       </c>
     </row>
     <row r="582">
@@ -7980,10 +7980,10 @@
         </is>
       </c>
       <c r="B582" t="n">
-        <v>0.050274</v>
+        <v>0.053897</v>
       </c>
       <c r="C582" t="n">
-        <v>0.457447</v>
+        <v>0.469657</v>
       </c>
     </row>
     <row r="583">
@@ -7993,10 +7993,10 @@
         </is>
       </c>
       <c r="B583" t="n">
-        <v>0.050554</v>
+        <v>0.054048</v>
       </c>
       <c r="C583" t="n">
-        <v>0.454787</v>
+        <v>0.467018</v>
       </c>
     </row>
     <row r="584">
@@ -8006,10 +8006,10 @@
         </is>
       </c>
       <c r="B584" t="n">
-        <v>0.050986</v>
+        <v>0.054456</v>
       </c>
       <c r="C584" t="n">
-        <v>0.452128</v>
+        <v>0.46438</v>
       </c>
     </row>
     <row r="585">
@@ -8019,10 +8019,10 @@
         </is>
       </c>
       <c r="B585" t="n">
-        <v>0.051099</v>
+        <v>0.054529</v>
       </c>
       <c r="C585" t="n">
-        <v>0.449468</v>
+        <v>0.461741</v>
       </c>
     </row>
     <row r="586">
@@ -8032,10 +8032,10 @@
         </is>
       </c>
       <c r="B586" t="n">
-        <v>0.051498</v>
+        <v>0.055705</v>
       </c>
       <c r="C586" t="n">
-        <v>0.446809</v>
+        <v>0.459103</v>
       </c>
     </row>
     <row r="587">
@@ -8045,10 +8045,10 @@
         </is>
       </c>
       <c r="B587" t="n">
-        <v>0.051636</v>
+        <v>0.055741</v>
       </c>
       <c r="C587" t="n">
-        <v>0.444149</v>
+        <v>0.456464</v>
       </c>
     </row>
     <row r="588">
@@ -8058,10 +8058,10 @@
         </is>
       </c>
       <c r="B588" t="n">
-        <v>0.05196</v>
+        <v>0.0558</v>
       </c>
       <c r="C588" t="n">
-        <v>0.441489</v>
+        <v>0.453826</v>
       </c>
     </row>
     <row r="589">
@@ -8071,10 +8071,10 @@
         </is>
       </c>
       <c r="B589" t="n">
-        <v>0.052149</v>
+        <v>0.056032</v>
       </c>
       <c r="C589" t="n">
-        <v>0.43883</v>
+        <v>0.451187</v>
       </c>
     </row>
     <row r="590">
@@ -8084,10 +8084,10 @@
         </is>
       </c>
       <c r="B590" t="n">
-        <v>0.052174</v>
+        <v>0.056138</v>
       </c>
       <c r="C590" t="n">
-        <v>0.43617</v>
+        <v>0.448549</v>
       </c>
     </row>
     <row r="591">
@@ -8097,10 +8097,10 @@
         </is>
       </c>
       <c r="B591" t="n">
-        <v>0.052306</v>
+        <v>0.056156</v>
       </c>
       <c r="C591" t="n">
-        <v>0.433511</v>
+        <v>0.44591</v>
       </c>
     </row>
     <row r="592">
@@ -8110,10 +8110,10 @@
         </is>
       </c>
       <c r="B592" t="n">
-        <v>0.052566</v>
+        <v>0.05715</v>
       </c>
       <c r="C592" t="n">
-        <v>0.430851</v>
+        <v>0.443272</v>
       </c>
     </row>
     <row r="593">
@@ -8123,10 +8123,10 @@
         </is>
       </c>
       <c r="B593" t="n">
-        <v>0.053421</v>
+        <v>0.057287</v>
       </c>
       <c r="C593" t="n">
-        <v>0.428191</v>
+        <v>0.440633</v>
       </c>
     </row>
     <row r="594">
@@ -8136,10 +8136,10 @@
         </is>
       </c>
       <c r="B594" t="n">
-        <v>0.054249</v>
+        <v>0.057297</v>
       </c>
       <c r="C594" t="n">
-        <v>0.425532</v>
+        <v>0.437995</v>
       </c>
     </row>
     <row r="595">
@@ -8149,10 +8149,10 @@
         </is>
       </c>
       <c r="B595" t="n">
-        <v>0.054469</v>
+        <v>0.057479</v>
       </c>
       <c r="C595" t="n">
-        <v>0.422872</v>
+        <v>0.435356</v>
       </c>
     </row>
     <row r="596">
@@ -8162,10 +8162,10 @@
         </is>
       </c>
       <c r="B596" t="n">
-        <v>0.054647</v>
+        <v>0.05887</v>
       </c>
       <c r="C596" t="n">
-        <v>0.420213</v>
+        <v>0.432718</v>
       </c>
     </row>
     <row r="597">
@@ -8175,10 +8175,10 @@
         </is>
       </c>
       <c r="B597" t="n">
-        <v>0.054803</v>
+        <v>0.059453</v>
       </c>
       <c r="C597" t="n">
-        <v>0.417553</v>
+        <v>0.430079</v>
       </c>
     </row>
     <row r="598">
@@ -8188,10 +8188,10 @@
         </is>
       </c>
       <c r="B598" t="n">
-        <v>0.05631</v>
+        <v>0.059885</v>
       </c>
       <c r="C598" t="n">
-        <v>0.414894</v>
+        <v>0.427441</v>
       </c>
     </row>
     <row r="599">
@@ -8201,10 +8201,10 @@
         </is>
       </c>
       <c r="B599" t="n">
-        <v>0.057265</v>
+        <v>0.05991</v>
       </c>
       <c r="C599" t="n">
-        <v>0.412234</v>
+        <v>0.424802</v>
       </c>
     </row>
     <row r="600">
@@ -8214,10 +8214,10 @@
         </is>
       </c>
       <c r="B600" t="n">
-        <v>0.057486</v>
+        <v>0.060341</v>
       </c>
       <c r="C600" t="n">
-        <v>0.409574</v>
+        <v>0.422164</v>
       </c>
     </row>
     <row r="601">
@@ -8227,10 +8227,10 @@
         </is>
       </c>
       <c r="B601" t="n">
-        <v>0.059105</v>
+        <v>0.062207</v>
       </c>
       <c r="C601" t="n">
-        <v>0.406915</v>
+        <v>0.419525</v>
       </c>
     </row>
     <row r="602">
@@ -8240,10 +8240,10 @@
         </is>
       </c>
       <c r="B602" t="n">
-        <v>0.059106</v>
+        <v>0.06257799999999999</v>
       </c>
       <c r="C602" t="n">
-        <v>0.404255</v>
+        <v>0.416887</v>
       </c>
     </row>
     <row r="603">
@@ -8253,10 +8253,10 @@
         </is>
       </c>
       <c r="B603" t="n">
-        <v>0.059827</v>
+        <v>0.062733</v>
       </c>
       <c r="C603" t="n">
-        <v>0.401596</v>
+        <v>0.414248</v>
       </c>
     </row>
     <row r="604">
@@ -8266,10 +8266,10 @@
         </is>
       </c>
       <c r="B604" t="n">
-        <v>0.059954</v>
+        <v>0.06338199999999999</v>
       </c>
       <c r="C604" t="n">
-        <v>0.398936</v>
+        <v>0.411609</v>
       </c>
     </row>
     <row r="605">
@@ -8279,10 +8279,10 @@
         </is>
       </c>
       <c r="B605" t="n">
-        <v>0.06015</v>
+        <v>0.064098</v>
       </c>
       <c r="C605" t="n">
-        <v>0.396277</v>
+        <v>0.408971</v>
       </c>
     </row>
     <row r="606">
@@ -8292,10 +8292,10 @@
         </is>
       </c>
       <c r="B606" t="n">
-        <v>0.060828</v>
+        <v>0.06593</v>
       </c>
       <c r="C606" t="n">
-        <v>0.393617</v>
+        <v>0.406332</v>
       </c>
     </row>
     <row r="607">
@@ -8305,10 +8305,10 @@
         </is>
       </c>
       <c r="B607" t="n">
-        <v>0.060973</v>
+        <v>0.066326</v>
       </c>
       <c r="C607" t="n">
-        <v>0.390957</v>
+        <v>0.403694</v>
       </c>
     </row>
     <row r="608">
@@ -8318,10 +8318,10 @@
         </is>
       </c>
       <c r="B608" t="n">
-        <v>0.061492</v>
+        <v>0.066454</v>
       </c>
       <c r="C608" t="n">
-        <v>0.388298</v>
+        <v>0.401055</v>
       </c>
     </row>
     <row r="609">
@@ -8331,10 +8331,10 @@
         </is>
       </c>
       <c r="B609" t="n">
-        <v>0.061675</v>
+        <v>0.066579</v>
       </c>
       <c r="C609" t="n">
-        <v>0.385638</v>
+        <v>0.398417</v>
       </c>
     </row>
     <row r="610">
@@ -8344,10 +8344,10 @@
         </is>
       </c>
       <c r="B610" t="n">
-        <v>0.061698</v>
+        <v>0.066731</v>
       </c>
       <c r="C610" t="n">
-        <v>0.382979</v>
+        <v>0.395778</v>
       </c>
     </row>
     <row r="611">
@@ -8357,10 +8357,10 @@
         </is>
       </c>
       <c r="B611" t="n">
-        <v>0.061947</v>
+        <v>0.066917</v>
       </c>
       <c r="C611" t="n">
-        <v>0.380319</v>
+        <v>0.39314</v>
       </c>
     </row>
     <row r="612">
@@ -8370,10 +8370,10 @@
         </is>
       </c>
       <c r="B612" t="n">
-        <v>0.062155</v>
+        <v>0.067105</v>
       </c>
       <c r="C612" t="n">
-        <v>0.37766</v>
+        <v>0.390501</v>
       </c>
     </row>
     <row r="613">
@@ -8383,10 +8383,10 @@
         </is>
       </c>
       <c r="B613" t="n">
-        <v>0.06267399999999999</v>
+        <v>0.06712899999999999</v>
       </c>
       <c r="C613" t="n">
-        <v>0.375</v>
+        <v>0.387863</v>
       </c>
     </row>
     <row r="614">
@@ -8396,10 +8396,10 @@
         </is>
       </c>
       <c r="B614" t="n">
-        <v>0.06274</v>
+        <v>0.06714100000000001</v>
       </c>
       <c r="C614" t="n">
-        <v>0.37234</v>
+        <v>0.385224</v>
       </c>
     </row>
     <row r="615">
@@ -8409,10 +8409,10 @@
         </is>
       </c>
       <c r="B615" t="n">
-        <v>0.062892</v>
+        <v>0.06783599999999999</v>
       </c>
       <c r="C615" t="n">
-        <v>0.369681</v>
+        <v>0.382586</v>
       </c>
     </row>
     <row r="616">
@@ -8422,10 +8422,10 @@
         </is>
       </c>
       <c r="B616" t="n">
-        <v>0.06310499999999999</v>
+        <v>0.06851500000000001</v>
       </c>
       <c r="C616" t="n">
-        <v>0.367021</v>
+        <v>0.379947</v>
       </c>
     </row>
     <row r="617">
@@ -8435,10 +8435,10 @@
         </is>
       </c>
       <c r="B617" t="n">
-        <v>0.063152</v>
+        <v>0.068607</v>
       </c>
       <c r="C617" t="n">
-        <v>0.364362</v>
+        <v>0.377309</v>
       </c>
     </row>
     <row r="618">
@@ -8448,10 +8448,10 @@
         </is>
       </c>
       <c r="B618" t="n">
-        <v>0.06340700000000001</v>
+        <v>0.06879</v>
       </c>
       <c r="C618" t="n">
-        <v>0.361702</v>
+        <v>0.37467</v>
       </c>
     </row>
     <row r="619">
@@ -8461,10 +8461,10 @@
         </is>
       </c>
       <c r="B619" t="n">
-        <v>0.063926</v>
+        <v>0.069324</v>
       </c>
       <c r="C619" t="n">
-        <v>0.359043</v>
+        <v>0.372032</v>
       </c>
     </row>
     <row r="620">
@@ -8474,10 +8474,10 @@
         </is>
       </c>
       <c r="B620" t="n">
-        <v>0.064183</v>
+        <v>0.06952999999999999</v>
       </c>
       <c r="C620" t="n">
-        <v>0.356383</v>
+        <v>0.369393</v>
       </c>
     </row>
     <row r="621">
@@ -8487,10 +8487,10 @@
         </is>
       </c>
       <c r="B621" t="n">
-        <v>0.064622</v>
+        <v>0.069549</v>
       </c>
       <c r="C621" t="n">
-        <v>0.353723</v>
+        <v>0.366755</v>
       </c>
     </row>
     <row r="622">
@@ -8500,10 +8500,10 @@
         </is>
       </c>
       <c r="B622" t="n">
-        <v>0.065391</v>
+        <v>0.069576</v>
       </c>
       <c r="C622" t="n">
-        <v>0.351064</v>
+        <v>0.364116</v>
       </c>
     </row>
     <row r="623">
@@ -8513,10 +8513,10 @@
         </is>
       </c>
       <c r="B623" t="n">
-        <v>0.06565799999999999</v>
+        <v>0.069808</v>
       </c>
       <c r="C623" t="n">
-        <v>0.348404</v>
+        <v>0.361478</v>
       </c>
     </row>
     <row r="624">
@@ -8526,10 +8526,10 @@
         </is>
       </c>
       <c r="B624" t="n">
-        <v>0.06615699999999999</v>
+        <v>0.069975</v>
       </c>
       <c r="C624" t="n">
-        <v>0.345745</v>
+        <v>0.358839</v>
       </c>
     </row>
     <row r="625">
@@ -8539,10 +8539,10 @@
         </is>
       </c>
       <c r="B625" t="n">
-        <v>0.066275</v>
+        <v>0.07097100000000001</v>
       </c>
       <c r="C625" t="n">
-        <v>0.343085</v>
+        <v>0.356201</v>
       </c>
     </row>
     <row r="626">
@@ -8552,10 +8552,10 @@
         </is>
       </c>
       <c r="B626" t="n">
-        <v>0.06665699999999999</v>
+        <v>0.07127</v>
       </c>
       <c r="C626" t="n">
-        <v>0.340426</v>
+        <v>0.353562</v>
       </c>
     </row>
     <row r="627">
@@ -8565,10 +8565,10 @@
         </is>
       </c>
       <c r="B627" t="n">
-        <v>0.066718</v>
+        <v>0.071532</v>
       </c>
       <c r="C627" t="n">
-        <v>0.337766</v>
+        <v>0.350923</v>
       </c>
     </row>
     <row r="628">
@@ -8578,10 +8578,10 @@
         </is>
       </c>
       <c r="B628" t="n">
-        <v>0.066894</v>
+        <v>0.071612</v>
       </c>
       <c r="C628" t="n">
-        <v>0.335106</v>
+        <v>0.348285</v>
       </c>
     </row>
     <row r="629">
@@ -8591,10 +8591,10 @@
         </is>
       </c>
       <c r="B629" t="n">
-        <v>0.068062</v>
+        <v>0.072672</v>
       </c>
       <c r="C629" t="n">
-        <v>0.332447</v>
+        <v>0.345646</v>
       </c>
     </row>
     <row r="630">
@@ -8604,10 +8604,10 @@
         </is>
       </c>
       <c r="B630" t="n">
-        <v>0.06837699999999999</v>
+        <v>0.07306699999999999</v>
       </c>
       <c r="C630" t="n">
-        <v>0.329787</v>
+        <v>0.343008</v>
       </c>
     </row>
     <row r="631">
@@ -8617,10 +8617,10 @@
         </is>
       </c>
       <c r="B631" t="n">
-        <v>0.06851</v>
+        <v>0.07411</v>
       </c>
       <c r="C631" t="n">
-        <v>0.327128</v>
+        <v>0.340369</v>
       </c>
     </row>
     <row r="632">
@@ -8630,10 +8630,10 @@
         </is>
       </c>
       <c r="B632" t="n">
-        <v>0.068568</v>
+        <v>0.074171</v>
       </c>
       <c r="C632" t="n">
-        <v>0.324468</v>
+        <v>0.337731</v>
       </c>
     </row>
     <row r="633">
@@ -8643,10 +8643,10 @@
         </is>
       </c>
       <c r="B633" t="n">
-        <v>0.06929299999999999</v>
+        <v>0.074208</v>
       </c>
       <c r="C633" t="n">
-        <v>0.321809</v>
+        <v>0.335092</v>
       </c>
     </row>
     <row r="634">
@@ -8656,10 +8656,10 @@
         </is>
       </c>
       <c r="B634" t="n">
-        <v>0.06981</v>
+        <v>0.075251</v>
       </c>
       <c r="C634" t="n">
-        <v>0.319149</v>
+        <v>0.332454</v>
       </c>
     </row>
     <row r="635">
@@ -8669,10 +8669,10 @@
         </is>
       </c>
       <c r="B635" t="n">
-        <v>0.06990399999999999</v>
+        <v>0.075336</v>
       </c>
       <c r="C635" t="n">
-        <v>0.316489</v>
+        <v>0.329815</v>
       </c>
     </row>
     <row r="636">
@@ -8682,10 +8682,10 @@
         </is>
       </c>
       <c r="B636" t="n">
-        <v>0.070462</v>
+        <v>0.075765</v>
       </c>
       <c r="C636" t="n">
-        <v>0.31383</v>
+        <v>0.327177</v>
       </c>
     </row>
     <row r="637">
@@ -8695,10 +8695,10 @@
         </is>
       </c>
       <c r="B637" t="n">
-        <v>0.07062</v>
+        <v>0.076504</v>
       </c>
       <c r="C637" t="n">
-        <v>0.31117</v>
+        <v>0.324538</v>
       </c>
     </row>
     <row r="638">
@@ -8708,10 +8708,10 @@
         </is>
       </c>
       <c r="B638" t="n">
-        <v>0.070713</v>
+        <v>0.07677100000000001</v>
       </c>
       <c r="C638" t="n">
-        <v>0.308511</v>
+        <v>0.3219</v>
       </c>
     </row>
     <row r="639">
@@ -8721,10 +8721,10 @@
         </is>
       </c>
       <c r="B639" t="n">
-        <v>0.07081899999999999</v>
+        <v>0.07700700000000001</v>
       </c>
       <c r="C639" t="n">
-        <v>0.305851</v>
+        <v>0.319261</v>
       </c>
     </row>
     <row r="640">
@@ -8734,10 +8734,10 @@
         </is>
       </c>
       <c r="B640" t="n">
-        <v>0.071283</v>
+        <v>0.077234</v>
       </c>
       <c r="C640" t="n">
-        <v>0.303191</v>
+        <v>0.316623</v>
       </c>
     </row>
     <row r="641">
@@ -8747,10 +8747,10 @@
         </is>
       </c>
       <c r="B641" t="n">
-        <v>0.072476</v>
+        <v>0.077345</v>
       </c>
       <c r="C641" t="n">
-        <v>0.300532</v>
+        <v>0.313984</v>
       </c>
     </row>
     <row r="642">
@@ -8760,10 +8760,10 @@
         </is>
       </c>
       <c r="B642" t="n">
-        <v>0.07283100000000001</v>
+        <v>0.077845</v>
       </c>
       <c r="C642" t="n">
-        <v>0.297872</v>
+        <v>0.311346</v>
       </c>
     </row>
     <row r="643">
@@ -8773,10 +8773,10 @@
         </is>
       </c>
       <c r="B643" t="n">
-        <v>0.073282</v>
+        <v>0.078677</v>
       </c>
       <c r="C643" t="n">
-        <v>0.295213</v>
+        <v>0.308707</v>
       </c>
     </row>
     <row r="644">
@@ -8786,10 +8786,10 @@
         </is>
       </c>
       <c r="B644" t="n">
-        <v>0.073453</v>
+        <v>0.078705</v>
       </c>
       <c r="C644" t="n">
-        <v>0.292553</v>
+        <v>0.306069</v>
       </c>
     </row>
     <row r="645">
@@ -8799,10 +8799,10 @@
         </is>
       </c>
       <c r="B645" t="n">
-        <v>0.074906</v>
+        <v>0.079037</v>
       </c>
       <c r="C645" t="n">
-        <v>0.289894</v>
+        <v>0.30343</v>
       </c>
     </row>
     <row r="646">
@@ -8812,10 +8812,10 @@
         </is>
       </c>
       <c r="B646" t="n">
-        <v>0.075296</v>
+        <v>0.07922700000000001</v>
       </c>
       <c r="C646" t="n">
-        <v>0.287234</v>
+        <v>0.300792</v>
       </c>
     </row>
     <row r="647">
@@ -8825,10 +8825,10 @@
         </is>
       </c>
       <c r="B647" t="n">
-        <v>0.075886</v>
+        <v>0.079641</v>
       </c>
       <c r="C647" t="n">
-        <v>0.284574</v>
+        <v>0.298153</v>
       </c>
     </row>
     <row r="648">
@@ -8838,10 +8838,10 @@
         </is>
       </c>
       <c r="B648" t="n">
-        <v>0.07615</v>
+        <v>0.07986</v>
       </c>
       <c r="C648" t="n">
-        <v>0.281915</v>
+        <v>0.295515</v>
       </c>
     </row>
     <row r="649">
@@ -8851,10 +8851,10 @@
         </is>
       </c>
       <c r="B649" t="n">
-        <v>0.076526</v>
+        <v>0.080543</v>
       </c>
       <c r="C649" t="n">
-        <v>0.279255</v>
+        <v>0.292876</v>
       </c>
     </row>
     <row r="650">
@@ -8864,10 +8864,10 @@
         </is>
       </c>
       <c r="B650" t="n">
-        <v>0.076887</v>
+        <v>0.08311300000000001</v>
       </c>
       <c r="C650" t="n">
-        <v>0.276596</v>
+        <v>0.290237</v>
       </c>
     </row>
     <row r="651">
@@ -8877,10 +8877,10 @@
         </is>
       </c>
       <c r="B651" t="n">
-        <v>0.07710500000000001</v>
+        <v>0.08384800000000001</v>
       </c>
       <c r="C651" t="n">
-        <v>0.273936</v>
+        <v>0.287599</v>
       </c>
     </row>
     <row r="652">
@@ -8890,10 +8890,10 @@
         </is>
       </c>
       <c r="B652" t="n">
-        <v>0.07987900000000001</v>
+        <v>0.08397399999999999</v>
       </c>
       <c r="C652" t="n">
-        <v>0.271277</v>
+        <v>0.28496</v>
       </c>
     </row>
     <row r="653">
@@ -8903,10 +8903,10 @@
         </is>
       </c>
       <c r="B653" t="n">
-        <v>0.08000699999999999</v>
+        <v>0.084896</v>
       </c>
       <c r="C653" t="n">
-        <v>0.268617</v>
+        <v>0.282322</v>
       </c>
     </row>
     <row r="654">
@@ -8916,10 +8916,10 @@
         </is>
       </c>
       <c r="B654" t="n">
-        <v>0.08071399999999999</v>
+        <v>0.085701</v>
       </c>
       <c r="C654" t="n">
-        <v>0.265957</v>
+        <v>0.279683</v>
       </c>
     </row>
     <row r="655">
@@ -8929,10 +8929,10 @@
         </is>
       </c>
       <c r="B655" t="n">
-        <v>0.080946</v>
+        <v>0.085898</v>
       </c>
       <c r="C655" t="n">
-        <v>0.263298</v>
+        <v>0.277045</v>
       </c>
     </row>
     <row r="656">
@@ -8942,10 +8942,10 @@
         </is>
       </c>
       <c r="B656" t="n">
-        <v>0.08137900000000001</v>
+        <v>0.085979</v>
       </c>
       <c r="C656" t="n">
-        <v>0.260638</v>
+        <v>0.274406</v>
       </c>
     </row>
     <row r="657">
@@ -8955,10 +8955,10 @@
         </is>
       </c>
       <c r="B657" t="n">
-        <v>0.08161499999999999</v>
+        <v>0.088051</v>
       </c>
       <c r="C657" t="n">
-        <v>0.257979</v>
+        <v>0.271768</v>
       </c>
     </row>
     <row r="658">
@@ -8968,10 +8968,10 @@
         </is>
       </c>
       <c r="B658" t="n">
-        <v>0.0824</v>
+        <v>0.08810800000000001</v>
       </c>
       <c r="C658" t="n">
-        <v>0.255319</v>
+        <v>0.269129</v>
       </c>
     </row>
     <row r="659">
@@ -8981,10 +8981,10 @@
         </is>
       </c>
       <c r="B659" t="n">
-        <v>0.083053</v>
+        <v>0.088436</v>
       </c>
       <c r="C659" t="n">
-        <v>0.25266</v>
+        <v>0.266491</v>
       </c>
     </row>
     <row r="660">
@@ -8994,10 +8994,10 @@
         </is>
       </c>
       <c r="B660" t="n">
-        <v>0.083201</v>
+        <v>0.088728</v>
       </c>
       <c r="C660" t="n">
-        <v>0.25</v>
+        <v>0.263852</v>
       </c>
     </row>
     <row r="661">
@@ -9007,10 +9007,10 @@
         </is>
       </c>
       <c r="B661" t="n">
-        <v>0.08387500000000001</v>
+        <v>0.08988699999999999</v>
       </c>
       <c r="C661" t="n">
-        <v>0.24734</v>
+        <v>0.261214</v>
       </c>
     </row>
     <row r="662">
@@ -9020,10 +9020,10 @@
         </is>
       </c>
       <c r="B662" t="n">
-        <v>0.0843</v>
+        <v>0.090041</v>
       </c>
       <c r="C662" t="n">
-        <v>0.244681</v>
+        <v>0.258575</v>
       </c>
     </row>
     <row r="663">
@@ -9033,10 +9033,10 @@
         </is>
       </c>
       <c r="B663" t="n">
-        <v>0.084425</v>
+        <v>0.090479</v>
       </c>
       <c r="C663" t="n">
-        <v>0.242021</v>
+        <v>0.255937</v>
       </c>
     </row>
     <row r="664">
@@ -9046,10 +9046,10 @@
         </is>
       </c>
       <c r="B664" t="n">
-        <v>0.08463</v>
+        <v>0.091014</v>
       </c>
       <c r="C664" t="n">
-        <v>0.239362</v>
+        <v>0.253298</v>
       </c>
     </row>
     <row r="665">
@@ -9059,10 +9059,10 @@
         </is>
       </c>
       <c r="B665" t="n">
-        <v>0.085004</v>
+        <v>0.091387</v>
       </c>
       <c r="C665" t="n">
-        <v>0.236702</v>
+        <v>0.25066</v>
       </c>
     </row>
     <row r="666">
@@ -9072,10 +9072,10 @@
         </is>
       </c>
       <c r="B666" t="n">
-        <v>0.085185</v>
+        <v>0.091737</v>
       </c>
       <c r="C666" t="n">
-        <v>0.234043</v>
+        <v>0.248021</v>
       </c>
     </row>
     <row r="667">
@@ -9085,10 +9085,10 @@
         </is>
       </c>
       <c r="B667" t="n">
-        <v>0.086906</v>
+        <v>0.092594</v>
       </c>
       <c r="C667" t="n">
-        <v>0.231383</v>
+        <v>0.245383</v>
       </c>
     </row>
     <row r="668">
@@ -9098,10 +9098,10 @@
         </is>
       </c>
       <c r="B668" t="n">
-        <v>0.08698599999999999</v>
+        <v>0.092686</v>
       </c>
       <c r="C668" t="n">
-        <v>0.228723</v>
+        <v>0.242744</v>
       </c>
     </row>
     <row r="669">
@@ -9111,10 +9111,10 @@
         </is>
       </c>
       <c r="B669" t="n">
-        <v>0.087474</v>
+        <v>0.093033</v>
       </c>
       <c r="C669" t="n">
-        <v>0.226064</v>
+        <v>0.240106</v>
       </c>
     </row>
     <row r="670">
@@ -9124,10 +9124,10 @@
         </is>
       </c>
       <c r="B670" t="n">
-        <v>0.087716</v>
+        <v>0.093144</v>
       </c>
       <c r="C670" t="n">
-        <v>0.223404</v>
+        <v>0.237467</v>
       </c>
     </row>
     <row r="671">
@@ -9137,10 +9137,10 @@
         </is>
       </c>
       <c r="B671" t="n">
-        <v>0.08802</v>
+        <v>0.094732</v>
       </c>
       <c r="C671" t="n">
-        <v>0.220745</v>
+        <v>0.234828</v>
       </c>
     </row>
     <row r="672">
@@ -9150,10 +9150,10 @@
         </is>
       </c>
       <c r="B672" t="n">
-        <v>0.088958</v>
+        <v>0.09575500000000001</v>
       </c>
       <c r="C672" t="n">
-        <v>0.218085</v>
+        <v>0.23219</v>
       </c>
     </row>
     <row r="673">
@@ -9163,10 +9163,10 @@
         </is>
       </c>
       <c r="B673" t="n">
-        <v>0.089104</v>
+        <v>0.097229</v>
       </c>
       <c r="C673" t="n">
-        <v>0.215426</v>
+        <v>0.229551</v>
       </c>
     </row>
     <row r="674">
@@ -9176,10 +9176,10 @@
         </is>
       </c>
       <c r="B674" t="n">
-        <v>0.089249</v>
+        <v>0.09755800000000001</v>
       </c>
       <c r="C674" t="n">
-        <v>0.212766</v>
+        <v>0.226913</v>
       </c>
     </row>
     <row r="675">
@@ -9189,10 +9189,10 @@
         </is>
       </c>
       <c r="B675" t="n">
-        <v>0.09063499999999999</v>
+        <v>0.099901</v>
       </c>
       <c r="C675" t="n">
-        <v>0.210106</v>
+        <v>0.224274</v>
       </c>
     </row>
     <row r="676">
@@ -9202,10 +9202,10 @@
         </is>
       </c>
       <c r="B676" t="n">
-        <v>0.090902</v>
+        <v>0.09998899999999999</v>
       </c>
       <c r="C676" t="n">
-        <v>0.207447</v>
+        <v>0.221636</v>
       </c>
     </row>
     <row r="677">
@@ -9215,10 +9215,10 @@
         </is>
       </c>
       <c r="B677" t="n">
-        <v>0.091964</v>
+        <v>0.100401</v>
       </c>
       <c r="C677" t="n">
-        <v>0.204787</v>
+        <v>0.218997</v>
       </c>
     </row>
     <row r="678">
@@ -9228,10 +9228,10 @@
         </is>
       </c>
       <c r="B678" t="n">
-        <v>0.092474</v>
+        <v>0.100825</v>
       </c>
       <c r="C678" t="n">
-        <v>0.202128</v>
+        <v>0.216359</v>
       </c>
     </row>
     <row r="679">
@@ -9241,10 +9241,10 @@
         </is>
       </c>
       <c r="B679" t="n">
-        <v>0.09306499999999999</v>
+        <v>0.100983</v>
       </c>
       <c r="C679" t="n">
-        <v>0.199468</v>
+        <v>0.21372</v>
       </c>
     </row>
     <row r="680">
@@ -9254,10 +9254,10 @@
         </is>
       </c>
       <c r="B680" t="n">
-        <v>0.094267</v>
+        <v>0.102291</v>
       </c>
       <c r="C680" t="n">
-        <v>0.196809</v>
+        <v>0.211082</v>
       </c>
     </row>
     <row r="681">
@@ -9267,10 +9267,10 @@
         </is>
       </c>
       <c r="B681" t="n">
-        <v>0.094307</v>
+        <v>0.102562</v>
       </c>
       <c r="C681" t="n">
-        <v>0.194149</v>
+        <v>0.208443</v>
       </c>
     </row>
     <row r="682">
@@ -9280,10 +9280,10 @@
         </is>
       </c>
       <c r="B682" t="n">
-        <v>0.09436799999999999</v>
+        <v>0.102617</v>
       </c>
       <c r="C682" t="n">
-        <v>0.191489</v>
+        <v>0.205805</v>
       </c>
     </row>
     <row r="683">
@@ -9293,10 +9293,10 @@
         </is>
       </c>
       <c r="B683" t="n">
-        <v>0.094981</v>
+        <v>0.103035</v>
       </c>
       <c r="C683" t="n">
-        <v>0.18883</v>
+        <v>0.203166</v>
       </c>
     </row>
     <row r="684">
@@ -9306,10 +9306,10 @@
         </is>
       </c>
       <c r="B684" t="n">
-        <v>0.09550500000000001</v>
+        <v>0.103709</v>
       </c>
       <c r="C684" t="n">
-        <v>0.18617</v>
+        <v>0.200528</v>
       </c>
     </row>
     <row r="685">
@@ -9319,10 +9319,10 @@
         </is>
       </c>
       <c r="B685" t="n">
-        <v>0.097443</v>
+        <v>0.104654</v>
       </c>
       <c r="C685" t="n">
-        <v>0.183511</v>
+        <v>0.197889</v>
       </c>
     </row>
     <row r="686">
@@ -9332,10 +9332,10 @@
         </is>
       </c>
       <c r="B686" t="n">
-        <v>0.097576</v>
+        <v>0.106101</v>
       </c>
       <c r="C686" t="n">
-        <v>0.180851</v>
+        <v>0.195251</v>
       </c>
     </row>
     <row r="687">
@@ -9345,10 +9345,10 @@
         </is>
       </c>
       <c r="B687" t="n">
-        <v>0.10056</v>
+        <v>0.106919</v>
       </c>
       <c r="C687" t="n">
-        <v>0.178191</v>
+        <v>0.192612</v>
       </c>
     </row>
     <row r="688">
@@ -9358,10 +9358,10 @@
         </is>
       </c>
       <c r="B688" t="n">
-        <v>0.102206</v>
+        <v>0.107298</v>
       </c>
       <c r="C688" t="n">
-        <v>0.175532</v>
+        <v>0.189974</v>
       </c>
     </row>
     <row r="689">
@@ -9371,10 +9371,10 @@
         </is>
       </c>
       <c r="B689" t="n">
-        <v>0.103992</v>
+        <v>0.107991</v>
       </c>
       <c r="C689" t="n">
-        <v>0.172872</v>
+        <v>0.187335</v>
       </c>
     </row>
     <row r="690">
@@ -9384,10 +9384,10 @@
         </is>
       </c>
       <c r="B690" t="n">
-        <v>0.104526</v>
+        <v>0.108116</v>
       </c>
       <c r="C690" t="n">
-        <v>0.170213</v>
+        <v>0.184697</v>
       </c>
     </row>
     <row r="691">
@@ -9397,10 +9397,10 @@
         </is>
       </c>
       <c r="B691" t="n">
-        <v>0.105089</v>
+        <v>0.110368</v>
       </c>
       <c r="C691" t="n">
-        <v>0.167553</v>
+        <v>0.182058</v>
       </c>
     </row>
     <row r="692">
@@ -9410,10 +9410,10 @@
         </is>
       </c>
       <c r="B692" t="n">
-        <v>0.105283</v>
+        <v>0.110464</v>
       </c>
       <c r="C692" t="n">
-        <v>0.164894</v>
+        <v>0.17942</v>
       </c>
     </row>
     <row r="693">
@@ -9423,10 +9423,10 @@
         </is>
       </c>
       <c r="B693" t="n">
-        <v>0.107938</v>
+        <v>0.110582</v>
       </c>
       <c r="C693" t="n">
-        <v>0.162234</v>
+        <v>0.176781</v>
       </c>
     </row>
     <row r="694">
@@ -9436,10 +9436,10 @@
         </is>
       </c>
       <c r="B694" t="n">
-        <v>0.108433</v>
+        <v>0.110788</v>
       </c>
       <c r="C694" t="n">
-        <v>0.159574</v>
+        <v>0.174142</v>
       </c>
     </row>
     <row r="695">
@@ -9449,10 +9449,10 @@
         </is>
       </c>
       <c r="B695" t="n">
-        <v>0.108788</v>
+        <v>0.111261</v>
       </c>
       <c r="C695" t="n">
-        <v>0.156915</v>
+        <v>0.171504</v>
       </c>
     </row>
     <row r="696">
@@ -9462,10 +9462,10 @@
         </is>
       </c>
       <c r="B696" t="n">
-        <v>0.110905</v>
+        <v>0.113695</v>
       </c>
       <c r="C696" t="n">
-        <v>0.154255</v>
+        <v>0.168865</v>
       </c>
     </row>
     <row r="697">
@@ -9475,10 +9475,10 @@
         </is>
       </c>
       <c r="B697" t="n">
-        <v>0.111574</v>
+        <v>0.119004</v>
       </c>
       <c r="C697" t="n">
-        <v>0.151596</v>
+        <v>0.166227</v>
       </c>
     </row>
     <row r="698">
@@ -9488,10 +9488,10 @@
         </is>
       </c>
       <c r="B698" t="n">
-        <v>0.112195</v>
+        <v>0.120494</v>
       </c>
       <c r="C698" t="n">
-        <v>0.148936</v>
+        <v>0.163588</v>
       </c>
     </row>
     <row r="699">
@@ -9501,10 +9501,10 @@
         </is>
       </c>
       <c r="B699" t="n">
-        <v>0.113543</v>
+        <v>0.120636</v>
       </c>
       <c r="C699" t="n">
-        <v>0.146277</v>
+        <v>0.16095</v>
       </c>
     </row>
     <row r="700">
@@ -9514,10 +9514,10 @@
         </is>
       </c>
       <c r="B700" t="n">
-        <v>0.114797</v>
+        <v>0.120744</v>
       </c>
       <c r="C700" t="n">
-        <v>0.143617</v>
+        <v>0.158311</v>
       </c>
     </row>
     <row r="701">
@@ -9527,10 +9527,10 @@
         </is>
       </c>
       <c r="B701" t="n">
-        <v>0.116567</v>
+        <v>0.125547</v>
       </c>
       <c r="C701" t="n">
-        <v>0.140957</v>
+        <v>0.155673</v>
       </c>
     </row>
     <row r="702">
@@ -9540,10 +9540,10 @@
         </is>
       </c>
       <c r="B702" t="n">
-        <v>0.116761</v>
+        <v>0.126672</v>
       </c>
       <c r="C702" t="n">
-        <v>0.138298</v>
+        <v>0.153034</v>
       </c>
     </row>
     <row r="703">
@@ -9553,10 +9553,10 @@
         </is>
       </c>
       <c r="B703" t="n">
-        <v>0.117243</v>
+        <v>0.127382</v>
       </c>
       <c r="C703" t="n">
-        <v>0.135638</v>
+        <v>0.150396</v>
       </c>
     </row>
     <row r="704">
@@ -9566,10 +9566,10 @@
         </is>
       </c>
       <c r="B704" t="n">
-        <v>0.117797</v>
+        <v>0.128121</v>
       </c>
       <c r="C704" t="n">
-        <v>0.132979</v>
+        <v>0.147757</v>
       </c>
     </row>
     <row r="705">
@@ -9579,10 +9579,10 @@
         </is>
       </c>
       <c r="B705" t="n">
-        <v>0.118039</v>
+        <v>0.128368</v>
       </c>
       <c r="C705" t="n">
-        <v>0.130319</v>
+        <v>0.145119</v>
       </c>
     </row>
     <row r="706">
@@ -9592,10 +9592,10 @@
         </is>
       </c>
       <c r="B706" t="n">
-        <v>0.119262</v>
+        <v>0.128719</v>
       </c>
       <c r="C706" t="n">
-        <v>0.12766</v>
+        <v>0.14248</v>
       </c>
     </row>
     <row r="707">
@@ -9605,10 +9605,10 @@
         </is>
       </c>
       <c r="B707" t="n">
-        <v>0.119439</v>
+        <v>0.128994</v>
       </c>
       <c r="C707" t="n">
-        <v>0.125</v>
+        <v>0.139842</v>
       </c>
     </row>
     <row r="708">
@@ -9618,10 +9618,10 @@
         </is>
       </c>
       <c r="B708" t="n">
-        <v>0.119873</v>
+        <v>0.129007</v>
       </c>
       <c r="C708" t="n">
-        <v>0.12234</v>
+        <v>0.137203</v>
       </c>
     </row>
     <row r="709">
@@ -9631,10 +9631,10 @@
         </is>
       </c>
       <c r="B709" t="n">
-        <v>0.122986</v>
+        <v>0.129223</v>
       </c>
       <c r="C709" t="n">
-        <v>0.119681</v>
+        <v>0.134565</v>
       </c>
     </row>
     <row r="710">
@@ -9644,10 +9644,10 @@
         </is>
       </c>
       <c r="B710" t="n">
-        <v>0.12344</v>
+        <v>0.129761</v>
       </c>
       <c r="C710" t="n">
-        <v>0.117021</v>
+        <v>0.131926</v>
       </c>
     </row>
     <row r="711">
@@ -9657,10 +9657,10 @@
         </is>
       </c>
       <c r="B711" t="n">
-        <v>0.124248</v>
+        <v>0.130485</v>
       </c>
       <c r="C711" t="n">
-        <v>0.114362</v>
+        <v>0.129288</v>
       </c>
     </row>
     <row r="712">
@@ -9670,10 +9670,10 @@
         </is>
       </c>
       <c r="B712" t="n">
-        <v>0.126154</v>
+        <v>0.13387</v>
       </c>
       <c r="C712" t="n">
-        <v>0.111702</v>
+        <v>0.126649</v>
       </c>
     </row>
     <row r="713">
@@ -9683,10 +9683,10 @@
         </is>
       </c>
       <c r="B713" t="n">
-        <v>0.12781</v>
+        <v>0.134734</v>
       </c>
       <c r="C713" t="n">
-        <v>0.109043</v>
+        <v>0.124011</v>
       </c>
     </row>
     <row r="714">
@@ -9696,10 +9696,10 @@
         </is>
       </c>
       <c r="B714" t="n">
-        <v>0.127819</v>
+        <v>0.135829</v>
       </c>
       <c r="C714" t="n">
-        <v>0.106383</v>
+        <v>0.121372</v>
       </c>
     </row>
     <row r="715">
@@ -9709,10 +9709,10 @@
         </is>
       </c>
       <c r="B715" t="n">
-        <v>0.128916</v>
+        <v>0.135981</v>
       </c>
       <c r="C715" t="n">
-        <v>0.103723</v>
+        <v>0.118734</v>
       </c>
     </row>
     <row r="716">
@@ -9722,10 +9722,10 @@
         </is>
       </c>
       <c r="B716" t="n">
-        <v>0.130024</v>
+        <v>0.138899</v>
       </c>
       <c r="C716" t="n">
-        <v>0.101064</v>
+        <v>0.116095</v>
       </c>
     </row>
     <row r="717">
@@ -9735,10 +9735,10 @@
         </is>
       </c>
       <c r="B717" t="n">
-        <v>0.130967</v>
+        <v>0.140277</v>
       </c>
       <c r="C717" t="n">
-        <v>0.09840400000000001</v>
+        <v>0.113456</v>
       </c>
     </row>
     <row r="718">
@@ -9748,10 +9748,10 @@
         </is>
       </c>
       <c r="B718" t="n">
-        <v>0.131323</v>
+        <v>0.141467</v>
       </c>
       <c r="C718" t="n">
-        <v>0.095745</v>
+        <v>0.110818</v>
       </c>
     </row>
     <row r="719">
@@ -9761,10 +9761,10 @@
         </is>
       </c>
       <c r="B719" t="n">
-        <v>0.13169</v>
+        <v>0.14148</v>
       </c>
       <c r="C719" t="n">
-        <v>0.093085</v>
+        <v>0.108179</v>
       </c>
     </row>
     <row r="720">
@@ -9774,10 +9774,10 @@
         </is>
       </c>
       <c r="B720" t="n">
-        <v>0.133358</v>
+        <v>0.142325</v>
       </c>
       <c r="C720" t="n">
-        <v>0.09042600000000001</v>
+        <v>0.105541</v>
       </c>
     </row>
     <row r="721">
@@ -9787,10 +9787,10 @@
         </is>
       </c>
       <c r="B721" t="n">
-        <v>0.133507</v>
+        <v>0.143001</v>
       </c>
       <c r="C721" t="n">
-        <v>0.087766</v>
+        <v>0.102902</v>
       </c>
     </row>
     <row r="722">
@@ -9800,10 +9800,10 @@
         </is>
       </c>
       <c r="B722" t="n">
-        <v>0.137073</v>
+        <v>0.145169</v>
       </c>
       <c r="C722" t="n">
-        <v>0.085106</v>
+        <v>0.100264</v>
       </c>
     </row>
     <row r="723">
@@ -9813,10 +9813,10 @@
         </is>
       </c>
       <c r="B723" t="n">
-        <v>0.146166</v>
+        <v>0.145655</v>
       </c>
       <c r="C723" t="n">
-        <v>0.08244700000000001</v>
+        <v>0.097625</v>
       </c>
     </row>
     <row r="724">
@@ -9826,10 +9826,10 @@
         </is>
       </c>
       <c r="B724" t="n">
-        <v>0.147565</v>
+        <v>0.149476</v>
       </c>
       <c r="C724" t="n">
-        <v>0.079787</v>
+        <v>0.094987</v>
       </c>
     </row>
     <row r="725">
@@ -9839,10 +9839,10 @@
         </is>
       </c>
       <c r="B725" t="n">
-        <v>0.149889</v>
+        <v>0.152893</v>
       </c>
       <c r="C725" t="n">
-        <v>0.077128</v>
+        <v>0.092348</v>
       </c>
     </row>
     <row r="726">
@@ -9852,10 +9852,10 @@
         </is>
       </c>
       <c r="B726" t="n">
-        <v>0.151093</v>
+        <v>0.153238</v>
       </c>
       <c r="C726" t="n">
-        <v>0.07446800000000001</v>
+        <v>0.08971</v>
       </c>
     </row>
     <row r="727">
@@ -9865,10 +9865,10 @@
         </is>
       </c>
       <c r="B727" t="n">
-        <v>0.152887</v>
+        <v>0.155304</v>
       </c>
       <c r="C727" t="n">
-        <v>0.071809</v>
+        <v>0.087071</v>
       </c>
     </row>
     <row r="728">
@@ -9878,10 +9878,10 @@
         </is>
       </c>
       <c r="B728" t="n">
-        <v>0.158037</v>
+        <v>0.156525</v>
       </c>
       <c r="C728" t="n">
-        <v>0.069149</v>
+        <v>0.08443299999999999</v>
       </c>
     </row>
     <row r="729">
@@ -9891,10 +9891,10 @@
         </is>
       </c>
       <c r="B729" t="n">
-        <v>0.158408</v>
+        <v>0.160131</v>
       </c>
       <c r="C729" t="n">
-        <v>0.06648900000000001</v>
+        <v>0.08179400000000001</v>
       </c>
     </row>
     <row r="730">
@@ -9904,10 +9904,10 @@
         </is>
       </c>
       <c r="B730" t="n">
-        <v>0.159013</v>
+        <v>0.162467</v>
       </c>
       <c r="C730" t="n">
-        <v>0.06383</v>
+        <v>0.079156</v>
       </c>
     </row>
     <row r="731">
@@ -9917,10 +9917,10 @@
         </is>
       </c>
       <c r="B731" t="n">
-        <v>0.16111</v>
+        <v>0.168054</v>
       </c>
       <c r="C731" t="n">
-        <v>0.06117</v>
+        <v>0.076517</v>
       </c>
     </row>
     <row r="732">
@@ -9930,10 +9930,10 @@
         </is>
       </c>
       <c r="B732" t="n">
-        <v>0.163852</v>
+        <v>0.168139</v>
       </c>
       <c r="C732" t="n">
-        <v>0.058511</v>
+        <v>0.073879</v>
       </c>
     </row>
     <row r="733">
@@ -9943,10 +9943,10 @@
         </is>
       </c>
       <c r="B733" t="n">
-        <v>0.165874</v>
+        <v>0.168438</v>
       </c>
       <c r="C733" t="n">
-        <v>0.055851</v>
+        <v>0.07124</v>
       </c>
     </row>
     <row r="734">
@@ -9956,10 +9956,10 @@
         </is>
       </c>
       <c r="B734" t="n">
-        <v>0.166506</v>
+        <v>0.175208</v>
       </c>
       <c r="C734" t="n">
-        <v>0.053191</v>
+        <v>0.068602</v>
       </c>
     </row>
     <row r="735">
@@ -9969,10 +9969,10 @@
         </is>
       </c>
       <c r="B735" t="n">
-        <v>0.169646</v>
+        <v>0.176597</v>
       </c>
       <c r="C735" t="n">
-        <v>0.050532</v>
+        <v>0.06596299999999999</v>
       </c>
     </row>
     <row r="736">
@@ -9982,10 +9982,10 @@
         </is>
       </c>
       <c r="B736" t="n">
-        <v>0.174797</v>
+        <v>0.176726</v>
       </c>
       <c r="C736" t="n">
-        <v>0.047872</v>
+        <v>0.06332500000000001</v>
       </c>
     </row>
     <row r="737">
@@ -9995,10 +9995,10 @@
         </is>
       </c>
       <c r="B737" t="n">
-        <v>0.17631</v>
+        <v>0.17768</v>
       </c>
       <c r="C737" t="n">
-        <v>0.045213</v>
+        <v>0.060686</v>
       </c>
     </row>
     <row r="738">
@@ -10008,10 +10008,10 @@
         </is>
       </c>
       <c r="B738" t="n">
-        <v>0.178845</v>
+        <v>0.179825</v>
       </c>
       <c r="C738" t="n">
-        <v>0.042553</v>
+        <v>0.058047</v>
       </c>
     </row>
     <row r="739">
@@ -10021,10 +10021,10 @@
         </is>
       </c>
       <c r="B739" t="n">
-        <v>0.180465</v>
+        <v>0.181904</v>
       </c>
       <c r="C739" t="n">
-        <v>0.039894</v>
+        <v>0.055409</v>
       </c>
     </row>
     <row r="740">
@@ -10034,10 +10034,10 @@
         </is>
       </c>
       <c r="B740" t="n">
-        <v>0.18879</v>
+        <v>0.18737</v>
       </c>
       <c r="C740" t="n">
-        <v>0.037234</v>
+        <v>0.05277</v>
       </c>
     </row>
     <row r="741">
@@ -10047,10 +10047,10 @@
         </is>
       </c>
       <c r="B741" t="n">
-        <v>0.193711</v>
+        <v>0.190427</v>
       </c>
       <c r="C741" t="n">
-        <v>0.034574</v>
+        <v>0.050132</v>
       </c>
     </row>
     <row r="742">
@@ -10060,10 +10060,10 @@
         </is>
       </c>
       <c r="B742" t="n">
-        <v>0.202325</v>
+        <v>0.199346</v>
       </c>
       <c r="C742" t="n">
-        <v>0.031915</v>
+        <v>0.047493</v>
       </c>
     </row>
     <row r="743">
@@ -10073,10 +10073,10 @@
         </is>
       </c>
       <c r="B743" t="n">
-        <v>0.206049</v>
+        <v>0.204105</v>
       </c>
       <c r="C743" t="n">
-        <v>0.029255</v>
+        <v>0.044855</v>
       </c>
     </row>
     <row r="744">
@@ -10086,10 +10086,10 @@
         </is>
       </c>
       <c r="B744" t="n">
-        <v>0.215387</v>
+        <v>0.204548</v>
       </c>
       <c r="C744" t="n">
-        <v>0.026596</v>
+        <v>0.042216</v>
       </c>
     </row>
     <row r="745">
@@ -10099,10 +10099,10 @@
         </is>
       </c>
       <c r="B745" t="n">
-        <v>0.223697</v>
+        <v>0.209218</v>
       </c>
       <c r="C745" t="n">
-        <v>0.023936</v>
+        <v>0.039578</v>
       </c>
     </row>
     <row r="746">
@@ -10112,10 +10112,10 @@
         </is>
       </c>
       <c r="B746" t="n">
-        <v>0.225171</v>
+        <v>0.223518</v>
       </c>
       <c r="C746" t="n">
-        <v>0.021277</v>
+        <v>0.036939</v>
       </c>
     </row>
     <row r="747">
@@ -10125,10 +10125,10 @@
         </is>
       </c>
       <c r="B747" t="n">
-        <v>0.232207</v>
+        <v>0.227054</v>
       </c>
       <c r="C747" t="n">
-        <v>0.018617</v>
+        <v>0.034301</v>
       </c>
     </row>
     <row r="748">
@@ -10138,10 +10138,10 @@
         </is>
       </c>
       <c r="B748" t="n">
-        <v>0.248446</v>
+        <v>0.233215</v>
       </c>
       <c r="C748" t="n">
-        <v>0.015957</v>
+        <v>0.031662</v>
       </c>
     </row>
     <row r="749">
@@ -10151,10 +10151,10 @@
         </is>
       </c>
       <c r="B749" t="n">
-        <v>0.278184</v>
+        <v>0.234656</v>
       </c>
       <c r="C749" t="n">
-        <v>0.013298</v>
+        <v>0.029024</v>
       </c>
     </row>
     <row r="750">
@@ -10164,10 +10164,10 @@
         </is>
       </c>
       <c r="B750" t="n">
-        <v>0.279905</v>
+        <v>0.234697</v>
       </c>
       <c r="C750" t="n">
-        <v>0.010638</v>
+        <v>0.026385</v>
       </c>
     </row>
     <row r="751">
@@ -10177,10 +10177,10 @@
         </is>
       </c>
       <c r="B751" t="n">
-        <v>0.313884</v>
+        <v>0.237466</v>
       </c>
       <c r="C751" t="n">
-        <v>0.007979</v>
+        <v>0.023747</v>
       </c>
     </row>
     <row r="752">
@@ -10190,10 +10190,10 @@
         </is>
       </c>
       <c r="B752" t="n">
-        <v>0.351465</v>
+        <v>0.258644</v>
       </c>
       <c r="C752" t="n">
-        <v>0.005319</v>
+        <v>0.021108</v>
       </c>
     </row>
     <row r="753">
@@ -10203,10 +10203,88 @@
         </is>
       </c>
       <c r="B753" t="n">
-        <v>0.407638</v>
+        <v>0.265808</v>
       </c>
       <c r="C753" t="n">
-        <v>0.00266</v>
+        <v>0.01847</v>
+      </c>
+    </row>
+    <row r="754">
+      <c r="A754" t="inlineStr">
+        <is>
+          <t>Adjusted target</t>
+        </is>
+      </c>
+      <c r="B754" t="n">
+        <v>0.26786</v>
+      </c>
+      <c r="C754" t="n">
+        <v>0.015831</v>
+      </c>
+    </row>
+    <row r="755">
+      <c r="A755" t="inlineStr">
+        <is>
+          <t>Adjusted target</t>
+        </is>
+      </c>
+      <c r="B755" t="n">
+        <v>0.295848</v>
+      </c>
+      <c r="C755" t="n">
+        <v>0.013193</v>
+      </c>
+    </row>
+    <row r="756">
+      <c r="A756" t="inlineStr">
+        <is>
+          <t>Adjusted target</t>
+        </is>
+      </c>
+      <c r="B756" t="n">
+        <v>0.30141</v>
+      </c>
+      <c r="C756" t="n">
+        <v>0.010554</v>
+      </c>
+    </row>
+    <row r="757">
+      <c r="A757" t="inlineStr">
+        <is>
+          <t>Adjusted target</t>
+        </is>
+      </c>
+      <c r="B757" t="n">
+        <v>0.336573</v>
+      </c>
+      <c r="C757" t="n">
+        <v>0.007915999999999999</v>
+      </c>
+    </row>
+    <row r="758">
+      <c r="A758" t="inlineStr">
+        <is>
+          <t>Adjusted target</t>
+        </is>
+      </c>
+      <c r="B758" t="n">
+        <v>0.406597</v>
+      </c>
+      <c r="C758" t="n">
+        <v>0.005277</v>
+      </c>
+    </row>
+    <row r="759">
+      <c r="A759" t="inlineStr">
+        <is>
+          <t>Adjusted target</t>
+        </is>
+      </c>
+      <c r="B759" t="n">
+        <v>0.476819</v>
+      </c>
+      <c r="C759" t="n">
+        <v>0.002639</v>
       </c>
     </row>
   </sheetData>

--- a/vignettes/vignette-1/tail_exceedance_plot_data.xlsx
+++ b/vignettes/vignette-1/tail_exceedance_plot_data.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C759"/>
+  <dimension ref="A1:C735"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -456,7 +456,7 @@
         <v>9.3e-05</v>
       </c>
       <c r="C3" t="n">
-        <v>0.9973610000000001</v>
+        <v>0.997275</v>
       </c>
     </row>
     <row r="4">
@@ -469,7 +469,7 @@
         <v>0.000441</v>
       </c>
       <c r="C4" t="n">
-        <v>0.994723</v>
+        <v>0.99455</v>
       </c>
     </row>
     <row r="5">
@@ -482,7 +482,7 @@
         <v>0.000522</v>
       </c>
       <c r="C5" t="n">
-        <v>0.992084</v>
+        <v>0.991826</v>
       </c>
     </row>
     <row r="6">
@@ -495,7 +495,7 @@
         <v>0.001163</v>
       </c>
       <c r="C6" t="n">
-        <v>0.989446</v>
+        <v>0.989101</v>
       </c>
     </row>
     <row r="7">
@@ -508,7 +508,7 @@
         <v>0.001681</v>
       </c>
       <c r="C7" t="n">
-        <v>0.986807</v>
+        <v>0.986376</v>
       </c>
     </row>
     <row r="8">
@@ -521,7 +521,7 @@
         <v>0.00295</v>
       </c>
       <c r="C8" t="n">
-        <v>0.984169</v>
+        <v>0.9836510000000001</v>
       </c>
     </row>
     <row r="9">
@@ -534,7 +534,7 @@
         <v>0.002998</v>
       </c>
       <c r="C9" t="n">
-        <v>0.98153</v>
+        <v>0.980926</v>
       </c>
     </row>
     <row r="10">
@@ -547,7 +547,7 @@
         <v>0.003455</v>
       </c>
       <c r="C10" t="n">
-        <v>0.978892</v>
+        <v>0.978202</v>
       </c>
     </row>
     <row r="11">
@@ -560,7 +560,7 @@
         <v>0.003769</v>
       </c>
       <c r="C11" t="n">
-        <v>0.976253</v>
+        <v>0.975477</v>
       </c>
     </row>
     <row r="12">
@@ -573,7 +573,7 @@
         <v>0.003788</v>
       </c>
       <c r="C12" t="n">
-        <v>0.973615</v>
+        <v>0.972752</v>
       </c>
     </row>
     <row r="13">
@@ -586,7 +586,7 @@
         <v>0.004717</v>
       </c>
       <c r="C13" t="n">
-        <v>0.970976</v>
+        <v>0.970027</v>
       </c>
     </row>
     <row r="14">
@@ -599,7 +599,7 @@
         <v>0.004779</v>
       </c>
       <c r="C14" t="n">
-        <v>0.968338</v>
+        <v>0.967302</v>
       </c>
     </row>
     <row r="15">
@@ -612,7 +612,7 @@
         <v>0.004912</v>
       </c>
       <c r="C15" t="n">
-        <v>0.965699</v>
+        <v>0.964578</v>
       </c>
     </row>
     <row r="16">
@@ -625,7 +625,7 @@
         <v>0.005429</v>
       </c>
       <c r="C16" t="n">
-        <v>0.9630609999999999</v>
+        <v>0.961853</v>
       </c>
     </row>
     <row r="17">
@@ -638,7 +638,7 @@
         <v>0.005649</v>
       </c>
       <c r="C17" t="n">
-        <v>0.960422</v>
+        <v>0.959128</v>
       </c>
     </row>
     <row r="18">
@@ -651,7 +651,7 @@
         <v>0.00593</v>
       </c>
       <c r="C18" t="n">
-        <v>0.957784</v>
+        <v>0.956403</v>
       </c>
     </row>
     <row r="19">
@@ -664,7 +664,7 @@
         <v>0.006143</v>
       </c>
       <c r="C19" t="n">
-        <v>0.955145</v>
+        <v>0.953678</v>
       </c>
     </row>
     <row r="20">
@@ -677,7 +677,7 @@
         <v>0.006394</v>
       </c>
       <c r="C20" t="n">
-        <v>0.952507</v>
+        <v>0.950954</v>
       </c>
     </row>
     <row r="21">
@@ -690,7 +690,7 @@
         <v>0.006914</v>
       </c>
       <c r="C21" t="n">
-        <v>0.949868</v>
+        <v>0.948229</v>
       </c>
     </row>
     <row r="22">
@@ -703,7 +703,7 @@
         <v>0.007419</v>
       </c>
       <c r="C22" t="n">
-        <v>0.94723</v>
+        <v>0.945504</v>
       </c>
     </row>
     <row r="23">
@@ -716,7 +716,7 @@
         <v>0.007582</v>
       </c>
       <c r="C23" t="n">
-        <v>0.944591</v>
+        <v>0.942779</v>
       </c>
     </row>
     <row r="24">
@@ -729,7 +729,7 @@
         <v>0.008029</v>
       </c>
       <c r="C24" t="n">
-        <v>0.941953</v>
+        <v>0.9400539999999999</v>
       </c>
     </row>
     <row r="25">
@@ -742,7 +742,7 @@
         <v>0.008069</v>
       </c>
       <c r="C25" t="n">
-        <v>0.939314</v>
+        <v>0.93733</v>
       </c>
     </row>
     <row r="26">
@@ -755,7 +755,7 @@
         <v>0.008173</v>
       </c>
       <c r="C26" t="n">
-        <v>0.936675</v>
+        <v>0.934605</v>
       </c>
     </row>
     <row r="27">
@@ -768,7 +768,7 @@
         <v>0.008377000000000001</v>
       </c>
       <c r="C27" t="n">
-        <v>0.934037</v>
+        <v>0.93188</v>
       </c>
     </row>
     <row r="28">
@@ -781,7 +781,7 @@
         <v>0.008593999999999999</v>
       </c>
       <c r="C28" t="n">
-        <v>0.9313979999999999</v>
+        <v>0.929155</v>
       </c>
     </row>
     <row r="29">
@@ -791,10 +791,10 @@
         </is>
       </c>
       <c r="B29" t="n">
-        <v>0.008658000000000001</v>
+        <v>0.008992</v>
       </c>
       <c r="C29" t="n">
-        <v>0.92876</v>
+        <v>0.926431</v>
       </c>
     </row>
     <row r="30">
@@ -804,10 +804,10 @@
         </is>
       </c>
       <c r="B30" t="n">
-        <v>0.008992</v>
+        <v>0.009165</v>
       </c>
       <c r="C30" t="n">
-        <v>0.926121</v>
+        <v>0.923706</v>
       </c>
     </row>
     <row r="31">
@@ -817,10 +817,10 @@
         </is>
       </c>
       <c r="B31" t="n">
-        <v>0.009165</v>
+        <v>0.009428000000000001</v>
       </c>
       <c r="C31" t="n">
-        <v>0.9234830000000001</v>
+        <v>0.920981</v>
       </c>
     </row>
     <row r="32">
@@ -830,10 +830,10 @@
         </is>
       </c>
       <c r="B32" t="n">
-        <v>0.009428000000000001</v>
+        <v>0.009578</v>
       </c>
       <c r="C32" t="n">
-        <v>0.920844</v>
+        <v>0.918256</v>
       </c>
     </row>
     <row r="33">
@@ -843,10 +843,10 @@
         </is>
       </c>
       <c r="B33" t="n">
-        <v>0.009578</v>
+        <v>0.009774</v>
       </c>
       <c r="C33" t="n">
-        <v>0.918206</v>
+        <v>0.915531</v>
       </c>
     </row>
     <row r="34">
@@ -856,10 +856,10 @@
         </is>
       </c>
       <c r="B34" t="n">
-        <v>0.009774</v>
+        <v>0.009811</v>
       </c>
       <c r="C34" t="n">
-        <v>0.915567</v>
+        <v>0.912807</v>
       </c>
     </row>
     <row r="35">
@@ -869,10 +869,10 @@
         </is>
       </c>
       <c r="B35" t="n">
-        <v>0.009811</v>
+        <v>0.010226</v>
       </c>
       <c r="C35" t="n">
-        <v>0.912929</v>
+        <v>0.9100819999999999</v>
       </c>
     </row>
     <row r="36">
@@ -882,10 +882,10 @@
         </is>
       </c>
       <c r="B36" t="n">
-        <v>0.010226</v>
+        <v>0.010518</v>
       </c>
       <c r="C36" t="n">
-        <v>0.91029</v>
+        <v>0.907357</v>
       </c>
     </row>
     <row r="37">
@@ -895,10 +895,10 @@
         </is>
       </c>
       <c r="B37" t="n">
-        <v>0.010518</v>
+        <v>0.010943</v>
       </c>
       <c r="C37" t="n">
-        <v>0.907652</v>
+        <v>0.904632</v>
       </c>
     </row>
     <row r="38">
@@ -908,10 +908,10 @@
         </is>
       </c>
       <c r="B38" t="n">
-        <v>0.010943</v>
+        <v>0.011156</v>
       </c>
       <c r="C38" t="n">
-        <v>0.905013</v>
+        <v>0.901907</v>
       </c>
     </row>
     <row r="39">
@@ -921,10 +921,10 @@
         </is>
       </c>
       <c r="B39" t="n">
-        <v>0.011156</v>
+        <v>0.011326</v>
       </c>
       <c r="C39" t="n">
-        <v>0.902375</v>
+        <v>0.899183</v>
       </c>
     </row>
     <row r="40">
@@ -934,10 +934,10 @@
         </is>
       </c>
       <c r="B40" t="n">
-        <v>0.011326</v>
+        <v>0.01145</v>
       </c>
       <c r="C40" t="n">
-        <v>0.899736</v>
+        <v>0.896458</v>
       </c>
     </row>
     <row r="41">
@@ -947,10 +947,10 @@
         </is>
       </c>
       <c r="B41" t="n">
-        <v>0.01145</v>
+        <v>0.012002</v>
       </c>
       <c r="C41" t="n">
-        <v>0.897098</v>
+        <v>0.893733</v>
       </c>
     </row>
     <row r="42">
@@ -960,10 +960,10 @@
         </is>
       </c>
       <c r="B42" t="n">
-        <v>0.012002</v>
+        <v>0.012035</v>
       </c>
       <c r="C42" t="n">
-        <v>0.894459</v>
+        <v>0.891008</v>
       </c>
     </row>
     <row r="43">
@@ -973,10 +973,10 @@
         </is>
       </c>
       <c r="B43" t="n">
-        <v>0.012035</v>
+        <v>0.012747</v>
       </c>
       <c r="C43" t="n">
-        <v>0.891821</v>
+        <v>0.888283</v>
       </c>
     </row>
     <row r="44">
@@ -986,10 +986,10 @@
         </is>
       </c>
       <c r="B44" t="n">
-        <v>0.012747</v>
+        <v>0.012918</v>
       </c>
       <c r="C44" t="n">
-        <v>0.889182</v>
+        <v>0.885559</v>
       </c>
     </row>
     <row r="45">
@@ -999,10 +999,10 @@
         </is>
       </c>
       <c r="B45" t="n">
-        <v>0.012918</v>
+        <v>0.013714</v>
       </c>
       <c r="C45" t="n">
-        <v>0.886544</v>
+        <v>0.882834</v>
       </c>
     </row>
     <row r="46">
@@ -1012,10 +1012,10 @@
         </is>
       </c>
       <c r="B46" t="n">
-        <v>0.013714</v>
+        <v>0.01393</v>
       </c>
       <c r="C46" t="n">
-        <v>0.8839050000000001</v>
+        <v>0.880109</v>
       </c>
     </row>
     <row r="47">
@@ -1025,10 +1025,10 @@
         </is>
       </c>
       <c r="B47" t="n">
-        <v>0.01393</v>
+        <v>0.013971</v>
       </c>
       <c r="C47" t="n">
-        <v>0.881266</v>
+        <v>0.8773840000000001</v>
       </c>
     </row>
     <row r="48">
@@ -1038,10 +1038,10 @@
         </is>
       </c>
       <c r="B48" t="n">
-        <v>0.013971</v>
+        <v>0.014018</v>
       </c>
       <c r="C48" t="n">
-        <v>0.878628</v>
+        <v>0.874659</v>
       </c>
     </row>
     <row r="49">
@@ -1051,10 +1051,10 @@
         </is>
       </c>
       <c r="B49" t="n">
-        <v>0.014018</v>
+        <v>0.01417</v>
       </c>
       <c r="C49" t="n">
-        <v>0.875989</v>
+        <v>0.871935</v>
       </c>
     </row>
     <row r="50">
@@ -1064,10 +1064,10 @@
         </is>
       </c>
       <c r="B50" t="n">
-        <v>0.01417</v>
+        <v>0.014481</v>
       </c>
       <c r="C50" t="n">
-        <v>0.873351</v>
+        <v>0.86921</v>
       </c>
     </row>
     <row r="51">
@@ -1077,10 +1077,10 @@
         </is>
       </c>
       <c r="B51" t="n">
-        <v>0.014481</v>
+        <v>0.014731</v>
       </c>
       <c r="C51" t="n">
-        <v>0.870712</v>
+        <v>0.8664849999999999</v>
       </c>
     </row>
     <row r="52">
@@ -1090,10 +1090,10 @@
         </is>
       </c>
       <c r="B52" t="n">
-        <v>0.014731</v>
+        <v>0.014841</v>
       </c>
       <c r="C52" t="n">
-        <v>0.868074</v>
+        <v>0.86376</v>
       </c>
     </row>
     <row r="53">
@@ -1103,10 +1103,10 @@
         </is>
       </c>
       <c r="B53" t="n">
-        <v>0.014841</v>
+        <v>0.01486</v>
       </c>
       <c r="C53" t="n">
-        <v>0.865435</v>
+        <v>0.861035</v>
       </c>
     </row>
     <row r="54">
@@ -1116,10 +1116,10 @@
         </is>
       </c>
       <c r="B54" t="n">
-        <v>0.01486</v>
+        <v>0.015041</v>
       </c>
       <c r="C54" t="n">
-        <v>0.862797</v>
+        <v>0.858311</v>
       </c>
     </row>
     <row r="55">
@@ -1129,10 +1129,10 @@
         </is>
       </c>
       <c r="B55" t="n">
-        <v>0.015041</v>
+        <v>0.015107</v>
       </c>
       <c r="C55" t="n">
-        <v>0.860158</v>
+        <v>0.855586</v>
       </c>
     </row>
     <row r="56">
@@ -1145,7 +1145,7 @@
         <v>0.015107</v>
       </c>
       <c r="C56" t="n">
-        <v>0.8575199999999999</v>
+        <v>0.852861</v>
       </c>
     </row>
     <row r="57">
@@ -1155,10 +1155,10 @@
         </is>
       </c>
       <c r="B57" t="n">
-        <v>0.015107</v>
+        <v>0.015553</v>
       </c>
       <c r="C57" t="n">
-        <v>0.854881</v>
+        <v>0.850136</v>
       </c>
     </row>
     <row r="58">
@@ -1168,10 +1168,10 @@
         </is>
       </c>
       <c r="B58" t="n">
-        <v>0.015553</v>
+        <v>0.016031</v>
       </c>
       <c r="C58" t="n">
-        <v>0.852243</v>
+        <v>0.847411</v>
       </c>
     </row>
     <row r="59">
@@ -1181,10 +1181,10 @@
         </is>
       </c>
       <c r="B59" t="n">
-        <v>0.016031</v>
+        <v>0.016343</v>
       </c>
       <c r="C59" t="n">
-        <v>0.849604</v>
+        <v>0.844687</v>
       </c>
     </row>
     <row r="60">
@@ -1194,10 +1194,10 @@
         </is>
       </c>
       <c r="B60" t="n">
-        <v>0.016343</v>
+        <v>0.016545</v>
       </c>
       <c r="C60" t="n">
-        <v>0.846966</v>
+        <v>0.841962</v>
       </c>
     </row>
     <row r="61">
@@ -1207,10 +1207,10 @@
         </is>
       </c>
       <c r="B61" t="n">
-        <v>0.016545</v>
+        <v>0.017135</v>
       </c>
       <c r="C61" t="n">
-        <v>0.844327</v>
+        <v>0.839237</v>
       </c>
     </row>
     <row r="62">
@@ -1220,10 +1220,10 @@
         </is>
       </c>
       <c r="B62" t="n">
-        <v>0.017135</v>
+        <v>0.017276</v>
       </c>
       <c r="C62" t="n">
-        <v>0.841689</v>
+        <v>0.836512</v>
       </c>
     </row>
     <row r="63">
@@ -1233,10 +1233,10 @@
         </is>
       </c>
       <c r="B63" t="n">
-        <v>0.017276</v>
+        <v>0.017621</v>
       </c>
       <c r="C63" t="n">
-        <v>0.83905</v>
+        <v>0.8337869999999999</v>
       </c>
     </row>
     <row r="64">
@@ -1246,10 +1246,10 @@
         </is>
       </c>
       <c r="B64" t="n">
-        <v>0.017621</v>
+        <v>0.017975</v>
       </c>
       <c r="C64" t="n">
-        <v>0.836412</v>
+        <v>0.831063</v>
       </c>
     </row>
     <row r="65">
@@ -1259,10 +1259,10 @@
         </is>
       </c>
       <c r="B65" t="n">
-        <v>0.017975</v>
+        <v>0.018505</v>
       </c>
       <c r="C65" t="n">
-        <v>0.833773</v>
+        <v>0.828338</v>
       </c>
     </row>
     <row r="66">
@@ -1272,10 +1272,10 @@
         </is>
       </c>
       <c r="B66" t="n">
-        <v>0.018257</v>
+        <v>0.018757</v>
       </c>
       <c r="C66" t="n">
-        <v>0.831135</v>
+        <v>0.825613</v>
       </c>
     </row>
     <row r="67">
@@ -1285,10 +1285,10 @@
         </is>
       </c>
       <c r="B67" t="n">
-        <v>0.018505</v>
+        <v>0.018801</v>
       </c>
       <c r="C67" t="n">
-        <v>0.828496</v>
+        <v>0.822888</v>
       </c>
     </row>
     <row r="68">
@@ -1298,10 +1298,10 @@
         </is>
       </c>
       <c r="B68" t="n">
-        <v>0.018757</v>
+        <v>0.018847</v>
       </c>
       <c r="C68" t="n">
-        <v>0.825858</v>
+        <v>0.820163</v>
       </c>
     </row>
     <row r="69">
@@ -1311,10 +1311,10 @@
         </is>
       </c>
       <c r="B69" t="n">
-        <v>0.018801</v>
+        <v>0.018931</v>
       </c>
       <c r="C69" t="n">
-        <v>0.823219</v>
+        <v>0.817439</v>
       </c>
     </row>
     <row r="70">
@@ -1324,10 +1324,10 @@
         </is>
       </c>
       <c r="B70" t="n">
-        <v>0.018847</v>
+        <v>0.019352</v>
       </c>
       <c r="C70" t="n">
-        <v>0.82058</v>
+        <v>0.814714</v>
       </c>
     </row>
     <row r="71">
@@ -1337,10 +1337,10 @@
         </is>
       </c>
       <c r="B71" t="n">
-        <v>0.018931</v>
+        <v>0.01962</v>
       </c>
       <c r="C71" t="n">
-        <v>0.8179419999999999</v>
+        <v>0.811989</v>
       </c>
     </row>
     <row r="72">
@@ -1350,10 +1350,10 @@
         </is>
       </c>
       <c r="B72" t="n">
-        <v>0.019352</v>
+        <v>0.019953</v>
       </c>
       <c r="C72" t="n">
-        <v>0.815303</v>
+        <v>0.809264</v>
       </c>
     </row>
     <row r="73">
@@ -1363,10 +1363,10 @@
         </is>
       </c>
       <c r="B73" t="n">
-        <v>0.01962</v>
+        <v>0.020186</v>
       </c>
       <c r="C73" t="n">
-        <v>0.812665</v>
+        <v>0.80654</v>
       </c>
     </row>
     <row r="74">
@@ -1376,10 +1376,10 @@
         </is>
       </c>
       <c r="B74" t="n">
-        <v>0.019953</v>
+        <v>0.020393</v>
       </c>
       <c r="C74" t="n">
-        <v>0.810026</v>
+        <v>0.8038149999999999</v>
       </c>
     </row>
     <row r="75">
@@ -1389,10 +1389,10 @@
         </is>
       </c>
       <c r="B75" t="n">
-        <v>0.020186</v>
+        <v>0.02048</v>
       </c>
       <c r="C75" t="n">
-        <v>0.807388</v>
+        <v>0.80109</v>
       </c>
     </row>
     <row r="76">
@@ -1402,10 +1402,10 @@
         </is>
       </c>
       <c r="B76" t="n">
-        <v>0.020393</v>
+        <v>0.021572</v>
       </c>
       <c r="C76" t="n">
-        <v>0.804749</v>
+        <v>0.798365</v>
       </c>
     </row>
     <row r="77">
@@ -1415,10 +1415,10 @@
         </is>
       </c>
       <c r="B77" t="n">
-        <v>0.02048</v>
+        <v>0.021604</v>
       </c>
       <c r="C77" t="n">
-        <v>0.802111</v>
+        <v>0.79564</v>
       </c>
     </row>
     <row r="78">
@@ -1428,10 +1428,10 @@
         </is>
       </c>
       <c r="B78" t="n">
-        <v>0.021572</v>
+        <v>0.021912</v>
       </c>
       <c r="C78" t="n">
-        <v>0.799472</v>
+        <v>0.792916</v>
       </c>
     </row>
     <row r="79">
@@ -1441,10 +1441,10 @@
         </is>
       </c>
       <c r="B79" t="n">
-        <v>0.021604</v>
+        <v>0.021918</v>
       </c>
       <c r="C79" t="n">
-        <v>0.796834</v>
+        <v>0.790191</v>
       </c>
     </row>
     <row r="80">
@@ -1454,10 +1454,10 @@
         </is>
       </c>
       <c r="B80" t="n">
-        <v>0.021912</v>
+        <v>0.021962</v>
       </c>
       <c r="C80" t="n">
-        <v>0.794195</v>
+        <v>0.787466</v>
       </c>
     </row>
     <row r="81">
@@ -1467,10 +1467,10 @@
         </is>
       </c>
       <c r="B81" t="n">
-        <v>0.021918</v>
+        <v>0.022008</v>
       </c>
       <c r="C81" t="n">
-        <v>0.791557</v>
+        <v>0.784741</v>
       </c>
     </row>
     <row r="82">
@@ -1480,10 +1480,10 @@
         </is>
       </c>
       <c r="B82" t="n">
-        <v>0.021962</v>
+        <v>0.022011</v>
       </c>
       <c r="C82" t="n">
-        <v>0.788918</v>
+        <v>0.782016</v>
       </c>
     </row>
     <row r="83">
@@ -1493,10 +1493,10 @@
         </is>
       </c>
       <c r="B83" t="n">
-        <v>0.022008</v>
+        <v>0.022121</v>
       </c>
       <c r="C83" t="n">
-        <v>0.78628</v>
+        <v>0.779292</v>
       </c>
     </row>
     <row r="84">
@@ -1506,10 +1506,10 @@
         </is>
       </c>
       <c r="B84" t="n">
-        <v>0.022011</v>
+        <v>0.022299</v>
       </c>
       <c r="C84" t="n">
-        <v>0.783641</v>
+        <v>0.776567</v>
       </c>
     </row>
     <row r="85">
@@ -1519,10 +1519,10 @@
         </is>
       </c>
       <c r="B85" t="n">
-        <v>0.022121</v>
+        <v>0.022324</v>
       </c>
       <c r="C85" t="n">
-        <v>0.781003</v>
+        <v>0.773842</v>
       </c>
     </row>
     <row r="86">
@@ -1532,10 +1532,10 @@
         </is>
       </c>
       <c r="B86" t="n">
-        <v>0.022299</v>
+        <v>0.022543</v>
       </c>
       <c r="C86" t="n">
-        <v>0.7783639999999999</v>
+        <v>0.7711170000000001</v>
       </c>
     </row>
     <row r="87">
@@ -1545,10 +1545,10 @@
         </is>
       </c>
       <c r="B87" t="n">
-        <v>0.022324</v>
+        <v>0.022891</v>
       </c>
       <c r="C87" t="n">
-        <v>0.775726</v>
+        <v>0.768392</v>
       </c>
     </row>
     <row r="88">
@@ -1558,10 +1558,10 @@
         </is>
       </c>
       <c r="B88" t="n">
-        <v>0.022543</v>
+        <v>0.023483</v>
       </c>
       <c r="C88" t="n">
-        <v>0.773087</v>
+        <v>0.765668</v>
       </c>
     </row>
     <row r="89">
@@ -1571,10 +1571,10 @@
         </is>
       </c>
       <c r="B89" t="n">
-        <v>0.022891</v>
+        <v>0.023843</v>
       </c>
       <c r="C89" t="n">
-        <v>0.7704490000000001</v>
+        <v>0.762943</v>
       </c>
     </row>
     <row r="90">
@@ -1584,10 +1584,10 @@
         </is>
       </c>
       <c r="B90" t="n">
-        <v>0.023483</v>
+        <v>0.023991</v>
       </c>
       <c r="C90" t="n">
-        <v>0.76781</v>
+        <v>0.7602179999999999</v>
       </c>
     </row>
     <row r="91">
@@ -1597,10 +1597,10 @@
         </is>
       </c>
       <c r="B91" t="n">
-        <v>0.023843</v>
+        <v>0.02408</v>
       </c>
       <c r="C91" t="n">
-        <v>0.765172</v>
+        <v>0.757493</v>
       </c>
     </row>
     <row r="92">
@@ -1610,10 +1610,10 @@
         </is>
       </c>
       <c r="B92" t="n">
-        <v>0.023991</v>
+        <v>0.024413</v>
       </c>
       <c r="C92" t="n">
-        <v>0.762533</v>
+        <v>0.754768</v>
       </c>
     </row>
     <row r="93">
@@ -1623,10 +1623,10 @@
         </is>
       </c>
       <c r="B93" t="n">
-        <v>0.02408</v>
+        <v>0.024896</v>
       </c>
       <c r="C93" t="n">
-        <v>0.759894</v>
+        <v>0.752044</v>
       </c>
     </row>
     <row r="94">
@@ -1636,10 +1636,10 @@
         </is>
       </c>
       <c r="B94" t="n">
-        <v>0.024413</v>
+        <v>0.025327</v>
       </c>
       <c r="C94" t="n">
-        <v>0.757256</v>
+        <v>0.749319</v>
       </c>
     </row>
     <row r="95">
@@ -1649,10 +1649,10 @@
         </is>
       </c>
       <c r="B95" t="n">
-        <v>0.024896</v>
+        <v>0.025416</v>
       </c>
       <c r="C95" t="n">
-        <v>0.754617</v>
+        <v>0.746594</v>
       </c>
     </row>
     <row r="96">
@@ -1662,10 +1662,10 @@
         </is>
       </c>
       <c r="B96" t="n">
-        <v>0.025327</v>
+        <v>0.025544</v>
       </c>
       <c r="C96" t="n">
-        <v>0.751979</v>
+        <v>0.743869</v>
       </c>
     </row>
     <row r="97">
@@ -1675,10 +1675,10 @@
         </is>
       </c>
       <c r="B97" t="n">
-        <v>0.025416</v>
+        <v>0.025755</v>
       </c>
       <c r="C97" t="n">
-        <v>0.74934</v>
+        <v>0.741144</v>
       </c>
     </row>
     <row r="98">
@@ -1688,10 +1688,10 @@
         </is>
       </c>
       <c r="B98" t="n">
-        <v>0.025544</v>
+        <v>0.026545</v>
       </c>
       <c r="C98" t="n">
-        <v>0.746702</v>
+        <v>0.73842</v>
       </c>
     </row>
     <row r="99">
@@ -1701,10 +1701,10 @@
         </is>
       </c>
       <c r="B99" t="n">
-        <v>0.025755</v>
+        <v>0.027214</v>
       </c>
       <c r="C99" t="n">
-        <v>0.744063</v>
+        <v>0.735695</v>
       </c>
     </row>
     <row r="100">
@@ -1714,10 +1714,10 @@
         </is>
       </c>
       <c r="B100" t="n">
-        <v>0.026545</v>
+        <v>0.027321</v>
       </c>
       <c r="C100" t="n">
-        <v>0.741425</v>
+        <v>0.73297</v>
       </c>
     </row>
     <row r="101">
@@ -1727,10 +1727,10 @@
         </is>
       </c>
       <c r="B101" t="n">
-        <v>0.027214</v>
+        <v>0.027355</v>
       </c>
       <c r="C101" t="n">
-        <v>0.7387860000000001</v>
+        <v>0.730245</v>
       </c>
     </row>
     <row r="102">
@@ -1740,10 +1740,10 @@
         </is>
       </c>
       <c r="B102" t="n">
-        <v>0.027321</v>
+        <v>0.028098</v>
       </c>
       <c r="C102" t="n">
-        <v>0.736148</v>
+        <v>0.7275199999999999</v>
       </c>
     </row>
     <row r="103">
@@ -1753,10 +1753,10 @@
         </is>
       </c>
       <c r="B103" t="n">
-        <v>0.027355</v>
+        <v>0.028186</v>
       </c>
       <c r="C103" t="n">
-        <v>0.733509</v>
+        <v>0.724796</v>
       </c>
     </row>
     <row r="104">
@@ -1766,10 +1766,10 @@
         </is>
       </c>
       <c r="B104" t="n">
-        <v>0.028098</v>
+        <v>0.028375</v>
       </c>
       <c r="C104" t="n">
-        <v>0.730871</v>
+        <v>0.722071</v>
       </c>
     </row>
     <row r="105">
@@ -1779,10 +1779,10 @@
         </is>
       </c>
       <c r="B105" t="n">
-        <v>0.028186</v>
+        <v>0.029046</v>
       </c>
       <c r="C105" t="n">
-        <v>0.728232</v>
+        <v>0.719346</v>
       </c>
     </row>
     <row r="106">
@@ -1792,10 +1792,10 @@
         </is>
       </c>
       <c r="B106" t="n">
-        <v>0.028375</v>
+        <v>0.029071</v>
       </c>
       <c r="C106" t="n">
-        <v>0.725594</v>
+        <v>0.716621</v>
       </c>
     </row>
     <row r="107">
@@ -1805,10 +1805,10 @@
         </is>
       </c>
       <c r="B107" t="n">
-        <v>0.029046</v>
+        <v>0.029588</v>
       </c>
       <c r="C107" t="n">
-        <v>0.722955</v>
+        <v>0.713896</v>
       </c>
     </row>
     <row r="108">
@@ -1818,10 +1818,10 @@
         </is>
       </c>
       <c r="B108" t="n">
-        <v>0.029071</v>
+        <v>0.029854</v>
       </c>
       <c r="C108" t="n">
-        <v>0.720317</v>
+        <v>0.711172</v>
       </c>
     </row>
     <row r="109">
@@ -1831,10 +1831,10 @@
         </is>
       </c>
       <c r="B109" t="n">
-        <v>0.029588</v>
+        <v>0.030158</v>
       </c>
       <c r="C109" t="n">
-        <v>0.717678</v>
+        <v>0.708447</v>
       </c>
     </row>
     <row r="110">
@@ -1844,10 +1844,10 @@
         </is>
       </c>
       <c r="B110" t="n">
-        <v>0.029854</v>
+        <v>0.030201</v>
       </c>
       <c r="C110" t="n">
-        <v>0.71504</v>
+        <v>0.705722</v>
       </c>
     </row>
     <row r="111">
@@ -1857,10 +1857,10 @@
         </is>
       </c>
       <c r="B111" t="n">
-        <v>0.030158</v>
+        <v>0.03027</v>
       </c>
       <c r="C111" t="n">
-        <v>0.712401</v>
+        <v>0.702997</v>
       </c>
     </row>
     <row r="112">
@@ -1870,10 +1870,10 @@
         </is>
       </c>
       <c r="B112" t="n">
-        <v>0.030201</v>
+        <v>0.030697</v>
       </c>
       <c r="C112" t="n">
-        <v>0.709763</v>
+        <v>0.700272</v>
       </c>
     </row>
     <row r="113">
@@ -1883,10 +1883,10 @@
         </is>
       </c>
       <c r="B113" t="n">
-        <v>0.03027</v>
+        <v>0.030903</v>
       </c>
       <c r="C113" t="n">
-        <v>0.707124</v>
+        <v>0.6975479999999999</v>
       </c>
     </row>
     <row r="114">
@@ -1896,10 +1896,10 @@
         </is>
       </c>
       <c r="B114" t="n">
-        <v>0.030697</v>
+        <v>0.031116</v>
       </c>
       <c r="C114" t="n">
-        <v>0.704485</v>
+        <v>0.694823</v>
       </c>
     </row>
     <row r="115">
@@ -1909,10 +1909,10 @@
         </is>
       </c>
       <c r="B115" t="n">
-        <v>0.030903</v>
+        <v>0.031127</v>
       </c>
       <c r="C115" t="n">
-        <v>0.701847</v>
+        <v>0.692098</v>
       </c>
     </row>
     <row r="116">
@@ -1922,10 +1922,10 @@
         </is>
       </c>
       <c r="B116" t="n">
-        <v>0.031116</v>
+        <v>0.031327</v>
       </c>
       <c r="C116" t="n">
-        <v>0.6992080000000001</v>
+        <v>0.689373</v>
       </c>
     </row>
     <row r="117">
@@ -1935,10 +1935,10 @@
         </is>
       </c>
       <c r="B117" t="n">
-        <v>0.031127</v>
+        <v>0.031556</v>
       </c>
       <c r="C117" t="n">
-        <v>0.69657</v>
+        <v>0.686649</v>
       </c>
     </row>
     <row r="118">
@@ -1948,10 +1948,10 @@
         </is>
       </c>
       <c r="B118" t="n">
-        <v>0.031327</v>
+        <v>0.031969</v>
       </c>
       <c r="C118" t="n">
-        <v>0.693931</v>
+        <v>0.683924</v>
       </c>
     </row>
     <row r="119">
@@ -1961,10 +1961,10 @@
         </is>
       </c>
       <c r="B119" t="n">
-        <v>0.031556</v>
+        <v>0.032545</v>
       </c>
       <c r="C119" t="n">
-        <v>0.691293</v>
+        <v>0.681199</v>
       </c>
     </row>
     <row r="120">
@@ -1974,10 +1974,10 @@
         </is>
       </c>
       <c r="B120" t="n">
-        <v>0.031969</v>
+        <v>0.032827</v>
       </c>
       <c r="C120" t="n">
-        <v>0.688654</v>
+        <v>0.678474</v>
       </c>
     </row>
     <row r="121">
@@ -1987,10 +1987,10 @@
         </is>
       </c>
       <c r="B121" t="n">
-        <v>0.032545</v>
+        <v>0.033481</v>
       </c>
       <c r="C121" t="n">
-        <v>0.686016</v>
+        <v>0.675749</v>
       </c>
     </row>
     <row r="122">
@@ -2000,10 +2000,10 @@
         </is>
       </c>
       <c r="B122" t="n">
-        <v>0.032827</v>
+        <v>0.033774</v>
       </c>
       <c r="C122" t="n">
-        <v>0.683377</v>
+        <v>0.673025</v>
       </c>
     </row>
     <row r="123">
@@ -2013,10 +2013,10 @@
         </is>
       </c>
       <c r="B123" t="n">
-        <v>0.033481</v>
+        <v>0.033884</v>
       </c>
       <c r="C123" t="n">
-        <v>0.680739</v>
+        <v>0.6703</v>
       </c>
     </row>
     <row r="124">
@@ -2026,10 +2026,10 @@
         </is>
       </c>
       <c r="B124" t="n">
-        <v>0.033774</v>
+        <v>0.034047</v>
       </c>
       <c r="C124" t="n">
-        <v>0.6781</v>
+        <v>0.667575</v>
       </c>
     </row>
     <row r="125">
@@ -2039,10 +2039,10 @@
         </is>
       </c>
       <c r="B125" t="n">
-        <v>0.033884</v>
+        <v>0.034274</v>
       </c>
       <c r="C125" t="n">
-        <v>0.675462</v>
+        <v>0.6648500000000001</v>
       </c>
     </row>
     <row r="126">
@@ -2052,10 +2052,10 @@
         </is>
       </c>
       <c r="B126" t="n">
-        <v>0.034047</v>
+        <v>0.034573</v>
       </c>
       <c r="C126" t="n">
-        <v>0.6728229999999999</v>
+        <v>0.662125</v>
       </c>
     </row>
     <row r="127">
@@ -2065,10 +2065,10 @@
         </is>
       </c>
       <c r="B127" t="n">
-        <v>0.034274</v>
+        <v>0.035039</v>
       </c>
       <c r="C127" t="n">
-        <v>0.670185</v>
+        <v>0.659401</v>
       </c>
     </row>
     <row r="128">
@@ -2078,10 +2078,10 @@
         </is>
       </c>
       <c r="B128" t="n">
-        <v>0.034573</v>
+        <v>0.035117</v>
       </c>
       <c r="C128" t="n">
-        <v>0.667546</v>
+        <v>0.656676</v>
       </c>
     </row>
     <row r="129">
@@ -2091,10 +2091,10 @@
         </is>
       </c>
       <c r="B129" t="n">
-        <v>0.035039</v>
+        <v>0.035159</v>
       </c>
       <c r="C129" t="n">
-        <v>0.6649080000000001</v>
+        <v>0.6539509999999999</v>
       </c>
     </row>
     <row r="130">
@@ -2104,10 +2104,10 @@
         </is>
       </c>
       <c r="B130" t="n">
-        <v>0.035117</v>
+        <v>0.035374</v>
       </c>
       <c r="C130" t="n">
-        <v>0.662269</v>
+        <v>0.651226</v>
       </c>
     </row>
     <row r="131">
@@ -2117,10 +2117,10 @@
         </is>
       </c>
       <c r="B131" t="n">
-        <v>0.035159</v>
+        <v>0.035654</v>
       </c>
       <c r="C131" t="n">
-        <v>0.659631</v>
+        <v>0.648501</v>
       </c>
     </row>
     <row r="132">
@@ -2130,10 +2130,10 @@
         </is>
       </c>
       <c r="B132" t="n">
-        <v>0.035374</v>
+        <v>0.036</v>
       </c>
       <c r="C132" t="n">
-        <v>0.656992</v>
+        <v>0.645777</v>
       </c>
     </row>
     <row r="133">
@@ -2143,10 +2143,10 @@
         </is>
       </c>
       <c r="B133" t="n">
-        <v>0.035654</v>
+        <v>0.036242</v>
       </c>
       <c r="C133" t="n">
-        <v>0.654354</v>
+        <v>0.643052</v>
       </c>
     </row>
     <row r="134">
@@ -2156,10 +2156,10 @@
         </is>
       </c>
       <c r="B134" t="n">
-        <v>0.036</v>
+        <v>0.037307</v>
       </c>
       <c r="C134" t="n">
-        <v>0.651715</v>
+        <v>0.640327</v>
       </c>
     </row>
     <row r="135">
@@ -2169,10 +2169,10 @@
         </is>
       </c>
       <c r="B135" t="n">
-        <v>0.036242</v>
+        <v>0.037805</v>
       </c>
       <c r="C135" t="n">
-        <v>0.649077</v>
+        <v>0.637602</v>
       </c>
     </row>
     <row r="136">
@@ -2182,10 +2182,10 @@
         </is>
       </c>
       <c r="B136" t="n">
-        <v>0.037307</v>
+        <v>0.03815</v>
       </c>
       <c r="C136" t="n">
-        <v>0.646438</v>
+        <v>0.634877</v>
       </c>
     </row>
     <row r="137">
@@ -2195,10 +2195,10 @@
         </is>
       </c>
       <c r="B137" t="n">
-        <v>0.037431</v>
+        <v>0.038316</v>
       </c>
       <c r="C137" t="n">
-        <v>0.643799</v>
+        <v>0.632153</v>
       </c>
     </row>
     <row r="138">
@@ -2208,10 +2208,10 @@
         </is>
       </c>
       <c r="B138" t="n">
-        <v>0.037805</v>
+        <v>0.03876</v>
       </c>
       <c r="C138" t="n">
-        <v>0.641161</v>
+        <v>0.629428</v>
       </c>
     </row>
     <row r="139">
@@ -2221,10 +2221,10 @@
         </is>
       </c>
       <c r="B139" t="n">
-        <v>0.03815</v>
+        <v>0.039595</v>
       </c>
       <c r="C139" t="n">
-        <v>0.638522</v>
+        <v>0.626703</v>
       </c>
     </row>
     <row r="140">
@@ -2234,10 +2234,10 @@
         </is>
       </c>
       <c r="B140" t="n">
-        <v>0.038316</v>
+        <v>0.03982</v>
       </c>
       <c r="C140" t="n">
-        <v>0.635884</v>
+        <v>0.623978</v>
       </c>
     </row>
     <row r="141">
@@ -2247,10 +2247,10 @@
         </is>
       </c>
       <c r="B141" t="n">
-        <v>0.03876</v>
+        <v>0.040867</v>
       </c>
       <c r="C141" t="n">
-        <v>0.6332449999999999</v>
+        <v>0.6212530000000001</v>
       </c>
     </row>
     <row r="142">
@@ -2260,10 +2260,10 @@
         </is>
       </c>
       <c r="B142" t="n">
-        <v>0.039595</v>
+        <v>0.040915</v>
       </c>
       <c r="C142" t="n">
-        <v>0.630607</v>
+        <v>0.618529</v>
       </c>
     </row>
     <row r="143">
@@ -2273,10 +2273,10 @@
         </is>
       </c>
       <c r="B143" t="n">
-        <v>0.03982</v>
+        <v>0.040931</v>
       </c>
       <c r="C143" t="n">
-        <v>0.627968</v>
+        <v>0.615804</v>
       </c>
     </row>
     <row r="144">
@@ -2286,10 +2286,10 @@
         </is>
       </c>
       <c r="B144" t="n">
-        <v>0.040867</v>
+        <v>0.040948</v>
       </c>
       <c r="C144" t="n">
-        <v>0.6253300000000001</v>
+        <v>0.613079</v>
       </c>
     </row>
     <row r="145">
@@ -2299,10 +2299,10 @@
         </is>
       </c>
       <c r="B145" t="n">
-        <v>0.040915</v>
+        <v>0.041019</v>
       </c>
       <c r="C145" t="n">
-        <v>0.622691</v>
+        <v>0.610354</v>
       </c>
     </row>
     <row r="146">
@@ -2312,10 +2312,10 @@
         </is>
       </c>
       <c r="B146" t="n">
-        <v>0.040931</v>
+        <v>0.041132</v>
       </c>
       <c r="C146" t="n">
-        <v>0.620053</v>
+        <v>0.607629</v>
       </c>
     </row>
     <row r="147">
@@ -2325,10 +2325,10 @@
         </is>
       </c>
       <c r="B147" t="n">
-        <v>0.040948</v>
+        <v>0.041331</v>
       </c>
       <c r="C147" t="n">
-        <v>0.617414</v>
+        <v>0.604905</v>
       </c>
     </row>
     <row r="148">
@@ -2338,10 +2338,10 @@
         </is>
       </c>
       <c r="B148" t="n">
-        <v>0.041019</v>
+        <v>0.041359</v>
       </c>
       <c r="C148" t="n">
-        <v>0.614776</v>
+        <v>0.60218</v>
       </c>
     </row>
     <row r="149">
@@ -2351,10 +2351,10 @@
         </is>
       </c>
       <c r="B149" t="n">
-        <v>0.041132</v>
+        <v>0.04197</v>
       </c>
       <c r="C149" t="n">
-        <v>0.612137</v>
+        <v>0.599455</v>
       </c>
     </row>
     <row r="150">
@@ -2364,10 +2364,10 @@
         </is>
       </c>
       <c r="B150" t="n">
-        <v>0.041331</v>
+        <v>0.042735</v>
       </c>
       <c r="C150" t="n">
-        <v>0.609499</v>
+        <v>0.59673</v>
       </c>
     </row>
     <row r="151">
@@ -2377,10 +2377,10 @@
         </is>
       </c>
       <c r="B151" t="n">
-        <v>0.041359</v>
+        <v>0.043468</v>
       </c>
       <c r="C151" t="n">
-        <v>0.60686</v>
+        <v>0.594005</v>
       </c>
     </row>
     <row r="152">
@@ -2390,10 +2390,10 @@
         </is>
       </c>
       <c r="B152" t="n">
-        <v>0.04197</v>
+        <v>0.044385</v>
       </c>
       <c r="C152" t="n">
-        <v>0.604222</v>
+        <v>0.5912809999999999</v>
       </c>
     </row>
     <row r="153">
@@ -2403,10 +2403,10 @@
         </is>
       </c>
       <c r="B153" t="n">
-        <v>0.042735</v>
+        <v>0.044556</v>
       </c>
       <c r="C153" t="n">
-        <v>0.601583</v>
+        <v>0.588556</v>
       </c>
     </row>
     <row r="154">
@@ -2416,10 +2416,10 @@
         </is>
       </c>
       <c r="B154" t="n">
-        <v>0.043468</v>
+        <v>0.044571</v>
       </c>
       <c r="C154" t="n">
-        <v>0.5989449999999999</v>
+        <v>0.585831</v>
       </c>
     </row>
     <row r="155">
@@ -2429,10 +2429,10 @@
         </is>
       </c>
       <c r="B155" t="n">
-        <v>0.044385</v>
+        <v>0.045962</v>
       </c>
       <c r="C155" t="n">
-        <v>0.596306</v>
+        <v>0.583106</v>
       </c>
     </row>
     <row r="156">
@@ -2442,10 +2442,10 @@
         </is>
       </c>
       <c r="B156" t="n">
-        <v>0.044556</v>
+        <v>0.046486</v>
       </c>
       <c r="C156" t="n">
-        <v>0.593668</v>
+        <v>0.580381</v>
       </c>
     </row>
     <row r="157">
@@ -2455,10 +2455,10 @@
         </is>
       </c>
       <c r="B157" t="n">
-        <v>0.044571</v>
+        <v>0.046763</v>
       </c>
       <c r="C157" t="n">
-        <v>0.591029</v>
+        <v>0.577657</v>
       </c>
     </row>
     <row r="158">
@@ -2468,10 +2468,10 @@
         </is>
       </c>
       <c r="B158" t="n">
-        <v>0.044773</v>
+        <v>0.046785</v>
       </c>
       <c r="C158" t="n">
-        <v>0.588391</v>
+        <v>0.574932</v>
       </c>
     </row>
     <row r="159">
@@ -2481,10 +2481,10 @@
         </is>
       </c>
       <c r="B159" t="n">
-        <v>0.045962</v>
+        <v>0.046943</v>
       </c>
       <c r="C159" t="n">
-        <v>0.5857520000000001</v>
+        <v>0.572207</v>
       </c>
     </row>
     <row r="160">
@@ -2494,10 +2494,10 @@
         </is>
       </c>
       <c r="B160" t="n">
-        <v>0.046486</v>
+        <v>0.047141</v>
       </c>
       <c r="C160" t="n">
-        <v>0.583113</v>
+        <v>0.569482</v>
       </c>
     </row>
     <row r="161">
@@ -2507,10 +2507,10 @@
         </is>
       </c>
       <c r="B161" t="n">
-        <v>0.046763</v>
+        <v>0.047421</v>
       </c>
       <c r="C161" t="n">
-        <v>0.580475</v>
+        <v>0.566757</v>
       </c>
     </row>
     <row r="162">
@@ -2520,10 +2520,10 @@
         </is>
       </c>
       <c r="B162" t="n">
-        <v>0.046785</v>
+        <v>0.048551</v>
       </c>
       <c r="C162" t="n">
-        <v>0.577836</v>
+        <v>0.564033</v>
       </c>
     </row>
     <row r="163">
@@ -2533,10 +2533,10 @@
         </is>
       </c>
       <c r="B163" t="n">
-        <v>0.046943</v>
+        <v>0.04906</v>
       </c>
       <c r="C163" t="n">
-        <v>0.575198</v>
+        <v>0.561308</v>
       </c>
     </row>
     <row r="164">
@@ -2546,10 +2546,10 @@
         </is>
       </c>
       <c r="B164" t="n">
-        <v>0.047141</v>
+        <v>0.049358</v>
       </c>
       <c r="C164" t="n">
-        <v>0.572559</v>
+        <v>0.5585830000000001</v>
       </c>
     </row>
     <row r="165">
@@ -2559,10 +2559,10 @@
         </is>
       </c>
       <c r="B165" t="n">
-        <v>0.047421</v>
+        <v>0.049478</v>
       </c>
       <c r="C165" t="n">
-        <v>0.569921</v>
+        <v>0.555858</v>
       </c>
     </row>
     <row r="166">
@@ -2572,10 +2572,10 @@
         </is>
       </c>
       <c r="B166" t="n">
-        <v>0.048551</v>
+        <v>0.049516</v>
       </c>
       <c r="C166" t="n">
-        <v>0.567282</v>
+        <v>0.553134</v>
       </c>
     </row>
     <row r="167">
@@ -2585,10 +2585,10 @@
         </is>
       </c>
       <c r="B167" t="n">
-        <v>0.04906</v>
+        <v>0.049728</v>
       </c>
       <c r="C167" t="n">
-        <v>0.564644</v>
+        <v>0.550409</v>
       </c>
     </row>
     <row r="168">
@@ -2598,10 +2598,10 @@
         </is>
       </c>
       <c r="B168" t="n">
-        <v>0.049358</v>
+        <v>0.049754</v>
       </c>
       <c r="C168" t="n">
-        <v>0.562005</v>
+        <v>0.5476839999999999</v>
       </c>
     </row>
     <row r="169">
@@ -2611,10 +2611,10 @@
         </is>
       </c>
       <c r="B169" t="n">
-        <v>0.049478</v>
+        <v>0.051151</v>
       </c>
       <c r="C169" t="n">
-        <v>0.5593669999999999</v>
+        <v>0.544959</v>
       </c>
     </row>
     <row r="170">
@@ -2624,10 +2624,10 @@
         </is>
       </c>
       <c r="B170" t="n">
-        <v>0.049516</v>
+        <v>0.051264</v>
       </c>
       <c r="C170" t="n">
-        <v>0.556728</v>
+        <v>0.542234</v>
       </c>
     </row>
     <row r="171">
@@ -2637,10 +2637,10 @@
         </is>
       </c>
       <c r="B171" t="n">
-        <v>0.049728</v>
+        <v>0.051423</v>
       </c>
       <c r="C171" t="n">
-        <v>0.55409</v>
+        <v>0.53951</v>
       </c>
     </row>
     <row r="172">
@@ -2650,10 +2650,10 @@
         </is>
       </c>
       <c r="B172" t="n">
-        <v>0.049754</v>
+        <v>0.051449</v>
       </c>
       <c r="C172" t="n">
-        <v>0.551451</v>
+        <v>0.536785</v>
       </c>
     </row>
     <row r="173">
@@ -2663,10 +2663,10 @@
         </is>
       </c>
       <c r="B173" t="n">
-        <v>0.051151</v>
+        <v>0.052376</v>
       </c>
       <c r="C173" t="n">
-        <v>0.548813</v>
+        <v>0.53406</v>
       </c>
     </row>
     <row r="174">
@@ -2676,10 +2676,10 @@
         </is>
       </c>
       <c r="B174" t="n">
-        <v>0.051264</v>
+        <v>0.052398</v>
       </c>
       <c r="C174" t="n">
-        <v>0.546174</v>
+        <v>0.531335</v>
       </c>
     </row>
     <row r="175">
@@ -2689,10 +2689,10 @@
         </is>
       </c>
       <c r="B175" t="n">
-        <v>0.051423</v>
+        <v>0.052682</v>
       </c>
       <c r="C175" t="n">
-        <v>0.543536</v>
+        <v>0.52861</v>
       </c>
     </row>
     <row r="176">
@@ -2702,10 +2702,10 @@
         </is>
       </c>
       <c r="B176" t="n">
-        <v>0.051449</v>
+        <v>0.052941</v>
       </c>
       <c r="C176" t="n">
-        <v>0.540897</v>
+        <v>0.525886</v>
       </c>
     </row>
     <row r="177">
@@ -2715,10 +2715,10 @@
         </is>
       </c>
       <c r="B177" t="n">
-        <v>0.051978</v>
+        <v>0.053227</v>
       </c>
       <c r="C177" t="n">
-        <v>0.538259</v>
+        <v>0.523161</v>
       </c>
     </row>
     <row r="178">
@@ -2728,10 +2728,10 @@
         </is>
       </c>
       <c r="B178" t="n">
-        <v>0.052376</v>
+        <v>0.053316</v>
       </c>
       <c r="C178" t="n">
-        <v>0.53562</v>
+        <v>0.520436</v>
       </c>
     </row>
     <row r="179">
@@ -2741,10 +2741,10 @@
         </is>
       </c>
       <c r="B179" t="n">
-        <v>0.052398</v>
+        <v>0.053555</v>
       </c>
       <c r="C179" t="n">
-        <v>0.532982</v>
+        <v>0.517711</v>
       </c>
     </row>
     <row r="180">
@@ -2754,10 +2754,10 @@
         </is>
       </c>
       <c r="B180" t="n">
-        <v>0.052682</v>
+        <v>0.05382</v>
       </c>
       <c r="C180" t="n">
-        <v>0.530343</v>
+        <v>0.5149860000000001</v>
       </c>
     </row>
     <row r="181">
@@ -2767,10 +2767,10 @@
         </is>
       </c>
       <c r="B181" t="n">
-        <v>0.052941</v>
+        <v>0.05439</v>
       </c>
       <c r="C181" t="n">
-        <v>0.527704</v>
+        <v>0.512262</v>
       </c>
     </row>
     <row r="182">
@@ -2780,10 +2780,10 @@
         </is>
       </c>
       <c r="B182" t="n">
-        <v>0.053227</v>
+        <v>0.054595</v>
       </c>
       <c r="C182" t="n">
-        <v>0.525066</v>
+        <v>0.509537</v>
       </c>
     </row>
     <row r="183">
@@ -2793,10 +2793,10 @@
         </is>
       </c>
       <c r="B183" t="n">
-        <v>0.053316</v>
+        <v>0.05496</v>
       </c>
       <c r="C183" t="n">
-        <v>0.522427</v>
+        <v>0.506812</v>
       </c>
     </row>
     <row r="184">
@@ -2806,10 +2806,10 @@
         </is>
       </c>
       <c r="B184" t="n">
-        <v>0.053555</v>
+        <v>0.0555</v>
       </c>
       <c r="C184" t="n">
-        <v>0.5197889999999999</v>
+        <v>0.504087</v>
       </c>
     </row>
     <row r="185">
@@ -2819,10 +2819,10 @@
         </is>
       </c>
       <c r="B185" t="n">
-        <v>0.05382</v>
+        <v>0.055621</v>
       </c>
       <c r="C185" t="n">
-        <v>0.51715</v>
+        <v>0.501362</v>
       </c>
     </row>
     <row r="186">
@@ -2832,10 +2832,10 @@
         </is>
       </c>
       <c r="B186" t="n">
-        <v>0.05439</v>
+        <v>0.055736</v>
       </c>
       <c r="C186" t="n">
-        <v>0.514512</v>
+        <v>0.498638</v>
       </c>
     </row>
     <row r="187">
@@ -2845,10 +2845,10 @@
         </is>
       </c>
       <c r="B187" t="n">
-        <v>0.054595</v>
+        <v>0.056242</v>
       </c>
       <c r="C187" t="n">
-        <v>0.511873</v>
+        <v>0.495913</v>
       </c>
     </row>
     <row r="188">
@@ -2858,10 +2858,10 @@
         </is>
       </c>
       <c r="B188" t="n">
-        <v>0.05496</v>
+        <v>0.056433</v>
       </c>
       <c r="C188" t="n">
-        <v>0.509235</v>
+        <v>0.493188</v>
       </c>
     </row>
     <row r="189">
@@ -2871,10 +2871,10 @@
         </is>
       </c>
       <c r="B189" t="n">
-        <v>0.0555</v>
+        <v>0.056487</v>
       </c>
       <c r="C189" t="n">
-        <v>0.506596</v>
+        <v>0.490463</v>
       </c>
     </row>
     <row r="190">
@@ -2884,10 +2884,10 @@
         </is>
       </c>
       <c r="B190" t="n">
-        <v>0.055621</v>
+        <v>0.056702</v>
       </c>
       <c r="C190" t="n">
-        <v>0.503958</v>
+        <v>0.487738</v>
       </c>
     </row>
     <row r="191">
@@ -2897,10 +2897,10 @@
         </is>
       </c>
       <c r="B191" t="n">
-        <v>0.055736</v>
+        <v>0.056785</v>
       </c>
       <c r="C191" t="n">
-        <v>0.501319</v>
+        <v>0.485014</v>
       </c>
     </row>
     <row r="192">
@@ -2910,10 +2910,10 @@
         </is>
       </c>
       <c r="B192" t="n">
-        <v>0.056242</v>
+        <v>0.05854</v>
       </c>
       <c r="C192" t="n">
-        <v>0.498681</v>
+        <v>0.482289</v>
       </c>
     </row>
     <row r="193">
@@ -2923,10 +2923,10 @@
         </is>
       </c>
       <c r="B193" t="n">
-        <v>0.056433</v>
+        <v>0.058745</v>
       </c>
       <c r="C193" t="n">
-        <v>0.496042</v>
+        <v>0.479564</v>
       </c>
     </row>
     <row r="194">
@@ -2936,10 +2936,10 @@
         </is>
       </c>
       <c r="B194" t="n">
-        <v>0.056487</v>
+        <v>0.058836</v>
       </c>
       <c r="C194" t="n">
-        <v>0.493404</v>
+        <v>0.476839</v>
       </c>
     </row>
     <row r="195">
@@ -2949,10 +2949,10 @@
         </is>
       </c>
       <c r="B195" t="n">
-        <v>0.056702</v>
+        <v>0.059279</v>
       </c>
       <c r="C195" t="n">
-        <v>0.490765</v>
+        <v>0.474114</v>
       </c>
     </row>
     <row r="196">
@@ -2962,10 +2962,10 @@
         </is>
       </c>
       <c r="B196" t="n">
-        <v>0.056785</v>
+        <v>0.059367</v>
       </c>
       <c r="C196" t="n">
-        <v>0.488127</v>
+        <v>0.47139</v>
       </c>
     </row>
     <row r="197">
@@ -2975,10 +2975,10 @@
         </is>
       </c>
       <c r="B197" t="n">
-        <v>0.05854</v>
+        <v>0.059553</v>
       </c>
       <c r="C197" t="n">
-        <v>0.485488</v>
+        <v>0.468665</v>
       </c>
     </row>
     <row r="198">
@@ -2988,10 +2988,10 @@
         </is>
       </c>
       <c r="B198" t="n">
-        <v>0.058745</v>
+        <v>0.059579</v>
       </c>
       <c r="C198" t="n">
-        <v>0.48285</v>
+        <v>0.46594</v>
       </c>
     </row>
     <row r="199">
@@ -3001,10 +3001,10 @@
         </is>
       </c>
       <c r="B199" t="n">
-        <v>0.058836</v>
+        <v>0.060111</v>
       </c>
       <c r="C199" t="n">
-        <v>0.480211</v>
+        <v>0.463215</v>
       </c>
     </row>
     <row r="200">
@@ -3014,10 +3014,10 @@
         </is>
       </c>
       <c r="B200" t="n">
-        <v>0.059279</v>
+        <v>0.060827</v>
       </c>
       <c r="C200" t="n">
-        <v>0.477573</v>
+        <v>0.46049</v>
       </c>
     </row>
     <row r="201">
@@ -3027,10 +3027,10 @@
         </is>
       </c>
       <c r="B201" t="n">
-        <v>0.059367</v>
+        <v>0.060882</v>
       </c>
       <c r="C201" t="n">
-        <v>0.474934</v>
+        <v>0.457766</v>
       </c>
     </row>
     <row r="202">
@@ -3040,10 +3040,10 @@
         </is>
       </c>
       <c r="B202" t="n">
-        <v>0.059553</v>
+        <v>0.061712</v>
       </c>
       <c r="C202" t="n">
-        <v>0.472296</v>
+        <v>0.455041</v>
       </c>
     </row>
     <row r="203">
@@ -3053,10 +3053,10 @@
         </is>
       </c>
       <c r="B203" t="n">
-        <v>0.059579</v>
+        <v>0.061784</v>
       </c>
       <c r="C203" t="n">
-        <v>0.469657</v>
+        <v>0.452316</v>
       </c>
     </row>
     <row r="204">
@@ -3066,10 +3066,10 @@
         </is>
       </c>
       <c r="B204" t="n">
-        <v>0.060111</v>
+        <v>0.06179</v>
       </c>
       <c r="C204" t="n">
-        <v>0.467018</v>
+        <v>0.449591</v>
       </c>
     </row>
     <row r="205">
@@ -3079,10 +3079,10 @@
         </is>
       </c>
       <c r="B205" t="n">
-        <v>0.060827</v>
+        <v>0.061969</v>
       </c>
       <c r="C205" t="n">
-        <v>0.46438</v>
+        <v>0.446866</v>
       </c>
     </row>
     <row r="206">
@@ -3092,10 +3092,10 @@
         </is>
       </c>
       <c r="B206" t="n">
-        <v>0.060882</v>
+        <v>0.062129</v>
       </c>
       <c r="C206" t="n">
-        <v>0.461741</v>
+        <v>0.444142</v>
       </c>
     </row>
     <row r="207">
@@ -3105,10 +3105,10 @@
         </is>
       </c>
       <c r="B207" t="n">
-        <v>0.061712</v>
+        <v>0.062168</v>
       </c>
       <c r="C207" t="n">
-        <v>0.459103</v>
+        <v>0.441417</v>
       </c>
     </row>
     <row r="208">
@@ -3118,10 +3118,10 @@
         </is>
       </c>
       <c r="B208" t="n">
-        <v>0.061784</v>
+        <v>0.062246</v>
       </c>
       <c r="C208" t="n">
-        <v>0.456464</v>
+        <v>0.438692</v>
       </c>
     </row>
     <row r="209">
@@ -3131,10 +3131,10 @@
         </is>
       </c>
       <c r="B209" t="n">
-        <v>0.06179</v>
+        <v>0.06263299999999999</v>
       </c>
       <c r="C209" t="n">
-        <v>0.453826</v>
+        <v>0.435967</v>
       </c>
     </row>
     <row r="210">
@@ -3144,10 +3144,10 @@
         </is>
       </c>
       <c r="B210" t="n">
-        <v>0.061969</v>
+        <v>0.062844</v>
       </c>
       <c r="C210" t="n">
-        <v>0.451187</v>
+        <v>0.433243</v>
       </c>
     </row>
     <row r="211">
@@ -3157,10 +3157,10 @@
         </is>
       </c>
       <c r="B211" t="n">
-        <v>0.062129</v>
+        <v>0.063808</v>
       </c>
       <c r="C211" t="n">
-        <v>0.448549</v>
+        <v>0.430518</v>
       </c>
     </row>
     <row r="212">
@@ -3170,10 +3170,10 @@
         </is>
       </c>
       <c r="B212" t="n">
-        <v>0.062168</v>
+        <v>0.06464300000000001</v>
       </c>
       <c r="C212" t="n">
-        <v>0.44591</v>
+        <v>0.427793</v>
       </c>
     </row>
     <row r="213">
@@ -3183,10 +3183,10 @@
         </is>
       </c>
       <c r="B213" t="n">
-        <v>0.062246</v>
+        <v>0.064842</v>
       </c>
       <c r="C213" t="n">
-        <v>0.443272</v>
+        <v>0.425068</v>
       </c>
     </row>
     <row r="214">
@@ -3196,10 +3196,10 @@
         </is>
       </c>
       <c r="B214" t="n">
-        <v>0.06263299999999999</v>
+        <v>0.06555900000000001</v>
       </c>
       <c r="C214" t="n">
-        <v>0.440633</v>
+        <v>0.422343</v>
       </c>
     </row>
     <row r="215">
@@ -3209,10 +3209,10 @@
         </is>
       </c>
       <c r="B215" t="n">
-        <v>0.062844</v>
+        <v>0.067176</v>
       </c>
       <c r="C215" t="n">
-        <v>0.437995</v>
+        <v>0.419619</v>
       </c>
     </row>
     <row r="216">
@@ -3222,10 +3222,10 @@
         </is>
       </c>
       <c r="B216" t="n">
-        <v>0.063808</v>
+        <v>0.06736399999999999</v>
       </c>
       <c r="C216" t="n">
-        <v>0.435356</v>
+        <v>0.416894</v>
       </c>
     </row>
     <row r="217">
@@ -3235,10 +3235,10 @@
         </is>
       </c>
       <c r="B217" t="n">
-        <v>0.06464300000000001</v>
+        <v>0.067375</v>
       </c>
       <c r="C217" t="n">
-        <v>0.432718</v>
+        <v>0.414169</v>
       </c>
     </row>
     <row r="218">
@@ -3248,10 +3248,10 @@
         </is>
       </c>
       <c r="B218" t="n">
-        <v>0.064842</v>
+        <v>0.067555</v>
       </c>
       <c r="C218" t="n">
-        <v>0.430079</v>
+        <v>0.411444</v>
       </c>
     </row>
     <row r="219">
@@ -3261,10 +3261,10 @@
         </is>
       </c>
       <c r="B219" t="n">
-        <v>0.06555900000000001</v>
+        <v>0.067604</v>
       </c>
       <c r="C219" t="n">
-        <v>0.427441</v>
+        <v>0.408719</v>
       </c>
     </row>
     <row r="220">
@@ -3274,10 +3274,10 @@
         </is>
       </c>
       <c r="B220" t="n">
-        <v>0.067176</v>
+        <v>0.067644</v>
       </c>
       <c r="C220" t="n">
-        <v>0.424802</v>
+        <v>0.405995</v>
       </c>
     </row>
     <row r="221">
@@ -3287,10 +3287,10 @@
         </is>
       </c>
       <c r="B221" t="n">
-        <v>0.06736399999999999</v>
+        <v>0.068111</v>
       </c>
       <c r="C221" t="n">
-        <v>0.422164</v>
+        <v>0.40327</v>
       </c>
     </row>
     <row r="222">
@@ -3300,10 +3300,10 @@
         </is>
       </c>
       <c r="B222" t="n">
-        <v>0.067375</v>
+        <v>0.068601</v>
       </c>
       <c r="C222" t="n">
-        <v>0.419525</v>
+        <v>0.400545</v>
       </c>
     </row>
     <row r="223">
@@ -3313,10 +3313,10 @@
         </is>
       </c>
       <c r="B223" t="n">
-        <v>0.067555</v>
+        <v>0.068939</v>
       </c>
       <c r="C223" t="n">
-        <v>0.416887</v>
+        <v>0.39782</v>
       </c>
     </row>
     <row r="224">
@@ -3326,10 +3326,10 @@
         </is>
       </c>
       <c r="B224" t="n">
-        <v>0.067604</v>
+        <v>0.06909</v>
       </c>
       <c r="C224" t="n">
-        <v>0.414248</v>
+        <v>0.395095</v>
       </c>
     </row>
     <row r="225">
@@ -3339,10 +3339,10 @@
         </is>
       </c>
       <c r="B225" t="n">
-        <v>0.067644</v>
+        <v>0.069253</v>
       </c>
       <c r="C225" t="n">
-        <v>0.411609</v>
+        <v>0.392371</v>
       </c>
     </row>
     <row r="226">
@@ -3352,10 +3352,10 @@
         </is>
       </c>
       <c r="B226" t="n">
-        <v>0.068111</v>
+        <v>0.070214</v>
       </c>
       <c r="C226" t="n">
-        <v>0.408971</v>
+        <v>0.389646</v>
       </c>
     </row>
     <row r="227">
@@ -3365,10 +3365,10 @@
         </is>
       </c>
       <c r="B227" t="n">
-        <v>0.068601</v>
+        <v>0.070659</v>
       </c>
       <c r="C227" t="n">
-        <v>0.406332</v>
+        <v>0.386921</v>
       </c>
     </row>
     <row r="228">
@@ -3378,10 +3378,10 @@
         </is>
       </c>
       <c r="B228" t="n">
-        <v>0.068939</v>
+        <v>0.071394</v>
       </c>
       <c r="C228" t="n">
-        <v>0.403694</v>
+        <v>0.384196</v>
       </c>
     </row>
     <row r="229">
@@ -3391,10 +3391,10 @@
         </is>
       </c>
       <c r="B229" t="n">
-        <v>0.06909</v>
+        <v>0.072684</v>
       </c>
       <c r="C229" t="n">
-        <v>0.401055</v>
+        <v>0.381471</v>
       </c>
     </row>
     <row r="230">
@@ -3404,10 +3404,10 @@
         </is>
       </c>
       <c r="B230" t="n">
-        <v>0.069253</v>
+        <v>0.072744</v>
       </c>
       <c r="C230" t="n">
-        <v>0.398417</v>
+        <v>0.378747</v>
       </c>
     </row>
     <row r="231">
@@ -3417,10 +3417,10 @@
         </is>
       </c>
       <c r="B231" t="n">
-        <v>0.070214</v>
+        <v>0.07295599999999999</v>
       </c>
       <c r="C231" t="n">
-        <v>0.395778</v>
+        <v>0.376022</v>
       </c>
     </row>
     <row r="232">
@@ -3430,10 +3430,10 @@
         </is>
       </c>
       <c r="B232" t="n">
-        <v>0.070659</v>
+        <v>0.07331</v>
       </c>
       <c r="C232" t="n">
-        <v>0.39314</v>
+        <v>0.373297</v>
       </c>
     </row>
     <row r="233">
@@ -3443,10 +3443,10 @@
         </is>
       </c>
       <c r="B233" t="n">
-        <v>0.071394</v>
+        <v>0.07380299999999999</v>
       </c>
       <c r="C233" t="n">
-        <v>0.390501</v>
+        <v>0.370572</v>
       </c>
     </row>
     <row r="234">
@@ -3456,10 +3456,10 @@
         </is>
       </c>
       <c r="B234" t="n">
-        <v>0.072684</v>
+        <v>0.07424799999999999</v>
       </c>
       <c r="C234" t="n">
-        <v>0.387863</v>
+        <v>0.367847</v>
       </c>
     </row>
     <row r="235">
@@ -3469,10 +3469,10 @@
         </is>
       </c>
       <c r="B235" t="n">
-        <v>0.072744</v>
+        <v>0.07437100000000001</v>
       </c>
       <c r="C235" t="n">
-        <v>0.385224</v>
+        <v>0.365123</v>
       </c>
     </row>
     <row r="236">
@@ -3482,10 +3482,10 @@
         </is>
       </c>
       <c r="B236" t="n">
-        <v>0.07295599999999999</v>
+        <v>0.075854</v>
       </c>
       <c r="C236" t="n">
-        <v>0.382586</v>
+        <v>0.362398</v>
       </c>
     </row>
     <row r="237">
@@ -3495,10 +3495,10 @@
         </is>
       </c>
       <c r="B237" t="n">
-        <v>0.07331</v>
+        <v>0.075876</v>
       </c>
       <c r="C237" t="n">
-        <v>0.379947</v>
+        <v>0.359673</v>
       </c>
     </row>
     <row r="238">
@@ -3508,10 +3508,10 @@
         </is>
       </c>
       <c r="B238" t="n">
-        <v>0.07380299999999999</v>
+        <v>0.076543</v>
       </c>
       <c r="C238" t="n">
-        <v>0.377309</v>
+        <v>0.356948</v>
       </c>
     </row>
     <row r="239">
@@ -3521,10 +3521,10 @@
         </is>
       </c>
       <c r="B239" t="n">
-        <v>0.07424799999999999</v>
+        <v>0.07708</v>
       </c>
       <c r="C239" t="n">
-        <v>0.37467</v>
+        <v>0.354223</v>
       </c>
     </row>
     <row r="240">
@@ -3534,10 +3534,10 @@
         </is>
       </c>
       <c r="B240" t="n">
-        <v>0.07437100000000001</v>
+        <v>0.077863</v>
       </c>
       <c r="C240" t="n">
-        <v>0.372032</v>
+        <v>0.351499</v>
       </c>
     </row>
     <row r="241">
@@ -3547,10 +3547,10 @@
         </is>
       </c>
       <c r="B241" t="n">
-        <v>0.075854</v>
+        <v>0.077912</v>
       </c>
       <c r="C241" t="n">
-        <v>0.369393</v>
+        <v>0.348774</v>
       </c>
     </row>
     <row r="242">
@@ -3560,10 +3560,10 @@
         </is>
       </c>
       <c r="B242" t="n">
-        <v>0.075876</v>
+        <v>0.078084</v>
       </c>
       <c r="C242" t="n">
-        <v>0.366755</v>
+        <v>0.346049</v>
       </c>
     </row>
     <row r="243">
@@ -3573,10 +3573,10 @@
         </is>
       </c>
       <c r="B243" t="n">
-        <v>0.076543</v>
+        <v>0.07921499999999999</v>
       </c>
       <c r="C243" t="n">
-        <v>0.364116</v>
+        <v>0.343324</v>
       </c>
     </row>
     <row r="244">
@@ -3586,10 +3586,10 @@
         </is>
       </c>
       <c r="B244" t="n">
-        <v>0.07708</v>
+        <v>0.08092199999999999</v>
       </c>
       <c r="C244" t="n">
-        <v>0.361478</v>
+        <v>0.340599</v>
       </c>
     </row>
     <row r="245">
@@ -3599,10 +3599,10 @@
         </is>
       </c>
       <c r="B245" t="n">
-        <v>0.07757799999999999</v>
+        <v>0.081607</v>
       </c>
       <c r="C245" t="n">
-        <v>0.358839</v>
+        <v>0.337875</v>
       </c>
     </row>
     <row r="246">
@@ -3612,10 +3612,10 @@
         </is>
       </c>
       <c r="B246" t="n">
-        <v>0.077863</v>
+        <v>0.081758</v>
       </c>
       <c r="C246" t="n">
-        <v>0.356201</v>
+        <v>0.33515</v>
       </c>
     </row>
     <row r="247">
@@ -3625,10 +3625,10 @@
         </is>
       </c>
       <c r="B247" t="n">
-        <v>0.077912</v>
+        <v>0.08192000000000001</v>
       </c>
       <c r="C247" t="n">
-        <v>0.353562</v>
+        <v>0.332425</v>
       </c>
     </row>
     <row r="248">
@@ -3638,10 +3638,10 @@
         </is>
       </c>
       <c r="B248" t="n">
-        <v>0.078084</v>
+        <v>0.082479</v>
       </c>
       <c r="C248" t="n">
-        <v>0.350923</v>
+        <v>0.3297</v>
       </c>
     </row>
     <row r="249">
@@ -3651,10 +3651,10 @@
         </is>
       </c>
       <c r="B249" t="n">
-        <v>0.07921499999999999</v>
+        <v>0.08254300000000001</v>
       </c>
       <c r="C249" t="n">
-        <v>0.348285</v>
+        <v>0.326975</v>
       </c>
     </row>
     <row r="250">
@@ -3664,10 +3664,10 @@
         </is>
       </c>
       <c r="B250" t="n">
-        <v>0.08092199999999999</v>
+        <v>0.082594</v>
       </c>
       <c r="C250" t="n">
-        <v>0.345646</v>
+        <v>0.324251</v>
       </c>
     </row>
     <row r="251">
@@ -3677,10 +3677,10 @@
         </is>
       </c>
       <c r="B251" t="n">
-        <v>0.081607</v>
+        <v>0.083297</v>
       </c>
       <c r="C251" t="n">
-        <v>0.343008</v>
+        <v>0.321526</v>
       </c>
     </row>
     <row r="252">
@@ -3690,10 +3690,10 @@
         </is>
       </c>
       <c r="B252" t="n">
-        <v>0.081758</v>
+        <v>0.083664</v>
       </c>
       <c r="C252" t="n">
-        <v>0.340369</v>
+        <v>0.318801</v>
       </c>
     </row>
     <row r="253">
@@ -3703,10 +3703,10 @@
         </is>
       </c>
       <c r="B253" t="n">
-        <v>0.08192000000000001</v>
+        <v>0.08384800000000001</v>
       </c>
       <c r="C253" t="n">
-        <v>0.337731</v>
+        <v>0.316076</v>
       </c>
     </row>
     <row r="254">
@@ -3716,10 +3716,10 @@
         </is>
       </c>
       <c r="B254" t="n">
-        <v>0.082479</v>
+        <v>0.084221</v>
       </c>
       <c r="C254" t="n">
-        <v>0.335092</v>
+        <v>0.313351</v>
       </c>
     </row>
     <row r="255">
@@ -3729,10 +3729,10 @@
         </is>
       </c>
       <c r="B255" t="n">
-        <v>0.08254300000000001</v>
+        <v>0.08483599999999999</v>
       </c>
       <c r="C255" t="n">
-        <v>0.332454</v>
+        <v>0.310627</v>
       </c>
     </row>
     <row r="256">
@@ -3742,10 +3742,10 @@
         </is>
       </c>
       <c r="B256" t="n">
-        <v>0.082594</v>
+        <v>0.08586199999999999</v>
       </c>
       <c r="C256" t="n">
-        <v>0.329815</v>
+        <v>0.307902</v>
       </c>
     </row>
     <row r="257">
@@ -3755,10 +3755,10 @@
         </is>
       </c>
       <c r="B257" t="n">
-        <v>0.083297</v>
+        <v>0.087156</v>
       </c>
       <c r="C257" t="n">
-        <v>0.327177</v>
+        <v>0.305177</v>
       </c>
     </row>
     <row r="258">
@@ -3768,10 +3768,10 @@
         </is>
       </c>
       <c r="B258" t="n">
-        <v>0.083664</v>
+        <v>0.08717999999999999</v>
       </c>
       <c r="C258" t="n">
-        <v>0.324538</v>
+        <v>0.302452</v>
       </c>
     </row>
     <row r="259">
@@ -3781,10 +3781,10 @@
         </is>
       </c>
       <c r="B259" t="n">
-        <v>0.08384800000000001</v>
+        <v>0.08820799999999999</v>
       </c>
       <c r="C259" t="n">
-        <v>0.3219</v>
+        <v>0.299728</v>
       </c>
     </row>
     <row r="260">
@@ -3794,10 +3794,10 @@
         </is>
       </c>
       <c r="B260" t="n">
-        <v>0.084221</v>
+        <v>0.088889</v>
       </c>
       <c r="C260" t="n">
-        <v>0.319261</v>
+        <v>0.297003</v>
       </c>
     </row>
     <row r="261">
@@ -3807,10 +3807,10 @@
         </is>
       </c>
       <c r="B261" t="n">
-        <v>0.08483599999999999</v>
+        <v>0.08917700000000001</v>
       </c>
       <c r="C261" t="n">
-        <v>0.316623</v>
+        <v>0.294278</v>
       </c>
     </row>
     <row r="262">
@@ -3820,10 +3820,10 @@
         </is>
       </c>
       <c r="B262" t="n">
-        <v>0.08586199999999999</v>
+        <v>0.089823</v>
       </c>
       <c r="C262" t="n">
-        <v>0.313984</v>
+        <v>0.291553</v>
       </c>
     </row>
     <row r="263">
@@ -3833,10 +3833,10 @@
         </is>
       </c>
       <c r="B263" t="n">
-        <v>0.087156</v>
+        <v>0.090265</v>
       </c>
       <c r="C263" t="n">
-        <v>0.311346</v>
+        <v>0.288828</v>
       </c>
     </row>
     <row r="264">
@@ -3846,10 +3846,10 @@
         </is>
       </c>
       <c r="B264" t="n">
-        <v>0.08717999999999999</v>
+        <v>0.090348</v>
       </c>
       <c r="C264" t="n">
-        <v>0.308707</v>
+        <v>0.286104</v>
       </c>
     </row>
     <row r="265">
@@ -3859,10 +3859,10 @@
         </is>
       </c>
       <c r="B265" t="n">
-        <v>0.08820799999999999</v>
+        <v>0.090809</v>
       </c>
       <c r="C265" t="n">
-        <v>0.306069</v>
+        <v>0.283379</v>
       </c>
     </row>
     <row r="266">
@@ -3872,10 +3872,10 @@
         </is>
       </c>
       <c r="B266" t="n">
-        <v>0.088889</v>
+        <v>0.091434</v>
       </c>
       <c r="C266" t="n">
-        <v>0.30343</v>
+        <v>0.280654</v>
       </c>
     </row>
     <row r="267">
@@ -3885,10 +3885,10 @@
         </is>
       </c>
       <c r="B267" t="n">
-        <v>0.08917700000000001</v>
+        <v>0.0929</v>
       </c>
       <c r="C267" t="n">
-        <v>0.300792</v>
+        <v>0.277929</v>
       </c>
     </row>
     <row r="268">
@@ -3898,10 +3898,10 @@
         </is>
       </c>
       <c r="B268" t="n">
-        <v>0.089823</v>
+        <v>0.097923</v>
       </c>
       <c r="C268" t="n">
-        <v>0.298153</v>
+        <v>0.275204</v>
       </c>
     </row>
     <row r="269">
@@ -3911,10 +3911,10 @@
         </is>
       </c>
       <c r="B269" t="n">
-        <v>0.090265</v>
+        <v>0.098237</v>
       </c>
       <c r="C269" t="n">
-        <v>0.295515</v>
+        <v>0.27248</v>
       </c>
     </row>
     <row r="270">
@@ -3924,10 +3924,10 @@
         </is>
       </c>
       <c r="B270" t="n">
-        <v>0.090348</v>
+        <v>0.09847400000000001</v>
       </c>
       <c r="C270" t="n">
-        <v>0.292876</v>
+        <v>0.269755</v>
       </c>
     </row>
     <row r="271">
@@ -3937,10 +3937,10 @@
         </is>
       </c>
       <c r="B271" t="n">
-        <v>0.090809</v>
+        <v>0.09907299999999999</v>
       </c>
       <c r="C271" t="n">
-        <v>0.290237</v>
+        <v>0.26703</v>
       </c>
     </row>
     <row r="272">
@@ -3950,10 +3950,10 @@
         </is>
       </c>
       <c r="B272" t="n">
-        <v>0.090958</v>
+        <v>0.09943399999999999</v>
       </c>
       <c r="C272" t="n">
-        <v>0.287599</v>
+        <v>0.264305</v>
       </c>
     </row>
     <row r="273">
@@ -3963,10 +3963,10 @@
         </is>
       </c>
       <c r="B273" t="n">
-        <v>0.091434</v>
+        <v>0.100571</v>
       </c>
       <c r="C273" t="n">
-        <v>0.28496</v>
+        <v>0.26158</v>
       </c>
     </row>
     <row r="274">
@@ -3976,10 +3976,10 @@
         </is>
       </c>
       <c r="B274" t="n">
-        <v>0.0929</v>
+        <v>0.101335</v>
       </c>
       <c r="C274" t="n">
-        <v>0.282322</v>
+        <v>0.258856</v>
       </c>
     </row>
     <row r="275">
@@ -3989,10 +3989,10 @@
         </is>
       </c>
       <c r="B275" t="n">
-        <v>0.093237</v>
+        <v>0.103451</v>
       </c>
       <c r="C275" t="n">
-        <v>0.279683</v>
+        <v>0.256131</v>
       </c>
     </row>
     <row r="276">
@@ -4002,10 +4002,10 @@
         </is>
       </c>
       <c r="B276" t="n">
-        <v>0.097923</v>
+        <v>0.103942</v>
       </c>
       <c r="C276" t="n">
-        <v>0.277045</v>
+        <v>0.253406</v>
       </c>
     </row>
     <row r="277">
@@ -4015,10 +4015,10 @@
         </is>
       </c>
       <c r="B277" t="n">
-        <v>0.098237</v>
+        <v>0.10427</v>
       </c>
       <c r="C277" t="n">
-        <v>0.274406</v>
+        <v>0.250681</v>
       </c>
     </row>
     <row r="278">
@@ -4028,10 +4028,10 @@
         </is>
       </c>
       <c r="B278" t="n">
-        <v>0.09847400000000001</v>
+        <v>0.105774</v>
       </c>
       <c r="C278" t="n">
-        <v>0.271768</v>
+        <v>0.247956</v>
       </c>
     </row>
     <row r="279">
@@ -4041,10 +4041,10 @@
         </is>
       </c>
       <c r="B279" t="n">
-        <v>0.09907299999999999</v>
+        <v>0.106391</v>
       </c>
       <c r="C279" t="n">
-        <v>0.269129</v>
+        <v>0.245232</v>
       </c>
     </row>
     <row r="280">
@@ -4054,10 +4054,10 @@
         </is>
       </c>
       <c r="B280" t="n">
-        <v>0.09943399999999999</v>
+        <v>0.106564</v>
       </c>
       <c r="C280" t="n">
-        <v>0.266491</v>
+        <v>0.242507</v>
       </c>
     </row>
     <row r="281">
@@ -4067,10 +4067,10 @@
         </is>
       </c>
       <c r="B281" t="n">
-        <v>0.100571</v>
+        <v>0.106852</v>
       </c>
       <c r="C281" t="n">
-        <v>0.263852</v>
+        <v>0.239782</v>
       </c>
     </row>
     <row r="282">
@@ -4080,10 +4080,10 @@
         </is>
       </c>
       <c r="B282" t="n">
-        <v>0.101335</v>
+        <v>0.107359</v>
       </c>
       <c r="C282" t="n">
-        <v>0.261214</v>
+        <v>0.237057</v>
       </c>
     </row>
     <row r="283">
@@ -4093,10 +4093,10 @@
         </is>
       </c>
       <c r="B283" t="n">
-        <v>0.103451</v>
+        <v>0.110708</v>
       </c>
       <c r="C283" t="n">
-        <v>0.258575</v>
+        <v>0.234332</v>
       </c>
     </row>
     <row r="284">
@@ -4106,10 +4106,10 @@
         </is>
       </c>
       <c r="B284" t="n">
-        <v>0.103942</v>
+        <v>0.111683</v>
       </c>
       <c r="C284" t="n">
-        <v>0.255937</v>
+        <v>0.231608</v>
       </c>
     </row>
     <row r="285">
@@ -4119,10 +4119,10 @@
         </is>
       </c>
       <c r="B285" t="n">
-        <v>0.10427</v>
+        <v>0.112861</v>
       </c>
       <c r="C285" t="n">
-        <v>0.253298</v>
+        <v>0.228883</v>
       </c>
     </row>
     <row r="286">
@@ -4132,10 +4132,10 @@
         </is>
       </c>
       <c r="B286" t="n">
-        <v>0.105774</v>
+        <v>0.11394</v>
       </c>
       <c r="C286" t="n">
-        <v>0.25066</v>
+        <v>0.226158</v>
       </c>
     </row>
     <row r="287">
@@ -4145,10 +4145,10 @@
         </is>
       </c>
       <c r="B287" t="n">
-        <v>0.106391</v>
+        <v>0.114179</v>
       </c>
       <c r="C287" t="n">
-        <v>0.248021</v>
+        <v>0.223433</v>
       </c>
     </row>
     <row r="288">
@@ -4158,10 +4158,10 @@
         </is>
       </c>
       <c r="B288" t="n">
-        <v>0.106564</v>
+        <v>0.11468</v>
       </c>
       <c r="C288" t="n">
-        <v>0.245383</v>
+        <v>0.220708</v>
       </c>
     </row>
     <row r="289">
@@ -4171,10 +4171,10 @@
         </is>
       </c>
       <c r="B289" t="n">
-        <v>0.106852</v>
+        <v>0.115972</v>
       </c>
       <c r="C289" t="n">
-        <v>0.242744</v>
+        <v>0.217984</v>
       </c>
     </row>
     <row r="290">
@@ -4184,10 +4184,10 @@
         </is>
       </c>
       <c r="B290" t="n">
-        <v>0.107359</v>
+        <v>0.117496</v>
       </c>
       <c r="C290" t="n">
-        <v>0.240106</v>
+        <v>0.215259</v>
       </c>
     </row>
     <row r="291">
@@ -4197,10 +4197,10 @@
         </is>
       </c>
       <c r="B291" t="n">
-        <v>0.110708</v>
+        <v>0.117846</v>
       </c>
       <c r="C291" t="n">
-        <v>0.237467</v>
+        <v>0.212534</v>
       </c>
     </row>
     <row r="292">
@@ -4210,10 +4210,10 @@
         </is>
       </c>
       <c r="B292" t="n">
-        <v>0.111683</v>
+        <v>0.119464</v>
       </c>
       <c r="C292" t="n">
-        <v>0.234828</v>
+        <v>0.209809</v>
       </c>
     </row>
     <row r="293">
@@ -4223,10 +4223,10 @@
         </is>
       </c>
       <c r="B293" t="n">
-        <v>0.112861</v>
+        <v>0.120351</v>
       </c>
       <c r="C293" t="n">
-        <v>0.23219</v>
+        <v>0.207084</v>
       </c>
     </row>
     <row r="294">
@@ -4236,10 +4236,10 @@
         </is>
       </c>
       <c r="B294" t="n">
-        <v>0.11394</v>
+        <v>0.120448</v>
       </c>
       <c r="C294" t="n">
-        <v>0.229551</v>
+        <v>0.20436</v>
       </c>
     </row>
     <row r="295">
@@ -4249,10 +4249,10 @@
         </is>
       </c>
       <c r="B295" t="n">
-        <v>0.114179</v>
+        <v>0.121637</v>
       </c>
       <c r="C295" t="n">
-        <v>0.226913</v>
+        <v>0.201635</v>
       </c>
     </row>
     <row r="296">
@@ -4262,10 +4262,10 @@
         </is>
       </c>
       <c r="B296" t="n">
-        <v>0.11468</v>
+        <v>0.12397</v>
       </c>
       <c r="C296" t="n">
-        <v>0.224274</v>
+        <v>0.19891</v>
       </c>
     </row>
     <row r="297">
@@ -4275,10 +4275,10 @@
         </is>
       </c>
       <c r="B297" t="n">
-        <v>0.115972</v>
+        <v>0.124167</v>
       </c>
       <c r="C297" t="n">
-        <v>0.221636</v>
+        <v>0.196185</v>
       </c>
     </row>
     <row r="298">
@@ -4288,10 +4288,10 @@
         </is>
       </c>
       <c r="B298" t="n">
-        <v>0.117496</v>
+        <v>0.126891</v>
       </c>
       <c r="C298" t="n">
-        <v>0.218997</v>
+        <v>0.19346</v>
       </c>
     </row>
     <row r="299">
@@ -4301,10 +4301,10 @@
         </is>
       </c>
       <c r="B299" t="n">
-        <v>0.117846</v>
+        <v>0.128021</v>
       </c>
       <c r="C299" t="n">
-        <v>0.216359</v>
+        <v>0.190736</v>
       </c>
     </row>
     <row r="300">
@@ -4314,10 +4314,10 @@
         </is>
       </c>
       <c r="B300" t="n">
-        <v>0.119464</v>
+        <v>0.128976</v>
       </c>
       <c r="C300" t="n">
-        <v>0.21372</v>
+        <v>0.188011</v>
       </c>
     </row>
     <row r="301">
@@ -4327,10 +4327,10 @@
         </is>
       </c>
       <c r="B301" t="n">
-        <v>0.120351</v>
+        <v>0.130439</v>
       </c>
       <c r="C301" t="n">
-        <v>0.211082</v>
+        <v>0.185286</v>
       </c>
     </row>
     <row r="302">
@@ -4340,10 +4340,10 @@
         </is>
       </c>
       <c r="B302" t="n">
-        <v>0.120448</v>
+        <v>0.130821</v>
       </c>
       <c r="C302" t="n">
-        <v>0.208443</v>
+        <v>0.182561</v>
       </c>
     </row>
     <row r="303">
@@ -4353,10 +4353,10 @@
         </is>
       </c>
       <c r="B303" t="n">
-        <v>0.121637</v>
+        <v>0.130916</v>
       </c>
       <c r="C303" t="n">
-        <v>0.205805</v>
+        <v>0.179837</v>
       </c>
     </row>
     <row r="304">
@@ -4366,10 +4366,10 @@
         </is>
       </c>
       <c r="B304" t="n">
-        <v>0.12397</v>
+        <v>0.135669</v>
       </c>
       <c r="C304" t="n">
-        <v>0.203166</v>
+        <v>0.177112</v>
       </c>
     </row>
     <row r="305">
@@ -4379,10 +4379,10 @@
         </is>
       </c>
       <c r="B305" t="n">
-        <v>0.124167</v>
+        <v>0.135827</v>
       </c>
       <c r="C305" t="n">
-        <v>0.200528</v>
+        <v>0.174387</v>
       </c>
     </row>
     <row r="306">
@@ -4392,10 +4392,10 @@
         </is>
       </c>
       <c r="B306" t="n">
-        <v>0.126891</v>
+        <v>0.137023</v>
       </c>
       <c r="C306" t="n">
-        <v>0.197889</v>
+        <v>0.171662</v>
       </c>
     </row>
     <row r="307">
@@ -4405,10 +4405,10 @@
         </is>
       </c>
       <c r="B307" t="n">
-        <v>0.128021</v>
+        <v>0.13733</v>
       </c>
       <c r="C307" t="n">
-        <v>0.195251</v>
+        <v>0.168937</v>
       </c>
     </row>
     <row r="308">
@@ -4418,10 +4418,10 @@
         </is>
       </c>
       <c r="B308" t="n">
-        <v>0.128976</v>
+        <v>0.138762</v>
       </c>
       <c r="C308" t="n">
-        <v>0.192612</v>
+        <v>0.166213</v>
       </c>
     </row>
     <row r="309">
@@ -4431,10 +4431,10 @@
         </is>
       </c>
       <c r="B309" t="n">
-        <v>0.130439</v>
+        <v>0.139275</v>
       </c>
       <c r="C309" t="n">
-        <v>0.189974</v>
+        <v>0.163488</v>
       </c>
     </row>
     <row r="310">
@@ -4444,10 +4444,10 @@
         </is>
       </c>
       <c r="B310" t="n">
-        <v>0.130821</v>
+        <v>0.140029</v>
       </c>
       <c r="C310" t="n">
-        <v>0.187335</v>
+        <v>0.160763</v>
       </c>
     </row>
     <row r="311">
@@ -4457,10 +4457,10 @@
         </is>
       </c>
       <c r="B311" t="n">
-        <v>0.130916</v>
+        <v>0.140099</v>
       </c>
       <c r="C311" t="n">
-        <v>0.184697</v>
+        <v>0.158038</v>
       </c>
     </row>
     <row r="312">
@@ -4470,10 +4470,10 @@
         </is>
       </c>
       <c r="B312" t="n">
-        <v>0.135669</v>
+        <v>0.140214</v>
       </c>
       <c r="C312" t="n">
-        <v>0.182058</v>
+        <v>0.155313</v>
       </c>
     </row>
     <row r="313">
@@ -4483,10 +4483,10 @@
         </is>
       </c>
       <c r="B313" t="n">
-        <v>0.135827</v>
+        <v>0.144579</v>
       </c>
       <c r="C313" t="n">
-        <v>0.17942</v>
+        <v>0.152589</v>
       </c>
     </row>
     <row r="314">
@@ -4496,10 +4496,10 @@
         </is>
       </c>
       <c r="B314" t="n">
-        <v>0.137023</v>
+        <v>0.145008</v>
       </c>
       <c r="C314" t="n">
-        <v>0.176781</v>
+        <v>0.149864</v>
       </c>
     </row>
     <row r="315">
@@ -4509,10 +4509,10 @@
         </is>
       </c>
       <c r="B315" t="n">
-        <v>0.13733</v>
+        <v>0.145291</v>
       </c>
       <c r="C315" t="n">
-        <v>0.174142</v>
+        <v>0.147139</v>
       </c>
     </row>
     <row r="316">
@@ -4522,10 +4522,10 @@
         </is>
       </c>
       <c r="B316" t="n">
-        <v>0.138762</v>
+        <v>0.145554</v>
       </c>
       <c r="C316" t="n">
-        <v>0.171504</v>
+        <v>0.144414</v>
       </c>
     </row>
     <row r="317">
@@ -4535,10 +4535,10 @@
         </is>
       </c>
       <c r="B317" t="n">
-        <v>0.139275</v>
+        <v>0.151419</v>
       </c>
       <c r="C317" t="n">
-        <v>0.168865</v>
+        <v>0.141689</v>
       </c>
     </row>
     <row r="318">
@@ -4548,10 +4548,10 @@
         </is>
       </c>
       <c r="B318" t="n">
-        <v>0.140029</v>
+        <v>0.151465</v>
       </c>
       <c r="C318" t="n">
-        <v>0.166227</v>
+        <v>0.138965</v>
       </c>
     </row>
     <row r="319">
@@ -4561,10 +4561,10 @@
         </is>
       </c>
       <c r="B319" t="n">
-        <v>0.140099</v>
+        <v>0.151822</v>
       </c>
       <c r="C319" t="n">
-        <v>0.163588</v>
+        <v>0.13624</v>
       </c>
     </row>
     <row r="320">
@@ -4574,10 +4574,10 @@
         </is>
       </c>
       <c r="B320" t="n">
-        <v>0.140214</v>
+        <v>0.15511</v>
       </c>
       <c r="C320" t="n">
-        <v>0.16095</v>
+        <v>0.133515</v>
       </c>
     </row>
     <row r="321">
@@ -4587,10 +4587,10 @@
         </is>
       </c>
       <c r="B321" t="n">
-        <v>0.141914</v>
+        <v>0.15559</v>
       </c>
       <c r="C321" t="n">
-        <v>0.158311</v>
+        <v>0.13079</v>
       </c>
     </row>
     <row r="322">
@@ -4600,10 +4600,10 @@
         </is>
       </c>
       <c r="B322" t="n">
-        <v>0.144579</v>
+        <v>0.155726</v>
       </c>
       <c r="C322" t="n">
-        <v>0.155673</v>
+        <v>0.128065</v>
       </c>
     </row>
     <row r="323">
@@ -4613,10 +4613,10 @@
         </is>
       </c>
       <c r="B323" t="n">
-        <v>0.145008</v>
+        <v>0.156434</v>
       </c>
       <c r="C323" t="n">
-        <v>0.153034</v>
+        <v>0.125341</v>
       </c>
     </row>
     <row r="324">
@@ -4626,10 +4626,10 @@
         </is>
       </c>
       <c r="B324" t="n">
-        <v>0.145291</v>
+        <v>0.158503</v>
       </c>
       <c r="C324" t="n">
-        <v>0.150396</v>
+        <v>0.122616</v>
       </c>
     </row>
     <row r="325">
@@ -4639,10 +4639,10 @@
         </is>
       </c>
       <c r="B325" t="n">
-        <v>0.145554</v>
+        <v>0.16241</v>
       </c>
       <c r="C325" t="n">
-        <v>0.147757</v>
+        <v>0.119891</v>
       </c>
     </row>
     <row r="326">
@@ -4652,10 +4652,10 @@
         </is>
       </c>
       <c r="B326" t="n">
-        <v>0.151419</v>
+        <v>0.167126</v>
       </c>
       <c r="C326" t="n">
-        <v>0.145119</v>
+        <v>0.117166</v>
       </c>
     </row>
     <row r="327">
@@ -4665,10 +4665,10 @@
         </is>
       </c>
       <c r="B327" t="n">
-        <v>0.151465</v>
+        <v>0.172262</v>
       </c>
       <c r="C327" t="n">
-        <v>0.14248</v>
+        <v>0.114441</v>
       </c>
     </row>
     <row r="328">
@@ -4678,10 +4678,10 @@
         </is>
       </c>
       <c r="B328" t="n">
-        <v>0.151822</v>
+        <v>0.179571</v>
       </c>
       <c r="C328" t="n">
-        <v>0.139842</v>
+        <v>0.111717</v>
       </c>
     </row>
     <row r="329">
@@ -4691,10 +4691,10 @@
         </is>
       </c>
       <c r="B329" t="n">
-        <v>0.15511</v>
+        <v>0.183042</v>
       </c>
       <c r="C329" t="n">
-        <v>0.137203</v>
+        <v>0.108992</v>
       </c>
     </row>
     <row r="330">
@@ -4704,10 +4704,10 @@
         </is>
       </c>
       <c r="B330" t="n">
-        <v>0.15559</v>
+        <v>0.187612</v>
       </c>
       <c r="C330" t="n">
-        <v>0.134565</v>
+        <v>0.106267</v>
       </c>
     </row>
     <row r="331">
@@ -4717,10 +4717,10 @@
         </is>
       </c>
       <c r="B331" t="n">
-        <v>0.155726</v>
+        <v>0.189387</v>
       </c>
       <c r="C331" t="n">
-        <v>0.131926</v>
+        <v>0.103542</v>
       </c>
     </row>
     <row r="332">
@@ -4730,10 +4730,10 @@
         </is>
       </c>
       <c r="B332" t="n">
-        <v>0.156434</v>
+        <v>0.193249</v>
       </c>
       <c r="C332" t="n">
-        <v>0.129288</v>
+        <v>0.100817</v>
       </c>
     </row>
     <row r="333">
@@ -4743,10 +4743,10 @@
         </is>
       </c>
       <c r="B333" t="n">
-        <v>0.158503</v>
+        <v>0.195388</v>
       </c>
       <c r="C333" t="n">
-        <v>0.126649</v>
+        <v>0.098093</v>
       </c>
     </row>
     <row r="334">
@@ -4756,10 +4756,10 @@
         </is>
       </c>
       <c r="B334" t="n">
-        <v>0.16241</v>
+        <v>0.200683</v>
       </c>
       <c r="C334" t="n">
-        <v>0.124011</v>
+        <v>0.09536799999999999</v>
       </c>
     </row>
     <row r="335">
@@ -4769,10 +4769,10 @@
         </is>
       </c>
       <c r="B335" t="n">
-        <v>0.167126</v>
+        <v>0.202141</v>
       </c>
       <c r="C335" t="n">
-        <v>0.121372</v>
+        <v>0.092643</v>
       </c>
     </row>
     <row r="336">
@@ -4782,10 +4782,10 @@
         </is>
       </c>
       <c r="B336" t="n">
-        <v>0.172262</v>
+        <v>0.206803</v>
       </c>
       <c r="C336" t="n">
-        <v>0.118734</v>
+        <v>0.089918</v>
       </c>
     </row>
     <row r="337">
@@ -4795,10 +4795,10 @@
         </is>
       </c>
       <c r="B337" t="n">
-        <v>0.179571</v>
+        <v>0.21126</v>
       </c>
       <c r="C337" t="n">
-        <v>0.116095</v>
+        <v>0.08719300000000001</v>
       </c>
     </row>
     <row r="338">
@@ -4808,10 +4808,10 @@
         </is>
       </c>
       <c r="B338" t="n">
-        <v>0.183042</v>
+        <v>0.212282</v>
       </c>
       <c r="C338" t="n">
-        <v>0.113456</v>
+        <v>0.084469</v>
       </c>
     </row>
     <row r="339">
@@ -4821,10 +4821,10 @@
         </is>
       </c>
       <c r="B339" t="n">
-        <v>0.187612</v>
+        <v>0.213977</v>
       </c>
       <c r="C339" t="n">
-        <v>0.110818</v>
+        <v>0.081744</v>
       </c>
     </row>
     <row r="340">
@@ -4834,10 +4834,10 @@
         </is>
       </c>
       <c r="B340" t="n">
-        <v>0.189387</v>
+        <v>0.224095</v>
       </c>
       <c r="C340" t="n">
-        <v>0.108179</v>
+        <v>0.07901900000000001</v>
       </c>
     </row>
     <row r="341">
@@ -4847,10 +4847,10 @@
         </is>
       </c>
       <c r="B341" t="n">
-        <v>0.193249</v>
+        <v>0.229443</v>
       </c>
       <c r="C341" t="n">
-        <v>0.105541</v>
+        <v>0.076294</v>
       </c>
     </row>
     <row r="342">
@@ -4860,10 +4860,10 @@
         </is>
       </c>
       <c r="B342" t="n">
-        <v>0.195388</v>
+        <v>0.235662</v>
       </c>
       <c r="C342" t="n">
-        <v>0.102902</v>
+        <v>0.073569</v>
       </c>
     </row>
     <row r="343">
@@ -4873,10 +4873,10 @@
         </is>
       </c>
       <c r="B343" t="n">
-        <v>0.200683</v>
+        <v>0.257813</v>
       </c>
       <c r="C343" t="n">
-        <v>0.100264</v>
+        <v>0.07084500000000001</v>
       </c>
     </row>
     <row r="344">
@@ -4886,10 +4886,10 @@
         </is>
       </c>
       <c r="B344" t="n">
-        <v>0.202141</v>
+        <v>0.279391</v>
       </c>
       <c r="C344" t="n">
-        <v>0.097625</v>
+        <v>0.06812</v>
       </c>
     </row>
     <row r="345">
@@ -4899,10 +4899,10 @@
         </is>
       </c>
       <c r="B345" t="n">
-        <v>0.206803</v>
+        <v>0.286735</v>
       </c>
       <c r="C345" t="n">
-        <v>0.094987</v>
+        <v>0.06539499999999999</v>
       </c>
     </row>
     <row r="346">
@@ -4912,10 +4912,10 @@
         </is>
       </c>
       <c r="B346" t="n">
-        <v>0.21126</v>
+        <v>0.28675</v>
       </c>
       <c r="C346" t="n">
-        <v>0.092348</v>
+        <v>0.06267</v>
       </c>
     </row>
     <row r="347">
@@ -4925,10 +4925,10 @@
         </is>
       </c>
       <c r="B347" t="n">
-        <v>0.212282</v>
+        <v>0.292707</v>
       </c>
       <c r="C347" t="n">
-        <v>0.08971</v>
+        <v>0.059946</v>
       </c>
     </row>
     <row r="348">
@@ -4938,10 +4938,10 @@
         </is>
       </c>
       <c r="B348" t="n">
-        <v>0.213977</v>
+        <v>0.303016</v>
       </c>
       <c r="C348" t="n">
-        <v>0.087071</v>
+        <v>0.057221</v>
       </c>
     </row>
     <row r="349">
@@ -4951,10 +4951,10 @@
         </is>
       </c>
       <c r="B349" t="n">
-        <v>0.224095</v>
+        <v>0.35577</v>
       </c>
       <c r="C349" t="n">
-        <v>0.08443299999999999</v>
+        <v>0.054496</v>
       </c>
     </row>
     <row r="350">
@@ -4964,10 +4964,10 @@
         </is>
       </c>
       <c r="B350" t="n">
-        <v>0.229443</v>
+        <v>0.359445</v>
       </c>
       <c r="C350" t="n">
-        <v>0.08179400000000001</v>
+        <v>0.051771</v>
       </c>
     </row>
     <row r="351">
@@ -4977,10 +4977,10 @@
         </is>
       </c>
       <c r="B351" t="n">
-        <v>0.235662</v>
+        <v>0.363732</v>
       </c>
       <c r="C351" t="n">
-        <v>0.079156</v>
+        <v>0.049046</v>
       </c>
     </row>
     <row r="352">
@@ -4990,10 +4990,10 @@
         </is>
       </c>
       <c r="B352" t="n">
-        <v>0.245733</v>
+        <v>0.36468</v>
       </c>
       <c r="C352" t="n">
-        <v>0.076517</v>
+        <v>0.046322</v>
       </c>
     </row>
     <row r="353">
@@ -5003,10 +5003,10 @@
         </is>
       </c>
       <c r="B353" t="n">
-        <v>0.257813</v>
+        <v>0.373827</v>
       </c>
       <c r="C353" t="n">
-        <v>0.073879</v>
+        <v>0.043597</v>
       </c>
     </row>
     <row r="354">
@@ -5016,10 +5016,10 @@
         </is>
       </c>
       <c r="B354" t="n">
-        <v>0.279391</v>
+        <v>0.389014</v>
       </c>
       <c r="C354" t="n">
-        <v>0.07124</v>
+        <v>0.040872</v>
       </c>
     </row>
     <row r="355">
@@ -5029,10 +5029,10 @@
         </is>
       </c>
       <c r="B355" t="n">
-        <v>0.286735</v>
+        <v>0.400164</v>
       </c>
       <c r="C355" t="n">
-        <v>0.068602</v>
+        <v>0.038147</v>
       </c>
     </row>
     <row r="356">
@@ -5042,10 +5042,10 @@
         </is>
       </c>
       <c r="B356" t="n">
-        <v>0.28675</v>
+        <v>0.40983</v>
       </c>
       <c r="C356" t="n">
-        <v>0.06596299999999999</v>
+        <v>0.035422</v>
       </c>
     </row>
     <row r="357">
@@ -5055,10 +5055,10 @@
         </is>
       </c>
       <c r="B357" t="n">
-        <v>0.292707</v>
+        <v>0.410903</v>
       </c>
       <c r="C357" t="n">
-        <v>0.06332500000000001</v>
+        <v>0.032698</v>
       </c>
     </row>
     <row r="358">
@@ -5068,10 +5068,10 @@
         </is>
       </c>
       <c r="B358" t="n">
-        <v>0.303016</v>
+        <v>0.419404</v>
       </c>
       <c r="C358" t="n">
-        <v>0.060686</v>
+        <v>0.029973</v>
       </c>
     </row>
     <row r="359">
@@ -5081,10 +5081,10 @@
         </is>
       </c>
       <c r="B359" t="n">
-        <v>0.35577</v>
+        <v>0.440642</v>
       </c>
       <c r="C359" t="n">
-        <v>0.058047</v>
+        <v>0.027248</v>
       </c>
     </row>
     <row r="360">
@@ -5094,10 +5094,10 @@
         </is>
       </c>
       <c r="B360" t="n">
-        <v>0.359445</v>
+        <v>0.587794</v>
       </c>
       <c r="C360" t="n">
-        <v>0.055409</v>
+        <v>0.024523</v>
       </c>
     </row>
     <row r="361">
@@ -5107,10 +5107,10 @@
         </is>
       </c>
       <c r="B361" t="n">
-        <v>0.363732</v>
+        <v>0.620194</v>
       </c>
       <c r="C361" t="n">
-        <v>0.05277</v>
+        <v>0.021798</v>
       </c>
     </row>
     <row r="362">
@@ -5120,10 +5120,10 @@
         </is>
       </c>
       <c r="B362" t="n">
-        <v>0.36468</v>
+        <v>0.634074</v>
       </c>
       <c r="C362" t="n">
-        <v>0.050132</v>
+        <v>0.019074</v>
       </c>
     </row>
     <row r="363">
@@ -5133,10 +5133,10 @@
         </is>
       </c>
       <c r="B363" t="n">
-        <v>0.373827</v>
+        <v>0.672434</v>
       </c>
       <c r="C363" t="n">
-        <v>0.047493</v>
+        <v>0.016349</v>
       </c>
     </row>
     <row r="364">
@@ -5146,10 +5146,10 @@
         </is>
       </c>
       <c r="B364" t="n">
-        <v>0.389014</v>
+        <v>0.707604</v>
       </c>
       <c r="C364" t="n">
-        <v>0.044855</v>
+        <v>0.013624</v>
       </c>
     </row>
     <row r="365">
@@ -5159,10 +5159,10 @@
         </is>
       </c>
       <c r="B365" t="n">
-        <v>0.400164</v>
+        <v>0.711338</v>
       </c>
       <c r="C365" t="n">
-        <v>0.042216</v>
+        <v>0.010899</v>
       </c>
     </row>
     <row r="366">
@@ -5172,10 +5172,10 @@
         </is>
       </c>
       <c r="B366" t="n">
-        <v>0.40983</v>
+        <v>0.76535</v>
       </c>
       <c r="C366" t="n">
-        <v>0.039578</v>
+        <v>0.008174000000000001</v>
       </c>
     </row>
     <row r="367">
@@ -5185,10 +5185,10 @@
         </is>
       </c>
       <c r="B367" t="n">
-        <v>0.410903</v>
+        <v>0.838984</v>
       </c>
       <c r="C367" t="n">
-        <v>0.036939</v>
+        <v>0.00545</v>
       </c>
     </row>
     <row r="368">
@@ -5198,166 +5198,166 @@
         </is>
       </c>
       <c r="B368" t="n">
-        <v>0.419404</v>
+        <v>1.015082</v>
       </c>
       <c r="C368" t="n">
-        <v>0.034301</v>
+        <v>0.002725</v>
       </c>
     </row>
     <row r="369">
       <c r="A369" t="inlineStr">
         <is>
-          <t>Raw market</t>
+          <t>Adjusted target</t>
         </is>
       </c>
       <c r="B369" t="n">
-        <v>0.440642</v>
+        <v>2e-06</v>
       </c>
       <c r="C369" t="n">
-        <v>0.031662</v>
+        <v>1</v>
       </c>
     </row>
     <row r="370">
       <c r="A370" t="inlineStr">
         <is>
-          <t>Raw market</t>
+          <t>Adjusted target</t>
         </is>
       </c>
       <c r="B370" t="n">
-        <v>0.454545</v>
+        <v>0.000116</v>
       </c>
       <c r="C370" t="n">
-        <v>0.029024</v>
+        <v>0.997275</v>
       </c>
     </row>
     <row r="371">
       <c r="A371" t="inlineStr">
         <is>
-          <t>Raw market</t>
+          <t>Adjusted target</t>
         </is>
       </c>
       <c r="B371" t="n">
-        <v>0.587794</v>
+        <v>0.000335</v>
       </c>
       <c r="C371" t="n">
-        <v>0.026385</v>
+        <v>0.99455</v>
       </c>
     </row>
     <row r="372">
       <c r="A372" t="inlineStr">
         <is>
-          <t>Raw market</t>
+          <t>Adjusted target</t>
         </is>
       </c>
       <c r="B372" t="n">
-        <v>0.620194</v>
+        <v>0.000546</v>
       </c>
       <c r="C372" t="n">
-        <v>0.023747</v>
+        <v>0.991826</v>
       </c>
     </row>
     <row r="373">
       <c r="A373" t="inlineStr">
         <is>
-          <t>Raw market</t>
+          <t>Adjusted target</t>
         </is>
       </c>
       <c r="B373" t="n">
-        <v>0.634074</v>
+        <v>0.001107</v>
       </c>
       <c r="C373" t="n">
-        <v>0.021108</v>
+        <v>0.989101</v>
       </c>
     </row>
     <row r="374">
       <c r="A374" t="inlineStr">
         <is>
-          <t>Raw market</t>
+          <t>Adjusted target</t>
         </is>
       </c>
       <c r="B374" t="n">
-        <v>0.672434</v>
+        <v>0.001715</v>
       </c>
       <c r="C374" t="n">
-        <v>0.01847</v>
+        <v>0.986376</v>
       </c>
     </row>
     <row r="375">
       <c r="A375" t="inlineStr">
         <is>
-          <t>Raw market</t>
+          <t>Adjusted target</t>
         </is>
       </c>
       <c r="B375" t="n">
-        <v>0.678189</v>
+        <v>0.002104</v>
       </c>
       <c r="C375" t="n">
-        <v>0.015831</v>
+        <v>0.9836510000000001</v>
       </c>
     </row>
     <row r="376">
       <c r="A376" t="inlineStr">
         <is>
-          <t>Raw market</t>
+          <t>Adjusted target</t>
         </is>
       </c>
       <c r="B376" t="n">
-        <v>0.707604</v>
+        <v>0.002118</v>
       </c>
       <c r="C376" t="n">
-        <v>0.013193</v>
+        <v>0.980926</v>
       </c>
     </row>
     <row r="377">
       <c r="A377" t="inlineStr">
         <is>
-          <t>Raw market</t>
+          <t>Adjusted target</t>
         </is>
       </c>
       <c r="B377" t="n">
-        <v>0.711338</v>
+        <v>0.002256</v>
       </c>
       <c r="C377" t="n">
-        <v>0.010554</v>
+        <v>0.978202</v>
       </c>
     </row>
     <row r="378">
       <c r="A378" t="inlineStr">
         <is>
-          <t>Raw market</t>
+          <t>Adjusted target</t>
         </is>
       </c>
       <c r="B378" t="n">
-        <v>0.76535</v>
+        <v>0.00306</v>
       </c>
       <c r="C378" t="n">
-        <v>0.007915999999999999</v>
+        <v>0.975477</v>
       </c>
     </row>
     <row r="379">
       <c r="A379" t="inlineStr">
         <is>
-          <t>Raw market</t>
+          <t>Adjusted target</t>
         </is>
       </c>
       <c r="B379" t="n">
-        <v>0.838984</v>
+        <v>0.003119</v>
       </c>
       <c r="C379" t="n">
-        <v>0.005277</v>
+        <v>0.972752</v>
       </c>
     </row>
     <row r="380">
       <c r="A380" t="inlineStr">
         <is>
-          <t>Raw market</t>
+          <t>Adjusted target</t>
         </is>
       </c>
       <c r="B380" t="n">
-        <v>1.015082</v>
+        <v>0.00341</v>
       </c>
       <c r="C380" t="n">
-        <v>0.002639</v>
+        <v>0.970027</v>
       </c>
     </row>
     <row r="381">
@@ -5367,10 +5367,10 @@
         </is>
       </c>
       <c r="B381" t="n">
-        <v>2e-06</v>
+        <v>0.003513</v>
       </c>
       <c r="C381" t="n">
-        <v>1</v>
+        <v>0.967302</v>
       </c>
     </row>
     <row r="382">
@@ -5380,10 +5380,10 @@
         </is>
       </c>
       <c r="B382" t="n">
-        <v>0.000116</v>
+        <v>0.004495</v>
       </c>
       <c r="C382" t="n">
-        <v>0.9973610000000001</v>
+        <v>0.964578</v>
       </c>
     </row>
     <row r="383">
@@ -5393,10 +5393,10 @@
         </is>
       </c>
       <c r="B383" t="n">
-        <v>0.000336</v>
+        <v>0.004551</v>
       </c>
       <c r="C383" t="n">
-        <v>0.994723</v>
+        <v>0.961853</v>
       </c>
     </row>
     <row r="384">
@@ -5406,10 +5406,10 @@
         </is>
       </c>
       <c r="B384" t="n">
-        <v>0.000546</v>
+        <v>0.004741</v>
       </c>
       <c r="C384" t="n">
-        <v>0.992084</v>
+        <v>0.959128</v>
       </c>
     </row>
     <row r="385">
@@ -5419,10 +5419,10 @@
         </is>
       </c>
       <c r="B385" t="n">
-        <v>0.001107</v>
+        <v>0.004825</v>
       </c>
       <c r="C385" t="n">
-        <v>0.989446</v>
+        <v>0.956403</v>
       </c>
     </row>
     <row r="386">
@@ -5432,10 +5432,10 @@
         </is>
       </c>
       <c r="B386" t="n">
-        <v>0.001722</v>
+        <v>0.00504</v>
       </c>
       <c r="C386" t="n">
-        <v>0.986807</v>
+        <v>0.953678</v>
       </c>
     </row>
     <row r="387">
@@ -5445,10 +5445,10 @@
         </is>
       </c>
       <c r="B387" t="n">
-        <v>0.00211</v>
+        <v>0.005114</v>
       </c>
       <c r="C387" t="n">
-        <v>0.984169</v>
+        <v>0.950954</v>
       </c>
     </row>
     <row r="388">
@@ -5458,10 +5458,10 @@
         </is>
       </c>
       <c r="B388" t="n">
-        <v>0.002121</v>
+        <v>0.005145</v>
       </c>
       <c r="C388" t="n">
-        <v>0.98153</v>
+        <v>0.948229</v>
       </c>
     </row>
     <row r="389">
@@ -5471,10 +5471,10 @@
         </is>
       </c>
       <c r="B389" t="n">
-        <v>0.002279</v>
+        <v>0.005184</v>
       </c>
       <c r="C389" t="n">
-        <v>0.978892</v>
+        <v>0.945504</v>
       </c>
     </row>
     <row r="390">
@@ -5484,10 +5484,10 @@
         </is>
       </c>
       <c r="B390" t="n">
-        <v>0.003079</v>
+        <v>0.0055</v>
       </c>
       <c r="C390" t="n">
-        <v>0.976253</v>
+        <v>0.942779</v>
       </c>
     </row>
     <row r="391">
@@ -5497,10 +5497,10 @@
         </is>
       </c>
       <c r="B391" t="n">
-        <v>0.00312</v>
+        <v>0.005563</v>
       </c>
       <c r="C391" t="n">
-        <v>0.973615</v>
+        <v>0.9400539999999999</v>
       </c>
     </row>
     <row r="392">
@@ -5510,10 +5510,10 @@
         </is>
       </c>
       <c r="B392" t="n">
-        <v>0.00341</v>
+        <v>0.005728</v>
       </c>
       <c r="C392" t="n">
-        <v>0.970976</v>
+        <v>0.93733</v>
       </c>
     </row>
     <row r="393">
@@ -5523,10 +5523,10 @@
         </is>
       </c>
       <c r="B393" t="n">
-        <v>0.003543</v>
+        <v>0.00621</v>
       </c>
       <c r="C393" t="n">
-        <v>0.968338</v>
+        <v>0.934605</v>
       </c>
     </row>
     <row r="394">
@@ -5536,10 +5536,10 @@
         </is>
       </c>
       <c r="B394" t="n">
-        <v>0.004494</v>
+        <v>0.006506</v>
       </c>
       <c r="C394" t="n">
-        <v>0.965699</v>
+        <v>0.93188</v>
       </c>
     </row>
     <row r="395">
@@ -5549,10 +5549,10 @@
         </is>
       </c>
       <c r="B395" t="n">
-        <v>0.004551</v>
+        <v>0.006598</v>
       </c>
       <c r="C395" t="n">
-        <v>0.9630609999999999</v>
+        <v>0.929155</v>
       </c>
     </row>
     <row r="396">
@@ -5562,10 +5562,10 @@
         </is>
       </c>
       <c r="B396" t="n">
-        <v>0.004861</v>
+        <v>0.007292</v>
       </c>
       <c r="C396" t="n">
-        <v>0.960422</v>
+        <v>0.926431</v>
       </c>
     </row>
     <row r="397">
@@ -5575,10 +5575,10 @@
         </is>
       </c>
       <c r="B397" t="n">
-        <v>0.004916</v>
+        <v>0.008071</v>
       </c>
       <c r="C397" t="n">
-        <v>0.957784</v>
+        <v>0.923706</v>
       </c>
     </row>
     <row r="398">
@@ -5588,10 +5588,10 @@
         </is>
       </c>
       <c r="B398" t="n">
-        <v>0.00504</v>
+        <v>0.008133</v>
       </c>
       <c r="C398" t="n">
-        <v>0.955145</v>
+        <v>0.920981</v>
       </c>
     </row>
     <row r="399">
@@ -5601,10 +5601,10 @@
         </is>
       </c>
       <c r="B399" t="n">
-        <v>0.005114</v>
+        <v>0.008434000000000001</v>
       </c>
       <c r="C399" t="n">
-        <v>0.952507</v>
+        <v>0.918256</v>
       </c>
     </row>
     <row r="400">
@@ -5614,10 +5614,10 @@
         </is>
       </c>
       <c r="B400" t="n">
-        <v>0.005212</v>
+        <v>0.008600999999999999</v>
       </c>
       <c r="C400" t="n">
-        <v>0.949868</v>
+        <v>0.915531</v>
       </c>
     </row>
     <row r="401">
@@ -5627,10 +5627,10 @@
         </is>
       </c>
       <c r="B401" t="n">
-        <v>0.005249</v>
+        <v>0.008747</v>
       </c>
       <c r="C401" t="n">
-        <v>0.94723</v>
+        <v>0.912807</v>
       </c>
     </row>
     <row r="402">
@@ -5640,10 +5640,10 @@
         </is>
       </c>
       <c r="B402" t="n">
-        <v>0.005568</v>
+        <v>0.008878</v>
       </c>
       <c r="C402" t="n">
-        <v>0.944591</v>
+        <v>0.9100819999999999</v>
       </c>
     </row>
     <row r="403">
@@ -5653,10 +5653,10 @@
         </is>
       </c>
       <c r="B403" t="n">
-        <v>0.005569</v>
+        <v>0.009226</v>
       </c>
       <c r="C403" t="n">
-        <v>0.941953</v>
+        <v>0.907357</v>
       </c>
     </row>
     <row r="404">
@@ -5666,10 +5666,10 @@
         </is>
       </c>
       <c r="B404" t="n">
-        <v>0.005738</v>
+        <v>0.009343000000000001</v>
       </c>
       <c r="C404" t="n">
-        <v>0.939314</v>
+        <v>0.904632</v>
       </c>
     </row>
     <row r="405">
@@ -5679,10 +5679,10 @@
         </is>
       </c>
       <c r="B405" t="n">
-        <v>0.006223</v>
+        <v>0.009362000000000001</v>
       </c>
       <c r="C405" t="n">
-        <v>0.936675</v>
+        <v>0.901907</v>
       </c>
     </row>
     <row r="406">
@@ -5692,10 +5692,10 @@
         </is>
       </c>
       <c r="B406" t="n">
-        <v>0.00651</v>
+        <v>0.009946</v>
       </c>
       <c r="C406" t="n">
-        <v>0.934037</v>
+        <v>0.899183</v>
       </c>
     </row>
     <row r="407">
@@ -5705,10 +5705,10 @@
         </is>
       </c>
       <c r="B407" t="n">
-        <v>0.006604</v>
+        <v>0.009993999999999999</v>
       </c>
       <c r="C407" t="n">
-        <v>0.9313979999999999</v>
+        <v>0.896458</v>
       </c>
     </row>
     <row r="408">
@@ -5718,10 +5718,10 @@
         </is>
       </c>
       <c r="B408" t="n">
-        <v>0.007292</v>
+        <v>0.010063</v>
       </c>
       <c r="C408" t="n">
-        <v>0.92876</v>
+        <v>0.893733</v>
       </c>
     </row>
     <row r="409">
@@ -5731,10 +5731,10 @@
         </is>
       </c>
       <c r="B409" t="n">
-        <v>0.008134000000000001</v>
+        <v>0.010277</v>
       </c>
       <c r="C409" t="n">
-        <v>0.926121</v>
+        <v>0.891008</v>
       </c>
     </row>
     <row r="410">
@@ -5744,10 +5744,10 @@
         </is>
       </c>
       <c r="B410" t="n">
-        <v>0.008196</v>
+        <v>0.01086</v>
       </c>
       <c r="C410" t="n">
-        <v>0.9234830000000001</v>
+        <v>0.888283</v>
       </c>
     </row>
     <row r="411">
@@ -5757,10 +5757,10 @@
         </is>
       </c>
       <c r="B411" t="n">
-        <v>0.008433</v>
+        <v>0.011202</v>
       </c>
       <c r="C411" t="n">
-        <v>0.920844</v>
+        <v>0.885559</v>
       </c>
     </row>
     <row r="412">
@@ -5770,10 +5770,10 @@
         </is>
       </c>
       <c r="B412" t="n">
-        <v>0.008607999999999999</v>
+        <v>0.011297</v>
       </c>
       <c r="C412" t="n">
-        <v>0.918206</v>
+        <v>0.882834</v>
       </c>
     </row>
     <row r="413">
@@ -5783,10 +5783,10 @@
         </is>
       </c>
       <c r="B413" t="n">
-        <v>0.008881999999999999</v>
+        <v>0.011303</v>
       </c>
       <c r="C413" t="n">
-        <v>0.915567</v>
+        <v>0.880109</v>
       </c>
     </row>
     <row r="414">
@@ -5796,10 +5796,10 @@
         </is>
       </c>
       <c r="B414" t="n">
-        <v>0.008884</v>
+        <v>0.011401</v>
       </c>
       <c r="C414" t="n">
-        <v>0.912929</v>
+        <v>0.8773840000000001</v>
       </c>
     </row>
     <row r="415">
@@ -5809,10 +5809,10 @@
         </is>
       </c>
       <c r="B415" t="n">
-        <v>0.009292</v>
+        <v>0.01173</v>
       </c>
       <c r="C415" t="n">
-        <v>0.91029</v>
+        <v>0.874659</v>
       </c>
     </row>
     <row r="416">
@@ -5822,10 +5822,10 @@
         </is>
       </c>
       <c r="B416" t="n">
-        <v>0.009342</v>
+        <v>0.012049</v>
       </c>
       <c r="C416" t="n">
-        <v>0.907652</v>
+        <v>0.871935</v>
       </c>
     </row>
     <row r="417">
@@ -5835,10 +5835,10 @@
         </is>
       </c>
       <c r="B417" t="n">
-        <v>0.009375</v>
+        <v>0.012282</v>
       </c>
       <c r="C417" t="n">
-        <v>0.905013</v>
+        <v>0.86921</v>
       </c>
     </row>
     <row r="418">
@@ -5848,10 +5848,10 @@
         </is>
       </c>
       <c r="B418" t="n">
-        <v>0.010007</v>
+        <v>0.01261</v>
       </c>
       <c r="C418" t="n">
-        <v>0.902375</v>
+        <v>0.8664849999999999</v>
       </c>
     </row>
     <row r="419">
@@ -5861,10 +5861,10 @@
         </is>
       </c>
       <c r="B419" t="n">
-        <v>0.010135</v>
+        <v>0.012624</v>
       </c>
       <c r="C419" t="n">
-        <v>0.899736</v>
+        <v>0.86376</v>
       </c>
     </row>
     <row r="420">
@@ -5874,10 +5874,10 @@
         </is>
       </c>
       <c r="B420" t="n">
-        <v>0.01014</v>
+        <v>0.012712</v>
       </c>
       <c r="C420" t="n">
-        <v>0.897098</v>
+        <v>0.861035</v>
       </c>
     </row>
     <row r="421">
@@ -5887,10 +5887,10 @@
         </is>
       </c>
       <c r="B421" t="n">
-        <v>0.010301</v>
+        <v>0.012816</v>
       </c>
       <c r="C421" t="n">
-        <v>0.894459</v>
+        <v>0.858311</v>
       </c>
     </row>
     <row r="422">
@@ -5900,10 +5900,10 @@
         </is>
       </c>
       <c r="B422" t="n">
-        <v>0.010561</v>
+        <v>0.012839</v>
       </c>
       <c r="C422" t="n">
-        <v>0.891821</v>
+        <v>0.855586</v>
       </c>
     </row>
     <row r="423">
@@ -5913,10 +5913,10 @@
         </is>
       </c>
       <c r="B423" t="n">
-        <v>0.010866</v>
+        <v>0.013047</v>
       </c>
       <c r="C423" t="n">
-        <v>0.889182</v>
+        <v>0.852861</v>
       </c>
     </row>
     <row r="424">
@@ -5926,10 +5926,10 @@
         </is>
       </c>
       <c r="B424" t="n">
-        <v>0.011201</v>
+        <v>0.01339</v>
       </c>
       <c r="C424" t="n">
-        <v>0.886544</v>
+        <v>0.850136</v>
       </c>
     </row>
     <row r="425">
@@ -5939,10 +5939,10 @@
         </is>
       </c>
       <c r="B425" t="n">
-        <v>0.011302</v>
+        <v>0.013577</v>
       </c>
       <c r="C425" t="n">
-        <v>0.8839050000000001</v>
+        <v>0.847411</v>
       </c>
     </row>
     <row r="426">
@@ -5952,10 +5952,10 @@
         </is>
       </c>
       <c r="B426" t="n">
-        <v>0.011417</v>
+        <v>0.013992</v>
       </c>
       <c r="C426" t="n">
-        <v>0.881266</v>
+        <v>0.844687</v>
       </c>
     </row>
     <row r="427">
@@ -5965,10 +5965,10 @@
         </is>
       </c>
       <c r="B427" t="n">
-        <v>0.011456</v>
+        <v>0.015067</v>
       </c>
       <c r="C427" t="n">
-        <v>0.878628</v>
+        <v>0.841962</v>
       </c>
     </row>
     <row r="428">
@@ -5978,10 +5978,10 @@
         </is>
       </c>
       <c r="B428" t="n">
-        <v>0.011855</v>
+        <v>0.015198</v>
       </c>
       <c r="C428" t="n">
-        <v>0.875989</v>
+        <v>0.839237</v>
       </c>
     </row>
     <row r="429">
@@ -5991,10 +5991,10 @@
         </is>
       </c>
       <c r="B429" t="n">
-        <v>0.01205</v>
+        <v>0.015329</v>
       </c>
       <c r="C429" t="n">
-        <v>0.873351</v>
+        <v>0.836512</v>
       </c>
     </row>
     <row r="430">
@@ -6004,10 +6004,10 @@
         </is>
       </c>
       <c r="B430" t="n">
-        <v>0.012327</v>
+        <v>0.015528</v>
       </c>
       <c r="C430" t="n">
-        <v>0.870712</v>
+        <v>0.8337869999999999</v>
       </c>
     </row>
     <row r="431">
@@ -6017,10 +6017,10 @@
         </is>
       </c>
       <c r="B431" t="n">
-        <v>0.012618</v>
+        <v>0.015664</v>
       </c>
       <c r="C431" t="n">
-        <v>0.868074</v>
+        <v>0.831063</v>
       </c>
     </row>
     <row r="432">
@@ -6030,10 +6030,10 @@
         </is>
       </c>
       <c r="B432" t="n">
-        <v>0.012623</v>
+        <v>0.015692</v>
       </c>
       <c r="C432" t="n">
-        <v>0.865435</v>
+        <v>0.828338</v>
       </c>
     </row>
     <row r="433">
@@ -6043,10 +6043,10 @@
         </is>
       </c>
       <c r="B433" t="n">
-        <v>0.012751</v>
+        <v>0.016126</v>
       </c>
       <c r="C433" t="n">
-        <v>0.862797</v>
+        <v>0.825613</v>
       </c>
     </row>
     <row r="434">
@@ -6056,10 +6056,10 @@
         </is>
       </c>
       <c r="B434" t="n">
-        <v>0.012816</v>
+        <v>0.016489</v>
       </c>
       <c r="C434" t="n">
-        <v>0.860158</v>
+        <v>0.822888</v>
       </c>
     </row>
     <row r="435">
@@ -6069,10 +6069,10 @@
         </is>
       </c>
       <c r="B435" t="n">
-        <v>0.013068</v>
+        <v>0.016704</v>
       </c>
       <c r="C435" t="n">
-        <v>0.8575199999999999</v>
+        <v>0.820163</v>
       </c>
     </row>
     <row r="436">
@@ -6082,10 +6082,10 @@
         </is>
       </c>
       <c r="B436" t="n">
-        <v>0.013098</v>
+        <v>0.016956</v>
       </c>
       <c r="C436" t="n">
-        <v>0.854881</v>
+        <v>0.817439</v>
       </c>
     </row>
     <row r="437">
@@ -6095,10 +6095,10 @@
         </is>
       </c>
       <c r="B437" t="n">
-        <v>0.0134</v>
+        <v>0.017087</v>
       </c>
       <c r="C437" t="n">
-        <v>0.852243</v>
+        <v>0.814714</v>
       </c>
     </row>
     <row r="438">
@@ -6108,10 +6108,10 @@
         </is>
       </c>
       <c r="B438" t="n">
-        <v>0.013608</v>
+        <v>0.017274</v>
       </c>
       <c r="C438" t="n">
-        <v>0.849604</v>
+        <v>0.811989</v>
       </c>
     </row>
     <row r="439">
@@ -6121,10 +6121,10 @@
         </is>
       </c>
       <c r="B439" t="n">
-        <v>0.013991</v>
+        <v>0.017479</v>
       </c>
       <c r="C439" t="n">
-        <v>0.846966</v>
+        <v>0.809264</v>
       </c>
     </row>
     <row r="440">
@@ -6134,10 +6134,10 @@
         </is>
       </c>
       <c r="B440" t="n">
-        <v>0.015068</v>
+        <v>0.017715</v>
       </c>
       <c r="C440" t="n">
-        <v>0.844327</v>
+        <v>0.80654</v>
       </c>
     </row>
     <row r="441">
@@ -6147,10 +6147,10 @@
         </is>
       </c>
       <c r="B441" t="n">
-        <v>0.015336</v>
+        <v>0.018035</v>
       </c>
       <c r="C441" t="n">
-        <v>0.841689</v>
+        <v>0.8038149999999999</v>
       </c>
     </row>
     <row r="442">
@@ -6160,10 +6160,10 @@
         </is>
       </c>
       <c r="B442" t="n">
-        <v>0.015375</v>
+        <v>0.01809</v>
       </c>
       <c r="C442" t="n">
-        <v>0.83905</v>
+        <v>0.80109</v>
       </c>
     </row>
     <row r="443">
@@ -6173,10 +6173,10 @@
         </is>
       </c>
       <c r="B443" t="n">
-        <v>0.015656</v>
+        <v>0.018262</v>
       </c>
       <c r="C443" t="n">
-        <v>0.836412</v>
+        <v>0.798365</v>
       </c>
     </row>
     <row r="444">
@@ -6186,10 +6186,10 @@
         </is>
       </c>
       <c r="B444" t="n">
-        <v>0.015695</v>
+        <v>0.018929</v>
       </c>
       <c r="C444" t="n">
-        <v>0.833773</v>
+        <v>0.79564</v>
       </c>
     </row>
     <row r="445">
@@ -6199,10 +6199,10 @@
         </is>
       </c>
       <c r="B445" t="n">
-        <v>0.015703</v>
+        <v>0.019002</v>
       </c>
       <c r="C445" t="n">
-        <v>0.831135</v>
+        <v>0.792916</v>
       </c>
     </row>
     <row r="446">
@@ -6212,10 +6212,10 @@
         </is>
       </c>
       <c r="B446" t="n">
-        <v>0.016145</v>
+        <v>0.019017</v>
       </c>
       <c r="C446" t="n">
-        <v>0.828496</v>
+        <v>0.790191</v>
       </c>
     </row>
     <row r="447">
@@ -6225,10 +6225,10 @@
         </is>
       </c>
       <c r="B447" t="n">
-        <v>0.016489</v>
+        <v>0.019102</v>
       </c>
       <c r="C447" t="n">
-        <v>0.825858</v>
+        <v>0.787466</v>
       </c>
     </row>
     <row r="448">
@@ -6238,10 +6238,10 @@
         </is>
       </c>
       <c r="B448" t="n">
-        <v>0.016774</v>
+        <v>0.019446</v>
       </c>
       <c r="C448" t="n">
-        <v>0.823219</v>
+        <v>0.784741</v>
       </c>
     </row>
     <row r="449">
@@ -6251,10 +6251,10 @@
         </is>
       </c>
       <c r="B449" t="n">
-        <v>0.016843</v>
+        <v>0.019602</v>
       </c>
       <c r="C449" t="n">
-        <v>0.82058</v>
+        <v>0.782016</v>
       </c>
     </row>
     <row r="450">
@@ -6264,10 +6264,10 @@
         </is>
       </c>
       <c r="B450" t="n">
-        <v>0.01697</v>
+        <v>0.020677</v>
       </c>
       <c r="C450" t="n">
-        <v>0.8179419999999999</v>
+        <v>0.779292</v>
       </c>
     </row>
     <row r="451">
@@ -6277,10 +6277,10 @@
         </is>
       </c>
       <c r="B451" t="n">
-        <v>0.01709</v>
+        <v>0.020788</v>
       </c>
       <c r="C451" t="n">
-        <v>0.815303</v>
+        <v>0.776567</v>
       </c>
     </row>
     <row r="452">
@@ -6290,10 +6290,10 @@
         </is>
       </c>
       <c r="B452" t="n">
-        <v>0.0173</v>
+        <v>0.02097</v>
       </c>
       <c r="C452" t="n">
-        <v>0.812665</v>
+        <v>0.773842</v>
       </c>
     </row>
     <row r="453">
@@ -6303,10 +6303,10 @@
         </is>
       </c>
       <c r="B453" t="n">
-        <v>0.017478</v>
+        <v>0.021199</v>
       </c>
       <c r="C453" t="n">
-        <v>0.810026</v>
+        <v>0.7711170000000001</v>
       </c>
     </row>
     <row r="454">
@@ -6316,10 +6316,10 @@
         </is>
       </c>
       <c r="B454" t="n">
-        <v>0.017808</v>
+        <v>0.021668</v>
       </c>
       <c r="C454" t="n">
-        <v>0.807388</v>
+        <v>0.768392</v>
       </c>
     </row>
     <row r="455">
@@ -6329,10 +6329,10 @@
         </is>
       </c>
       <c r="B455" t="n">
-        <v>0.018065</v>
+        <v>0.02197</v>
       </c>
       <c r="C455" t="n">
-        <v>0.804749</v>
+        <v>0.765668</v>
       </c>
     </row>
     <row r="456">
@@ -6342,10 +6342,10 @@
         </is>
       </c>
       <c r="B456" t="n">
-        <v>0.01814</v>
+        <v>0.022517</v>
       </c>
       <c r="C456" t="n">
-        <v>0.802111</v>
+        <v>0.762943</v>
       </c>
     </row>
     <row r="457">
@@ -6355,10 +6355,10 @@
         </is>
       </c>
       <c r="B457" t="n">
-        <v>0.018332</v>
+        <v>0.022992</v>
       </c>
       <c r="C457" t="n">
-        <v>0.799472</v>
+        <v>0.7602179999999999</v>
       </c>
     </row>
     <row r="458">
@@ -6368,10 +6368,10 @@
         </is>
       </c>
       <c r="B458" t="n">
-        <v>0.01893</v>
+        <v>0.023838</v>
       </c>
       <c r="C458" t="n">
-        <v>0.796834</v>
+        <v>0.757493</v>
       </c>
     </row>
     <row r="459">
@@ -6381,10 +6381,10 @@
         </is>
       </c>
       <c r="B459" t="n">
-        <v>0.019017</v>
+        <v>0.024054</v>
       </c>
       <c r="C459" t="n">
-        <v>0.794195</v>
+        <v>0.754768</v>
       </c>
     </row>
     <row r="460">
@@ -6394,10 +6394,10 @@
         </is>
       </c>
       <c r="B460" t="n">
-        <v>0.019053</v>
+        <v>0.024239</v>
       </c>
       <c r="C460" t="n">
-        <v>0.791557</v>
+        <v>0.752044</v>
       </c>
     </row>
     <row r="461">
@@ -6407,10 +6407,10 @@
         </is>
       </c>
       <c r="B461" t="n">
-        <v>0.019106</v>
+        <v>0.024485</v>
       </c>
       <c r="C461" t="n">
-        <v>0.788918</v>
+        <v>0.749319</v>
       </c>
     </row>
     <row r="462">
@@ -6420,10 +6420,10 @@
         </is>
       </c>
       <c r="B462" t="n">
-        <v>0.019445</v>
+        <v>0.024714</v>
       </c>
       <c r="C462" t="n">
-        <v>0.78628</v>
+        <v>0.746594</v>
       </c>
     </row>
     <row r="463">
@@ -6433,10 +6433,10 @@
         </is>
       </c>
       <c r="B463" t="n">
-        <v>0.019672</v>
+        <v>0.025205</v>
       </c>
       <c r="C463" t="n">
-        <v>0.783641</v>
+        <v>0.743869</v>
       </c>
     </row>
     <row r="464">
@@ -6446,10 +6446,10 @@
         </is>
       </c>
       <c r="B464" t="n">
-        <v>0.019993</v>
+        <v>0.025259</v>
       </c>
       <c r="C464" t="n">
-        <v>0.781003</v>
+        <v>0.741144</v>
       </c>
     </row>
     <row r="465">
@@ -6459,10 +6459,10 @@
         </is>
       </c>
       <c r="B465" t="n">
-        <v>0.020675</v>
+        <v>0.025313</v>
       </c>
       <c r="C465" t="n">
-        <v>0.7783639999999999</v>
+        <v>0.73842</v>
       </c>
     </row>
     <row r="466">
@@ -6472,10 +6472,10 @@
         </is>
       </c>
       <c r="B466" t="n">
-        <v>0.020863</v>
+        <v>0.02551</v>
       </c>
       <c r="C466" t="n">
-        <v>0.775726</v>
+        <v>0.735695</v>
       </c>
     </row>
     <row r="467">
@@ -6485,10 +6485,10 @@
         </is>
       </c>
       <c r="B467" t="n">
-        <v>0.02097</v>
+        <v>0.025777</v>
       </c>
       <c r="C467" t="n">
-        <v>0.773087</v>
+        <v>0.73297</v>
       </c>
     </row>
     <row r="468">
@@ -6498,10 +6498,10 @@
         </is>
       </c>
       <c r="B468" t="n">
-        <v>0.021295</v>
+        <v>0.026013</v>
       </c>
       <c r="C468" t="n">
-        <v>0.7704490000000001</v>
+        <v>0.730245</v>
       </c>
     </row>
     <row r="469">
@@ -6511,10 +6511,10 @@
         </is>
       </c>
       <c r="B469" t="n">
-        <v>0.021695</v>
+        <v>0.026329</v>
       </c>
       <c r="C469" t="n">
-        <v>0.76781</v>
+        <v>0.7275199999999999</v>
       </c>
     </row>
     <row r="470">
@@ -6524,10 +6524,10 @@
         </is>
       </c>
       <c r="B470" t="n">
-        <v>0.021979</v>
+        <v>0.027274</v>
       </c>
       <c r="C470" t="n">
-        <v>0.765172</v>
+        <v>0.724796</v>
       </c>
     </row>
     <row r="471">
@@ -6537,10 +6537,10 @@
         </is>
       </c>
       <c r="B471" t="n">
-        <v>0.022548</v>
+        <v>0.027389</v>
       </c>
       <c r="C471" t="n">
-        <v>0.762533</v>
+        <v>0.722071</v>
       </c>
     </row>
     <row r="472">
@@ -6550,10 +6550,10 @@
         </is>
       </c>
       <c r="B472" t="n">
-        <v>0.023039</v>
+        <v>0.027418</v>
       </c>
       <c r="C472" t="n">
-        <v>0.759894</v>
+        <v>0.719346</v>
       </c>
     </row>
     <row r="473">
@@ -6563,10 +6563,10 @@
         </is>
       </c>
       <c r="B473" t="n">
-        <v>0.024101</v>
+        <v>0.027444</v>
       </c>
       <c r="C473" t="n">
-        <v>0.757256</v>
+        <v>0.716621</v>
       </c>
     </row>
     <row r="474">
@@ -6576,10 +6576,10 @@
         </is>
       </c>
       <c r="B474" t="n">
-        <v>0.024145</v>
+        <v>0.027611</v>
       </c>
       <c r="C474" t="n">
-        <v>0.754617</v>
+        <v>0.713896</v>
       </c>
     </row>
     <row r="475">
@@ -6589,10 +6589,10 @@
         </is>
       </c>
       <c r="B475" t="n">
-        <v>0.024241</v>
+        <v>0.027768</v>
       </c>
       <c r="C475" t="n">
-        <v>0.751979</v>
+        <v>0.711172</v>
       </c>
     </row>
     <row r="476">
@@ -6602,10 +6602,10 @@
         </is>
       </c>
       <c r="B476" t="n">
-        <v>0.024526</v>
+        <v>0.027782</v>
       </c>
       <c r="C476" t="n">
-        <v>0.74934</v>
+        <v>0.708447</v>
       </c>
     </row>
     <row r="477">
@@ -6615,10 +6615,10 @@
         </is>
       </c>
       <c r="B477" t="n">
-        <v>0.024843</v>
+        <v>0.028126</v>
       </c>
       <c r="C477" t="n">
-        <v>0.746702</v>
+        <v>0.705722</v>
       </c>
     </row>
     <row r="478">
@@ -6628,10 +6628,10 @@
         </is>
       </c>
       <c r="B478" t="n">
-        <v>0.025216</v>
+        <v>0.028144</v>
       </c>
       <c r="C478" t="n">
-        <v>0.744063</v>
+        <v>0.702997</v>
       </c>
     </row>
     <row r="479">
@@ -6641,10 +6641,10 @@
         </is>
       </c>
       <c r="B479" t="n">
-        <v>0.025284</v>
+        <v>0.028296</v>
       </c>
       <c r="C479" t="n">
-        <v>0.741425</v>
+        <v>0.700272</v>
       </c>
     </row>
     <row r="480">
@@ -6654,10 +6654,10 @@
         </is>
       </c>
       <c r="B480" t="n">
-        <v>0.025313</v>
+        <v>0.02878</v>
       </c>
       <c r="C480" t="n">
-        <v>0.7387860000000001</v>
+        <v>0.6975479999999999</v>
       </c>
     </row>
     <row r="481">
@@ -6667,10 +6667,10 @@
         </is>
       </c>
       <c r="B481" t="n">
-        <v>0.025698</v>
+        <v>0.029052</v>
       </c>
       <c r="C481" t="n">
-        <v>0.736148</v>
+        <v>0.694823</v>
       </c>
     </row>
     <row r="482">
@@ -6680,10 +6680,10 @@
         </is>
       </c>
       <c r="B482" t="n">
-        <v>0.025774</v>
+        <v>0.029307</v>
       </c>
       <c r="C482" t="n">
-        <v>0.733509</v>
+        <v>0.692098</v>
       </c>
     </row>
     <row r="483">
@@ -6693,10 +6693,10 @@
         </is>
       </c>
       <c r="B483" t="n">
-        <v>0.026152</v>
+        <v>0.029538</v>
       </c>
       <c r="C483" t="n">
-        <v>0.730871</v>
+        <v>0.689373</v>
       </c>
     </row>
     <row r="484">
@@ -6706,10 +6706,10 @@
         </is>
       </c>
       <c r="B484" t="n">
-        <v>0.0266</v>
+        <v>0.029644</v>
       </c>
       <c r="C484" t="n">
-        <v>0.728232</v>
+        <v>0.686649</v>
       </c>
     </row>
     <row r="485">
@@ -6719,10 +6719,10 @@
         </is>
       </c>
       <c r="B485" t="n">
-        <v>0.027307</v>
+        <v>0.030029</v>
       </c>
       <c r="C485" t="n">
-        <v>0.725594</v>
+        <v>0.683924</v>
       </c>
     </row>
     <row r="486">
@@ -6732,10 +6732,10 @@
         </is>
       </c>
       <c r="B486" t="n">
-        <v>0.027503</v>
+        <v>0.030292</v>
       </c>
       <c r="C486" t="n">
-        <v>0.722955</v>
+        <v>0.681199</v>
       </c>
     </row>
     <row r="487">
@@ -6745,10 +6745,10 @@
         </is>
       </c>
       <c r="B487" t="n">
-        <v>0.027753</v>
+        <v>0.030311</v>
       </c>
       <c r="C487" t="n">
-        <v>0.720317</v>
+        <v>0.678474</v>
       </c>
     </row>
     <row r="488">
@@ -6758,10 +6758,10 @@
         </is>
       </c>
       <c r="B488" t="n">
-        <v>0.027865</v>
+        <v>0.03044</v>
       </c>
       <c r="C488" t="n">
-        <v>0.717678</v>
+        <v>0.675749</v>
       </c>
     </row>
     <row r="489">
@@ -6771,10 +6771,10 @@
         </is>
       </c>
       <c r="B489" t="n">
-        <v>0.027894</v>
+        <v>0.030882</v>
       </c>
       <c r="C489" t="n">
-        <v>0.71504</v>
+        <v>0.673025</v>
       </c>
     </row>
     <row r="490">
@@ -6784,10 +6784,10 @@
         </is>
       </c>
       <c r="B490" t="n">
-        <v>0.027903</v>
+        <v>0.0311</v>
       </c>
       <c r="C490" t="n">
-        <v>0.712401</v>
+        <v>0.6703</v>
       </c>
     </row>
     <row r="491">
@@ -6797,10 +6797,10 @@
         </is>
       </c>
       <c r="B491" t="n">
-        <v>0.027908</v>
+        <v>0.03133</v>
       </c>
       <c r="C491" t="n">
-        <v>0.709763</v>
+        <v>0.667575</v>
       </c>
     </row>
     <row r="492">
@@ -6810,10 +6810,10 @@
         </is>
       </c>
       <c r="B492" t="n">
-        <v>0.028124</v>
+        <v>0.03175</v>
       </c>
       <c r="C492" t="n">
-        <v>0.707124</v>
+        <v>0.6648500000000001</v>
       </c>
     </row>
     <row r="493">
@@ -6823,10 +6823,10 @@
         </is>
       </c>
       <c r="B493" t="n">
-        <v>0.028198</v>
+        <v>0.032586</v>
       </c>
       <c r="C493" t="n">
-        <v>0.704485</v>
+        <v>0.662125</v>
       </c>
     </row>
     <row r="494">
@@ -6836,10 +6836,10 @@
         </is>
       </c>
       <c r="B494" t="n">
-        <v>0.028394</v>
+        <v>0.032694</v>
       </c>
       <c r="C494" t="n">
-        <v>0.701847</v>
+        <v>0.659401</v>
       </c>
     </row>
     <row r="495">
@@ -6849,10 +6849,10 @@
         </is>
       </c>
       <c r="B495" t="n">
-        <v>0.028776</v>
+        <v>0.032807</v>
       </c>
       <c r="C495" t="n">
-        <v>0.6992080000000001</v>
+        <v>0.656676</v>
       </c>
     </row>
     <row r="496">
@@ -6862,10 +6862,10 @@
         </is>
       </c>
       <c r="B496" t="n">
-        <v>0.029099</v>
+        <v>0.032818</v>
       </c>
       <c r="C496" t="n">
-        <v>0.69657</v>
+        <v>0.6539509999999999</v>
       </c>
     </row>
     <row r="497">
@@ -6875,10 +6875,10 @@
         </is>
       </c>
       <c r="B497" t="n">
-        <v>0.029319</v>
+        <v>0.033753</v>
       </c>
       <c r="C497" t="n">
-        <v>0.693931</v>
+        <v>0.651226</v>
       </c>
     </row>
     <row r="498">
@@ -6888,10 +6888,10 @@
         </is>
       </c>
       <c r="B498" t="n">
-        <v>0.02965</v>
+        <v>0.033985</v>
       </c>
       <c r="C498" t="n">
-        <v>0.691293</v>
+        <v>0.648501</v>
       </c>
     </row>
     <row r="499">
@@ -6901,10 +6901,10 @@
         </is>
       </c>
       <c r="B499" t="n">
-        <v>0.029793</v>
+        <v>0.034032</v>
       </c>
       <c r="C499" t="n">
-        <v>0.688654</v>
+        <v>0.645777</v>
       </c>
     </row>
     <row r="500">
@@ -6914,10 +6914,10 @@
         </is>
       </c>
       <c r="B500" t="n">
-        <v>0.03004</v>
+        <v>0.034287</v>
       </c>
       <c r="C500" t="n">
-        <v>0.686016</v>
+        <v>0.643052</v>
       </c>
     </row>
     <row r="501">
@@ -6927,10 +6927,10 @@
         </is>
       </c>
       <c r="B501" t="n">
-        <v>0.030355</v>
+        <v>0.034379</v>
       </c>
       <c r="C501" t="n">
-        <v>0.683377</v>
+        <v>0.640327</v>
       </c>
     </row>
     <row r="502">
@@ -6940,10 +6940,10 @@
         </is>
       </c>
       <c r="B502" t="n">
-        <v>0.030366</v>
+        <v>0.034518</v>
       </c>
       <c r="C502" t="n">
-        <v>0.680739</v>
+        <v>0.637602</v>
       </c>
     </row>
     <row r="503">
@@ -6953,10 +6953,10 @@
         </is>
       </c>
       <c r="B503" t="n">
-        <v>0.030519</v>
+        <v>0.034532</v>
       </c>
       <c r="C503" t="n">
-        <v>0.6781</v>
+        <v>0.634877</v>
       </c>
     </row>
     <row r="504">
@@ -6966,10 +6966,10 @@
         </is>
       </c>
       <c r="B504" t="n">
-        <v>0.030911</v>
+        <v>0.03473</v>
       </c>
       <c r="C504" t="n">
-        <v>0.675462</v>
+        <v>0.632153</v>
       </c>
     </row>
     <row r="505">
@@ -6979,10 +6979,10 @@
         </is>
       </c>
       <c r="B505" t="n">
-        <v>0.031097</v>
+        <v>0.035098</v>
       </c>
       <c r="C505" t="n">
-        <v>0.6728229999999999</v>
+        <v>0.629428</v>
       </c>
     </row>
     <row r="506">
@@ -6992,10 +6992,10 @@
         </is>
       </c>
       <c r="B506" t="n">
-        <v>0.031436</v>
+        <v>0.035145</v>
       </c>
       <c r="C506" t="n">
-        <v>0.670185</v>
+        <v>0.626703</v>
       </c>
     </row>
     <row r="507">
@@ -7005,10 +7005,10 @@
         </is>
       </c>
       <c r="B507" t="n">
-        <v>0.031779</v>
+        <v>0.035805</v>
       </c>
       <c r="C507" t="n">
-        <v>0.667546</v>
+        <v>0.623978</v>
       </c>
     </row>
     <row r="508">
@@ -7018,10 +7018,10 @@
         </is>
       </c>
       <c r="B508" t="n">
-        <v>0.032816</v>
+        <v>0.036</v>
       </c>
       <c r="C508" t="n">
-        <v>0.6649080000000001</v>
+        <v>0.6212530000000001</v>
       </c>
     </row>
     <row r="509">
@@ -7031,10 +7031,10 @@
         </is>
       </c>
       <c r="B509" t="n">
-        <v>0.032838</v>
+        <v>0.036602</v>
       </c>
       <c r="C509" t="n">
-        <v>0.662269</v>
+        <v>0.618529</v>
       </c>
     </row>
     <row r="510">
@@ -7044,10 +7044,10 @@
         </is>
       </c>
       <c r="B510" t="n">
-        <v>0.032872</v>
+        <v>0.036885</v>
       </c>
       <c r="C510" t="n">
-        <v>0.659631</v>
+        <v>0.615804</v>
       </c>
     </row>
     <row r="511">
@@ -7057,10 +7057,10 @@
         </is>
       </c>
       <c r="B511" t="n">
-        <v>0.03302</v>
+        <v>0.037297</v>
       </c>
       <c r="C511" t="n">
-        <v>0.656992</v>
+        <v>0.613079</v>
       </c>
     </row>
     <row r="512">
@@ -7070,10 +7070,10 @@
         </is>
       </c>
       <c r="B512" t="n">
-        <v>0.033951</v>
+        <v>0.037747</v>
       </c>
       <c r="C512" t="n">
-        <v>0.654354</v>
+        <v>0.610354</v>
       </c>
     </row>
     <row r="513">
@@ -7083,10 +7083,10 @@
         </is>
       </c>
       <c r="B513" t="n">
-        <v>0.033987</v>
+        <v>0.037931</v>
       </c>
       <c r="C513" t="n">
-        <v>0.651715</v>
+        <v>0.607629</v>
       </c>
     </row>
     <row r="514">
@@ -7096,10 +7096,10 @@
         </is>
       </c>
       <c r="B514" t="n">
-        <v>0.034062</v>
+        <v>0.03797</v>
       </c>
       <c r="C514" t="n">
-        <v>0.649077</v>
+        <v>0.604905</v>
       </c>
     </row>
     <row r="515">
@@ -7109,10 +7109,10 @@
         </is>
       </c>
       <c r="B515" t="n">
-        <v>0.034303</v>
+        <v>0.038469</v>
       </c>
       <c r="C515" t="n">
-        <v>0.646438</v>
+        <v>0.60218</v>
       </c>
     </row>
     <row r="516">
@@ -7122,10 +7122,10 @@
         </is>
       </c>
       <c r="B516" t="n">
-        <v>0.034487</v>
+        <v>0.038746</v>
       </c>
       <c r="C516" t="n">
-        <v>0.643799</v>
+        <v>0.599455</v>
       </c>
     </row>
     <row r="517">
@@ -7135,10 +7135,10 @@
         </is>
       </c>
       <c r="B517" t="n">
-        <v>0.034515</v>
+        <v>0.038914</v>
       </c>
       <c r="C517" t="n">
-        <v>0.641161</v>
+        <v>0.59673</v>
       </c>
     </row>
     <row r="518">
@@ -7148,10 +7148,10 @@
         </is>
       </c>
       <c r="B518" t="n">
-        <v>0.034933</v>
+        <v>0.039088</v>
       </c>
       <c r="C518" t="n">
-        <v>0.638522</v>
+        <v>0.594005</v>
       </c>
     </row>
     <row r="519">
@@ -7161,10 +7161,10 @@
         </is>
       </c>
       <c r="B519" t="n">
-        <v>0.035141</v>
+        <v>0.039287</v>
       </c>
       <c r="C519" t="n">
-        <v>0.635884</v>
+        <v>0.5912809999999999</v>
       </c>
     </row>
     <row r="520">
@@ -7174,10 +7174,10 @@
         </is>
       </c>
       <c r="B520" t="n">
-        <v>0.035145</v>
+        <v>0.039627</v>
       </c>
       <c r="C520" t="n">
-        <v>0.6332449999999999</v>
+        <v>0.588556</v>
       </c>
     </row>
     <row r="521">
@@ -7187,10 +7187,10 @@
         </is>
       </c>
       <c r="B521" t="n">
-        <v>0.035148</v>
+        <v>0.039653</v>
       </c>
       <c r="C521" t="n">
-        <v>0.630607</v>
+        <v>0.585831</v>
       </c>
     </row>
     <row r="522">
@@ -7200,10 +7200,10 @@
         </is>
       </c>
       <c r="B522" t="n">
-        <v>0.035942</v>
+        <v>0.039782</v>
       </c>
       <c r="C522" t="n">
-        <v>0.627968</v>
+        <v>0.583106</v>
       </c>
     </row>
     <row r="523">
@@ -7213,10 +7213,10 @@
         </is>
       </c>
       <c r="B523" t="n">
-        <v>0.036</v>
+        <v>0.04032</v>
       </c>
       <c r="C523" t="n">
-        <v>0.6253300000000001</v>
+        <v>0.580381</v>
       </c>
     </row>
     <row r="524">
@@ -7226,10 +7226,10 @@
         </is>
       </c>
       <c r="B524" t="n">
-        <v>0.036685</v>
+        <v>0.04091</v>
       </c>
       <c r="C524" t="n">
-        <v>0.622691</v>
+        <v>0.577657</v>
       </c>
     </row>
     <row r="525">
@@ -7239,10 +7239,10 @@
         </is>
       </c>
       <c r="B525" t="n">
-        <v>0.037036</v>
+        <v>0.041075</v>
       </c>
       <c r="C525" t="n">
-        <v>0.620053</v>
+        <v>0.574932</v>
       </c>
     </row>
     <row r="526">
@@ -7252,10 +7252,10 @@
         </is>
       </c>
       <c r="B526" t="n">
-        <v>0.037314</v>
+        <v>0.041331</v>
       </c>
       <c r="C526" t="n">
-        <v>0.617414</v>
+        <v>0.572207</v>
       </c>
     </row>
     <row r="527">
@@ -7265,10 +7265,10 @@
         </is>
       </c>
       <c r="B527" t="n">
-        <v>0.037796</v>
+        <v>0.041574</v>
       </c>
       <c r="C527" t="n">
-        <v>0.614776</v>
+        <v>0.569482</v>
       </c>
     </row>
     <row r="528">
@@ -7278,10 +7278,10 @@
         </is>
       </c>
       <c r="B528" t="n">
-        <v>0.038005</v>
+        <v>0.041575</v>
       </c>
       <c r="C528" t="n">
-        <v>0.612137</v>
+        <v>0.566757</v>
       </c>
     </row>
     <row r="529">
@@ -7291,10 +7291,10 @@
         </is>
       </c>
       <c r="B529" t="n">
-        <v>0.038265</v>
+        <v>0.041684</v>
       </c>
       <c r="C529" t="n">
-        <v>0.609499</v>
+        <v>0.564033</v>
       </c>
     </row>
     <row r="530">
@@ -7304,10 +7304,10 @@
         </is>
       </c>
       <c r="B530" t="n">
-        <v>0.038466</v>
+        <v>0.042129</v>
       </c>
       <c r="C530" t="n">
-        <v>0.60686</v>
+        <v>0.561308</v>
       </c>
     </row>
     <row r="531">
@@ -7317,10 +7317,10 @@
         </is>
       </c>
       <c r="B531" t="n">
-        <v>0.038821</v>
+        <v>0.042725</v>
       </c>
       <c r="C531" t="n">
-        <v>0.604222</v>
+        <v>0.5585830000000001</v>
       </c>
     </row>
     <row r="532">
@@ -7330,10 +7330,10 @@
         </is>
       </c>
       <c r="B532" t="n">
-        <v>0.039013</v>
+        <v>0.042904</v>
       </c>
       <c r="C532" t="n">
-        <v>0.601583</v>
+        <v>0.555858</v>
       </c>
     </row>
     <row r="533">
@@ -7343,10 +7343,10 @@
         </is>
       </c>
       <c r="B533" t="n">
-        <v>0.039064</v>
+        <v>0.042904</v>
       </c>
       <c r="C533" t="n">
-        <v>0.5989449999999999</v>
+        <v>0.553134</v>
       </c>
     </row>
     <row r="534">
@@ -7356,10 +7356,10 @@
         </is>
       </c>
       <c r="B534" t="n">
-        <v>0.039142</v>
+        <v>0.04317</v>
       </c>
       <c r="C534" t="n">
-        <v>0.596306</v>
+        <v>0.550409</v>
       </c>
     </row>
     <row r="535">
@@ -7369,10 +7369,10 @@
         </is>
       </c>
       <c r="B535" t="n">
-        <v>0.039338</v>
+        <v>0.043192</v>
       </c>
       <c r="C535" t="n">
-        <v>0.593668</v>
+        <v>0.5476839999999999</v>
       </c>
     </row>
     <row r="536">
@@ -7382,10 +7382,10 @@
         </is>
       </c>
       <c r="B536" t="n">
-        <v>0.039669</v>
+        <v>0.043237</v>
       </c>
       <c r="C536" t="n">
-        <v>0.591029</v>
+        <v>0.544959</v>
       </c>
     </row>
     <row r="537">
@@ -7395,10 +7395,10 @@
         </is>
       </c>
       <c r="B537" t="n">
-        <v>0.039782</v>
+        <v>0.043289</v>
       </c>
       <c r="C537" t="n">
-        <v>0.588391</v>
+        <v>0.542234</v>
       </c>
     </row>
     <row r="538">
@@ -7408,10 +7408,10 @@
         </is>
       </c>
       <c r="B538" t="n">
-        <v>0.039782</v>
+        <v>0.043753</v>
       </c>
       <c r="C538" t="n">
-        <v>0.5857520000000001</v>
+        <v>0.53951</v>
       </c>
     </row>
     <row r="539">
@@ -7421,10 +7421,10 @@
         </is>
       </c>
       <c r="B539" t="n">
-        <v>0.040328</v>
+        <v>0.043966</v>
       </c>
       <c r="C539" t="n">
-        <v>0.583113</v>
+        <v>0.536785</v>
       </c>
     </row>
     <row r="540">
@@ -7434,10 +7434,10 @@
         </is>
       </c>
       <c r="B540" t="n">
-        <v>0.041065</v>
+        <v>0.044188</v>
       </c>
       <c r="C540" t="n">
-        <v>0.580475</v>
+        <v>0.53406</v>
       </c>
     </row>
     <row r="541">
@@ -7447,10 +7447,10 @@
         </is>
       </c>
       <c r="B541" t="n">
-        <v>0.041301</v>
+        <v>0.044568</v>
       </c>
       <c r="C541" t="n">
-        <v>0.577836</v>
+        <v>0.531335</v>
       </c>
     </row>
     <row r="542">
@@ -7460,10 +7460,10 @@
         </is>
       </c>
       <c r="B542" t="n">
-        <v>0.041598</v>
+        <v>0.045008</v>
       </c>
       <c r="C542" t="n">
-        <v>0.575198</v>
+        <v>0.52861</v>
       </c>
     </row>
     <row r="543">
@@ -7473,10 +7473,10 @@
         </is>
       </c>
       <c r="B543" t="n">
-        <v>0.041685</v>
+        <v>0.045086</v>
       </c>
       <c r="C543" t="n">
-        <v>0.572559</v>
+        <v>0.525886</v>
       </c>
     </row>
     <row r="544">
@@ -7486,10 +7486,10 @@
         </is>
       </c>
       <c r="B544" t="n">
-        <v>0.041722</v>
+        <v>0.045407</v>
       </c>
       <c r="C544" t="n">
-        <v>0.569921</v>
+        <v>0.523161</v>
       </c>
     </row>
     <row r="545">
@@ -7499,10 +7499,10 @@
         </is>
       </c>
       <c r="B545" t="n">
-        <v>0.042018</v>
+        <v>0.045736</v>
       </c>
       <c r="C545" t="n">
-        <v>0.567282</v>
+        <v>0.520436</v>
       </c>
     </row>
     <row r="546">
@@ -7512,10 +7512,10 @@
         </is>
       </c>
       <c r="B546" t="n">
-        <v>0.042255</v>
+        <v>0.045738</v>
       </c>
       <c r="C546" t="n">
-        <v>0.564644</v>
+        <v>0.517711</v>
       </c>
     </row>
     <row r="547">
@@ -7525,10 +7525,10 @@
         </is>
       </c>
       <c r="B547" t="n">
-        <v>0.042901</v>
+        <v>0.046461</v>
       </c>
       <c r="C547" t="n">
-        <v>0.562005</v>
+        <v>0.5149860000000001</v>
       </c>
     </row>
     <row r="548">
@@ -7538,10 +7538,10 @@
         </is>
       </c>
       <c r="B548" t="n">
-        <v>0.042941</v>
+        <v>0.047411</v>
       </c>
       <c r="C548" t="n">
-        <v>0.5593669999999999</v>
+        <v>0.512262</v>
       </c>
     </row>
     <row r="549">
@@ -7551,10 +7551,10 @@
         </is>
       </c>
       <c r="B549" t="n">
-        <v>0.043133</v>
+        <v>0.047793</v>
       </c>
       <c r="C549" t="n">
-        <v>0.556728</v>
+        <v>0.509537</v>
       </c>
     </row>
     <row r="550">
@@ -7564,10 +7564,10 @@
         </is>
       </c>
       <c r="B550" t="n">
-        <v>0.043233</v>
+        <v>0.047894</v>
       </c>
       <c r="C550" t="n">
-        <v>0.55409</v>
+        <v>0.506812</v>
       </c>
     </row>
     <row r="551">
@@ -7577,10 +7577,10 @@
         </is>
       </c>
       <c r="B551" t="n">
-        <v>0.043273</v>
+        <v>0.047915</v>
       </c>
       <c r="C551" t="n">
-        <v>0.551451</v>
+        <v>0.504087</v>
       </c>
     </row>
     <row r="552">
@@ -7590,10 +7590,10 @@
         </is>
       </c>
       <c r="B552" t="n">
-        <v>0.043302</v>
+        <v>0.047994</v>
       </c>
       <c r="C552" t="n">
-        <v>0.548813</v>
+        <v>0.501362</v>
       </c>
     </row>
     <row r="553">
@@ -7603,10 +7603,10 @@
         </is>
       </c>
       <c r="B553" t="n">
-        <v>0.04334</v>
+        <v>0.048197</v>
       </c>
       <c r="C553" t="n">
-        <v>0.546174</v>
+        <v>0.498638</v>
       </c>
     </row>
     <row r="554">
@@ -7616,10 +7616,10 @@
         </is>
       </c>
       <c r="B554" t="n">
-        <v>0.043754</v>
+        <v>0.049639</v>
       </c>
       <c r="C554" t="n">
-        <v>0.543536</v>
+        <v>0.495913</v>
       </c>
     </row>
     <row r="555">
@@ -7629,10 +7629,10 @@
         </is>
       </c>
       <c r="B555" t="n">
-        <v>0.044035</v>
+        <v>0.05038</v>
       </c>
       <c r="C555" t="n">
-        <v>0.540897</v>
+        <v>0.493188</v>
       </c>
     </row>
     <row r="556">
@@ -7642,10 +7642,10 @@
         </is>
       </c>
       <c r="B556" t="n">
-        <v>0.044195</v>
+        <v>0.050796</v>
       </c>
       <c r="C556" t="n">
-        <v>0.538259</v>
+        <v>0.490463</v>
       </c>
     </row>
     <row r="557">
@@ -7655,10 +7655,10 @@
         </is>
       </c>
       <c r="B557" t="n">
-        <v>0.044566</v>
+        <v>0.050916</v>
       </c>
       <c r="C557" t="n">
-        <v>0.53562</v>
+        <v>0.487738</v>
       </c>
     </row>
     <row r="558">
@@ -7668,10 +7668,10 @@
         </is>
       </c>
       <c r="B558" t="n">
-        <v>0.045058</v>
+        <v>0.051789</v>
       </c>
       <c r="C558" t="n">
-        <v>0.532982</v>
+        <v>0.485014</v>
       </c>
     </row>
     <row r="559">
@@ -7681,10 +7681,10 @@
         </is>
       </c>
       <c r="B559" t="n">
-        <v>0.04509</v>
+        <v>0.052526</v>
       </c>
       <c r="C559" t="n">
-        <v>0.530343</v>
+        <v>0.482289</v>
       </c>
     </row>
     <row r="560">
@@ -7694,10 +7694,10 @@
         </is>
       </c>
       <c r="B560" t="n">
-        <v>0.045484</v>
+        <v>0.05261</v>
       </c>
       <c r="C560" t="n">
-        <v>0.527704</v>
+        <v>0.479564</v>
       </c>
     </row>
     <row r="561">
@@ -7707,10 +7707,10 @@
         </is>
       </c>
       <c r="B561" t="n">
-        <v>0.045773</v>
+        <v>0.052801</v>
       </c>
       <c r="C561" t="n">
-        <v>0.525066</v>
+        <v>0.476839</v>
       </c>
     </row>
     <row r="562">
@@ -7720,10 +7720,10 @@
         </is>
       </c>
       <c r="B562" t="n">
-        <v>0.045904</v>
+        <v>0.053339</v>
       </c>
       <c r="C562" t="n">
-        <v>0.522427</v>
+        <v>0.474114</v>
       </c>
     </row>
     <row r="563">
@@ -7733,10 +7733,10 @@
         </is>
       </c>
       <c r="B563" t="n">
-        <v>0.04667</v>
+        <v>0.053454</v>
       </c>
       <c r="C563" t="n">
-        <v>0.5197889999999999</v>
+        <v>0.47139</v>
       </c>
     </row>
     <row r="564">
@@ -7746,10 +7746,10 @@
         </is>
       </c>
       <c r="B564" t="n">
-        <v>0.047614</v>
+        <v>0.053866</v>
       </c>
       <c r="C564" t="n">
-        <v>0.51715</v>
+        <v>0.468665</v>
       </c>
     </row>
     <row r="565">
@@ -7759,10 +7759,10 @@
         </is>
       </c>
       <c r="B565" t="n">
-        <v>0.047796</v>
+        <v>0.054453</v>
       </c>
       <c r="C565" t="n">
-        <v>0.514512</v>
+        <v>0.46594</v>
       </c>
     </row>
     <row r="566">
@@ -7772,10 +7772,10 @@
         </is>
       </c>
       <c r="B566" t="n">
-        <v>0.04799</v>
+        <v>0.054461</v>
       </c>
       <c r="C566" t="n">
-        <v>0.511873</v>
+        <v>0.463215</v>
       </c>
     </row>
     <row r="567">
@@ -7785,10 +7785,10 @@
         </is>
       </c>
       <c r="B567" t="n">
-        <v>0.048249</v>
+        <v>0.055481</v>
       </c>
       <c r="C567" t="n">
-        <v>0.509235</v>
+        <v>0.46049</v>
       </c>
     </row>
     <row r="568">
@@ -7798,10 +7798,10 @@
         </is>
       </c>
       <c r="B568" t="n">
-        <v>0.048291</v>
+        <v>0.055692</v>
       </c>
       <c r="C568" t="n">
-        <v>0.506596</v>
+        <v>0.457766</v>
       </c>
     </row>
     <row r="569">
@@ -7811,10 +7811,10 @@
         </is>
       </c>
       <c r="B569" t="n">
-        <v>0.048355</v>
+        <v>0.055711</v>
       </c>
       <c r="C569" t="n">
-        <v>0.503958</v>
+        <v>0.455041</v>
       </c>
     </row>
     <row r="570">
@@ -7824,10 +7824,10 @@
         </is>
       </c>
       <c r="B570" t="n">
-        <v>0.048734</v>
+        <v>0.055749</v>
       </c>
       <c r="C570" t="n">
-        <v>0.501319</v>
+        <v>0.452316</v>
       </c>
     </row>
     <row r="571">
@@ -7837,10 +7837,10 @@
         </is>
       </c>
       <c r="B571" t="n">
-        <v>0.049271</v>
+        <v>0.056054</v>
       </c>
       <c r="C571" t="n">
-        <v>0.498681</v>
+        <v>0.449591</v>
       </c>
     </row>
     <row r="572">
@@ -7850,10 +7850,10 @@
         </is>
       </c>
       <c r="B572" t="n">
-        <v>0.04965</v>
+        <v>0.056274</v>
       </c>
       <c r="C572" t="n">
-        <v>0.496042</v>
+        <v>0.446866</v>
       </c>
     </row>
     <row r="573">
@@ -7863,10 +7863,10 @@
         </is>
       </c>
       <c r="B573" t="n">
-        <v>0.050794</v>
+        <v>0.057076</v>
       </c>
       <c r="C573" t="n">
-        <v>0.493404</v>
+        <v>0.444142</v>
       </c>
     </row>
     <row r="574">
@@ -7876,10 +7876,10 @@
         </is>
       </c>
       <c r="B574" t="n">
-        <v>0.051071</v>
+        <v>0.057273</v>
       </c>
       <c r="C574" t="n">
-        <v>0.490765</v>
+        <v>0.441417</v>
       </c>
     </row>
     <row r="575">
@@ -7889,10 +7889,10 @@
         </is>
       </c>
       <c r="B575" t="n">
-        <v>0.051169</v>
+        <v>0.057293</v>
       </c>
       <c r="C575" t="n">
-        <v>0.488127</v>
+        <v>0.438692</v>
       </c>
     </row>
     <row r="576">
@@ -7902,10 +7902,10 @@
         </is>
       </c>
       <c r="B576" t="n">
-        <v>0.051203</v>
+        <v>0.057472</v>
       </c>
       <c r="C576" t="n">
-        <v>0.485488</v>
+        <v>0.435967</v>
       </c>
     </row>
     <row r="577">
@@ -7915,10 +7915,10 @@
         </is>
       </c>
       <c r="B577" t="n">
-        <v>0.051866</v>
+        <v>0.059202</v>
       </c>
       <c r="C577" t="n">
-        <v>0.48285</v>
+        <v>0.433243</v>
       </c>
     </row>
     <row r="578">
@@ -7928,10 +7928,10 @@
         </is>
       </c>
       <c r="B578" t="n">
-        <v>0.0526</v>
+        <v>0.059884</v>
       </c>
       <c r="C578" t="n">
-        <v>0.480211</v>
+        <v>0.430518</v>
       </c>
     </row>
     <row r="579">
@@ -7941,10 +7941,10 @@
         </is>
       </c>
       <c r="B579" t="n">
-        <v>0.052799</v>
+        <v>0.059908</v>
       </c>
       <c r="C579" t="n">
-        <v>0.477573</v>
+        <v>0.427793</v>
       </c>
     </row>
     <row r="580">
@@ -7954,10 +7954,10 @@
         </is>
       </c>
       <c r="B580" t="n">
-        <v>0.053378</v>
+        <v>0.060333</v>
       </c>
       <c r="C580" t="n">
-        <v>0.474934</v>
+        <v>0.425068</v>
       </c>
     </row>
     <row r="581">
@@ -7967,10 +7967,10 @@
         </is>
       </c>
       <c r="B581" t="n">
-        <v>0.053381</v>
+        <v>0.062121</v>
       </c>
       <c r="C581" t="n">
-        <v>0.472296</v>
+        <v>0.422343</v>
       </c>
     </row>
     <row r="582">
@@ -7980,10 +7980,10 @@
         </is>
       </c>
       <c r="B582" t="n">
-        <v>0.053897</v>
+        <v>0.06227</v>
       </c>
       <c r="C582" t="n">
-        <v>0.469657</v>
+        <v>0.419619</v>
       </c>
     </row>
     <row r="583">
@@ -7993,10 +7993,10 @@
         </is>
       </c>
       <c r="B583" t="n">
-        <v>0.054048</v>
+        <v>0.06271</v>
       </c>
       <c r="C583" t="n">
-        <v>0.467018</v>
+        <v>0.416894</v>
       </c>
     </row>
     <row r="584">
@@ -8006,10 +8006,10 @@
         </is>
       </c>
       <c r="B584" t="n">
-        <v>0.054456</v>
+        <v>0.063384</v>
       </c>
       <c r="C584" t="n">
-        <v>0.46438</v>
+        <v>0.414169</v>
       </c>
     </row>
     <row r="585">
@@ -8019,10 +8019,10 @@
         </is>
       </c>
       <c r="B585" t="n">
-        <v>0.054529</v>
+        <v>0.06400500000000001</v>
       </c>
       <c r="C585" t="n">
-        <v>0.461741</v>
+        <v>0.411444</v>
       </c>
     </row>
     <row r="586">
@@ -8032,10 +8032,10 @@
         </is>
       </c>
       <c r="B586" t="n">
-        <v>0.055705</v>
+        <v>0.06585199999999999</v>
       </c>
       <c r="C586" t="n">
-        <v>0.459103</v>
+        <v>0.408719</v>
       </c>
     </row>
     <row r="587">
@@ -8045,10 +8045,10 @@
         </is>
       </c>
       <c r="B587" t="n">
-        <v>0.055741</v>
+        <v>0.06641900000000001</v>
       </c>
       <c r="C587" t="n">
-        <v>0.456464</v>
+        <v>0.405995</v>
       </c>
     </row>
     <row r="588">
@@ -8058,10 +8058,10 @@
         </is>
       </c>
       <c r="B588" t="n">
-        <v>0.0558</v>
+        <v>0.066428</v>
       </c>
       <c r="C588" t="n">
-        <v>0.453826</v>
+        <v>0.40327</v>
       </c>
     </row>
     <row r="589">
@@ -8071,10 +8071,10 @@
         </is>
       </c>
       <c r="B589" t="n">
-        <v>0.056032</v>
+        <v>0.06673800000000001</v>
       </c>
       <c r="C589" t="n">
-        <v>0.451187</v>
+        <v>0.400545</v>
       </c>
     </row>
     <row r="590">
@@ -8084,10 +8084,10 @@
         </is>
       </c>
       <c r="B590" t="n">
-        <v>0.056138</v>
+        <v>0.06682200000000001</v>
       </c>
       <c r="C590" t="n">
-        <v>0.448549</v>
+        <v>0.39782</v>
       </c>
     </row>
     <row r="591">
@@ -8097,10 +8097,10 @@
         </is>
       </c>
       <c r="B591" t="n">
-        <v>0.056156</v>
+        <v>0.066843</v>
       </c>
       <c r="C591" t="n">
-        <v>0.44591</v>
+        <v>0.395095</v>
       </c>
     </row>
     <row r="592">
@@ -8110,10 +8110,10 @@
         </is>
       </c>
       <c r="B592" t="n">
-        <v>0.05715</v>
+        <v>0.06707200000000001</v>
       </c>
       <c r="C592" t="n">
-        <v>0.443272</v>
+        <v>0.392371</v>
       </c>
     </row>
     <row r="593">
@@ -8123,10 +8123,10 @@
         </is>
       </c>
       <c r="B593" t="n">
-        <v>0.057287</v>
+        <v>0.067136</v>
       </c>
       <c r="C593" t="n">
-        <v>0.440633</v>
+        <v>0.389646</v>
       </c>
     </row>
     <row r="594">
@@ -8136,10 +8136,10 @@
         </is>
       </c>
       <c r="B594" t="n">
-        <v>0.057297</v>
+        <v>0.067621</v>
       </c>
       <c r="C594" t="n">
-        <v>0.437995</v>
+        <v>0.386921</v>
       </c>
     </row>
     <row r="595">
@@ -8149,10 +8149,10 @@
         </is>
       </c>
       <c r="B595" t="n">
-        <v>0.057479</v>
+        <v>0.06851599999999999</v>
       </c>
       <c r="C595" t="n">
-        <v>0.435356</v>
+        <v>0.384196</v>
       </c>
     </row>
     <row r="596">
@@ -8162,10 +8162,10 @@
         </is>
       </c>
       <c r="B596" t="n">
-        <v>0.05887</v>
+        <v>0.06858499999999999</v>
       </c>
       <c r="C596" t="n">
-        <v>0.432718</v>
+        <v>0.381471</v>
       </c>
     </row>
     <row r="597">
@@ -8175,10 +8175,10 @@
         </is>
       </c>
       <c r="B597" t="n">
-        <v>0.059453</v>
+        <v>0.068633</v>
       </c>
       <c r="C597" t="n">
-        <v>0.430079</v>
+        <v>0.378747</v>
       </c>
     </row>
     <row r="598">
@@ -8188,10 +8188,10 @@
         </is>
       </c>
       <c r="B598" t="n">
-        <v>0.059885</v>
+        <v>0.06868100000000001</v>
       </c>
       <c r="C598" t="n">
-        <v>0.427441</v>
+        <v>0.376022</v>
       </c>
     </row>
     <row r="599">
@@ -8201,10 +8201,10 @@
         </is>
       </c>
       <c r="B599" t="n">
-        <v>0.05991</v>
+        <v>0.068772</v>
       </c>
       <c r="C599" t="n">
-        <v>0.424802</v>
+        <v>0.373297</v>
       </c>
     </row>
     <row r="600">
@@ -8214,10 +8214,10 @@
         </is>
       </c>
       <c r="B600" t="n">
-        <v>0.060341</v>
+        <v>0.068797</v>
       </c>
       <c r="C600" t="n">
-        <v>0.422164</v>
+        <v>0.370572</v>
       </c>
     </row>
     <row r="601">
@@ -8227,10 +8227,10 @@
         </is>
       </c>
       <c r="B601" t="n">
-        <v>0.062207</v>
+        <v>0.06907099999999999</v>
       </c>
       <c r="C601" t="n">
-        <v>0.419525</v>
+        <v>0.367847</v>
       </c>
     </row>
     <row r="602">
@@ -8240,10 +8240,10 @@
         </is>
       </c>
       <c r="B602" t="n">
-        <v>0.06257799999999999</v>
+        <v>0.069635</v>
       </c>
       <c r="C602" t="n">
-        <v>0.416887</v>
+        <v>0.365123</v>
       </c>
     </row>
     <row r="603">
@@ -8253,10 +8253,10 @@
         </is>
       </c>
       <c r="B603" t="n">
-        <v>0.062733</v>
+        <v>0.069715</v>
       </c>
       <c r="C603" t="n">
-        <v>0.414248</v>
+        <v>0.362398</v>
       </c>
     </row>
     <row r="604">
@@ -8266,10 +8266,10 @@
         </is>
       </c>
       <c r="B604" t="n">
-        <v>0.06338199999999999</v>
+        <v>0.069913</v>
       </c>
       <c r="C604" t="n">
-        <v>0.411609</v>
+        <v>0.359673</v>
       </c>
     </row>
     <row r="605">
@@ -8279,10 +8279,10 @@
         </is>
       </c>
       <c r="B605" t="n">
-        <v>0.064098</v>
+        <v>0.07043000000000001</v>
       </c>
       <c r="C605" t="n">
-        <v>0.408971</v>
+        <v>0.356948</v>
       </c>
     </row>
     <row r="606">
@@ -8292,10 +8292,10 @@
         </is>
       </c>
       <c r="B606" t="n">
-        <v>0.06593</v>
+        <v>0.070589</v>
       </c>
       <c r="C606" t="n">
-        <v>0.406332</v>
+        <v>0.354223</v>
       </c>
     </row>
     <row r="607">
@@ -8305,10 +8305,10 @@
         </is>
       </c>
       <c r="B607" t="n">
-        <v>0.066326</v>
+        <v>0.070856</v>
       </c>
       <c r="C607" t="n">
-        <v>0.403694</v>
+        <v>0.351499</v>
       </c>
     </row>
     <row r="608">
@@ -8318,10 +8318,10 @@
         </is>
       </c>
       <c r="B608" t="n">
-        <v>0.066454</v>
+        <v>0.072675</v>
       </c>
       <c r="C608" t="n">
-        <v>0.401055</v>
+        <v>0.348774</v>
       </c>
     </row>
     <row r="609">
@@ -8331,10 +8331,10 @@
         </is>
       </c>
       <c r="B609" t="n">
-        <v>0.066579</v>
+        <v>0.073064</v>
       </c>
       <c r="C609" t="n">
-        <v>0.398417</v>
+        <v>0.346049</v>
       </c>
     </row>
     <row r="610">
@@ -8344,10 +8344,10 @@
         </is>
       </c>
       <c r="B610" t="n">
-        <v>0.066731</v>
+        <v>0.073578</v>
       </c>
       <c r="C610" t="n">
-        <v>0.395778</v>
+        <v>0.343324</v>
       </c>
     </row>
     <row r="611">
@@ -8357,10 +8357,10 @@
         </is>
       </c>
       <c r="B611" t="n">
-        <v>0.066917</v>
+        <v>0.07417799999999999</v>
       </c>
       <c r="C611" t="n">
-        <v>0.39314</v>
+        <v>0.340599</v>
       </c>
     </row>
     <row r="612">
@@ -8370,10 +8370,10 @@
         </is>
       </c>
       <c r="B612" t="n">
-        <v>0.067105</v>
+        <v>0.074201</v>
       </c>
       <c r="C612" t="n">
-        <v>0.390501</v>
+        <v>0.337875</v>
       </c>
     </row>
     <row r="613">
@@ -8383,10 +8383,10 @@
         </is>
       </c>
       <c r="B613" t="n">
-        <v>0.06712899999999999</v>
+        <v>0.074906</v>
       </c>
       <c r="C613" t="n">
-        <v>0.387863</v>
+        <v>0.33515</v>
       </c>
     </row>
     <row r="614">
@@ -8396,10 +8396,10 @@
         </is>
       </c>
       <c r="B614" t="n">
-        <v>0.06714100000000001</v>
+        <v>0.07517799999999999</v>
       </c>
       <c r="C614" t="n">
-        <v>0.385224</v>
+        <v>0.332425</v>
       </c>
     </row>
     <row r="615">
@@ -8409,10 +8409,10 @@
         </is>
       </c>
       <c r="B615" t="n">
-        <v>0.06783599999999999</v>
+        <v>0.07575900000000001</v>
       </c>
       <c r="C615" t="n">
-        <v>0.382586</v>
+        <v>0.3297</v>
       </c>
     </row>
     <row r="616">
@@ -8422,10 +8422,10 @@
         </is>
       </c>
       <c r="B616" t="n">
-        <v>0.06851500000000001</v>
+        <v>0.076026</v>
       </c>
       <c r="C616" t="n">
-        <v>0.379947</v>
+        <v>0.326975</v>
       </c>
     </row>
     <row r="617">
@@ -8435,10 +8435,10 @@
         </is>
       </c>
       <c r="B617" t="n">
-        <v>0.068607</v>
+        <v>0.076561</v>
       </c>
       <c r="C617" t="n">
-        <v>0.377309</v>
+        <v>0.324251</v>
       </c>
     </row>
     <row r="618">
@@ -8448,10 +8448,10 @@
         </is>
       </c>
       <c r="B618" t="n">
-        <v>0.06879</v>
+        <v>0.076671</v>
       </c>
       <c r="C618" t="n">
-        <v>0.37467</v>
+        <v>0.321526</v>
       </c>
     </row>
     <row r="619">
@@ -8461,10 +8461,10 @@
         </is>
       </c>
       <c r="B619" t="n">
-        <v>0.069324</v>
+        <v>0.07670399999999999</v>
       </c>
       <c r="C619" t="n">
-        <v>0.372032</v>
+        <v>0.318801</v>
       </c>
     </row>
     <row r="620">
@@ -8474,10 +8474,10 @@
         </is>
       </c>
       <c r="B620" t="n">
-        <v>0.06952999999999999</v>
+        <v>0.077157</v>
       </c>
       <c r="C620" t="n">
-        <v>0.369393</v>
+        <v>0.316076</v>
       </c>
     </row>
     <row r="621">
@@ -8487,10 +8487,10 @@
         </is>
       </c>
       <c r="B621" t="n">
-        <v>0.069549</v>
+        <v>0.077236</v>
       </c>
       <c r="C621" t="n">
-        <v>0.366755</v>
+        <v>0.313351</v>
       </c>
     </row>
     <row r="622">
@@ -8500,10 +8500,10 @@
         </is>
       </c>
       <c r="B622" t="n">
-        <v>0.069576</v>
+        <v>0.07775</v>
       </c>
       <c r="C622" t="n">
-        <v>0.364116</v>
+        <v>0.310627</v>
       </c>
     </row>
     <row r="623">
@@ -8513,10 +8513,10 @@
         </is>
       </c>
       <c r="B623" t="n">
-        <v>0.069808</v>
+        <v>0.078609</v>
       </c>
       <c r="C623" t="n">
-        <v>0.361478</v>
+        <v>0.307902</v>
       </c>
     </row>
     <row r="624">
@@ -8526,10 +8526,10 @@
         </is>
       </c>
       <c r="B624" t="n">
-        <v>0.069975</v>
+        <v>0.07861600000000001</v>
       </c>
       <c r="C624" t="n">
-        <v>0.358839</v>
+        <v>0.305177</v>
       </c>
     </row>
     <row r="625">
@@ -8539,10 +8539,10 @@
         </is>
       </c>
       <c r="B625" t="n">
-        <v>0.07097100000000001</v>
+        <v>0.078679</v>
       </c>
       <c r="C625" t="n">
-        <v>0.356201</v>
+        <v>0.302452</v>
       </c>
     </row>
     <row r="626">
@@ -8552,10 +8552,10 @@
         </is>
       </c>
       <c r="B626" t="n">
-        <v>0.07127</v>
+        <v>0.079042</v>
       </c>
       <c r="C626" t="n">
-        <v>0.353562</v>
+        <v>0.299728</v>
       </c>
     </row>
     <row r="627">
@@ -8565,10 +8565,10 @@
         </is>
       </c>
       <c r="B627" t="n">
-        <v>0.071532</v>
+        <v>0.079559</v>
       </c>
       <c r="C627" t="n">
-        <v>0.350923</v>
+        <v>0.297003</v>
       </c>
     </row>
     <row r="628">
@@ -8578,10 +8578,10 @@
         </is>
       </c>
       <c r="B628" t="n">
-        <v>0.071612</v>
+        <v>0.080522</v>
       </c>
       <c r="C628" t="n">
-        <v>0.348285</v>
+        <v>0.294278</v>
       </c>
     </row>
     <row r="629">
@@ -8591,10 +8591,10 @@
         </is>
       </c>
       <c r="B629" t="n">
-        <v>0.072672</v>
+        <v>0.08293200000000001</v>
       </c>
       <c r="C629" t="n">
-        <v>0.345646</v>
+        <v>0.291553</v>
       </c>
     </row>
     <row r="630">
@@ -8604,10 +8604,10 @@
         </is>
       </c>
       <c r="B630" t="n">
-        <v>0.07306699999999999</v>
+        <v>0.083263</v>
       </c>
       <c r="C630" t="n">
-        <v>0.343008</v>
+        <v>0.288828</v>
       </c>
     </row>
     <row r="631">
@@ -8617,10 +8617,10 @@
         </is>
       </c>
       <c r="B631" t="n">
-        <v>0.07411</v>
+        <v>0.083843</v>
       </c>
       <c r="C631" t="n">
-        <v>0.340369</v>
+        <v>0.286104</v>
       </c>
     </row>
     <row r="632">
@@ -8630,10 +8630,10 @@
         </is>
       </c>
       <c r="B632" t="n">
-        <v>0.074171</v>
+        <v>0.085711</v>
       </c>
       <c r="C632" t="n">
-        <v>0.337731</v>
+        <v>0.283379</v>
       </c>
     </row>
     <row r="633">
@@ -8643,10 +8643,10 @@
         </is>
       </c>
       <c r="B633" t="n">
-        <v>0.074208</v>
+        <v>0.085775</v>
       </c>
       <c r="C633" t="n">
-        <v>0.335092</v>
+        <v>0.280654</v>
       </c>
     </row>
     <row r="634">
@@ -8656,10 +8656,10 @@
         </is>
       </c>
       <c r="B634" t="n">
-        <v>0.075251</v>
+        <v>0.085794</v>
       </c>
       <c r="C634" t="n">
-        <v>0.332454</v>
+        <v>0.277929</v>
       </c>
     </row>
     <row r="635">
@@ -8669,10 +8669,10 @@
         </is>
       </c>
       <c r="B635" t="n">
-        <v>0.075336</v>
+        <v>0.08666500000000001</v>
       </c>
       <c r="C635" t="n">
-        <v>0.329815</v>
+        <v>0.275204</v>
       </c>
     </row>
     <row r="636">
@@ -8682,10 +8682,10 @@
         </is>
       </c>
       <c r="B636" t="n">
-        <v>0.075765</v>
+        <v>0.08805200000000001</v>
       </c>
       <c r="C636" t="n">
-        <v>0.327177</v>
+        <v>0.27248</v>
       </c>
     </row>
     <row r="637">
@@ -8695,10 +8695,10 @@
         </is>
       </c>
       <c r="B637" t="n">
-        <v>0.076504</v>
+        <v>0.08833100000000001</v>
       </c>
       <c r="C637" t="n">
-        <v>0.324538</v>
+        <v>0.269755</v>
       </c>
     </row>
     <row r="638">
@@ -8708,10 +8708,10 @@
         </is>
       </c>
       <c r="B638" t="n">
-        <v>0.07677100000000001</v>
+        <v>0.08873</v>
       </c>
       <c r="C638" t="n">
-        <v>0.3219</v>
+        <v>0.26703</v>
       </c>
     </row>
     <row r="639">
@@ -8721,10 +8721,10 @@
         </is>
       </c>
       <c r="B639" t="n">
-        <v>0.07700700000000001</v>
+        <v>0.08887100000000001</v>
       </c>
       <c r="C639" t="n">
-        <v>0.319261</v>
+        <v>0.264305</v>
       </c>
     </row>
     <row r="640">
@@ -8734,10 +8734,10 @@
         </is>
       </c>
       <c r="B640" t="n">
-        <v>0.077234</v>
+        <v>0.090004</v>
       </c>
       <c r="C640" t="n">
-        <v>0.316623</v>
+        <v>0.26158</v>
       </c>
     </row>
     <row r="641">
@@ -8747,10 +8747,10 @@
         </is>
       </c>
       <c r="B641" t="n">
-        <v>0.077345</v>
+        <v>0.090264</v>
       </c>
       <c r="C641" t="n">
-        <v>0.313984</v>
+        <v>0.258856</v>
       </c>
     </row>
     <row r="642">
@@ -8760,10 +8760,10 @@
         </is>
       </c>
       <c r="B642" t="n">
-        <v>0.077845</v>
+        <v>0.09088499999999999</v>
       </c>
       <c r="C642" t="n">
-        <v>0.311346</v>
+        <v>0.256131</v>
       </c>
     </row>
     <row r="643">
@@ -8773,10 +8773,10 @@
         </is>
       </c>
       <c r="B643" t="n">
-        <v>0.078677</v>
+        <v>0.091005</v>
       </c>
       <c r="C643" t="n">
-        <v>0.308707</v>
+        <v>0.253406</v>
       </c>
     </row>
     <row r="644">
@@ -8786,10 +8786,10 @@
         </is>
       </c>
       <c r="B644" t="n">
-        <v>0.078705</v>
+        <v>0.09166100000000001</v>
       </c>
       <c r="C644" t="n">
-        <v>0.306069</v>
+        <v>0.250681</v>
       </c>
     </row>
     <row r="645">
@@ -8799,10 +8799,10 @@
         </is>
       </c>
       <c r="B645" t="n">
-        <v>0.079037</v>
+        <v>0.09174599999999999</v>
       </c>
       <c r="C645" t="n">
-        <v>0.30343</v>
+        <v>0.247956</v>
       </c>
     </row>
     <row r="646">
@@ -8812,10 +8812,10 @@
         </is>
       </c>
       <c r="B646" t="n">
-        <v>0.07922700000000001</v>
+        <v>0.092386</v>
       </c>
       <c r="C646" t="n">
-        <v>0.300792</v>
+        <v>0.245232</v>
       </c>
     </row>
     <row r="647">
@@ -8825,10 +8825,10 @@
         </is>
       </c>
       <c r="B647" t="n">
-        <v>0.079641</v>
+        <v>0.092499</v>
       </c>
       <c r="C647" t="n">
-        <v>0.298153</v>
+        <v>0.242507</v>
       </c>
     </row>
     <row r="648">
@@ -8838,10 +8838,10 @@
         </is>
       </c>
       <c r="B648" t="n">
-        <v>0.07986</v>
+        <v>0.092678</v>
       </c>
       <c r="C648" t="n">
-        <v>0.295515</v>
+        <v>0.239782</v>
       </c>
     </row>
     <row r="649">
@@ -8851,10 +8851,10 @@
         </is>
       </c>
       <c r="B649" t="n">
-        <v>0.080543</v>
+        <v>0.093691</v>
       </c>
       <c r="C649" t="n">
-        <v>0.292876</v>
+        <v>0.237057</v>
       </c>
     </row>
     <row r="650">
@@ -8864,10 +8864,10 @@
         </is>
       </c>
       <c r="B650" t="n">
-        <v>0.08311300000000001</v>
+        <v>0.095345</v>
       </c>
       <c r="C650" t="n">
-        <v>0.290237</v>
+        <v>0.234332</v>
       </c>
     </row>
     <row r="651">
@@ -8877,10 +8877,10 @@
         </is>
       </c>
       <c r="B651" t="n">
-        <v>0.08384800000000001</v>
+        <v>0.095887</v>
       </c>
       <c r="C651" t="n">
-        <v>0.287599</v>
+        <v>0.231608</v>
       </c>
     </row>
     <row r="652">
@@ -8890,10 +8890,10 @@
         </is>
       </c>
       <c r="B652" t="n">
-        <v>0.08397399999999999</v>
+        <v>0.097552</v>
       </c>
       <c r="C652" t="n">
-        <v>0.28496</v>
+        <v>0.228883</v>
       </c>
     </row>
     <row r="653">
@@ -8903,10 +8903,10 @@
         </is>
       </c>
       <c r="B653" t="n">
-        <v>0.084896</v>
+        <v>0.09991</v>
       </c>
       <c r="C653" t="n">
-        <v>0.282322</v>
+        <v>0.226158</v>
       </c>
     </row>
     <row r="654">
@@ -8916,10 +8916,10 @@
         </is>
       </c>
       <c r="B654" t="n">
-        <v>0.085701</v>
+        <v>0.099982</v>
       </c>
       <c r="C654" t="n">
-        <v>0.279683</v>
+        <v>0.223433</v>
       </c>
     </row>
     <row r="655">
@@ -8929,10 +8929,10 @@
         </is>
       </c>
       <c r="B655" t="n">
-        <v>0.085898</v>
+        <v>0.100283</v>
       </c>
       <c r="C655" t="n">
-        <v>0.277045</v>
+        <v>0.220708</v>
       </c>
     </row>
     <row r="656">
@@ -8942,10 +8942,10 @@
         </is>
       </c>
       <c r="B656" t="n">
-        <v>0.085979</v>
+        <v>0.100487</v>
       </c>
       <c r="C656" t="n">
-        <v>0.274406</v>
+        <v>0.217984</v>
       </c>
     </row>
     <row r="657">
@@ -8955,10 +8955,10 @@
         </is>
       </c>
       <c r="B657" t="n">
-        <v>0.088051</v>
+        <v>0.100958</v>
       </c>
       <c r="C657" t="n">
-        <v>0.271768</v>
+        <v>0.215259</v>
       </c>
     </row>
     <row r="658">
@@ -8968,10 +8968,10 @@
         </is>
       </c>
       <c r="B658" t="n">
-        <v>0.08810800000000001</v>
+        <v>0.101654</v>
       </c>
       <c r="C658" t="n">
-        <v>0.269129</v>
+        <v>0.212534</v>
       </c>
     </row>
     <row r="659">
@@ -8981,10 +8981,10 @@
         </is>
       </c>
       <c r="B659" t="n">
-        <v>0.088436</v>
+        <v>0.101845</v>
       </c>
       <c r="C659" t="n">
-        <v>0.266491</v>
+        <v>0.209809</v>
       </c>
     </row>
     <row r="660">
@@ -8994,10 +8994,10 @@
         </is>
       </c>
       <c r="B660" t="n">
-        <v>0.088728</v>
+        <v>0.102475</v>
       </c>
       <c r="C660" t="n">
-        <v>0.263852</v>
+        <v>0.207084</v>
       </c>
     </row>
     <row r="661">
@@ -9007,10 +9007,10 @@
         </is>
       </c>
       <c r="B661" t="n">
-        <v>0.08988699999999999</v>
+        <v>0.102848</v>
       </c>
       <c r="C661" t="n">
-        <v>0.261214</v>
+        <v>0.20436</v>
       </c>
     </row>
     <row r="662">
@@ -9020,10 +9020,10 @@
         </is>
       </c>
       <c r="B662" t="n">
-        <v>0.090041</v>
+        <v>0.103193</v>
       </c>
       <c r="C662" t="n">
-        <v>0.258575</v>
+        <v>0.201635</v>
       </c>
     </row>
     <row r="663">
@@ -9033,10 +9033,10 @@
         </is>
       </c>
       <c r="B663" t="n">
-        <v>0.090479</v>
+        <v>0.10456</v>
       </c>
       <c r="C663" t="n">
-        <v>0.255937</v>
+        <v>0.19891</v>
       </c>
     </row>
     <row r="664">
@@ -9046,10 +9046,10 @@
         </is>
       </c>
       <c r="B664" t="n">
-        <v>0.091014</v>
+        <v>0.105442</v>
       </c>
       <c r="C664" t="n">
-        <v>0.253298</v>
+        <v>0.196185</v>
       </c>
     </row>
     <row r="665">
@@ -9059,10 +9059,10 @@
         </is>
       </c>
       <c r="B665" t="n">
-        <v>0.091387</v>
+        <v>0.106059</v>
       </c>
       <c r="C665" t="n">
-        <v>0.25066</v>
+        <v>0.19346</v>
       </c>
     </row>
     <row r="666">
@@ -9072,10 +9072,10 @@
         </is>
       </c>
       <c r="B666" t="n">
-        <v>0.091737</v>
+        <v>0.106893</v>
       </c>
       <c r="C666" t="n">
-        <v>0.248021</v>
+        <v>0.190736</v>
       </c>
     </row>
     <row r="667">
@@ -9085,10 +9085,10 @@
         </is>
       </c>
       <c r="B667" t="n">
-        <v>0.092594</v>
+        <v>0.108126</v>
       </c>
       <c r="C667" t="n">
-        <v>0.245383</v>
+        <v>0.188011</v>
       </c>
     </row>
     <row r="668">
@@ -9098,10 +9098,10 @@
         </is>
       </c>
       <c r="B668" t="n">
-        <v>0.092686</v>
+        <v>0.110051</v>
       </c>
       <c r="C668" t="n">
-        <v>0.242744</v>
+        <v>0.185286</v>
       </c>
     </row>
     <row r="669">
@@ -9111,10 +9111,10 @@
         </is>
       </c>
       <c r="B669" t="n">
-        <v>0.093033</v>
+        <v>0.110334</v>
       </c>
       <c r="C669" t="n">
-        <v>0.240106</v>
+        <v>0.182561</v>
       </c>
     </row>
     <row r="670">
@@ -9124,10 +9124,10 @@
         </is>
       </c>
       <c r="B670" t="n">
-        <v>0.093144</v>
+        <v>0.110424</v>
       </c>
       <c r="C670" t="n">
-        <v>0.237467</v>
+        <v>0.179837</v>
       </c>
     </row>
     <row r="671">
@@ -9137,10 +9137,10 @@
         </is>
       </c>
       <c r="B671" t="n">
-        <v>0.094732</v>
+        <v>0.110593</v>
       </c>
       <c r="C671" t="n">
-        <v>0.234828</v>
+        <v>0.177112</v>
       </c>
     </row>
     <row r="672">
@@ -9150,10 +9150,10 @@
         </is>
       </c>
       <c r="B672" t="n">
-        <v>0.09575500000000001</v>
+        <v>0.110749</v>
       </c>
       <c r="C672" t="n">
-        <v>0.23219</v>
+        <v>0.174387</v>
       </c>
     </row>
     <row r="673">
@@ -9163,10 +9163,10 @@
         </is>
       </c>
       <c r="B673" t="n">
-        <v>0.097229</v>
+        <v>0.113548</v>
       </c>
       <c r="C673" t="n">
-        <v>0.229551</v>
+        <v>0.171662</v>
       </c>
     </row>
     <row r="674">
@@ -9176,10 +9176,10 @@
         </is>
       </c>
       <c r="B674" t="n">
-        <v>0.09755800000000001</v>
+        <v>0.119003</v>
       </c>
       <c r="C674" t="n">
-        <v>0.226913</v>
+        <v>0.168937</v>
       </c>
     </row>
     <row r="675">
@@ -9189,10 +9189,10 @@
         </is>
       </c>
       <c r="B675" t="n">
-        <v>0.099901</v>
+        <v>0.120247</v>
       </c>
       <c r="C675" t="n">
-        <v>0.224274</v>
+        <v>0.166213</v>
       </c>
     </row>
     <row r="676">
@@ -9202,10 +9202,10 @@
         </is>
       </c>
       <c r="B676" t="n">
-        <v>0.09998899999999999</v>
+        <v>0.120637</v>
       </c>
       <c r="C676" t="n">
-        <v>0.221636</v>
+        <v>0.163488</v>
       </c>
     </row>
     <row r="677">
@@ -9215,10 +9215,10 @@
         </is>
       </c>
       <c r="B677" t="n">
-        <v>0.100401</v>
+        <v>0.120712</v>
       </c>
       <c r="C677" t="n">
-        <v>0.218997</v>
+        <v>0.160763</v>
       </c>
     </row>
     <row r="678">
@@ -9228,10 +9228,10 @@
         </is>
       </c>
       <c r="B678" t="n">
-        <v>0.100825</v>
+        <v>0.125157</v>
       </c>
       <c r="C678" t="n">
-        <v>0.216359</v>
+        <v>0.158038</v>
       </c>
     </row>
     <row r="679">
@@ -9241,10 +9241,10 @@
         </is>
       </c>
       <c r="B679" t="n">
-        <v>0.100983</v>
+        <v>0.126534</v>
       </c>
       <c r="C679" t="n">
-        <v>0.21372</v>
+        <v>0.155313</v>
       </c>
     </row>
     <row r="680">
@@ -9254,10 +9254,10 @@
         </is>
       </c>
       <c r="B680" t="n">
-        <v>0.102291</v>
+        <v>0.126949</v>
       </c>
       <c r="C680" t="n">
-        <v>0.211082</v>
+        <v>0.152589</v>
       </c>
     </row>
     <row r="681">
@@ -9267,10 +9267,10 @@
         </is>
       </c>
       <c r="B681" t="n">
-        <v>0.102562</v>
+        <v>0.127871</v>
       </c>
       <c r="C681" t="n">
-        <v>0.208443</v>
+        <v>0.149864</v>
       </c>
     </row>
     <row r="682">
@@ -9280,10 +9280,10 @@
         </is>
       </c>
       <c r="B682" t="n">
-        <v>0.102617</v>
+        <v>0.128016</v>
       </c>
       <c r="C682" t="n">
-        <v>0.205805</v>
+        <v>0.147139</v>
       </c>
     </row>
     <row r="683">
@@ -9293,10 +9293,10 @@
         </is>
       </c>
       <c r="B683" t="n">
-        <v>0.103035</v>
+        <v>0.128487</v>
       </c>
       <c r="C683" t="n">
-        <v>0.203166</v>
+        <v>0.144414</v>
       </c>
     </row>
     <row r="684">
@@ -9306,10 +9306,10 @@
         </is>
       </c>
       <c r="B684" t="n">
-        <v>0.103709</v>
+        <v>0.128585</v>
       </c>
       <c r="C684" t="n">
-        <v>0.200528</v>
+        <v>0.141689</v>
       </c>
     </row>
     <row r="685">
@@ -9319,10 +9319,10 @@
         </is>
       </c>
       <c r="B685" t="n">
-        <v>0.104654</v>
+        <v>0.128888</v>
       </c>
       <c r="C685" t="n">
-        <v>0.197889</v>
+        <v>0.138965</v>
       </c>
     </row>
     <row r="686">
@@ -9332,10 +9332,10 @@
         </is>
       </c>
       <c r="B686" t="n">
-        <v>0.106101</v>
+        <v>0.129008</v>
       </c>
       <c r="C686" t="n">
-        <v>0.195251</v>
+        <v>0.13624</v>
       </c>
     </row>
     <row r="687">
@@ -9345,10 +9345,10 @@
         </is>
       </c>
       <c r="B687" t="n">
-        <v>0.106919</v>
+        <v>0.130367</v>
       </c>
       <c r="C687" t="n">
-        <v>0.192612</v>
+        <v>0.133515</v>
       </c>
     </row>
     <row r="688">
@@ -9358,10 +9358,10 @@
         </is>
       </c>
       <c r="B688" t="n">
-        <v>0.107298</v>
+        <v>0.133153</v>
       </c>
       <c r="C688" t="n">
-        <v>0.189974</v>
+        <v>0.13079</v>
       </c>
     </row>
     <row r="689">
@@ -9371,10 +9371,10 @@
         </is>
       </c>
       <c r="B689" t="n">
-        <v>0.107991</v>
+        <v>0.133759</v>
       </c>
       <c r="C689" t="n">
-        <v>0.187335</v>
+        <v>0.128065</v>
       </c>
     </row>
     <row r="690">
@@ -9384,10 +9384,10 @@
         </is>
       </c>
       <c r="B690" t="n">
-        <v>0.108116</v>
+        <v>0.135512</v>
       </c>
       <c r="C690" t="n">
-        <v>0.184697</v>
+        <v>0.125341</v>
       </c>
     </row>
     <row r="691">
@@ -9397,10 +9397,10 @@
         </is>
       </c>
       <c r="B691" t="n">
-        <v>0.110368</v>
+        <v>0.135837</v>
       </c>
       <c r="C691" t="n">
-        <v>0.182058</v>
+        <v>0.122616</v>
       </c>
     </row>
     <row r="692">
@@ -9410,10 +9410,10 @@
         </is>
       </c>
       <c r="B692" t="n">
-        <v>0.110464</v>
+        <v>0.138829</v>
       </c>
       <c r="C692" t="n">
-        <v>0.17942</v>
+        <v>0.119891</v>
       </c>
     </row>
     <row r="693">
@@ -9423,10 +9423,10 @@
         </is>
       </c>
       <c r="B693" t="n">
-        <v>0.110582</v>
+        <v>0.139849</v>
       </c>
       <c r="C693" t="n">
-        <v>0.176781</v>
+        <v>0.117166</v>
       </c>
     </row>
     <row r="694">
@@ -9436,10 +9436,10 @@
         </is>
       </c>
       <c r="B694" t="n">
-        <v>0.110788</v>
+        <v>0.140268</v>
       </c>
       <c r="C694" t="n">
-        <v>0.174142</v>
+        <v>0.114441</v>
       </c>
     </row>
     <row r="695">
@@ -9449,10 +9449,10 @@
         </is>
       </c>
       <c r="B695" t="n">
-        <v>0.111261</v>
+        <v>0.140846</v>
       </c>
       <c r="C695" t="n">
-        <v>0.171504</v>
+        <v>0.111717</v>
       </c>
     </row>
     <row r="696">
@@ -9462,10 +9462,10 @@
         </is>
       </c>
       <c r="B696" t="n">
-        <v>0.113695</v>
+        <v>0.141462</v>
       </c>
       <c r="C696" t="n">
-        <v>0.168865</v>
+        <v>0.108992</v>
       </c>
     </row>
     <row r="697">
@@ -9475,10 +9475,10 @@
         </is>
       </c>
       <c r="B697" t="n">
-        <v>0.119004</v>
+        <v>0.142334</v>
       </c>
       <c r="C697" t="n">
-        <v>0.166227</v>
+        <v>0.106267</v>
       </c>
     </row>
     <row r="698">
@@ -9488,10 +9488,10 @@
         </is>
       </c>
       <c r="B698" t="n">
-        <v>0.120494</v>
+        <v>0.144657</v>
       </c>
       <c r="C698" t="n">
-        <v>0.163588</v>
+        <v>0.103542</v>
       </c>
     </row>
     <row r="699">
@@ -9501,10 +9501,10 @@
         </is>
       </c>
       <c r="B699" t="n">
-        <v>0.120636</v>
+        <v>0.14552</v>
       </c>
       <c r="C699" t="n">
-        <v>0.16095</v>
+        <v>0.100817</v>
       </c>
     </row>
     <row r="700">
@@ -9514,10 +9514,10 @@
         </is>
       </c>
       <c r="B700" t="n">
-        <v>0.120744</v>
+        <v>0.148262</v>
       </c>
       <c r="C700" t="n">
-        <v>0.158311</v>
+        <v>0.098093</v>
       </c>
     </row>
     <row r="701">
@@ -9527,10 +9527,10 @@
         </is>
       </c>
       <c r="B701" t="n">
-        <v>0.125547</v>
+        <v>0.152583</v>
       </c>
       <c r="C701" t="n">
-        <v>0.155673</v>
+        <v>0.09536799999999999</v>
       </c>
     </row>
     <row r="702">
@@ -9540,10 +9540,10 @@
         </is>
       </c>
       <c r="B702" t="n">
-        <v>0.126672</v>
+        <v>0.152671</v>
       </c>
       <c r="C702" t="n">
-        <v>0.153034</v>
+        <v>0.092643</v>
       </c>
     </row>
     <row r="703">
@@ -9553,10 +9553,10 @@
         </is>
       </c>
       <c r="B703" t="n">
-        <v>0.127382</v>
+        <v>0.153247</v>
       </c>
       <c r="C703" t="n">
-        <v>0.150396</v>
+        <v>0.089918</v>
       </c>
     </row>
     <row r="704">
@@ -9566,10 +9566,10 @@
         </is>
       </c>
       <c r="B704" t="n">
-        <v>0.128121</v>
+        <v>0.155248</v>
       </c>
       <c r="C704" t="n">
-        <v>0.147757</v>
+        <v>0.08719300000000001</v>
       </c>
     </row>
     <row r="705">
@@ -9579,10 +9579,10 @@
         </is>
       </c>
       <c r="B705" t="n">
-        <v>0.128368</v>
+        <v>0.15996</v>
       </c>
       <c r="C705" t="n">
-        <v>0.145119</v>
+        <v>0.084469</v>
       </c>
     </row>
     <row r="706">
@@ -9592,10 +9592,10 @@
         </is>
       </c>
       <c r="B706" t="n">
-        <v>0.128719</v>
+        <v>0.162434</v>
       </c>
       <c r="C706" t="n">
-        <v>0.14248</v>
+        <v>0.081744</v>
       </c>
     </row>
     <row r="707">
@@ -9605,10 +9605,10 @@
         </is>
       </c>
       <c r="B707" t="n">
-        <v>0.128994</v>
+        <v>0.167594</v>
       </c>
       <c r="C707" t="n">
-        <v>0.139842</v>
+        <v>0.07901900000000001</v>
       </c>
     </row>
     <row r="708">
@@ -9618,10 +9618,10 @@
         </is>
       </c>
       <c r="B708" t="n">
-        <v>0.129007</v>
+        <v>0.16785</v>
       </c>
       <c r="C708" t="n">
-        <v>0.137203</v>
+        <v>0.076294</v>
       </c>
     </row>
     <row r="709">
@@ -9631,10 +9631,10 @@
         </is>
       </c>
       <c r="B709" t="n">
-        <v>0.129223</v>
+        <v>0.168454</v>
       </c>
       <c r="C709" t="n">
-        <v>0.134565</v>
+        <v>0.073569</v>
       </c>
     </row>
     <row r="710">
@@ -9644,10 +9644,10 @@
         </is>
       </c>
       <c r="B710" t="n">
-        <v>0.129761</v>
+        <v>0.174682</v>
       </c>
       <c r="C710" t="n">
-        <v>0.131926</v>
+        <v>0.07084500000000001</v>
       </c>
     </row>
     <row r="711">
@@ -9657,10 +9657,10 @@
         </is>
       </c>
       <c r="B711" t="n">
-        <v>0.130485</v>
+        <v>0.175427</v>
       </c>
       <c r="C711" t="n">
-        <v>0.129288</v>
+        <v>0.06812</v>
       </c>
     </row>
     <row r="712">
@@ -9670,10 +9670,10 @@
         </is>
       </c>
       <c r="B712" t="n">
-        <v>0.13387</v>
+        <v>0.176559</v>
       </c>
       <c r="C712" t="n">
-        <v>0.126649</v>
+        <v>0.06539499999999999</v>
       </c>
     </row>
     <row r="713">
@@ -9683,10 +9683,10 @@
         </is>
       </c>
       <c r="B713" t="n">
-        <v>0.134734</v>
+        <v>0.177643</v>
       </c>
       <c r="C713" t="n">
-        <v>0.124011</v>
+        <v>0.06267</v>
       </c>
     </row>
     <row r="714">
@@ -9696,10 +9696,10 @@
         </is>
       </c>
       <c r="B714" t="n">
-        <v>0.135829</v>
+        <v>0.178705</v>
       </c>
       <c r="C714" t="n">
-        <v>0.121372</v>
+        <v>0.059946</v>
       </c>
     </row>
     <row r="715">
@@ -9709,10 +9709,10 @@
         </is>
       </c>
       <c r="B715" t="n">
-        <v>0.135981</v>
+        <v>0.180773</v>
       </c>
       <c r="C715" t="n">
-        <v>0.118734</v>
+        <v>0.057221</v>
       </c>
     </row>
     <row r="716">
@@ -9722,10 +9722,10 @@
         </is>
       </c>
       <c r="B716" t="n">
-        <v>0.138899</v>
+        <v>0.187018</v>
       </c>
       <c r="C716" t="n">
-        <v>0.116095</v>
+        <v>0.054496</v>
       </c>
     </row>
     <row r="717">
@@ -9735,10 +9735,10 @@
         </is>
       </c>
       <c r="B717" t="n">
-        <v>0.140277</v>
+        <v>0.188728</v>
       </c>
       <c r="C717" t="n">
-        <v>0.113456</v>
+        <v>0.051771</v>
       </c>
     </row>
     <row r="718">
@@ -9748,10 +9748,10 @@
         </is>
       </c>
       <c r="B718" t="n">
-        <v>0.141467</v>
+        <v>0.198577</v>
       </c>
       <c r="C718" t="n">
-        <v>0.110818</v>
+        <v>0.049046</v>
       </c>
     </row>
     <row r="719">
@@ -9761,10 +9761,10 @@
         </is>
       </c>
       <c r="B719" t="n">
-        <v>0.14148</v>
+        <v>0.202868</v>
       </c>
       <c r="C719" t="n">
-        <v>0.108179</v>
+        <v>0.046322</v>
       </c>
     </row>
     <row r="720">
@@ -9774,10 +9774,10 @@
         </is>
       </c>
       <c r="B720" t="n">
-        <v>0.142325</v>
+        <v>0.203404</v>
       </c>
       <c r="C720" t="n">
-        <v>0.105541</v>
+        <v>0.043597</v>
       </c>
     </row>
     <row r="721">
@@ -9787,10 +9787,10 @@
         </is>
       </c>
       <c r="B721" t="n">
-        <v>0.143001</v>
+        <v>0.209185</v>
       </c>
       <c r="C721" t="n">
-        <v>0.102902</v>
+        <v>0.040872</v>
       </c>
     </row>
     <row r="722">
@@ -9800,10 +9800,10 @@
         </is>
       </c>
       <c r="B722" t="n">
-        <v>0.145169</v>
+        <v>0.221322</v>
       </c>
       <c r="C722" t="n">
-        <v>0.100264</v>
+        <v>0.038147</v>
       </c>
     </row>
     <row r="723">
@@ -9813,10 +9813,10 @@
         </is>
       </c>
       <c r="B723" t="n">
-        <v>0.145655</v>
+        <v>0.227055</v>
       </c>
       <c r="C723" t="n">
-        <v>0.097625</v>
+        <v>0.035422</v>
       </c>
     </row>
     <row r="724">
@@ -9826,10 +9826,10 @@
         </is>
       </c>
       <c r="B724" t="n">
-        <v>0.149476</v>
+        <v>0.228311</v>
       </c>
       <c r="C724" t="n">
-        <v>0.094987</v>
+        <v>0.032698</v>
       </c>
     </row>
     <row r="725">
@@ -9839,10 +9839,10 @@
         </is>
       </c>
       <c r="B725" t="n">
-        <v>0.152893</v>
+        <v>0.231994</v>
       </c>
       <c r="C725" t="n">
-        <v>0.092348</v>
+        <v>0.029973</v>
       </c>
     </row>
     <row r="726">
@@ -9852,10 +9852,10 @@
         </is>
       </c>
       <c r="B726" t="n">
-        <v>0.153238</v>
+        <v>0.232268</v>
       </c>
       <c r="C726" t="n">
-        <v>0.08971</v>
+        <v>0.027248</v>
       </c>
     </row>
     <row r="727">
@@ -9865,10 +9865,10 @@
         </is>
       </c>
       <c r="B727" t="n">
-        <v>0.155304</v>
+        <v>0.234728</v>
       </c>
       <c r="C727" t="n">
-        <v>0.087071</v>
+        <v>0.024523</v>
       </c>
     </row>
     <row r="728">
@@ -9878,10 +9878,10 @@
         </is>
       </c>
       <c r="B728" t="n">
-        <v>0.156525</v>
+        <v>0.257967</v>
       </c>
       <c r="C728" t="n">
-        <v>0.08443299999999999</v>
+        <v>0.021798</v>
       </c>
     </row>
     <row r="729">
@@ -9891,10 +9891,10 @@
         </is>
       </c>
       <c r="B729" t="n">
-        <v>0.160131</v>
+        <v>0.264434</v>
       </c>
       <c r="C729" t="n">
-        <v>0.08179400000000001</v>
+        <v>0.019074</v>
       </c>
     </row>
     <row r="730">
@@ -9904,10 +9904,10 @@
         </is>
       </c>
       <c r="B730" t="n">
-        <v>0.162467</v>
+        <v>0.267543</v>
       </c>
       <c r="C730" t="n">
-        <v>0.079156</v>
+        <v>0.016349</v>
       </c>
     </row>
     <row r="731">
@@ -9917,10 +9917,10 @@
         </is>
       </c>
       <c r="B731" t="n">
-        <v>0.168054</v>
+        <v>0.295806</v>
       </c>
       <c r="C731" t="n">
-        <v>0.076517</v>
+        <v>0.013624</v>
       </c>
     </row>
     <row r="732">
@@ -9930,10 +9930,10 @@
         </is>
       </c>
       <c r="B732" t="n">
-        <v>0.168139</v>
+        <v>0.298916</v>
       </c>
       <c r="C732" t="n">
-        <v>0.073879</v>
+        <v>0.010899</v>
       </c>
     </row>
     <row r="733">
@@ -9943,10 +9943,10 @@
         </is>
       </c>
       <c r="B733" t="n">
-        <v>0.168438</v>
+        <v>0.336419</v>
       </c>
       <c r="C733" t="n">
-        <v>0.07124</v>
+        <v>0.008174000000000001</v>
       </c>
     </row>
     <row r="734">
@@ -9956,10 +9956,10 @@
         </is>
       </c>
       <c r="B734" t="n">
-        <v>0.175208</v>
+        <v>0.404876</v>
       </c>
       <c r="C734" t="n">
-        <v>0.068602</v>
+        <v>0.00545</v>
       </c>
     </row>
     <row r="735">
@@ -9969,322 +9969,10 @@
         </is>
       </c>
       <c r="B735" t="n">
-        <v>0.176597</v>
+        <v>0.475786</v>
       </c>
       <c r="C735" t="n">
-        <v>0.06596299999999999</v>
-      </c>
-    </row>
-    <row r="736">
-      <c r="A736" t="inlineStr">
-        <is>
-          <t>Adjusted target</t>
-        </is>
-      </c>
-      <c r="B736" t="n">
-        <v>0.176726</v>
-      </c>
-      <c r="C736" t="n">
-        <v>0.06332500000000001</v>
-      </c>
-    </row>
-    <row r="737">
-      <c r="A737" t="inlineStr">
-        <is>
-          <t>Adjusted target</t>
-        </is>
-      </c>
-      <c r="B737" t="n">
-        <v>0.17768</v>
-      </c>
-      <c r="C737" t="n">
-        <v>0.060686</v>
-      </c>
-    </row>
-    <row r="738">
-      <c r="A738" t="inlineStr">
-        <is>
-          <t>Adjusted target</t>
-        </is>
-      </c>
-      <c r="B738" t="n">
-        <v>0.179825</v>
-      </c>
-      <c r="C738" t="n">
-        <v>0.058047</v>
-      </c>
-    </row>
-    <row r="739">
-      <c r="A739" t="inlineStr">
-        <is>
-          <t>Adjusted target</t>
-        </is>
-      </c>
-      <c r="B739" t="n">
-        <v>0.181904</v>
-      </c>
-      <c r="C739" t="n">
-        <v>0.055409</v>
-      </c>
-    </row>
-    <row r="740">
-      <c r="A740" t="inlineStr">
-        <is>
-          <t>Adjusted target</t>
-        </is>
-      </c>
-      <c r="B740" t="n">
-        <v>0.18737</v>
-      </c>
-      <c r="C740" t="n">
-        <v>0.05277</v>
-      </c>
-    </row>
-    <row r="741">
-      <c r="A741" t="inlineStr">
-        <is>
-          <t>Adjusted target</t>
-        </is>
-      </c>
-      <c r="B741" t="n">
-        <v>0.190427</v>
-      </c>
-      <c r="C741" t="n">
-        <v>0.050132</v>
-      </c>
-    </row>
-    <row r="742">
-      <c r="A742" t="inlineStr">
-        <is>
-          <t>Adjusted target</t>
-        </is>
-      </c>
-      <c r="B742" t="n">
-        <v>0.199346</v>
-      </c>
-      <c r="C742" t="n">
-        <v>0.047493</v>
-      </c>
-    </row>
-    <row r="743">
-      <c r="A743" t="inlineStr">
-        <is>
-          <t>Adjusted target</t>
-        </is>
-      </c>
-      <c r="B743" t="n">
-        <v>0.204105</v>
-      </c>
-      <c r="C743" t="n">
-        <v>0.044855</v>
-      </c>
-    </row>
-    <row r="744">
-      <c r="A744" t="inlineStr">
-        <is>
-          <t>Adjusted target</t>
-        </is>
-      </c>
-      <c r="B744" t="n">
-        <v>0.204548</v>
-      </c>
-      <c r="C744" t="n">
-        <v>0.042216</v>
-      </c>
-    </row>
-    <row r="745">
-      <c r="A745" t="inlineStr">
-        <is>
-          <t>Adjusted target</t>
-        </is>
-      </c>
-      <c r="B745" t="n">
-        <v>0.209218</v>
-      </c>
-      <c r="C745" t="n">
-        <v>0.039578</v>
-      </c>
-    </row>
-    <row r="746">
-      <c r="A746" t="inlineStr">
-        <is>
-          <t>Adjusted target</t>
-        </is>
-      </c>
-      <c r="B746" t="n">
-        <v>0.223518</v>
-      </c>
-      <c r="C746" t="n">
-        <v>0.036939</v>
-      </c>
-    </row>
-    <row r="747">
-      <c r="A747" t="inlineStr">
-        <is>
-          <t>Adjusted target</t>
-        </is>
-      </c>
-      <c r="B747" t="n">
-        <v>0.227054</v>
-      </c>
-      <c r="C747" t="n">
-        <v>0.034301</v>
-      </c>
-    </row>
-    <row r="748">
-      <c r="A748" t="inlineStr">
-        <is>
-          <t>Adjusted target</t>
-        </is>
-      </c>
-      <c r="B748" t="n">
-        <v>0.233215</v>
-      </c>
-      <c r="C748" t="n">
-        <v>0.031662</v>
-      </c>
-    </row>
-    <row r="749">
-      <c r="A749" t="inlineStr">
-        <is>
-          <t>Adjusted target</t>
-        </is>
-      </c>
-      <c r="B749" t="n">
-        <v>0.234656</v>
-      </c>
-      <c r="C749" t="n">
-        <v>0.029024</v>
-      </c>
-    </row>
-    <row r="750">
-      <c r="A750" t="inlineStr">
-        <is>
-          <t>Adjusted target</t>
-        </is>
-      </c>
-      <c r="B750" t="n">
-        <v>0.234697</v>
-      </c>
-      <c r="C750" t="n">
-        <v>0.026385</v>
-      </c>
-    </row>
-    <row r="751">
-      <c r="A751" t="inlineStr">
-        <is>
-          <t>Adjusted target</t>
-        </is>
-      </c>
-      <c r="B751" t="n">
-        <v>0.237466</v>
-      </c>
-      <c r="C751" t="n">
-        <v>0.023747</v>
-      </c>
-    </row>
-    <row r="752">
-      <c r="A752" t="inlineStr">
-        <is>
-          <t>Adjusted target</t>
-        </is>
-      </c>
-      <c r="B752" t="n">
-        <v>0.258644</v>
-      </c>
-      <c r="C752" t="n">
-        <v>0.021108</v>
-      </c>
-    </row>
-    <row r="753">
-      <c r="A753" t="inlineStr">
-        <is>
-          <t>Adjusted target</t>
-        </is>
-      </c>
-      <c r="B753" t="n">
-        <v>0.265808</v>
-      </c>
-      <c r="C753" t="n">
-        <v>0.01847</v>
-      </c>
-    </row>
-    <row r="754">
-      <c r="A754" t="inlineStr">
-        <is>
-          <t>Adjusted target</t>
-        </is>
-      </c>
-      <c r="B754" t="n">
-        <v>0.26786</v>
-      </c>
-      <c r="C754" t="n">
-        <v>0.015831</v>
-      </c>
-    </row>
-    <row r="755">
-      <c r="A755" t="inlineStr">
-        <is>
-          <t>Adjusted target</t>
-        </is>
-      </c>
-      <c r="B755" t="n">
-        <v>0.295848</v>
-      </c>
-      <c r="C755" t="n">
-        <v>0.013193</v>
-      </c>
-    </row>
-    <row r="756">
-      <c r="A756" t="inlineStr">
-        <is>
-          <t>Adjusted target</t>
-        </is>
-      </c>
-      <c r="B756" t="n">
-        <v>0.30141</v>
-      </c>
-      <c r="C756" t="n">
-        <v>0.010554</v>
-      </c>
-    </row>
-    <row r="757">
-      <c r="A757" t="inlineStr">
-        <is>
-          <t>Adjusted target</t>
-        </is>
-      </c>
-      <c r="B757" t="n">
-        <v>0.336573</v>
-      </c>
-      <c r="C757" t="n">
-        <v>0.007915999999999999</v>
-      </c>
-    </row>
-    <row r="758">
-      <c r="A758" t="inlineStr">
-        <is>
-          <t>Adjusted target</t>
-        </is>
-      </c>
-      <c r="B758" t="n">
-        <v>0.406597</v>
-      </c>
-      <c r="C758" t="n">
-        <v>0.005277</v>
-      </c>
-    </row>
-    <row r="759">
-      <c r="A759" t="inlineStr">
-        <is>
-          <t>Adjusted target</t>
-        </is>
-      </c>
-      <c r="B759" t="n">
-        <v>0.476819</v>
-      </c>
-      <c r="C759" t="n">
-        <v>0.002639</v>
+        <v>0.002725</v>
       </c>
     </row>
   </sheetData>

--- a/vignettes/vignette-1/tail_exceedance_plot_data.xlsx
+++ b/vignettes/vignette-1/tail_exceedance_plot_data.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C735"/>
+  <dimension ref="A1:C737"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -456,7 +456,7 @@
         <v>9.3e-05</v>
       </c>
       <c r="C3" t="n">
-        <v>0.997275</v>
+        <v>0.997283</v>
       </c>
     </row>
     <row r="4">
@@ -469,7 +469,7 @@
         <v>0.000441</v>
       </c>
       <c r="C4" t="n">
-        <v>0.99455</v>
+        <v>0.994565</v>
       </c>
     </row>
     <row r="5">
@@ -482,7 +482,7 @@
         <v>0.000522</v>
       </c>
       <c r="C5" t="n">
-        <v>0.991826</v>
+        <v>0.991848</v>
       </c>
     </row>
     <row r="6">
@@ -495,7 +495,7 @@
         <v>0.001163</v>
       </c>
       <c r="C6" t="n">
-        <v>0.989101</v>
+        <v>0.98913</v>
       </c>
     </row>
     <row r="7">
@@ -508,7 +508,7 @@
         <v>0.001681</v>
       </c>
       <c r="C7" t="n">
-        <v>0.986376</v>
+        <v>0.986413</v>
       </c>
     </row>
     <row r="8">
@@ -521,7 +521,7 @@
         <v>0.00295</v>
       </c>
       <c r="C8" t="n">
-        <v>0.9836510000000001</v>
+        <v>0.983696</v>
       </c>
     </row>
     <row r="9">
@@ -534,7 +534,7 @@
         <v>0.002998</v>
       </c>
       <c r="C9" t="n">
-        <v>0.980926</v>
+        <v>0.980978</v>
       </c>
     </row>
     <row r="10">
@@ -547,7 +547,7 @@
         <v>0.003455</v>
       </c>
       <c r="C10" t="n">
-        <v>0.978202</v>
+        <v>0.978261</v>
       </c>
     </row>
     <row r="11">
@@ -560,7 +560,7 @@
         <v>0.003769</v>
       </c>
       <c r="C11" t="n">
-        <v>0.975477</v>
+        <v>0.975543</v>
       </c>
     </row>
     <row r="12">
@@ -573,7 +573,7 @@
         <v>0.003788</v>
       </c>
       <c r="C12" t="n">
-        <v>0.972752</v>
+        <v>0.972826</v>
       </c>
     </row>
     <row r="13">
@@ -583,10 +583,10 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>0.004717</v>
+        <v>0.004039</v>
       </c>
       <c r="C13" t="n">
-        <v>0.970027</v>
+        <v>0.970109</v>
       </c>
     </row>
     <row r="14">
@@ -596,10 +596,10 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>0.004779</v>
+        <v>0.004717</v>
       </c>
       <c r="C14" t="n">
-        <v>0.967302</v>
+        <v>0.967391</v>
       </c>
     </row>
     <row r="15">
@@ -609,10 +609,10 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>0.004912</v>
+        <v>0.004779</v>
       </c>
       <c r="C15" t="n">
-        <v>0.964578</v>
+        <v>0.964674</v>
       </c>
     </row>
     <row r="16">
@@ -622,10 +622,10 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>0.005429</v>
+        <v>0.004912</v>
       </c>
       <c r="C16" t="n">
-        <v>0.961853</v>
+        <v>0.961957</v>
       </c>
     </row>
     <row r="17">
@@ -635,10 +635,10 @@
         </is>
       </c>
       <c r="B17" t="n">
-        <v>0.005649</v>
+        <v>0.005429</v>
       </c>
       <c r="C17" t="n">
-        <v>0.959128</v>
+        <v>0.959239</v>
       </c>
     </row>
     <row r="18">
@@ -648,10 +648,10 @@
         </is>
       </c>
       <c r="B18" t="n">
-        <v>0.00593</v>
+        <v>0.005649</v>
       </c>
       <c r="C18" t="n">
-        <v>0.956403</v>
+        <v>0.956522</v>
       </c>
     </row>
     <row r="19">
@@ -661,10 +661,10 @@
         </is>
       </c>
       <c r="B19" t="n">
-        <v>0.006143</v>
+        <v>0.00593</v>
       </c>
       <c r="C19" t="n">
-        <v>0.953678</v>
+        <v>0.953804</v>
       </c>
     </row>
     <row r="20">
@@ -674,10 +674,10 @@
         </is>
       </c>
       <c r="B20" t="n">
-        <v>0.006394</v>
+        <v>0.006143</v>
       </c>
       <c r="C20" t="n">
-        <v>0.950954</v>
+        <v>0.951087</v>
       </c>
     </row>
     <row r="21">
@@ -687,10 +687,10 @@
         </is>
       </c>
       <c r="B21" t="n">
-        <v>0.006914</v>
+        <v>0.006394</v>
       </c>
       <c r="C21" t="n">
-        <v>0.948229</v>
+        <v>0.94837</v>
       </c>
     </row>
     <row r="22">
@@ -700,10 +700,10 @@
         </is>
       </c>
       <c r="B22" t="n">
-        <v>0.007419</v>
+        <v>0.006914</v>
       </c>
       <c r="C22" t="n">
-        <v>0.945504</v>
+        <v>0.945652</v>
       </c>
     </row>
     <row r="23">
@@ -713,10 +713,10 @@
         </is>
       </c>
       <c r="B23" t="n">
-        <v>0.007582</v>
+        <v>0.007419</v>
       </c>
       <c r="C23" t="n">
-        <v>0.942779</v>
+        <v>0.942935</v>
       </c>
     </row>
     <row r="24">
@@ -726,10 +726,10 @@
         </is>
       </c>
       <c r="B24" t="n">
-        <v>0.008029</v>
+        <v>0.007582</v>
       </c>
       <c r="C24" t="n">
-        <v>0.9400539999999999</v>
+        <v>0.940217</v>
       </c>
     </row>
     <row r="25">
@@ -739,10 +739,10 @@
         </is>
       </c>
       <c r="B25" t="n">
-        <v>0.008069</v>
+        <v>0.008029</v>
       </c>
       <c r="C25" t="n">
-        <v>0.93733</v>
+        <v>0.9375</v>
       </c>
     </row>
     <row r="26">
@@ -752,10 +752,10 @@
         </is>
       </c>
       <c r="B26" t="n">
-        <v>0.008173</v>
+        <v>0.008069</v>
       </c>
       <c r="C26" t="n">
-        <v>0.934605</v>
+        <v>0.934783</v>
       </c>
     </row>
     <row r="27">
@@ -765,10 +765,10 @@
         </is>
       </c>
       <c r="B27" t="n">
-        <v>0.008377000000000001</v>
+        <v>0.008173</v>
       </c>
       <c r="C27" t="n">
-        <v>0.93188</v>
+        <v>0.932065</v>
       </c>
     </row>
     <row r="28">
@@ -778,10 +778,10 @@
         </is>
       </c>
       <c r="B28" t="n">
-        <v>0.008593999999999999</v>
+        <v>0.008377000000000001</v>
       </c>
       <c r="C28" t="n">
-        <v>0.929155</v>
+        <v>0.929348</v>
       </c>
     </row>
     <row r="29">
@@ -791,10 +791,10 @@
         </is>
       </c>
       <c r="B29" t="n">
-        <v>0.008992</v>
+        <v>0.008593999999999999</v>
       </c>
       <c r="C29" t="n">
-        <v>0.926431</v>
+        <v>0.92663</v>
       </c>
     </row>
     <row r="30">
@@ -807,7 +807,7 @@
         <v>0.009165</v>
       </c>
       <c r="C30" t="n">
-        <v>0.923706</v>
+        <v>0.923913</v>
       </c>
     </row>
     <row r="31">
@@ -820,7 +820,7 @@
         <v>0.009428000000000001</v>
       </c>
       <c r="C31" t="n">
-        <v>0.920981</v>
+        <v>0.921196</v>
       </c>
     </row>
     <row r="32">
@@ -833,7 +833,7 @@
         <v>0.009578</v>
       </c>
       <c r="C32" t="n">
-        <v>0.918256</v>
+        <v>0.918478</v>
       </c>
     </row>
     <row r="33">
@@ -846,7 +846,7 @@
         <v>0.009774</v>
       </c>
       <c r="C33" t="n">
-        <v>0.915531</v>
+        <v>0.915761</v>
       </c>
     </row>
     <row r="34">
@@ -859,7 +859,7 @@
         <v>0.009811</v>
       </c>
       <c r="C34" t="n">
-        <v>0.912807</v>
+        <v>0.913043</v>
       </c>
     </row>
     <row r="35">
@@ -872,7 +872,7 @@
         <v>0.010226</v>
       </c>
       <c r="C35" t="n">
-        <v>0.9100819999999999</v>
+        <v>0.910326</v>
       </c>
     </row>
     <row r="36">
@@ -885,7 +885,7 @@
         <v>0.010518</v>
       </c>
       <c r="C36" t="n">
-        <v>0.907357</v>
+        <v>0.907609</v>
       </c>
     </row>
     <row r="37">
@@ -898,7 +898,7 @@
         <v>0.010943</v>
       </c>
       <c r="C37" t="n">
-        <v>0.904632</v>
+        <v>0.904891</v>
       </c>
     </row>
     <row r="38">
@@ -911,7 +911,7 @@
         <v>0.011156</v>
       </c>
       <c r="C38" t="n">
-        <v>0.901907</v>
+        <v>0.902174</v>
       </c>
     </row>
     <row r="39">
@@ -924,7 +924,7 @@
         <v>0.011326</v>
       </c>
       <c r="C39" t="n">
-        <v>0.899183</v>
+        <v>0.899457</v>
       </c>
     </row>
     <row r="40">
@@ -937,7 +937,7 @@
         <v>0.01145</v>
       </c>
       <c r="C40" t="n">
-        <v>0.896458</v>
+        <v>0.896739</v>
       </c>
     </row>
     <row r="41">
@@ -947,10 +947,10 @@
         </is>
       </c>
       <c r="B41" t="n">
-        <v>0.012002</v>
+        <v>0.012035</v>
       </c>
       <c r="C41" t="n">
-        <v>0.893733</v>
+        <v>0.894022</v>
       </c>
     </row>
     <row r="42">
@@ -960,10 +960,10 @@
         </is>
       </c>
       <c r="B42" t="n">
-        <v>0.012035</v>
+        <v>0.012747</v>
       </c>
       <c r="C42" t="n">
-        <v>0.891008</v>
+        <v>0.891304</v>
       </c>
     </row>
     <row r="43">
@@ -973,10 +973,10 @@
         </is>
       </c>
       <c r="B43" t="n">
-        <v>0.012747</v>
+        <v>0.012918</v>
       </c>
       <c r="C43" t="n">
-        <v>0.888283</v>
+        <v>0.888587</v>
       </c>
     </row>
     <row r="44">
@@ -986,10 +986,10 @@
         </is>
       </c>
       <c r="B44" t="n">
-        <v>0.012918</v>
+        <v>0.013202</v>
       </c>
       <c r="C44" t="n">
-        <v>0.885559</v>
+        <v>0.88587</v>
       </c>
     </row>
     <row r="45">
@@ -1002,7 +1002,7 @@
         <v>0.013714</v>
       </c>
       <c r="C45" t="n">
-        <v>0.882834</v>
+        <v>0.883152</v>
       </c>
     </row>
     <row r="46">
@@ -1015,7 +1015,7 @@
         <v>0.01393</v>
       </c>
       <c r="C46" t="n">
-        <v>0.880109</v>
+        <v>0.880435</v>
       </c>
     </row>
     <row r="47">
@@ -1028,7 +1028,7 @@
         <v>0.013971</v>
       </c>
       <c r="C47" t="n">
-        <v>0.8773840000000001</v>
+        <v>0.877717</v>
       </c>
     </row>
     <row r="48">
@@ -1041,7 +1041,7 @@
         <v>0.014018</v>
       </c>
       <c r="C48" t="n">
-        <v>0.874659</v>
+        <v>0.875</v>
       </c>
     </row>
     <row r="49">
@@ -1054,7 +1054,7 @@
         <v>0.01417</v>
       </c>
       <c r="C49" t="n">
-        <v>0.871935</v>
+        <v>0.872283</v>
       </c>
     </row>
     <row r="50">
@@ -1067,7 +1067,7 @@
         <v>0.014481</v>
       </c>
       <c r="C50" t="n">
-        <v>0.86921</v>
+        <v>0.869565</v>
       </c>
     </row>
     <row r="51">
@@ -1080,7 +1080,7 @@
         <v>0.014731</v>
       </c>
       <c r="C51" t="n">
-        <v>0.8664849999999999</v>
+        <v>0.866848</v>
       </c>
     </row>
     <row r="52">
@@ -1093,7 +1093,7 @@
         <v>0.014841</v>
       </c>
       <c r="C52" t="n">
-        <v>0.86376</v>
+        <v>0.86413</v>
       </c>
     </row>
     <row r="53">
@@ -1106,7 +1106,7 @@
         <v>0.01486</v>
       </c>
       <c r="C53" t="n">
-        <v>0.861035</v>
+        <v>0.861413</v>
       </c>
     </row>
     <row r="54">
@@ -1119,7 +1119,7 @@
         <v>0.015041</v>
       </c>
       <c r="C54" t="n">
-        <v>0.858311</v>
+        <v>0.858696</v>
       </c>
     </row>
     <row r="55">
@@ -1132,7 +1132,7 @@
         <v>0.015107</v>
       </c>
       <c r="C55" t="n">
-        <v>0.855586</v>
+        <v>0.855978</v>
       </c>
     </row>
     <row r="56">
@@ -1145,7 +1145,7 @@
         <v>0.015107</v>
       </c>
       <c r="C56" t="n">
-        <v>0.852861</v>
+        <v>0.853261</v>
       </c>
     </row>
     <row r="57">
@@ -1158,7 +1158,7 @@
         <v>0.015553</v>
       </c>
       <c r="C57" t="n">
-        <v>0.850136</v>
+        <v>0.850543</v>
       </c>
     </row>
     <row r="58">
@@ -1171,7 +1171,7 @@
         <v>0.016031</v>
       </c>
       <c r="C58" t="n">
-        <v>0.847411</v>
+        <v>0.847826</v>
       </c>
     </row>
     <row r="59">
@@ -1184,7 +1184,7 @@
         <v>0.016343</v>
       </c>
       <c r="C59" t="n">
-        <v>0.844687</v>
+        <v>0.845109</v>
       </c>
     </row>
     <row r="60">
@@ -1197,7 +1197,7 @@
         <v>0.016545</v>
       </c>
       <c r="C60" t="n">
-        <v>0.841962</v>
+        <v>0.842391</v>
       </c>
     </row>
     <row r="61">
@@ -1210,7 +1210,7 @@
         <v>0.017135</v>
       </c>
       <c r="C61" t="n">
-        <v>0.839237</v>
+        <v>0.839674</v>
       </c>
     </row>
     <row r="62">
@@ -1223,7 +1223,7 @@
         <v>0.017276</v>
       </c>
       <c r="C62" t="n">
-        <v>0.836512</v>
+        <v>0.836957</v>
       </c>
     </row>
     <row r="63">
@@ -1236,7 +1236,7 @@
         <v>0.017621</v>
       </c>
       <c r="C63" t="n">
-        <v>0.8337869999999999</v>
+        <v>0.834239</v>
       </c>
     </row>
     <row r="64">
@@ -1249,7 +1249,7 @@
         <v>0.017975</v>
       </c>
       <c r="C64" t="n">
-        <v>0.831063</v>
+        <v>0.831522</v>
       </c>
     </row>
     <row r="65">
@@ -1262,7 +1262,7 @@
         <v>0.018505</v>
       </c>
       <c r="C65" t="n">
-        <v>0.828338</v>
+        <v>0.828804</v>
       </c>
     </row>
     <row r="66">
@@ -1275,7 +1275,7 @@
         <v>0.018757</v>
       </c>
       <c r="C66" t="n">
-        <v>0.825613</v>
+        <v>0.826087</v>
       </c>
     </row>
     <row r="67">
@@ -1288,7 +1288,7 @@
         <v>0.018801</v>
       </c>
       <c r="C67" t="n">
-        <v>0.822888</v>
+        <v>0.82337</v>
       </c>
     </row>
     <row r="68">
@@ -1301,7 +1301,7 @@
         <v>0.018847</v>
       </c>
       <c r="C68" t="n">
-        <v>0.820163</v>
+        <v>0.820652</v>
       </c>
     </row>
     <row r="69">
@@ -1314,7 +1314,7 @@
         <v>0.018931</v>
       </c>
       <c r="C69" t="n">
-        <v>0.817439</v>
+        <v>0.817935</v>
       </c>
     </row>
     <row r="70">
@@ -1324,10 +1324,10 @@
         </is>
       </c>
       <c r="B70" t="n">
-        <v>0.019352</v>
+        <v>0.019288</v>
       </c>
       <c r="C70" t="n">
-        <v>0.814714</v>
+        <v>0.815217</v>
       </c>
     </row>
     <row r="71">
@@ -1337,10 +1337,10 @@
         </is>
       </c>
       <c r="B71" t="n">
-        <v>0.01962</v>
+        <v>0.019352</v>
       </c>
       <c r="C71" t="n">
-        <v>0.811989</v>
+        <v>0.8125</v>
       </c>
     </row>
     <row r="72">
@@ -1350,10 +1350,10 @@
         </is>
       </c>
       <c r="B72" t="n">
-        <v>0.019953</v>
+        <v>0.01962</v>
       </c>
       <c r="C72" t="n">
-        <v>0.809264</v>
+        <v>0.809783</v>
       </c>
     </row>
     <row r="73">
@@ -1363,10 +1363,10 @@
         </is>
       </c>
       <c r="B73" t="n">
-        <v>0.020186</v>
+        <v>0.019953</v>
       </c>
       <c r="C73" t="n">
-        <v>0.80654</v>
+        <v>0.807065</v>
       </c>
     </row>
     <row r="74">
@@ -1376,10 +1376,10 @@
         </is>
       </c>
       <c r="B74" t="n">
-        <v>0.020393</v>
+        <v>0.020186</v>
       </c>
       <c r="C74" t="n">
-        <v>0.8038149999999999</v>
+        <v>0.804348</v>
       </c>
     </row>
     <row r="75">
@@ -1389,10 +1389,10 @@
         </is>
       </c>
       <c r="B75" t="n">
-        <v>0.02048</v>
+        <v>0.020393</v>
       </c>
       <c r="C75" t="n">
-        <v>0.80109</v>
+        <v>0.80163</v>
       </c>
     </row>
     <row r="76">
@@ -1402,10 +1402,10 @@
         </is>
       </c>
       <c r="B76" t="n">
-        <v>0.021572</v>
+        <v>0.02048</v>
       </c>
       <c r="C76" t="n">
-        <v>0.798365</v>
+        <v>0.798913</v>
       </c>
     </row>
     <row r="77">
@@ -1415,10 +1415,10 @@
         </is>
       </c>
       <c r="B77" t="n">
-        <v>0.021604</v>
+        <v>0.021572</v>
       </c>
       <c r="C77" t="n">
-        <v>0.79564</v>
+        <v>0.796196</v>
       </c>
     </row>
     <row r="78">
@@ -1428,10 +1428,10 @@
         </is>
       </c>
       <c r="B78" t="n">
-        <v>0.021912</v>
+        <v>0.021604</v>
       </c>
       <c r="C78" t="n">
-        <v>0.792916</v>
+        <v>0.793478</v>
       </c>
     </row>
     <row r="79">
@@ -1441,10 +1441,10 @@
         </is>
       </c>
       <c r="B79" t="n">
-        <v>0.021918</v>
+        <v>0.021912</v>
       </c>
       <c r="C79" t="n">
-        <v>0.790191</v>
+        <v>0.790761</v>
       </c>
     </row>
     <row r="80">
@@ -1454,10 +1454,10 @@
         </is>
       </c>
       <c r="B80" t="n">
-        <v>0.021962</v>
+        <v>0.021918</v>
       </c>
       <c r="C80" t="n">
-        <v>0.787466</v>
+        <v>0.788043</v>
       </c>
     </row>
     <row r="81">
@@ -1467,10 +1467,10 @@
         </is>
       </c>
       <c r="B81" t="n">
-        <v>0.022008</v>
+        <v>0.021962</v>
       </c>
       <c r="C81" t="n">
-        <v>0.784741</v>
+        <v>0.785326</v>
       </c>
     </row>
     <row r="82">
@@ -1480,10 +1480,10 @@
         </is>
       </c>
       <c r="B82" t="n">
-        <v>0.022011</v>
+        <v>0.022008</v>
       </c>
       <c r="C82" t="n">
-        <v>0.782016</v>
+        <v>0.782609</v>
       </c>
     </row>
     <row r="83">
@@ -1493,10 +1493,10 @@
         </is>
       </c>
       <c r="B83" t="n">
-        <v>0.022121</v>
+        <v>0.022011</v>
       </c>
       <c r="C83" t="n">
-        <v>0.779292</v>
+        <v>0.779891</v>
       </c>
     </row>
     <row r="84">
@@ -1506,10 +1506,10 @@
         </is>
       </c>
       <c r="B84" t="n">
-        <v>0.022299</v>
+        <v>0.022121</v>
       </c>
       <c r="C84" t="n">
-        <v>0.776567</v>
+        <v>0.777174</v>
       </c>
     </row>
     <row r="85">
@@ -1519,10 +1519,10 @@
         </is>
       </c>
       <c r="B85" t="n">
-        <v>0.022324</v>
+        <v>0.022299</v>
       </c>
       <c r="C85" t="n">
-        <v>0.773842</v>
+        <v>0.774457</v>
       </c>
     </row>
     <row r="86">
@@ -1532,10 +1532,10 @@
         </is>
       </c>
       <c r="B86" t="n">
-        <v>0.022543</v>
+        <v>0.022324</v>
       </c>
       <c r="C86" t="n">
-        <v>0.7711170000000001</v>
+        <v>0.771739</v>
       </c>
     </row>
     <row r="87">
@@ -1545,10 +1545,10 @@
         </is>
       </c>
       <c r="B87" t="n">
-        <v>0.022891</v>
+        <v>0.022543</v>
       </c>
       <c r="C87" t="n">
-        <v>0.768392</v>
+        <v>0.769022</v>
       </c>
     </row>
     <row r="88">
@@ -1558,10 +1558,10 @@
         </is>
       </c>
       <c r="B88" t="n">
-        <v>0.023483</v>
+        <v>0.022891</v>
       </c>
       <c r="C88" t="n">
-        <v>0.765668</v>
+        <v>0.766304</v>
       </c>
     </row>
     <row r="89">
@@ -1571,10 +1571,10 @@
         </is>
       </c>
       <c r="B89" t="n">
-        <v>0.023843</v>
+        <v>0.023483</v>
       </c>
       <c r="C89" t="n">
-        <v>0.762943</v>
+        <v>0.763587</v>
       </c>
     </row>
     <row r="90">
@@ -1584,10 +1584,10 @@
         </is>
       </c>
       <c r="B90" t="n">
-        <v>0.023991</v>
+        <v>0.023843</v>
       </c>
       <c r="C90" t="n">
-        <v>0.7602179999999999</v>
+        <v>0.76087</v>
       </c>
     </row>
     <row r="91">
@@ -1597,10 +1597,10 @@
         </is>
       </c>
       <c r="B91" t="n">
-        <v>0.02408</v>
+        <v>0.023991</v>
       </c>
       <c r="C91" t="n">
-        <v>0.757493</v>
+        <v>0.758152</v>
       </c>
     </row>
     <row r="92">
@@ -1610,10 +1610,10 @@
         </is>
       </c>
       <c r="B92" t="n">
-        <v>0.024413</v>
+        <v>0.02408</v>
       </c>
       <c r="C92" t="n">
-        <v>0.754768</v>
+        <v>0.755435</v>
       </c>
     </row>
     <row r="93">
@@ -1623,10 +1623,10 @@
         </is>
       </c>
       <c r="B93" t="n">
-        <v>0.024896</v>
+        <v>0.024413</v>
       </c>
       <c r="C93" t="n">
-        <v>0.752044</v>
+        <v>0.752717</v>
       </c>
     </row>
     <row r="94">
@@ -1636,10 +1636,10 @@
         </is>
       </c>
       <c r="B94" t="n">
-        <v>0.025327</v>
+        <v>0.024896</v>
       </c>
       <c r="C94" t="n">
-        <v>0.749319</v>
+        <v>0.75</v>
       </c>
     </row>
     <row r="95">
@@ -1649,10 +1649,10 @@
         </is>
       </c>
       <c r="B95" t="n">
-        <v>0.025416</v>
+        <v>0.025327</v>
       </c>
       <c r="C95" t="n">
-        <v>0.746594</v>
+        <v>0.747283</v>
       </c>
     </row>
     <row r="96">
@@ -1662,10 +1662,10 @@
         </is>
       </c>
       <c r="B96" t="n">
-        <v>0.025544</v>
+        <v>0.025416</v>
       </c>
       <c r="C96" t="n">
-        <v>0.743869</v>
+        <v>0.744565</v>
       </c>
     </row>
     <row r="97">
@@ -1675,10 +1675,10 @@
         </is>
       </c>
       <c r="B97" t="n">
-        <v>0.025755</v>
+        <v>0.025544</v>
       </c>
       <c r="C97" t="n">
-        <v>0.741144</v>
+        <v>0.741848</v>
       </c>
     </row>
     <row r="98">
@@ -1688,10 +1688,10 @@
         </is>
       </c>
       <c r="B98" t="n">
-        <v>0.026545</v>
+        <v>0.025755</v>
       </c>
       <c r="C98" t="n">
-        <v>0.73842</v>
+        <v>0.73913</v>
       </c>
     </row>
     <row r="99">
@@ -1701,10 +1701,10 @@
         </is>
       </c>
       <c r="B99" t="n">
-        <v>0.027214</v>
+        <v>0.026545</v>
       </c>
       <c r="C99" t="n">
-        <v>0.735695</v>
+        <v>0.736413</v>
       </c>
     </row>
     <row r="100">
@@ -1714,10 +1714,10 @@
         </is>
       </c>
       <c r="B100" t="n">
-        <v>0.027321</v>
+        <v>0.027214</v>
       </c>
       <c r="C100" t="n">
-        <v>0.73297</v>
+        <v>0.733696</v>
       </c>
     </row>
     <row r="101">
@@ -1727,10 +1727,10 @@
         </is>
       </c>
       <c r="B101" t="n">
-        <v>0.027355</v>
+        <v>0.027321</v>
       </c>
       <c r="C101" t="n">
-        <v>0.730245</v>
+        <v>0.730978</v>
       </c>
     </row>
     <row r="102">
@@ -1740,10 +1740,10 @@
         </is>
       </c>
       <c r="B102" t="n">
-        <v>0.028098</v>
+        <v>0.027355</v>
       </c>
       <c r="C102" t="n">
-        <v>0.7275199999999999</v>
+        <v>0.728261</v>
       </c>
     </row>
     <row r="103">
@@ -1753,10 +1753,10 @@
         </is>
       </c>
       <c r="B103" t="n">
-        <v>0.028186</v>
+        <v>0.028098</v>
       </c>
       <c r="C103" t="n">
-        <v>0.724796</v>
+        <v>0.725543</v>
       </c>
     </row>
     <row r="104">
@@ -1766,10 +1766,10 @@
         </is>
       </c>
       <c r="B104" t="n">
-        <v>0.028375</v>
+        <v>0.028186</v>
       </c>
       <c r="C104" t="n">
-        <v>0.722071</v>
+        <v>0.722826</v>
       </c>
     </row>
     <row r="105">
@@ -1779,10 +1779,10 @@
         </is>
       </c>
       <c r="B105" t="n">
-        <v>0.029046</v>
+        <v>0.028375</v>
       </c>
       <c r="C105" t="n">
-        <v>0.719346</v>
+        <v>0.720109</v>
       </c>
     </row>
     <row r="106">
@@ -1792,10 +1792,10 @@
         </is>
       </c>
       <c r="B106" t="n">
-        <v>0.029071</v>
+        <v>0.029046</v>
       </c>
       <c r="C106" t="n">
-        <v>0.716621</v>
+        <v>0.717391</v>
       </c>
     </row>
     <row r="107">
@@ -1805,10 +1805,10 @@
         </is>
       </c>
       <c r="B107" t="n">
-        <v>0.029588</v>
+        <v>0.029071</v>
       </c>
       <c r="C107" t="n">
-        <v>0.713896</v>
+        <v>0.714674</v>
       </c>
     </row>
     <row r="108">
@@ -1818,10 +1818,10 @@
         </is>
       </c>
       <c r="B108" t="n">
-        <v>0.029854</v>
+        <v>0.029588</v>
       </c>
       <c r="C108" t="n">
-        <v>0.711172</v>
+        <v>0.711957</v>
       </c>
     </row>
     <row r="109">
@@ -1831,10 +1831,10 @@
         </is>
       </c>
       <c r="B109" t="n">
-        <v>0.030158</v>
+        <v>0.029854</v>
       </c>
       <c r="C109" t="n">
-        <v>0.708447</v>
+        <v>0.709239</v>
       </c>
     </row>
     <row r="110">
@@ -1844,10 +1844,10 @@
         </is>
       </c>
       <c r="B110" t="n">
-        <v>0.030201</v>
+        <v>0.030158</v>
       </c>
       <c r="C110" t="n">
-        <v>0.705722</v>
+        <v>0.706522</v>
       </c>
     </row>
     <row r="111">
@@ -1857,10 +1857,10 @@
         </is>
       </c>
       <c r="B111" t="n">
-        <v>0.03027</v>
+        <v>0.030201</v>
       </c>
       <c r="C111" t="n">
-        <v>0.702997</v>
+        <v>0.703804</v>
       </c>
     </row>
     <row r="112">
@@ -1870,10 +1870,10 @@
         </is>
       </c>
       <c r="B112" t="n">
-        <v>0.030697</v>
+        <v>0.03027</v>
       </c>
       <c r="C112" t="n">
-        <v>0.700272</v>
+        <v>0.701087</v>
       </c>
     </row>
     <row r="113">
@@ -1883,10 +1883,10 @@
         </is>
       </c>
       <c r="B113" t="n">
-        <v>0.030903</v>
+        <v>0.030697</v>
       </c>
       <c r="C113" t="n">
-        <v>0.6975479999999999</v>
+        <v>0.69837</v>
       </c>
     </row>
     <row r="114">
@@ -1896,10 +1896,10 @@
         </is>
       </c>
       <c r="B114" t="n">
-        <v>0.031116</v>
+        <v>0.030903</v>
       </c>
       <c r="C114" t="n">
-        <v>0.694823</v>
+        <v>0.695652</v>
       </c>
     </row>
     <row r="115">
@@ -1909,10 +1909,10 @@
         </is>
       </c>
       <c r="B115" t="n">
-        <v>0.031127</v>
+        <v>0.031116</v>
       </c>
       <c r="C115" t="n">
-        <v>0.692098</v>
+        <v>0.692935</v>
       </c>
     </row>
     <row r="116">
@@ -1922,10 +1922,10 @@
         </is>
       </c>
       <c r="B116" t="n">
-        <v>0.031327</v>
+        <v>0.031127</v>
       </c>
       <c r="C116" t="n">
-        <v>0.689373</v>
+        <v>0.690217</v>
       </c>
     </row>
     <row r="117">
@@ -1935,10 +1935,10 @@
         </is>
       </c>
       <c r="B117" t="n">
-        <v>0.031556</v>
+        <v>0.031327</v>
       </c>
       <c r="C117" t="n">
-        <v>0.686649</v>
+        <v>0.6875</v>
       </c>
     </row>
     <row r="118">
@@ -1948,10 +1948,10 @@
         </is>
       </c>
       <c r="B118" t="n">
-        <v>0.031969</v>
+        <v>0.031556</v>
       </c>
       <c r="C118" t="n">
-        <v>0.683924</v>
+        <v>0.684783</v>
       </c>
     </row>
     <row r="119">
@@ -1961,10 +1961,10 @@
         </is>
       </c>
       <c r="B119" t="n">
-        <v>0.032545</v>
+        <v>0.031969</v>
       </c>
       <c r="C119" t="n">
-        <v>0.681199</v>
+        <v>0.682065</v>
       </c>
     </row>
     <row r="120">
@@ -1974,10 +1974,10 @@
         </is>
       </c>
       <c r="B120" t="n">
-        <v>0.032827</v>
+        <v>0.032545</v>
       </c>
       <c r="C120" t="n">
-        <v>0.678474</v>
+        <v>0.679348</v>
       </c>
     </row>
     <row r="121">
@@ -1987,10 +1987,10 @@
         </is>
       </c>
       <c r="B121" t="n">
-        <v>0.033481</v>
+        <v>0.032827</v>
       </c>
       <c r="C121" t="n">
-        <v>0.675749</v>
+        <v>0.67663</v>
       </c>
     </row>
     <row r="122">
@@ -2000,10 +2000,10 @@
         </is>
       </c>
       <c r="B122" t="n">
-        <v>0.033774</v>
+        <v>0.033481</v>
       </c>
       <c r="C122" t="n">
-        <v>0.673025</v>
+        <v>0.673913</v>
       </c>
     </row>
     <row r="123">
@@ -2013,10 +2013,10 @@
         </is>
       </c>
       <c r="B123" t="n">
-        <v>0.033884</v>
+        <v>0.033774</v>
       </c>
       <c r="C123" t="n">
-        <v>0.6703</v>
+        <v>0.671196</v>
       </c>
     </row>
     <row r="124">
@@ -2026,10 +2026,10 @@
         </is>
       </c>
       <c r="B124" t="n">
-        <v>0.034047</v>
+        <v>0.033884</v>
       </c>
       <c r="C124" t="n">
-        <v>0.667575</v>
+        <v>0.668478</v>
       </c>
     </row>
     <row r="125">
@@ -2039,10 +2039,10 @@
         </is>
       </c>
       <c r="B125" t="n">
-        <v>0.034274</v>
+        <v>0.034047</v>
       </c>
       <c r="C125" t="n">
-        <v>0.6648500000000001</v>
+        <v>0.665761</v>
       </c>
     </row>
     <row r="126">
@@ -2052,10 +2052,10 @@
         </is>
       </c>
       <c r="B126" t="n">
-        <v>0.034573</v>
+        <v>0.034274</v>
       </c>
       <c r="C126" t="n">
-        <v>0.662125</v>
+        <v>0.663043</v>
       </c>
     </row>
     <row r="127">
@@ -2065,10 +2065,10 @@
         </is>
       </c>
       <c r="B127" t="n">
-        <v>0.035039</v>
+        <v>0.034573</v>
       </c>
       <c r="C127" t="n">
-        <v>0.659401</v>
+        <v>0.660326</v>
       </c>
     </row>
     <row r="128">
@@ -2078,10 +2078,10 @@
         </is>
       </c>
       <c r="B128" t="n">
-        <v>0.035117</v>
+        <v>0.035039</v>
       </c>
       <c r="C128" t="n">
-        <v>0.656676</v>
+        <v>0.657609</v>
       </c>
     </row>
     <row r="129">
@@ -2091,10 +2091,10 @@
         </is>
       </c>
       <c r="B129" t="n">
-        <v>0.035159</v>
+        <v>0.035117</v>
       </c>
       <c r="C129" t="n">
-        <v>0.6539509999999999</v>
+        <v>0.654891</v>
       </c>
     </row>
     <row r="130">
@@ -2104,10 +2104,10 @@
         </is>
       </c>
       <c r="B130" t="n">
-        <v>0.035374</v>
+        <v>0.035159</v>
       </c>
       <c r="C130" t="n">
-        <v>0.651226</v>
+        <v>0.652174</v>
       </c>
     </row>
     <row r="131">
@@ -2117,10 +2117,10 @@
         </is>
       </c>
       <c r="B131" t="n">
-        <v>0.035654</v>
+        <v>0.035374</v>
       </c>
       <c r="C131" t="n">
-        <v>0.648501</v>
+        <v>0.649457</v>
       </c>
     </row>
     <row r="132">
@@ -2130,10 +2130,10 @@
         </is>
       </c>
       <c r="B132" t="n">
-        <v>0.036</v>
+        <v>0.035654</v>
       </c>
       <c r="C132" t="n">
-        <v>0.645777</v>
+        <v>0.646739</v>
       </c>
     </row>
     <row r="133">
@@ -2143,10 +2143,10 @@
         </is>
       </c>
       <c r="B133" t="n">
-        <v>0.036242</v>
+        <v>0.036</v>
       </c>
       <c r="C133" t="n">
-        <v>0.643052</v>
+        <v>0.644022</v>
       </c>
     </row>
     <row r="134">
@@ -2156,10 +2156,10 @@
         </is>
       </c>
       <c r="B134" t="n">
-        <v>0.037307</v>
+        <v>0.036242</v>
       </c>
       <c r="C134" t="n">
-        <v>0.640327</v>
+        <v>0.641304</v>
       </c>
     </row>
     <row r="135">
@@ -2169,10 +2169,10 @@
         </is>
       </c>
       <c r="B135" t="n">
-        <v>0.037805</v>
+        <v>0.037307</v>
       </c>
       <c r="C135" t="n">
-        <v>0.637602</v>
+        <v>0.638587</v>
       </c>
     </row>
     <row r="136">
@@ -2182,10 +2182,10 @@
         </is>
       </c>
       <c r="B136" t="n">
-        <v>0.03815</v>
+        <v>0.037805</v>
       </c>
       <c r="C136" t="n">
-        <v>0.634877</v>
+        <v>0.63587</v>
       </c>
     </row>
     <row r="137">
@@ -2195,10 +2195,10 @@
         </is>
       </c>
       <c r="B137" t="n">
-        <v>0.038316</v>
+        <v>0.03815</v>
       </c>
       <c r="C137" t="n">
-        <v>0.632153</v>
+        <v>0.633152</v>
       </c>
     </row>
     <row r="138">
@@ -2208,10 +2208,10 @@
         </is>
       </c>
       <c r="B138" t="n">
-        <v>0.03876</v>
+        <v>0.038316</v>
       </c>
       <c r="C138" t="n">
-        <v>0.629428</v>
+        <v>0.630435</v>
       </c>
     </row>
     <row r="139">
@@ -2221,10 +2221,10 @@
         </is>
       </c>
       <c r="B139" t="n">
-        <v>0.039595</v>
+        <v>0.03876</v>
       </c>
       <c r="C139" t="n">
-        <v>0.626703</v>
+        <v>0.627717</v>
       </c>
     </row>
     <row r="140">
@@ -2234,10 +2234,10 @@
         </is>
       </c>
       <c r="B140" t="n">
-        <v>0.03982</v>
+        <v>0.039595</v>
       </c>
       <c r="C140" t="n">
-        <v>0.623978</v>
+        <v>0.625</v>
       </c>
     </row>
     <row r="141">
@@ -2247,10 +2247,10 @@
         </is>
       </c>
       <c r="B141" t="n">
-        <v>0.040867</v>
+        <v>0.03982</v>
       </c>
       <c r="C141" t="n">
-        <v>0.6212530000000001</v>
+        <v>0.622283</v>
       </c>
     </row>
     <row r="142">
@@ -2260,10 +2260,10 @@
         </is>
       </c>
       <c r="B142" t="n">
-        <v>0.040915</v>
+        <v>0.040867</v>
       </c>
       <c r="C142" t="n">
-        <v>0.618529</v>
+        <v>0.619565</v>
       </c>
     </row>
     <row r="143">
@@ -2273,10 +2273,10 @@
         </is>
       </c>
       <c r="B143" t="n">
-        <v>0.040931</v>
+        <v>0.040915</v>
       </c>
       <c r="C143" t="n">
-        <v>0.615804</v>
+        <v>0.616848</v>
       </c>
     </row>
     <row r="144">
@@ -2286,10 +2286,10 @@
         </is>
       </c>
       <c r="B144" t="n">
-        <v>0.040948</v>
+        <v>0.040931</v>
       </c>
       <c r="C144" t="n">
-        <v>0.613079</v>
+        <v>0.61413</v>
       </c>
     </row>
     <row r="145">
@@ -2299,10 +2299,10 @@
         </is>
       </c>
       <c r="B145" t="n">
-        <v>0.041019</v>
+        <v>0.040948</v>
       </c>
       <c r="C145" t="n">
-        <v>0.610354</v>
+        <v>0.611413</v>
       </c>
     </row>
     <row r="146">
@@ -2312,10 +2312,10 @@
         </is>
       </c>
       <c r="B146" t="n">
-        <v>0.041132</v>
+        <v>0.041019</v>
       </c>
       <c r="C146" t="n">
-        <v>0.607629</v>
+        <v>0.608696</v>
       </c>
     </row>
     <row r="147">
@@ -2325,10 +2325,10 @@
         </is>
       </c>
       <c r="B147" t="n">
-        <v>0.041331</v>
+        <v>0.041132</v>
       </c>
       <c r="C147" t="n">
-        <v>0.604905</v>
+        <v>0.605978</v>
       </c>
     </row>
     <row r="148">
@@ -2338,10 +2338,10 @@
         </is>
       </c>
       <c r="B148" t="n">
-        <v>0.041359</v>
+        <v>0.041331</v>
       </c>
       <c r="C148" t="n">
-        <v>0.60218</v>
+        <v>0.603261</v>
       </c>
     </row>
     <row r="149">
@@ -2351,10 +2351,10 @@
         </is>
       </c>
       <c r="B149" t="n">
-        <v>0.04197</v>
+        <v>0.041359</v>
       </c>
       <c r="C149" t="n">
-        <v>0.599455</v>
+        <v>0.600543</v>
       </c>
     </row>
     <row r="150">
@@ -2364,10 +2364,10 @@
         </is>
       </c>
       <c r="B150" t="n">
-        <v>0.042735</v>
+        <v>0.04197</v>
       </c>
       <c r="C150" t="n">
-        <v>0.59673</v>
+        <v>0.597826</v>
       </c>
     </row>
     <row r="151">
@@ -2377,10 +2377,10 @@
         </is>
       </c>
       <c r="B151" t="n">
-        <v>0.043468</v>
+        <v>0.042735</v>
       </c>
       <c r="C151" t="n">
-        <v>0.594005</v>
+        <v>0.595109</v>
       </c>
     </row>
     <row r="152">
@@ -2390,10 +2390,10 @@
         </is>
       </c>
       <c r="B152" t="n">
-        <v>0.044385</v>
+        <v>0.043468</v>
       </c>
       <c r="C152" t="n">
-        <v>0.5912809999999999</v>
+        <v>0.592391</v>
       </c>
     </row>
     <row r="153">
@@ -2403,10 +2403,10 @@
         </is>
       </c>
       <c r="B153" t="n">
-        <v>0.044556</v>
+        <v>0.044385</v>
       </c>
       <c r="C153" t="n">
-        <v>0.588556</v>
+        <v>0.589674</v>
       </c>
     </row>
     <row r="154">
@@ -2416,10 +2416,10 @@
         </is>
       </c>
       <c r="B154" t="n">
-        <v>0.044571</v>
+        <v>0.044556</v>
       </c>
       <c r="C154" t="n">
-        <v>0.585831</v>
+        <v>0.586957</v>
       </c>
     </row>
     <row r="155">
@@ -2429,10 +2429,10 @@
         </is>
       </c>
       <c r="B155" t="n">
-        <v>0.045962</v>
+        <v>0.044571</v>
       </c>
       <c r="C155" t="n">
-        <v>0.583106</v>
+        <v>0.584239</v>
       </c>
     </row>
     <row r="156">
@@ -2442,10 +2442,10 @@
         </is>
       </c>
       <c r="B156" t="n">
-        <v>0.046486</v>
+        <v>0.045962</v>
       </c>
       <c r="C156" t="n">
-        <v>0.580381</v>
+        <v>0.581522</v>
       </c>
     </row>
     <row r="157">
@@ -2455,10 +2455,10 @@
         </is>
       </c>
       <c r="B157" t="n">
-        <v>0.046763</v>
+        <v>0.046486</v>
       </c>
       <c r="C157" t="n">
-        <v>0.577657</v>
+        <v>0.578804</v>
       </c>
     </row>
     <row r="158">
@@ -2468,10 +2468,10 @@
         </is>
       </c>
       <c r="B158" t="n">
-        <v>0.046785</v>
+        <v>0.046763</v>
       </c>
       <c r="C158" t="n">
-        <v>0.574932</v>
+        <v>0.576087</v>
       </c>
     </row>
     <row r="159">
@@ -2481,10 +2481,10 @@
         </is>
       </c>
       <c r="B159" t="n">
-        <v>0.046943</v>
+        <v>0.046785</v>
       </c>
       <c r="C159" t="n">
-        <v>0.572207</v>
+        <v>0.57337</v>
       </c>
     </row>
     <row r="160">
@@ -2494,10 +2494,10 @@
         </is>
       </c>
       <c r="B160" t="n">
-        <v>0.047141</v>
+        <v>0.046943</v>
       </c>
       <c r="C160" t="n">
-        <v>0.569482</v>
+        <v>0.570652</v>
       </c>
     </row>
     <row r="161">
@@ -2507,10 +2507,10 @@
         </is>
       </c>
       <c r="B161" t="n">
-        <v>0.047421</v>
+        <v>0.047141</v>
       </c>
       <c r="C161" t="n">
-        <v>0.566757</v>
+        <v>0.567935</v>
       </c>
     </row>
     <row r="162">
@@ -2520,10 +2520,10 @@
         </is>
       </c>
       <c r="B162" t="n">
-        <v>0.048551</v>
+        <v>0.047327</v>
       </c>
       <c r="C162" t="n">
-        <v>0.564033</v>
+        <v>0.565217</v>
       </c>
     </row>
     <row r="163">
@@ -2533,10 +2533,10 @@
         </is>
       </c>
       <c r="B163" t="n">
-        <v>0.04906</v>
+        <v>0.047421</v>
       </c>
       <c r="C163" t="n">
-        <v>0.561308</v>
+        <v>0.5625</v>
       </c>
     </row>
     <row r="164">
@@ -2546,10 +2546,10 @@
         </is>
       </c>
       <c r="B164" t="n">
-        <v>0.049358</v>
+        <v>0.048551</v>
       </c>
       <c r="C164" t="n">
-        <v>0.5585830000000001</v>
+        <v>0.559783</v>
       </c>
     </row>
     <row r="165">
@@ -2559,10 +2559,10 @@
         </is>
       </c>
       <c r="B165" t="n">
-        <v>0.049478</v>
+        <v>0.04906</v>
       </c>
       <c r="C165" t="n">
-        <v>0.555858</v>
+        <v>0.557065</v>
       </c>
     </row>
     <row r="166">
@@ -2572,10 +2572,10 @@
         </is>
       </c>
       <c r="B166" t="n">
-        <v>0.049516</v>
+        <v>0.049358</v>
       </c>
       <c r="C166" t="n">
-        <v>0.553134</v>
+        <v>0.554348</v>
       </c>
     </row>
     <row r="167">
@@ -2585,10 +2585,10 @@
         </is>
       </c>
       <c r="B167" t="n">
-        <v>0.049728</v>
+        <v>0.049478</v>
       </c>
       <c r="C167" t="n">
-        <v>0.550409</v>
+        <v>0.55163</v>
       </c>
     </row>
     <row r="168">
@@ -2598,10 +2598,10 @@
         </is>
       </c>
       <c r="B168" t="n">
-        <v>0.049754</v>
+        <v>0.049516</v>
       </c>
       <c r="C168" t="n">
-        <v>0.5476839999999999</v>
+        <v>0.548913</v>
       </c>
     </row>
     <row r="169">
@@ -2611,10 +2611,10 @@
         </is>
       </c>
       <c r="B169" t="n">
-        <v>0.051151</v>
+        <v>0.049728</v>
       </c>
       <c r="C169" t="n">
-        <v>0.544959</v>
+        <v>0.546196</v>
       </c>
     </row>
     <row r="170">
@@ -2624,10 +2624,10 @@
         </is>
       </c>
       <c r="B170" t="n">
-        <v>0.051264</v>
+        <v>0.049754</v>
       </c>
       <c r="C170" t="n">
-        <v>0.542234</v>
+        <v>0.543478</v>
       </c>
     </row>
     <row r="171">
@@ -2637,10 +2637,10 @@
         </is>
       </c>
       <c r="B171" t="n">
-        <v>0.051423</v>
+        <v>0.051151</v>
       </c>
       <c r="C171" t="n">
-        <v>0.53951</v>
+        <v>0.540761</v>
       </c>
     </row>
     <row r="172">
@@ -2650,10 +2650,10 @@
         </is>
       </c>
       <c r="B172" t="n">
-        <v>0.051449</v>
+        <v>0.051264</v>
       </c>
       <c r="C172" t="n">
-        <v>0.536785</v>
+        <v>0.538043</v>
       </c>
     </row>
     <row r="173">
@@ -2663,10 +2663,10 @@
         </is>
       </c>
       <c r="B173" t="n">
-        <v>0.052376</v>
+        <v>0.051423</v>
       </c>
       <c r="C173" t="n">
-        <v>0.53406</v>
+        <v>0.535326</v>
       </c>
     </row>
     <row r="174">
@@ -2676,10 +2676,10 @@
         </is>
       </c>
       <c r="B174" t="n">
-        <v>0.052398</v>
+        <v>0.051449</v>
       </c>
       <c r="C174" t="n">
-        <v>0.531335</v>
+        <v>0.532609</v>
       </c>
     </row>
     <row r="175">
@@ -2689,10 +2689,10 @@
         </is>
       </c>
       <c r="B175" t="n">
-        <v>0.052682</v>
+        <v>0.052376</v>
       </c>
       <c r="C175" t="n">
-        <v>0.52861</v>
+        <v>0.529891</v>
       </c>
     </row>
     <row r="176">
@@ -2702,10 +2702,10 @@
         </is>
       </c>
       <c r="B176" t="n">
-        <v>0.052941</v>
+        <v>0.052398</v>
       </c>
       <c r="C176" t="n">
-        <v>0.525886</v>
+        <v>0.527174</v>
       </c>
     </row>
     <row r="177">
@@ -2715,10 +2715,10 @@
         </is>
       </c>
       <c r="B177" t="n">
-        <v>0.053227</v>
+        <v>0.052682</v>
       </c>
       <c r="C177" t="n">
-        <v>0.523161</v>
+        <v>0.524457</v>
       </c>
     </row>
     <row r="178">
@@ -2728,10 +2728,10 @@
         </is>
       </c>
       <c r="B178" t="n">
-        <v>0.053316</v>
+        <v>0.053227</v>
       </c>
       <c r="C178" t="n">
-        <v>0.520436</v>
+        <v>0.521739</v>
       </c>
     </row>
     <row r="179">
@@ -2741,10 +2741,10 @@
         </is>
       </c>
       <c r="B179" t="n">
-        <v>0.053555</v>
+        <v>0.053316</v>
       </c>
       <c r="C179" t="n">
-        <v>0.517711</v>
+        <v>0.519022</v>
       </c>
     </row>
     <row r="180">
@@ -2754,10 +2754,10 @@
         </is>
       </c>
       <c r="B180" t="n">
-        <v>0.05382</v>
+        <v>0.053555</v>
       </c>
       <c r="C180" t="n">
-        <v>0.5149860000000001</v>
+        <v>0.516304</v>
       </c>
     </row>
     <row r="181">
@@ -2767,10 +2767,10 @@
         </is>
       </c>
       <c r="B181" t="n">
-        <v>0.05439</v>
+        <v>0.05382</v>
       </c>
       <c r="C181" t="n">
-        <v>0.512262</v>
+        <v>0.513587</v>
       </c>
     </row>
     <row r="182">
@@ -2780,10 +2780,10 @@
         </is>
       </c>
       <c r="B182" t="n">
-        <v>0.054595</v>
+        <v>0.05439</v>
       </c>
       <c r="C182" t="n">
-        <v>0.509537</v>
+        <v>0.51087</v>
       </c>
     </row>
     <row r="183">
@@ -2793,10 +2793,10 @@
         </is>
       </c>
       <c r="B183" t="n">
-        <v>0.05496</v>
+        <v>0.054595</v>
       </c>
       <c r="C183" t="n">
-        <v>0.506812</v>
+        <v>0.508152</v>
       </c>
     </row>
     <row r="184">
@@ -2806,10 +2806,10 @@
         </is>
       </c>
       <c r="B184" t="n">
-        <v>0.0555</v>
+        <v>0.05496</v>
       </c>
       <c r="C184" t="n">
-        <v>0.504087</v>
+        <v>0.505435</v>
       </c>
     </row>
     <row r="185">
@@ -2819,10 +2819,10 @@
         </is>
       </c>
       <c r="B185" t="n">
-        <v>0.055621</v>
+        <v>0.0555</v>
       </c>
       <c r="C185" t="n">
-        <v>0.501362</v>
+        <v>0.502717</v>
       </c>
     </row>
     <row r="186">
@@ -2832,10 +2832,10 @@
         </is>
       </c>
       <c r="B186" t="n">
-        <v>0.055736</v>
+        <v>0.055621</v>
       </c>
       <c r="C186" t="n">
-        <v>0.498638</v>
+        <v>0.5</v>
       </c>
     </row>
     <row r="187">
@@ -2845,10 +2845,10 @@
         </is>
       </c>
       <c r="B187" t="n">
-        <v>0.056242</v>
+        <v>0.055736</v>
       </c>
       <c r="C187" t="n">
-        <v>0.495913</v>
+        <v>0.497283</v>
       </c>
     </row>
     <row r="188">
@@ -2858,10 +2858,10 @@
         </is>
       </c>
       <c r="B188" t="n">
-        <v>0.056433</v>
+        <v>0.056242</v>
       </c>
       <c r="C188" t="n">
-        <v>0.493188</v>
+        <v>0.494565</v>
       </c>
     </row>
     <row r="189">
@@ -2871,10 +2871,10 @@
         </is>
       </c>
       <c r="B189" t="n">
-        <v>0.056487</v>
+        <v>0.056433</v>
       </c>
       <c r="C189" t="n">
-        <v>0.490463</v>
+        <v>0.491848</v>
       </c>
     </row>
     <row r="190">
@@ -2884,10 +2884,10 @@
         </is>
       </c>
       <c r="B190" t="n">
-        <v>0.056702</v>
+        <v>0.056487</v>
       </c>
       <c r="C190" t="n">
-        <v>0.487738</v>
+        <v>0.48913</v>
       </c>
     </row>
     <row r="191">
@@ -2897,10 +2897,10 @@
         </is>
       </c>
       <c r="B191" t="n">
-        <v>0.056785</v>
+        <v>0.056702</v>
       </c>
       <c r="C191" t="n">
-        <v>0.485014</v>
+        <v>0.486413</v>
       </c>
     </row>
     <row r="192">
@@ -2910,10 +2910,10 @@
         </is>
       </c>
       <c r="B192" t="n">
-        <v>0.05854</v>
+        <v>0.056785</v>
       </c>
       <c r="C192" t="n">
-        <v>0.482289</v>
+        <v>0.483696</v>
       </c>
     </row>
     <row r="193">
@@ -2923,10 +2923,10 @@
         </is>
       </c>
       <c r="B193" t="n">
-        <v>0.058745</v>
+        <v>0.05854</v>
       </c>
       <c r="C193" t="n">
-        <v>0.479564</v>
+        <v>0.480978</v>
       </c>
     </row>
     <row r="194">
@@ -2936,10 +2936,10 @@
         </is>
       </c>
       <c r="B194" t="n">
-        <v>0.058836</v>
+        <v>0.058745</v>
       </c>
       <c r="C194" t="n">
-        <v>0.476839</v>
+        <v>0.478261</v>
       </c>
     </row>
     <row r="195">
@@ -2949,10 +2949,10 @@
         </is>
       </c>
       <c r="B195" t="n">
-        <v>0.059279</v>
+        <v>0.058836</v>
       </c>
       <c r="C195" t="n">
-        <v>0.474114</v>
+        <v>0.475543</v>
       </c>
     </row>
     <row r="196">
@@ -2962,10 +2962,10 @@
         </is>
       </c>
       <c r="B196" t="n">
-        <v>0.059367</v>
+        <v>0.059279</v>
       </c>
       <c r="C196" t="n">
-        <v>0.47139</v>
+        <v>0.472826</v>
       </c>
     </row>
     <row r="197">
@@ -2975,10 +2975,10 @@
         </is>
       </c>
       <c r="B197" t="n">
-        <v>0.059553</v>
+        <v>0.059367</v>
       </c>
       <c r="C197" t="n">
-        <v>0.468665</v>
+        <v>0.470109</v>
       </c>
     </row>
     <row r="198">
@@ -2988,10 +2988,10 @@
         </is>
       </c>
       <c r="B198" t="n">
-        <v>0.059579</v>
+        <v>0.059553</v>
       </c>
       <c r="C198" t="n">
-        <v>0.46594</v>
+        <v>0.467391</v>
       </c>
     </row>
     <row r="199">
@@ -3001,10 +3001,10 @@
         </is>
       </c>
       <c r="B199" t="n">
-        <v>0.060111</v>
+        <v>0.059579</v>
       </c>
       <c r="C199" t="n">
-        <v>0.463215</v>
+        <v>0.464674</v>
       </c>
     </row>
     <row r="200">
@@ -3014,10 +3014,10 @@
         </is>
       </c>
       <c r="B200" t="n">
-        <v>0.060827</v>
+        <v>0.060111</v>
       </c>
       <c r="C200" t="n">
-        <v>0.46049</v>
+        <v>0.461957</v>
       </c>
     </row>
     <row r="201">
@@ -3027,10 +3027,10 @@
         </is>
       </c>
       <c r="B201" t="n">
-        <v>0.060882</v>
+        <v>0.060827</v>
       </c>
       <c r="C201" t="n">
-        <v>0.457766</v>
+        <v>0.459239</v>
       </c>
     </row>
     <row r="202">
@@ -3040,10 +3040,10 @@
         </is>
       </c>
       <c r="B202" t="n">
-        <v>0.061712</v>
+        <v>0.060882</v>
       </c>
       <c r="C202" t="n">
-        <v>0.455041</v>
+        <v>0.456522</v>
       </c>
     </row>
     <row r="203">
@@ -3053,10 +3053,10 @@
         </is>
       </c>
       <c r="B203" t="n">
-        <v>0.061784</v>
+        <v>0.061437</v>
       </c>
       <c r="C203" t="n">
-        <v>0.452316</v>
+        <v>0.453804</v>
       </c>
     </row>
     <row r="204">
@@ -3066,10 +3066,10 @@
         </is>
       </c>
       <c r="B204" t="n">
-        <v>0.06179</v>
+        <v>0.061712</v>
       </c>
       <c r="C204" t="n">
-        <v>0.449591</v>
+        <v>0.451087</v>
       </c>
     </row>
     <row r="205">
@@ -3079,10 +3079,10 @@
         </is>
       </c>
       <c r="B205" t="n">
-        <v>0.061969</v>
+        <v>0.061784</v>
       </c>
       <c r="C205" t="n">
-        <v>0.446866</v>
+        <v>0.44837</v>
       </c>
     </row>
     <row r="206">
@@ -3092,10 +3092,10 @@
         </is>
       </c>
       <c r="B206" t="n">
-        <v>0.062129</v>
+        <v>0.06179</v>
       </c>
       <c r="C206" t="n">
-        <v>0.444142</v>
+        <v>0.445652</v>
       </c>
     </row>
     <row r="207">
@@ -3105,10 +3105,10 @@
         </is>
       </c>
       <c r="B207" t="n">
-        <v>0.062168</v>
+        <v>0.061969</v>
       </c>
       <c r="C207" t="n">
-        <v>0.441417</v>
+        <v>0.442935</v>
       </c>
     </row>
     <row r="208">
@@ -3118,10 +3118,10 @@
         </is>
       </c>
       <c r="B208" t="n">
-        <v>0.062246</v>
+        <v>0.062129</v>
       </c>
       <c r="C208" t="n">
-        <v>0.438692</v>
+        <v>0.440217</v>
       </c>
     </row>
     <row r="209">
@@ -3131,10 +3131,10 @@
         </is>
       </c>
       <c r="B209" t="n">
-        <v>0.06263299999999999</v>
+        <v>0.062168</v>
       </c>
       <c r="C209" t="n">
-        <v>0.435967</v>
+        <v>0.4375</v>
       </c>
     </row>
     <row r="210">
@@ -3144,10 +3144,10 @@
         </is>
       </c>
       <c r="B210" t="n">
-        <v>0.062844</v>
+        <v>0.062246</v>
       </c>
       <c r="C210" t="n">
-        <v>0.433243</v>
+        <v>0.434783</v>
       </c>
     </row>
     <row r="211">
@@ -3157,10 +3157,10 @@
         </is>
       </c>
       <c r="B211" t="n">
-        <v>0.063808</v>
+        <v>0.06263299999999999</v>
       </c>
       <c r="C211" t="n">
-        <v>0.430518</v>
+        <v>0.432065</v>
       </c>
     </row>
     <row r="212">
@@ -3170,10 +3170,10 @@
         </is>
       </c>
       <c r="B212" t="n">
-        <v>0.06464300000000001</v>
+        <v>0.062844</v>
       </c>
       <c r="C212" t="n">
-        <v>0.427793</v>
+        <v>0.429348</v>
       </c>
     </row>
     <row r="213">
@@ -3183,10 +3183,10 @@
         </is>
       </c>
       <c r="B213" t="n">
-        <v>0.064842</v>
+        <v>0.063808</v>
       </c>
       <c r="C213" t="n">
-        <v>0.425068</v>
+        <v>0.42663</v>
       </c>
     </row>
     <row r="214">
@@ -3196,10 +3196,10 @@
         </is>
       </c>
       <c r="B214" t="n">
-        <v>0.06555900000000001</v>
+        <v>0.06464300000000001</v>
       </c>
       <c r="C214" t="n">
-        <v>0.422343</v>
+        <v>0.423913</v>
       </c>
     </row>
     <row r="215">
@@ -3209,10 +3209,10 @@
         </is>
       </c>
       <c r="B215" t="n">
-        <v>0.067176</v>
+        <v>0.064842</v>
       </c>
       <c r="C215" t="n">
-        <v>0.419619</v>
+        <v>0.421196</v>
       </c>
     </row>
     <row r="216">
@@ -3222,10 +3222,10 @@
         </is>
       </c>
       <c r="B216" t="n">
-        <v>0.06736399999999999</v>
+        <v>0.06555900000000001</v>
       </c>
       <c r="C216" t="n">
-        <v>0.416894</v>
+        <v>0.418478</v>
       </c>
     </row>
     <row r="217">
@@ -3235,10 +3235,10 @@
         </is>
       </c>
       <c r="B217" t="n">
-        <v>0.067375</v>
+        <v>0.067176</v>
       </c>
       <c r="C217" t="n">
-        <v>0.414169</v>
+        <v>0.415761</v>
       </c>
     </row>
     <row r="218">
@@ -3248,10 +3248,10 @@
         </is>
       </c>
       <c r="B218" t="n">
-        <v>0.067555</v>
+        <v>0.06736399999999999</v>
       </c>
       <c r="C218" t="n">
-        <v>0.411444</v>
+        <v>0.413043</v>
       </c>
     </row>
     <row r="219">
@@ -3261,10 +3261,10 @@
         </is>
       </c>
       <c r="B219" t="n">
-        <v>0.067604</v>
+        <v>0.067375</v>
       </c>
       <c r="C219" t="n">
-        <v>0.408719</v>
+        <v>0.410326</v>
       </c>
     </row>
     <row r="220">
@@ -3274,10 +3274,10 @@
         </is>
       </c>
       <c r="B220" t="n">
-        <v>0.067644</v>
+        <v>0.067555</v>
       </c>
       <c r="C220" t="n">
-        <v>0.405995</v>
+        <v>0.407609</v>
       </c>
     </row>
     <row r="221">
@@ -3287,10 +3287,10 @@
         </is>
       </c>
       <c r="B221" t="n">
-        <v>0.068111</v>
+        <v>0.067604</v>
       </c>
       <c r="C221" t="n">
-        <v>0.40327</v>
+        <v>0.404891</v>
       </c>
     </row>
     <row r="222">
@@ -3300,10 +3300,10 @@
         </is>
       </c>
       <c r="B222" t="n">
-        <v>0.068601</v>
+        <v>0.067644</v>
       </c>
       <c r="C222" t="n">
-        <v>0.400545</v>
+        <v>0.402174</v>
       </c>
     </row>
     <row r="223">
@@ -3313,10 +3313,10 @@
         </is>
       </c>
       <c r="B223" t="n">
-        <v>0.068939</v>
+        <v>0.068111</v>
       </c>
       <c r="C223" t="n">
-        <v>0.39782</v>
+        <v>0.399457</v>
       </c>
     </row>
     <row r="224">
@@ -3326,10 +3326,10 @@
         </is>
       </c>
       <c r="B224" t="n">
-        <v>0.06909</v>
+        <v>0.068538</v>
       </c>
       <c r="C224" t="n">
-        <v>0.395095</v>
+        <v>0.396739</v>
       </c>
     </row>
     <row r="225">
@@ -3339,10 +3339,10 @@
         </is>
       </c>
       <c r="B225" t="n">
-        <v>0.069253</v>
+        <v>0.068601</v>
       </c>
       <c r="C225" t="n">
-        <v>0.392371</v>
+        <v>0.394022</v>
       </c>
     </row>
     <row r="226">
@@ -3352,10 +3352,10 @@
         </is>
       </c>
       <c r="B226" t="n">
-        <v>0.070214</v>
+        <v>0.068939</v>
       </c>
       <c r="C226" t="n">
-        <v>0.389646</v>
+        <v>0.391304</v>
       </c>
     </row>
     <row r="227">
@@ -3365,10 +3365,10 @@
         </is>
       </c>
       <c r="B227" t="n">
-        <v>0.070659</v>
+        <v>0.06909</v>
       </c>
       <c r="C227" t="n">
-        <v>0.386921</v>
+        <v>0.388587</v>
       </c>
     </row>
     <row r="228">
@@ -3378,10 +3378,10 @@
         </is>
       </c>
       <c r="B228" t="n">
-        <v>0.071394</v>
+        <v>0.069253</v>
       </c>
       <c r="C228" t="n">
-        <v>0.384196</v>
+        <v>0.38587</v>
       </c>
     </row>
     <row r="229">
@@ -3391,10 +3391,10 @@
         </is>
       </c>
       <c r="B229" t="n">
-        <v>0.072684</v>
+        <v>0.070214</v>
       </c>
       <c r="C229" t="n">
-        <v>0.381471</v>
+        <v>0.383152</v>
       </c>
     </row>
     <row r="230">
@@ -3404,10 +3404,10 @@
         </is>
       </c>
       <c r="B230" t="n">
-        <v>0.072744</v>
+        <v>0.070659</v>
       </c>
       <c r="C230" t="n">
-        <v>0.378747</v>
+        <v>0.380435</v>
       </c>
     </row>
     <row r="231">
@@ -3417,10 +3417,10 @@
         </is>
       </c>
       <c r="B231" t="n">
-        <v>0.07295599999999999</v>
+        <v>0.072684</v>
       </c>
       <c r="C231" t="n">
-        <v>0.376022</v>
+        <v>0.377717</v>
       </c>
     </row>
     <row r="232">
@@ -3430,10 +3430,10 @@
         </is>
       </c>
       <c r="B232" t="n">
-        <v>0.07331</v>
+        <v>0.072744</v>
       </c>
       <c r="C232" t="n">
-        <v>0.373297</v>
+        <v>0.375</v>
       </c>
     </row>
     <row r="233">
@@ -3443,10 +3443,10 @@
         </is>
       </c>
       <c r="B233" t="n">
-        <v>0.07380299999999999</v>
+        <v>0.07295599999999999</v>
       </c>
       <c r="C233" t="n">
-        <v>0.370572</v>
+        <v>0.372283</v>
       </c>
     </row>
     <row r="234">
@@ -3456,10 +3456,10 @@
         </is>
       </c>
       <c r="B234" t="n">
-        <v>0.07424799999999999</v>
+        <v>0.07331</v>
       </c>
       <c r="C234" t="n">
-        <v>0.367847</v>
+        <v>0.369565</v>
       </c>
     </row>
     <row r="235">
@@ -3469,10 +3469,10 @@
         </is>
       </c>
       <c r="B235" t="n">
-        <v>0.07437100000000001</v>
+        <v>0.07380299999999999</v>
       </c>
       <c r="C235" t="n">
-        <v>0.365123</v>
+        <v>0.366848</v>
       </c>
     </row>
     <row r="236">
@@ -3482,10 +3482,10 @@
         </is>
       </c>
       <c r="B236" t="n">
-        <v>0.075854</v>
+        <v>0.07424799999999999</v>
       </c>
       <c r="C236" t="n">
-        <v>0.362398</v>
+        <v>0.36413</v>
       </c>
     </row>
     <row r="237">
@@ -3495,10 +3495,10 @@
         </is>
       </c>
       <c r="B237" t="n">
-        <v>0.075876</v>
+        <v>0.07437100000000001</v>
       </c>
       <c r="C237" t="n">
-        <v>0.359673</v>
+        <v>0.361413</v>
       </c>
     </row>
     <row r="238">
@@ -3508,10 +3508,10 @@
         </is>
       </c>
       <c r="B238" t="n">
-        <v>0.076543</v>
+        <v>0.075854</v>
       </c>
       <c r="C238" t="n">
-        <v>0.356948</v>
+        <v>0.358696</v>
       </c>
     </row>
     <row r="239">
@@ -3521,10 +3521,10 @@
         </is>
       </c>
       <c r="B239" t="n">
-        <v>0.07708</v>
+        <v>0.075876</v>
       </c>
       <c r="C239" t="n">
-        <v>0.354223</v>
+        <v>0.355978</v>
       </c>
     </row>
     <row r="240">
@@ -3534,10 +3534,10 @@
         </is>
       </c>
       <c r="B240" t="n">
-        <v>0.077863</v>
+        <v>0.076543</v>
       </c>
       <c r="C240" t="n">
-        <v>0.351499</v>
+        <v>0.353261</v>
       </c>
     </row>
     <row r="241">
@@ -3547,10 +3547,10 @@
         </is>
       </c>
       <c r="B241" t="n">
-        <v>0.077912</v>
+        <v>0.07708</v>
       </c>
       <c r="C241" t="n">
-        <v>0.348774</v>
+        <v>0.350543</v>
       </c>
     </row>
     <row r="242">
@@ -3560,10 +3560,10 @@
         </is>
       </c>
       <c r="B242" t="n">
-        <v>0.078084</v>
+        <v>0.077863</v>
       </c>
       <c r="C242" t="n">
-        <v>0.346049</v>
+        <v>0.347826</v>
       </c>
     </row>
     <row r="243">
@@ -3573,10 +3573,10 @@
         </is>
       </c>
       <c r="B243" t="n">
-        <v>0.07921499999999999</v>
+        <v>0.077912</v>
       </c>
       <c r="C243" t="n">
-        <v>0.343324</v>
+        <v>0.345109</v>
       </c>
     </row>
     <row r="244">
@@ -3586,10 +3586,10 @@
         </is>
       </c>
       <c r="B244" t="n">
-        <v>0.08092199999999999</v>
+        <v>0.078084</v>
       </c>
       <c r="C244" t="n">
-        <v>0.340599</v>
+        <v>0.342391</v>
       </c>
     </row>
     <row r="245">
@@ -3599,10 +3599,10 @@
         </is>
       </c>
       <c r="B245" t="n">
-        <v>0.081607</v>
+        <v>0.07843899999999999</v>
       </c>
       <c r="C245" t="n">
-        <v>0.337875</v>
+        <v>0.339674</v>
       </c>
     </row>
     <row r="246">
@@ -3612,10 +3612,10 @@
         </is>
       </c>
       <c r="B246" t="n">
-        <v>0.081758</v>
+        <v>0.07921499999999999</v>
       </c>
       <c r="C246" t="n">
-        <v>0.33515</v>
+        <v>0.336957</v>
       </c>
     </row>
     <row r="247">
@@ -3625,10 +3625,10 @@
         </is>
       </c>
       <c r="B247" t="n">
-        <v>0.08192000000000001</v>
+        <v>0.08092199999999999</v>
       </c>
       <c r="C247" t="n">
-        <v>0.332425</v>
+        <v>0.334239</v>
       </c>
     </row>
     <row r="248">
@@ -3638,10 +3638,10 @@
         </is>
       </c>
       <c r="B248" t="n">
-        <v>0.082479</v>
+        <v>0.081607</v>
       </c>
       <c r="C248" t="n">
-        <v>0.3297</v>
+        <v>0.331522</v>
       </c>
     </row>
     <row r="249">
@@ -3651,10 +3651,10 @@
         </is>
       </c>
       <c r="B249" t="n">
-        <v>0.08254300000000001</v>
+        <v>0.081758</v>
       </c>
       <c r="C249" t="n">
-        <v>0.326975</v>
+        <v>0.328804</v>
       </c>
     </row>
     <row r="250">
@@ -3664,10 +3664,10 @@
         </is>
       </c>
       <c r="B250" t="n">
-        <v>0.082594</v>
+        <v>0.082479</v>
       </c>
       <c r="C250" t="n">
-        <v>0.324251</v>
+        <v>0.326087</v>
       </c>
     </row>
     <row r="251">
@@ -3677,10 +3677,10 @@
         </is>
       </c>
       <c r="B251" t="n">
-        <v>0.083297</v>
+        <v>0.08254300000000001</v>
       </c>
       <c r="C251" t="n">
-        <v>0.321526</v>
+        <v>0.32337</v>
       </c>
     </row>
     <row r="252">
@@ -3690,10 +3690,10 @@
         </is>
       </c>
       <c r="B252" t="n">
-        <v>0.083664</v>
+        <v>0.082594</v>
       </c>
       <c r="C252" t="n">
-        <v>0.318801</v>
+        <v>0.320652</v>
       </c>
     </row>
     <row r="253">
@@ -3703,10 +3703,10 @@
         </is>
       </c>
       <c r="B253" t="n">
-        <v>0.08384800000000001</v>
+        <v>0.083297</v>
       </c>
       <c r="C253" t="n">
-        <v>0.316076</v>
+        <v>0.317935</v>
       </c>
     </row>
     <row r="254">
@@ -3716,10 +3716,10 @@
         </is>
       </c>
       <c r="B254" t="n">
-        <v>0.084221</v>
+        <v>0.083664</v>
       </c>
       <c r="C254" t="n">
-        <v>0.313351</v>
+        <v>0.315217</v>
       </c>
     </row>
     <row r="255">
@@ -3729,10 +3729,10 @@
         </is>
       </c>
       <c r="B255" t="n">
-        <v>0.08483599999999999</v>
+        <v>0.08384800000000001</v>
       </c>
       <c r="C255" t="n">
-        <v>0.310627</v>
+        <v>0.3125</v>
       </c>
     </row>
     <row r="256">
@@ -3742,10 +3742,10 @@
         </is>
       </c>
       <c r="B256" t="n">
-        <v>0.08586199999999999</v>
+        <v>0.084221</v>
       </c>
       <c r="C256" t="n">
-        <v>0.307902</v>
+        <v>0.309783</v>
       </c>
     </row>
     <row r="257">
@@ -3755,10 +3755,10 @@
         </is>
       </c>
       <c r="B257" t="n">
-        <v>0.087156</v>
+        <v>0.08483599999999999</v>
       </c>
       <c r="C257" t="n">
-        <v>0.305177</v>
+        <v>0.307065</v>
       </c>
     </row>
     <row r="258">
@@ -3768,10 +3768,10 @@
         </is>
       </c>
       <c r="B258" t="n">
-        <v>0.08717999999999999</v>
+        <v>0.08586199999999999</v>
       </c>
       <c r="C258" t="n">
-        <v>0.302452</v>
+        <v>0.304348</v>
       </c>
     </row>
     <row r="259">
@@ -3781,10 +3781,10 @@
         </is>
       </c>
       <c r="B259" t="n">
-        <v>0.08820799999999999</v>
+        <v>0.087156</v>
       </c>
       <c r="C259" t="n">
-        <v>0.299728</v>
+        <v>0.30163</v>
       </c>
     </row>
     <row r="260">
@@ -3794,10 +3794,10 @@
         </is>
       </c>
       <c r="B260" t="n">
-        <v>0.088889</v>
+        <v>0.08717999999999999</v>
       </c>
       <c r="C260" t="n">
-        <v>0.297003</v>
+        <v>0.298913</v>
       </c>
     </row>
     <row r="261">
@@ -3807,10 +3807,10 @@
         </is>
       </c>
       <c r="B261" t="n">
-        <v>0.08917700000000001</v>
+        <v>0.08820799999999999</v>
       </c>
       <c r="C261" t="n">
-        <v>0.294278</v>
+        <v>0.296196</v>
       </c>
     </row>
     <row r="262">
@@ -3820,10 +3820,10 @@
         </is>
       </c>
       <c r="B262" t="n">
-        <v>0.089823</v>
+        <v>0.088889</v>
       </c>
       <c r="C262" t="n">
-        <v>0.291553</v>
+        <v>0.293478</v>
       </c>
     </row>
     <row r="263">
@@ -3833,10 +3833,10 @@
         </is>
       </c>
       <c r="B263" t="n">
-        <v>0.090265</v>
+        <v>0.08917700000000001</v>
       </c>
       <c r="C263" t="n">
-        <v>0.288828</v>
+        <v>0.290761</v>
       </c>
     </row>
     <row r="264">
@@ -3846,10 +3846,10 @@
         </is>
       </c>
       <c r="B264" t="n">
-        <v>0.090348</v>
+        <v>0.089823</v>
       </c>
       <c r="C264" t="n">
-        <v>0.286104</v>
+        <v>0.288043</v>
       </c>
     </row>
     <row r="265">
@@ -3859,10 +3859,10 @@
         </is>
       </c>
       <c r="B265" t="n">
-        <v>0.090809</v>
+        <v>0.090265</v>
       </c>
       <c r="C265" t="n">
-        <v>0.283379</v>
+        <v>0.285326</v>
       </c>
     </row>
     <row r="266">
@@ -3872,10 +3872,10 @@
         </is>
       </c>
       <c r="B266" t="n">
-        <v>0.091434</v>
+        <v>0.090348</v>
       </c>
       <c r="C266" t="n">
-        <v>0.280654</v>
+        <v>0.282609</v>
       </c>
     </row>
     <row r="267">
@@ -3885,10 +3885,10 @@
         </is>
       </c>
       <c r="B267" t="n">
-        <v>0.0929</v>
+        <v>0.090809</v>
       </c>
       <c r="C267" t="n">
-        <v>0.277929</v>
+        <v>0.279891</v>
       </c>
     </row>
     <row r="268">
@@ -3898,10 +3898,10 @@
         </is>
       </c>
       <c r="B268" t="n">
-        <v>0.097923</v>
+        <v>0.091434</v>
       </c>
       <c r="C268" t="n">
-        <v>0.275204</v>
+        <v>0.277174</v>
       </c>
     </row>
     <row r="269">
@@ -3911,10 +3911,10 @@
         </is>
       </c>
       <c r="B269" t="n">
-        <v>0.098237</v>
+        <v>0.0929</v>
       </c>
       <c r="C269" t="n">
-        <v>0.27248</v>
+        <v>0.274457</v>
       </c>
     </row>
     <row r="270">
@@ -3924,10 +3924,10 @@
         </is>
       </c>
       <c r="B270" t="n">
-        <v>0.09847400000000001</v>
+        <v>0.097923</v>
       </c>
       <c r="C270" t="n">
-        <v>0.269755</v>
+        <v>0.271739</v>
       </c>
     </row>
     <row r="271">
@@ -3937,10 +3937,10 @@
         </is>
       </c>
       <c r="B271" t="n">
-        <v>0.09907299999999999</v>
+        <v>0.098237</v>
       </c>
       <c r="C271" t="n">
-        <v>0.26703</v>
+        <v>0.269022</v>
       </c>
     </row>
     <row r="272">
@@ -3950,10 +3950,10 @@
         </is>
       </c>
       <c r="B272" t="n">
-        <v>0.09943399999999999</v>
+        <v>0.09847400000000001</v>
       </c>
       <c r="C272" t="n">
-        <v>0.264305</v>
+        <v>0.266304</v>
       </c>
     </row>
     <row r="273">
@@ -3963,10 +3963,10 @@
         </is>
       </c>
       <c r="B273" t="n">
-        <v>0.100571</v>
+        <v>0.09907299999999999</v>
       </c>
       <c r="C273" t="n">
-        <v>0.26158</v>
+        <v>0.263587</v>
       </c>
     </row>
     <row r="274">
@@ -3976,10 +3976,10 @@
         </is>
       </c>
       <c r="B274" t="n">
-        <v>0.101335</v>
+        <v>0.09943399999999999</v>
       </c>
       <c r="C274" t="n">
-        <v>0.258856</v>
+        <v>0.26087</v>
       </c>
     </row>
     <row r="275">
@@ -3989,10 +3989,10 @@
         </is>
       </c>
       <c r="B275" t="n">
-        <v>0.103451</v>
+        <v>0.100571</v>
       </c>
       <c r="C275" t="n">
-        <v>0.256131</v>
+        <v>0.258152</v>
       </c>
     </row>
     <row r="276">
@@ -4002,10 +4002,10 @@
         </is>
       </c>
       <c r="B276" t="n">
-        <v>0.103942</v>
+        <v>0.101335</v>
       </c>
       <c r="C276" t="n">
-        <v>0.253406</v>
+        <v>0.255435</v>
       </c>
     </row>
     <row r="277">
@@ -4015,10 +4015,10 @@
         </is>
       </c>
       <c r="B277" t="n">
-        <v>0.10427</v>
+        <v>0.103451</v>
       </c>
       <c r="C277" t="n">
-        <v>0.250681</v>
+        <v>0.252717</v>
       </c>
     </row>
     <row r="278">
@@ -4028,10 +4028,10 @@
         </is>
       </c>
       <c r="B278" t="n">
-        <v>0.105774</v>
+        <v>0.103942</v>
       </c>
       <c r="C278" t="n">
-        <v>0.247956</v>
+        <v>0.25</v>
       </c>
     </row>
     <row r="279">
@@ -4041,10 +4041,10 @@
         </is>
       </c>
       <c r="B279" t="n">
-        <v>0.106391</v>
+        <v>0.10427</v>
       </c>
       <c r="C279" t="n">
-        <v>0.245232</v>
+        <v>0.247283</v>
       </c>
     </row>
     <row r="280">
@@ -4054,10 +4054,10 @@
         </is>
       </c>
       <c r="B280" t="n">
-        <v>0.106564</v>
+        <v>0.105774</v>
       </c>
       <c r="C280" t="n">
-        <v>0.242507</v>
+        <v>0.244565</v>
       </c>
     </row>
     <row r="281">
@@ -4067,10 +4067,10 @@
         </is>
       </c>
       <c r="B281" t="n">
-        <v>0.106852</v>
+        <v>0.106391</v>
       </c>
       <c r="C281" t="n">
-        <v>0.239782</v>
+        <v>0.241848</v>
       </c>
     </row>
     <row r="282">
@@ -4080,10 +4080,10 @@
         </is>
       </c>
       <c r="B282" t="n">
-        <v>0.107359</v>
+        <v>0.106564</v>
       </c>
       <c r="C282" t="n">
-        <v>0.237057</v>
+        <v>0.23913</v>
       </c>
     </row>
     <row r="283">
@@ -4093,10 +4093,10 @@
         </is>
       </c>
       <c r="B283" t="n">
-        <v>0.110708</v>
+        <v>0.106852</v>
       </c>
       <c r="C283" t="n">
-        <v>0.234332</v>
+        <v>0.236413</v>
       </c>
     </row>
     <row r="284">
@@ -4106,10 +4106,10 @@
         </is>
       </c>
       <c r="B284" t="n">
-        <v>0.111683</v>
+        <v>0.107359</v>
       </c>
       <c r="C284" t="n">
-        <v>0.231608</v>
+        <v>0.233696</v>
       </c>
     </row>
     <row r="285">
@@ -4119,10 +4119,10 @@
         </is>
       </c>
       <c r="B285" t="n">
-        <v>0.112861</v>
+        <v>0.110708</v>
       </c>
       <c r="C285" t="n">
-        <v>0.228883</v>
+        <v>0.230978</v>
       </c>
     </row>
     <row r="286">
@@ -4132,10 +4132,10 @@
         </is>
       </c>
       <c r="B286" t="n">
-        <v>0.11394</v>
+        <v>0.111683</v>
       </c>
       <c r="C286" t="n">
-        <v>0.226158</v>
+        <v>0.228261</v>
       </c>
     </row>
     <row r="287">
@@ -4145,10 +4145,10 @@
         </is>
       </c>
       <c r="B287" t="n">
-        <v>0.114179</v>
+        <v>0.112861</v>
       </c>
       <c r="C287" t="n">
-        <v>0.223433</v>
+        <v>0.225543</v>
       </c>
     </row>
     <row r="288">
@@ -4158,10 +4158,10 @@
         </is>
       </c>
       <c r="B288" t="n">
-        <v>0.11468</v>
+        <v>0.11394</v>
       </c>
       <c r="C288" t="n">
-        <v>0.220708</v>
+        <v>0.222826</v>
       </c>
     </row>
     <row r="289">
@@ -4171,10 +4171,10 @@
         </is>
       </c>
       <c r="B289" t="n">
-        <v>0.115972</v>
+        <v>0.114179</v>
       </c>
       <c r="C289" t="n">
-        <v>0.217984</v>
+        <v>0.220109</v>
       </c>
     </row>
     <row r="290">
@@ -4184,10 +4184,10 @@
         </is>
       </c>
       <c r="B290" t="n">
-        <v>0.117496</v>
+        <v>0.11468</v>
       </c>
       <c r="C290" t="n">
-        <v>0.215259</v>
+        <v>0.217391</v>
       </c>
     </row>
     <row r="291">
@@ -4197,10 +4197,10 @@
         </is>
       </c>
       <c r="B291" t="n">
-        <v>0.117846</v>
+        <v>0.115972</v>
       </c>
       <c r="C291" t="n">
-        <v>0.212534</v>
+        <v>0.214674</v>
       </c>
     </row>
     <row r="292">
@@ -4210,10 +4210,10 @@
         </is>
       </c>
       <c r="B292" t="n">
-        <v>0.119464</v>
+        <v>0.117496</v>
       </c>
       <c r="C292" t="n">
-        <v>0.209809</v>
+        <v>0.211957</v>
       </c>
     </row>
     <row r="293">
@@ -4223,10 +4223,10 @@
         </is>
       </c>
       <c r="B293" t="n">
-        <v>0.120351</v>
+        <v>0.117846</v>
       </c>
       <c r="C293" t="n">
-        <v>0.207084</v>
+        <v>0.209239</v>
       </c>
     </row>
     <row r="294">
@@ -4236,10 +4236,10 @@
         </is>
       </c>
       <c r="B294" t="n">
-        <v>0.120448</v>
+        <v>0.119464</v>
       </c>
       <c r="C294" t="n">
-        <v>0.20436</v>
+        <v>0.206522</v>
       </c>
     </row>
     <row r="295">
@@ -4249,10 +4249,10 @@
         </is>
       </c>
       <c r="B295" t="n">
-        <v>0.121637</v>
+        <v>0.120351</v>
       </c>
       <c r="C295" t="n">
-        <v>0.201635</v>
+        <v>0.203804</v>
       </c>
     </row>
     <row r="296">
@@ -4262,10 +4262,10 @@
         </is>
       </c>
       <c r="B296" t="n">
-        <v>0.12397</v>
+        <v>0.120448</v>
       </c>
       <c r="C296" t="n">
-        <v>0.19891</v>
+        <v>0.201087</v>
       </c>
     </row>
     <row r="297">
@@ -4275,10 +4275,10 @@
         </is>
       </c>
       <c r="B297" t="n">
-        <v>0.124167</v>
+        <v>0.121637</v>
       </c>
       <c r="C297" t="n">
-        <v>0.196185</v>
+        <v>0.19837</v>
       </c>
     </row>
     <row r="298">
@@ -4288,10 +4288,10 @@
         </is>
       </c>
       <c r="B298" t="n">
-        <v>0.126891</v>
+        <v>0.12397</v>
       </c>
       <c r="C298" t="n">
-        <v>0.19346</v>
+        <v>0.195652</v>
       </c>
     </row>
     <row r="299">
@@ -4301,10 +4301,10 @@
         </is>
       </c>
       <c r="B299" t="n">
-        <v>0.128021</v>
+        <v>0.124167</v>
       </c>
       <c r="C299" t="n">
-        <v>0.190736</v>
+        <v>0.192935</v>
       </c>
     </row>
     <row r="300">
@@ -4314,10 +4314,10 @@
         </is>
       </c>
       <c r="B300" t="n">
-        <v>0.128976</v>
+        <v>0.126891</v>
       </c>
       <c r="C300" t="n">
-        <v>0.188011</v>
+        <v>0.190217</v>
       </c>
     </row>
     <row r="301">
@@ -4327,10 +4327,10 @@
         </is>
       </c>
       <c r="B301" t="n">
-        <v>0.130439</v>
+        <v>0.128021</v>
       </c>
       <c r="C301" t="n">
-        <v>0.185286</v>
+        <v>0.1875</v>
       </c>
     </row>
     <row r="302">
@@ -4340,10 +4340,10 @@
         </is>
       </c>
       <c r="B302" t="n">
-        <v>0.130821</v>
+        <v>0.128976</v>
       </c>
       <c r="C302" t="n">
-        <v>0.182561</v>
+        <v>0.184783</v>
       </c>
     </row>
     <row r="303">
@@ -4353,10 +4353,10 @@
         </is>
       </c>
       <c r="B303" t="n">
-        <v>0.130916</v>
+        <v>0.130439</v>
       </c>
       <c r="C303" t="n">
-        <v>0.179837</v>
+        <v>0.182065</v>
       </c>
     </row>
     <row r="304">
@@ -4366,10 +4366,10 @@
         </is>
       </c>
       <c r="B304" t="n">
-        <v>0.135669</v>
+        <v>0.130821</v>
       </c>
       <c r="C304" t="n">
-        <v>0.177112</v>
+        <v>0.179348</v>
       </c>
     </row>
     <row r="305">
@@ -4379,10 +4379,10 @@
         </is>
       </c>
       <c r="B305" t="n">
-        <v>0.135827</v>
+        <v>0.130916</v>
       </c>
       <c r="C305" t="n">
-        <v>0.174387</v>
+        <v>0.17663</v>
       </c>
     </row>
     <row r="306">
@@ -4392,10 +4392,10 @@
         </is>
       </c>
       <c r="B306" t="n">
-        <v>0.137023</v>
+        <v>0.135669</v>
       </c>
       <c r="C306" t="n">
-        <v>0.171662</v>
+        <v>0.173913</v>
       </c>
     </row>
     <row r="307">
@@ -4405,10 +4405,10 @@
         </is>
       </c>
       <c r="B307" t="n">
-        <v>0.13733</v>
+        <v>0.135827</v>
       </c>
       <c r="C307" t="n">
-        <v>0.168937</v>
+        <v>0.171196</v>
       </c>
     </row>
     <row r="308">
@@ -4418,10 +4418,10 @@
         </is>
       </c>
       <c r="B308" t="n">
-        <v>0.138762</v>
+        <v>0.137023</v>
       </c>
       <c r="C308" t="n">
-        <v>0.166213</v>
+        <v>0.168478</v>
       </c>
     </row>
     <row r="309">
@@ -4431,10 +4431,10 @@
         </is>
       </c>
       <c r="B309" t="n">
-        <v>0.139275</v>
+        <v>0.13733</v>
       </c>
       <c r="C309" t="n">
-        <v>0.163488</v>
+        <v>0.165761</v>
       </c>
     </row>
     <row r="310">
@@ -4444,10 +4444,10 @@
         </is>
       </c>
       <c r="B310" t="n">
-        <v>0.140029</v>
+        <v>0.138613</v>
       </c>
       <c r="C310" t="n">
-        <v>0.160763</v>
+        <v>0.163043</v>
       </c>
     </row>
     <row r="311">
@@ -4457,10 +4457,10 @@
         </is>
       </c>
       <c r="B311" t="n">
-        <v>0.140099</v>
+        <v>0.138762</v>
       </c>
       <c r="C311" t="n">
-        <v>0.158038</v>
+        <v>0.160326</v>
       </c>
     </row>
     <row r="312">
@@ -4470,10 +4470,10 @@
         </is>
       </c>
       <c r="B312" t="n">
-        <v>0.140214</v>
+        <v>0.139275</v>
       </c>
       <c r="C312" t="n">
-        <v>0.155313</v>
+        <v>0.157609</v>
       </c>
     </row>
     <row r="313">
@@ -4483,10 +4483,10 @@
         </is>
       </c>
       <c r="B313" t="n">
-        <v>0.144579</v>
+        <v>0.140029</v>
       </c>
       <c r="C313" t="n">
-        <v>0.152589</v>
+        <v>0.154891</v>
       </c>
     </row>
     <row r="314">
@@ -4496,10 +4496,10 @@
         </is>
       </c>
       <c r="B314" t="n">
-        <v>0.145008</v>
+        <v>0.140099</v>
       </c>
       <c r="C314" t="n">
-        <v>0.149864</v>
+        <v>0.152174</v>
       </c>
     </row>
     <row r="315">
@@ -4509,10 +4509,10 @@
         </is>
       </c>
       <c r="B315" t="n">
-        <v>0.145291</v>
+        <v>0.140214</v>
       </c>
       <c r="C315" t="n">
-        <v>0.147139</v>
+        <v>0.149457</v>
       </c>
     </row>
     <row r="316">
@@ -4522,10 +4522,10 @@
         </is>
       </c>
       <c r="B316" t="n">
-        <v>0.145554</v>
+        <v>0.143039</v>
       </c>
       <c r="C316" t="n">
-        <v>0.144414</v>
+        <v>0.146739</v>
       </c>
     </row>
     <row r="317">
@@ -4535,10 +4535,10 @@
         </is>
       </c>
       <c r="B317" t="n">
-        <v>0.151419</v>
+        <v>0.144579</v>
       </c>
       <c r="C317" t="n">
-        <v>0.141689</v>
+        <v>0.144022</v>
       </c>
     </row>
     <row r="318">
@@ -4548,10 +4548,10 @@
         </is>
       </c>
       <c r="B318" t="n">
-        <v>0.151465</v>
+        <v>0.145291</v>
       </c>
       <c r="C318" t="n">
-        <v>0.138965</v>
+        <v>0.141304</v>
       </c>
     </row>
     <row r="319">
@@ -4561,10 +4561,10 @@
         </is>
       </c>
       <c r="B319" t="n">
-        <v>0.151822</v>
+        <v>0.145554</v>
       </c>
       <c r="C319" t="n">
-        <v>0.13624</v>
+        <v>0.138587</v>
       </c>
     </row>
     <row r="320">
@@ -4574,10 +4574,10 @@
         </is>
       </c>
       <c r="B320" t="n">
-        <v>0.15511</v>
+        <v>0.151419</v>
       </c>
       <c r="C320" t="n">
-        <v>0.133515</v>
+        <v>0.13587</v>
       </c>
     </row>
     <row r="321">
@@ -4587,10 +4587,10 @@
         </is>
       </c>
       <c r="B321" t="n">
-        <v>0.15559</v>
+        <v>0.151465</v>
       </c>
       <c r="C321" t="n">
-        <v>0.13079</v>
+        <v>0.133152</v>
       </c>
     </row>
     <row r="322">
@@ -4600,10 +4600,10 @@
         </is>
       </c>
       <c r="B322" t="n">
-        <v>0.155726</v>
+        <v>0.15511</v>
       </c>
       <c r="C322" t="n">
-        <v>0.128065</v>
+        <v>0.130435</v>
       </c>
     </row>
     <row r="323">
@@ -4613,10 +4613,10 @@
         </is>
       </c>
       <c r="B323" t="n">
-        <v>0.156434</v>
+        <v>0.15559</v>
       </c>
       <c r="C323" t="n">
-        <v>0.125341</v>
+        <v>0.127717</v>
       </c>
     </row>
     <row r="324">
@@ -4626,10 +4626,10 @@
         </is>
       </c>
       <c r="B324" t="n">
-        <v>0.158503</v>
+        <v>0.155726</v>
       </c>
       <c r="C324" t="n">
-        <v>0.122616</v>
+        <v>0.125</v>
       </c>
     </row>
     <row r="325">
@@ -4639,10 +4639,10 @@
         </is>
       </c>
       <c r="B325" t="n">
-        <v>0.16241</v>
+        <v>0.156434</v>
       </c>
       <c r="C325" t="n">
-        <v>0.119891</v>
+        <v>0.122283</v>
       </c>
     </row>
     <row r="326">
@@ -4652,10 +4652,10 @@
         </is>
       </c>
       <c r="B326" t="n">
-        <v>0.167126</v>
+        <v>0.158503</v>
       </c>
       <c r="C326" t="n">
-        <v>0.117166</v>
+        <v>0.119565</v>
       </c>
     </row>
     <row r="327">
@@ -4665,10 +4665,10 @@
         </is>
       </c>
       <c r="B327" t="n">
-        <v>0.172262</v>
+        <v>0.16241</v>
       </c>
       <c r="C327" t="n">
-        <v>0.114441</v>
+        <v>0.116848</v>
       </c>
     </row>
     <row r="328">
@@ -4678,10 +4678,10 @@
         </is>
       </c>
       <c r="B328" t="n">
-        <v>0.179571</v>
+        <v>0.167126</v>
       </c>
       <c r="C328" t="n">
-        <v>0.111717</v>
+        <v>0.11413</v>
       </c>
     </row>
     <row r="329">
@@ -4691,10 +4691,10 @@
         </is>
       </c>
       <c r="B329" t="n">
-        <v>0.183042</v>
+        <v>0.172262</v>
       </c>
       <c r="C329" t="n">
-        <v>0.108992</v>
+        <v>0.111413</v>
       </c>
     </row>
     <row r="330">
@@ -4704,10 +4704,10 @@
         </is>
       </c>
       <c r="B330" t="n">
-        <v>0.187612</v>
+        <v>0.179571</v>
       </c>
       <c r="C330" t="n">
-        <v>0.106267</v>
+        <v>0.108696</v>
       </c>
     </row>
     <row r="331">
@@ -4717,10 +4717,10 @@
         </is>
       </c>
       <c r="B331" t="n">
-        <v>0.189387</v>
+        <v>0.183042</v>
       </c>
       <c r="C331" t="n">
-        <v>0.103542</v>
+        <v>0.105978</v>
       </c>
     </row>
     <row r="332">
@@ -4730,10 +4730,10 @@
         </is>
       </c>
       <c r="B332" t="n">
-        <v>0.193249</v>
+        <v>0.187612</v>
       </c>
       <c r="C332" t="n">
-        <v>0.100817</v>
+        <v>0.103261</v>
       </c>
     </row>
     <row r="333">
@@ -4743,10 +4743,10 @@
         </is>
       </c>
       <c r="B333" t="n">
-        <v>0.195388</v>
+        <v>0.189387</v>
       </c>
       <c r="C333" t="n">
-        <v>0.098093</v>
+        <v>0.100543</v>
       </c>
     </row>
     <row r="334">
@@ -4756,10 +4756,10 @@
         </is>
       </c>
       <c r="B334" t="n">
-        <v>0.200683</v>
+        <v>0.193249</v>
       </c>
       <c r="C334" t="n">
-        <v>0.09536799999999999</v>
+        <v>0.097826</v>
       </c>
     </row>
     <row r="335">
@@ -4769,10 +4769,10 @@
         </is>
       </c>
       <c r="B335" t="n">
-        <v>0.202141</v>
+        <v>0.195388</v>
       </c>
       <c r="C335" t="n">
-        <v>0.092643</v>
+        <v>0.095109</v>
       </c>
     </row>
     <row r="336">
@@ -4782,10 +4782,10 @@
         </is>
       </c>
       <c r="B336" t="n">
-        <v>0.206803</v>
+        <v>0.200683</v>
       </c>
       <c r="C336" t="n">
-        <v>0.089918</v>
+        <v>0.092391</v>
       </c>
     </row>
     <row r="337">
@@ -4795,10 +4795,10 @@
         </is>
       </c>
       <c r="B337" t="n">
-        <v>0.21126</v>
+        <v>0.202141</v>
       </c>
       <c r="C337" t="n">
-        <v>0.08719300000000001</v>
+        <v>0.089674</v>
       </c>
     </row>
     <row r="338">
@@ -4808,10 +4808,10 @@
         </is>
       </c>
       <c r="B338" t="n">
-        <v>0.212282</v>
+        <v>0.206803</v>
       </c>
       <c r="C338" t="n">
-        <v>0.084469</v>
+        <v>0.08695700000000001</v>
       </c>
     </row>
     <row r="339">
@@ -4821,10 +4821,10 @@
         </is>
       </c>
       <c r="B339" t="n">
-        <v>0.213977</v>
+        <v>0.21126</v>
       </c>
       <c r="C339" t="n">
-        <v>0.081744</v>
+        <v>0.08423899999999999</v>
       </c>
     </row>
     <row r="340">
@@ -4834,10 +4834,10 @@
         </is>
       </c>
       <c r="B340" t="n">
-        <v>0.224095</v>
+        <v>0.212282</v>
       </c>
       <c r="C340" t="n">
-        <v>0.07901900000000001</v>
+        <v>0.081522</v>
       </c>
     </row>
     <row r="341">
@@ -4847,10 +4847,10 @@
         </is>
       </c>
       <c r="B341" t="n">
-        <v>0.229443</v>
+        <v>0.213977</v>
       </c>
       <c r="C341" t="n">
-        <v>0.076294</v>
+        <v>0.078804</v>
       </c>
     </row>
     <row r="342">
@@ -4860,10 +4860,10 @@
         </is>
       </c>
       <c r="B342" t="n">
-        <v>0.235662</v>
+        <v>0.224095</v>
       </c>
       <c r="C342" t="n">
-        <v>0.073569</v>
+        <v>0.076087</v>
       </c>
     </row>
     <row r="343">
@@ -4873,10 +4873,10 @@
         </is>
       </c>
       <c r="B343" t="n">
-        <v>0.257813</v>
+        <v>0.229443</v>
       </c>
       <c r="C343" t="n">
-        <v>0.07084500000000001</v>
+        <v>0.07337</v>
       </c>
     </row>
     <row r="344">
@@ -4886,10 +4886,10 @@
         </is>
       </c>
       <c r="B344" t="n">
-        <v>0.279391</v>
+        <v>0.235662</v>
       </c>
       <c r="C344" t="n">
-        <v>0.06812</v>
+        <v>0.07065200000000001</v>
       </c>
     </row>
     <row r="345">
@@ -4899,10 +4899,10 @@
         </is>
       </c>
       <c r="B345" t="n">
-        <v>0.286735</v>
+        <v>0.257813</v>
       </c>
       <c r="C345" t="n">
-        <v>0.06539499999999999</v>
+        <v>0.067935</v>
       </c>
     </row>
     <row r="346">
@@ -4912,10 +4912,10 @@
         </is>
       </c>
       <c r="B346" t="n">
-        <v>0.28675</v>
+        <v>0.279391</v>
       </c>
       <c r="C346" t="n">
-        <v>0.06267</v>
+        <v>0.065217</v>
       </c>
     </row>
     <row r="347">
@@ -4925,10 +4925,10 @@
         </is>
       </c>
       <c r="B347" t="n">
-        <v>0.292707</v>
+        <v>0.286735</v>
       </c>
       <c r="C347" t="n">
-        <v>0.059946</v>
+        <v>0.0625</v>
       </c>
     </row>
     <row r="348">
@@ -4938,10 +4938,10 @@
         </is>
       </c>
       <c r="B348" t="n">
-        <v>0.303016</v>
+        <v>0.28675</v>
       </c>
       <c r="C348" t="n">
-        <v>0.057221</v>
+        <v>0.059783</v>
       </c>
     </row>
     <row r="349">
@@ -4951,10 +4951,10 @@
         </is>
       </c>
       <c r="B349" t="n">
-        <v>0.35577</v>
+        <v>0.292707</v>
       </c>
       <c r="C349" t="n">
-        <v>0.054496</v>
+        <v>0.057065</v>
       </c>
     </row>
     <row r="350">
@@ -4964,10 +4964,10 @@
         </is>
       </c>
       <c r="B350" t="n">
-        <v>0.359445</v>
+        <v>0.303016</v>
       </c>
       <c r="C350" t="n">
-        <v>0.051771</v>
+        <v>0.054348</v>
       </c>
     </row>
     <row r="351">
@@ -4977,10 +4977,10 @@
         </is>
       </c>
       <c r="B351" t="n">
-        <v>0.363732</v>
+        <v>0.35577</v>
       </c>
       <c r="C351" t="n">
-        <v>0.049046</v>
+        <v>0.05163</v>
       </c>
     </row>
     <row r="352">
@@ -4990,10 +4990,10 @@
         </is>
       </c>
       <c r="B352" t="n">
-        <v>0.36468</v>
+        <v>0.359445</v>
       </c>
       <c r="C352" t="n">
-        <v>0.046322</v>
+        <v>0.048913</v>
       </c>
     </row>
     <row r="353">
@@ -5003,10 +5003,10 @@
         </is>
       </c>
       <c r="B353" t="n">
-        <v>0.373827</v>
+        <v>0.363732</v>
       </c>
       <c r="C353" t="n">
-        <v>0.043597</v>
+        <v>0.046196</v>
       </c>
     </row>
     <row r="354">
@@ -5016,10 +5016,10 @@
         </is>
       </c>
       <c r="B354" t="n">
-        <v>0.389014</v>
+        <v>0.36468</v>
       </c>
       <c r="C354" t="n">
-        <v>0.040872</v>
+        <v>0.043478</v>
       </c>
     </row>
     <row r="355">
@@ -5029,10 +5029,10 @@
         </is>
       </c>
       <c r="B355" t="n">
-        <v>0.400164</v>
+        <v>0.373827</v>
       </c>
       <c r="C355" t="n">
-        <v>0.038147</v>
+        <v>0.040761</v>
       </c>
     </row>
     <row r="356">
@@ -5042,10 +5042,10 @@
         </is>
       </c>
       <c r="B356" t="n">
-        <v>0.40983</v>
+        <v>0.389014</v>
       </c>
       <c r="C356" t="n">
-        <v>0.035422</v>
+        <v>0.038043</v>
       </c>
     </row>
     <row r="357">
@@ -5055,10 +5055,10 @@
         </is>
       </c>
       <c r="B357" t="n">
-        <v>0.410903</v>
+        <v>0.397465</v>
       </c>
       <c r="C357" t="n">
-        <v>0.032698</v>
+        <v>0.035326</v>
       </c>
     </row>
     <row r="358">
@@ -5068,10 +5068,10 @@
         </is>
       </c>
       <c r="B358" t="n">
-        <v>0.419404</v>
+        <v>0.400164</v>
       </c>
       <c r="C358" t="n">
-        <v>0.029973</v>
+        <v>0.032609</v>
       </c>
     </row>
     <row r="359">
@@ -5081,10 +5081,10 @@
         </is>
       </c>
       <c r="B359" t="n">
-        <v>0.440642</v>
+        <v>0.40983</v>
       </c>
       <c r="C359" t="n">
-        <v>0.027248</v>
+        <v>0.029891</v>
       </c>
     </row>
     <row r="360">
@@ -5094,10 +5094,10 @@
         </is>
       </c>
       <c r="B360" t="n">
-        <v>0.587794</v>
+        <v>0.410903</v>
       </c>
       <c r="C360" t="n">
-        <v>0.024523</v>
+        <v>0.027174</v>
       </c>
     </row>
     <row r="361">
@@ -5107,10 +5107,10 @@
         </is>
       </c>
       <c r="B361" t="n">
-        <v>0.620194</v>
+        <v>0.419404</v>
       </c>
       <c r="C361" t="n">
-        <v>0.021798</v>
+        <v>0.024457</v>
       </c>
     </row>
     <row r="362">
@@ -5120,10 +5120,10 @@
         </is>
       </c>
       <c r="B362" t="n">
-        <v>0.634074</v>
+        <v>0.440642</v>
       </c>
       <c r="C362" t="n">
-        <v>0.019074</v>
+        <v>0.021739</v>
       </c>
     </row>
     <row r="363">
@@ -5133,10 +5133,10 @@
         </is>
       </c>
       <c r="B363" t="n">
-        <v>0.672434</v>
+        <v>0.620194</v>
       </c>
       <c r="C363" t="n">
-        <v>0.016349</v>
+        <v>0.019022</v>
       </c>
     </row>
     <row r="364">
@@ -5146,10 +5146,10 @@
         </is>
       </c>
       <c r="B364" t="n">
-        <v>0.707604</v>
+        <v>0.634074</v>
       </c>
       <c r="C364" t="n">
-        <v>0.013624</v>
+        <v>0.016304</v>
       </c>
     </row>
     <row r="365">
@@ -5159,10 +5159,10 @@
         </is>
       </c>
       <c r="B365" t="n">
-        <v>0.711338</v>
+        <v>0.672434</v>
       </c>
       <c r="C365" t="n">
-        <v>0.010899</v>
+        <v>0.013587</v>
       </c>
     </row>
     <row r="366">
@@ -5172,10 +5172,10 @@
         </is>
       </c>
       <c r="B366" t="n">
-        <v>0.76535</v>
+        <v>0.711338</v>
       </c>
       <c r="C366" t="n">
-        <v>0.008174000000000001</v>
+        <v>0.01087</v>
       </c>
     </row>
     <row r="367">
@@ -5185,10 +5185,10 @@
         </is>
       </c>
       <c r="B367" t="n">
-        <v>0.838984</v>
+        <v>0.76535</v>
       </c>
       <c r="C367" t="n">
-        <v>0.00545</v>
+        <v>0.008152</v>
       </c>
     </row>
     <row r="368">
@@ -5198,23 +5198,23 @@
         </is>
       </c>
       <c r="B368" t="n">
-        <v>1.015082</v>
+        <v>0.838984</v>
       </c>
       <c r="C368" t="n">
-        <v>0.002725</v>
+        <v>0.005435</v>
       </c>
     </row>
     <row r="369">
       <c r="A369" t="inlineStr">
         <is>
-          <t>Adjusted target</t>
+          <t>Raw market</t>
         </is>
       </c>
       <c r="B369" t="n">
-        <v>2e-06</v>
+        <v>1.015082</v>
       </c>
       <c r="C369" t="n">
-        <v>1</v>
+        <v>0.002717</v>
       </c>
     </row>
     <row r="370">
@@ -5224,10 +5224,10 @@
         </is>
       </c>
       <c r="B370" t="n">
-        <v>0.000116</v>
+        <v>2e-06</v>
       </c>
       <c r="C370" t="n">
-        <v>0.997275</v>
+        <v>1</v>
       </c>
     </row>
     <row r="371">
@@ -5237,10 +5237,10 @@
         </is>
       </c>
       <c r="B371" t="n">
-        <v>0.000335</v>
+        <v>0.000115</v>
       </c>
       <c r="C371" t="n">
-        <v>0.99455</v>
+        <v>0.997283</v>
       </c>
     </row>
     <row r="372">
@@ -5250,10 +5250,10 @@
         </is>
       </c>
       <c r="B372" t="n">
-        <v>0.000546</v>
+        <v>0.000339</v>
       </c>
       <c r="C372" t="n">
-        <v>0.991826</v>
+        <v>0.994565</v>
       </c>
     </row>
     <row r="373">
@@ -5263,10 +5263,10 @@
         </is>
       </c>
       <c r="B373" t="n">
-        <v>0.001107</v>
+        <v>0.000545</v>
       </c>
       <c r="C373" t="n">
-        <v>0.989101</v>
+        <v>0.991848</v>
       </c>
     </row>
     <row r="374">
@@ -5276,10 +5276,10 @@
         </is>
       </c>
       <c r="B374" t="n">
-        <v>0.001715</v>
+        <v>0.001109</v>
       </c>
       <c r="C374" t="n">
-        <v>0.986376</v>
+        <v>0.98913</v>
       </c>
     </row>
     <row r="375">
@@ -5289,10 +5289,10 @@
         </is>
       </c>
       <c r="B375" t="n">
-        <v>0.002104</v>
+        <v>0.001755</v>
       </c>
       <c r="C375" t="n">
-        <v>0.9836510000000001</v>
+        <v>0.986413</v>
       </c>
     </row>
     <row r="376">
@@ -5302,10 +5302,10 @@
         </is>
       </c>
       <c r="B376" t="n">
-        <v>0.002118</v>
+        <v>0.002084</v>
       </c>
       <c r="C376" t="n">
-        <v>0.980926</v>
+        <v>0.983696</v>
       </c>
     </row>
     <row r="377">
@@ -5315,10 +5315,10 @@
         </is>
       </c>
       <c r="B377" t="n">
-        <v>0.002256</v>
+        <v>0.00215</v>
       </c>
       <c r="C377" t="n">
-        <v>0.978202</v>
+        <v>0.980978</v>
       </c>
     </row>
     <row r="378">
@@ -5328,10 +5328,10 @@
         </is>
       </c>
       <c r="B378" t="n">
-        <v>0.00306</v>
+        <v>0.002341</v>
       </c>
       <c r="C378" t="n">
-        <v>0.975477</v>
+        <v>0.978261</v>
       </c>
     </row>
     <row r="379">
@@ -5341,10 +5341,10 @@
         </is>
       </c>
       <c r="B379" t="n">
-        <v>0.003119</v>
+        <v>0.002477</v>
       </c>
       <c r="C379" t="n">
-        <v>0.972752</v>
+        <v>0.975543</v>
       </c>
     </row>
     <row r="380">
@@ -5354,10 +5354,10 @@
         </is>
       </c>
       <c r="B380" t="n">
-        <v>0.00341</v>
+        <v>0.003145</v>
       </c>
       <c r="C380" t="n">
-        <v>0.970027</v>
+        <v>0.972826</v>
       </c>
     </row>
     <row r="381">
@@ -5367,10 +5367,10 @@
         </is>
       </c>
       <c r="B381" t="n">
-        <v>0.003513</v>
+        <v>0.003149</v>
       </c>
       <c r="C381" t="n">
-        <v>0.967302</v>
+        <v>0.970109</v>
       </c>
     </row>
     <row r="382">
@@ -5380,10 +5380,10 @@
         </is>
       </c>
       <c r="B382" t="n">
-        <v>0.004495</v>
+        <v>0.003426</v>
       </c>
       <c r="C382" t="n">
-        <v>0.964578</v>
+        <v>0.967391</v>
       </c>
     </row>
     <row r="383">
@@ -5393,10 +5393,10 @@
         </is>
       </c>
       <c r="B383" t="n">
-        <v>0.004551</v>
+        <v>0.003634</v>
       </c>
       <c r="C383" t="n">
-        <v>0.961853</v>
+        <v>0.964674</v>
       </c>
     </row>
     <row r="384">
@@ -5406,10 +5406,10 @@
         </is>
       </c>
       <c r="B384" t="n">
-        <v>0.004741</v>
+        <v>0.004504</v>
       </c>
       <c r="C384" t="n">
-        <v>0.959128</v>
+        <v>0.961957</v>
       </c>
     </row>
     <row r="385">
@@ -5419,10 +5419,10 @@
         </is>
       </c>
       <c r="B385" t="n">
-        <v>0.004825</v>
+        <v>0.004566</v>
       </c>
       <c r="C385" t="n">
-        <v>0.956403</v>
+        <v>0.959239</v>
       </c>
     </row>
     <row r="386">
@@ -5432,10 +5432,10 @@
         </is>
       </c>
       <c r="B386" t="n">
-        <v>0.00504</v>
+        <v>0.005056</v>
       </c>
       <c r="C386" t="n">
-        <v>0.953678</v>
+        <v>0.956522</v>
       </c>
     </row>
     <row r="387">
@@ -5445,10 +5445,10 @@
         </is>
       </c>
       <c r="B387" t="n">
-        <v>0.005114</v>
+        <v>0.005058</v>
       </c>
       <c r="C387" t="n">
-        <v>0.950954</v>
+        <v>0.953804</v>
       </c>
     </row>
     <row r="388">
@@ -5458,10 +5458,10 @@
         </is>
       </c>
       <c r="B388" t="n">
-        <v>0.005145</v>
+        <v>0.005091</v>
       </c>
       <c r="C388" t="n">
-        <v>0.948229</v>
+        <v>0.951087</v>
       </c>
     </row>
     <row r="389">
@@ -5471,10 +5471,10 @@
         </is>
       </c>
       <c r="B389" t="n">
-        <v>0.005184</v>
+        <v>0.005147</v>
       </c>
       <c r="C389" t="n">
-        <v>0.945504</v>
+        <v>0.94837</v>
       </c>
     </row>
     <row r="390">
@@ -5484,10 +5484,10 @@
         </is>
       </c>
       <c r="B390" t="n">
-        <v>0.0055</v>
+        <v>0.005323</v>
       </c>
       <c r="C390" t="n">
-        <v>0.942779</v>
+        <v>0.945652</v>
       </c>
     </row>
     <row r="391">
@@ -5497,10 +5497,10 @@
         </is>
       </c>
       <c r="B391" t="n">
-        <v>0.005563</v>
+        <v>0.005401</v>
       </c>
       <c r="C391" t="n">
-        <v>0.9400539999999999</v>
+        <v>0.942935</v>
       </c>
     </row>
     <row r="392">
@@ -5510,10 +5510,10 @@
         </is>
       </c>
       <c r="B392" t="n">
-        <v>0.005728</v>
+        <v>0.005442</v>
       </c>
       <c r="C392" t="n">
-        <v>0.93733</v>
+        <v>0.940217</v>
       </c>
     </row>
     <row r="393">
@@ -5523,10 +5523,10 @@
         </is>
       </c>
       <c r="B393" t="n">
-        <v>0.00621</v>
+        <v>0.005633</v>
       </c>
       <c r="C393" t="n">
-        <v>0.934605</v>
+        <v>0.9375</v>
       </c>
     </row>
     <row r="394">
@@ -5536,10 +5536,10 @@
         </is>
       </c>
       <c r="B394" t="n">
-        <v>0.006506</v>
+        <v>0.005683</v>
       </c>
       <c r="C394" t="n">
-        <v>0.93188</v>
+        <v>0.934783</v>
       </c>
     </row>
     <row r="395">
@@ -5549,10 +5549,10 @@
         </is>
       </c>
       <c r="B395" t="n">
-        <v>0.006598</v>
+        <v>0.006314</v>
       </c>
       <c r="C395" t="n">
-        <v>0.929155</v>
+        <v>0.932065</v>
       </c>
     </row>
     <row r="396">
@@ -5562,10 +5562,10 @@
         </is>
       </c>
       <c r="B396" t="n">
-        <v>0.007292</v>
+        <v>0.006577</v>
       </c>
       <c r="C396" t="n">
-        <v>0.926431</v>
+        <v>0.929348</v>
       </c>
     </row>
     <row r="397">
@@ -5575,10 +5575,10 @@
         </is>
       </c>
       <c r="B397" t="n">
-        <v>0.008071</v>
+        <v>0.006674</v>
       </c>
       <c r="C397" t="n">
-        <v>0.923706</v>
+        <v>0.92663</v>
       </c>
     </row>
     <row r="398">
@@ -5588,10 +5588,10 @@
         </is>
       </c>
       <c r="B398" t="n">
-        <v>0.008133</v>
+        <v>0.007328</v>
       </c>
       <c r="C398" t="n">
-        <v>0.920981</v>
+        <v>0.923913</v>
       </c>
     </row>
     <row r="399">
@@ -5601,10 +5601,10 @@
         </is>
       </c>
       <c r="B399" t="n">
-        <v>0.008434000000000001</v>
+        <v>0.008163999999999999</v>
       </c>
       <c r="C399" t="n">
-        <v>0.918256</v>
+        <v>0.921196</v>
       </c>
     </row>
     <row r="400">
@@ -5614,10 +5614,10 @@
         </is>
       </c>
       <c r="B400" t="n">
-        <v>0.008600999999999999</v>
+        <v>0.008189999999999999</v>
       </c>
       <c r="C400" t="n">
-        <v>0.915531</v>
+        <v>0.918478</v>
       </c>
     </row>
     <row r="401">
@@ -5627,10 +5627,10 @@
         </is>
       </c>
       <c r="B401" t="n">
-        <v>0.008747</v>
+        <v>0.008462000000000001</v>
       </c>
       <c r="C401" t="n">
-        <v>0.912807</v>
+        <v>0.915761</v>
       </c>
     </row>
     <row r="402">
@@ -5640,10 +5640,10 @@
         </is>
       </c>
       <c r="B402" t="n">
-        <v>0.008878</v>
+        <v>0.008697999999999999</v>
       </c>
       <c r="C402" t="n">
-        <v>0.9100819999999999</v>
+        <v>0.913043</v>
       </c>
     </row>
     <row r="403">
@@ -5653,10 +5653,10 @@
         </is>
       </c>
       <c r="B403" t="n">
-        <v>0.009226</v>
+        <v>0.008959</v>
       </c>
       <c r="C403" t="n">
-        <v>0.907357</v>
+        <v>0.910326</v>
       </c>
     </row>
     <row r="404">
@@ -5666,10 +5666,10 @@
         </is>
       </c>
       <c r="B404" t="n">
-        <v>0.009343000000000001</v>
+        <v>0.009088000000000001</v>
       </c>
       <c r="C404" t="n">
-        <v>0.904632</v>
+        <v>0.907609</v>
       </c>
     </row>
     <row r="405">
@@ -5679,10 +5679,10 @@
         </is>
       </c>
       <c r="B405" t="n">
-        <v>0.009362000000000001</v>
+        <v>0.009175000000000001</v>
       </c>
       <c r="C405" t="n">
-        <v>0.901907</v>
+        <v>0.904891</v>
       </c>
     </row>
     <row r="406">
@@ -5692,10 +5692,10 @@
         </is>
       </c>
       <c r="B406" t="n">
-        <v>0.009946</v>
+        <v>0.009303000000000001</v>
       </c>
       <c r="C406" t="n">
-        <v>0.899183</v>
+        <v>0.902174</v>
       </c>
     </row>
     <row r="407">
@@ -5705,10 +5705,10 @@
         </is>
       </c>
       <c r="B407" t="n">
-        <v>0.009993999999999999</v>
+        <v>0.009379999999999999</v>
       </c>
       <c r="C407" t="n">
-        <v>0.896458</v>
+        <v>0.899457</v>
       </c>
     </row>
     <row r="408">
@@ -5718,10 +5718,10 @@
         </is>
       </c>
       <c r="B408" t="n">
-        <v>0.010063</v>
+        <v>0.00991</v>
       </c>
       <c r="C408" t="n">
-        <v>0.893733</v>
+        <v>0.896739</v>
       </c>
     </row>
     <row r="409">
@@ -5731,10 +5731,10 @@
         </is>
       </c>
       <c r="B409" t="n">
-        <v>0.010277</v>
+        <v>0.010231</v>
       </c>
       <c r="C409" t="n">
-        <v>0.891008</v>
+        <v>0.894022</v>
       </c>
     </row>
     <row r="410">
@@ -5744,10 +5744,10 @@
         </is>
       </c>
       <c r="B410" t="n">
-        <v>0.01086</v>
+        <v>0.010453</v>
       </c>
       <c r="C410" t="n">
-        <v>0.888283</v>
+        <v>0.891304</v>
       </c>
     </row>
     <row r="411">
@@ -5757,10 +5757,10 @@
         </is>
       </c>
       <c r="B411" t="n">
-        <v>0.011202</v>
+        <v>0.01046</v>
       </c>
       <c r="C411" t="n">
-        <v>0.885559</v>
+        <v>0.888587</v>
       </c>
     </row>
     <row r="412">
@@ -5770,10 +5770,10 @@
         </is>
       </c>
       <c r="B412" t="n">
-        <v>0.011297</v>
+        <v>0.01097</v>
       </c>
       <c r="C412" t="n">
-        <v>0.882834</v>
+        <v>0.88587</v>
       </c>
     </row>
     <row r="413">
@@ -5783,10 +5783,10 @@
         </is>
       </c>
       <c r="B413" t="n">
-        <v>0.011303</v>
+        <v>0.011207</v>
       </c>
       <c r="C413" t="n">
-        <v>0.880109</v>
+        <v>0.883152</v>
       </c>
     </row>
     <row r="414">
@@ -5796,10 +5796,10 @@
         </is>
       </c>
       <c r="B414" t="n">
-        <v>0.011401</v>
+        <v>0.011326</v>
       </c>
       <c r="C414" t="n">
-        <v>0.8773840000000001</v>
+        <v>0.880435</v>
       </c>
     </row>
     <row r="415">
@@ -5809,10 +5809,10 @@
         </is>
       </c>
       <c r="B415" t="n">
-        <v>0.01173</v>
+        <v>0.011528</v>
       </c>
       <c r="C415" t="n">
-        <v>0.874659</v>
+        <v>0.877717</v>
       </c>
     </row>
     <row r="416">
@@ -5822,10 +5822,10 @@
         </is>
       </c>
       <c r="B416" t="n">
-        <v>0.012049</v>
+        <v>0.011814</v>
       </c>
       <c r="C416" t="n">
-        <v>0.871935</v>
+        <v>0.875</v>
       </c>
     </row>
     <row r="417">
@@ -5835,10 +5835,10 @@
         </is>
       </c>
       <c r="B417" t="n">
-        <v>0.012282</v>
+        <v>0.012126</v>
       </c>
       <c r="C417" t="n">
-        <v>0.86921</v>
+        <v>0.872283</v>
       </c>
     </row>
     <row r="418">
@@ -5848,10 +5848,10 @@
         </is>
       </c>
       <c r="B418" t="n">
-        <v>0.01261</v>
+        <v>0.012145</v>
       </c>
       <c r="C418" t="n">
-        <v>0.8664849999999999</v>
+        <v>0.869565</v>
       </c>
     </row>
     <row r="419">
@@ -5861,10 +5861,10 @@
         </is>
       </c>
       <c r="B419" t="n">
-        <v>0.012624</v>
+        <v>0.012466</v>
       </c>
       <c r="C419" t="n">
-        <v>0.86376</v>
+        <v>0.866848</v>
       </c>
     </row>
     <row r="420">
@@ -5874,10 +5874,10 @@
         </is>
       </c>
       <c r="B420" t="n">
-        <v>0.012712</v>
+        <v>0.012558</v>
       </c>
       <c r="C420" t="n">
-        <v>0.861035</v>
+        <v>0.86413</v>
       </c>
     </row>
     <row r="421">
@@ -5887,10 +5887,10 @@
         </is>
       </c>
       <c r="B421" t="n">
-        <v>0.012816</v>
+        <v>0.012629</v>
       </c>
       <c r="C421" t="n">
-        <v>0.858311</v>
+        <v>0.861413</v>
       </c>
     </row>
     <row r="422">
@@ -5900,10 +5900,10 @@
         </is>
       </c>
       <c r="B422" t="n">
-        <v>0.012839</v>
+        <v>0.012884</v>
       </c>
       <c r="C422" t="n">
-        <v>0.855586</v>
+        <v>0.858696</v>
       </c>
     </row>
     <row r="423">
@@ -5913,10 +5913,10 @@
         </is>
       </c>
       <c r="B423" t="n">
-        <v>0.013047</v>
+        <v>0.012969</v>
       </c>
       <c r="C423" t="n">
-        <v>0.852861</v>
+        <v>0.855978</v>
       </c>
     </row>
     <row r="424">
@@ -5926,10 +5926,10 @@
         </is>
       </c>
       <c r="B424" t="n">
-        <v>0.01339</v>
+        <v>0.013243</v>
       </c>
       <c r="C424" t="n">
-        <v>0.850136</v>
+        <v>0.853261</v>
       </c>
     </row>
     <row r="425">
@@ -5939,10 +5939,10 @@
         </is>
       </c>
       <c r="B425" t="n">
-        <v>0.013577</v>
+        <v>0.013328</v>
       </c>
       <c r="C425" t="n">
-        <v>0.847411</v>
+        <v>0.850543</v>
       </c>
     </row>
     <row r="426">
@@ -5952,10 +5952,10 @@
         </is>
       </c>
       <c r="B426" t="n">
-        <v>0.013992</v>
+        <v>0.013576</v>
       </c>
       <c r="C426" t="n">
-        <v>0.844687</v>
+        <v>0.847826</v>
       </c>
     </row>
     <row r="427">
@@ -5965,10 +5965,10 @@
         </is>
       </c>
       <c r="B427" t="n">
-        <v>0.015067</v>
+        <v>0.013817</v>
       </c>
       <c r="C427" t="n">
-        <v>0.841962</v>
+        <v>0.845109</v>
       </c>
     </row>
     <row r="428">
@@ -5978,10 +5978,10 @@
         </is>
       </c>
       <c r="B428" t="n">
-        <v>0.015198</v>
+        <v>0.014039</v>
       </c>
       <c r="C428" t="n">
-        <v>0.839237</v>
+        <v>0.842391</v>
       </c>
     </row>
     <row r="429">
@@ -5991,10 +5991,10 @@
         </is>
       </c>
       <c r="B429" t="n">
-        <v>0.015329</v>
+        <v>0.015057</v>
       </c>
       <c r="C429" t="n">
-        <v>0.836512</v>
+        <v>0.839674</v>
       </c>
     </row>
     <row r="430">
@@ -6004,10 +6004,10 @@
         </is>
       </c>
       <c r="B430" t="n">
-        <v>0.015528</v>
+        <v>0.015277</v>
       </c>
       <c r="C430" t="n">
-        <v>0.8337869999999999</v>
+        <v>0.836957</v>
       </c>
     </row>
     <row r="431">
@@ -6017,10 +6017,10 @@
         </is>
       </c>
       <c r="B431" t="n">
-        <v>0.015664</v>
+        <v>0.015284</v>
       </c>
       <c r="C431" t="n">
-        <v>0.831063</v>
+        <v>0.834239</v>
       </c>
     </row>
     <row r="432">
@@ -6030,10 +6030,10 @@
         </is>
       </c>
       <c r="B432" t="n">
-        <v>0.015692</v>
+        <v>0.015663</v>
       </c>
       <c r="C432" t="n">
-        <v>0.828338</v>
+        <v>0.831522</v>
       </c>
     </row>
     <row r="433">
@@ -6043,10 +6043,10 @@
         </is>
       </c>
       <c r="B433" t="n">
-        <v>0.016126</v>
+        <v>0.01582</v>
       </c>
       <c r="C433" t="n">
-        <v>0.825613</v>
+        <v>0.828804</v>
       </c>
     </row>
     <row r="434">
@@ -6056,10 +6056,10 @@
         </is>
       </c>
       <c r="B434" t="n">
-        <v>0.016489</v>
+        <v>0.015952</v>
       </c>
       <c r="C434" t="n">
-        <v>0.822888</v>
+        <v>0.826087</v>
       </c>
     </row>
     <row r="435">
@@ -6069,10 +6069,10 @@
         </is>
       </c>
       <c r="B435" t="n">
-        <v>0.016704</v>
+        <v>0.016029</v>
       </c>
       <c r="C435" t="n">
-        <v>0.820163</v>
+        <v>0.82337</v>
       </c>
     </row>
     <row r="436">
@@ -6082,10 +6082,10 @@
         </is>
       </c>
       <c r="B436" t="n">
-        <v>0.016956</v>
+        <v>0.016482</v>
       </c>
       <c r="C436" t="n">
-        <v>0.817439</v>
+        <v>0.820652</v>
       </c>
     </row>
     <row r="437">
@@ -6095,10 +6095,10 @@
         </is>
       </c>
       <c r="B437" t="n">
-        <v>0.017087</v>
+        <v>0.017063</v>
       </c>
       <c r="C437" t="n">
-        <v>0.814714</v>
+        <v>0.817935</v>
       </c>
     </row>
     <row r="438">
@@ -6108,10 +6108,10 @@
         </is>
       </c>
       <c r="B438" t="n">
-        <v>0.017274</v>
+        <v>0.017097</v>
       </c>
       <c r="C438" t="n">
-        <v>0.811989</v>
+        <v>0.815217</v>
       </c>
     </row>
     <row r="439">
@@ -6121,10 +6121,10 @@
         </is>
       </c>
       <c r="B439" t="n">
-        <v>0.017479</v>
+        <v>0.017151</v>
       </c>
       <c r="C439" t="n">
-        <v>0.809264</v>
+        <v>0.8125</v>
       </c>
     </row>
     <row r="440">
@@ -6134,10 +6134,10 @@
         </is>
       </c>
       <c r="B440" t="n">
-        <v>0.017715</v>
+        <v>0.017156</v>
       </c>
       <c r="C440" t="n">
-        <v>0.80654</v>
+        <v>0.809783</v>
       </c>
     </row>
     <row r="441">
@@ -6147,10 +6147,10 @@
         </is>
       </c>
       <c r="B441" t="n">
-        <v>0.018035</v>
+        <v>0.017482</v>
       </c>
       <c r="C441" t="n">
-        <v>0.8038149999999999</v>
+        <v>0.807065</v>
       </c>
     </row>
     <row r="442">
@@ -6160,10 +6160,10 @@
         </is>
       </c>
       <c r="B442" t="n">
-        <v>0.01809</v>
+        <v>0.017533</v>
       </c>
       <c r="C442" t="n">
-        <v>0.80109</v>
+        <v>0.804348</v>
       </c>
     </row>
     <row r="443">
@@ -6173,10 +6173,10 @@
         </is>
       </c>
       <c r="B443" t="n">
-        <v>0.018262</v>
+        <v>0.018054</v>
       </c>
       <c r="C443" t="n">
-        <v>0.798365</v>
+        <v>0.80163</v>
       </c>
     </row>
     <row r="444">
@@ -6186,10 +6186,10 @@
         </is>
       </c>
       <c r="B444" t="n">
-        <v>0.018929</v>
+        <v>0.018311</v>
       </c>
       <c r="C444" t="n">
-        <v>0.79564</v>
+        <v>0.798913</v>
       </c>
     </row>
     <row r="445">
@@ -6199,10 +6199,10 @@
         </is>
       </c>
       <c r="B445" t="n">
-        <v>0.019002</v>
+        <v>0.018438</v>
       </c>
       <c r="C445" t="n">
-        <v>0.792916</v>
+        <v>0.796196</v>
       </c>
     </row>
     <row r="446">
@@ -6212,10 +6212,10 @@
         </is>
       </c>
       <c r="B446" t="n">
-        <v>0.019017</v>
+        <v>0.019053</v>
       </c>
       <c r="C446" t="n">
-        <v>0.790191</v>
+        <v>0.793478</v>
       </c>
     </row>
     <row r="447">
@@ -6225,10 +6225,10 @@
         </is>
       </c>
       <c r="B447" t="n">
-        <v>0.019102</v>
+        <v>0.019121</v>
       </c>
       <c r="C447" t="n">
-        <v>0.787466</v>
+        <v>0.790761</v>
       </c>
     </row>
     <row r="448">
@@ -6238,10 +6238,10 @@
         </is>
       </c>
       <c r="B448" t="n">
-        <v>0.019446</v>
+        <v>0.019252</v>
       </c>
       <c r="C448" t="n">
-        <v>0.784741</v>
+        <v>0.788043</v>
       </c>
     </row>
     <row r="449">
@@ -6251,10 +6251,10 @@
         </is>
       </c>
       <c r="B449" t="n">
-        <v>0.019602</v>
+        <v>0.019362</v>
       </c>
       <c r="C449" t="n">
-        <v>0.782016</v>
+        <v>0.785326</v>
       </c>
     </row>
     <row r="450">
@@ -6264,10 +6264,10 @@
         </is>
       </c>
       <c r="B450" t="n">
-        <v>0.020677</v>
+        <v>0.019387</v>
       </c>
       <c r="C450" t="n">
-        <v>0.779292</v>
+        <v>0.782609</v>
       </c>
     </row>
     <row r="451">
@@ -6277,10 +6277,10 @@
         </is>
       </c>
       <c r="B451" t="n">
-        <v>0.020788</v>
+        <v>0.019478</v>
       </c>
       <c r="C451" t="n">
-        <v>0.776567</v>
+        <v>0.779891</v>
       </c>
     </row>
     <row r="452">
@@ -6290,10 +6290,10 @@
         </is>
       </c>
       <c r="B452" t="n">
-        <v>0.02097</v>
+        <v>0.020561</v>
       </c>
       <c r="C452" t="n">
-        <v>0.773842</v>
+        <v>0.777174</v>
       </c>
     </row>
     <row r="453">
@@ -6303,10 +6303,10 @@
         </is>
       </c>
       <c r="B453" t="n">
-        <v>0.021199</v>
+        <v>0.020755</v>
       </c>
       <c r="C453" t="n">
-        <v>0.7711170000000001</v>
+        <v>0.774457</v>
       </c>
     </row>
     <row r="454">
@@ -6316,10 +6316,10 @@
         </is>
       </c>
       <c r="B454" t="n">
-        <v>0.021668</v>
+        <v>0.021092</v>
       </c>
       <c r="C454" t="n">
-        <v>0.768392</v>
+        <v>0.771739</v>
       </c>
     </row>
     <row r="455">
@@ -6329,10 +6329,10 @@
         </is>
       </c>
       <c r="B455" t="n">
-        <v>0.02197</v>
+        <v>0.021536</v>
       </c>
       <c r="C455" t="n">
-        <v>0.765668</v>
+        <v>0.769022</v>
       </c>
     </row>
     <row r="456">
@@ -6342,10 +6342,10 @@
         </is>
       </c>
       <c r="B456" t="n">
-        <v>0.022517</v>
+        <v>0.02172</v>
       </c>
       <c r="C456" t="n">
-        <v>0.762943</v>
+        <v>0.766304</v>
       </c>
     </row>
     <row r="457">
@@ -6355,10 +6355,10 @@
         </is>
       </c>
       <c r="B457" t="n">
-        <v>0.022992</v>
+        <v>0.022173</v>
       </c>
       <c r="C457" t="n">
-        <v>0.7602179999999999</v>
+        <v>0.763587</v>
       </c>
     </row>
     <row r="458">
@@ -6368,10 +6368,10 @@
         </is>
       </c>
       <c r="B458" t="n">
-        <v>0.023838</v>
+        <v>0.022371</v>
       </c>
       <c r="C458" t="n">
-        <v>0.757493</v>
+        <v>0.76087</v>
       </c>
     </row>
     <row r="459">
@@ -6381,10 +6381,10 @@
         </is>
       </c>
       <c r="B459" t="n">
-        <v>0.024054</v>
+        <v>0.02338</v>
       </c>
       <c r="C459" t="n">
-        <v>0.754768</v>
+        <v>0.758152</v>
       </c>
     </row>
     <row r="460">
@@ -6394,10 +6394,10 @@
         </is>
       </c>
       <c r="B460" t="n">
-        <v>0.024239</v>
+        <v>0.023403</v>
       </c>
       <c r="C460" t="n">
-        <v>0.752044</v>
+        <v>0.755435</v>
       </c>
     </row>
     <row r="461">
@@ -6407,10 +6407,10 @@
         </is>
       </c>
       <c r="B461" t="n">
-        <v>0.024485</v>
+        <v>0.023862</v>
       </c>
       <c r="C461" t="n">
-        <v>0.749319</v>
+        <v>0.752717</v>
       </c>
     </row>
     <row r="462">
@@ -6420,10 +6420,10 @@
         </is>
       </c>
       <c r="B462" t="n">
-        <v>0.024714</v>
+        <v>0.024222</v>
       </c>
       <c r="C462" t="n">
-        <v>0.746594</v>
+        <v>0.75</v>
       </c>
     </row>
     <row r="463">
@@ -6433,10 +6433,10 @@
         </is>
       </c>
       <c r="B463" t="n">
-        <v>0.025205</v>
+        <v>0.024862</v>
       </c>
       <c r="C463" t="n">
-        <v>0.743869</v>
+        <v>0.747283</v>
       </c>
     </row>
     <row r="464">
@@ -6446,10 +6446,10 @@
         </is>
       </c>
       <c r="B464" t="n">
-        <v>0.025259</v>
+        <v>0.025123</v>
       </c>
       <c r="C464" t="n">
-        <v>0.741144</v>
+        <v>0.744565</v>
       </c>
     </row>
     <row r="465">
@@ -6459,10 +6459,10 @@
         </is>
       </c>
       <c r="B465" t="n">
-        <v>0.025313</v>
+        <v>0.025125</v>
       </c>
       <c r="C465" t="n">
-        <v>0.73842</v>
+        <v>0.741848</v>
       </c>
     </row>
     <row r="466">
@@ -6472,10 +6472,10 @@
         </is>
       </c>
       <c r="B466" t="n">
-        <v>0.02551</v>
+        <v>0.025128</v>
       </c>
       <c r="C466" t="n">
-        <v>0.735695</v>
+        <v>0.73913</v>
       </c>
     </row>
     <row r="467">
@@ -6485,10 +6485,10 @@
         </is>
       </c>
       <c r="B467" t="n">
-        <v>0.025777</v>
+        <v>0.025317</v>
       </c>
       <c r="C467" t="n">
-        <v>0.73297</v>
+        <v>0.736413</v>
       </c>
     </row>
     <row r="468">
@@ -6498,10 +6498,10 @@
         </is>
       </c>
       <c r="B468" t="n">
-        <v>0.026013</v>
+        <v>0.025363</v>
       </c>
       <c r="C468" t="n">
-        <v>0.730245</v>
+        <v>0.733696</v>
       </c>
     </row>
     <row r="469">
@@ -6511,10 +6511,10 @@
         </is>
       </c>
       <c r="B469" t="n">
-        <v>0.026329</v>
+        <v>0.02567</v>
       </c>
       <c r="C469" t="n">
-        <v>0.7275199999999999</v>
+        <v>0.730978</v>
       </c>
     </row>
     <row r="470">
@@ -6524,10 +6524,10 @@
         </is>
       </c>
       <c r="B470" t="n">
-        <v>0.027274</v>
+        <v>0.025842</v>
       </c>
       <c r="C470" t="n">
-        <v>0.724796</v>
+        <v>0.728261</v>
       </c>
     </row>
     <row r="471">
@@ -6537,10 +6537,10 @@
         </is>
       </c>
       <c r="B471" t="n">
-        <v>0.027389</v>
+        <v>0.02588</v>
       </c>
       <c r="C471" t="n">
-        <v>0.722071</v>
+        <v>0.725543</v>
       </c>
     </row>
     <row r="472">
@@ -6550,10 +6550,10 @@
         </is>
       </c>
       <c r="B472" t="n">
-        <v>0.027418</v>
+        <v>0.026926</v>
       </c>
       <c r="C472" t="n">
-        <v>0.719346</v>
+        <v>0.722826</v>
       </c>
     </row>
     <row r="473">
@@ -6563,10 +6563,10 @@
         </is>
       </c>
       <c r="B473" t="n">
-        <v>0.027444</v>
+        <v>0.027141</v>
       </c>
       <c r="C473" t="n">
-        <v>0.716621</v>
+        <v>0.720109</v>
       </c>
     </row>
     <row r="474">
@@ -6576,10 +6576,10 @@
         </is>
       </c>
       <c r="B474" t="n">
-        <v>0.027611</v>
+        <v>0.027503</v>
       </c>
       <c r="C474" t="n">
-        <v>0.713896</v>
+        <v>0.717391</v>
       </c>
     </row>
     <row r="475">
@@ -6589,10 +6589,10 @@
         </is>
       </c>
       <c r="B475" t="n">
-        <v>0.027768</v>
+        <v>0.027642</v>
       </c>
       <c r="C475" t="n">
-        <v>0.711172</v>
+        <v>0.714674</v>
       </c>
     </row>
     <row r="476">
@@ -6602,10 +6602,10 @@
         </is>
       </c>
       <c r="B476" t="n">
-        <v>0.027782</v>
+        <v>0.027917</v>
       </c>
       <c r="C476" t="n">
-        <v>0.708447</v>
+        <v>0.711957</v>
       </c>
     </row>
     <row r="477">
@@ -6615,10 +6615,10 @@
         </is>
       </c>
       <c r="B477" t="n">
-        <v>0.028126</v>
+        <v>0.027991</v>
       </c>
       <c r="C477" t="n">
-        <v>0.705722</v>
+        <v>0.709239</v>
       </c>
     </row>
     <row r="478">
@@ -6628,10 +6628,10 @@
         </is>
       </c>
       <c r="B478" t="n">
-        <v>0.028144</v>
+        <v>0.028249</v>
       </c>
       <c r="C478" t="n">
-        <v>0.702997</v>
+        <v>0.706522</v>
       </c>
     </row>
     <row r="479">
@@ -6641,10 +6641,10 @@
         </is>
       </c>
       <c r="B479" t="n">
-        <v>0.028296</v>
+        <v>0.028486</v>
       </c>
       <c r="C479" t="n">
-        <v>0.700272</v>
+        <v>0.703804</v>
       </c>
     </row>
     <row r="480">
@@ -6654,10 +6654,10 @@
         </is>
       </c>
       <c r="B480" t="n">
-        <v>0.02878</v>
+        <v>0.028603</v>
       </c>
       <c r="C480" t="n">
-        <v>0.6975479999999999</v>
+        <v>0.701087</v>
       </c>
     </row>
     <row r="481">
@@ -6667,10 +6667,10 @@
         </is>
       </c>
       <c r="B481" t="n">
-        <v>0.029052</v>
+        <v>0.028868</v>
       </c>
       <c r="C481" t="n">
-        <v>0.694823</v>
+        <v>0.69837</v>
       </c>
     </row>
     <row r="482">
@@ -6680,10 +6680,10 @@
         </is>
       </c>
       <c r="B482" t="n">
-        <v>0.029307</v>
+        <v>0.028891</v>
       </c>
       <c r="C482" t="n">
-        <v>0.692098</v>
+        <v>0.695652</v>
       </c>
     </row>
     <row r="483">
@@ -6693,10 +6693,10 @@
         </is>
       </c>
       <c r="B483" t="n">
-        <v>0.029538</v>
+        <v>0.029493</v>
       </c>
       <c r="C483" t="n">
-        <v>0.689373</v>
+        <v>0.692935</v>
       </c>
     </row>
     <row r="484">
@@ -6706,10 +6706,10 @@
         </is>
       </c>
       <c r="B484" t="n">
-        <v>0.029644</v>
+        <v>0.029576</v>
       </c>
       <c r="C484" t="n">
-        <v>0.686649</v>
+        <v>0.690217</v>
       </c>
     </row>
     <row r="485">
@@ -6719,10 +6719,10 @@
         </is>
       </c>
       <c r="B485" t="n">
-        <v>0.030029</v>
+        <v>0.029871</v>
       </c>
       <c r="C485" t="n">
-        <v>0.683924</v>
+        <v>0.6875</v>
       </c>
     </row>
     <row r="486">
@@ -6732,10 +6732,10 @@
         </is>
       </c>
       <c r="B486" t="n">
-        <v>0.030292</v>
+        <v>0.029943</v>
       </c>
       <c r="C486" t="n">
-        <v>0.681199</v>
+        <v>0.684783</v>
       </c>
     </row>
     <row r="487">
@@ -6745,10 +6745,10 @@
         </is>
       </c>
       <c r="B487" t="n">
-        <v>0.030311</v>
+        <v>0.030038</v>
       </c>
       <c r="C487" t="n">
-        <v>0.678474</v>
+        <v>0.682065</v>
       </c>
     </row>
     <row r="488">
@@ -6758,10 +6758,10 @@
         </is>
       </c>
       <c r="B488" t="n">
-        <v>0.03044</v>
+        <v>0.030078</v>
       </c>
       <c r="C488" t="n">
-        <v>0.675749</v>
+        <v>0.679348</v>
       </c>
     </row>
     <row r="489">
@@ -6771,10 +6771,10 @@
         </is>
       </c>
       <c r="B489" t="n">
-        <v>0.030882</v>
+        <v>0.030154</v>
       </c>
       <c r="C489" t="n">
-        <v>0.673025</v>
+        <v>0.67663</v>
       </c>
     </row>
     <row r="490">
@@ -6784,10 +6784,10 @@
         </is>
       </c>
       <c r="B490" t="n">
-        <v>0.0311</v>
+        <v>0.030558</v>
       </c>
       <c r="C490" t="n">
-        <v>0.6703</v>
+        <v>0.673913</v>
       </c>
     </row>
     <row r="491">
@@ -6797,10 +6797,10 @@
         </is>
       </c>
       <c r="B491" t="n">
-        <v>0.03133</v>
+        <v>0.031231</v>
       </c>
       <c r="C491" t="n">
-        <v>0.667575</v>
+        <v>0.671196</v>
       </c>
     </row>
     <row r="492">
@@ -6810,10 +6810,10 @@
         </is>
       </c>
       <c r="B492" t="n">
-        <v>0.03175</v>
+        <v>0.031258</v>
       </c>
       <c r="C492" t="n">
-        <v>0.6648500000000001</v>
+        <v>0.668478</v>
       </c>
     </row>
     <row r="493">
@@ -6823,10 +6823,10 @@
         </is>
       </c>
       <c r="B493" t="n">
-        <v>0.032586</v>
+        <v>0.031993</v>
       </c>
       <c r="C493" t="n">
-        <v>0.662125</v>
+        <v>0.665761</v>
       </c>
     </row>
     <row r="494">
@@ -6836,10 +6836,10 @@
         </is>
       </c>
       <c r="B494" t="n">
-        <v>0.032694</v>
+        <v>0.032085</v>
       </c>
       <c r="C494" t="n">
-        <v>0.659401</v>
+        <v>0.663043</v>
       </c>
     </row>
     <row r="495">
@@ -6849,10 +6849,10 @@
         </is>
       </c>
       <c r="B495" t="n">
-        <v>0.032807</v>
+        <v>0.032133</v>
       </c>
       <c r="C495" t="n">
-        <v>0.656676</v>
+        <v>0.660326</v>
       </c>
     </row>
     <row r="496">
@@ -6862,10 +6862,10 @@
         </is>
       </c>
       <c r="B496" t="n">
-        <v>0.032818</v>
+        <v>0.032733</v>
       </c>
       <c r="C496" t="n">
-        <v>0.6539509999999999</v>
+        <v>0.657609</v>
       </c>
     </row>
     <row r="497">
@@ -6875,10 +6875,10 @@
         </is>
       </c>
       <c r="B497" t="n">
-        <v>0.033753</v>
+        <v>0.033574</v>
       </c>
       <c r="C497" t="n">
-        <v>0.651226</v>
+        <v>0.654891</v>
       </c>
     </row>
     <row r="498">
@@ -6888,10 +6888,10 @@
         </is>
       </c>
       <c r="B498" t="n">
-        <v>0.033985</v>
+        <v>0.03376</v>
       </c>
       <c r="C498" t="n">
-        <v>0.648501</v>
+        <v>0.652174</v>
       </c>
     </row>
     <row r="499">
@@ -6901,10 +6901,10 @@
         </is>
       </c>
       <c r="B499" t="n">
-        <v>0.034032</v>
+        <v>0.03386</v>
       </c>
       <c r="C499" t="n">
-        <v>0.645777</v>
+        <v>0.649457</v>
       </c>
     </row>
     <row r="500">
@@ -6914,10 +6914,10 @@
         </is>
       </c>
       <c r="B500" t="n">
-        <v>0.034287</v>
+        <v>0.03392</v>
       </c>
       <c r="C500" t="n">
-        <v>0.643052</v>
+        <v>0.646739</v>
       </c>
     </row>
     <row r="501">
@@ -6927,10 +6927,10 @@
         </is>
       </c>
       <c r="B501" t="n">
-        <v>0.034379</v>
+        <v>0.033963</v>
       </c>
       <c r="C501" t="n">
-        <v>0.640327</v>
+        <v>0.644022</v>
       </c>
     </row>
     <row r="502">
@@ -6940,10 +6940,10 @@
         </is>
       </c>
       <c r="B502" t="n">
-        <v>0.034518</v>
+        <v>0.034112</v>
       </c>
       <c r="C502" t="n">
-        <v>0.637602</v>
+        <v>0.641304</v>
       </c>
     </row>
     <row r="503">
@@ -6953,10 +6953,10 @@
         </is>
       </c>
       <c r="B503" t="n">
-        <v>0.034532</v>
+        <v>0.034614</v>
       </c>
       <c r="C503" t="n">
-        <v>0.634877</v>
+        <v>0.638587</v>
       </c>
     </row>
     <row r="504">
@@ -6966,10 +6966,10 @@
         </is>
       </c>
       <c r="B504" t="n">
-        <v>0.03473</v>
+        <v>0.034674</v>
       </c>
       <c r="C504" t="n">
-        <v>0.632153</v>
+        <v>0.63587</v>
       </c>
     </row>
     <row r="505">
@@ -6979,10 +6979,10 @@
         </is>
       </c>
       <c r="B505" t="n">
-        <v>0.035098</v>
+        <v>0.034699</v>
       </c>
       <c r="C505" t="n">
-        <v>0.629428</v>
+        <v>0.633152</v>
       </c>
     </row>
     <row r="506">
@@ -6992,10 +6992,10 @@
         </is>
       </c>
       <c r="B506" t="n">
-        <v>0.035145</v>
+        <v>0.03487</v>
       </c>
       <c r="C506" t="n">
-        <v>0.626703</v>
+        <v>0.630435</v>
       </c>
     </row>
     <row r="507">
@@ -7005,10 +7005,10 @@
         </is>
       </c>
       <c r="B507" t="n">
-        <v>0.035805</v>
+        <v>0.035083</v>
       </c>
       <c r="C507" t="n">
-        <v>0.623978</v>
+        <v>0.627717</v>
       </c>
     </row>
     <row r="508">
@@ -7018,10 +7018,10 @@
         </is>
       </c>
       <c r="B508" t="n">
-        <v>0.036</v>
+        <v>0.035377</v>
       </c>
       <c r="C508" t="n">
-        <v>0.6212530000000001</v>
+        <v>0.625</v>
       </c>
     </row>
     <row r="509">
@@ -7031,10 +7031,10 @@
         </is>
       </c>
       <c r="B509" t="n">
-        <v>0.036602</v>
+        <v>0.0354</v>
       </c>
       <c r="C509" t="n">
-        <v>0.618529</v>
+        <v>0.622283</v>
       </c>
     </row>
     <row r="510">
@@ -7044,10 +7044,10 @@
         </is>
       </c>
       <c r="B510" t="n">
-        <v>0.036885</v>
+        <v>0.036</v>
       </c>
       <c r="C510" t="n">
-        <v>0.615804</v>
+        <v>0.619565</v>
       </c>
     </row>
     <row r="511">
@@ -7057,10 +7057,10 @@
         </is>
       </c>
       <c r="B511" t="n">
-        <v>0.037297</v>
+        <v>0.036284</v>
       </c>
       <c r="C511" t="n">
-        <v>0.613079</v>
+        <v>0.616848</v>
       </c>
     </row>
     <row r="512">
@@ -7070,10 +7070,10 @@
         </is>
       </c>
       <c r="B512" t="n">
-        <v>0.037747</v>
+        <v>0.037507</v>
       </c>
       <c r="C512" t="n">
-        <v>0.610354</v>
+        <v>0.61413</v>
       </c>
     </row>
     <row r="513">
@@ -7083,10 +7083,10 @@
         </is>
       </c>
       <c r="B513" t="n">
-        <v>0.037931</v>
+        <v>0.037653</v>
       </c>
       <c r="C513" t="n">
-        <v>0.607629</v>
+        <v>0.611413</v>
       </c>
     </row>
     <row r="514">
@@ -7096,10 +7096,10 @@
         </is>
       </c>
       <c r="B514" t="n">
-        <v>0.03797</v>
+        <v>0.037745</v>
       </c>
       <c r="C514" t="n">
-        <v>0.604905</v>
+        <v>0.608696</v>
       </c>
     </row>
     <row r="515">
@@ -7109,10 +7109,10 @@
         </is>
       </c>
       <c r="B515" t="n">
-        <v>0.038469</v>
+        <v>0.038517</v>
       </c>
       <c r="C515" t="n">
-        <v>0.60218</v>
+        <v>0.605978</v>
       </c>
     </row>
     <row r="516">
@@ -7122,10 +7122,10 @@
         </is>
       </c>
       <c r="B516" t="n">
-        <v>0.038746</v>
+        <v>0.038555</v>
       </c>
       <c r="C516" t="n">
-        <v>0.599455</v>
+        <v>0.603261</v>
       </c>
     </row>
     <row r="517">
@@ -7135,10 +7135,10 @@
         </is>
       </c>
       <c r="B517" t="n">
-        <v>0.038914</v>
+        <v>0.038556</v>
       </c>
       <c r="C517" t="n">
-        <v>0.59673</v>
+        <v>0.600543</v>
       </c>
     </row>
     <row r="518">
@@ -7148,10 +7148,10 @@
         </is>
       </c>
       <c r="B518" t="n">
-        <v>0.039088</v>
+        <v>0.039037</v>
       </c>
       <c r="C518" t="n">
-        <v>0.594005</v>
+        <v>0.597826</v>
       </c>
     </row>
     <row r="519">
@@ -7161,10 +7161,10 @@
         </is>
       </c>
       <c r="B519" t="n">
-        <v>0.039287</v>
+        <v>0.039205</v>
       </c>
       <c r="C519" t="n">
-        <v>0.5912809999999999</v>
+        <v>0.595109</v>
       </c>
     </row>
     <row r="520">
@@ -7174,10 +7174,10 @@
         </is>
       </c>
       <c r="B520" t="n">
-        <v>0.039627</v>
+        <v>0.039382</v>
       </c>
       <c r="C520" t="n">
-        <v>0.588556</v>
+        <v>0.592391</v>
       </c>
     </row>
     <row r="521">
@@ -7187,10 +7187,10 @@
         </is>
       </c>
       <c r="B521" t="n">
-        <v>0.039653</v>
+        <v>0.039644</v>
       </c>
       <c r="C521" t="n">
-        <v>0.585831</v>
+        <v>0.589674</v>
       </c>
     </row>
     <row r="522">
@@ -7200,10 +7200,10 @@
         </is>
       </c>
       <c r="B522" t="n">
-        <v>0.039782</v>
+        <v>0.039784</v>
       </c>
       <c r="C522" t="n">
-        <v>0.583106</v>
+        <v>0.586957</v>
       </c>
     </row>
     <row r="523">
@@ -7213,10 +7213,10 @@
         </is>
       </c>
       <c r="B523" t="n">
-        <v>0.04032</v>
+        <v>0.040018</v>
       </c>
       <c r="C523" t="n">
-        <v>0.580381</v>
+        <v>0.584239</v>
       </c>
     </row>
     <row r="524">
@@ -7226,10 +7226,10 @@
         </is>
       </c>
       <c r="B524" t="n">
-        <v>0.04091</v>
+        <v>0.040251</v>
       </c>
       <c r="C524" t="n">
-        <v>0.577657</v>
+        <v>0.581522</v>
       </c>
     </row>
     <row r="525">
@@ -7239,10 +7239,10 @@
         </is>
       </c>
       <c r="B525" t="n">
-        <v>0.041075</v>
+        <v>0.040529</v>
       </c>
       <c r="C525" t="n">
-        <v>0.574932</v>
+        <v>0.578804</v>
       </c>
     </row>
     <row r="526">
@@ -7252,10 +7252,10 @@
         </is>
       </c>
       <c r="B526" t="n">
-        <v>0.041331</v>
+        <v>0.04167</v>
       </c>
       <c r="C526" t="n">
-        <v>0.572207</v>
+        <v>0.576087</v>
       </c>
     </row>
     <row r="527">
@@ -7265,10 +7265,10 @@
         </is>
       </c>
       <c r="B527" t="n">
-        <v>0.041574</v>
+        <v>0.041827</v>
       </c>
       <c r="C527" t="n">
-        <v>0.569482</v>
+        <v>0.57337</v>
       </c>
     </row>
     <row r="528">
@@ -7278,10 +7278,10 @@
         </is>
       </c>
       <c r="B528" t="n">
-        <v>0.041575</v>
+        <v>0.042015</v>
       </c>
       <c r="C528" t="n">
-        <v>0.566757</v>
+        <v>0.570652</v>
       </c>
     </row>
     <row r="529">
@@ -7291,10 +7291,10 @@
         </is>
       </c>
       <c r="B529" t="n">
-        <v>0.041684</v>
+        <v>0.042187</v>
       </c>
       <c r="C529" t="n">
-        <v>0.564033</v>
+        <v>0.567935</v>
       </c>
     </row>
     <row r="530">
@@ -7304,10 +7304,10 @@
         </is>
       </c>
       <c r="B530" t="n">
-        <v>0.042129</v>
+        <v>0.042475</v>
       </c>
       <c r="C530" t="n">
-        <v>0.561308</v>
+        <v>0.565217</v>
       </c>
     </row>
     <row r="531">
@@ -7317,10 +7317,10 @@
         </is>
       </c>
       <c r="B531" t="n">
-        <v>0.042725</v>
+        <v>0.04255</v>
       </c>
       <c r="C531" t="n">
-        <v>0.5585830000000001</v>
+        <v>0.5625</v>
       </c>
     </row>
     <row r="532">
@@ -7330,10 +7330,10 @@
         </is>
       </c>
       <c r="B532" t="n">
-        <v>0.042904</v>
+        <v>0.042673</v>
       </c>
       <c r="C532" t="n">
-        <v>0.555858</v>
+        <v>0.559783</v>
       </c>
     </row>
     <row r="533">
@@ -7343,10 +7343,10 @@
         </is>
       </c>
       <c r="B533" t="n">
-        <v>0.042904</v>
+        <v>0.042967</v>
       </c>
       <c r="C533" t="n">
-        <v>0.553134</v>
+        <v>0.557065</v>
       </c>
     </row>
     <row r="534">
@@ -7356,10 +7356,10 @@
         </is>
       </c>
       <c r="B534" t="n">
-        <v>0.04317</v>
+        <v>0.042974</v>
       </c>
       <c r="C534" t="n">
-        <v>0.550409</v>
+        <v>0.554348</v>
       </c>
     </row>
     <row r="535">
@@ -7369,10 +7369,10 @@
         </is>
       </c>
       <c r="B535" t="n">
-        <v>0.043192</v>
+        <v>0.043181</v>
       </c>
       <c r="C535" t="n">
-        <v>0.5476839999999999</v>
+        <v>0.55163</v>
       </c>
     </row>
     <row r="536">
@@ -7382,10 +7382,10 @@
         </is>
       </c>
       <c r="B536" t="n">
-        <v>0.043237</v>
+        <v>0.043192</v>
       </c>
       <c r="C536" t="n">
-        <v>0.544959</v>
+        <v>0.548913</v>
       </c>
     </row>
     <row r="537">
@@ -7395,10 +7395,10 @@
         </is>
       </c>
       <c r="B537" t="n">
-        <v>0.043289</v>
+        <v>0.043392</v>
       </c>
       <c r="C537" t="n">
-        <v>0.542234</v>
+        <v>0.546196</v>
       </c>
     </row>
     <row r="538">
@@ -7408,10 +7408,10 @@
         </is>
       </c>
       <c r="B538" t="n">
-        <v>0.043753</v>
+        <v>0.043414</v>
       </c>
       <c r="C538" t="n">
-        <v>0.53951</v>
+        <v>0.543478</v>
       </c>
     </row>
     <row r="539">
@@ -7421,10 +7421,10 @@
         </is>
       </c>
       <c r="B539" t="n">
-        <v>0.043966</v>
+        <v>0.04374</v>
       </c>
       <c r="C539" t="n">
-        <v>0.536785</v>
+        <v>0.540761</v>
       </c>
     </row>
     <row r="540">
@@ -7434,10 +7434,10 @@
         </is>
       </c>
       <c r="B540" t="n">
-        <v>0.044188</v>
+        <v>0.043888</v>
       </c>
       <c r="C540" t="n">
-        <v>0.53406</v>
+        <v>0.538043</v>
       </c>
     </row>
     <row r="541">
@@ -7447,10 +7447,10 @@
         </is>
       </c>
       <c r="B541" t="n">
-        <v>0.044568</v>
+        <v>0.044514</v>
       </c>
       <c r="C541" t="n">
-        <v>0.531335</v>
+        <v>0.535326</v>
       </c>
     </row>
     <row r="542">
@@ -7460,10 +7460,10 @@
         </is>
       </c>
       <c r="B542" t="n">
-        <v>0.045008</v>
+        <v>0.044625</v>
       </c>
       <c r="C542" t="n">
-        <v>0.52861</v>
+        <v>0.532609</v>
       </c>
     </row>
     <row r="543">
@@ -7473,10 +7473,10 @@
         </is>
       </c>
       <c r="B543" t="n">
-        <v>0.045086</v>
+        <v>0.044781</v>
       </c>
       <c r="C543" t="n">
-        <v>0.525886</v>
+        <v>0.529891</v>
       </c>
     </row>
     <row r="544">
@@ -7486,10 +7486,10 @@
         </is>
       </c>
       <c r="B544" t="n">
-        <v>0.045407</v>
+        <v>0.045068</v>
       </c>
       <c r="C544" t="n">
-        <v>0.523161</v>
+        <v>0.527174</v>
       </c>
     </row>
     <row r="545">
@@ -7499,10 +7499,10 @@
         </is>
       </c>
       <c r="B545" t="n">
-        <v>0.045736</v>
+        <v>0.045227</v>
       </c>
       <c r="C545" t="n">
-        <v>0.520436</v>
+        <v>0.524457</v>
       </c>
     </row>
     <row r="546">
@@ -7512,10 +7512,10 @@
         </is>
       </c>
       <c r="B546" t="n">
-        <v>0.045738</v>
+        <v>0.04539</v>
       </c>
       <c r="C546" t="n">
-        <v>0.517711</v>
+        <v>0.521739</v>
       </c>
     </row>
     <row r="547">
@@ -7525,10 +7525,10 @@
         </is>
       </c>
       <c r="B547" t="n">
-        <v>0.046461</v>
+        <v>0.045593</v>
       </c>
       <c r="C547" t="n">
-        <v>0.5149860000000001</v>
+        <v>0.519022</v>
       </c>
     </row>
     <row r="548">
@@ -7538,10 +7538,10 @@
         </is>
       </c>
       <c r="B548" t="n">
-        <v>0.047411</v>
+        <v>0.04626</v>
       </c>
       <c r="C548" t="n">
-        <v>0.512262</v>
+        <v>0.516304</v>
       </c>
     </row>
     <row r="549">
@@ -7551,10 +7551,10 @@
         </is>
       </c>
       <c r="B549" t="n">
-        <v>0.047793</v>
+        <v>0.046845</v>
       </c>
       <c r="C549" t="n">
-        <v>0.509537</v>
+        <v>0.513587</v>
       </c>
     </row>
     <row r="550">
@@ -7564,10 +7564,10 @@
         </is>
       </c>
       <c r="B550" t="n">
-        <v>0.047894</v>
+        <v>0.047096</v>
       </c>
       <c r="C550" t="n">
-        <v>0.506812</v>
+        <v>0.51087</v>
       </c>
     </row>
     <row r="551">
@@ -7577,10 +7577,10 @@
         </is>
       </c>
       <c r="B551" t="n">
-        <v>0.047915</v>
+        <v>0.047595</v>
       </c>
       <c r="C551" t="n">
-        <v>0.504087</v>
+        <v>0.508152</v>
       </c>
     </row>
     <row r="552">
@@ -7590,10 +7590,10 @@
         </is>
       </c>
       <c r="B552" t="n">
-        <v>0.047994</v>
+        <v>0.047765</v>
       </c>
       <c r="C552" t="n">
-        <v>0.501362</v>
+        <v>0.505435</v>
       </c>
     </row>
     <row r="553">
@@ -7603,10 +7603,10 @@
         </is>
       </c>
       <c r="B553" t="n">
-        <v>0.048197</v>
+        <v>0.048177</v>
       </c>
       <c r="C553" t="n">
-        <v>0.498638</v>
+        <v>0.502717</v>
       </c>
     </row>
     <row r="554">
@@ -7616,10 +7616,10 @@
         </is>
       </c>
       <c r="B554" t="n">
-        <v>0.049639</v>
+        <v>0.04899</v>
       </c>
       <c r="C554" t="n">
-        <v>0.495913</v>
+        <v>0.5</v>
       </c>
     </row>
     <row r="555">
@@ -7629,10 +7629,10 @@
         </is>
       </c>
       <c r="B555" t="n">
-        <v>0.05038</v>
+        <v>0.049385</v>
       </c>
       <c r="C555" t="n">
-        <v>0.493188</v>
+        <v>0.497283</v>
       </c>
     </row>
     <row r="556">
@@ -7642,10 +7642,10 @@
         </is>
       </c>
       <c r="B556" t="n">
-        <v>0.050796</v>
+        <v>0.049416</v>
       </c>
       <c r="C556" t="n">
-        <v>0.490463</v>
+        <v>0.494565</v>
       </c>
     </row>
     <row r="557">
@@ -7655,10 +7655,10 @@
         </is>
       </c>
       <c r="B557" t="n">
-        <v>0.050916</v>
+        <v>0.049541</v>
       </c>
       <c r="C557" t="n">
-        <v>0.487738</v>
+        <v>0.491848</v>
       </c>
     </row>
     <row r="558">
@@ -7668,10 +7668,10 @@
         </is>
       </c>
       <c r="B558" t="n">
-        <v>0.051789</v>
+        <v>0.050824</v>
       </c>
       <c r="C558" t="n">
-        <v>0.485014</v>
+        <v>0.48913</v>
       </c>
     </row>
     <row r="559">
@@ -7681,10 +7681,10 @@
         </is>
       </c>
       <c r="B559" t="n">
-        <v>0.052526</v>
+        <v>0.051619</v>
       </c>
       <c r="C559" t="n">
-        <v>0.482289</v>
+        <v>0.486413</v>
       </c>
     </row>
     <row r="560">
@@ -7694,10 +7694,10 @@
         </is>
       </c>
       <c r="B560" t="n">
-        <v>0.05261</v>
+        <v>0.051942</v>
       </c>
       <c r="C560" t="n">
-        <v>0.479564</v>
+        <v>0.483696</v>
       </c>
     </row>
     <row r="561">
@@ -7707,10 +7707,10 @@
         </is>
       </c>
       <c r="B561" t="n">
-        <v>0.052801</v>
+        <v>0.052547</v>
       </c>
       <c r="C561" t="n">
-        <v>0.476839</v>
+        <v>0.480978</v>
       </c>
     </row>
     <row r="562">
@@ -7720,10 +7720,10 @@
         </is>
       </c>
       <c r="B562" t="n">
-        <v>0.053339</v>
+        <v>0.053066</v>
       </c>
       <c r="C562" t="n">
-        <v>0.474114</v>
+        <v>0.478261</v>
       </c>
     </row>
     <row r="563">
@@ -7733,10 +7733,10 @@
         </is>
       </c>
       <c r="B563" t="n">
-        <v>0.053454</v>
+        <v>0.053281</v>
       </c>
       <c r="C563" t="n">
-        <v>0.47139</v>
+        <v>0.475543</v>
       </c>
     </row>
     <row r="564">
@@ -7746,10 +7746,10 @@
         </is>
       </c>
       <c r="B564" t="n">
-        <v>0.053866</v>
+        <v>0.053663</v>
       </c>
       <c r="C564" t="n">
-        <v>0.468665</v>
+        <v>0.472826</v>
       </c>
     </row>
     <row r="565">
@@ -7759,10 +7759,10 @@
         </is>
       </c>
       <c r="B565" t="n">
-        <v>0.054453</v>
+        <v>0.053931</v>
       </c>
       <c r="C565" t="n">
-        <v>0.46594</v>
+        <v>0.470109</v>
       </c>
     </row>
     <row r="566">
@@ -7772,10 +7772,10 @@
         </is>
       </c>
       <c r="B566" t="n">
-        <v>0.054461</v>
+        <v>0.054494</v>
       </c>
       <c r="C566" t="n">
-        <v>0.463215</v>
+        <v>0.467391</v>
       </c>
     </row>
     <row r="567">
@@ -7785,10 +7785,10 @@
         </is>
       </c>
       <c r="B567" t="n">
-        <v>0.055481</v>
+        <v>0.054545</v>
       </c>
       <c r="C567" t="n">
-        <v>0.46049</v>
+        <v>0.464674</v>
       </c>
     </row>
     <row r="568">
@@ -7798,10 +7798,10 @@
         </is>
       </c>
       <c r="B568" t="n">
-        <v>0.055692</v>
+        <v>0.055198</v>
       </c>
       <c r="C568" t="n">
-        <v>0.457766</v>
+        <v>0.461957</v>
       </c>
     </row>
     <row r="569">
@@ -7811,10 +7811,10 @@
         </is>
       </c>
       <c r="B569" t="n">
-        <v>0.055711</v>
+        <v>0.055231</v>
       </c>
       <c r="C569" t="n">
-        <v>0.455041</v>
+        <v>0.459239</v>
       </c>
     </row>
     <row r="570">
@@ -7824,10 +7824,10 @@
         </is>
       </c>
       <c r="B570" t="n">
-        <v>0.055749</v>
+        <v>0.05541</v>
       </c>
       <c r="C570" t="n">
-        <v>0.452316</v>
+        <v>0.456522</v>
       </c>
     </row>
     <row r="571">
@@ -7837,10 +7837,10 @@
         </is>
       </c>
       <c r="B571" t="n">
-        <v>0.056054</v>
+        <v>0.055463</v>
       </c>
       <c r="C571" t="n">
-        <v>0.449591</v>
+        <v>0.453804</v>
       </c>
     </row>
     <row r="572">
@@ -7850,10 +7850,10 @@
         </is>
       </c>
       <c r="B572" t="n">
-        <v>0.056274</v>
+        <v>0.055584</v>
       </c>
       <c r="C572" t="n">
-        <v>0.446866</v>
+        <v>0.451087</v>
       </c>
     </row>
     <row r="573">
@@ -7863,10 +7863,10 @@
         </is>
       </c>
       <c r="B573" t="n">
-        <v>0.057076</v>
+        <v>0.055621</v>
       </c>
       <c r="C573" t="n">
-        <v>0.444142</v>
+        <v>0.44837</v>
       </c>
     </row>
     <row r="574">
@@ -7876,10 +7876,10 @@
         </is>
       </c>
       <c r="B574" t="n">
-        <v>0.057273</v>
+        <v>0.055839</v>
       </c>
       <c r="C574" t="n">
-        <v>0.441417</v>
+        <v>0.445652</v>
       </c>
     </row>
     <row r="575">
@@ -7889,10 +7889,10 @@
         </is>
       </c>
       <c r="B575" t="n">
-        <v>0.057293</v>
+        <v>0.057096</v>
       </c>
       <c r="C575" t="n">
-        <v>0.438692</v>
+        <v>0.442935</v>
       </c>
     </row>
     <row r="576">
@@ -7902,10 +7902,10 @@
         </is>
       </c>
       <c r="B576" t="n">
-        <v>0.057472</v>
+        <v>0.057478</v>
       </c>
       <c r="C576" t="n">
-        <v>0.435967</v>
+        <v>0.440217</v>
       </c>
     </row>
     <row r="577">
@@ -7915,10 +7915,10 @@
         </is>
       </c>
       <c r="B577" t="n">
-        <v>0.059202</v>
+        <v>0.057876</v>
       </c>
       <c r="C577" t="n">
-        <v>0.433243</v>
+        <v>0.4375</v>
       </c>
     </row>
     <row r="578">
@@ -7928,10 +7928,10 @@
         </is>
       </c>
       <c r="B578" t="n">
-        <v>0.059884</v>
+        <v>0.058496</v>
       </c>
       <c r="C578" t="n">
-        <v>0.430518</v>
+        <v>0.434783</v>
       </c>
     </row>
     <row r="579">
@@ -7941,10 +7941,10 @@
         </is>
       </c>
       <c r="B579" t="n">
-        <v>0.059908</v>
+        <v>0.059825</v>
       </c>
       <c r="C579" t="n">
-        <v>0.427793</v>
+        <v>0.432065</v>
       </c>
     </row>
     <row r="580">
@@ -7954,10 +7954,10 @@
         </is>
       </c>
       <c r="B580" t="n">
-        <v>0.060333</v>
+        <v>0.059871</v>
       </c>
       <c r="C580" t="n">
-        <v>0.425068</v>
+        <v>0.429348</v>
       </c>
     </row>
     <row r="581">
@@ -7967,10 +7967,10 @@
         </is>
       </c>
       <c r="B581" t="n">
-        <v>0.062121</v>
+        <v>0.059884</v>
       </c>
       <c r="C581" t="n">
-        <v>0.422343</v>
+        <v>0.42663</v>
       </c>
     </row>
     <row r="582">
@@ -7980,10 +7980,10 @@
         </is>
       </c>
       <c r="B582" t="n">
-        <v>0.06227</v>
+        <v>0.060254</v>
       </c>
       <c r="C582" t="n">
-        <v>0.419619</v>
+        <v>0.423913</v>
       </c>
     </row>
     <row r="583">
@@ -7993,10 +7993,10 @@
         </is>
       </c>
       <c r="B583" t="n">
-        <v>0.06271</v>
+        <v>0.060748</v>
       </c>
       <c r="C583" t="n">
-        <v>0.416894</v>
+        <v>0.421196</v>
       </c>
     </row>
     <row r="584">
@@ -8006,10 +8006,10 @@
         </is>
       </c>
       <c r="B584" t="n">
-        <v>0.063384</v>
+        <v>0.061163</v>
       </c>
       <c r="C584" t="n">
-        <v>0.414169</v>
+        <v>0.418478</v>
       </c>
     </row>
     <row r="585">
@@ -8019,10 +8019,10 @@
         </is>
       </c>
       <c r="B585" t="n">
-        <v>0.06400500000000001</v>
+        <v>0.061501</v>
       </c>
       <c r="C585" t="n">
-        <v>0.411444</v>
+        <v>0.415761</v>
       </c>
     </row>
     <row r="586">
@@ -8032,10 +8032,10 @@
         </is>
       </c>
       <c r="B586" t="n">
-        <v>0.06585199999999999</v>
+        <v>0.061709</v>
       </c>
       <c r="C586" t="n">
-        <v>0.408719</v>
+        <v>0.413043</v>
       </c>
     </row>
     <row r="587">
@@ -8045,10 +8045,10 @@
         </is>
       </c>
       <c r="B587" t="n">
-        <v>0.06641900000000001</v>
+        <v>0.062537</v>
       </c>
       <c r="C587" t="n">
-        <v>0.405995</v>
+        <v>0.410326</v>
       </c>
     </row>
     <row r="588">
@@ -8058,10 +8058,10 @@
         </is>
       </c>
       <c r="B588" t="n">
-        <v>0.066428</v>
+        <v>0.063568</v>
       </c>
       <c r="C588" t="n">
-        <v>0.40327</v>
+        <v>0.407609</v>
       </c>
     </row>
     <row r="589">
@@ -8071,10 +8071,10 @@
         </is>
       </c>
       <c r="B589" t="n">
-        <v>0.06673800000000001</v>
+        <v>0.06386500000000001</v>
       </c>
       <c r="C589" t="n">
-        <v>0.400545</v>
+        <v>0.404891</v>
       </c>
     </row>
     <row r="590">
@@ -8084,10 +8084,10 @@
         </is>
       </c>
       <c r="B590" t="n">
-        <v>0.06682200000000001</v>
+        <v>0.065997</v>
       </c>
       <c r="C590" t="n">
-        <v>0.39782</v>
+        <v>0.402174</v>
       </c>
     </row>
     <row r="591">
@@ -8097,10 +8097,10 @@
         </is>
       </c>
       <c r="B591" t="n">
-        <v>0.066843</v>
+        <v>0.066236</v>
       </c>
       <c r="C591" t="n">
-        <v>0.395095</v>
+        <v>0.399457</v>
       </c>
     </row>
     <row r="592">
@@ -8110,10 +8110,10 @@
         </is>
       </c>
       <c r="B592" t="n">
-        <v>0.06707200000000001</v>
+        <v>0.066733</v>
       </c>
       <c r="C592" t="n">
-        <v>0.392371</v>
+        <v>0.396739</v>
       </c>
     </row>
     <row r="593">
@@ -8123,10 +8123,10 @@
         </is>
       </c>
       <c r="B593" t="n">
-        <v>0.067136</v>
+        <v>0.066843</v>
       </c>
       <c r="C593" t="n">
-        <v>0.389646</v>
+        <v>0.394022</v>
       </c>
     </row>
     <row r="594">
@@ -8136,10 +8136,10 @@
         </is>
       </c>
       <c r="B594" t="n">
-        <v>0.067621</v>
+        <v>0.066885</v>
       </c>
       <c r="C594" t="n">
-        <v>0.386921</v>
+        <v>0.391304</v>
       </c>
     </row>
     <row r="595">
@@ -8149,10 +8149,10 @@
         </is>
       </c>
       <c r="B595" t="n">
-        <v>0.06851599999999999</v>
+        <v>0.067568</v>
       </c>
       <c r="C595" t="n">
-        <v>0.384196</v>
+        <v>0.388587</v>
       </c>
     </row>
     <row r="596">
@@ -8162,10 +8162,10 @@
         </is>
       </c>
       <c r="B596" t="n">
-        <v>0.06858499999999999</v>
+        <v>0.067622</v>
       </c>
       <c r="C596" t="n">
-        <v>0.381471</v>
+        <v>0.38587</v>
       </c>
     </row>
     <row r="597">
@@ -8175,10 +8175,10 @@
         </is>
       </c>
       <c r="B597" t="n">
-        <v>0.068633</v>
+        <v>0.06771000000000001</v>
       </c>
       <c r="C597" t="n">
-        <v>0.378747</v>
+        <v>0.383152</v>
       </c>
     </row>
     <row r="598">
@@ -8188,10 +8188,10 @@
         </is>
       </c>
       <c r="B598" t="n">
-        <v>0.06868100000000001</v>
+        <v>0.06807199999999999</v>
       </c>
       <c r="C598" t="n">
-        <v>0.376022</v>
+        <v>0.380435</v>
       </c>
     </row>
     <row r="599">
@@ -8201,10 +8201,10 @@
         </is>
       </c>
       <c r="B599" t="n">
-        <v>0.068772</v>
+        <v>0.068519</v>
       </c>
       <c r="C599" t="n">
-        <v>0.373297</v>
+        <v>0.377717</v>
       </c>
     </row>
     <row r="600">
@@ -8214,10 +8214,10 @@
         </is>
       </c>
       <c r="B600" t="n">
-        <v>0.068797</v>
+        <v>0.06897200000000001</v>
       </c>
       <c r="C600" t="n">
-        <v>0.370572</v>
+        <v>0.375</v>
       </c>
     </row>
     <row r="601">
@@ -8227,10 +8227,10 @@
         </is>
       </c>
       <c r="B601" t="n">
-        <v>0.06907099999999999</v>
+        <v>0.069174</v>
       </c>
       <c r="C601" t="n">
-        <v>0.367847</v>
+        <v>0.372283</v>
       </c>
     </row>
     <row r="602">
@@ -8240,10 +8240,10 @@
         </is>
       </c>
       <c r="B602" t="n">
-        <v>0.069635</v>
+        <v>0.069176</v>
       </c>
       <c r="C602" t="n">
-        <v>0.365123</v>
+        <v>0.369565</v>
       </c>
     </row>
     <row r="603">
@@ -8253,10 +8253,10 @@
         </is>
       </c>
       <c r="B603" t="n">
-        <v>0.069715</v>
+        <v>0.06956</v>
       </c>
       <c r="C603" t="n">
-        <v>0.362398</v>
+        <v>0.366848</v>
       </c>
     </row>
     <row r="604">
@@ -8266,10 +8266,10 @@
         </is>
       </c>
       <c r="B604" t="n">
-        <v>0.069913</v>
+        <v>0.06965200000000001</v>
       </c>
       <c r="C604" t="n">
-        <v>0.359673</v>
+        <v>0.36413</v>
       </c>
     </row>
     <row r="605">
@@ -8279,10 +8279,10 @@
         </is>
       </c>
       <c r="B605" t="n">
-        <v>0.07043000000000001</v>
+        <v>0.06968000000000001</v>
       </c>
       <c r="C605" t="n">
-        <v>0.356948</v>
+        <v>0.361413</v>
       </c>
     </row>
     <row r="606">
@@ -8292,10 +8292,10 @@
         </is>
       </c>
       <c r="B606" t="n">
-        <v>0.070589</v>
+        <v>0.070913</v>
       </c>
       <c r="C606" t="n">
-        <v>0.354223</v>
+        <v>0.358696</v>
       </c>
     </row>
     <row r="607">
@@ -8305,10 +8305,10 @@
         </is>
       </c>
       <c r="B607" t="n">
-        <v>0.070856</v>
+        <v>0.071634</v>
       </c>
       <c r="C607" t="n">
-        <v>0.351499</v>
+        <v>0.355978</v>
       </c>
     </row>
     <row r="608">
@@ -8318,10 +8318,10 @@
         </is>
       </c>
       <c r="B608" t="n">
-        <v>0.072675</v>
+        <v>0.07173499999999999</v>
       </c>
       <c r="C608" t="n">
-        <v>0.348774</v>
+        <v>0.353261</v>
       </c>
     </row>
     <row r="609">
@@ -8331,10 +8331,10 @@
         </is>
       </c>
       <c r="B609" t="n">
-        <v>0.073064</v>
+        <v>0.072724</v>
       </c>
       <c r="C609" t="n">
-        <v>0.346049</v>
+        <v>0.350543</v>
       </c>
     </row>
     <row r="610">
@@ -8344,10 +8344,10 @@
         </is>
       </c>
       <c r="B610" t="n">
-        <v>0.073578</v>
+        <v>0.073514</v>
       </c>
       <c r="C610" t="n">
-        <v>0.343324</v>
+        <v>0.347826</v>
       </c>
     </row>
     <row r="611">
@@ -8357,10 +8357,10 @@
         </is>
       </c>
       <c r="B611" t="n">
-        <v>0.07417799999999999</v>
+        <v>0.07398100000000001</v>
       </c>
       <c r="C611" t="n">
-        <v>0.340599</v>
+        <v>0.345109</v>
       </c>
     </row>
     <row r="612">
@@ -8370,10 +8370,10 @@
         </is>
       </c>
       <c r="B612" t="n">
-        <v>0.074201</v>
+        <v>0.07413500000000001</v>
       </c>
       <c r="C612" t="n">
-        <v>0.337875</v>
+        <v>0.342391</v>
       </c>
     </row>
     <row r="613">
@@ -8383,10 +8383,10 @@
         </is>
       </c>
       <c r="B613" t="n">
-        <v>0.074906</v>
+        <v>0.07430200000000001</v>
       </c>
       <c r="C613" t="n">
-        <v>0.33515</v>
+        <v>0.339674</v>
       </c>
     </row>
     <row r="614">
@@ -8396,10 +8396,10 @@
         </is>
       </c>
       <c r="B614" t="n">
-        <v>0.07517799999999999</v>
+        <v>0.074549</v>
       </c>
       <c r="C614" t="n">
-        <v>0.332425</v>
+        <v>0.336957</v>
       </c>
     </row>
     <row r="615">
@@ -8409,10 +8409,10 @@
         </is>
       </c>
       <c r="B615" t="n">
-        <v>0.07575900000000001</v>
+        <v>0.074602</v>
       </c>
       <c r="C615" t="n">
-        <v>0.3297</v>
+        <v>0.334239</v>
       </c>
     </row>
     <row r="616">
@@ -8422,10 +8422,10 @@
         </is>
       </c>
       <c r="B616" t="n">
-        <v>0.076026</v>
+        <v>0.075512</v>
       </c>
       <c r="C616" t="n">
-        <v>0.326975</v>
+        <v>0.331522</v>
       </c>
     </row>
     <row r="617">
@@ -8435,10 +8435,10 @@
         </is>
       </c>
       <c r="B617" t="n">
-        <v>0.076561</v>
+        <v>0.075693</v>
       </c>
       <c r="C617" t="n">
-        <v>0.324251</v>
+        <v>0.328804</v>
       </c>
     </row>
     <row r="618">
@@ -8448,10 +8448,10 @@
         </is>
       </c>
       <c r="B618" t="n">
-        <v>0.076671</v>
+        <v>0.075881</v>
       </c>
       <c r="C618" t="n">
-        <v>0.321526</v>
+        <v>0.326087</v>
       </c>
     </row>
     <row r="619">
@@ -8461,10 +8461,10 @@
         </is>
       </c>
       <c r="B619" t="n">
-        <v>0.07670399999999999</v>
+        <v>0.07727100000000001</v>
       </c>
       <c r="C619" t="n">
-        <v>0.318801</v>
+        <v>0.32337</v>
       </c>
     </row>
     <row r="620">
@@ -8474,10 +8474,10 @@
         </is>
       </c>
       <c r="B620" t="n">
-        <v>0.077157</v>
+        <v>0.077406</v>
       </c>
       <c r="C620" t="n">
-        <v>0.316076</v>
+        <v>0.320652</v>
       </c>
     </row>
     <row r="621">
@@ -8487,10 +8487,10 @@
         </is>
       </c>
       <c r="B621" t="n">
-        <v>0.077236</v>
+        <v>0.077641</v>
       </c>
       <c r="C621" t="n">
-        <v>0.313351</v>
+        <v>0.317935</v>
       </c>
     </row>
     <row r="622">
@@ -8500,10 +8500,10 @@
         </is>
       </c>
       <c r="B622" t="n">
-        <v>0.07775</v>
+        <v>0.077734</v>
       </c>
       <c r="C622" t="n">
-        <v>0.310627</v>
+        <v>0.315217</v>
       </c>
     </row>
     <row r="623">
@@ -8513,10 +8513,10 @@
         </is>
       </c>
       <c r="B623" t="n">
-        <v>0.078609</v>
+        <v>0.078125</v>
       </c>
       <c r="C623" t="n">
-        <v>0.307902</v>
+        <v>0.3125</v>
       </c>
     </row>
     <row r="624">
@@ -8526,10 +8526,10 @@
         </is>
       </c>
       <c r="B624" t="n">
-        <v>0.07861600000000001</v>
+        <v>0.078233</v>
       </c>
       <c r="C624" t="n">
-        <v>0.305177</v>
+        <v>0.309783</v>
       </c>
     </row>
     <row r="625">
@@ -8539,10 +8539,10 @@
         </is>
       </c>
       <c r="B625" t="n">
-        <v>0.078679</v>
+        <v>0.078558</v>
       </c>
       <c r="C625" t="n">
-        <v>0.302452</v>
+        <v>0.307065</v>
       </c>
     </row>
     <row r="626">
@@ -8552,10 +8552,10 @@
         </is>
       </c>
       <c r="B626" t="n">
-        <v>0.079042</v>
+        <v>0.078664</v>
       </c>
       <c r="C626" t="n">
-        <v>0.299728</v>
+        <v>0.304348</v>
       </c>
     </row>
     <row r="627">
@@ -8565,10 +8565,10 @@
         </is>
       </c>
       <c r="B627" t="n">
-        <v>0.079559</v>
+        <v>0.07870199999999999</v>
       </c>
       <c r="C627" t="n">
-        <v>0.297003</v>
+        <v>0.30163</v>
       </c>
     </row>
     <row r="628">
@@ -8578,10 +8578,10 @@
         </is>
       </c>
       <c r="B628" t="n">
-        <v>0.080522</v>
+        <v>0.079123</v>
       </c>
       <c r="C628" t="n">
-        <v>0.294278</v>
+        <v>0.298913</v>
       </c>
     </row>
     <row r="629">
@@ -8591,10 +8591,10 @@
         </is>
       </c>
       <c r="B629" t="n">
-        <v>0.08293200000000001</v>
+        <v>0.080346</v>
       </c>
       <c r="C629" t="n">
-        <v>0.291553</v>
+        <v>0.296196</v>
       </c>
     </row>
     <row r="630">
@@ -8604,10 +8604,10 @@
         </is>
       </c>
       <c r="B630" t="n">
-        <v>0.083263</v>
+        <v>0.083567</v>
       </c>
       <c r="C630" t="n">
-        <v>0.288828</v>
+        <v>0.293478</v>
       </c>
     </row>
     <row r="631">
@@ -8617,10 +8617,10 @@
         </is>
       </c>
       <c r="B631" t="n">
-        <v>0.083843</v>
+        <v>0.083783</v>
       </c>
       <c r="C631" t="n">
-        <v>0.286104</v>
+        <v>0.290761</v>
       </c>
     </row>
     <row r="632">
@@ -8630,10 +8630,10 @@
         </is>
       </c>
       <c r="B632" t="n">
-        <v>0.085711</v>
+        <v>0.084368</v>
       </c>
       <c r="C632" t="n">
-        <v>0.283379</v>
+        <v>0.288043</v>
       </c>
     </row>
     <row r="633">
@@ -8643,10 +8643,10 @@
         </is>
       </c>
       <c r="B633" t="n">
-        <v>0.085775</v>
+        <v>0.085267</v>
       </c>
       <c r="C633" t="n">
-        <v>0.280654</v>
+        <v>0.285326</v>
       </c>
     </row>
     <row r="634">
@@ -8656,10 +8656,10 @@
         </is>
       </c>
       <c r="B634" t="n">
-        <v>0.085794</v>
+        <v>0.085907</v>
       </c>
       <c r="C634" t="n">
-        <v>0.277929</v>
+        <v>0.282609</v>
       </c>
     </row>
     <row r="635">
@@ -8669,10 +8669,10 @@
         </is>
       </c>
       <c r="B635" t="n">
-        <v>0.08666500000000001</v>
+        <v>0.086119</v>
       </c>
       <c r="C635" t="n">
-        <v>0.275204</v>
+        <v>0.279891</v>
       </c>
     </row>
     <row r="636">
@@ -8682,10 +8682,10 @@
         </is>
       </c>
       <c r="B636" t="n">
-        <v>0.08805200000000001</v>
+        <v>0.087307</v>
       </c>
       <c r="C636" t="n">
-        <v>0.27248</v>
+        <v>0.277174</v>
       </c>
     </row>
     <row r="637">
@@ -8695,10 +8695,10 @@
         </is>
       </c>
       <c r="B637" t="n">
-        <v>0.08833100000000001</v>
+        <v>0.08731700000000001</v>
       </c>
       <c r="C637" t="n">
-        <v>0.269755</v>
+        <v>0.274457</v>
       </c>
     </row>
     <row r="638">
@@ -8708,10 +8708,10 @@
         </is>
       </c>
       <c r="B638" t="n">
-        <v>0.08873</v>
+        <v>0.087342</v>
       </c>
       <c r="C638" t="n">
-        <v>0.26703</v>
+        <v>0.271739</v>
       </c>
     </row>
     <row r="639">
@@ -8721,10 +8721,10 @@
         </is>
       </c>
       <c r="B639" t="n">
-        <v>0.08887100000000001</v>
+        <v>0.088059</v>
       </c>
       <c r="C639" t="n">
-        <v>0.264305</v>
+        <v>0.269022</v>
       </c>
     </row>
     <row r="640">
@@ -8734,10 +8734,10 @@
         </is>
       </c>
       <c r="B640" t="n">
-        <v>0.090004</v>
+        <v>0.08874899999999999</v>
       </c>
       <c r="C640" t="n">
-        <v>0.26158</v>
+        <v>0.266304</v>
       </c>
     </row>
     <row r="641">
@@ -8747,10 +8747,10 @@
         </is>
       </c>
       <c r="B641" t="n">
-        <v>0.090264</v>
+        <v>0.089513</v>
       </c>
       <c r="C641" t="n">
-        <v>0.258856</v>
+        <v>0.263587</v>
       </c>
     </row>
     <row r="642">
@@ -8760,10 +8760,10 @@
         </is>
       </c>
       <c r="B642" t="n">
-        <v>0.09088499999999999</v>
+        <v>0.089728</v>
       </c>
       <c r="C642" t="n">
-        <v>0.256131</v>
+        <v>0.26087</v>
       </c>
     </row>
     <row r="643">
@@ -8773,10 +8773,10 @@
         </is>
       </c>
       <c r="B643" t="n">
-        <v>0.091005</v>
+        <v>0.090035</v>
       </c>
       <c r="C643" t="n">
-        <v>0.253406</v>
+        <v>0.258152</v>
       </c>
     </row>
     <row r="644">
@@ -8786,10 +8786,10 @@
         </is>
       </c>
       <c r="B644" t="n">
-        <v>0.09166100000000001</v>
+        <v>0.090933</v>
       </c>
       <c r="C644" t="n">
-        <v>0.250681</v>
+        <v>0.255435</v>
       </c>
     </row>
     <row r="645">
@@ -8799,10 +8799,10 @@
         </is>
       </c>
       <c r="B645" t="n">
-        <v>0.09174599999999999</v>
+        <v>0.09107</v>
       </c>
       <c r="C645" t="n">
-        <v>0.247956</v>
+        <v>0.252717</v>
       </c>
     </row>
     <row r="646">
@@ -8812,10 +8812,10 @@
         </is>
       </c>
       <c r="B646" t="n">
-        <v>0.092386</v>
+        <v>0.091888</v>
       </c>
       <c r="C646" t="n">
-        <v>0.245232</v>
+        <v>0.25</v>
       </c>
     </row>
     <row r="647">
@@ -8825,10 +8825,10 @@
         </is>
       </c>
       <c r="B647" t="n">
-        <v>0.092499</v>
+        <v>0.092057</v>
       </c>
       <c r="C647" t="n">
-        <v>0.242507</v>
+        <v>0.247283</v>
       </c>
     </row>
     <row r="648">
@@ -8838,10 +8838,10 @@
         </is>
       </c>
       <c r="B648" t="n">
-        <v>0.092678</v>
+        <v>0.092192</v>
       </c>
       <c r="C648" t="n">
-        <v>0.239782</v>
+        <v>0.244565</v>
       </c>
     </row>
     <row r="649">
@@ -8851,10 +8851,10 @@
         </is>
       </c>
       <c r="B649" t="n">
-        <v>0.093691</v>
+        <v>0.092596</v>
       </c>
       <c r="C649" t="n">
-        <v>0.237057</v>
+        <v>0.241848</v>
       </c>
     </row>
     <row r="650">
@@ -8864,10 +8864,10 @@
         </is>
       </c>
       <c r="B650" t="n">
-        <v>0.095345</v>
+        <v>0.093151</v>
       </c>
       <c r="C650" t="n">
-        <v>0.234332</v>
+        <v>0.23913</v>
       </c>
     </row>
     <row r="651">
@@ -8877,10 +8877,10 @@
         </is>
       </c>
       <c r="B651" t="n">
-        <v>0.095887</v>
+        <v>0.093668</v>
       </c>
       <c r="C651" t="n">
-        <v>0.231608</v>
+        <v>0.236413</v>
       </c>
     </row>
     <row r="652">
@@ -8890,10 +8890,10 @@
         </is>
       </c>
       <c r="B652" t="n">
-        <v>0.097552</v>
+        <v>0.097619</v>
       </c>
       <c r="C652" t="n">
-        <v>0.228883</v>
+        <v>0.233696</v>
       </c>
     </row>
     <row r="653">
@@ -8903,10 +8903,10 @@
         </is>
       </c>
       <c r="B653" t="n">
-        <v>0.09991</v>
+        <v>0.09816900000000001</v>
       </c>
       <c r="C653" t="n">
-        <v>0.226158</v>
+        <v>0.230978</v>
       </c>
     </row>
     <row r="654">
@@ -8916,10 +8916,10 @@
         </is>
       </c>
       <c r="B654" t="n">
-        <v>0.099982</v>
+        <v>0.09941700000000001</v>
       </c>
       <c r="C654" t="n">
-        <v>0.223433</v>
+        <v>0.228261</v>
       </c>
     </row>
     <row r="655">
@@ -8929,10 +8929,10 @@
         </is>
       </c>
       <c r="B655" t="n">
-        <v>0.100283</v>
+        <v>0.099678</v>
       </c>
       <c r="C655" t="n">
-        <v>0.220708</v>
+        <v>0.225543</v>
       </c>
     </row>
     <row r="656">
@@ -8942,10 +8942,10 @@
         </is>
       </c>
       <c r="B656" t="n">
-        <v>0.100487</v>
+        <v>0.099971</v>
       </c>
       <c r="C656" t="n">
-        <v>0.217984</v>
+        <v>0.222826</v>
       </c>
     </row>
     <row r="657">
@@ -8955,10 +8955,10 @@
         </is>
       </c>
       <c r="B657" t="n">
-        <v>0.100958</v>
+        <v>0.100061</v>
       </c>
       <c r="C657" t="n">
-        <v>0.215259</v>
+        <v>0.220109</v>
       </c>
     </row>
     <row r="658">
@@ -8968,10 +8968,10 @@
         </is>
       </c>
       <c r="B658" t="n">
-        <v>0.101654</v>
+        <v>0.100268</v>
       </c>
       <c r="C658" t="n">
-        <v>0.212534</v>
+        <v>0.217391</v>
       </c>
     </row>
     <row r="659">
@@ -8981,10 +8981,10 @@
         </is>
       </c>
       <c r="B659" t="n">
-        <v>0.101845</v>
+        <v>0.100625</v>
       </c>
       <c r="C659" t="n">
-        <v>0.209809</v>
+        <v>0.214674</v>
       </c>
     </row>
     <row r="660">
@@ -8994,10 +8994,10 @@
         </is>
       </c>
       <c r="B660" t="n">
-        <v>0.102475</v>
+        <v>0.101773</v>
       </c>
       <c r="C660" t="n">
-        <v>0.207084</v>
+        <v>0.211957</v>
       </c>
     </row>
     <row r="661">
@@ -9007,10 +9007,10 @@
         </is>
       </c>
       <c r="B661" t="n">
-        <v>0.102848</v>
+        <v>0.101871</v>
       </c>
       <c r="C661" t="n">
-        <v>0.20436</v>
+        <v>0.209239</v>
       </c>
     </row>
     <row r="662">
@@ -9020,10 +9020,10 @@
         </is>
       </c>
       <c r="B662" t="n">
-        <v>0.103193</v>
+        <v>0.101972</v>
       </c>
       <c r="C662" t="n">
-        <v>0.201635</v>
+        <v>0.206522</v>
       </c>
     </row>
     <row r="663">
@@ -9033,10 +9033,10 @@
         </is>
       </c>
       <c r="B663" t="n">
-        <v>0.10456</v>
+        <v>0.102054</v>
       </c>
       <c r="C663" t="n">
-        <v>0.19891</v>
+        <v>0.203804</v>
       </c>
     </row>
     <row r="664">
@@ -9046,10 +9046,10 @@
         </is>
       </c>
       <c r="B664" t="n">
-        <v>0.105442</v>
+        <v>0.103475</v>
       </c>
       <c r="C664" t="n">
-        <v>0.196185</v>
+        <v>0.201087</v>
       </c>
     </row>
     <row r="665">
@@ -9059,10 +9059,10 @@
         </is>
       </c>
       <c r="B665" t="n">
-        <v>0.106059</v>
+        <v>0.104028</v>
       </c>
       <c r="C665" t="n">
-        <v>0.19346</v>
+        <v>0.19837</v>
       </c>
     </row>
     <row r="666">
@@ -9072,10 +9072,10 @@
         </is>
       </c>
       <c r="B666" t="n">
-        <v>0.106893</v>
+        <v>0.104299</v>
       </c>
       <c r="C666" t="n">
-        <v>0.190736</v>
+        <v>0.195652</v>
       </c>
     </row>
     <row r="667">
@@ -9085,10 +9085,10 @@
         </is>
       </c>
       <c r="B667" t="n">
-        <v>0.108126</v>
+        <v>0.105687</v>
       </c>
       <c r="C667" t="n">
-        <v>0.188011</v>
+        <v>0.192935</v>
       </c>
     </row>
     <row r="668">
@@ -9098,10 +9098,10 @@
         </is>
       </c>
       <c r="B668" t="n">
-        <v>0.110051</v>
+        <v>0.107026</v>
       </c>
       <c r="C668" t="n">
-        <v>0.185286</v>
+        <v>0.190217</v>
       </c>
     </row>
     <row r="669">
@@ -9111,10 +9111,10 @@
         </is>
       </c>
       <c r="B669" t="n">
-        <v>0.110334</v>
+        <v>0.108516</v>
       </c>
       <c r="C669" t="n">
-        <v>0.182561</v>
+        <v>0.1875</v>
       </c>
     </row>
     <row r="670">
@@ -9124,10 +9124,10 @@
         </is>
       </c>
       <c r="B670" t="n">
-        <v>0.110424</v>
+        <v>0.110065</v>
       </c>
       <c r="C670" t="n">
-        <v>0.179837</v>
+        <v>0.184783</v>
       </c>
     </row>
     <row r="671">
@@ -9137,10 +9137,10 @@
         </is>
       </c>
       <c r="B671" t="n">
-        <v>0.110593</v>
+        <v>0.110445</v>
       </c>
       <c r="C671" t="n">
-        <v>0.177112</v>
+        <v>0.182065</v>
       </c>
     </row>
     <row r="672">
@@ -9150,10 +9150,10 @@
         </is>
       </c>
       <c r="B672" t="n">
-        <v>0.110749</v>
+        <v>0.110998</v>
       </c>
       <c r="C672" t="n">
-        <v>0.174387</v>
+        <v>0.179348</v>
       </c>
     </row>
     <row r="673">
@@ -9163,10 +9163,10 @@
         </is>
       </c>
       <c r="B673" t="n">
-        <v>0.113548</v>
+        <v>0.111408</v>
       </c>
       <c r="C673" t="n">
-        <v>0.171662</v>
+        <v>0.17663</v>
       </c>
     </row>
     <row r="674">
@@ -9176,10 +9176,10 @@
         </is>
       </c>
       <c r="B674" t="n">
-        <v>0.119003</v>
+        <v>0.112827</v>
       </c>
       <c r="C674" t="n">
-        <v>0.168937</v>
+        <v>0.173913</v>
       </c>
     </row>
     <row r="675">
@@ -9189,10 +9189,10 @@
         </is>
       </c>
       <c r="B675" t="n">
-        <v>0.120247</v>
+        <v>0.11441</v>
       </c>
       <c r="C675" t="n">
-        <v>0.166213</v>
+        <v>0.171196</v>
       </c>
     </row>
     <row r="676">
@@ -9202,10 +9202,10 @@
         </is>
       </c>
       <c r="B676" t="n">
-        <v>0.120637</v>
+        <v>0.119253</v>
       </c>
       <c r="C676" t="n">
-        <v>0.163488</v>
+        <v>0.168478</v>
       </c>
     </row>
     <row r="677">
@@ -9215,10 +9215,10 @@
         </is>
       </c>
       <c r="B677" t="n">
-        <v>0.120712</v>
+        <v>0.119685</v>
       </c>
       <c r="C677" t="n">
-        <v>0.160763</v>
+        <v>0.165761</v>
       </c>
     </row>
     <row r="678">
@@ -9228,10 +9228,10 @@
         </is>
       </c>
       <c r="B678" t="n">
-        <v>0.125157</v>
+        <v>0.120444</v>
       </c>
       <c r="C678" t="n">
-        <v>0.158038</v>
+        <v>0.163043</v>
       </c>
     </row>
     <row r="679">
@@ -9241,10 +9241,10 @@
         </is>
       </c>
       <c r="B679" t="n">
-        <v>0.126534</v>
+        <v>0.121304</v>
       </c>
       <c r="C679" t="n">
-        <v>0.155313</v>
+        <v>0.160326</v>
       </c>
     </row>
     <row r="680">
@@ -9254,10 +9254,10 @@
         </is>
       </c>
       <c r="B680" t="n">
-        <v>0.126949</v>
+        <v>0.123874</v>
       </c>
       <c r="C680" t="n">
-        <v>0.152589</v>
+        <v>0.157609</v>
       </c>
     </row>
     <row r="681">
@@ -9267,10 +9267,10 @@
         </is>
       </c>
       <c r="B681" t="n">
-        <v>0.127871</v>
+        <v>0.125588</v>
       </c>
       <c r="C681" t="n">
-        <v>0.149864</v>
+        <v>0.154891</v>
       </c>
     </row>
     <row r="682">
@@ -9280,10 +9280,10 @@
         </is>
       </c>
       <c r="B682" t="n">
-        <v>0.128016</v>
+        <v>0.125807</v>
       </c>
       <c r="C682" t="n">
-        <v>0.147139</v>
+        <v>0.152174</v>
       </c>
     </row>
     <row r="683">
@@ -9293,10 +9293,10 @@
         </is>
       </c>
       <c r="B683" t="n">
-        <v>0.128487</v>
+        <v>0.1275</v>
       </c>
       <c r="C683" t="n">
-        <v>0.144414</v>
+        <v>0.149457</v>
       </c>
     </row>
     <row r="684">
@@ -9306,10 +9306,10 @@
         </is>
       </c>
       <c r="B684" t="n">
-        <v>0.128585</v>
+        <v>0.128215</v>
       </c>
       <c r="C684" t="n">
-        <v>0.141689</v>
+        <v>0.146739</v>
       </c>
     </row>
     <row r="685">
@@ -9319,10 +9319,10 @@
         </is>
       </c>
       <c r="B685" t="n">
-        <v>0.128888</v>
+        <v>0.129437</v>
       </c>
       <c r="C685" t="n">
-        <v>0.138965</v>
+        <v>0.144022</v>
       </c>
     </row>
     <row r="686">
@@ -9332,10 +9332,10 @@
         </is>
       </c>
       <c r="B686" t="n">
-        <v>0.129008</v>
+        <v>0.129977</v>
       </c>
       <c r="C686" t="n">
-        <v>0.13624</v>
+        <v>0.141304</v>
       </c>
     </row>
     <row r="687">
@@ -9345,10 +9345,10 @@
         </is>
       </c>
       <c r="B687" t="n">
-        <v>0.130367</v>
+        <v>0.130363</v>
       </c>
       <c r="C687" t="n">
-        <v>0.133515</v>
+        <v>0.138587</v>
       </c>
     </row>
     <row r="688">
@@ -9358,10 +9358,10 @@
         </is>
       </c>
       <c r="B688" t="n">
-        <v>0.133153</v>
+        <v>0.130479</v>
       </c>
       <c r="C688" t="n">
-        <v>0.13079</v>
+        <v>0.13587</v>
       </c>
     </row>
     <row r="689">
@@ -9371,10 +9371,10 @@
         </is>
       </c>
       <c r="B689" t="n">
-        <v>0.133759</v>
+        <v>0.131886</v>
       </c>
       <c r="C689" t="n">
-        <v>0.128065</v>
+        <v>0.133152</v>
       </c>
     </row>
     <row r="690">
@@ -9384,10 +9384,10 @@
         </is>
       </c>
       <c r="B690" t="n">
-        <v>0.135512</v>
+        <v>0.131936</v>
       </c>
       <c r="C690" t="n">
-        <v>0.125341</v>
+        <v>0.130435</v>
       </c>
     </row>
     <row r="691">
@@ -9397,10 +9397,10 @@
         </is>
       </c>
       <c r="B691" t="n">
-        <v>0.135837</v>
+        <v>0.133107</v>
       </c>
       <c r="C691" t="n">
-        <v>0.122616</v>
+        <v>0.127717</v>
       </c>
     </row>
     <row r="692">
@@ -9410,10 +9410,10 @@
         </is>
       </c>
       <c r="B692" t="n">
-        <v>0.138829</v>
+        <v>0.135963</v>
       </c>
       <c r="C692" t="n">
-        <v>0.119891</v>
+        <v>0.125</v>
       </c>
     </row>
     <row r="693">
@@ -9423,10 +9423,10 @@
         </is>
       </c>
       <c r="B693" t="n">
-        <v>0.139849</v>
+        <v>0.137372</v>
       </c>
       <c r="C693" t="n">
-        <v>0.117166</v>
+        <v>0.122283</v>
       </c>
     </row>
     <row r="694">
@@ -9436,10 +9436,10 @@
         </is>
       </c>
       <c r="B694" t="n">
-        <v>0.140268</v>
+        <v>0.138164</v>
       </c>
       <c r="C694" t="n">
-        <v>0.114441</v>
+        <v>0.119565</v>
       </c>
     </row>
     <row r="695">
@@ -9449,10 +9449,10 @@
         </is>
       </c>
       <c r="B695" t="n">
-        <v>0.140846</v>
+        <v>0.138343</v>
       </c>
       <c r="C695" t="n">
-        <v>0.111717</v>
+        <v>0.116848</v>
       </c>
     </row>
     <row r="696">
@@ -9462,10 +9462,10 @@
         </is>
       </c>
       <c r="B696" t="n">
-        <v>0.141462</v>
+        <v>0.138419</v>
       </c>
       <c r="C696" t="n">
-        <v>0.108992</v>
+        <v>0.11413</v>
       </c>
     </row>
     <row r="697">
@@ -9475,10 +9475,10 @@
         </is>
       </c>
       <c r="B697" t="n">
-        <v>0.142334</v>
+        <v>0.13867</v>
       </c>
       <c r="C697" t="n">
-        <v>0.106267</v>
+        <v>0.111413</v>
       </c>
     </row>
     <row r="698">
@@ -9488,10 +9488,10 @@
         </is>
       </c>
       <c r="B698" t="n">
-        <v>0.144657</v>
+        <v>0.14116</v>
       </c>
       <c r="C698" t="n">
-        <v>0.103542</v>
+        <v>0.108696</v>
       </c>
     </row>
     <row r="699">
@@ -9501,10 +9501,10 @@
         </is>
       </c>
       <c r="B699" t="n">
-        <v>0.14552</v>
+        <v>0.1414</v>
       </c>
       <c r="C699" t="n">
-        <v>0.100817</v>
+        <v>0.105978</v>
       </c>
     </row>
     <row r="700">
@@ -9514,10 +9514,10 @@
         </is>
       </c>
       <c r="B700" t="n">
-        <v>0.148262</v>
+        <v>0.142461</v>
       </c>
       <c r="C700" t="n">
-        <v>0.098093</v>
+        <v>0.103261</v>
       </c>
     </row>
     <row r="701">
@@ -9527,10 +9527,10 @@
         </is>
       </c>
       <c r="B701" t="n">
-        <v>0.152583</v>
+        <v>0.143079</v>
       </c>
       <c r="C701" t="n">
-        <v>0.09536799999999999</v>
+        <v>0.100543</v>
       </c>
     </row>
     <row r="702">
@@ -9540,10 +9540,10 @@
         </is>
       </c>
       <c r="B702" t="n">
-        <v>0.152671</v>
+        <v>0.144764</v>
       </c>
       <c r="C702" t="n">
-        <v>0.092643</v>
+        <v>0.097826</v>
       </c>
     </row>
     <row r="703">
@@ -9553,10 +9553,10 @@
         </is>
       </c>
       <c r="B703" t="n">
-        <v>0.153247</v>
+        <v>0.145934</v>
       </c>
       <c r="C703" t="n">
-        <v>0.089918</v>
+        <v>0.095109</v>
       </c>
     </row>
     <row r="704">
@@ -9566,10 +9566,10 @@
         </is>
       </c>
       <c r="B704" t="n">
-        <v>0.155248</v>
+        <v>0.153384</v>
       </c>
       <c r="C704" t="n">
-        <v>0.08719300000000001</v>
+        <v>0.092391</v>
       </c>
     </row>
     <row r="705">
@@ -9579,10 +9579,10 @@
         </is>
       </c>
       <c r="B705" t="n">
-        <v>0.15996</v>
+        <v>0.154815</v>
       </c>
       <c r="C705" t="n">
-        <v>0.084469</v>
+        <v>0.089674</v>
       </c>
     </row>
     <row r="706">
@@ -9592,10 +9592,10 @@
         </is>
       </c>
       <c r="B706" t="n">
-        <v>0.162434</v>
+        <v>0.154891</v>
       </c>
       <c r="C706" t="n">
-        <v>0.081744</v>
+        <v>0.08695700000000001</v>
       </c>
     </row>
     <row r="707">
@@ -9605,10 +9605,10 @@
         </is>
       </c>
       <c r="B707" t="n">
-        <v>0.167594</v>
+        <v>0.159054</v>
       </c>
       <c r="C707" t="n">
-        <v>0.07901900000000001</v>
+        <v>0.08423899999999999</v>
       </c>
     </row>
     <row r="708">
@@ -9618,10 +9618,10 @@
         </is>
       </c>
       <c r="B708" t="n">
-        <v>0.16785</v>
+        <v>0.162137</v>
       </c>
       <c r="C708" t="n">
-        <v>0.076294</v>
+        <v>0.081522</v>
       </c>
     </row>
     <row r="709">
@@ -9631,10 +9631,10 @@
         </is>
       </c>
       <c r="B709" t="n">
-        <v>0.168454</v>
+        <v>0.162906</v>
       </c>
       <c r="C709" t="n">
-        <v>0.073569</v>
+        <v>0.078804</v>
       </c>
     </row>
     <row r="710">
@@ -9644,10 +9644,10 @@
         </is>
       </c>
       <c r="B710" t="n">
-        <v>0.174682</v>
+        <v>0.165839</v>
       </c>
       <c r="C710" t="n">
-        <v>0.07084500000000001</v>
+        <v>0.076087</v>
       </c>
     </row>
     <row r="711">
@@ -9657,10 +9657,10 @@
         </is>
       </c>
       <c r="B711" t="n">
-        <v>0.175427</v>
+        <v>0.169061</v>
       </c>
       <c r="C711" t="n">
-        <v>0.06812</v>
+        <v>0.07337</v>
       </c>
     </row>
     <row r="712">
@@ -9670,10 +9670,10 @@
         </is>
       </c>
       <c r="B712" t="n">
-        <v>0.176559</v>
+        <v>0.170113</v>
       </c>
       <c r="C712" t="n">
-        <v>0.06539499999999999</v>
+        <v>0.07065200000000001</v>
       </c>
     </row>
     <row r="713">
@@ -9683,10 +9683,10 @@
         </is>
       </c>
       <c r="B713" t="n">
-        <v>0.177643</v>
+        <v>0.177933</v>
       </c>
       <c r="C713" t="n">
-        <v>0.06267</v>
+        <v>0.067935</v>
       </c>
     </row>
     <row r="714">
@@ -9696,10 +9696,10 @@
         </is>
       </c>
       <c r="B714" t="n">
-        <v>0.178705</v>
+        <v>0.178189</v>
       </c>
       <c r="C714" t="n">
-        <v>0.059946</v>
+        <v>0.065217</v>
       </c>
     </row>
     <row r="715">
@@ -9709,10 +9709,10 @@
         </is>
       </c>
       <c r="B715" t="n">
-        <v>0.180773</v>
+        <v>0.179015</v>
       </c>
       <c r="C715" t="n">
-        <v>0.057221</v>
+        <v>0.0625</v>
       </c>
     </row>
     <row r="716">
@@ -9722,10 +9722,10 @@
         </is>
       </c>
       <c r="B716" t="n">
-        <v>0.187018</v>
+        <v>0.180992</v>
       </c>
       <c r="C716" t="n">
-        <v>0.054496</v>
+        <v>0.059783</v>
       </c>
     </row>
     <row r="717">
@@ -9735,10 +9735,10 @@
         </is>
       </c>
       <c r="B717" t="n">
-        <v>0.188728</v>
+        <v>0.183889</v>
       </c>
       <c r="C717" t="n">
-        <v>0.051771</v>
+        <v>0.057065</v>
       </c>
     </row>
     <row r="718">
@@ -9748,10 +9748,10 @@
         </is>
       </c>
       <c r="B718" t="n">
-        <v>0.198577</v>
+        <v>0.185548</v>
       </c>
       <c r="C718" t="n">
-        <v>0.049046</v>
+        <v>0.054348</v>
       </c>
     </row>
     <row r="719">
@@ -9761,10 +9761,10 @@
         </is>
       </c>
       <c r="B719" t="n">
-        <v>0.202868</v>
+        <v>0.186009</v>
       </c>
       <c r="C719" t="n">
-        <v>0.046322</v>
+        <v>0.05163</v>
       </c>
     </row>
     <row r="720">
@@ -9774,10 +9774,10 @@
         </is>
       </c>
       <c r="B720" t="n">
-        <v>0.203404</v>
+        <v>0.195397</v>
       </c>
       <c r="C720" t="n">
-        <v>0.043597</v>
+        <v>0.048913</v>
       </c>
     </row>
     <row r="721">
@@ -9787,10 +9787,10 @@
         </is>
       </c>
       <c r="B721" t="n">
-        <v>0.209185</v>
+        <v>0.196313</v>
       </c>
       <c r="C721" t="n">
-        <v>0.040872</v>
+        <v>0.046196</v>
       </c>
     </row>
     <row r="722">
@@ -9800,10 +9800,10 @@
         </is>
       </c>
       <c r="B722" t="n">
-        <v>0.221322</v>
+        <v>0.200034</v>
       </c>
       <c r="C722" t="n">
-        <v>0.038147</v>
+        <v>0.043478</v>
       </c>
     </row>
     <row r="723">
@@ -9813,10 +9813,10 @@
         </is>
       </c>
       <c r="B723" t="n">
-        <v>0.227055</v>
+        <v>0.208874</v>
       </c>
       <c r="C723" t="n">
-        <v>0.035422</v>
+        <v>0.040761</v>
       </c>
     </row>
     <row r="724">
@@ -9826,10 +9826,10 @@
         </is>
       </c>
       <c r="B724" t="n">
-        <v>0.228311</v>
+        <v>0.208976</v>
       </c>
       <c r="C724" t="n">
-        <v>0.032698</v>
+        <v>0.038043</v>
       </c>
     </row>
     <row r="725">
@@ -9839,10 +9839,10 @@
         </is>
       </c>
       <c r="B725" t="n">
-        <v>0.231994</v>
+        <v>0.214644</v>
       </c>
       <c r="C725" t="n">
-        <v>0.029973</v>
+        <v>0.035326</v>
       </c>
     </row>
     <row r="726">
@@ -9852,10 +9852,10 @@
         </is>
       </c>
       <c r="B726" t="n">
-        <v>0.232268</v>
+        <v>0.228307</v>
       </c>
       <c r="C726" t="n">
-        <v>0.027248</v>
+        <v>0.032609</v>
       </c>
     </row>
     <row r="727">
@@ -9865,10 +9865,10 @@
         </is>
       </c>
       <c r="B727" t="n">
-        <v>0.234728</v>
+        <v>0.232818</v>
       </c>
       <c r="C727" t="n">
-        <v>0.024523</v>
+        <v>0.029891</v>
       </c>
     </row>
     <row r="728">
@@ -9878,10 +9878,10 @@
         </is>
       </c>
       <c r="B728" t="n">
-        <v>0.257967</v>
+        <v>0.241414</v>
       </c>
       <c r="C728" t="n">
-        <v>0.021798</v>
+        <v>0.027174</v>
       </c>
     </row>
     <row r="729">
@@ -9891,10 +9891,10 @@
         </is>
       </c>
       <c r="B729" t="n">
-        <v>0.264434</v>
+        <v>0.241966</v>
       </c>
       <c r="C729" t="n">
-        <v>0.019074</v>
+        <v>0.024457</v>
       </c>
     </row>
     <row r="730">
@@ -9904,10 +9904,10 @@
         </is>
       </c>
       <c r="B730" t="n">
-        <v>0.267543</v>
+        <v>0.244353</v>
       </c>
       <c r="C730" t="n">
-        <v>0.016349</v>
+        <v>0.021739</v>
       </c>
     </row>
     <row r="731">
@@ -9917,10 +9917,10 @@
         </is>
       </c>
       <c r="B731" t="n">
-        <v>0.295806</v>
+        <v>0.260987</v>
       </c>
       <c r="C731" t="n">
-        <v>0.013624</v>
+        <v>0.019022</v>
       </c>
     </row>
     <row r="732">
@@ -9930,10 +9930,10 @@
         </is>
       </c>
       <c r="B732" t="n">
-        <v>0.298916</v>
+        <v>0.262818</v>
       </c>
       <c r="C732" t="n">
-        <v>0.010899</v>
+        <v>0.016304</v>
       </c>
     </row>
     <row r="733">
@@ -9943,10 +9943,10 @@
         </is>
       </c>
       <c r="B733" t="n">
-        <v>0.336419</v>
+        <v>0.271117</v>
       </c>
       <c r="C733" t="n">
-        <v>0.008174000000000001</v>
+        <v>0.013587</v>
       </c>
     </row>
     <row r="734">
@@ -9956,10 +9956,10 @@
         </is>
       </c>
       <c r="B734" t="n">
-        <v>0.404876</v>
+        <v>0.295407</v>
       </c>
       <c r="C734" t="n">
-        <v>0.00545</v>
+        <v>0.01087</v>
       </c>
     </row>
     <row r="735">
@@ -9969,10 +9969,36 @@
         </is>
       </c>
       <c r="B735" t="n">
-        <v>0.475786</v>
+        <v>0.30904</v>
       </c>
       <c r="C735" t="n">
-        <v>0.002725</v>
+        <v>0.008152</v>
+      </c>
+    </row>
+    <row r="736">
+      <c r="A736" t="inlineStr">
+        <is>
+          <t>Adjusted target</t>
+        </is>
+      </c>
+      <c r="B736" t="n">
+        <v>0.33963</v>
+      </c>
+      <c r="C736" t="n">
+        <v>0.005435</v>
+      </c>
+    </row>
+    <row r="737">
+      <c r="A737" t="inlineStr">
+        <is>
+          <t>Adjusted target</t>
+        </is>
+      </c>
+      <c r="B737" t="n">
+        <v>0.483999</v>
+      </c>
+      <c r="C737" t="n">
+        <v>0.002717</v>
       </c>
     </row>
   </sheetData>

--- a/vignettes/vignette-1/tail_exceedance_plot_data.xlsx
+++ b/vignettes/vignette-1/tail_exceedance_plot_data.xlsx
@@ -5237,7 +5237,7 @@
         </is>
       </c>
       <c r="B371" t="n">
-        <v>0.000115</v>
+        <v>0.000114</v>
       </c>
       <c r="C371" t="n">
         <v>0.997283</v>
@@ -5250,7 +5250,7 @@
         </is>
       </c>
       <c r="B372" t="n">
-        <v>0.000339</v>
+        <v>0.000341</v>
       </c>
       <c r="C372" t="n">
         <v>0.994565</v>
@@ -5263,7 +5263,7 @@
         </is>
       </c>
       <c r="B373" t="n">
-        <v>0.000545</v>
+        <v>0.000544</v>
       </c>
       <c r="C373" t="n">
         <v>0.991848</v>
@@ -5276,7 +5276,7 @@
         </is>
       </c>
       <c r="B374" t="n">
-        <v>0.001109</v>
+        <v>0.00111</v>
       </c>
       <c r="C374" t="n">
         <v>0.98913</v>
@@ -5289,7 +5289,7 @@
         </is>
       </c>
       <c r="B375" t="n">
-        <v>0.001755</v>
+        <v>0.001769</v>
       </c>
       <c r="C375" t="n">
         <v>0.986413</v>
@@ -5302,7 +5302,7 @@
         </is>
       </c>
       <c r="B376" t="n">
-        <v>0.002084</v>
+        <v>0.002068</v>
       </c>
       <c r="C376" t="n">
         <v>0.983696</v>
@@ -5315,7 +5315,7 @@
         </is>
       </c>
       <c r="B377" t="n">
-        <v>0.00215</v>
+        <v>0.002163</v>
       </c>
       <c r="C377" t="n">
         <v>0.980978</v>
@@ -5328,7 +5328,7 @@
         </is>
       </c>
       <c r="B378" t="n">
-        <v>0.002341</v>
+        <v>0.002363</v>
       </c>
       <c r="C378" t="n">
         <v>0.978261</v>
@@ -5341,7 +5341,7 @@
         </is>
       </c>
       <c r="B379" t="n">
-        <v>0.002477</v>
+        <v>0.002496</v>
       </c>
       <c r="C379" t="n">
         <v>0.975543</v>
@@ -5354,7 +5354,7 @@
         </is>
       </c>
       <c r="B380" t="n">
-        <v>0.003145</v>
+        <v>0.003158</v>
       </c>
       <c r="C380" t="n">
         <v>0.972826</v>
@@ -5367,7 +5367,7 @@
         </is>
       </c>
       <c r="B381" t="n">
-        <v>0.003149</v>
+        <v>0.003176</v>
       </c>
       <c r="C381" t="n">
         <v>0.970109</v>
@@ -5380,7 +5380,7 @@
         </is>
       </c>
       <c r="B382" t="n">
-        <v>0.003426</v>
+        <v>0.003434</v>
       </c>
       <c r="C382" t="n">
         <v>0.967391</v>
@@ -5393,7 +5393,7 @@
         </is>
       </c>
       <c r="B383" t="n">
-        <v>0.003634</v>
+        <v>0.003667</v>
       </c>
       <c r="C383" t="n">
         <v>0.964674</v>
@@ -5406,7 +5406,7 @@
         </is>
       </c>
       <c r="B384" t="n">
-        <v>0.004504</v>
+        <v>0.00451</v>
       </c>
       <c r="C384" t="n">
         <v>0.961957</v>
@@ -5419,7 +5419,7 @@
         </is>
       </c>
       <c r="B385" t="n">
-        <v>0.004566</v>
+        <v>0.004575</v>
       </c>
       <c r="C385" t="n">
         <v>0.959239</v>
@@ -5432,7 +5432,7 @@
         </is>
       </c>
       <c r="B386" t="n">
-        <v>0.005056</v>
+        <v>0.005065</v>
       </c>
       <c r="C386" t="n">
         <v>0.956522</v>
@@ -5445,7 +5445,7 @@
         </is>
       </c>
       <c r="B387" t="n">
-        <v>0.005058</v>
+        <v>0.005097</v>
       </c>
       <c r="C387" t="n">
         <v>0.953804</v>
@@ -5458,7 +5458,7 @@
         </is>
       </c>
       <c r="B388" t="n">
-        <v>0.005091</v>
+        <v>0.005135</v>
       </c>
       <c r="C388" t="n">
         <v>0.951087</v>
@@ -5471,7 +5471,7 @@
         </is>
       </c>
       <c r="B389" t="n">
-        <v>0.005147</v>
+        <v>0.005164</v>
       </c>
       <c r="C389" t="n">
         <v>0.94837</v>
@@ -5484,7 +5484,7 @@
         </is>
       </c>
       <c r="B390" t="n">
-        <v>0.005323</v>
+        <v>0.005289</v>
       </c>
       <c r="C390" t="n">
         <v>0.945652</v>
@@ -5497,7 +5497,7 @@
         </is>
       </c>
       <c r="B391" t="n">
-        <v>0.005401</v>
+        <v>0.005368</v>
       </c>
       <c r="C391" t="n">
         <v>0.942935</v>
@@ -5510,7 +5510,7 @@
         </is>
       </c>
       <c r="B392" t="n">
-        <v>0.005442</v>
+        <v>0.005488</v>
       </c>
       <c r="C392" t="n">
         <v>0.940217</v>
@@ -5523,7 +5523,7 @@
         </is>
       </c>
       <c r="B393" t="n">
-        <v>0.005633</v>
+        <v>0.00565</v>
       </c>
       <c r="C393" t="n">
         <v>0.9375</v>
@@ -5536,7 +5536,7 @@
         </is>
       </c>
       <c r="B394" t="n">
-        <v>0.005683</v>
+        <v>0.005663</v>
       </c>
       <c r="C394" t="n">
         <v>0.934783</v>
@@ -5549,7 +5549,7 @@
         </is>
       </c>
       <c r="B395" t="n">
-        <v>0.006314</v>
+        <v>0.006356</v>
       </c>
       <c r="C395" t="n">
         <v>0.932065</v>
@@ -5562,7 +5562,7 @@
         </is>
       </c>
       <c r="B396" t="n">
-        <v>0.006577</v>
+        <v>0.00661</v>
       </c>
       <c r="C396" t="n">
         <v>0.929348</v>
@@ -5575,7 +5575,7 @@
         </is>
       </c>
       <c r="B397" t="n">
-        <v>0.006674</v>
+        <v>0.006708</v>
       </c>
       <c r="C397" t="n">
         <v>0.92663</v>
@@ -5588,7 +5588,7 @@
         </is>
       </c>
       <c r="B398" t="n">
-        <v>0.007328</v>
+        <v>0.007348</v>
       </c>
       <c r="C398" t="n">
         <v>0.923913</v>
@@ -5601,7 +5601,7 @@
         </is>
       </c>
       <c r="B399" t="n">
-        <v>0.008163999999999999</v>
+        <v>0.008219000000000001</v>
       </c>
       <c r="C399" t="n">
         <v>0.921196</v>
@@ -5614,7 +5614,7 @@
         </is>
       </c>
       <c r="B400" t="n">
-        <v>0.008189999999999999</v>
+        <v>0.008238000000000001</v>
       </c>
       <c r="C400" t="n">
         <v>0.918478</v>
@@ -5627,7 +5627,7 @@
         </is>
       </c>
       <c r="B401" t="n">
-        <v>0.008462000000000001</v>
+        <v>0.008538</v>
       </c>
       <c r="C401" t="n">
         <v>0.915761</v>
@@ -5640,7 +5640,7 @@
         </is>
       </c>
       <c r="B402" t="n">
-        <v>0.008697999999999999</v>
+        <v>0.008742</v>
       </c>
       <c r="C402" t="n">
         <v>0.913043</v>
@@ -5653,7 +5653,7 @@
         </is>
       </c>
       <c r="B403" t="n">
-        <v>0.008959</v>
+        <v>0.008954999999999999</v>
       </c>
       <c r="C403" t="n">
         <v>0.910326</v>
@@ -5666,7 +5666,7 @@
         </is>
       </c>
       <c r="B404" t="n">
-        <v>0.009088000000000001</v>
+        <v>0.008997</v>
       </c>
       <c r="C404" t="n">
         <v>0.907609</v>
@@ -5679,7 +5679,7 @@
         </is>
       </c>
       <c r="B405" t="n">
-        <v>0.009175000000000001</v>
+        <v>0.009256</v>
       </c>
       <c r="C405" t="n">
         <v>0.904891</v>
@@ -5692,7 +5692,7 @@
         </is>
       </c>
       <c r="B406" t="n">
-        <v>0.009303000000000001</v>
+        <v>0.009259999999999999</v>
       </c>
       <c r="C406" t="n">
         <v>0.902174</v>
@@ -5705,7 +5705,7 @@
         </is>
       </c>
       <c r="B407" t="n">
-        <v>0.009379999999999999</v>
+        <v>0.0094</v>
       </c>
       <c r="C407" t="n">
         <v>0.899457</v>
@@ -5718,7 +5718,7 @@
         </is>
       </c>
       <c r="B408" t="n">
-        <v>0.00991</v>
+        <v>0.00976</v>
       </c>
       <c r="C408" t="n">
         <v>0.896739</v>
@@ -5731,7 +5731,7 @@
         </is>
       </c>
       <c r="B409" t="n">
-        <v>0.010231</v>
+        <v>0.010318</v>
       </c>
       <c r="C409" t="n">
         <v>0.894022</v>
@@ -5744,7 +5744,7 @@
         </is>
       </c>
       <c r="B410" t="n">
-        <v>0.010453</v>
+        <v>0.010531</v>
       </c>
       <c r="C410" t="n">
         <v>0.891304</v>
@@ -5757,7 +5757,7 @@
         </is>
       </c>
       <c r="B411" t="n">
-        <v>0.01046</v>
+        <v>0.010547</v>
       </c>
       <c r="C411" t="n">
         <v>0.888587</v>
@@ -5770,7 +5770,7 @@
         </is>
       </c>
       <c r="B412" t="n">
-        <v>0.01097</v>
+        <v>0.011021</v>
       </c>
       <c r="C412" t="n">
         <v>0.88587</v>
@@ -5783,7 +5783,7 @@
         </is>
       </c>
       <c r="B413" t="n">
-        <v>0.011207</v>
+        <v>0.01121</v>
       </c>
       <c r="C413" t="n">
         <v>0.883152</v>
@@ -5796,7 +5796,7 @@
         </is>
       </c>
       <c r="B414" t="n">
-        <v>0.011326</v>
+        <v>0.011271</v>
       </c>
       <c r="C414" t="n">
         <v>0.880435</v>
@@ -5809,7 +5809,7 @@
         </is>
       </c>
       <c r="B415" t="n">
-        <v>0.011528</v>
+        <v>0.01131</v>
       </c>
       <c r="C415" t="n">
         <v>0.877717</v>
@@ -5822,7 +5822,7 @@
         </is>
       </c>
       <c r="B416" t="n">
-        <v>0.011814</v>
+        <v>0.011921</v>
       </c>
       <c r="C416" t="n">
         <v>0.875</v>
@@ -5835,7 +5835,7 @@
         </is>
       </c>
       <c r="B417" t="n">
-        <v>0.012126</v>
+        <v>0.012032</v>
       </c>
       <c r="C417" t="n">
         <v>0.872283</v>
@@ -5848,7 +5848,7 @@
         </is>
       </c>
       <c r="B418" t="n">
-        <v>0.012145</v>
+        <v>0.012166</v>
       </c>
       <c r="C418" t="n">
         <v>0.869565</v>
@@ -5861,7 +5861,7 @@
         </is>
       </c>
       <c r="B419" t="n">
-        <v>0.012466</v>
+        <v>0.012484</v>
       </c>
       <c r="C419" t="n">
         <v>0.866848</v>
@@ -5874,7 +5874,7 @@
         </is>
       </c>
       <c r="B420" t="n">
-        <v>0.012558</v>
+        <v>0.012522</v>
       </c>
       <c r="C420" t="n">
         <v>0.86413</v>
@@ -5887,7 +5887,7 @@
         </is>
       </c>
       <c r="B421" t="n">
-        <v>0.012629</v>
+        <v>0.012632</v>
       </c>
       <c r="C421" t="n">
         <v>0.861413</v>
@@ -5900,7 +5900,7 @@
         </is>
       </c>
       <c r="B422" t="n">
-        <v>0.012884</v>
+        <v>0.01292</v>
       </c>
       <c r="C422" t="n">
         <v>0.858696</v>
@@ -5913,7 +5913,7 @@
         </is>
       </c>
       <c r="B423" t="n">
-        <v>0.012969</v>
+        <v>0.013064</v>
       </c>
       <c r="C423" t="n">
         <v>0.855978</v>
@@ -5926,7 +5926,7 @@
         </is>
       </c>
       <c r="B424" t="n">
-        <v>0.013243</v>
+        <v>0.013286</v>
       </c>
       <c r="C424" t="n">
         <v>0.853261</v>
@@ -5939,7 +5939,7 @@
         </is>
       </c>
       <c r="B425" t="n">
-        <v>0.013328</v>
+        <v>0.013326</v>
       </c>
       <c r="C425" t="n">
         <v>0.850543</v>
@@ -5952,7 +5952,7 @@
         </is>
       </c>
       <c r="B426" t="n">
-        <v>0.013576</v>
+        <v>0.013691</v>
       </c>
       <c r="C426" t="n">
         <v>0.847826</v>
@@ -5965,7 +5965,7 @@
         </is>
       </c>
       <c r="B427" t="n">
-        <v>0.013817</v>
+        <v>0.013911</v>
       </c>
       <c r="C427" t="n">
         <v>0.845109</v>
@@ -5978,7 +5978,7 @@
         </is>
       </c>
       <c r="B428" t="n">
-        <v>0.014039</v>
+        <v>0.014065</v>
       </c>
       <c r="C428" t="n">
         <v>0.842391</v>
@@ -5991,7 +5991,7 @@
         </is>
       </c>
       <c r="B429" t="n">
-        <v>0.015057</v>
+        <v>0.01504</v>
       </c>
       <c r="C429" t="n">
         <v>0.839674</v>
@@ -6004,7 +6004,7 @@
         </is>
       </c>
       <c r="B430" t="n">
-        <v>0.015277</v>
+        <v>0.015051</v>
       </c>
       <c r="C430" t="n">
         <v>0.836957</v>
@@ -6017,7 +6017,7 @@
         </is>
       </c>
       <c r="B431" t="n">
-        <v>0.015284</v>
+        <v>0.015243</v>
       </c>
       <c r="C431" t="n">
         <v>0.834239</v>
@@ -6030,7 +6030,7 @@
         </is>
       </c>
       <c r="B432" t="n">
-        <v>0.015663</v>
+        <v>0.015645</v>
       </c>
       <c r="C432" t="n">
         <v>0.831522</v>
@@ -6043,7 +6043,7 @@
         </is>
       </c>
       <c r="B433" t="n">
-        <v>0.01582</v>
+        <v>0.01596</v>
       </c>
       <c r="C433" t="n">
         <v>0.828804</v>
@@ -6056,7 +6056,7 @@
         </is>
       </c>
       <c r="B434" t="n">
-        <v>0.015952</v>
+        <v>0.015963</v>
       </c>
       <c r="C434" t="n">
         <v>0.826087</v>
@@ -6069,7 +6069,7 @@
         </is>
       </c>
       <c r="B435" t="n">
-        <v>0.016029</v>
+        <v>0.016064</v>
       </c>
       <c r="C435" t="n">
         <v>0.82337</v>
@@ -6082,7 +6082,7 @@
         </is>
       </c>
       <c r="B436" t="n">
-        <v>0.016482</v>
+        <v>0.016479</v>
       </c>
       <c r="C436" t="n">
         <v>0.820652</v>
@@ -6095,7 +6095,7 @@
         </is>
       </c>
       <c r="B437" t="n">
-        <v>0.017063</v>
+        <v>0.017049</v>
       </c>
       <c r="C437" t="n">
         <v>0.817935</v>
@@ -6108,7 +6108,7 @@
         </is>
       </c>
       <c r="B438" t="n">
-        <v>0.017097</v>
+        <v>0.017071</v>
       </c>
       <c r="C438" t="n">
         <v>0.815217</v>
@@ -6121,7 +6121,7 @@
         </is>
       </c>
       <c r="B439" t="n">
-        <v>0.017151</v>
+        <v>0.017233</v>
       </c>
       <c r="C439" t="n">
         <v>0.8125</v>
@@ -6134,7 +6134,7 @@
         </is>
       </c>
       <c r="B440" t="n">
-        <v>0.017156</v>
+        <v>0.01724</v>
       </c>
       <c r="C440" t="n">
         <v>0.809783</v>
@@ -6147,7 +6147,7 @@
         </is>
       </c>
       <c r="B441" t="n">
-        <v>0.017482</v>
+        <v>0.017276</v>
       </c>
       <c r="C441" t="n">
         <v>0.807065</v>
@@ -6160,7 +6160,7 @@
         </is>
       </c>
       <c r="B442" t="n">
-        <v>0.017533</v>
+        <v>0.017563</v>
       </c>
       <c r="C442" t="n">
         <v>0.804348</v>
@@ -6173,7 +6173,7 @@
         </is>
       </c>
       <c r="B443" t="n">
-        <v>0.018054</v>
+        <v>0.01788</v>
       </c>
       <c r="C443" t="n">
         <v>0.80163</v>
@@ -6186,7 +6186,7 @@
         </is>
       </c>
       <c r="B444" t="n">
-        <v>0.018311</v>
+        <v>0.018426</v>
       </c>
       <c r="C444" t="n">
         <v>0.798913</v>
@@ -6199,7 +6199,7 @@
         </is>
       </c>
       <c r="B445" t="n">
-        <v>0.018438</v>
+        <v>0.018571</v>
       </c>
       <c r="C445" t="n">
         <v>0.796196</v>
@@ -6212,7 +6212,7 @@
         </is>
       </c>
       <c r="B446" t="n">
-        <v>0.019053</v>
+        <v>0.019116</v>
       </c>
       <c r="C446" t="n">
         <v>0.793478</v>
@@ -6225,7 +6225,7 @@
         </is>
       </c>
       <c r="B447" t="n">
-        <v>0.019121</v>
+        <v>0.019176</v>
       </c>
       <c r="C447" t="n">
         <v>0.790761</v>
@@ -6238,7 +6238,7 @@
         </is>
       </c>
       <c r="B448" t="n">
-        <v>0.019252</v>
+        <v>0.01921</v>
       </c>
       <c r="C448" t="n">
         <v>0.788043</v>
@@ -6251,7 +6251,7 @@
         </is>
       </c>
       <c r="B449" t="n">
-        <v>0.019362</v>
+        <v>0.019326</v>
       </c>
       <c r="C449" t="n">
         <v>0.785326</v>
@@ -6264,7 +6264,7 @@
         </is>
       </c>
       <c r="B450" t="n">
-        <v>0.019387</v>
+        <v>0.019496</v>
       </c>
       <c r="C450" t="n">
         <v>0.782609</v>
@@ -6277,7 +6277,7 @@
         </is>
       </c>
       <c r="B451" t="n">
-        <v>0.019478</v>
+        <v>0.0195</v>
       </c>
       <c r="C451" t="n">
         <v>0.779891</v>
@@ -6290,7 +6290,7 @@
         </is>
       </c>
       <c r="B452" t="n">
-        <v>0.020561</v>
+        <v>0.020373</v>
       </c>
       <c r="C452" t="n">
         <v>0.777174</v>
@@ -6303,7 +6303,7 @@
         </is>
       </c>
       <c r="B453" t="n">
-        <v>0.020755</v>
+        <v>0.020797</v>
       </c>
       <c r="C453" t="n">
         <v>0.774457</v>
@@ -6316,7 +6316,7 @@
         </is>
       </c>
       <c r="B454" t="n">
-        <v>0.021092</v>
+        <v>0.021156</v>
       </c>
       <c r="C454" t="n">
         <v>0.771739</v>
@@ -6329,7 +6329,7 @@
         </is>
       </c>
       <c r="B455" t="n">
-        <v>0.021536</v>
+        <v>0.021443</v>
       </c>
       <c r="C455" t="n">
         <v>0.769022</v>
@@ -6342,7 +6342,7 @@
         </is>
       </c>
       <c r="B456" t="n">
-        <v>0.02172</v>
+        <v>0.021895</v>
       </c>
       <c r="C456" t="n">
         <v>0.766304</v>
@@ -6355,7 +6355,7 @@
         </is>
       </c>
       <c r="B457" t="n">
-        <v>0.022173</v>
+        <v>0.022266</v>
       </c>
       <c r="C457" t="n">
         <v>0.763587</v>
@@ -6368,7 +6368,7 @@
         </is>
       </c>
       <c r="B458" t="n">
-        <v>0.022371</v>
+        <v>0.022271</v>
       </c>
       <c r="C458" t="n">
         <v>0.76087</v>
@@ -6381,7 +6381,7 @@
         </is>
       </c>
       <c r="B459" t="n">
-        <v>0.02338</v>
+        <v>0.022904</v>
       </c>
       <c r="C459" t="n">
         <v>0.758152</v>
@@ -6394,7 +6394,7 @@
         </is>
       </c>
       <c r="B460" t="n">
-        <v>0.023403</v>
+        <v>0.023535</v>
       </c>
       <c r="C460" t="n">
         <v>0.755435</v>
@@ -6407,7 +6407,7 @@
         </is>
       </c>
       <c r="B461" t="n">
-        <v>0.023862</v>
+        <v>0.023719</v>
       </c>
       <c r="C461" t="n">
         <v>0.752717</v>
@@ -6420,7 +6420,7 @@
         </is>
       </c>
       <c r="B462" t="n">
-        <v>0.024222</v>
+        <v>0.024212</v>
       </c>
       <c r="C462" t="n">
         <v>0.75</v>
@@ -6433,7 +6433,7 @@
         </is>
       </c>
       <c r="B463" t="n">
-        <v>0.024862</v>
+        <v>0.024754</v>
       </c>
       <c r="C463" t="n">
         <v>0.747283</v>
@@ -6446,7 +6446,7 @@
         </is>
       </c>
       <c r="B464" t="n">
-        <v>0.025123</v>
+        <v>0.025019</v>
       </c>
       <c r="C464" t="n">
         <v>0.744565</v>
@@ -6459,7 +6459,7 @@
         </is>
       </c>
       <c r="B465" t="n">
-        <v>0.025125</v>
+        <v>0.02503</v>
       </c>
       <c r="C465" t="n">
         <v>0.741848</v>
@@ -6472,7 +6472,7 @@
         </is>
       </c>
       <c r="B466" t="n">
-        <v>0.025128</v>
+        <v>0.025078</v>
       </c>
       <c r="C466" t="n">
         <v>0.73913</v>
@@ -6485,7 +6485,7 @@
         </is>
       </c>
       <c r="B467" t="n">
-        <v>0.025317</v>
+        <v>0.02532</v>
       </c>
       <c r="C467" t="n">
         <v>0.736413</v>
@@ -6498,7 +6498,7 @@
         </is>
       </c>
       <c r="B468" t="n">
-        <v>0.025363</v>
+        <v>0.025364</v>
       </c>
       <c r="C468" t="n">
         <v>0.733696</v>
@@ -6511,7 +6511,7 @@
         </is>
       </c>
       <c r="B469" t="n">
-        <v>0.02567</v>
+        <v>0.025404</v>
       </c>
       <c r="C469" t="n">
         <v>0.730978</v>
@@ -6524,7 +6524,7 @@
         </is>
       </c>
       <c r="B470" t="n">
-        <v>0.025842</v>
+        <v>0.025574</v>
       </c>
       <c r="C470" t="n">
         <v>0.728261</v>
@@ -6537,7 +6537,7 @@
         </is>
       </c>
       <c r="B471" t="n">
-        <v>0.02588</v>
+        <v>0.025879</v>
       </c>
       <c r="C471" t="n">
         <v>0.725543</v>
@@ -6550,7 +6550,7 @@
         </is>
       </c>
       <c r="B472" t="n">
-        <v>0.026926</v>
+        <v>0.026372</v>
       </c>
       <c r="C472" t="n">
         <v>0.722826</v>
@@ -6563,7 +6563,7 @@
         </is>
       </c>
       <c r="B473" t="n">
-        <v>0.027141</v>
+        <v>0.026642</v>
       </c>
       <c r="C473" t="n">
         <v>0.720109</v>
@@ -6576,7 +6576,7 @@
         </is>
       </c>
       <c r="B474" t="n">
-        <v>0.027503</v>
+        <v>0.02728</v>
       </c>
       <c r="C474" t="n">
         <v>0.717391</v>
@@ -6589,7 +6589,7 @@
         </is>
       </c>
       <c r="B475" t="n">
-        <v>0.027642</v>
+        <v>0.027742</v>
       </c>
       <c r="C475" t="n">
         <v>0.714674</v>
@@ -6602,7 +6602,7 @@
         </is>
       </c>
       <c r="B476" t="n">
-        <v>0.027917</v>
+        <v>0.027802</v>
       </c>
       <c r="C476" t="n">
         <v>0.711957</v>
@@ -6615,7 +6615,7 @@
         </is>
       </c>
       <c r="B477" t="n">
-        <v>0.027991</v>
+        <v>0.028106</v>
       </c>
       <c r="C477" t="n">
         <v>0.709239</v>
@@ -6628,7 +6628,7 @@
         </is>
       </c>
       <c r="B478" t="n">
-        <v>0.028249</v>
+        <v>0.028315</v>
       </c>
       <c r="C478" t="n">
         <v>0.706522</v>
@@ -6641,7 +6641,7 @@
         </is>
       </c>
       <c r="B479" t="n">
-        <v>0.028486</v>
+        <v>0.028721</v>
       </c>
       <c r="C479" t="n">
         <v>0.703804</v>
@@ -6654,7 +6654,7 @@
         </is>
       </c>
       <c r="B480" t="n">
-        <v>0.028603</v>
+        <v>0.02879</v>
       </c>
       <c r="C480" t="n">
         <v>0.701087</v>
@@ -6667,7 +6667,7 @@
         </is>
       </c>
       <c r="B481" t="n">
-        <v>0.028868</v>
+        <v>0.028918</v>
       </c>
       <c r="C481" t="n">
         <v>0.69837</v>
@@ -6680,7 +6680,7 @@
         </is>
       </c>
       <c r="B482" t="n">
-        <v>0.028891</v>
+        <v>0.02914</v>
       </c>
       <c r="C482" t="n">
         <v>0.695652</v>
@@ -6693,7 +6693,7 @@
         </is>
       </c>
       <c r="B483" t="n">
-        <v>0.029493</v>
+        <v>0.029677</v>
       </c>
       <c r="C483" t="n">
         <v>0.692935</v>
@@ -6706,7 +6706,7 @@
         </is>
       </c>
       <c r="B484" t="n">
-        <v>0.029576</v>
+        <v>0.029706</v>
       </c>
       <c r="C484" t="n">
         <v>0.690217</v>
@@ -6719,7 +6719,7 @@
         </is>
       </c>
       <c r="B485" t="n">
-        <v>0.029871</v>
+        <v>0.029846</v>
       </c>
       <c r="C485" t="n">
         <v>0.6875</v>
@@ -6732,7 +6732,7 @@
         </is>
       </c>
       <c r="B486" t="n">
-        <v>0.029943</v>
+        <v>0.029887</v>
       </c>
       <c r="C486" t="n">
         <v>0.684783</v>
@@ -6745,7 +6745,7 @@
         </is>
       </c>
       <c r="B487" t="n">
-        <v>0.030038</v>
+        <v>0.029906</v>
       </c>
       <c r="C487" t="n">
         <v>0.682065</v>
@@ -6758,7 +6758,7 @@
         </is>
       </c>
       <c r="B488" t="n">
-        <v>0.030078</v>
+        <v>0.029931</v>
       </c>
       <c r="C488" t="n">
         <v>0.679348</v>
@@ -6771,7 +6771,7 @@
         </is>
       </c>
       <c r="B489" t="n">
-        <v>0.030154</v>
+        <v>0.029984</v>
       </c>
       <c r="C489" t="n">
         <v>0.67663</v>
@@ -6784,7 +6784,7 @@
         </is>
       </c>
       <c r="B490" t="n">
-        <v>0.030558</v>
+        <v>0.030831</v>
       </c>
       <c r="C490" t="n">
         <v>0.673913</v>
@@ -6797,7 +6797,7 @@
         </is>
       </c>
       <c r="B491" t="n">
-        <v>0.031231</v>
+        <v>0.031302</v>
       </c>
       <c r="C491" t="n">
         <v>0.671196</v>
@@ -6810,7 +6810,7 @@
         </is>
       </c>
       <c r="B492" t="n">
-        <v>0.031258</v>
+        <v>0.031426</v>
       </c>
       <c r="C492" t="n">
         <v>0.668478</v>
@@ -6823,7 +6823,7 @@
         </is>
       </c>
       <c r="B493" t="n">
-        <v>0.031993</v>
+        <v>0.031596</v>
       </c>
       <c r="C493" t="n">
         <v>0.665761</v>
@@ -6836,7 +6836,7 @@
         </is>
       </c>
       <c r="B494" t="n">
-        <v>0.032085</v>
+        <v>0.032234</v>
       </c>
       <c r="C494" t="n">
         <v>0.663043</v>
@@ -6849,7 +6849,7 @@
         </is>
       </c>
       <c r="B495" t="n">
-        <v>0.032133</v>
+        <v>0.032305</v>
       </c>
       <c r="C495" t="n">
         <v>0.660326</v>
@@ -6862,7 +6862,7 @@
         </is>
       </c>
       <c r="B496" t="n">
-        <v>0.032733</v>
+        <v>0.032685</v>
       </c>
       <c r="C496" t="n">
         <v>0.657609</v>
@@ -6875,7 +6875,7 @@
         </is>
       </c>
       <c r="B497" t="n">
-        <v>0.033574</v>
+        <v>0.033244</v>
       </c>
       <c r="C497" t="n">
         <v>0.654891</v>
@@ -6888,7 +6888,7 @@
         </is>
       </c>
       <c r="B498" t="n">
-        <v>0.03376</v>
+        <v>0.033423</v>
       </c>
       <c r="C498" t="n">
         <v>0.652174</v>
@@ -6901,7 +6901,7 @@
         </is>
       </c>
       <c r="B499" t="n">
-        <v>0.03386</v>
+        <v>0.033742</v>
       </c>
       <c r="C499" t="n">
         <v>0.649457</v>
@@ -6914,7 +6914,7 @@
         </is>
       </c>
       <c r="B500" t="n">
-        <v>0.03392</v>
+        <v>0.033854</v>
       </c>
       <c r="C500" t="n">
         <v>0.646739</v>
@@ -6927,7 +6927,7 @@
         </is>
       </c>
       <c r="B501" t="n">
-        <v>0.033963</v>
+        <v>0.03395</v>
       </c>
       <c r="C501" t="n">
         <v>0.644022</v>
@@ -6940,7 +6940,7 @@
         </is>
       </c>
       <c r="B502" t="n">
-        <v>0.034112</v>
+        <v>0.034049</v>
       </c>
       <c r="C502" t="n">
         <v>0.641304</v>
@@ -6953,7 +6953,7 @@
         </is>
       </c>
       <c r="B503" t="n">
-        <v>0.034614</v>
+        <v>0.034706</v>
       </c>
       <c r="C503" t="n">
         <v>0.638587</v>
@@ -6966,7 +6966,7 @@
         </is>
       </c>
       <c r="B504" t="n">
-        <v>0.034674</v>
+        <v>0.034758</v>
       </c>
       <c r="C504" t="n">
         <v>0.63587</v>
@@ -6979,7 +6979,7 @@
         </is>
       </c>
       <c r="B505" t="n">
-        <v>0.034699</v>
+        <v>0.03477</v>
       </c>
       <c r="C505" t="n">
         <v>0.633152</v>
@@ -6992,7 +6992,7 @@
         </is>
       </c>
       <c r="B506" t="n">
-        <v>0.03487</v>
+        <v>0.034993</v>
       </c>
       <c r="C506" t="n">
         <v>0.630435</v>
@@ -7005,7 +7005,7 @@
         </is>
       </c>
       <c r="B507" t="n">
-        <v>0.035083</v>
+        <v>0.035062</v>
       </c>
       <c r="C507" t="n">
         <v>0.627717</v>
@@ -7018,7 +7018,7 @@
         </is>
       </c>
       <c r="B508" t="n">
-        <v>0.035377</v>
+        <v>0.035343</v>
       </c>
       <c r="C508" t="n">
         <v>0.625</v>
@@ -7031,7 +7031,7 @@
         </is>
       </c>
       <c r="B509" t="n">
-        <v>0.0354</v>
+        <v>0.035495</v>
       </c>
       <c r="C509" t="n">
         <v>0.622283</v>
@@ -7057,7 +7057,7 @@
         </is>
       </c>
       <c r="B511" t="n">
-        <v>0.036284</v>
+        <v>0.036041</v>
       </c>
       <c r="C511" t="n">
         <v>0.616848</v>
@@ -7070,7 +7070,7 @@
         </is>
       </c>
       <c r="B512" t="n">
-        <v>0.037507</v>
+        <v>0.037335</v>
       </c>
       <c r="C512" t="n">
         <v>0.61413</v>
@@ -7083,7 +7083,7 @@
         </is>
       </c>
       <c r="B513" t="n">
-        <v>0.037653</v>
+        <v>0.037822</v>
       </c>
       <c r="C513" t="n">
         <v>0.611413</v>
@@ -7096,7 +7096,7 @@
         </is>
       </c>
       <c r="B514" t="n">
-        <v>0.037745</v>
+        <v>0.038043</v>
       </c>
       <c r="C514" t="n">
         <v>0.608696</v>
@@ -7109,7 +7109,7 @@
         </is>
       </c>
       <c r="B515" t="n">
-        <v>0.038517</v>
+        <v>0.038277</v>
       </c>
       <c r="C515" t="n">
         <v>0.605978</v>
@@ -7122,7 +7122,7 @@
         </is>
       </c>
       <c r="B516" t="n">
-        <v>0.038555</v>
+        <v>0.038545</v>
       </c>
       <c r="C516" t="n">
         <v>0.603261</v>
@@ -7135,7 +7135,7 @@
         </is>
       </c>
       <c r="B517" t="n">
-        <v>0.038556</v>
+        <v>0.038808</v>
       </c>
       <c r="C517" t="n">
         <v>0.600543</v>
@@ -7148,7 +7148,7 @@
         </is>
       </c>
       <c r="B518" t="n">
-        <v>0.039037</v>
+        <v>0.038859</v>
       </c>
       <c r="C518" t="n">
         <v>0.597826</v>
@@ -7161,7 +7161,7 @@
         </is>
       </c>
       <c r="B519" t="n">
-        <v>0.039205</v>
+        <v>0.039551</v>
       </c>
       <c r="C519" t="n">
         <v>0.595109</v>
@@ -7174,7 +7174,7 @@
         </is>
       </c>
       <c r="B520" t="n">
-        <v>0.039382</v>
+        <v>0.039641</v>
       </c>
       <c r="C520" t="n">
         <v>0.592391</v>
@@ -7187,7 +7187,7 @@
         </is>
       </c>
       <c r="B521" t="n">
-        <v>0.039644</v>
+        <v>0.039785</v>
       </c>
       <c r="C521" t="n">
         <v>0.589674</v>
@@ -7200,7 +7200,7 @@
         </is>
       </c>
       <c r="B522" t="n">
-        <v>0.039784</v>
+        <v>0.039882</v>
       </c>
       <c r="C522" t="n">
         <v>0.586957</v>
@@ -7213,7 +7213,7 @@
         </is>
       </c>
       <c r="B523" t="n">
-        <v>0.040018</v>
+        <v>0.040194</v>
       </c>
       <c r="C523" t="n">
         <v>0.584239</v>
@@ -7226,7 +7226,7 @@
         </is>
       </c>
       <c r="B524" t="n">
-        <v>0.040251</v>
+        <v>0.040208</v>
       </c>
       <c r="C524" t="n">
         <v>0.581522</v>
@@ -7239,7 +7239,7 @@
         </is>
       </c>
       <c r="B525" t="n">
-        <v>0.040529</v>
+        <v>0.040846</v>
       </c>
       <c r="C525" t="n">
         <v>0.578804</v>
@@ -7252,7 +7252,7 @@
         </is>
       </c>
       <c r="B526" t="n">
-        <v>0.04167</v>
+        <v>0.041278</v>
       </c>
       <c r="C526" t="n">
         <v>0.576087</v>
@@ -7265,7 +7265,7 @@
         </is>
       </c>
       <c r="B527" t="n">
-        <v>0.041827</v>
+        <v>0.041661</v>
       </c>
       <c r="C527" t="n">
         <v>0.57337</v>
@@ -7278,7 +7278,7 @@
         </is>
       </c>
       <c r="B528" t="n">
-        <v>0.042015</v>
+        <v>0.042152</v>
       </c>
       <c r="C528" t="n">
         <v>0.570652</v>
@@ -7291,7 +7291,7 @@
         </is>
       </c>
       <c r="B529" t="n">
-        <v>0.042187</v>
+        <v>0.042256</v>
       </c>
       <c r="C529" t="n">
         <v>0.567935</v>
@@ -7304,7 +7304,7 @@
         </is>
       </c>
       <c r="B530" t="n">
-        <v>0.042475</v>
+        <v>0.04254</v>
       </c>
       <c r="C530" t="n">
         <v>0.565217</v>
@@ -7317,7 +7317,7 @@
         </is>
       </c>
       <c r="B531" t="n">
-        <v>0.04255</v>
+        <v>0.0428</v>
       </c>
       <c r="C531" t="n">
         <v>0.5625</v>
@@ -7330,7 +7330,7 @@
         </is>
       </c>
       <c r="B532" t="n">
-        <v>0.042673</v>
+        <v>0.042916</v>
       </c>
       <c r="C532" t="n">
         <v>0.559783</v>
@@ -7343,7 +7343,7 @@
         </is>
       </c>
       <c r="B533" t="n">
-        <v>0.042967</v>
+        <v>0.043004</v>
       </c>
       <c r="C533" t="n">
         <v>0.557065</v>
@@ -7356,7 +7356,7 @@
         </is>
       </c>
       <c r="B534" t="n">
-        <v>0.042974</v>
+        <v>0.043112</v>
       </c>
       <c r="C534" t="n">
         <v>0.554348</v>
@@ -7369,7 +7369,7 @@
         </is>
       </c>
       <c r="B535" t="n">
-        <v>0.043181</v>
+        <v>0.04329</v>
       </c>
       <c r="C535" t="n">
         <v>0.55163</v>
@@ -7382,7 +7382,7 @@
         </is>
       </c>
       <c r="B536" t="n">
-        <v>0.043192</v>
+        <v>0.043477</v>
       </c>
       <c r="C536" t="n">
         <v>0.548913</v>
@@ -7395,7 +7395,7 @@
         </is>
       </c>
       <c r="B537" t="n">
-        <v>0.043392</v>
+        <v>0.043583</v>
       </c>
       <c r="C537" t="n">
         <v>0.546196</v>
@@ -7408,7 +7408,7 @@
         </is>
       </c>
       <c r="B538" t="n">
-        <v>0.043414</v>
+        <v>0.043643</v>
       </c>
       <c r="C538" t="n">
         <v>0.543478</v>
@@ -7421,7 +7421,7 @@
         </is>
       </c>
       <c r="B539" t="n">
-        <v>0.04374</v>
+        <v>0.043733</v>
       </c>
       <c r="C539" t="n">
         <v>0.540761</v>
@@ -7434,7 +7434,7 @@
         </is>
       </c>
       <c r="B540" t="n">
-        <v>0.043888</v>
+        <v>0.044173</v>
       </c>
       <c r="C540" t="n">
         <v>0.538043</v>
@@ -7447,7 +7447,7 @@
         </is>
       </c>
       <c r="B541" t="n">
-        <v>0.044514</v>
+        <v>0.044677</v>
       </c>
       <c r="C541" t="n">
         <v>0.535326</v>
@@ -7460,7 +7460,7 @@
         </is>
       </c>
       <c r="B542" t="n">
-        <v>0.044625</v>
+        <v>0.044806</v>
       </c>
       <c r="C542" t="n">
         <v>0.532609</v>
@@ -7473,7 +7473,7 @@
         </is>
       </c>
       <c r="B543" t="n">
-        <v>0.044781</v>
+        <v>0.044819</v>
       </c>
       <c r="C543" t="n">
         <v>0.529891</v>
@@ -7486,7 +7486,7 @@
         </is>
       </c>
       <c r="B544" t="n">
-        <v>0.045068</v>
+        <v>0.044895</v>
       </c>
       <c r="C544" t="n">
         <v>0.527174</v>
@@ -7499,7 +7499,7 @@
         </is>
       </c>
       <c r="B545" t="n">
-        <v>0.045227</v>
+        <v>0.044901</v>
       </c>
       <c r="C545" t="n">
         <v>0.524457</v>
@@ -7512,7 +7512,7 @@
         </is>
       </c>
       <c r="B546" t="n">
-        <v>0.04539</v>
+        <v>0.045545</v>
       </c>
       <c r="C546" t="n">
         <v>0.521739</v>
@@ -7525,7 +7525,7 @@
         </is>
       </c>
       <c r="B547" t="n">
-        <v>0.045593</v>
+        <v>0.04585</v>
       </c>
       <c r="C547" t="n">
         <v>0.519022</v>
@@ -7538,7 +7538,7 @@
         </is>
       </c>
       <c r="B548" t="n">
-        <v>0.04626</v>
+        <v>0.046267</v>
       </c>
       <c r="C548" t="n">
         <v>0.516304</v>
@@ -7551,7 +7551,7 @@
         </is>
       </c>
       <c r="B549" t="n">
-        <v>0.046845</v>
+        <v>0.046363</v>
       </c>
       <c r="C549" t="n">
         <v>0.513587</v>
@@ -7564,7 +7564,7 @@
         </is>
       </c>
       <c r="B550" t="n">
-        <v>0.047096</v>
+        <v>0.046497</v>
       </c>
       <c r="C550" t="n">
         <v>0.51087</v>
@@ -7577,7 +7577,7 @@
         </is>
       </c>
       <c r="B551" t="n">
-        <v>0.047595</v>
+        <v>0.047747</v>
       </c>
       <c r="C551" t="n">
         <v>0.508152</v>
@@ -7590,7 +7590,7 @@
         </is>
       </c>
       <c r="B552" t="n">
-        <v>0.047765</v>
+        <v>0.047979</v>
       </c>
       <c r="C552" t="n">
         <v>0.505435</v>
@@ -7603,7 +7603,7 @@
         </is>
       </c>
       <c r="B553" t="n">
-        <v>0.048177</v>
+        <v>0.048217</v>
       </c>
       <c r="C553" t="n">
         <v>0.502717</v>
@@ -7616,7 +7616,7 @@
         </is>
       </c>
       <c r="B554" t="n">
-        <v>0.04899</v>
+        <v>0.048277</v>
       </c>
       <c r="C554" t="n">
         <v>0.5</v>
@@ -7629,7 +7629,7 @@
         </is>
       </c>
       <c r="B555" t="n">
-        <v>0.049385</v>
+        <v>0.049311</v>
       </c>
       <c r="C555" t="n">
         <v>0.497283</v>
@@ -7642,7 +7642,7 @@
         </is>
       </c>
       <c r="B556" t="n">
-        <v>0.049416</v>
+        <v>0.049479</v>
       </c>
       <c r="C556" t="n">
         <v>0.494565</v>
@@ -7655,7 +7655,7 @@
         </is>
       </c>
       <c r="B557" t="n">
-        <v>0.049541</v>
+        <v>0.049815</v>
       </c>
       <c r="C557" t="n">
         <v>0.491848</v>
@@ -7668,7 +7668,7 @@
         </is>
       </c>
       <c r="B558" t="n">
-        <v>0.050824</v>
+        <v>0.05042</v>
       </c>
       <c r="C558" t="n">
         <v>0.48913</v>
@@ -7681,7 +7681,7 @@
         </is>
       </c>
       <c r="B559" t="n">
-        <v>0.051619</v>
+        <v>0.050841</v>
       </c>
       <c r="C559" t="n">
         <v>0.486413</v>
@@ -7694,7 +7694,7 @@
         </is>
       </c>
       <c r="B560" t="n">
-        <v>0.051942</v>
+        <v>0.052325</v>
       </c>
       <c r="C560" t="n">
         <v>0.483696</v>
@@ -7707,7 +7707,7 @@
         </is>
       </c>
       <c r="B561" t="n">
-        <v>0.052547</v>
+        <v>0.052868</v>
       </c>
       <c r="C561" t="n">
         <v>0.480978</v>
@@ -7720,7 +7720,7 @@
         </is>
       </c>
       <c r="B562" t="n">
-        <v>0.053066</v>
+        <v>0.053207</v>
       </c>
       <c r="C562" t="n">
         <v>0.478261</v>
@@ -7733,7 +7733,7 @@
         </is>
       </c>
       <c r="B563" t="n">
-        <v>0.053281</v>
+        <v>0.053393</v>
       </c>
       <c r="C563" t="n">
         <v>0.475543</v>
@@ -7746,7 +7746,7 @@
         </is>
       </c>
       <c r="B564" t="n">
-        <v>0.053663</v>
+        <v>0.053528</v>
       </c>
       <c r="C564" t="n">
         <v>0.472826</v>
@@ -7759,7 +7759,7 @@
         </is>
       </c>
       <c r="B565" t="n">
-        <v>0.053931</v>
+        <v>0.053602</v>
       </c>
       <c r="C565" t="n">
         <v>0.470109</v>
@@ -7772,7 +7772,7 @@
         </is>
       </c>
       <c r="B566" t="n">
-        <v>0.054494</v>
+        <v>0.053864</v>
       </c>
       <c r="C566" t="n">
         <v>0.467391</v>
@@ -7785,7 +7785,7 @@
         </is>
       </c>
       <c r="B567" t="n">
-        <v>0.054545</v>
+        <v>0.054203</v>
       </c>
       <c r="C567" t="n">
         <v>0.464674</v>
@@ -7798,7 +7798,7 @@
         </is>
       </c>
       <c r="B568" t="n">
-        <v>0.055198</v>
+        <v>0.054594</v>
       </c>
       <c r="C568" t="n">
         <v>0.461957</v>
@@ -7811,7 +7811,7 @@
         </is>
       </c>
       <c r="B569" t="n">
-        <v>0.055231</v>
+        <v>0.055216</v>
       </c>
       <c r="C569" t="n">
         <v>0.459239</v>
@@ -7824,7 +7824,7 @@
         </is>
       </c>
       <c r="B570" t="n">
-        <v>0.05541</v>
+        <v>0.055266</v>
       </c>
       <c r="C570" t="n">
         <v>0.456522</v>
@@ -7837,7 +7837,7 @@
         </is>
       </c>
       <c r="B571" t="n">
-        <v>0.055463</v>
+        <v>0.055299</v>
       </c>
       <c r="C571" t="n">
         <v>0.453804</v>
@@ -7850,7 +7850,7 @@
         </is>
       </c>
       <c r="B572" t="n">
-        <v>0.055584</v>
+        <v>0.055563</v>
       </c>
       <c r="C572" t="n">
         <v>0.451087</v>
@@ -7863,7 +7863,7 @@
         </is>
       </c>
       <c r="B573" t="n">
-        <v>0.055621</v>
+        <v>0.055912</v>
       </c>
       <c r="C573" t="n">
         <v>0.44837</v>
@@ -7876,7 +7876,7 @@
         </is>
       </c>
       <c r="B574" t="n">
-        <v>0.055839</v>
+        <v>0.056087</v>
       </c>
       <c r="C574" t="n">
         <v>0.445652</v>
@@ -7889,7 +7889,7 @@
         </is>
       </c>
       <c r="B575" t="n">
-        <v>0.057096</v>
+        <v>0.05698</v>
       </c>
       <c r="C575" t="n">
         <v>0.442935</v>
@@ -7902,7 +7902,7 @@
         </is>
       </c>
       <c r="B576" t="n">
-        <v>0.057478</v>
+        <v>0.05758</v>
       </c>
       <c r="C576" t="n">
         <v>0.440217</v>
@@ -7915,7 +7915,7 @@
         </is>
       </c>
       <c r="B577" t="n">
-        <v>0.057876</v>
+        <v>0.057897</v>
       </c>
       <c r="C577" t="n">
         <v>0.4375</v>
@@ -7928,7 +7928,7 @@
         </is>
       </c>
       <c r="B578" t="n">
-        <v>0.058496</v>
+        <v>0.058081</v>
       </c>
       <c r="C578" t="n">
         <v>0.434783</v>
@@ -7941,7 +7941,7 @@
         </is>
       </c>
       <c r="B579" t="n">
-        <v>0.059825</v>
+        <v>0.059321</v>
       </c>
       <c r="C579" t="n">
         <v>0.432065</v>
@@ -7954,7 +7954,7 @@
         </is>
       </c>
       <c r="B580" t="n">
-        <v>0.059871</v>
+        <v>0.059863</v>
       </c>
       <c r="C580" t="n">
         <v>0.429348</v>
@@ -7967,7 +7967,7 @@
         </is>
       </c>
       <c r="B581" t="n">
-        <v>0.059884</v>
+        <v>0.05987</v>
       </c>
       <c r="C581" t="n">
         <v>0.42663</v>
@@ -7980,7 +7980,7 @@
         </is>
       </c>
       <c r="B582" t="n">
-        <v>0.060254</v>
+        <v>0.060205</v>
       </c>
       <c r="C582" t="n">
         <v>0.423913</v>
@@ -7993,7 +7993,7 @@
         </is>
       </c>
       <c r="B583" t="n">
-        <v>0.060748</v>
+        <v>0.060766</v>
       </c>
       <c r="C583" t="n">
         <v>0.421196</v>
@@ -8006,7 +8006,7 @@
         </is>
       </c>
       <c r="B584" t="n">
-        <v>0.061163</v>
+        <v>0.061329</v>
       </c>
       <c r="C584" t="n">
         <v>0.418478</v>
@@ -8019,7 +8019,7 @@
         </is>
       </c>
       <c r="B585" t="n">
-        <v>0.061501</v>
+        <v>0.061413</v>
       </c>
       <c r="C585" t="n">
         <v>0.415761</v>
@@ -8032,7 +8032,7 @@
         </is>
       </c>
       <c r="B586" t="n">
-        <v>0.061709</v>
+        <v>0.061913</v>
       </c>
       <c r="C586" t="n">
         <v>0.413043</v>
@@ -8045,7 +8045,7 @@
         </is>
       </c>
       <c r="B587" t="n">
-        <v>0.062537</v>
+        <v>0.062426</v>
       </c>
       <c r="C587" t="n">
         <v>0.410326</v>
@@ -8058,7 +8058,7 @@
         </is>
       </c>
       <c r="B588" t="n">
-        <v>0.063568</v>
+        <v>0.063253</v>
       </c>
       <c r="C588" t="n">
         <v>0.407609</v>
@@ -8071,7 +8071,7 @@
         </is>
       </c>
       <c r="B589" t="n">
-        <v>0.06386500000000001</v>
+        <v>0.064389</v>
       </c>
       <c r="C589" t="n">
         <v>0.404891</v>
@@ -8084,7 +8084,7 @@
         </is>
       </c>
       <c r="B590" t="n">
-        <v>0.065997</v>
+        <v>0.06528399999999999</v>
       </c>
       <c r="C590" t="n">
         <v>0.402174</v>
@@ -8097,7 +8097,7 @@
         </is>
       </c>
       <c r="B591" t="n">
-        <v>0.066236</v>
+        <v>0.066112</v>
       </c>
       <c r="C591" t="n">
         <v>0.399457</v>
@@ -8110,7 +8110,7 @@
         </is>
       </c>
       <c r="B592" t="n">
-        <v>0.066733</v>
+        <v>0.066692</v>
       </c>
       <c r="C592" t="n">
         <v>0.396739</v>
@@ -8123,7 +8123,7 @@
         </is>
       </c>
       <c r="B593" t="n">
-        <v>0.066843</v>
+        <v>0.066969</v>
       </c>
       <c r="C593" t="n">
         <v>0.394022</v>
@@ -8136,7 +8136,7 @@
         </is>
       </c>
       <c r="B594" t="n">
-        <v>0.066885</v>
+        <v>0.067117</v>
       </c>
       <c r="C594" t="n">
         <v>0.391304</v>
@@ -8149,7 +8149,7 @@
         </is>
       </c>
       <c r="B595" t="n">
-        <v>0.067568</v>
+        <v>0.067134</v>
       </c>
       <c r="C595" t="n">
         <v>0.388587</v>
@@ -8162,7 +8162,7 @@
         </is>
       </c>
       <c r="B596" t="n">
-        <v>0.067622</v>
+        <v>0.06777</v>
       </c>
       <c r="C596" t="n">
         <v>0.38587</v>
@@ -8175,7 +8175,7 @@
         </is>
       </c>
       <c r="B597" t="n">
-        <v>0.06771000000000001</v>
+        <v>0.067789</v>
       </c>
       <c r="C597" t="n">
         <v>0.383152</v>
@@ -8188,7 +8188,7 @@
         </is>
       </c>
       <c r="B598" t="n">
-        <v>0.06807199999999999</v>
+        <v>0.068091</v>
       </c>
       <c r="C598" t="n">
         <v>0.380435</v>
@@ -8201,7 +8201,7 @@
         </is>
       </c>
       <c r="B599" t="n">
-        <v>0.068519</v>
+        <v>0.068092</v>
       </c>
       <c r="C599" t="n">
         <v>0.377717</v>
@@ -8214,7 +8214,7 @@
         </is>
       </c>
       <c r="B600" t="n">
-        <v>0.06897200000000001</v>
+        <v>0.06845999999999999</v>
       </c>
       <c r="C600" t="n">
         <v>0.375</v>
@@ -8227,7 +8227,7 @@
         </is>
       </c>
       <c r="B601" t="n">
-        <v>0.069174</v>
+        <v>0.068522</v>
       </c>
       <c r="C601" t="n">
         <v>0.372283</v>
@@ -8240,7 +8240,7 @@
         </is>
       </c>
       <c r="B602" t="n">
-        <v>0.069176</v>
+        <v>0.068814</v>
       </c>
       <c r="C602" t="n">
         <v>0.369565</v>
@@ -8253,7 +8253,7 @@
         </is>
       </c>
       <c r="B603" t="n">
-        <v>0.06956</v>
+        <v>0.06907099999999999</v>
       </c>
       <c r="C603" t="n">
         <v>0.366848</v>
@@ -8266,7 +8266,7 @@
         </is>
       </c>
       <c r="B604" t="n">
-        <v>0.06965200000000001</v>
+        <v>0.069317</v>
       </c>
       <c r="C604" t="n">
         <v>0.36413</v>
@@ -8279,7 +8279,7 @@
         </is>
       </c>
       <c r="B605" t="n">
-        <v>0.06968000000000001</v>
+        <v>0.069463</v>
       </c>
       <c r="C605" t="n">
         <v>0.361413</v>
@@ -8292,7 +8292,7 @@
         </is>
       </c>
       <c r="B606" t="n">
-        <v>0.070913</v>
+        <v>0.071409</v>
       </c>
       <c r="C606" t="n">
         <v>0.358696</v>
@@ -8305,7 +8305,7 @@
         </is>
       </c>
       <c r="B607" t="n">
-        <v>0.071634</v>
+        <v>0.072283</v>
       </c>
       <c r="C607" t="n">
         <v>0.355978</v>
@@ -8318,7 +8318,7 @@
         </is>
       </c>
       <c r="B608" t="n">
-        <v>0.07173499999999999</v>
+        <v>0.072382</v>
       </c>
       <c r="C608" t="n">
         <v>0.353261</v>
@@ -8331,7 +8331,7 @@
         </is>
       </c>
       <c r="B609" t="n">
-        <v>0.072724</v>
+        <v>0.072753</v>
       </c>
       <c r="C609" t="n">
         <v>0.350543</v>
@@ -8344,7 +8344,7 @@
         </is>
       </c>
       <c r="B610" t="n">
-        <v>0.073514</v>
+        <v>0.073181</v>
       </c>
       <c r="C610" t="n">
         <v>0.347826</v>
@@ -8357,7 +8357,7 @@
         </is>
       </c>
       <c r="B611" t="n">
-        <v>0.07398100000000001</v>
+        <v>0.07374699999999999</v>
       </c>
       <c r="C611" t="n">
         <v>0.345109</v>
@@ -8370,7 +8370,7 @@
         </is>
       </c>
       <c r="B612" t="n">
-        <v>0.07413500000000001</v>
+        <v>0.074073</v>
       </c>
       <c r="C612" t="n">
         <v>0.342391</v>
@@ -8383,7 +8383,7 @@
         </is>
       </c>
       <c r="B613" t="n">
-        <v>0.07430200000000001</v>
+        <v>0.07409399999999999</v>
       </c>
       <c r="C613" t="n">
         <v>0.339674</v>
@@ -8396,7 +8396,7 @@
         </is>
       </c>
       <c r="B614" t="n">
-        <v>0.074549</v>
+        <v>0.07437299999999999</v>
       </c>
       <c r="C614" t="n">
         <v>0.336957</v>
@@ -8409,7 +8409,7 @@
         </is>
       </c>
       <c r="B615" t="n">
-        <v>0.074602</v>
+        <v>0.074558</v>
       </c>
       <c r="C615" t="n">
         <v>0.334239</v>
@@ -8422,7 +8422,7 @@
         </is>
       </c>
       <c r="B616" t="n">
-        <v>0.075512</v>
+        <v>0.075156</v>
       </c>
       <c r="C616" t="n">
         <v>0.331522</v>
@@ -8435,7 +8435,7 @@
         </is>
       </c>
       <c r="B617" t="n">
-        <v>0.075693</v>
+        <v>0.075652</v>
       </c>
       <c r="C617" t="n">
         <v>0.328804</v>
@@ -8448,7 +8448,7 @@
         </is>
       </c>
       <c r="B618" t="n">
-        <v>0.075881</v>
+        <v>0.076223</v>
       </c>
       <c r="C618" t="n">
         <v>0.326087</v>
@@ -8461,7 +8461,7 @@
         </is>
       </c>
       <c r="B619" t="n">
-        <v>0.07727100000000001</v>
+        <v>0.076545</v>
       </c>
       <c r="C619" t="n">
         <v>0.32337</v>
@@ -8474,7 +8474,7 @@
         </is>
       </c>
       <c r="B620" t="n">
-        <v>0.077406</v>
+        <v>0.076932</v>
       </c>
       <c r="C620" t="n">
         <v>0.320652</v>
@@ -8487,7 +8487,7 @@
         </is>
       </c>
       <c r="B621" t="n">
-        <v>0.077641</v>
+        <v>0.077782</v>
       </c>
       <c r="C621" t="n">
         <v>0.317935</v>
@@ -8500,7 +8500,7 @@
         </is>
       </c>
       <c r="B622" t="n">
-        <v>0.077734</v>
+        <v>0.07785599999999999</v>
       </c>
       <c r="C622" t="n">
         <v>0.315217</v>
@@ -8513,7 +8513,7 @@
         </is>
       </c>
       <c r="B623" t="n">
-        <v>0.078125</v>
+        <v>0.077919</v>
       </c>
       <c r="C623" t="n">
         <v>0.3125</v>
@@ -8526,7 +8526,7 @@
         </is>
       </c>
       <c r="B624" t="n">
-        <v>0.078233</v>
+        <v>0.078192</v>
       </c>
       <c r="C624" t="n">
         <v>0.309783</v>
@@ -8539,7 +8539,7 @@
         </is>
       </c>
       <c r="B625" t="n">
-        <v>0.078558</v>
+        <v>0.07871599999999999</v>
       </c>
       <c r="C625" t="n">
         <v>0.307065</v>
@@ -8552,7 +8552,7 @@
         </is>
       </c>
       <c r="B626" t="n">
-        <v>0.078664</v>
+        <v>0.078904</v>
       </c>
       <c r="C626" t="n">
         <v>0.304348</v>
@@ -8565,7 +8565,7 @@
         </is>
       </c>
       <c r="B627" t="n">
-        <v>0.07870199999999999</v>
+        <v>0.07910399999999999</v>
       </c>
       <c r="C627" t="n">
         <v>0.30163</v>
@@ -8578,7 +8578,7 @@
         </is>
       </c>
       <c r="B628" t="n">
-        <v>0.079123</v>
+        <v>0.07917</v>
       </c>
       <c r="C628" t="n">
         <v>0.298913</v>
@@ -8591,7 +8591,7 @@
         </is>
       </c>
       <c r="B629" t="n">
-        <v>0.080346</v>
+        <v>0.080233</v>
       </c>
       <c r="C629" t="n">
         <v>0.296196</v>
@@ -8604,7 +8604,7 @@
         </is>
       </c>
       <c r="B630" t="n">
-        <v>0.083567</v>
+        <v>0.083747</v>
       </c>
       <c r="C630" t="n">
         <v>0.293478</v>
@@ -8617,7 +8617,7 @@
         </is>
       </c>
       <c r="B631" t="n">
-        <v>0.083783</v>
+        <v>0.084022</v>
       </c>
       <c r="C631" t="n">
         <v>0.290761</v>
@@ -8630,7 +8630,7 @@
         </is>
       </c>
       <c r="B632" t="n">
-        <v>0.084368</v>
+        <v>0.084894</v>
       </c>
       <c r="C632" t="n">
         <v>0.288043</v>
@@ -8643,7 +8643,7 @@
         </is>
       </c>
       <c r="B633" t="n">
-        <v>0.085267</v>
+        <v>0.084939</v>
       </c>
       <c r="C633" t="n">
         <v>0.285326</v>
@@ -8656,7 +8656,7 @@
         </is>
       </c>
       <c r="B634" t="n">
-        <v>0.085907</v>
+        <v>0.08558399999999999</v>
       </c>
       <c r="C634" t="n">
         <v>0.282609</v>
@@ -8669,7 +8669,7 @@
         </is>
       </c>
       <c r="B635" t="n">
-        <v>0.086119</v>
+        <v>0.086018</v>
       </c>
       <c r="C635" t="n">
         <v>0.279891</v>
@@ -8682,7 +8682,7 @@
         </is>
       </c>
       <c r="B636" t="n">
-        <v>0.087307</v>
+        <v>0.08688800000000001</v>
       </c>
       <c r="C636" t="n">
         <v>0.277174</v>
@@ -8695,7 +8695,7 @@
         </is>
       </c>
       <c r="B637" t="n">
-        <v>0.08731700000000001</v>
+        <v>0.087052</v>
       </c>
       <c r="C637" t="n">
         <v>0.274457</v>
@@ -8708,7 +8708,7 @@
         </is>
       </c>
       <c r="B638" t="n">
-        <v>0.087342</v>
+        <v>0.087921</v>
       </c>
       <c r="C638" t="n">
         <v>0.271739</v>
@@ -8721,7 +8721,7 @@
         </is>
       </c>
       <c r="B639" t="n">
-        <v>0.088059</v>
+        <v>0.088004</v>
       </c>
       <c r="C639" t="n">
         <v>0.269022</v>
@@ -8734,7 +8734,7 @@
         </is>
       </c>
       <c r="B640" t="n">
-        <v>0.08874899999999999</v>
+        <v>0.088063</v>
       </c>
       <c r="C640" t="n">
         <v>0.266304</v>
@@ -8747,7 +8747,7 @@
         </is>
       </c>
       <c r="B641" t="n">
-        <v>0.089513</v>
+        <v>0.08876100000000001</v>
       </c>
       <c r="C641" t="n">
         <v>0.263587</v>
@@ -8760,7 +8760,7 @@
         </is>
       </c>
       <c r="B642" t="n">
-        <v>0.089728</v>
+        <v>0.089491</v>
       </c>
       <c r="C642" t="n">
         <v>0.26087</v>
@@ -8773,7 +8773,7 @@
         </is>
       </c>
       <c r="B643" t="n">
-        <v>0.090035</v>
+        <v>0.089549</v>
       </c>
       <c r="C643" t="n">
         <v>0.258152</v>
@@ -8786,7 +8786,7 @@
         </is>
       </c>
       <c r="B644" t="n">
-        <v>0.090933</v>
+        <v>0.090027</v>
       </c>
       <c r="C644" t="n">
         <v>0.255435</v>
@@ -8799,7 +8799,7 @@
         </is>
       </c>
       <c r="B645" t="n">
-        <v>0.09107</v>
+        <v>0.09027499999999999</v>
       </c>
       <c r="C645" t="n">
         <v>0.252717</v>
@@ -8812,7 +8812,7 @@
         </is>
       </c>
       <c r="B646" t="n">
-        <v>0.091888</v>
+        <v>0.091874</v>
       </c>
       <c r="C646" t="n">
         <v>0.25</v>
@@ -8825,7 +8825,7 @@
         </is>
       </c>
       <c r="B647" t="n">
-        <v>0.092057</v>
+        <v>0.092524</v>
       </c>
       <c r="C647" t="n">
         <v>0.247283</v>
@@ -8838,7 +8838,7 @@
         </is>
       </c>
       <c r="B648" t="n">
-        <v>0.092192</v>
+        <v>0.092546</v>
       </c>
       <c r="C648" t="n">
         <v>0.244565</v>
@@ -8851,7 +8851,7 @@
         </is>
       </c>
       <c r="B649" t="n">
-        <v>0.092596</v>
+        <v>0.092748</v>
       </c>
       <c r="C649" t="n">
         <v>0.241848</v>
@@ -8864,7 +8864,7 @@
         </is>
       </c>
       <c r="B650" t="n">
-        <v>0.093151</v>
+        <v>0.093891</v>
       </c>
       <c r="C650" t="n">
         <v>0.23913</v>
@@ -8877,7 +8877,7 @@
         </is>
       </c>
       <c r="B651" t="n">
-        <v>0.093668</v>
+        <v>0.09418600000000001</v>
       </c>
       <c r="C651" t="n">
         <v>0.236413</v>
@@ -8890,7 +8890,7 @@
         </is>
       </c>
       <c r="B652" t="n">
-        <v>0.097619</v>
+        <v>0.098229</v>
       </c>
       <c r="C652" t="n">
         <v>0.233696</v>
@@ -8903,7 +8903,7 @@
         </is>
       </c>
       <c r="B653" t="n">
-        <v>0.09816900000000001</v>
+        <v>0.098398</v>
       </c>
       <c r="C653" t="n">
         <v>0.230978</v>
@@ -8916,7 +8916,7 @@
         </is>
       </c>
       <c r="B654" t="n">
-        <v>0.09941700000000001</v>
+        <v>0.098486</v>
       </c>
       <c r="C654" t="n">
         <v>0.228261</v>
@@ -8929,7 +8929,7 @@
         </is>
       </c>
       <c r="B655" t="n">
-        <v>0.099678</v>
+        <v>0.09854499999999999</v>
       </c>
       <c r="C655" t="n">
         <v>0.225543</v>
@@ -8942,7 +8942,7 @@
         </is>
       </c>
       <c r="B656" t="n">
-        <v>0.099971</v>
+        <v>0.09925100000000001</v>
       </c>
       <c r="C656" t="n">
         <v>0.222826</v>
@@ -8955,7 +8955,7 @@
         </is>
       </c>
       <c r="B657" t="n">
-        <v>0.100061</v>
+        <v>0.100148</v>
       </c>
       <c r="C657" t="n">
         <v>0.220109</v>
@@ -8968,7 +8968,7 @@
         </is>
       </c>
       <c r="B658" t="n">
-        <v>0.100268</v>
+        <v>0.100708</v>
       </c>
       <c r="C658" t="n">
         <v>0.217391</v>
@@ -8981,7 +8981,7 @@
         </is>
       </c>
       <c r="B659" t="n">
-        <v>0.100625</v>
+        <v>0.100955</v>
       </c>
       <c r="C659" t="n">
         <v>0.214674</v>
@@ -8994,7 +8994,7 @@
         </is>
       </c>
       <c r="B660" t="n">
-        <v>0.101773</v>
+        <v>0.101141</v>
       </c>
       <c r="C660" t="n">
         <v>0.211957</v>
@@ -9007,7 +9007,7 @@
         </is>
       </c>
       <c r="B661" t="n">
-        <v>0.101871</v>
+        <v>0.101172</v>
       </c>
       <c r="C661" t="n">
         <v>0.209239</v>
@@ -9020,7 +9020,7 @@
         </is>
       </c>
       <c r="B662" t="n">
-        <v>0.101972</v>
+        <v>0.101465</v>
       </c>
       <c r="C662" t="n">
         <v>0.206522</v>
@@ -9033,7 +9033,7 @@
         </is>
       </c>
       <c r="B663" t="n">
-        <v>0.102054</v>
+        <v>0.101628</v>
       </c>
       <c r="C663" t="n">
         <v>0.203804</v>
@@ -9046,7 +9046,7 @@
         </is>
       </c>
       <c r="B664" t="n">
-        <v>0.103475</v>
+        <v>0.102175</v>
       </c>
       <c r="C664" t="n">
         <v>0.201087</v>
@@ -9059,7 +9059,7 @@
         </is>
       </c>
       <c r="B665" t="n">
-        <v>0.104028</v>
+        <v>0.103661</v>
       </c>
       <c r="C665" t="n">
         <v>0.19837</v>
@@ -9072,7 +9072,7 @@
         </is>
       </c>
       <c r="B666" t="n">
-        <v>0.104299</v>
+        <v>0.104685</v>
       </c>
       <c r="C666" t="n">
         <v>0.195652</v>
@@ -9085,7 +9085,7 @@
         </is>
       </c>
       <c r="B667" t="n">
-        <v>0.105687</v>
+        <v>0.105134</v>
       </c>
       <c r="C667" t="n">
         <v>0.192935</v>
@@ -9098,7 +9098,7 @@
         </is>
       </c>
       <c r="B668" t="n">
-        <v>0.107026</v>
+        <v>0.107492</v>
       </c>
       <c r="C668" t="n">
         <v>0.190217</v>
@@ -9111,7 +9111,7 @@
         </is>
       </c>
       <c r="B669" t="n">
-        <v>0.108516</v>
+        <v>0.108731</v>
       </c>
       <c r="C669" t="n">
         <v>0.1875</v>
@@ -9124,7 +9124,7 @@
         </is>
       </c>
       <c r="B670" t="n">
-        <v>0.110065</v>
+        <v>0.109892</v>
       </c>
       <c r="C670" t="n">
         <v>0.184783</v>
@@ -9137,7 +9137,7 @@
         </is>
       </c>
       <c r="B671" t="n">
-        <v>0.110445</v>
+        <v>0.110249</v>
       </c>
       <c r="C671" t="n">
         <v>0.182065</v>
@@ -9150,7 +9150,7 @@
         </is>
       </c>
       <c r="B672" t="n">
-        <v>0.110998</v>
+        <v>0.111221</v>
       </c>
       <c r="C672" t="n">
         <v>0.179348</v>
@@ -9163,7 +9163,7 @@
         </is>
       </c>
       <c r="B673" t="n">
-        <v>0.111408</v>
+        <v>0.111884</v>
       </c>
       <c r="C673" t="n">
         <v>0.17663</v>
@@ -9176,7 +9176,7 @@
         </is>
       </c>
       <c r="B674" t="n">
-        <v>0.112827</v>
+        <v>0.112312</v>
       </c>
       <c r="C674" t="n">
         <v>0.173913</v>
@@ -9189,7 +9189,7 @@
         </is>
       </c>
       <c r="B675" t="n">
-        <v>0.11441</v>
+        <v>0.115447</v>
       </c>
       <c r="C675" t="n">
         <v>0.171196</v>
@@ -9202,7 +9202,7 @@
         </is>
       </c>
       <c r="B676" t="n">
-        <v>0.119253</v>
+        <v>0.118503</v>
       </c>
       <c r="C676" t="n">
         <v>0.168478</v>
@@ -9215,7 +9215,7 @@
         </is>
       </c>
       <c r="B677" t="n">
-        <v>0.119685</v>
+        <v>0.120042</v>
       </c>
       <c r="C677" t="n">
         <v>0.165761</v>
@@ -9228,7 +9228,7 @@
         </is>
       </c>
       <c r="B678" t="n">
-        <v>0.120444</v>
+        <v>0.120274</v>
       </c>
       <c r="C678" t="n">
         <v>0.163043</v>
@@ -9241,7 +9241,7 @@
         </is>
       </c>
       <c r="B679" t="n">
-        <v>0.121304</v>
+        <v>0.121653</v>
       </c>
       <c r="C679" t="n">
         <v>0.160326</v>
@@ -9254,7 +9254,7 @@
         </is>
       </c>
       <c r="B680" t="n">
-        <v>0.123874</v>
+        <v>0.122844</v>
       </c>
       <c r="C680" t="n">
         <v>0.157609</v>
@@ -9267,7 +9267,7 @@
         </is>
       </c>
       <c r="B681" t="n">
-        <v>0.125588</v>
+        <v>0.124478</v>
       </c>
       <c r="C681" t="n">
         <v>0.154891</v>
@@ -9280,7 +9280,7 @@
         </is>
       </c>
       <c r="B682" t="n">
-        <v>0.125807</v>
+        <v>0.125298</v>
       </c>
       <c r="C682" t="n">
         <v>0.152174</v>
@@ -9293,7 +9293,7 @@
         </is>
       </c>
       <c r="B683" t="n">
-        <v>0.1275</v>
+        <v>0.126769</v>
       </c>
       <c r="C683" t="n">
         <v>0.149457</v>
@@ -9306,7 +9306,7 @@
         </is>
       </c>
       <c r="B684" t="n">
-        <v>0.128215</v>
+        <v>0.127751</v>
       </c>
       <c r="C684" t="n">
         <v>0.146739</v>
@@ -9319,7 +9319,7 @@
         </is>
       </c>
       <c r="B685" t="n">
-        <v>0.129437</v>
+        <v>0.129674</v>
       </c>
       <c r="C685" t="n">
         <v>0.144022</v>
@@ -9332,7 +9332,7 @@
         </is>
       </c>
       <c r="B686" t="n">
-        <v>0.129977</v>
+        <v>0.130566</v>
       </c>
       <c r="C686" t="n">
         <v>0.141304</v>
@@ -9345,7 +9345,7 @@
         </is>
       </c>
       <c r="B687" t="n">
-        <v>0.130363</v>
+        <v>0.130831</v>
       </c>
       <c r="C687" t="n">
         <v>0.138587</v>
@@ -9358,7 +9358,7 @@
         </is>
       </c>
       <c r="B688" t="n">
-        <v>0.130479</v>
+        <v>0.131416</v>
       </c>
       <c r="C688" t="n">
         <v>0.13587</v>
@@ -9371,7 +9371,7 @@
         </is>
       </c>
       <c r="B689" t="n">
-        <v>0.131886</v>
+        <v>0.132641</v>
       </c>
       <c r="C689" t="n">
         <v>0.133152</v>
@@ -9384,7 +9384,7 @@
         </is>
       </c>
       <c r="B690" t="n">
-        <v>0.131936</v>
+        <v>0.132662</v>
       </c>
       <c r="C690" t="n">
         <v>0.130435</v>
@@ -9397,7 +9397,7 @@
         </is>
       </c>
       <c r="B691" t="n">
-        <v>0.133107</v>
+        <v>0.13297</v>
       </c>
       <c r="C691" t="n">
         <v>0.127717</v>
@@ -9410,7 +9410,7 @@
         </is>
       </c>
       <c r="B692" t="n">
-        <v>0.135963</v>
+        <v>0.134626</v>
       </c>
       <c r="C692" t="n">
         <v>0.125</v>
@@ -9423,7 +9423,7 @@
         </is>
       </c>
       <c r="B693" t="n">
-        <v>0.137372</v>
+        <v>0.134864</v>
       </c>
       <c r="C693" t="n">
         <v>0.122283</v>
@@ -9436,7 +9436,7 @@
         </is>
       </c>
       <c r="B694" t="n">
-        <v>0.138164</v>
+        <v>0.136036</v>
       </c>
       <c r="C694" t="n">
         <v>0.119565</v>
@@ -9449,7 +9449,7 @@
         </is>
       </c>
       <c r="B695" t="n">
-        <v>0.138343</v>
+        <v>0.138023</v>
       </c>
       <c r="C695" t="n">
         <v>0.116848</v>
@@ -9462,7 +9462,7 @@
         </is>
       </c>
       <c r="B696" t="n">
-        <v>0.138419</v>
+        <v>0.139471</v>
       </c>
       <c r="C696" t="n">
         <v>0.11413</v>
@@ -9475,7 +9475,7 @@
         </is>
       </c>
       <c r="B697" t="n">
-        <v>0.13867</v>
+        <v>0.139928</v>
       </c>
       <c r="C697" t="n">
         <v>0.111413</v>
@@ -9488,7 +9488,7 @@
         </is>
       </c>
       <c r="B698" t="n">
-        <v>0.14116</v>
+        <v>0.141362</v>
       </c>
       <c r="C698" t="n">
         <v>0.108696</v>
@@ -9501,7 +9501,7 @@
         </is>
       </c>
       <c r="B699" t="n">
-        <v>0.1414</v>
+        <v>0.141618</v>
       </c>
       <c r="C699" t="n">
         <v>0.105978</v>
@@ -9514,7 +9514,7 @@
         </is>
       </c>
       <c r="B700" t="n">
-        <v>0.142461</v>
+        <v>0.141784</v>
       </c>
       <c r="C700" t="n">
         <v>0.103261</v>
@@ -9527,7 +9527,7 @@
         </is>
       </c>
       <c r="B701" t="n">
-        <v>0.143079</v>
+        <v>0.142535</v>
       </c>
       <c r="C701" t="n">
         <v>0.100543</v>
@@ -9540,7 +9540,7 @@
         </is>
       </c>
       <c r="B702" t="n">
-        <v>0.144764</v>
+        <v>0.143625</v>
       </c>
       <c r="C702" t="n">
         <v>0.097826</v>
@@ -9553,7 +9553,7 @@
         </is>
       </c>
       <c r="B703" t="n">
-        <v>0.145934</v>
+        <v>0.144243</v>
       </c>
       <c r="C703" t="n">
         <v>0.095109</v>
@@ -9566,7 +9566,7 @@
         </is>
       </c>
       <c r="B704" t="n">
-        <v>0.153384</v>
+        <v>0.153464</v>
       </c>
       <c r="C704" t="n">
         <v>0.092391</v>
@@ -9579,7 +9579,7 @@
         </is>
       </c>
       <c r="B705" t="n">
-        <v>0.154815</v>
+        <v>0.154536</v>
       </c>
       <c r="C705" t="n">
         <v>0.089674</v>
@@ -9592,7 +9592,7 @@
         </is>
       </c>
       <c r="B706" t="n">
-        <v>0.154891</v>
+        <v>0.155832</v>
       </c>
       <c r="C706" t="n">
         <v>0.08695700000000001</v>
@@ -9605,7 +9605,7 @@
         </is>
       </c>
       <c r="B707" t="n">
-        <v>0.159054</v>
+        <v>0.15842</v>
       </c>
       <c r="C707" t="n">
         <v>0.08423899999999999</v>
@@ -9618,7 +9618,7 @@
         </is>
       </c>
       <c r="B708" t="n">
-        <v>0.162137</v>
+        <v>0.161951</v>
       </c>
       <c r="C708" t="n">
         <v>0.081522</v>
@@ -9631,7 +9631,7 @@
         </is>
       </c>
       <c r="B709" t="n">
-        <v>0.162906</v>
+        <v>0.164151</v>
       </c>
       <c r="C709" t="n">
         <v>0.078804</v>
@@ -9644,7 +9644,7 @@
         </is>
       </c>
       <c r="B710" t="n">
-        <v>0.165839</v>
+        <v>0.16442</v>
       </c>
       <c r="C710" t="n">
         <v>0.076087</v>
@@ -9657,7 +9657,7 @@
         </is>
       </c>
       <c r="B711" t="n">
-        <v>0.169061</v>
+        <v>0.169395</v>
       </c>
       <c r="C711" t="n">
         <v>0.07337</v>
@@ -9670,7 +9670,7 @@
         </is>
       </c>
       <c r="B712" t="n">
-        <v>0.170113</v>
+        <v>0.171096</v>
       </c>
       <c r="C712" t="n">
         <v>0.07065200000000001</v>
@@ -9683,7 +9683,7 @@
         </is>
       </c>
       <c r="B713" t="n">
-        <v>0.177933</v>
+        <v>0.178615</v>
       </c>
       <c r="C713" t="n">
         <v>0.067935</v>
@@ -9696,7 +9696,7 @@
         </is>
       </c>
       <c r="B714" t="n">
-        <v>0.178189</v>
+        <v>0.179498</v>
       </c>
       <c r="C714" t="n">
         <v>0.065217</v>
@@ -9709,7 +9709,7 @@
         </is>
       </c>
       <c r="B715" t="n">
-        <v>0.179015</v>
+        <v>0.179697</v>
       </c>
       <c r="C715" t="n">
         <v>0.0625</v>
@@ -9722,7 +9722,7 @@
         </is>
       </c>
       <c r="B716" t="n">
-        <v>0.180992</v>
+        <v>0.182582</v>
       </c>
       <c r="C716" t="n">
         <v>0.059783</v>
@@ -9735,7 +9735,7 @@
         </is>
       </c>
       <c r="B717" t="n">
-        <v>0.183889</v>
+        <v>0.184452</v>
       </c>
       <c r="C717" t="n">
         <v>0.057065</v>
@@ -9748,7 +9748,7 @@
         </is>
       </c>
       <c r="B718" t="n">
-        <v>0.185548</v>
+        <v>0.185465</v>
       </c>
       <c r="C718" t="n">
         <v>0.054348</v>
@@ -9761,7 +9761,7 @@
         </is>
       </c>
       <c r="B719" t="n">
-        <v>0.186009</v>
+        <v>0.187602</v>
       </c>
       <c r="C719" t="n">
         <v>0.05163</v>
@@ -9774,7 +9774,7 @@
         </is>
       </c>
       <c r="B720" t="n">
-        <v>0.195397</v>
+        <v>0.194423</v>
       </c>
       <c r="C720" t="n">
         <v>0.048913</v>
@@ -9787,7 +9787,7 @@
         </is>
       </c>
       <c r="B721" t="n">
-        <v>0.196313</v>
+        <v>0.197149</v>
       </c>
       <c r="C721" t="n">
         <v>0.046196</v>
@@ -9800,7 +9800,7 @@
         </is>
       </c>
       <c r="B722" t="n">
-        <v>0.200034</v>
+        <v>0.197429</v>
       </c>
       <c r="C722" t="n">
         <v>0.043478</v>
@@ -9813,7 +9813,7 @@
         </is>
       </c>
       <c r="B723" t="n">
-        <v>0.208874</v>
+        <v>0.208681</v>
       </c>
       <c r="C723" t="n">
         <v>0.040761</v>
@@ -9826,7 +9826,7 @@
         </is>
       </c>
       <c r="B724" t="n">
-        <v>0.208976</v>
+        <v>0.210734</v>
       </c>
       <c r="C724" t="n">
         <v>0.038043</v>
@@ -9839,7 +9839,7 @@
         </is>
       </c>
       <c r="B725" t="n">
-        <v>0.214644</v>
+        <v>0.210786</v>
       </c>
       <c r="C725" t="n">
         <v>0.035326</v>
@@ -9852,7 +9852,7 @@
         </is>
       </c>
       <c r="B726" t="n">
-        <v>0.228307</v>
+        <v>0.228963</v>
       </c>
       <c r="C726" t="n">
         <v>0.032609</v>
@@ -9865,7 +9865,7 @@
         </is>
       </c>
       <c r="B727" t="n">
-        <v>0.232818</v>
+        <v>0.23467</v>
       </c>
       <c r="C727" t="n">
         <v>0.029891</v>
@@ -9878,7 +9878,7 @@
         </is>
       </c>
       <c r="B728" t="n">
-        <v>0.241414</v>
+        <v>0.243604</v>
       </c>
       <c r="C728" t="n">
         <v>0.027174</v>
@@ -9891,7 +9891,7 @@
         </is>
       </c>
       <c r="B729" t="n">
-        <v>0.241966</v>
+        <v>0.24397</v>
       </c>
       <c r="C729" t="n">
         <v>0.024457</v>
@@ -9904,7 +9904,7 @@
         </is>
       </c>
       <c r="B730" t="n">
-        <v>0.244353</v>
+        <v>0.246569</v>
       </c>
       <c r="C730" t="n">
         <v>0.021739</v>
@@ -9917,7 +9917,7 @@
         </is>
       </c>
       <c r="B731" t="n">
-        <v>0.260987</v>
+        <v>0.257932</v>
       </c>
       <c r="C731" t="n">
         <v>0.019022</v>
@@ -9930,7 +9930,7 @@
         </is>
       </c>
       <c r="B732" t="n">
-        <v>0.262818</v>
+        <v>0.264682</v>
       </c>
       <c r="C732" t="n">
         <v>0.016304</v>
@@ -9943,7 +9943,7 @@
         </is>
       </c>
       <c r="B733" t="n">
-        <v>0.271117</v>
+        <v>0.272675</v>
       </c>
       <c r="C733" t="n">
         <v>0.013587</v>
@@ -9956,7 +9956,7 @@
         </is>
       </c>
       <c r="B734" t="n">
-        <v>0.295407</v>
+        <v>0.295159</v>
       </c>
       <c r="C734" t="n">
         <v>0.01087</v>
@@ -9969,7 +9969,7 @@
         </is>
       </c>
       <c r="B735" t="n">
-        <v>0.30904</v>
+        <v>0.311792</v>
       </c>
       <c r="C735" t="n">
         <v>0.008152</v>
@@ -9982,7 +9982,7 @@
         </is>
       </c>
       <c r="B736" t="n">
-        <v>0.33963</v>
+        <v>0.34116</v>
       </c>
       <c r="C736" t="n">
         <v>0.005435</v>
@@ -9995,7 +9995,7 @@
         </is>
       </c>
       <c r="B737" t="n">
-        <v>0.483999</v>
+        <v>0.487269</v>
       </c>
       <c r="C737" t="n">
         <v>0.002717</v>

--- a/vignettes/vignette-1/tail_exceedance_plot_data.xlsx
+++ b/vignettes/vignette-1/tail_exceedance_plot_data.xlsx
@@ -778,7 +778,7 @@
         </is>
       </c>
       <c r="B28" t="n">
-        <v>0.008377000000000001</v>
+        <v>0.008333999999999999</v>
       </c>
       <c r="C28" t="n">
         <v>0.929348</v>
@@ -791,7 +791,7 @@
         </is>
       </c>
       <c r="B29" t="n">
-        <v>0.008593999999999999</v>
+        <v>0.008377000000000001</v>
       </c>
       <c r="C29" t="n">
         <v>0.92663</v>
@@ -804,7 +804,7 @@
         </is>
       </c>
       <c r="B30" t="n">
-        <v>0.009165</v>
+        <v>0.008593999999999999</v>
       </c>
       <c r="C30" t="n">
         <v>0.923913</v>
@@ -817,7 +817,7 @@
         </is>
       </c>
       <c r="B31" t="n">
-        <v>0.009428000000000001</v>
+        <v>0.009165</v>
       </c>
       <c r="C31" t="n">
         <v>0.921196</v>
@@ -830,7 +830,7 @@
         </is>
       </c>
       <c r="B32" t="n">
-        <v>0.009578</v>
+        <v>0.009428000000000001</v>
       </c>
       <c r="C32" t="n">
         <v>0.918478</v>
@@ -843,7 +843,7 @@
         </is>
       </c>
       <c r="B33" t="n">
-        <v>0.009774</v>
+        <v>0.009578</v>
       </c>
       <c r="C33" t="n">
         <v>0.915761</v>
@@ -856,7 +856,7 @@
         </is>
       </c>
       <c r="B34" t="n">
-        <v>0.009811</v>
+        <v>0.009774</v>
       </c>
       <c r="C34" t="n">
         <v>0.913043</v>
@@ -869,7 +869,7 @@
         </is>
       </c>
       <c r="B35" t="n">
-        <v>0.010226</v>
+        <v>0.009811</v>
       </c>
       <c r="C35" t="n">
         <v>0.910326</v>
@@ -882,7 +882,7 @@
         </is>
       </c>
       <c r="B36" t="n">
-        <v>0.010518</v>
+        <v>0.010226</v>
       </c>
       <c r="C36" t="n">
         <v>0.907609</v>
@@ -895,7 +895,7 @@
         </is>
       </c>
       <c r="B37" t="n">
-        <v>0.010943</v>
+        <v>0.010518</v>
       </c>
       <c r="C37" t="n">
         <v>0.904891</v>
@@ -908,7 +908,7 @@
         </is>
       </c>
       <c r="B38" t="n">
-        <v>0.011156</v>
+        <v>0.010943</v>
       </c>
       <c r="C38" t="n">
         <v>0.902174</v>
@@ -921,7 +921,7 @@
         </is>
       </c>
       <c r="B39" t="n">
-        <v>0.011326</v>
+        <v>0.011156</v>
       </c>
       <c r="C39" t="n">
         <v>0.899457</v>
@@ -934,7 +934,7 @@
         </is>
       </c>
       <c r="B40" t="n">
-        <v>0.01145</v>
+        <v>0.011326</v>
       </c>
       <c r="C40" t="n">
         <v>0.896739</v>
@@ -947,7 +947,7 @@
         </is>
       </c>
       <c r="B41" t="n">
-        <v>0.012035</v>
+        <v>0.01145</v>
       </c>
       <c r="C41" t="n">
         <v>0.894022</v>
@@ -960,7 +960,7 @@
         </is>
       </c>
       <c r="B42" t="n">
-        <v>0.012747</v>
+        <v>0.012035</v>
       </c>
       <c r="C42" t="n">
         <v>0.891304</v>
@@ -973,7 +973,7 @@
         </is>
       </c>
       <c r="B43" t="n">
-        <v>0.012918</v>
+        <v>0.012747</v>
       </c>
       <c r="C43" t="n">
         <v>0.888587</v>
@@ -986,7 +986,7 @@
         </is>
       </c>
       <c r="B44" t="n">
-        <v>0.013202</v>
+        <v>0.012918</v>
       </c>
       <c r="C44" t="n">
         <v>0.88587</v>
@@ -999,7 +999,7 @@
         </is>
       </c>
       <c r="B45" t="n">
-        <v>0.013714</v>
+        <v>0.013202</v>
       </c>
       <c r="C45" t="n">
         <v>0.883152</v>
@@ -1012,7 +1012,7 @@
         </is>
       </c>
       <c r="B46" t="n">
-        <v>0.01393</v>
+        <v>0.013714</v>
       </c>
       <c r="C46" t="n">
         <v>0.880435</v>
@@ -1025,7 +1025,7 @@
         </is>
       </c>
       <c r="B47" t="n">
-        <v>0.013971</v>
+        <v>0.01393</v>
       </c>
       <c r="C47" t="n">
         <v>0.877717</v>
@@ -1038,7 +1038,7 @@
         </is>
       </c>
       <c r="B48" t="n">
-        <v>0.014018</v>
+        <v>0.013971</v>
       </c>
       <c r="C48" t="n">
         <v>0.875</v>
@@ -1051,7 +1051,7 @@
         </is>
       </c>
       <c r="B49" t="n">
-        <v>0.01417</v>
+        <v>0.014018</v>
       </c>
       <c r="C49" t="n">
         <v>0.872283</v>
@@ -1064,7 +1064,7 @@
         </is>
       </c>
       <c r="B50" t="n">
-        <v>0.014481</v>
+        <v>0.01417</v>
       </c>
       <c r="C50" t="n">
         <v>0.869565</v>
@@ -1077,7 +1077,7 @@
         </is>
       </c>
       <c r="B51" t="n">
-        <v>0.014731</v>
+        <v>0.014481</v>
       </c>
       <c r="C51" t="n">
         <v>0.866848</v>
@@ -1090,7 +1090,7 @@
         </is>
       </c>
       <c r="B52" t="n">
-        <v>0.014841</v>
+        <v>0.014731</v>
       </c>
       <c r="C52" t="n">
         <v>0.86413</v>
@@ -1103,7 +1103,7 @@
         </is>
       </c>
       <c r="B53" t="n">
-        <v>0.01486</v>
+        <v>0.014841</v>
       </c>
       <c r="C53" t="n">
         <v>0.861413</v>
@@ -1116,7 +1116,7 @@
         </is>
       </c>
       <c r="B54" t="n">
-        <v>0.015041</v>
+        <v>0.01486</v>
       </c>
       <c r="C54" t="n">
         <v>0.858696</v>
@@ -1129,7 +1129,7 @@
         </is>
       </c>
       <c r="B55" t="n">
-        <v>0.015107</v>
+        <v>0.015041</v>
       </c>
       <c r="C55" t="n">
         <v>0.855978</v>
@@ -1155,7 +1155,7 @@
         </is>
       </c>
       <c r="B57" t="n">
-        <v>0.015553</v>
+        <v>0.015107</v>
       </c>
       <c r="C57" t="n">
         <v>0.850543</v>
@@ -1168,7 +1168,7 @@
         </is>
       </c>
       <c r="B58" t="n">
-        <v>0.016031</v>
+        <v>0.015553</v>
       </c>
       <c r="C58" t="n">
         <v>0.847826</v>
@@ -1181,7 +1181,7 @@
         </is>
       </c>
       <c r="B59" t="n">
-        <v>0.016343</v>
+        <v>0.016031</v>
       </c>
       <c r="C59" t="n">
         <v>0.845109</v>
@@ -1194,7 +1194,7 @@
         </is>
       </c>
       <c r="B60" t="n">
-        <v>0.016545</v>
+        <v>0.016343</v>
       </c>
       <c r="C60" t="n">
         <v>0.842391</v>
@@ -1207,7 +1207,7 @@
         </is>
       </c>
       <c r="B61" t="n">
-        <v>0.017135</v>
+        <v>0.016545</v>
       </c>
       <c r="C61" t="n">
         <v>0.839674</v>
@@ -1220,7 +1220,7 @@
         </is>
       </c>
       <c r="B62" t="n">
-        <v>0.017276</v>
+        <v>0.017135</v>
       </c>
       <c r="C62" t="n">
         <v>0.836957</v>
@@ -1233,7 +1233,7 @@
         </is>
       </c>
       <c r="B63" t="n">
-        <v>0.017621</v>
+        <v>0.017276</v>
       </c>
       <c r="C63" t="n">
         <v>0.834239</v>
@@ -1246,7 +1246,7 @@
         </is>
       </c>
       <c r="B64" t="n">
-        <v>0.017975</v>
+        <v>0.017621</v>
       </c>
       <c r="C64" t="n">
         <v>0.831522</v>
@@ -1259,7 +1259,7 @@
         </is>
       </c>
       <c r="B65" t="n">
-        <v>0.018505</v>
+        <v>0.017975</v>
       </c>
       <c r="C65" t="n">
         <v>0.828804</v>
@@ -1272,7 +1272,7 @@
         </is>
       </c>
       <c r="B66" t="n">
-        <v>0.018757</v>
+        <v>0.018505</v>
       </c>
       <c r="C66" t="n">
         <v>0.826087</v>
@@ -1285,7 +1285,7 @@
         </is>
       </c>
       <c r="B67" t="n">
-        <v>0.018801</v>
+        <v>0.018757</v>
       </c>
       <c r="C67" t="n">
         <v>0.82337</v>
@@ -1298,7 +1298,7 @@
         </is>
       </c>
       <c r="B68" t="n">
-        <v>0.018847</v>
+        <v>0.018801</v>
       </c>
       <c r="C68" t="n">
         <v>0.820652</v>
@@ -1311,7 +1311,7 @@
         </is>
       </c>
       <c r="B69" t="n">
-        <v>0.018931</v>
+        <v>0.018847</v>
       </c>
       <c r="C69" t="n">
         <v>0.817935</v>
@@ -1324,7 +1324,7 @@
         </is>
       </c>
       <c r="B70" t="n">
-        <v>0.019288</v>
+        <v>0.018931</v>
       </c>
       <c r="C70" t="n">
         <v>0.815217</v>
@@ -1337,7 +1337,7 @@
         </is>
       </c>
       <c r="B71" t="n">
-        <v>0.019352</v>
+        <v>0.019288</v>
       </c>
       <c r="C71" t="n">
         <v>0.8125</v>
@@ -1350,7 +1350,7 @@
         </is>
       </c>
       <c r="B72" t="n">
-        <v>0.01962</v>
+        <v>0.019352</v>
       </c>
       <c r="C72" t="n">
         <v>0.809783</v>
@@ -1363,7 +1363,7 @@
         </is>
       </c>
       <c r="B73" t="n">
-        <v>0.019953</v>
+        <v>0.01962</v>
       </c>
       <c r="C73" t="n">
         <v>0.807065</v>
@@ -1376,7 +1376,7 @@
         </is>
       </c>
       <c r="B74" t="n">
-        <v>0.020186</v>
+        <v>0.019953</v>
       </c>
       <c r="C74" t="n">
         <v>0.804348</v>
@@ -1389,7 +1389,7 @@
         </is>
       </c>
       <c r="B75" t="n">
-        <v>0.020393</v>
+        <v>0.020186</v>
       </c>
       <c r="C75" t="n">
         <v>0.80163</v>
@@ -1402,7 +1402,7 @@
         </is>
       </c>
       <c r="B76" t="n">
-        <v>0.02048</v>
+        <v>0.020393</v>
       </c>
       <c r="C76" t="n">
         <v>0.798913</v>
@@ -1415,7 +1415,7 @@
         </is>
       </c>
       <c r="B77" t="n">
-        <v>0.021572</v>
+        <v>0.02048</v>
       </c>
       <c r="C77" t="n">
         <v>0.796196</v>
@@ -1428,7 +1428,7 @@
         </is>
       </c>
       <c r="B78" t="n">
-        <v>0.021604</v>
+        <v>0.021572</v>
       </c>
       <c r="C78" t="n">
         <v>0.793478</v>
@@ -1441,7 +1441,7 @@
         </is>
       </c>
       <c r="B79" t="n">
-        <v>0.021912</v>
+        <v>0.021604</v>
       </c>
       <c r="C79" t="n">
         <v>0.790761</v>
@@ -1454,7 +1454,7 @@
         </is>
       </c>
       <c r="B80" t="n">
-        <v>0.021918</v>
+        <v>0.021912</v>
       </c>
       <c r="C80" t="n">
         <v>0.788043</v>
@@ -1467,7 +1467,7 @@
         </is>
       </c>
       <c r="B81" t="n">
-        <v>0.021962</v>
+        <v>0.021918</v>
       </c>
       <c r="C81" t="n">
         <v>0.785326</v>
@@ -1480,7 +1480,7 @@
         </is>
       </c>
       <c r="B82" t="n">
-        <v>0.022008</v>
+        <v>0.021962</v>
       </c>
       <c r="C82" t="n">
         <v>0.782609</v>
@@ -1493,7 +1493,7 @@
         </is>
       </c>
       <c r="B83" t="n">
-        <v>0.022011</v>
+        <v>0.022008</v>
       </c>
       <c r="C83" t="n">
         <v>0.779891</v>
@@ -1506,7 +1506,7 @@
         </is>
       </c>
       <c r="B84" t="n">
-        <v>0.022121</v>
+        <v>0.022011</v>
       </c>
       <c r="C84" t="n">
         <v>0.777174</v>
@@ -1519,7 +1519,7 @@
         </is>
       </c>
       <c r="B85" t="n">
-        <v>0.022299</v>
+        <v>0.022121</v>
       </c>
       <c r="C85" t="n">
         <v>0.774457</v>
@@ -1532,7 +1532,7 @@
         </is>
       </c>
       <c r="B86" t="n">
-        <v>0.022324</v>
+        <v>0.022299</v>
       </c>
       <c r="C86" t="n">
         <v>0.771739</v>
@@ -1545,7 +1545,7 @@
         </is>
       </c>
       <c r="B87" t="n">
-        <v>0.022543</v>
+        <v>0.022324</v>
       </c>
       <c r="C87" t="n">
         <v>0.769022</v>
@@ -1558,7 +1558,7 @@
         </is>
       </c>
       <c r="B88" t="n">
-        <v>0.022891</v>
+        <v>0.022543</v>
       </c>
       <c r="C88" t="n">
         <v>0.766304</v>
@@ -1571,7 +1571,7 @@
         </is>
       </c>
       <c r="B89" t="n">
-        <v>0.023483</v>
+        <v>0.022891</v>
       </c>
       <c r="C89" t="n">
         <v>0.763587</v>
@@ -1584,7 +1584,7 @@
         </is>
       </c>
       <c r="B90" t="n">
-        <v>0.023843</v>
+        <v>0.023483</v>
       </c>
       <c r="C90" t="n">
         <v>0.76087</v>
@@ -1597,7 +1597,7 @@
         </is>
       </c>
       <c r="B91" t="n">
-        <v>0.023991</v>
+        <v>0.023843</v>
       </c>
       <c r="C91" t="n">
         <v>0.758152</v>
@@ -1610,7 +1610,7 @@
         </is>
       </c>
       <c r="B92" t="n">
-        <v>0.02408</v>
+        <v>0.023991</v>
       </c>
       <c r="C92" t="n">
         <v>0.755435</v>
@@ -1623,7 +1623,7 @@
         </is>
       </c>
       <c r="B93" t="n">
-        <v>0.024413</v>
+        <v>0.02408</v>
       </c>
       <c r="C93" t="n">
         <v>0.752717</v>
@@ -1636,7 +1636,7 @@
         </is>
       </c>
       <c r="B94" t="n">
-        <v>0.024896</v>
+        <v>0.024413</v>
       </c>
       <c r="C94" t="n">
         <v>0.75</v>
@@ -1649,7 +1649,7 @@
         </is>
       </c>
       <c r="B95" t="n">
-        <v>0.025327</v>
+        <v>0.024896</v>
       </c>
       <c r="C95" t="n">
         <v>0.747283</v>
@@ -1662,7 +1662,7 @@
         </is>
       </c>
       <c r="B96" t="n">
-        <v>0.025416</v>
+        <v>0.025327</v>
       </c>
       <c r="C96" t="n">
         <v>0.744565</v>
@@ -1675,7 +1675,7 @@
         </is>
       </c>
       <c r="B97" t="n">
-        <v>0.025544</v>
+        <v>0.025416</v>
       </c>
       <c r="C97" t="n">
         <v>0.741848</v>
@@ -1688,7 +1688,7 @@
         </is>
       </c>
       <c r="B98" t="n">
-        <v>0.025755</v>
+        <v>0.025544</v>
       </c>
       <c r="C98" t="n">
         <v>0.73913</v>
@@ -1701,7 +1701,7 @@
         </is>
       </c>
       <c r="B99" t="n">
-        <v>0.026545</v>
+        <v>0.025755</v>
       </c>
       <c r="C99" t="n">
         <v>0.736413</v>
@@ -1714,7 +1714,7 @@
         </is>
       </c>
       <c r="B100" t="n">
-        <v>0.027214</v>
+        <v>0.026545</v>
       </c>
       <c r="C100" t="n">
         <v>0.733696</v>
@@ -1727,7 +1727,7 @@
         </is>
       </c>
       <c r="B101" t="n">
-        <v>0.027321</v>
+        <v>0.027214</v>
       </c>
       <c r="C101" t="n">
         <v>0.730978</v>
@@ -1740,7 +1740,7 @@
         </is>
       </c>
       <c r="B102" t="n">
-        <v>0.027355</v>
+        <v>0.027321</v>
       </c>
       <c r="C102" t="n">
         <v>0.728261</v>
@@ -1753,7 +1753,7 @@
         </is>
       </c>
       <c r="B103" t="n">
-        <v>0.028098</v>
+        <v>0.027355</v>
       </c>
       <c r="C103" t="n">
         <v>0.725543</v>
@@ -1766,7 +1766,7 @@
         </is>
       </c>
       <c r="B104" t="n">
-        <v>0.028186</v>
+        <v>0.028098</v>
       </c>
       <c r="C104" t="n">
         <v>0.722826</v>
@@ -1779,7 +1779,7 @@
         </is>
       </c>
       <c r="B105" t="n">
-        <v>0.028375</v>
+        <v>0.028186</v>
       </c>
       <c r="C105" t="n">
         <v>0.720109</v>
@@ -1792,7 +1792,7 @@
         </is>
       </c>
       <c r="B106" t="n">
-        <v>0.029046</v>
+        <v>0.028375</v>
       </c>
       <c r="C106" t="n">
         <v>0.717391</v>
@@ -1805,7 +1805,7 @@
         </is>
       </c>
       <c r="B107" t="n">
-        <v>0.029071</v>
+        <v>0.029046</v>
       </c>
       <c r="C107" t="n">
         <v>0.714674</v>
@@ -1818,7 +1818,7 @@
         </is>
       </c>
       <c r="B108" t="n">
-        <v>0.029588</v>
+        <v>0.029071</v>
       </c>
       <c r="C108" t="n">
         <v>0.711957</v>
@@ -1831,7 +1831,7 @@
         </is>
       </c>
       <c r="B109" t="n">
-        <v>0.029854</v>
+        <v>0.029588</v>
       </c>
       <c r="C109" t="n">
         <v>0.709239</v>
@@ -1844,7 +1844,7 @@
         </is>
       </c>
       <c r="B110" t="n">
-        <v>0.030158</v>
+        <v>0.029854</v>
       </c>
       <c r="C110" t="n">
         <v>0.706522</v>
@@ -1857,7 +1857,7 @@
         </is>
       </c>
       <c r="B111" t="n">
-        <v>0.030201</v>
+        <v>0.030158</v>
       </c>
       <c r="C111" t="n">
         <v>0.703804</v>
@@ -1870,7 +1870,7 @@
         </is>
       </c>
       <c r="B112" t="n">
-        <v>0.03027</v>
+        <v>0.030201</v>
       </c>
       <c r="C112" t="n">
         <v>0.701087</v>
@@ -1883,7 +1883,7 @@
         </is>
       </c>
       <c r="B113" t="n">
-        <v>0.030697</v>
+        <v>0.03027</v>
       </c>
       <c r="C113" t="n">
         <v>0.69837</v>
@@ -1896,7 +1896,7 @@
         </is>
       </c>
       <c r="B114" t="n">
-        <v>0.030903</v>
+        <v>0.030697</v>
       </c>
       <c r="C114" t="n">
         <v>0.695652</v>
@@ -1909,7 +1909,7 @@
         </is>
       </c>
       <c r="B115" t="n">
-        <v>0.031116</v>
+        <v>0.030903</v>
       </c>
       <c r="C115" t="n">
         <v>0.692935</v>
@@ -1922,7 +1922,7 @@
         </is>
       </c>
       <c r="B116" t="n">
-        <v>0.031127</v>
+        <v>0.031116</v>
       </c>
       <c r="C116" t="n">
         <v>0.690217</v>
@@ -1935,7 +1935,7 @@
         </is>
       </c>
       <c r="B117" t="n">
-        <v>0.031327</v>
+        <v>0.031127</v>
       </c>
       <c r="C117" t="n">
         <v>0.6875</v>
@@ -1948,7 +1948,7 @@
         </is>
       </c>
       <c r="B118" t="n">
-        <v>0.031556</v>
+        <v>0.031327</v>
       </c>
       <c r="C118" t="n">
         <v>0.684783</v>
@@ -1961,7 +1961,7 @@
         </is>
       </c>
       <c r="B119" t="n">
-        <v>0.031969</v>
+        <v>0.031556</v>
       </c>
       <c r="C119" t="n">
         <v>0.682065</v>
@@ -1974,7 +1974,7 @@
         </is>
       </c>
       <c r="B120" t="n">
-        <v>0.032545</v>
+        <v>0.031969</v>
       </c>
       <c r="C120" t="n">
         <v>0.679348</v>
@@ -1987,7 +1987,7 @@
         </is>
       </c>
       <c r="B121" t="n">
-        <v>0.032827</v>
+        <v>0.032545</v>
       </c>
       <c r="C121" t="n">
         <v>0.67663</v>
@@ -2000,7 +2000,7 @@
         </is>
       </c>
       <c r="B122" t="n">
-        <v>0.033481</v>
+        <v>0.032827</v>
       </c>
       <c r="C122" t="n">
         <v>0.673913</v>
@@ -2013,7 +2013,7 @@
         </is>
       </c>
       <c r="B123" t="n">
-        <v>0.033774</v>
+        <v>0.033481</v>
       </c>
       <c r="C123" t="n">
         <v>0.671196</v>
@@ -2026,7 +2026,7 @@
         </is>
       </c>
       <c r="B124" t="n">
-        <v>0.033884</v>
+        <v>0.033774</v>
       </c>
       <c r="C124" t="n">
         <v>0.668478</v>
@@ -2039,7 +2039,7 @@
         </is>
       </c>
       <c r="B125" t="n">
-        <v>0.034047</v>
+        <v>0.033884</v>
       </c>
       <c r="C125" t="n">
         <v>0.665761</v>
@@ -2052,7 +2052,7 @@
         </is>
       </c>
       <c r="B126" t="n">
-        <v>0.034274</v>
+        <v>0.034047</v>
       </c>
       <c r="C126" t="n">
         <v>0.663043</v>
@@ -2065,7 +2065,7 @@
         </is>
       </c>
       <c r="B127" t="n">
-        <v>0.034573</v>
+        <v>0.034274</v>
       </c>
       <c r="C127" t="n">
         <v>0.660326</v>
@@ -2078,7 +2078,7 @@
         </is>
       </c>
       <c r="B128" t="n">
-        <v>0.035039</v>
+        <v>0.034573</v>
       </c>
       <c r="C128" t="n">
         <v>0.657609</v>
@@ -2091,7 +2091,7 @@
         </is>
       </c>
       <c r="B129" t="n">
-        <v>0.035117</v>
+        <v>0.035039</v>
       </c>
       <c r="C129" t="n">
         <v>0.654891</v>
@@ -2104,7 +2104,7 @@
         </is>
       </c>
       <c r="B130" t="n">
-        <v>0.035159</v>
+        <v>0.035117</v>
       </c>
       <c r="C130" t="n">
         <v>0.652174</v>
@@ -2117,7 +2117,7 @@
         </is>
       </c>
       <c r="B131" t="n">
-        <v>0.035374</v>
+        <v>0.035159</v>
       </c>
       <c r="C131" t="n">
         <v>0.649457</v>
@@ -2130,7 +2130,7 @@
         </is>
       </c>
       <c r="B132" t="n">
-        <v>0.035654</v>
+        <v>0.035374</v>
       </c>
       <c r="C132" t="n">
         <v>0.646739</v>
@@ -2143,7 +2143,7 @@
         </is>
       </c>
       <c r="B133" t="n">
-        <v>0.036</v>
+        <v>0.035654</v>
       </c>
       <c r="C133" t="n">
         <v>0.644022</v>
@@ -2156,7 +2156,7 @@
         </is>
       </c>
       <c r="B134" t="n">
-        <v>0.036242</v>
+        <v>0.036</v>
       </c>
       <c r="C134" t="n">
         <v>0.641304</v>
@@ -2169,7 +2169,7 @@
         </is>
       </c>
       <c r="B135" t="n">
-        <v>0.037307</v>
+        <v>0.036242</v>
       </c>
       <c r="C135" t="n">
         <v>0.638587</v>
@@ -2182,7 +2182,7 @@
         </is>
       </c>
       <c r="B136" t="n">
-        <v>0.037805</v>
+        <v>0.037156</v>
       </c>
       <c r="C136" t="n">
         <v>0.63587</v>
@@ -2195,7 +2195,7 @@
         </is>
       </c>
       <c r="B137" t="n">
-        <v>0.03815</v>
+        <v>0.037307</v>
       </c>
       <c r="C137" t="n">
         <v>0.633152</v>
@@ -2208,7 +2208,7 @@
         </is>
       </c>
       <c r="B138" t="n">
-        <v>0.038316</v>
+        <v>0.037805</v>
       </c>
       <c r="C138" t="n">
         <v>0.630435</v>
@@ -2221,7 +2221,7 @@
         </is>
       </c>
       <c r="B139" t="n">
-        <v>0.03876</v>
+        <v>0.038316</v>
       </c>
       <c r="C139" t="n">
         <v>0.627717</v>
@@ -2234,7 +2234,7 @@
         </is>
       </c>
       <c r="B140" t="n">
-        <v>0.039595</v>
+        <v>0.03876</v>
       </c>
       <c r="C140" t="n">
         <v>0.625</v>
@@ -2247,7 +2247,7 @@
         </is>
       </c>
       <c r="B141" t="n">
-        <v>0.03982</v>
+        <v>0.039595</v>
       </c>
       <c r="C141" t="n">
         <v>0.622283</v>
@@ -2260,7 +2260,7 @@
         </is>
       </c>
       <c r="B142" t="n">
-        <v>0.040867</v>
+        <v>0.03982</v>
       </c>
       <c r="C142" t="n">
         <v>0.619565</v>
@@ -2273,7 +2273,7 @@
         </is>
       </c>
       <c r="B143" t="n">
-        <v>0.040915</v>
+        <v>0.040867</v>
       </c>
       <c r="C143" t="n">
         <v>0.616848</v>
@@ -2286,7 +2286,7 @@
         </is>
       </c>
       <c r="B144" t="n">
-        <v>0.040931</v>
+        <v>0.040915</v>
       </c>
       <c r="C144" t="n">
         <v>0.61413</v>
@@ -2299,7 +2299,7 @@
         </is>
       </c>
       <c r="B145" t="n">
-        <v>0.040948</v>
+        <v>0.040931</v>
       </c>
       <c r="C145" t="n">
         <v>0.611413</v>
@@ -2312,7 +2312,7 @@
         </is>
       </c>
       <c r="B146" t="n">
-        <v>0.041019</v>
+        <v>0.040948</v>
       </c>
       <c r="C146" t="n">
         <v>0.608696</v>
@@ -2325,7 +2325,7 @@
         </is>
       </c>
       <c r="B147" t="n">
-        <v>0.041132</v>
+        <v>0.041019</v>
       </c>
       <c r="C147" t="n">
         <v>0.605978</v>
@@ -2338,7 +2338,7 @@
         </is>
       </c>
       <c r="B148" t="n">
-        <v>0.041331</v>
+        <v>0.041132</v>
       </c>
       <c r="C148" t="n">
         <v>0.603261</v>
@@ -2351,7 +2351,7 @@
         </is>
       </c>
       <c r="B149" t="n">
-        <v>0.041359</v>
+        <v>0.041331</v>
       </c>
       <c r="C149" t="n">
         <v>0.600543</v>
@@ -2793,7 +2793,7 @@
         </is>
       </c>
       <c r="B183" t="n">
-        <v>0.054595</v>
+        <v>0.05496</v>
       </c>
       <c r="C183" t="n">
         <v>0.508152</v>
@@ -2806,7 +2806,7 @@
         </is>
       </c>
       <c r="B184" t="n">
-        <v>0.05496</v>
+        <v>0.0555</v>
       </c>
       <c r="C184" t="n">
         <v>0.505435</v>
@@ -2819,7 +2819,7 @@
         </is>
       </c>
       <c r="B185" t="n">
-        <v>0.0555</v>
+        <v>0.055621</v>
       </c>
       <c r="C185" t="n">
         <v>0.502717</v>
@@ -2832,7 +2832,7 @@
         </is>
       </c>
       <c r="B186" t="n">
-        <v>0.055621</v>
+        <v>0.055736</v>
       </c>
       <c r="C186" t="n">
         <v>0.5</v>
@@ -2845,7 +2845,7 @@
         </is>
       </c>
       <c r="B187" t="n">
-        <v>0.055736</v>
+        <v>0.056242</v>
       </c>
       <c r="C187" t="n">
         <v>0.497283</v>
@@ -2858,7 +2858,7 @@
         </is>
       </c>
       <c r="B188" t="n">
-        <v>0.056242</v>
+        <v>0.056433</v>
       </c>
       <c r="C188" t="n">
         <v>0.494565</v>
@@ -2871,7 +2871,7 @@
         </is>
       </c>
       <c r="B189" t="n">
-        <v>0.056433</v>
+        <v>0.056487</v>
       </c>
       <c r="C189" t="n">
         <v>0.491848</v>
@@ -2884,7 +2884,7 @@
         </is>
       </c>
       <c r="B190" t="n">
-        <v>0.056487</v>
+        <v>0.056702</v>
       </c>
       <c r="C190" t="n">
         <v>0.48913</v>
@@ -2897,7 +2897,7 @@
         </is>
       </c>
       <c r="B191" t="n">
-        <v>0.056702</v>
+        <v>0.056785</v>
       </c>
       <c r="C191" t="n">
         <v>0.486413</v>
@@ -2910,7 +2910,7 @@
         </is>
       </c>
       <c r="B192" t="n">
-        <v>0.056785</v>
+        <v>0.05854</v>
       </c>
       <c r="C192" t="n">
         <v>0.483696</v>
@@ -2923,7 +2923,7 @@
         </is>
       </c>
       <c r="B193" t="n">
-        <v>0.05854</v>
+        <v>0.058745</v>
       </c>
       <c r="C193" t="n">
         <v>0.480978</v>
@@ -2936,7 +2936,7 @@
         </is>
       </c>
       <c r="B194" t="n">
-        <v>0.058745</v>
+        <v>0.058836</v>
       </c>
       <c r="C194" t="n">
         <v>0.478261</v>
@@ -2949,7 +2949,7 @@
         </is>
       </c>
       <c r="B195" t="n">
-        <v>0.058836</v>
+        <v>0.059279</v>
       </c>
       <c r="C195" t="n">
         <v>0.475543</v>
@@ -2962,7 +2962,7 @@
         </is>
       </c>
       <c r="B196" t="n">
-        <v>0.059279</v>
+        <v>0.059367</v>
       </c>
       <c r="C196" t="n">
         <v>0.472826</v>
@@ -2975,7 +2975,7 @@
         </is>
       </c>
       <c r="B197" t="n">
-        <v>0.059367</v>
+        <v>0.059553</v>
       </c>
       <c r="C197" t="n">
         <v>0.470109</v>
@@ -2988,7 +2988,7 @@
         </is>
       </c>
       <c r="B198" t="n">
-        <v>0.059553</v>
+        <v>0.059579</v>
       </c>
       <c r="C198" t="n">
         <v>0.467391</v>
@@ -3001,7 +3001,7 @@
         </is>
       </c>
       <c r="B199" t="n">
-        <v>0.059579</v>
+        <v>0.060111</v>
       </c>
       <c r="C199" t="n">
         <v>0.464674</v>
@@ -3014,7 +3014,7 @@
         </is>
       </c>
       <c r="B200" t="n">
-        <v>0.060111</v>
+        <v>0.060827</v>
       </c>
       <c r="C200" t="n">
         <v>0.461957</v>
@@ -3027,7 +3027,7 @@
         </is>
       </c>
       <c r="B201" t="n">
-        <v>0.060827</v>
+        <v>0.060882</v>
       </c>
       <c r="C201" t="n">
         <v>0.459239</v>
@@ -3040,7 +3040,7 @@
         </is>
       </c>
       <c r="B202" t="n">
-        <v>0.060882</v>
+        <v>0.061437</v>
       </c>
       <c r="C202" t="n">
         <v>0.456522</v>
@@ -3053,7 +3053,7 @@
         </is>
       </c>
       <c r="B203" t="n">
-        <v>0.061437</v>
+        <v>0.061712</v>
       </c>
       <c r="C203" t="n">
         <v>0.453804</v>
@@ -3066,7 +3066,7 @@
         </is>
       </c>
       <c r="B204" t="n">
-        <v>0.061712</v>
+        <v>0.061784</v>
       </c>
       <c r="C204" t="n">
         <v>0.451087</v>
@@ -3079,7 +3079,7 @@
         </is>
       </c>
       <c r="B205" t="n">
-        <v>0.061784</v>
+        <v>0.06179</v>
       </c>
       <c r="C205" t="n">
         <v>0.44837</v>
@@ -3092,7 +3092,7 @@
         </is>
       </c>
       <c r="B206" t="n">
-        <v>0.06179</v>
+        <v>0.061969</v>
       </c>
       <c r="C206" t="n">
         <v>0.445652</v>
@@ -3105,7 +3105,7 @@
         </is>
       </c>
       <c r="B207" t="n">
-        <v>0.061969</v>
+        <v>0.062129</v>
       </c>
       <c r="C207" t="n">
         <v>0.442935</v>
@@ -3118,7 +3118,7 @@
         </is>
       </c>
       <c r="B208" t="n">
-        <v>0.062129</v>
+        <v>0.062168</v>
       </c>
       <c r="C208" t="n">
         <v>0.440217</v>
@@ -3131,7 +3131,7 @@
         </is>
       </c>
       <c r="B209" t="n">
-        <v>0.062168</v>
+        <v>0.062246</v>
       </c>
       <c r="C209" t="n">
         <v>0.4375</v>
@@ -3144,7 +3144,7 @@
         </is>
       </c>
       <c r="B210" t="n">
-        <v>0.062246</v>
+        <v>0.06263299999999999</v>
       </c>
       <c r="C210" t="n">
         <v>0.434783</v>
@@ -3157,7 +3157,7 @@
         </is>
       </c>
       <c r="B211" t="n">
-        <v>0.06263299999999999</v>
+        <v>0.062844</v>
       </c>
       <c r="C211" t="n">
         <v>0.432065</v>
@@ -3170,7 +3170,7 @@
         </is>
       </c>
       <c r="B212" t="n">
-        <v>0.062844</v>
+        <v>0.063808</v>
       </c>
       <c r="C212" t="n">
         <v>0.429348</v>
@@ -3183,7 +3183,7 @@
         </is>
       </c>
       <c r="B213" t="n">
-        <v>0.063808</v>
+        <v>0.064842</v>
       </c>
       <c r="C213" t="n">
         <v>0.42663</v>
@@ -3196,7 +3196,7 @@
         </is>
       </c>
       <c r="B214" t="n">
-        <v>0.06464300000000001</v>
+        <v>0.06555900000000001</v>
       </c>
       <c r="C214" t="n">
         <v>0.423913</v>
@@ -3209,7 +3209,7 @@
         </is>
       </c>
       <c r="B215" t="n">
-        <v>0.064842</v>
+        <v>0.067176</v>
       </c>
       <c r="C215" t="n">
         <v>0.421196</v>
@@ -3222,7 +3222,7 @@
         </is>
       </c>
       <c r="B216" t="n">
-        <v>0.06555900000000001</v>
+        <v>0.06736399999999999</v>
       </c>
       <c r="C216" t="n">
         <v>0.418478</v>
@@ -3235,7 +3235,7 @@
         </is>
       </c>
       <c r="B217" t="n">
-        <v>0.067176</v>
+        <v>0.067375</v>
       </c>
       <c r="C217" t="n">
         <v>0.415761</v>
@@ -3248,7 +3248,7 @@
         </is>
       </c>
       <c r="B218" t="n">
-        <v>0.06736399999999999</v>
+        <v>0.067555</v>
       </c>
       <c r="C218" t="n">
         <v>0.413043</v>
@@ -3261,7 +3261,7 @@
         </is>
       </c>
       <c r="B219" t="n">
-        <v>0.067375</v>
+        <v>0.067604</v>
       </c>
       <c r="C219" t="n">
         <v>0.410326</v>
@@ -3274,7 +3274,7 @@
         </is>
       </c>
       <c r="B220" t="n">
-        <v>0.067555</v>
+        <v>0.067644</v>
       </c>
       <c r="C220" t="n">
         <v>0.407609</v>
@@ -3287,7 +3287,7 @@
         </is>
       </c>
       <c r="B221" t="n">
-        <v>0.067604</v>
+        <v>0.068111</v>
       </c>
       <c r="C221" t="n">
         <v>0.404891</v>
@@ -3300,7 +3300,7 @@
         </is>
       </c>
       <c r="B222" t="n">
-        <v>0.067644</v>
+        <v>0.068538</v>
       </c>
       <c r="C222" t="n">
         <v>0.402174</v>
@@ -3313,7 +3313,7 @@
         </is>
       </c>
       <c r="B223" t="n">
-        <v>0.068111</v>
+        <v>0.068601</v>
       </c>
       <c r="C223" t="n">
         <v>0.399457</v>
@@ -3326,7 +3326,7 @@
         </is>
       </c>
       <c r="B224" t="n">
-        <v>0.068538</v>
+        <v>0.068939</v>
       </c>
       <c r="C224" t="n">
         <v>0.396739</v>
@@ -3339,7 +3339,7 @@
         </is>
       </c>
       <c r="B225" t="n">
-        <v>0.068601</v>
+        <v>0.06909</v>
       </c>
       <c r="C225" t="n">
         <v>0.394022</v>
@@ -3352,7 +3352,7 @@
         </is>
       </c>
       <c r="B226" t="n">
-        <v>0.068939</v>
+        <v>0.069253</v>
       </c>
       <c r="C226" t="n">
         <v>0.391304</v>
@@ -3365,7 +3365,7 @@
         </is>
       </c>
       <c r="B227" t="n">
-        <v>0.06909</v>
+        <v>0.070214</v>
       </c>
       <c r="C227" t="n">
         <v>0.388587</v>
@@ -3378,7 +3378,7 @@
         </is>
       </c>
       <c r="B228" t="n">
-        <v>0.069253</v>
+        <v>0.070659</v>
       </c>
       <c r="C228" t="n">
         <v>0.38587</v>
@@ -3391,7 +3391,7 @@
         </is>
       </c>
       <c r="B229" t="n">
-        <v>0.070214</v>
+        <v>0.072684</v>
       </c>
       <c r="C229" t="n">
         <v>0.383152</v>
@@ -3404,7 +3404,7 @@
         </is>
       </c>
       <c r="B230" t="n">
-        <v>0.070659</v>
+        <v>0.072744</v>
       </c>
       <c r="C230" t="n">
         <v>0.380435</v>
@@ -3417,7 +3417,7 @@
         </is>
       </c>
       <c r="B231" t="n">
-        <v>0.072684</v>
+        <v>0.07295599999999999</v>
       </c>
       <c r="C231" t="n">
         <v>0.377717</v>
@@ -3430,7 +3430,7 @@
         </is>
       </c>
       <c r="B232" t="n">
-        <v>0.072744</v>
+        <v>0.07331</v>
       </c>
       <c r="C232" t="n">
         <v>0.375</v>
@@ -3443,7 +3443,7 @@
         </is>
       </c>
       <c r="B233" t="n">
-        <v>0.07295599999999999</v>
+        <v>0.07380299999999999</v>
       </c>
       <c r="C233" t="n">
         <v>0.372283</v>
@@ -3456,7 +3456,7 @@
         </is>
       </c>
       <c r="B234" t="n">
-        <v>0.07331</v>
+        <v>0.07424799999999999</v>
       </c>
       <c r="C234" t="n">
         <v>0.369565</v>
@@ -3469,7 +3469,7 @@
         </is>
       </c>
       <c r="B235" t="n">
-        <v>0.07380299999999999</v>
+        <v>0.07437100000000001</v>
       </c>
       <c r="C235" t="n">
         <v>0.366848</v>
@@ -3482,7 +3482,7 @@
         </is>
       </c>
       <c r="B236" t="n">
-        <v>0.07424799999999999</v>
+        <v>0.075854</v>
       </c>
       <c r="C236" t="n">
         <v>0.36413</v>
@@ -3495,7 +3495,7 @@
         </is>
       </c>
       <c r="B237" t="n">
-        <v>0.07437100000000001</v>
+        <v>0.075876</v>
       </c>
       <c r="C237" t="n">
         <v>0.361413</v>
@@ -3508,7 +3508,7 @@
         </is>
       </c>
       <c r="B238" t="n">
-        <v>0.075854</v>
+        <v>0.076543</v>
       </c>
       <c r="C238" t="n">
         <v>0.358696</v>
@@ -3521,7 +3521,7 @@
         </is>
       </c>
       <c r="B239" t="n">
-        <v>0.075876</v>
+        <v>0.07708</v>
       </c>
       <c r="C239" t="n">
         <v>0.355978</v>
@@ -3534,7 +3534,7 @@
         </is>
       </c>
       <c r="B240" t="n">
-        <v>0.076543</v>
+        <v>0.077863</v>
       </c>
       <c r="C240" t="n">
         <v>0.353261</v>
@@ -3547,7 +3547,7 @@
         </is>
       </c>
       <c r="B241" t="n">
-        <v>0.07708</v>
+        <v>0.077912</v>
       </c>
       <c r="C241" t="n">
         <v>0.350543</v>
@@ -3560,7 +3560,7 @@
         </is>
       </c>
       <c r="B242" t="n">
-        <v>0.077863</v>
+        <v>0.078084</v>
       </c>
       <c r="C242" t="n">
         <v>0.347826</v>
@@ -3573,7 +3573,7 @@
         </is>
       </c>
       <c r="B243" t="n">
-        <v>0.077912</v>
+        <v>0.07843899999999999</v>
       </c>
       <c r="C243" t="n">
         <v>0.345109</v>
@@ -3586,7 +3586,7 @@
         </is>
       </c>
       <c r="B244" t="n">
-        <v>0.078084</v>
+        <v>0.07921499999999999</v>
       </c>
       <c r="C244" t="n">
         <v>0.342391</v>
@@ -3599,7 +3599,7 @@
         </is>
       </c>
       <c r="B245" t="n">
-        <v>0.07843899999999999</v>
+        <v>0.080791</v>
       </c>
       <c r="C245" t="n">
         <v>0.339674</v>
@@ -3612,7 +3612,7 @@
         </is>
       </c>
       <c r="B246" t="n">
-        <v>0.07921499999999999</v>
+        <v>0.08092199999999999</v>
       </c>
       <c r="C246" t="n">
         <v>0.336957</v>
@@ -3625,7 +3625,7 @@
         </is>
       </c>
       <c r="B247" t="n">
-        <v>0.08092199999999999</v>
+        <v>0.080995</v>
       </c>
       <c r="C247" t="n">
         <v>0.334239</v>
@@ -5250,7 +5250,7 @@
         </is>
       </c>
       <c r="B372" t="n">
-        <v>0.000341</v>
+        <v>0.000342</v>
       </c>
       <c r="C372" t="n">
         <v>0.994565</v>
@@ -5276,7 +5276,7 @@
         </is>
       </c>
       <c r="B374" t="n">
-        <v>0.00111</v>
+        <v>0.001111</v>
       </c>
       <c r="C374" t="n">
         <v>0.98913</v>
@@ -5289,7 +5289,7 @@
         </is>
       </c>
       <c r="B375" t="n">
-        <v>0.001769</v>
+        <v>0.001775</v>
       </c>
       <c r="C375" t="n">
         <v>0.986413</v>
@@ -5302,7 +5302,7 @@
         </is>
       </c>
       <c r="B376" t="n">
-        <v>0.002068</v>
+        <v>0.002062</v>
       </c>
       <c r="C376" t="n">
         <v>0.983696</v>
@@ -5315,7 +5315,7 @@
         </is>
       </c>
       <c r="B377" t="n">
-        <v>0.002163</v>
+        <v>0.002169</v>
       </c>
       <c r="C377" t="n">
         <v>0.980978</v>
@@ -5328,7 +5328,7 @@
         </is>
       </c>
       <c r="B378" t="n">
-        <v>0.002363</v>
+        <v>0.002374</v>
       </c>
       <c r="C378" t="n">
         <v>0.978261</v>
@@ -5341,7 +5341,7 @@
         </is>
       </c>
       <c r="B379" t="n">
-        <v>0.002496</v>
+        <v>0.002505</v>
       </c>
       <c r="C379" t="n">
         <v>0.975543</v>
@@ -5354,7 +5354,7 @@
         </is>
       </c>
       <c r="B380" t="n">
-        <v>0.003158</v>
+        <v>0.003163</v>
       </c>
       <c r="C380" t="n">
         <v>0.972826</v>
@@ -5367,7 +5367,7 @@
         </is>
       </c>
       <c r="B381" t="n">
-        <v>0.003176</v>
+        <v>0.00319</v>
       </c>
       <c r="C381" t="n">
         <v>0.970109</v>
@@ -5380,7 +5380,7 @@
         </is>
       </c>
       <c r="B382" t="n">
-        <v>0.003434</v>
+        <v>0.003438</v>
       </c>
       <c r="C382" t="n">
         <v>0.967391</v>
@@ -5393,7 +5393,7 @@
         </is>
       </c>
       <c r="B383" t="n">
-        <v>0.003667</v>
+        <v>0.003683</v>
       </c>
       <c r="C383" t="n">
         <v>0.964674</v>
@@ -5406,7 +5406,7 @@
         </is>
       </c>
       <c r="B384" t="n">
-        <v>0.00451</v>
+        <v>0.004512</v>
       </c>
       <c r="C384" t="n">
         <v>0.961957</v>
@@ -5419,7 +5419,7 @@
         </is>
       </c>
       <c r="B385" t="n">
-        <v>0.004575</v>
+        <v>0.004578</v>
       </c>
       <c r="C385" t="n">
         <v>0.959239</v>
@@ -5432,7 +5432,7 @@
         </is>
       </c>
       <c r="B386" t="n">
-        <v>0.005065</v>
+        <v>0.005069</v>
       </c>
       <c r="C386" t="n">
         <v>0.956522</v>
@@ -5445,7 +5445,7 @@
         </is>
       </c>
       <c r="B387" t="n">
-        <v>0.005097</v>
+        <v>0.005124</v>
       </c>
       <c r="C387" t="n">
         <v>0.953804</v>
@@ -5458,7 +5458,7 @@
         </is>
       </c>
       <c r="B388" t="n">
-        <v>0.005135</v>
+        <v>0.005161</v>
       </c>
       <c r="C388" t="n">
         <v>0.951087</v>
@@ -5471,7 +5471,7 @@
         </is>
       </c>
       <c r="B389" t="n">
-        <v>0.005164</v>
+        <v>0.005171</v>
       </c>
       <c r="C389" t="n">
         <v>0.94837</v>
@@ -5484,7 +5484,7 @@
         </is>
       </c>
       <c r="B390" t="n">
-        <v>0.005289</v>
+        <v>0.005246</v>
       </c>
       <c r="C390" t="n">
         <v>0.945652</v>
@@ -5497,7 +5497,7 @@
         </is>
       </c>
       <c r="B391" t="n">
-        <v>0.005368</v>
+        <v>0.00539</v>
       </c>
       <c r="C391" t="n">
         <v>0.942935</v>
@@ -5510,7 +5510,7 @@
         </is>
       </c>
       <c r="B392" t="n">
-        <v>0.005488</v>
+        <v>0.005516</v>
       </c>
       <c r="C392" t="n">
         <v>0.940217</v>
@@ -5523,7 +5523,7 @@
         </is>
       </c>
       <c r="B393" t="n">
-        <v>0.00565</v>
+        <v>0.005637</v>
       </c>
       <c r="C393" t="n">
         <v>0.9375</v>
@@ -5536,7 +5536,7 @@
         </is>
       </c>
       <c r="B394" t="n">
-        <v>0.005663</v>
+        <v>0.005677</v>
       </c>
       <c r="C394" t="n">
         <v>0.934783</v>
@@ -5549,7 +5549,7 @@
         </is>
       </c>
       <c r="B395" t="n">
-        <v>0.006356</v>
+        <v>0.006375</v>
       </c>
       <c r="C395" t="n">
         <v>0.932065</v>
@@ -5562,7 +5562,7 @@
         </is>
       </c>
       <c r="B396" t="n">
-        <v>0.00661</v>
+        <v>0.006624</v>
       </c>
       <c r="C396" t="n">
         <v>0.929348</v>
@@ -5575,7 +5575,7 @@
         </is>
       </c>
       <c r="B397" t="n">
-        <v>0.006708</v>
+        <v>0.006724</v>
       </c>
       <c r="C397" t="n">
         <v>0.92663</v>
@@ -5588,7 +5588,7 @@
         </is>
       </c>
       <c r="B398" t="n">
-        <v>0.007348</v>
+        <v>0.007356</v>
       </c>
       <c r="C398" t="n">
         <v>0.923913</v>
@@ -5601,7 +5601,7 @@
         </is>
       </c>
       <c r="B399" t="n">
-        <v>0.008219000000000001</v>
+        <v>0.008232</v>
       </c>
       <c r="C399" t="n">
         <v>0.921196</v>
@@ -5614,7 +5614,7 @@
         </is>
       </c>
       <c r="B400" t="n">
-        <v>0.008238000000000001</v>
+        <v>0.008276</v>
       </c>
       <c r="C400" t="n">
         <v>0.918478</v>
@@ -5627,7 +5627,7 @@
         </is>
       </c>
       <c r="B401" t="n">
-        <v>0.008538</v>
+        <v>0.008581</v>
       </c>
       <c r="C401" t="n">
         <v>0.915761</v>
@@ -5640,7 +5640,7 @@
         </is>
       </c>
       <c r="B402" t="n">
-        <v>0.008742</v>
+        <v>0.008762000000000001</v>
       </c>
       <c r="C402" t="n">
         <v>0.913043</v>
@@ -5653,7 +5653,7 @@
         </is>
       </c>
       <c r="B403" t="n">
-        <v>0.008954999999999999</v>
+        <v>0.008904</v>
       </c>
       <c r="C403" t="n">
         <v>0.910326</v>
@@ -5666,7 +5666,7 @@
         </is>
       </c>
       <c r="B404" t="n">
-        <v>0.008997</v>
+        <v>0.009015</v>
       </c>
       <c r="C404" t="n">
         <v>0.907609</v>
@@ -5679,7 +5679,7 @@
         </is>
       </c>
       <c r="B405" t="n">
-        <v>0.009256</v>
+        <v>0.009242999999999999</v>
       </c>
       <c r="C405" t="n">
         <v>0.904891</v>
@@ -5692,7 +5692,7 @@
         </is>
       </c>
       <c r="B406" t="n">
-        <v>0.009259999999999999</v>
+        <v>0.009303000000000001</v>
       </c>
       <c r="C406" t="n">
         <v>0.902174</v>
@@ -5705,7 +5705,7 @@
         </is>
       </c>
       <c r="B407" t="n">
-        <v>0.0094</v>
+        <v>0.009408</v>
       </c>
       <c r="C407" t="n">
         <v>0.899457</v>
@@ -5718,7 +5718,7 @@
         </is>
       </c>
       <c r="B408" t="n">
-        <v>0.00976</v>
+        <v>0.009702000000000001</v>
       </c>
       <c r="C408" t="n">
         <v>0.896739</v>
@@ -5731,7 +5731,7 @@
         </is>
       </c>
       <c r="B409" t="n">
-        <v>0.010318</v>
+        <v>0.009769</v>
       </c>
       <c r="C409" t="n">
         <v>0.894022</v>
@@ -5744,7 +5744,7 @@
         </is>
       </c>
       <c r="B410" t="n">
-        <v>0.010531</v>
+        <v>0.010361</v>
       </c>
       <c r="C410" t="n">
         <v>0.891304</v>
@@ -5757,7 +5757,7 @@
         </is>
       </c>
       <c r="B411" t="n">
-        <v>0.010547</v>
+        <v>0.010565</v>
       </c>
       <c r="C411" t="n">
         <v>0.888587</v>
@@ -5770,7 +5770,7 @@
         </is>
       </c>
       <c r="B412" t="n">
-        <v>0.011021</v>
+        <v>0.010599</v>
       </c>
       <c r="C412" t="n">
         <v>0.88587</v>
@@ -5783,7 +5783,7 @@
         </is>
       </c>
       <c r="B413" t="n">
-        <v>0.01121</v>
+        <v>0.011044</v>
       </c>
       <c r="C413" t="n">
         <v>0.883152</v>
@@ -5796,7 +5796,7 @@
         </is>
       </c>
       <c r="B414" t="n">
-        <v>0.011271</v>
+        <v>0.011211</v>
       </c>
       <c r="C414" t="n">
         <v>0.880435</v>
@@ -5809,7 +5809,7 @@
         </is>
       </c>
       <c r="B415" t="n">
-        <v>0.01131</v>
+        <v>0.011227</v>
       </c>
       <c r="C415" t="n">
         <v>0.877717</v>
@@ -5822,7 +5822,7 @@
         </is>
       </c>
       <c r="B416" t="n">
-        <v>0.011921</v>
+        <v>0.011249</v>
       </c>
       <c r="C416" t="n">
         <v>0.875</v>
@@ -5835,7 +5835,7 @@
         </is>
       </c>
       <c r="B417" t="n">
-        <v>0.012032</v>
+        <v>0.01198</v>
       </c>
       <c r="C417" t="n">
         <v>0.872283</v>
@@ -5848,7 +5848,7 @@
         </is>
       </c>
       <c r="B418" t="n">
-        <v>0.012166</v>
+        <v>0.011987</v>
       </c>
       <c r="C418" t="n">
         <v>0.869565</v>
@@ -5861,7 +5861,7 @@
         </is>
       </c>
       <c r="B419" t="n">
-        <v>0.012484</v>
+        <v>0.012183</v>
       </c>
       <c r="C419" t="n">
         <v>0.866848</v>
@@ -5874,7 +5874,7 @@
         </is>
       </c>
       <c r="B420" t="n">
-        <v>0.012522</v>
+        <v>0.012492</v>
       </c>
       <c r="C420" t="n">
         <v>0.86413</v>
@@ -5887,7 +5887,7 @@
         </is>
       </c>
       <c r="B421" t="n">
-        <v>0.012632</v>
+        <v>0.012508</v>
       </c>
       <c r="C421" t="n">
         <v>0.861413</v>
@@ -5900,7 +5900,7 @@
         </is>
       </c>
       <c r="B422" t="n">
-        <v>0.01292</v>
+        <v>0.012634</v>
       </c>
       <c r="C422" t="n">
         <v>0.858696</v>
@@ -5913,7 +5913,7 @@
         </is>
       </c>
       <c r="B423" t="n">
-        <v>0.013064</v>
+        <v>0.012936</v>
       </c>
       <c r="C423" t="n">
         <v>0.855978</v>
@@ -5926,7 +5926,7 @@
         </is>
       </c>
       <c r="B424" t="n">
-        <v>0.013286</v>
+        <v>0.013109</v>
       </c>
       <c r="C424" t="n">
         <v>0.853261</v>
@@ -5939,7 +5939,7 @@
         </is>
       </c>
       <c r="B425" t="n">
-        <v>0.013326</v>
+        <v>0.013269</v>
       </c>
       <c r="C425" t="n">
         <v>0.850543</v>
@@ -5952,7 +5952,7 @@
         </is>
       </c>
       <c r="B426" t="n">
-        <v>0.013691</v>
+        <v>0.013363</v>
       </c>
       <c r="C426" t="n">
         <v>0.847826</v>
@@ -5965,7 +5965,7 @@
         </is>
       </c>
       <c r="B427" t="n">
-        <v>0.013911</v>
+        <v>0.013762</v>
       </c>
       <c r="C427" t="n">
         <v>0.845109</v>
@@ -5978,7 +5978,7 @@
         </is>
       </c>
       <c r="B428" t="n">
-        <v>0.014065</v>
+        <v>0.013955</v>
       </c>
       <c r="C428" t="n">
         <v>0.842391</v>
@@ -5991,7 +5991,7 @@
         </is>
       </c>
       <c r="B429" t="n">
-        <v>0.01504</v>
+        <v>0.014076</v>
       </c>
       <c r="C429" t="n">
         <v>0.839674</v>
@@ -6004,7 +6004,7 @@
         </is>
       </c>
       <c r="B430" t="n">
-        <v>0.015051</v>
+        <v>0.014946</v>
       </c>
       <c r="C430" t="n">
         <v>0.836957</v>
@@ -6017,7 +6017,7 @@
         </is>
       </c>
       <c r="B431" t="n">
-        <v>0.015243</v>
+        <v>0.015049</v>
       </c>
       <c r="C431" t="n">
         <v>0.834239</v>
@@ -6030,7 +6030,7 @@
         </is>
       </c>
       <c r="B432" t="n">
-        <v>0.015645</v>
+        <v>0.015229</v>
       </c>
       <c r="C432" t="n">
         <v>0.831522</v>
@@ -6043,7 +6043,7 @@
         </is>
       </c>
       <c r="B433" t="n">
-        <v>0.01596</v>
+        <v>0.015638</v>
       </c>
       <c r="C433" t="n">
         <v>0.828804</v>
@@ -6056,7 +6056,7 @@
         </is>
       </c>
       <c r="B434" t="n">
-        <v>0.015963</v>
+        <v>0.015932</v>
       </c>
       <c r="C434" t="n">
         <v>0.826087</v>
@@ -6069,7 +6069,7 @@
         </is>
       </c>
       <c r="B435" t="n">
-        <v>0.016064</v>
+        <v>0.016041</v>
       </c>
       <c r="C435" t="n">
         <v>0.82337</v>
@@ -6082,7 +6082,7 @@
         </is>
       </c>
       <c r="B436" t="n">
-        <v>0.016479</v>
+        <v>0.016116</v>
       </c>
       <c r="C436" t="n">
         <v>0.820652</v>
@@ -6095,7 +6095,7 @@
         </is>
       </c>
       <c r="B437" t="n">
-        <v>0.017049</v>
+        <v>0.016477</v>
       </c>
       <c r="C437" t="n">
         <v>0.817935</v>
@@ -6108,7 +6108,7 @@
         </is>
       </c>
       <c r="B438" t="n">
-        <v>0.017071</v>
+        <v>0.017036</v>
       </c>
       <c r="C438" t="n">
         <v>0.815217</v>
@@ -6121,7 +6121,7 @@
         </is>
       </c>
       <c r="B439" t="n">
-        <v>0.017233</v>
+        <v>0.017042</v>
       </c>
       <c r="C439" t="n">
         <v>0.8125</v>
@@ -6134,7 +6134,7 @@
         </is>
       </c>
       <c r="B440" t="n">
-        <v>0.01724</v>
+        <v>0.017194</v>
       </c>
       <c r="C440" t="n">
         <v>0.809783</v>
@@ -6147,7 +6147,7 @@
         </is>
       </c>
       <c r="B441" t="n">
-        <v>0.017276</v>
+        <v>0.01728</v>
       </c>
       <c r="C441" t="n">
         <v>0.807065</v>
@@ -6160,7 +6160,7 @@
         </is>
       </c>
       <c r="B442" t="n">
-        <v>0.017563</v>
+        <v>0.017298</v>
       </c>
       <c r="C442" t="n">
         <v>0.804348</v>
@@ -6173,7 +6173,7 @@
         </is>
       </c>
       <c r="B443" t="n">
-        <v>0.01788</v>
+        <v>0.017576</v>
       </c>
       <c r="C443" t="n">
         <v>0.80163</v>
@@ -6186,7 +6186,7 @@
         </is>
       </c>
       <c r="B444" t="n">
-        <v>0.018426</v>
+        <v>0.017811</v>
       </c>
       <c r="C444" t="n">
         <v>0.798913</v>
@@ -6199,7 +6199,7 @@
         </is>
       </c>
       <c r="B445" t="n">
-        <v>0.018571</v>
+        <v>0.018479</v>
       </c>
       <c r="C445" t="n">
         <v>0.796196</v>
@@ -6212,7 +6212,7 @@
         </is>
       </c>
       <c r="B446" t="n">
-        <v>0.019116</v>
+        <v>0.018633</v>
       </c>
       <c r="C446" t="n">
         <v>0.793478</v>
@@ -6225,7 +6225,7 @@
         </is>
       </c>
       <c r="B447" t="n">
-        <v>0.019176</v>
+        <v>0.019139</v>
       </c>
       <c r="C447" t="n">
         <v>0.790761</v>
@@ -6238,7 +6238,7 @@
         </is>
       </c>
       <c r="B448" t="n">
-        <v>0.01921</v>
+        <v>0.019144</v>
       </c>
       <c r="C448" t="n">
         <v>0.788043</v>
@@ -6251,7 +6251,7 @@
         </is>
       </c>
       <c r="B449" t="n">
-        <v>0.019326</v>
+        <v>0.0192</v>
       </c>
       <c r="C449" t="n">
         <v>0.785326</v>
@@ -6264,7 +6264,7 @@
         </is>
       </c>
       <c r="B450" t="n">
-        <v>0.019496</v>
+        <v>0.019359</v>
       </c>
       <c r="C450" t="n">
         <v>0.782609</v>
@@ -6277,7 +6277,7 @@
         </is>
       </c>
       <c r="B451" t="n">
-        <v>0.0195</v>
+        <v>0.019504</v>
       </c>
       <c r="C451" t="n">
         <v>0.779891</v>
@@ -6290,7 +6290,7 @@
         </is>
       </c>
       <c r="B452" t="n">
-        <v>0.020373</v>
+        <v>0.019565</v>
       </c>
       <c r="C452" t="n">
         <v>0.777174</v>
@@ -6303,7 +6303,7 @@
         </is>
       </c>
       <c r="B453" t="n">
-        <v>0.020797</v>
+        <v>0.020298</v>
       </c>
       <c r="C453" t="n">
         <v>0.774457</v>
@@ -6316,7 +6316,7 @@
         </is>
       </c>
       <c r="B454" t="n">
-        <v>0.021156</v>
+        <v>0.020816</v>
       </c>
       <c r="C454" t="n">
         <v>0.771739</v>
@@ -6329,7 +6329,7 @@
         </is>
       </c>
       <c r="B455" t="n">
-        <v>0.021443</v>
+        <v>0.021184</v>
       </c>
       <c r="C455" t="n">
         <v>0.769022</v>
@@ -6342,7 +6342,7 @@
         </is>
       </c>
       <c r="B456" t="n">
-        <v>0.021895</v>
+        <v>0.021404</v>
       </c>
       <c r="C456" t="n">
         <v>0.766304</v>
@@ -6355,7 +6355,7 @@
         </is>
       </c>
       <c r="B457" t="n">
-        <v>0.022266</v>
+        <v>0.02198</v>
       </c>
       <c r="C457" t="n">
         <v>0.763587</v>
@@ -6368,7 +6368,7 @@
         </is>
       </c>
       <c r="B458" t="n">
-        <v>0.022271</v>
+        <v>0.022223</v>
       </c>
       <c r="C458" t="n">
         <v>0.76087</v>
@@ -6381,7 +6381,7 @@
         </is>
       </c>
       <c r="B459" t="n">
-        <v>0.022904</v>
+        <v>0.022314</v>
       </c>
       <c r="C459" t="n">
         <v>0.758152</v>
@@ -6394,7 +6394,7 @@
         </is>
       </c>
       <c r="B460" t="n">
-        <v>0.023535</v>
+        <v>0.022715</v>
       </c>
       <c r="C460" t="n">
         <v>0.755435</v>
@@ -6407,7 +6407,7 @@
         </is>
       </c>
       <c r="B461" t="n">
-        <v>0.023719</v>
+        <v>0.023607</v>
       </c>
       <c r="C461" t="n">
         <v>0.752717</v>
@@ -6420,7 +6420,7 @@
         </is>
       </c>
       <c r="B462" t="n">
-        <v>0.024212</v>
+        <v>0.02366</v>
       </c>
       <c r="C462" t="n">
         <v>0.75</v>
@@ -6433,7 +6433,7 @@
         </is>
       </c>
       <c r="B463" t="n">
-        <v>0.024754</v>
+        <v>0.024207</v>
       </c>
       <c r="C463" t="n">
         <v>0.747283</v>
@@ -6446,7 +6446,7 @@
         </is>
       </c>
       <c r="B464" t="n">
-        <v>0.025019</v>
+        <v>0.02461</v>
       </c>
       <c r="C464" t="n">
         <v>0.744565</v>
@@ -6459,7 +6459,7 @@
         </is>
       </c>
       <c r="B465" t="n">
-        <v>0.02503</v>
+        <v>0.024991</v>
       </c>
       <c r="C465" t="n">
         <v>0.741848</v>
@@ -6472,7 +6472,7 @@
         </is>
       </c>
       <c r="B466" t="n">
-        <v>0.025078</v>
+        <v>0.025057</v>
       </c>
       <c r="C466" t="n">
         <v>0.73913</v>
@@ -6485,7 +6485,7 @@
         </is>
       </c>
       <c r="B467" t="n">
-        <v>0.02532</v>
+        <v>0.025091</v>
       </c>
       <c r="C467" t="n">
         <v>0.736413</v>
@@ -6498,7 +6498,7 @@
         </is>
       </c>
       <c r="B468" t="n">
-        <v>0.025364</v>
+        <v>0.025222</v>
       </c>
       <c r="C468" t="n">
         <v>0.733696</v>
@@ -6511,7 +6511,7 @@
         </is>
       </c>
       <c r="B469" t="n">
-        <v>0.025404</v>
+        <v>0.025243</v>
       </c>
       <c r="C469" t="n">
         <v>0.730978</v>
@@ -6524,7 +6524,7 @@
         </is>
       </c>
       <c r="B470" t="n">
-        <v>0.025574</v>
+        <v>0.025321</v>
       </c>
       <c r="C470" t="n">
         <v>0.728261</v>
@@ -6537,7 +6537,7 @@
         </is>
       </c>
       <c r="B471" t="n">
-        <v>0.025879</v>
+        <v>0.025676</v>
       </c>
       <c r="C471" t="n">
         <v>0.725543</v>
@@ -6550,7 +6550,7 @@
         </is>
       </c>
       <c r="B472" t="n">
-        <v>0.026372</v>
+        <v>0.025894</v>
       </c>
       <c r="C472" t="n">
         <v>0.722826</v>
@@ -6563,7 +6563,7 @@
         </is>
       </c>
       <c r="B473" t="n">
-        <v>0.026642</v>
+        <v>0.026161</v>
       </c>
       <c r="C473" t="n">
         <v>0.720109</v>
@@ -6576,7 +6576,7 @@
         </is>
       </c>
       <c r="B474" t="n">
-        <v>0.02728</v>
+        <v>0.026451</v>
       </c>
       <c r="C474" t="n">
         <v>0.717391</v>
@@ -6589,7 +6589,7 @@
         </is>
       </c>
       <c r="B475" t="n">
-        <v>0.027742</v>
+        <v>0.027191</v>
       </c>
       <c r="C475" t="n">
         <v>0.714674</v>
@@ -6602,7 +6602,7 @@
         </is>
       </c>
       <c r="B476" t="n">
-        <v>0.027802</v>
+        <v>0.027642</v>
       </c>
       <c r="C476" t="n">
         <v>0.711957</v>
@@ -6615,7 +6615,7 @@
         </is>
       </c>
       <c r="B477" t="n">
-        <v>0.028106</v>
+        <v>0.027875</v>
       </c>
       <c r="C477" t="n">
         <v>0.709239</v>
@@ -6628,7 +6628,7 @@
         </is>
       </c>
       <c r="B478" t="n">
-        <v>0.028315</v>
+        <v>0.028193</v>
       </c>
       <c r="C478" t="n">
         <v>0.706522</v>
@@ -6641,7 +6641,7 @@
         </is>
       </c>
       <c r="B479" t="n">
-        <v>0.028721</v>
+        <v>0.028344</v>
       </c>
       <c r="C479" t="n">
         <v>0.703804</v>
@@ -6654,7 +6654,7 @@
         </is>
       </c>
       <c r="B480" t="n">
-        <v>0.02879</v>
+        <v>0.028835</v>
       </c>
       <c r="C480" t="n">
         <v>0.701087</v>
@@ -6667,7 +6667,7 @@
         </is>
       </c>
       <c r="B481" t="n">
-        <v>0.028918</v>
+        <v>0.028876</v>
       </c>
       <c r="C481" t="n">
         <v>0.69837</v>
@@ -6680,7 +6680,7 @@
         </is>
       </c>
       <c r="B482" t="n">
-        <v>0.02914</v>
+        <v>0.028939</v>
       </c>
       <c r="C482" t="n">
         <v>0.695652</v>
@@ -6693,7 +6693,7 @@
         </is>
       </c>
       <c r="B483" t="n">
-        <v>0.029677</v>
+        <v>0.02929</v>
       </c>
       <c r="C483" t="n">
         <v>0.692935</v>
@@ -6706,7 +6706,7 @@
         </is>
       </c>
       <c r="B484" t="n">
-        <v>0.029706</v>
+        <v>0.029762</v>
       </c>
       <c r="C484" t="n">
         <v>0.690217</v>
@@ -6719,7 +6719,7 @@
         </is>
       </c>
       <c r="B485" t="n">
-        <v>0.029846</v>
+        <v>0.029763</v>
       </c>
       <c r="C485" t="n">
         <v>0.6875</v>
@@ -6732,7 +6732,7 @@
         </is>
       </c>
       <c r="B486" t="n">
-        <v>0.029887</v>
+        <v>0.029768</v>
       </c>
       <c r="C486" t="n">
         <v>0.684783</v>
@@ -6745,7 +6745,7 @@
         </is>
       </c>
       <c r="B487" t="n">
-        <v>0.029906</v>
+        <v>0.029835</v>
       </c>
       <c r="C487" t="n">
         <v>0.682065</v>
@@ -6758,7 +6758,7 @@
         </is>
       </c>
       <c r="B488" t="n">
-        <v>0.029931</v>
+        <v>0.029841</v>
       </c>
       <c r="C488" t="n">
         <v>0.679348</v>
@@ -6771,7 +6771,7 @@
         </is>
       </c>
       <c r="B489" t="n">
-        <v>0.029984</v>
+        <v>0.029863</v>
       </c>
       <c r="C489" t="n">
         <v>0.67663</v>
@@ -6784,7 +6784,7 @@
         </is>
       </c>
       <c r="B490" t="n">
-        <v>0.030831</v>
+        <v>0.030034</v>
       </c>
       <c r="C490" t="n">
         <v>0.673913</v>
@@ -6797,7 +6797,7 @@
         </is>
       </c>
       <c r="B491" t="n">
-        <v>0.031302</v>
+        <v>0.030971</v>
       </c>
       <c r="C491" t="n">
         <v>0.671196</v>
@@ -6810,7 +6810,7 @@
         </is>
       </c>
       <c r="B492" t="n">
-        <v>0.031426</v>
+        <v>0.031333</v>
       </c>
       <c r="C492" t="n">
         <v>0.668478</v>
@@ -6823,7 +6823,7 @@
         </is>
       </c>
       <c r="B493" t="n">
-        <v>0.031596</v>
+        <v>0.031406</v>
       </c>
       <c r="C493" t="n">
         <v>0.665761</v>
@@ -6836,7 +6836,7 @@
         </is>
       </c>
       <c r="B494" t="n">
-        <v>0.032234</v>
+        <v>0.031502</v>
       </c>
       <c r="C494" t="n">
         <v>0.663043</v>
@@ -6849,7 +6849,7 @@
         </is>
       </c>
       <c r="B495" t="n">
-        <v>0.032305</v>
+        <v>0.032349</v>
       </c>
       <c r="C495" t="n">
         <v>0.660326</v>
@@ -6862,7 +6862,7 @@
         </is>
       </c>
       <c r="B496" t="n">
-        <v>0.032685</v>
+        <v>0.032382</v>
       </c>
       <c r="C496" t="n">
         <v>0.657609</v>
@@ -6875,7 +6875,7 @@
         </is>
       </c>
       <c r="B497" t="n">
-        <v>0.033244</v>
+        <v>0.032665</v>
       </c>
       <c r="C497" t="n">
         <v>0.654891</v>
@@ -6888,7 +6888,7 @@
         </is>
       </c>
       <c r="B498" t="n">
-        <v>0.033423</v>
+        <v>0.032987</v>
       </c>
       <c r="C498" t="n">
         <v>0.652174</v>
@@ -6901,7 +6901,7 @@
         </is>
       </c>
       <c r="B499" t="n">
-        <v>0.033742</v>
+        <v>0.033161</v>
       </c>
       <c r="C499" t="n">
         <v>0.649457</v>
@@ -6914,7 +6914,7 @@
         </is>
       </c>
       <c r="B500" t="n">
-        <v>0.033854</v>
+        <v>0.033693</v>
       </c>
       <c r="C500" t="n">
         <v>0.646739</v>
@@ -6927,7 +6927,7 @@
         </is>
       </c>
       <c r="B501" t="n">
-        <v>0.03395</v>
+        <v>0.033944</v>
       </c>
       <c r="C501" t="n">
         <v>0.644022</v>
@@ -6940,7 +6940,7 @@
         </is>
       </c>
       <c r="B502" t="n">
-        <v>0.034049</v>
+        <v>0.033992</v>
       </c>
       <c r="C502" t="n">
         <v>0.641304</v>
@@ -6953,7 +6953,7 @@
         </is>
       </c>
       <c r="B503" t="n">
-        <v>0.034706</v>
+        <v>0.034191</v>
       </c>
       <c r="C503" t="n">
         <v>0.638587</v>
@@ -6966,7 +6966,7 @@
         </is>
       </c>
       <c r="B504" t="n">
-        <v>0.034758</v>
+        <v>0.034639</v>
       </c>
       <c r="C504" t="n">
         <v>0.63587</v>
@@ -6979,7 +6979,7 @@
         </is>
       </c>
       <c r="B505" t="n">
-        <v>0.03477</v>
+        <v>0.034795</v>
       </c>
       <c r="C505" t="n">
         <v>0.633152</v>
@@ -6992,7 +6992,7 @@
         </is>
       </c>
       <c r="B506" t="n">
-        <v>0.034993</v>
+        <v>0.034839</v>
       </c>
       <c r="C506" t="n">
         <v>0.630435</v>
@@ -7005,7 +7005,7 @@
         </is>
       </c>
       <c r="B507" t="n">
-        <v>0.035062</v>
+        <v>0.034928</v>
       </c>
       <c r="C507" t="n">
         <v>0.627717</v>
@@ -7018,7 +7018,7 @@
         </is>
       </c>
       <c r="B508" t="n">
-        <v>0.035343</v>
+        <v>0.035138</v>
       </c>
       <c r="C508" t="n">
         <v>0.625</v>
@@ -7031,7 +7031,7 @@
         </is>
       </c>
       <c r="B509" t="n">
-        <v>0.035495</v>
+        <v>0.035466</v>
       </c>
       <c r="C509" t="n">
         <v>0.622283</v>
@@ -7044,7 +7044,7 @@
         </is>
       </c>
       <c r="B510" t="n">
-        <v>0.036</v>
+        <v>0.035547</v>
       </c>
       <c r="C510" t="n">
         <v>0.619565</v>
@@ -7057,7 +7057,7 @@
         </is>
       </c>
       <c r="B511" t="n">
-        <v>0.036041</v>
+        <v>0.035943</v>
       </c>
       <c r="C511" t="n">
         <v>0.616848</v>
@@ -7070,7 +7070,7 @@
         </is>
       </c>
       <c r="B512" t="n">
-        <v>0.037335</v>
+        <v>0.036</v>
       </c>
       <c r="C512" t="n">
         <v>0.61413</v>
@@ -7083,7 +7083,7 @@
         </is>
       </c>
       <c r="B513" t="n">
-        <v>0.037822</v>
+        <v>0.037265</v>
       </c>
       <c r="C513" t="n">
         <v>0.611413</v>
@@ -7096,7 +7096,7 @@
         </is>
       </c>
       <c r="B514" t="n">
-        <v>0.038043</v>
+        <v>0.037898</v>
       </c>
       <c r="C514" t="n">
         <v>0.608696</v>
@@ -7109,7 +7109,7 @@
         </is>
       </c>
       <c r="B515" t="n">
-        <v>0.038277</v>
+        <v>0.038164</v>
       </c>
       <c r="C515" t="n">
         <v>0.605978</v>
@@ -7122,7 +7122,7 @@
         </is>
       </c>
       <c r="B516" t="n">
-        <v>0.038545</v>
+        <v>0.038186</v>
       </c>
       <c r="C516" t="n">
         <v>0.603261</v>
@@ -7135,7 +7135,7 @@
         </is>
       </c>
       <c r="B517" t="n">
-        <v>0.038808</v>
+        <v>0.038557</v>
       </c>
       <c r="C517" t="n">
         <v>0.600543</v>
@@ -7148,7 +7148,7 @@
         </is>
       </c>
       <c r="B518" t="n">
-        <v>0.038859</v>
+        <v>0.038786</v>
       </c>
       <c r="C518" t="n">
         <v>0.597826</v>
@@ -7161,7 +7161,7 @@
         </is>
       </c>
       <c r="B519" t="n">
-        <v>0.039551</v>
+        <v>0.038925</v>
       </c>
       <c r="C519" t="n">
         <v>0.595109</v>
@@ -7174,7 +7174,7 @@
         </is>
       </c>
       <c r="B520" t="n">
-        <v>0.039641</v>
+        <v>0.039727</v>
       </c>
       <c r="C520" t="n">
         <v>0.592391</v>
@@ -7187,7 +7187,7 @@
         </is>
       </c>
       <c r="B521" t="n">
-        <v>0.039785</v>
+        <v>0.03976</v>
       </c>
       <c r="C521" t="n">
         <v>0.589674</v>
@@ -7200,7 +7200,7 @@
         </is>
       </c>
       <c r="B522" t="n">
-        <v>0.039882</v>
+        <v>0.039785</v>
       </c>
       <c r="C522" t="n">
         <v>0.586957</v>
@@ -7213,7 +7213,7 @@
         </is>
       </c>
       <c r="B523" t="n">
-        <v>0.040194</v>
+        <v>0.03999</v>
       </c>
       <c r="C523" t="n">
         <v>0.584239</v>
@@ -7226,7 +7226,7 @@
         </is>
       </c>
       <c r="B524" t="n">
-        <v>0.040208</v>
+        <v>0.04019</v>
       </c>
       <c r="C524" t="n">
         <v>0.581522</v>
@@ -7239,7 +7239,7 @@
         </is>
       </c>
       <c r="B525" t="n">
-        <v>0.040846</v>
+        <v>0.040272</v>
       </c>
       <c r="C525" t="n">
         <v>0.578804</v>
@@ -7252,7 +7252,7 @@
         </is>
       </c>
       <c r="B526" t="n">
-        <v>0.041278</v>
+        <v>0.040995</v>
       </c>
       <c r="C526" t="n">
         <v>0.576087</v>
@@ -7265,7 +7265,7 @@
         </is>
       </c>
       <c r="B527" t="n">
-        <v>0.041661</v>
+        <v>0.040997</v>
       </c>
       <c r="C527" t="n">
         <v>0.57337</v>
@@ -7278,7 +7278,7 @@
         </is>
       </c>
       <c r="B528" t="n">
-        <v>0.042152</v>
+        <v>0.04209</v>
       </c>
       <c r="C528" t="n">
         <v>0.570652</v>
@@ -7291,7 +7291,7 @@
         </is>
       </c>
       <c r="B529" t="n">
-        <v>0.042256</v>
+        <v>0.042306</v>
       </c>
       <c r="C529" t="n">
         <v>0.567935</v>
@@ -7304,7 +7304,7 @@
         </is>
       </c>
       <c r="B530" t="n">
-        <v>0.04254</v>
+        <v>0.042713</v>
       </c>
       <c r="C530" t="n">
         <v>0.565217</v>
@@ -7317,7 +7317,7 @@
         </is>
       </c>
       <c r="B531" t="n">
-        <v>0.0428</v>
+        <v>0.042954</v>
       </c>
       <c r="C531" t="n">
         <v>0.5625</v>
@@ -7330,7 +7330,7 @@
         </is>
       </c>
       <c r="B532" t="n">
-        <v>0.042916</v>
+        <v>0.04302</v>
       </c>
       <c r="C532" t="n">
         <v>0.559783</v>
@@ -7343,7 +7343,7 @@
         </is>
       </c>
       <c r="B533" t="n">
-        <v>0.043004</v>
+        <v>0.043083</v>
       </c>
       <c r="C533" t="n">
         <v>0.557065</v>
@@ -7356,7 +7356,7 @@
         </is>
       </c>
       <c r="B534" t="n">
-        <v>0.043112</v>
+        <v>0.043099</v>
       </c>
       <c r="C534" t="n">
         <v>0.554348</v>
@@ -7369,7 +7369,7 @@
         </is>
       </c>
       <c r="B535" t="n">
-        <v>0.04329</v>
+        <v>0.043438</v>
       </c>
       <c r="C535" t="n">
         <v>0.55163</v>
@@ -7382,7 +7382,7 @@
         </is>
       </c>
       <c r="B536" t="n">
-        <v>0.043477</v>
+        <v>0.043513</v>
       </c>
       <c r="C536" t="n">
         <v>0.548913</v>
@@ -7395,7 +7395,7 @@
         </is>
       </c>
       <c r="B537" t="n">
-        <v>0.043583</v>
+        <v>0.04373</v>
       </c>
       <c r="C537" t="n">
         <v>0.546196</v>
@@ -7408,7 +7408,7 @@
         </is>
       </c>
       <c r="B538" t="n">
-        <v>0.043643</v>
+        <v>0.043747</v>
       </c>
       <c r="C538" t="n">
         <v>0.543478</v>
@@ -7421,7 +7421,7 @@
         </is>
       </c>
       <c r="B539" t="n">
-        <v>0.043733</v>
+        <v>0.043791</v>
       </c>
       <c r="C539" t="n">
         <v>0.540761</v>
@@ -7434,7 +7434,7 @@
         </is>
       </c>
       <c r="B540" t="n">
-        <v>0.044173</v>
+        <v>0.044304</v>
       </c>
       <c r="C540" t="n">
         <v>0.538043</v>
@@ -7447,7 +7447,7 @@
         </is>
       </c>
       <c r="B541" t="n">
-        <v>0.044677</v>
+        <v>0.044638</v>
       </c>
       <c r="C541" t="n">
         <v>0.535326</v>
@@ -7460,7 +7460,7 @@
         </is>
       </c>
       <c r="B542" t="n">
-        <v>0.044806</v>
+        <v>0.044749</v>
       </c>
       <c r="C542" t="n">
         <v>0.532609</v>
@@ -7473,7 +7473,7 @@
         </is>
       </c>
       <c r="B543" t="n">
-        <v>0.044819</v>
+        <v>0.044944</v>
       </c>
       <c r="C543" t="n">
         <v>0.529891</v>
@@ -7486,7 +7486,7 @@
         </is>
       </c>
       <c r="B544" t="n">
-        <v>0.044895</v>
+        <v>0.045027</v>
       </c>
       <c r="C544" t="n">
         <v>0.527174</v>
@@ -7499,7 +7499,7 @@
         </is>
       </c>
       <c r="B545" t="n">
-        <v>0.044901</v>
+        <v>0.045613</v>
       </c>
       <c r="C545" t="n">
         <v>0.524457</v>
@@ -7512,7 +7512,7 @@
         </is>
       </c>
       <c r="B546" t="n">
-        <v>0.045545</v>
+        <v>0.045948</v>
       </c>
       <c r="C546" t="n">
         <v>0.521739</v>
@@ -7525,7 +7525,7 @@
         </is>
       </c>
       <c r="B547" t="n">
-        <v>0.04585</v>
+        <v>0.045967</v>
       </c>
       <c r="C547" t="n">
         <v>0.519022</v>
@@ -7538,7 +7538,7 @@
         </is>
       </c>
       <c r="B548" t="n">
-        <v>0.046267</v>
+        <v>0.046172</v>
       </c>
       <c r="C548" t="n">
         <v>0.516304</v>
@@ -7551,7 +7551,7 @@
         </is>
       </c>
       <c r="B549" t="n">
-        <v>0.046363</v>
+        <v>0.046605</v>
       </c>
       <c r="C549" t="n">
         <v>0.513587</v>
@@ -7564,7 +7564,7 @@
         </is>
       </c>
       <c r="B550" t="n">
-        <v>0.046497</v>
+        <v>0.04774</v>
       </c>
       <c r="C550" t="n">
         <v>0.51087</v>
@@ -7577,7 +7577,7 @@
         </is>
       </c>
       <c r="B551" t="n">
-        <v>0.047747</v>
+        <v>0.04777</v>
       </c>
       <c r="C551" t="n">
         <v>0.508152</v>
@@ -7590,7 +7590,7 @@
         </is>
       </c>
       <c r="B552" t="n">
-        <v>0.047979</v>
+        <v>0.048164</v>
       </c>
       <c r="C552" t="n">
         <v>0.505435</v>
@@ -7603,7 +7603,7 @@
         </is>
       </c>
       <c r="B553" t="n">
-        <v>0.048217</v>
+        <v>0.04832</v>
       </c>
       <c r="C553" t="n">
         <v>0.502717</v>
@@ -7616,7 +7616,7 @@
         </is>
       </c>
       <c r="B554" t="n">
-        <v>0.048277</v>
+        <v>0.049453</v>
       </c>
       <c r="C554" t="n">
         <v>0.5</v>
@@ -7629,7 +7629,7 @@
         </is>
       </c>
       <c r="B555" t="n">
-        <v>0.049311</v>
+        <v>0.04946</v>
       </c>
       <c r="C555" t="n">
         <v>0.497283</v>
@@ -7642,7 +7642,7 @@
         </is>
       </c>
       <c r="B556" t="n">
-        <v>0.049479</v>
+        <v>0.049971</v>
       </c>
       <c r="C556" t="n">
         <v>0.494565</v>
@@ -7655,7 +7655,7 @@
         </is>
       </c>
       <c r="B557" t="n">
-        <v>0.049815</v>
+        <v>0.05003</v>
       </c>
       <c r="C557" t="n">
         <v>0.491848</v>
@@ -7668,7 +7668,7 @@
         </is>
       </c>
       <c r="B558" t="n">
-        <v>0.05042</v>
+        <v>0.050848</v>
       </c>
       <c r="C558" t="n">
         <v>0.48913</v>
@@ -7681,7 +7681,7 @@
         </is>
       </c>
       <c r="B559" t="n">
-        <v>0.050841</v>
+        <v>0.052505</v>
       </c>
       <c r="C559" t="n">
         <v>0.486413</v>
@@ -7694,7 +7694,7 @@
         </is>
       </c>
       <c r="B560" t="n">
-        <v>0.052325</v>
+        <v>0.052976</v>
       </c>
       <c r="C560" t="n">
         <v>0.483696</v>
@@ -7707,7 +7707,7 @@
         </is>
       </c>
       <c r="B561" t="n">
-        <v>0.052868</v>
+        <v>0.053014</v>
       </c>
       <c r="C561" t="n">
         <v>0.480978</v>
@@ -7720,7 +7720,7 @@
         </is>
       </c>
       <c r="B562" t="n">
-        <v>0.053207</v>
+        <v>0.053268</v>
       </c>
       <c r="C562" t="n">
         <v>0.478261</v>
@@ -7733,7 +7733,7 @@
         </is>
       </c>
       <c r="B563" t="n">
-        <v>0.053393</v>
+        <v>0.053366</v>
       </c>
       <c r="C563" t="n">
         <v>0.475543</v>
@@ -7746,7 +7746,7 @@
         </is>
       </c>
       <c r="B564" t="n">
-        <v>0.053528</v>
+        <v>0.053472</v>
       </c>
       <c r="C564" t="n">
         <v>0.472826</v>
@@ -7759,7 +7759,7 @@
         </is>
       </c>
       <c r="B565" t="n">
-        <v>0.053602</v>
+        <v>0.053748</v>
       </c>
       <c r="C565" t="n">
         <v>0.470109</v>
@@ -7772,7 +7772,7 @@
         </is>
       </c>
       <c r="B566" t="n">
-        <v>0.053864</v>
+        <v>0.054325</v>
       </c>
       <c r="C566" t="n">
         <v>0.467391</v>
@@ -7785,7 +7785,7 @@
         </is>
       </c>
       <c r="B567" t="n">
-        <v>0.054203</v>
+        <v>0.054615</v>
       </c>
       <c r="C567" t="n">
         <v>0.464674</v>
@@ -7798,7 +7798,7 @@
         </is>
       </c>
       <c r="B568" t="n">
-        <v>0.054594</v>
+        <v>0.055136</v>
       </c>
       <c r="C568" t="n">
         <v>0.461957</v>
@@ -7811,7 +7811,7 @@
         </is>
       </c>
       <c r="B569" t="n">
-        <v>0.055216</v>
+        <v>0.055168</v>
       </c>
       <c r="C569" t="n">
         <v>0.459239</v>
@@ -7824,7 +7824,7 @@
         </is>
       </c>
       <c r="B570" t="n">
-        <v>0.055266</v>
+        <v>0.055184</v>
       </c>
       <c r="C570" t="n">
         <v>0.456522</v>
@@ -7837,7 +7837,7 @@
         </is>
       </c>
       <c r="B571" t="n">
-        <v>0.055299</v>
+        <v>0.055714</v>
       </c>
       <c r="C571" t="n">
         <v>0.453804</v>
@@ -7850,7 +7850,7 @@
         </is>
       </c>
       <c r="B572" t="n">
-        <v>0.055563</v>
+        <v>0.055943</v>
       </c>
       <c r="C572" t="n">
         <v>0.451087</v>
@@ -7863,7 +7863,7 @@
         </is>
       </c>
       <c r="B573" t="n">
-        <v>0.055912</v>
+        <v>0.056356</v>
       </c>
       <c r="C573" t="n">
         <v>0.44837</v>
@@ -7876,7 +7876,7 @@
         </is>
       </c>
       <c r="B574" t="n">
-        <v>0.056087</v>
+        <v>0.056399</v>
       </c>
       <c r="C574" t="n">
         <v>0.445652</v>
@@ -7889,7 +7889,7 @@
         </is>
       </c>
       <c r="B575" t="n">
-        <v>0.05698</v>
+        <v>0.056932</v>
       </c>
       <c r="C575" t="n">
         <v>0.442935</v>
@@ -7902,7 +7902,7 @@
         </is>
       </c>
       <c r="B576" t="n">
-        <v>0.05758</v>
+        <v>0.057625</v>
       </c>
       <c r="C576" t="n">
         <v>0.440217</v>
@@ -7915,7 +7915,7 @@
         </is>
       </c>
       <c r="B577" t="n">
-        <v>0.057897</v>
+        <v>0.057659</v>
       </c>
       <c r="C577" t="n">
         <v>0.4375</v>
@@ -7928,7 +7928,7 @@
         </is>
       </c>
       <c r="B578" t="n">
-        <v>0.058081</v>
+        <v>0.058171</v>
       </c>
       <c r="C578" t="n">
         <v>0.434783</v>
@@ -7941,7 +7941,7 @@
         </is>
       </c>
       <c r="B579" t="n">
-        <v>0.059321</v>
+        <v>0.059118</v>
       </c>
       <c r="C579" t="n">
         <v>0.432065</v>
@@ -7954,7 +7954,7 @@
         </is>
       </c>
       <c r="B580" t="n">
-        <v>0.059863</v>
+        <v>0.059859</v>
       </c>
       <c r="C580" t="n">
         <v>0.429348</v>
@@ -7967,7 +7967,7 @@
         </is>
       </c>
       <c r="B581" t="n">
-        <v>0.05987</v>
+        <v>0.059864</v>
       </c>
       <c r="C581" t="n">
         <v>0.42663</v>
@@ -7980,7 +7980,7 @@
         </is>
       </c>
       <c r="B582" t="n">
-        <v>0.060205</v>
+        <v>0.060184</v>
       </c>
       <c r="C582" t="n">
         <v>0.423913</v>
@@ -7993,7 +7993,7 @@
         </is>
       </c>
       <c r="B583" t="n">
-        <v>0.060766</v>
+        <v>0.060774</v>
       </c>
       <c r="C583" t="n">
         <v>0.421196</v>
@@ -8006,7 +8006,7 @@
         </is>
       </c>
       <c r="B584" t="n">
-        <v>0.061329</v>
+        <v>0.061292</v>
       </c>
       <c r="C584" t="n">
         <v>0.418478</v>
@@ -8019,7 +8019,7 @@
         </is>
       </c>
       <c r="B585" t="n">
-        <v>0.061413</v>
+        <v>0.061402</v>
       </c>
       <c r="C585" t="n">
         <v>0.415761</v>
@@ -8032,7 +8032,7 @@
         </is>
       </c>
       <c r="B586" t="n">
-        <v>0.061913</v>
+        <v>0.062237</v>
       </c>
       <c r="C586" t="n">
         <v>0.413043</v>
@@ -8045,7 +8045,7 @@
         </is>
       </c>
       <c r="B587" t="n">
-        <v>0.062426</v>
+        <v>0.062379</v>
       </c>
       <c r="C587" t="n">
         <v>0.410326</v>
@@ -8058,7 +8058,7 @@
         </is>
       </c>
       <c r="B588" t="n">
-        <v>0.063253</v>
+        <v>0.06464399999999999</v>
       </c>
       <c r="C588" t="n">
         <v>0.407609</v>
@@ -8071,7 +8071,7 @@
         </is>
       </c>
       <c r="B589" t="n">
-        <v>0.064389</v>
+        <v>0.065002</v>
       </c>
       <c r="C589" t="n">
         <v>0.404891</v>
@@ -8084,7 +8084,7 @@
         </is>
       </c>
       <c r="B590" t="n">
-        <v>0.06528399999999999</v>
+        <v>0.06605999999999999</v>
       </c>
       <c r="C590" t="n">
         <v>0.402174</v>
@@ -8097,7 +8097,7 @@
         </is>
       </c>
       <c r="B591" t="n">
-        <v>0.066112</v>
+        <v>0.06662999999999999</v>
       </c>
       <c r="C591" t="n">
         <v>0.399457</v>
@@ -8110,7 +8110,7 @@
         </is>
       </c>
       <c r="B592" t="n">
-        <v>0.066692</v>
+        <v>0.06676700000000001</v>
       </c>
       <c r="C592" t="n">
         <v>0.396739</v>
@@ -8123,7 +8123,7 @@
         </is>
       </c>
       <c r="B593" t="n">
-        <v>0.066969</v>
+        <v>0.067005</v>
       </c>
       <c r="C593" t="n">
         <v>0.394022</v>
@@ -8136,7 +8136,7 @@
         </is>
       </c>
       <c r="B594" t="n">
-        <v>0.067117</v>
+        <v>0.06723800000000001</v>
       </c>
       <c r="C594" t="n">
         <v>0.391304</v>
@@ -8149,7 +8149,7 @@
         </is>
       </c>
       <c r="B595" t="n">
-        <v>0.067134</v>
+        <v>0.067292</v>
       </c>
       <c r="C595" t="n">
         <v>0.388587</v>
@@ -8162,7 +8162,7 @@
         </is>
       </c>
       <c r="B596" t="n">
-        <v>0.06777</v>
+        <v>0.067886</v>
       </c>
       <c r="C596" t="n">
         <v>0.38587</v>
@@ -8175,7 +8175,7 @@
         </is>
       </c>
       <c r="B597" t="n">
-        <v>0.067789</v>
+        <v>0.067991</v>
       </c>
       <c r="C597" t="n">
         <v>0.383152</v>
@@ -8188,7 +8188,7 @@
         </is>
       </c>
       <c r="B598" t="n">
-        <v>0.068091</v>
+        <v>0.068263</v>
       </c>
       <c r="C598" t="n">
         <v>0.380435</v>
@@ -8201,7 +8201,7 @@
         </is>
       </c>
       <c r="B599" t="n">
-        <v>0.068092</v>
+        <v>0.068311</v>
       </c>
       <c r="C599" t="n">
         <v>0.377717</v>
@@ -8214,7 +8214,7 @@
         </is>
       </c>
       <c r="B600" t="n">
-        <v>0.06845999999999999</v>
+        <v>0.068484</v>
       </c>
       <c r="C600" t="n">
         <v>0.375</v>
@@ -8227,7 +8227,7 @@
         </is>
       </c>
       <c r="B601" t="n">
-        <v>0.068522</v>
+        <v>0.068523</v>
       </c>
       <c r="C601" t="n">
         <v>0.372283</v>
@@ -8240,7 +8240,7 @@
         </is>
       </c>
       <c r="B602" t="n">
-        <v>0.068814</v>
+        <v>0.06911399999999999</v>
       </c>
       <c r="C602" t="n">
         <v>0.369565</v>
@@ -8253,7 +8253,7 @@
         </is>
       </c>
       <c r="B603" t="n">
-        <v>0.06907099999999999</v>
+        <v>0.069216</v>
       </c>
       <c r="C603" t="n">
         <v>0.366848</v>
@@ -8266,7 +8266,7 @@
         </is>
       </c>
       <c r="B604" t="n">
-        <v>0.069317</v>
+        <v>0.069591</v>
       </c>
       <c r="C604" t="n">
         <v>0.36413</v>
@@ -8279,7 +8279,7 @@
         </is>
       </c>
       <c r="B605" t="n">
-        <v>0.069463</v>
+        <v>0.071641</v>
       </c>
       <c r="C605" t="n">
         <v>0.361413</v>
@@ -8292,7 +8292,7 @@
         </is>
       </c>
       <c r="B606" t="n">
-        <v>0.071409</v>
+        <v>0.07263699999999999</v>
       </c>
       <c r="C606" t="n">
         <v>0.358696</v>
@@ -8305,7 +8305,7 @@
         </is>
       </c>
       <c r="B607" t="n">
-        <v>0.072283</v>
+        <v>0.072742</v>
       </c>
       <c r="C607" t="n">
         <v>0.355978</v>
@@ -8318,7 +8318,7 @@
         </is>
       </c>
       <c r="B608" t="n">
-        <v>0.072382</v>
+        <v>0.072765</v>
       </c>
       <c r="C608" t="n">
         <v>0.353261</v>
@@ -8331,7 +8331,7 @@
         </is>
       </c>
       <c r="B609" t="n">
-        <v>0.072753</v>
+        <v>0.072864</v>
       </c>
       <c r="C609" t="n">
         <v>0.350543</v>
@@ -8344,7 +8344,7 @@
         </is>
       </c>
       <c r="B610" t="n">
-        <v>0.073181</v>
+        <v>0.073849</v>
       </c>
       <c r="C610" t="n">
         <v>0.347826</v>
@@ -8357,7 +8357,7 @@
         </is>
       </c>
       <c r="B611" t="n">
-        <v>0.07374699999999999</v>
+        <v>0.073879</v>
       </c>
       <c r="C611" t="n">
         <v>0.345109</v>
@@ -8370,7 +8370,7 @@
         </is>
       </c>
       <c r="B612" t="n">
-        <v>0.074073</v>
+        <v>0.074077</v>
       </c>
       <c r="C612" t="n">
         <v>0.342391</v>
@@ -8383,7 +8383,7 @@
         </is>
       </c>
       <c r="B613" t="n">
-        <v>0.07409399999999999</v>
+        <v>0.074183</v>
       </c>
       <c r="C613" t="n">
         <v>0.339674</v>
@@ -8396,7 +8396,7 @@
         </is>
       </c>
       <c r="B614" t="n">
-        <v>0.07437299999999999</v>
+        <v>0.074403</v>
       </c>
       <c r="C614" t="n">
         <v>0.336957</v>
@@ -8409,7 +8409,7 @@
         </is>
       </c>
       <c r="B615" t="n">
-        <v>0.074558</v>
+        <v>0.07555000000000001</v>
       </c>
       <c r="C615" t="n">
         <v>0.334239</v>
@@ -8422,7 +8422,7 @@
         </is>
       </c>
       <c r="B616" t="n">
-        <v>0.075156</v>
+        <v>0.07563499999999999</v>
       </c>
       <c r="C616" t="n">
         <v>0.331522</v>
@@ -8435,7 +8435,7 @@
         </is>
       </c>
       <c r="B617" t="n">
-        <v>0.075652</v>
+        <v>0.075765</v>
       </c>
       <c r="C617" t="n">
         <v>0.328804</v>
@@ -8448,7 +8448,7 @@
         </is>
       </c>
       <c r="B618" t="n">
-        <v>0.076223</v>
+        <v>0.076792</v>
       </c>
       <c r="C618" t="n">
         <v>0.326087</v>
@@ -8461,7 +8461,7 @@
         </is>
       </c>
       <c r="B619" t="n">
-        <v>0.076545</v>
+        <v>0.076879</v>
       </c>
       <c r="C619" t="n">
         <v>0.32337</v>
@@ -8474,7 +8474,7 @@
         </is>
       </c>
       <c r="B620" t="n">
-        <v>0.076932</v>
+        <v>0.077622</v>
       </c>
       <c r="C620" t="n">
         <v>0.320652</v>
@@ -8487,7 +8487,7 @@
         </is>
       </c>
       <c r="B621" t="n">
-        <v>0.077782</v>
+        <v>0.07764</v>
       </c>
       <c r="C621" t="n">
         <v>0.317935</v>
@@ -8500,7 +8500,7 @@
         </is>
       </c>
       <c r="B622" t="n">
-        <v>0.07785599999999999</v>
+        <v>0.077949</v>
       </c>
       <c r="C622" t="n">
         <v>0.315217</v>
@@ -8513,7 +8513,7 @@
         </is>
       </c>
       <c r="B623" t="n">
-        <v>0.077919</v>
+        <v>0.078401</v>
       </c>
       <c r="C623" t="n">
         <v>0.3125</v>
@@ -8526,7 +8526,7 @@
         </is>
       </c>
       <c r="B624" t="n">
-        <v>0.078192</v>
+        <v>0.078721</v>
       </c>
       <c r="C624" t="n">
         <v>0.309783</v>
@@ -8539,7 +8539,7 @@
         </is>
       </c>
       <c r="B625" t="n">
-        <v>0.07871599999999999</v>
+        <v>0.07919</v>
       </c>
       <c r="C625" t="n">
         <v>0.307065</v>
@@ -8552,7 +8552,7 @@
         </is>
       </c>
       <c r="B626" t="n">
-        <v>0.078904</v>
+        <v>0.079237</v>
       </c>
       <c r="C626" t="n">
         <v>0.304348</v>
@@ -8565,7 +8565,7 @@
         </is>
       </c>
       <c r="B627" t="n">
-        <v>0.07910399999999999</v>
+        <v>0.079359</v>
       </c>
       <c r="C627" t="n">
         <v>0.30163</v>
@@ -8578,7 +8578,7 @@
         </is>
       </c>
       <c r="B628" t="n">
-        <v>0.07917</v>
+        <v>0.08018599999999999</v>
       </c>
       <c r="C628" t="n">
         <v>0.298913</v>
@@ -8591,7 +8591,7 @@
         </is>
       </c>
       <c r="B629" t="n">
-        <v>0.080233</v>
+        <v>0.083731</v>
       </c>
       <c r="C629" t="n">
         <v>0.296196</v>
@@ -8604,7 +8604,7 @@
         </is>
       </c>
       <c r="B630" t="n">
-        <v>0.083747</v>
+        <v>0.084456</v>
       </c>
       <c r="C630" t="n">
         <v>0.293478</v>
@@ -8617,7 +8617,7 @@
         </is>
       </c>
       <c r="B631" t="n">
-        <v>0.084022</v>
+        <v>0.084741</v>
       </c>
       <c r="C631" t="n">
         <v>0.290761</v>
@@ -8630,7 +8630,7 @@
         </is>
       </c>
       <c r="B632" t="n">
-        <v>0.084894</v>
+        <v>0.084929</v>
       </c>
       <c r="C632" t="n">
         <v>0.288043</v>
@@ -8643,7 +8643,7 @@
         </is>
       </c>
       <c r="B633" t="n">
-        <v>0.084939</v>
+        <v>0.085204</v>
       </c>
       <c r="C633" t="n">
         <v>0.285326</v>
@@ -8656,7 +8656,7 @@
         </is>
       </c>
       <c r="B634" t="n">
-        <v>0.08558399999999999</v>
+        <v>0.086066</v>
       </c>
       <c r="C634" t="n">
         <v>0.282609</v>
@@ -8669,7 +8669,7 @@
         </is>
       </c>
       <c r="B635" t="n">
-        <v>0.086018</v>
+        <v>0.086932</v>
       </c>
       <c r="C635" t="n">
         <v>0.279891</v>
@@ -8682,7 +8682,7 @@
         </is>
       </c>
       <c r="B636" t="n">
-        <v>0.08688800000000001</v>
+        <v>0.08724</v>
       </c>
       <c r="C636" t="n">
         <v>0.277174</v>
@@ -8695,7 +8695,7 @@
         </is>
       </c>
       <c r="B637" t="n">
-        <v>0.087052</v>
+        <v>0.087282</v>
       </c>
       <c r="C637" t="n">
         <v>0.274457</v>
@@ -8708,7 +8708,7 @@
         </is>
       </c>
       <c r="B638" t="n">
-        <v>0.087921</v>
+        <v>0.088064</v>
       </c>
       <c r="C638" t="n">
         <v>0.271739</v>
@@ -8721,7 +8721,7 @@
         </is>
       </c>
       <c r="B639" t="n">
-        <v>0.088004</v>
+        <v>0.088202</v>
       </c>
       <c r="C639" t="n">
         <v>0.269022</v>
@@ -8734,7 +8734,7 @@
         </is>
       </c>
       <c r="B640" t="n">
-        <v>0.088063</v>
+        <v>0.088766</v>
       </c>
       <c r="C640" t="n">
         <v>0.266304</v>
@@ -8747,7 +8747,7 @@
         </is>
       </c>
       <c r="B641" t="n">
-        <v>0.08876100000000001</v>
+        <v>0.088933</v>
       </c>
       <c r="C641" t="n">
         <v>0.263587</v>
@@ -8760,7 +8760,7 @@
         </is>
       </c>
       <c r="B642" t="n">
-        <v>0.089491</v>
+        <v>0.089474</v>
       </c>
       <c r="C642" t="n">
         <v>0.26087</v>
@@ -8773,7 +8773,7 @@
         </is>
       </c>
       <c r="B643" t="n">
-        <v>0.089549</v>
+        <v>0.089596</v>
       </c>
       <c r="C643" t="n">
         <v>0.258152</v>
@@ -8786,7 +8786,7 @@
         </is>
       </c>
       <c r="B644" t="n">
-        <v>0.090027</v>
+        <v>0.09026099999999999</v>
       </c>
       <c r="C644" t="n">
         <v>0.255435</v>
@@ -8799,7 +8799,7 @@
         </is>
       </c>
       <c r="B645" t="n">
-        <v>0.09027499999999999</v>
+        <v>0.09234199999999999</v>
       </c>
       <c r="C645" t="n">
         <v>0.252717</v>
@@ -8812,7 +8812,7 @@
         </is>
       </c>
       <c r="B646" t="n">
-        <v>0.091874</v>
+        <v>0.092525</v>
       </c>
       <c r="C646" t="n">
         <v>0.25</v>
@@ -8825,7 +8825,7 @@
         </is>
       </c>
       <c r="B647" t="n">
-        <v>0.092524</v>
+        <v>0.09282</v>
       </c>
       <c r="C647" t="n">
         <v>0.247283</v>
@@ -8838,7 +8838,7 @@
         </is>
       </c>
       <c r="B648" t="n">
-        <v>0.092546</v>
+        <v>0.093002</v>
       </c>
       <c r="C648" t="n">
         <v>0.244565</v>
@@ -8851,7 +8851,7 @@
         </is>
       </c>
       <c r="B649" t="n">
-        <v>0.092748</v>
+        <v>0.093648</v>
       </c>
       <c r="C649" t="n">
         <v>0.241848</v>
@@ -8864,7 +8864,7 @@
         </is>
       </c>
       <c r="B650" t="n">
-        <v>0.093891</v>
+        <v>0.094246</v>
       </c>
       <c r="C650" t="n">
         <v>0.23913</v>
@@ -8877,7 +8877,7 @@
         </is>
       </c>
       <c r="B651" t="n">
-        <v>0.09418600000000001</v>
+        <v>0.094421</v>
       </c>
       <c r="C651" t="n">
         <v>0.236413</v>
@@ -8890,7 +8890,7 @@
         </is>
       </c>
       <c r="B652" t="n">
-        <v>0.098229</v>
+        <v>0.09755900000000001</v>
       </c>
       <c r="C652" t="n">
         <v>0.233696</v>
@@ -8903,7 +8903,7 @@
         </is>
       </c>
       <c r="B653" t="n">
-        <v>0.098398</v>
+        <v>0.09819600000000001</v>
       </c>
       <c r="C653" t="n">
         <v>0.230978</v>
@@ -8916,7 +8916,7 @@
         </is>
       </c>
       <c r="B654" t="n">
-        <v>0.098486</v>
+        <v>0.098625</v>
       </c>
       <c r="C654" t="n">
         <v>0.228261</v>
@@ -8929,7 +8929,7 @@
         </is>
       </c>
       <c r="B655" t="n">
-        <v>0.09854499999999999</v>
+        <v>0.098772</v>
       </c>
       <c r="C655" t="n">
         <v>0.225543</v>
@@ -8942,7 +8942,7 @@
         </is>
       </c>
       <c r="B656" t="n">
-        <v>0.09925100000000001</v>
+        <v>0.099076</v>
       </c>
       <c r="C656" t="n">
         <v>0.222826</v>
@@ -8955,7 +8955,7 @@
         </is>
       </c>
       <c r="B657" t="n">
-        <v>0.100148</v>
+        <v>0.100186</v>
       </c>
       <c r="C657" t="n">
         <v>0.220109</v>
@@ -8968,7 +8968,7 @@
         </is>
       </c>
       <c r="B658" t="n">
-        <v>0.100708</v>
+        <v>0.100249</v>
       </c>
       <c r="C658" t="n">
         <v>0.217391</v>
@@ -8981,7 +8981,7 @@
         </is>
       </c>
       <c r="B659" t="n">
-        <v>0.100955</v>
+        <v>0.1011</v>
       </c>
       <c r="C659" t="n">
         <v>0.214674</v>
@@ -8994,7 +8994,7 @@
         </is>
       </c>
       <c r="B660" t="n">
-        <v>0.101141</v>
+        <v>0.101225</v>
       </c>
       <c r="C660" t="n">
         <v>0.211957</v>
@@ -9007,7 +9007,7 @@
         </is>
       </c>
       <c r="B661" t="n">
-        <v>0.101172</v>
+        <v>0.101485</v>
       </c>
       <c r="C661" t="n">
         <v>0.209239</v>
@@ -9020,7 +9020,7 @@
         </is>
       </c>
       <c r="B662" t="n">
-        <v>0.101465</v>
+        <v>0.101676</v>
       </c>
       <c r="C662" t="n">
         <v>0.206522</v>
@@ -9033,7 +9033,7 @@
         </is>
       </c>
       <c r="B663" t="n">
-        <v>0.101628</v>
+        <v>0.102353</v>
       </c>
       <c r="C663" t="n">
         <v>0.203804</v>
@@ -9046,7 +9046,7 @@
         </is>
       </c>
       <c r="B664" t="n">
-        <v>0.102175</v>
+        <v>0.10351</v>
       </c>
       <c r="C664" t="n">
         <v>0.201087</v>
@@ -9059,7 +9059,7 @@
         </is>
       </c>
       <c r="B665" t="n">
-        <v>0.103661</v>
+        <v>0.104284</v>
       </c>
       <c r="C665" t="n">
         <v>0.19837</v>
@@ -9072,7 +9072,7 @@
         </is>
       </c>
       <c r="B666" t="n">
-        <v>0.104685</v>
+        <v>0.105536</v>
       </c>
       <c r="C666" t="n">
         <v>0.195652</v>
@@ -9085,7 +9085,7 @@
         </is>
       </c>
       <c r="B667" t="n">
-        <v>0.105134</v>
+        <v>0.107699</v>
       </c>
       <c r="C667" t="n">
         <v>0.192935</v>
@@ -9098,7 +9098,7 @@
         </is>
       </c>
       <c r="B668" t="n">
-        <v>0.107492</v>
+        <v>0.108823</v>
       </c>
       <c r="C668" t="n">
         <v>0.190217</v>
@@ -9111,7 +9111,7 @@
         </is>
       </c>
       <c r="B669" t="n">
-        <v>0.108731</v>
+        <v>0.109819</v>
       </c>
       <c r="C669" t="n">
         <v>0.1875</v>
@@ -9124,7 +9124,7 @@
         </is>
       </c>
       <c r="B670" t="n">
-        <v>0.109892</v>
+        <v>0.110167</v>
       </c>
       <c r="C670" t="n">
         <v>0.184783</v>
@@ -9137,7 +9137,7 @@
         </is>
       </c>
       <c r="B671" t="n">
-        <v>0.110249</v>
+        <v>0.111317</v>
       </c>
       <c r="C671" t="n">
         <v>0.182065</v>
@@ -9150,7 +9150,7 @@
         </is>
       </c>
       <c r="B672" t="n">
-        <v>0.111221</v>
+        <v>0.112096</v>
       </c>
       <c r="C672" t="n">
         <v>0.179348</v>
@@ -9163,7 +9163,7 @@
         </is>
       </c>
       <c r="B673" t="n">
-        <v>0.111884</v>
+        <v>0.112101</v>
       </c>
       <c r="C673" t="n">
         <v>0.17663</v>
@@ -9176,7 +9176,7 @@
         </is>
       </c>
       <c r="B674" t="n">
-        <v>0.112312</v>
+        <v>0.115999</v>
       </c>
       <c r="C674" t="n">
         <v>0.173913</v>
@@ -9189,7 +9189,7 @@
         </is>
       </c>
       <c r="B675" t="n">
-        <v>0.115447</v>
+        <v>0.118198</v>
       </c>
       <c r="C675" t="n">
         <v>0.171196</v>
@@ -9202,7 +9202,7 @@
         </is>
       </c>
       <c r="B676" t="n">
-        <v>0.118503</v>
+        <v>0.120197</v>
       </c>
       <c r="C676" t="n">
         <v>0.168478</v>
@@ -9215,7 +9215,7 @@
         </is>
       </c>
       <c r="B677" t="n">
-        <v>0.120042</v>
+        <v>0.120202</v>
       </c>
       <c r="C677" t="n">
         <v>0.165761</v>
@@ -9228,7 +9228,7 @@
         </is>
       </c>
       <c r="B678" t="n">
-        <v>0.120274</v>
+        <v>0.121806</v>
       </c>
       <c r="C678" t="n">
         <v>0.163043</v>
@@ -9241,7 +9241,7 @@
         </is>
       </c>
       <c r="B679" t="n">
-        <v>0.121653</v>
+        <v>0.12243</v>
       </c>
       <c r="C679" t="n">
         <v>0.160326</v>
@@ -9254,7 +9254,7 @@
         </is>
       </c>
       <c r="B680" t="n">
-        <v>0.122844</v>
+        <v>0.124033</v>
       </c>
       <c r="C680" t="n">
         <v>0.157609</v>
@@ -9267,7 +9267,7 @@
         </is>
       </c>
       <c r="B681" t="n">
-        <v>0.124478</v>
+        <v>0.125088</v>
       </c>
       <c r="C681" t="n">
         <v>0.154891</v>
@@ -9280,7 +9280,7 @@
         </is>
       </c>
       <c r="B682" t="n">
-        <v>0.125298</v>
+        <v>0.12531</v>
       </c>
       <c r="C682" t="n">
         <v>0.152174</v>
@@ -9293,7 +9293,7 @@
         </is>
       </c>
       <c r="B683" t="n">
-        <v>0.126769</v>
+        <v>0.12647</v>
       </c>
       <c r="C683" t="n">
         <v>0.149457</v>
@@ -9306,7 +9306,7 @@
         </is>
       </c>
       <c r="B684" t="n">
-        <v>0.127751</v>
+        <v>0.127559</v>
       </c>
       <c r="C684" t="n">
         <v>0.146739</v>
@@ -9319,7 +9319,7 @@
         </is>
       </c>
       <c r="B685" t="n">
-        <v>0.129674</v>
+        <v>0.129776</v>
       </c>
       <c r="C685" t="n">
         <v>0.144022</v>
@@ -9332,7 +9332,7 @@
         </is>
       </c>
       <c r="B686" t="n">
-        <v>0.130566</v>
+        <v>0.130653</v>
       </c>
       <c r="C686" t="n">
         <v>0.141304</v>
@@ -9345,7 +9345,7 @@
         </is>
       </c>
       <c r="B687" t="n">
-        <v>0.130831</v>
+        <v>0.131226</v>
       </c>
       <c r="C687" t="n">
         <v>0.138587</v>
@@ -9358,7 +9358,7 @@
         </is>
       </c>
       <c r="B688" t="n">
-        <v>0.131416</v>
+        <v>0.131856</v>
       </c>
       <c r="C688" t="n">
         <v>0.13587</v>
@@ -9371,7 +9371,7 @@
         </is>
       </c>
       <c r="B689" t="n">
-        <v>0.132641</v>
+        <v>0.132478</v>
       </c>
       <c r="C689" t="n">
         <v>0.133152</v>
@@ -9384,7 +9384,7 @@
         </is>
       </c>
       <c r="B690" t="n">
-        <v>0.132662</v>
+        <v>0.132959</v>
       </c>
       <c r="C690" t="n">
         <v>0.130435</v>
@@ -9397,7 +9397,7 @@
         </is>
       </c>
       <c r="B691" t="n">
-        <v>0.13297</v>
+        <v>0.133496</v>
       </c>
       <c r="C691" t="n">
         <v>0.127717</v>
@@ -9410,7 +9410,7 @@
         </is>
       </c>
       <c r="B692" t="n">
-        <v>0.134626</v>
+        <v>0.133583</v>
       </c>
       <c r="C692" t="n">
         <v>0.125</v>
@@ -9423,7 +9423,7 @@
         </is>
       </c>
       <c r="B693" t="n">
-        <v>0.134864</v>
+        <v>0.13363</v>
       </c>
       <c r="C693" t="n">
         <v>0.122283</v>
@@ -9436,7 +9436,7 @@
         </is>
       </c>
       <c r="B694" t="n">
-        <v>0.136036</v>
+        <v>0.136068</v>
       </c>
       <c r="C694" t="n">
         <v>0.119565</v>
@@ -9449,7 +9449,7 @@
         </is>
       </c>
       <c r="B695" t="n">
-        <v>0.138023</v>
+        <v>0.13789</v>
       </c>
       <c r="C695" t="n">
         <v>0.116848</v>
@@ -9462,7 +9462,7 @@
         </is>
       </c>
       <c r="B696" t="n">
-        <v>0.139471</v>
+        <v>0.13997</v>
       </c>
       <c r="C696" t="n">
         <v>0.11413</v>
@@ -9475,7 +9475,7 @@
         </is>
       </c>
       <c r="B697" t="n">
-        <v>0.139928</v>
+        <v>0.140606</v>
       </c>
       <c r="C697" t="n">
         <v>0.111413</v>
@@ -9488,7 +9488,7 @@
         </is>
       </c>
       <c r="B698" t="n">
-        <v>0.141362</v>
+        <v>0.141265</v>
       </c>
       <c r="C698" t="n">
         <v>0.108696</v>
@@ -9501,7 +9501,7 @@
         </is>
       </c>
       <c r="B699" t="n">
-        <v>0.141618</v>
+        <v>0.141345</v>
       </c>
       <c r="C699" t="n">
         <v>0.105978</v>
@@ -9514,7 +9514,7 @@
         </is>
       </c>
       <c r="B700" t="n">
-        <v>0.141784</v>
+        <v>0.141819</v>
       </c>
       <c r="C700" t="n">
         <v>0.103261</v>
@@ -9527,7 +9527,7 @@
         </is>
       </c>
       <c r="B701" t="n">
-        <v>0.142535</v>
+        <v>0.142567</v>
       </c>
       <c r="C701" t="n">
         <v>0.100543</v>
@@ -9540,7 +9540,7 @@
         </is>
       </c>
       <c r="B702" t="n">
-        <v>0.143625</v>
+        <v>0.142731</v>
       </c>
       <c r="C702" t="n">
         <v>0.097826</v>
@@ -9553,7 +9553,7 @@
         </is>
       </c>
       <c r="B703" t="n">
-        <v>0.144243</v>
+        <v>0.144027</v>
       </c>
       <c r="C703" t="n">
         <v>0.095109</v>
@@ -9566,7 +9566,7 @@
         </is>
       </c>
       <c r="B704" t="n">
-        <v>0.153464</v>
+        <v>0.153499</v>
       </c>
       <c r="C704" t="n">
         <v>0.092391</v>
@@ -9579,7 +9579,7 @@
         </is>
       </c>
       <c r="B705" t="n">
-        <v>0.154536</v>
+        <v>0.154418</v>
       </c>
       <c r="C705" t="n">
         <v>0.089674</v>
@@ -9592,7 +9592,7 @@
         </is>
       </c>
       <c r="B706" t="n">
-        <v>0.155832</v>
+        <v>0.156262</v>
       </c>
       <c r="C706" t="n">
         <v>0.08695700000000001</v>
@@ -9605,7 +9605,7 @@
         </is>
       </c>
       <c r="B707" t="n">
-        <v>0.15842</v>
+        <v>0.158159</v>
       </c>
       <c r="C707" t="n">
         <v>0.08423899999999999</v>
@@ -9618,7 +9618,7 @@
         </is>
       </c>
       <c r="B708" t="n">
-        <v>0.161951</v>
+        <v>0.161872</v>
       </c>
       <c r="C708" t="n">
         <v>0.081522</v>
@@ -9631,7 +9631,7 @@
         </is>
       </c>
       <c r="B709" t="n">
-        <v>0.164151</v>
+        <v>0.16385</v>
       </c>
       <c r="C709" t="n">
         <v>0.078804</v>
@@ -9644,7 +9644,7 @@
         </is>
       </c>
       <c r="B710" t="n">
-        <v>0.16442</v>
+        <v>0.165011</v>
       </c>
       <c r="C710" t="n">
         <v>0.076087</v>
@@ -9657,7 +9657,7 @@
         </is>
       </c>
       <c r="B711" t="n">
-        <v>0.169395</v>
+        <v>0.169539</v>
       </c>
       <c r="C711" t="n">
         <v>0.07337</v>
@@ -9670,7 +9670,7 @@
         </is>
       </c>
       <c r="B712" t="n">
-        <v>0.171096</v>
+        <v>0.171543</v>
       </c>
       <c r="C712" t="n">
         <v>0.07065200000000001</v>
@@ -9683,7 +9683,7 @@
         </is>
       </c>
       <c r="B713" t="n">
-        <v>0.178615</v>
+        <v>0.178916</v>
       </c>
       <c r="C713" t="n">
         <v>0.067935</v>
@@ -9696,7 +9696,7 @@
         </is>
       </c>
       <c r="B714" t="n">
-        <v>0.179498</v>
+        <v>0.179998</v>
       </c>
       <c r="C714" t="n">
         <v>0.065217</v>
@@ -9709,7 +9709,7 @@
         </is>
       </c>
       <c r="B715" t="n">
-        <v>0.179697</v>
+        <v>0.180114</v>
       </c>
       <c r="C715" t="n">
         <v>0.0625</v>
@@ -9722,7 +9722,7 @@
         </is>
       </c>
       <c r="B716" t="n">
-        <v>0.182582</v>
+        <v>0.183384</v>
       </c>
       <c r="C716" t="n">
         <v>0.059783</v>
@@ -9735,7 +9735,7 @@
         </is>
       </c>
       <c r="B717" t="n">
-        <v>0.184452</v>
+        <v>0.184006</v>
       </c>
       <c r="C717" t="n">
         <v>0.057065</v>
@@ -9748,7 +9748,7 @@
         </is>
       </c>
       <c r="B718" t="n">
-        <v>0.185465</v>
+        <v>0.186247</v>
       </c>
       <c r="C718" t="n">
         <v>0.054348</v>
@@ -9761,7 +9761,7 @@
         </is>
       </c>
       <c r="B719" t="n">
-        <v>0.187602</v>
+        <v>0.188392</v>
       </c>
       <c r="C719" t="n">
         <v>0.05163</v>
@@ -9774,7 +9774,7 @@
         </is>
       </c>
       <c r="B720" t="n">
-        <v>0.194423</v>
+        <v>0.193669</v>
       </c>
       <c r="C720" t="n">
         <v>0.048913</v>
@@ -9787,7 +9787,7 @@
         </is>
       </c>
       <c r="B721" t="n">
-        <v>0.197149</v>
+        <v>0.196407</v>
       </c>
       <c r="C721" t="n">
         <v>0.046196</v>
@@ -9800,7 +9800,7 @@
         </is>
       </c>
       <c r="B722" t="n">
-        <v>0.197429</v>
+        <v>0.198054</v>
       </c>
       <c r="C722" t="n">
         <v>0.043478</v>
@@ -9813,7 +9813,7 @@
         </is>
       </c>
       <c r="B723" t="n">
-        <v>0.208681</v>
+        <v>0.208599</v>
       </c>
       <c r="C723" t="n">
         <v>0.040761</v>
@@ -9826,7 +9826,7 @@
         </is>
       </c>
       <c r="B724" t="n">
-        <v>0.210734</v>
+        <v>0.209307</v>
       </c>
       <c r="C724" t="n">
         <v>0.038043</v>
@@ -9839,7 +9839,7 @@
         </is>
       </c>
       <c r="B725" t="n">
-        <v>0.210786</v>
+        <v>0.211597</v>
       </c>
       <c r="C725" t="n">
         <v>0.035326</v>
@@ -9852,7 +9852,7 @@
         </is>
       </c>
       <c r="B726" t="n">
-        <v>0.228963</v>
+        <v>0.22925</v>
       </c>
       <c r="C726" t="n">
         <v>0.032609</v>
@@ -9865,7 +9865,7 @@
         </is>
       </c>
       <c r="B727" t="n">
-        <v>0.23467</v>
+        <v>0.235561</v>
       </c>
       <c r="C727" t="n">
         <v>0.029891</v>
@@ -9878,7 +9878,7 @@
         </is>
       </c>
       <c r="B728" t="n">
-        <v>0.243604</v>
+        <v>0.244778</v>
       </c>
       <c r="C728" t="n">
         <v>0.027174</v>
@@ -9891,7 +9891,7 @@
         </is>
       </c>
       <c r="B729" t="n">
-        <v>0.24397</v>
+        <v>0.24524</v>
       </c>
       <c r="C729" t="n">
         <v>0.024457</v>
@@ -9904,7 +9904,7 @@
         </is>
       </c>
       <c r="B730" t="n">
-        <v>0.246569</v>
+        <v>0.247761</v>
       </c>
       <c r="C730" t="n">
         <v>0.021739</v>
@@ -9917,7 +9917,7 @@
         </is>
       </c>
       <c r="B731" t="n">
-        <v>0.257932</v>
+        <v>0.256726</v>
       </c>
       <c r="C731" t="n">
         <v>0.019022</v>
@@ -9930,7 +9930,7 @@
         </is>
       </c>
       <c r="B732" t="n">
-        <v>0.264682</v>
+        <v>0.265554</v>
       </c>
       <c r="C732" t="n">
         <v>0.016304</v>
@@ -9943,7 +9943,7 @@
         </is>
       </c>
       <c r="B733" t="n">
-        <v>0.272675</v>
+        <v>0.273383</v>
       </c>
       <c r="C733" t="n">
         <v>0.013587</v>
@@ -9956,7 +9956,7 @@
         </is>
       </c>
       <c r="B734" t="n">
-        <v>0.295159</v>
+        <v>0.295054</v>
       </c>
       <c r="C734" t="n">
         <v>0.01087</v>
@@ -9969,7 +9969,7 @@
         </is>
       </c>
       <c r="B735" t="n">
-        <v>0.311792</v>
+        <v>0.3132</v>
       </c>
       <c r="C735" t="n">
         <v>0.008152</v>
@@ -9982,7 +9982,7 @@
         </is>
       </c>
       <c r="B736" t="n">
-        <v>0.34116</v>
+        <v>0.341841</v>
       </c>
       <c r="C736" t="n">
         <v>0.005435</v>
@@ -9995,7 +9995,7 @@
         </is>
       </c>
       <c r="B737" t="n">
-        <v>0.487269</v>
+        <v>0.488786</v>
       </c>
       <c r="C737" t="n">
         <v>0.002717</v>

--- a/vignettes/vignette-1/tail_exceedance_plot_data.xlsx
+++ b/vignettes/vignette-1/tail_exceedance_plot_data.xlsx
@@ -5679,7 +5679,7 @@
         </is>
       </c>
       <c r="B405" t="n">
-        <v>0.001846</v>
+        <v>0.001845</v>
       </c>
       <c r="C405" t="n">
         <v>0.987437</v>
@@ -5692,7 +5692,7 @@
         </is>
       </c>
       <c r="B406" t="n">
-        <v>0.002018</v>
+        <v>0.00202</v>
       </c>
       <c r="C406" t="n">
         <v>0.9849250000000001</v>
@@ -5705,7 +5705,7 @@
         </is>
       </c>
       <c r="B407" t="n">
-        <v>0.002228</v>
+        <v>0.002227</v>
       </c>
       <c r="C407" t="n">
         <v>0.982412</v>
@@ -5731,7 +5731,7 @@
         </is>
       </c>
       <c r="B409" t="n">
-        <v>0.002517</v>
+        <v>0.002518</v>
       </c>
       <c r="C409" t="n">
         <v>0.977387</v>
@@ -5757,7 +5757,7 @@
         </is>
       </c>
       <c r="B411" t="n">
-        <v>0.002745</v>
+        <v>0.002749</v>
       </c>
       <c r="C411" t="n">
         <v>0.9723619999999999</v>
@@ -5770,7 +5770,7 @@
         </is>
       </c>
       <c r="B412" t="n">
-        <v>0.002889</v>
+        <v>0.002894</v>
       </c>
       <c r="C412" t="n">
         <v>0.969849</v>
@@ -5796,7 +5796,7 @@
         </is>
       </c>
       <c r="B414" t="n">
-        <v>0.003345</v>
+        <v>0.003346</v>
       </c>
       <c r="C414" t="n">
         <v>0.964824</v>
@@ -5809,7 +5809,7 @@
         </is>
       </c>
       <c r="B415" t="n">
-        <v>0.003468</v>
+        <v>0.003467</v>
       </c>
       <c r="C415" t="n">
         <v>0.9623119999999999</v>
@@ -5822,7 +5822,7 @@
         </is>
       </c>
       <c r="B416" t="n">
-        <v>0.003888</v>
+        <v>0.00389</v>
       </c>
       <c r="C416" t="n">
         <v>0.959799</v>
@@ -5835,7 +5835,7 @@
         </is>
       </c>
       <c r="B417" t="n">
-        <v>0.004531</v>
+        <v>0.00453</v>
       </c>
       <c r="C417" t="n">
         <v>0.957286</v>
@@ -5848,7 +5848,7 @@
         </is>
       </c>
       <c r="B418" t="n">
-        <v>0.004608</v>
+        <v>0.004607</v>
       </c>
       <c r="C418" t="n">
         <v>0.954774</v>
@@ -5861,7 +5861,7 @@
         </is>
       </c>
       <c r="B419" t="n">
-        <v>0.004828</v>
+        <v>0.004829</v>
       </c>
       <c r="C419" t="n">
         <v>0.952261</v>
@@ -5874,7 +5874,7 @@
         </is>
       </c>
       <c r="B420" t="n">
-        <v>0.005</v>
+        <v>0.005012</v>
       </c>
       <c r="C420" t="n">
         <v>0.949749</v>
@@ -5887,7 +5887,7 @@
         </is>
       </c>
       <c r="B421" t="n">
-        <v>0.005102</v>
+        <v>0.005101</v>
       </c>
       <c r="C421" t="n">
         <v>0.947236</v>
@@ -5900,7 +5900,7 @@
         </is>
       </c>
       <c r="B422" t="n">
-        <v>0.005116</v>
+        <v>0.005123</v>
       </c>
       <c r="C422" t="n">
         <v>0.944724</v>
@@ -5913,7 +5913,7 @@
         </is>
       </c>
       <c r="B423" t="n">
-        <v>0.005235</v>
+        <v>0.005234</v>
       </c>
       <c r="C423" t="n">
         <v>0.942211</v>
@@ -5926,7 +5926,7 @@
         </is>
       </c>
       <c r="B424" t="n">
-        <v>0.005542</v>
+        <v>0.005545</v>
       </c>
       <c r="C424" t="n">
         <v>0.939698</v>
@@ -5939,7 +5939,7 @@
         </is>
       </c>
       <c r="B425" t="n">
-        <v>0.005577</v>
+        <v>0.005587</v>
       </c>
       <c r="C425" t="n">
         <v>0.937186</v>
@@ -5965,7 +5965,7 @@
         </is>
       </c>
       <c r="B427" t="n">
-        <v>0.005807</v>
+        <v>0.005805</v>
       </c>
       <c r="C427" t="n">
         <v>0.932161</v>
@@ -5978,7 +5978,7 @@
         </is>
       </c>
       <c r="B428" t="n">
-        <v>0.005978</v>
+        <v>0.005982</v>
       </c>
       <c r="C428" t="n">
         <v>0.929648</v>
@@ -5991,7 +5991,7 @@
         </is>
       </c>
       <c r="B429" t="n">
-        <v>0.005983</v>
+        <v>0.005989</v>
       </c>
       <c r="C429" t="n">
         <v>0.927136</v>
@@ -6004,7 +6004,7 @@
         </is>
       </c>
       <c r="B430" t="n">
-        <v>0.006566</v>
+        <v>0.006564</v>
       </c>
       <c r="C430" t="n">
         <v>0.924623</v>
@@ -6017,7 +6017,7 @@
         </is>
       </c>
       <c r="B431" t="n">
-        <v>0.006866</v>
+        <v>0.006864</v>
       </c>
       <c r="C431" t="n">
         <v>0.922111</v>
@@ -6030,7 +6030,7 @@
         </is>
       </c>
       <c r="B432" t="n">
-        <v>0.007427</v>
+        <v>0.007425</v>
       </c>
       <c r="C432" t="n">
         <v>0.919598</v>
@@ -6043,7 +6043,7 @@
         </is>
       </c>
       <c r="B433" t="n">
-        <v>0.008344000000000001</v>
+        <v>0.008342</v>
       </c>
       <c r="C433" t="n">
         <v>0.917085</v>
@@ -6056,7 +6056,7 @@
         </is>
       </c>
       <c r="B434" t="n">
-        <v>0.008581999999999999</v>
+        <v>0.008597</v>
       </c>
       <c r="C434" t="n">
         <v>0.914573</v>
@@ -6069,7 +6069,7 @@
         </is>
       </c>
       <c r="B435" t="n">
-        <v>0.008765999999999999</v>
+        <v>0.008770999999999999</v>
       </c>
       <c r="C435" t="n">
         <v>0.91206</v>
@@ -6082,7 +6082,7 @@
         </is>
       </c>
       <c r="B436" t="n">
-        <v>0.008921</v>
+        <v>0.00894</v>
       </c>
       <c r="C436" t="n">
         <v>0.909548</v>
@@ -6095,7 +6095,7 @@
         </is>
       </c>
       <c r="B437" t="n">
-        <v>0.008945</v>
+        <v>0.008942</v>
       </c>
       <c r="C437" t="n">
         <v>0.907035</v>
@@ -6108,7 +6108,7 @@
         </is>
       </c>
       <c r="B438" t="n">
-        <v>0.009116000000000001</v>
+        <v>0.00912</v>
       </c>
       <c r="C438" t="n">
         <v>0.904523</v>
@@ -6121,7 +6121,7 @@
         </is>
       </c>
       <c r="B439" t="n">
-        <v>0.009168000000000001</v>
+        <v>0.009166000000000001</v>
       </c>
       <c r="C439" t="n">
         <v>0.90201</v>
@@ -6134,7 +6134,7 @@
         </is>
       </c>
       <c r="B440" t="n">
-        <v>0.009209</v>
+        <v>0.009220000000000001</v>
       </c>
       <c r="C440" t="n">
         <v>0.899497</v>
@@ -6147,7 +6147,7 @@
         </is>
       </c>
       <c r="B441" t="n">
-        <v>0.009480000000000001</v>
+        <v>0.009479</v>
       </c>
       <c r="C441" t="n">
         <v>0.896985</v>
@@ -6160,7 +6160,7 @@
         </is>
       </c>
       <c r="B442" t="n">
-        <v>0.009611</v>
+        <v>0.009617000000000001</v>
       </c>
       <c r="C442" t="n">
         <v>0.894472</v>
@@ -6173,7 +6173,7 @@
         </is>
       </c>
       <c r="B443" t="n">
-        <v>0.009792</v>
+        <v>0.009793</v>
       </c>
       <c r="C443" t="n">
         <v>0.89196</v>
@@ -6186,7 +6186,7 @@
         </is>
       </c>
       <c r="B444" t="n">
-        <v>0.009988</v>
+        <v>0.01</v>
       </c>
       <c r="C444" t="n">
         <v>0.889447</v>
@@ -6199,7 +6199,7 @@
         </is>
       </c>
       <c r="B445" t="n">
-        <v>0.010736</v>
+        <v>0.01076</v>
       </c>
       <c r="C445" t="n">
         <v>0.886935</v>
@@ -6212,7 +6212,7 @@
         </is>
       </c>
       <c r="B446" t="n">
-        <v>0.010855</v>
+        <v>0.010857</v>
       </c>
       <c r="C446" t="n">
         <v>0.884422</v>
@@ -6225,7 +6225,7 @@
         </is>
       </c>
       <c r="B447" t="n">
-        <v>0.010898</v>
+        <v>0.010896</v>
       </c>
       <c r="C447" t="n">
         <v>0.88191</v>
@@ -6238,7 +6238,7 @@
         </is>
       </c>
       <c r="B448" t="n">
-        <v>0.01109</v>
+        <v>0.011095</v>
       </c>
       <c r="C448" t="n">
         <v>0.879397</v>
@@ -6264,7 +6264,7 @@
         </is>
       </c>
       <c r="B450" t="n">
-        <v>0.011253</v>
+        <v>0.01125</v>
       </c>
       <c r="C450" t="n">
         <v>0.874372</v>
@@ -6277,7 +6277,7 @@
         </is>
       </c>
       <c r="B451" t="n">
-        <v>0.011342</v>
+        <v>0.011354</v>
       </c>
       <c r="C451" t="n">
         <v>0.8718590000000001</v>
@@ -6290,7 +6290,7 @@
         </is>
       </c>
       <c r="B452" t="n">
-        <v>0.011541</v>
+        <v>0.011539</v>
       </c>
       <c r="C452" t="n">
         <v>0.869347</v>
@@ -6303,7 +6303,7 @@
         </is>
       </c>
       <c r="B453" t="n">
-        <v>0.011684</v>
+        <v>0.011696</v>
       </c>
       <c r="C453" t="n">
         <v>0.866834</v>
@@ -6316,7 +6316,7 @@
         </is>
       </c>
       <c r="B454" t="n">
-        <v>0.012034</v>
+        <v>0.012035</v>
       </c>
       <c r="C454" t="n">
         <v>0.864322</v>
@@ -6329,7 +6329,7 @@
         </is>
       </c>
       <c r="B455" t="n">
-        <v>0.012333</v>
+        <v>0.012331</v>
       </c>
       <c r="C455" t="n">
         <v>0.861809</v>
@@ -6342,7 +6342,7 @@
         </is>
       </c>
       <c r="B456" t="n">
-        <v>0.012399</v>
+        <v>0.012402</v>
       </c>
       <c r="C456" t="n">
         <v>0.8592959999999999</v>
@@ -6355,7 +6355,7 @@
         </is>
       </c>
       <c r="B457" t="n">
-        <v>0.012556</v>
+        <v>0.012555</v>
       </c>
       <c r="C457" t="n">
         <v>0.856784</v>
@@ -6381,7 +6381,7 @@
         </is>
       </c>
       <c r="B459" t="n">
-        <v>0.013068</v>
+        <v>0.013066</v>
       </c>
       <c r="C459" t="n">
         <v>0.851759</v>
@@ -6394,7 +6394,7 @@
         </is>
       </c>
       <c r="B460" t="n">
-        <v>0.013135</v>
+        <v>0.013145</v>
       </c>
       <c r="C460" t="n">
         <v>0.8492459999999999</v>
@@ -6407,7 +6407,7 @@
         </is>
       </c>
       <c r="B461" t="n">
-        <v>0.013141</v>
+        <v>0.013169</v>
       </c>
       <c r="C461" t="n">
         <v>0.846734</v>
@@ -6420,7 +6420,7 @@
         </is>
       </c>
       <c r="B462" t="n">
-        <v>0.013573</v>
+        <v>0.01357</v>
       </c>
       <c r="C462" t="n">
         <v>0.844221</v>
@@ -6433,7 +6433,7 @@
         </is>
       </c>
       <c r="B463" t="n">
-        <v>0.013727</v>
+        <v>0.013723</v>
       </c>
       <c r="C463" t="n">
         <v>0.841709</v>
@@ -6446,7 +6446,7 @@
         </is>
       </c>
       <c r="B464" t="n">
-        <v>0.014168</v>
+        <v>0.014166</v>
       </c>
       <c r="C464" t="n">
         <v>0.8391960000000001</v>
@@ -6459,7 +6459,7 @@
         </is>
       </c>
       <c r="B465" t="n">
-        <v>0.014321</v>
+        <v>0.014317</v>
       </c>
       <c r="C465" t="n">
         <v>0.836683</v>
@@ -6472,7 +6472,7 @@
         </is>
       </c>
       <c r="B466" t="n">
-        <v>0.01437</v>
+        <v>0.014389</v>
       </c>
       <c r="C466" t="n">
         <v>0.834171</v>
@@ -6485,7 +6485,7 @@
         </is>
       </c>
       <c r="B467" t="n">
-        <v>0.014393</v>
+        <v>0.014396</v>
       </c>
       <c r="C467" t="n">
         <v>0.831658</v>
@@ -6498,7 +6498,7 @@
         </is>
       </c>
       <c r="B468" t="n">
-        <v>0.014414</v>
+        <v>0.014432</v>
       </c>
       <c r="C468" t="n">
         <v>0.829146</v>
@@ -6511,7 +6511,7 @@
         </is>
       </c>
       <c r="B469" t="n">
-        <v>0.014568</v>
+        <v>0.014566</v>
       </c>
       <c r="C469" t="n">
         <v>0.826633</v>
@@ -6524,7 +6524,7 @@
         </is>
       </c>
       <c r="B470" t="n">
-        <v>0.01491</v>
+        <v>0.014938</v>
       </c>
       <c r="C470" t="n">
         <v>0.824121</v>
@@ -6550,7 +6550,7 @@
         </is>
       </c>
       <c r="B472" t="n">
-        <v>0.015121</v>
+        <v>0.015124</v>
       </c>
       <c r="C472" t="n">
         <v>0.819095</v>
@@ -6563,7 +6563,7 @@
         </is>
       </c>
       <c r="B473" t="n">
-        <v>0.015169</v>
+        <v>0.015189</v>
       </c>
       <c r="C473" t="n">
         <v>0.8165829999999999</v>
@@ -6576,7 +6576,7 @@
         </is>
       </c>
       <c r="B474" t="n">
-        <v>0.015579</v>
+        <v>0.01558</v>
       </c>
       <c r="C474" t="n">
         <v>0.81407</v>
@@ -6589,7 +6589,7 @@
         </is>
       </c>
       <c r="B475" t="n">
-        <v>0.015727</v>
+        <v>0.015734</v>
       </c>
       <c r="C475" t="n">
         <v>0.811558</v>
@@ -6615,7 +6615,7 @@
         </is>
       </c>
       <c r="B477" t="n">
-        <v>0.016642</v>
+        <v>0.016638</v>
       </c>
       <c r="C477" t="n">
         <v>0.8065330000000001</v>
@@ -6628,7 +6628,7 @@
         </is>
       </c>
       <c r="B478" t="n">
-        <v>0.016668</v>
+        <v>0.01669</v>
       </c>
       <c r="C478" t="n">
         <v>0.80402</v>
@@ -6641,7 +6641,7 @@
         </is>
       </c>
       <c r="B479" t="n">
-        <v>0.016786</v>
+        <v>0.016794</v>
       </c>
       <c r="C479" t="n">
         <v>0.801508</v>
@@ -6654,7 +6654,7 @@
         </is>
       </c>
       <c r="B480" t="n">
-        <v>0.016994</v>
+        <v>0.016995</v>
       </c>
       <c r="C480" t="n">
         <v>0.798995</v>
@@ -6667,7 +6667,7 @@
         </is>
       </c>
       <c r="B481" t="n">
-        <v>0.017065</v>
+        <v>0.017078</v>
       </c>
       <c r="C481" t="n">
         <v>0.796482</v>
@@ -6680,7 +6680,7 @@
         </is>
       </c>
       <c r="B482" t="n">
-        <v>0.01735</v>
+        <v>0.017368</v>
       </c>
       <c r="C482" t="n">
         <v>0.79397</v>
@@ -6693,7 +6693,7 @@
         </is>
       </c>
       <c r="B483" t="n">
-        <v>0.017682</v>
+        <v>0.017679</v>
       </c>
       <c r="C483" t="n">
         <v>0.791457</v>
@@ -6706,7 +6706,7 @@
         </is>
       </c>
       <c r="B484" t="n">
-        <v>0.017739</v>
+        <v>0.017736</v>
       </c>
       <c r="C484" t="n">
         <v>0.788945</v>
@@ -6719,7 +6719,7 @@
         </is>
       </c>
       <c r="B485" t="n">
-        <v>0.017965</v>
+        <v>0.017995</v>
       </c>
       <c r="C485" t="n">
         <v>0.786432</v>
@@ -6732,7 +6732,7 @@
         </is>
       </c>
       <c r="B486" t="n">
-        <v>0.017997</v>
+        <v>0.018009</v>
       </c>
       <c r="C486" t="n">
         <v>0.78392</v>
@@ -6745,7 +6745,7 @@
         </is>
       </c>
       <c r="B487" t="n">
-        <v>0.018664</v>
+        <v>0.018682</v>
       </c>
       <c r="C487" t="n">
         <v>0.781407</v>
@@ -6758,7 +6758,7 @@
         </is>
       </c>
       <c r="B488" t="n">
-        <v>0.018763</v>
+        <v>0.018758</v>
       </c>
       <c r="C488" t="n">
         <v>0.778894</v>
@@ -6771,7 +6771,7 @@
         </is>
       </c>
       <c r="B489" t="n">
-        <v>0.018991</v>
+        <v>0.018985</v>
       </c>
       <c r="C489" t="n">
         <v>0.776382</v>
@@ -6784,7 +6784,7 @@
         </is>
       </c>
       <c r="B490" t="n">
-        <v>0.019265</v>
+        <v>0.019261</v>
       </c>
       <c r="C490" t="n">
         <v>0.773869</v>
@@ -6797,7 +6797,7 @@
         </is>
       </c>
       <c r="B491" t="n">
-        <v>0.019384</v>
+        <v>0.01938</v>
       </c>
       <c r="C491" t="n">
         <v>0.771357</v>
@@ -6810,7 +6810,7 @@
         </is>
       </c>
       <c r="B492" t="n">
-        <v>0.019403</v>
+        <v>0.019399</v>
       </c>
       <c r="C492" t="n">
         <v>0.768844</v>
@@ -6823,7 +6823,7 @@
         </is>
       </c>
       <c r="B493" t="n">
-        <v>0.019567</v>
+        <v>0.019565</v>
       </c>
       <c r="C493" t="n">
         <v>0.766332</v>
@@ -6836,7 +6836,7 @@
         </is>
       </c>
       <c r="B494" t="n">
-        <v>0.019647</v>
+        <v>0.019642</v>
       </c>
       <c r="C494" t="n">
         <v>0.763819</v>
@@ -6849,7 +6849,7 @@
         </is>
       </c>
       <c r="B495" t="n">
-        <v>0.019796</v>
+        <v>0.019815</v>
       </c>
       <c r="C495" t="n">
         <v>0.761307</v>
@@ -6862,7 +6862,7 @@
         </is>
       </c>
       <c r="B496" t="n">
-        <v>0.019995</v>
+        <v>0.020003</v>
       </c>
       <c r="C496" t="n">
         <v>0.758794</v>
@@ -6875,7 +6875,7 @@
         </is>
       </c>
       <c r="B497" t="n">
-        <v>0.020219</v>
+        <v>0.020214</v>
       </c>
       <c r="C497" t="n">
         <v>0.756281</v>
@@ -6888,7 +6888,7 @@
         </is>
       </c>
       <c r="B498" t="n">
-        <v>0.020969</v>
+        <v>0.020965</v>
       </c>
       <c r="C498" t="n">
         <v>0.753769</v>
@@ -6901,7 +6901,7 @@
         </is>
       </c>
       <c r="B499" t="n">
-        <v>0.021125</v>
+        <v>0.021134</v>
       </c>
       <c r="C499" t="n">
         <v>0.751256</v>
@@ -6914,7 +6914,7 @@
         </is>
       </c>
       <c r="B500" t="n">
-        <v>0.021422</v>
+        <v>0.021417</v>
       </c>
       <c r="C500" t="n">
         <v>0.748744</v>
@@ -6927,7 +6927,7 @@
         </is>
       </c>
       <c r="B501" t="n">
-        <v>0.021666</v>
+        <v>0.021699</v>
       </c>
       <c r="C501" t="n">
         <v>0.746231</v>
@@ -6940,7 +6940,7 @@
         </is>
       </c>
       <c r="B502" t="n">
-        <v>0.021913</v>
+        <v>0.021923</v>
       </c>
       <c r="C502" t="n">
         <v>0.743719</v>
@@ -6953,7 +6953,7 @@
         </is>
       </c>
       <c r="B503" t="n">
-        <v>0.022087</v>
+        <v>0.022106</v>
       </c>
       <c r="C503" t="n">
         <v>0.741206</v>
@@ -6966,7 +6966,7 @@
         </is>
       </c>
       <c r="B504" t="n">
-        <v>0.022703</v>
+        <v>0.022697</v>
       </c>
       <c r="C504" t="n">
         <v>0.738693</v>
@@ -6979,7 +6979,7 @@
         </is>
       </c>
       <c r="B505" t="n">
-        <v>0.022809</v>
+        <v>0.022876</v>
       </c>
       <c r="C505" t="n">
         <v>0.736181</v>
@@ -6992,7 +6992,7 @@
         </is>
       </c>
       <c r="B506" t="n">
-        <v>0.0229</v>
+        <v>0.022898</v>
       </c>
       <c r="C506" t="n">
         <v>0.733668</v>
@@ -7005,7 +7005,7 @@
         </is>
       </c>
       <c r="B507" t="n">
-        <v>0.023248</v>
+        <v>0.023262</v>
       </c>
       <c r="C507" t="n">
         <v>0.731156</v>
@@ -7018,7 +7018,7 @@
         </is>
       </c>
       <c r="B508" t="n">
-        <v>0.0237</v>
+        <v>0.023694</v>
       </c>
       <c r="C508" t="n">
         <v>0.728643</v>
@@ -7031,7 +7031,7 @@
         </is>
       </c>
       <c r="B509" t="n">
-        <v>0.023713</v>
+        <v>0.023753</v>
       </c>
       <c r="C509" t="n">
         <v>0.726131</v>
@@ -7044,7 +7044,7 @@
         </is>
       </c>
       <c r="B510" t="n">
-        <v>0.023984</v>
+        <v>0.023994</v>
       </c>
       <c r="C510" t="n">
         <v>0.723618</v>
@@ -7057,7 +7057,7 @@
         </is>
       </c>
       <c r="B511" t="n">
-        <v>0.024138</v>
+        <v>0.02419</v>
       </c>
       <c r="C511" t="n">
         <v>0.721106</v>
@@ -7070,7 +7070,7 @@
         </is>
       </c>
       <c r="B512" t="n">
-        <v>0.024319</v>
+        <v>0.024313</v>
       </c>
       <c r="C512" t="n">
         <v>0.718593</v>
@@ -7083,7 +7083,7 @@
         </is>
       </c>
       <c r="B513" t="n">
-        <v>0.024465</v>
+        <v>0.024497</v>
       </c>
       <c r="C513" t="n">
         <v>0.71608</v>
@@ -7096,7 +7096,7 @@
         </is>
       </c>
       <c r="B514" t="n">
-        <v>0.024706</v>
+        <v>0.024715</v>
       </c>
       <c r="C514" t="n">
         <v>0.713568</v>
@@ -7109,7 +7109,7 @@
         </is>
       </c>
       <c r="B515" t="n">
-        <v>0.024898</v>
+        <v>0.024903</v>
       </c>
       <c r="C515" t="n">
         <v>0.711055</v>
@@ -7122,7 +7122,7 @@
         </is>
       </c>
       <c r="B516" t="n">
-        <v>0.024943</v>
+        <v>0.025004</v>
       </c>
       <c r="C516" t="n">
         <v>0.708543</v>
@@ -7135,7 +7135,7 @@
         </is>
       </c>
       <c r="B517" t="n">
-        <v>0.025315</v>
+        <v>0.02533</v>
       </c>
       <c r="C517" t="n">
         <v>0.70603</v>
@@ -7148,7 +7148,7 @@
         </is>
       </c>
       <c r="B518" t="n">
-        <v>0.02533</v>
+        <v>0.02537</v>
       </c>
       <c r="C518" t="n">
         <v>0.703518</v>
@@ -7161,7 +7161,7 @@
         </is>
       </c>
       <c r="B519" t="n">
-        <v>0.025789</v>
+        <v>0.025782</v>
       </c>
       <c r="C519" t="n">
         <v>0.701005</v>
@@ -7174,7 +7174,7 @@
         </is>
       </c>
       <c r="B520" t="n">
-        <v>0.025845</v>
+        <v>0.025843</v>
       </c>
       <c r="C520" t="n">
         <v>0.698492</v>
@@ -7187,7 +7187,7 @@
         </is>
       </c>
       <c r="B521" t="n">
-        <v>0.025973</v>
+        <v>0.025966</v>
       </c>
       <c r="C521" t="n">
         <v>0.69598</v>
@@ -7200,7 +7200,7 @@
         </is>
       </c>
       <c r="B522" t="n">
-        <v>0.026024</v>
+        <v>0.026021</v>
       </c>
       <c r="C522" t="n">
         <v>0.6934669999999999</v>
@@ -7213,7 +7213,7 @@
         </is>
       </c>
       <c r="B523" t="n">
-        <v>0.026398</v>
+        <v>0.026403</v>
       </c>
       <c r="C523" t="n">
         <v>0.690955</v>
@@ -7226,7 +7226,7 @@
         </is>
       </c>
       <c r="B524" t="n">
-        <v>0.026496</v>
+        <v>0.026494</v>
       </c>
       <c r="C524" t="n">
         <v>0.688442</v>
@@ -7239,7 +7239,7 @@
         </is>
       </c>
       <c r="B525" t="n">
-        <v>0.026581</v>
+        <v>0.026603</v>
       </c>
       <c r="C525" t="n">
         <v>0.68593</v>
@@ -7252,7 +7252,7 @@
         </is>
       </c>
       <c r="B526" t="n">
-        <v>0.026742</v>
+        <v>0.026757</v>
       </c>
       <c r="C526" t="n">
         <v>0.6834170000000001</v>
@@ -7278,7 +7278,7 @@
         </is>
       </c>
       <c r="B528" t="n">
-        <v>0.026969</v>
+        <v>0.026994</v>
       </c>
       <c r="C528" t="n">
         <v>0.678392</v>
@@ -7291,7 +7291,7 @@
         </is>
       </c>
       <c r="B529" t="n">
-        <v>0.028562</v>
+        <v>0.028554</v>
       </c>
       <c r="C529" t="n">
         <v>0.675879</v>
@@ -7304,7 +7304,7 @@
         </is>
       </c>
       <c r="B530" t="n">
-        <v>0.028587</v>
+        <v>0.028582</v>
       </c>
       <c r="C530" t="n">
         <v>0.673367</v>
@@ -7317,7 +7317,7 @@
         </is>
       </c>
       <c r="B531" t="n">
-        <v>0.028712</v>
+        <v>0.028711</v>
       </c>
       <c r="C531" t="n">
         <v>0.670854</v>
@@ -7330,7 +7330,7 @@
         </is>
       </c>
       <c r="B532" t="n">
-        <v>0.02906</v>
+        <v>0.029053</v>
       </c>
       <c r="C532" t="n">
         <v>0.668342</v>
@@ -7343,7 +7343,7 @@
         </is>
       </c>
       <c r="B533" t="n">
-        <v>0.029115</v>
+        <v>0.029112</v>
       </c>
       <c r="C533" t="n">
         <v>0.665829</v>
@@ -7356,7 +7356,7 @@
         </is>
       </c>
       <c r="B534" t="n">
-        <v>0.029221</v>
+        <v>0.029242</v>
       </c>
       <c r="C534" t="n">
         <v>0.663317</v>
@@ -7369,7 +7369,7 @@
         </is>
       </c>
       <c r="B535" t="n">
-        <v>0.029223</v>
+        <v>0.029244</v>
       </c>
       <c r="C535" t="n">
         <v>0.6608039999999999</v>
@@ -7382,7 +7382,7 @@
         </is>
       </c>
       <c r="B536" t="n">
-        <v>0.029686</v>
+        <v>0.029691</v>
       </c>
       <c r="C536" t="n">
         <v>0.658291</v>
@@ -7395,7 +7395,7 @@
         </is>
       </c>
       <c r="B537" t="n">
-        <v>0.029721</v>
+        <v>0.029713</v>
       </c>
       <c r="C537" t="n">
         <v>0.655779</v>
@@ -7421,7 +7421,7 @@
         </is>
       </c>
       <c r="B539" t="n">
-        <v>0.030234</v>
+        <v>0.030287</v>
       </c>
       <c r="C539" t="n">
         <v>0.6507540000000001</v>
@@ -7434,7 +7434,7 @@
         </is>
       </c>
       <c r="B540" t="n">
-        <v>0.030472</v>
+        <v>0.030464</v>
       </c>
       <c r="C540" t="n">
         <v>0.648241</v>
@@ -7447,7 +7447,7 @@
         </is>
       </c>
       <c r="B541" t="n">
-        <v>0.030577</v>
+        <v>0.030569</v>
       </c>
       <c r="C541" t="n">
         <v>0.645729</v>
@@ -7460,7 +7460,7 @@
         </is>
       </c>
       <c r="B542" t="n">
-        <v>0.0311</v>
+        <v>0.031105</v>
       </c>
       <c r="C542" t="n">
         <v>0.643216</v>
@@ -7473,7 +7473,7 @@
         </is>
       </c>
       <c r="B543" t="n">
-        <v>0.031485</v>
+        <v>0.031559</v>
       </c>
       <c r="C543" t="n">
         <v>0.6407040000000001</v>
@@ -7486,7 +7486,7 @@
         </is>
       </c>
       <c r="B544" t="n">
-        <v>0.031591</v>
+        <v>0.031585</v>
       </c>
       <c r="C544" t="n">
         <v>0.638191</v>
@@ -7499,7 +7499,7 @@
         </is>
       </c>
       <c r="B545" t="n">
-        <v>0.031638</v>
+        <v>0.031701</v>
       </c>
       <c r="C545" t="n">
         <v>0.635678</v>
@@ -7512,7 +7512,7 @@
         </is>
       </c>
       <c r="B546" t="n">
-        <v>0.031648</v>
+        <v>0.031714</v>
       </c>
       <c r="C546" t="n">
         <v>0.633166</v>
@@ -7525,7 +7525,7 @@
         </is>
       </c>
       <c r="B547" t="n">
-        <v>0.031922</v>
+        <v>0.031917</v>
       </c>
       <c r="C547" t="n">
         <v>0.630653</v>
@@ -7538,7 +7538,7 @@
         </is>
       </c>
       <c r="B548" t="n">
-        <v>0.032209</v>
+        <v>0.0322</v>
       </c>
       <c r="C548" t="n">
         <v>0.6281409999999999</v>
@@ -7551,7 +7551,7 @@
         </is>
       </c>
       <c r="B549" t="n">
-        <v>0.032512</v>
+        <v>0.032516</v>
       </c>
       <c r="C549" t="n">
         <v>0.625628</v>
@@ -7564,7 +7564,7 @@
         </is>
       </c>
       <c r="B550" t="n">
-        <v>0.03267</v>
+        <v>0.032692</v>
       </c>
       <c r="C550" t="n">
         <v>0.623116</v>
@@ -7577,7 +7577,7 @@
         </is>
       </c>
       <c r="B551" t="n">
-        <v>0.032696</v>
+        <v>0.032708</v>
       </c>
       <c r="C551" t="n">
         <v>0.620603</v>
@@ -7590,7 +7590,7 @@
         </is>
       </c>
       <c r="B552" t="n">
-        <v>0.032866</v>
+        <v>0.032917</v>
       </c>
       <c r="C552" t="n">
         <v>0.61809</v>
@@ -7603,7 +7603,7 @@
         </is>
       </c>
       <c r="B553" t="n">
-        <v>0.033102</v>
+        <v>0.033093</v>
       </c>
       <c r="C553" t="n">
         <v>0.615578</v>
@@ -7616,7 +7616,7 @@
         </is>
       </c>
       <c r="B554" t="n">
-        <v>0.033334</v>
+        <v>0.033345</v>
       </c>
       <c r="C554" t="n">
         <v>0.613065</v>
@@ -7629,7 +7629,7 @@
         </is>
       </c>
       <c r="B555" t="n">
-        <v>0.033539</v>
+        <v>0.033533</v>
       </c>
       <c r="C555" t="n">
         <v>0.610553</v>
@@ -7655,7 +7655,7 @@
         </is>
       </c>
       <c r="B557" t="n">
-        <v>0.033744</v>
+        <v>0.033775</v>
       </c>
       <c r="C557" t="n">
         <v>0.605528</v>
@@ -7668,7 +7668,7 @@
         </is>
       </c>
       <c r="B558" t="n">
-        <v>0.033899</v>
+        <v>0.033901</v>
       </c>
       <c r="C558" t="n">
         <v>0.603015</v>
@@ -7681,7 +7681,7 @@
         </is>
       </c>
       <c r="B559" t="n">
-        <v>0.034029</v>
+        <v>0.034063</v>
       </c>
       <c r="C559" t="n">
         <v>0.600503</v>
@@ -7694,7 +7694,7 @@
         </is>
       </c>
       <c r="B560" t="n">
-        <v>0.034155</v>
+        <v>0.034171</v>
       </c>
       <c r="C560" t="n">
         <v>0.59799</v>
@@ -7707,7 +7707,7 @@
         </is>
       </c>
       <c r="B561" t="n">
-        <v>0.034265</v>
+        <v>0.034255</v>
       </c>
       <c r="C561" t="n">
         <v>0.595477</v>
@@ -7720,7 +7720,7 @@
         </is>
       </c>
       <c r="B562" t="n">
-        <v>0.035101</v>
+        <v>0.035095</v>
       </c>
       <c r="C562" t="n">
         <v>0.592965</v>
@@ -7733,7 +7733,7 @@
         </is>
       </c>
       <c r="B563" t="n">
-        <v>0.035257</v>
+        <v>0.035281</v>
       </c>
       <c r="C563" t="n">
         <v>0.590452</v>
@@ -7746,7 +7746,7 @@
         </is>
       </c>
       <c r="B564" t="n">
-        <v>0.035463</v>
+        <v>0.035453</v>
       </c>
       <c r="C564" t="n">
         <v>0.58794</v>
@@ -7759,7 +7759,7 @@
         </is>
       </c>
       <c r="B565" t="n">
-        <v>0.03553</v>
+        <v>0.035531</v>
       </c>
       <c r="C565" t="n">
         <v>0.585427</v>
@@ -7772,7 +7772,7 @@
         </is>
       </c>
       <c r="B566" t="n">
-        <v>0.035825</v>
+        <v>0.035829</v>
       </c>
       <c r="C566" t="n">
         <v>0.582915</v>
@@ -7785,7 +7785,7 @@
         </is>
       </c>
       <c r="B567" t="n">
-        <v>0.035996</v>
+        <v>0.035988</v>
       </c>
       <c r="C567" t="n">
         <v>0.580402</v>
@@ -7811,7 +7811,7 @@
         </is>
       </c>
       <c r="B569" t="n">
-        <v>0.036072</v>
+        <v>0.036084</v>
       </c>
       <c r="C569" t="n">
         <v>0.575377</v>
@@ -7824,7 +7824,7 @@
         </is>
       </c>
       <c r="B570" t="n">
-        <v>0.036734</v>
+        <v>0.036727</v>
       </c>
       <c r="C570" t="n">
         <v>0.572864</v>
@@ -7837,7 +7837,7 @@
         </is>
       </c>
       <c r="B571" t="n">
-        <v>0.036757</v>
+        <v>0.036773</v>
       </c>
       <c r="C571" t="n">
         <v>0.570352</v>
@@ -7850,7 +7850,7 @@
         </is>
       </c>
       <c r="B572" t="n">
-        <v>0.036783</v>
+        <v>0.036785</v>
       </c>
       <c r="C572" t="n">
         <v>0.567839</v>
@@ -7863,7 +7863,7 @@
         </is>
       </c>
       <c r="B573" t="n">
-        <v>0.037385</v>
+        <v>0.037413</v>
       </c>
       <c r="C573" t="n">
         <v>0.565327</v>
@@ -7876,7 +7876,7 @@
         </is>
       </c>
       <c r="B574" t="n">
-        <v>0.037737</v>
+        <v>0.037832</v>
       </c>
       <c r="C574" t="n">
         <v>0.562814</v>
@@ -7889,7 +7889,7 @@
         </is>
       </c>
       <c r="B575" t="n">
-        <v>0.038258</v>
+        <v>0.038276</v>
       </c>
       <c r="C575" t="n">
         <v>0.560302</v>
@@ -7902,7 +7902,7 @@
         </is>
       </c>
       <c r="B576" t="n">
-        <v>0.038576</v>
+        <v>0.038565</v>
       </c>
       <c r="C576" t="n">
         <v>0.557789</v>
@@ -7915,7 +7915,7 @@
         </is>
       </c>
       <c r="B577" t="n">
-        <v>0.038654</v>
+        <v>0.038651</v>
       </c>
       <c r="C577" t="n">
         <v>0.555276</v>
@@ -7928,7 +7928,7 @@
         </is>
       </c>
       <c r="B578" t="n">
-        <v>0.039295</v>
+        <v>0.039375</v>
       </c>
       <c r="C578" t="n">
         <v>0.552764</v>
@@ -7941,7 +7941,7 @@
         </is>
       </c>
       <c r="B579" t="n">
-        <v>0.039584</v>
+        <v>0.039592</v>
       </c>
       <c r="C579" t="n">
         <v>0.550251</v>
@@ -7954,7 +7954,7 @@
         </is>
       </c>
       <c r="B580" t="n">
-        <v>0.039714</v>
+        <v>0.03971</v>
       </c>
       <c r="C580" t="n">
         <v>0.547739</v>
@@ -7967,7 +7967,7 @@
         </is>
       </c>
       <c r="B581" t="n">
-        <v>0.039789</v>
+        <v>0.039788</v>
       </c>
       <c r="C581" t="n">
         <v>0.545226</v>
@@ -7980,7 +7980,7 @@
         </is>
       </c>
       <c r="B582" t="n">
-        <v>0.040049</v>
+        <v>0.040053</v>
       </c>
       <c r="C582" t="n">
         <v>0.542714</v>
@@ -7993,7 +7993,7 @@
         </is>
       </c>
       <c r="B583" t="n">
-        <v>0.040049</v>
+        <v>0.040061</v>
       </c>
       <c r="C583" t="n">
         <v>0.540201</v>
@@ -8006,7 +8006,7 @@
         </is>
       </c>
       <c r="B584" t="n">
-        <v>0.040072</v>
+        <v>0.040097</v>
       </c>
       <c r="C584" t="n">
         <v>0.5376880000000001</v>
@@ -8019,7 +8019,7 @@
         </is>
       </c>
       <c r="B585" t="n">
-        <v>0.04093</v>
+        <v>0.04092</v>
       </c>
       <c r="C585" t="n">
         <v>0.535176</v>
@@ -8045,7 +8045,7 @@
         </is>
       </c>
       <c r="B587" t="n">
-        <v>0.04097</v>
+        <v>0.040959</v>
       </c>
       <c r="C587" t="n">
         <v>0.530151</v>
@@ -8058,7 +8058,7 @@
         </is>
       </c>
       <c r="B588" t="n">
-        <v>0.040987</v>
+        <v>0.041013</v>
       </c>
       <c r="C588" t="n">
         <v>0.5276380000000001</v>
@@ -8071,7 +8071,7 @@
         </is>
       </c>
       <c r="B589" t="n">
-        <v>0.041025</v>
+        <v>0.04103</v>
       </c>
       <c r="C589" t="n">
         <v>0.525126</v>
@@ -8084,7 +8084,7 @@
         </is>
       </c>
       <c r="B590" t="n">
-        <v>0.042605</v>
+        <v>0.0426</v>
       </c>
       <c r="C590" t="n">
         <v>0.522613</v>
@@ -8097,7 +8097,7 @@
         </is>
       </c>
       <c r="B591" t="n">
-        <v>0.042862</v>
+        <v>0.042868</v>
       </c>
       <c r="C591" t="n">
         <v>0.520101</v>
@@ -8110,7 +8110,7 @@
         </is>
       </c>
       <c r="B592" t="n">
-        <v>0.043146</v>
+        <v>0.043143</v>
       </c>
       <c r="C592" t="n">
         <v>0.517588</v>
@@ -8123,7 +8123,7 @@
         </is>
       </c>
       <c r="B593" t="n">
-        <v>0.043512</v>
+        <v>0.043556</v>
       </c>
       <c r="C593" t="n">
         <v>0.5150749999999999</v>
@@ -8149,7 +8149,7 @@
         </is>
       </c>
       <c r="B595" t="n">
-        <v>0.043818</v>
+        <v>0.043811</v>
       </c>
       <c r="C595" t="n">
         <v>0.51005</v>
@@ -8162,7 +8162,7 @@
         </is>
       </c>
       <c r="B596" t="n">
-        <v>0.043944</v>
+        <v>0.043938</v>
       </c>
       <c r="C596" t="n">
         <v>0.507538</v>
@@ -8175,7 +8175,7 @@
         </is>
       </c>
       <c r="B597" t="n">
-        <v>0.044036</v>
+        <v>0.044127</v>
       </c>
       <c r="C597" t="n">
         <v>0.5050249999999999</v>
@@ -8188,7 +8188,7 @@
         </is>
       </c>
       <c r="B598" t="n">
-        <v>0.044567</v>
+        <v>0.04456</v>
       </c>
       <c r="C598" t="n">
         <v>0.502513</v>
@@ -8201,7 +8201,7 @@
         </is>
       </c>
       <c r="B599" t="n">
-        <v>0.044655</v>
+        <v>0.044657</v>
       </c>
       <c r="C599" t="n">
         <v>0.5</v>
@@ -8214,7 +8214,7 @@
         </is>
       </c>
       <c r="B600" t="n">
-        <v>0.044707</v>
+        <v>0.044694</v>
       </c>
       <c r="C600" t="n">
         <v>0.497487</v>
@@ -8227,7 +8227,7 @@
         </is>
       </c>
       <c r="B601" t="n">
-        <v>0.044908</v>
+        <v>0.044957</v>
       </c>
       <c r="C601" t="n">
         <v>0.494975</v>
@@ -8240,7 +8240,7 @@
         </is>
       </c>
       <c r="B602" t="n">
-        <v>0.044965</v>
+        <v>0.044958</v>
       </c>
       <c r="C602" t="n">
         <v>0.492462</v>
@@ -8253,7 +8253,7 @@
         </is>
       </c>
       <c r="B603" t="n">
-        <v>0.045098</v>
+        <v>0.045093</v>
       </c>
       <c r="C603" t="n">
         <v>0.48995</v>
@@ -8266,7 +8266,7 @@
         </is>
       </c>
       <c r="B604" t="n">
-        <v>0.045206</v>
+        <v>0.045212</v>
       </c>
       <c r="C604" t="n">
         <v>0.487437</v>
@@ -8279,7 +8279,7 @@
         </is>
       </c>
       <c r="B605" t="n">
-        <v>0.045277</v>
+        <v>0.045367</v>
       </c>
       <c r="C605" t="n">
         <v>0.484925</v>
@@ -8292,7 +8292,7 @@
         </is>
       </c>
       <c r="B606" t="n">
-        <v>0.045378</v>
+        <v>0.045411</v>
       </c>
       <c r="C606" t="n">
         <v>0.482412</v>
@@ -8305,7 +8305,7 @@
         </is>
       </c>
       <c r="B607" t="n">
-        <v>0.045587</v>
+        <v>0.045575</v>
       </c>
       <c r="C607" t="n">
         <v>0.479899</v>
@@ -8318,7 +8318,7 @@
         </is>
       </c>
       <c r="B608" t="n">
-        <v>0.046203</v>
+        <v>0.046192</v>
       </c>
       <c r="C608" t="n">
         <v>0.477387</v>
@@ -8331,7 +8331,7 @@
         </is>
       </c>
       <c r="B609" t="n">
-        <v>0.046246</v>
+        <v>0.046234</v>
       </c>
       <c r="C609" t="n">
         <v>0.474874</v>
@@ -8344,7 +8344,7 @@
         </is>
       </c>
       <c r="B610" t="n">
-        <v>0.046478</v>
+        <v>0.046507</v>
       </c>
       <c r="C610" t="n">
         <v>0.472362</v>
@@ -8357,7 +8357,7 @@
         </is>
       </c>
       <c r="B611" t="n">
-        <v>0.046904</v>
+        <v>0.046923</v>
       </c>
       <c r="C611" t="n">
         <v>0.469849</v>
@@ -8370,7 +8370,7 @@
         </is>
       </c>
       <c r="B612" t="n">
-        <v>0.047062</v>
+        <v>0.047048</v>
       </c>
       <c r="C612" t="n">
         <v>0.467337</v>
@@ -8383,7 +8383,7 @@
         </is>
       </c>
       <c r="B613" t="n">
-        <v>0.04744</v>
+        <v>0.047573</v>
       </c>
       <c r="C613" t="n">
         <v>0.464824</v>
@@ -8396,7 +8396,7 @@
         </is>
       </c>
       <c r="B614" t="n">
-        <v>0.047589</v>
+        <v>0.047576</v>
       </c>
       <c r="C614" t="n">
         <v>0.462312</v>
@@ -8409,7 +8409,7 @@
         </is>
       </c>
       <c r="B615" t="n">
-        <v>0.047682</v>
+        <v>0.047684</v>
       </c>
       <c r="C615" t="n">
         <v>0.459799</v>
@@ -8422,7 +8422,7 @@
         </is>
       </c>
       <c r="B616" t="n">
-        <v>0.048681</v>
+        <v>0.048673</v>
       </c>
       <c r="C616" t="n">
         <v>0.457286</v>
@@ -8435,7 +8435,7 @@
         </is>
       </c>
       <c r="B617" t="n">
-        <v>0.049252</v>
+        <v>0.049257</v>
       </c>
       <c r="C617" t="n">
         <v>0.454774</v>
@@ -8448,7 +8448,7 @@
         </is>
       </c>
       <c r="B618" t="n">
-        <v>0.050171</v>
+        <v>0.050167</v>
       </c>
       <c r="C618" t="n">
         <v>0.452261</v>
@@ -8461,7 +8461,7 @@
         </is>
       </c>
       <c r="B619" t="n">
-        <v>0.050542</v>
+        <v>0.050663</v>
       </c>
       <c r="C619" t="n">
         <v>0.449749</v>
@@ -8474,7 +8474,7 @@
         </is>
       </c>
       <c r="B620" t="n">
-        <v>0.050588</v>
+        <v>0.050737</v>
       </c>
       <c r="C620" t="n">
         <v>0.447236</v>
@@ -8487,7 +8487,7 @@
         </is>
       </c>
       <c r="B621" t="n">
-        <v>0.050752</v>
+        <v>0.050857</v>
       </c>
       <c r="C621" t="n">
         <v>0.444724</v>
@@ -8500,7 +8500,7 @@
         </is>
       </c>
       <c r="B622" t="n">
-        <v>0.050905</v>
+        <v>0.050903</v>
       </c>
       <c r="C622" t="n">
         <v>0.442211</v>
@@ -8513,7 +8513,7 @@
         </is>
       </c>
       <c r="B623" t="n">
-        <v>0.050916</v>
+        <v>0.050903</v>
       </c>
       <c r="C623" t="n">
         <v>0.439698</v>
@@ -8526,7 +8526,7 @@
         </is>
       </c>
       <c r="B624" t="n">
-        <v>0.051922</v>
+        <v>0.052036</v>
       </c>
       <c r="C624" t="n">
         <v>0.437186</v>
@@ -8539,7 +8539,7 @@
         </is>
       </c>
       <c r="B625" t="n">
-        <v>0.052557</v>
+        <v>0.052567</v>
       </c>
       <c r="C625" t="n">
         <v>0.434673</v>
@@ -8552,7 +8552,7 @@
         </is>
       </c>
       <c r="B626" t="n">
-        <v>0.052938</v>
+        <v>0.052978</v>
       </c>
       <c r="C626" t="n">
         <v>0.432161</v>
@@ -8565,7 +8565,7 @@
         </is>
       </c>
       <c r="B627" t="n">
-        <v>0.053051</v>
+        <v>0.053063</v>
       </c>
       <c r="C627" t="n">
         <v>0.429648</v>
@@ -8578,7 +8578,7 @@
         </is>
       </c>
       <c r="B628" t="n">
-        <v>0.053156</v>
+        <v>0.053223</v>
       </c>
       <c r="C628" t="n">
         <v>0.427136</v>
@@ -8591,7 +8591,7 @@
         </is>
       </c>
       <c r="B629" t="n">
-        <v>0.053755</v>
+        <v>0.053777</v>
       </c>
       <c r="C629" t="n">
         <v>0.424623</v>
@@ -8604,7 +8604,7 @@
         </is>
       </c>
       <c r="B630" t="n">
-        <v>0.053787</v>
+        <v>0.053888</v>
       </c>
       <c r="C630" t="n">
         <v>0.422111</v>
@@ -8617,7 +8617,7 @@
         </is>
       </c>
       <c r="B631" t="n">
-        <v>0.054241</v>
+        <v>0.054272</v>
       </c>
       <c r="C631" t="n">
         <v>0.419598</v>
@@ -8630,7 +8630,7 @@
         </is>
       </c>
       <c r="B632" t="n">
-        <v>0.054358</v>
+        <v>0.054348</v>
       </c>
       <c r="C632" t="n">
         <v>0.417085</v>
@@ -8643,7 +8643,7 @@
         </is>
       </c>
       <c r="B633" t="n">
-        <v>0.054421</v>
+        <v>0.054405</v>
       </c>
       <c r="C633" t="n">
         <v>0.414573</v>
@@ -8656,7 +8656,7 @@
         </is>
       </c>
       <c r="B634" t="n">
-        <v>0.054546</v>
+        <v>0.054564</v>
       </c>
       <c r="C634" t="n">
         <v>0.41206</v>
@@ -8669,7 +8669,7 @@
         </is>
       </c>
       <c r="B635" t="n">
-        <v>0.054584</v>
+        <v>0.054603</v>
       </c>
       <c r="C635" t="n">
         <v>0.409548</v>
@@ -8682,7 +8682,7 @@
         </is>
       </c>
       <c r="B636" t="n">
-        <v>0.05465</v>
+        <v>0.054654</v>
       </c>
       <c r="C636" t="n">
         <v>0.407035</v>
@@ -8695,7 +8695,7 @@
         </is>
       </c>
       <c r="B637" t="n">
-        <v>0.054655</v>
+        <v>0.054779</v>
       </c>
       <c r="C637" t="n">
         <v>0.404523</v>
@@ -8708,7 +8708,7 @@
         </is>
       </c>
       <c r="B638" t="n">
-        <v>0.054783</v>
+        <v>0.054789</v>
       </c>
       <c r="C638" t="n">
         <v>0.40201</v>
@@ -8721,7 +8721,7 @@
         </is>
       </c>
       <c r="B639" t="n">
-        <v>0.05515</v>
+        <v>0.055135</v>
       </c>
       <c r="C639" t="n">
         <v>0.399497</v>
@@ -8734,7 +8734,7 @@
         </is>
       </c>
       <c r="B640" t="n">
-        <v>0.055443</v>
+        <v>0.055428</v>
       </c>
       <c r="C640" t="n">
         <v>0.396985</v>
@@ -8747,7 +8747,7 @@
         </is>
       </c>
       <c r="B641" t="n">
-        <v>0.056085</v>
+        <v>0.056147</v>
       </c>
       <c r="C641" t="n">
         <v>0.394472</v>
@@ -8760,7 +8760,7 @@
         </is>
       </c>
       <c r="B642" t="n">
-        <v>0.056198</v>
+        <v>0.056192</v>
       </c>
       <c r="C642" t="n">
         <v>0.39196</v>
@@ -8773,7 +8773,7 @@
         </is>
       </c>
       <c r="B643" t="n">
-        <v>0.056566</v>
+        <v>0.056577</v>
       </c>
       <c r="C643" t="n">
         <v>0.389447</v>
@@ -8786,7 +8786,7 @@
         </is>
       </c>
       <c r="B644" t="n">
-        <v>0.056756</v>
+        <v>0.056744</v>
       </c>
       <c r="C644" t="n">
         <v>0.386935</v>
@@ -8799,7 +8799,7 @@
         </is>
       </c>
       <c r="B645" t="n">
-        <v>0.057161</v>
+        <v>0.057145</v>
       </c>
       <c r="C645" t="n">
         <v>0.384422</v>
@@ -8812,7 +8812,7 @@
         </is>
       </c>
       <c r="B646" t="n">
-        <v>0.057745</v>
+        <v>0.057797</v>
       </c>
       <c r="C646" t="n">
         <v>0.38191</v>
@@ -8825,7 +8825,7 @@
         </is>
       </c>
       <c r="B647" t="n">
-        <v>0.057938</v>
+        <v>0.057982</v>
       </c>
       <c r="C647" t="n">
         <v>0.379397</v>
@@ -8838,7 +8838,7 @@
         </is>
       </c>
       <c r="B648" t="n">
-        <v>0.05799</v>
+        <v>0.058013</v>
       </c>
       <c r="C648" t="n">
         <v>0.376884</v>
@@ -8851,7 +8851,7 @@
         </is>
       </c>
       <c r="B649" t="n">
-        <v>0.058953</v>
+        <v>0.058939</v>
       </c>
       <c r="C649" t="n">
         <v>0.374372</v>
@@ -8864,7 +8864,7 @@
         </is>
       </c>
       <c r="B650" t="n">
-        <v>0.059816</v>
+        <v>0.059817</v>
       </c>
       <c r="C650" t="n">
         <v>0.371859</v>
@@ -8877,7 +8877,7 @@
         </is>
       </c>
       <c r="B651" t="n">
-        <v>0.059832</v>
+        <v>0.059833</v>
       </c>
       <c r="C651" t="n">
         <v>0.369347</v>
@@ -8890,7 +8890,7 @@
         </is>
       </c>
       <c r="B652" t="n">
-        <v>0.059881</v>
+        <v>0.059921</v>
       </c>
       <c r="C652" t="n">
         <v>0.366834</v>
@@ -8903,7 +8903,7 @@
         </is>
       </c>
       <c r="B653" t="n">
-        <v>0.060024</v>
+        <v>0.060028</v>
       </c>
       <c r="C653" t="n">
         <v>0.364322</v>
@@ -8916,7 +8916,7 @@
         </is>
       </c>
       <c r="B654" t="n">
-        <v>0.060419</v>
+        <v>0.060447</v>
       </c>
       <c r="C654" t="n">
         <v>0.361809</v>
@@ -8929,7 +8929,7 @@
         </is>
       </c>
       <c r="B655" t="n">
-        <v>0.060627</v>
+        <v>0.060611</v>
       </c>
       <c r="C655" t="n">
         <v>0.359296</v>
@@ -8942,7 +8942,7 @@
         </is>
       </c>
       <c r="B656" t="n">
-        <v>0.060836</v>
+        <v>0.060835</v>
       </c>
       <c r="C656" t="n">
         <v>0.356784</v>
@@ -8955,7 +8955,7 @@
         </is>
       </c>
       <c r="B657" t="n">
-        <v>0.062016</v>
+        <v>0.062004</v>
       </c>
       <c r="C657" t="n">
         <v>0.354271</v>
@@ -8968,7 +8968,7 @@
         </is>
       </c>
       <c r="B658" t="n">
-        <v>0.062023</v>
+        <v>0.062033</v>
       </c>
       <c r="C658" t="n">
         <v>0.351759</v>
@@ -8981,7 +8981,7 @@
         </is>
       </c>
       <c r="B659" t="n">
-        <v>0.063151</v>
+        <v>0.063225</v>
       </c>
       <c r="C659" t="n">
         <v>0.349246</v>
@@ -8994,7 +8994,7 @@
         </is>
       </c>
       <c r="B660" t="n">
-        <v>0.064138</v>
+        <v>0.064293</v>
       </c>
       <c r="C660" t="n">
         <v>0.346734</v>
@@ -9007,7 +9007,7 @@
         </is>
       </c>
       <c r="B661" t="n">
-        <v>0.064303</v>
+        <v>0.064488</v>
       </c>
       <c r="C661" t="n">
         <v>0.344221</v>
@@ -9020,7 +9020,7 @@
         </is>
       </c>
       <c r="B662" t="n">
-        <v>0.064461</v>
+        <v>0.06456099999999999</v>
       </c>
       <c r="C662" t="n">
         <v>0.341709</v>
@@ -9033,7 +9033,7 @@
         </is>
       </c>
       <c r="B663" t="n">
-        <v>0.065174</v>
+        <v>0.065307</v>
       </c>
       <c r="C663" t="n">
         <v>0.339196</v>
@@ -9046,7 +9046,7 @@
         </is>
       </c>
       <c r="B664" t="n">
-        <v>0.065481</v>
+        <v>0.065565</v>
       </c>
       <c r="C664" t="n">
         <v>0.336683</v>
@@ -9059,7 +9059,7 @@
         </is>
       </c>
       <c r="B665" t="n">
-        <v>0.065664</v>
+        <v>0.065675</v>
       </c>
       <c r="C665" t="n">
         <v>0.334171</v>
@@ -9072,7 +9072,7 @@
         </is>
       </c>
       <c r="B666" t="n">
-        <v>0.06615500000000001</v>
+        <v>0.06616900000000001</v>
       </c>
       <c r="C666" t="n">
         <v>0.331658</v>
@@ -9085,7 +9085,7 @@
         </is>
       </c>
       <c r="B667" t="n">
-        <v>0.066357</v>
+        <v>0.066445</v>
       </c>
       <c r="C667" t="n">
         <v>0.329146</v>
@@ -9098,7 +9098,7 @@
         </is>
       </c>
       <c r="B668" t="n">
-        <v>0.067298</v>
+        <v>0.067291</v>
       </c>
       <c r="C668" t="n">
         <v>0.326633</v>
@@ -9111,7 +9111,7 @@
         </is>
       </c>
       <c r="B669" t="n">
-        <v>0.06744799999999999</v>
+        <v>0.06744600000000001</v>
       </c>
       <c r="C669" t="n">
         <v>0.324121</v>
@@ -9124,7 +9124,7 @@
         </is>
       </c>
       <c r="B670" t="n">
-        <v>0.068476</v>
+        <v>0.068499</v>
       </c>
       <c r="C670" t="n">
         <v>0.321608</v>
@@ -9150,7 +9150,7 @@
         </is>
       </c>
       <c r="B672" t="n">
-        <v>0.06872399999999999</v>
+        <v>0.06870800000000001</v>
       </c>
       <c r="C672" t="n">
         <v>0.316583</v>
@@ -9163,7 +9163,7 @@
         </is>
       </c>
       <c r="B673" t="n">
-        <v>0.068939</v>
+        <v>0.06891899999999999</v>
       </c>
       <c r="C673" t="n">
         <v>0.31407</v>
@@ -9176,7 +9176,7 @@
         </is>
       </c>
       <c r="B674" t="n">
-        <v>0.069462</v>
+        <v>0.069454</v>
       </c>
       <c r="C674" t="n">
         <v>0.311558</v>
@@ -9189,7 +9189,7 @@
         </is>
       </c>
       <c r="B675" t="n">
-        <v>0.069886</v>
+        <v>0.069866</v>
       </c>
       <c r="C675" t="n">
         <v>0.309045</v>
@@ -9202,7 +9202,7 @@
         </is>
       </c>
       <c r="B676" t="n">
-        <v>0.070033</v>
+        <v>0.07020899999999999</v>
       </c>
       <c r="C676" t="n">
         <v>0.306533</v>
@@ -9215,7 +9215,7 @@
         </is>
       </c>
       <c r="B677" t="n">
-        <v>0.070504</v>
+        <v>0.07048699999999999</v>
       </c>
       <c r="C677" t="n">
         <v>0.30402</v>
@@ -9228,7 +9228,7 @@
         </is>
       </c>
       <c r="B678" t="n">
-        <v>0.070789</v>
+        <v>0.070872</v>
       </c>
       <c r="C678" t="n">
         <v>0.301508</v>
@@ -9241,7 +9241,7 @@
         </is>
       </c>
       <c r="B679" t="n">
-        <v>0.07142800000000001</v>
+        <v>0.07152500000000001</v>
       </c>
       <c r="C679" t="n">
         <v>0.298995</v>
@@ -9254,7 +9254,7 @@
         </is>
       </c>
       <c r="B680" t="n">
-        <v>0.071787</v>
+        <v>0.07188899999999999</v>
       </c>
       <c r="C680" t="n">
         <v>0.296482</v>
@@ -9267,7 +9267,7 @@
         </is>
       </c>
       <c r="B681" t="n">
-        <v>0.07252599999999999</v>
+        <v>0.072573</v>
       </c>
       <c r="C681" t="n">
         <v>0.29397</v>
@@ -9280,7 +9280,7 @@
         </is>
       </c>
       <c r="B682" t="n">
-        <v>0.072738</v>
+        <v>0.072728</v>
       </c>
       <c r="C682" t="n">
         <v>0.291457</v>
@@ -9293,7 +9293,7 @@
         </is>
       </c>
       <c r="B683" t="n">
-        <v>0.072862</v>
+        <v>0.07285999999999999</v>
       </c>
       <c r="C683" t="n">
         <v>0.288945</v>
@@ -9306,7 +9306,7 @@
         </is>
       </c>
       <c r="B684" t="n">
-        <v>0.07292999999999999</v>
+        <v>0.073058</v>
       </c>
       <c r="C684" t="n">
         <v>0.286432</v>
@@ -9319,7 +9319,7 @@
         </is>
       </c>
       <c r="B685" t="n">
-        <v>0.07394199999999999</v>
+        <v>0.073946</v>
       </c>
       <c r="C685" t="n">
         <v>0.28392</v>
@@ -9332,7 +9332,7 @@
         </is>
       </c>
       <c r="B686" t="n">
-        <v>0.07396800000000001</v>
+        <v>0.073951</v>
       </c>
       <c r="C686" t="n">
         <v>0.281407</v>
@@ -9345,7 +9345,7 @@
         </is>
       </c>
       <c r="B687" t="n">
-        <v>0.07464999999999999</v>
+        <v>0.074644</v>
       </c>
       <c r="C687" t="n">
         <v>0.278894</v>
@@ -9358,7 +9358,7 @@
         </is>
       </c>
       <c r="B688" t="n">
-        <v>0.074724</v>
+        <v>0.074707</v>
       </c>
       <c r="C688" t="n">
         <v>0.276382</v>
@@ -9371,7 +9371,7 @@
         </is>
       </c>
       <c r="B689" t="n">
-        <v>0.075501</v>
+        <v>0.075504</v>
       </c>
       <c r="C689" t="n">
         <v>0.273869</v>
@@ -9384,7 +9384,7 @@
         </is>
       </c>
       <c r="B690" t="n">
-        <v>0.075637</v>
+        <v>0.075714</v>
       </c>
       <c r="C690" t="n">
         <v>0.271357</v>
@@ -9397,7 +9397,7 @@
         </is>
       </c>
       <c r="B691" t="n">
-        <v>0.075781</v>
+        <v>0.07581300000000001</v>
       </c>
       <c r="C691" t="n">
         <v>0.268844</v>
@@ -9410,7 +9410,7 @@
         </is>
       </c>
       <c r="B692" t="n">
-        <v>0.07661800000000001</v>
+        <v>0.076651</v>
       </c>
       <c r="C692" t="n">
         <v>0.266332</v>
@@ -9423,7 +9423,7 @@
         </is>
       </c>
       <c r="B693" t="n">
-        <v>0.07746500000000001</v>
+        <v>0.077533</v>
       </c>
       <c r="C693" t="n">
         <v>0.263819</v>
@@ -9436,7 +9436,7 @@
         </is>
       </c>
       <c r="B694" t="n">
-        <v>0.07874200000000001</v>
+        <v>0.07872700000000001</v>
       </c>
       <c r="C694" t="n">
         <v>0.261307</v>
@@ -9449,7 +9449,7 @@
         </is>
       </c>
       <c r="B695" t="n">
-        <v>0.078768</v>
+        <v>0.078767</v>
       </c>
       <c r="C695" t="n">
         <v>0.258794</v>
@@ -9462,7 +9462,7 @@
         </is>
       </c>
       <c r="B696" t="n">
-        <v>0.07935200000000001</v>
+        <v>0.079348</v>
       </c>
       <c r="C696" t="n">
         <v>0.256281</v>
@@ -9475,7 +9475,7 @@
         </is>
       </c>
       <c r="B697" t="n">
-        <v>0.07982400000000001</v>
+        <v>0.079834</v>
       </c>
       <c r="C697" t="n">
         <v>0.253769</v>
@@ -9488,7 +9488,7 @@
         </is>
       </c>
       <c r="B698" t="n">
-        <v>0.080383</v>
+        <v>0.08036</v>
       </c>
       <c r="C698" t="n">
         <v>0.251256</v>
@@ -9501,7 +9501,7 @@
         </is>
       </c>
       <c r="B699" t="n">
-        <v>0.080827</v>
+        <v>0.080845</v>
       </c>
       <c r="C699" t="n">
         <v>0.248744</v>
@@ -9514,7 +9514,7 @@
         </is>
       </c>
       <c r="B700" t="n">
-        <v>0.081091</v>
+        <v>0.08128100000000001</v>
       </c>
       <c r="C700" t="n">
         <v>0.246231</v>
@@ -9527,7 +9527,7 @@
         </is>
       </c>
       <c r="B701" t="n">
-        <v>0.081913</v>
+        <v>0.08189399999999999</v>
       </c>
       <c r="C701" t="n">
         <v>0.243719</v>
@@ -9540,7 +9540,7 @@
         </is>
       </c>
       <c r="B702" t="n">
-        <v>0.08290400000000001</v>
+        <v>0.083069</v>
       </c>
       <c r="C702" t="n">
         <v>0.241206</v>
@@ -9553,7 +9553,7 @@
         </is>
       </c>
       <c r="B703" t="n">
-        <v>0.08290699999999999</v>
+        <v>0.083133</v>
       </c>
       <c r="C703" t="n">
         <v>0.238693</v>
@@ -9566,7 +9566,7 @@
         </is>
       </c>
       <c r="B704" t="n">
-        <v>0.08305999999999999</v>
+        <v>0.08314100000000001</v>
       </c>
       <c r="C704" t="n">
         <v>0.236181</v>
@@ -9579,7 +9579,7 @@
         </is>
       </c>
       <c r="B705" t="n">
-        <v>0.08361</v>
+        <v>0.08361300000000001</v>
       </c>
       <c r="C705" t="n">
         <v>0.233668</v>
@@ -9592,7 +9592,7 @@
         </is>
       </c>
       <c r="B706" t="n">
-        <v>0.083629</v>
+        <v>0.083665</v>
       </c>
       <c r="C706" t="n">
         <v>0.231156</v>
@@ -9605,7 +9605,7 @@
         </is>
       </c>
       <c r="B707" t="n">
-        <v>0.085511</v>
+        <v>0.08566699999999999</v>
       </c>
       <c r="C707" t="n">
         <v>0.228643</v>
@@ -9618,7 +9618,7 @@
         </is>
       </c>
       <c r="B708" t="n">
-        <v>0.085603</v>
+        <v>0.085799</v>
       </c>
       <c r="C708" t="n">
         <v>0.226131</v>
@@ -9631,7 +9631,7 @@
         </is>
       </c>
       <c r="B709" t="n">
-        <v>0.086044</v>
+        <v>0.08607099999999999</v>
       </c>
       <c r="C709" t="n">
         <v>0.223618</v>
@@ -9644,7 +9644,7 @@
         </is>
       </c>
       <c r="B710" t="n">
-        <v>0.08645600000000001</v>
+        <v>0.086447</v>
       </c>
       <c r="C710" t="n">
         <v>0.221106</v>
@@ -9657,7 +9657,7 @@
         </is>
       </c>
       <c r="B711" t="n">
-        <v>0.087834</v>
+        <v>0.087812</v>
       </c>
       <c r="C711" t="n">
         <v>0.218593</v>
@@ -9683,7 +9683,7 @@
         </is>
       </c>
       <c r="B713" t="n">
-        <v>0.088805</v>
+        <v>0.08880399999999999</v>
       </c>
       <c r="C713" t="n">
         <v>0.213568</v>
@@ -9696,7 +9696,7 @@
         </is>
       </c>
       <c r="B714" t="n">
-        <v>0.088905</v>
+        <v>0.088922</v>
       </c>
       <c r="C714" t="n">
         <v>0.211055</v>
@@ -9709,7 +9709,7 @@
         </is>
       </c>
       <c r="B715" t="n">
-        <v>0.091015</v>
+        <v>0.090993</v>
       </c>
       <c r="C715" t="n">
         <v>0.208543</v>
@@ -9722,7 +9722,7 @@
         </is>
       </c>
       <c r="B716" t="n">
-        <v>0.092117</v>
+        <v>0.092151</v>
       </c>
       <c r="C716" t="n">
         <v>0.20603</v>
@@ -9735,7 +9735,7 @@
         </is>
       </c>
       <c r="B717" t="n">
-        <v>0.09227299999999999</v>
+        <v>0.092318</v>
       </c>
       <c r="C717" t="n">
         <v>0.203518</v>
@@ -9748,7 +9748,7 @@
         </is>
       </c>
       <c r="B718" t="n">
-        <v>0.09246799999999999</v>
+        <v>0.092442</v>
       </c>
       <c r="C718" t="n">
         <v>0.201005</v>
@@ -9761,7 +9761,7 @@
         </is>
       </c>
       <c r="B719" t="n">
-        <v>0.093531</v>
+        <v>0.093721</v>
       </c>
       <c r="C719" t="n">
         <v>0.198492</v>
@@ -9774,7 +9774,7 @@
         </is>
       </c>
       <c r="B720" t="n">
-        <v>0.09439500000000001</v>
+        <v>0.09481299999999999</v>
       </c>
       <c r="C720" t="n">
         <v>0.19598</v>
@@ -9787,7 +9787,7 @@
         </is>
       </c>
       <c r="B721" t="n">
-        <v>0.09543</v>
+        <v>0.095403</v>
       </c>
       <c r="C721" t="n">
         <v>0.193467</v>
@@ -9800,7 +9800,7 @@
         </is>
       </c>
       <c r="B722" t="n">
-        <v>0.09578299999999999</v>
+        <v>0.095761</v>
       </c>
       <c r="C722" t="n">
         <v>0.190955</v>
@@ -9813,7 +9813,7 @@
         </is>
       </c>
       <c r="B723" t="n">
-        <v>0.095841</v>
+        <v>0.09593</v>
       </c>
       <c r="C723" t="n">
         <v>0.188442</v>
@@ -9826,7 +9826,7 @@
         </is>
       </c>
       <c r="B724" t="n">
-        <v>0.096613</v>
+        <v>0.09658600000000001</v>
       </c>
       <c r="C724" t="n">
         <v>0.18593</v>
@@ -9839,7 +9839,7 @@
         </is>
       </c>
       <c r="B725" t="n">
-        <v>0.097264</v>
+        <v>0.097386</v>
       </c>
       <c r="C725" t="n">
         <v>0.183417</v>
@@ -9852,7 +9852,7 @@
         </is>
       </c>
       <c r="B726" t="n">
-        <v>0.0978</v>
+        <v>0.097841</v>
       </c>
       <c r="C726" t="n">
         <v>0.180905</v>
@@ -9865,7 +9865,7 @@
         </is>
       </c>
       <c r="B727" t="n">
-        <v>0.09805700000000001</v>
+        <v>0.098048</v>
       </c>
       <c r="C727" t="n">
         <v>0.178392</v>
@@ -9878,7 +9878,7 @@
         </is>
       </c>
       <c r="B728" t="n">
-        <v>0.099347</v>
+        <v>0.099486</v>
       </c>
       <c r="C728" t="n">
         <v>0.175879</v>
@@ -9891,7 +9891,7 @@
         </is>
       </c>
       <c r="B729" t="n">
-        <v>0.099823</v>
+        <v>0.0998</v>
       </c>
       <c r="C729" t="n">
         <v>0.173367</v>
@@ -9904,7 +9904,7 @@
         </is>
       </c>
       <c r="B730" t="n">
-        <v>0.100432</v>
+        <v>0.100465</v>
       </c>
       <c r="C730" t="n">
         <v>0.170854</v>
@@ -9917,7 +9917,7 @@
         </is>
       </c>
       <c r="B731" t="n">
-        <v>0.100487</v>
+        <v>0.10048</v>
       </c>
       <c r="C731" t="n">
         <v>0.168342</v>
@@ -9930,7 +9930,7 @@
         </is>
       </c>
       <c r="B732" t="n">
-        <v>0.101613</v>
+        <v>0.101716</v>
       </c>
       <c r="C732" t="n">
         <v>0.165829</v>
@@ -9943,7 +9943,7 @@
         </is>
       </c>
       <c r="B733" t="n">
-        <v>0.102349</v>
+        <v>0.102325</v>
       </c>
       <c r="C733" t="n">
         <v>0.163317</v>
@@ -9956,7 +9956,7 @@
         </is>
       </c>
       <c r="B734" t="n">
-        <v>0.102395</v>
+        <v>0.10243</v>
       </c>
       <c r="C734" t="n">
         <v>0.160804</v>
@@ -9969,7 +9969,7 @@
         </is>
       </c>
       <c r="B735" t="n">
-        <v>0.103921</v>
+        <v>0.103894</v>
       </c>
       <c r="C735" t="n">
         <v>0.158291</v>
@@ -9982,7 +9982,7 @@
         </is>
       </c>
       <c r="B736" t="n">
-        <v>0.109265</v>
+        <v>0.109281</v>
       </c>
       <c r="C736" t="n">
         <v>0.155779</v>
@@ -9995,7 +9995,7 @@
         </is>
       </c>
       <c r="B737" t="n">
-        <v>0.109542</v>
+        <v>0.109517</v>
       </c>
       <c r="C737" t="n">
         <v>0.153266</v>
@@ -10008,7 +10008,7 @@
         </is>
       </c>
       <c r="B738" t="n">
-        <v>0.109547</v>
+        <v>0.10956</v>
       </c>
       <c r="C738" t="n">
         <v>0.150754</v>
@@ -10021,7 +10021,7 @@
         </is>
       </c>
       <c r="B739" t="n">
-        <v>0.109593</v>
+        <v>0.109576</v>
       </c>
       <c r="C739" t="n">
         <v>0.148241</v>
@@ -10034,7 +10034,7 @@
         </is>
       </c>
       <c r="B740" t="n">
-        <v>0.109882</v>
+        <v>0.109873</v>
       </c>
       <c r="C740" t="n">
         <v>0.145729</v>
@@ -10047,7 +10047,7 @@
         </is>
       </c>
       <c r="B741" t="n">
-        <v>0.110574</v>
+        <v>0.110623</v>
       </c>
       <c r="C741" t="n">
         <v>0.143216</v>
@@ -10060,7 +10060,7 @@
         </is>
       </c>
       <c r="B742" t="n">
-        <v>0.112118</v>
+        <v>0.112101</v>
       </c>
       <c r="C742" t="n">
         <v>0.140704</v>
@@ -10073,7 +10073,7 @@
         </is>
       </c>
       <c r="B743" t="n">
-        <v>0.11398</v>
+        <v>0.113949</v>
       </c>
       <c r="C743" t="n">
         <v>0.138191</v>
@@ -10086,7 +10086,7 @@
         </is>
       </c>
       <c r="B744" t="n">
-        <v>0.116061</v>
+        <v>0.116135</v>
       </c>
       <c r="C744" t="n">
         <v>0.135678</v>
@@ -10099,7 +10099,7 @@
         </is>
       </c>
       <c r="B745" t="n">
-        <v>0.119087</v>
+        <v>0.119412</v>
       </c>
       <c r="C745" t="n">
         <v>0.133166</v>
@@ -10112,7 +10112,7 @@
         </is>
       </c>
       <c r="B746" t="n">
-        <v>0.119619</v>
+        <v>0.119668</v>
       </c>
       <c r="C746" t="n">
         <v>0.130653</v>
@@ -10125,7 +10125,7 @@
         </is>
       </c>
       <c r="B747" t="n">
-        <v>0.119653</v>
+        <v>0.119724</v>
       </c>
       <c r="C747" t="n">
         <v>0.128141</v>
@@ -10138,7 +10138,7 @@
         </is>
       </c>
       <c r="B748" t="n">
-        <v>0.121035</v>
+        <v>0.121149</v>
       </c>
       <c r="C748" t="n">
         <v>0.125628</v>
@@ -10151,7 +10151,7 @@
         </is>
       </c>
       <c r="B749" t="n">
-        <v>0.121528</v>
+        <v>0.121502</v>
       </c>
       <c r="C749" t="n">
         <v>0.123116</v>
@@ -10164,7 +10164,7 @@
         </is>
       </c>
       <c r="B750" t="n">
-        <v>0.12322</v>
+        <v>0.123301</v>
       </c>
       <c r="C750" t="n">
         <v>0.120603</v>
@@ -10177,7 +10177,7 @@
         </is>
       </c>
       <c r="B751" t="n">
-        <v>0.123557</v>
+        <v>0.123606</v>
       </c>
       <c r="C751" t="n">
         <v>0.11809</v>
@@ -10190,7 +10190,7 @@
         </is>
       </c>
       <c r="B752" t="n">
-        <v>0.12615</v>
+        <v>0.126194</v>
       </c>
       <c r="C752" t="n">
         <v>0.115578</v>
@@ -10203,7 +10203,7 @@
         </is>
       </c>
       <c r="B753" t="n">
-        <v>0.126728</v>
+        <v>0.127097</v>
       </c>
       <c r="C753" t="n">
         <v>0.113065</v>
@@ -10216,7 +10216,7 @@
         </is>
       </c>
       <c r="B754" t="n">
-        <v>0.12749</v>
+        <v>0.127793</v>
       </c>
       <c r="C754" t="n">
         <v>0.110553</v>
@@ -10229,7 +10229,7 @@
         </is>
       </c>
       <c r="B755" t="n">
-        <v>0.130624</v>
+        <v>0.130605</v>
       </c>
       <c r="C755" t="n">
         <v>0.10804</v>
@@ -10242,7 +10242,7 @@
         </is>
       </c>
       <c r="B756" t="n">
-        <v>0.131116</v>
+        <v>0.131158</v>
       </c>
       <c r="C756" t="n">
         <v>0.105528</v>
@@ -10255,7 +10255,7 @@
         </is>
       </c>
       <c r="B757" t="n">
-        <v>0.131371</v>
+        <v>0.131355</v>
       </c>
       <c r="C757" t="n">
         <v>0.103015</v>
@@ -10268,7 +10268,7 @@
         </is>
       </c>
       <c r="B758" t="n">
-        <v>0.133053</v>
+        <v>0.133056</v>
       </c>
       <c r="C758" t="n">
         <v>0.100503</v>
@@ -10281,7 +10281,7 @@
         </is>
       </c>
       <c r="B759" t="n">
-        <v>0.13632</v>
+        <v>0.136293</v>
       </c>
       <c r="C759" t="n">
         <v>0.09798999999999999</v>
@@ -10294,7 +10294,7 @@
         </is>
       </c>
       <c r="B760" t="n">
-        <v>0.136322</v>
+        <v>0.136314</v>
       </c>
       <c r="C760" t="n">
         <v>0.09547700000000001</v>
@@ -10307,7 +10307,7 @@
         </is>
       </c>
       <c r="B761" t="n">
-        <v>0.136884</v>
+        <v>0.136913</v>
       </c>
       <c r="C761" t="n">
         <v>0.09296500000000001</v>
@@ -10320,7 +10320,7 @@
         </is>
       </c>
       <c r="B762" t="n">
-        <v>0.137248</v>
+        <v>0.137498</v>
       </c>
       <c r="C762" t="n">
         <v>0.090452</v>
@@ -10333,7 +10333,7 @@
         </is>
       </c>
       <c r="B763" t="n">
-        <v>0.139299</v>
+        <v>0.139296</v>
       </c>
       <c r="C763" t="n">
         <v>0.08794</v>
@@ -10346,7 +10346,7 @@
         </is>
       </c>
       <c r="B764" t="n">
-        <v>0.141219</v>
+        <v>0.141222</v>
       </c>
       <c r="C764" t="n">
         <v>0.085427</v>
@@ -10359,7 +10359,7 @@
         </is>
       </c>
       <c r="B765" t="n">
-        <v>0.142442</v>
+        <v>0.142491</v>
       </c>
       <c r="C765" t="n">
         <v>0.082915</v>
@@ -10372,7 +10372,7 @@
         </is>
       </c>
       <c r="B766" t="n">
-        <v>0.142822</v>
+        <v>0.142816</v>
       </c>
       <c r="C766" t="n">
         <v>0.080402</v>
@@ -10385,7 +10385,7 @@
         </is>
       </c>
       <c r="B767" t="n">
-        <v>0.143551</v>
+        <v>0.143518</v>
       </c>
       <c r="C767" t="n">
         <v>0.077889</v>
@@ -10398,7 +10398,7 @@
         </is>
       </c>
       <c r="B768" t="n">
-        <v>0.145185</v>
+        <v>0.145162</v>
       </c>
       <c r="C768" t="n">
         <v>0.075377</v>
@@ -10411,7 +10411,7 @@
         </is>
       </c>
       <c r="B769" t="n">
-        <v>0.153528</v>
+        <v>0.153553</v>
       </c>
       <c r="C769" t="n">
         <v>0.072864</v>
@@ -10424,7 +10424,7 @@
         </is>
       </c>
       <c r="B770" t="n">
-        <v>0.156252</v>
+        <v>0.156313</v>
       </c>
       <c r="C770" t="n">
         <v>0.070352</v>
@@ -10437,7 +10437,7 @@
         </is>
       </c>
       <c r="B771" t="n">
-        <v>0.159995</v>
+        <v>0.16014</v>
       </c>
       <c r="C771" t="n">
         <v>0.067839</v>
@@ -10450,7 +10450,7 @@
         </is>
       </c>
       <c r="B772" t="n">
-        <v>0.160384</v>
+        <v>0.160339</v>
       </c>
       <c r="C772" t="n">
         <v>0.065327</v>
@@ -10463,7 +10463,7 @@
         </is>
       </c>
       <c r="B773" t="n">
-        <v>0.161266</v>
+        <v>0.161282</v>
       </c>
       <c r="C773" t="n">
         <v>0.06281399999999999</v>
@@ -10476,7 +10476,7 @@
         </is>
       </c>
       <c r="B774" t="n">
-        <v>0.170738</v>
+        <v>0.170712</v>
       </c>
       <c r="C774" t="n">
         <v>0.060302</v>
@@ -10489,7 +10489,7 @@
         </is>
       </c>
       <c r="B775" t="n">
-        <v>0.175768</v>
+        <v>0.175718</v>
       </c>
       <c r="C775" t="n">
         <v>0.057789</v>
@@ -10502,7 +10502,7 @@
         </is>
       </c>
       <c r="B776" t="n">
-        <v>0.180637</v>
+        <v>0.180963</v>
       </c>
       <c r="C776" t="n">
         <v>0.055276</v>
@@ -10515,7 +10515,7 @@
         </is>
       </c>
       <c r="B777" t="n">
-        <v>0.180855</v>
+        <v>0.181119</v>
       </c>
       <c r="C777" t="n">
         <v>0.052764</v>
@@ -10528,7 +10528,7 @@
         </is>
       </c>
       <c r="B778" t="n">
-        <v>0.181561</v>
+        <v>0.181514</v>
       </c>
       <c r="C778" t="n">
         <v>0.050251</v>
@@ -10541,7 +10541,7 @@
         </is>
       </c>
       <c r="B779" t="n">
-        <v>0.182641</v>
+        <v>0.182595</v>
       </c>
       <c r="C779" t="n">
         <v>0.047739</v>
@@ -10554,7 +10554,7 @@
         </is>
       </c>
       <c r="B780" t="n">
-        <v>0.186446</v>
+        <v>0.186411</v>
       </c>
       <c r="C780" t="n">
         <v>0.045226</v>
@@ -10567,7 +10567,7 @@
         </is>
       </c>
       <c r="B781" t="n">
-        <v>0.187043</v>
+        <v>0.187097</v>
       </c>
       <c r="C781" t="n">
         <v>0.042714</v>
@@ -10580,7 +10580,7 @@
         </is>
       </c>
       <c r="B782" t="n">
-        <v>0.188646</v>
+        <v>0.188841</v>
       </c>
       <c r="C782" t="n">
         <v>0.040201</v>
@@ -10593,7 +10593,7 @@
         </is>
       </c>
       <c r="B783" t="n">
-        <v>0.189913</v>
+        <v>0.19019</v>
       </c>
       <c r="C783" t="n">
         <v>0.037688</v>
@@ -10606,7 +10606,7 @@
         </is>
       </c>
       <c r="B784" t="n">
-        <v>0.197461</v>
+        <v>0.197482</v>
       </c>
       <c r="C784" t="n">
         <v>0.035176</v>
@@ -10619,7 +10619,7 @@
         </is>
       </c>
       <c r="B785" t="n">
-        <v>0.200467</v>
+        <v>0.200888</v>
       </c>
       <c r="C785" t="n">
         <v>0.032663</v>
@@ -10632,7 +10632,7 @@
         </is>
       </c>
       <c r="B786" t="n">
-        <v>0.207966</v>
+        <v>0.207983</v>
       </c>
       <c r="C786" t="n">
         <v>0.030151</v>
@@ -10645,7 +10645,7 @@
         </is>
       </c>
       <c r="B787" t="n">
-        <v>0.221318</v>
+        <v>0.221327</v>
       </c>
       <c r="C787" t="n">
         <v>0.027638</v>
@@ -10658,7 +10658,7 @@
         </is>
       </c>
       <c r="B788" t="n">
-        <v>0.245136</v>
+        <v>0.245114</v>
       </c>
       <c r="C788" t="n">
         <v>0.025126</v>
@@ -10671,7 +10671,7 @@
         </is>
       </c>
       <c r="B789" t="n">
-        <v>0.248924</v>
+        <v>0.249245</v>
       </c>
       <c r="C789" t="n">
         <v>0.022613</v>
@@ -10684,7 +10684,7 @@
         </is>
       </c>
       <c r="B790" t="n">
-        <v>0.260321</v>
+        <v>0.260509</v>
       </c>
       <c r="C790" t="n">
         <v>0.020101</v>
@@ -10697,7 +10697,7 @@
         </is>
       </c>
       <c r="B791" t="n">
-        <v>0.263619</v>
+        <v>0.263815</v>
       </c>
       <c r="C791" t="n">
         <v>0.017588</v>
@@ -10710,7 +10710,7 @@
         </is>
       </c>
       <c r="B792" t="n">
-        <v>0.266352</v>
+        <v>0.2669</v>
       </c>
       <c r="C792" t="n">
         <v>0.015075</v>
@@ -10723,7 +10723,7 @@
         </is>
       </c>
       <c r="B793" t="n">
-        <v>0.274368</v>
+        <v>0.274307</v>
       </c>
       <c r="C793" t="n">
         <v>0.012563</v>
@@ -10736,7 +10736,7 @@
         </is>
       </c>
       <c r="B794" t="n">
-        <v>0.330368</v>
+        <v>0.33048</v>
       </c>
       <c r="C794" t="n">
         <v>0.01005</v>
@@ -10749,7 +10749,7 @@
         </is>
       </c>
       <c r="B795" t="n">
-        <v>0.347965</v>
+        <v>0.347869</v>
       </c>
       <c r="C795" t="n">
         <v>0.007538</v>
@@ -10762,7 +10762,7 @@
         </is>
       </c>
       <c r="B796" t="n">
-        <v>0.359432</v>
+        <v>0.35942</v>
       </c>
       <c r="C796" t="n">
         <v>0.005025</v>
@@ -10775,7 +10775,7 @@
         </is>
       </c>
       <c r="B797" t="n">
-        <v>0.503824</v>
+        <v>0.5037</v>
       </c>
       <c r="C797" t="n">
         <v>0.002513</v>

--- a/vignettes/vignette-1/tail_exceedance_plot_data.xlsx
+++ b/vignettes/vignette-1/tail_exceedance_plot_data.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C797"/>
+  <dimension ref="A1:C789"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -456,7 +456,7 @@
         <v>0.000441</v>
       </c>
       <c r="C3" t="n">
-        <v>0.997487</v>
+        <v>0.997462</v>
       </c>
     </row>
     <row r="4">
@@ -469,7 +469,7 @@
         <v>0.000608</v>
       </c>
       <c r="C4" t="n">
-        <v>0.9949750000000001</v>
+        <v>0.994924</v>
       </c>
     </row>
     <row r="5">
@@ -482,7 +482,7 @@
         <v>0.001141</v>
       </c>
       <c r="C5" t="n">
-        <v>0.992462</v>
+        <v>0.992386</v>
       </c>
     </row>
     <row r="6">
@@ -495,7 +495,7 @@
         <v>0.001163</v>
       </c>
       <c r="C6" t="n">
-        <v>0.98995</v>
+        <v>0.989848</v>
       </c>
     </row>
     <row r="7">
@@ -508,7 +508,7 @@
         <v>0.001681</v>
       </c>
       <c r="C7" t="n">
-        <v>0.987437</v>
+        <v>0.98731</v>
       </c>
     </row>
     <row r="8">
@@ -521,7 +521,7 @@
         <v>0.002113</v>
       </c>
       <c r="C8" t="n">
-        <v>0.9849250000000001</v>
+        <v>0.984772</v>
       </c>
     </row>
     <row r="9">
@@ -534,7 +534,7 @@
         <v>0.002155</v>
       </c>
       <c r="C9" t="n">
-        <v>0.982412</v>
+        <v>0.9822340000000001</v>
       </c>
     </row>
     <row r="10">
@@ -547,7 +547,7 @@
         <v>0.002259</v>
       </c>
       <c r="C10" t="n">
-        <v>0.979899</v>
+        <v>0.979695</v>
       </c>
     </row>
     <row r="11">
@@ -560,7 +560,7 @@
         <v>0.00295</v>
       </c>
       <c r="C11" t="n">
-        <v>0.977387</v>
+        <v>0.9771570000000001</v>
       </c>
     </row>
     <row r="12">
@@ -573,7 +573,7 @@
         <v>0.002998</v>
       </c>
       <c r="C12" t="n">
-        <v>0.974874</v>
+        <v>0.974619</v>
       </c>
     </row>
     <row r="13">
@@ -586,7 +586,7 @@
         <v>0.003455</v>
       </c>
       <c r="C13" t="n">
-        <v>0.9723619999999999</v>
+        <v>0.972081</v>
       </c>
     </row>
     <row r="14">
@@ -599,7 +599,7 @@
         <v>0.003769</v>
       </c>
       <c r="C14" t="n">
-        <v>0.969849</v>
+        <v>0.969543</v>
       </c>
     </row>
     <row r="15">
@@ -612,7 +612,7 @@
         <v>0.003788</v>
       </c>
       <c r="C15" t="n">
-        <v>0.967337</v>
+        <v>0.967005</v>
       </c>
     </row>
     <row r="16">
@@ -625,7 +625,7 @@
         <v>0.003948</v>
       </c>
       <c r="C16" t="n">
-        <v>0.964824</v>
+        <v>0.964467</v>
       </c>
     </row>
     <row r="17">
@@ -638,7 +638,7 @@
         <v>0.004039</v>
       </c>
       <c r="C17" t="n">
-        <v>0.9623119999999999</v>
+        <v>0.961929</v>
       </c>
     </row>
     <row r="18">
@@ -651,7 +651,7 @@
         <v>0.004622</v>
       </c>
       <c r="C18" t="n">
-        <v>0.959799</v>
+        <v>0.959391</v>
       </c>
     </row>
     <row r="19">
@@ -664,7 +664,7 @@
         <v>0.004717</v>
       </c>
       <c r="C19" t="n">
-        <v>0.957286</v>
+        <v>0.956853</v>
       </c>
     </row>
     <row r="20">
@@ -677,7 +677,7 @@
         <v>0.004779</v>
       </c>
       <c r="C20" t="n">
-        <v>0.954774</v>
+        <v>0.954315</v>
       </c>
     </row>
     <row r="21">
@@ -690,7 +690,7 @@
         <v>0.004912</v>
       </c>
       <c r="C21" t="n">
-        <v>0.952261</v>
+        <v>0.951777</v>
       </c>
     </row>
     <row r="22">
@@ -703,7 +703,7 @@
         <v>0.005429</v>
       </c>
       <c r="C22" t="n">
-        <v>0.949749</v>
+        <v>0.9492390000000001</v>
       </c>
     </row>
     <row r="23">
@@ -716,7 +716,7 @@
         <v>0.005649</v>
       </c>
       <c r="C23" t="n">
-        <v>0.947236</v>
+        <v>0.946701</v>
       </c>
     </row>
     <row r="24">
@@ -729,7 +729,7 @@
         <v>0.00593</v>
       </c>
       <c r="C24" t="n">
-        <v>0.944724</v>
+        <v>0.9441619999999999</v>
       </c>
     </row>
     <row r="25">
@@ -742,7 +742,7 @@
         <v>0.006143</v>
       </c>
       <c r="C25" t="n">
-        <v>0.942211</v>
+        <v>0.941624</v>
       </c>
     </row>
     <row r="26">
@@ -755,7 +755,7 @@
         <v>0.006328</v>
       </c>
       <c r="C26" t="n">
-        <v>0.939698</v>
+        <v>0.939086</v>
       </c>
     </row>
     <row r="27">
@@ -768,7 +768,7 @@
         <v>0.006394</v>
       </c>
       <c r="C27" t="n">
-        <v>0.937186</v>
+        <v>0.936548</v>
       </c>
     </row>
     <row r="28">
@@ -781,7 +781,7 @@
         <v>0.007419</v>
       </c>
       <c r="C28" t="n">
-        <v>0.934673</v>
+        <v>0.93401</v>
       </c>
     </row>
     <row r="29">
@@ -794,7 +794,7 @@
         <v>0.007582</v>
       </c>
       <c r="C29" t="n">
-        <v>0.932161</v>
+        <v>0.931472</v>
       </c>
     </row>
     <row r="30">
@@ -807,7 +807,7 @@
         <v>0.008029</v>
       </c>
       <c r="C30" t="n">
-        <v>0.929648</v>
+        <v>0.928934</v>
       </c>
     </row>
     <row r="31">
@@ -820,7 +820,7 @@
         <v>0.008069</v>
       </c>
       <c r="C31" t="n">
-        <v>0.927136</v>
+        <v>0.926396</v>
       </c>
     </row>
     <row r="32">
@@ -833,7 +833,7 @@
         <v>0.008173</v>
       </c>
       <c r="C32" t="n">
-        <v>0.924623</v>
+        <v>0.923858</v>
       </c>
     </row>
     <row r="33">
@@ -846,7 +846,7 @@
         <v>0.008333999999999999</v>
       </c>
       <c r="C33" t="n">
-        <v>0.922111</v>
+        <v>0.92132</v>
       </c>
     </row>
     <row r="34">
@@ -859,7 +859,7 @@
         <v>0.008544</v>
       </c>
       <c r="C34" t="n">
-        <v>0.919598</v>
+        <v>0.918782</v>
       </c>
     </row>
     <row r="35">
@@ -872,7 +872,7 @@
         <v>0.008593999999999999</v>
       </c>
       <c r="C35" t="n">
-        <v>0.917085</v>
+        <v>0.9162439999999999</v>
       </c>
     </row>
     <row r="36">
@@ -885,7 +885,7 @@
         <v>0.009011</v>
       </c>
       <c r="C36" t="n">
-        <v>0.914573</v>
+        <v>0.913706</v>
       </c>
     </row>
     <row r="37">
@@ -898,7 +898,7 @@
         <v>0.009165</v>
       </c>
       <c r="C37" t="n">
-        <v>0.91206</v>
+        <v>0.911168</v>
       </c>
     </row>
     <row r="38">
@@ -911,7 +911,7 @@
         <v>0.009428000000000001</v>
       </c>
       <c r="C38" t="n">
-        <v>0.909548</v>
+        <v>0.908629</v>
       </c>
     </row>
     <row r="39">
@@ -924,7 +924,7 @@
         <v>0.009578</v>
       </c>
       <c r="C39" t="n">
-        <v>0.907035</v>
+        <v>0.906091</v>
       </c>
     </row>
     <row r="40">
@@ -937,7 +937,7 @@
         <v>0.009774</v>
       </c>
       <c r="C40" t="n">
-        <v>0.904523</v>
+        <v>0.9035530000000001</v>
       </c>
     </row>
     <row r="41">
@@ -950,7 +950,7 @@
         <v>0.009811</v>
       </c>
       <c r="C41" t="n">
-        <v>0.90201</v>
+        <v>0.901015</v>
       </c>
     </row>
     <row r="42">
@@ -963,7 +963,7 @@
         <v>0.010226</v>
       </c>
       <c r="C42" t="n">
-        <v>0.899497</v>
+        <v>0.898477</v>
       </c>
     </row>
     <row r="43">
@@ -976,7 +976,7 @@
         <v>0.010518</v>
       </c>
       <c r="C43" t="n">
-        <v>0.896985</v>
+        <v>0.895939</v>
       </c>
     </row>
     <row r="44">
@@ -989,7 +989,7 @@
         <v>0.010943</v>
       </c>
       <c r="C44" t="n">
-        <v>0.894472</v>
+        <v>0.893401</v>
       </c>
     </row>
     <row r="45">
@@ -1002,7 +1002,7 @@
         <v>0.011156</v>
       </c>
       <c r="C45" t="n">
-        <v>0.89196</v>
+        <v>0.890863</v>
       </c>
     </row>
     <row r="46">
@@ -1015,7 +1015,7 @@
         <v>0.01117</v>
       </c>
       <c r="C46" t="n">
-        <v>0.889447</v>
+        <v>0.888325</v>
       </c>
     </row>
     <row r="47">
@@ -1028,7 +1028,7 @@
         <v>0.011326</v>
       </c>
       <c r="C47" t="n">
-        <v>0.886935</v>
+        <v>0.885787</v>
       </c>
     </row>
     <row r="48">
@@ -1041,7 +1041,7 @@
         <v>0.01145</v>
       </c>
       <c r="C48" t="n">
-        <v>0.884422</v>
+        <v>0.883249</v>
       </c>
     </row>
     <row r="49">
@@ -1054,7 +1054,7 @@
         <v>0.011715</v>
       </c>
       <c r="C49" t="n">
-        <v>0.88191</v>
+        <v>0.880711</v>
       </c>
     </row>
     <row r="50">
@@ -1067,7 +1067,7 @@
         <v>0.011815</v>
       </c>
       <c r="C50" t="n">
-        <v>0.879397</v>
+        <v>0.878173</v>
       </c>
     </row>
     <row r="51">
@@ -1080,7 +1080,7 @@
         <v>0.012035</v>
       </c>
       <c r="C51" t="n">
-        <v>0.876884</v>
+        <v>0.8756350000000001</v>
       </c>
     </row>
     <row r="52">
@@ -1093,7 +1093,7 @@
         <v>0.012336</v>
       </c>
       <c r="C52" t="n">
-        <v>0.874372</v>
+        <v>0.873096</v>
       </c>
     </row>
     <row r="53">
@@ -1106,7 +1106,7 @@
         <v>0.012459</v>
       </c>
       <c r="C53" t="n">
-        <v>0.8718590000000001</v>
+        <v>0.8705580000000001</v>
       </c>
     </row>
     <row r="54">
@@ -1119,7 +1119,7 @@
         <v>0.012747</v>
       </c>
       <c r="C54" t="n">
-        <v>0.869347</v>
+        <v>0.86802</v>
       </c>
     </row>
     <row r="55">
@@ -1132,7 +1132,7 @@
         <v>0.012918</v>
       </c>
       <c r="C55" t="n">
-        <v>0.866834</v>
+        <v>0.865482</v>
       </c>
     </row>
     <row r="56">
@@ -1145,7 +1145,7 @@
         <v>0.013202</v>
       </c>
       <c r="C56" t="n">
-        <v>0.864322</v>
+        <v>0.862944</v>
       </c>
     </row>
     <row r="57">
@@ -1158,7 +1158,7 @@
         <v>0.013714</v>
       </c>
       <c r="C57" t="n">
-        <v>0.861809</v>
+        <v>0.860406</v>
       </c>
     </row>
     <row r="58">
@@ -1171,7 +1171,7 @@
         <v>0.01393</v>
       </c>
       <c r="C58" t="n">
-        <v>0.8592959999999999</v>
+        <v>0.857868</v>
       </c>
     </row>
     <row r="59">
@@ -1184,7 +1184,7 @@
         <v>0.013971</v>
       </c>
       <c r="C59" t="n">
-        <v>0.856784</v>
+        <v>0.85533</v>
       </c>
     </row>
     <row r="60">
@@ -1197,7 +1197,7 @@
         <v>0.014018</v>
       </c>
       <c r="C60" t="n">
-        <v>0.854271</v>
+        <v>0.852792</v>
       </c>
     </row>
     <row r="61">
@@ -1210,7 +1210,7 @@
         <v>0.01417</v>
       </c>
       <c r="C61" t="n">
-        <v>0.851759</v>
+        <v>0.850254</v>
       </c>
     </row>
     <row r="62">
@@ -1223,7 +1223,7 @@
         <v>0.014481</v>
       </c>
       <c r="C62" t="n">
-        <v>0.8492459999999999</v>
+        <v>0.847716</v>
       </c>
     </row>
     <row r="63">
@@ -1236,7 +1236,7 @@
         <v>0.014731</v>
       </c>
       <c r="C63" t="n">
-        <v>0.846734</v>
+        <v>0.845178</v>
       </c>
     </row>
     <row r="64">
@@ -1249,7 +1249,7 @@
         <v>0.014841</v>
       </c>
       <c r="C64" t="n">
-        <v>0.844221</v>
+        <v>0.8426399999999999</v>
       </c>
     </row>
     <row r="65">
@@ -1262,7 +1262,7 @@
         <v>0.015041</v>
       </c>
       <c r="C65" t="n">
-        <v>0.841709</v>
+        <v>0.840102</v>
       </c>
     </row>
     <row r="66">
@@ -1275,7 +1275,7 @@
         <v>0.015107</v>
       </c>
       <c r="C66" t="n">
-        <v>0.8391960000000001</v>
+        <v>0.8375629999999999</v>
       </c>
     </row>
     <row r="67">
@@ -1288,7 +1288,7 @@
         <v>0.015107</v>
       </c>
       <c r="C67" t="n">
-        <v>0.836683</v>
+        <v>0.835025</v>
       </c>
     </row>
     <row r="68">
@@ -1301,7 +1301,7 @@
         <v>0.015553</v>
       </c>
       <c r="C68" t="n">
-        <v>0.834171</v>
+        <v>0.832487</v>
       </c>
     </row>
     <row r="69">
@@ -1314,7 +1314,7 @@
         <v>0.016031</v>
       </c>
       <c r="C69" t="n">
-        <v>0.831658</v>
+        <v>0.829949</v>
       </c>
     </row>
     <row r="70">
@@ -1327,7 +1327,7 @@
         <v>0.016343</v>
       </c>
       <c r="C70" t="n">
-        <v>0.829146</v>
+        <v>0.827411</v>
       </c>
     </row>
     <row r="71">
@@ -1340,7 +1340,7 @@
         <v>0.016345</v>
       </c>
       <c r="C71" t="n">
-        <v>0.826633</v>
+        <v>0.824873</v>
       </c>
     </row>
     <row r="72">
@@ -1353,7 +1353,7 @@
         <v>0.016545</v>
       </c>
       <c r="C72" t="n">
-        <v>0.824121</v>
+        <v>0.822335</v>
       </c>
     </row>
     <row r="73">
@@ -1366,7 +1366,7 @@
         <v>0.017135</v>
       </c>
       <c r="C73" t="n">
-        <v>0.821608</v>
+        <v>0.819797</v>
       </c>
     </row>
     <row r="74">
@@ -1379,7 +1379,7 @@
         <v>0.017276</v>
       </c>
       <c r="C74" t="n">
-        <v>0.819095</v>
+        <v>0.817259</v>
       </c>
     </row>
     <row r="75">
@@ -1392,7 +1392,7 @@
         <v>0.017537</v>
       </c>
       <c r="C75" t="n">
-        <v>0.8165829999999999</v>
+        <v>0.814721</v>
       </c>
     </row>
     <row r="76">
@@ -1405,7 +1405,7 @@
         <v>0.017621</v>
       </c>
       <c r="C76" t="n">
-        <v>0.81407</v>
+        <v>0.812183</v>
       </c>
     </row>
     <row r="77">
@@ -1418,7 +1418,7 @@
         <v>0.017975</v>
       </c>
       <c r="C77" t="n">
-        <v>0.811558</v>
+        <v>0.8096449999999999</v>
       </c>
     </row>
     <row r="78">
@@ -1431,7 +1431,7 @@
         <v>0.018225</v>
       </c>
       <c r="C78" t="n">
-        <v>0.809045</v>
+        <v>0.807107</v>
       </c>
     </row>
     <row r="79">
@@ -1444,7 +1444,7 @@
         <v>0.018505</v>
       </c>
       <c r="C79" t="n">
-        <v>0.8065330000000001</v>
+        <v>0.804569</v>
       </c>
     </row>
     <row r="80">
@@ -1457,7 +1457,7 @@
         <v>0.018757</v>
       </c>
       <c r="C80" t="n">
-        <v>0.80402</v>
+        <v>0.80203</v>
       </c>
     </row>
     <row r="81">
@@ -1470,7 +1470,7 @@
         <v>0.018801</v>
       </c>
       <c r="C81" t="n">
-        <v>0.801508</v>
+        <v>0.799492</v>
       </c>
     </row>
     <row r="82">
@@ -1483,7 +1483,7 @@
         <v>0.018847</v>
       </c>
       <c r="C82" t="n">
-        <v>0.798995</v>
+        <v>0.7969540000000001</v>
       </c>
     </row>
     <row r="83">
@@ -1496,7 +1496,7 @@
         <v>0.018931</v>
       </c>
       <c r="C83" t="n">
-        <v>0.796482</v>
+        <v>0.794416</v>
       </c>
     </row>
     <row r="84">
@@ -1509,7 +1509,7 @@
         <v>0.019049</v>
       </c>
       <c r="C84" t="n">
-        <v>0.79397</v>
+        <v>0.791878</v>
       </c>
     </row>
     <row r="85">
@@ -1522,7 +1522,7 @@
         <v>0.019288</v>
       </c>
       <c r="C85" t="n">
-        <v>0.791457</v>
+        <v>0.78934</v>
       </c>
     </row>
     <row r="86">
@@ -1535,7 +1535,7 @@
         <v>0.019352</v>
       </c>
       <c r="C86" t="n">
-        <v>0.788945</v>
+        <v>0.786802</v>
       </c>
     </row>
     <row r="87">
@@ -1548,7 +1548,7 @@
         <v>0.01962</v>
       </c>
       <c r="C87" t="n">
-        <v>0.786432</v>
+        <v>0.784264</v>
       </c>
     </row>
     <row r="88">
@@ -1561,7 +1561,7 @@
         <v>0.019953</v>
       </c>
       <c r="C88" t="n">
-        <v>0.78392</v>
+        <v>0.781726</v>
       </c>
     </row>
     <row r="89">
@@ -1574,7 +1574,7 @@
         <v>0.020186</v>
       </c>
       <c r="C89" t="n">
-        <v>0.781407</v>
+        <v>0.779188</v>
       </c>
     </row>
     <row r="90">
@@ -1587,7 +1587,7 @@
         <v>0.020393</v>
       </c>
       <c r="C90" t="n">
-        <v>0.778894</v>
+        <v>0.77665</v>
       </c>
     </row>
     <row r="91">
@@ -1600,7 +1600,7 @@
         <v>0.02048</v>
       </c>
       <c r="C91" t="n">
-        <v>0.776382</v>
+        <v>0.774112</v>
       </c>
     </row>
     <row r="92">
@@ -1613,7 +1613,7 @@
         <v>0.021399</v>
       </c>
       <c r="C92" t="n">
-        <v>0.773869</v>
+        <v>0.771574</v>
       </c>
     </row>
     <row r="93">
@@ -1626,7 +1626,7 @@
         <v>0.021572</v>
       </c>
       <c r="C93" t="n">
-        <v>0.771357</v>
+        <v>0.7690360000000001</v>
       </c>
     </row>
     <row r="94">
@@ -1639,7 +1639,7 @@
         <v>0.021604</v>
       </c>
       <c r="C94" t="n">
-        <v>0.768844</v>
+        <v>0.766497</v>
       </c>
     </row>
     <row r="95">
@@ -1652,7 +1652,7 @@
         <v>0.021912</v>
       </c>
       <c r="C95" t="n">
-        <v>0.766332</v>
+        <v>0.7639590000000001</v>
       </c>
     </row>
     <row r="96">
@@ -1665,7 +1665,7 @@
         <v>0.021918</v>
       </c>
       <c r="C96" t="n">
-        <v>0.763819</v>
+        <v>0.761421</v>
       </c>
     </row>
     <row r="97">
@@ -1678,7 +1678,7 @@
         <v>0.021962</v>
       </c>
       <c r="C97" t="n">
-        <v>0.761307</v>
+        <v>0.758883</v>
       </c>
     </row>
     <row r="98">
@@ -1691,7 +1691,7 @@
         <v>0.022008</v>
       </c>
       <c r="C98" t="n">
-        <v>0.758794</v>
+        <v>0.756345</v>
       </c>
     </row>
     <row r="99">
@@ -1704,7 +1704,7 @@
         <v>0.022011</v>
       </c>
       <c r="C99" t="n">
-        <v>0.756281</v>
+        <v>0.753807</v>
       </c>
     </row>
     <row r="100">
@@ -1717,7 +1717,7 @@
         <v>0.022299</v>
       </c>
       <c r="C100" t="n">
-        <v>0.753769</v>
+        <v>0.751269</v>
       </c>
     </row>
     <row r="101">
@@ -1730,7 +1730,7 @@
         <v>0.022324</v>
       </c>
       <c r="C101" t="n">
-        <v>0.751256</v>
+        <v>0.748731</v>
       </c>
     </row>
     <row r="102">
@@ -1743,7 +1743,7 @@
         <v>0.022543</v>
       </c>
       <c r="C102" t="n">
-        <v>0.748744</v>
+        <v>0.746193</v>
       </c>
     </row>
     <row r="103">
@@ -1756,7 +1756,7 @@
         <v>0.022891</v>
       </c>
       <c r="C103" t="n">
-        <v>0.746231</v>
+        <v>0.743655</v>
       </c>
     </row>
     <row r="104">
@@ -1769,7 +1769,7 @@
         <v>0.02306</v>
       </c>
       <c r="C104" t="n">
-        <v>0.743719</v>
+        <v>0.741117</v>
       </c>
     </row>
     <row r="105">
@@ -1782,7 +1782,7 @@
         <v>0.023483</v>
       </c>
       <c r="C105" t="n">
-        <v>0.741206</v>
+        <v>0.738579</v>
       </c>
     </row>
     <row r="106">
@@ -1795,7 +1795,7 @@
         <v>0.023676</v>
       </c>
       <c r="C106" t="n">
-        <v>0.738693</v>
+        <v>0.7360409999999999</v>
       </c>
     </row>
     <row r="107">
@@ -1808,7 +1808,7 @@
         <v>0.023901</v>
       </c>
       <c r="C107" t="n">
-        <v>0.736181</v>
+        <v>0.733503</v>
       </c>
     </row>
     <row r="108">
@@ -1821,7 +1821,7 @@
         <v>0.023991</v>
       </c>
       <c r="C108" t="n">
-        <v>0.733668</v>
+        <v>0.7309639999999999</v>
       </c>
     </row>
     <row r="109">
@@ -1834,7 +1834,7 @@
         <v>0.02408</v>
       </c>
       <c r="C109" t="n">
-        <v>0.731156</v>
+        <v>0.728426</v>
       </c>
     </row>
     <row r="110">
@@ -1847,7 +1847,7 @@
         <v>0.024413</v>
       </c>
       <c r="C110" t="n">
-        <v>0.728643</v>
+        <v>0.725888</v>
       </c>
     </row>
     <row r="111">
@@ -1860,7 +1860,7 @@
         <v>0.024763</v>
       </c>
       <c r="C111" t="n">
-        <v>0.726131</v>
+        <v>0.72335</v>
       </c>
     </row>
     <row r="112">
@@ -1873,7 +1873,7 @@
         <v>0.024837</v>
       </c>
       <c r="C112" t="n">
-        <v>0.723618</v>
+        <v>0.720812</v>
       </c>
     </row>
     <row r="113">
@@ -1886,7 +1886,7 @@
         <v>0.024896</v>
       </c>
       <c r="C113" t="n">
-        <v>0.721106</v>
+        <v>0.718274</v>
       </c>
     </row>
     <row r="114">
@@ -1899,7 +1899,7 @@
         <v>0.025416</v>
       </c>
       <c r="C114" t="n">
-        <v>0.718593</v>
+        <v>0.715736</v>
       </c>
     </row>
     <row r="115">
@@ -1912,7 +1912,7 @@
         <v>0.025755</v>
       </c>
       <c r="C115" t="n">
-        <v>0.71608</v>
+        <v>0.713198</v>
       </c>
     </row>
     <row r="116">
@@ -1925,7 +1925,7 @@
         <v>0.026032</v>
       </c>
       <c r="C116" t="n">
-        <v>0.713568</v>
+        <v>0.71066</v>
       </c>
     </row>
     <row r="117">
@@ -1938,7 +1938,7 @@
         <v>0.026545</v>
       </c>
       <c r="C117" t="n">
-        <v>0.711055</v>
+        <v>0.708122</v>
       </c>
     </row>
     <row r="118">
@@ -1951,7 +1951,7 @@
         <v>0.026628</v>
       </c>
       <c r="C118" t="n">
-        <v>0.708543</v>
+        <v>0.705584</v>
       </c>
     </row>
     <row r="119">
@@ -1964,7 +1964,7 @@
         <v>0.027214</v>
       </c>
       <c r="C119" t="n">
-        <v>0.70603</v>
+        <v>0.7030459999999999</v>
       </c>
     </row>
     <row r="120">
@@ -1977,7 +1977,7 @@
         <v>0.027321</v>
       </c>
       <c r="C120" t="n">
-        <v>0.703518</v>
+        <v>0.700508</v>
       </c>
     </row>
     <row r="121">
@@ -1990,7 +1990,7 @@
         <v>0.027355</v>
       </c>
       <c r="C121" t="n">
-        <v>0.701005</v>
+        <v>0.69797</v>
       </c>
     </row>
     <row r="122">
@@ -2003,7 +2003,7 @@
         <v>0.027413</v>
       </c>
       <c r="C122" t="n">
-        <v>0.698492</v>
+        <v>0.695431</v>
       </c>
     </row>
     <row r="123">
@@ -2016,7 +2016,7 @@
         <v>0.027528</v>
       </c>
       <c r="C123" t="n">
-        <v>0.69598</v>
+        <v>0.692893</v>
       </c>
     </row>
     <row r="124">
@@ -2029,7 +2029,7 @@
         <v>0.027692</v>
       </c>
       <c r="C124" t="n">
-        <v>0.6934669999999999</v>
+        <v>0.6903550000000001</v>
       </c>
     </row>
     <row r="125">
@@ -2042,7 +2042,7 @@
         <v>0.027943</v>
       </c>
       <c r="C125" t="n">
-        <v>0.690955</v>
+        <v>0.687817</v>
       </c>
     </row>
     <row r="126">
@@ -2055,7 +2055,7 @@
         <v>0.028098</v>
       </c>
       <c r="C126" t="n">
-        <v>0.688442</v>
+        <v>0.685279</v>
       </c>
     </row>
     <row r="127">
@@ -2068,7 +2068,7 @@
         <v>0.028186</v>
       </c>
       <c r="C127" t="n">
-        <v>0.68593</v>
+        <v>0.682741</v>
       </c>
     </row>
     <row r="128">
@@ -2081,7 +2081,7 @@
         <v>0.028375</v>
       </c>
       <c r="C128" t="n">
-        <v>0.6834170000000001</v>
+        <v>0.680203</v>
       </c>
     </row>
     <row r="129">
@@ -2094,7 +2094,7 @@
         <v>0.028398</v>
       </c>
       <c r="C129" t="n">
-        <v>0.680905</v>
+        <v>0.677665</v>
       </c>
     </row>
     <row r="130">
@@ -2107,7 +2107,7 @@
         <v>0.029046</v>
       </c>
       <c r="C130" t="n">
-        <v>0.678392</v>
+        <v>0.675127</v>
       </c>
     </row>
     <row r="131">
@@ -2120,7 +2120,7 @@
         <v>0.029071</v>
       </c>
       <c r="C131" t="n">
-        <v>0.675879</v>
+        <v>0.672589</v>
       </c>
     </row>
     <row r="132">
@@ -2133,7 +2133,7 @@
         <v>0.029562</v>
       </c>
       <c r="C132" t="n">
-        <v>0.673367</v>
+        <v>0.670051</v>
       </c>
     </row>
     <row r="133">
@@ -2146,7 +2146,7 @@
         <v>0.029588</v>
       </c>
       <c r="C133" t="n">
-        <v>0.670854</v>
+        <v>0.667513</v>
       </c>
     </row>
     <row r="134">
@@ -2159,7 +2159,7 @@
         <v>0.029854</v>
       </c>
       <c r="C134" t="n">
-        <v>0.668342</v>
+        <v>0.664975</v>
       </c>
     </row>
     <row r="135">
@@ -2172,7 +2172,7 @@
         <v>0.030158</v>
       </c>
       <c r="C135" t="n">
-        <v>0.665829</v>
+        <v>0.6624370000000001</v>
       </c>
     </row>
     <row r="136">
@@ -2185,7 +2185,7 @@
         <v>0.030201</v>
       </c>
       <c r="C136" t="n">
-        <v>0.663317</v>
+        <v>0.659898</v>
       </c>
     </row>
     <row r="137">
@@ -2198,7 +2198,7 @@
         <v>0.03027</v>
       </c>
       <c r="C137" t="n">
-        <v>0.6608039999999999</v>
+        <v>0.6573600000000001</v>
       </c>
     </row>
     <row r="138">
@@ -2211,7 +2211,7 @@
         <v>0.030697</v>
       </c>
       <c r="C138" t="n">
-        <v>0.658291</v>
+        <v>0.654822</v>
       </c>
     </row>
     <row r="139">
@@ -2224,7 +2224,7 @@
         <v>0.030903</v>
       </c>
       <c r="C139" t="n">
-        <v>0.655779</v>
+        <v>0.652284</v>
       </c>
     </row>
     <row r="140">
@@ -2237,7 +2237,7 @@
         <v>0.031116</v>
       </c>
       <c r="C140" t="n">
-        <v>0.653266</v>
+        <v>0.649746</v>
       </c>
     </row>
     <row r="141">
@@ -2250,7 +2250,7 @@
         <v>0.031127</v>
       </c>
       <c r="C141" t="n">
-        <v>0.6507540000000001</v>
+        <v>0.647208</v>
       </c>
     </row>
     <row r="142">
@@ -2263,7 +2263,7 @@
         <v>0.031327</v>
       </c>
       <c r="C142" t="n">
-        <v>0.648241</v>
+        <v>0.64467</v>
       </c>
     </row>
     <row r="143">
@@ -2276,7 +2276,7 @@
         <v>0.0315</v>
       </c>
       <c r="C143" t="n">
-        <v>0.645729</v>
+        <v>0.642132</v>
       </c>
     </row>
     <row r="144">
@@ -2289,7 +2289,7 @@
         <v>0.031556</v>
       </c>
       <c r="C144" t="n">
-        <v>0.643216</v>
+        <v>0.639594</v>
       </c>
     </row>
     <row r="145">
@@ -2302,7 +2302,7 @@
         <v>0.031969</v>
       </c>
       <c r="C145" t="n">
-        <v>0.6407040000000001</v>
+        <v>0.637056</v>
       </c>
     </row>
     <row r="146">
@@ -2315,7 +2315,7 @@
         <v>0.032545</v>
       </c>
       <c r="C146" t="n">
-        <v>0.638191</v>
+        <v>0.634518</v>
       </c>
     </row>
     <row r="147">
@@ -2328,7 +2328,7 @@
         <v>0.032827</v>
       </c>
       <c r="C147" t="n">
-        <v>0.635678</v>
+        <v>0.63198</v>
       </c>
     </row>
     <row r="148">
@@ -2341,7 +2341,7 @@
         <v>0.033481</v>
       </c>
       <c r="C148" t="n">
-        <v>0.633166</v>
+        <v>0.6294419999999999</v>
       </c>
     </row>
     <row r="149">
@@ -2354,7 +2354,7 @@
         <v>0.033774</v>
       </c>
       <c r="C149" t="n">
-        <v>0.630653</v>
+        <v>0.626904</v>
       </c>
     </row>
     <row r="150">
@@ -2367,7 +2367,7 @@
         <v>0.033884</v>
       </c>
       <c r="C150" t="n">
-        <v>0.6281409999999999</v>
+        <v>0.6243649999999999</v>
       </c>
     </row>
     <row r="151">
@@ -2380,7 +2380,7 @@
         <v>0.034047</v>
       </c>
       <c r="C151" t="n">
-        <v>0.625628</v>
+        <v>0.621827</v>
       </c>
     </row>
     <row r="152">
@@ -2393,7 +2393,7 @@
         <v>0.034274</v>
       </c>
       <c r="C152" t="n">
-        <v>0.623116</v>
+        <v>0.619289</v>
       </c>
     </row>
     <row r="153">
@@ -2406,7 +2406,7 @@
         <v>0.03466</v>
       </c>
       <c r="C153" t="n">
-        <v>0.620603</v>
+        <v>0.616751</v>
       </c>
     </row>
     <row r="154">
@@ -2419,7 +2419,7 @@
         <v>0.035039</v>
       </c>
       <c r="C154" t="n">
-        <v>0.61809</v>
+        <v>0.614213</v>
       </c>
     </row>
     <row r="155">
@@ -2432,7 +2432,7 @@
         <v>0.035117</v>
       </c>
       <c r="C155" t="n">
-        <v>0.615578</v>
+        <v>0.611675</v>
       </c>
     </row>
     <row r="156">
@@ -2445,7 +2445,7 @@
         <v>0.035159</v>
       </c>
       <c r="C156" t="n">
-        <v>0.613065</v>
+        <v>0.609137</v>
       </c>
     </row>
     <row r="157">
@@ -2458,7 +2458,7 @@
         <v>0.035374</v>
       </c>
       <c r="C157" t="n">
-        <v>0.610553</v>
+        <v>0.606599</v>
       </c>
     </row>
     <row r="158">
@@ -2471,7 +2471,7 @@
         <v>0.035654</v>
       </c>
       <c r="C158" t="n">
-        <v>0.60804</v>
+        <v>0.604061</v>
       </c>
     </row>
     <row r="159">
@@ -2484,7 +2484,7 @@
         <v>0.036</v>
       </c>
       <c r="C159" t="n">
-        <v>0.605528</v>
+        <v>0.601523</v>
       </c>
     </row>
     <row r="160">
@@ -2497,7 +2497,7 @@
         <v>0.036324</v>
       </c>
       <c r="C160" t="n">
-        <v>0.603015</v>
+        <v>0.598985</v>
       </c>
     </row>
     <row r="161">
@@ -2510,7 +2510,7 @@
         <v>0.03642</v>
       </c>
       <c r="C161" t="n">
-        <v>0.600503</v>
+        <v>0.5964469999999999</v>
       </c>
     </row>
     <row r="162">
@@ -2523,7 +2523,7 @@
         <v>0.03678</v>
       </c>
       <c r="C162" t="n">
-        <v>0.59799</v>
+        <v>0.593909</v>
       </c>
     </row>
     <row r="163">
@@ -2536,7 +2536,7 @@
         <v>0.037099</v>
       </c>
       <c r="C163" t="n">
-        <v>0.595477</v>
+        <v>0.591371</v>
       </c>
     </row>
     <row r="164">
@@ -2549,7 +2549,7 @@
         <v>0.037156</v>
       </c>
       <c r="C164" t="n">
-        <v>0.592965</v>
+        <v>0.588832</v>
       </c>
     </row>
     <row r="165">
@@ -2562,7 +2562,7 @@
         <v>0.037307</v>
       </c>
       <c r="C165" t="n">
-        <v>0.590452</v>
+        <v>0.586294</v>
       </c>
     </row>
     <row r="166">
@@ -2575,7 +2575,7 @@
         <v>0.037805</v>
       </c>
       <c r="C166" t="n">
-        <v>0.58794</v>
+        <v>0.5837560000000001</v>
       </c>
     </row>
     <row r="167">
@@ -2588,7 +2588,7 @@
         <v>0.037855</v>
       </c>
       <c r="C167" t="n">
-        <v>0.585427</v>
+        <v>0.581218</v>
       </c>
     </row>
     <row r="168">
@@ -2601,7 +2601,7 @@
         <v>0.038316</v>
       </c>
       <c r="C168" t="n">
-        <v>0.582915</v>
+        <v>0.57868</v>
       </c>
     </row>
     <row r="169">
@@ -2614,7 +2614,7 @@
         <v>0.03876</v>
       </c>
       <c r="C169" t="n">
-        <v>0.580402</v>
+        <v>0.576142</v>
       </c>
     </row>
     <row r="170">
@@ -2627,7 +2627,7 @@
         <v>0.039595</v>
       </c>
       <c r="C170" t="n">
-        <v>0.577889</v>
+        <v>0.573604</v>
       </c>
     </row>
     <row r="171">
@@ -2640,7 +2640,7 @@
         <v>0.03982</v>
       </c>
       <c r="C171" t="n">
-        <v>0.575377</v>
+        <v>0.571066</v>
       </c>
     </row>
     <row r="172">
@@ -2653,7 +2653,7 @@
         <v>0.040867</v>
       </c>
       <c r="C172" t="n">
-        <v>0.572864</v>
+        <v>0.568528</v>
       </c>
     </row>
     <row r="173">
@@ -2666,7 +2666,7 @@
         <v>0.040915</v>
       </c>
       <c r="C173" t="n">
-        <v>0.570352</v>
+        <v>0.56599</v>
       </c>
     </row>
     <row r="174">
@@ -2676,10 +2676,10 @@
         </is>
       </c>
       <c r="B174" t="n">
-        <v>0.040931</v>
+        <v>0.040948</v>
       </c>
       <c r="C174" t="n">
-        <v>0.567839</v>
+        <v>0.563452</v>
       </c>
     </row>
     <row r="175">
@@ -2689,10 +2689,10 @@
         </is>
       </c>
       <c r="B175" t="n">
-        <v>0.040948</v>
+        <v>0.040975</v>
       </c>
       <c r="C175" t="n">
-        <v>0.565327</v>
+        <v>0.560914</v>
       </c>
     </row>
     <row r="176">
@@ -2702,10 +2702,10 @@
         </is>
       </c>
       <c r="B176" t="n">
-        <v>0.040975</v>
+        <v>0.041019</v>
       </c>
       <c r="C176" t="n">
-        <v>0.562814</v>
+        <v>0.558376</v>
       </c>
     </row>
     <row r="177">
@@ -2715,10 +2715,10 @@
         </is>
       </c>
       <c r="B177" t="n">
-        <v>0.041019</v>
+        <v>0.041132</v>
       </c>
       <c r="C177" t="n">
-        <v>0.560302</v>
+        <v>0.5558380000000001</v>
       </c>
     </row>
     <row r="178">
@@ -2728,10 +2728,10 @@
         </is>
       </c>
       <c r="B178" t="n">
-        <v>0.041132</v>
+        <v>0.041331</v>
       </c>
       <c r="C178" t="n">
-        <v>0.557789</v>
+        <v>0.553299</v>
       </c>
     </row>
     <row r="179">
@@ -2741,10 +2741,10 @@
         </is>
       </c>
       <c r="B179" t="n">
-        <v>0.041331</v>
+        <v>0.041457</v>
       </c>
       <c r="C179" t="n">
-        <v>0.555276</v>
+        <v>0.5507609999999999</v>
       </c>
     </row>
     <row r="180">
@@ -2754,10 +2754,10 @@
         </is>
       </c>
       <c r="B180" t="n">
-        <v>0.041457</v>
+        <v>0.041762</v>
       </c>
       <c r="C180" t="n">
-        <v>0.552764</v>
+        <v>0.548223</v>
       </c>
     </row>
     <row r="181">
@@ -2767,10 +2767,10 @@
         </is>
       </c>
       <c r="B181" t="n">
-        <v>0.041762</v>
+        <v>0.04197</v>
       </c>
       <c r="C181" t="n">
-        <v>0.550251</v>
+        <v>0.545685</v>
       </c>
     </row>
     <row r="182">
@@ -2780,10 +2780,10 @@
         </is>
       </c>
       <c r="B182" t="n">
-        <v>0.04197</v>
+        <v>0.042735</v>
       </c>
       <c r="C182" t="n">
-        <v>0.547739</v>
+        <v>0.543147</v>
       </c>
     </row>
     <row r="183">
@@ -2793,10 +2793,10 @@
         </is>
       </c>
       <c r="B183" t="n">
-        <v>0.042735</v>
+        <v>0.043144</v>
       </c>
       <c r="C183" t="n">
-        <v>0.545226</v>
+        <v>0.540609</v>
       </c>
     </row>
     <row r="184">
@@ -2806,10 +2806,10 @@
         </is>
       </c>
       <c r="B184" t="n">
-        <v>0.043144</v>
+        <v>0.043468</v>
       </c>
       <c r="C184" t="n">
-        <v>0.542714</v>
+        <v>0.538071</v>
       </c>
     </row>
     <row r="185">
@@ -2819,10 +2819,10 @@
         </is>
       </c>
       <c r="B185" t="n">
-        <v>0.043468</v>
+        <v>0.04427</v>
       </c>
       <c r="C185" t="n">
-        <v>0.540201</v>
+        <v>0.535533</v>
       </c>
     </row>
     <row r="186">
@@ -2832,10 +2832,10 @@
         </is>
       </c>
       <c r="B186" t="n">
-        <v>0.04427</v>
+        <v>0.044385</v>
       </c>
       <c r="C186" t="n">
-        <v>0.5376880000000001</v>
+        <v>0.532995</v>
       </c>
     </row>
     <row r="187">
@@ -2845,10 +2845,10 @@
         </is>
       </c>
       <c r="B187" t="n">
-        <v>0.044385</v>
+        <v>0.044556</v>
       </c>
       <c r="C187" t="n">
-        <v>0.535176</v>
+        <v>0.530457</v>
       </c>
     </row>
     <row r="188">
@@ -2858,10 +2858,10 @@
         </is>
       </c>
       <c r="B188" t="n">
-        <v>0.044556</v>
+        <v>0.044571</v>
       </c>
       <c r="C188" t="n">
-        <v>0.532663</v>
+        <v>0.527919</v>
       </c>
     </row>
     <row r="189">
@@ -2871,10 +2871,10 @@
         </is>
       </c>
       <c r="B189" t="n">
-        <v>0.044571</v>
+        <v>0.044939</v>
       </c>
       <c r="C189" t="n">
-        <v>0.530151</v>
+        <v>0.525381</v>
       </c>
     </row>
     <row r="190">
@@ -2884,10 +2884,10 @@
         </is>
       </c>
       <c r="B190" t="n">
-        <v>0.044939</v>
+        <v>0.045962</v>
       </c>
       <c r="C190" t="n">
-        <v>0.5276380000000001</v>
+        <v>0.5228429999999999</v>
       </c>
     </row>
     <row r="191">
@@ -2897,10 +2897,10 @@
         </is>
       </c>
       <c r="B191" t="n">
-        <v>0.045962</v>
+        <v>0.046161</v>
       </c>
       <c r="C191" t="n">
-        <v>0.525126</v>
+        <v>0.520305</v>
       </c>
     </row>
     <row r="192">
@@ -2910,10 +2910,10 @@
         </is>
       </c>
       <c r="B192" t="n">
-        <v>0.046161</v>
+        <v>0.046486</v>
       </c>
       <c r="C192" t="n">
-        <v>0.522613</v>
+        <v>0.5177659999999999</v>
       </c>
     </row>
     <row r="193">
@@ -2923,10 +2923,10 @@
         </is>
       </c>
       <c r="B193" t="n">
-        <v>0.046486</v>
+        <v>0.046763</v>
       </c>
       <c r="C193" t="n">
-        <v>0.520101</v>
+        <v>0.515228</v>
       </c>
     </row>
     <row r="194">
@@ -2936,10 +2936,10 @@
         </is>
       </c>
       <c r="B194" t="n">
-        <v>0.046763</v>
+        <v>0.046785</v>
       </c>
       <c r="C194" t="n">
-        <v>0.517588</v>
+        <v>0.51269</v>
       </c>
     </row>
     <row r="195">
@@ -2949,10 +2949,10 @@
         </is>
       </c>
       <c r="B195" t="n">
-        <v>0.046785</v>
+        <v>0.046943</v>
       </c>
       <c r="C195" t="n">
-        <v>0.5150749999999999</v>
+        <v>0.510152</v>
       </c>
     </row>
     <row r="196">
@@ -2962,10 +2962,10 @@
         </is>
       </c>
       <c r="B196" t="n">
-        <v>0.046943</v>
+        <v>0.047141</v>
       </c>
       <c r="C196" t="n">
-        <v>0.512563</v>
+        <v>0.507614</v>
       </c>
     </row>
     <row r="197">
@@ -2975,10 +2975,10 @@
         </is>
       </c>
       <c r="B197" t="n">
-        <v>0.047141</v>
+        <v>0.047327</v>
       </c>
       <c r="C197" t="n">
-        <v>0.51005</v>
+        <v>0.505076</v>
       </c>
     </row>
     <row r="198">
@@ -2988,10 +2988,10 @@
         </is>
       </c>
       <c r="B198" t="n">
-        <v>0.047327</v>
+        <v>0.047421</v>
       </c>
       <c r="C198" t="n">
-        <v>0.507538</v>
+        <v>0.502538</v>
       </c>
     </row>
     <row r="199">
@@ -3001,10 +3001,10 @@
         </is>
       </c>
       <c r="B199" t="n">
-        <v>0.047421</v>
+        <v>0.047498</v>
       </c>
       <c r="C199" t="n">
-        <v>0.5050249999999999</v>
+        <v>0.5</v>
       </c>
     </row>
     <row r="200">
@@ -3017,7 +3017,7 @@
         <v>0.047901</v>
       </c>
       <c r="C200" t="n">
-        <v>0.502513</v>
+        <v>0.497462</v>
       </c>
     </row>
     <row r="201">
@@ -3030,7 +3030,7 @@
         <v>0.04832</v>
       </c>
       <c r="C201" t="n">
-        <v>0.5</v>
+        <v>0.494924</v>
       </c>
     </row>
     <row r="202">
@@ -3043,7 +3043,7 @@
         <v>0.048551</v>
       </c>
       <c r="C202" t="n">
-        <v>0.497487</v>
+        <v>0.492386</v>
       </c>
     </row>
     <row r="203">
@@ -3053,10 +3053,10 @@
         </is>
       </c>
       <c r="B203" t="n">
-        <v>0.04906</v>
+        <v>0.04875</v>
       </c>
       <c r="C203" t="n">
-        <v>0.494975</v>
+        <v>0.489848</v>
       </c>
     </row>
     <row r="204">
@@ -3066,10 +3066,10 @@
         </is>
       </c>
       <c r="B204" t="n">
-        <v>0.049358</v>
+        <v>0.04906</v>
       </c>
       <c r="C204" t="n">
-        <v>0.492462</v>
+        <v>0.48731</v>
       </c>
     </row>
     <row r="205">
@@ -3079,10 +3079,10 @@
         </is>
       </c>
       <c r="B205" t="n">
-        <v>0.049478</v>
+        <v>0.049358</v>
       </c>
       <c r="C205" t="n">
-        <v>0.48995</v>
+        <v>0.484772</v>
       </c>
     </row>
     <row r="206">
@@ -3092,10 +3092,10 @@
         </is>
       </c>
       <c r="B206" t="n">
-        <v>0.049516</v>
+        <v>0.049478</v>
       </c>
       <c r="C206" t="n">
-        <v>0.487437</v>
+        <v>0.482234</v>
       </c>
     </row>
     <row r="207">
@@ -3105,10 +3105,10 @@
         </is>
       </c>
       <c r="B207" t="n">
-        <v>0.049728</v>
+        <v>0.049516</v>
       </c>
       <c r="C207" t="n">
-        <v>0.484925</v>
+        <v>0.479695</v>
       </c>
     </row>
     <row r="208">
@@ -3118,10 +3118,10 @@
         </is>
       </c>
       <c r="B208" t="n">
-        <v>0.050809</v>
+        <v>0.049728</v>
       </c>
       <c r="C208" t="n">
-        <v>0.482412</v>
+        <v>0.477157</v>
       </c>
     </row>
     <row r="209">
@@ -3131,10 +3131,10 @@
         </is>
       </c>
       <c r="B209" t="n">
-        <v>0.051151</v>
+        <v>0.050809</v>
       </c>
       <c r="C209" t="n">
-        <v>0.479899</v>
+        <v>0.474619</v>
       </c>
     </row>
     <row r="210">
@@ -3144,10 +3144,10 @@
         </is>
       </c>
       <c r="B210" t="n">
-        <v>0.051264</v>
+        <v>0.051151</v>
       </c>
       <c r="C210" t="n">
-        <v>0.477387</v>
+        <v>0.472081</v>
       </c>
     </row>
     <row r="211">
@@ -3157,10 +3157,10 @@
         </is>
       </c>
       <c r="B211" t="n">
-        <v>0.051423</v>
+        <v>0.051264</v>
       </c>
       <c r="C211" t="n">
-        <v>0.474874</v>
+        <v>0.469543</v>
       </c>
     </row>
     <row r="212">
@@ -3170,10 +3170,10 @@
         </is>
       </c>
       <c r="B212" t="n">
-        <v>0.051449</v>
+        <v>0.051423</v>
       </c>
       <c r="C212" t="n">
-        <v>0.472362</v>
+        <v>0.467005</v>
       </c>
     </row>
     <row r="213">
@@ -3183,10 +3183,10 @@
         </is>
       </c>
       <c r="B213" t="n">
-        <v>0.052376</v>
+        <v>0.051449</v>
       </c>
       <c r="C213" t="n">
-        <v>0.469849</v>
+        <v>0.464467</v>
       </c>
     </row>
     <row r="214">
@@ -3196,10 +3196,10 @@
         </is>
       </c>
       <c r="B214" t="n">
-        <v>0.052398</v>
+        <v>0.052376</v>
       </c>
       <c r="C214" t="n">
-        <v>0.467337</v>
+        <v>0.461929</v>
       </c>
     </row>
     <row r="215">
@@ -3209,10 +3209,10 @@
         </is>
       </c>
       <c r="B215" t="n">
-        <v>0.052682</v>
+        <v>0.052398</v>
       </c>
       <c r="C215" t="n">
-        <v>0.464824</v>
+        <v>0.459391</v>
       </c>
     </row>
     <row r="216">
@@ -3222,10 +3222,10 @@
         </is>
       </c>
       <c r="B216" t="n">
-        <v>0.053144</v>
+        <v>0.052682</v>
       </c>
       <c r="C216" t="n">
-        <v>0.462312</v>
+        <v>0.456853</v>
       </c>
     </row>
     <row r="217">
@@ -3235,10 +3235,10 @@
         </is>
       </c>
       <c r="B217" t="n">
-        <v>0.053227</v>
+        <v>0.053144</v>
       </c>
       <c r="C217" t="n">
-        <v>0.459799</v>
+        <v>0.454315</v>
       </c>
     </row>
     <row r="218">
@@ -3248,10 +3248,10 @@
         </is>
       </c>
       <c r="B218" t="n">
-        <v>0.053316</v>
+        <v>0.053227</v>
       </c>
       <c r="C218" t="n">
-        <v>0.457286</v>
+        <v>0.451777</v>
       </c>
     </row>
     <row r="219">
@@ -3261,10 +3261,10 @@
         </is>
       </c>
       <c r="B219" t="n">
-        <v>0.053555</v>
+        <v>0.053316</v>
       </c>
       <c r="C219" t="n">
-        <v>0.454774</v>
+        <v>0.449239</v>
       </c>
     </row>
     <row r="220">
@@ -3274,10 +3274,10 @@
         </is>
       </c>
       <c r="B220" t="n">
-        <v>0.05382</v>
+        <v>0.053555</v>
       </c>
       <c r="C220" t="n">
-        <v>0.452261</v>
+        <v>0.446701</v>
       </c>
     </row>
     <row r="221">
@@ -3287,10 +3287,10 @@
         </is>
       </c>
       <c r="B221" t="n">
-        <v>0.05439</v>
+        <v>0.05382</v>
       </c>
       <c r="C221" t="n">
-        <v>0.449749</v>
+        <v>0.444162</v>
       </c>
     </row>
     <row r="222">
@@ -3300,10 +3300,10 @@
         </is>
       </c>
       <c r="B222" t="n">
-        <v>0.05496</v>
+        <v>0.05439</v>
       </c>
       <c r="C222" t="n">
-        <v>0.447236</v>
+        <v>0.441624</v>
       </c>
     </row>
     <row r="223">
@@ -3313,10 +3313,10 @@
         </is>
       </c>
       <c r="B223" t="n">
-        <v>0.055028</v>
+        <v>0.05496</v>
       </c>
       <c r="C223" t="n">
-        <v>0.444724</v>
+        <v>0.439086</v>
       </c>
     </row>
     <row r="224">
@@ -3326,10 +3326,10 @@
         </is>
       </c>
       <c r="B224" t="n">
-        <v>0.0555</v>
+        <v>0.055028</v>
       </c>
       <c r="C224" t="n">
-        <v>0.442211</v>
+        <v>0.436548</v>
       </c>
     </row>
     <row r="225">
@@ -3339,10 +3339,10 @@
         </is>
       </c>
       <c r="B225" t="n">
-        <v>0.055621</v>
+        <v>0.0555</v>
       </c>
       <c r="C225" t="n">
-        <v>0.439698</v>
+        <v>0.43401</v>
       </c>
     </row>
     <row r="226">
@@ -3352,10 +3352,10 @@
         </is>
       </c>
       <c r="B226" t="n">
-        <v>0.055736</v>
+        <v>0.055621</v>
       </c>
       <c r="C226" t="n">
-        <v>0.437186</v>
+        <v>0.431472</v>
       </c>
     </row>
     <row r="227">
@@ -3365,10 +3365,10 @@
         </is>
       </c>
       <c r="B227" t="n">
-        <v>0.056242</v>
+        <v>0.055736</v>
       </c>
       <c r="C227" t="n">
-        <v>0.434673</v>
+        <v>0.428934</v>
       </c>
     </row>
     <row r="228">
@@ -3378,10 +3378,10 @@
         </is>
       </c>
       <c r="B228" t="n">
-        <v>0.056433</v>
+        <v>0.056242</v>
       </c>
       <c r="C228" t="n">
-        <v>0.432161</v>
+        <v>0.426396</v>
       </c>
     </row>
     <row r="229">
@@ -3391,10 +3391,10 @@
         </is>
       </c>
       <c r="B229" t="n">
-        <v>0.056487</v>
+        <v>0.056433</v>
       </c>
       <c r="C229" t="n">
-        <v>0.429648</v>
+        <v>0.423858</v>
       </c>
     </row>
     <row r="230">
@@ -3404,10 +3404,10 @@
         </is>
       </c>
       <c r="B230" t="n">
-        <v>0.056702</v>
+        <v>0.056487</v>
       </c>
       <c r="C230" t="n">
-        <v>0.427136</v>
+        <v>0.42132</v>
       </c>
     </row>
     <row r="231">
@@ -3417,10 +3417,10 @@
         </is>
       </c>
       <c r="B231" t="n">
-        <v>0.056785</v>
+        <v>0.056702</v>
       </c>
       <c r="C231" t="n">
-        <v>0.424623</v>
+        <v>0.418782</v>
       </c>
     </row>
     <row r="232">
@@ -3430,10 +3430,10 @@
         </is>
       </c>
       <c r="B232" t="n">
-        <v>0.057942</v>
+        <v>0.056785</v>
       </c>
       <c r="C232" t="n">
-        <v>0.422111</v>
+        <v>0.416244</v>
       </c>
     </row>
     <row r="233">
@@ -3443,10 +3443,10 @@
         </is>
       </c>
       <c r="B233" t="n">
-        <v>0.05854</v>
+        <v>0.057942</v>
       </c>
       <c r="C233" t="n">
-        <v>0.419598</v>
+        <v>0.413706</v>
       </c>
     </row>
     <row r="234">
@@ -3456,10 +3456,10 @@
         </is>
       </c>
       <c r="B234" t="n">
-        <v>0.058745</v>
+        <v>0.05854</v>
       </c>
       <c r="C234" t="n">
-        <v>0.417085</v>
+        <v>0.411168</v>
       </c>
     </row>
     <row r="235">
@@ -3469,10 +3469,10 @@
         </is>
       </c>
       <c r="B235" t="n">
-        <v>0.058836</v>
+        <v>0.058745</v>
       </c>
       <c r="C235" t="n">
-        <v>0.414573</v>
+        <v>0.408629</v>
       </c>
     </row>
     <row r="236">
@@ -3482,10 +3482,10 @@
         </is>
       </c>
       <c r="B236" t="n">
-        <v>0.059279</v>
+        <v>0.058836</v>
       </c>
       <c r="C236" t="n">
-        <v>0.41206</v>
+        <v>0.406091</v>
       </c>
     </row>
     <row r="237">
@@ -3495,10 +3495,10 @@
         </is>
       </c>
       <c r="B237" t="n">
-        <v>0.059367</v>
+        <v>0.059279</v>
       </c>
       <c r="C237" t="n">
-        <v>0.409548</v>
+        <v>0.403553</v>
       </c>
     </row>
     <row r="238">
@@ -3508,10 +3508,10 @@
         </is>
       </c>
       <c r="B238" t="n">
-        <v>0.059553</v>
+        <v>0.059367</v>
       </c>
       <c r="C238" t="n">
-        <v>0.407035</v>
+        <v>0.401015</v>
       </c>
     </row>
     <row r="239">
@@ -3521,10 +3521,10 @@
         </is>
       </c>
       <c r="B239" t="n">
-        <v>0.059579</v>
+        <v>0.059553</v>
       </c>
       <c r="C239" t="n">
-        <v>0.404523</v>
+        <v>0.398477</v>
       </c>
     </row>
     <row r="240">
@@ -3534,10 +3534,10 @@
         </is>
       </c>
       <c r="B240" t="n">
-        <v>0.060111</v>
+        <v>0.059579</v>
       </c>
       <c r="C240" t="n">
-        <v>0.40201</v>
+        <v>0.395939</v>
       </c>
     </row>
     <row r="241">
@@ -3547,10 +3547,10 @@
         </is>
       </c>
       <c r="B241" t="n">
-        <v>0.060827</v>
+        <v>0.060111</v>
       </c>
       <c r="C241" t="n">
-        <v>0.399497</v>
+        <v>0.393401</v>
       </c>
     </row>
     <row r="242">
@@ -3560,10 +3560,10 @@
         </is>
       </c>
       <c r="B242" t="n">
-        <v>0.060882</v>
+        <v>0.060827</v>
       </c>
       <c r="C242" t="n">
-        <v>0.396985</v>
+        <v>0.390863</v>
       </c>
     </row>
     <row r="243">
@@ -3573,10 +3573,10 @@
         </is>
       </c>
       <c r="B243" t="n">
-        <v>0.061437</v>
+        <v>0.060882</v>
       </c>
       <c r="C243" t="n">
-        <v>0.394472</v>
+        <v>0.388325</v>
       </c>
     </row>
     <row r="244">
@@ -3586,10 +3586,10 @@
         </is>
       </c>
       <c r="B244" t="n">
-        <v>0.061712</v>
+        <v>0.061437</v>
       </c>
       <c r="C244" t="n">
-        <v>0.39196</v>
+        <v>0.385787</v>
       </c>
     </row>
     <row r="245">
@@ -3599,10 +3599,10 @@
         </is>
       </c>
       <c r="B245" t="n">
-        <v>0.061784</v>
+        <v>0.061712</v>
       </c>
       <c r="C245" t="n">
-        <v>0.389447</v>
+        <v>0.383249</v>
       </c>
     </row>
     <row r="246">
@@ -3612,10 +3612,10 @@
         </is>
       </c>
       <c r="B246" t="n">
-        <v>0.06179</v>
+        <v>0.061784</v>
       </c>
       <c r="C246" t="n">
-        <v>0.386935</v>
+        <v>0.380711</v>
       </c>
     </row>
     <row r="247">
@@ -3625,10 +3625,10 @@
         </is>
       </c>
       <c r="B247" t="n">
-        <v>0.061969</v>
+        <v>0.06179</v>
       </c>
       <c r="C247" t="n">
-        <v>0.384422</v>
+        <v>0.378173</v>
       </c>
     </row>
     <row r="248">
@@ -3638,10 +3638,10 @@
         </is>
       </c>
       <c r="B248" t="n">
-        <v>0.062129</v>
+        <v>0.061969</v>
       </c>
       <c r="C248" t="n">
-        <v>0.38191</v>
+        <v>0.375635</v>
       </c>
     </row>
     <row r="249">
@@ -3651,10 +3651,10 @@
         </is>
       </c>
       <c r="B249" t="n">
-        <v>0.062168</v>
+        <v>0.062129</v>
       </c>
       <c r="C249" t="n">
-        <v>0.379397</v>
+        <v>0.373096</v>
       </c>
     </row>
     <row r="250">
@@ -3664,10 +3664,10 @@
         </is>
       </c>
       <c r="B250" t="n">
-        <v>0.062246</v>
+        <v>0.062168</v>
       </c>
       <c r="C250" t="n">
-        <v>0.376884</v>
+        <v>0.370558</v>
       </c>
     </row>
     <row r="251">
@@ -3680,7 +3680,7 @@
         <v>0.06263299999999999</v>
       </c>
       <c r="C251" t="n">
-        <v>0.374372</v>
+        <v>0.36802</v>
       </c>
     </row>
     <row r="252">
@@ -3693,7 +3693,7 @@
         <v>0.062844</v>
       </c>
       <c r="C252" t="n">
-        <v>0.371859</v>
+        <v>0.365482</v>
       </c>
     </row>
     <row r="253">
@@ -3706,7 +3706,7 @@
         <v>0.063808</v>
       </c>
       <c r="C253" t="n">
-        <v>0.369347</v>
+        <v>0.362944</v>
       </c>
     </row>
     <row r="254">
@@ -3719,7 +3719,7 @@
         <v>0.064842</v>
       </c>
       <c r="C254" t="n">
-        <v>0.366834</v>
+        <v>0.360406</v>
       </c>
     </row>
     <row r="255">
@@ -3732,7 +3732,7 @@
         <v>0.06555900000000001</v>
       </c>
       <c r="C255" t="n">
-        <v>0.364322</v>
+        <v>0.357868</v>
       </c>
     </row>
     <row r="256">
@@ -3745,7 +3745,7 @@
         <v>0.067176</v>
       </c>
       <c r="C256" t="n">
-        <v>0.361809</v>
+        <v>0.35533</v>
       </c>
     </row>
     <row r="257">
@@ -3758,7 +3758,7 @@
         <v>0.06736399999999999</v>
       </c>
       <c r="C257" t="n">
-        <v>0.359296</v>
+        <v>0.352792</v>
       </c>
     </row>
     <row r="258">
@@ -3771,7 +3771,7 @@
         <v>0.067375</v>
       </c>
       <c r="C258" t="n">
-        <v>0.356784</v>
+        <v>0.350254</v>
       </c>
     </row>
     <row r="259">
@@ -3784,7 +3784,7 @@
         <v>0.067555</v>
       </c>
       <c r="C259" t="n">
-        <v>0.354271</v>
+        <v>0.347716</v>
       </c>
     </row>
     <row r="260">
@@ -3797,7 +3797,7 @@
         <v>0.067604</v>
       </c>
       <c r="C260" t="n">
-        <v>0.351759</v>
+        <v>0.345178</v>
       </c>
     </row>
     <row r="261">
@@ -3810,7 +3810,7 @@
         <v>0.067644</v>
       </c>
       <c r="C261" t="n">
-        <v>0.349246</v>
+        <v>0.34264</v>
       </c>
     </row>
     <row r="262">
@@ -3823,7 +3823,7 @@
         <v>0.068111</v>
       </c>
       <c r="C262" t="n">
-        <v>0.346734</v>
+        <v>0.340102</v>
       </c>
     </row>
     <row r="263">
@@ -3836,7 +3836,7 @@
         <v>0.068538</v>
       </c>
       <c r="C263" t="n">
-        <v>0.344221</v>
+        <v>0.337563</v>
       </c>
     </row>
     <row r="264">
@@ -3849,7 +3849,7 @@
         <v>0.068601</v>
       </c>
       <c r="C264" t="n">
-        <v>0.341709</v>
+        <v>0.335025</v>
       </c>
     </row>
     <row r="265">
@@ -3859,10 +3859,10 @@
         </is>
       </c>
       <c r="B265" t="n">
-        <v>0.068939</v>
+        <v>0.068845</v>
       </c>
       <c r="C265" t="n">
-        <v>0.339196</v>
+        <v>0.332487</v>
       </c>
     </row>
     <row r="266">
@@ -3872,10 +3872,10 @@
         </is>
       </c>
       <c r="B266" t="n">
-        <v>0.06909</v>
+        <v>0.068939</v>
       </c>
       <c r="C266" t="n">
-        <v>0.336683</v>
+        <v>0.329949</v>
       </c>
     </row>
     <row r="267">
@@ -3885,10 +3885,10 @@
         </is>
       </c>
       <c r="B267" t="n">
-        <v>0.069253</v>
+        <v>0.06909</v>
       </c>
       <c r="C267" t="n">
-        <v>0.334171</v>
+        <v>0.327411</v>
       </c>
     </row>
     <row r="268">
@@ -3898,10 +3898,10 @@
         </is>
       </c>
       <c r="B268" t="n">
-        <v>0.070214</v>
+        <v>0.069253</v>
       </c>
       <c r="C268" t="n">
-        <v>0.331658</v>
+        <v>0.324873</v>
       </c>
     </row>
     <row r="269">
@@ -3911,10 +3911,10 @@
         </is>
       </c>
       <c r="B269" t="n">
-        <v>0.070659</v>
+        <v>0.070214</v>
       </c>
       <c r="C269" t="n">
-        <v>0.329146</v>
+        <v>0.322335</v>
       </c>
     </row>
     <row r="270">
@@ -3924,10 +3924,10 @@
         </is>
       </c>
       <c r="B270" t="n">
-        <v>0.071449</v>
+        <v>0.070659</v>
       </c>
       <c r="C270" t="n">
-        <v>0.326633</v>
+        <v>0.319797</v>
       </c>
     </row>
     <row r="271">
@@ -3940,7 +3940,7 @@
         <v>0.07172199999999999</v>
       </c>
       <c r="C271" t="n">
-        <v>0.324121</v>
+        <v>0.317259</v>
       </c>
     </row>
     <row r="272">
@@ -3953,7 +3953,7 @@
         <v>0.072684</v>
       </c>
       <c r="C272" t="n">
-        <v>0.321608</v>
+        <v>0.314721</v>
       </c>
     </row>
     <row r="273">
@@ -3966,7 +3966,7 @@
         <v>0.072744</v>
       </c>
       <c r="C273" t="n">
-        <v>0.319095</v>
+        <v>0.312183</v>
       </c>
     </row>
     <row r="274">
@@ -3979,7 +3979,7 @@
         <v>0.07295599999999999</v>
       </c>
       <c r="C274" t="n">
-        <v>0.316583</v>
+        <v>0.309645</v>
       </c>
     </row>
     <row r="275">
@@ -3992,7 +3992,7 @@
         <v>0.07331</v>
       </c>
       <c r="C275" t="n">
-        <v>0.31407</v>
+        <v>0.307107</v>
       </c>
     </row>
     <row r="276">
@@ -4005,7 +4005,7 @@
         <v>0.07346</v>
       </c>
       <c r="C276" t="n">
-        <v>0.311558</v>
+        <v>0.304569</v>
       </c>
     </row>
     <row r="277">
@@ -4018,7 +4018,7 @@
         <v>0.07380299999999999</v>
       </c>
       <c r="C277" t="n">
-        <v>0.309045</v>
+        <v>0.30203</v>
       </c>
     </row>
     <row r="278">
@@ -4031,7 +4031,7 @@
         <v>0.07424799999999999</v>
       </c>
       <c r="C278" t="n">
-        <v>0.306533</v>
+        <v>0.299492</v>
       </c>
     </row>
     <row r="279">
@@ -4044,7 +4044,7 @@
         <v>0.07437100000000001</v>
       </c>
       <c r="C279" t="n">
-        <v>0.30402</v>
+        <v>0.296954</v>
       </c>
     </row>
     <row r="280">
@@ -4057,7 +4057,7 @@
         <v>0.075854</v>
       </c>
       <c r="C280" t="n">
-        <v>0.301508</v>
+        <v>0.294416</v>
       </c>
     </row>
     <row r="281">
@@ -4070,7 +4070,7 @@
         <v>0.075876</v>
       </c>
       <c r="C281" t="n">
-        <v>0.298995</v>
+        <v>0.291878</v>
       </c>
     </row>
     <row r="282">
@@ -4083,7 +4083,7 @@
         <v>0.076543</v>
       </c>
       <c r="C282" t="n">
-        <v>0.296482</v>
+        <v>0.28934</v>
       </c>
     </row>
     <row r="283">
@@ -4096,7 +4096,7 @@
         <v>0.07708</v>
       </c>
       <c r="C283" t="n">
-        <v>0.29397</v>
+        <v>0.286802</v>
       </c>
     </row>
     <row r="284">
@@ -4109,7 +4109,7 @@
         <v>0.077419</v>
       </c>
       <c r="C284" t="n">
-        <v>0.291457</v>
+        <v>0.284264</v>
       </c>
     </row>
     <row r="285">
@@ -4122,7 +4122,7 @@
         <v>0.077863</v>
       </c>
       <c r="C285" t="n">
-        <v>0.288945</v>
+        <v>0.281726</v>
       </c>
     </row>
     <row r="286">
@@ -4135,7 +4135,7 @@
         <v>0.077912</v>
       </c>
       <c r="C286" t="n">
-        <v>0.286432</v>
+        <v>0.279188</v>
       </c>
     </row>
     <row r="287">
@@ -4148,7 +4148,7 @@
         <v>0.078084</v>
       </c>
       <c r="C287" t="n">
-        <v>0.28392</v>
+        <v>0.27665</v>
       </c>
     </row>
     <row r="288">
@@ -4161,7 +4161,7 @@
         <v>0.07843899999999999</v>
       </c>
       <c r="C288" t="n">
-        <v>0.281407</v>
+        <v>0.274112</v>
       </c>
     </row>
     <row r="289">
@@ -4174,7 +4174,7 @@
         <v>0.07921499999999999</v>
       </c>
       <c r="C289" t="n">
-        <v>0.278894</v>
+        <v>0.271574</v>
       </c>
     </row>
     <row r="290">
@@ -4187,7 +4187,7 @@
         <v>0.080791</v>
       </c>
       <c r="C290" t="n">
-        <v>0.276382</v>
+        <v>0.269036</v>
       </c>
     </row>
     <row r="291">
@@ -4200,7 +4200,7 @@
         <v>0.08092199999999999</v>
       </c>
       <c r="C291" t="n">
-        <v>0.273869</v>
+        <v>0.266497</v>
       </c>
     </row>
     <row r="292">
@@ -4213,7 +4213,7 @@
         <v>0.080995</v>
       </c>
       <c r="C292" t="n">
-        <v>0.271357</v>
+        <v>0.263959</v>
       </c>
     </row>
     <row r="293">
@@ -4226,7 +4226,7 @@
         <v>0.081607</v>
       </c>
       <c r="C293" t="n">
-        <v>0.268844</v>
+        <v>0.261421</v>
       </c>
     </row>
     <row r="294">
@@ -4239,7 +4239,7 @@
         <v>0.081758</v>
       </c>
       <c r="C294" t="n">
-        <v>0.266332</v>
+        <v>0.258883</v>
       </c>
     </row>
     <row r="295">
@@ -4252,7 +4252,7 @@
         <v>0.082479</v>
       </c>
       <c r="C295" t="n">
-        <v>0.263819</v>
+        <v>0.256345</v>
       </c>
     </row>
     <row r="296">
@@ -4265,7 +4265,7 @@
         <v>0.082594</v>
       </c>
       <c r="C296" t="n">
-        <v>0.261307</v>
+        <v>0.253807</v>
       </c>
     </row>
     <row r="297">
@@ -4278,7 +4278,7 @@
         <v>0.08294600000000001</v>
       </c>
       <c r="C297" t="n">
-        <v>0.258794</v>
+        <v>0.251269</v>
       </c>
     </row>
     <row r="298">
@@ -4291,7 +4291,7 @@
         <v>0.083297</v>
       </c>
       <c r="C298" t="n">
-        <v>0.256281</v>
+        <v>0.248731</v>
       </c>
     </row>
     <row r="299">
@@ -4304,7 +4304,7 @@
         <v>0.08384800000000001</v>
       </c>
       <c r="C299" t="n">
-        <v>0.253769</v>
+        <v>0.246193</v>
       </c>
     </row>
     <row r="300">
@@ -4317,7 +4317,7 @@
         <v>0.084221</v>
       </c>
       <c r="C300" t="n">
-        <v>0.251256</v>
+        <v>0.243655</v>
       </c>
     </row>
     <row r="301">
@@ -4330,7 +4330,7 @@
         <v>0.08483599999999999</v>
       </c>
       <c r="C301" t="n">
-        <v>0.248744</v>
+        <v>0.241117</v>
       </c>
     </row>
     <row r="302">
@@ -4343,7 +4343,7 @@
         <v>0.087156</v>
       </c>
       <c r="C302" t="n">
-        <v>0.246231</v>
+        <v>0.238579</v>
       </c>
     </row>
     <row r="303">
@@ -4356,7 +4356,7 @@
         <v>0.08717999999999999</v>
       </c>
       <c r="C303" t="n">
-        <v>0.243719</v>
+        <v>0.236041</v>
       </c>
     </row>
     <row r="304">
@@ -4369,7 +4369,7 @@
         <v>0.08820799999999999</v>
       </c>
       <c r="C304" t="n">
-        <v>0.241206</v>
+        <v>0.233503</v>
       </c>
     </row>
     <row r="305">
@@ -4382,7 +4382,7 @@
         <v>0.088889</v>
       </c>
       <c r="C305" t="n">
-        <v>0.238693</v>
+        <v>0.230964</v>
       </c>
     </row>
     <row r="306">
@@ -4395,7 +4395,7 @@
         <v>0.08917700000000001</v>
       </c>
       <c r="C306" t="n">
-        <v>0.236181</v>
+        <v>0.228426</v>
       </c>
     </row>
     <row r="307">
@@ -4408,7 +4408,7 @@
         <v>0.089823</v>
       </c>
       <c r="C307" t="n">
-        <v>0.233668</v>
+        <v>0.225888</v>
       </c>
     </row>
     <row r="308">
@@ -4421,7 +4421,7 @@
         <v>0.090265</v>
       </c>
       <c r="C308" t="n">
-        <v>0.231156</v>
+        <v>0.22335</v>
       </c>
     </row>
     <row r="309">
@@ -4434,7 +4434,7 @@
         <v>0.090348</v>
       </c>
       <c r="C309" t="n">
-        <v>0.228643</v>
+        <v>0.220812</v>
       </c>
     </row>
     <row r="310">
@@ -4447,7 +4447,7 @@
         <v>0.091434</v>
       </c>
       <c r="C310" t="n">
-        <v>0.226131</v>
+        <v>0.218274</v>
       </c>
     </row>
     <row r="311">
@@ -4460,7 +4460,7 @@
         <v>0.0929</v>
       </c>
       <c r="C311" t="n">
-        <v>0.223618</v>
+        <v>0.215736</v>
       </c>
     </row>
     <row r="312">
@@ -4473,7 +4473,7 @@
         <v>0.09744</v>
       </c>
       <c r="C312" t="n">
-        <v>0.221106</v>
+        <v>0.213198</v>
       </c>
     </row>
     <row r="313">
@@ -4486,7 +4486,7 @@
         <v>0.097923</v>
       </c>
       <c r="C313" t="n">
-        <v>0.218593</v>
+        <v>0.21066</v>
       </c>
     </row>
     <row r="314">
@@ -4496,10 +4496,10 @@
         </is>
       </c>
       <c r="B314" t="n">
-        <v>0.098237</v>
+        <v>0.09847400000000001</v>
       </c>
       <c r="C314" t="n">
-        <v>0.21608</v>
+        <v>0.208122</v>
       </c>
     </row>
     <row r="315">
@@ -4509,10 +4509,10 @@
         </is>
       </c>
       <c r="B315" t="n">
-        <v>0.09847400000000001</v>
+        <v>0.09907299999999999</v>
       </c>
       <c r="C315" t="n">
-        <v>0.213568</v>
+        <v>0.205584</v>
       </c>
     </row>
     <row r="316">
@@ -4522,10 +4522,10 @@
         </is>
       </c>
       <c r="B316" t="n">
-        <v>0.09907299999999999</v>
+        <v>0.09943399999999999</v>
       </c>
       <c r="C316" t="n">
-        <v>0.211055</v>
+        <v>0.203046</v>
       </c>
     </row>
     <row r="317">
@@ -4535,10 +4535,10 @@
         </is>
       </c>
       <c r="B317" t="n">
-        <v>0.09943399999999999</v>
+        <v>0.100571</v>
       </c>
       <c r="C317" t="n">
-        <v>0.208543</v>
+        <v>0.200508</v>
       </c>
     </row>
     <row r="318">
@@ -4548,10 +4548,10 @@
         </is>
       </c>
       <c r="B318" t="n">
-        <v>0.100571</v>
+        <v>0.101335</v>
       </c>
       <c r="C318" t="n">
-        <v>0.20603</v>
+        <v>0.19797</v>
       </c>
     </row>
     <row r="319">
@@ -4561,10 +4561,10 @@
         </is>
       </c>
       <c r="B319" t="n">
-        <v>0.101335</v>
+        <v>0.103451</v>
       </c>
       <c r="C319" t="n">
-        <v>0.203518</v>
+        <v>0.195431</v>
       </c>
     </row>
     <row r="320">
@@ -4574,10 +4574,10 @@
         </is>
       </c>
       <c r="B320" t="n">
-        <v>0.103451</v>
+        <v>0.103942</v>
       </c>
       <c r="C320" t="n">
-        <v>0.201005</v>
+        <v>0.192893</v>
       </c>
     </row>
     <row r="321">
@@ -4587,10 +4587,10 @@
         </is>
       </c>
       <c r="B321" t="n">
-        <v>0.103942</v>
+        <v>0.10427</v>
       </c>
       <c r="C321" t="n">
-        <v>0.198492</v>
+        <v>0.190355</v>
       </c>
     </row>
     <row r="322">
@@ -4600,10 +4600,10 @@
         </is>
       </c>
       <c r="B322" t="n">
-        <v>0.10427</v>
+        <v>0.105774</v>
       </c>
       <c r="C322" t="n">
-        <v>0.19598</v>
+        <v>0.187817</v>
       </c>
     </row>
     <row r="323">
@@ -4613,10 +4613,10 @@
         </is>
       </c>
       <c r="B323" t="n">
-        <v>0.105774</v>
+        <v>0.106391</v>
       </c>
       <c r="C323" t="n">
-        <v>0.193467</v>
+        <v>0.185279</v>
       </c>
     </row>
     <row r="324">
@@ -4626,10 +4626,10 @@
         </is>
       </c>
       <c r="B324" t="n">
-        <v>0.106391</v>
+        <v>0.106564</v>
       </c>
       <c r="C324" t="n">
-        <v>0.190955</v>
+        <v>0.182741</v>
       </c>
     </row>
     <row r="325">
@@ -4639,10 +4639,10 @@
         </is>
       </c>
       <c r="B325" t="n">
-        <v>0.106564</v>
+        <v>0.106852</v>
       </c>
       <c r="C325" t="n">
-        <v>0.188442</v>
+        <v>0.180203</v>
       </c>
     </row>
     <row r="326">
@@ -4652,10 +4652,10 @@
         </is>
       </c>
       <c r="B326" t="n">
-        <v>0.106852</v>
+        <v>0.110708</v>
       </c>
       <c r="C326" t="n">
-        <v>0.18593</v>
+        <v>0.177665</v>
       </c>
     </row>
     <row r="327">
@@ -4665,10 +4665,10 @@
         </is>
       </c>
       <c r="B327" t="n">
-        <v>0.110708</v>
+        <v>0.112861</v>
       </c>
       <c r="C327" t="n">
-        <v>0.183417</v>
+        <v>0.175127</v>
       </c>
     </row>
     <row r="328">
@@ -4678,10 +4678,10 @@
         </is>
       </c>
       <c r="B328" t="n">
-        <v>0.112861</v>
+        <v>0.11394</v>
       </c>
       <c r="C328" t="n">
-        <v>0.180905</v>
+        <v>0.172589</v>
       </c>
     </row>
     <row r="329">
@@ -4691,10 +4691,10 @@
         </is>
       </c>
       <c r="B329" t="n">
-        <v>0.11394</v>
+        <v>0.114179</v>
       </c>
       <c r="C329" t="n">
-        <v>0.178392</v>
+        <v>0.170051</v>
       </c>
     </row>
     <row r="330">
@@ -4704,10 +4704,10 @@
         </is>
       </c>
       <c r="B330" t="n">
-        <v>0.114179</v>
+        <v>0.11468</v>
       </c>
       <c r="C330" t="n">
-        <v>0.175879</v>
+        <v>0.167513</v>
       </c>
     </row>
     <row r="331">
@@ -4717,10 +4717,10 @@
         </is>
       </c>
       <c r="B331" t="n">
-        <v>0.11468</v>
+        <v>0.114922</v>
       </c>
       <c r="C331" t="n">
-        <v>0.173367</v>
+        <v>0.164975</v>
       </c>
     </row>
     <row r="332">
@@ -4730,10 +4730,10 @@
         </is>
       </c>
       <c r="B332" t="n">
-        <v>0.114922</v>
+        <v>0.115972</v>
       </c>
       <c r="C332" t="n">
-        <v>0.170854</v>
+        <v>0.162437</v>
       </c>
     </row>
     <row r="333">
@@ -4743,10 +4743,10 @@
         </is>
       </c>
       <c r="B333" t="n">
-        <v>0.115972</v>
+        <v>0.117496</v>
       </c>
       <c r="C333" t="n">
-        <v>0.168342</v>
+        <v>0.159898</v>
       </c>
     </row>
     <row r="334">
@@ -4756,10 +4756,10 @@
         </is>
       </c>
       <c r="B334" t="n">
-        <v>0.117496</v>
+        <v>0.117846</v>
       </c>
       <c r="C334" t="n">
-        <v>0.165829</v>
+        <v>0.15736</v>
       </c>
     </row>
     <row r="335">
@@ -4769,10 +4769,10 @@
         </is>
       </c>
       <c r="B335" t="n">
-        <v>0.117846</v>
+        <v>0.119464</v>
       </c>
       <c r="C335" t="n">
-        <v>0.163317</v>
+        <v>0.154822</v>
       </c>
     </row>
     <row r="336">
@@ -4782,10 +4782,10 @@
         </is>
       </c>
       <c r="B336" t="n">
-        <v>0.119464</v>
+        <v>0.120448</v>
       </c>
       <c r="C336" t="n">
-        <v>0.160804</v>
+        <v>0.152284</v>
       </c>
     </row>
     <row r="337">
@@ -4795,10 +4795,10 @@
         </is>
       </c>
       <c r="B337" t="n">
-        <v>0.120351</v>
+        <v>0.121637</v>
       </c>
       <c r="C337" t="n">
-        <v>0.158291</v>
+        <v>0.149746</v>
       </c>
     </row>
     <row r="338">
@@ -4808,10 +4808,10 @@
         </is>
       </c>
       <c r="B338" t="n">
-        <v>0.120448</v>
+        <v>0.12397</v>
       </c>
       <c r="C338" t="n">
-        <v>0.155779</v>
+        <v>0.147208</v>
       </c>
     </row>
     <row r="339">
@@ -4821,10 +4821,10 @@
         </is>
       </c>
       <c r="B339" t="n">
-        <v>0.121637</v>
+        <v>0.124167</v>
       </c>
       <c r="C339" t="n">
-        <v>0.153266</v>
+        <v>0.14467</v>
       </c>
     </row>
     <row r="340">
@@ -4834,10 +4834,10 @@
         </is>
       </c>
       <c r="B340" t="n">
-        <v>0.12397</v>
+        <v>0.126891</v>
       </c>
       <c r="C340" t="n">
-        <v>0.150754</v>
+        <v>0.142132</v>
       </c>
     </row>
     <row r="341">
@@ -4847,10 +4847,10 @@
         </is>
       </c>
       <c r="B341" t="n">
-        <v>0.124167</v>
+        <v>0.128021</v>
       </c>
       <c r="C341" t="n">
-        <v>0.148241</v>
+        <v>0.139594</v>
       </c>
     </row>
     <row r="342">
@@ -4860,10 +4860,10 @@
         </is>
       </c>
       <c r="B342" t="n">
-        <v>0.126891</v>
+        <v>0.128976</v>
       </c>
       <c r="C342" t="n">
-        <v>0.145729</v>
+        <v>0.137056</v>
       </c>
     </row>
     <row r="343">
@@ -4873,10 +4873,10 @@
         </is>
       </c>
       <c r="B343" t="n">
-        <v>0.128021</v>
+        <v>0.130439</v>
       </c>
       <c r="C343" t="n">
-        <v>0.143216</v>
+        <v>0.134518</v>
       </c>
     </row>
     <row r="344">
@@ -4886,10 +4886,10 @@
         </is>
       </c>
       <c r="B344" t="n">
-        <v>0.128976</v>
+        <v>0.130821</v>
       </c>
       <c r="C344" t="n">
-        <v>0.140704</v>
+        <v>0.13198</v>
       </c>
     </row>
     <row r="345">
@@ -4899,10 +4899,10 @@
         </is>
       </c>
       <c r="B345" t="n">
-        <v>0.130439</v>
+        <v>0.130916</v>
       </c>
       <c r="C345" t="n">
-        <v>0.138191</v>
+        <v>0.129442</v>
       </c>
     </row>
     <row r="346">
@@ -4912,10 +4912,10 @@
         </is>
       </c>
       <c r="B346" t="n">
-        <v>0.130821</v>
+        <v>0.131982</v>
       </c>
       <c r="C346" t="n">
-        <v>0.135678</v>
+        <v>0.126904</v>
       </c>
     </row>
     <row r="347">
@@ -4925,10 +4925,10 @@
         </is>
       </c>
       <c r="B347" t="n">
-        <v>0.130916</v>
+        <v>0.135669</v>
       </c>
       <c r="C347" t="n">
-        <v>0.133166</v>
+        <v>0.124365</v>
       </c>
     </row>
     <row r="348">
@@ -4938,10 +4938,10 @@
         </is>
       </c>
       <c r="B348" t="n">
-        <v>0.131982</v>
+        <v>0.135827</v>
       </c>
       <c r="C348" t="n">
-        <v>0.130653</v>
+        <v>0.121827</v>
       </c>
     </row>
     <row r="349">
@@ -4951,10 +4951,10 @@
         </is>
       </c>
       <c r="B349" t="n">
-        <v>0.135669</v>
+        <v>0.13733</v>
       </c>
       <c r="C349" t="n">
-        <v>0.128141</v>
+        <v>0.119289</v>
       </c>
     </row>
     <row r="350">
@@ -4964,10 +4964,10 @@
         </is>
       </c>
       <c r="B350" t="n">
-        <v>0.135827</v>
+        <v>0.138613</v>
       </c>
       <c r="C350" t="n">
-        <v>0.125628</v>
+        <v>0.116751</v>
       </c>
     </row>
     <row r="351">
@@ -4977,10 +4977,10 @@
         </is>
       </c>
       <c r="B351" t="n">
-        <v>0.13733</v>
+        <v>0.138762</v>
       </c>
       <c r="C351" t="n">
-        <v>0.123116</v>
+        <v>0.114213</v>
       </c>
     </row>
     <row r="352">
@@ -4990,10 +4990,10 @@
         </is>
       </c>
       <c r="B352" t="n">
-        <v>0.138613</v>
+        <v>0.140029</v>
       </c>
       <c r="C352" t="n">
-        <v>0.120603</v>
+        <v>0.111675</v>
       </c>
     </row>
     <row r="353">
@@ -5003,10 +5003,10 @@
         </is>
       </c>
       <c r="B353" t="n">
-        <v>0.138762</v>
+        <v>0.140099</v>
       </c>
       <c r="C353" t="n">
-        <v>0.11809</v>
+        <v>0.109137</v>
       </c>
     </row>
     <row r="354">
@@ -5016,10 +5016,10 @@
         </is>
       </c>
       <c r="B354" t="n">
-        <v>0.139275</v>
+        <v>0.140214</v>
       </c>
       <c r="C354" t="n">
-        <v>0.115578</v>
+        <v>0.106599</v>
       </c>
     </row>
     <row r="355">
@@ -5029,10 +5029,10 @@
         </is>
       </c>
       <c r="B355" t="n">
-        <v>0.140029</v>
+        <v>0.143039</v>
       </c>
       <c r="C355" t="n">
-        <v>0.113065</v>
+        <v>0.104061</v>
       </c>
     </row>
     <row r="356">
@@ -5042,10 +5042,10 @@
         </is>
       </c>
       <c r="B356" t="n">
-        <v>0.140099</v>
+        <v>0.144579</v>
       </c>
       <c r="C356" t="n">
-        <v>0.110553</v>
+        <v>0.101523</v>
       </c>
     </row>
     <row r="357">
@@ -5055,10 +5055,10 @@
         </is>
       </c>
       <c r="B357" t="n">
-        <v>0.140214</v>
+        <v>0.145291</v>
       </c>
       <c r="C357" t="n">
-        <v>0.10804</v>
+        <v>0.098985</v>
       </c>
     </row>
     <row r="358">
@@ -5068,10 +5068,10 @@
         </is>
       </c>
       <c r="B358" t="n">
-        <v>0.143039</v>
+        <v>0.145554</v>
       </c>
       <c r="C358" t="n">
-        <v>0.105528</v>
+        <v>0.096447</v>
       </c>
     </row>
     <row r="359">
@@ -5081,10 +5081,10 @@
         </is>
       </c>
       <c r="B359" t="n">
-        <v>0.144579</v>
+        <v>0.151419</v>
       </c>
       <c r="C359" t="n">
-        <v>0.103015</v>
+        <v>0.09390900000000001</v>
       </c>
     </row>
     <row r="360">
@@ -5094,10 +5094,10 @@
         </is>
       </c>
       <c r="B360" t="n">
-        <v>0.145291</v>
+        <v>0.151465</v>
       </c>
       <c r="C360" t="n">
-        <v>0.100503</v>
+        <v>0.09137099999999999</v>
       </c>
     </row>
     <row r="361">
@@ -5107,10 +5107,10 @@
         </is>
       </c>
       <c r="B361" t="n">
-        <v>0.145554</v>
+        <v>0.15511</v>
       </c>
       <c r="C361" t="n">
-        <v>0.09798999999999999</v>
+        <v>0.08883199999999999</v>
       </c>
     </row>
     <row r="362">
@@ -5120,10 +5120,10 @@
         </is>
       </c>
       <c r="B362" t="n">
-        <v>0.151419</v>
+        <v>0.15559</v>
       </c>
       <c r="C362" t="n">
-        <v>0.09547700000000001</v>
+        <v>0.086294</v>
       </c>
     </row>
     <row r="363">
@@ -5133,10 +5133,10 @@
         </is>
       </c>
       <c r="B363" t="n">
-        <v>0.151465</v>
+        <v>0.155726</v>
       </c>
       <c r="C363" t="n">
-        <v>0.09296500000000001</v>
+        <v>0.083756</v>
       </c>
     </row>
     <row r="364">
@@ -5146,10 +5146,10 @@
         </is>
       </c>
       <c r="B364" t="n">
-        <v>0.15511</v>
+        <v>0.158503</v>
       </c>
       <c r="C364" t="n">
-        <v>0.090452</v>
+        <v>0.081218</v>
       </c>
     </row>
     <row r="365">
@@ -5159,10 +5159,10 @@
         </is>
       </c>
       <c r="B365" t="n">
-        <v>0.15559</v>
+        <v>0.16241</v>
       </c>
       <c r="C365" t="n">
-        <v>0.08794</v>
+        <v>0.07868</v>
       </c>
     </row>
     <row r="366">
@@ -5172,10 +5172,10 @@
         </is>
       </c>
       <c r="B366" t="n">
-        <v>0.155726</v>
+        <v>0.179571</v>
       </c>
       <c r="C366" t="n">
-        <v>0.085427</v>
+        <v>0.076142</v>
       </c>
     </row>
     <row r="367">
@@ -5185,10 +5185,10 @@
         </is>
       </c>
       <c r="B367" t="n">
-        <v>0.158503</v>
+        <v>0.183042</v>
       </c>
       <c r="C367" t="n">
-        <v>0.082915</v>
+        <v>0.073604</v>
       </c>
     </row>
     <row r="368">
@@ -5198,10 +5198,10 @@
         </is>
       </c>
       <c r="B368" t="n">
-        <v>0.16241</v>
+        <v>0.189387</v>
       </c>
       <c r="C368" t="n">
-        <v>0.080402</v>
+        <v>0.071066</v>
       </c>
     </row>
     <row r="369">
@@ -5211,10 +5211,10 @@
         </is>
       </c>
       <c r="B369" t="n">
-        <v>0.179571</v>
+        <v>0.193249</v>
       </c>
       <c r="C369" t="n">
-        <v>0.077889</v>
+        <v>0.06852800000000001</v>
       </c>
     </row>
     <row r="370">
@@ -5224,10 +5224,10 @@
         </is>
       </c>
       <c r="B370" t="n">
-        <v>0.183042</v>
+        <v>0.195388</v>
       </c>
       <c r="C370" t="n">
-        <v>0.075377</v>
+        <v>0.06598999999999999</v>
       </c>
     </row>
     <row r="371">
@@ -5237,10 +5237,10 @@
         </is>
       </c>
       <c r="B371" t="n">
-        <v>0.189387</v>
+        <v>0.200683</v>
       </c>
       <c r="C371" t="n">
-        <v>0.072864</v>
+        <v>0.06345199999999999</v>
       </c>
     </row>
     <row r="372">
@@ -5250,10 +5250,10 @@
         </is>
       </c>
       <c r="B372" t="n">
-        <v>0.193249</v>
+        <v>0.202141</v>
       </c>
       <c r="C372" t="n">
-        <v>0.070352</v>
+        <v>0.060914</v>
       </c>
     </row>
     <row r="373">
@@ -5263,10 +5263,10 @@
         </is>
       </c>
       <c r="B373" t="n">
-        <v>0.195388</v>
+        <v>0.21126</v>
       </c>
       <c r="C373" t="n">
-        <v>0.067839</v>
+        <v>0.058376</v>
       </c>
     </row>
     <row r="374">
@@ -5276,10 +5276,10 @@
         </is>
       </c>
       <c r="B374" t="n">
-        <v>0.200683</v>
+        <v>0.212282</v>
       </c>
       <c r="C374" t="n">
-        <v>0.065327</v>
+        <v>0.055838</v>
       </c>
     </row>
     <row r="375">
@@ -5289,10 +5289,10 @@
         </is>
       </c>
       <c r="B375" t="n">
-        <v>0.202141</v>
+        <v>0.213977</v>
       </c>
       <c r="C375" t="n">
-        <v>0.06281399999999999</v>
+        <v>0.053299</v>
       </c>
     </row>
     <row r="376">
@@ -5302,10 +5302,10 @@
         </is>
       </c>
       <c r="B376" t="n">
-        <v>0.21126</v>
+        <v>0.224095</v>
       </c>
       <c r="C376" t="n">
-        <v>0.060302</v>
+        <v>0.050761</v>
       </c>
     </row>
     <row r="377">
@@ -5315,10 +5315,10 @@
         </is>
       </c>
       <c r="B377" t="n">
-        <v>0.212282</v>
+        <v>0.229443</v>
       </c>
       <c r="C377" t="n">
-        <v>0.057789</v>
+        <v>0.048223</v>
       </c>
     </row>
     <row r="378">
@@ -5328,10 +5328,10 @@
         </is>
       </c>
       <c r="B378" t="n">
-        <v>0.213977</v>
+        <v>0.235662</v>
       </c>
       <c r="C378" t="n">
-        <v>0.055276</v>
+        <v>0.045685</v>
       </c>
     </row>
     <row r="379">
@@ -5341,10 +5341,10 @@
         </is>
       </c>
       <c r="B379" t="n">
-        <v>0.224095</v>
+        <v>0.279391</v>
       </c>
       <c r="C379" t="n">
-        <v>0.052764</v>
+        <v>0.043147</v>
       </c>
     </row>
     <row r="380">
@@ -5354,10 +5354,10 @@
         </is>
       </c>
       <c r="B380" t="n">
-        <v>0.229443</v>
+        <v>0.28675</v>
       </c>
       <c r="C380" t="n">
-        <v>0.050251</v>
+        <v>0.040609</v>
       </c>
     </row>
     <row r="381">
@@ -5367,10 +5367,10 @@
         </is>
       </c>
       <c r="B381" t="n">
-        <v>0.235662</v>
+        <v>0.303016</v>
       </c>
       <c r="C381" t="n">
-        <v>0.047739</v>
+        <v>0.038071</v>
       </c>
     </row>
     <row r="382">
@@ -5380,10 +5380,10 @@
         </is>
       </c>
       <c r="B382" t="n">
-        <v>0.279391</v>
+        <v>0.359445</v>
       </c>
       <c r="C382" t="n">
-        <v>0.045226</v>
+        <v>0.035533</v>
       </c>
     </row>
     <row r="383">
@@ -5393,10 +5393,10 @@
         </is>
       </c>
       <c r="B383" t="n">
-        <v>0.28675</v>
+        <v>0.371876</v>
       </c>
       <c r="C383" t="n">
-        <v>0.042714</v>
+        <v>0.032995</v>
       </c>
     </row>
     <row r="384">
@@ -5406,10 +5406,10 @@
         </is>
       </c>
       <c r="B384" t="n">
-        <v>0.303016</v>
+        <v>0.397465</v>
       </c>
       <c r="C384" t="n">
-        <v>0.040201</v>
+        <v>0.030457</v>
       </c>
     </row>
     <row r="385">
@@ -5419,10 +5419,10 @@
         </is>
       </c>
       <c r="B385" t="n">
-        <v>0.359445</v>
+        <v>0.400164</v>
       </c>
       <c r="C385" t="n">
-        <v>0.037688</v>
+        <v>0.027919</v>
       </c>
     </row>
     <row r="386">
@@ -5432,10 +5432,10 @@
         </is>
       </c>
       <c r="B386" t="n">
-        <v>0.371876</v>
+        <v>0.40983</v>
       </c>
       <c r="C386" t="n">
-        <v>0.035176</v>
+        <v>0.025381</v>
       </c>
     </row>
     <row r="387">
@@ -5445,10 +5445,10 @@
         </is>
       </c>
       <c r="B387" t="n">
-        <v>0.389014</v>
+        <v>0.419404</v>
       </c>
       <c r="C387" t="n">
-        <v>0.032663</v>
+        <v>0.022843</v>
       </c>
     </row>
     <row r="388">
@@ -5458,10 +5458,10 @@
         </is>
       </c>
       <c r="B388" t="n">
-        <v>0.397465</v>
+        <v>0.6049369999999999</v>
       </c>
       <c r="C388" t="n">
-        <v>0.030151</v>
+        <v>0.020305</v>
       </c>
     </row>
     <row r="389">
@@ -5471,10 +5471,10 @@
         </is>
       </c>
       <c r="B389" t="n">
-        <v>0.400164</v>
+        <v>0.620194</v>
       </c>
       <c r="C389" t="n">
-        <v>0.027638</v>
+        <v>0.017766</v>
       </c>
     </row>
     <row r="390">
@@ -5484,10 +5484,10 @@
         </is>
       </c>
       <c r="B390" t="n">
-        <v>0.40983</v>
+        <v>0.634074</v>
       </c>
       <c r="C390" t="n">
-        <v>0.025126</v>
+        <v>0.015228</v>
       </c>
     </row>
     <row r="391">
@@ -5497,10 +5497,10 @@
         </is>
       </c>
       <c r="B391" t="n">
-        <v>0.419404</v>
+        <v>0.672434</v>
       </c>
       <c r="C391" t="n">
-        <v>0.022613</v>
+        <v>0.01269</v>
       </c>
     </row>
     <row r="392">
@@ -5510,10 +5510,10 @@
         </is>
       </c>
       <c r="B392" t="n">
-        <v>0.6049369999999999</v>
+        <v>0.711338</v>
       </c>
       <c r="C392" t="n">
-        <v>0.020101</v>
+        <v>0.010152</v>
       </c>
     </row>
     <row r="393">
@@ -5523,10 +5523,10 @@
         </is>
       </c>
       <c r="B393" t="n">
-        <v>0.620194</v>
+        <v>0.76535</v>
       </c>
       <c r="C393" t="n">
-        <v>0.017588</v>
+        <v>0.007614</v>
       </c>
     </row>
     <row r="394">
@@ -5536,10 +5536,10 @@
         </is>
       </c>
       <c r="B394" t="n">
-        <v>0.634074</v>
+        <v>0.838984</v>
       </c>
       <c r="C394" t="n">
-        <v>0.015075</v>
+        <v>0.005076</v>
       </c>
     </row>
     <row r="395">
@@ -5549,62 +5549,62 @@
         </is>
       </c>
       <c r="B395" t="n">
-        <v>0.672434</v>
+        <v>1.015082</v>
       </c>
       <c r="C395" t="n">
-        <v>0.012563</v>
+        <v>0.002538</v>
       </c>
     </row>
     <row r="396">
       <c r="A396" t="inlineStr">
         <is>
-          <t>Raw market</t>
+          <t>Adjusted target</t>
         </is>
       </c>
       <c r="B396" t="n">
-        <v>0.711338</v>
+        <v>0.000111</v>
       </c>
       <c r="C396" t="n">
-        <v>0.01005</v>
+        <v>1</v>
       </c>
     </row>
     <row r="397">
       <c r="A397" t="inlineStr">
         <is>
-          <t>Raw market</t>
+          <t>Adjusted target</t>
         </is>
       </c>
       <c r="B397" t="n">
-        <v>0.76535</v>
+        <v>0.000351</v>
       </c>
       <c r="C397" t="n">
-        <v>0.007538</v>
+        <v>0.997462</v>
       </c>
     </row>
     <row r="398">
       <c r="A398" t="inlineStr">
         <is>
-          <t>Raw market</t>
+          <t>Adjusted target</t>
         </is>
       </c>
       <c r="B398" t="n">
-        <v>0.838984</v>
+        <v>0.000614</v>
       </c>
       <c r="C398" t="n">
-        <v>0.005025</v>
+        <v>0.994924</v>
       </c>
     </row>
     <row r="399">
       <c r="A399" t="inlineStr">
         <is>
-          <t>Raw market</t>
+          <t>Adjusted target</t>
         </is>
       </c>
       <c r="B399" t="n">
-        <v>1.015082</v>
+        <v>0.001035</v>
       </c>
       <c r="C399" t="n">
-        <v>0.002513</v>
+        <v>0.992386</v>
       </c>
     </row>
     <row r="400">
@@ -5614,10 +5614,10 @@
         </is>
       </c>
       <c r="B400" t="n">
-        <v>0.000111</v>
+        <v>0.001117</v>
       </c>
       <c r="C400" t="n">
-        <v>1</v>
+        <v>0.989848</v>
       </c>
     </row>
     <row r="401">
@@ -5627,10 +5627,10 @@
         </is>
       </c>
       <c r="B401" t="n">
-        <v>0.000349</v>
+        <v>0.001861</v>
       </c>
       <c r="C401" t="n">
-        <v>0.997487</v>
+        <v>0.98731</v>
       </c>
     </row>
     <row r="402">
@@ -5640,10 +5640,10 @@
         </is>
       </c>
       <c r="B402" t="n">
-        <v>0.000614</v>
+        <v>0.002009</v>
       </c>
       <c r="C402" t="n">
-        <v>0.9949750000000001</v>
+        <v>0.984772</v>
       </c>
     </row>
     <row r="403">
@@ -5653,10 +5653,10 @@
         </is>
       </c>
       <c r="B403" t="n">
-        <v>0.001033</v>
+        <v>0.00224</v>
       </c>
       <c r="C403" t="n">
-        <v>0.992462</v>
+        <v>0.9822340000000001</v>
       </c>
     </row>
     <row r="404">
@@ -5666,10 +5666,10 @@
         </is>
       </c>
       <c r="B404" t="n">
-        <v>0.001116</v>
+        <v>0.002354</v>
       </c>
       <c r="C404" t="n">
-        <v>0.98995</v>
+        <v>0.979695</v>
       </c>
     </row>
     <row r="405">
@@ -5679,10 +5679,10 @@
         </is>
       </c>
       <c r="B405" t="n">
-        <v>0.001845</v>
+        <v>0.002547</v>
       </c>
       <c r="C405" t="n">
-        <v>0.987437</v>
+        <v>0.9771570000000001</v>
       </c>
     </row>
     <row r="406">
@@ -5692,10 +5692,10 @@
         </is>
       </c>
       <c r="B406" t="n">
-        <v>0.00202</v>
+        <v>0.00262</v>
       </c>
       <c r="C406" t="n">
-        <v>0.9849250000000001</v>
+        <v>0.974619</v>
       </c>
     </row>
     <row r="407">
@@ -5705,10 +5705,10 @@
         </is>
       </c>
       <c r="B407" t="n">
-        <v>0.002227</v>
+        <v>0.002726</v>
       </c>
       <c r="C407" t="n">
-        <v>0.982412</v>
+        <v>0.972081</v>
       </c>
     </row>
     <row r="408">
@@ -5718,10 +5718,10 @@
         </is>
       </c>
       <c r="B408" t="n">
-        <v>0.002357</v>
+        <v>0.002865</v>
       </c>
       <c r="C408" t="n">
-        <v>0.979899</v>
+        <v>0.969543</v>
       </c>
     </row>
     <row r="409">
@@ -5731,10 +5731,10 @@
         </is>
       </c>
       <c r="B409" t="n">
-        <v>0.002518</v>
+        <v>0.003223</v>
       </c>
       <c r="C409" t="n">
-        <v>0.977387</v>
+        <v>0.967005</v>
       </c>
     </row>
     <row r="410">
@@ -5744,10 +5744,10 @@
         </is>
       </c>
       <c r="B410" t="n">
-        <v>0.002599</v>
+        <v>0.003379</v>
       </c>
       <c r="C410" t="n">
-        <v>0.974874</v>
+        <v>0.964467</v>
       </c>
     </row>
     <row r="411">
@@ -5757,10 +5757,10 @@
         </is>
       </c>
       <c r="B411" t="n">
-        <v>0.002749</v>
+        <v>0.003475</v>
       </c>
       <c r="C411" t="n">
-        <v>0.9723619999999999</v>
+        <v>0.961929</v>
       </c>
     </row>
     <row r="412">
@@ -5770,10 +5770,10 @@
         </is>
       </c>
       <c r="B412" t="n">
-        <v>0.002894</v>
+        <v>0.003932</v>
       </c>
       <c r="C412" t="n">
-        <v>0.969849</v>
+        <v>0.959391</v>
       </c>
     </row>
     <row r="413">
@@ -5783,10 +5783,10 @@
         </is>
       </c>
       <c r="B413" t="n">
-        <v>0.003212</v>
+        <v>0.004535</v>
       </c>
       <c r="C413" t="n">
-        <v>0.967337</v>
+        <v>0.956853</v>
       </c>
     </row>
     <row r="414">
@@ -5796,10 +5796,10 @@
         </is>
       </c>
       <c r="B414" t="n">
-        <v>0.003346</v>
+        <v>0.004615</v>
       </c>
       <c r="C414" t="n">
-        <v>0.964824</v>
+        <v>0.954315</v>
       </c>
     </row>
     <row r="415">
@@ -5809,10 +5809,10 @@
         </is>
       </c>
       <c r="B415" t="n">
-        <v>0.003467</v>
+        <v>0.004823</v>
       </c>
       <c r="C415" t="n">
-        <v>0.9623119999999999</v>
+        <v>0.951777</v>
       </c>
     </row>
     <row r="416">
@@ -5822,10 +5822,10 @@
         </is>
       </c>
       <c r="B416" t="n">
-        <v>0.00389</v>
+        <v>0.004945</v>
       </c>
       <c r="C416" t="n">
-        <v>0.959799</v>
+        <v>0.9492390000000001</v>
       </c>
     </row>
     <row r="417">
@@ -5835,10 +5835,10 @@
         </is>
       </c>
       <c r="B417" t="n">
-        <v>0.00453</v>
+        <v>0.005079</v>
       </c>
       <c r="C417" t="n">
-        <v>0.957286</v>
+        <v>0.946701</v>
       </c>
     </row>
     <row r="418">
@@ -5848,10 +5848,10 @@
         </is>
       </c>
       <c r="B418" t="n">
-        <v>0.004607</v>
+        <v>0.005109</v>
       </c>
       <c r="C418" t="n">
-        <v>0.954774</v>
+        <v>0.9441619999999999</v>
       </c>
     </row>
     <row r="419">
@@ -5861,10 +5861,10 @@
         </is>
       </c>
       <c r="B419" t="n">
-        <v>0.004829</v>
+        <v>0.005249</v>
       </c>
       <c r="C419" t="n">
-        <v>0.952261</v>
+        <v>0.941624</v>
       </c>
     </row>
     <row r="420">
@@ -5874,10 +5874,10 @@
         </is>
       </c>
       <c r="B420" t="n">
-        <v>0.005012</v>
+        <v>0.005521</v>
       </c>
       <c r="C420" t="n">
-        <v>0.949749</v>
+        <v>0.939086</v>
       </c>
     </row>
     <row r="421">
@@ -5887,10 +5887,10 @@
         </is>
       </c>
       <c r="B421" t="n">
-        <v>0.005101</v>
+        <v>0.005664</v>
       </c>
       <c r="C421" t="n">
-        <v>0.947236</v>
+        <v>0.936548</v>
       </c>
     </row>
     <row r="422">
@@ -5900,10 +5900,10 @@
         </is>
       </c>
       <c r="B422" t="n">
-        <v>0.005123</v>
+        <v>0.005687</v>
       </c>
       <c r="C422" t="n">
-        <v>0.944724</v>
+        <v>0.93401</v>
       </c>
     </row>
     <row r="423">
@@ -5913,10 +5913,10 @@
         </is>
       </c>
       <c r="B423" t="n">
-        <v>0.005234</v>
+        <v>0.005835</v>
       </c>
       <c r="C423" t="n">
-        <v>0.942211</v>
+        <v>0.931472</v>
       </c>
     </row>
     <row r="424">
@@ -5926,10 +5926,10 @@
         </is>
       </c>
       <c r="B424" t="n">
-        <v>0.005545</v>
+        <v>0.006023</v>
       </c>
       <c r="C424" t="n">
-        <v>0.939698</v>
+        <v>0.928934</v>
       </c>
     </row>
     <row r="425">
@@ -5939,10 +5939,10 @@
         </is>
       </c>
       <c r="B425" t="n">
-        <v>0.005587</v>
+        <v>0.006073</v>
       </c>
       <c r="C425" t="n">
-        <v>0.937186</v>
+        <v>0.926396</v>
       </c>
     </row>
     <row r="426">
@@ -5952,10 +5952,10 @@
         </is>
       </c>
       <c r="B426" t="n">
-        <v>0.005634</v>
+        <v>0.006608</v>
       </c>
       <c r="C426" t="n">
-        <v>0.934673</v>
+        <v>0.923858</v>
       </c>
     </row>
     <row r="427">
@@ -5965,10 +5965,10 @@
         </is>
       </c>
       <c r="B427" t="n">
-        <v>0.005805</v>
+        <v>0.006897</v>
       </c>
       <c r="C427" t="n">
-        <v>0.932161</v>
+        <v>0.92132</v>
       </c>
     </row>
     <row r="428">
@@ -5978,10 +5978,10 @@
         </is>
       </c>
       <c r="B428" t="n">
-        <v>0.005982</v>
+        <v>0.007442</v>
       </c>
       <c r="C428" t="n">
-        <v>0.929648</v>
+        <v>0.918782</v>
       </c>
     </row>
     <row r="429">
@@ -5991,10 +5991,10 @@
         </is>
       </c>
       <c r="B429" t="n">
-        <v>0.005989</v>
+        <v>0.008368</v>
       </c>
       <c r="C429" t="n">
-        <v>0.927136</v>
+        <v>0.9162439999999999</v>
       </c>
     </row>
     <row r="430">
@@ -6004,10 +6004,10 @@
         </is>
       </c>
       <c r="B430" t="n">
-        <v>0.006564</v>
+        <v>0.008512</v>
       </c>
       <c r="C430" t="n">
-        <v>0.924623</v>
+        <v>0.913706</v>
       </c>
     </row>
     <row r="431">
@@ -6017,10 +6017,10 @@
         </is>
       </c>
       <c r="B431" t="n">
-        <v>0.006864</v>
+        <v>0.008832</v>
       </c>
       <c r="C431" t="n">
-        <v>0.922111</v>
+        <v>0.911168</v>
       </c>
     </row>
     <row r="432">
@@ -6030,10 +6030,10 @@
         </is>
       </c>
       <c r="B432" t="n">
-        <v>0.007425</v>
+        <v>0.008869999999999999</v>
       </c>
       <c r="C432" t="n">
-        <v>0.919598</v>
+        <v>0.908629</v>
       </c>
     </row>
     <row r="433">
@@ -6043,10 +6043,10 @@
         </is>
       </c>
       <c r="B433" t="n">
-        <v>0.008342</v>
+        <v>0.008985</v>
       </c>
       <c r="C433" t="n">
-        <v>0.917085</v>
+        <v>0.906091</v>
       </c>
     </row>
     <row r="434">
@@ -6056,10 +6056,10 @@
         </is>
       </c>
       <c r="B434" t="n">
-        <v>0.008597</v>
+        <v>0.009088000000000001</v>
       </c>
       <c r="C434" t="n">
-        <v>0.914573</v>
+        <v>0.9035530000000001</v>
       </c>
     </row>
     <row r="435">
@@ -6069,10 +6069,10 @@
         </is>
       </c>
       <c r="B435" t="n">
-        <v>0.008770999999999999</v>
+        <v>0.009202</v>
       </c>
       <c r="C435" t="n">
-        <v>0.91206</v>
+        <v>0.901015</v>
       </c>
     </row>
     <row r="436">
@@ -6082,10 +6082,10 @@
         </is>
       </c>
       <c r="B436" t="n">
-        <v>0.00894</v>
+        <v>0.009339999999999999</v>
       </c>
       <c r="C436" t="n">
-        <v>0.909548</v>
+        <v>0.898477</v>
       </c>
     </row>
     <row r="437">
@@ -6095,10 +6095,10 @@
         </is>
       </c>
       <c r="B437" t="n">
-        <v>0.008942</v>
+        <v>0.009495999999999999</v>
       </c>
       <c r="C437" t="n">
-        <v>0.907035</v>
+        <v>0.895939</v>
       </c>
     </row>
     <row r="438">
@@ -6108,10 +6108,10 @@
         </is>
       </c>
       <c r="B438" t="n">
-        <v>0.00912</v>
+        <v>0.009577</v>
       </c>
       <c r="C438" t="n">
-        <v>0.904523</v>
+        <v>0.893401</v>
       </c>
     </row>
     <row r="439">
@@ -6121,10 +6121,10 @@
         </is>
       </c>
       <c r="B439" t="n">
-        <v>0.009166000000000001</v>
+        <v>0.009887</v>
       </c>
       <c r="C439" t="n">
-        <v>0.90201</v>
+        <v>0.890863</v>
       </c>
     </row>
     <row r="440">
@@ -6134,10 +6134,10 @@
         </is>
       </c>
       <c r="B440" t="n">
-        <v>0.009220000000000001</v>
+        <v>0.010131</v>
       </c>
       <c r="C440" t="n">
-        <v>0.899497</v>
+        <v>0.888325</v>
       </c>
     </row>
     <row r="441">
@@ -6147,10 +6147,10 @@
         </is>
       </c>
       <c r="B441" t="n">
-        <v>0.009479</v>
+        <v>0.010628</v>
       </c>
       <c r="C441" t="n">
-        <v>0.896985</v>
+        <v>0.885787</v>
       </c>
     </row>
     <row r="442">
@@ -6160,10 +6160,10 @@
         </is>
       </c>
       <c r="B442" t="n">
-        <v>0.009617000000000001</v>
+        <v>0.010962</v>
       </c>
       <c r="C442" t="n">
-        <v>0.894472</v>
+        <v>0.883249</v>
       </c>
     </row>
     <row r="443">
@@ -6173,10 +6173,10 @@
         </is>
       </c>
       <c r="B443" t="n">
-        <v>0.009793</v>
+        <v>0.010971</v>
       </c>
       <c r="C443" t="n">
-        <v>0.89196</v>
+        <v>0.880711</v>
       </c>
     </row>
     <row r="444">
@@ -6186,10 +6186,10 @@
         </is>
       </c>
       <c r="B444" t="n">
-        <v>0.01</v>
+        <v>0.011055</v>
       </c>
       <c r="C444" t="n">
-        <v>0.889447</v>
+        <v>0.878173</v>
       </c>
     </row>
     <row r="445">
@@ -6199,10 +6199,10 @@
         </is>
       </c>
       <c r="B445" t="n">
-        <v>0.01076</v>
+        <v>0.011225</v>
       </c>
       <c r="C445" t="n">
-        <v>0.886935</v>
+        <v>0.8756350000000001</v>
       </c>
     </row>
     <row r="446">
@@ -6212,10 +6212,10 @@
         </is>
       </c>
       <c r="B446" t="n">
-        <v>0.010857</v>
+        <v>0.011298</v>
       </c>
       <c r="C446" t="n">
-        <v>0.884422</v>
+        <v>0.873096</v>
       </c>
     </row>
     <row r="447">
@@ -6225,10 +6225,10 @@
         </is>
       </c>
       <c r="B447" t="n">
-        <v>0.010896</v>
+        <v>0.011497</v>
       </c>
       <c r="C447" t="n">
-        <v>0.88191</v>
+        <v>0.8705580000000001</v>
       </c>
     </row>
     <row r="448">
@@ -6238,10 +6238,10 @@
         </is>
       </c>
       <c r="B448" t="n">
-        <v>0.011095</v>
+        <v>0.011558</v>
       </c>
       <c r="C448" t="n">
-        <v>0.879397</v>
+        <v>0.86802</v>
       </c>
     </row>
     <row r="449">
@@ -6251,10 +6251,10 @@
         </is>
       </c>
       <c r="B449" t="n">
-        <v>0.011222</v>
+        <v>0.011618</v>
       </c>
       <c r="C449" t="n">
-        <v>0.876884</v>
+        <v>0.865482</v>
       </c>
     </row>
     <row r="450">
@@ -6264,10 +6264,10 @@
         </is>
       </c>
       <c r="B450" t="n">
-        <v>0.01125</v>
+        <v>0.012029</v>
       </c>
       <c r="C450" t="n">
-        <v>0.874372</v>
+        <v>0.862944</v>
       </c>
     </row>
     <row r="451">
@@ -6277,10 +6277,10 @@
         </is>
       </c>
       <c r="B451" t="n">
-        <v>0.011354</v>
+        <v>0.012366</v>
       </c>
       <c r="C451" t="n">
-        <v>0.8718590000000001</v>
+        <v>0.860406</v>
       </c>
     </row>
     <row r="452">
@@ -6290,10 +6290,10 @@
         </is>
       </c>
       <c r="B452" t="n">
-        <v>0.011539</v>
+        <v>0.012375</v>
       </c>
       <c r="C452" t="n">
-        <v>0.869347</v>
+        <v>0.857868</v>
       </c>
     </row>
     <row r="453">
@@ -6303,10 +6303,10 @@
         </is>
       </c>
       <c r="B453" t="n">
-        <v>0.011696</v>
+        <v>0.01257</v>
       </c>
       <c r="C453" t="n">
-        <v>0.866834</v>
+        <v>0.85533</v>
       </c>
     </row>
     <row r="454">
@@ -6316,10 +6316,10 @@
         </is>
       </c>
       <c r="B454" t="n">
-        <v>0.012035</v>
+        <v>0.012647</v>
       </c>
       <c r="C454" t="n">
-        <v>0.864322</v>
+        <v>0.852792</v>
       </c>
     </row>
     <row r="455">
@@ -6329,10 +6329,10 @@
         </is>
       </c>
       <c r="B455" t="n">
-        <v>0.012331</v>
+        <v>0.012988</v>
       </c>
       <c r="C455" t="n">
-        <v>0.861809</v>
+        <v>0.850254</v>
       </c>
     </row>
     <row r="456">
@@ -6342,10 +6342,10 @@
         </is>
       </c>
       <c r="B456" t="n">
-        <v>0.012402</v>
+        <v>0.013098</v>
       </c>
       <c r="C456" t="n">
-        <v>0.8592959999999999</v>
+        <v>0.847716</v>
       </c>
     </row>
     <row r="457">
@@ -6355,10 +6355,10 @@
         </is>
       </c>
       <c r="B457" t="n">
-        <v>0.012555</v>
+        <v>0.013112</v>
       </c>
       <c r="C457" t="n">
-        <v>0.856784</v>
+        <v>0.845178</v>
       </c>
     </row>
     <row r="458">
@@ -6368,10 +6368,10 @@
         </is>
       </c>
       <c r="B458" t="n">
-        <v>0.012644</v>
+        <v>0.013673</v>
       </c>
       <c r="C458" t="n">
-        <v>0.854271</v>
+        <v>0.8426399999999999</v>
       </c>
     </row>
     <row r="459">
@@ -6381,10 +6381,10 @@
         </is>
       </c>
       <c r="B459" t="n">
-        <v>0.013066</v>
+        <v>0.013806</v>
       </c>
       <c r="C459" t="n">
-        <v>0.851759</v>
+        <v>0.840102</v>
       </c>
     </row>
     <row r="460">
@@ -6394,10 +6394,10 @@
         </is>
       </c>
       <c r="B460" t="n">
-        <v>0.013145</v>
+        <v>0.014188</v>
       </c>
       <c r="C460" t="n">
-        <v>0.8492459999999999</v>
+        <v>0.8375629999999999</v>
       </c>
     </row>
     <row r="461">
@@ -6407,10 +6407,10 @@
         </is>
       </c>
       <c r="B461" t="n">
-        <v>0.013169</v>
+        <v>0.014242</v>
       </c>
       <c r="C461" t="n">
-        <v>0.846734</v>
+        <v>0.835025</v>
       </c>
     </row>
     <row r="462">
@@ -6420,10 +6420,10 @@
         </is>
       </c>
       <c r="B462" t="n">
-        <v>0.01357</v>
+        <v>0.014313</v>
       </c>
       <c r="C462" t="n">
-        <v>0.844221</v>
+        <v>0.832487</v>
       </c>
     </row>
     <row r="463">
@@ -6433,10 +6433,10 @@
         </is>
       </c>
       <c r="B463" t="n">
-        <v>0.013723</v>
+        <v>0.014401</v>
       </c>
       <c r="C463" t="n">
-        <v>0.841709</v>
+        <v>0.829949</v>
       </c>
     </row>
     <row r="464">
@@ -6446,10 +6446,10 @@
         </is>
       </c>
       <c r="B464" t="n">
-        <v>0.014166</v>
+        <v>0.014488</v>
       </c>
       <c r="C464" t="n">
-        <v>0.8391960000000001</v>
+        <v>0.827411</v>
       </c>
     </row>
     <row r="465">
@@ -6459,10 +6459,10 @@
         </is>
       </c>
       <c r="B465" t="n">
-        <v>0.014317</v>
+        <v>0.014691</v>
       </c>
       <c r="C465" t="n">
-        <v>0.836683</v>
+        <v>0.824873</v>
       </c>
     </row>
     <row r="466">
@@ -6472,10 +6472,10 @@
         </is>
       </c>
       <c r="B466" t="n">
-        <v>0.014389</v>
+        <v>0.015024</v>
       </c>
       <c r="C466" t="n">
-        <v>0.834171</v>
+        <v>0.822335</v>
       </c>
     </row>
     <row r="467">
@@ -6485,10 +6485,10 @@
         </is>
       </c>
       <c r="B467" t="n">
-        <v>0.014396</v>
+        <v>0.015061</v>
       </c>
       <c r="C467" t="n">
-        <v>0.831658</v>
+        <v>0.819797</v>
       </c>
     </row>
     <row r="468">
@@ -6498,10 +6498,10 @@
         </is>
       </c>
       <c r="B468" t="n">
-        <v>0.014432</v>
+        <v>0.015097</v>
       </c>
       <c r="C468" t="n">
-        <v>0.829146</v>
+        <v>0.817259</v>
       </c>
     </row>
     <row r="469">
@@ -6511,10 +6511,10 @@
         </is>
       </c>
       <c r="B469" t="n">
-        <v>0.014566</v>
+        <v>0.015147</v>
       </c>
       <c r="C469" t="n">
-        <v>0.826633</v>
+        <v>0.814721</v>
       </c>
     </row>
     <row r="470">
@@ -6524,10 +6524,10 @@
         </is>
       </c>
       <c r="B470" t="n">
-        <v>0.014938</v>
+        <v>0.015566</v>
       </c>
       <c r="C470" t="n">
-        <v>0.824121</v>
+        <v>0.812183</v>
       </c>
     </row>
     <row r="471">
@@ -6537,10 +6537,10 @@
         </is>
       </c>
       <c r="B471" t="n">
-        <v>0.015029</v>
+        <v>0.015682</v>
       </c>
       <c r="C471" t="n">
-        <v>0.821608</v>
+        <v>0.8096449999999999</v>
       </c>
     </row>
     <row r="472">
@@ -6550,10 +6550,10 @@
         </is>
       </c>
       <c r="B472" t="n">
-        <v>0.015124</v>
+        <v>0.016461</v>
       </c>
       <c r="C472" t="n">
-        <v>0.819095</v>
+        <v>0.807107</v>
       </c>
     </row>
     <row r="473">
@@ -6563,10 +6563,10 @@
         </is>
       </c>
       <c r="B473" t="n">
-        <v>0.015189</v>
+        <v>0.016552</v>
       </c>
       <c r="C473" t="n">
-        <v>0.8165829999999999</v>
+        <v>0.804569</v>
       </c>
     </row>
     <row r="474">
@@ -6576,10 +6576,10 @@
         </is>
       </c>
       <c r="B474" t="n">
-        <v>0.01558</v>
+        <v>0.01673</v>
       </c>
       <c r="C474" t="n">
-        <v>0.81407</v>
+        <v>0.80203</v>
       </c>
     </row>
     <row r="475">
@@ -6589,10 +6589,10 @@
         </is>
       </c>
       <c r="B475" t="n">
-        <v>0.015734</v>
+        <v>0.016756</v>
       </c>
       <c r="C475" t="n">
-        <v>0.811558</v>
+        <v>0.799492</v>
       </c>
     </row>
     <row r="476">
@@ -6602,10 +6602,10 @@
         </is>
       </c>
       <c r="B476" t="n">
-        <v>0.016464</v>
+        <v>0.016983</v>
       </c>
       <c r="C476" t="n">
-        <v>0.809045</v>
+        <v>0.7969540000000001</v>
       </c>
     </row>
     <row r="477">
@@ -6615,10 +6615,10 @@
         </is>
       </c>
       <c r="B477" t="n">
-        <v>0.016638</v>
+        <v>0.017248</v>
       </c>
       <c r="C477" t="n">
-        <v>0.8065330000000001</v>
+        <v>0.794416</v>
       </c>
     </row>
     <row r="478">
@@ -6628,10 +6628,10 @@
         </is>
       </c>
       <c r="B478" t="n">
-        <v>0.01669</v>
+        <v>0.017282</v>
       </c>
       <c r="C478" t="n">
-        <v>0.80402</v>
+        <v>0.791878</v>
       </c>
     </row>
     <row r="479">
@@ -6641,10 +6641,10 @@
         </is>
       </c>
       <c r="B479" t="n">
-        <v>0.016794</v>
+        <v>0.017705</v>
       </c>
       <c r="C479" t="n">
-        <v>0.801508</v>
+        <v>0.78934</v>
       </c>
     </row>
     <row r="480">
@@ -6654,10 +6654,10 @@
         </is>
       </c>
       <c r="B480" t="n">
-        <v>0.016995</v>
+        <v>0.017771</v>
       </c>
       <c r="C480" t="n">
-        <v>0.798995</v>
+        <v>0.786802</v>
       </c>
     </row>
     <row r="481">
@@ -6667,10 +6667,10 @@
         </is>
       </c>
       <c r="B481" t="n">
-        <v>0.017078</v>
+        <v>0.017881</v>
       </c>
       <c r="C481" t="n">
-        <v>0.796482</v>
+        <v>0.784264</v>
       </c>
     </row>
     <row r="482">
@@ -6680,10 +6680,10 @@
         </is>
       </c>
       <c r="B482" t="n">
-        <v>0.017368</v>
+        <v>0.018148</v>
       </c>
       <c r="C482" t="n">
-        <v>0.79397</v>
+        <v>0.781726</v>
       </c>
     </row>
     <row r="483">
@@ -6693,10 +6693,10 @@
         </is>
       </c>
       <c r="B483" t="n">
-        <v>0.017679</v>
+        <v>0.018559</v>
       </c>
       <c r="C483" t="n">
-        <v>0.791457</v>
+        <v>0.779188</v>
       </c>
     </row>
     <row r="484">
@@ -6706,10 +6706,10 @@
         </is>
       </c>
       <c r="B484" t="n">
-        <v>0.017736</v>
+        <v>0.018854</v>
       </c>
       <c r="C484" t="n">
-        <v>0.788945</v>
+        <v>0.77665</v>
       </c>
     </row>
     <row r="485">
@@ -6719,10 +6719,10 @@
         </is>
       </c>
       <c r="B485" t="n">
-        <v>0.017995</v>
+        <v>0.019102</v>
       </c>
       <c r="C485" t="n">
-        <v>0.786432</v>
+        <v>0.774112</v>
       </c>
     </row>
     <row r="486">
@@ -6732,10 +6732,10 @@
         </is>
       </c>
       <c r="B486" t="n">
-        <v>0.018009</v>
+        <v>0.019402</v>
       </c>
       <c r="C486" t="n">
-        <v>0.78392</v>
+        <v>0.771574</v>
       </c>
     </row>
     <row r="487">
@@ -6745,10 +6745,10 @@
         </is>
       </c>
       <c r="B487" t="n">
-        <v>0.018682</v>
+        <v>0.019437</v>
       </c>
       <c r="C487" t="n">
-        <v>0.781407</v>
+        <v>0.7690360000000001</v>
       </c>
     </row>
     <row r="488">
@@ -6758,10 +6758,10 @@
         </is>
       </c>
       <c r="B488" t="n">
-        <v>0.018758</v>
+        <v>0.019447</v>
       </c>
       <c r="C488" t="n">
-        <v>0.778894</v>
+        <v>0.766497</v>
       </c>
     </row>
     <row r="489">
@@ -6771,10 +6771,10 @@
         </is>
       </c>
       <c r="B489" t="n">
-        <v>0.018985</v>
+        <v>0.019581</v>
       </c>
       <c r="C489" t="n">
-        <v>0.776382</v>
+        <v>0.7639590000000001</v>
       </c>
     </row>
     <row r="490">
@@ -6784,10 +6784,10 @@
         </is>
       </c>
       <c r="B490" t="n">
-        <v>0.019261</v>
+        <v>0.019685</v>
       </c>
       <c r="C490" t="n">
-        <v>0.773869</v>
+        <v>0.761421</v>
       </c>
     </row>
     <row r="491">
@@ -6797,10 +6797,10 @@
         </is>
       </c>
       <c r="B491" t="n">
-        <v>0.01938</v>
+        <v>0.01971</v>
       </c>
       <c r="C491" t="n">
-        <v>0.771357</v>
+        <v>0.758883</v>
       </c>
     </row>
     <row r="492">
@@ -6810,10 +6810,10 @@
         </is>
       </c>
       <c r="B492" t="n">
-        <v>0.019399</v>
+        <v>0.020222</v>
       </c>
       <c r="C492" t="n">
-        <v>0.768844</v>
+        <v>0.756345</v>
       </c>
     </row>
     <row r="493">
@@ -6823,10 +6823,10 @@
         </is>
       </c>
       <c r="B493" t="n">
-        <v>0.019565</v>
+        <v>0.020361</v>
       </c>
       <c r="C493" t="n">
-        <v>0.766332</v>
+        <v>0.753807</v>
       </c>
     </row>
     <row r="494">
@@ -6836,10 +6836,10 @@
         </is>
       </c>
       <c r="B494" t="n">
-        <v>0.019642</v>
+        <v>0.021002</v>
       </c>
       <c r="C494" t="n">
-        <v>0.763819</v>
+        <v>0.751269</v>
       </c>
     </row>
     <row r="495">
@@ -6849,10 +6849,10 @@
         </is>
       </c>
       <c r="B495" t="n">
-        <v>0.019815</v>
+        <v>0.021064</v>
       </c>
       <c r="C495" t="n">
-        <v>0.761307</v>
+        <v>0.748731</v>
       </c>
     </row>
     <row r="496">
@@ -6862,10 +6862,10 @@
         </is>
       </c>
       <c r="B496" t="n">
-        <v>0.020003</v>
+        <v>0.021474</v>
       </c>
       <c r="C496" t="n">
-        <v>0.758794</v>
+        <v>0.746193</v>
       </c>
     </row>
     <row r="497">
@@ -6875,10 +6875,10 @@
         </is>
       </c>
       <c r="B497" t="n">
-        <v>0.020214</v>
+        <v>0.021496</v>
       </c>
       <c r="C497" t="n">
-        <v>0.756281</v>
+        <v>0.743655</v>
       </c>
     </row>
     <row r="498">
@@ -6888,10 +6888,10 @@
         </is>
       </c>
       <c r="B498" t="n">
-        <v>0.020965</v>
+        <v>0.021845</v>
       </c>
       <c r="C498" t="n">
-        <v>0.753769</v>
+        <v>0.741117</v>
       </c>
     </row>
     <row r="499">
@@ -6901,10 +6901,10 @@
         </is>
       </c>
       <c r="B499" t="n">
-        <v>0.021134</v>
+        <v>0.021976</v>
       </c>
       <c r="C499" t="n">
-        <v>0.751256</v>
+        <v>0.738579</v>
       </c>
     </row>
     <row r="500">
@@ -6914,10 +6914,10 @@
         </is>
       </c>
       <c r="B500" t="n">
-        <v>0.021417</v>
+        <v>0.022788</v>
       </c>
       <c r="C500" t="n">
-        <v>0.748744</v>
+        <v>0.7360409999999999</v>
       </c>
     </row>
     <row r="501">
@@ -6927,10 +6927,10 @@
         </is>
       </c>
       <c r="B501" t="n">
-        <v>0.021699</v>
+        <v>0.023098</v>
       </c>
       <c r="C501" t="n">
-        <v>0.746231</v>
+        <v>0.733503</v>
       </c>
     </row>
     <row r="502">
@@ -6940,10 +6940,10 @@
         </is>
       </c>
       <c r="B502" t="n">
-        <v>0.021923</v>
+        <v>0.023157</v>
       </c>
       <c r="C502" t="n">
-        <v>0.743719</v>
+        <v>0.7309639999999999</v>
       </c>
     </row>
     <row r="503">
@@ -6953,10 +6953,10 @@
         </is>
       </c>
       <c r="B503" t="n">
-        <v>0.022106</v>
+        <v>0.023223</v>
       </c>
       <c r="C503" t="n">
-        <v>0.741206</v>
+        <v>0.728426</v>
       </c>
     </row>
     <row r="504">
@@ -6966,10 +6966,10 @@
         </is>
       </c>
       <c r="B504" t="n">
-        <v>0.022697</v>
+        <v>0.023515</v>
       </c>
       <c r="C504" t="n">
-        <v>0.738693</v>
+        <v>0.725888</v>
       </c>
     </row>
     <row r="505">
@@ -6979,10 +6979,10 @@
         </is>
       </c>
       <c r="B505" t="n">
-        <v>0.022876</v>
+        <v>0.023789</v>
       </c>
       <c r="C505" t="n">
-        <v>0.736181</v>
+        <v>0.72335</v>
       </c>
     </row>
     <row r="506">
@@ -6992,10 +6992,10 @@
         </is>
       </c>
       <c r="B506" t="n">
-        <v>0.022898</v>
+        <v>0.023898</v>
       </c>
       <c r="C506" t="n">
-        <v>0.733668</v>
+        <v>0.720812</v>
       </c>
     </row>
     <row r="507">
@@ -7005,10 +7005,10 @@
         </is>
       </c>
       <c r="B507" t="n">
-        <v>0.023262</v>
+        <v>0.023916</v>
       </c>
       <c r="C507" t="n">
-        <v>0.731156</v>
+        <v>0.718274</v>
       </c>
     </row>
     <row r="508">
@@ -7018,10 +7018,10 @@
         </is>
       </c>
       <c r="B508" t="n">
-        <v>0.023694</v>
+        <v>0.024293</v>
       </c>
       <c r="C508" t="n">
-        <v>0.728643</v>
+        <v>0.715736</v>
       </c>
     </row>
     <row r="509">
@@ -7031,10 +7031,10 @@
         </is>
       </c>
       <c r="B509" t="n">
-        <v>0.023753</v>
+        <v>0.024473</v>
       </c>
       <c r="C509" t="n">
-        <v>0.726131</v>
+        <v>0.713198</v>
       </c>
     </row>
     <row r="510">
@@ -7044,10 +7044,10 @@
         </is>
       </c>
       <c r="B510" t="n">
-        <v>0.023994</v>
+        <v>0.024644</v>
       </c>
       <c r="C510" t="n">
-        <v>0.723618</v>
+        <v>0.71066</v>
       </c>
     </row>
     <row r="511">
@@ -7057,10 +7057,10 @@
         </is>
       </c>
       <c r="B511" t="n">
-        <v>0.02419</v>
+        <v>0.024673</v>
       </c>
       <c r="C511" t="n">
-        <v>0.721106</v>
+        <v>0.708122</v>
       </c>
     </row>
     <row r="512">
@@ -7070,10 +7070,10 @@
         </is>
       </c>
       <c r="B512" t="n">
-        <v>0.024313</v>
+        <v>0.024863</v>
       </c>
       <c r="C512" t="n">
-        <v>0.718593</v>
+        <v>0.705584</v>
       </c>
     </row>
     <row r="513">
@@ -7083,10 +7083,10 @@
         </is>
       </c>
       <c r="B513" t="n">
-        <v>0.024497</v>
+        <v>0.025064</v>
       </c>
       <c r="C513" t="n">
-        <v>0.71608</v>
+        <v>0.7030459999999999</v>
       </c>
     </row>
     <row r="514">
@@ -7096,10 +7096,10 @@
         </is>
       </c>
       <c r="B514" t="n">
-        <v>0.024715</v>
+        <v>0.025332</v>
       </c>
       <c r="C514" t="n">
-        <v>0.713568</v>
+        <v>0.700508</v>
       </c>
     </row>
     <row r="515">
@@ -7109,10 +7109,10 @@
         </is>
       </c>
       <c r="B515" t="n">
-        <v>0.024903</v>
+        <v>0.025862</v>
       </c>
       <c r="C515" t="n">
-        <v>0.711055</v>
+        <v>0.69797</v>
       </c>
     </row>
     <row r="516">
@@ -7122,10 +7122,10 @@
         </is>
       </c>
       <c r="B516" t="n">
-        <v>0.025004</v>
+        <v>0.025941</v>
       </c>
       <c r="C516" t="n">
-        <v>0.708543</v>
+        <v>0.695431</v>
       </c>
     </row>
     <row r="517">
@@ -7135,10 +7135,10 @@
         </is>
       </c>
       <c r="B517" t="n">
-        <v>0.02533</v>
+        <v>0.026052</v>
       </c>
       <c r="C517" t="n">
-        <v>0.70603</v>
+        <v>0.692893</v>
       </c>
     </row>
     <row r="518">
@@ -7148,10 +7148,10 @@
         </is>
       </c>
       <c r="B518" t="n">
-        <v>0.02537</v>
+        <v>0.026138</v>
       </c>
       <c r="C518" t="n">
-        <v>0.703518</v>
+        <v>0.6903550000000001</v>
       </c>
     </row>
     <row r="519">
@@ -7161,10 +7161,10 @@
         </is>
       </c>
       <c r="B519" t="n">
-        <v>0.025782</v>
+        <v>0.02636</v>
       </c>
       <c r="C519" t="n">
-        <v>0.701005</v>
+        <v>0.687817</v>
       </c>
     </row>
     <row r="520">
@@ -7174,10 +7174,10 @@
         </is>
       </c>
       <c r="B520" t="n">
-        <v>0.025843</v>
+        <v>0.026446</v>
       </c>
       <c r="C520" t="n">
-        <v>0.698492</v>
+        <v>0.685279</v>
       </c>
     </row>
     <row r="521">
@@ -7187,10 +7187,10 @@
         </is>
       </c>
       <c r="B521" t="n">
-        <v>0.025966</v>
+        <v>0.026516</v>
       </c>
       <c r="C521" t="n">
-        <v>0.69598</v>
+        <v>0.682741</v>
       </c>
     </row>
     <row r="522">
@@ -7200,10 +7200,10 @@
         </is>
       </c>
       <c r="B522" t="n">
-        <v>0.026021</v>
+        <v>0.026641</v>
       </c>
       <c r="C522" t="n">
-        <v>0.6934669999999999</v>
+        <v>0.680203</v>
       </c>
     </row>
     <row r="523">
@@ -7213,10 +7213,10 @@
         </is>
       </c>
       <c r="B523" t="n">
-        <v>0.026403</v>
+        <v>0.02682</v>
       </c>
       <c r="C523" t="n">
-        <v>0.690955</v>
+        <v>0.677665</v>
       </c>
     </row>
     <row r="524">
@@ -7226,10 +7226,10 @@
         </is>
       </c>
       <c r="B524" t="n">
-        <v>0.026494</v>
+        <v>0.027059</v>
       </c>
       <c r="C524" t="n">
-        <v>0.688442</v>
+        <v>0.675127</v>
       </c>
     </row>
     <row r="525">
@@ -7239,10 +7239,10 @@
         </is>
       </c>
       <c r="B525" t="n">
-        <v>0.026603</v>
+        <v>0.02864</v>
       </c>
       <c r="C525" t="n">
-        <v>0.68593</v>
+        <v>0.672589</v>
       </c>
     </row>
     <row r="526">
@@ -7252,10 +7252,10 @@
         </is>
       </c>
       <c r="B526" t="n">
-        <v>0.026757</v>
+        <v>0.028712</v>
       </c>
       <c r="C526" t="n">
-        <v>0.6834170000000001</v>
+        <v>0.670051</v>
       </c>
     </row>
     <row r="527">
@@ -7265,10 +7265,10 @@
         </is>
       </c>
       <c r="B527" t="n">
-        <v>0.026814</v>
+        <v>0.028964</v>
       </c>
       <c r="C527" t="n">
-        <v>0.680905</v>
+        <v>0.667513</v>
       </c>
     </row>
     <row r="528">
@@ -7278,10 +7278,10 @@
         </is>
       </c>
       <c r="B528" t="n">
-        <v>0.026994</v>
+        <v>0.029085</v>
       </c>
       <c r="C528" t="n">
-        <v>0.678392</v>
+        <v>0.664975</v>
       </c>
     </row>
     <row r="529">
@@ -7291,10 +7291,10 @@
         </is>
       </c>
       <c r="B529" t="n">
-        <v>0.028554</v>
+        <v>0.029103</v>
       </c>
       <c r="C529" t="n">
-        <v>0.675879</v>
+        <v>0.6624370000000001</v>
       </c>
     </row>
     <row r="530">
@@ -7304,10 +7304,10 @@
         </is>
       </c>
       <c r="B530" t="n">
-        <v>0.028582</v>
+        <v>0.029154</v>
       </c>
       <c r="C530" t="n">
-        <v>0.673367</v>
+        <v>0.659898</v>
       </c>
     </row>
     <row r="531">
@@ -7317,10 +7317,10 @@
         </is>
       </c>
       <c r="B531" t="n">
-        <v>0.028711</v>
+        <v>0.029248</v>
       </c>
       <c r="C531" t="n">
-        <v>0.670854</v>
+        <v>0.6573600000000001</v>
       </c>
     </row>
     <row r="532">
@@ -7330,10 +7330,10 @@
         </is>
       </c>
       <c r="B532" t="n">
-        <v>0.029053</v>
+        <v>0.029646</v>
       </c>
       <c r="C532" t="n">
-        <v>0.668342</v>
+        <v>0.654822</v>
       </c>
     </row>
     <row r="533">
@@ -7343,10 +7343,10 @@
         </is>
       </c>
       <c r="B533" t="n">
-        <v>0.029112</v>
+        <v>0.029904</v>
       </c>
       <c r="C533" t="n">
-        <v>0.665829</v>
+        <v>0.652284</v>
       </c>
     </row>
     <row r="534">
@@ -7356,10 +7356,10 @@
         </is>
       </c>
       <c r="B534" t="n">
-        <v>0.029242</v>
+        <v>0.029975</v>
       </c>
       <c r="C534" t="n">
-        <v>0.663317</v>
+        <v>0.649746</v>
       </c>
     </row>
     <row r="535">
@@ -7369,10 +7369,10 @@
         </is>
       </c>
       <c r="B535" t="n">
-        <v>0.029244</v>
+        <v>0.030369</v>
       </c>
       <c r="C535" t="n">
-        <v>0.6608039999999999</v>
+        <v>0.647208</v>
       </c>
     </row>
     <row r="536">
@@ -7382,10 +7382,10 @@
         </is>
       </c>
       <c r="B536" t="n">
-        <v>0.029691</v>
+        <v>0.030567</v>
       </c>
       <c r="C536" t="n">
-        <v>0.658291</v>
+        <v>0.64467</v>
       </c>
     </row>
     <row r="537">
@@ -7395,10 +7395,10 @@
         </is>
       </c>
       <c r="B537" t="n">
-        <v>0.029713</v>
+        <v>0.030755</v>
       </c>
       <c r="C537" t="n">
-        <v>0.655779</v>
+        <v>0.642132</v>
       </c>
     </row>
     <row r="538">
@@ -7408,10 +7408,10 @@
         </is>
       </c>
       <c r="B538" t="n">
-        <v>0.030097</v>
+        <v>0.031062</v>
       </c>
       <c r="C538" t="n">
-        <v>0.653266</v>
+        <v>0.639594</v>
       </c>
     </row>
     <row r="539">
@@ -7421,10 +7421,10 @@
         </is>
       </c>
       <c r="B539" t="n">
-        <v>0.030287</v>
+        <v>0.031152</v>
       </c>
       <c r="C539" t="n">
-        <v>0.6507540000000001</v>
+        <v>0.637056</v>
       </c>
     </row>
     <row r="540">
@@ -7434,10 +7434,10 @@
         </is>
       </c>
       <c r="B540" t="n">
-        <v>0.030464</v>
+        <v>0.0313</v>
       </c>
       <c r="C540" t="n">
-        <v>0.648241</v>
+        <v>0.634518</v>
       </c>
     </row>
     <row r="541">
@@ -7447,10 +7447,10 @@
         </is>
       </c>
       <c r="B541" t="n">
-        <v>0.030569</v>
+        <v>0.031647</v>
       </c>
       <c r="C541" t="n">
-        <v>0.645729</v>
+        <v>0.63198</v>
       </c>
     </row>
     <row r="542">
@@ -7460,10 +7460,10 @@
         </is>
       </c>
       <c r="B542" t="n">
-        <v>0.031105</v>
+        <v>0.03198</v>
       </c>
       <c r="C542" t="n">
-        <v>0.643216</v>
+        <v>0.6294419999999999</v>
       </c>
     </row>
     <row r="543">
@@ -7473,10 +7473,10 @@
         </is>
       </c>
       <c r="B543" t="n">
-        <v>0.031559</v>
+        <v>0.032136</v>
       </c>
       <c r="C543" t="n">
-        <v>0.6407040000000001</v>
+        <v>0.626904</v>
       </c>
     </row>
     <row r="544">
@@ -7486,10 +7486,10 @@
         </is>
       </c>
       <c r="B544" t="n">
-        <v>0.031585</v>
+        <v>0.032478</v>
       </c>
       <c r="C544" t="n">
-        <v>0.638191</v>
+        <v>0.6243649999999999</v>
       </c>
     </row>
     <row r="545">
@@ -7499,10 +7499,10 @@
         </is>
       </c>
       <c r="B545" t="n">
-        <v>0.031701</v>
+        <v>0.032531</v>
       </c>
       <c r="C545" t="n">
-        <v>0.635678</v>
+        <v>0.621827</v>
       </c>
     </row>
     <row r="546">
@@ -7512,10 +7512,10 @@
         </is>
       </c>
       <c r="B546" t="n">
-        <v>0.031714</v>
+        <v>0.032606</v>
       </c>
       <c r="C546" t="n">
-        <v>0.633166</v>
+        <v>0.619289</v>
       </c>
     </row>
     <row r="547">
@@ -7525,10 +7525,10 @@
         </is>
       </c>
       <c r="B547" t="n">
-        <v>0.031917</v>
+        <v>0.033063</v>
       </c>
       <c r="C547" t="n">
-        <v>0.630653</v>
+        <v>0.616751</v>
       </c>
     </row>
     <row r="548">
@@ -7538,10 +7538,10 @@
         </is>
       </c>
       <c r="B548" t="n">
-        <v>0.0322</v>
+        <v>0.033255</v>
       </c>
       <c r="C548" t="n">
-        <v>0.6281409999999999</v>
+        <v>0.614213</v>
       </c>
     </row>
     <row r="549">
@@ -7551,10 +7551,10 @@
         </is>
       </c>
       <c r="B549" t="n">
-        <v>0.032516</v>
+        <v>0.033259</v>
       </c>
       <c r="C549" t="n">
-        <v>0.625628</v>
+        <v>0.611675</v>
       </c>
     </row>
     <row r="550">
@@ -7564,10 +7564,10 @@
         </is>
       </c>
       <c r="B550" t="n">
-        <v>0.032692</v>
+        <v>0.033562</v>
       </c>
       <c r="C550" t="n">
-        <v>0.623116</v>
+        <v>0.609137</v>
       </c>
     </row>
     <row r="551">
@@ -7577,10 +7577,10 @@
         </is>
       </c>
       <c r="B551" t="n">
-        <v>0.032708</v>
+        <v>0.033796</v>
       </c>
       <c r="C551" t="n">
-        <v>0.620603</v>
+        <v>0.606599</v>
       </c>
     </row>
     <row r="552">
@@ -7590,10 +7590,10 @@
         </is>
       </c>
       <c r="B552" t="n">
-        <v>0.032917</v>
+        <v>0.03383</v>
       </c>
       <c r="C552" t="n">
-        <v>0.61809</v>
+        <v>0.604061</v>
       </c>
     </row>
     <row r="553">
@@ -7603,10 +7603,10 @@
         </is>
       </c>
       <c r="B553" t="n">
-        <v>0.033093</v>
+        <v>0.033869</v>
       </c>
       <c r="C553" t="n">
-        <v>0.615578</v>
+        <v>0.601523</v>
       </c>
     </row>
     <row r="554">
@@ -7616,10 +7616,10 @@
         </is>
       </c>
       <c r="B554" t="n">
-        <v>0.033345</v>
+        <v>0.03389</v>
       </c>
       <c r="C554" t="n">
-        <v>0.613065</v>
+        <v>0.598985</v>
       </c>
     </row>
     <row r="555">
@@ -7629,10 +7629,10 @@
         </is>
       </c>
       <c r="B555" t="n">
-        <v>0.033533</v>
+        <v>0.034048</v>
       </c>
       <c r="C555" t="n">
-        <v>0.610553</v>
+        <v>0.5964469999999999</v>
       </c>
     </row>
     <row r="556">
@@ -7642,10 +7642,10 @@
         </is>
       </c>
       <c r="B556" t="n">
-        <v>0.03356</v>
+        <v>0.034462</v>
       </c>
       <c r="C556" t="n">
-        <v>0.60804</v>
+        <v>0.593909</v>
       </c>
     </row>
     <row r="557">
@@ -7655,10 +7655,10 @@
         </is>
       </c>
       <c r="B557" t="n">
-        <v>0.033775</v>
+        <v>0.035106</v>
       </c>
       <c r="C557" t="n">
-        <v>0.605528</v>
+        <v>0.591371</v>
       </c>
     </row>
     <row r="558">
@@ -7668,10 +7668,10 @@
         </is>
       </c>
       <c r="B558" t="n">
-        <v>0.033901</v>
+        <v>0.035169</v>
       </c>
       <c r="C558" t="n">
-        <v>0.603015</v>
+        <v>0.588832</v>
       </c>
     </row>
     <row r="559">
@@ -7681,10 +7681,10 @@
         </is>
       </c>
       <c r="B559" t="n">
-        <v>0.034063</v>
+        <v>0.035599</v>
       </c>
       <c r="C559" t="n">
-        <v>0.600503</v>
+        <v>0.586294</v>
       </c>
     </row>
     <row r="560">
@@ -7694,10 +7694,10 @@
         </is>
       </c>
       <c r="B560" t="n">
-        <v>0.034171</v>
+        <v>0.035861</v>
       </c>
       <c r="C560" t="n">
-        <v>0.59799</v>
+        <v>0.5837560000000001</v>
       </c>
     </row>
     <row r="561">
@@ -7707,10 +7707,10 @@
         </is>
       </c>
       <c r="B561" t="n">
-        <v>0.034255</v>
+        <v>0.036</v>
       </c>
       <c r="C561" t="n">
-        <v>0.595477</v>
+        <v>0.581218</v>
       </c>
     </row>
     <row r="562">
@@ -7720,10 +7720,10 @@
         </is>
       </c>
       <c r="B562" t="n">
-        <v>0.035095</v>
+        <v>0.036095</v>
       </c>
       <c r="C562" t="n">
-        <v>0.592965</v>
+        <v>0.57868</v>
       </c>
     </row>
     <row r="563">
@@ -7733,10 +7733,10 @@
         </is>
       </c>
       <c r="B563" t="n">
-        <v>0.035281</v>
+        <v>0.036176</v>
       </c>
       <c r="C563" t="n">
-        <v>0.590452</v>
+        <v>0.576142</v>
       </c>
     </row>
     <row r="564">
@@ -7746,10 +7746,10 @@
         </is>
       </c>
       <c r="B564" t="n">
-        <v>0.035453</v>
+        <v>0.036472</v>
       </c>
       <c r="C564" t="n">
-        <v>0.58794</v>
+        <v>0.573604</v>
       </c>
     </row>
     <row r="565">
@@ -7759,10 +7759,10 @@
         </is>
       </c>
       <c r="B565" t="n">
-        <v>0.035531</v>
+        <v>0.036644</v>
       </c>
       <c r="C565" t="n">
-        <v>0.585427</v>
+        <v>0.571066</v>
       </c>
     </row>
     <row r="566">
@@ -7772,10 +7772,10 @@
         </is>
       </c>
       <c r="B566" t="n">
-        <v>0.035829</v>
+        <v>0.037008</v>
       </c>
       <c r="C566" t="n">
-        <v>0.582915</v>
+        <v>0.568528</v>
       </c>
     </row>
     <row r="567">
@@ -7785,10 +7785,10 @@
         </is>
       </c>
       <c r="B567" t="n">
-        <v>0.035988</v>
+        <v>0.037136</v>
       </c>
       <c r="C567" t="n">
-        <v>0.580402</v>
+        <v>0.56599</v>
       </c>
     </row>
     <row r="568">
@@ -7798,10 +7798,10 @@
         </is>
       </c>
       <c r="B568" t="n">
-        <v>0.036</v>
+        <v>0.037214</v>
       </c>
       <c r="C568" t="n">
-        <v>0.577889</v>
+        <v>0.563452</v>
       </c>
     </row>
     <row r="569">
@@ -7811,10 +7811,10 @@
         </is>
       </c>
       <c r="B569" t="n">
-        <v>0.036084</v>
+        <v>0.037324</v>
       </c>
       <c r="C569" t="n">
-        <v>0.575377</v>
+        <v>0.560914</v>
       </c>
     </row>
     <row r="570">
@@ -7824,10 +7824,10 @@
         </is>
       </c>
       <c r="B570" t="n">
-        <v>0.036727</v>
+        <v>0.038142</v>
       </c>
       <c r="C570" t="n">
-        <v>0.572864</v>
+        <v>0.558376</v>
       </c>
     </row>
     <row r="571">
@@ -7837,10 +7837,10 @@
         </is>
       </c>
       <c r="B571" t="n">
-        <v>0.036773</v>
+        <v>0.038675</v>
       </c>
       <c r="C571" t="n">
-        <v>0.570352</v>
+        <v>0.5558380000000001</v>
       </c>
     </row>
     <row r="572">
@@ -7850,10 +7850,10 @@
         </is>
       </c>
       <c r="B572" t="n">
-        <v>0.036785</v>
+        <v>0.038724</v>
       </c>
       <c r="C572" t="n">
-        <v>0.567839</v>
+        <v>0.553299</v>
       </c>
     </row>
     <row r="573">
@@ -7863,10 +7863,10 @@
         </is>
       </c>
       <c r="B573" t="n">
-        <v>0.037413</v>
+        <v>0.038919</v>
       </c>
       <c r="C573" t="n">
-        <v>0.565327</v>
+        <v>0.5507609999999999</v>
       </c>
     </row>
     <row r="574">
@@ -7876,10 +7876,10 @@
         </is>
       </c>
       <c r="B574" t="n">
-        <v>0.037832</v>
+        <v>0.039522</v>
       </c>
       <c r="C574" t="n">
-        <v>0.562814</v>
+        <v>0.548223</v>
       </c>
     </row>
     <row r="575">
@@ -7889,10 +7889,10 @@
         </is>
       </c>
       <c r="B575" t="n">
-        <v>0.038276</v>
+        <v>0.039789</v>
       </c>
       <c r="C575" t="n">
-        <v>0.560302</v>
+        <v>0.545685</v>
       </c>
     </row>
     <row r="576">
@@ -7902,10 +7902,10 @@
         </is>
       </c>
       <c r="B576" t="n">
-        <v>0.038565</v>
+        <v>0.039789</v>
       </c>
       <c r="C576" t="n">
-        <v>0.557789</v>
+        <v>0.543147</v>
       </c>
     </row>
     <row r="577">
@@ -7915,10 +7915,10 @@
         </is>
       </c>
       <c r="B577" t="n">
-        <v>0.038651</v>
+        <v>0.040018</v>
       </c>
       <c r="C577" t="n">
-        <v>0.555276</v>
+        <v>0.540609</v>
       </c>
     </row>
     <row r="578">
@@ -7928,10 +7928,10 @@
         </is>
       </c>
       <c r="B578" t="n">
-        <v>0.039375</v>
+        <v>0.040044</v>
       </c>
       <c r="C578" t="n">
-        <v>0.552764</v>
+        <v>0.538071</v>
       </c>
     </row>
     <row r="579">
@@ -7941,10 +7941,10 @@
         </is>
       </c>
       <c r="B579" t="n">
-        <v>0.039592</v>
+        <v>0.040321</v>
       </c>
       <c r="C579" t="n">
-        <v>0.550251</v>
+        <v>0.535533</v>
       </c>
     </row>
     <row r="580">
@@ -7954,10 +7954,10 @@
         </is>
       </c>
       <c r="B580" t="n">
-        <v>0.03971</v>
+        <v>0.040743</v>
       </c>
       <c r="C580" t="n">
-        <v>0.547739</v>
+        <v>0.532995</v>
       </c>
     </row>
     <row r="581">
@@ -7967,10 +7967,10 @@
         </is>
       </c>
       <c r="B581" t="n">
-        <v>0.039788</v>
+        <v>0.040934</v>
       </c>
       <c r="C581" t="n">
-        <v>0.545226</v>
+        <v>0.530457</v>
       </c>
     </row>
     <row r="582">
@@ -7980,10 +7980,10 @@
         </is>
       </c>
       <c r="B582" t="n">
-        <v>0.040053</v>
+        <v>0.041123</v>
       </c>
       <c r="C582" t="n">
-        <v>0.542714</v>
+        <v>0.527919</v>
       </c>
     </row>
     <row r="583">
@@ -7993,10 +7993,10 @@
         </is>
       </c>
       <c r="B583" t="n">
-        <v>0.040061</v>
+        <v>0.041185</v>
       </c>
       <c r="C583" t="n">
-        <v>0.540201</v>
+        <v>0.525381</v>
       </c>
     </row>
     <row r="584">
@@ -8006,10 +8006,10 @@
         </is>
       </c>
       <c r="B584" t="n">
-        <v>0.040097</v>
+        <v>0.04125</v>
       </c>
       <c r="C584" t="n">
-        <v>0.5376880000000001</v>
+        <v>0.5228429999999999</v>
       </c>
     </row>
     <row r="585">
@@ -8019,10 +8019,10 @@
         </is>
       </c>
       <c r="B585" t="n">
-        <v>0.04092</v>
+        <v>0.042813</v>
       </c>
       <c r="C585" t="n">
-        <v>0.535176</v>
+        <v>0.520305</v>
       </c>
     </row>
     <row r="586">
@@ -8032,10 +8032,10 @@
         </is>
       </c>
       <c r="B586" t="n">
-        <v>0.040933</v>
+        <v>0.042952</v>
       </c>
       <c r="C586" t="n">
-        <v>0.532663</v>
+        <v>0.5177659999999999</v>
       </c>
     </row>
     <row r="587">
@@ -8045,10 +8045,10 @@
         </is>
       </c>
       <c r="B587" t="n">
-        <v>0.040959</v>
+        <v>0.043174</v>
       </c>
       <c r="C587" t="n">
-        <v>0.530151</v>
+        <v>0.515228</v>
       </c>
     </row>
     <row r="588">
@@ -8058,10 +8058,10 @@
         </is>
       </c>
       <c r="B588" t="n">
-        <v>0.041013</v>
+        <v>0.043264</v>
       </c>
       <c r="C588" t="n">
-        <v>0.5276380000000001</v>
+        <v>0.51269</v>
       </c>
     </row>
     <row r="589">
@@ -8071,10 +8071,10 @@
         </is>
       </c>
       <c r="B589" t="n">
-        <v>0.04103</v>
+        <v>0.043613</v>
       </c>
       <c r="C589" t="n">
-        <v>0.525126</v>
+        <v>0.510152</v>
       </c>
     </row>
     <row r="590">
@@ -8084,10 +8084,10 @@
         </is>
       </c>
       <c r="B590" t="n">
-        <v>0.0426</v>
+        <v>0.043699</v>
       </c>
       <c r="C590" t="n">
-        <v>0.522613</v>
+        <v>0.507614</v>
       </c>
     </row>
     <row r="591">
@@ -8097,10 +8097,10 @@
         </is>
       </c>
       <c r="B591" t="n">
-        <v>0.042868</v>
+        <v>0.043885</v>
       </c>
       <c r="C591" t="n">
-        <v>0.520101</v>
+        <v>0.505076</v>
       </c>
     </row>
     <row r="592">
@@ -8110,10 +8110,10 @@
         </is>
       </c>
       <c r="B592" t="n">
-        <v>0.043143</v>
+        <v>0.044298</v>
       </c>
       <c r="C592" t="n">
-        <v>0.517588</v>
+        <v>0.502538</v>
       </c>
     </row>
     <row r="593">
@@ -8123,10 +8123,10 @@
         </is>
       </c>
       <c r="B593" t="n">
-        <v>0.043556</v>
+        <v>0.044318</v>
       </c>
       <c r="C593" t="n">
-        <v>0.5150749999999999</v>
+        <v>0.5</v>
       </c>
     </row>
     <row r="594">
@@ -8136,10 +8136,10 @@
         </is>
       </c>
       <c r="B594" t="n">
-        <v>0.043705</v>
+        <v>0.044629</v>
       </c>
       <c r="C594" t="n">
-        <v>0.512563</v>
+        <v>0.497462</v>
       </c>
     </row>
     <row r="595">
@@ -8149,10 +8149,10 @@
         </is>
       </c>
       <c r="B595" t="n">
-        <v>0.043811</v>
+        <v>0.044724</v>
       </c>
       <c r="C595" t="n">
-        <v>0.51005</v>
+        <v>0.494924</v>
       </c>
     </row>
     <row r="596">
@@ -8162,10 +8162,10 @@
         </is>
       </c>
       <c r="B596" t="n">
-        <v>0.043938</v>
+        <v>0.044916</v>
       </c>
       <c r="C596" t="n">
-        <v>0.507538</v>
+        <v>0.492386</v>
       </c>
     </row>
     <row r="597">
@@ -8175,10 +8175,10 @@
         </is>
       </c>
       <c r="B597" t="n">
-        <v>0.044127</v>
+        <v>0.044917</v>
       </c>
       <c r="C597" t="n">
-        <v>0.5050249999999999</v>
+        <v>0.489848</v>
       </c>
     </row>
     <row r="598">
@@ -8188,10 +8188,10 @@
         </is>
       </c>
       <c r="B598" t="n">
-        <v>0.04456</v>
+        <v>0.045073</v>
       </c>
       <c r="C598" t="n">
-        <v>0.502513</v>
+        <v>0.48731</v>
       </c>
     </row>
     <row r="599">
@@ -8201,10 +8201,10 @@
         </is>
       </c>
       <c r="B599" t="n">
-        <v>0.044657</v>
+        <v>0.045296</v>
       </c>
       <c r="C599" t="n">
-        <v>0.5</v>
+        <v>0.484772</v>
       </c>
     </row>
     <row r="600">
@@ -8214,10 +8214,10 @@
         </is>
       </c>
       <c r="B600" t="n">
-        <v>0.044694</v>
+        <v>0.045467</v>
       </c>
       <c r="C600" t="n">
-        <v>0.497487</v>
+        <v>0.482234</v>
       </c>
     </row>
     <row r="601">
@@ -8227,10 +8227,10 @@
         </is>
       </c>
       <c r="B601" t="n">
-        <v>0.044957</v>
+        <v>0.045516</v>
       </c>
       <c r="C601" t="n">
-        <v>0.494975</v>
+        <v>0.479695</v>
       </c>
     </row>
     <row r="602">
@@ -8240,10 +8240,10 @@
         </is>
       </c>
       <c r="B602" t="n">
-        <v>0.044958</v>
+        <v>0.045657</v>
       </c>
       <c r="C602" t="n">
-        <v>0.492462</v>
+        <v>0.477157</v>
       </c>
     </row>
     <row r="603">
@@ -8253,10 +8253,10 @@
         </is>
       </c>
       <c r="B603" t="n">
-        <v>0.045093</v>
+        <v>0.045787</v>
       </c>
       <c r="C603" t="n">
-        <v>0.48995</v>
+        <v>0.474619</v>
       </c>
     </row>
     <row r="604">
@@ -8266,10 +8266,10 @@
         </is>
       </c>
       <c r="B604" t="n">
-        <v>0.045212</v>
+        <v>0.045865</v>
       </c>
       <c r="C604" t="n">
-        <v>0.487437</v>
+        <v>0.472081</v>
       </c>
     </row>
     <row r="605">
@@ -8279,10 +8279,10 @@
         </is>
       </c>
       <c r="B605" t="n">
-        <v>0.045367</v>
+        <v>0.046332</v>
       </c>
       <c r="C605" t="n">
-        <v>0.484925</v>
+        <v>0.469543</v>
       </c>
     </row>
     <row r="606">
@@ -8292,10 +8292,10 @@
         </is>
       </c>
       <c r="B606" t="n">
-        <v>0.045411</v>
+        <v>0.046879</v>
       </c>
       <c r="C606" t="n">
-        <v>0.482412</v>
+        <v>0.467005</v>
       </c>
     </row>
     <row r="607">
@@ -8305,10 +8305,10 @@
         </is>
       </c>
       <c r="B607" t="n">
-        <v>0.045575</v>
+        <v>0.047047</v>
       </c>
       <c r="C607" t="n">
-        <v>0.479899</v>
+        <v>0.464467</v>
       </c>
     </row>
     <row r="608">
@@ -8318,10 +8318,10 @@
         </is>
       </c>
       <c r="B608" t="n">
-        <v>0.046192</v>
+        <v>0.047301</v>
       </c>
       <c r="C608" t="n">
-        <v>0.477387</v>
+        <v>0.461929</v>
       </c>
     </row>
     <row r="609">
@@ -8331,10 +8331,10 @@
         </is>
       </c>
       <c r="B609" t="n">
-        <v>0.046234</v>
+        <v>0.047434</v>
       </c>
       <c r="C609" t="n">
-        <v>0.474874</v>
+        <v>0.459391</v>
       </c>
     </row>
     <row r="610">
@@ -8344,10 +8344,10 @@
         </is>
       </c>
       <c r="B610" t="n">
-        <v>0.046507</v>
+        <v>0.04767</v>
       </c>
       <c r="C610" t="n">
-        <v>0.472362</v>
+        <v>0.456853</v>
       </c>
     </row>
     <row r="611">
@@ -8357,10 +8357,10 @@
         </is>
       </c>
       <c r="B611" t="n">
-        <v>0.046923</v>
+        <v>0.047805</v>
       </c>
       <c r="C611" t="n">
-        <v>0.469849</v>
+        <v>0.454315</v>
       </c>
     </row>
     <row r="612">
@@ -8370,10 +8370,10 @@
         </is>
       </c>
       <c r="B612" t="n">
-        <v>0.047048</v>
+        <v>0.04876</v>
       </c>
       <c r="C612" t="n">
-        <v>0.467337</v>
+        <v>0.451777</v>
       </c>
     </row>
     <row r="613">
@@ -8383,10 +8383,10 @@
         </is>
       </c>
       <c r="B613" t="n">
-        <v>0.047573</v>
+        <v>0.049165</v>
       </c>
       <c r="C613" t="n">
-        <v>0.464824</v>
+        <v>0.449239</v>
       </c>
     </row>
     <row r="614">
@@ -8396,10 +8396,10 @@
         </is>
       </c>
       <c r="B614" t="n">
-        <v>0.047576</v>
+        <v>0.049207</v>
       </c>
       <c r="C614" t="n">
-        <v>0.462312</v>
+        <v>0.446701</v>
       </c>
     </row>
     <row r="615">
@@ -8409,10 +8409,10 @@
         </is>
       </c>
       <c r="B615" t="n">
-        <v>0.047684</v>
+        <v>0.049972</v>
       </c>
       <c r="C615" t="n">
-        <v>0.459799</v>
+        <v>0.444162</v>
       </c>
     </row>
     <row r="616">
@@ -8422,10 +8422,10 @@
         </is>
       </c>
       <c r="B616" t="n">
-        <v>0.048673</v>
+        <v>0.050003</v>
       </c>
       <c r="C616" t="n">
-        <v>0.457286</v>
+        <v>0.441624</v>
       </c>
     </row>
     <row r="617">
@@ -8435,10 +8435,10 @@
         </is>
       </c>
       <c r="B617" t="n">
-        <v>0.049257</v>
+        <v>0.050263</v>
       </c>
       <c r="C617" t="n">
-        <v>0.454774</v>
+        <v>0.439086</v>
       </c>
     </row>
     <row r="618">
@@ -8448,10 +8448,10 @@
         </is>
       </c>
       <c r="B618" t="n">
-        <v>0.050167</v>
+        <v>0.050604</v>
       </c>
       <c r="C618" t="n">
-        <v>0.452261</v>
+        <v>0.436548</v>
       </c>
     </row>
     <row r="619">
@@ -8461,10 +8461,10 @@
         </is>
       </c>
       <c r="B619" t="n">
-        <v>0.050663</v>
+        <v>0.050917</v>
       </c>
       <c r="C619" t="n">
-        <v>0.449749</v>
+        <v>0.43401</v>
       </c>
     </row>
     <row r="620">
@@ -8474,10 +8474,10 @@
         </is>
       </c>
       <c r="B620" t="n">
-        <v>0.050737</v>
+        <v>0.051233</v>
       </c>
       <c r="C620" t="n">
-        <v>0.447236</v>
+        <v>0.431472</v>
       </c>
     </row>
     <row r="621">
@@ -8487,10 +8487,10 @@
         </is>
       </c>
       <c r="B621" t="n">
-        <v>0.050857</v>
+        <v>0.051402</v>
       </c>
       <c r="C621" t="n">
-        <v>0.444724</v>
+        <v>0.428934</v>
       </c>
     </row>
     <row r="622">
@@ -8500,10 +8500,10 @@
         </is>
       </c>
       <c r="B622" t="n">
-        <v>0.050903</v>
+        <v>0.052692</v>
       </c>
       <c r="C622" t="n">
-        <v>0.442211</v>
+        <v>0.426396</v>
       </c>
     </row>
     <row r="623">
@@ -8513,10 +8513,10 @@
         </is>
       </c>
       <c r="B623" t="n">
-        <v>0.050903</v>
+        <v>0.052796</v>
       </c>
       <c r="C623" t="n">
-        <v>0.439698</v>
+        <v>0.423858</v>
       </c>
     </row>
     <row r="624">
@@ -8526,10 +8526,10 @@
         </is>
       </c>
       <c r="B624" t="n">
-        <v>0.052036</v>
+        <v>0.052958</v>
       </c>
       <c r="C624" t="n">
-        <v>0.437186</v>
+        <v>0.42132</v>
       </c>
     </row>
     <row r="625">
@@ -8539,10 +8539,10 @@
         </is>
       </c>
       <c r="B625" t="n">
-        <v>0.052567</v>
+        <v>0.053098</v>
       </c>
       <c r="C625" t="n">
-        <v>0.434673</v>
+        <v>0.418782</v>
       </c>
     </row>
     <row r="626">
@@ -8552,10 +8552,10 @@
         </is>
       </c>
       <c r="B626" t="n">
-        <v>0.052978</v>
+        <v>0.05317</v>
       </c>
       <c r="C626" t="n">
-        <v>0.432161</v>
+        <v>0.416244</v>
       </c>
     </row>
     <row r="627">
@@ -8565,10 +8565,10 @@
         </is>
       </c>
       <c r="B627" t="n">
-        <v>0.053063</v>
+        <v>0.053901</v>
       </c>
       <c r="C627" t="n">
-        <v>0.429648</v>
+        <v>0.413706</v>
       </c>
     </row>
     <row r="628">
@@ -8578,10 +8578,10 @@
         </is>
       </c>
       <c r="B628" t="n">
-        <v>0.053223</v>
+        <v>0.054036</v>
       </c>
       <c r="C628" t="n">
-        <v>0.427136</v>
+        <v>0.411168</v>
       </c>
     </row>
     <row r="629">
@@ -8591,10 +8591,10 @@
         </is>
       </c>
       <c r="B629" t="n">
-        <v>0.053777</v>
+        <v>0.054064</v>
       </c>
       <c r="C629" t="n">
-        <v>0.424623</v>
+        <v>0.408629</v>
       </c>
     </row>
     <row r="630">
@@ -8604,10 +8604,10 @@
         </is>
       </c>
       <c r="B630" t="n">
-        <v>0.053888</v>
+        <v>0.054416</v>
       </c>
       <c r="C630" t="n">
-        <v>0.422111</v>
+        <v>0.406091</v>
       </c>
     </row>
     <row r="631">
@@ -8617,10 +8617,10 @@
         </is>
       </c>
       <c r="B631" t="n">
-        <v>0.054272</v>
+        <v>0.054452</v>
       </c>
       <c r="C631" t="n">
-        <v>0.419598</v>
+        <v>0.403553</v>
       </c>
     </row>
     <row r="632">
@@ -8630,10 +8630,10 @@
         </is>
       </c>
       <c r="B632" t="n">
-        <v>0.054348</v>
+        <v>0.054614</v>
       </c>
       <c r="C632" t="n">
-        <v>0.417085</v>
+        <v>0.401015</v>
       </c>
     </row>
     <row r="633">
@@ -8643,10 +8643,10 @@
         </is>
       </c>
       <c r="B633" t="n">
-        <v>0.054405</v>
+        <v>0.054727</v>
       </c>
       <c r="C633" t="n">
-        <v>0.414573</v>
+        <v>0.398477</v>
       </c>
     </row>
     <row r="634">
@@ -8656,10 +8656,10 @@
         </is>
       </c>
       <c r="B634" t="n">
-        <v>0.054564</v>
+        <v>0.054759</v>
       </c>
       <c r="C634" t="n">
-        <v>0.41206</v>
+        <v>0.395939</v>
       </c>
     </row>
     <row r="635">
@@ -8669,10 +8669,10 @@
         </is>
       </c>
       <c r="B635" t="n">
-        <v>0.054603</v>
+        <v>0.05482</v>
       </c>
       <c r="C635" t="n">
-        <v>0.409548</v>
+        <v>0.393401</v>
       </c>
     </row>
     <row r="636">
@@ -8682,10 +8682,10 @@
         </is>
       </c>
       <c r="B636" t="n">
-        <v>0.054654</v>
+        <v>0.055456</v>
       </c>
       <c r="C636" t="n">
-        <v>0.407035</v>
+        <v>0.390863</v>
       </c>
     </row>
     <row r="637">
@@ -8695,10 +8695,10 @@
         </is>
       </c>
       <c r="B637" t="n">
-        <v>0.054779</v>
+        <v>0.055688</v>
       </c>
       <c r="C637" t="n">
-        <v>0.404523</v>
+        <v>0.388325</v>
       </c>
     </row>
     <row r="638">
@@ -8708,10 +8708,10 @@
         </is>
       </c>
       <c r="B638" t="n">
-        <v>0.054789</v>
+        <v>0.055737</v>
       </c>
       <c r="C638" t="n">
-        <v>0.40201</v>
+        <v>0.385787</v>
       </c>
     </row>
     <row r="639">
@@ -8721,10 +8721,10 @@
         </is>
       </c>
       <c r="B639" t="n">
-        <v>0.055135</v>
+        <v>0.056254</v>
       </c>
       <c r="C639" t="n">
-        <v>0.399497</v>
+        <v>0.383249</v>
       </c>
     </row>
     <row r="640">
@@ -8734,10 +8734,10 @@
         </is>
       </c>
       <c r="B640" t="n">
-        <v>0.055428</v>
+        <v>0.056486</v>
       </c>
       <c r="C640" t="n">
-        <v>0.396985</v>
+        <v>0.380711</v>
       </c>
     </row>
     <row r="641">
@@ -8747,10 +8747,10 @@
         </is>
       </c>
       <c r="B641" t="n">
-        <v>0.056147</v>
+        <v>0.057153</v>
       </c>
       <c r="C641" t="n">
-        <v>0.394472</v>
+        <v>0.378173</v>
       </c>
     </row>
     <row r="642">
@@ -8760,10 +8760,10 @@
         </is>
       </c>
       <c r="B642" t="n">
-        <v>0.056192</v>
+        <v>0.057442</v>
       </c>
       <c r="C642" t="n">
-        <v>0.39196</v>
+        <v>0.375635</v>
       </c>
     </row>
     <row r="643">
@@ -8773,10 +8773,10 @@
         </is>
       </c>
       <c r="B643" t="n">
-        <v>0.056577</v>
+        <v>0.057477</v>
       </c>
       <c r="C643" t="n">
-        <v>0.389447</v>
+        <v>0.373096</v>
       </c>
     </row>
     <row r="644">
@@ -8786,10 +8786,10 @@
         </is>
       </c>
       <c r="B644" t="n">
-        <v>0.056744</v>
+        <v>0.057535</v>
       </c>
       <c r="C644" t="n">
-        <v>0.386935</v>
+        <v>0.370558</v>
       </c>
     </row>
     <row r="645">
@@ -8799,10 +8799,10 @@
         </is>
       </c>
       <c r="B645" t="n">
-        <v>0.057145</v>
+        <v>0.05807</v>
       </c>
       <c r="C645" t="n">
-        <v>0.384422</v>
+        <v>0.36802</v>
       </c>
     </row>
     <row r="646">
@@ -8812,10 +8812,10 @@
         </is>
       </c>
       <c r="B646" t="n">
-        <v>0.057797</v>
+        <v>0.059125</v>
       </c>
       <c r="C646" t="n">
-        <v>0.38191</v>
+        <v>0.365482</v>
       </c>
     </row>
     <row r="647">
@@ -8825,10 +8825,10 @@
         </is>
       </c>
       <c r="B647" t="n">
-        <v>0.057982</v>
+        <v>0.059806</v>
       </c>
       <c r="C647" t="n">
-        <v>0.379397</v>
+        <v>0.362944</v>
       </c>
     </row>
     <row r="648">
@@ -8838,10 +8838,10 @@
         </is>
       </c>
       <c r="B648" t="n">
-        <v>0.058013</v>
+        <v>0.059827</v>
       </c>
       <c r="C648" t="n">
-        <v>0.376884</v>
+        <v>0.360406</v>
       </c>
     </row>
     <row r="649">
@@ -8851,10 +8851,10 @@
         </is>
       </c>
       <c r="B649" t="n">
-        <v>0.058939</v>
+        <v>0.059988</v>
       </c>
       <c r="C649" t="n">
-        <v>0.374372</v>
+        <v>0.357868</v>
       </c>
     </row>
     <row r="650">
@@ -8864,10 +8864,10 @@
         </is>
       </c>
       <c r="B650" t="n">
-        <v>0.059817</v>
+        <v>0.060226</v>
       </c>
       <c r="C650" t="n">
-        <v>0.371859</v>
+        <v>0.35533</v>
       </c>
     </row>
     <row r="651">
@@ -8877,10 +8877,10 @@
         </is>
       </c>
       <c r="B651" t="n">
-        <v>0.059833</v>
+        <v>0.060626</v>
       </c>
       <c r="C651" t="n">
-        <v>0.369347</v>
+        <v>0.352792</v>
       </c>
     </row>
     <row r="652">
@@ -8890,10 +8890,10 @@
         </is>
       </c>
       <c r="B652" t="n">
-        <v>0.059921</v>
+        <v>0.06085</v>
       </c>
       <c r="C652" t="n">
-        <v>0.366834</v>
+        <v>0.350254</v>
       </c>
     </row>
     <row r="653">
@@ -8903,10 +8903,10 @@
         </is>
       </c>
       <c r="B653" t="n">
-        <v>0.060028</v>
+        <v>0.061945</v>
       </c>
       <c r="C653" t="n">
-        <v>0.364322</v>
+        <v>0.347716</v>
       </c>
     </row>
     <row r="654">
@@ -8916,10 +8916,10 @@
         </is>
       </c>
       <c r="B654" t="n">
-        <v>0.060447</v>
+        <v>0.062151</v>
       </c>
       <c r="C654" t="n">
-        <v>0.361809</v>
+        <v>0.345178</v>
       </c>
     </row>
     <row r="655">
@@ -8929,10 +8929,10 @@
         </is>
       </c>
       <c r="B655" t="n">
-        <v>0.060611</v>
+        <v>0.06274200000000001</v>
       </c>
       <c r="C655" t="n">
-        <v>0.359296</v>
+        <v>0.34264</v>
       </c>
     </row>
     <row r="656">
@@ -8942,10 +8942,10 @@
         </is>
       </c>
       <c r="B656" t="n">
-        <v>0.060835</v>
+        <v>0.06345199999999999</v>
       </c>
       <c r="C656" t="n">
-        <v>0.356784</v>
+        <v>0.340102</v>
       </c>
     </row>
     <row r="657">
@@ -8955,10 +8955,10 @@
         </is>
       </c>
       <c r="B657" t="n">
-        <v>0.062004</v>
+        <v>0.06353200000000001</v>
       </c>
       <c r="C657" t="n">
-        <v>0.354271</v>
+        <v>0.337563</v>
       </c>
     </row>
     <row r="658">
@@ -8968,10 +8968,10 @@
         </is>
       </c>
       <c r="B658" t="n">
-        <v>0.062033</v>
+        <v>0.06395099999999999</v>
       </c>
       <c r="C658" t="n">
-        <v>0.351759</v>
+        <v>0.335025</v>
       </c>
     </row>
     <row r="659">
@@ -8981,10 +8981,10 @@
         </is>
       </c>
       <c r="B659" t="n">
-        <v>0.063225</v>
+        <v>0.064552</v>
       </c>
       <c r="C659" t="n">
-        <v>0.349246</v>
+        <v>0.332487</v>
       </c>
     </row>
     <row r="660">
@@ -8994,10 +8994,10 @@
         </is>
       </c>
       <c r="B660" t="n">
-        <v>0.064293</v>
+        <v>0.065026</v>
       </c>
       <c r="C660" t="n">
-        <v>0.346734</v>
+        <v>0.329949</v>
       </c>
     </row>
     <row r="661">
@@ -9007,10 +9007,10 @@
         </is>
       </c>
       <c r="B661" t="n">
-        <v>0.064488</v>
+        <v>0.065577</v>
       </c>
       <c r="C661" t="n">
-        <v>0.344221</v>
+        <v>0.327411</v>
       </c>
     </row>
     <row r="662">
@@ -9020,10 +9020,10 @@
         </is>
       </c>
       <c r="B662" t="n">
-        <v>0.06456099999999999</v>
+        <v>0.065888</v>
       </c>
       <c r="C662" t="n">
-        <v>0.341709</v>
+        <v>0.324873</v>
       </c>
     </row>
     <row r="663">
@@ -9033,10 +9033,10 @@
         </is>
       </c>
       <c r="B663" t="n">
-        <v>0.065307</v>
+        <v>0.066051</v>
       </c>
       <c r="C663" t="n">
-        <v>0.339196</v>
+        <v>0.322335</v>
       </c>
     </row>
     <row r="664">
@@ -9046,10 +9046,10 @@
         </is>
       </c>
       <c r="B664" t="n">
-        <v>0.065565</v>
+        <v>0.06736200000000001</v>
       </c>
       <c r="C664" t="n">
-        <v>0.336683</v>
+        <v>0.319797</v>
       </c>
     </row>
     <row r="665">
@@ -9059,10 +9059,10 @@
         </is>
       </c>
       <c r="B665" t="n">
-        <v>0.065675</v>
+        <v>0.068051</v>
       </c>
       <c r="C665" t="n">
-        <v>0.334171</v>
+        <v>0.317259</v>
       </c>
     </row>
     <row r="666">
@@ -9072,10 +9072,10 @@
         </is>
       </c>
       <c r="B666" t="n">
-        <v>0.06616900000000001</v>
+        <v>0.068313</v>
       </c>
       <c r="C666" t="n">
-        <v>0.331658</v>
+        <v>0.314721</v>
       </c>
     </row>
     <row r="667">
@@ -9085,10 +9085,10 @@
         </is>
       </c>
       <c r="B667" t="n">
-        <v>0.066445</v>
+        <v>0.068532</v>
       </c>
       <c r="C667" t="n">
-        <v>0.329146</v>
+        <v>0.312183</v>
       </c>
     </row>
     <row r="668">
@@ -9098,10 +9098,10 @@
         </is>
       </c>
       <c r="B668" t="n">
-        <v>0.067291</v>
+        <v>0.068908</v>
       </c>
       <c r="C668" t="n">
-        <v>0.326633</v>
+        <v>0.309645</v>
       </c>
     </row>
     <row r="669">
@@ -9111,10 +9111,10 @@
         </is>
       </c>
       <c r="B669" t="n">
-        <v>0.06744600000000001</v>
+        <v>0.06926599999999999</v>
       </c>
       <c r="C669" t="n">
-        <v>0.324121</v>
+        <v>0.307107</v>
       </c>
     </row>
     <row r="670">
@@ -9124,10 +9124,10 @@
         </is>
       </c>
       <c r="B670" t="n">
-        <v>0.068499</v>
+        <v>0.069298</v>
       </c>
       <c r="C670" t="n">
-        <v>0.321608</v>
+        <v>0.304569</v>
       </c>
     </row>
     <row r="671">
@@ -9137,10 +9137,10 @@
         </is>
       </c>
       <c r="B671" t="n">
-        <v>0.06852999999999999</v>
+        <v>0.069538</v>
       </c>
       <c r="C671" t="n">
-        <v>0.319095</v>
+        <v>0.30203</v>
       </c>
     </row>
     <row r="672">
@@ -9150,10 +9150,10 @@
         </is>
       </c>
       <c r="B672" t="n">
-        <v>0.06870800000000001</v>
+        <v>0.070239</v>
       </c>
       <c r="C672" t="n">
-        <v>0.316583</v>
+        <v>0.299492</v>
       </c>
     </row>
     <row r="673">
@@ -9163,10 +9163,10 @@
         </is>
       </c>
       <c r="B673" t="n">
-        <v>0.06891899999999999</v>
+        <v>0.07033</v>
       </c>
       <c r="C673" t="n">
-        <v>0.31407</v>
+        <v>0.296954</v>
       </c>
     </row>
     <row r="674">
@@ -9176,10 +9176,10 @@
         </is>
       </c>
       <c r="B674" t="n">
-        <v>0.069454</v>
+        <v>0.07091600000000001</v>
       </c>
       <c r="C674" t="n">
-        <v>0.311558</v>
+        <v>0.294416</v>
       </c>
     </row>
     <row r="675">
@@ -9189,10 +9189,10 @@
         </is>
       </c>
       <c r="B675" t="n">
-        <v>0.069866</v>
+        <v>0.07098</v>
       </c>
       <c r="C675" t="n">
-        <v>0.309045</v>
+        <v>0.291878</v>
       </c>
     </row>
     <row r="676">
@@ -9202,10 +9202,10 @@
         </is>
       </c>
       <c r="B676" t="n">
-        <v>0.07020899999999999</v>
+        <v>0.071259</v>
       </c>
       <c r="C676" t="n">
-        <v>0.306533</v>
+        <v>0.28934</v>
       </c>
     </row>
     <row r="677">
@@ -9215,10 +9215,10 @@
         </is>
       </c>
       <c r="B677" t="n">
-        <v>0.07048699999999999</v>
+        <v>0.072227</v>
       </c>
       <c r="C677" t="n">
-        <v>0.30402</v>
+        <v>0.286802</v>
       </c>
     </row>
     <row r="678">
@@ -9228,10 +9228,10 @@
         </is>
       </c>
       <c r="B678" t="n">
-        <v>0.070872</v>
+        <v>0.07230399999999999</v>
       </c>
       <c r="C678" t="n">
-        <v>0.301508</v>
+        <v>0.284264</v>
       </c>
     </row>
     <row r="679">
@@ -9241,10 +9241,10 @@
         </is>
       </c>
       <c r="B679" t="n">
-        <v>0.07152500000000001</v>
+        <v>0.072839</v>
       </c>
       <c r="C679" t="n">
-        <v>0.298995</v>
+        <v>0.281726</v>
       </c>
     </row>
     <row r="680">
@@ -9254,10 +9254,10 @@
         </is>
       </c>
       <c r="B680" t="n">
-        <v>0.07188899999999999</v>
+        <v>0.072884</v>
       </c>
       <c r="C680" t="n">
-        <v>0.296482</v>
+        <v>0.279188</v>
       </c>
     </row>
     <row r="681">
@@ -9267,10 +9267,10 @@
         </is>
       </c>
       <c r="B681" t="n">
-        <v>0.072573</v>
+        <v>0.07391200000000001</v>
       </c>
       <c r="C681" t="n">
-        <v>0.29397</v>
+        <v>0.27665</v>
       </c>
     </row>
     <row r="682">
@@ -9280,10 +9280,10 @@
         </is>
       </c>
       <c r="B682" t="n">
-        <v>0.072728</v>
+        <v>0.074473</v>
       </c>
       <c r="C682" t="n">
-        <v>0.291457</v>
+        <v>0.274112</v>
       </c>
     </row>
     <row r="683">
@@ -9293,10 +9293,10 @@
         </is>
       </c>
       <c r="B683" t="n">
-        <v>0.07285999999999999</v>
+        <v>0.07470400000000001</v>
       </c>
       <c r="C683" t="n">
-        <v>0.288945</v>
+        <v>0.271574</v>
       </c>
     </row>
     <row r="684">
@@ -9306,10 +9306,10 @@
         </is>
       </c>
       <c r="B684" t="n">
-        <v>0.073058</v>
+        <v>0.074916</v>
       </c>
       <c r="C684" t="n">
-        <v>0.286432</v>
+        <v>0.269036</v>
       </c>
     </row>
     <row r="685">
@@ -9319,10 +9319,10 @@
         </is>
       </c>
       <c r="B685" t="n">
-        <v>0.073946</v>
+        <v>0.075199</v>
       </c>
       <c r="C685" t="n">
-        <v>0.28392</v>
+        <v>0.266497</v>
       </c>
     </row>
     <row r="686">
@@ -9332,10 +9332,10 @@
         </is>
       </c>
       <c r="B686" t="n">
-        <v>0.073951</v>
+        <v>0.075471</v>
       </c>
       <c r="C686" t="n">
-        <v>0.281407</v>
+        <v>0.263959</v>
       </c>
     </row>
     <row r="687">
@@ -9345,10 +9345,10 @@
         </is>
       </c>
       <c r="B687" t="n">
-        <v>0.074644</v>
+        <v>0.075558</v>
       </c>
       <c r="C687" t="n">
-        <v>0.278894</v>
+        <v>0.261421</v>
       </c>
     </row>
     <row r="688">
@@ -9358,10 +9358,10 @@
         </is>
       </c>
       <c r="B688" t="n">
-        <v>0.074707</v>
+        <v>0.076393</v>
       </c>
       <c r="C688" t="n">
-        <v>0.276382</v>
+        <v>0.258883</v>
       </c>
     </row>
     <row r="689">
@@ -9371,10 +9371,10 @@
         </is>
       </c>
       <c r="B689" t="n">
-        <v>0.075504</v>
+        <v>0.078482</v>
       </c>
       <c r="C689" t="n">
-        <v>0.273869</v>
+        <v>0.256345</v>
       </c>
     </row>
     <row r="690">
@@ -9384,10 +9384,10 @@
         </is>
       </c>
       <c r="B690" t="n">
-        <v>0.075714</v>
+        <v>0.078779</v>
       </c>
       <c r="C690" t="n">
-        <v>0.271357</v>
+        <v>0.253807</v>
       </c>
     </row>
     <row r="691">
@@ -9397,10 +9397,10 @@
         </is>
       </c>
       <c r="B691" t="n">
-        <v>0.07581300000000001</v>
+        <v>0.078916</v>
       </c>
       <c r="C691" t="n">
-        <v>0.268844</v>
+        <v>0.251269</v>
       </c>
     </row>
     <row r="692">
@@ -9410,10 +9410,10 @@
         </is>
       </c>
       <c r="B692" t="n">
-        <v>0.076651</v>
+        <v>0.079387</v>
       </c>
       <c r="C692" t="n">
-        <v>0.266332</v>
+        <v>0.248731</v>
       </c>
     </row>
     <row r="693">
@@ -9423,10 +9423,10 @@
         </is>
       </c>
       <c r="B693" t="n">
-        <v>0.077533</v>
+        <v>0.079745</v>
       </c>
       <c r="C693" t="n">
-        <v>0.263819</v>
+        <v>0.246193</v>
       </c>
     </row>
     <row r="694">
@@ -9436,10 +9436,10 @@
         </is>
       </c>
       <c r="B694" t="n">
-        <v>0.07872700000000001</v>
+        <v>0.08024199999999999</v>
       </c>
       <c r="C694" t="n">
-        <v>0.261307</v>
+        <v>0.243655</v>
       </c>
     </row>
     <row r="695">
@@ -9449,10 +9449,10 @@
         </is>
       </c>
       <c r="B695" t="n">
-        <v>0.078767</v>
+        <v>0.080814</v>
       </c>
       <c r="C695" t="n">
-        <v>0.258794</v>
+        <v>0.241117</v>
       </c>
     </row>
     <row r="696">
@@ -9462,10 +9462,10 @@
         </is>
       </c>
       <c r="B696" t="n">
-        <v>0.079348</v>
+        <v>0.08167199999999999</v>
       </c>
       <c r="C696" t="n">
-        <v>0.256281</v>
+        <v>0.238579</v>
       </c>
     </row>
     <row r="697">
@@ -9475,10 +9475,10 @@
         </is>
       </c>
       <c r="B697" t="n">
-        <v>0.079834</v>
+        <v>0.08194700000000001</v>
       </c>
       <c r="C697" t="n">
-        <v>0.253769</v>
+        <v>0.236041</v>
       </c>
     </row>
     <row r="698">
@@ -9488,10 +9488,10 @@
         </is>
       </c>
       <c r="B698" t="n">
-        <v>0.08036</v>
+        <v>0.082467</v>
       </c>
       <c r="C698" t="n">
-        <v>0.251256</v>
+        <v>0.233503</v>
       </c>
     </row>
     <row r="699">
@@ -9501,10 +9501,10 @@
         </is>
       </c>
       <c r="B699" t="n">
-        <v>0.080845</v>
+        <v>0.083384</v>
       </c>
       <c r="C699" t="n">
-        <v>0.248744</v>
+        <v>0.230964</v>
       </c>
     </row>
     <row r="700">
@@ -9514,10 +9514,10 @@
         </is>
       </c>
       <c r="B700" t="n">
-        <v>0.08128100000000001</v>
+        <v>0.08358400000000001</v>
       </c>
       <c r="C700" t="n">
-        <v>0.246231</v>
+        <v>0.228426</v>
       </c>
     </row>
     <row r="701">
@@ -9527,10 +9527,10 @@
         </is>
       </c>
       <c r="B701" t="n">
-        <v>0.08189399999999999</v>
+        <v>0.08388</v>
       </c>
       <c r="C701" t="n">
-        <v>0.243719</v>
+        <v>0.225888</v>
       </c>
     </row>
     <row r="702">
@@ -9540,10 +9540,10 @@
         </is>
       </c>
       <c r="B702" t="n">
-        <v>0.083069</v>
+        <v>0.084398</v>
       </c>
       <c r="C702" t="n">
-        <v>0.241206</v>
+        <v>0.22335</v>
       </c>
     </row>
     <row r="703">
@@ -9553,10 +9553,10 @@
         </is>
       </c>
       <c r="B703" t="n">
-        <v>0.083133</v>
+        <v>0.08472</v>
       </c>
       <c r="C703" t="n">
-        <v>0.238693</v>
+        <v>0.220812</v>
       </c>
     </row>
     <row r="704">
@@ -9566,10 +9566,10 @@
         </is>
       </c>
       <c r="B704" t="n">
-        <v>0.08314100000000001</v>
+        <v>0.084755</v>
       </c>
       <c r="C704" t="n">
-        <v>0.236181</v>
+        <v>0.218274</v>
       </c>
     </row>
     <row r="705">
@@ -9579,10 +9579,10 @@
         </is>
       </c>
       <c r="B705" t="n">
-        <v>0.08361300000000001</v>
+        <v>0.08584799999999999</v>
       </c>
       <c r="C705" t="n">
-        <v>0.233668</v>
+        <v>0.215736</v>
       </c>
     </row>
     <row r="706">
@@ -9592,10 +9592,10 @@
         </is>
       </c>
       <c r="B706" t="n">
-        <v>0.083665</v>
+        <v>0.08654100000000001</v>
       </c>
       <c r="C706" t="n">
-        <v>0.231156</v>
+        <v>0.213198</v>
       </c>
     </row>
     <row r="707">
@@ -9605,10 +9605,10 @@
         </is>
       </c>
       <c r="B707" t="n">
-        <v>0.08566699999999999</v>
+        <v>0.08808100000000001</v>
       </c>
       <c r="C707" t="n">
-        <v>0.228643</v>
+        <v>0.21066</v>
       </c>
     </row>
     <row r="708">
@@ -9618,10 +9618,10 @@
         </is>
       </c>
       <c r="B708" t="n">
-        <v>0.085799</v>
+        <v>0.088405</v>
       </c>
       <c r="C708" t="n">
-        <v>0.226131</v>
+        <v>0.208122</v>
       </c>
     </row>
     <row r="709">
@@ -9631,10 +9631,10 @@
         </is>
       </c>
       <c r="B709" t="n">
-        <v>0.08607099999999999</v>
+        <v>0.08878</v>
       </c>
       <c r="C709" t="n">
-        <v>0.223618</v>
+        <v>0.205584</v>
       </c>
     </row>
     <row r="710">
@@ -9644,10 +9644,10 @@
         </is>
       </c>
       <c r="B710" t="n">
-        <v>0.086447</v>
+        <v>0.088813</v>
       </c>
       <c r="C710" t="n">
-        <v>0.221106</v>
+        <v>0.203046</v>
       </c>
     </row>
     <row r="711">
@@ -9657,10 +9657,10 @@
         </is>
       </c>
       <c r="B711" t="n">
-        <v>0.087812</v>
+        <v>0.091626</v>
       </c>
       <c r="C711" t="n">
-        <v>0.218593</v>
+        <v>0.200508</v>
       </c>
     </row>
     <row r="712">
@@ -9670,10 +9670,10 @@
         </is>
       </c>
       <c r="B712" t="n">
-        <v>0.088078</v>
+        <v>0.09197</v>
       </c>
       <c r="C712" t="n">
-        <v>0.21608</v>
+        <v>0.19797</v>
       </c>
     </row>
     <row r="713">
@@ -9683,10 +9683,10 @@
         </is>
       </c>
       <c r="B713" t="n">
-        <v>0.08880399999999999</v>
+        <v>0.092641</v>
       </c>
       <c r="C713" t="n">
-        <v>0.213568</v>
+        <v>0.195431</v>
       </c>
     </row>
     <row r="714">
@@ -9696,10 +9696,10 @@
         </is>
       </c>
       <c r="B714" t="n">
-        <v>0.088922</v>
+        <v>0.092949</v>
       </c>
       <c r="C714" t="n">
-        <v>0.211055</v>
+        <v>0.192893</v>
       </c>
     </row>
     <row r="715">
@@ -9709,10 +9709,10 @@
         </is>
       </c>
       <c r="B715" t="n">
-        <v>0.090993</v>
+        <v>0.09314699999999999</v>
       </c>
       <c r="C715" t="n">
-        <v>0.208543</v>
+        <v>0.190355</v>
       </c>
     </row>
     <row r="716">
@@ -9722,10 +9722,10 @@
         </is>
       </c>
       <c r="B716" t="n">
-        <v>0.092151</v>
+        <v>0.095321</v>
       </c>
       <c r="C716" t="n">
-        <v>0.20603</v>
+        <v>0.187817</v>
       </c>
     </row>
     <row r="717">
@@ -9735,10 +9735,10 @@
         </is>
       </c>
       <c r="B717" t="n">
-        <v>0.092318</v>
+        <v>0.095959</v>
       </c>
       <c r="C717" t="n">
-        <v>0.203518</v>
+        <v>0.185279</v>
       </c>
     </row>
     <row r="718">
@@ -9748,10 +9748,10 @@
         </is>
       </c>
       <c r="B718" t="n">
-        <v>0.092442</v>
+        <v>0.096373</v>
       </c>
       <c r="C718" t="n">
-        <v>0.201005</v>
+        <v>0.182741</v>
       </c>
     </row>
     <row r="719">
@@ -9761,10 +9761,10 @@
         </is>
       </c>
       <c r="B719" t="n">
-        <v>0.093721</v>
+        <v>0.096426</v>
       </c>
       <c r="C719" t="n">
-        <v>0.198492</v>
+        <v>0.180203</v>
       </c>
     </row>
     <row r="720">
@@ -9774,10 +9774,10 @@
         </is>
       </c>
       <c r="B720" t="n">
-        <v>0.09481299999999999</v>
+        <v>0.096605</v>
       </c>
       <c r="C720" t="n">
-        <v>0.19598</v>
+        <v>0.177665</v>
       </c>
     </row>
     <row r="721">
@@ -9787,10 +9787,10 @@
         </is>
       </c>
       <c r="B721" t="n">
-        <v>0.095403</v>
+        <v>0.097092</v>
       </c>
       <c r="C721" t="n">
-        <v>0.193467</v>
+        <v>0.175127</v>
       </c>
     </row>
     <row r="722">
@@ -9800,10 +9800,10 @@
         </is>
       </c>
       <c r="B722" t="n">
-        <v>0.095761</v>
+        <v>0.09751899999999999</v>
       </c>
       <c r="C722" t="n">
-        <v>0.190955</v>
+        <v>0.172589</v>
       </c>
     </row>
     <row r="723">
@@ -9813,10 +9813,10 @@
         </is>
       </c>
       <c r="B723" t="n">
-        <v>0.09593</v>
+        <v>0.09888</v>
       </c>
       <c r="C723" t="n">
-        <v>0.188442</v>
+        <v>0.170051</v>
       </c>
     </row>
     <row r="724">
@@ -9826,10 +9826,10 @@
         </is>
       </c>
       <c r="B724" t="n">
-        <v>0.09658600000000001</v>
+        <v>0.100086</v>
       </c>
       <c r="C724" t="n">
-        <v>0.18593</v>
+        <v>0.167513</v>
       </c>
     </row>
     <row r="725">
@@ -9839,10 +9839,10 @@
         </is>
       </c>
       <c r="B725" t="n">
-        <v>0.097386</v>
+        <v>0.1002</v>
       </c>
       <c r="C725" t="n">
-        <v>0.183417</v>
+        <v>0.164975</v>
       </c>
     </row>
     <row r="726">
@@ -9852,10 +9852,10 @@
         </is>
       </c>
       <c r="B726" t="n">
-        <v>0.097841</v>
+        <v>0.100554</v>
       </c>
       <c r="C726" t="n">
-        <v>0.180905</v>
+        <v>0.162437</v>
       </c>
     </row>
     <row r="727">
@@ -9865,10 +9865,10 @@
         </is>
       </c>
       <c r="B727" t="n">
-        <v>0.098048</v>
+        <v>0.100806</v>
       </c>
       <c r="C727" t="n">
-        <v>0.178392</v>
+        <v>0.159898</v>
       </c>
     </row>
     <row r="728">
@@ -9878,10 +9878,10 @@
         </is>
       </c>
       <c r="B728" t="n">
-        <v>0.099486</v>
+        <v>0.101023</v>
       </c>
       <c r="C728" t="n">
-        <v>0.175879</v>
+        <v>0.15736</v>
       </c>
     </row>
     <row r="729">
@@ -9891,10 +9891,10 @@
         </is>
       </c>
       <c r="B729" t="n">
-        <v>0.0998</v>
+        <v>0.102149</v>
       </c>
       <c r="C729" t="n">
-        <v>0.173367</v>
+        <v>0.154822</v>
       </c>
     </row>
     <row r="730">
@@ -9904,10 +9904,10 @@
         </is>
       </c>
       <c r="B730" t="n">
-        <v>0.100465</v>
+        <v>0.102622</v>
       </c>
       <c r="C730" t="n">
-        <v>0.170854</v>
+        <v>0.152284</v>
       </c>
     </row>
     <row r="731">
@@ -9917,10 +9917,10 @@
         </is>
       </c>
       <c r="B731" t="n">
-        <v>0.10048</v>
+        <v>0.104264</v>
       </c>
       <c r="C731" t="n">
-        <v>0.168342</v>
+        <v>0.149746</v>
       </c>
     </row>
     <row r="732">
@@ -9930,10 +9930,10 @@
         </is>
       </c>
       <c r="B732" t="n">
-        <v>0.101716</v>
+        <v>0.109143</v>
       </c>
       <c r="C732" t="n">
-        <v>0.165829</v>
+        <v>0.147208</v>
       </c>
     </row>
     <row r="733">
@@ -9943,10 +9943,10 @@
         </is>
       </c>
       <c r="B733" t="n">
-        <v>0.102325</v>
+        <v>0.109404</v>
       </c>
       <c r="C733" t="n">
-        <v>0.163317</v>
+        <v>0.14467</v>
       </c>
     </row>
     <row r="734">
@@ -9956,10 +9956,10 @@
         </is>
       </c>
       <c r="B734" t="n">
-        <v>0.10243</v>
+        <v>0.109762</v>
       </c>
       <c r="C734" t="n">
-        <v>0.160804</v>
+        <v>0.142132</v>
       </c>
     </row>
     <row r="735">
@@ -9969,10 +9969,10 @@
         </is>
       </c>
       <c r="B735" t="n">
-        <v>0.103894</v>
+        <v>0.109952</v>
       </c>
       <c r="C735" t="n">
-        <v>0.158291</v>
+        <v>0.139594</v>
       </c>
     </row>
     <row r="736">
@@ -9982,10 +9982,10 @@
         </is>
       </c>
       <c r="B736" t="n">
-        <v>0.109281</v>
+        <v>0.110237</v>
       </c>
       <c r="C736" t="n">
-        <v>0.155779</v>
+        <v>0.137056</v>
       </c>
     </row>
     <row r="737">
@@ -9995,10 +9995,10 @@
         </is>
       </c>
       <c r="B737" t="n">
-        <v>0.109517</v>
+        <v>0.110819</v>
       </c>
       <c r="C737" t="n">
-        <v>0.153266</v>
+        <v>0.134518</v>
       </c>
     </row>
     <row r="738">
@@ -10008,10 +10008,10 @@
         </is>
       </c>
       <c r="B738" t="n">
-        <v>0.10956</v>
+        <v>0.114393</v>
       </c>
       <c r="C738" t="n">
-        <v>0.150754</v>
+        <v>0.13198</v>
       </c>
     </row>
     <row r="739">
@@ -10021,10 +10021,10 @@
         </is>
       </c>
       <c r="B739" t="n">
-        <v>0.109576</v>
+        <v>0.11559</v>
       </c>
       <c r="C739" t="n">
-        <v>0.148241</v>
+        <v>0.129442</v>
       </c>
     </row>
     <row r="740">
@@ -10034,10 +10034,10 @@
         </is>
       </c>
       <c r="B740" t="n">
-        <v>0.109873</v>
+        <v>0.117709</v>
       </c>
       <c r="C740" t="n">
-        <v>0.145729</v>
+        <v>0.126904</v>
       </c>
     </row>
     <row r="741">
@@ -10047,10 +10047,10 @@
         </is>
       </c>
       <c r="B741" t="n">
-        <v>0.110623</v>
+        <v>0.119532</v>
       </c>
       <c r="C741" t="n">
-        <v>0.143216</v>
+        <v>0.124365</v>
       </c>
     </row>
     <row r="742">
@@ -10060,10 +10060,10 @@
         </is>
       </c>
       <c r="B742" t="n">
-        <v>0.112101</v>
+        <v>0.120373</v>
       </c>
       <c r="C742" t="n">
-        <v>0.140704</v>
+        <v>0.121827</v>
       </c>
     </row>
     <row r="743">
@@ -10073,10 +10073,10 @@
         </is>
       </c>
       <c r="B743" t="n">
-        <v>0.113949</v>
+        <v>0.121819</v>
       </c>
       <c r="C743" t="n">
-        <v>0.138191</v>
+        <v>0.119289</v>
       </c>
     </row>
     <row r="744">
@@ -10086,10 +10086,10 @@
         </is>
       </c>
       <c r="B744" t="n">
-        <v>0.116135</v>
+        <v>0.12322</v>
       </c>
       <c r="C744" t="n">
-        <v>0.135678</v>
+        <v>0.116751</v>
       </c>
     </row>
     <row r="745">
@@ -10099,10 +10099,10 @@
         </is>
       </c>
       <c r="B745" t="n">
-        <v>0.119412</v>
+        <v>0.124747</v>
       </c>
       <c r="C745" t="n">
-        <v>0.133166</v>
+        <v>0.114213</v>
       </c>
     </row>
     <row r="746">
@@ -10112,10 +10112,10 @@
         </is>
       </c>
       <c r="B746" t="n">
-        <v>0.119668</v>
+        <v>0.125198</v>
       </c>
       <c r="C746" t="n">
-        <v>0.130653</v>
+        <v>0.111675</v>
       </c>
     </row>
     <row r="747">
@@ -10125,10 +10125,10 @@
         </is>
       </c>
       <c r="B747" t="n">
-        <v>0.119724</v>
+        <v>0.125839</v>
       </c>
       <c r="C747" t="n">
-        <v>0.128141</v>
+        <v>0.109137</v>
       </c>
     </row>
     <row r="748">
@@ -10138,10 +10138,10 @@
         </is>
       </c>
       <c r="B748" t="n">
-        <v>0.121149</v>
+        <v>0.126142</v>
       </c>
       <c r="C748" t="n">
-        <v>0.125628</v>
+        <v>0.106599</v>
       </c>
     </row>
     <row r="749">
@@ -10151,10 +10151,10 @@
         </is>
       </c>
       <c r="B749" t="n">
-        <v>0.121502</v>
+        <v>0.130816</v>
       </c>
       <c r="C749" t="n">
-        <v>0.123116</v>
+        <v>0.104061</v>
       </c>
     </row>
     <row r="750">
@@ -10164,10 +10164,10 @@
         </is>
       </c>
       <c r="B750" t="n">
-        <v>0.123301</v>
+        <v>0.131529</v>
       </c>
       <c r="C750" t="n">
-        <v>0.120603</v>
+        <v>0.101523</v>
       </c>
     </row>
     <row r="751">
@@ -10177,10 +10177,10 @@
         </is>
       </c>
       <c r="B751" t="n">
-        <v>0.123606</v>
+        <v>0.133028</v>
       </c>
       <c r="C751" t="n">
-        <v>0.11809</v>
+        <v>0.098985</v>
       </c>
     </row>
     <row r="752">
@@ -10190,10 +10190,10 @@
         </is>
       </c>
       <c r="B752" t="n">
-        <v>0.126194</v>
+        <v>0.136036</v>
       </c>
       <c r="C752" t="n">
-        <v>0.115578</v>
+        <v>0.096447</v>
       </c>
     </row>
     <row r="753">
@@ -10203,10 +10203,10 @@
         </is>
       </c>
       <c r="B753" t="n">
-        <v>0.127097</v>
+        <v>0.136375</v>
       </c>
       <c r="C753" t="n">
-        <v>0.113065</v>
+        <v>0.09390900000000001</v>
       </c>
     </row>
     <row r="754">
@@ -10216,10 +10216,10 @@
         </is>
       </c>
       <c r="B754" t="n">
-        <v>0.127793</v>
+        <v>0.136663</v>
       </c>
       <c r="C754" t="n">
-        <v>0.110553</v>
+        <v>0.09137099999999999</v>
       </c>
     </row>
     <row r="755">
@@ -10229,10 +10229,10 @@
         </is>
       </c>
       <c r="B755" t="n">
-        <v>0.130605</v>
+        <v>0.13729</v>
       </c>
       <c r="C755" t="n">
-        <v>0.10804</v>
+        <v>0.08883199999999999</v>
       </c>
     </row>
     <row r="756">
@@ -10242,10 +10242,10 @@
         </is>
       </c>
       <c r="B756" t="n">
-        <v>0.131158</v>
+        <v>0.140549</v>
       </c>
       <c r="C756" t="n">
-        <v>0.105528</v>
+        <v>0.086294</v>
       </c>
     </row>
     <row r="757">
@@ -10255,10 +10255,10 @@
         </is>
       </c>
       <c r="B757" t="n">
-        <v>0.131355</v>
+        <v>0.141191</v>
       </c>
       <c r="C757" t="n">
-        <v>0.103015</v>
+        <v>0.083756</v>
       </c>
     </row>
     <row r="758">
@@ -10268,10 +10268,10 @@
         </is>
       </c>
       <c r="B758" t="n">
-        <v>0.133056</v>
+        <v>0.142093</v>
       </c>
       <c r="C758" t="n">
-        <v>0.100503</v>
+        <v>0.081218</v>
       </c>
     </row>
     <row r="759">
@@ -10281,10 +10281,10 @@
         </is>
       </c>
       <c r="B759" t="n">
-        <v>0.136293</v>
+        <v>0.142878</v>
       </c>
       <c r="C759" t="n">
-        <v>0.09798999999999999</v>
+        <v>0.07868</v>
       </c>
     </row>
     <row r="760">
@@ -10294,10 +10294,10 @@
         </is>
       </c>
       <c r="B760" t="n">
-        <v>0.136314</v>
+        <v>0.14393</v>
       </c>
       <c r="C760" t="n">
-        <v>0.09547700000000001</v>
+        <v>0.076142</v>
       </c>
     </row>
     <row r="761">
@@ -10307,10 +10307,10 @@
         </is>
       </c>
       <c r="B761" t="n">
-        <v>0.136913</v>
+        <v>0.146313</v>
       </c>
       <c r="C761" t="n">
-        <v>0.09296500000000001</v>
+        <v>0.073604</v>
       </c>
     </row>
     <row r="762">
@@ -10320,10 +10320,10 @@
         </is>
       </c>
       <c r="B762" t="n">
-        <v>0.137498</v>
+        <v>0.153331</v>
       </c>
       <c r="C762" t="n">
-        <v>0.090452</v>
+        <v>0.071066</v>
       </c>
     </row>
     <row r="763">
@@ -10333,10 +10333,10 @@
         </is>
       </c>
       <c r="B763" t="n">
-        <v>0.139296</v>
+        <v>0.155832</v>
       </c>
       <c r="C763" t="n">
-        <v>0.08794</v>
+        <v>0.06852800000000001</v>
       </c>
     </row>
     <row r="764">
@@ -10346,10 +10346,10 @@
         </is>
       </c>
       <c r="B764" t="n">
-        <v>0.141222</v>
+        <v>0.159144</v>
       </c>
       <c r="C764" t="n">
-        <v>0.085427</v>
+        <v>0.06598999999999999</v>
       </c>
     </row>
     <row r="765">
@@ -10359,10 +10359,10 @@
         </is>
       </c>
       <c r="B765" t="n">
-        <v>0.142491</v>
+        <v>0.161132</v>
       </c>
       <c r="C765" t="n">
-        <v>0.082915</v>
+        <v>0.06345199999999999</v>
       </c>
     </row>
     <row r="766">
@@ -10372,10 +10372,10 @@
         </is>
       </c>
       <c r="B766" t="n">
-        <v>0.142816</v>
+        <v>0.161282</v>
       </c>
       <c r="C766" t="n">
-        <v>0.080402</v>
+        <v>0.060914</v>
       </c>
     </row>
     <row r="767">
@@ -10385,10 +10385,10 @@
         </is>
       </c>
       <c r="B767" t="n">
-        <v>0.143518</v>
+        <v>0.171001</v>
       </c>
       <c r="C767" t="n">
-        <v>0.077889</v>
+        <v>0.058376</v>
       </c>
     </row>
     <row r="768">
@@ -10398,10 +10398,10 @@
         </is>
       </c>
       <c r="B768" t="n">
-        <v>0.145162</v>
+        <v>0.176689</v>
       </c>
       <c r="C768" t="n">
-        <v>0.075377</v>
+        <v>0.055838</v>
       </c>
     </row>
     <row r="769">
@@ -10411,10 +10411,10 @@
         </is>
       </c>
       <c r="B769" t="n">
-        <v>0.153553</v>
+        <v>0.18016</v>
       </c>
       <c r="C769" t="n">
-        <v>0.072864</v>
+        <v>0.053299</v>
       </c>
     </row>
     <row r="770">
@@ -10424,10 +10424,10 @@
         </is>
       </c>
       <c r="B770" t="n">
-        <v>0.156313</v>
+        <v>0.18214</v>
       </c>
       <c r="C770" t="n">
-        <v>0.070352</v>
+        <v>0.050761</v>
       </c>
     </row>
     <row r="771">
@@ -10437,10 +10437,10 @@
         </is>
       </c>
       <c r="B771" t="n">
-        <v>0.16014</v>
+        <v>0.18322</v>
       </c>
       <c r="C771" t="n">
-        <v>0.067839</v>
+        <v>0.048223</v>
       </c>
     </row>
     <row r="772">
@@ -10450,10 +10450,10 @@
         </is>
       </c>
       <c r="B772" t="n">
-        <v>0.160339</v>
+        <v>0.183821</v>
       </c>
       <c r="C772" t="n">
-        <v>0.065327</v>
+        <v>0.045685</v>
       </c>
     </row>
     <row r="773">
@@ -10463,10 +10463,10 @@
         </is>
       </c>
       <c r="B773" t="n">
-        <v>0.161282</v>
+        <v>0.187537</v>
       </c>
       <c r="C773" t="n">
-        <v>0.06281399999999999</v>
+        <v>0.043147</v>
       </c>
     </row>
     <row r="774">
@@ -10476,10 +10476,10 @@
         </is>
       </c>
       <c r="B774" t="n">
-        <v>0.170712</v>
+        <v>0.187818</v>
       </c>
       <c r="C774" t="n">
-        <v>0.060302</v>
+        <v>0.040609</v>
       </c>
     </row>
     <row r="775">
@@ -10489,10 +10489,10 @@
         </is>
       </c>
       <c r="B775" t="n">
-        <v>0.175718</v>
+        <v>0.188479</v>
       </c>
       <c r="C775" t="n">
-        <v>0.057789</v>
+        <v>0.038071</v>
       </c>
     </row>
     <row r="776">
@@ -10502,10 +10502,10 @@
         </is>
       </c>
       <c r="B776" t="n">
-        <v>0.180963</v>
+        <v>0.189068</v>
       </c>
       <c r="C776" t="n">
-        <v>0.055276</v>
+        <v>0.035533</v>
       </c>
     </row>
     <row r="777">
@@ -10515,10 +10515,10 @@
         </is>
       </c>
       <c r="B777" t="n">
-        <v>0.181119</v>
+        <v>0.198512</v>
       </c>
       <c r="C777" t="n">
-        <v>0.052764</v>
+        <v>0.032995</v>
       </c>
     </row>
     <row r="778">
@@ -10528,10 +10528,10 @@
         </is>
       </c>
       <c r="B778" t="n">
-        <v>0.181514</v>
+        <v>0.199406</v>
       </c>
       <c r="C778" t="n">
-        <v>0.050251</v>
+        <v>0.030457</v>
       </c>
     </row>
     <row r="779">
@@ -10541,10 +10541,10 @@
         </is>
       </c>
       <c r="B779" t="n">
-        <v>0.182595</v>
+        <v>0.207827</v>
       </c>
       <c r="C779" t="n">
-        <v>0.047739</v>
+        <v>0.027919</v>
       </c>
     </row>
     <row r="780">
@@ -10554,10 +10554,10 @@
         </is>
       </c>
       <c r="B780" t="n">
-        <v>0.186411</v>
+        <v>0.247202</v>
       </c>
       <c r="C780" t="n">
-        <v>0.045226</v>
+        <v>0.025381</v>
       </c>
     </row>
     <row r="781">
@@ -10567,10 +10567,10 @@
         </is>
       </c>
       <c r="B781" t="n">
-        <v>0.187097</v>
+        <v>0.247202</v>
       </c>
       <c r="C781" t="n">
-        <v>0.042714</v>
+        <v>0.022843</v>
       </c>
     </row>
     <row r="782">
@@ -10580,10 +10580,10 @@
         </is>
       </c>
       <c r="B782" t="n">
-        <v>0.188841</v>
+        <v>0.263604</v>
       </c>
       <c r="C782" t="n">
-        <v>0.040201</v>
+        <v>0.020305</v>
       </c>
     </row>
     <row r="783">
@@ -10593,10 +10593,10 @@
         </is>
       </c>
       <c r="B783" t="n">
-        <v>0.19019</v>
+        <v>0.266966</v>
       </c>
       <c r="C783" t="n">
-        <v>0.037688</v>
+        <v>0.017766</v>
       </c>
     </row>
     <row r="784">
@@ -10606,10 +10606,10 @@
         </is>
       </c>
       <c r="B784" t="n">
-        <v>0.197482</v>
+        <v>0.270696</v>
       </c>
       <c r="C784" t="n">
-        <v>0.035176</v>
+        <v>0.015228</v>
       </c>
     </row>
     <row r="785">
@@ -10619,10 +10619,10 @@
         </is>
       </c>
       <c r="B785" t="n">
-        <v>0.200888</v>
+        <v>0.27628</v>
       </c>
       <c r="C785" t="n">
-        <v>0.032663</v>
+        <v>0.01269</v>
       </c>
     </row>
     <row r="786">
@@ -10632,10 +10632,10 @@
         </is>
       </c>
       <c r="B786" t="n">
-        <v>0.207983</v>
+        <v>0.334027</v>
       </c>
       <c r="C786" t="n">
-        <v>0.030151</v>
+        <v>0.010152</v>
       </c>
     </row>
     <row r="787">
@@ -10645,10 +10645,10 @@
         </is>
       </c>
       <c r="B787" t="n">
-        <v>0.221327</v>
+        <v>0.349304</v>
       </c>
       <c r="C787" t="n">
-        <v>0.027638</v>
+        <v>0.007614</v>
       </c>
     </row>
     <row r="788">
@@ -10658,10 +10658,10 @@
         </is>
       </c>
       <c r="B788" t="n">
-        <v>0.245114</v>
+        <v>0.362633</v>
       </c>
       <c r="C788" t="n">
-        <v>0.025126</v>
+        <v>0.005076</v>
       </c>
     </row>
     <row r="789">
@@ -10671,114 +10671,10 @@
         </is>
       </c>
       <c r="B789" t="n">
-        <v>0.249245</v>
+        <v>0.507092</v>
       </c>
       <c r="C789" t="n">
-        <v>0.022613</v>
-      </c>
-    </row>
-    <row r="790">
-      <c r="A790" t="inlineStr">
-        <is>
-          <t>Adjusted target</t>
-        </is>
-      </c>
-      <c r="B790" t="n">
-        <v>0.260509</v>
-      </c>
-      <c r="C790" t="n">
-        <v>0.020101</v>
-      </c>
-    </row>
-    <row r="791">
-      <c r="A791" t="inlineStr">
-        <is>
-          <t>Adjusted target</t>
-        </is>
-      </c>
-      <c r="B791" t="n">
-        <v>0.263815</v>
-      </c>
-      <c r="C791" t="n">
-        <v>0.017588</v>
-      </c>
-    </row>
-    <row r="792">
-      <c r="A792" t="inlineStr">
-        <is>
-          <t>Adjusted target</t>
-        </is>
-      </c>
-      <c r="B792" t="n">
-        <v>0.2669</v>
-      </c>
-      <c r="C792" t="n">
-        <v>0.015075</v>
-      </c>
-    </row>
-    <row r="793">
-      <c r="A793" t="inlineStr">
-        <is>
-          <t>Adjusted target</t>
-        </is>
-      </c>
-      <c r="B793" t="n">
-        <v>0.274307</v>
-      </c>
-      <c r="C793" t="n">
-        <v>0.012563</v>
-      </c>
-    </row>
-    <row r="794">
-      <c r="A794" t="inlineStr">
-        <is>
-          <t>Adjusted target</t>
-        </is>
-      </c>
-      <c r="B794" t="n">
-        <v>0.33048</v>
-      </c>
-      <c r="C794" t="n">
-        <v>0.01005</v>
-      </c>
-    </row>
-    <row r="795">
-      <c r="A795" t="inlineStr">
-        <is>
-          <t>Adjusted target</t>
-        </is>
-      </c>
-      <c r="B795" t="n">
-        <v>0.347869</v>
-      </c>
-      <c r="C795" t="n">
-        <v>0.007538</v>
-      </c>
-    </row>
-    <row r="796">
-      <c r="A796" t="inlineStr">
-        <is>
-          <t>Adjusted target</t>
-        </is>
-      </c>
-      <c r="B796" t="n">
-        <v>0.35942</v>
-      </c>
-      <c r="C796" t="n">
-        <v>0.005025</v>
-      </c>
-    </row>
-    <row r="797">
-      <c r="A797" t="inlineStr">
-        <is>
-          <t>Adjusted target</t>
-        </is>
-      </c>
-      <c r="B797" t="n">
-        <v>0.5037</v>
-      </c>
-      <c r="C797" t="n">
-        <v>0.002513</v>
+        <v>0.002538</v>
       </c>
     </row>
   </sheetData>

--- a/vignettes/vignette-1/tail_exceedance_plot_data.xlsx
+++ b/vignettes/vignette-1/tail_exceedance_plot_data.xlsx
@@ -3404,7 +3404,7 @@
         </is>
       </c>
       <c r="B230" t="n">
-        <v>0.056487</v>
+        <v>0.056702</v>
       </c>
       <c r="C230" t="n">
         <v>0.42132</v>
@@ -3417,7 +3417,7 @@
         </is>
       </c>
       <c r="B231" t="n">
-        <v>0.056702</v>
+        <v>0.056785</v>
       </c>
       <c r="C231" t="n">
         <v>0.418782</v>
@@ -3430,7 +3430,7 @@
         </is>
       </c>
       <c r="B232" t="n">
-        <v>0.056785</v>
+        <v>0.057942</v>
       </c>
       <c r="C232" t="n">
         <v>0.416244</v>
@@ -3443,7 +3443,7 @@
         </is>
       </c>
       <c r="B233" t="n">
-        <v>0.057942</v>
+        <v>0.05854</v>
       </c>
       <c r="C233" t="n">
         <v>0.413706</v>
@@ -3456,7 +3456,7 @@
         </is>
       </c>
       <c r="B234" t="n">
-        <v>0.05854</v>
+        <v>0.058745</v>
       </c>
       <c r="C234" t="n">
         <v>0.411168</v>
@@ -3469,7 +3469,7 @@
         </is>
       </c>
       <c r="B235" t="n">
-        <v>0.058745</v>
+        <v>0.058836</v>
       </c>
       <c r="C235" t="n">
         <v>0.408629</v>
@@ -3482,7 +3482,7 @@
         </is>
       </c>
       <c r="B236" t="n">
-        <v>0.058836</v>
+        <v>0.059279</v>
       </c>
       <c r="C236" t="n">
         <v>0.406091</v>
@@ -3495,7 +3495,7 @@
         </is>
       </c>
       <c r="B237" t="n">
-        <v>0.059279</v>
+        <v>0.059367</v>
       </c>
       <c r="C237" t="n">
         <v>0.403553</v>
@@ -3508,7 +3508,7 @@
         </is>
       </c>
       <c r="B238" t="n">
-        <v>0.059367</v>
+        <v>0.059553</v>
       </c>
       <c r="C238" t="n">
         <v>0.401015</v>
@@ -3521,7 +3521,7 @@
         </is>
       </c>
       <c r="B239" t="n">
-        <v>0.059553</v>
+        <v>0.059579</v>
       </c>
       <c r="C239" t="n">
         <v>0.398477</v>
@@ -3534,7 +3534,7 @@
         </is>
       </c>
       <c r="B240" t="n">
-        <v>0.059579</v>
+        <v>0.060111</v>
       </c>
       <c r="C240" t="n">
         <v>0.395939</v>
@@ -3547,7 +3547,7 @@
         </is>
       </c>
       <c r="B241" t="n">
-        <v>0.060111</v>
+        <v>0.060827</v>
       </c>
       <c r="C241" t="n">
         <v>0.393401</v>
@@ -3560,7 +3560,7 @@
         </is>
       </c>
       <c r="B242" t="n">
-        <v>0.060827</v>
+        <v>0.060882</v>
       </c>
       <c r="C242" t="n">
         <v>0.390863</v>
@@ -3573,7 +3573,7 @@
         </is>
       </c>
       <c r="B243" t="n">
-        <v>0.060882</v>
+        <v>0.061437</v>
       </c>
       <c r="C243" t="n">
         <v>0.388325</v>
@@ -3586,7 +3586,7 @@
         </is>
       </c>
       <c r="B244" t="n">
-        <v>0.061437</v>
+        <v>0.061712</v>
       </c>
       <c r="C244" t="n">
         <v>0.385787</v>
@@ -3599,7 +3599,7 @@
         </is>
       </c>
       <c r="B245" t="n">
-        <v>0.061712</v>
+        <v>0.061784</v>
       </c>
       <c r="C245" t="n">
         <v>0.383249</v>
@@ -3612,7 +3612,7 @@
         </is>
       </c>
       <c r="B246" t="n">
-        <v>0.061784</v>
+        <v>0.06179</v>
       </c>
       <c r="C246" t="n">
         <v>0.380711</v>
@@ -3625,7 +3625,7 @@
         </is>
       </c>
       <c r="B247" t="n">
-        <v>0.06179</v>
+        <v>0.061969</v>
       </c>
       <c r="C247" t="n">
         <v>0.378173</v>
@@ -3638,7 +3638,7 @@
         </is>
       </c>
       <c r="B248" t="n">
-        <v>0.061969</v>
+        <v>0.062129</v>
       </c>
       <c r="C248" t="n">
         <v>0.375635</v>
@@ -3651,7 +3651,7 @@
         </is>
       </c>
       <c r="B249" t="n">
-        <v>0.062129</v>
+        <v>0.062168</v>
       </c>
       <c r="C249" t="n">
         <v>0.373096</v>
@@ -3664,7 +3664,7 @@
         </is>
       </c>
       <c r="B250" t="n">
-        <v>0.062168</v>
+        <v>0.06263299999999999</v>
       </c>
       <c r="C250" t="n">
         <v>0.370558</v>
@@ -3677,7 +3677,7 @@
         </is>
       </c>
       <c r="B251" t="n">
-        <v>0.06263299999999999</v>
+        <v>0.062844</v>
       </c>
       <c r="C251" t="n">
         <v>0.36802</v>
@@ -3690,7 +3690,7 @@
         </is>
       </c>
       <c r="B252" t="n">
-        <v>0.062844</v>
+        <v>0.063808</v>
       </c>
       <c r="C252" t="n">
         <v>0.365482</v>
@@ -3703,7 +3703,7 @@
         </is>
       </c>
       <c r="B253" t="n">
-        <v>0.063808</v>
+        <v>0.064842</v>
       </c>
       <c r="C253" t="n">
         <v>0.362944</v>
@@ -3716,7 +3716,7 @@
         </is>
       </c>
       <c r="B254" t="n">
-        <v>0.064842</v>
+        <v>0.06555900000000001</v>
       </c>
       <c r="C254" t="n">
         <v>0.360406</v>
@@ -3729,7 +3729,7 @@
         </is>
       </c>
       <c r="B255" t="n">
-        <v>0.06555900000000001</v>
+        <v>0.067176</v>
       </c>
       <c r="C255" t="n">
         <v>0.357868</v>
@@ -3742,7 +3742,7 @@
         </is>
       </c>
       <c r="B256" t="n">
-        <v>0.067176</v>
+        <v>0.06736399999999999</v>
       </c>
       <c r="C256" t="n">
         <v>0.35533</v>
@@ -3755,7 +3755,7 @@
         </is>
       </c>
       <c r="B257" t="n">
-        <v>0.06736399999999999</v>
+        <v>0.067375</v>
       </c>
       <c r="C257" t="n">
         <v>0.352792</v>
@@ -3768,7 +3768,7 @@
         </is>
       </c>
       <c r="B258" t="n">
-        <v>0.067375</v>
+        <v>0.067555</v>
       </c>
       <c r="C258" t="n">
         <v>0.350254</v>
@@ -3781,7 +3781,7 @@
         </is>
       </c>
       <c r="B259" t="n">
-        <v>0.067555</v>
+        <v>0.067604</v>
       </c>
       <c r="C259" t="n">
         <v>0.347716</v>
@@ -3794,7 +3794,7 @@
         </is>
       </c>
       <c r="B260" t="n">
-        <v>0.067604</v>
+        <v>0.067644</v>
       </c>
       <c r="C260" t="n">
         <v>0.345178</v>
@@ -3807,7 +3807,7 @@
         </is>
       </c>
       <c r="B261" t="n">
-        <v>0.067644</v>
+        <v>0.068111</v>
       </c>
       <c r="C261" t="n">
         <v>0.34264</v>
@@ -3820,7 +3820,7 @@
         </is>
       </c>
       <c r="B262" t="n">
-        <v>0.068111</v>
+        <v>0.068538</v>
       </c>
       <c r="C262" t="n">
         <v>0.340102</v>
@@ -3833,7 +3833,7 @@
         </is>
       </c>
       <c r="B263" t="n">
-        <v>0.068538</v>
+        <v>0.068601</v>
       </c>
       <c r="C263" t="n">
         <v>0.337563</v>
@@ -3846,7 +3846,7 @@
         </is>
       </c>
       <c r="B264" t="n">
-        <v>0.068601</v>
+        <v>0.068845</v>
       </c>
       <c r="C264" t="n">
         <v>0.335025</v>
@@ -3859,7 +3859,7 @@
         </is>
       </c>
       <c r="B265" t="n">
-        <v>0.068845</v>
+        <v>0.068939</v>
       </c>
       <c r="C265" t="n">
         <v>0.332487</v>
@@ -3872,7 +3872,7 @@
         </is>
       </c>
       <c r="B266" t="n">
-        <v>0.068939</v>
+        <v>0.06909</v>
       </c>
       <c r="C266" t="n">
         <v>0.329949</v>
@@ -3885,7 +3885,7 @@
         </is>
       </c>
       <c r="B267" t="n">
-        <v>0.06909</v>
+        <v>0.069253</v>
       </c>
       <c r="C267" t="n">
         <v>0.327411</v>
@@ -3898,7 +3898,7 @@
         </is>
       </c>
       <c r="B268" t="n">
-        <v>0.069253</v>
+        <v>0.070214</v>
       </c>
       <c r="C268" t="n">
         <v>0.324873</v>
@@ -3911,7 +3911,7 @@
         </is>
       </c>
       <c r="B269" t="n">
-        <v>0.070214</v>
+        <v>0.070659</v>
       </c>
       <c r="C269" t="n">
         <v>0.322335</v>
@@ -3924,7 +3924,7 @@
         </is>
       </c>
       <c r="B270" t="n">
-        <v>0.070659</v>
+        <v>0.071449</v>
       </c>
       <c r="C270" t="n">
         <v>0.319797</v>
@@ -5627,7 +5627,7 @@
         </is>
       </c>
       <c r="B401" t="n">
-        <v>0.001861</v>
+        <v>0.001862</v>
       </c>
       <c r="C401" t="n">
         <v>0.98731</v>
@@ -5653,7 +5653,7 @@
         </is>
       </c>
       <c r="B403" t="n">
-        <v>0.00224</v>
+        <v>0.002241</v>
       </c>
       <c r="C403" t="n">
         <v>0.9822340000000001</v>
@@ -5679,7 +5679,7 @@
         </is>
       </c>
       <c r="B405" t="n">
-        <v>0.002547</v>
+        <v>0.00255</v>
       </c>
       <c r="C405" t="n">
         <v>0.9771570000000001</v>
@@ -5692,7 +5692,7 @@
         </is>
       </c>
       <c r="B406" t="n">
-        <v>0.00262</v>
+        <v>0.002621</v>
       </c>
       <c r="C406" t="n">
         <v>0.974619</v>
@@ -5705,7 +5705,7 @@
         </is>
       </c>
       <c r="B407" t="n">
-        <v>0.002726</v>
+        <v>0.002725</v>
       </c>
       <c r="C407" t="n">
         <v>0.972081</v>
@@ -5731,7 +5731,7 @@
         </is>
       </c>
       <c r="B409" t="n">
-        <v>0.003223</v>
+        <v>0.003224</v>
       </c>
       <c r="C409" t="n">
         <v>0.967005</v>
@@ -5744,7 +5744,7 @@
         </is>
       </c>
       <c r="B410" t="n">
-        <v>0.003379</v>
+        <v>0.003381</v>
       </c>
       <c r="C410" t="n">
         <v>0.964467</v>
@@ -5770,7 +5770,7 @@
         </is>
       </c>
       <c r="B412" t="n">
-        <v>0.003932</v>
+        <v>0.003935</v>
       </c>
       <c r="C412" t="n">
         <v>0.959391</v>
@@ -5887,7 +5887,7 @@
         </is>
       </c>
       <c r="B421" t="n">
-        <v>0.005664</v>
+        <v>0.005672</v>
       </c>
       <c r="C421" t="n">
         <v>0.936548</v>
@@ -5900,7 +5900,7 @@
         </is>
       </c>
       <c r="B422" t="n">
-        <v>0.005687</v>
+        <v>0.00569</v>
       </c>
       <c r="C422" t="n">
         <v>0.93401</v>
@@ -5913,7 +5913,7 @@
         </is>
       </c>
       <c r="B423" t="n">
-        <v>0.005835</v>
+        <v>0.005837</v>
       </c>
       <c r="C423" t="n">
         <v>0.931472</v>
@@ -5926,7 +5926,7 @@
         </is>
       </c>
       <c r="B424" t="n">
-        <v>0.006023</v>
+        <v>0.006025</v>
       </c>
       <c r="C424" t="n">
         <v>0.928934</v>
@@ -5939,7 +5939,7 @@
         </is>
       </c>
       <c r="B425" t="n">
-        <v>0.006073</v>
+        <v>0.006083</v>
       </c>
       <c r="C425" t="n">
         <v>0.926396</v>
@@ -5952,7 +5952,7 @@
         </is>
       </c>
       <c r="B426" t="n">
-        <v>0.006608</v>
+        <v>0.00661</v>
       </c>
       <c r="C426" t="n">
         <v>0.923858</v>
@@ -5965,7 +5965,7 @@
         </is>
       </c>
       <c r="B427" t="n">
-        <v>0.006897</v>
+        <v>0.006898</v>
       </c>
       <c r="C427" t="n">
         <v>0.92132</v>
@@ -5978,7 +5978,7 @@
         </is>
       </c>
       <c r="B428" t="n">
-        <v>0.007442</v>
+        <v>0.007443</v>
       </c>
       <c r="C428" t="n">
         <v>0.918782</v>
@@ -5991,7 +5991,7 @@
         </is>
       </c>
       <c r="B429" t="n">
-        <v>0.008368</v>
+        <v>0.008369</v>
       </c>
       <c r="C429" t="n">
         <v>0.9162439999999999</v>
@@ -6004,7 +6004,7 @@
         </is>
       </c>
       <c r="B430" t="n">
-        <v>0.008512</v>
+        <v>0.008510999999999999</v>
       </c>
       <c r="C430" t="n">
         <v>0.913706</v>
@@ -6030,7 +6030,7 @@
         </is>
       </c>
       <c r="B432" t="n">
-        <v>0.008869999999999999</v>
+        <v>0.008879</v>
       </c>
       <c r="C432" t="n">
         <v>0.908629</v>
@@ -6043,7 +6043,7 @@
         </is>
       </c>
       <c r="B433" t="n">
-        <v>0.008985</v>
+        <v>0.008987</v>
       </c>
       <c r="C433" t="n">
         <v>0.906091</v>
@@ -6069,7 +6069,7 @@
         </is>
       </c>
       <c r="B435" t="n">
-        <v>0.009202</v>
+        <v>0.009202999999999999</v>
       </c>
       <c r="C435" t="n">
         <v>0.901015</v>
@@ -6082,7 +6082,7 @@
         </is>
       </c>
       <c r="B436" t="n">
-        <v>0.009339999999999999</v>
+        <v>0.009351999999999999</v>
       </c>
       <c r="C436" t="n">
         <v>0.898477</v>
@@ -6095,7 +6095,7 @@
         </is>
       </c>
       <c r="B437" t="n">
-        <v>0.009495999999999999</v>
+        <v>0.009497</v>
       </c>
       <c r="C437" t="n">
         <v>0.895939</v>
@@ -6108,7 +6108,7 @@
         </is>
       </c>
       <c r="B438" t="n">
-        <v>0.009577</v>
+        <v>0.009575999999999999</v>
       </c>
       <c r="C438" t="n">
         <v>0.893401</v>
@@ -6121,7 +6121,7 @@
         </is>
       </c>
       <c r="B439" t="n">
-        <v>0.009887</v>
+        <v>0.009894</v>
       </c>
       <c r="C439" t="n">
         <v>0.890863</v>
@@ -6134,7 +6134,7 @@
         </is>
       </c>
       <c r="B440" t="n">
-        <v>0.010131</v>
+        <v>0.010144</v>
       </c>
       <c r="C440" t="n">
         <v>0.888325</v>
@@ -6160,7 +6160,7 @@
         </is>
       </c>
       <c r="B442" t="n">
-        <v>0.010962</v>
+        <v>0.010969</v>
       </c>
       <c r="C442" t="n">
         <v>0.883249</v>
@@ -6173,7 +6173,7 @@
         </is>
       </c>
       <c r="B443" t="n">
-        <v>0.010971</v>
+        <v>0.010975</v>
       </c>
       <c r="C443" t="n">
         <v>0.880711</v>
@@ -6186,7 +6186,7 @@
         </is>
       </c>
       <c r="B444" t="n">
-        <v>0.011055</v>
+        <v>0.011054</v>
       </c>
       <c r="C444" t="n">
         <v>0.878173</v>
@@ -6212,7 +6212,7 @@
         </is>
       </c>
       <c r="B446" t="n">
-        <v>0.011298</v>
+        <v>0.0113</v>
       </c>
       <c r="C446" t="n">
         <v>0.873096</v>
@@ -6225,7 +6225,7 @@
         </is>
       </c>
       <c r="B447" t="n">
-        <v>0.011497</v>
+        <v>0.011512</v>
       </c>
       <c r="C447" t="n">
         <v>0.8705580000000001</v>
@@ -6251,7 +6251,7 @@
         </is>
       </c>
       <c r="B449" t="n">
-        <v>0.011618</v>
+        <v>0.011617</v>
       </c>
       <c r="C449" t="n">
         <v>0.865482</v>
@@ -6277,7 +6277,7 @@
         </is>
       </c>
       <c r="B451" t="n">
-        <v>0.012366</v>
+        <v>0.012368</v>
       </c>
       <c r="C451" t="n">
         <v>0.860406</v>
@@ -6290,7 +6290,7 @@
         </is>
       </c>
       <c r="B452" t="n">
-        <v>0.012375</v>
+        <v>0.012374</v>
       </c>
       <c r="C452" t="n">
         <v>0.857868</v>
@@ -6303,7 +6303,7 @@
         </is>
       </c>
       <c r="B453" t="n">
-        <v>0.01257</v>
+        <v>0.012571</v>
       </c>
       <c r="C453" t="n">
         <v>0.85533</v>
@@ -6342,7 +6342,7 @@
         </is>
       </c>
       <c r="B456" t="n">
-        <v>0.013098</v>
+        <v>0.013099</v>
       </c>
       <c r="C456" t="n">
         <v>0.847716</v>
@@ -6368,7 +6368,7 @@
         </is>
       </c>
       <c r="B458" t="n">
-        <v>0.013673</v>
+        <v>0.013679</v>
       </c>
       <c r="C458" t="n">
         <v>0.8426399999999999</v>
@@ -6381,7 +6381,7 @@
         </is>
       </c>
       <c r="B459" t="n">
-        <v>0.013806</v>
+        <v>0.01381</v>
       </c>
       <c r="C459" t="n">
         <v>0.840102</v>
@@ -6394,7 +6394,7 @@
         </is>
       </c>
       <c r="B460" t="n">
-        <v>0.014188</v>
+        <v>0.014189</v>
       </c>
       <c r="C460" t="n">
         <v>0.8375629999999999</v>
@@ -6420,7 +6420,7 @@
         </is>
       </c>
       <c r="B462" t="n">
-        <v>0.014313</v>
+        <v>0.014312</v>
       </c>
       <c r="C462" t="n">
         <v>0.832487</v>
@@ -6433,7 +6433,7 @@
         </is>
       </c>
       <c r="B463" t="n">
-        <v>0.014401</v>
+        <v>0.014405</v>
       </c>
       <c r="C463" t="n">
         <v>0.829949</v>
@@ -6446,7 +6446,7 @@
         </is>
       </c>
       <c r="B464" t="n">
-        <v>0.014488</v>
+        <v>0.014493</v>
       </c>
       <c r="C464" t="n">
         <v>0.827411</v>
@@ -6459,7 +6459,7 @@
         </is>
       </c>
       <c r="B465" t="n">
-        <v>0.014691</v>
+        <v>0.014699</v>
       </c>
       <c r="C465" t="n">
         <v>0.824873</v>
@@ -6485,7 +6485,7 @@
         </is>
       </c>
       <c r="B467" t="n">
-        <v>0.015061</v>
+        <v>0.01506</v>
       </c>
       <c r="C467" t="n">
         <v>0.819797</v>
@@ -6511,7 +6511,7 @@
         </is>
       </c>
       <c r="B469" t="n">
-        <v>0.015147</v>
+        <v>0.015172</v>
       </c>
       <c r="C469" t="n">
         <v>0.814721</v>
@@ -6524,7 +6524,7 @@
         </is>
       </c>
       <c r="B470" t="n">
-        <v>0.015566</v>
+        <v>0.015565</v>
       </c>
       <c r="C470" t="n">
         <v>0.812183</v>
@@ -6537,7 +6537,7 @@
         </is>
       </c>
       <c r="B471" t="n">
-        <v>0.015682</v>
+        <v>0.015681</v>
       </c>
       <c r="C471" t="n">
         <v>0.8096449999999999</v>
@@ -6563,7 +6563,7 @@
         </is>
       </c>
       <c r="B473" t="n">
-        <v>0.016552</v>
+        <v>0.01655</v>
       </c>
       <c r="C473" t="n">
         <v>0.804569</v>
@@ -6576,7 +6576,7 @@
         </is>
       </c>
       <c r="B474" t="n">
-        <v>0.01673</v>
+        <v>0.016729</v>
       </c>
       <c r="C474" t="n">
         <v>0.80203</v>
@@ -6589,7 +6589,7 @@
         </is>
       </c>
       <c r="B475" t="n">
-        <v>0.016756</v>
+        <v>0.016762</v>
       </c>
       <c r="C475" t="n">
         <v>0.799492</v>
@@ -6615,7 +6615,7 @@
         </is>
       </c>
       <c r="B477" t="n">
-        <v>0.017248</v>
+        <v>0.017247</v>
       </c>
       <c r="C477" t="n">
         <v>0.794416</v>
@@ -6628,7 +6628,7 @@
         </is>
       </c>
       <c r="B478" t="n">
-        <v>0.017282</v>
+        <v>0.0173</v>
       </c>
       <c r="C478" t="n">
         <v>0.791878</v>
@@ -6641,7 +6641,7 @@
         </is>
       </c>
       <c r="B479" t="n">
-        <v>0.017705</v>
+        <v>0.017706</v>
       </c>
       <c r="C479" t="n">
         <v>0.78934</v>
@@ -6654,7 +6654,7 @@
         </is>
       </c>
       <c r="B480" t="n">
-        <v>0.017771</v>
+        <v>0.017772</v>
       </c>
       <c r="C480" t="n">
         <v>0.786802</v>
@@ -6667,7 +6667,7 @@
         </is>
       </c>
       <c r="B481" t="n">
-        <v>0.017881</v>
+        <v>0.01789</v>
       </c>
       <c r="C481" t="n">
         <v>0.784264</v>
@@ -6680,7 +6680,7 @@
         </is>
       </c>
       <c r="B482" t="n">
-        <v>0.018148</v>
+        <v>0.018157</v>
       </c>
       <c r="C482" t="n">
         <v>0.781726</v>
@@ -6693,7 +6693,7 @@
         </is>
       </c>
       <c r="B483" t="n">
-        <v>0.018559</v>
+        <v>0.018557</v>
       </c>
       <c r="C483" t="n">
         <v>0.779188</v>
@@ -6706,7 +6706,7 @@
         </is>
       </c>
       <c r="B484" t="n">
-        <v>0.018854</v>
+        <v>0.018858</v>
       </c>
       <c r="C484" t="n">
         <v>0.77665</v>
@@ -6719,7 +6719,7 @@
         </is>
       </c>
       <c r="B485" t="n">
-        <v>0.019102</v>
+        <v>0.019108</v>
       </c>
       <c r="C485" t="n">
         <v>0.774112</v>
@@ -6732,7 +6732,7 @@
         </is>
       </c>
       <c r="B486" t="n">
-        <v>0.019402</v>
+        <v>0.01941</v>
       </c>
       <c r="C486" t="n">
         <v>0.771574</v>
@@ -6745,7 +6745,7 @@
         </is>
       </c>
       <c r="B487" t="n">
-        <v>0.019437</v>
+        <v>0.019439</v>
       </c>
       <c r="C487" t="n">
         <v>0.7690360000000001</v>
@@ -6758,7 +6758,7 @@
         </is>
       </c>
       <c r="B488" t="n">
-        <v>0.019447</v>
+        <v>0.019449</v>
       </c>
       <c r="C488" t="n">
         <v>0.766497</v>
@@ -6784,7 +6784,7 @@
         </is>
       </c>
       <c r="B490" t="n">
-        <v>0.019685</v>
+        <v>0.019683</v>
       </c>
       <c r="C490" t="n">
         <v>0.761421</v>
@@ -6797,7 +6797,7 @@
         </is>
       </c>
       <c r="B491" t="n">
-        <v>0.01971</v>
+        <v>0.019713</v>
       </c>
       <c r="C491" t="n">
         <v>0.758883</v>
@@ -6810,7 +6810,7 @@
         </is>
       </c>
       <c r="B492" t="n">
-        <v>0.020222</v>
+        <v>0.02024</v>
       </c>
       <c r="C492" t="n">
         <v>0.756345</v>
@@ -6823,7 +6823,7 @@
         </is>
       </c>
       <c r="B493" t="n">
-        <v>0.020361</v>
+        <v>0.020369</v>
       </c>
       <c r="C493" t="n">
         <v>0.753807</v>
@@ -6836,7 +6836,7 @@
         </is>
       </c>
       <c r="B494" t="n">
-        <v>0.021002</v>
+        <v>0.021003</v>
       </c>
       <c r="C494" t="n">
         <v>0.751269</v>
@@ -6849,7 +6849,7 @@
         </is>
       </c>
       <c r="B495" t="n">
-        <v>0.021064</v>
+        <v>0.021062</v>
       </c>
       <c r="C495" t="n">
         <v>0.748731</v>
@@ -6862,7 +6862,7 @@
         </is>
       </c>
       <c r="B496" t="n">
-        <v>0.021474</v>
+        <v>0.021476</v>
       </c>
       <c r="C496" t="n">
         <v>0.746193</v>
@@ -6875,7 +6875,7 @@
         </is>
       </c>
       <c r="B497" t="n">
-        <v>0.021496</v>
+        <v>0.021495</v>
       </c>
       <c r="C497" t="n">
         <v>0.743655</v>
@@ -6888,7 +6888,7 @@
         </is>
       </c>
       <c r="B498" t="n">
-        <v>0.021845</v>
+        <v>0.021843</v>
       </c>
       <c r="C498" t="n">
         <v>0.741117</v>
@@ -6901,7 +6901,7 @@
         </is>
       </c>
       <c r="B499" t="n">
-        <v>0.021976</v>
+        <v>0.021974</v>
       </c>
       <c r="C499" t="n">
         <v>0.738579</v>
@@ -6914,7 +6914,7 @@
         </is>
       </c>
       <c r="B500" t="n">
-        <v>0.022788</v>
+        <v>0.022792</v>
       </c>
       <c r="C500" t="n">
         <v>0.7360409999999999</v>
@@ -6927,7 +6927,7 @@
         </is>
       </c>
       <c r="B501" t="n">
-        <v>0.023098</v>
+        <v>0.023111</v>
       </c>
       <c r="C501" t="n">
         <v>0.733503</v>
@@ -6940,7 +6940,7 @@
         </is>
       </c>
       <c r="B502" t="n">
-        <v>0.023157</v>
+        <v>0.023155</v>
       </c>
       <c r="C502" t="n">
         <v>0.7309639999999999</v>
@@ -6953,7 +6953,7 @@
         </is>
       </c>
       <c r="B503" t="n">
-        <v>0.023223</v>
+        <v>0.023273</v>
       </c>
       <c r="C503" t="n">
         <v>0.728426</v>
@@ -6966,7 +6966,7 @@
         </is>
       </c>
       <c r="B504" t="n">
-        <v>0.023515</v>
+        <v>0.023514</v>
       </c>
       <c r="C504" t="n">
         <v>0.725888</v>
@@ -6979,7 +6979,7 @@
         </is>
       </c>
       <c r="B505" t="n">
-        <v>0.023789</v>
+        <v>0.023793</v>
       </c>
       <c r="C505" t="n">
         <v>0.72335</v>
@@ -6992,7 +6992,7 @@
         </is>
       </c>
       <c r="B506" t="n">
-        <v>0.023898</v>
+        <v>0.023897</v>
       </c>
       <c r="C506" t="n">
         <v>0.720812</v>
@@ -7005,7 +7005,7 @@
         </is>
       </c>
       <c r="B507" t="n">
-        <v>0.023916</v>
+        <v>0.023914</v>
       </c>
       <c r="C507" t="n">
         <v>0.718274</v>
@@ -7018,7 +7018,7 @@
         </is>
       </c>
       <c r="B508" t="n">
-        <v>0.024293</v>
+        <v>0.024291</v>
       </c>
       <c r="C508" t="n">
         <v>0.715736</v>
@@ -7031,7 +7031,7 @@
         </is>
       </c>
       <c r="B509" t="n">
-        <v>0.024473</v>
+        <v>0.024482</v>
       </c>
       <c r="C509" t="n">
         <v>0.713198</v>
@@ -7044,7 +7044,7 @@
         </is>
       </c>
       <c r="B510" t="n">
-        <v>0.024644</v>
+        <v>0.024642</v>
       </c>
       <c r="C510" t="n">
         <v>0.71066</v>
@@ -7070,7 +7070,7 @@
         </is>
       </c>
       <c r="B512" t="n">
-        <v>0.024863</v>
+        <v>0.024862</v>
       </c>
       <c r="C512" t="n">
         <v>0.705584</v>
@@ -7083,7 +7083,7 @@
         </is>
       </c>
       <c r="B513" t="n">
-        <v>0.025064</v>
+        <v>0.025063</v>
       </c>
       <c r="C513" t="n">
         <v>0.7030459999999999</v>
@@ -7109,7 +7109,7 @@
         </is>
       </c>
       <c r="B515" t="n">
-        <v>0.025862</v>
+        <v>0.025863</v>
       </c>
       <c r="C515" t="n">
         <v>0.69797</v>
@@ -7122,7 +7122,7 @@
         </is>
       </c>
       <c r="B516" t="n">
-        <v>0.025941</v>
+        <v>0.025949</v>
       </c>
       <c r="C516" t="n">
         <v>0.695431</v>
@@ -7135,7 +7135,7 @@
         </is>
       </c>
       <c r="B517" t="n">
-        <v>0.026052</v>
+        <v>0.026053</v>
       </c>
       <c r="C517" t="n">
         <v>0.692893</v>
@@ -7148,7 +7148,7 @@
         </is>
       </c>
       <c r="B518" t="n">
-        <v>0.026138</v>
+        <v>0.026148</v>
       </c>
       <c r="C518" t="n">
         <v>0.6903550000000001</v>
@@ -7161,7 +7161,7 @@
         </is>
       </c>
       <c r="B519" t="n">
-        <v>0.02636</v>
+        <v>0.026358</v>
       </c>
       <c r="C519" t="n">
         <v>0.687817</v>
@@ -7174,7 +7174,7 @@
         </is>
       </c>
       <c r="B520" t="n">
-        <v>0.026446</v>
+        <v>0.026444</v>
       </c>
       <c r="C520" t="n">
         <v>0.685279</v>
@@ -7187,7 +7187,7 @@
         </is>
       </c>
       <c r="B521" t="n">
-        <v>0.026516</v>
+        <v>0.026517</v>
       </c>
       <c r="C521" t="n">
         <v>0.682741</v>
@@ -7200,7 +7200,7 @@
         </is>
       </c>
       <c r="B522" t="n">
-        <v>0.026641</v>
+        <v>0.026639</v>
       </c>
       <c r="C522" t="n">
         <v>0.680203</v>
@@ -7213,7 +7213,7 @@
         </is>
       </c>
       <c r="B523" t="n">
-        <v>0.02682</v>
+        <v>0.026818</v>
       </c>
       <c r="C523" t="n">
         <v>0.677665</v>
@@ -7226,7 +7226,7 @@
         </is>
       </c>
       <c r="B524" t="n">
-        <v>0.027059</v>
+        <v>0.027076</v>
       </c>
       <c r="C524" t="n">
         <v>0.675127</v>
@@ -7239,7 +7239,7 @@
         </is>
       </c>
       <c r="B525" t="n">
-        <v>0.02864</v>
+        <v>0.028642</v>
       </c>
       <c r="C525" t="n">
         <v>0.672589</v>
@@ -7252,7 +7252,7 @@
         </is>
       </c>
       <c r="B526" t="n">
-        <v>0.028712</v>
+        <v>0.02872</v>
       </c>
       <c r="C526" t="n">
         <v>0.670051</v>
@@ -7265,7 +7265,7 @@
         </is>
       </c>
       <c r="B527" t="n">
-        <v>0.028964</v>
+        <v>0.028981</v>
       </c>
       <c r="C527" t="n">
         <v>0.667513</v>
@@ -7278,7 +7278,7 @@
         </is>
       </c>
       <c r="B528" t="n">
-        <v>0.029085</v>
+        <v>0.029082</v>
       </c>
       <c r="C528" t="n">
         <v>0.664975</v>
@@ -7291,7 +7291,7 @@
         </is>
       </c>
       <c r="B529" t="n">
-        <v>0.029103</v>
+        <v>0.0291</v>
       </c>
       <c r="C529" t="n">
         <v>0.6624370000000001</v>
@@ -7304,7 +7304,7 @@
         </is>
       </c>
       <c r="B530" t="n">
-        <v>0.029154</v>
+        <v>0.029155</v>
       </c>
       <c r="C530" t="n">
         <v>0.659898</v>
@@ -7317,7 +7317,7 @@
         </is>
       </c>
       <c r="B531" t="n">
-        <v>0.029248</v>
+        <v>0.029259</v>
       </c>
       <c r="C531" t="n">
         <v>0.6573600000000001</v>
@@ -7330,7 +7330,7 @@
         </is>
       </c>
       <c r="B532" t="n">
-        <v>0.029646</v>
+        <v>0.029645</v>
       </c>
       <c r="C532" t="n">
         <v>0.654822</v>
@@ -7343,7 +7343,7 @@
         </is>
       </c>
       <c r="B533" t="n">
-        <v>0.029904</v>
+        <v>0.029914</v>
       </c>
       <c r="C533" t="n">
         <v>0.652284</v>
@@ -7356,7 +7356,7 @@
         </is>
       </c>
       <c r="B534" t="n">
-        <v>0.029975</v>
+        <v>0.029973</v>
       </c>
       <c r="C534" t="n">
         <v>0.649746</v>
@@ -7369,7 +7369,7 @@
         </is>
       </c>
       <c r="B535" t="n">
-        <v>0.030369</v>
+        <v>0.030387</v>
       </c>
       <c r="C535" t="n">
         <v>0.647208</v>
@@ -7382,7 +7382,7 @@
         </is>
       </c>
       <c r="B536" t="n">
-        <v>0.030567</v>
+        <v>0.030572</v>
       </c>
       <c r="C536" t="n">
         <v>0.64467</v>
@@ -7395,7 +7395,7 @@
         </is>
       </c>
       <c r="B537" t="n">
-        <v>0.030755</v>
+        <v>0.030764</v>
       </c>
       <c r="C537" t="n">
         <v>0.642132</v>
@@ -7408,7 +7408,7 @@
         </is>
       </c>
       <c r="B538" t="n">
-        <v>0.031062</v>
+        <v>0.031061</v>
       </c>
       <c r="C538" t="n">
         <v>0.639594</v>
@@ -7434,7 +7434,7 @@
         </is>
       </c>
       <c r="B540" t="n">
-        <v>0.0313</v>
+        <v>0.031301</v>
       </c>
       <c r="C540" t="n">
         <v>0.634518</v>
@@ -7447,7 +7447,7 @@
         </is>
       </c>
       <c r="B541" t="n">
-        <v>0.031647</v>
+        <v>0.031649</v>
       </c>
       <c r="C541" t="n">
         <v>0.63198</v>
@@ -7460,7 +7460,7 @@
         </is>
       </c>
       <c r="B542" t="n">
-        <v>0.03198</v>
+        <v>0.031982</v>
       </c>
       <c r="C542" t="n">
         <v>0.6294419999999999</v>
@@ -7473,7 +7473,7 @@
         </is>
       </c>
       <c r="B543" t="n">
-        <v>0.032136</v>
+        <v>0.032186</v>
       </c>
       <c r="C543" t="n">
         <v>0.626904</v>
@@ -7486,7 +7486,7 @@
         </is>
       </c>
       <c r="B544" t="n">
-        <v>0.032478</v>
+        <v>0.032477</v>
       </c>
       <c r="C544" t="n">
         <v>0.6243649999999999</v>
@@ -7499,7 +7499,7 @@
         </is>
       </c>
       <c r="B545" t="n">
-        <v>0.032531</v>
+        <v>0.032528</v>
       </c>
       <c r="C545" t="n">
         <v>0.621827</v>
@@ -7512,7 +7512,7 @@
         </is>
       </c>
       <c r="B546" t="n">
-        <v>0.032606</v>
+        <v>0.032604</v>
       </c>
       <c r="C546" t="n">
         <v>0.619289</v>
@@ -7525,7 +7525,7 @@
         </is>
       </c>
       <c r="B547" t="n">
-        <v>0.033063</v>
+        <v>0.033092</v>
       </c>
       <c r="C547" t="n">
         <v>0.616751</v>
@@ -7538,7 +7538,7 @@
         </is>
       </c>
       <c r="B548" t="n">
-        <v>0.033255</v>
+        <v>0.033253</v>
       </c>
       <c r="C548" t="n">
         <v>0.614213</v>
@@ -7551,7 +7551,7 @@
         </is>
       </c>
       <c r="B549" t="n">
-        <v>0.033259</v>
+        <v>0.033267</v>
       </c>
       <c r="C549" t="n">
         <v>0.611675</v>
@@ -7564,7 +7564,7 @@
         </is>
       </c>
       <c r="B550" t="n">
-        <v>0.033562</v>
+        <v>0.033559</v>
       </c>
       <c r="C550" t="n">
         <v>0.609137</v>
@@ -7577,7 +7577,7 @@
         </is>
       </c>
       <c r="B551" t="n">
-        <v>0.033796</v>
+        <v>0.033812</v>
       </c>
       <c r="C551" t="n">
         <v>0.606599</v>
@@ -7590,7 +7590,7 @@
         </is>
       </c>
       <c r="B552" t="n">
-        <v>0.03383</v>
+        <v>0.033828</v>
       </c>
       <c r="C552" t="n">
         <v>0.604061</v>
@@ -7603,7 +7603,7 @@
         </is>
       </c>
       <c r="B553" t="n">
-        <v>0.033869</v>
+        <v>0.033889</v>
       </c>
       <c r="C553" t="n">
         <v>0.601523</v>
@@ -7629,7 +7629,7 @@
         </is>
       </c>
       <c r="B555" t="n">
-        <v>0.034048</v>
+        <v>0.034046</v>
       </c>
       <c r="C555" t="n">
         <v>0.5964469999999999</v>
@@ -7642,7 +7642,7 @@
         </is>
       </c>
       <c r="B556" t="n">
-        <v>0.034462</v>
+        <v>0.034472</v>
       </c>
       <c r="C556" t="n">
         <v>0.593909</v>
@@ -7655,7 +7655,7 @@
         </is>
       </c>
       <c r="B557" t="n">
-        <v>0.035106</v>
+        <v>0.035103</v>
       </c>
       <c r="C557" t="n">
         <v>0.591371</v>
@@ -7668,7 +7668,7 @@
         </is>
       </c>
       <c r="B558" t="n">
-        <v>0.035169</v>
+        <v>0.035171</v>
       </c>
       <c r="C558" t="n">
         <v>0.588832</v>
@@ -7681,7 +7681,7 @@
         </is>
       </c>
       <c r="B559" t="n">
-        <v>0.035599</v>
+        <v>0.035605</v>
       </c>
       <c r="C559" t="n">
         <v>0.586294</v>
@@ -7694,7 +7694,7 @@
         </is>
       </c>
       <c r="B560" t="n">
-        <v>0.035861</v>
+        <v>0.035883</v>
       </c>
       <c r="C560" t="n">
         <v>0.5837560000000001</v>
@@ -7720,7 +7720,7 @@
         </is>
       </c>
       <c r="B562" t="n">
-        <v>0.036095</v>
+        <v>0.036099</v>
       </c>
       <c r="C562" t="n">
         <v>0.57868</v>
@@ -7733,7 +7733,7 @@
         </is>
       </c>
       <c r="B563" t="n">
-        <v>0.036176</v>
+        <v>0.036201</v>
       </c>
       <c r="C563" t="n">
         <v>0.576142</v>
@@ -7746,7 +7746,7 @@
         </is>
       </c>
       <c r="B564" t="n">
-        <v>0.036472</v>
+        <v>0.036503</v>
       </c>
       <c r="C564" t="n">
         <v>0.573604</v>
@@ -7759,7 +7759,7 @@
         </is>
       </c>
       <c r="B565" t="n">
-        <v>0.036644</v>
+        <v>0.036642</v>
       </c>
       <c r="C565" t="n">
         <v>0.571066</v>
@@ -7772,7 +7772,7 @@
         </is>
       </c>
       <c r="B566" t="n">
-        <v>0.037008</v>
+        <v>0.037025</v>
       </c>
       <c r="C566" t="n">
         <v>0.568528</v>
@@ -7785,7 +7785,7 @@
         </is>
       </c>
       <c r="B567" t="n">
-        <v>0.037136</v>
+        <v>0.037161</v>
       </c>
       <c r="C567" t="n">
         <v>0.56599</v>
@@ -7798,7 +7798,7 @@
         </is>
       </c>
       <c r="B568" t="n">
-        <v>0.037214</v>
+        <v>0.037211</v>
       </c>
       <c r="C568" t="n">
         <v>0.563452</v>
@@ -7824,7 +7824,7 @@
         </is>
       </c>
       <c r="B570" t="n">
-        <v>0.038142</v>
+        <v>0.03814</v>
       </c>
       <c r="C570" t="n">
         <v>0.558376</v>
@@ -7850,7 +7850,7 @@
         </is>
       </c>
       <c r="B572" t="n">
-        <v>0.038724</v>
+        <v>0.038731</v>
       </c>
       <c r="C572" t="n">
         <v>0.553299</v>
@@ -7863,7 +7863,7 @@
         </is>
       </c>
       <c r="B573" t="n">
-        <v>0.038919</v>
+        <v>0.038918</v>
       </c>
       <c r="C573" t="n">
         <v>0.5507609999999999</v>
@@ -7876,7 +7876,7 @@
         </is>
       </c>
       <c r="B574" t="n">
-        <v>0.039522</v>
+        <v>0.03952</v>
       </c>
       <c r="C574" t="n">
         <v>0.548223</v>
@@ -7889,7 +7889,7 @@
         </is>
       </c>
       <c r="B575" t="n">
-        <v>0.039789</v>
+        <v>0.039786</v>
       </c>
       <c r="C575" t="n">
         <v>0.545685</v>
@@ -7915,7 +7915,7 @@
         </is>
       </c>
       <c r="B577" t="n">
-        <v>0.040018</v>
+        <v>0.040017</v>
       </c>
       <c r="C577" t="n">
         <v>0.540609</v>
@@ -7928,7 +7928,7 @@
         </is>
       </c>
       <c r="B578" t="n">
-        <v>0.040044</v>
+        <v>0.040065</v>
       </c>
       <c r="C578" t="n">
         <v>0.538071</v>
@@ -7941,7 +7941,7 @@
         </is>
       </c>
       <c r="B579" t="n">
-        <v>0.040321</v>
+        <v>0.040335</v>
       </c>
       <c r="C579" t="n">
         <v>0.535533</v>
@@ -7954,7 +7954,7 @@
         </is>
       </c>
       <c r="B580" t="n">
-        <v>0.040743</v>
+        <v>0.04074</v>
       </c>
       <c r="C580" t="n">
         <v>0.532995</v>
@@ -7980,7 +7980,7 @@
         </is>
       </c>
       <c r="B582" t="n">
-        <v>0.041123</v>
+        <v>0.04113</v>
       </c>
       <c r="C582" t="n">
         <v>0.527919</v>
@@ -7993,7 +7993,7 @@
         </is>
       </c>
       <c r="B583" t="n">
-        <v>0.041185</v>
+        <v>0.041199</v>
       </c>
       <c r="C583" t="n">
         <v>0.525381</v>
@@ -8006,7 +8006,7 @@
         </is>
       </c>
       <c r="B584" t="n">
-        <v>0.04125</v>
+        <v>0.041262</v>
       </c>
       <c r="C584" t="n">
         <v>0.5228429999999999</v>
@@ -8019,7 +8019,7 @@
         </is>
       </c>
       <c r="B585" t="n">
-        <v>0.042813</v>
+        <v>0.042811</v>
       </c>
       <c r="C585" t="n">
         <v>0.520305</v>
@@ -8032,7 +8032,7 @@
         </is>
       </c>
       <c r="B586" t="n">
-        <v>0.042952</v>
+        <v>0.042974</v>
       </c>
       <c r="C586" t="n">
         <v>0.5177659999999999</v>
@@ -8045,7 +8045,7 @@
         </is>
       </c>
       <c r="B587" t="n">
-        <v>0.043174</v>
+        <v>0.043175</v>
       </c>
       <c r="C587" t="n">
         <v>0.515228</v>
@@ -8058,7 +8058,7 @@
         </is>
       </c>
       <c r="B588" t="n">
-        <v>0.043264</v>
+        <v>0.04326</v>
       </c>
       <c r="C588" t="n">
         <v>0.51269</v>
@@ -8071,7 +8071,7 @@
         </is>
       </c>
       <c r="B589" t="n">
-        <v>0.043613</v>
+        <v>0.043612</v>
       </c>
       <c r="C589" t="n">
         <v>0.510152</v>
@@ -8097,7 +8097,7 @@
         </is>
       </c>
       <c r="B591" t="n">
-        <v>0.043885</v>
+        <v>0.043887</v>
       </c>
       <c r="C591" t="n">
         <v>0.505076</v>
@@ -8110,7 +8110,7 @@
         </is>
       </c>
       <c r="B592" t="n">
-        <v>0.044298</v>
+        <v>0.04432</v>
       </c>
       <c r="C592" t="n">
         <v>0.502538</v>
@@ -8123,7 +8123,7 @@
         </is>
       </c>
       <c r="B593" t="n">
-        <v>0.044318</v>
+        <v>0.044321</v>
       </c>
       <c r="C593" t="n">
         <v>0.5</v>
@@ -8136,7 +8136,7 @@
         </is>
       </c>
       <c r="B594" t="n">
-        <v>0.044629</v>
+        <v>0.044625</v>
       </c>
       <c r="C594" t="n">
         <v>0.497462</v>
@@ -8149,7 +8149,7 @@
         </is>
       </c>
       <c r="B595" t="n">
-        <v>0.044724</v>
+        <v>0.044727</v>
       </c>
       <c r="C595" t="n">
         <v>0.494924</v>
@@ -8162,7 +8162,7 @@
         </is>
       </c>
       <c r="B596" t="n">
-        <v>0.044916</v>
+        <v>0.044938</v>
       </c>
       <c r="C596" t="n">
         <v>0.492386</v>
@@ -8175,7 +8175,7 @@
         </is>
       </c>
       <c r="B597" t="n">
-        <v>0.044917</v>
+        <v>0.045102</v>
       </c>
       <c r="C597" t="n">
         <v>0.489848</v>
@@ -8188,7 +8188,7 @@
         </is>
       </c>
       <c r="B598" t="n">
-        <v>0.045073</v>
+        <v>0.045316</v>
       </c>
       <c r="C598" t="n">
         <v>0.48731</v>
@@ -8201,7 +8201,7 @@
         </is>
       </c>
       <c r="B599" t="n">
-        <v>0.045296</v>
+        <v>0.04549</v>
       </c>
       <c r="C599" t="n">
         <v>0.484772</v>
@@ -8214,7 +8214,7 @@
         </is>
       </c>
       <c r="B600" t="n">
-        <v>0.045467</v>
+        <v>0.045521</v>
       </c>
       <c r="C600" t="n">
         <v>0.482234</v>
@@ -8227,7 +8227,7 @@
         </is>
       </c>
       <c r="B601" t="n">
-        <v>0.045516</v>
+        <v>0.04569</v>
       </c>
       <c r="C601" t="n">
         <v>0.479695</v>
@@ -8240,7 +8240,7 @@
         </is>
       </c>
       <c r="B602" t="n">
-        <v>0.045657</v>
+        <v>0.04579</v>
       </c>
       <c r="C602" t="n">
         <v>0.477157</v>
@@ -8253,7 +8253,7 @@
         </is>
       </c>
       <c r="B603" t="n">
-        <v>0.045787</v>
+        <v>0.045881</v>
       </c>
       <c r="C603" t="n">
         <v>0.474619</v>
@@ -8266,7 +8266,7 @@
         </is>
       </c>
       <c r="B604" t="n">
-        <v>0.045865</v>
+        <v>0.046337</v>
       </c>
       <c r="C604" t="n">
         <v>0.472081</v>
@@ -8279,7 +8279,7 @@
         </is>
       </c>
       <c r="B605" t="n">
-        <v>0.046332</v>
+        <v>0.046881</v>
       </c>
       <c r="C605" t="n">
         <v>0.469543</v>
@@ -8292,7 +8292,7 @@
         </is>
       </c>
       <c r="B606" t="n">
-        <v>0.046879</v>
+        <v>0.047095</v>
       </c>
       <c r="C606" t="n">
         <v>0.467005</v>
@@ -8305,7 +8305,7 @@
         </is>
       </c>
       <c r="B607" t="n">
-        <v>0.047047</v>
+        <v>0.047313</v>
       </c>
       <c r="C607" t="n">
         <v>0.464467</v>
@@ -8318,7 +8318,7 @@
         </is>
       </c>
       <c r="B608" t="n">
-        <v>0.047301</v>
+        <v>0.047476</v>
       </c>
       <c r="C608" t="n">
         <v>0.461929</v>
@@ -8331,7 +8331,7 @@
         </is>
       </c>
       <c r="B609" t="n">
-        <v>0.047434</v>
+        <v>0.047669</v>
       </c>
       <c r="C609" t="n">
         <v>0.459391</v>
@@ -8344,7 +8344,7 @@
         </is>
       </c>
       <c r="B610" t="n">
-        <v>0.04767</v>
+        <v>0.047815</v>
       </c>
       <c r="C610" t="n">
         <v>0.456853</v>
@@ -8357,7 +8357,7 @@
         </is>
       </c>
       <c r="B611" t="n">
-        <v>0.047805</v>
+        <v>0.048763</v>
       </c>
       <c r="C611" t="n">
         <v>0.454315</v>
@@ -8370,7 +8370,7 @@
         </is>
       </c>
       <c r="B612" t="n">
-        <v>0.04876</v>
+        <v>0.049183</v>
       </c>
       <c r="C612" t="n">
         <v>0.451777</v>
@@ -8383,7 +8383,7 @@
         </is>
       </c>
       <c r="B613" t="n">
-        <v>0.049165</v>
+        <v>0.049206</v>
       </c>
       <c r="C613" t="n">
         <v>0.449239</v>
@@ -8396,7 +8396,7 @@
         </is>
       </c>
       <c r="B614" t="n">
-        <v>0.049207</v>
+        <v>0.049976</v>
       </c>
       <c r="C614" t="n">
         <v>0.446701</v>
@@ -8409,7 +8409,7 @@
         </is>
       </c>
       <c r="B615" t="n">
-        <v>0.049972</v>
+        <v>0.050003</v>
       </c>
       <c r="C615" t="n">
         <v>0.444162</v>
@@ -8422,7 +8422,7 @@
         </is>
       </c>
       <c r="B616" t="n">
-        <v>0.050003</v>
+        <v>0.050261</v>
       </c>
       <c r="C616" t="n">
         <v>0.441624</v>
@@ -8435,7 +8435,7 @@
         </is>
       </c>
       <c r="B617" t="n">
-        <v>0.050263</v>
+        <v>0.050632</v>
       </c>
       <c r="C617" t="n">
         <v>0.439086</v>
@@ -8448,7 +8448,7 @@
         </is>
       </c>
       <c r="B618" t="n">
-        <v>0.050604</v>
+        <v>0.050917</v>
       </c>
       <c r="C618" t="n">
         <v>0.436548</v>
@@ -8461,7 +8461,7 @@
         </is>
       </c>
       <c r="B619" t="n">
-        <v>0.050917</v>
+        <v>0.051251</v>
       </c>
       <c r="C619" t="n">
         <v>0.43401</v>
@@ -8474,7 +8474,7 @@
         </is>
       </c>
       <c r="B620" t="n">
-        <v>0.051233</v>
+        <v>0.051402</v>
       </c>
       <c r="C620" t="n">
         <v>0.431472</v>
@@ -8487,7 +8487,7 @@
         </is>
       </c>
       <c r="B621" t="n">
-        <v>0.051402</v>
+        <v>0.052688</v>
       </c>
       <c r="C621" t="n">
         <v>0.428934</v>
@@ -8500,7 +8500,7 @@
         </is>
       </c>
       <c r="B622" t="n">
-        <v>0.052692</v>
+        <v>0.052792</v>
       </c>
       <c r="C622" t="n">
         <v>0.426396</v>
@@ -8513,7 +8513,7 @@
         </is>
       </c>
       <c r="B623" t="n">
-        <v>0.052796</v>
+        <v>0.052956</v>
       </c>
       <c r="C623" t="n">
         <v>0.423858</v>
@@ -8526,7 +8526,7 @@
         </is>
       </c>
       <c r="B624" t="n">
-        <v>0.052958</v>
+        <v>0.053137</v>
       </c>
       <c r="C624" t="n">
         <v>0.42132</v>
@@ -8539,7 +8539,7 @@
         </is>
       </c>
       <c r="B625" t="n">
-        <v>0.053098</v>
+        <v>0.05317</v>
       </c>
       <c r="C625" t="n">
         <v>0.418782</v>
@@ -8552,7 +8552,7 @@
         </is>
       </c>
       <c r="B626" t="n">
-        <v>0.05317</v>
+        <v>0.053906</v>
       </c>
       <c r="C626" t="n">
         <v>0.416244</v>
@@ -8565,7 +8565,7 @@
         </is>
       </c>
       <c r="B627" t="n">
-        <v>0.053901</v>
+        <v>0.054032</v>
       </c>
       <c r="C627" t="n">
         <v>0.413706</v>
@@ -8578,7 +8578,7 @@
         </is>
       </c>
       <c r="B628" t="n">
-        <v>0.054036</v>
+        <v>0.054064</v>
       </c>
       <c r="C628" t="n">
         <v>0.411168</v>
@@ -8591,7 +8591,7 @@
         </is>
       </c>
       <c r="B629" t="n">
-        <v>0.054064</v>
+        <v>0.054413</v>
       </c>
       <c r="C629" t="n">
         <v>0.408629</v>
@@ -8604,7 +8604,7 @@
         </is>
       </c>
       <c r="B630" t="n">
-        <v>0.054416</v>
+        <v>0.054448</v>
       </c>
       <c r="C630" t="n">
         <v>0.406091</v>
@@ -8617,7 +8617,7 @@
         </is>
       </c>
       <c r="B631" t="n">
-        <v>0.054452</v>
+        <v>0.054613</v>
       </c>
       <c r="C631" t="n">
         <v>0.403553</v>
@@ -8630,7 +8630,7 @@
         </is>
       </c>
       <c r="B632" t="n">
-        <v>0.054614</v>
+        <v>0.054743</v>
       </c>
       <c r="C632" t="n">
         <v>0.401015</v>
@@ -8643,7 +8643,7 @@
         </is>
       </c>
       <c r="B633" t="n">
-        <v>0.054727</v>
+        <v>0.054783</v>
       </c>
       <c r="C633" t="n">
         <v>0.398477</v>
@@ -8656,7 +8656,7 @@
         </is>
       </c>
       <c r="B634" t="n">
-        <v>0.054759</v>
+        <v>0.054821</v>
       </c>
       <c r="C634" t="n">
         <v>0.395939</v>
@@ -8669,7 +8669,7 @@
         </is>
       </c>
       <c r="B635" t="n">
-        <v>0.05482</v>
+        <v>0.055472</v>
       </c>
       <c r="C635" t="n">
         <v>0.393401</v>
@@ -8682,7 +8682,7 @@
         </is>
       </c>
       <c r="B636" t="n">
-        <v>0.055456</v>
+        <v>0.055699</v>
       </c>
       <c r="C636" t="n">
         <v>0.390863</v>
@@ -8695,7 +8695,7 @@
         </is>
       </c>
       <c r="B637" t="n">
-        <v>0.055688</v>
+        <v>0.055733</v>
       </c>
       <c r="C637" t="n">
         <v>0.388325</v>
@@ -8708,7 +8708,7 @@
         </is>
       </c>
       <c r="B638" t="n">
-        <v>0.055737</v>
+        <v>0.056256</v>
       </c>
       <c r="C638" t="n">
         <v>0.385787</v>
@@ -8721,7 +8721,7 @@
         </is>
       </c>
       <c r="B639" t="n">
-        <v>0.056254</v>
+        <v>0.056484</v>
       </c>
       <c r="C639" t="n">
         <v>0.383249</v>
@@ -8734,7 +8734,7 @@
         </is>
       </c>
       <c r="B640" t="n">
-        <v>0.056486</v>
+        <v>0.057176</v>
       </c>
       <c r="C640" t="n">
         <v>0.380711</v>
@@ -8747,7 +8747,7 @@
         </is>
       </c>
       <c r="B641" t="n">
-        <v>0.057153</v>
+        <v>0.057438</v>
       </c>
       <c r="C641" t="n">
         <v>0.378173</v>
@@ -8760,7 +8760,7 @@
         </is>
       </c>
       <c r="B642" t="n">
-        <v>0.057442</v>
+        <v>0.057493</v>
       </c>
       <c r="C642" t="n">
         <v>0.375635</v>
@@ -8773,7 +8773,7 @@
         </is>
       </c>
       <c r="B643" t="n">
-        <v>0.057477</v>
+        <v>0.057531</v>
       </c>
       <c r="C643" t="n">
         <v>0.373096</v>
@@ -8786,7 +8786,7 @@
         </is>
       </c>
       <c r="B644" t="n">
-        <v>0.057535</v>
+        <v>0.058073</v>
       </c>
       <c r="C644" t="n">
         <v>0.370558</v>
@@ -8799,7 +8799,7 @@
         </is>
       </c>
       <c r="B645" t="n">
-        <v>0.05807</v>
+        <v>0.059132</v>
       </c>
       <c r="C645" t="n">
         <v>0.36802</v>
@@ -8812,7 +8812,7 @@
         </is>
       </c>
       <c r="B646" t="n">
-        <v>0.059125</v>
+        <v>0.059805</v>
       </c>
       <c r="C646" t="n">
         <v>0.365482</v>
@@ -8825,7 +8825,7 @@
         </is>
       </c>
       <c r="B647" t="n">
-        <v>0.059806</v>
+        <v>0.059826</v>
       </c>
       <c r="C647" t="n">
         <v>0.362944</v>
@@ -8838,7 +8838,7 @@
         </is>
       </c>
       <c r="B648" t="n">
-        <v>0.059827</v>
+        <v>0.059987</v>
       </c>
       <c r="C648" t="n">
         <v>0.360406</v>
@@ -8851,7 +8851,7 @@
         </is>
       </c>
       <c r="B649" t="n">
-        <v>0.059988</v>
+        <v>0.060222</v>
       </c>
       <c r="C649" t="n">
         <v>0.357868</v>
@@ -8864,7 +8864,7 @@
         </is>
       </c>
       <c r="B650" t="n">
-        <v>0.060226</v>
+        <v>0.060689</v>
       </c>
       <c r="C650" t="n">
         <v>0.35533</v>
@@ -8877,7 +8877,7 @@
         </is>
       </c>
       <c r="B651" t="n">
-        <v>0.060626</v>
+        <v>0.060844</v>
       </c>
       <c r="C651" t="n">
         <v>0.352792</v>
@@ -8890,7 +8890,7 @@
         </is>
       </c>
       <c r="B652" t="n">
-        <v>0.06085</v>
+        <v>0.060851</v>
       </c>
       <c r="C652" t="n">
         <v>0.350254</v>
@@ -8903,7 +8903,7 @@
         </is>
       </c>
       <c r="B653" t="n">
-        <v>0.061945</v>
+        <v>0.061943</v>
       </c>
       <c r="C653" t="n">
         <v>0.347716</v>
@@ -8916,7 +8916,7 @@
         </is>
       </c>
       <c r="B654" t="n">
-        <v>0.062151</v>
+        <v>0.062156</v>
       </c>
       <c r="C654" t="n">
         <v>0.345178</v>
@@ -8929,7 +8929,7 @@
         </is>
       </c>
       <c r="B655" t="n">
-        <v>0.06274200000000001</v>
+        <v>0.062738</v>
       </c>
       <c r="C655" t="n">
         <v>0.34264</v>
@@ -8942,7 +8942,7 @@
         </is>
       </c>
       <c r="B656" t="n">
-        <v>0.06345199999999999</v>
+        <v>0.063453</v>
       </c>
       <c r="C656" t="n">
         <v>0.340102</v>
@@ -8955,7 +8955,7 @@
         </is>
       </c>
       <c r="B657" t="n">
-        <v>0.06353200000000001</v>
+        <v>0.06353499999999999</v>
       </c>
       <c r="C657" t="n">
         <v>0.337563</v>
@@ -8968,7 +8968,7 @@
         </is>
       </c>
       <c r="B658" t="n">
-        <v>0.06395099999999999</v>
+        <v>0.063947</v>
       </c>
       <c r="C658" t="n">
         <v>0.335025</v>
@@ -8981,7 +8981,7 @@
         </is>
       </c>
       <c r="B659" t="n">
-        <v>0.064552</v>
+        <v>0.06455</v>
       </c>
       <c r="C659" t="n">
         <v>0.332487</v>
@@ -8994,7 +8994,7 @@
         </is>
       </c>
       <c r="B660" t="n">
-        <v>0.065026</v>
+        <v>0.065022</v>
       </c>
       <c r="C660" t="n">
         <v>0.329949</v>
@@ -9007,7 +9007,7 @@
         </is>
       </c>
       <c r="B661" t="n">
-        <v>0.065577</v>
+        <v>0.06557399999999999</v>
       </c>
       <c r="C661" t="n">
         <v>0.327411</v>
@@ -9020,7 +9020,7 @@
         </is>
       </c>
       <c r="B662" t="n">
-        <v>0.065888</v>
+        <v>0.065883</v>
       </c>
       <c r="C662" t="n">
         <v>0.324873</v>
@@ -9033,7 +9033,7 @@
         </is>
       </c>
       <c r="B663" t="n">
-        <v>0.066051</v>
+        <v>0.066048</v>
       </c>
       <c r="C663" t="n">
         <v>0.322335</v>
@@ -9046,7 +9046,7 @@
         </is>
       </c>
       <c r="B664" t="n">
-        <v>0.06736200000000001</v>
+        <v>0.06736399999999999</v>
       </c>
       <c r="C664" t="n">
         <v>0.319797</v>
@@ -9059,7 +9059,7 @@
         </is>
       </c>
       <c r="B665" t="n">
-        <v>0.068051</v>
+        <v>0.068092</v>
       </c>
       <c r="C665" t="n">
         <v>0.317259</v>
@@ -9072,7 +9072,7 @@
         </is>
       </c>
       <c r="B666" t="n">
-        <v>0.068313</v>
+        <v>0.06830899999999999</v>
       </c>
       <c r="C666" t="n">
         <v>0.314721</v>
@@ -9098,7 +9098,7 @@
         </is>
       </c>
       <c r="B668" t="n">
-        <v>0.068908</v>
+        <v>0.068915</v>
       </c>
       <c r="C668" t="n">
         <v>0.309645</v>
@@ -9111,7 +9111,7 @@
         </is>
       </c>
       <c r="B669" t="n">
-        <v>0.06926599999999999</v>
+        <v>0.069267</v>
       </c>
       <c r="C669" t="n">
         <v>0.307107</v>
@@ -9124,7 +9124,7 @@
         </is>
       </c>
       <c r="B670" t="n">
-        <v>0.069298</v>
+        <v>0.069316</v>
       </c>
       <c r="C670" t="n">
         <v>0.304569</v>
@@ -9137,7 +9137,7 @@
         </is>
       </c>
       <c r="B671" t="n">
-        <v>0.069538</v>
+        <v>0.06954100000000001</v>
       </c>
       <c r="C671" t="n">
         <v>0.30203</v>
@@ -9150,7 +9150,7 @@
         </is>
       </c>
       <c r="B672" t="n">
-        <v>0.070239</v>
+        <v>0.070257</v>
       </c>
       <c r="C672" t="n">
         <v>0.299492</v>
@@ -9163,7 +9163,7 @@
         </is>
       </c>
       <c r="B673" t="n">
-        <v>0.07033</v>
+        <v>0.070325</v>
       </c>
       <c r="C673" t="n">
         <v>0.296954</v>
@@ -9176,7 +9176,7 @@
         </is>
       </c>
       <c r="B674" t="n">
-        <v>0.07091600000000001</v>
+        <v>0.070911</v>
       </c>
       <c r="C674" t="n">
         <v>0.294416</v>
@@ -9189,7 +9189,7 @@
         </is>
       </c>
       <c r="B675" t="n">
-        <v>0.07098</v>
+        <v>0.071007</v>
       </c>
       <c r="C675" t="n">
         <v>0.291878</v>
@@ -9202,7 +9202,7 @@
         </is>
       </c>
       <c r="B676" t="n">
-        <v>0.071259</v>
+        <v>0.071254</v>
       </c>
       <c r="C676" t="n">
         <v>0.28934</v>
@@ -9215,7 +9215,7 @@
         </is>
       </c>
       <c r="B677" t="n">
-        <v>0.072227</v>
+        <v>0.07222099999999999</v>
       </c>
       <c r="C677" t="n">
         <v>0.286802</v>
@@ -9228,7 +9228,7 @@
         </is>
       </c>
       <c r="B678" t="n">
-        <v>0.07230399999999999</v>
+        <v>0.0723</v>
       </c>
       <c r="C678" t="n">
         <v>0.284264</v>
@@ -9241,7 +9241,7 @@
         </is>
       </c>
       <c r="B679" t="n">
-        <v>0.072839</v>
+        <v>0.072843</v>
       </c>
       <c r="C679" t="n">
         <v>0.281726</v>
@@ -9267,7 +9267,7 @@
         </is>
       </c>
       <c r="B681" t="n">
-        <v>0.07391200000000001</v>
+        <v>0.073911</v>
       </c>
       <c r="C681" t="n">
         <v>0.27665</v>
@@ -9280,7 +9280,7 @@
         </is>
       </c>
       <c r="B682" t="n">
-        <v>0.074473</v>
+        <v>0.074502</v>
       </c>
       <c r="C682" t="n">
         <v>0.274112</v>
@@ -9293,7 +9293,7 @@
         </is>
       </c>
       <c r="B683" t="n">
-        <v>0.07470400000000001</v>
+        <v>0.07470599999999999</v>
       </c>
       <c r="C683" t="n">
         <v>0.271574</v>
@@ -9306,7 +9306,7 @@
         </is>
       </c>
       <c r="B684" t="n">
-        <v>0.074916</v>
+        <v>0.074924</v>
       </c>
       <c r="C684" t="n">
         <v>0.269036</v>
@@ -9319,7 +9319,7 @@
         </is>
       </c>
       <c r="B685" t="n">
-        <v>0.075199</v>
+        <v>0.075193</v>
       </c>
       <c r="C685" t="n">
         <v>0.266497</v>
@@ -9332,7 +9332,7 @@
         </is>
       </c>
       <c r="B686" t="n">
-        <v>0.075471</v>
+        <v>0.07547</v>
       </c>
       <c r="C686" t="n">
         <v>0.263959</v>
@@ -9345,7 +9345,7 @@
         </is>
       </c>
       <c r="B687" t="n">
-        <v>0.075558</v>
+        <v>0.075553</v>
       </c>
       <c r="C687" t="n">
         <v>0.261421</v>
@@ -9358,7 +9358,7 @@
         </is>
       </c>
       <c r="B688" t="n">
-        <v>0.076393</v>
+        <v>0.076388</v>
       </c>
       <c r="C688" t="n">
         <v>0.258883</v>
@@ -9371,7 +9371,7 @@
         </is>
       </c>
       <c r="B689" t="n">
-        <v>0.078482</v>
+        <v>0.078573</v>
       </c>
       <c r="C689" t="n">
         <v>0.256345</v>
@@ -9397,7 +9397,7 @@
         </is>
       </c>
       <c r="B691" t="n">
-        <v>0.078916</v>
+        <v>0.07892299999999999</v>
       </c>
       <c r="C691" t="n">
         <v>0.251269</v>
@@ -9410,7 +9410,7 @@
         </is>
       </c>
       <c r="B692" t="n">
-        <v>0.079387</v>
+        <v>0.079388</v>
       </c>
       <c r="C692" t="n">
         <v>0.248731</v>
@@ -9423,7 +9423,7 @@
         </is>
       </c>
       <c r="B693" t="n">
-        <v>0.079745</v>
+        <v>0.07974199999999999</v>
       </c>
       <c r="C693" t="n">
         <v>0.246193</v>
@@ -9449,7 +9449,7 @@
         </is>
       </c>
       <c r="B695" t="n">
-        <v>0.080814</v>
+        <v>0.08083600000000001</v>
       </c>
       <c r="C695" t="n">
         <v>0.241117</v>
@@ -9462,7 +9462,7 @@
         </is>
       </c>
       <c r="B696" t="n">
-        <v>0.08167199999999999</v>
+        <v>0.081735</v>
       </c>
       <c r="C696" t="n">
         <v>0.238579</v>
@@ -9475,7 +9475,7 @@
         </is>
       </c>
       <c r="B697" t="n">
-        <v>0.08194700000000001</v>
+        <v>0.081951</v>
       </c>
       <c r="C697" t="n">
         <v>0.236041</v>
@@ -9488,7 +9488,7 @@
         </is>
       </c>
       <c r="B698" t="n">
-        <v>0.082467</v>
+        <v>0.082499</v>
       </c>
       <c r="C698" t="n">
         <v>0.233503</v>
@@ -9501,7 +9501,7 @@
         </is>
       </c>
       <c r="B699" t="n">
-        <v>0.083384</v>
+        <v>0.08337799999999999</v>
       </c>
       <c r="C699" t="n">
         <v>0.230964</v>
@@ -9514,7 +9514,7 @@
         </is>
       </c>
       <c r="B700" t="n">
-        <v>0.08358400000000001</v>
+        <v>0.083583</v>
       </c>
       <c r="C700" t="n">
         <v>0.228426</v>
@@ -9527,7 +9527,7 @@
         </is>
       </c>
       <c r="B701" t="n">
-        <v>0.08388</v>
+        <v>0.083938</v>
       </c>
       <c r="C701" t="n">
         <v>0.225888</v>
@@ -9540,7 +9540,7 @@
         </is>
       </c>
       <c r="B702" t="n">
-        <v>0.084398</v>
+        <v>0.084576</v>
       </c>
       <c r="C702" t="n">
         <v>0.22335</v>
@@ -9553,7 +9553,7 @@
         </is>
       </c>
       <c r="B703" t="n">
-        <v>0.08472</v>
+        <v>0.084719</v>
       </c>
       <c r="C703" t="n">
         <v>0.220812</v>
@@ -9566,7 +9566,7 @@
         </is>
       </c>
       <c r="B704" t="n">
-        <v>0.084755</v>
+        <v>0.08475100000000001</v>
       </c>
       <c r="C704" t="n">
         <v>0.218274</v>
@@ -9579,7 +9579,7 @@
         </is>
       </c>
       <c r="B705" t="n">
-        <v>0.08584799999999999</v>
+        <v>0.085843</v>
       </c>
       <c r="C705" t="n">
         <v>0.215736</v>
@@ -9592,7 +9592,7 @@
         </is>
       </c>
       <c r="B706" t="n">
-        <v>0.08654100000000001</v>
+        <v>0.086544</v>
       </c>
       <c r="C706" t="n">
         <v>0.213198</v>
@@ -9618,7 +9618,7 @@
         </is>
       </c>
       <c r="B708" t="n">
-        <v>0.088405</v>
+        <v>0.088437</v>
       </c>
       <c r="C708" t="n">
         <v>0.208122</v>
@@ -9631,7 +9631,7 @@
         </is>
       </c>
       <c r="B709" t="n">
-        <v>0.08878</v>
+        <v>0.08877699999999999</v>
       </c>
       <c r="C709" t="n">
         <v>0.205584</v>
@@ -9644,7 +9644,7 @@
         </is>
       </c>
       <c r="B710" t="n">
-        <v>0.088813</v>
+        <v>0.088814</v>
       </c>
       <c r="C710" t="n">
         <v>0.203046</v>
@@ -9657,7 +9657,7 @@
         </is>
       </c>
       <c r="B711" t="n">
-        <v>0.091626</v>
+        <v>0.09166000000000001</v>
       </c>
       <c r="C711" t="n">
         <v>0.200508</v>
@@ -9670,7 +9670,7 @@
         </is>
       </c>
       <c r="B712" t="n">
-        <v>0.09197</v>
+        <v>0.091963</v>
       </c>
       <c r="C712" t="n">
         <v>0.19797</v>
@@ -9683,7 +9683,7 @@
         </is>
       </c>
       <c r="B713" t="n">
-        <v>0.092641</v>
+        <v>0.092638</v>
       </c>
       <c r="C713" t="n">
         <v>0.195431</v>
@@ -9696,7 +9696,7 @@
         </is>
       </c>
       <c r="B714" t="n">
-        <v>0.092949</v>
+        <v>0.092974</v>
       </c>
       <c r="C714" t="n">
         <v>0.192893</v>
@@ -9709,7 +9709,7 @@
         </is>
       </c>
       <c r="B715" t="n">
-        <v>0.09314699999999999</v>
+        <v>0.09322800000000001</v>
       </c>
       <c r="C715" t="n">
         <v>0.190355</v>
@@ -9722,7 +9722,7 @@
         </is>
       </c>
       <c r="B716" t="n">
-        <v>0.095321</v>
+        <v>0.09531299999999999</v>
       </c>
       <c r="C716" t="n">
         <v>0.187817</v>
@@ -9735,7 +9735,7 @@
         </is>
       </c>
       <c r="B717" t="n">
-        <v>0.095959</v>
+        <v>0.095986</v>
       </c>
       <c r="C717" t="n">
         <v>0.185279</v>
@@ -9748,7 +9748,7 @@
         </is>
       </c>
       <c r="B718" t="n">
-        <v>0.096373</v>
+        <v>0.09646299999999999</v>
       </c>
       <c r="C718" t="n">
         <v>0.182741</v>
@@ -9761,7 +9761,7 @@
         </is>
       </c>
       <c r="B719" t="n">
-        <v>0.096426</v>
+        <v>0.096598</v>
       </c>
       <c r="C719" t="n">
         <v>0.180203</v>
@@ -9774,7 +9774,7 @@
         </is>
       </c>
       <c r="B720" t="n">
-        <v>0.096605</v>
+        <v>0.09664300000000001</v>
       </c>
       <c r="C720" t="n">
         <v>0.177665</v>
@@ -9787,7 +9787,7 @@
         </is>
       </c>
       <c r="B721" t="n">
-        <v>0.097092</v>
+        <v>0.09711500000000001</v>
       </c>
       <c r="C721" t="n">
         <v>0.175127</v>
@@ -9800,7 +9800,7 @@
         </is>
       </c>
       <c r="B722" t="n">
-        <v>0.09751899999999999</v>
+        <v>0.097513</v>
       </c>
       <c r="C722" t="n">
         <v>0.172589</v>
@@ -9813,7 +9813,7 @@
         </is>
       </c>
       <c r="B723" t="n">
-        <v>0.09888</v>
+        <v>0.09893299999999999</v>
       </c>
       <c r="C723" t="n">
         <v>0.170051</v>
@@ -9826,7 +9826,7 @@
         </is>
       </c>
       <c r="B724" t="n">
-        <v>0.100086</v>
+        <v>0.100096</v>
       </c>
       <c r="C724" t="n">
         <v>0.167513</v>
@@ -9839,7 +9839,7 @@
         </is>
       </c>
       <c r="B725" t="n">
-        <v>0.1002</v>
+        <v>0.100195</v>
       </c>
       <c r="C725" t="n">
         <v>0.164975</v>
@@ -9852,7 +9852,7 @@
         </is>
       </c>
       <c r="B726" t="n">
-        <v>0.100554</v>
+        <v>0.100556</v>
       </c>
       <c r="C726" t="n">
         <v>0.162437</v>
@@ -9865,7 +9865,7 @@
         </is>
       </c>
       <c r="B727" t="n">
-        <v>0.100806</v>
+        <v>0.10095</v>
       </c>
       <c r="C727" t="n">
         <v>0.159898</v>
@@ -9878,7 +9878,7 @@
         </is>
       </c>
       <c r="B728" t="n">
-        <v>0.101023</v>
+        <v>0.101015</v>
       </c>
       <c r="C728" t="n">
         <v>0.15736</v>
@@ -9891,7 +9891,7 @@
         </is>
       </c>
       <c r="B729" t="n">
-        <v>0.102149</v>
+        <v>0.102143</v>
       </c>
       <c r="C729" t="n">
         <v>0.154822</v>
@@ -9904,7 +9904,7 @@
         </is>
       </c>
       <c r="B730" t="n">
-        <v>0.102622</v>
+        <v>0.102633</v>
       </c>
       <c r="C730" t="n">
         <v>0.152284</v>
@@ -9917,7 +9917,7 @@
         </is>
       </c>
       <c r="B731" t="n">
-        <v>0.104264</v>
+        <v>0.104279</v>
       </c>
       <c r="C731" t="n">
         <v>0.149746</v>
@@ -9930,7 +9930,7 @@
         </is>
       </c>
       <c r="B732" t="n">
-        <v>0.109143</v>
+        <v>0.10914</v>
       </c>
       <c r="C732" t="n">
         <v>0.147208</v>
@@ -9943,7 +9943,7 @@
         </is>
       </c>
       <c r="B733" t="n">
-        <v>0.109404</v>
+        <v>0.109401</v>
       </c>
       <c r="C733" t="n">
         <v>0.14467</v>
@@ -9956,7 +9956,7 @@
         </is>
       </c>
       <c r="B734" t="n">
-        <v>0.109762</v>
+        <v>0.109768</v>
       </c>
       <c r="C734" t="n">
         <v>0.142132</v>
@@ -9969,7 +9969,7 @@
         </is>
       </c>
       <c r="B735" t="n">
-        <v>0.109952</v>
+        <v>0.10997</v>
       </c>
       <c r="C735" t="n">
         <v>0.139594</v>
@@ -9982,7 +9982,7 @@
         </is>
       </c>
       <c r="B736" t="n">
-        <v>0.110237</v>
+        <v>0.11023</v>
       </c>
       <c r="C736" t="n">
         <v>0.137056</v>
@@ -9995,7 +9995,7 @@
         </is>
       </c>
       <c r="B737" t="n">
-        <v>0.110819</v>
+        <v>0.11088</v>
       </c>
       <c r="C737" t="n">
         <v>0.134518</v>
@@ -10008,7 +10008,7 @@
         </is>
       </c>
       <c r="B738" t="n">
-        <v>0.114393</v>
+        <v>0.114411</v>
       </c>
       <c r="C738" t="n">
         <v>0.13198</v>
@@ -10021,7 +10021,7 @@
         </is>
       </c>
       <c r="B739" t="n">
-        <v>0.11559</v>
+        <v>0.115581</v>
       </c>
       <c r="C739" t="n">
         <v>0.129442</v>
@@ -10034,7 +10034,7 @@
         </is>
       </c>
       <c r="B740" t="n">
-        <v>0.117709</v>
+        <v>0.117714</v>
       </c>
       <c r="C740" t="n">
         <v>0.126904</v>
@@ -10047,7 +10047,7 @@
         </is>
       </c>
       <c r="B741" t="n">
-        <v>0.119532</v>
+        <v>0.119529</v>
       </c>
       <c r="C741" t="n">
         <v>0.124365</v>
@@ -10060,7 +10060,7 @@
         </is>
       </c>
       <c r="B742" t="n">
-        <v>0.120373</v>
+        <v>0.120364</v>
       </c>
       <c r="C742" t="n">
         <v>0.121827</v>
@@ -10073,7 +10073,7 @@
         </is>
       </c>
       <c r="B743" t="n">
-        <v>0.121819</v>
+        <v>0.121831</v>
       </c>
       <c r="C743" t="n">
         <v>0.119289</v>
@@ -10086,7 +10086,7 @@
         </is>
       </c>
       <c r="B744" t="n">
-        <v>0.12322</v>
+        <v>0.123212</v>
       </c>
       <c r="C744" t="n">
         <v>0.116751</v>
@@ -10099,7 +10099,7 @@
         </is>
       </c>
       <c r="B745" t="n">
-        <v>0.124747</v>
+        <v>0.124877</v>
       </c>
       <c r="C745" t="n">
         <v>0.114213</v>
@@ -10112,7 +10112,7 @@
         </is>
       </c>
       <c r="B746" t="n">
-        <v>0.125198</v>
+        <v>0.125206</v>
       </c>
       <c r="C746" t="n">
         <v>0.111675</v>
@@ -10125,7 +10125,7 @@
         </is>
       </c>
       <c r="B747" t="n">
-        <v>0.125839</v>
+        <v>0.125832</v>
       </c>
       <c r="C747" t="n">
         <v>0.109137</v>
@@ -10138,7 +10138,7 @@
         </is>
       </c>
       <c r="B748" t="n">
-        <v>0.126142</v>
+        <v>0.126143</v>
       </c>
       <c r="C748" t="n">
         <v>0.106599</v>
@@ -10151,7 +10151,7 @@
         </is>
       </c>
       <c r="B749" t="n">
-        <v>0.130816</v>
+        <v>0.130809</v>
       </c>
       <c r="C749" t="n">
         <v>0.104061</v>
@@ -10164,7 +10164,7 @@
         </is>
       </c>
       <c r="B750" t="n">
-        <v>0.131529</v>
+        <v>0.131534</v>
       </c>
       <c r="C750" t="n">
         <v>0.101523</v>
@@ -10177,7 +10177,7 @@
         </is>
       </c>
       <c r="B751" t="n">
-        <v>0.133028</v>
+        <v>0.133027</v>
       </c>
       <c r="C751" t="n">
         <v>0.098985</v>
@@ -10190,7 +10190,7 @@
         </is>
       </c>
       <c r="B752" t="n">
-        <v>0.136036</v>
+        <v>0.136031</v>
       </c>
       <c r="C752" t="n">
         <v>0.096447</v>
@@ -10203,7 +10203,7 @@
         </is>
       </c>
       <c r="B753" t="n">
-        <v>0.136375</v>
+        <v>0.136377</v>
       </c>
       <c r="C753" t="n">
         <v>0.09390900000000001</v>
@@ -10216,7 +10216,7 @@
         </is>
       </c>
       <c r="B754" t="n">
-        <v>0.136663</v>
+        <v>0.136657</v>
       </c>
       <c r="C754" t="n">
         <v>0.09137099999999999</v>
@@ -10229,7 +10229,7 @@
         </is>
       </c>
       <c r="B755" t="n">
-        <v>0.13729</v>
+        <v>0.137347</v>
       </c>
       <c r="C755" t="n">
         <v>0.08883199999999999</v>
@@ -10242,7 +10242,7 @@
         </is>
       </c>
       <c r="B756" t="n">
-        <v>0.140549</v>
+        <v>0.140633</v>
       </c>
       <c r="C756" t="n">
         <v>0.086294</v>
@@ -10255,7 +10255,7 @@
         </is>
       </c>
       <c r="B757" t="n">
-        <v>0.141191</v>
+        <v>0.14119</v>
       </c>
       <c r="C757" t="n">
         <v>0.083756</v>
@@ -10268,7 +10268,7 @@
         </is>
       </c>
       <c r="B758" t="n">
-        <v>0.142093</v>
+        <v>0.142085</v>
       </c>
       <c r="C758" t="n">
         <v>0.081218</v>
@@ -10281,7 +10281,7 @@
         </is>
       </c>
       <c r="B759" t="n">
-        <v>0.142878</v>
+        <v>0.14288</v>
       </c>
       <c r="C759" t="n">
         <v>0.07868</v>
@@ -10294,7 +10294,7 @@
         </is>
       </c>
       <c r="B760" t="n">
-        <v>0.14393</v>
+        <v>0.143946</v>
       </c>
       <c r="C760" t="n">
         <v>0.076142</v>
@@ -10307,7 +10307,7 @@
         </is>
       </c>
       <c r="B761" t="n">
-        <v>0.146313</v>
+        <v>0.146383</v>
       </c>
       <c r="C761" t="n">
         <v>0.073604</v>
@@ -10320,7 +10320,7 @@
         </is>
       </c>
       <c r="B762" t="n">
-        <v>0.153331</v>
+        <v>0.153326</v>
       </c>
       <c r="C762" t="n">
         <v>0.071066</v>
@@ -10333,7 +10333,7 @@
         </is>
       </c>
       <c r="B763" t="n">
-        <v>0.155832</v>
+        <v>0.155822</v>
       </c>
       <c r="C763" t="n">
         <v>0.06852800000000001</v>
@@ -10346,7 +10346,7 @@
         </is>
       </c>
       <c r="B764" t="n">
-        <v>0.159144</v>
+        <v>0.159132</v>
       </c>
       <c r="C764" t="n">
         <v>0.06598999999999999</v>
@@ -10359,7 +10359,7 @@
         </is>
       </c>
       <c r="B765" t="n">
-        <v>0.161132</v>
+        <v>0.161128</v>
       </c>
       <c r="C765" t="n">
         <v>0.06345199999999999</v>
@@ -10372,7 +10372,7 @@
         </is>
       </c>
       <c r="B766" t="n">
-        <v>0.161282</v>
+        <v>0.161328</v>
       </c>
       <c r="C766" t="n">
         <v>0.060914</v>
@@ -10385,7 +10385,7 @@
         </is>
       </c>
       <c r="B767" t="n">
-        <v>0.171001</v>
+        <v>0.171011</v>
       </c>
       <c r="C767" t="n">
         <v>0.058376</v>
@@ -10398,7 +10398,7 @@
         </is>
       </c>
       <c r="B768" t="n">
-        <v>0.176689</v>
+        <v>0.176735</v>
       </c>
       <c r="C768" t="n">
         <v>0.055838</v>
@@ -10411,7 +10411,7 @@
         </is>
       </c>
       <c r="B769" t="n">
-        <v>0.18016</v>
+        <v>0.180146</v>
       </c>
       <c r="C769" t="n">
         <v>0.053299</v>
@@ -10424,7 +10424,7 @@
         </is>
       </c>
       <c r="B770" t="n">
-        <v>0.18214</v>
+        <v>0.182164</v>
       </c>
       <c r="C770" t="n">
         <v>0.050761</v>
@@ -10437,7 +10437,7 @@
         </is>
       </c>
       <c r="B771" t="n">
-        <v>0.18322</v>
+        <v>0.183245</v>
       </c>
       <c r="C771" t="n">
         <v>0.048223</v>
@@ -10450,7 +10450,7 @@
         </is>
       </c>
       <c r="B772" t="n">
-        <v>0.183821</v>
+        <v>0.184192</v>
       </c>
       <c r="C772" t="n">
         <v>0.045685</v>
@@ -10463,7 +10463,7 @@
         </is>
       </c>
       <c r="B773" t="n">
-        <v>0.187537</v>
+        <v>0.187522</v>
       </c>
       <c r="C773" t="n">
         <v>0.043147</v>
@@ -10476,7 +10476,7 @@
         </is>
       </c>
       <c r="B774" t="n">
-        <v>0.187818</v>
+        <v>0.1879</v>
       </c>
       <c r="C774" t="n">
         <v>0.040609</v>
@@ -10489,7 +10489,7 @@
         </is>
       </c>
       <c r="B775" t="n">
-        <v>0.188479</v>
+        <v>0.188467</v>
       </c>
       <c r="C775" t="n">
         <v>0.038071</v>
@@ -10502,7 +10502,7 @@
         </is>
       </c>
       <c r="B776" t="n">
-        <v>0.189068</v>
+        <v>0.189223</v>
       </c>
       <c r="C776" t="n">
         <v>0.035533</v>
@@ -10515,7 +10515,7 @@
         </is>
       </c>
       <c r="B777" t="n">
-        <v>0.198512</v>
+        <v>0.198508</v>
       </c>
       <c r="C777" t="n">
         <v>0.032995</v>
@@ -10528,7 +10528,7 @@
         </is>
       </c>
       <c r="B778" t="n">
-        <v>0.199406</v>
+        <v>0.199544</v>
       </c>
       <c r="C778" t="n">
         <v>0.030457</v>
@@ -10541,7 +10541,7 @@
         </is>
       </c>
       <c r="B779" t="n">
-        <v>0.207827</v>
+        <v>0.207823</v>
       </c>
       <c r="C779" t="n">
         <v>0.027919</v>
@@ -10554,7 +10554,7 @@
         </is>
       </c>
       <c r="B780" t="n">
-        <v>0.247202</v>
+        <v>0.247184</v>
       </c>
       <c r="C780" t="n">
         <v>0.025381</v>
@@ -10567,7 +10567,7 @@
         </is>
       </c>
       <c r="B781" t="n">
-        <v>0.247202</v>
+        <v>0.247336</v>
       </c>
       <c r="C781" t="n">
         <v>0.022843</v>
@@ -10580,7 +10580,7 @@
         </is>
       </c>
       <c r="B782" t="n">
-        <v>0.263604</v>
+        <v>0.263887</v>
       </c>
       <c r="C782" t="n">
         <v>0.020305</v>
@@ -10593,7 +10593,7 @@
         </is>
       </c>
       <c r="B783" t="n">
-        <v>0.266966</v>
+        <v>0.267257</v>
       </c>
       <c r="C783" t="n">
         <v>0.017766</v>
@@ -10606,7 +10606,7 @@
         </is>
       </c>
       <c r="B784" t="n">
-        <v>0.270696</v>
+        <v>0.271167</v>
       </c>
       <c r="C784" t="n">
         <v>0.015228</v>
@@ -10619,7 +10619,7 @@
         </is>
       </c>
       <c r="B785" t="n">
-        <v>0.27628</v>
+        <v>0.27639</v>
       </c>
       <c r="C785" t="n">
         <v>0.01269</v>
@@ -10632,7 +10632,7 @@
         </is>
       </c>
       <c r="B786" t="n">
-        <v>0.334027</v>
+        <v>0.334312</v>
       </c>
       <c r="C786" t="n">
         <v>0.010152</v>
@@ -10645,7 +10645,7 @@
         </is>
       </c>
       <c r="B787" t="n">
-        <v>0.349304</v>
+        <v>0.349364</v>
       </c>
       <c r="C787" t="n">
         <v>0.007614</v>
@@ -10658,7 +10658,7 @@
         </is>
       </c>
       <c r="B788" t="n">
-        <v>0.362633</v>
+        <v>0.362846</v>
       </c>
       <c r="C788" t="n">
         <v>0.005076</v>
@@ -10671,7 +10671,7 @@
         </is>
       </c>
       <c r="B789" t="n">
-        <v>0.507092</v>
+        <v>0.507274</v>
       </c>
       <c r="C789" t="n">
         <v>0.002538</v>

--- a/vignettes/vignette-1/tail_exceedance_plot_data.xlsx
+++ b/vignettes/vignette-1/tail_exceedance_plot_data.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C789"/>
+  <dimension ref="A1:C779"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -456,7 +456,7 @@
         <v>0.000441</v>
       </c>
       <c r="C3" t="n">
-        <v>0.997462</v>
+        <v>0.997429</v>
       </c>
     </row>
     <row r="4">
@@ -469,7 +469,7 @@
         <v>0.000608</v>
       </c>
       <c r="C4" t="n">
-        <v>0.994924</v>
+        <v>0.994859</v>
       </c>
     </row>
     <row r="5">
@@ -482,7 +482,7 @@
         <v>0.001141</v>
       </c>
       <c r="C5" t="n">
-        <v>0.992386</v>
+        <v>0.9922879999999999</v>
       </c>
     </row>
     <row r="6">
@@ -495,7 +495,7 @@
         <v>0.001163</v>
       </c>
       <c r="C6" t="n">
-        <v>0.989848</v>
+        <v>0.989717</v>
       </c>
     </row>
     <row r="7">
@@ -508,7 +508,7 @@
         <v>0.001681</v>
       </c>
       <c r="C7" t="n">
-        <v>0.98731</v>
+        <v>0.987147</v>
       </c>
     </row>
     <row r="8">
@@ -521,7 +521,7 @@
         <v>0.002113</v>
       </c>
       <c r="C8" t="n">
-        <v>0.984772</v>
+        <v>0.984576</v>
       </c>
     </row>
     <row r="9">
@@ -534,7 +534,7 @@
         <v>0.002155</v>
       </c>
       <c r="C9" t="n">
-        <v>0.9822340000000001</v>
+        <v>0.982005</v>
       </c>
     </row>
     <row r="10">
@@ -547,7 +547,7 @@
         <v>0.002259</v>
       </c>
       <c r="C10" t="n">
-        <v>0.979695</v>
+        <v>0.979434</v>
       </c>
     </row>
     <row r="11">
@@ -560,7 +560,7 @@
         <v>0.00295</v>
       </c>
       <c r="C11" t="n">
-        <v>0.9771570000000001</v>
+        <v>0.976864</v>
       </c>
     </row>
     <row r="12">
@@ -573,7 +573,7 @@
         <v>0.002998</v>
       </c>
       <c r="C12" t="n">
-        <v>0.974619</v>
+        <v>0.974293</v>
       </c>
     </row>
     <row r="13">
@@ -586,7 +586,7 @@
         <v>0.003455</v>
       </c>
       <c r="C13" t="n">
-        <v>0.972081</v>
+        <v>0.971722</v>
       </c>
     </row>
     <row r="14">
@@ -599,7 +599,7 @@
         <v>0.003769</v>
       </c>
       <c r="C14" t="n">
-        <v>0.969543</v>
+        <v>0.969152</v>
       </c>
     </row>
     <row r="15">
@@ -612,7 +612,7 @@
         <v>0.003788</v>
       </c>
       <c r="C15" t="n">
-        <v>0.967005</v>
+        <v>0.966581</v>
       </c>
     </row>
     <row r="16">
@@ -625,7 +625,7 @@
         <v>0.003948</v>
       </c>
       <c r="C16" t="n">
-        <v>0.964467</v>
+        <v>0.96401</v>
       </c>
     </row>
     <row r="17">
@@ -638,7 +638,7 @@
         <v>0.004039</v>
       </c>
       <c r="C17" t="n">
-        <v>0.961929</v>
+        <v>0.96144</v>
       </c>
     </row>
     <row r="18">
@@ -651,7 +651,7 @@
         <v>0.004622</v>
       </c>
       <c r="C18" t="n">
-        <v>0.959391</v>
+        <v>0.958869</v>
       </c>
     </row>
     <row r="19">
@@ -664,7 +664,7 @@
         <v>0.004717</v>
       </c>
       <c r="C19" t="n">
-        <v>0.956853</v>
+        <v>0.956298</v>
       </c>
     </row>
     <row r="20">
@@ -677,7 +677,7 @@
         <v>0.004779</v>
       </c>
       <c r="C20" t="n">
-        <v>0.954315</v>
+        <v>0.953728</v>
       </c>
     </row>
     <row r="21">
@@ -690,7 +690,7 @@
         <v>0.004912</v>
       </c>
       <c r="C21" t="n">
-        <v>0.951777</v>
+        <v>0.951157</v>
       </c>
     </row>
     <row r="22">
@@ -703,7 +703,7 @@
         <v>0.005429</v>
       </c>
       <c r="C22" t="n">
-        <v>0.9492390000000001</v>
+        <v>0.948586</v>
       </c>
     </row>
     <row r="23">
@@ -716,7 +716,7 @@
         <v>0.005649</v>
       </c>
       <c r="C23" t="n">
-        <v>0.946701</v>
+        <v>0.9460150000000001</v>
       </c>
     </row>
     <row r="24">
@@ -729,7 +729,7 @@
         <v>0.00593</v>
       </c>
       <c r="C24" t="n">
-        <v>0.9441619999999999</v>
+        <v>0.943445</v>
       </c>
     </row>
     <row r="25">
@@ -742,7 +742,7 @@
         <v>0.006143</v>
       </c>
       <c r="C25" t="n">
-        <v>0.941624</v>
+        <v>0.940874</v>
       </c>
     </row>
     <row r="26">
@@ -755,7 +755,7 @@
         <v>0.006328</v>
       </c>
       <c r="C26" t="n">
-        <v>0.939086</v>
+        <v>0.938303</v>
       </c>
     </row>
     <row r="27">
@@ -768,7 +768,7 @@
         <v>0.006394</v>
       </c>
       <c r="C27" t="n">
-        <v>0.936548</v>
+        <v>0.935733</v>
       </c>
     </row>
     <row r="28">
@@ -781,7 +781,7 @@
         <v>0.007419</v>
       </c>
       <c r="C28" t="n">
-        <v>0.93401</v>
+        <v>0.933162</v>
       </c>
     </row>
     <row r="29">
@@ -794,7 +794,7 @@
         <v>0.007582</v>
       </c>
       <c r="C29" t="n">
-        <v>0.931472</v>
+        <v>0.9305909999999999</v>
       </c>
     </row>
     <row r="30">
@@ -807,7 +807,7 @@
         <v>0.008029</v>
       </c>
       <c r="C30" t="n">
-        <v>0.928934</v>
+        <v>0.928021</v>
       </c>
     </row>
     <row r="31">
@@ -820,7 +820,7 @@
         <v>0.008069</v>
       </c>
       <c r="C31" t="n">
-        <v>0.926396</v>
+        <v>0.92545</v>
       </c>
     </row>
     <row r="32">
@@ -833,7 +833,7 @@
         <v>0.008173</v>
       </c>
       <c r="C32" t="n">
-        <v>0.923858</v>
+        <v>0.922879</v>
       </c>
     </row>
     <row r="33">
@@ -846,7 +846,7 @@
         <v>0.008333999999999999</v>
       </c>
       <c r="C33" t="n">
-        <v>0.92132</v>
+        <v>0.920308</v>
       </c>
     </row>
     <row r="34">
@@ -859,7 +859,7 @@
         <v>0.008544</v>
       </c>
       <c r="C34" t="n">
-        <v>0.918782</v>
+        <v>0.9177380000000001</v>
       </c>
     </row>
     <row r="35">
@@ -872,7 +872,7 @@
         <v>0.008593999999999999</v>
       </c>
       <c r="C35" t="n">
-        <v>0.9162439999999999</v>
+        <v>0.915167</v>
       </c>
     </row>
     <row r="36">
@@ -885,7 +885,7 @@
         <v>0.009011</v>
       </c>
       <c r="C36" t="n">
-        <v>0.913706</v>
+        <v>0.912596</v>
       </c>
     </row>
     <row r="37">
@@ -898,7 +898,7 @@
         <v>0.009165</v>
       </c>
       <c r="C37" t="n">
-        <v>0.911168</v>
+        <v>0.910026</v>
       </c>
     </row>
     <row r="38">
@@ -911,7 +911,7 @@
         <v>0.009428000000000001</v>
       </c>
       <c r="C38" t="n">
-        <v>0.908629</v>
+        <v>0.907455</v>
       </c>
     </row>
     <row r="39">
@@ -924,7 +924,7 @@
         <v>0.009578</v>
       </c>
       <c r="C39" t="n">
-        <v>0.906091</v>
+        <v>0.904884</v>
       </c>
     </row>
     <row r="40">
@@ -937,7 +937,7 @@
         <v>0.009774</v>
       </c>
       <c r="C40" t="n">
-        <v>0.9035530000000001</v>
+        <v>0.9023139999999999</v>
       </c>
     </row>
     <row r="41">
@@ -950,7 +950,7 @@
         <v>0.009811</v>
       </c>
       <c r="C41" t="n">
-        <v>0.901015</v>
+        <v>0.899743</v>
       </c>
     </row>
     <row r="42">
@@ -963,7 +963,7 @@
         <v>0.010226</v>
       </c>
       <c r="C42" t="n">
-        <v>0.898477</v>
+        <v>0.897172</v>
       </c>
     </row>
     <row r="43">
@@ -976,7 +976,7 @@
         <v>0.010518</v>
       </c>
       <c r="C43" t="n">
-        <v>0.895939</v>
+        <v>0.894602</v>
       </c>
     </row>
     <row r="44">
@@ -989,7 +989,7 @@
         <v>0.010943</v>
       </c>
       <c r="C44" t="n">
-        <v>0.893401</v>
+        <v>0.892031</v>
       </c>
     </row>
     <row r="45">
@@ -1002,7 +1002,7 @@
         <v>0.011156</v>
       </c>
       <c r="C45" t="n">
-        <v>0.890863</v>
+        <v>0.88946</v>
       </c>
     </row>
     <row r="46">
@@ -1015,7 +1015,7 @@
         <v>0.01117</v>
       </c>
       <c r="C46" t="n">
-        <v>0.888325</v>
+        <v>0.886889</v>
       </c>
     </row>
     <row r="47">
@@ -1028,7 +1028,7 @@
         <v>0.011326</v>
       </c>
       <c r="C47" t="n">
-        <v>0.885787</v>
+        <v>0.884319</v>
       </c>
     </row>
     <row r="48">
@@ -1041,7 +1041,7 @@
         <v>0.01145</v>
       </c>
       <c r="C48" t="n">
-        <v>0.883249</v>
+        <v>0.881748</v>
       </c>
     </row>
     <row r="49">
@@ -1054,7 +1054,7 @@
         <v>0.011715</v>
       </c>
       <c r="C49" t="n">
-        <v>0.880711</v>
+        <v>0.879177</v>
       </c>
     </row>
     <row r="50">
@@ -1067,7 +1067,7 @@
         <v>0.011815</v>
       </c>
       <c r="C50" t="n">
-        <v>0.878173</v>
+        <v>0.876607</v>
       </c>
     </row>
     <row r="51">
@@ -1080,7 +1080,7 @@
         <v>0.012035</v>
       </c>
       <c r="C51" t="n">
-        <v>0.8756350000000001</v>
+        <v>0.874036</v>
       </c>
     </row>
     <row r="52">
@@ -1093,7 +1093,7 @@
         <v>0.012336</v>
       </c>
       <c r="C52" t="n">
-        <v>0.873096</v>
+        <v>0.871465</v>
       </c>
     </row>
     <row r="53">
@@ -1106,7 +1106,7 @@
         <v>0.012459</v>
       </c>
       <c r="C53" t="n">
-        <v>0.8705580000000001</v>
+        <v>0.868895</v>
       </c>
     </row>
     <row r="54">
@@ -1119,7 +1119,7 @@
         <v>0.012747</v>
       </c>
       <c r="C54" t="n">
-        <v>0.86802</v>
+        <v>0.866324</v>
       </c>
     </row>
     <row r="55">
@@ -1132,7 +1132,7 @@
         <v>0.012918</v>
       </c>
       <c r="C55" t="n">
-        <v>0.865482</v>
+        <v>0.863753</v>
       </c>
     </row>
     <row r="56">
@@ -1145,7 +1145,7 @@
         <v>0.013202</v>
       </c>
       <c r="C56" t="n">
-        <v>0.862944</v>
+        <v>0.861183</v>
       </c>
     </row>
     <row r="57">
@@ -1158,7 +1158,7 @@
         <v>0.013714</v>
       </c>
       <c r="C57" t="n">
-        <v>0.860406</v>
+        <v>0.858612</v>
       </c>
     </row>
     <row r="58">
@@ -1171,7 +1171,7 @@
         <v>0.01393</v>
       </c>
       <c r="C58" t="n">
-        <v>0.857868</v>
+        <v>0.8560410000000001</v>
       </c>
     </row>
     <row r="59">
@@ -1184,7 +1184,7 @@
         <v>0.013971</v>
       </c>
       <c r="C59" t="n">
-        <v>0.85533</v>
+        <v>0.85347</v>
       </c>
     </row>
     <row r="60">
@@ -1197,7 +1197,7 @@
         <v>0.014018</v>
       </c>
       <c r="C60" t="n">
-        <v>0.852792</v>
+        <v>0.8509</v>
       </c>
     </row>
     <row r="61">
@@ -1210,7 +1210,7 @@
         <v>0.01417</v>
       </c>
       <c r="C61" t="n">
-        <v>0.850254</v>
+        <v>0.848329</v>
       </c>
     </row>
     <row r="62">
@@ -1223,7 +1223,7 @@
         <v>0.014481</v>
       </c>
       <c r="C62" t="n">
-        <v>0.847716</v>
+        <v>0.845758</v>
       </c>
     </row>
     <row r="63">
@@ -1236,7 +1236,7 @@
         <v>0.014731</v>
       </c>
       <c r="C63" t="n">
-        <v>0.845178</v>
+        <v>0.843188</v>
       </c>
     </row>
     <row r="64">
@@ -1249,7 +1249,7 @@
         <v>0.014841</v>
       </c>
       <c r="C64" t="n">
-        <v>0.8426399999999999</v>
+        <v>0.8406169999999999</v>
       </c>
     </row>
     <row r="65">
@@ -1262,7 +1262,7 @@
         <v>0.015041</v>
       </c>
       <c r="C65" t="n">
-        <v>0.840102</v>
+        <v>0.838046</v>
       </c>
     </row>
     <row r="66">
@@ -1275,7 +1275,7 @@
         <v>0.015107</v>
       </c>
       <c r="C66" t="n">
-        <v>0.8375629999999999</v>
+        <v>0.835476</v>
       </c>
     </row>
     <row r="67">
@@ -1288,7 +1288,7 @@
         <v>0.015107</v>
       </c>
       <c r="C67" t="n">
-        <v>0.835025</v>
+        <v>0.832905</v>
       </c>
     </row>
     <row r="68">
@@ -1301,7 +1301,7 @@
         <v>0.015553</v>
       </c>
       <c r="C68" t="n">
-        <v>0.832487</v>
+        <v>0.830334</v>
       </c>
     </row>
     <row r="69">
@@ -1314,7 +1314,7 @@
         <v>0.016031</v>
       </c>
       <c r="C69" t="n">
-        <v>0.829949</v>
+        <v>0.827763</v>
       </c>
     </row>
     <row r="70">
@@ -1327,7 +1327,7 @@
         <v>0.016343</v>
       </c>
       <c r="C70" t="n">
-        <v>0.827411</v>
+        <v>0.825193</v>
       </c>
     </row>
     <row r="71">
@@ -1340,7 +1340,7 @@
         <v>0.016345</v>
       </c>
       <c r="C71" t="n">
-        <v>0.824873</v>
+        <v>0.822622</v>
       </c>
     </row>
     <row r="72">
@@ -1353,7 +1353,7 @@
         <v>0.016545</v>
       </c>
       <c r="C72" t="n">
-        <v>0.822335</v>
+        <v>0.820051</v>
       </c>
     </row>
     <row r="73">
@@ -1366,7 +1366,7 @@
         <v>0.017135</v>
       </c>
       <c r="C73" t="n">
-        <v>0.819797</v>
+        <v>0.817481</v>
       </c>
     </row>
     <row r="74">
@@ -1379,7 +1379,7 @@
         <v>0.017276</v>
       </c>
       <c r="C74" t="n">
-        <v>0.817259</v>
+        <v>0.81491</v>
       </c>
     </row>
     <row r="75">
@@ -1392,7 +1392,7 @@
         <v>0.017537</v>
       </c>
       <c r="C75" t="n">
-        <v>0.814721</v>
+        <v>0.812339</v>
       </c>
     </row>
     <row r="76">
@@ -1405,7 +1405,7 @@
         <v>0.017621</v>
       </c>
       <c r="C76" t="n">
-        <v>0.812183</v>
+        <v>0.809769</v>
       </c>
     </row>
     <row r="77">
@@ -1418,7 +1418,7 @@
         <v>0.017975</v>
       </c>
       <c r="C77" t="n">
-        <v>0.8096449999999999</v>
+        <v>0.807198</v>
       </c>
     </row>
     <row r="78">
@@ -1431,7 +1431,7 @@
         <v>0.018225</v>
       </c>
       <c r="C78" t="n">
-        <v>0.807107</v>
+        <v>0.804627</v>
       </c>
     </row>
     <row r="79">
@@ -1444,7 +1444,7 @@
         <v>0.018505</v>
       </c>
       <c r="C79" t="n">
-        <v>0.804569</v>
+        <v>0.802057</v>
       </c>
     </row>
     <row r="80">
@@ -1457,7 +1457,7 @@
         <v>0.018757</v>
       </c>
       <c r="C80" t="n">
-        <v>0.80203</v>
+        <v>0.799486</v>
       </c>
     </row>
     <row r="81">
@@ -1470,7 +1470,7 @@
         <v>0.018801</v>
       </c>
       <c r="C81" t="n">
-        <v>0.799492</v>
+        <v>0.796915</v>
       </c>
     </row>
     <row r="82">
@@ -1483,7 +1483,7 @@
         <v>0.018847</v>
       </c>
       <c r="C82" t="n">
-        <v>0.7969540000000001</v>
+        <v>0.7943440000000001</v>
       </c>
     </row>
     <row r="83">
@@ -1496,7 +1496,7 @@
         <v>0.018931</v>
       </c>
       <c r="C83" t="n">
-        <v>0.794416</v>
+        <v>0.791774</v>
       </c>
     </row>
     <row r="84">
@@ -1509,7 +1509,7 @@
         <v>0.019049</v>
       </c>
       <c r="C84" t="n">
-        <v>0.791878</v>
+        <v>0.789203</v>
       </c>
     </row>
     <row r="85">
@@ -1522,7 +1522,7 @@
         <v>0.019288</v>
       </c>
       <c r="C85" t="n">
-        <v>0.78934</v>
+        <v>0.786632</v>
       </c>
     </row>
     <row r="86">
@@ -1535,7 +1535,7 @@
         <v>0.019352</v>
       </c>
       <c r="C86" t="n">
-        <v>0.786802</v>
+        <v>0.784062</v>
       </c>
     </row>
     <row r="87">
@@ -1548,7 +1548,7 @@
         <v>0.01962</v>
       </c>
       <c r="C87" t="n">
-        <v>0.784264</v>
+        <v>0.781491</v>
       </c>
     </row>
     <row r="88">
@@ -1561,7 +1561,7 @@
         <v>0.019953</v>
       </c>
       <c r="C88" t="n">
-        <v>0.781726</v>
+        <v>0.7789199999999999</v>
       </c>
     </row>
     <row r="89">
@@ -1574,7 +1574,7 @@
         <v>0.020186</v>
       </c>
       <c r="C89" t="n">
-        <v>0.779188</v>
+        <v>0.77635</v>
       </c>
     </row>
     <row r="90">
@@ -1587,7 +1587,7 @@
         <v>0.020393</v>
       </c>
       <c r="C90" t="n">
-        <v>0.77665</v>
+        <v>0.773779</v>
       </c>
     </row>
     <row r="91">
@@ -1600,7 +1600,7 @@
         <v>0.02048</v>
       </c>
       <c r="C91" t="n">
-        <v>0.774112</v>
+        <v>0.771208</v>
       </c>
     </row>
     <row r="92">
@@ -1613,7 +1613,7 @@
         <v>0.021399</v>
       </c>
       <c r="C92" t="n">
-        <v>0.771574</v>
+        <v>0.768638</v>
       </c>
     </row>
     <row r="93">
@@ -1626,7 +1626,7 @@
         <v>0.021572</v>
       </c>
       <c r="C93" t="n">
-        <v>0.7690360000000001</v>
+        <v>0.7660670000000001</v>
       </c>
     </row>
     <row r="94">
@@ -1639,7 +1639,7 @@
         <v>0.021604</v>
       </c>
       <c r="C94" t="n">
-        <v>0.766497</v>
+        <v>0.763496</v>
       </c>
     </row>
     <row r="95">
@@ -1652,7 +1652,7 @@
         <v>0.021912</v>
       </c>
       <c r="C95" t="n">
-        <v>0.7639590000000001</v>
+        <v>0.760925</v>
       </c>
     </row>
     <row r="96">
@@ -1665,7 +1665,7 @@
         <v>0.021918</v>
       </c>
       <c r="C96" t="n">
-        <v>0.761421</v>
+        <v>0.758355</v>
       </c>
     </row>
     <row r="97">
@@ -1678,7 +1678,7 @@
         <v>0.021962</v>
       </c>
       <c r="C97" t="n">
-        <v>0.758883</v>
+        <v>0.755784</v>
       </c>
     </row>
     <row r="98">
@@ -1691,7 +1691,7 @@
         <v>0.022008</v>
       </c>
       <c r="C98" t="n">
-        <v>0.756345</v>
+        <v>0.753213</v>
       </c>
     </row>
     <row r="99">
@@ -1704,7 +1704,7 @@
         <v>0.022011</v>
       </c>
       <c r="C99" t="n">
-        <v>0.753807</v>
+        <v>0.7506429999999999</v>
       </c>
     </row>
     <row r="100">
@@ -1717,7 +1717,7 @@
         <v>0.022299</v>
       </c>
       <c r="C100" t="n">
-        <v>0.751269</v>
+        <v>0.748072</v>
       </c>
     </row>
     <row r="101">
@@ -1730,7 +1730,7 @@
         <v>0.022324</v>
       </c>
       <c r="C101" t="n">
-        <v>0.748731</v>
+        <v>0.745501</v>
       </c>
     </row>
     <row r="102">
@@ -1743,7 +1743,7 @@
         <v>0.022543</v>
       </c>
       <c r="C102" t="n">
-        <v>0.746193</v>
+        <v>0.742931</v>
       </c>
     </row>
     <row r="103">
@@ -1756,7 +1756,7 @@
         <v>0.022891</v>
       </c>
       <c r="C103" t="n">
-        <v>0.743655</v>
+        <v>0.74036</v>
       </c>
     </row>
     <row r="104">
@@ -1769,7 +1769,7 @@
         <v>0.02306</v>
       </c>
       <c r="C104" t="n">
-        <v>0.741117</v>
+        <v>0.737789</v>
       </c>
     </row>
     <row r="105">
@@ -1782,7 +1782,7 @@
         <v>0.023483</v>
       </c>
       <c r="C105" t="n">
-        <v>0.738579</v>
+        <v>0.735219</v>
       </c>
     </row>
     <row r="106">
@@ -1795,7 +1795,7 @@
         <v>0.023676</v>
       </c>
       <c r="C106" t="n">
-        <v>0.7360409999999999</v>
+        <v>0.732648</v>
       </c>
     </row>
     <row r="107">
@@ -1808,7 +1808,7 @@
         <v>0.023901</v>
       </c>
       <c r="C107" t="n">
-        <v>0.733503</v>
+        <v>0.730077</v>
       </c>
     </row>
     <row r="108">
@@ -1821,7 +1821,7 @@
         <v>0.023991</v>
       </c>
       <c r="C108" t="n">
-        <v>0.7309639999999999</v>
+        <v>0.727506</v>
       </c>
     </row>
     <row r="109">
@@ -1834,7 +1834,7 @@
         <v>0.02408</v>
       </c>
       <c r="C109" t="n">
-        <v>0.728426</v>
+        <v>0.724936</v>
       </c>
     </row>
     <row r="110">
@@ -1847,7 +1847,7 @@
         <v>0.024413</v>
       </c>
       <c r="C110" t="n">
-        <v>0.725888</v>
+        <v>0.722365</v>
       </c>
     </row>
     <row r="111">
@@ -1860,7 +1860,7 @@
         <v>0.024763</v>
       </c>
       <c r="C111" t="n">
-        <v>0.72335</v>
+        <v>0.719794</v>
       </c>
     </row>
     <row r="112">
@@ -1873,7 +1873,7 @@
         <v>0.024837</v>
       </c>
       <c r="C112" t="n">
-        <v>0.720812</v>
+        <v>0.717224</v>
       </c>
     </row>
     <row r="113">
@@ -1886,7 +1886,7 @@
         <v>0.024896</v>
       </c>
       <c r="C113" t="n">
-        <v>0.718274</v>
+        <v>0.714653</v>
       </c>
     </row>
     <row r="114">
@@ -1899,7 +1899,7 @@
         <v>0.025416</v>
       </c>
       <c r="C114" t="n">
-        <v>0.715736</v>
+        <v>0.712082</v>
       </c>
     </row>
     <row r="115">
@@ -1912,7 +1912,7 @@
         <v>0.025755</v>
       </c>
       <c r="C115" t="n">
-        <v>0.713198</v>
+        <v>0.709512</v>
       </c>
     </row>
     <row r="116">
@@ -1925,7 +1925,7 @@
         <v>0.026032</v>
       </c>
       <c r="C116" t="n">
-        <v>0.71066</v>
+        <v>0.706941</v>
       </c>
     </row>
     <row r="117">
@@ -1938,7 +1938,7 @@
         <v>0.026545</v>
       </c>
       <c r="C117" t="n">
-        <v>0.708122</v>
+        <v>0.7043700000000001</v>
       </c>
     </row>
     <row r="118">
@@ -1951,7 +1951,7 @@
         <v>0.026628</v>
       </c>
       <c r="C118" t="n">
-        <v>0.705584</v>
+        <v>0.701799</v>
       </c>
     </row>
     <row r="119">
@@ -1964,7 +1964,7 @@
         <v>0.027214</v>
       </c>
       <c r="C119" t="n">
-        <v>0.7030459999999999</v>
+        <v>0.699229</v>
       </c>
     </row>
     <row r="120">
@@ -1977,7 +1977,7 @@
         <v>0.027321</v>
       </c>
       <c r="C120" t="n">
-        <v>0.700508</v>
+        <v>0.696658</v>
       </c>
     </row>
     <row r="121">
@@ -1990,7 +1990,7 @@
         <v>0.027355</v>
       </c>
       <c r="C121" t="n">
-        <v>0.69797</v>
+        <v>0.694087</v>
       </c>
     </row>
     <row r="122">
@@ -2003,7 +2003,7 @@
         <v>0.027413</v>
       </c>
       <c r="C122" t="n">
-        <v>0.695431</v>
+        <v>0.691517</v>
       </c>
     </row>
     <row r="123">
@@ -2016,7 +2016,7 @@
         <v>0.027528</v>
       </c>
       <c r="C123" t="n">
-        <v>0.692893</v>
+        <v>0.6889459999999999</v>
       </c>
     </row>
     <row r="124">
@@ -2026,10 +2026,10 @@
         </is>
       </c>
       <c r="B124" t="n">
-        <v>0.027692</v>
+        <v>0.027943</v>
       </c>
       <c r="C124" t="n">
-        <v>0.6903550000000001</v>
+        <v>0.686375</v>
       </c>
     </row>
     <row r="125">
@@ -2039,10 +2039,10 @@
         </is>
       </c>
       <c r="B125" t="n">
-        <v>0.027943</v>
+        <v>0.028098</v>
       </c>
       <c r="C125" t="n">
-        <v>0.687817</v>
+        <v>0.683805</v>
       </c>
     </row>
     <row r="126">
@@ -2052,10 +2052,10 @@
         </is>
       </c>
       <c r="B126" t="n">
-        <v>0.028098</v>
+        <v>0.028186</v>
       </c>
       <c r="C126" t="n">
-        <v>0.685279</v>
+        <v>0.681234</v>
       </c>
     </row>
     <row r="127">
@@ -2065,10 +2065,10 @@
         </is>
       </c>
       <c r="B127" t="n">
-        <v>0.028186</v>
+        <v>0.028375</v>
       </c>
       <c r="C127" t="n">
-        <v>0.682741</v>
+        <v>0.678663</v>
       </c>
     </row>
     <row r="128">
@@ -2078,10 +2078,10 @@
         </is>
       </c>
       <c r="B128" t="n">
-        <v>0.028375</v>
+        <v>0.028398</v>
       </c>
       <c r="C128" t="n">
-        <v>0.680203</v>
+        <v>0.6760930000000001</v>
       </c>
     </row>
     <row r="129">
@@ -2091,10 +2091,10 @@
         </is>
       </c>
       <c r="B129" t="n">
-        <v>0.028398</v>
+        <v>0.029046</v>
       </c>
       <c r="C129" t="n">
-        <v>0.677665</v>
+        <v>0.673522</v>
       </c>
     </row>
     <row r="130">
@@ -2104,10 +2104,10 @@
         </is>
       </c>
       <c r="B130" t="n">
-        <v>0.029046</v>
+        <v>0.029071</v>
       </c>
       <c r="C130" t="n">
-        <v>0.675127</v>
+        <v>0.670951</v>
       </c>
     </row>
     <row r="131">
@@ -2117,10 +2117,10 @@
         </is>
       </c>
       <c r="B131" t="n">
-        <v>0.029071</v>
+        <v>0.029562</v>
       </c>
       <c r="C131" t="n">
-        <v>0.672589</v>
+        <v>0.66838</v>
       </c>
     </row>
     <row r="132">
@@ -2130,10 +2130,10 @@
         </is>
       </c>
       <c r="B132" t="n">
-        <v>0.029562</v>
+        <v>0.029588</v>
       </c>
       <c r="C132" t="n">
-        <v>0.670051</v>
+        <v>0.66581</v>
       </c>
     </row>
     <row r="133">
@@ -2143,10 +2143,10 @@
         </is>
       </c>
       <c r="B133" t="n">
-        <v>0.029588</v>
+        <v>0.029854</v>
       </c>
       <c r="C133" t="n">
-        <v>0.667513</v>
+        <v>0.663239</v>
       </c>
     </row>
     <row r="134">
@@ -2156,10 +2156,10 @@
         </is>
       </c>
       <c r="B134" t="n">
-        <v>0.029854</v>
+        <v>0.030158</v>
       </c>
       <c r="C134" t="n">
-        <v>0.664975</v>
+        <v>0.660668</v>
       </c>
     </row>
     <row r="135">
@@ -2169,10 +2169,10 @@
         </is>
       </c>
       <c r="B135" t="n">
-        <v>0.030158</v>
+        <v>0.030201</v>
       </c>
       <c r="C135" t="n">
-        <v>0.6624370000000001</v>
+        <v>0.658098</v>
       </c>
     </row>
     <row r="136">
@@ -2182,10 +2182,10 @@
         </is>
       </c>
       <c r="B136" t="n">
-        <v>0.030201</v>
+        <v>0.03027</v>
       </c>
       <c r="C136" t="n">
-        <v>0.659898</v>
+        <v>0.655527</v>
       </c>
     </row>
     <row r="137">
@@ -2195,10 +2195,10 @@
         </is>
       </c>
       <c r="B137" t="n">
-        <v>0.03027</v>
+        <v>0.030697</v>
       </c>
       <c r="C137" t="n">
-        <v>0.6573600000000001</v>
+        <v>0.652956</v>
       </c>
     </row>
     <row r="138">
@@ -2208,10 +2208,10 @@
         </is>
       </c>
       <c r="B138" t="n">
-        <v>0.030697</v>
+        <v>0.030903</v>
       </c>
       <c r="C138" t="n">
-        <v>0.654822</v>
+        <v>0.650386</v>
       </c>
     </row>
     <row r="139">
@@ -2221,10 +2221,10 @@
         </is>
       </c>
       <c r="B139" t="n">
-        <v>0.030903</v>
+        <v>0.031116</v>
       </c>
       <c r="C139" t="n">
-        <v>0.652284</v>
+        <v>0.647815</v>
       </c>
     </row>
     <row r="140">
@@ -2234,10 +2234,10 @@
         </is>
       </c>
       <c r="B140" t="n">
-        <v>0.031116</v>
+        <v>0.031127</v>
       </c>
       <c r="C140" t="n">
-        <v>0.649746</v>
+        <v>0.645244</v>
       </c>
     </row>
     <row r="141">
@@ -2247,10 +2247,10 @@
         </is>
       </c>
       <c r="B141" t="n">
-        <v>0.031127</v>
+        <v>0.031327</v>
       </c>
       <c r="C141" t="n">
-        <v>0.647208</v>
+        <v>0.642674</v>
       </c>
     </row>
     <row r="142">
@@ -2260,10 +2260,10 @@
         </is>
       </c>
       <c r="B142" t="n">
-        <v>0.031327</v>
+        <v>0.0315</v>
       </c>
       <c r="C142" t="n">
-        <v>0.64467</v>
+        <v>0.640103</v>
       </c>
     </row>
     <row r="143">
@@ -2273,10 +2273,10 @@
         </is>
       </c>
       <c r="B143" t="n">
-        <v>0.0315</v>
+        <v>0.031556</v>
       </c>
       <c r="C143" t="n">
-        <v>0.642132</v>
+        <v>0.637532</v>
       </c>
     </row>
     <row r="144">
@@ -2286,10 +2286,10 @@
         </is>
       </c>
       <c r="B144" t="n">
-        <v>0.031556</v>
+        <v>0.031969</v>
       </c>
       <c r="C144" t="n">
-        <v>0.639594</v>
+        <v>0.634961</v>
       </c>
     </row>
     <row r="145">
@@ -2299,10 +2299,10 @@
         </is>
       </c>
       <c r="B145" t="n">
-        <v>0.031969</v>
+        <v>0.032545</v>
       </c>
       <c r="C145" t="n">
-        <v>0.637056</v>
+        <v>0.632391</v>
       </c>
     </row>
     <row r="146">
@@ -2312,10 +2312,10 @@
         </is>
       </c>
       <c r="B146" t="n">
-        <v>0.032545</v>
+        <v>0.032827</v>
       </c>
       <c r="C146" t="n">
-        <v>0.634518</v>
+        <v>0.62982</v>
       </c>
     </row>
     <row r="147">
@@ -2325,10 +2325,10 @@
         </is>
       </c>
       <c r="B147" t="n">
-        <v>0.032827</v>
+        <v>0.033481</v>
       </c>
       <c r="C147" t="n">
-        <v>0.63198</v>
+        <v>0.6272489999999999</v>
       </c>
     </row>
     <row r="148">
@@ -2338,10 +2338,10 @@
         </is>
       </c>
       <c r="B148" t="n">
-        <v>0.033481</v>
+        <v>0.033774</v>
       </c>
       <c r="C148" t="n">
-        <v>0.6294419999999999</v>
+        <v>0.624679</v>
       </c>
     </row>
     <row r="149">
@@ -2351,10 +2351,10 @@
         </is>
       </c>
       <c r="B149" t="n">
-        <v>0.033774</v>
+        <v>0.033884</v>
       </c>
       <c r="C149" t="n">
-        <v>0.626904</v>
+        <v>0.622108</v>
       </c>
     </row>
     <row r="150">
@@ -2364,10 +2364,10 @@
         </is>
       </c>
       <c r="B150" t="n">
-        <v>0.033884</v>
+        <v>0.034047</v>
       </c>
       <c r="C150" t="n">
-        <v>0.6243649999999999</v>
+        <v>0.619537</v>
       </c>
     </row>
     <row r="151">
@@ -2377,10 +2377,10 @@
         </is>
       </c>
       <c r="B151" t="n">
-        <v>0.034047</v>
+        <v>0.034274</v>
       </c>
       <c r="C151" t="n">
-        <v>0.621827</v>
+        <v>0.616967</v>
       </c>
     </row>
     <row r="152">
@@ -2390,10 +2390,10 @@
         </is>
       </c>
       <c r="B152" t="n">
-        <v>0.034274</v>
+        <v>0.03466</v>
       </c>
       <c r="C152" t="n">
-        <v>0.619289</v>
+        <v>0.6143960000000001</v>
       </c>
     </row>
     <row r="153">
@@ -2403,10 +2403,10 @@
         </is>
       </c>
       <c r="B153" t="n">
-        <v>0.03466</v>
+        <v>0.035039</v>
       </c>
       <c r="C153" t="n">
-        <v>0.616751</v>
+        <v>0.611825</v>
       </c>
     </row>
     <row r="154">
@@ -2416,10 +2416,10 @@
         </is>
       </c>
       <c r="B154" t="n">
-        <v>0.035039</v>
+        <v>0.035117</v>
       </c>
       <c r="C154" t="n">
-        <v>0.614213</v>
+        <v>0.609254</v>
       </c>
     </row>
     <row r="155">
@@ -2429,10 +2429,10 @@
         </is>
       </c>
       <c r="B155" t="n">
-        <v>0.035117</v>
+        <v>0.035159</v>
       </c>
       <c r="C155" t="n">
-        <v>0.611675</v>
+        <v>0.606684</v>
       </c>
     </row>
     <row r="156">
@@ -2442,10 +2442,10 @@
         </is>
       </c>
       <c r="B156" t="n">
-        <v>0.035159</v>
+        <v>0.035374</v>
       </c>
       <c r="C156" t="n">
-        <v>0.609137</v>
+        <v>0.604113</v>
       </c>
     </row>
     <row r="157">
@@ -2455,10 +2455,10 @@
         </is>
       </c>
       <c r="B157" t="n">
-        <v>0.035374</v>
+        <v>0.035654</v>
       </c>
       <c r="C157" t="n">
-        <v>0.606599</v>
+        <v>0.601542</v>
       </c>
     </row>
     <row r="158">
@@ -2468,10 +2468,10 @@
         </is>
       </c>
       <c r="B158" t="n">
-        <v>0.035654</v>
+        <v>0.036</v>
       </c>
       <c r="C158" t="n">
-        <v>0.604061</v>
+        <v>0.5989719999999999</v>
       </c>
     </row>
     <row r="159">
@@ -2481,10 +2481,10 @@
         </is>
       </c>
       <c r="B159" t="n">
-        <v>0.036</v>
+        <v>0.036324</v>
       </c>
       <c r="C159" t="n">
-        <v>0.601523</v>
+        <v>0.596401</v>
       </c>
     </row>
     <row r="160">
@@ -2494,10 +2494,10 @@
         </is>
       </c>
       <c r="B160" t="n">
-        <v>0.036324</v>
+        <v>0.03642</v>
       </c>
       <c r="C160" t="n">
-        <v>0.598985</v>
+        <v>0.59383</v>
       </c>
     </row>
     <row r="161">
@@ -2507,10 +2507,10 @@
         </is>
       </c>
       <c r="B161" t="n">
-        <v>0.03642</v>
+        <v>0.03678</v>
       </c>
       <c r="C161" t="n">
-        <v>0.5964469999999999</v>
+        <v>0.59126</v>
       </c>
     </row>
     <row r="162">
@@ -2520,10 +2520,10 @@
         </is>
       </c>
       <c r="B162" t="n">
-        <v>0.03678</v>
+        <v>0.037099</v>
       </c>
       <c r="C162" t="n">
-        <v>0.593909</v>
+        <v>0.588689</v>
       </c>
     </row>
     <row r="163">
@@ -2533,10 +2533,10 @@
         </is>
       </c>
       <c r="B163" t="n">
-        <v>0.037099</v>
+        <v>0.037156</v>
       </c>
       <c r="C163" t="n">
-        <v>0.591371</v>
+        <v>0.586118</v>
       </c>
     </row>
     <row r="164">
@@ -2546,10 +2546,10 @@
         </is>
       </c>
       <c r="B164" t="n">
-        <v>0.037156</v>
+        <v>0.037307</v>
       </c>
       <c r="C164" t="n">
-        <v>0.588832</v>
+        <v>0.583548</v>
       </c>
     </row>
     <row r="165">
@@ -2559,10 +2559,10 @@
         </is>
       </c>
       <c r="B165" t="n">
-        <v>0.037307</v>
+        <v>0.037805</v>
       </c>
       <c r="C165" t="n">
-        <v>0.586294</v>
+        <v>0.580977</v>
       </c>
     </row>
     <row r="166">
@@ -2572,10 +2572,10 @@
         </is>
       </c>
       <c r="B166" t="n">
-        <v>0.037805</v>
+        <v>0.037855</v>
       </c>
       <c r="C166" t="n">
-        <v>0.5837560000000001</v>
+        <v>0.578406</v>
       </c>
     </row>
     <row r="167">
@@ -2585,10 +2585,10 @@
         </is>
       </c>
       <c r="B167" t="n">
-        <v>0.037855</v>
+        <v>0.038316</v>
       </c>
       <c r="C167" t="n">
-        <v>0.581218</v>
+        <v>0.575835</v>
       </c>
     </row>
     <row r="168">
@@ -2598,10 +2598,10 @@
         </is>
       </c>
       <c r="B168" t="n">
-        <v>0.038316</v>
+        <v>0.03876</v>
       </c>
       <c r="C168" t="n">
-        <v>0.57868</v>
+        <v>0.573265</v>
       </c>
     </row>
     <row r="169">
@@ -2611,10 +2611,10 @@
         </is>
       </c>
       <c r="B169" t="n">
-        <v>0.03876</v>
+        <v>0.039595</v>
       </c>
       <c r="C169" t="n">
-        <v>0.576142</v>
+        <v>0.570694</v>
       </c>
     </row>
     <row r="170">
@@ -2624,10 +2624,10 @@
         </is>
       </c>
       <c r="B170" t="n">
-        <v>0.039595</v>
+        <v>0.039761</v>
       </c>
       <c r="C170" t="n">
-        <v>0.573604</v>
+        <v>0.568123</v>
       </c>
     </row>
     <row r="171">
@@ -2640,7 +2640,7 @@
         <v>0.03982</v>
       </c>
       <c r="C171" t="n">
-        <v>0.571066</v>
+        <v>0.565553</v>
       </c>
     </row>
     <row r="172">
@@ -2653,7 +2653,7 @@
         <v>0.040867</v>
       </c>
       <c r="C172" t="n">
-        <v>0.568528</v>
+        <v>0.562982</v>
       </c>
     </row>
     <row r="173">
@@ -2666,7 +2666,7 @@
         <v>0.040915</v>
       </c>
       <c r="C173" t="n">
-        <v>0.56599</v>
+        <v>0.560411</v>
       </c>
     </row>
     <row r="174">
@@ -2679,7 +2679,7 @@
         <v>0.040948</v>
       </c>
       <c r="C174" t="n">
-        <v>0.563452</v>
+        <v>0.557841</v>
       </c>
     </row>
     <row r="175">
@@ -2692,7 +2692,7 @@
         <v>0.040975</v>
       </c>
       <c r="C175" t="n">
-        <v>0.560914</v>
+        <v>0.55527</v>
       </c>
     </row>
     <row r="176">
@@ -2705,7 +2705,7 @@
         <v>0.041019</v>
       </c>
       <c r="C176" t="n">
-        <v>0.558376</v>
+        <v>0.5526990000000001</v>
       </c>
     </row>
     <row r="177">
@@ -2718,7 +2718,7 @@
         <v>0.041132</v>
       </c>
       <c r="C177" t="n">
-        <v>0.5558380000000001</v>
+        <v>0.550129</v>
       </c>
     </row>
     <row r="178">
@@ -2731,7 +2731,7 @@
         <v>0.041331</v>
       </c>
       <c r="C178" t="n">
-        <v>0.553299</v>
+        <v>0.547558</v>
       </c>
     </row>
     <row r="179">
@@ -2744,7 +2744,7 @@
         <v>0.041457</v>
       </c>
       <c r="C179" t="n">
-        <v>0.5507609999999999</v>
+        <v>0.544987</v>
       </c>
     </row>
     <row r="180">
@@ -2757,7 +2757,7 @@
         <v>0.041762</v>
       </c>
       <c r="C180" t="n">
-        <v>0.548223</v>
+        <v>0.542416</v>
       </c>
     </row>
     <row r="181">
@@ -2770,7 +2770,7 @@
         <v>0.04197</v>
       </c>
       <c r="C181" t="n">
-        <v>0.545685</v>
+        <v>0.539846</v>
       </c>
     </row>
     <row r="182">
@@ -2783,7 +2783,7 @@
         <v>0.042735</v>
       </c>
       <c r="C182" t="n">
-        <v>0.543147</v>
+        <v>0.5372749999999999</v>
       </c>
     </row>
     <row r="183">
@@ -2796,7 +2796,7 @@
         <v>0.043144</v>
       </c>
       <c r="C183" t="n">
-        <v>0.540609</v>
+        <v>0.534704</v>
       </c>
     </row>
     <row r="184">
@@ -2809,7 +2809,7 @@
         <v>0.043468</v>
       </c>
       <c r="C184" t="n">
-        <v>0.538071</v>
+        <v>0.532134</v>
       </c>
     </row>
     <row r="185">
@@ -2822,7 +2822,7 @@
         <v>0.04427</v>
       </c>
       <c r="C185" t="n">
-        <v>0.535533</v>
+        <v>0.529563</v>
       </c>
     </row>
     <row r="186">
@@ -2835,7 +2835,7 @@
         <v>0.044385</v>
       </c>
       <c r="C186" t="n">
-        <v>0.532995</v>
+        <v>0.526992</v>
       </c>
     </row>
     <row r="187">
@@ -2848,7 +2848,7 @@
         <v>0.044556</v>
       </c>
       <c r="C187" t="n">
-        <v>0.530457</v>
+        <v>0.5244220000000001</v>
       </c>
     </row>
     <row r="188">
@@ -2861,7 +2861,7 @@
         <v>0.044571</v>
       </c>
       <c r="C188" t="n">
-        <v>0.527919</v>
+        <v>0.521851</v>
       </c>
     </row>
     <row r="189">
@@ -2874,7 +2874,7 @@
         <v>0.044939</v>
       </c>
       <c r="C189" t="n">
-        <v>0.525381</v>
+        <v>0.51928</v>
       </c>
     </row>
     <row r="190">
@@ -2887,7 +2887,7 @@
         <v>0.045962</v>
       </c>
       <c r="C190" t="n">
-        <v>0.5228429999999999</v>
+        <v>0.51671</v>
       </c>
     </row>
     <row r="191">
@@ -2900,7 +2900,7 @@
         <v>0.046161</v>
       </c>
       <c r="C191" t="n">
-        <v>0.520305</v>
+        <v>0.514139</v>
       </c>
     </row>
     <row r="192">
@@ -2913,7 +2913,7 @@
         <v>0.046486</v>
       </c>
       <c r="C192" t="n">
-        <v>0.5177659999999999</v>
+        <v>0.511568</v>
       </c>
     </row>
     <row r="193">
@@ -2926,7 +2926,7 @@
         <v>0.046763</v>
       </c>
       <c r="C193" t="n">
-        <v>0.515228</v>
+        <v>0.508997</v>
       </c>
     </row>
     <row r="194">
@@ -2939,7 +2939,7 @@
         <v>0.046785</v>
       </c>
       <c r="C194" t="n">
-        <v>0.51269</v>
+        <v>0.506427</v>
       </c>
     </row>
     <row r="195">
@@ -2952,7 +2952,7 @@
         <v>0.046943</v>
       </c>
       <c r="C195" t="n">
-        <v>0.510152</v>
+        <v>0.503856</v>
       </c>
     </row>
     <row r="196">
@@ -2965,7 +2965,7 @@
         <v>0.047141</v>
       </c>
       <c r="C196" t="n">
-        <v>0.507614</v>
+        <v>0.501285</v>
       </c>
     </row>
     <row r="197">
@@ -2978,7 +2978,7 @@
         <v>0.047327</v>
       </c>
       <c r="C197" t="n">
-        <v>0.505076</v>
+        <v>0.498715</v>
       </c>
     </row>
     <row r="198">
@@ -2991,7 +2991,7 @@
         <v>0.047421</v>
       </c>
       <c r="C198" t="n">
-        <v>0.502538</v>
+        <v>0.496144</v>
       </c>
     </row>
     <row r="199">
@@ -3004,7 +3004,7 @@
         <v>0.047498</v>
       </c>
       <c r="C199" t="n">
-        <v>0.5</v>
+        <v>0.493573</v>
       </c>
     </row>
     <row r="200">
@@ -3017,7 +3017,7 @@
         <v>0.047901</v>
       </c>
       <c r="C200" t="n">
-        <v>0.497462</v>
+        <v>0.491003</v>
       </c>
     </row>
     <row r="201">
@@ -3030,7 +3030,7 @@
         <v>0.04832</v>
       </c>
       <c r="C201" t="n">
-        <v>0.494924</v>
+        <v>0.488432</v>
       </c>
     </row>
     <row r="202">
@@ -3043,7 +3043,7 @@
         <v>0.048551</v>
       </c>
       <c r="C202" t="n">
-        <v>0.492386</v>
+        <v>0.485861</v>
       </c>
     </row>
     <row r="203">
@@ -3056,7 +3056,7 @@
         <v>0.04875</v>
       </c>
       <c r="C203" t="n">
-        <v>0.489848</v>
+        <v>0.48329</v>
       </c>
     </row>
     <row r="204">
@@ -3069,7 +3069,7 @@
         <v>0.04906</v>
       </c>
       <c r="C204" t="n">
-        <v>0.48731</v>
+        <v>0.48072</v>
       </c>
     </row>
     <row r="205">
@@ -3082,7 +3082,7 @@
         <v>0.049358</v>
       </c>
       <c r="C205" t="n">
-        <v>0.484772</v>
+        <v>0.478149</v>
       </c>
     </row>
     <row r="206">
@@ -3095,7 +3095,7 @@
         <v>0.049478</v>
       </c>
       <c r="C206" t="n">
-        <v>0.482234</v>
+        <v>0.475578</v>
       </c>
     </row>
     <row r="207">
@@ -3108,7 +3108,7 @@
         <v>0.049516</v>
       </c>
       <c r="C207" t="n">
-        <v>0.479695</v>
+        <v>0.473008</v>
       </c>
     </row>
     <row r="208">
@@ -3121,7 +3121,7 @@
         <v>0.049728</v>
       </c>
       <c r="C208" t="n">
-        <v>0.477157</v>
+        <v>0.470437</v>
       </c>
     </row>
     <row r="209">
@@ -3134,7 +3134,7 @@
         <v>0.050809</v>
       </c>
       <c r="C209" t="n">
-        <v>0.474619</v>
+        <v>0.467866</v>
       </c>
     </row>
     <row r="210">
@@ -3147,7 +3147,7 @@
         <v>0.051151</v>
       </c>
       <c r="C210" t="n">
-        <v>0.472081</v>
+        <v>0.465296</v>
       </c>
     </row>
     <row r="211">
@@ -3157,10 +3157,10 @@
         </is>
       </c>
       <c r="B211" t="n">
-        <v>0.051264</v>
+        <v>0.051423</v>
       </c>
       <c r="C211" t="n">
-        <v>0.469543</v>
+        <v>0.462725</v>
       </c>
     </row>
     <row r="212">
@@ -3170,10 +3170,10 @@
         </is>
       </c>
       <c r="B212" t="n">
-        <v>0.051423</v>
+        <v>0.051449</v>
       </c>
       <c r="C212" t="n">
-        <v>0.467005</v>
+        <v>0.460154</v>
       </c>
     </row>
     <row r="213">
@@ -3183,10 +3183,10 @@
         </is>
       </c>
       <c r="B213" t="n">
-        <v>0.051449</v>
+        <v>0.052376</v>
       </c>
       <c r="C213" t="n">
-        <v>0.464467</v>
+        <v>0.457584</v>
       </c>
     </row>
     <row r="214">
@@ -3196,10 +3196,10 @@
         </is>
       </c>
       <c r="B214" t="n">
-        <v>0.052376</v>
+        <v>0.052398</v>
       </c>
       <c r="C214" t="n">
-        <v>0.461929</v>
+        <v>0.455013</v>
       </c>
     </row>
     <row r="215">
@@ -3209,10 +3209,10 @@
         </is>
       </c>
       <c r="B215" t="n">
-        <v>0.052398</v>
+        <v>0.052682</v>
       </c>
       <c r="C215" t="n">
-        <v>0.459391</v>
+        <v>0.452442</v>
       </c>
     </row>
     <row r="216">
@@ -3222,10 +3222,10 @@
         </is>
       </c>
       <c r="B216" t="n">
-        <v>0.052682</v>
+        <v>0.053144</v>
       </c>
       <c r="C216" t="n">
-        <v>0.456853</v>
+        <v>0.449871</v>
       </c>
     </row>
     <row r="217">
@@ -3235,10 +3235,10 @@
         </is>
       </c>
       <c r="B217" t="n">
-        <v>0.053144</v>
+        <v>0.053227</v>
       </c>
       <c r="C217" t="n">
-        <v>0.454315</v>
+        <v>0.447301</v>
       </c>
     </row>
     <row r="218">
@@ -3248,10 +3248,10 @@
         </is>
       </c>
       <c r="B218" t="n">
-        <v>0.053227</v>
+        <v>0.053316</v>
       </c>
       <c r="C218" t="n">
-        <v>0.451777</v>
+        <v>0.44473</v>
       </c>
     </row>
     <row r="219">
@@ -3261,10 +3261,10 @@
         </is>
       </c>
       <c r="B219" t="n">
-        <v>0.053316</v>
+        <v>0.053555</v>
       </c>
       <c r="C219" t="n">
-        <v>0.449239</v>
+        <v>0.442159</v>
       </c>
     </row>
     <row r="220">
@@ -3274,10 +3274,10 @@
         </is>
       </c>
       <c r="B220" t="n">
-        <v>0.053555</v>
+        <v>0.05382</v>
       </c>
       <c r="C220" t="n">
-        <v>0.446701</v>
+        <v>0.439589</v>
       </c>
     </row>
     <row r="221">
@@ -3287,10 +3287,10 @@
         </is>
       </c>
       <c r="B221" t="n">
-        <v>0.05382</v>
+        <v>0.05439</v>
       </c>
       <c r="C221" t="n">
-        <v>0.444162</v>
+        <v>0.437018</v>
       </c>
     </row>
     <row r="222">
@@ -3300,10 +3300,10 @@
         </is>
       </c>
       <c r="B222" t="n">
-        <v>0.05439</v>
+        <v>0.05496</v>
       </c>
       <c r="C222" t="n">
-        <v>0.441624</v>
+        <v>0.434447</v>
       </c>
     </row>
     <row r="223">
@@ -3313,10 +3313,10 @@
         </is>
       </c>
       <c r="B223" t="n">
-        <v>0.05496</v>
+        <v>0.055028</v>
       </c>
       <c r="C223" t="n">
-        <v>0.439086</v>
+        <v>0.431877</v>
       </c>
     </row>
     <row r="224">
@@ -3326,10 +3326,10 @@
         </is>
       </c>
       <c r="B224" t="n">
-        <v>0.055028</v>
+        <v>0.0555</v>
       </c>
       <c r="C224" t="n">
-        <v>0.436548</v>
+        <v>0.429306</v>
       </c>
     </row>
     <row r="225">
@@ -3339,10 +3339,10 @@
         </is>
       </c>
       <c r="B225" t="n">
-        <v>0.0555</v>
+        <v>0.055621</v>
       </c>
       <c r="C225" t="n">
-        <v>0.43401</v>
+        <v>0.426735</v>
       </c>
     </row>
     <row r="226">
@@ -3352,10 +3352,10 @@
         </is>
       </c>
       <c r="B226" t="n">
-        <v>0.055621</v>
+        <v>0.056242</v>
       </c>
       <c r="C226" t="n">
-        <v>0.431472</v>
+        <v>0.424165</v>
       </c>
     </row>
     <row r="227">
@@ -3365,10 +3365,10 @@
         </is>
       </c>
       <c r="B227" t="n">
-        <v>0.055736</v>
+        <v>0.056433</v>
       </c>
       <c r="C227" t="n">
-        <v>0.428934</v>
+        <v>0.421594</v>
       </c>
     </row>
     <row r="228">
@@ -3378,10 +3378,10 @@
         </is>
       </c>
       <c r="B228" t="n">
-        <v>0.056242</v>
+        <v>0.056702</v>
       </c>
       <c r="C228" t="n">
-        <v>0.426396</v>
+        <v>0.419023</v>
       </c>
     </row>
     <row r="229">
@@ -3391,10 +3391,10 @@
         </is>
       </c>
       <c r="B229" t="n">
-        <v>0.056433</v>
+        <v>0.056785</v>
       </c>
       <c r="C229" t="n">
-        <v>0.423858</v>
+        <v>0.416452</v>
       </c>
     </row>
     <row r="230">
@@ -3404,10 +3404,10 @@
         </is>
       </c>
       <c r="B230" t="n">
-        <v>0.056702</v>
+        <v>0.057942</v>
       </c>
       <c r="C230" t="n">
-        <v>0.42132</v>
+        <v>0.413882</v>
       </c>
     </row>
     <row r="231">
@@ -3417,10 +3417,10 @@
         </is>
       </c>
       <c r="B231" t="n">
-        <v>0.056785</v>
+        <v>0.05854</v>
       </c>
       <c r="C231" t="n">
-        <v>0.418782</v>
+        <v>0.411311</v>
       </c>
     </row>
     <row r="232">
@@ -3430,10 +3430,10 @@
         </is>
       </c>
       <c r="B232" t="n">
-        <v>0.057942</v>
+        <v>0.058745</v>
       </c>
       <c r="C232" t="n">
-        <v>0.416244</v>
+        <v>0.40874</v>
       </c>
     </row>
     <row r="233">
@@ -3443,10 +3443,10 @@
         </is>
       </c>
       <c r="B233" t="n">
-        <v>0.05854</v>
+        <v>0.058836</v>
       </c>
       <c r="C233" t="n">
-        <v>0.413706</v>
+        <v>0.40617</v>
       </c>
     </row>
     <row r="234">
@@ -3456,10 +3456,10 @@
         </is>
       </c>
       <c r="B234" t="n">
-        <v>0.058745</v>
+        <v>0.059279</v>
       </c>
       <c r="C234" t="n">
-        <v>0.411168</v>
+        <v>0.403599</v>
       </c>
     </row>
     <row r="235">
@@ -3469,10 +3469,10 @@
         </is>
       </c>
       <c r="B235" t="n">
-        <v>0.058836</v>
+        <v>0.059367</v>
       </c>
       <c r="C235" t="n">
-        <v>0.408629</v>
+        <v>0.401028</v>
       </c>
     </row>
     <row r="236">
@@ -3482,10 +3482,10 @@
         </is>
       </c>
       <c r="B236" t="n">
-        <v>0.059279</v>
+        <v>0.059553</v>
       </c>
       <c r="C236" t="n">
-        <v>0.406091</v>
+        <v>0.398458</v>
       </c>
     </row>
     <row r="237">
@@ -3495,10 +3495,10 @@
         </is>
       </c>
       <c r="B237" t="n">
-        <v>0.059367</v>
+        <v>0.059579</v>
       </c>
       <c r="C237" t="n">
-        <v>0.403553</v>
+        <v>0.395887</v>
       </c>
     </row>
     <row r="238">
@@ -3508,10 +3508,10 @@
         </is>
       </c>
       <c r="B238" t="n">
-        <v>0.059553</v>
+        <v>0.060111</v>
       </c>
       <c r="C238" t="n">
-        <v>0.401015</v>
+        <v>0.393316</v>
       </c>
     </row>
     <row r="239">
@@ -3521,10 +3521,10 @@
         </is>
       </c>
       <c r="B239" t="n">
-        <v>0.059579</v>
+        <v>0.060827</v>
       </c>
       <c r="C239" t="n">
-        <v>0.398477</v>
+        <v>0.390746</v>
       </c>
     </row>
     <row r="240">
@@ -3534,10 +3534,10 @@
         </is>
       </c>
       <c r="B240" t="n">
-        <v>0.060111</v>
+        <v>0.060882</v>
       </c>
       <c r="C240" t="n">
-        <v>0.395939</v>
+        <v>0.388175</v>
       </c>
     </row>
     <row r="241">
@@ -3547,10 +3547,10 @@
         </is>
       </c>
       <c r="B241" t="n">
-        <v>0.060827</v>
+        <v>0.061437</v>
       </c>
       <c r="C241" t="n">
-        <v>0.393401</v>
+        <v>0.385604</v>
       </c>
     </row>
     <row r="242">
@@ -3560,10 +3560,10 @@
         </is>
       </c>
       <c r="B242" t="n">
-        <v>0.060882</v>
+        <v>0.061712</v>
       </c>
       <c r="C242" t="n">
-        <v>0.390863</v>
+        <v>0.383033</v>
       </c>
     </row>
     <row r="243">
@@ -3573,10 +3573,10 @@
         </is>
       </c>
       <c r="B243" t="n">
-        <v>0.061437</v>
+        <v>0.061784</v>
       </c>
       <c r="C243" t="n">
-        <v>0.388325</v>
+        <v>0.380463</v>
       </c>
     </row>
     <row r="244">
@@ -3586,10 +3586,10 @@
         </is>
       </c>
       <c r="B244" t="n">
-        <v>0.061712</v>
+        <v>0.06179</v>
       </c>
       <c r="C244" t="n">
-        <v>0.385787</v>
+        <v>0.377892</v>
       </c>
     </row>
     <row r="245">
@@ -3599,10 +3599,10 @@
         </is>
       </c>
       <c r="B245" t="n">
-        <v>0.061784</v>
+        <v>0.061969</v>
       </c>
       <c r="C245" t="n">
-        <v>0.383249</v>
+        <v>0.375321</v>
       </c>
     </row>
     <row r="246">
@@ -3612,10 +3612,10 @@
         </is>
       </c>
       <c r="B246" t="n">
-        <v>0.06179</v>
+        <v>0.062129</v>
       </c>
       <c r="C246" t="n">
-        <v>0.380711</v>
+        <v>0.372751</v>
       </c>
     </row>
     <row r="247">
@@ -3625,10 +3625,10 @@
         </is>
       </c>
       <c r="B247" t="n">
-        <v>0.061969</v>
+        <v>0.062168</v>
       </c>
       <c r="C247" t="n">
-        <v>0.378173</v>
+        <v>0.37018</v>
       </c>
     </row>
     <row r="248">
@@ -3638,10 +3638,10 @@
         </is>
       </c>
       <c r="B248" t="n">
-        <v>0.062129</v>
+        <v>0.06263299999999999</v>
       </c>
       <c r="C248" t="n">
-        <v>0.375635</v>
+        <v>0.367609</v>
       </c>
     </row>
     <row r="249">
@@ -3651,10 +3651,10 @@
         </is>
       </c>
       <c r="B249" t="n">
-        <v>0.062168</v>
+        <v>0.062844</v>
       </c>
       <c r="C249" t="n">
-        <v>0.373096</v>
+        <v>0.365039</v>
       </c>
     </row>
     <row r="250">
@@ -3664,10 +3664,10 @@
         </is>
       </c>
       <c r="B250" t="n">
-        <v>0.06263299999999999</v>
+        <v>0.063808</v>
       </c>
       <c r="C250" t="n">
-        <v>0.370558</v>
+        <v>0.362468</v>
       </c>
     </row>
     <row r="251">
@@ -3677,10 +3677,10 @@
         </is>
       </c>
       <c r="B251" t="n">
-        <v>0.062844</v>
+        <v>0.064842</v>
       </c>
       <c r="C251" t="n">
-        <v>0.36802</v>
+        <v>0.359897</v>
       </c>
     </row>
     <row r="252">
@@ -3690,10 +3690,10 @@
         </is>
       </c>
       <c r="B252" t="n">
-        <v>0.063808</v>
+        <v>0.06555900000000001</v>
       </c>
       <c r="C252" t="n">
-        <v>0.365482</v>
+        <v>0.357326</v>
       </c>
     </row>
     <row r="253">
@@ -3703,10 +3703,10 @@
         </is>
       </c>
       <c r="B253" t="n">
-        <v>0.064842</v>
+        <v>0.067176</v>
       </c>
       <c r="C253" t="n">
-        <v>0.362944</v>
+        <v>0.354756</v>
       </c>
     </row>
     <row r="254">
@@ -3716,10 +3716,10 @@
         </is>
       </c>
       <c r="B254" t="n">
-        <v>0.06555900000000001</v>
+        <v>0.06736399999999999</v>
       </c>
       <c r="C254" t="n">
-        <v>0.360406</v>
+        <v>0.352185</v>
       </c>
     </row>
     <row r="255">
@@ -3729,10 +3729,10 @@
         </is>
       </c>
       <c r="B255" t="n">
-        <v>0.067176</v>
+        <v>0.067375</v>
       </c>
       <c r="C255" t="n">
-        <v>0.357868</v>
+        <v>0.349614</v>
       </c>
     </row>
     <row r="256">
@@ -3742,10 +3742,10 @@
         </is>
       </c>
       <c r="B256" t="n">
-        <v>0.06736399999999999</v>
+        <v>0.067555</v>
       </c>
       <c r="C256" t="n">
-        <v>0.35533</v>
+        <v>0.347044</v>
       </c>
     </row>
     <row r="257">
@@ -3755,10 +3755,10 @@
         </is>
       </c>
       <c r="B257" t="n">
-        <v>0.067375</v>
+        <v>0.067604</v>
       </c>
       <c r="C257" t="n">
-        <v>0.352792</v>
+        <v>0.344473</v>
       </c>
     </row>
     <row r="258">
@@ -3768,10 +3768,10 @@
         </is>
       </c>
       <c r="B258" t="n">
-        <v>0.067555</v>
+        <v>0.067644</v>
       </c>
       <c r="C258" t="n">
-        <v>0.350254</v>
+        <v>0.341902</v>
       </c>
     </row>
     <row r="259">
@@ -3781,10 +3781,10 @@
         </is>
       </c>
       <c r="B259" t="n">
-        <v>0.067604</v>
+        <v>0.068111</v>
       </c>
       <c r="C259" t="n">
-        <v>0.347716</v>
+        <v>0.339332</v>
       </c>
     </row>
     <row r="260">
@@ -3794,10 +3794,10 @@
         </is>
       </c>
       <c r="B260" t="n">
-        <v>0.067644</v>
+        <v>0.068538</v>
       </c>
       <c r="C260" t="n">
-        <v>0.345178</v>
+        <v>0.336761</v>
       </c>
     </row>
     <row r="261">
@@ -3807,10 +3807,10 @@
         </is>
       </c>
       <c r="B261" t="n">
-        <v>0.068111</v>
+        <v>0.068601</v>
       </c>
       <c r="C261" t="n">
-        <v>0.34264</v>
+        <v>0.33419</v>
       </c>
     </row>
     <row r="262">
@@ -3820,10 +3820,10 @@
         </is>
       </c>
       <c r="B262" t="n">
-        <v>0.068538</v>
+        <v>0.068939</v>
       </c>
       <c r="C262" t="n">
-        <v>0.340102</v>
+        <v>0.33162</v>
       </c>
     </row>
     <row r="263">
@@ -3833,10 +3833,10 @@
         </is>
       </c>
       <c r="B263" t="n">
-        <v>0.068601</v>
+        <v>0.06909</v>
       </c>
       <c r="C263" t="n">
-        <v>0.337563</v>
+        <v>0.329049</v>
       </c>
     </row>
     <row r="264">
@@ -3846,10 +3846,10 @@
         </is>
       </c>
       <c r="B264" t="n">
-        <v>0.068845</v>
+        <v>0.069253</v>
       </c>
       <c r="C264" t="n">
-        <v>0.335025</v>
+        <v>0.326478</v>
       </c>
     </row>
     <row r="265">
@@ -3859,10 +3859,10 @@
         </is>
       </c>
       <c r="B265" t="n">
-        <v>0.068939</v>
+        <v>0.070214</v>
       </c>
       <c r="C265" t="n">
-        <v>0.332487</v>
+        <v>0.323907</v>
       </c>
     </row>
     <row r="266">
@@ -3872,10 +3872,10 @@
         </is>
       </c>
       <c r="B266" t="n">
-        <v>0.06909</v>
+        <v>0.070659</v>
       </c>
       <c r="C266" t="n">
-        <v>0.329949</v>
+        <v>0.321337</v>
       </c>
     </row>
     <row r="267">
@@ -3885,10 +3885,10 @@
         </is>
       </c>
       <c r="B267" t="n">
-        <v>0.069253</v>
+        <v>0.071449</v>
       </c>
       <c r="C267" t="n">
-        <v>0.327411</v>
+        <v>0.318766</v>
       </c>
     </row>
     <row r="268">
@@ -3898,10 +3898,10 @@
         </is>
       </c>
       <c r="B268" t="n">
-        <v>0.070214</v>
+        <v>0.07172199999999999</v>
       </c>
       <c r="C268" t="n">
-        <v>0.324873</v>
+        <v>0.316195</v>
       </c>
     </row>
     <row r="269">
@@ -3911,10 +3911,10 @@
         </is>
       </c>
       <c r="B269" t="n">
-        <v>0.070659</v>
+        <v>0.072684</v>
       </c>
       <c r="C269" t="n">
-        <v>0.322335</v>
+        <v>0.313625</v>
       </c>
     </row>
     <row r="270">
@@ -3924,10 +3924,10 @@
         </is>
       </c>
       <c r="B270" t="n">
-        <v>0.071449</v>
+        <v>0.072744</v>
       </c>
       <c r="C270" t="n">
-        <v>0.319797</v>
+        <v>0.311054</v>
       </c>
     </row>
     <row r="271">
@@ -3937,10 +3937,10 @@
         </is>
       </c>
       <c r="B271" t="n">
-        <v>0.07172199999999999</v>
+        <v>0.07295599999999999</v>
       </c>
       <c r="C271" t="n">
-        <v>0.317259</v>
+        <v>0.308483</v>
       </c>
     </row>
     <row r="272">
@@ -3950,10 +3950,10 @@
         </is>
       </c>
       <c r="B272" t="n">
-        <v>0.072684</v>
+        <v>0.07331</v>
       </c>
       <c r="C272" t="n">
-        <v>0.314721</v>
+        <v>0.305913</v>
       </c>
     </row>
     <row r="273">
@@ -3963,10 +3963,10 @@
         </is>
       </c>
       <c r="B273" t="n">
-        <v>0.072744</v>
+        <v>0.07346</v>
       </c>
       <c r="C273" t="n">
-        <v>0.312183</v>
+        <v>0.303342</v>
       </c>
     </row>
     <row r="274">
@@ -3976,10 +3976,10 @@
         </is>
       </c>
       <c r="B274" t="n">
-        <v>0.07295599999999999</v>
+        <v>0.07380299999999999</v>
       </c>
       <c r="C274" t="n">
-        <v>0.309645</v>
+        <v>0.300771</v>
       </c>
     </row>
     <row r="275">
@@ -3989,10 +3989,10 @@
         </is>
       </c>
       <c r="B275" t="n">
-        <v>0.07331</v>
+        <v>0.07424799999999999</v>
       </c>
       <c r="C275" t="n">
-        <v>0.307107</v>
+        <v>0.298201</v>
       </c>
     </row>
     <row r="276">
@@ -4002,10 +4002,10 @@
         </is>
       </c>
       <c r="B276" t="n">
-        <v>0.07346</v>
+        <v>0.07437100000000001</v>
       </c>
       <c r="C276" t="n">
-        <v>0.304569</v>
+        <v>0.29563</v>
       </c>
     </row>
     <row r="277">
@@ -4015,10 +4015,10 @@
         </is>
       </c>
       <c r="B277" t="n">
-        <v>0.07380299999999999</v>
+        <v>0.075854</v>
       </c>
       <c r="C277" t="n">
-        <v>0.30203</v>
+        <v>0.293059</v>
       </c>
     </row>
     <row r="278">
@@ -4028,10 +4028,10 @@
         </is>
       </c>
       <c r="B278" t="n">
-        <v>0.07424799999999999</v>
+        <v>0.075876</v>
       </c>
       <c r="C278" t="n">
-        <v>0.299492</v>
+        <v>0.290488</v>
       </c>
     </row>
     <row r="279">
@@ -4041,10 +4041,10 @@
         </is>
       </c>
       <c r="B279" t="n">
-        <v>0.07437100000000001</v>
+        <v>0.076543</v>
       </c>
       <c r="C279" t="n">
-        <v>0.296954</v>
+        <v>0.287918</v>
       </c>
     </row>
     <row r="280">
@@ -4054,10 +4054,10 @@
         </is>
       </c>
       <c r="B280" t="n">
-        <v>0.075854</v>
+        <v>0.07708</v>
       </c>
       <c r="C280" t="n">
-        <v>0.294416</v>
+        <v>0.285347</v>
       </c>
     </row>
     <row r="281">
@@ -4067,10 +4067,10 @@
         </is>
       </c>
       <c r="B281" t="n">
-        <v>0.075876</v>
+        <v>0.077419</v>
       </c>
       <c r="C281" t="n">
-        <v>0.291878</v>
+        <v>0.282776</v>
       </c>
     </row>
     <row r="282">
@@ -4080,10 +4080,10 @@
         </is>
       </c>
       <c r="B282" t="n">
-        <v>0.076543</v>
+        <v>0.077863</v>
       </c>
       <c r="C282" t="n">
-        <v>0.28934</v>
+        <v>0.280206</v>
       </c>
     </row>
     <row r="283">
@@ -4093,10 +4093,10 @@
         </is>
       </c>
       <c r="B283" t="n">
-        <v>0.07708</v>
+        <v>0.077912</v>
       </c>
       <c r="C283" t="n">
-        <v>0.286802</v>
+        <v>0.277635</v>
       </c>
     </row>
     <row r="284">
@@ -4106,10 +4106,10 @@
         </is>
       </c>
       <c r="B284" t="n">
-        <v>0.077419</v>
+        <v>0.078084</v>
       </c>
       <c r="C284" t="n">
-        <v>0.284264</v>
+        <v>0.275064</v>
       </c>
     </row>
     <row r="285">
@@ -4119,10 +4119,10 @@
         </is>
       </c>
       <c r="B285" t="n">
-        <v>0.077863</v>
+        <v>0.07843899999999999</v>
       </c>
       <c r="C285" t="n">
-        <v>0.281726</v>
+        <v>0.272494</v>
       </c>
     </row>
     <row r="286">
@@ -4132,10 +4132,10 @@
         </is>
       </c>
       <c r="B286" t="n">
-        <v>0.077912</v>
+        <v>0.07921499999999999</v>
       </c>
       <c r="C286" t="n">
-        <v>0.279188</v>
+        <v>0.269923</v>
       </c>
     </row>
     <row r="287">
@@ -4145,10 +4145,10 @@
         </is>
       </c>
       <c r="B287" t="n">
-        <v>0.078084</v>
+        <v>0.080791</v>
       </c>
       <c r="C287" t="n">
-        <v>0.27665</v>
+        <v>0.267352</v>
       </c>
     </row>
     <row r="288">
@@ -4158,10 +4158,10 @@
         </is>
       </c>
       <c r="B288" t="n">
-        <v>0.07843899999999999</v>
+        <v>0.08092199999999999</v>
       </c>
       <c r="C288" t="n">
-        <v>0.274112</v>
+        <v>0.264781</v>
       </c>
     </row>
     <row r="289">
@@ -4171,10 +4171,10 @@
         </is>
       </c>
       <c r="B289" t="n">
-        <v>0.07921499999999999</v>
+        <v>0.080995</v>
       </c>
       <c r="C289" t="n">
-        <v>0.271574</v>
+        <v>0.262211</v>
       </c>
     </row>
     <row r="290">
@@ -4184,10 +4184,10 @@
         </is>
       </c>
       <c r="B290" t="n">
-        <v>0.080791</v>
+        <v>0.081607</v>
       </c>
       <c r="C290" t="n">
-        <v>0.269036</v>
+        <v>0.25964</v>
       </c>
     </row>
     <row r="291">
@@ -4197,10 +4197,10 @@
         </is>
       </c>
       <c r="B291" t="n">
-        <v>0.08092199999999999</v>
+        <v>0.081758</v>
       </c>
       <c r="C291" t="n">
-        <v>0.266497</v>
+        <v>0.257069</v>
       </c>
     </row>
     <row r="292">
@@ -4210,10 +4210,10 @@
         </is>
       </c>
       <c r="B292" t="n">
-        <v>0.080995</v>
+        <v>0.082479</v>
       </c>
       <c r="C292" t="n">
-        <v>0.263959</v>
+        <v>0.254499</v>
       </c>
     </row>
     <row r="293">
@@ -4223,10 +4223,10 @@
         </is>
       </c>
       <c r="B293" t="n">
-        <v>0.081607</v>
+        <v>0.082594</v>
       </c>
       <c r="C293" t="n">
-        <v>0.261421</v>
+        <v>0.251928</v>
       </c>
     </row>
     <row r="294">
@@ -4236,10 +4236,10 @@
         </is>
       </c>
       <c r="B294" t="n">
-        <v>0.081758</v>
+        <v>0.08294600000000001</v>
       </c>
       <c r="C294" t="n">
-        <v>0.258883</v>
+        <v>0.249357</v>
       </c>
     </row>
     <row r="295">
@@ -4249,10 +4249,10 @@
         </is>
       </c>
       <c r="B295" t="n">
-        <v>0.082479</v>
+        <v>0.083297</v>
       </c>
       <c r="C295" t="n">
-        <v>0.256345</v>
+        <v>0.246787</v>
       </c>
     </row>
     <row r="296">
@@ -4262,10 +4262,10 @@
         </is>
       </c>
       <c r="B296" t="n">
-        <v>0.082594</v>
+        <v>0.08384800000000001</v>
       </c>
       <c r="C296" t="n">
-        <v>0.253807</v>
+        <v>0.244216</v>
       </c>
     </row>
     <row r="297">
@@ -4275,10 +4275,10 @@
         </is>
       </c>
       <c r="B297" t="n">
-        <v>0.08294600000000001</v>
+        <v>0.084221</v>
       </c>
       <c r="C297" t="n">
-        <v>0.251269</v>
+        <v>0.241645</v>
       </c>
     </row>
     <row r="298">
@@ -4288,10 +4288,10 @@
         </is>
       </c>
       <c r="B298" t="n">
-        <v>0.083297</v>
+        <v>0.08483599999999999</v>
       </c>
       <c r="C298" t="n">
-        <v>0.248731</v>
+        <v>0.239075</v>
       </c>
     </row>
     <row r="299">
@@ -4301,10 +4301,10 @@
         </is>
       </c>
       <c r="B299" t="n">
-        <v>0.08384800000000001</v>
+        <v>0.087156</v>
       </c>
       <c r="C299" t="n">
-        <v>0.246193</v>
+        <v>0.236504</v>
       </c>
     </row>
     <row r="300">
@@ -4314,10 +4314,10 @@
         </is>
       </c>
       <c r="B300" t="n">
-        <v>0.084221</v>
+        <v>0.08717999999999999</v>
       </c>
       <c r="C300" t="n">
-        <v>0.243655</v>
+        <v>0.233933</v>
       </c>
     </row>
     <row r="301">
@@ -4327,10 +4327,10 @@
         </is>
       </c>
       <c r="B301" t="n">
-        <v>0.08483599999999999</v>
+        <v>0.08820799999999999</v>
       </c>
       <c r="C301" t="n">
-        <v>0.241117</v>
+        <v>0.231362</v>
       </c>
     </row>
     <row r="302">
@@ -4340,10 +4340,10 @@
         </is>
       </c>
       <c r="B302" t="n">
-        <v>0.087156</v>
+        <v>0.088889</v>
       </c>
       <c r="C302" t="n">
-        <v>0.238579</v>
+        <v>0.228792</v>
       </c>
     </row>
     <row r="303">
@@ -4353,10 +4353,10 @@
         </is>
       </c>
       <c r="B303" t="n">
-        <v>0.08717999999999999</v>
+        <v>0.08917700000000001</v>
       </c>
       <c r="C303" t="n">
-        <v>0.236041</v>
+        <v>0.226221</v>
       </c>
     </row>
     <row r="304">
@@ -4366,10 +4366,10 @@
         </is>
       </c>
       <c r="B304" t="n">
-        <v>0.08820799999999999</v>
+        <v>0.089823</v>
       </c>
       <c r="C304" t="n">
-        <v>0.233503</v>
+        <v>0.22365</v>
       </c>
     </row>
     <row r="305">
@@ -4379,10 +4379,10 @@
         </is>
       </c>
       <c r="B305" t="n">
-        <v>0.088889</v>
+        <v>0.090348</v>
       </c>
       <c r="C305" t="n">
-        <v>0.230964</v>
+        <v>0.22108</v>
       </c>
     </row>
     <row r="306">
@@ -4392,10 +4392,10 @@
         </is>
       </c>
       <c r="B306" t="n">
-        <v>0.08917700000000001</v>
+        <v>0.091434</v>
       </c>
       <c r="C306" t="n">
-        <v>0.228426</v>
+        <v>0.218509</v>
       </c>
     </row>
     <row r="307">
@@ -4405,10 +4405,10 @@
         </is>
       </c>
       <c r="B307" t="n">
-        <v>0.089823</v>
+        <v>0.0929</v>
       </c>
       <c r="C307" t="n">
-        <v>0.225888</v>
+        <v>0.215938</v>
       </c>
     </row>
     <row r="308">
@@ -4418,10 +4418,10 @@
         </is>
       </c>
       <c r="B308" t="n">
-        <v>0.090265</v>
+        <v>0.093496</v>
       </c>
       <c r="C308" t="n">
-        <v>0.22335</v>
+        <v>0.213368</v>
       </c>
     </row>
     <row r="309">
@@ -4431,10 +4431,10 @@
         </is>
       </c>
       <c r="B309" t="n">
-        <v>0.090348</v>
+        <v>0.09744</v>
       </c>
       <c r="C309" t="n">
-        <v>0.220812</v>
+        <v>0.210797</v>
       </c>
     </row>
     <row r="310">
@@ -4444,10 +4444,10 @@
         </is>
       </c>
       <c r="B310" t="n">
-        <v>0.091434</v>
+        <v>0.097923</v>
       </c>
       <c r="C310" t="n">
-        <v>0.218274</v>
+        <v>0.208226</v>
       </c>
     </row>
     <row r="311">
@@ -4457,10 +4457,10 @@
         </is>
       </c>
       <c r="B311" t="n">
-        <v>0.0929</v>
+        <v>0.09847400000000001</v>
       </c>
       <c r="C311" t="n">
-        <v>0.215736</v>
+        <v>0.205656</v>
       </c>
     </row>
     <row r="312">
@@ -4470,10 +4470,10 @@
         </is>
       </c>
       <c r="B312" t="n">
-        <v>0.09744</v>
+        <v>0.09907299999999999</v>
       </c>
       <c r="C312" t="n">
-        <v>0.213198</v>
+        <v>0.203085</v>
       </c>
     </row>
     <row r="313">
@@ -4483,10 +4483,10 @@
         </is>
       </c>
       <c r="B313" t="n">
-        <v>0.097923</v>
+        <v>0.09943399999999999</v>
       </c>
       <c r="C313" t="n">
-        <v>0.21066</v>
+        <v>0.200514</v>
       </c>
     </row>
     <row r="314">
@@ -4496,10 +4496,10 @@
         </is>
       </c>
       <c r="B314" t="n">
-        <v>0.09847400000000001</v>
+        <v>0.100571</v>
       </c>
       <c r="C314" t="n">
-        <v>0.208122</v>
+        <v>0.197943</v>
       </c>
     </row>
     <row r="315">
@@ -4509,10 +4509,10 @@
         </is>
       </c>
       <c r="B315" t="n">
-        <v>0.09907299999999999</v>
+        <v>0.101335</v>
       </c>
       <c r="C315" t="n">
-        <v>0.205584</v>
+        <v>0.195373</v>
       </c>
     </row>
     <row r="316">
@@ -4522,10 +4522,10 @@
         </is>
       </c>
       <c r="B316" t="n">
-        <v>0.09943399999999999</v>
+        <v>0.103451</v>
       </c>
       <c r="C316" t="n">
-        <v>0.203046</v>
+        <v>0.192802</v>
       </c>
     </row>
     <row r="317">
@@ -4535,10 +4535,10 @@
         </is>
       </c>
       <c r="B317" t="n">
-        <v>0.100571</v>
+        <v>0.103942</v>
       </c>
       <c r="C317" t="n">
-        <v>0.200508</v>
+        <v>0.190231</v>
       </c>
     </row>
     <row r="318">
@@ -4548,10 +4548,10 @@
         </is>
       </c>
       <c r="B318" t="n">
-        <v>0.101335</v>
+        <v>0.10427</v>
       </c>
       <c r="C318" t="n">
-        <v>0.19797</v>
+        <v>0.187661</v>
       </c>
     </row>
     <row r="319">
@@ -4561,10 +4561,10 @@
         </is>
       </c>
       <c r="B319" t="n">
-        <v>0.103451</v>
+        <v>0.106391</v>
       </c>
       <c r="C319" t="n">
-        <v>0.195431</v>
+        <v>0.18509</v>
       </c>
     </row>
     <row r="320">
@@ -4574,10 +4574,10 @@
         </is>
       </c>
       <c r="B320" t="n">
-        <v>0.103942</v>
+        <v>0.106564</v>
       </c>
       <c r="C320" t="n">
-        <v>0.192893</v>
+        <v>0.182519</v>
       </c>
     </row>
     <row r="321">
@@ -4587,10 +4587,10 @@
         </is>
       </c>
       <c r="B321" t="n">
-        <v>0.10427</v>
+        <v>0.106852</v>
       </c>
       <c r="C321" t="n">
-        <v>0.190355</v>
+        <v>0.179949</v>
       </c>
     </row>
     <row r="322">
@@ -4600,10 +4600,10 @@
         </is>
       </c>
       <c r="B322" t="n">
-        <v>0.105774</v>
+        <v>0.110708</v>
       </c>
       <c r="C322" t="n">
-        <v>0.187817</v>
+        <v>0.177378</v>
       </c>
     </row>
     <row r="323">
@@ -4613,10 +4613,10 @@
         </is>
       </c>
       <c r="B323" t="n">
-        <v>0.106391</v>
+        <v>0.112861</v>
       </c>
       <c r="C323" t="n">
-        <v>0.185279</v>
+        <v>0.174807</v>
       </c>
     </row>
     <row r="324">
@@ -4626,10 +4626,10 @@
         </is>
       </c>
       <c r="B324" t="n">
-        <v>0.106564</v>
+        <v>0.11394</v>
       </c>
       <c r="C324" t="n">
-        <v>0.182741</v>
+        <v>0.172237</v>
       </c>
     </row>
     <row r="325">
@@ -4639,10 +4639,10 @@
         </is>
       </c>
       <c r="B325" t="n">
-        <v>0.106852</v>
+        <v>0.114179</v>
       </c>
       <c r="C325" t="n">
-        <v>0.180203</v>
+        <v>0.169666</v>
       </c>
     </row>
     <row r="326">
@@ -4652,10 +4652,10 @@
         </is>
       </c>
       <c r="B326" t="n">
-        <v>0.110708</v>
+        <v>0.11468</v>
       </c>
       <c r="C326" t="n">
-        <v>0.177665</v>
+        <v>0.167095</v>
       </c>
     </row>
     <row r="327">
@@ -4665,10 +4665,10 @@
         </is>
       </c>
       <c r="B327" t="n">
-        <v>0.112861</v>
+        <v>0.114922</v>
       </c>
       <c r="C327" t="n">
-        <v>0.175127</v>
+        <v>0.164524</v>
       </c>
     </row>
     <row r="328">
@@ -4678,10 +4678,10 @@
         </is>
       </c>
       <c r="B328" t="n">
-        <v>0.11394</v>
+        <v>0.115972</v>
       </c>
       <c r="C328" t="n">
-        <v>0.172589</v>
+        <v>0.161954</v>
       </c>
     </row>
     <row r="329">
@@ -4691,10 +4691,10 @@
         </is>
       </c>
       <c r="B329" t="n">
-        <v>0.114179</v>
+        <v>0.117496</v>
       </c>
       <c r="C329" t="n">
-        <v>0.170051</v>
+        <v>0.159383</v>
       </c>
     </row>
     <row r="330">
@@ -4704,10 +4704,10 @@
         </is>
       </c>
       <c r="B330" t="n">
-        <v>0.11468</v>
+        <v>0.117846</v>
       </c>
       <c r="C330" t="n">
-        <v>0.167513</v>
+        <v>0.156812</v>
       </c>
     </row>
     <row r="331">
@@ -4717,10 +4717,10 @@
         </is>
       </c>
       <c r="B331" t="n">
-        <v>0.114922</v>
+        <v>0.119464</v>
       </c>
       <c r="C331" t="n">
-        <v>0.164975</v>
+        <v>0.154242</v>
       </c>
     </row>
     <row r="332">
@@ -4730,10 +4730,10 @@
         </is>
       </c>
       <c r="B332" t="n">
-        <v>0.115972</v>
+        <v>0.120448</v>
       </c>
       <c r="C332" t="n">
-        <v>0.162437</v>
+        <v>0.151671</v>
       </c>
     </row>
     <row r="333">
@@ -4743,10 +4743,10 @@
         </is>
       </c>
       <c r="B333" t="n">
-        <v>0.117496</v>
+        <v>0.121637</v>
       </c>
       <c r="C333" t="n">
-        <v>0.159898</v>
+        <v>0.1491</v>
       </c>
     </row>
     <row r="334">
@@ -4756,10 +4756,10 @@
         </is>
       </c>
       <c r="B334" t="n">
-        <v>0.117846</v>
+        <v>0.12397</v>
       </c>
       <c r="C334" t="n">
-        <v>0.15736</v>
+        <v>0.14653</v>
       </c>
     </row>
     <row r="335">
@@ -4769,10 +4769,10 @@
         </is>
       </c>
       <c r="B335" t="n">
-        <v>0.119464</v>
+        <v>0.124167</v>
       </c>
       <c r="C335" t="n">
-        <v>0.154822</v>
+        <v>0.143959</v>
       </c>
     </row>
     <row r="336">
@@ -4782,10 +4782,10 @@
         </is>
       </c>
       <c r="B336" t="n">
-        <v>0.120448</v>
+        <v>0.126891</v>
       </c>
       <c r="C336" t="n">
-        <v>0.152284</v>
+        <v>0.141388</v>
       </c>
     </row>
     <row r="337">
@@ -4795,10 +4795,10 @@
         </is>
       </c>
       <c r="B337" t="n">
-        <v>0.121637</v>
+        <v>0.128021</v>
       </c>
       <c r="C337" t="n">
-        <v>0.149746</v>
+        <v>0.138817</v>
       </c>
     </row>
     <row r="338">
@@ -4808,10 +4808,10 @@
         </is>
       </c>
       <c r="B338" t="n">
-        <v>0.12397</v>
+        <v>0.128976</v>
       </c>
       <c r="C338" t="n">
-        <v>0.147208</v>
+        <v>0.136247</v>
       </c>
     </row>
     <row r="339">
@@ -4821,10 +4821,10 @@
         </is>
       </c>
       <c r="B339" t="n">
-        <v>0.124167</v>
+        <v>0.130439</v>
       </c>
       <c r="C339" t="n">
-        <v>0.14467</v>
+        <v>0.133676</v>
       </c>
     </row>
     <row r="340">
@@ -4834,10 +4834,10 @@
         </is>
       </c>
       <c r="B340" t="n">
-        <v>0.126891</v>
+        <v>0.130821</v>
       </c>
       <c r="C340" t="n">
-        <v>0.142132</v>
+        <v>0.131105</v>
       </c>
     </row>
     <row r="341">
@@ -4847,10 +4847,10 @@
         </is>
       </c>
       <c r="B341" t="n">
-        <v>0.128021</v>
+        <v>0.130916</v>
       </c>
       <c r="C341" t="n">
-        <v>0.139594</v>
+        <v>0.128535</v>
       </c>
     </row>
     <row r="342">
@@ -4860,10 +4860,10 @@
         </is>
       </c>
       <c r="B342" t="n">
-        <v>0.128976</v>
+        <v>0.131982</v>
       </c>
       <c r="C342" t="n">
-        <v>0.137056</v>
+        <v>0.125964</v>
       </c>
     </row>
     <row r="343">
@@ -4873,10 +4873,10 @@
         </is>
       </c>
       <c r="B343" t="n">
-        <v>0.130439</v>
+        <v>0.135669</v>
       </c>
       <c r="C343" t="n">
-        <v>0.134518</v>
+        <v>0.123393</v>
       </c>
     </row>
     <row r="344">
@@ -4886,10 +4886,10 @@
         </is>
       </c>
       <c r="B344" t="n">
-        <v>0.130821</v>
+        <v>0.135827</v>
       </c>
       <c r="C344" t="n">
-        <v>0.13198</v>
+        <v>0.120823</v>
       </c>
     </row>
     <row r="345">
@@ -4899,10 +4899,10 @@
         </is>
       </c>
       <c r="B345" t="n">
-        <v>0.130916</v>
+        <v>0.13733</v>
       </c>
       <c r="C345" t="n">
-        <v>0.129442</v>
+        <v>0.118252</v>
       </c>
     </row>
     <row r="346">
@@ -4912,10 +4912,10 @@
         </is>
       </c>
       <c r="B346" t="n">
-        <v>0.131982</v>
+        <v>0.138613</v>
       </c>
       <c r="C346" t="n">
-        <v>0.126904</v>
+        <v>0.115681</v>
       </c>
     </row>
     <row r="347">
@@ -4925,10 +4925,10 @@
         </is>
       </c>
       <c r="B347" t="n">
-        <v>0.135669</v>
+        <v>0.138762</v>
       </c>
       <c r="C347" t="n">
-        <v>0.124365</v>
+        <v>0.113111</v>
       </c>
     </row>
     <row r="348">
@@ -4938,10 +4938,10 @@
         </is>
       </c>
       <c r="B348" t="n">
-        <v>0.135827</v>
+        <v>0.140029</v>
       </c>
       <c r="C348" t="n">
-        <v>0.121827</v>
+        <v>0.11054</v>
       </c>
     </row>
     <row r="349">
@@ -4951,10 +4951,10 @@
         </is>
       </c>
       <c r="B349" t="n">
-        <v>0.13733</v>
+        <v>0.140099</v>
       </c>
       <c r="C349" t="n">
-        <v>0.119289</v>
+        <v>0.107969</v>
       </c>
     </row>
     <row r="350">
@@ -4964,10 +4964,10 @@
         </is>
       </c>
       <c r="B350" t="n">
-        <v>0.138613</v>
+        <v>0.140214</v>
       </c>
       <c r="C350" t="n">
-        <v>0.116751</v>
+        <v>0.105398</v>
       </c>
     </row>
     <row r="351">
@@ -4977,10 +4977,10 @@
         </is>
       </c>
       <c r="B351" t="n">
-        <v>0.138762</v>
+        <v>0.143039</v>
       </c>
       <c r="C351" t="n">
-        <v>0.114213</v>
+        <v>0.102828</v>
       </c>
     </row>
     <row r="352">
@@ -4990,10 +4990,10 @@
         </is>
       </c>
       <c r="B352" t="n">
-        <v>0.140029</v>
+        <v>0.144579</v>
       </c>
       <c r="C352" t="n">
-        <v>0.111675</v>
+        <v>0.100257</v>
       </c>
     </row>
     <row r="353">
@@ -5003,10 +5003,10 @@
         </is>
       </c>
       <c r="B353" t="n">
-        <v>0.140099</v>
+        <v>0.145291</v>
       </c>
       <c r="C353" t="n">
-        <v>0.109137</v>
+        <v>0.097686</v>
       </c>
     </row>
     <row r="354">
@@ -5016,10 +5016,10 @@
         </is>
       </c>
       <c r="B354" t="n">
-        <v>0.140214</v>
+        <v>0.145554</v>
       </c>
       <c r="C354" t="n">
-        <v>0.106599</v>
+        <v>0.09511600000000001</v>
       </c>
     </row>
     <row r="355">
@@ -5029,10 +5029,10 @@
         </is>
       </c>
       <c r="B355" t="n">
-        <v>0.143039</v>
+        <v>0.151419</v>
       </c>
       <c r="C355" t="n">
-        <v>0.104061</v>
+        <v>0.092545</v>
       </c>
     </row>
     <row r="356">
@@ -5042,10 +5042,10 @@
         </is>
       </c>
       <c r="B356" t="n">
-        <v>0.144579</v>
+        <v>0.151465</v>
       </c>
       <c r="C356" t="n">
-        <v>0.101523</v>
+        <v>0.089974</v>
       </c>
     </row>
     <row r="357">
@@ -5055,10 +5055,10 @@
         </is>
       </c>
       <c r="B357" t="n">
-        <v>0.145291</v>
+        <v>0.15511</v>
       </c>
       <c r="C357" t="n">
-        <v>0.098985</v>
+        <v>0.087404</v>
       </c>
     </row>
     <row r="358">
@@ -5068,10 +5068,10 @@
         </is>
       </c>
       <c r="B358" t="n">
-        <v>0.145554</v>
+        <v>0.15559</v>
       </c>
       <c r="C358" t="n">
-        <v>0.096447</v>
+        <v>0.08483300000000001</v>
       </c>
     </row>
     <row r="359">
@@ -5081,10 +5081,10 @@
         </is>
       </c>
       <c r="B359" t="n">
-        <v>0.151419</v>
+        <v>0.155726</v>
       </c>
       <c r="C359" t="n">
-        <v>0.09390900000000001</v>
+        <v>0.082262</v>
       </c>
     </row>
     <row r="360">
@@ -5094,10 +5094,10 @@
         </is>
       </c>
       <c r="B360" t="n">
-        <v>0.151465</v>
+        <v>0.158503</v>
       </c>
       <c r="C360" t="n">
-        <v>0.09137099999999999</v>
+        <v>0.079692</v>
       </c>
     </row>
     <row r="361">
@@ -5107,10 +5107,10 @@
         </is>
       </c>
       <c r="B361" t="n">
-        <v>0.15511</v>
+        <v>0.16241</v>
       </c>
       <c r="C361" t="n">
-        <v>0.08883199999999999</v>
+        <v>0.077121</v>
       </c>
     </row>
     <row r="362">
@@ -5120,10 +5120,10 @@
         </is>
       </c>
       <c r="B362" t="n">
-        <v>0.15559</v>
+        <v>0.179571</v>
       </c>
       <c r="C362" t="n">
-        <v>0.086294</v>
+        <v>0.07455000000000001</v>
       </c>
     </row>
     <row r="363">
@@ -5133,10 +5133,10 @@
         </is>
       </c>
       <c r="B363" t="n">
-        <v>0.155726</v>
+        <v>0.183042</v>
       </c>
       <c r="C363" t="n">
-        <v>0.083756</v>
+        <v>0.071979</v>
       </c>
     </row>
     <row r="364">
@@ -5146,10 +5146,10 @@
         </is>
       </c>
       <c r="B364" t="n">
-        <v>0.158503</v>
+        <v>0.189387</v>
       </c>
       <c r="C364" t="n">
-        <v>0.081218</v>
+        <v>0.069409</v>
       </c>
     </row>
     <row r="365">
@@ -5159,10 +5159,10 @@
         </is>
       </c>
       <c r="B365" t="n">
-        <v>0.16241</v>
+        <v>0.193249</v>
       </c>
       <c r="C365" t="n">
-        <v>0.07868</v>
+        <v>0.06683799999999999</v>
       </c>
     </row>
     <row r="366">
@@ -5172,10 +5172,10 @@
         </is>
       </c>
       <c r="B366" t="n">
-        <v>0.179571</v>
+        <v>0.195388</v>
       </c>
       <c r="C366" t="n">
-        <v>0.076142</v>
+        <v>0.064267</v>
       </c>
     </row>
     <row r="367">
@@ -5185,10 +5185,10 @@
         </is>
       </c>
       <c r="B367" t="n">
-        <v>0.183042</v>
+        <v>0.200683</v>
       </c>
       <c r="C367" t="n">
-        <v>0.073604</v>
+        <v>0.061697</v>
       </c>
     </row>
     <row r="368">
@@ -5198,10 +5198,10 @@
         </is>
       </c>
       <c r="B368" t="n">
-        <v>0.189387</v>
+        <v>0.202141</v>
       </c>
       <c r="C368" t="n">
-        <v>0.071066</v>
+        <v>0.059126</v>
       </c>
     </row>
     <row r="369">
@@ -5211,10 +5211,10 @@
         </is>
       </c>
       <c r="B369" t="n">
-        <v>0.193249</v>
+        <v>0.21126</v>
       </c>
       <c r="C369" t="n">
-        <v>0.06852800000000001</v>
+        <v>0.056555</v>
       </c>
     </row>
     <row r="370">
@@ -5224,10 +5224,10 @@
         </is>
       </c>
       <c r="B370" t="n">
-        <v>0.195388</v>
+        <v>0.212282</v>
       </c>
       <c r="C370" t="n">
-        <v>0.06598999999999999</v>
+        <v>0.053985</v>
       </c>
     </row>
     <row r="371">
@@ -5237,10 +5237,10 @@
         </is>
       </c>
       <c r="B371" t="n">
-        <v>0.200683</v>
+        <v>0.213977</v>
       </c>
       <c r="C371" t="n">
-        <v>0.06345199999999999</v>
+        <v>0.051414</v>
       </c>
     </row>
     <row r="372">
@@ -5250,10 +5250,10 @@
         </is>
       </c>
       <c r="B372" t="n">
-        <v>0.202141</v>
+        <v>0.224095</v>
       </c>
       <c r="C372" t="n">
-        <v>0.060914</v>
+        <v>0.048843</v>
       </c>
     </row>
     <row r="373">
@@ -5263,10 +5263,10 @@
         </is>
       </c>
       <c r="B373" t="n">
-        <v>0.21126</v>
+        <v>0.229443</v>
       </c>
       <c r="C373" t="n">
-        <v>0.058376</v>
+        <v>0.046272</v>
       </c>
     </row>
     <row r="374">
@@ -5276,10 +5276,10 @@
         </is>
       </c>
       <c r="B374" t="n">
-        <v>0.212282</v>
+        <v>0.235662</v>
       </c>
       <c r="C374" t="n">
-        <v>0.055838</v>
+        <v>0.043702</v>
       </c>
     </row>
     <row r="375">
@@ -5289,10 +5289,10 @@
         </is>
       </c>
       <c r="B375" t="n">
-        <v>0.213977</v>
+        <v>0.279391</v>
       </c>
       <c r="C375" t="n">
-        <v>0.053299</v>
+        <v>0.041131</v>
       </c>
     </row>
     <row r="376">
@@ -5302,10 +5302,10 @@
         </is>
       </c>
       <c r="B376" t="n">
-        <v>0.224095</v>
+        <v>0.28675</v>
       </c>
       <c r="C376" t="n">
-        <v>0.050761</v>
+        <v>0.03856</v>
       </c>
     </row>
     <row r="377">
@@ -5315,10 +5315,10 @@
         </is>
       </c>
       <c r="B377" t="n">
-        <v>0.229443</v>
+        <v>0.303016</v>
       </c>
       <c r="C377" t="n">
-        <v>0.048223</v>
+        <v>0.03599</v>
       </c>
     </row>
     <row r="378">
@@ -5328,10 +5328,10 @@
         </is>
       </c>
       <c r="B378" t="n">
-        <v>0.235662</v>
+        <v>0.359445</v>
       </c>
       <c r="C378" t="n">
-        <v>0.045685</v>
+        <v>0.033419</v>
       </c>
     </row>
     <row r="379">
@@ -5341,10 +5341,10 @@
         </is>
       </c>
       <c r="B379" t="n">
-        <v>0.279391</v>
+        <v>0.371876</v>
       </c>
       <c r="C379" t="n">
-        <v>0.043147</v>
+        <v>0.030848</v>
       </c>
     </row>
     <row r="380">
@@ -5354,10 +5354,10 @@
         </is>
       </c>
       <c r="B380" t="n">
-        <v>0.28675</v>
+        <v>0.397465</v>
       </c>
       <c r="C380" t="n">
-        <v>0.040609</v>
+        <v>0.028278</v>
       </c>
     </row>
     <row r="381">
@@ -5367,10 +5367,10 @@
         </is>
       </c>
       <c r="B381" t="n">
-        <v>0.303016</v>
+        <v>0.400164</v>
       </c>
       <c r="C381" t="n">
-        <v>0.038071</v>
+        <v>0.025707</v>
       </c>
     </row>
     <row r="382">
@@ -5380,10 +5380,10 @@
         </is>
       </c>
       <c r="B382" t="n">
-        <v>0.359445</v>
+        <v>0.40983</v>
       </c>
       <c r="C382" t="n">
-        <v>0.035533</v>
+        <v>0.023136</v>
       </c>
     </row>
     <row r="383">
@@ -5393,10 +5393,10 @@
         </is>
       </c>
       <c r="B383" t="n">
-        <v>0.371876</v>
+        <v>0.419404</v>
       </c>
       <c r="C383" t="n">
-        <v>0.032995</v>
+        <v>0.020566</v>
       </c>
     </row>
     <row r="384">
@@ -5406,10 +5406,10 @@
         </is>
       </c>
       <c r="B384" t="n">
-        <v>0.397465</v>
+        <v>0.6049369999999999</v>
       </c>
       <c r="C384" t="n">
-        <v>0.030457</v>
+        <v>0.017995</v>
       </c>
     </row>
     <row r="385">
@@ -5419,10 +5419,10 @@
         </is>
       </c>
       <c r="B385" t="n">
-        <v>0.400164</v>
+        <v>0.620194</v>
       </c>
       <c r="C385" t="n">
-        <v>0.027919</v>
+        <v>0.015424</v>
       </c>
     </row>
     <row r="386">
@@ -5432,10 +5432,10 @@
         </is>
       </c>
       <c r="B386" t="n">
-        <v>0.40983</v>
+        <v>0.634074</v>
       </c>
       <c r="C386" t="n">
-        <v>0.025381</v>
+        <v>0.012853</v>
       </c>
     </row>
     <row r="387">
@@ -5445,10 +5445,10 @@
         </is>
       </c>
       <c r="B387" t="n">
-        <v>0.419404</v>
+        <v>0.672434</v>
       </c>
       <c r="C387" t="n">
-        <v>0.022843</v>
+        <v>0.010283</v>
       </c>
     </row>
     <row r="388">
@@ -5458,10 +5458,10 @@
         </is>
       </c>
       <c r="B388" t="n">
-        <v>0.6049369999999999</v>
+        <v>0.711338</v>
       </c>
       <c r="C388" t="n">
-        <v>0.020305</v>
+        <v>0.007712</v>
       </c>
     </row>
     <row r="389">
@@ -5471,10 +5471,10 @@
         </is>
       </c>
       <c r="B389" t="n">
-        <v>0.620194</v>
+        <v>0.76535</v>
       </c>
       <c r="C389" t="n">
-        <v>0.017766</v>
+        <v>0.005141</v>
       </c>
     </row>
     <row r="390">
@@ -5484,75 +5484,75 @@
         </is>
       </c>
       <c r="B390" t="n">
-        <v>0.634074</v>
+        <v>1.015082</v>
       </c>
       <c r="C390" t="n">
-        <v>0.015228</v>
+        <v>0.002571</v>
       </c>
     </row>
     <row r="391">
       <c r="A391" t="inlineStr">
         <is>
-          <t>Raw market</t>
+          <t>Adjusted target</t>
         </is>
       </c>
       <c r="B391" t="n">
-        <v>0.672434</v>
+        <v>0.000111</v>
       </c>
       <c r="C391" t="n">
-        <v>0.01269</v>
+        <v>1</v>
       </c>
     </row>
     <row r="392">
       <c r="A392" t="inlineStr">
         <is>
-          <t>Raw market</t>
+          <t>Adjusted target</t>
         </is>
       </c>
       <c r="B392" t="n">
-        <v>0.711338</v>
+        <v>0.000353</v>
       </c>
       <c r="C392" t="n">
-        <v>0.010152</v>
+        <v>0.997429</v>
       </c>
     </row>
     <row r="393">
       <c r="A393" t="inlineStr">
         <is>
-          <t>Raw market</t>
+          <t>Adjusted target</t>
         </is>
       </c>
       <c r="B393" t="n">
-        <v>0.76535</v>
+        <v>0.000614</v>
       </c>
       <c r="C393" t="n">
-        <v>0.007614</v>
+        <v>0.994859</v>
       </c>
     </row>
     <row r="394">
       <c r="A394" t="inlineStr">
         <is>
-          <t>Raw market</t>
+          <t>Adjusted target</t>
         </is>
       </c>
       <c r="B394" t="n">
-        <v>0.838984</v>
+        <v>0.001036</v>
       </c>
       <c r="C394" t="n">
-        <v>0.005076</v>
+        <v>0.9922879999999999</v>
       </c>
     </row>
     <row r="395">
       <c r="A395" t="inlineStr">
         <is>
-          <t>Raw market</t>
+          <t>Adjusted target</t>
         </is>
       </c>
       <c r="B395" t="n">
-        <v>1.015082</v>
+        <v>0.001117</v>
       </c>
       <c r="C395" t="n">
-        <v>0.002538</v>
+        <v>0.989717</v>
       </c>
     </row>
     <row r="396">
@@ -5562,10 +5562,10 @@
         </is>
       </c>
       <c r="B396" t="n">
-        <v>0.000111</v>
+        <v>0.001886</v>
       </c>
       <c r="C396" t="n">
-        <v>1</v>
+        <v>0.987147</v>
       </c>
     </row>
     <row r="397">
@@ -5575,10 +5575,10 @@
         </is>
       </c>
       <c r="B397" t="n">
-        <v>0.000351</v>
+        <v>0.002014</v>
       </c>
       <c r="C397" t="n">
-        <v>0.997462</v>
+        <v>0.984576</v>
       </c>
     </row>
     <row r="398">
@@ -5588,10 +5588,10 @@
         </is>
       </c>
       <c r="B398" t="n">
-        <v>0.000614</v>
+        <v>0.002255</v>
       </c>
       <c r="C398" t="n">
-        <v>0.994924</v>
+        <v>0.982005</v>
       </c>
     </row>
     <row r="399">
@@ -5601,10 +5601,10 @@
         </is>
       </c>
       <c r="B399" t="n">
-        <v>0.001035</v>
+        <v>0.002354</v>
       </c>
       <c r="C399" t="n">
-        <v>0.992386</v>
+        <v>0.979434</v>
       </c>
     </row>
     <row r="400">
@@ -5614,10 +5614,10 @@
         </is>
       </c>
       <c r="B400" t="n">
-        <v>0.001117</v>
+        <v>0.002624</v>
       </c>
       <c r="C400" t="n">
-        <v>0.989848</v>
+        <v>0.976864</v>
       </c>
     </row>
     <row r="401">
@@ -5627,10 +5627,10 @@
         </is>
       </c>
       <c r="B401" t="n">
-        <v>0.001862</v>
+        <v>0.002651</v>
       </c>
       <c r="C401" t="n">
-        <v>0.98731</v>
+        <v>0.974293</v>
       </c>
     </row>
     <row r="402">
@@ -5640,10 +5640,10 @@
         </is>
       </c>
       <c r="B402" t="n">
-        <v>0.002009</v>
+        <v>0.002742</v>
       </c>
       <c r="C402" t="n">
-        <v>0.984772</v>
+        <v>0.971722</v>
       </c>
     </row>
     <row r="403">
@@ -5653,10 +5653,10 @@
         </is>
       </c>
       <c r="B403" t="n">
-        <v>0.002241</v>
+        <v>0.002889</v>
       </c>
       <c r="C403" t="n">
-        <v>0.9822340000000001</v>
+        <v>0.969152</v>
       </c>
     </row>
     <row r="404">
@@ -5666,10 +5666,10 @@
         </is>
       </c>
       <c r="B404" t="n">
-        <v>0.002354</v>
+        <v>0.003231</v>
       </c>
       <c r="C404" t="n">
-        <v>0.979695</v>
+        <v>0.966581</v>
       </c>
     </row>
     <row r="405">
@@ -5679,10 +5679,10 @@
         </is>
       </c>
       <c r="B405" t="n">
-        <v>0.00255</v>
+        <v>0.003446</v>
       </c>
       <c r="C405" t="n">
-        <v>0.9771570000000001</v>
+        <v>0.96401</v>
       </c>
     </row>
     <row r="406">
@@ -5692,10 +5692,10 @@
         </is>
       </c>
       <c r="B406" t="n">
-        <v>0.002621</v>
+        <v>0.003478</v>
       </c>
       <c r="C406" t="n">
-        <v>0.974619</v>
+        <v>0.96144</v>
       </c>
     </row>
     <row r="407">
@@ -5705,10 +5705,10 @@
         </is>
       </c>
       <c r="B407" t="n">
-        <v>0.002725</v>
+        <v>0.004034</v>
       </c>
       <c r="C407" t="n">
-        <v>0.972081</v>
+        <v>0.958869</v>
       </c>
     </row>
     <row r="408">
@@ -5718,10 +5718,10 @@
         </is>
       </c>
       <c r="B408" t="n">
-        <v>0.002865</v>
+        <v>0.004536</v>
       </c>
       <c r="C408" t="n">
-        <v>0.969543</v>
+        <v>0.956298</v>
       </c>
     </row>
     <row r="409">
@@ -5731,10 +5731,10 @@
         </is>
       </c>
       <c r="B409" t="n">
-        <v>0.003224</v>
+        <v>0.004617</v>
       </c>
       <c r="C409" t="n">
-        <v>0.967005</v>
+        <v>0.953728</v>
       </c>
     </row>
     <row r="410">
@@ -5744,10 +5744,10 @@
         </is>
       </c>
       <c r="B410" t="n">
-        <v>0.003381</v>
+        <v>0.004823</v>
       </c>
       <c r="C410" t="n">
-        <v>0.964467</v>
+        <v>0.951157</v>
       </c>
     </row>
     <row r="411">
@@ -5757,10 +5757,10 @@
         </is>
       </c>
       <c r="B411" t="n">
-        <v>0.003475</v>
+        <v>0.00502</v>
       </c>
       <c r="C411" t="n">
-        <v>0.961929</v>
+        <v>0.948586</v>
       </c>
     </row>
     <row r="412">
@@ -5770,10 +5770,10 @@
         </is>
       </c>
       <c r="B412" t="n">
-        <v>0.003935</v>
+        <v>0.005109</v>
       </c>
       <c r="C412" t="n">
-        <v>0.959391</v>
+        <v>0.9460150000000001</v>
       </c>
     </row>
     <row r="413">
@@ -5783,10 +5783,10 @@
         </is>
       </c>
       <c r="B413" t="n">
-        <v>0.004535</v>
+        <v>0.005111</v>
       </c>
       <c r="C413" t="n">
-        <v>0.956853</v>
+        <v>0.943445</v>
       </c>
     </row>
     <row r="414">
@@ -5796,10 +5796,10 @@
         </is>
       </c>
       <c r="B414" t="n">
-        <v>0.004615</v>
+        <v>0.005257</v>
       </c>
       <c r="C414" t="n">
-        <v>0.954315</v>
+        <v>0.940874</v>
       </c>
     </row>
     <row r="415">
@@ -5809,10 +5809,10 @@
         </is>
       </c>
       <c r="B415" t="n">
-        <v>0.004823</v>
+        <v>0.005528</v>
       </c>
       <c r="C415" t="n">
-        <v>0.951777</v>
+        <v>0.938303</v>
       </c>
     </row>
     <row r="416">
@@ -5822,10 +5822,10 @@
         </is>
       </c>
       <c r="B416" t="n">
-        <v>0.004945</v>
+        <v>0.005785</v>
       </c>
       <c r="C416" t="n">
-        <v>0.9492390000000001</v>
+        <v>0.935733</v>
       </c>
     </row>
     <row r="417">
@@ -5835,10 +5835,10 @@
         </is>
       </c>
       <c r="B417" t="n">
-        <v>0.005079</v>
+        <v>0.005863</v>
       </c>
       <c r="C417" t="n">
-        <v>0.946701</v>
+        <v>0.933162</v>
       </c>
     </row>
     <row r="418">
@@ -5848,10 +5848,10 @@
         </is>
       </c>
       <c r="B418" t="n">
-        <v>0.005109</v>
+        <v>0.005966</v>
       </c>
       <c r="C418" t="n">
-        <v>0.9441619999999999</v>
+        <v>0.9305909999999999</v>
       </c>
     </row>
     <row r="419">
@@ -5861,10 +5861,10 @@
         </is>
       </c>
       <c r="B419" t="n">
-        <v>0.005249</v>
+        <v>0.006076</v>
       </c>
       <c r="C419" t="n">
-        <v>0.941624</v>
+        <v>0.928021</v>
       </c>
     </row>
     <row r="420">
@@ -5874,10 +5874,10 @@
         </is>
       </c>
       <c r="B420" t="n">
-        <v>0.005521</v>
+        <v>0.006421</v>
       </c>
       <c r="C420" t="n">
-        <v>0.939086</v>
+        <v>0.92545</v>
       </c>
     </row>
     <row r="421">
@@ -5887,10 +5887,10 @@
         </is>
       </c>
       <c r="B421" t="n">
-        <v>0.005672</v>
+        <v>0.006659</v>
       </c>
       <c r="C421" t="n">
-        <v>0.936548</v>
+        <v>0.922879</v>
       </c>
     </row>
     <row r="422">
@@ -5900,10 +5900,10 @@
         </is>
       </c>
       <c r="B422" t="n">
-        <v>0.00569</v>
+        <v>0.006925</v>
       </c>
       <c r="C422" t="n">
-        <v>0.93401</v>
+        <v>0.920308</v>
       </c>
     </row>
     <row r="423">
@@ -5913,10 +5913,10 @@
         </is>
       </c>
       <c r="B423" t="n">
-        <v>0.005837</v>
+        <v>0.00745</v>
       </c>
       <c r="C423" t="n">
-        <v>0.931472</v>
+        <v>0.9177380000000001</v>
       </c>
     </row>
     <row r="424">
@@ -5926,10 +5926,10 @@
         </is>
       </c>
       <c r="B424" t="n">
-        <v>0.006025</v>
+        <v>0.008384000000000001</v>
       </c>
       <c r="C424" t="n">
-        <v>0.928934</v>
+        <v>0.915167</v>
       </c>
     </row>
     <row r="425">
@@ -5939,10 +5939,10 @@
         </is>
       </c>
       <c r="B425" t="n">
-        <v>0.006083</v>
+        <v>0.008581</v>
       </c>
       <c r="C425" t="n">
-        <v>0.926396</v>
+        <v>0.912596</v>
       </c>
     </row>
     <row r="426">
@@ -5952,10 +5952,10 @@
         </is>
       </c>
       <c r="B426" t="n">
-        <v>0.00661</v>
+        <v>0.008940999999999999</v>
       </c>
       <c r="C426" t="n">
-        <v>0.923858</v>
+        <v>0.910026</v>
       </c>
     </row>
     <row r="427">
@@ -5965,10 +5965,10 @@
         </is>
       </c>
       <c r="B427" t="n">
-        <v>0.006898</v>
+        <v>0.009021</v>
       </c>
       <c r="C427" t="n">
-        <v>0.92132</v>
+        <v>0.907455</v>
       </c>
     </row>
     <row r="428">
@@ -5978,10 +5978,10 @@
         </is>
       </c>
       <c r="B428" t="n">
-        <v>0.007443</v>
+        <v>0.009095000000000001</v>
       </c>
       <c r="C428" t="n">
-        <v>0.918782</v>
+        <v>0.904884</v>
       </c>
     </row>
     <row r="429">
@@ -5991,10 +5991,10 @@
         </is>
       </c>
       <c r="B429" t="n">
-        <v>0.008369</v>
+        <v>0.009129</v>
       </c>
       <c r="C429" t="n">
-        <v>0.9162439999999999</v>
+        <v>0.9023139999999999</v>
       </c>
     </row>
     <row r="430">
@@ -6004,10 +6004,10 @@
         </is>
       </c>
       <c r="B430" t="n">
-        <v>0.008510999999999999</v>
+        <v>0.009228</v>
       </c>
       <c r="C430" t="n">
-        <v>0.913706</v>
+        <v>0.899743</v>
       </c>
     </row>
     <row r="431">
@@ -6017,10 +6017,10 @@
         </is>
       </c>
       <c r="B431" t="n">
-        <v>0.008832</v>
+        <v>0.009502999999999999</v>
       </c>
       <c r="C431" t="n">
-        <v>0.911168</v>
+        <v>0.897172</v>
       </c>
     </row>
     <row r="432">
@@ -6030,10 +6030,10 @@
         </is>
       </c>
       <c r="B432" t="n">
-        <v>0.008879</v>
+        <v>0.009587999999999999</v>
       </c>
       <c r="C432" t="n">
-        <v>0.908629</v>
+        <v>0.894602</v>
       </c>
     </row>
     <row r="433">
@@ -6043,10 +6043,10 @@
         </is>
       </c>
       <c r="B433" t="n">
-        <v>0.008987</v>
+        <v>0.009752</v>
       </c>
       <c r="C433" t="n">
-        <v>0.906091</v>
+        <v>0.892031</v>
       </c>
     </row>
     <row r="434">
@@ -6056,10 +6056,10 @@
         </is>
       </c>
       <c r="B434" t="n">
-        <v>0.009088000000000001</v>
+        <v>0.010071</v>
       </c>
       <c r="C434" t="n">
-        <v>0.9035530000000001</v>
+        <v>0.88946</v>
       </c>
     </row>
     <row r="435">
@@ -6069,10 +6069,10 @@
         </is>
       </c>
       <c r="B435" t="n">
-        <v>0.009202999999999999</v>
+        <v>0.010583</v>
       </c>
       <c r="C435" t="n">
-        <v>0.901015</v>
+        <v>0.886889</v>
       </c>
     </row>
     <row r="436">
@@ -6082,10 +6082,10 @@
         </is>
       </c>
       <c r="B436" t="n">
-        <v>0.009351999999999999</v>
+        <v>0.010764</v>
       </c>
       <c r="C436" t="n">
-        <v>0.898477</v>
+        <v>0.884319</v>
       </c>
     </row>
     <row r="437">
@@ -6095,10 +6095,10 @@
         </is>
       </c>
       <c r="B437" t="n">
-        <v>0.009497</v>
+        <v>0.011064</v>
       </c>
       <c r="C437" t="n">
-        <v>0.895939</v>
+        <v>0.881748</v>
       </c>
     </row>
     <row r="438">
@@ -6108,10 +6108,10 @@
         </is>
       </c>
       <c r="B438" t="n">
-        <v>0.009575999999999999</v>
+        <v>0.011066</v>
       </c>
       <c r="C438" t="n">
-        <v>0.893401</v>
+        <v>0.879177</v>
       </c>
     </row>
     <row r="439">
@@ -6121,10 +6121,10 @@
         </is>
       </c>
       <c r="B439" t="n">
-        <v>0.009894</v>
+        <v>0.011171</v>
       </c>
       <c r="C439" t="n">
-        <v>0.890863</v>
+        <v>0.876607</v>
       </c>
     </row>
     <row r="440">
@@ -6134,10 +6134,10 @@
         </is>
       </c>
       <c r="B440" t="n">
-        <v>0.010144</v>
+        <v>0.011225</v>
       </c>
       <c r="C440" t="n">
-        <v>0.888325</v>
+        <v>0.874036</v>
       </c>
     </row>
     <row r="441">
@@ -6147,10 +6147,10 @@
         </is>
       </c>
       <c r="B441" t="n">
-        <v>0.010628</v>
+        <v>0.011336</v>
       </c>
       <c r="C441" t="n">
-        <v>0.885787</v>
+        <v>0.871465</v>
       </c>
     </row>
     <row r="442">
@@ -6160,10 +6160,10 @@
         </is>
       </c>
       <c r="B442" t="n">
-        <v>0.010969</v>
+        <v>0.011565</v>
       </c>
       <c r="C442" t="n">
-        <v>0.883249</v>
+        <v>0.868895</v>
       </c>
     </row>
     <row r="443">
@@ -6173,10 +6173,10 @@
         </is>
       </c>
       <c r="B443" t="n">
-        <v>0.010975</v>
+        <v>0.011659</v>
       </c>
       <c r="C443" t="n">
-        <v>0.880711</v>
+        <v>0.866324</v>
       </c>
     </row>
     <row r="444">
@@ -6186,10 +6186,10 @@
         </is>
       </c>
       <c r="B444" t="n">
-        <v>0.011054</v>
+        <v>0.011964</v>
       </c>
       <c r="C444" t="n">
-        <v>0.878173</v>
+        <v>0.863753</v>
       </c>
     </row>
     <row r="445">
@@ -6199,10 +6199,10 @@
         </is>
       </c>
       <c r="B445" t="n">
-        <v>0.011225</v>
+        <v>0.012028</v>
       </c>
       <c r="C445" t="n">
-        <v>0.8756350000000001</v>
+        <v>0.861183</v>
       </c>
     </row>
     <row r="446">
@@ -6212,10 +6212,10 @@
         </is>
       </c>
       <c r="B446" t="n">
-        <v>0.0113</v>
+        <v>0.012272</v>
       </c>
       <c r="C446" t="n">
-        <v>0.873096</v>
+        <v>0.858612</v>
       </c>
     </row>
     <row r="447">
@@ -6225,10 +6225,10 @@
         </is>
       </c>
       <c r="B447" t="n">
-        <v>0.011512</v>
+        <v>0.012377</v>
       </c>
       <c r="C447" t="n">
-        <v>0.8705580000000001</v>
+        <v>0.8560410000000001</v>
       </c>
     </row>
     <row r="448">
@@ -6238,10 +6238,10 @@
         </is>
       </c>
       <c r="B448" t="n">
-        <v>0.011558</v>
+        <v>0.012386</v>
       </c>
       <c r="C448" t="n">
-        <v>0.86802</v>
+        <v>0.85347</v>
       </c>
     </row>
     <row r="449">
@@ -6251,10 +6251,10 @@
         </is>
       </c>
       <c r="B449" t="n">
-        <v>0.011617</v>
+        <v>0.012575</v>
       </c>
       <c r="C449" t="n">
-        <v>0.865482</v>
+        <v>0.8509</v>
       </c>
     </row>
     <row r="450">
@@ -6264,10 +6264,10 @@
         </is>
       </c>
       <c r="B450" t="n">
-        <v>0.012029</v>
+        <v>0.012647</v>
       </c>
       <c r="C450" t="n">
-        <v>0.862944</v>
+        <v>0.848329</v>
       </c>
     </row>
     <row r="451">
@@ -6277,10 +6277,10 @@
         </is>
       </c>
       <c r="B451" t="n">
-        <v>0.012368</v>
+        <v>0.013113</v>
       </c>
       <c r="C451" t="n">
-        <v>0.860406</v>
+        <v>0.845758</v>
       </c>
     </row>
     <row r="452">
@@ -6290,10 +6290,10 @@
         </is>
       </c>
       <c r="B452" t="n">
-        <v>0.012374</v>
+        <v>0.013116</v>
       </c>
       <c r="C452" t="n">
-        <v>0.857868</v>
+        <v>0.843188</v>
       </c>
     </row>
     <row r="453">
@@ -6303,10 +6303,10 @@
         </is>
       </c>
       <c r="B453" t="n">
-        <v>0.012571</v>
+        <v>0.013196</v>
       </c>
       <c r="C453" t="n">
-        <v>0.85533</v>
+        <v>0.8406169999999999</v>
       </c>
     </row>
     <row r="454">
@@ -6316,10 +6316,10 @@
         </is>
       </c>
       <c r="B454" t="n">
-        <v>0.012647</v>
+        <v>0.01382</v>
       </c>
       <c r="C454" t="n">
-        <v>0.852792</v>
+        <v>0.838046</v>
       </c>
     </row>
     <row r="455">
@@ -6329,10 +6329,10 @@
         </is>
       </c>
       <c r="B455" t="n">
-        <v>0.012988</v>
+        <v>0.013896</v>
       </c>
       <c r="C455" t="n">
-        <v>0.850254</v>
+        <v>0.835476</v>
       </c>
     </row>
     <row r="456">
@@ -6342,10 +6342,10 @@
         </is>
       </c>
       <c r="B456" t="n">
-        <v>0.013099</v>
+        <v>0.014196</v>
       </c>
       <c r="C456" t="n">
-        <v>0.847716</v>
+        <v>0.832905</v>
       </c>
     </row>
     <row r="457">
@@ -6355,10 +6355,10 @@
         </is>
       </c>
       <c r="B457" t="n">
-        <v>0.013112</v>
+        <v>0.014378</v>
       </c>
       <c r="C457" t="n">
-        <v>0.845178</v>
+        <v>0.830334</v>
       </c>
     </row>
     <row r="458">
@@ -6368,10 +6368,10 @@
         </is>
       </c>
       <c r="B458" t="n">
-        <v>0.013679</v>
+        <v>0.014393</v>
       </c>
       <c r="C458" t="n">
-        <v>0.8426399999999999</v>
+        <v>0.827763</v>
       </c>
     </row>
     <row r="459">
@@ -6381,10 +6381,10 @@
         </is>
       </c>
       <c r="B459" t="n">
-        <v>0.01381</v>
+        <v>0.014489</v>
       </c>
       <c r="C459" t="n">
-        <v>0.840102</v>
+        <v>0.825193</v>
       </c>
     </row>
     <row r="460">
@@ -6394,10 +6394,10 @@
         </is>
       </c>
       <c r="B460" t="n">
-        <v>0.014189</v>
+        <v>0.014612</v>
       </c>
       <c r="C460" t="n">
-        <v>0.8375629999999999</v>
+        <v>0.822622</v>
       </c>
     </row>
     <row r="461">
@@ -6407,10 +6407,10 @@
         </is>
       </c>
       <c r="B461" t="n">
-        <v>0.014242</v>
+        <v>0.014898</v>
       </c>
       <c r="C461" t="n">
-        <v>0.835025</v>
+        <v>0.820051</v>
       </c>
     </row>
     <row r="462">
@@ -6420,10 +6420,10 @@
         </is>
       </c>
       <c r="B462" t="n">
-        <v>0.014312</v>
+        <v>0.015024</v>
       </c>
       <c r="C462" t="n">
-        <v>0.832487</v>
+        <v>0.817481</v>
       </c>
     </row>
     <row r="463">
@@ -6433,10 +6433,10 @@
         </is>
       </c>
       <c r="B463" t="n">
-        <v>0.014405</v>
+        <v>0.015098</v>
       </c>
       <c r="C463" t="n">
-        <v>0.829949</v>
+        <v>0.81491</v>
       </c>
     </row>
     <row r="464">
@@ -6446,10 +6446,10 @@
         </is>
       </c>
       <c r="B464" t="n">
-        <v>0.014493</v>
+        <v>0.015149</v>
       </c>
       <c r="C464" t="n">
-        <v>0.827411</v>
+        <v>0.812339</v>
       </c>
     </row>
     <row r="465">
@@ -6459,10 +6459,10 @@
         </is>
       </c>
       <c r="B465" t="n">
-        <v>0.014699</v>
+        <v>0.015565</v>
       </c>
       <c r="C465" t="n">
-        <v>0.824873</v>
+        <v>0.809769</v>
       </c>
     </row>
     <row r="466">
@@ -6472,10 +6472,10 @@
         </is>
       </c>
       <c r="B466" t="n">
-        <v>0.015024</v>
+        <v>0.015692</v>
       </c>
       <c r="C466" t="n">
-        <v>0.822335</v>
+        <v>0.807198</v>
       </c>
     </row>
     <row r="467">
@@ -6485,10 +6485,10 @@
         </is>
       </c>
       <c r="B467" t="n">
-        <v>0.01506</v>
+        <v>0.01601</v>
       </c>
       <c r="C467" t="n">
-        <v>0.819797</v>
+        <v>0.804627</v>
       </c>
     </row>
     <row r="468">
@@ -6498,10 +6498,10 @@
         </is>
       </c>
       <c r="B468" t="n">
-        <v>0.015097</v>
+        <v>0.016461</v>
       </c>
       <c r="C468" t="n">
-        <v>0.817259</v>
+        <v>0.802057</v>
       </c>
     </row>
     <row r="469">
@@ -6511,10 +6511,10 @@
         </is>
       </c>
       <c r="B469" t="n">
-        <v>0.015172</v>
+        <v>0.016644</v>
       </c>
       <c r="C469" t="n">
-        <v>0.814721</v>
+        <v>0.799486</v>
       </c>
     </row>
     <row r="470">
@@ -6524,10 +6524,10 @@
         </is>
       </c>
       <c r="B470" t="n">
-        <v>0.015565</v>
+        <v>0.016746</v>
       </c>
       <c r="C470" t="n">
-        <v>0.812183</v>
+        <v>0.796915</v>
       </c>
     </row>
     <row r="471">
@@ -6537,10 +6537,10 @@
         </is>
       </c>
       <c r="B471" t="n">
-        <v>0.015681</v>
+        <v>0.01691</v>
       </c>
       <c r="C471" t="n">
-        <v>0.8096449999999999</v>
+        <v>0.7943440000000001</v>
       </c>
     </row>
     <row r="472">
@@ -6550,10 +6550,10 @@
         </is>
       </c>
       <c r="B472" t="n">
-        <v>0.016461</v>
+        <v>0.016982</v>
       </c>
       <c r="C472" t="n">
-        <v>0.807107</v>
+        <v>0.791774</v>
       </c>
     </row>
     <row r="473">
@@ -6563,10 +6563,10 @@
         </is>
       </c>
       <c r="B473" t="n">
-        <v>0.01655</v>
+        <v>0.017313</v>
       </c>
       <c r="C473" t="n">
-        <v>0.804569</v>
+        <v>0.789203</v>
       </c>
     </row>
     <row r="474">
@@ -6576,10 +6576,10 @@
         </is>
       </c>
       <c r="B474" t="n">
-        <v>0.016729</v>
+        <v>0.017714</v>
       </c>
       <c r="C474" t="n">
-        <v>0.80203</v>
+        <v>0.786632</v>
       </c>
     </row>
     <row r="475">
@@ -6589,10 +6589,10 @@
         </is>
       </c>
       <c r="B475" t="n">
-        <v>0.016762</v>
+        <v>0.017867</v>
       </c>
       <c r="C475" t="n">
-        <v>0.799492</v>
+        <v>0.784062</v>
       </c>
     </row>
     <row r="476">
@@ -6602,10 +6602,10 @@
         </is>
       </c>
       <c r="B476" t="n">
-        <v>0.016983</v>
+        <v>0.018033</v>
       </c>
       <c r="C476" t="n">
-        <v>0.7969540000000001</v>
+        <v>0.781491</v>
       </c>
     </row>
     <row r="477">
@@ -6615,10 +6615,10 @@
         </is>
       </c>
       <c r="B477" t="n">
-        <v>0.017247</v>
+        <v>0.018109</v>
       </c>
       <c r="C477" t="n">
-        <v>0.794416</v>
+        <v>0.7789199999999999</v>
       </c>
     </row>
     <row r="478">
@@ -6628,10 +6628,10 @@
         </is>
       </c>
       <c r="B478" t="n">
-        <v>0.0173</v>
+        <v>0.018399</v>
       </c>
       <c r="C478" t="n">
-        <v>0.791878</v>
+        <v>0.77635</v>
       </c>
     </row>
     <row r="479">
@@ -6641,10 +6641,10 @@
         </is>
       </c>
       <c r="B479" t="n">
-        <v>0.017706</v>
+        <v>0.018622</v>
       </c>
       <c r="C479" t="n">
-        <v>0.78934</v>
+        <v>0.773779</v>
       </c>
     </row>
     <row r="480">
@@ -6654,10 +6654,10 @@
         </is>
       </c>
       <c r="B480" t="n">
-        <v>0.017772</v>
+        <v>0.018942</v>
       </c>
       <c r="C480" t="n">
-        <v>0.786802</v>
+        <v>0.771208</v>
       </c>
     </row>
     <row r="481">
@@ -6667,10 +6667,10 @@
         </is>
       </c>
       <c r="B481" t="n">
-        <v>0.01789</v>
+        <v>0.019231</v>
       </c>
       <c r="C481" t="n">
-        <v>0.784264</v>
+        <v>0.768638</v>
       </c>
     </row>
     <row r="482">
@@ -6680,10 +6680,10 @@
         </is>
       </c>
       <c r="B482" t="n">
-        <v>0.018157</v>
+        <v>0.019469</v>
       </c>
       <c r="C482" t="n">
-        <v>0.781726</v>
+        <v>0.7660670000000001</v>
       </c>
     </row>
     <row r="483">
@@ -6693,10 +6693,10 @@
         </is>
       </c>
       <c r="B483" t="n">
-        <v>0.018557</v>
+        <v>0.019472</v>
       </c>
       <c r="C483" t="n">
-        <v>0.779188</v>
+        <v>0.763496</v>
       </c>
     </row>
     <row r="484">
@@ -6706,10 +6706,10 @@
         </is>
       </c>
       <c r="B484" t="n">
-        <v>0.018858</v>
+        <v>0.019585</v>
       </c>
       <c r="C484" t="n">
-        <v>0.77665</v>
+        <v>0.760925</v>
       </c>
     </row>
     <row r="485">
@@ -6719,10 +6719,10 @@
         </is>
       </c>
       <c r="B485" t="n">
-        <v>0.019108</v>
+        <v>0.019594</v>
       </c>
       <c r="C485" t="n">
-        <v>0.774112</v>
+        <v>0.758355</v>
       </c>
     </row>
     <row r="486">
@@ -6732,10 +6732,10 @@
         </is>
       </c>
       <c r="B486" t="n">
-        <v>0.01941</v>
+        <v>0.019752</v>
       </c>
       <c r="C486" t="n">
-        <v>0.771574</v>
+        <v>0.755784</v>
       </c>
     </row>
     <row r="487">
@@ -6745,10 +6745,10 @@
         </is>
       </c>
       <c r="B487" t="n">
-        <v>0.019439</v>
+        <v>0.019754</v>
       </c>
       <c r="C487" t="n">
-        <v>0.7690360000000001</v>
+        <v>0.753213</v>
       </c>
     </row>
     <row r="488">
@@ -6758,10 +6758,10 @@
         </is>
       </c>
       <c r="B488" t="n">
-        <v>0.019449</v>
+        <v>0.020557</v>
       </c>
       <c r="C488" t="n">
-        <v>0.766497</v>
+        <v>0.7506429999999999</v>
       </c>
     </row>
     <row r="489">
@@ -6771,10 +6771,10 @@
         </is>
       </c>
       <c r="B489" t="n">
-        <v>0.019581</v>
+        <v>0.020756</v>
       </c>
       <c r="C489" t="n">
-        <v>0.7639590000000001</v>
+        <v>0.748072</v>
       </c>
     </row>
     <row r="490">
@@ -6784,10 +6784,10 @@
         </is>
       </c>
       <c r="B490" t="n">
-        <v>0.019683</v>
+        <v>0.021017</v>
       </c>
       <c r="C490" t="n">
-        <v>0.761421</v>
+        <v>0.745501</v>
       </c>
     </row>
     <row r="491">
@@ -6797,10 +6797,10 @@
         </is>
       </c>
       <c r="B491" t="n">
-        <v>0.019713</v>
+        <v>0.021078</v>
       </c>
       <c r="C491" t="n">
-        <v>0.758883</v>
+        <v>0.742931</v>
       </c>
     </row>
     <row r="492">
@@ -6810,10 +6810,10 @@
         </is>
       </c>
       <c r="B492" t="n">
-        <v>0.02024</v>
+        <v>0.021504</v>
       </c>
       <c r="C492" t="n">
-        <v>0.756345</v>
+        <v>0.74036</v>
       </c>
     </row>
     <row r="493">
@@ -6823,10 +6823,10 @@
         </is>
       </c>
       <c r="B493" t="n">
-        <v>0.020369</v>
+        <v>0.021653</v>
       </c>
       <c r="C493" t="n">
-        <v>0.753807</v>
+        <v>0.737789</v>
       </c>
     </row>
     <row r="494">
@@ -6836,10 +6836,10 @@
         </is>
       </c>
       <c r="B494" t="n">
-        <v>0.021003</v>
+        <v>0.021863</v>
       </c>
       <c r="C494" t="n">
-        <v>0.751269</v>
+        <v>0.735219</v>
       </c>
     </row>
     <row r="495">
@@ -6849,10 +6849,10 @@
         </is>
       </c>
       <c r="B495" t="n">
-        <v>0.021062</v>
+        <v>0.022035</v>
       </c>
       <c r="C495" t="n">
-        <v>0.748731</v>
+        <v>0.732648</v>
       </c>
     </row>
     <row r="496">
@@ -6862,10 +6862,10 @@
         </is>
       </c>
       <c r="B496" t="n">
-        <v>0.021476</v>
+        <v>0.022855</v>
       </c>
       <c r="C496" t="n">
-        <v>0.746193</v>
+        <v>0.730077</v>
       </c>
     </row>
     <row r="497">
@@ -6875,10 +6875,10 @@
         </is>
       </c>
       <c r="B497" t="n">
-        <v>0.021495</v>
+        <v>0.023191</v>
       </c>
       <c r="C497" t="n">
-        <v>0.743655</v>
+        <v>0.727506</v>
       </c>
     </row>
     <row r="498">
@@ -6888,10 +6888,10 @@
         </is>
       </c>
       <c r="B498" t="n">
-        <v>0.021843</v>
+        <v>0.02344</v>
       </c>
       <c r="C498" t="n">
-        <v>0.741117</v>
+        <v>0.724936</v>
       </c>
     </row>
     <row r="499">
@@ -6901,10 +6901,10 @@
         </is>
       </c>
       <c r="B499" t="n">
-        <v>0.021974</v>
+        <v>0.023712</v>
       </c>
       <c r="C499" t="n">
-        <v>0.738579</v>
+        <v>0.722365</v>
       </c>
     </row>
     <row r="500">
@@ -6914,10 +6914,10 @@
         </is>
       </c>
       <c r="B500" t="n">
-        <v>0.022792</v>
+        <v>0.023859</v>
       </c>
       <c r="C500" t="n">
-        <v>0.7360409999999999</v>
+        <v>0.719794</v>
       </c>
     </row>
     <row r="501">
@@ -6927,10 +6927,10 @@
         </is>
       </c>
       <c r="B501" t="n">
-        <v>0.023111</v>
+        <v>0.023931</v>
       </c>
       <c r="C501" t="n">
-        <v>0.733503</v>
+        <v>0.717224</v>
       </c>
     </row>
     <row r="502">
@@ -6940,10 +6940,10 @@
         </is>
       </c>
       <c r="B502" t="n">
-        <v>0.023155</v>
+        <v>0.024191</v>
       </c>
       <c r="C502" t="n">
-        <v>0.7309639999999999</v>
+        <v>0.714653</v>
       </c>
     </row>
     <row r="503">
@@ -6953,10 +6953,10 @@
         </is>
       </c>
       <c r="B503" t="n">
-        <v>0.023273</v>
+        <v>0.024431</v>
       </c>
       <c r="C503" t="n">
-        <v>0.728426</v>
+        <v>0.712082</v>
       </c>
     </row>
     <row r="504">
@@ -6966,10 +6966,10 @@
         </is>
       </c>
       <c r="B504" t="n">
-        <v>0.023514</v>
+        <v>0.024655</v>
       </c>
       <c r="C504" t="n">
-        <v>0.725888</v>
+        <v>0.709512</v>
       </c>
     </row>
     <row r="505">
@@ -6979,10 +6979,10 @@
         </is>
       </c>
       <c r="B505" t="n">
-        <v>0.023793</v>
+        <v>0.024667</v>
       </c>
       <c r="C505" t="n">
-        <v>0.72335</v>
+        <v>0.706941</v>
       </c>
     </row>
     <row r="506">
@@ -6992,10 +6992,10 @@
         </is>
       </c>
       <c r="B506" t="n">
-        <v>0.023897</v>
+        <v>0.024864</v>
       </c>
       <c r="C506" t="n">
-        <v>0.720812</v>
+        <v>0.7043700000000001</v>
       </c>
     </row>
     <row r="507">
@@ -7005,10 +7005,10 @@
         </is>
       </c>
       <c r="B507" t="n">
-        <v>0.023914</v>
+        <v>0.025018</v>
       </c>
       <c r="C507" t="n">
-        <v>0.718274</v>
+        <v>0.701799</v>
       </c>
     </row>
     <row r="508">
@@ -7018,10 +7018,10 @@
         </is>
       </c>
       <c r="B508" t="n">
-        <v>0.024291</v>
+        <v>0.02504</v>
       </c>
       <c r="C508" t="n">
-        <v>0.715736</v>
+        <v>0.699229</v>
       </c>
     </row>
     <row r="509">
@@ -7031,10 +7031,10 @@
         </is>
       </c>
       <c r="B509" t="n">
-        <v>0.024482</v>
+        <v>0.025333</v>
       </c>
       <c r="C509" t="n">
-        <v>0.713198</v>
+        <v>0.696658</v>
       </c>
     </row>
     <row r="510">
@@ -7044,10 +7044,10 @@
         </is>
       </c>
       <c r="B510" t="n">
-        <v>0.024642</v>
+        <v>0.025371</v>
       </c>
       <c r="C510" t="n">
-        <v>0.71066</v>
+        <v>0.694087</v>
       </c>
     </row>
     <row r="511">
@@ -7057,10 +7057,10 @@
         </is>
       </c>
       <c r="B511" t="n">
-        <v>0.024673</v>
+        <v>0.025868</v>
       </c>
       <c r="C511" t="n">
-        <v>0.708122</v>
+        <v>0.691517</v>
       </c>
     </row>
     <row r="512">
@@ -7070,10 +7070,10 @@
         </is>
       </c>
       <c r="B512" t="n">
-        <v>0.024862</v>
+        <v>0.026062</v>
       </c>
       <c r="C512" t="n">
-        <v>0.705584</v>
+        <v>0.6889459999999999</v>
       </c>
     </row>
     <row r="513">
@@ -7083,10 +7083,10 @@
         </is>
       </c>
       <c r="B513" t="n">
-        <v>0.025063</v>
+        <v>0.026118</v>
       </c>
       <c r="C513" t="n">
-        <v>0.7030459999999999</v>
+        <v>0.686375</v>
       </c>
     </row>
     <row r="514">
@@ -7096,10 +7096,10 @@
         </is>
       </c>
       <c r="B514" t="n">
-        <v>0.025332</v>
+        <v>0.026347</v>
       </c>
       <c r="C514" t="n">
-        <v>0.700508</v>
+        <v>0.683805</v>
       </c>
     </row>
     <row r="515">
@@ -7109,10 +7109,10 @@
         </is>
       </c>
       <c r="B515" t="n">
-        <v>0.025863</v>
+        <v>0.02636</v>
       </c>
       <c r="C515" t="n">
-        <v>0.69797</v>
+        <v>0.681234</v>
       </c>
     </row>
     <row r="516">
@@ -7122,10 +7122,10 @@
         </is>
       </c>
       <c r="B516" t="n">
-        <v>0.025949</v>
+        <v>0.026517</v>
       </c>
       <c r="C516" t="n">
-        <v>0.695431</v>
+        <v>0.678663</v>
       </c>
     </row>
     <row r="517">
@@ -7135,10 +7135,10 @@
         </is>
       </c>
       <c r="B517" t="n">
-        <v>0.026053</v>
+        <v>0.026523</v>
       </c>
       <c r="C517" t="n">
-        <v>0.692893</v>
+        <v>0.6760930000000001</v>
       </c>
     </row>
     <row r="518">
@@ -7148,10 +7148,10 @@
         </is>
       </c>
       <c r="B518" t="n">
-        <v>0.026148</v>
+        <v>0.026676</v>
       </c>
       <c r="C518" t="n">
-        <v>0.6903550000000001</v>
+        <v>0.673522</v>
       </c>
     </row>
     <row r="519">
@@ -7161,10 +7161,10 @@
         </is>
       </c>
       <c r="B519" t="n">
-        <v>0.026358</v>
+        <v>0.026908</v>
       </c>
       <c r="C519" t="n">
-        <v>0.687817</v>
+        <v>0.670951</v>
       </c>
     </row>
     <row r="520">
@@ -7174,10 +7174,10 @@
         </is>
       </c>
       <c r="B520" t="n">
-        <v>0.026444</v>
+        <v>0.026981</v>
       </c>
       <c r="C520" t="n">
-        <v>0.685279</v>
+        <v>0.66838</v>
       </c>
     </row>
     <row r="521">
@@ -7187,10 +7187,10 @@
         </is>
       </c>
       <c r="B521" t="n">
-        <v>0.026517</v>
+        <v>0.027507</v>
       </c>
       <c r="C521" t="n">
-        <v>0.682741</v>
+        <v>0.66581</v>
       </c>
     </row>
     <row r="522">
@@ -7200,10 +7200,10 @@
         </is>
       </c>
       <c r="B522" t="n">
-        <v>0.026639</v>
+        <v>0.028665</v>
       </c>
       <c r="C522" t="n">
-        <v>0.680203</v>
+        <v>0.663239</v>
       </c>
     </row>
     <row r="523">
@@ -7213,10 +7213,10 @@
         </is>
       </c>
       <c r="B523" t="n">
-        <v>0.026818</v>
+        <v>0.02887</v>
       </c>
       <c r="C523" t="n">
-        <v>0.677665</v>
+        <v>0.660668</v>
       </c>
     </row>
     <row r="524">
@@ -7226,10 +7226,10 @@
         </is>
       </c>
       <c r="B524" t="n">
-        <v>0.027076</v>
+        <v>0.02915</v>
       </c>
       <c r="C524" t="n">
-        <v>0.675127</v>
+        <v>0.658098</v>
       </c>
     </row>
     <row r="525">
@@ -7239,10 +7239,10 @@
         </is>
       </c>
       <c r="B525" t="n">
-        <v>0.028642</v>
+        <v>0.02915</v>
       </c>
       <c r="C525" t="n">
-        <v>0.672589</v>
+        <v>0.655527</v>
       </c>
     </row>
     <row r="526">
@@ -7252,10 +7252,10 @@
         </is>
       </c>
       <c r="B526" t="n">
-        <v>0.02872</v>
+        <v>0.029169</v>
       </c>
       <c r="C526" t="n">
-        <v>0.670051</v>
+        <v>0.652956</v>
       </c>
     </row>
     <row r="527">
@@ -7265,10 +7265,10 @@
         </is>
       </c>
       <c r="B527" t="n">
-        <v>0.028981</v>
+        <v>0.029408</v>
       </c>
       <c r="C527" t="n">
-        <v>0.667513</v>
+        <v>0.650386</v>
       </c>
     </row>
     <row r="528">
@@ -7278,10 +7278,10 @@
         </is>
       </c>
       <c r="B528" t="n">
-        <v>0.029082</v>
+        <v>0.029489</v>
       </c>
       <c r="C528" t="n">
-        <v>0.664975</v>
+        <v>0.647815</v>
       </c>
     </row>
     <row r="529">
@@ -7291,10 +7291,10 @@
         </is>
       </c>
       <c r="B529" t="n">
-        <v>0.0291</v>
+        <v>0.029646</v>
       </c>
       <c r="C529" t="n">
-        <v>0.6624370000000001</v>
+        <v>0.645244</v>
       </c>
     </row>
     <row r="530">
@@ -7304,10 +7304,10 @@
         </is>
       </c>
       <c r="B530" t="n">
-        <v>0.029155</v>
+        <v>0.030129</v>
       </c>
       <c r="C530" t="n">
-        <v>0.659898</v>
+        <v>0.642674</v>
       </c>
     </row>
     <row r="531">
@@ -7317,10 +7317,10 @@
         </is>
       </c>
       <c r="B531" t="n">
-        <v>0.029259</v>
+        <v>0.03024</v>
       </c>
       <c r="C531" t="n">
-        <v>0.6573600000000001</v>
+        <v>0.640103</v>
       </c>
     </row>
     <row r="532">
@@ -7330,10 +7330,10 @@
         </is>
       </c>
       <c r="B532" t="n">
-        <v>0.029645</v>
+        <v>0.030633</v>
       </c>
       <c r="C532" t="n">
-        <v>0.654822</v>
+        <v>0.637532</v>
       </c>
     </row>
     <row r="533">
@@ -7343,10 +7343,10 @@
         </is>
       </c>
       <c r="B533" t="n">
-        <v>0.029914</v>
+        <v>0.03086</v>
       </c>
       <c r="C533" t="n">
-        <v>0.652284</v>
+        <v>0.634961</v>
       </c>
     </row>
     <row r="534">
@@ -7356,10 +7356,10 @@
         </is>
       </c>
       <c r="B534" t="n">
-        <v>0.029973</v>
+        <v>0.03096</v>
       </c>
       <c r="C534" t="n">
-        <v>0.649746</v>
+        <v>0.632391</v>
       </c>
     </row>
     <row r="535">
@@ -7369,10 +7369,10 @@
         </is>
       </c>
       <c r="B535" t="n">
-        <v>0.030387</v>
+        <v>0.031062</v>
       </c>
       <c r="C535" t="n">
-        <v>0.647208</v>
+        <v>0.62982</v>
       </c>
     </row>
     <row r="536">
@@ -7382,10 +7382,10 @@
         </is>
       </c>
       <c r="B536" t="n">
-        <v>0.030572</v>
+        <v>0.031591</v>
       </c>
       <c r="C536" t="n">
-        <v>0.64467</v>
+        <v>0.6272489999999999</v>
       </c>
     </row>
     <row r="537">
@@ -7395,10 +7395,10 @@
         </is>
       </c>
       <c r="B537" t="n">
-        <v>0.030764</v>
+        <v>0.031674</v>
       </c>
       <c r="C537" t="n">
-        <v>0.642132</v>
+        <v>0.624679</v>
       </c>
     </row>
     <row r="538">
@@ -7408,10 +7408,10 @@
         </is>
       </c>
       <c r="B538" t="n">
-        <v>0.031061</v>
+        <v>0.03175</v>
       </c>
       <c r="C538" t="n">
-        <v>0.639594</v>
+        <v>0.622108</v>
       </c>
     </row>
     <row r="539">
@@ -7421,10 +7421,10 @@
         </is>
       </c>
       <c r="B539" t="n">
-        <v>0.031152</v>
+        <v>0.032007</v>
       </c>
       <c r="C539" t="n">
-        <v>0.637056</v>
+        <v>0.619537</v>
       </c>
     </row>
     <row r="540">
@@ -7434,10 +7434,10 @@
         </is>
       </c>
       <c r="B540" t="n">
-        <v>0.031301</v>
+        <v>0.032477</v>
       </c>
       <c r="C540" t="n">
-        <v>0.634518</v>
+        <v>0.616967</v>
       </c>
     </row>
     <row r="541">
@@ -7447,10 +7447,10 @@
         </is>
       </c>
       <c r="B541" t="n">
-        <v>0.031649</v>
+        <v>0.032847</v>
       </c>
       <c r="C541" t="n">
-        <v>0.63198</v>
+        <v>0.6143960000000001</v>
       </c>
     </row>
     <row r="542">
@@ -7460,10 +7460,10 @@
         </is>
       </c>
       <c r="B542" t="n">
-        <v>0.031982</v>
+        <v>0.033267</v>
       </c>
       <c r="C542" t="n">
-        <v>0.6294419999999999</v>
+        <v>0.611825</v>
       </c>
     </row>
     <row r="543">
@@ -7473,10 +7473,10 @@
         </is>
       </c>
       <c r="B543" t="n">
-        <v>0.032186</v>
+        <v>0.03341</v>
       </c>
       <c r="C543" t="n">
-        <v>0.626904</v>
+        <v>0.609254</v>
       </c>
     </row>
     <row r="544">
@@ -7486,10 +7486,10 @@
         </is>
       </c>
       <c r="B544" t="n">
-        <v>0.032477</v>
+        <v>0.033667</v>
       </c>
       <c r="C544" t="n">
-        <v>0.6243649999999999</v>
+        <v>0.606684</v>
       </c>
     </row>
     <row r="545">
@@ -7499,10 +7499,10 @@
         </is>
       </c>
       <c r="B545" t="n">
-        <v>0.032528</v>
+        <v>0.033844</v>
       </c>
       <c r="C545" t="n">
-        <v>0.621827</v>
+        <v>0.604113</v>
       </c>
     </row>
     <row r="546">
@@ -7512,10 +7512,10 @@
         </is>
       </c>
       <c r="B546" t="n">
-        <v>0.032604</v>
+        <v>0.033888</v>
       </c>
       <c r="C546" t="n">
-        <v>0.619289</v>
+        <v>0.601542</v>
       </c>
     </row>
     <row r="547">
@@ -7525,10 +7525,10 @@
         </is>
       </c>
       <c r="B547" t="n">
-        <v>0.033092</v>
+        <v>0.033917</v>
       </c>
       <c r="C547" t="n">
-        <v>0.616751</v>
+        <v>0.5989719999999999</v>
       </c>
     </row>
     <row r="548">
@@ -7538,10 +7538,10 @@
         </is>
       </c>
       <c r="B548" t="n">
-        <v>0.033253</v>
+        <v>0.033957</v>
       </c>
       <c r="C548" t="n">
-        <v>0.614213</v>
+        <v>0.596401</v>
       </c>
     </row>
     <row r="549">
@@ -7551,10 +7551,10 @@
         </is>
       </c>
       <c r="B549" t="n">
-        <v>0.033267</v>
+        <v>0.034076</v>
       </c>
       <c r="C549" t="n">
-        <v>0.611675</v>
+        <v>0.59383</v>
       </c>
     </row>
     <row r="550">
@@ -7564,10 +7564,10 @@
         </is>
       </c>
       <c r="B550" t="n">
-        <v>0.033559</v>
+        <v>0.034187</v>
       </c>
       <c r="C550" t="n">
-        <v>0.609137</v>
+        <v>0.59126</v>
       </c>
     </row>
     <row r="551">
@@ -7577,10 +7577,10 @@
         </is>
       </c>
       <c r="B551" t="n">
-        <v>0.033812</v>
+        <v>0.034442</v>
       </c>
       <c r="C551" t="n">
-        <v>0.606599</v>
+        <v>0.588689</v>
       </c>
     </row>
     <row r="552">
@@ -7590,10 +7590,10 @@
         </is>
       </c>
       <c r="B552" t="n">
-        <v>0.033828</v>
+        <v>0.034687</v>
       </c>
       <c r="C552" t="n">
-        <v>0.604061</v>
+        <v>0.586118</v>
       </c>
     </row>
     <row r="553">
@@ -7603,10 +7603,10 @@
         </is>
       </c>
       <c r="B553" t="n">
-        <v>0.033889</v>
+        <v>0.03517</v>
       </c>
       <c r="C553" t="n">
-        <v>0.601523</v>
+        <v>0.583548</v>
       </c>
     </row>
     <row r="554">
@@ -7616,10 +7616,10 @@
         </is>
       </c>
       <c r="B554" t="n">
-        <v>0.03389</v>
+        <v>0.035202</v>
       </c>
       <c r="C554" t="n">
-        <v>0.598985</v>
+        <v>0.580977</v>
       </c>
     </row>
     <row r="555">
@@ -7629,10 +7629,10 @@
         </is>
       </c>
       <c r="B555" t="n">
-        <v>0.034046</v>
+        <v>0.035708</v>
       </c>
       <c r="C555" t="n">
-        <v>0.5964469999999999</v>
+        <v>0.578406</v>
       </c>
     </row>
     <row r="556">
@@ -7642,10 +7642,10 @@
         </is>
       </c>
       <c r="B556" t="n">
-        <v>0.034472</v>
+        <v>0.036</v>
       </c>
       <c r="C556" t="n">
-        <v>0.593909</v>
+        <v>0.575835</v>
       </c>
     </row>
     <row r="557">
@@ -7655,10 +7655,10 @@
         </is>
       </c>
       <c r="B557" t="n">
-        <v>0.035103</v>
+        <v>0.036155</v>
       </c>
       <c r="C557" t="n">
-        <v>0.591371</v>
+        <v>0.573265</v>
       </c>
     </row>
     <row r="558">
@@ -7668,10 +7668,10 @@
         </is>
       </c>
       <c r="B558" t="n">
-        <v>0.035171</v>
+        <v>0.036479</v>
       </c>
       <c r="C558" t="n">
-        <v>0.588832</v>
+        <v>0.570694</v>
       </c>
     </row>
     <row r="559">
@@ -7681,10 +7681,10 @@
         </is>
       </c>
       <c r="B559" t="n">
-        <v>0.035605</v>
+        <v>0.036672</v>
       </c>
       <c r="C559" t="n">
-        <v>0.586294</v>
+        <v>0.568123</v>
       </c>
     </row>
     <row r="560">
@@ -7694,10 +7694,10 @@
         </is>
       </c>
       <c r="B560" t="n">
-        <v>0.035883</v>
+        <v>0.036869</v>
       </c>
       <c r="C560" t="n">
-        <v>0.5837560000000001</v>
+        <v>0.565553</v>
       </c>
     </row>
     <row r="561">
@@ -7707,10 +7707,10 @@
         </is>
       </c>
       <c r="B561" t="n">
-        <v>0.036</v>
+        <v>0.037294</v>
       </c>
       <c r="C561" t="n">
-        <v>0.581218</v>
+        <v>0.562982</v>
       </c>
     </row>
     <row r="562">
@@ -7720,10 +7720,10 @@
         </is>
       </c>
       <c r="B562" t="n">
-        <v>0.036099</v>
+        <v>0.037387</v>
       </c>
       <c r="C562" t="n">
-        <v>0.57868</v>
+        <v>0.560411</v>
       </c>
     </row>
     <row r="563">
@@ -7733,10 +7733,10 @@
         </is>
       </c>
       <c r="B563" t="n">
-        <v>0.036201</v>
+        <v>0.037414</v>
       </c>
       <c r="C563" t="n">
-        <v>0.576142</v>
+        <v>0.557841</v>
       </c>
     </row>
     <row r="564">
@@ -7746,10 +7746,10 @@
         </is>
       </c>
       <c r="B564" t="n">
-        <v>0.036503</v>
+        <v>0.03782</v>
       </c>
       <c r="C564" t="n">
-        <v>0.573604</v>
+        <v>0.55527</v>
       </c>
     </row>
     <row r="565">
@@ -7759,10 +7759,10 @@
         </is>
       </c>
       <c r="B565" t="n">
-        <v>0.036642</v>
+        <v>0.037895</v>
       </c>
       <c r="C565" t="n">
-        <v>0.571066</v>
+        <v>0.5526990000000001</v>
       </c>
     </row>
     <row r="566">
@@ -7772,10 +7772,10 @@
         </is>
       </c>
       <c r="B566" t="n">
-        <v>0.037025</v>
+        <v>0.038171</v>
       </c>
       <c r="C566" t="n">
-        <v>0.568528</v>
+        <v>0.550129</v>
       </c>
     </row>
     <row r="567">
@@ -7785,10 +7785,10 @@
         </is>
       </c>
       <c r="B567" t="n">
-        <v>0.037161</v>
+        <v>0.038681</v>
       </c>
       <c r="C567" t="n">
-        <v>0.56599</v>
+        <v>0.547558</v>
       </c>
     </row>
     <row r="568">
@@ -7798,10 +7798,10 @@
         </is>
       </c>
       <c r="B568" t="n">
-        <v>0.037211</v>
+        <v>0.038843</v>
       </c>
       <c r="C568" t="n">
-        <v>0.563452</v>
+        <v>0.544987</v>
       </c>
     </row>
     <row r="569">
@@ -7811,10 +7811,10 @@
         </is>
       </c>
       <c r="B569" t="n">
-        <v>0.037324</v>
+        <v>0.039359</v>
       </c>
       <c r="C569" t="n">
-        <v>0.560914</v>
+        <v>0.542416</v>
       </c>
     </row>
     <row r="570">
@@ -7824,10 +7824,10 @@
         </is>
       </c>
       <c r="B570" t="n">
-        <v>0.03814</v>
+        <v>0.039524</v>
       </c>
       <c r="C570" t="n">
-        <v>0.558376</v>
+        <v>0.539846</v>
       </c>
     </row>
     <row r="571">
@@ -7837,10 +7837,10 @@
         </is>
       </c>
       <c r="B571" t="n">
-        <v>0.038675</v>
+        <v>0.039789</v>
       </c>
       <c r="C571" t="n">
-        <v>0.5558380000000001</v>
+        <v>0.5372749999999999</v>
       </c>
     </row>
     <row r="572">
@@ -7850,10 +7850,10 @@
         </is>
       </c>
       <c r="B572" t="n">
-        <v>0.038731</v>
+        <v>0.039979</v>
       </c>
       <c r="C572" t="n">
-        <v>0.553299</v>
+        <v>0.534704</v>
       </c>
     </row>
     <row r="573">
@@ -7863,10 +7863,10 @@
         </is>
       </c>
       <c r="B573" t="n">
-        <v>0.038918</v>
+        <v>0.040016</v>
       </c>
       <c r="C573" t="n">
-        <v>0.5507609999999999</v>
+        <v>0.532134</v>
       </c>
     </row>
     <row r="574">
@@ -7876,10 +7876,10 @@
         </is>
       </c>
       <c r="B574" t="n">
-        <v>0.03952</v>
+        <v>0.040589</v>
       </c>
       <c r="C574" t="n">
-        <v>0.548223</v>
+        <v>0.529563</v>
       </c>
     </row>
     <row r="575">
@@ -7889,10 +7889,10 @@
         </is>
       </c>
       <c r="B575" t="n">
-        <v>0.039786</v>
+        <v>0.040628</v>
       </c>
       <c r="C575" t="n">
-        <v>0.545685</v>
+        <v>0.526992</v>
       </c>
     </row>
     <row r="576">
@@ -7902,10 +7902,10 @@
         </is>
       </c>
       <c r="B576" t="n">
-        <v>0.039789</v>
+        <v>0.040902</v>
       </c>
       <c r="C576" t="n">
-        <v>0.543147</v>
+        <v>0.5244220000000001</v>
       </c>
     </row>
     <row r="577">
@@ -7915,10 +7915,10 @@
         </is>
       </c>
       <c r="B577" t="n">
-        <v>0.040017</v>
+        <v>0.040934</v>
       </c>
       <c r="C577" t="n">
-        <v>0.540609</v>
+        <v>0.521851</v>
       </c>
     </row>
     <row r="578">
@@ -7928,10 +7928,10 @@
         </is>
       </c>
       <c r="B578" t="n">
-        <v>0.040065</v>
+        <v>0.041243</v>
       </c>
       <c r="C578" t="n">
-        <v>0.538071</v>
+        <v>0.51928</v>
       </c>
     </row>
     <row r="579">
@@ -7941,10 +7941,10 @@
         </is>
       </c>
       <c r="B579" t="n">
-        <v>0.040335</v>
+        <v>0.041497</v>
       </c>
       <c r="C579" t="n">
-        <v>0.535533</v>
+        <v>0.51671</v>
       </c>
     </row>
     <row r="580">
@@ -7954,10 +7954,10 @@
         </is>
       </c>
       <c r="B580" t="n">
-        <v>0.04074</v>
+        <v>0.041497</v>
       </c>
       <c r="C580" t="n">
-        <v>0.532995</v>
+        <v>0.514139</v>
       </c>
     </row>
     <row r="581">
@@ -7967,10 +7967,10 @@
         </is>
       </c>
       <c r="B581" t="n">
-        <v>0.040934</v>
+        <v>0.042812</v>
       </c>
       <c r="C581" t="n">
-        <v>0.530457</v>
+        <v>0.511568</v>
       </c>
     </row>
     <row r="582">
@@ -7980,10 +7980,10 @@
         </is>
       </c>
       <c r="B582" t="n">
-        <v>0.04113</v>
+        <v>0.043182</v>
       </c>
       <c r="C582" t="n">
-        <v>0.527919</v>
+        <v>0.508997</v>
       </c>
     </row>
     <row r="583">
@@ -7993,10 +7993,10 @@
         </is>
       </c>
       <c r="B583" t="n">
-        <v>0.041199</v>
+        <v>0.043418</v>
       </c>
       <c r="C583" t="n">
-        <v>0.525381</v>
+        <v>0.506427</v>
       </c>
     </row>
     <row r="584">
@@ -8006,10 +8006,10 @@
         </is>
       </c>
       <c r="B584" t="n">
-        <v>0.041262</v>
+        <v>0.043514</v>
       </c>
       <c r="C584" t="n">
-        <v>0.5228429999999999</v>
+        <v>0.503856</v>
       </c>
     </row>
     <row r="585">
@@ -8019,10 +8019,10 @@
         </is>
       </c>
       <c r="B585" t="n">
-        <v>0.042811</v>
+        <v>0.043698</v>
       </c>
       <c r="C585" t="n">
-        <v>0.520305</v>
+        <v>0.501285</v>
       </c>
     </row>
     <row r="586">
@@ -8032,10 +8032,10 @@
         </is>
       </c>
       <c r="B586" t="n">
-        <v>0.042974</v>
+        <v>0.043913</v>
       </c>
       <c r="C586" t="n">
-        <v>0.5177659999999999</v>
+        <v>0.498715</v>
       </c>
     </row>
     <row r="587">
@@ -8045,10 +8045,10 @@
         </is>
       </c>
       <c r="B587" t="n">
-        <v>0.043175</v>
+        <v>0.04411</v>
       </c>
       <c r="C587" t="n">
-        <v>0.515228</v>
+        <v>0.496144</v>
       </c>
     </row>
     <row r="588">
@@ -8058,10 +8058,10 @@
         </is>
       </c>
       <c r="B588" t="n">
-        <v>0.04326</v>
+        <v>0.044348</v>
       </c>
       <c r="C588" t="n">
-        <v>0.51269</v>
+        <v>0.493573</v>
       </c>
     </row>
     <row r="589">
@@ -8071,10 +8071,10 @@
         </is>
       </c>
       <c r="B589" t="n">
-        <v>0.043612</v>
+        <v>0.044821</v>
       </c>
       <c r="C589" t="n">
-        <v>0.510152</v>
+        <v>0.491003</v>
       </c>
     </row>
     <row r="590">
@@ -8084,10 +8084,10 @@
         </is>
       </c>
       <c r="B590" t="n">
-        <v>0.043699</v>
+        <v>0.044863</v>
       </c>
       <c r="C590" t="n">
-        <v>0.507614</v>
+        <v>0.488432</v>
       </c>
     </row>
     <row r="591">
@@ -8097,10 +8097,10 @@
         </is>
       </c>
       <c r="B591" t="n">
-        <v>0.043887</v>
+        <v>0.045457</v>
       </c>
       <c r="C591" t="n">
-        <v>0.505076</v>
+        <v>0.485861</v>
       </c>
     </row>
     <row r="592">
@@ -8110,10 +8110,10 @@
         </is>
       </c>
       <c r="B592" t="n">
-        <v>0.04432</v>
+        <v>0.045599</v>
       </c>
       <c r="C592" t="n">
-        <v>0.502538</v>
+        <v>0.48329</v>
       </c>
     </row>
     <row r="593">
@@ -8123,10 +8123,10 @@
         </is>
       </c>
       <c r="B593" t="n">
-        <v>0.044321</v>
+        <v>0.045607</v>
       </c>
       <c r="C593" t="n">
-        <v>0.5</v>
+        <v>0.48072</v>
       </c>
     </row>
     <row r="594">
@@ -8136,10 +8136,10 @@
         </is>
       </c>
       <c r="B594" t="n">
-        <v>0.044625</v>
+        <v>0.045777</v>
       </c>
       <c r="C594" t="n">
-        <v>0.497462</v>
+        <v>0.478149</v>
       </c>
     </row>
     <row r="595">
@@ -8149,10 +8149,10 @@
         </is>
       </c>
       <c r="B595" t="n">
-        <v>0.044727</v>
+        <v>0.045814</v>
       </c>
       <c r="C595" t="n">
-        <v>0.494924</v>
+        <v>0.475578</v>
       </c>
     </row>
     <row r="596">
@@ -8162,10 +8162,10 @@
         </is>
       </c>
       <c r="B596" t="n">
-        <v>0.044938</v>
+        <v>0.045857</v>
       </c>
       <c r="C596" t="n">
-        <v>0.492386</v>
+        <v>0.473008</v>
       </c>
     </row>
     <row r="597">
@@ -8175,10 +8175,10 @@
         </is>
       </c>
       <c r="B597" t="n">
-        <v>0.045102</v>
+        <v>0.046065</v>
       </c>
       <c r="C597" t="n">
-        <v>0.489848</v>
+        <v>0.470437</v>
       </c>
     </row>
     <row r="598">
@@ -8188,10 +8188,10 @@
         </is>
       </c>
       <c r="B598" t="n">
-        <v>0.045316</v>
+        <v>0.046203</v>
       </c>
       <c r="C598" t="n">
-        <v>0.48731</v>
+        <v>0.467866</v>
       </c>
     </row>
     <row r="599">
@@ -8201,10 +8201,10 @@
         </is>
       </c>
       <c r="B599" t="n">
-        <v>0.04549</v>
+        <v>0.046413</v>
       </c>
       <c r="C599" t="n">
-        <v>0.484772</v>
+        <v>0.465296</v>
       </c>
     </row>
     <row r="600">
@@ -8214,10 +8214,10 @@
         </is>
       </c>
       <c r="B600" t="n">
-        <v>0.045521</v>
+        <v>0.046572</v>
       </c>
       <c r="C600" t="n">
-        <v>0.482234</v>
+        <v>0.462725</v>
       </c>
     </row>
     <row r="601">
@@ -8227,10 +8227,10 @@
         </is>
       </c>
       <c r="B601" t="n">
-        <v>0.04569</v>
+        <v>0.047544</v>
       </c>
       <c r="C601" t="n">
-        <v>0.479695</v>
+        <v>0.460154</v>
       </c>
     </row>
     <row r="602">
@@ -8240,10 +8240,10 @@
         </is>
       </c>
       <c r="B602" t="n">
-        <v>0.04579</v>
+        <v>0.047668</v>
       </c>
       <c r="C602" t="n">
-        <v>0.477157</v>
+        <v>0.457584</v>
       </c>
     </row>
     <row r="603">
@@ -8253,10 +8253,10 @@
         </is>
       </c>
       <c r="B603" t="n">
-        <v>0.045881</v>
+        <v>0.047731</v>
       </c>
       <c r="C603" t="n">
-        <v>0.474619</v>
+        <v>0.455013</v>
       </c>
     </row>
     <row r="604">
@@ -8266,10 +8266,10 @@
         </is>
       </c>
       <c r="B604" t="n">
-        <v>0.046337</v>
+        <v>0.048002</v>
       </c>
       <c r="C604" t="n">
-        <v>0.472081</v>
+        <v>0.452442</v>
       </c>
     </row>
     <row r="605">
@@ -8279,10 +8279,10 @@
         </is>
       </c>
       <c r="B605" t="n">
-        <v>0.046881</v>
+        <v>0.048519</v>
       </c>
       <c r="C605" t="n">
-        <v>0.469543</v>
+        <v>0.449871</v>
       </c>
     </row>
     <row r="606">
@@ -8292,10 +8292,10 @@
         </is>
       </c>
       <c r="B606" t="n">
-        <v>0.047095</v>
+        <v>0.048673</v>
       </c>
       <c r="C606" t="n">
-        <v>0.467005</v>
+        <v>0.447301</v>
       </c>
     </row>
     <row r="607">
@@ -8305,10 +8305,10 @@
         </is>
       </c>
       <c r="B607" t="n">
-        <v>0.047313</v>
+        <v>0.048795</v>
       </c>
       <c r="C607" t="n">
-        <v>0.464467</v>
+        <v>0.44473</v>
       </c>
     </row>
     <row r="608">
@@ -8318,10 +8318,10 @@
         </is>
       </c>
       <c r="B608" t="n">
-        <v>0.047476</v>
+        <v>0.049205</v>
       </c>
       <c r="C608" t="n">
-        <v>0.461929</v>
+        <v>0.442159</v>
       </c>
     </row>
     <row r="609">
@@ -8331,10 +8331,10 @@
         </is>
       </c>
       <c r="B609" t="n">
-        <v>0.047669</v>
+        <v>0.050722</v>
       </c>
       <c r="C609" t="n">
-        <v>0.459391</v>
+        <v>0.439589</v>
       </c>
     </row>
     <row r="610">
@@ -8344,10 +8344,10 @@
         </is>
       </c>
       <c r="B610" t="n">
-        <v>0.047815</v>
+        <v>0.050841</v>
       </c>
       <c r="C610" t="n">
-        <v>0.456853</v>
+        <v>0.437018</v>
       </c>
     </row>
     <row r="611">
@@ -8357,10 +8357,10 @@
         </is>
       </c>
       <c r="B611" t="n">
-        <v>0.048763</v>
+        <v>0.05092</v>
       </c>
       <c r="C611" t="n">
-        <v>0.454315</v>
+        <v>0.434447</v>
       </c>
     </row>
     <row r="612">
@@ -8370,10 +8370,10 @@
         </is>
       </c>
       <c r="B612" t="n">
-        <v>0.049183</v>
+        <v>0.050944</v>
       </c>
       <c r="C612" t="n">
-        <v>0.451777</v>
+        <v>0.431877</v>
       </c>
     </row>
     <row r="613">
@@ -8383,10 +8383,10 @@
         </is>
       </c>
       <c r="B613" t="n">
-        <v>0.049206</v>
+        <v>0.051347</v>
       </c>
       <c r="C613" t="n">
-        <v>0.449239</v>
+        <v>0.429306</v>
       </c>
     </row>
     <row r="614">
@@ -8396,10 +8396,10 @@
         </is>
       </c>
       <c r="B614" t="n">
-        <v>0.049976</v>
+        <v>0.051623</v>
       </c>
       <c r="C614" t="n">
-        <v>0.446701</v>
+        <v>0.426735</v>
       </c>
     </row>
     <row r="615">
@@ -8409,10 +8409,10 @@
         </is>
       </c>
       <c r="B615" t="n">
-        <v>0.050003</v>
+        <v>0.052045</v>
       </c>
       <c r="C615" t="n">
-        <v>0.444162</v>
+        <v>0.424165</v>
       </c>
     </row>
     <row r="616">
@@ -8422,10 +8422,10 @@
         </is>
       </c>
       <c r="B616" t="n">
-        <v>0.050261</v>
+        <v>0.052808</v>
       </c>
       <c r="C616" t="n">
-        <v>0.441624</v>
+        <v>0.421594</v>
       </c>
     </row>
     <row r="617">
@@ -8435,10 +8435,10 @@
         </is>
       </c>
       <c r="B617" t="n">
-        <v>0.050632</v>
+        <v>0.052964</v>
       </c>
       <c r="C617" t="n">
-        <v>0.439086</v>
+        <v>0.419023</v>
       </c>
     </row>
     <row r="618">
@@ -8448,10 +8448,10 @@
         </is>
       </c>
       <c r="B618" t="n">
-        <v>0.050917</v>
+        <v>0.053073</v>
       </c>
       <c r="C618" t="n">
-        <v>0.436548</v>
+        <v>0.416452</v>
       </c>
     </row>
     <row r="619">
@@ -8461,10 +8461,10 @@
         </is>
       </c>
       <c r="B619" t="n">
-        <v>0.051251</v>
+        <v>0.05396</v>
       </c>
       <c r="C619" t="n">
-        <v>0.43401</v>
+        <v>0.413882</v>
       </c>
     </row>
     <row r="620">
@@ -8474,10 +8474,10 @@
         </is>
       </c>
       <c r="B620" t="n">
-        <v>0.051402</v>
+        <v>0.053972</v>
       </c>
       <c r="C620" t="n">
-        <v>0.431472</v>
+        <v>0.411311</v>
       </c>
     </row>
     <row r="621">
@@ -8487,10 +8487,10 @@
         </is>
       </c>
       <c r="B621" t="n">
-        <v>0.052688</v>
+        <v>0.054108</v>
       </c>
       <c r="C621" t="n">
-        <v>0.428934</v>
+        <v>0.40874</v>
       </c>
     </row>
     <row r="622">
@@ -8500,10 +8500,10 @@
         </is>
       </c>
       <c r="B622" t="n">
-        <v>0.052792</v>
+        <v>0.054231</v>
       </c>
       <c r="C622" t="n">
-        <v>0.426396</v>
+        <v>0.40617</v>
       </c>
     </row>
     <row r="623">
@@ -8513,10 +8513,10 @@
         </is>
       </c>
       <c r="B623" t="n">
-        <v>0.052956</v>
+        <v>0.054436</v>
       </c>
       <c r="C623" t="n">
-        <v>0.423858</v>
+        <v>0.403599</v>
       </c>
     </row>
     <row r="624">
@@ -8526,10 +8526,10 @@
         </is>
       </c>
       <c r="B624" t="n">
-        <v>0.053137</v>
+        <v>0.054473</v>
       </c>
       <c r="C624" t="n">
-        <v>0.42132</v>
+        <v>0.401028</v>
       </c>
     </row>
     <row r="625">
@@ -8539,10 +8539,10 @@
         </is>
       </c>
       <c r="B625" t="n">
-        <v>0.05317</v>
+        <v>0.054611</v>
       </c>
       <c r="C625" t="n">
-        <v>0.418782</v>
+        <v>0.398458</v>
       </c>
     </row>
     <row r="626">
@@ -8552,10 +8552,10 @@
         </is>
       </c>
       <c r="B626" t="n">
-        <v>0.053906</v>
+        <v>0.05483</v>
       </c>
       <c r="C626" t="n">
-        <v>0.416244</v>
+        <v>0.395887</v>
       </c>
     </row>
     <row r="627">
@@ -8565,10 +8565,10 @@
         </is>
       </c>
       <c r="B627" t="n">
-        <v>0.054032</v>
+        <v>0.054867</v>
       </c>
       <c r="C627" t="n">
-        <v>0.413706</v>
+        <v>0.393316</v>
       </c>
     </row>
     <row r="628">
@@ -8578,10 +8578,10 @@
         </is>
       </c>
       <c r="B628" t="n">
-        <v>0.054064</v>
+        <v>0.05507</v>
       </c>
       <c r="C628" t="n">
-        <v>0.411168</v>
+        <v>0.390746</v>
       </c>
     </row>
     <row r="629">
@@ -8591,10 +8591,10 @@
         </is>
       </c>
       <c r="B629" t="n">
-        <v>0.054413</v>
+        <v>0.055345</v>
       </c>
       <c r="C629" t="n">
-        <v>0.408629</v>
+        <v>0.388175</v>
       </c>
     </row>
     <row r="630">
@@ -8604,10 +8604,10 @@
         </is>
       </c>
       <c r="B630" t="n">
-        <v>0.054448</v>
+        <v>0.055792</v>
       </c>
       <c r="C630" t="n">
-        <v>0.406091</v>
+        <v>0.385604</v>
       </c>
     </row>
     <row r="631">
@@ -8617,10 +8617,10 @@
         </is>
       </c>
       <c r="B631" t="n">
-        <v>0.054613</v>
+        <v>0.055908</v>
       </c>
       <c r="C631" t="n">
-        <v>0.403553</v>
+        <v>0.383033</v>
       </c>
     </row>
     <row r="632">
@@ -8630,10 +8630,10 @@
         </is>
       </c>
       <c r="B632" t="n">
-        <v>0.054743</v>
+        <v>0.055976</v>
       </c>
       <c r="C632" t="n">
-        <v>0.401015</v>
+        <v>0.380463</v>
       </c>
     </row>
     <row r="633">
@@ -8643,10 +8643,10 @@
         </is>
       </c>
       <c r="B633" t="n">
-        <v>0.054783</v>
+        <v>0.056273</v>
       </c>
       <c r="C633" t="n">
-        <v>0.398477</v>
+        <v>0.377892</v>
       </c>
     </row>
     <row r="634">
@@ -8656,10 +8656,10 @@
         </is>
       </c>
       <c r="B634" t="n">
-        <v>0.054821</v>
+        <v>0.056487</v>
       </c>
       <c r="C634" t="n">
-        <v>0.395939</v>
+        <v>0.375321</v>
       </c>
     </row>
     <row r="635">
@@ -8669,10 +8669,10 @@
         </is>
       </c>
       <c r="B635" t="n">
-        <v>0.055472</v>
+        <v>0.05761</v>
       </c>
       <c r="C635" t="n">
-        <v>0.393401</v>
+        <v>0.372751</v>
       </c>
     </row>
     <row r="636">
@@ -8682,10 +8682,10 @@
         </is>
       </c>
       <c r="B636" t="n">
-        <v>0.055699</v>
+        <v>0.057702</v>
       </c>
       <c r="C636" t="n">
-        <v>0.390863</v>
+        <v>0.37018</v>
       </c>
     </row>
     <row r="637">
@@ -8695,10 +8695,10 @@
         </is>
       </c>
       <c r="B637" t="n">
-        <v>0.055733</v>
+        <v>0.057823</v>
       </c>
       <c r="C637" t="n">
-        <v>0.388325</v>
+        <v>0.367609</v>
       </c>
     </row>
     <row r="638">
@@ -8708,10 +8708,10 @@
         </is>
       </c>
       <c r="B638" t="n">
-        <v>0.056256</v>
+        <v>0.057855</v>
       </c>
       <c r="C638" t="n">
-        <v>0.385787</v>
+        <v>0.365039</v>
       </c>
     </row>
     <row r="639">
@@ -8721,10 +8721,10 @@
         </is>
       </c>
       <c r="B639" t="n">
-        <v>0.056484</v>
+        <v>0.058103</v>
       </c>
       <c r="C639" t="n">
-        <v>0.383249</v>
+        <v>0.362468</v>
       </c>
     </row>
     <row r="640">
@@ -8734,10 +8734,10 @@
         </is>
       </c>
       <c r="B640" t="n">
-        <v>0.057176</v>
+        <v>0.059236</v>
       </c>
       <c r="C640" t="n">
-        <v>0.380711</v>
+        <v>0.359897</v>
       </c>
     </row>
     <row r="641">
@@ -8747,10 +8747,10 @@
         </is>
       </c>
       <c r="B641" t="n">
-        <v>0.057438</v>
+        <v>0.059804</v>
       </c>
       <c r="C641" t="n">
-        <v>0.378173</v>
+        <v>0.357326</v>
       </c>
     </row>
     <row r="642">
@@ -8760,10 +8760,10 @@
         </is>
       </c>
       <c r="B642" t="n">
-        <v>0.057493</v>
+        <v>0.059826</v>
       </c>
       <c r="C642" t="n">
-        <v>0.375635</v>
+        <v>0.354756</v>
       </c>
     </row>
     <row r="643">
@@ -8773,10 +8773,10 @@
         </is>
       </c>
       <c r="B643" t="n">
-        <v>0.057531</v>
+        <v>0.059985</v>
       </c>
       <c r="C643" t="n">
-        <v>0.373096</v>
+        <v>0.352185</v>
       </c>
     </row>
     <row r="644">
@@ -8786,10 +8786,10 @@
         </is>
       </c>
       <c r="B644" t="n">
-        <v>0.058073</v>
+        <v>0.060278</v>
       </c>
       <c r="C644" t="n">
-        <v>0.370558</v>
+        <v>0.349614</v>
       </c>
     </row>
     <row r="645">
@@ -8799,10 +8799,10 @@
         </is>
       </c>
       <c r="B645" t="n">
-        <v>0.059132</v>
+        <v>0.060853</v>
       </c>
       <c r="C645" t="n">
-        <v>0.36802</v>
+        <v>0.347044</v>
       </c>
     </row>
     <row r="646">
@@ -8812,10 +8812,10 @@
         </is>
       </c>
       <c r="B646" t="n">
-        <v>0.059805</v>
+        <v>0.060988</v>
       </c>
       <c r="C646" t="n">
-        <v>0.365482</v>
+        <v>0.344473</v>
       </c>
     </row>
     <row r="647">
@@ -8825,10 +8825,10 @@
         </is>
       </c>
       <c r="B647" t="n">
-        <v>0.059826</v>
+        <v>0.061944</v>
       </c>
       <c r="C647" t="n">
-        <v>0.362944</v>
+        <v>0.341902</v>
       </c>
     </row>
     <row r="648">
@@ -8838,10 +8838,10 @@
         </is>
       </c>
       <c r="B648" t="n">
-        <v>0.059987</v>
+        <v>0.062222</v>
       </c>
       <c r="C648" t="n">
-        <v>0.360406</v>
+        <v>0.339332</v>
       </c>
     </row>
     <row r="649">
@@ -8851,10 +8851,10 @@
         </is>
       </c>
       <c r="B649" t="n">
-        <v>0.060222</v>
+        <v>0.062595</v>
       </c>
       <c r="C649" t="n">
-        <v>0.357868</v>
+        <v>0.336761</v>
       </c>
     </row>
     <row r="650">
@@ -8864,10 +8864,10 @@
         </is>
       </c>
       <c r="B650" t="n">
-        <v>0.060689</v>
+        <v>0.063039</v>
       </c>
       <c r="C650" t="n">
-        <v>0.35533</v>
+        <v>0.33419</v>
       </c>
     </row>
     <row r="651">
@@ -8877,10 +8877,10 @@
         </is>
       </c>
       <c r="B651" t="n">
-        <v>0.060844</v>
+        <v>0.064372</v>
       </c>
       <c r="C651" t="n">
-        <v>0.352792</v>
+        <v>0.33162</v>
       </c>
     </row>
     <row r="652">
@@ -8890,10 +8890,10 @@
         </is>
       </c>
       <c r="B652" t="n">
-        <v>0.060851</v>
+        <v>0.064424</v>
       </c>
       <c r="C652" t="n">
-        <v>0.350254</v>
+        <v>0.329049</v>
       </c>
     </row>
     <row r="653">
@@ -8903,10 +8903,10 @@
         </is>
       </c>
       <c r="B653" t="n">
-        <v>0.061943</v>
+        <v>0.064725</v>
       </c>
       <c r="C653" t="n">
-        <v>0.347716</v>
+        <v>0.326478</v>
       </c>
     </row>
     <row r="654">
@@ -8916,10 +8916,10 @@
         </is>
       </c>
       <c r="B654" t="n">
-        <v>0.062156</v>
+        <v>0.065279</v>
       </c>
       <c r="C654" t="n">
-        <v>0.345178</v>
+        <v>0.323907</v>
       </c>
     </row>
     <row r="655">
@@ -8929,10 +8929,10 @@
         </is>
       </c>
       <c r="B655" t="n">
-        <v>0.062738</v>
+        <v>0.065386</v>
       </c>
       <c r="C655" t="n">
-        <v>0.34264</v>
+        <v>0.321337</v>
       </c>
     </row>
     <row r="656">
@@ -8942,10 +8942,10 @@
         </is>
       </c>
       <c r="B656" t="n">
-        <v>0.063453</v>
+        <v>0.065577</v>
       </c>
       <c r="C656" t="n">
-        <v>0.340102</v>
+        <v>0.318766</v>
       </c>
     </row>
     <row r="657">
@@ -8955,10 +8955,10 @@
         </is>
       </c>
       <c r="B657" t="n">
-        <v>0.06353499999999999</v>
+        <v>0.066055</v>
       </c>
       <c r="C657" t="n">
-        <v>0.337563</v>
+        <v>0.316195</v>
       </c>
     </row>
     <row r="658">
@@ -8968,10 +8968,10 @@
         </is>
       </c>
       <c r="B658" t="n">
-        <v>0.063947</v>
+        <v>0.067384</v>
       </c>
       <c r="C658" t="n">
-        <v>0.335025</v>
+        <v>0.313625</v>
       </c>
     </row>
     <row r="659">
@@ -8981,10 +8981,10 @@
         </is>
       </c>
       <c r="B659" t="n">
-        <v>0.06455</v>
+        <v>0.068338</v>
       </c>
       <c r="C659" t="n">
-        <v>0.332487</v>
+        <v>0.311054</v>
       </c>
     </row>
     <row r="660">
@@ -8994,10 +8994,10 @@
         </is>
       </c>
       <c r="B660" t="n">
-        <v>0.065022</v>
+        <v>0.068532</v>
       </c>
       <c r="C660" t="n">
-        <v>0.329949</v>
+        <v>0.308483</v>
       </c>
     </row>
     <row r="661">
@@ -9007,10 +9007,10 @@
         </is>
       </c>
       <c r="B661" t="n">
-        <v>0.06557399999999999</v>
+        <v>0.069019</v>
       </c>
       <c r="C661" t="n">
-        <v>0.327411</v>
+        <v>0.305913</v>
       </c>
     </row>
     <row r="662">
@@ -9020,10 +9020,10 @@
         </is>
       </c>
       <c r="B662" t="n">
-        <v>0.065883</v>
+        <v>0.069132</v>
       </c>
       <c r="C662" t="n">
-        <v>0.324873</v>
+        <v>0.303342</v>
       </c>
     </row>
     <row r="663">
@@ -9033,10 +9033,10 @@
         </is>
       </c>
       <c r="B663" t="n">
-        <v>0.066048</v>
+        <v>0.069566</v>
       </c>
       <c r="C663" t="n">
-        <v>0.322335</v>
+        <v>0.300771</v>
       </c>
     </row>
     <row r="664">
@@ -9046,10 +9046,10 @@
         </is>
       </c>
       <c r="B664" t="n">
-        <v>0.06736399999999999</v>
+        <v>0.069672</v>
       </c>
       <c r="C664" t="n">
-        <v>0.319797</v>
+        <v>0.298201</v>
       </c>
     </row>
     <row r="665">
@@ -9059,10 +9059,10 @@
         </is>
       </c>
       <c r="B665" t="n">
-        <v>0.068092</v>
+        <v>0.070326</v>
       </c>
       <c r="C665" t="n">
-        <v>0.317259</v>
+        <v>0.29563</v>
       </c>
     </row>
     <row r="666">
@@ -9072,10 +9072,10 @@
         </is>
       </c>
       <c r="B666" t="n">
-        <v>0.06830899999999999</v>
+        <v>0.071338</v>
       </c>
       <c r="C666" t="n">
-        <v>0.314721</v>
+        <v>0.293059</v>
       </c>
     </row>
     <row r="667">
@@ -9085,10 +9085,10 @@
         </is>
       </c>
       <c r="B667" t="n">
-        <v>0.068532</v>
+        <v>0.071614</v>
       </c>
       <c r="C667" t="n">
-        <v>0.312183</v>
+        <v>0.290488</v>
       </c>
     </row>
     <row r="668">
@@ -9098,10 +9098,10 @@
         </is>
       </c>
       <c r="B668" t="n">
-        <v>0.068915</v>
+        <v>0.07170899999999999</v>
       </c>
       <c r="C668" t="n">
-        <v>0.309645</v>
+        <v>0.287918</v>
       </c>
     </row>
     <row r="669">
@@ -9111,10 +9111,10 @@
         </is>
       </c>
       <c r="B669" t="n">
-        <v>0.069267</v>
+        <v>0.07234599999999999</v>
       </c>
       <c r="C669" t="n">
-        <v>0.307107</v>
+        <v>0.285347</v>
       </c>
     </row>
     <row r="670">
@@ -9124,10 +9124,10 @@
         </is>
       </c>
       <c r="B670" t="n">
-        <v>0.069316</v>
+        <v>0.07288</v>
       </c>
       <c r="C670" t="n">
-        <v>0.304569</v>
+        <v>0.282776</v>
       </c>
     </row>
     <row r="671">
@@ -9137,10 +9137,10 @@
         </is>
       </c>
       <c r="B671" t="n">
-        <v>0.06954100000000001</v>
+        <v>0.072889</v>
       </c>
       <c r="C671" t="n">
-        <v>0.30203</v>
+        <v>0.280206</v>
       </c>
     </row>
     <row r="672">
@@ -9150,10 +9150,10 @@
         </is>
       </c>
       <c r="B672" t="n">
-        <v>0.070257</v>
+        <v>0.072947</v>
       </c>
       <c r="C672" t="n">
-        <v>0.299492</v>
+        <v>0.277635</v>
       </c>
     </row>
     <row r="673">
@@ -9163,10 +9163,10 @@
         </is>
       </c>
       <c r="B673" t="n">
-        <v>0.070325</v>
+        <v>0.073908</v>
       </c>
       <c r="C673" t="n">
-        <v>0.296954</v>
+        <v>0.275064</v>
       </c>
     </row>
     <row r="674">
@@ -9176,10 +9176,10 @@
         </is>
       </c>
       <c r="B674" t="n">
-        <v>0.070911</v>
+        <v>0.074721</v>
       </c>
       <c r="C674" t="n">
-        <v>0.294416</v>
+        <v>0.272494</v>
       </c>
     </row>
     <row r="675">
@@ -9189,10 +9189,10 @@
         </is>
       </c>
       <c r="B675" t="n">
-        <v>0.071007</v>
+        <v>0.075029</v>
       </c>
       <c r="C675" t="n">
-        <v>0.291878</v>
+        <v>0.269923</v>
       </c>
     </row>
     <row r="676">
@@ -9202,10 +9202,10 @@
         </is>
       </c>
       <c r="B676" t="n">
-        <v>0.071254</v>
+        <v>0.075153</v>
       </c>
       <c r="C676" t="n">
-        <v>0.28934</v>
+        <v>0.267352</v>
       </c>
     </row>
     <row r="677">
@@ -9215,10 +9215,10 @@
         </is>
       </c>
       <c r="B677" t="n">
-        <v>0.07222099999999999</v>
+        <v>0.07546700000000001</v>
       </c>
       <c r="C677" t="n">
-        <v>0.286802</v>
+        <v>0.264781</v>
       </c>
     </row>
     <row r="678">
@@ -9228,10 +9228,10 @@
         </is>
       </c>
       <c r="B678" t="n">
-        <v>0.0723</v>
+        <v>0.075476</v>
       </c>
       <c r="C678" t="n">
-        <v>0.284264</v>
+        <v>0.262211</v>
       </c>
     </row>
     <row r="679">
@@ -9241,10 +9241,10 @@
         </is>
       </c>
       <c r="B679" t="n">
-        <v>0.072843</v>
+        <v>0.07561</v>
       </c>
       <c r="C679" t="n">
-        <v>0.281726</v>
+        <v>0.25964</v>
       </c>
     </row>
     <row r="680">
@@ -9254,10 +9254,10 @@
         </is>
       </c>
       <c r="B680" t="n">
-        <v>0.072884</v>
+        <v>0.076445</v>
       </c>
       <c r="C680" t="n">
-        <v>0.279188</v>
+        <v>0.257069</v>
       </c>
     </row>
     <row r="681">
@@ -9267,10 +9267,10 @@
         </is>
       </c>
       <c r="B681" t="n">
-        <v>0.073911</v>
+        <v>0.078781</v>
       </c>
       <c r="C681" t="n">
-        <v>0.27665</v>
+        <v>0.254499</v>
       </c>
     </row>
     <row r="682">
@@ -9280,10 +9280,10 @@
         </is>
       </c>
       <c r="B682" t="n">
-        <v>0.074502</v>
+        <v>0.079009</v>
       </c>
       <c r="C682" t="n">
-        <v>0.274112</v>
+        <v>0.251928</v>
       </c>
     </row>
     <row r="683">
@@ -9293,10 +9293,10 @@
         </is>
       </c>
       <c r="B683" t="n">
-        <v>0.07470599999999999</v>
+        <v>0.07939599999999999</v>
       </c>
       <c r="C683" t="n">
-        <v>0.271574</v>
+        <v>0.249357</v>
       </c>
     </row>
     <row r="684">
@@ -9306,10 +9306,10 @@
         </is>
       </c>
       <c r="B684" t="n">
-        <v>0.074924</v>
+        <v>0.07974100000000001</v>
       </c>
       <c r="C684" t="n">
-        <v>0.269036</v>
+        <v>0.246787</v>
       </c>
     </row>
     <row r="685">
@@ -9319,10 +9319,10 @@
         </is>
       </c>
       <c r="B685" t="n">
-        <v>0.075193</v>
+        <v>0.08135100000000001</v>
       </c>
       <c r="C685" t="n">
-        <v>0.266497</v>
+        <v>0.244216</v>
       </c>
     </row>
     <row r="686">
@@ -9332,10 +9332,10 @@
         </is>
       </c>
       <c r="B686" t="n">
-        <v>0.07547</v>
+        <v>0.081356</v>
       </c>
       <c r="C686" t="n">
-        <v>0.263959</v>
+        <v>0.241645</v>
       </c>
     </row>
     <row r="687">
@@ -9345,10 +9345,10 @@
         </is>
       </c>
       <c r="B687" t="n">
-        <v>0.075553</v>
+        <v>0.083207</v>
       </c>
       <c r="C687" t="n">
-        <v>0.261421</v>
+        <v>0.239075</v>
       </c>
     </row>
     <row r="688">
@@ -9358,10 +9358,10 @@
         </is>
       </c>
       <c r="B688" t="n">
-        <v>0.076388</v>
+        <v>0.083368</v>
       </c>
       <c r="C688" t="n">
-        <v>0.258883</v>
+        <v>0.236504</v>
       </c>
     </row>
     <row r="689">
@@ -9371,10 +9371,10 @@
         </is>
       </c>
       <c r="B689" t="n">
-        <v>0.078573</v>
+        <v>0.083441</v>
       </c>
       <c r="C689" t="n">
-        <v>0.256345</v>
+        <v>0.233933</v>
       </c>
     </row>
     <row r="690">
@@ -9384,10 +9384,10 @@
         </is>
       </c>
       <c r="B690" t="n">
-        <v>0.078779</v>
+        <v>0.08347300000000001</v>
       </c>
       <c r="C690" t="n">
-        <v>0.253807</v>
+        <v>0.231362</v>
       </c>
     </row>
     <row r="691">
@@ -9397,10 +9397,10 @@
         </is>
       </c>
       <c r="B691" t="n">
-        <v>0.07892299999999999</v>
+        <v>0.08358</v>
       </c>
       <c r="C691" t="n">
-        <v>0.251269</v>
+        <v>0.228792</v>
       </c>
     </row>
     <row r="692">
@@ -9410,10 +9410,10 @@
         </is>
       </c>
       <c r="B692" t="n">
-        <v>0.079388</v>
+        <v>0.085517</v>
       </c>
       <c r="C692" t="n">
-        <v>0.248731</v>
+        <v>0.226221</v>
       </c>
     </row>
     <row r="693">
@@ -9423,10 +9423,10 @@
         </is>
       </c>
       <c r="B693" t="n">
-        <v>0.07974199999999999</v>
+        <v>0.085559</v>
       </c>
       <c r="C693" t="n">
-        <v>0.246193</v>
+        <v>0.22365</v>
       </c>
     </row>
     <row r="694">
@@ -9436,10 +9436,10 @@
         </is>
       </c>
       <c r="B694" t="n">
-        <v>0.08024199999999999</v>
+        <v>0.085853</v>
       </c>
       <c r="C694" t="n">
-        <v>0.243655</v>
+        <v>0.22108</v>
       </c>
     </row>
     <row r="695">
@@ -9449,10 +9449,10 @@
         </is>
       </c>
       <c r="B695" t="n">
-        <v>0.08083600000000001</v>
+        <v>0.08587500000000001</v>
       </c>
       <c r="C695" t="n">
-        <v>0.241117</v>
+        <v>0.218509</v>
       </c>
     </row>
     <row r="696">
@@ -9462,10 +9462,10 @@
         </is>
       </c>
       <c r="B696" t="n">
-        <v>0.081735</v>
+        <v>0.086571</v>
       </c>
       <c r="C696" t="n">
-        <v>0.238579</v>
+        <v>0.215938</v>
       </c>
     </row>
     <row r="697">
@@ -9475,10 +9475,10 @@
         </is>
       </c>
       <c r="B697" t="n">
-        <v>0.081951</v>
+        <v>0.08808199999999999</v>
       </c>
       <c r="C697" t="n">
-        <v>0.236041</v>
+        <v>0.213368</v>
       </c>
     </row>
     <row r="698">
@@ -9488,10 +9488,10 @@
         </is>
       </c>
       <c r="B698" t="n">
-        <v>0.082499</v>
+        <v>0.088782</v>
       </c>
       <c r="C698" t="n">
-        <v>0.233503</v>
+        <v>0.210797</v>
       </c>
     </row>
     <row r="699">
@@ -9501,10 +9501,10 @@
         </is>
       </c>
       <c r="B699" t="n">
-        <v>0.08337799999999999</v>
+        <v>0.08881500000000001</v>
       </c>
       <c r="C699" t="n">
-        <v>0.230964</v>
+        <v>0.208226</v>
       </c>
     </row>
     <row r="700">
@@ -9514,10 +9514,10 @@
         </is>
       </c>
       <c r="B700" t="n">
-        <v>0.083583</v>
+        <v>0.089139</v>
       </c>
       <c r="C700" t="n">
-        <v>0.228426</v>
+        <v>0.205656</v>
       </c>
     </row>
     <row r="701">
@@ -9527,10 +9527,10 @@
         </is>
       </c>
       <c r="B701" t="n">
-        <v>0.083938</v>
+        <v>0.090822</v>
       </c>
       <c r="C701" t="n">
-        <v>0.225888</v>
+        <v>0.203085</v>
       </c>
     </row>
     <row r="702">
@@ -9540,10 +9540,10 @@
         </is>
       </c>
       <c r="B702" t="n">
-        <v>0.084576</v>
+        <v>0.092055</v>
       </c>
       <c r="C702" t="n">
-        <v>0.22335</v>
+        <v>0.200514</v>
       </c>
     </row>
     <row r="703">
@@ -9553,10 +9553,10 @@
         </is>
       </c>
       <c r="B703" t="n">
-        <v>0.084719</v>
+        <v>0.092434</v>
       </c>
       <c r="C703" t="n">
-        <v>0.220812</v>
+        <v>0.197943</v>
       </c>
     </row>
     <row r="704">
@@ -9566,10 +9566,10 @@
         </is>
       </c>
       <c r="B704" t="n">
-        <v>0.08475100000000001</v>
+        <v>0.09345000000000001</v>
       </c>
       <c r="C704" t="n">
-        <v>0.218274</v>
+        <v>0.195373</v>
       </c>
     </row>
     <row r="705">
@@ -9579,10 +9579,10 @@
         </is>
       </c>
       <c r="B705" t="n">
-        <v>0.085843</v>
+        <v>0.093676</v>
       </c>
       <c r="C705" t="n">
-        <v>0.215736</v>
+        <v>0.192802</v>
       </c>
     </row>
     <row r="706">
@@ -9592,10 +9592,10 @@
         </is>
       </c>
       <c r="B706" t="n">
-        <v>0.086544</v>
+        <v>0.09553</v>
       </c>
       <c r="C706" t="n">
-        <v>0.213198</v>
+        <v>0.190231</v>
       </c>
     </row>
     <row r="707">
@@ -9605,10 +9605,10 @@
         </is>
       </c>
       <c r="B707" t="n">
-        <v>0.08808100000000001</v>
+        <v>0.095622</v>
       </c>
       <c r="C707" t="n">
-        <v>0.21066</v>
+        <v>0.187661</v>
       </c>
     </row>
     <row r="708">
@@ -9618,10 +9618,10 @@
         </is>
       </c>
       <c r="B708" t="n">
-        <v>0.088437</v>
+        <v>0.096542</v>
       </c>
       <c r="C708" t="n">
-        <v>0.208122</v>
+        <v>0.18509</v>
       </c>
     </row>
     <row r="709">
@@ -9631,10 +9631,10 @@
         </is>
       </c>
       <c r="B709" t="n">
-        <v>0.08877699999999999</v>
+        <v>0.097112</v>
       </c>
       <c r="C709" t="n">
-        <v>0.205584</v>
+        <v>0.182519</v>
       </c>
     </row>
     <row r="710">
@@ -9644,10 +9644,10 @@
         </is>
       </c>
       <c r="B710" t="n">
-        <v>0.088814</v>
+        <v>0.097279</v>
       </c>
       <c r="C710" t="n">
-        <v>0.203046</v>
+        <v>0.179949</v>
       </c>
     </row>
     <row r="711">
@@ -9657,10 +9657,10 @@
         </is>
       </c>
       <c r="B711" t="n">
-        <v>0.09166000000000001</v>
+        <v>0.097568</v>
       </c>
       <c r="C711" t="n">
-        <v>0.200508</v>
+        <v>0.177378</v>
       </c>
     </row>
     <row r="712">
@@ -9670,10 +9670,10 @@
         </is>
       </c>
       <c r="B712" t="n">
-        <v>0.091963</v>
+        <v>0.097582</v>
       </c>
       <c r="C712" t="n">
-        <v>0.19797</v>
+        <v>0.174807</v>
       </c>
     </row>
     <row r="713">
@@ -9683,10 +9683,10 @@
         </is>
       </c>
       <c r="B713" t="n">
-        <v>0.092638</v>
+        <v>0.100234</v>
       </c>
       <c r="C713" t="n">
-        <v>0.195431</v>
+        <v>0.172237</v>
       </c>
     </row>
     <row r="714">
@@ -9696,10 +9696,10 @@
         </is>
       </c>
       <c r="B714" t="n">
-        <v>0.092974</v>
+        <v>0.100243</v>
       </c>
       <c r="C714" t="n">
-        <v>0.192893</v>
+        <v>0.169666</v>
       </c>
     </row>
     <row r="715">
@@ -9709,10 +9709,10 @@
         </is>
       </c>
       <c r="B715" t="n">
-        <v>0.09322800000000001</v>
+        <v>0.100251</v>
       </c>
       <c r="C715" t="n">
-        <v>0.190355</v>
+        <v>0.167095</v>
       </c>
     </row>
     <row r="716">
@@ -9722,10 +9722,10 @@
         </is>
       </c>
       <c r="B716" t="n">
-        <v>0.09531299999999999</v>
+        <v>0.100573</v>
       </c>
       <c r="C716" t="n">
-        <v>0.187817</v>
+        <v>0.164524</v>
       </c>
     </row>
     <row r="717">
@@ -9735,10 +9735,10 @@
         </is>
       </c>
       <c r="B717" t="n">
-        <v>0.095986</v>
+        <v>0.101396</v>
       </c>
       <c r="C717" t="n">
-        <v>0.185279</v>
+        <v>0.161954</v>
       </c>
     </row>
     <row r="718">
@@ -9748,10 +9748,10 @@
         </is>
       </c>
       <c r="B718" t="n">
-        <v>0.09646299999999999</v>
+        <v>0.102188</v>
       </c>
       <c r="C718" t="n">
-        <v>0.182741</v>
+        <v>0.159383</v>
       </c>
     </row>
     <row r="719">
@@ -9761,10 +9761,10 @@
         </is>
       </c>
       <c r="B719" t="n">
-        <v>0.096598</v>
+        <v>0.102789</v>
       </c>
       <c r="C719" t="n">
-        <v>0.180203</v>
+        <v>0.156812</v>
       </c>
     </row>
     <row r="720">
@@ -9774,10 +9774,10 @@
         </is>
       </c>
       <c r="B720" t="n">
-        <v>0.09664300000000001</v>
+        <v>0.104508</v>
       </c>
       <c r="C720" t="n">
-        <v>0.177665</v>
+        <v>0.154242</v>
       </c>
     </row>
     <row r="721">
@@ -9787,10 +9787,10 @@
         </is>
       </c>
       <c r="B721" t="n">
-        <v>0.09711500000000001</v>
+        <v>0.105585</v>
       </c>
       <c r="C721" t="n">
-        <v>0.175127</v>
+        <v>0.151671</v>
       </c>
     </row>
     <row r="722">
@@ -9800,10 +9800,10 @@
         </is>
       </c>
       <c r="B722" t="n">
-        <v>0.097513</v>
+        <v>0.106649</v>
       </c>
       <c r="C722" t="n">
-        <v>0.172589</v>
+        <v>0.1491</v>
       </c>
     </row>
     <row r="723">
@@ -9813,10 +9813,10 @@
         </is>
       </c>
       <c r="B723" t="n">
-        <v>0.09893299999999999</v>
+        <v>0.10914</v>
       </c>
       <c r="C723" t="n">
-        <v>0.170051</v>
+        <v>0.14653</v>
       </c>
     </row>
     <row r="724">
@@ -9826,10 +9826,10 @@
         </is>
       </c>
       <c r="B724" t="n">
-        <v>0.100096</v>
+        <v>0.109403</v>
       </c>
       <c r="C724" t="n">
-        <v>0.167513</v>
+        <v>0.143959</v>
       </c>
     </row>
     <row r="725">
@@ -9839,10 +9839,10 @@
         </is>
       </c>
       <c r="B725" t="n">
-        <v>0.100195</v>
+        <v>0.109834</v>
       </c>
       <c r="C725" t="n">
-        <v>0.164975</v>
+        <v>0.141388</v>
       </c>
     </row>
     <row r="726">
@@ -9852,10 +9852,10 @@
         </is>
       </c>
       <c r="B726" t="n">
-        <v>0.100556</v>
+        <v>0.110266</v>
       </c>
       <c r="C726" t="n">
-        <v>0.162437</v>
+        <v>0.138817</v>
       </c>
     </row>
     <row r="727">
@@ -9865,10 +9865,10 @@
         </is>
       </c>
       <c r="B727" t="n">
-        <v>0.10095</v>
+        <v>0.110321</v>
       </c>
       <c r="C727" t="n">
-        <v>0.159898</v>
+        <v>0.136247</v>
       </c>
     </row>
     <row r="728">
@@ -9878,10 +9878,10 @@
         </is>
       </c>
       <c r="B728" t="n">
-        <v>0.101015</v>
+        <v>0.112411</v>
       </c>
       <c r="C728" t="n">
-        <v>0.15736</v>
+        <v>0.133676</v>
       </c>
     </row>
     <row r="729">
@@ -9891,10 +9891,10 @@
         </is>
       </c>
       <c r="B729" t="n">
-        <v>0.102143</v>
+        <v>0.114707</v>
       </c>
       <c r="C729" t="n">
-        <v>0.154822</v>
+        <v>0.131105</v>
       </c>
     </row>
     <row r="730">
@@ -9904,10 +9904,10 @@
         </is>
       </c>
       <c r="B730" t="n">
-        <v>0.102633</v>
+        <v>0.115773</v>
       </c>
       <c r="C730" t="n">
-        <v>0.152284</v>
+        <v>0.128535</v>
       </c>
     </row>
     <row r="731">
@@ -9917,10 +9917,10 @@
         </is>
       </c>
       <c r="B731" t="n">
-        <v>0.104279</v>
+        <v>0.119527</v>
       </c>
       <c r="C731" t="n">
-        <v>0.149746</v>
+        <v>0.125964</v>
       </c>
     </row>
     <row r="732">
@@ -9930,10 +9930,10 @@
         </is>
       </c>
       <c r="B732" t="n">
-        <v>0.10914</v>
+        <v>0.119749</v>
       </c>
       <c r="C732" t="n">
-        <v>0.147208</v>
+        <v>0.123393</v>
       </c>
     </row>
     <row r="733">
@@ -9943,10 +9943,10 @@
         </is>
       </c>
       <c r="B733" t="n">
-        <v>0.109401</v>
+        <v>0.120761</v>
       </c>
       <c r="C733" t="n">
-        <v>0.14467</v>
+        <v>0.120823</v>
       </c>
     </row>
     <row r="734">
@@ -9956,10 +9956,10 @@
         </is>
       </c>
       <c r="B734" t="n">
-        <v>0.109768</v>
+        <v>0.121984</v>
       </c>
       <c r="C734" t="n">
-        <v>0.142132</v>
+        <v>0.118252</v>
       </c>
     </row>
     <row r="735">
@@ -9969,10 +9969,10 @@
         </is>
       </c>
       <c r="B735" t="n">
-        <v>0.10997</v>
+        <v>0.123289</v>
       </c>
       <c r="C735" t="n">
-        <v>0.139594</v>
+        <v>0.115681</v>
       </c>
     </row>
     <row r="736">
@@ -9982,10 +9982,10 @@
         </is>
       </c>
       <c r="B736" t="n">
-        <v>0.11023</v>
+        <v>0.125891</v>
       </c>
       <c r="C736" t="n">
-        <v>0.137056</v>
+        <v>0.113111</v>
       </c>
     </row>
     <row r="737">
@@ -9995,10 +9995,10 @@
         </is>
       </c>
       <c r="B737" t="n">
-        <v>0.11088</v>
+        <v>0.127587</v>
       </c>
       <c r="C737" t="n">
-        <v>0.134518</v>
+        <v>0.11054</v>
       </c>
     </row>
     <row r="738">
@@ -10008,10 +10008,10 @@
         </is>
       </c>
       <c r="B738" t="n">
-        <v>0.114411</v>
+        <v>0.127924</v>
       </c>
       <c r="C738" t="n">
-        <v>0.13198</v>
+        <v>0.107969</v>
       </c>
     </row>
     <row r="739">
@@ -10021,10 +10021,10 @@
         </is>
       </c>
       <c r="B739" t="n">
-        <v>0.115581</v>
+        <v>0.128763</v>
       </c>
       <c r="C739" t="n">
-        <v>0.129442</v>
+        <v>0.105398</v>
       </c>
     </row>
     <row r="740">
@@ -10034,10 +10034,10 @@
         </is>
       </c>
       <c r="B740" t="n">
-        <v>0.117714</v>
+        <v>0.130858</v>
       </c>
       <c r="C740" t="n">
-        <v>0.126904</v>
+        <v>0.102828</v>
       </c>
     </row>
     <row r="741">
@@ -10047,10 +10047,10 @@
         </is>
       </c>
       <c r="B741" t="n">
-        <v>0.119529</v>
+        <v>0.131588</v>
       </c>
       <c r="C741" t="n">
-        <v>0.124365</v>
+        <v>0.100257</v>
       </c>
     </row>
     <row r="742">
@@ -10060,10 +10060,10 @@
         </is>
       </c>
       <c r="B742" t="n">
-        <v>0.120364</v>
+        <v>0.133024</v>
       </c>
       <c r="C742" t="n">
-        <v>0.121827</v>
+        <v>0.097686</v>
       </c>
     </row>
     <row r="743">
@@ -10073,10 +10073,10 @@
         </is>
       </c>
       <c r="B743" t="n">
-        <v>0.121831</v>
+        <v>0.136389</v>
       </c>
       <c r="C743" t="n">
-        <v>0.119289</v>
+        <v>0.09511600000000001</v>
       </c>
     </row>
     <row r="744">
@@ -10086,10 +10086,10 @@
         </is>
       </c>
       <c r="B744" t="n">
-        <v>0.123212</v>
+        <v>0.136672</v>
       </c>
       <c r="C744" t="n">
-        <v>0.116751</v>
+        <v>0.092545</v>
       </c>
     </row>
     <row r="745">
@@ -10099,10 +10099,10 @@
         </is>
       </c>
       <c r="B745" t="n">
-        <v>0.124877</v>
+        <v>0.137322</v>
       </c>
       <c r="C745" t="n">
-        <v>0.114213</v>
+        <v>0.089974</v>
       </c>
     </row>
     <row r="746">
@@ -10112,10 +10112,10 @@
         </is>
       </c>
       <c r="B746" t="n">
-        <v>0.125206</v>
+        <v>0.138648</v>
       </c>
       <c r="C746" t="n">
-        <v>0.111675</v>
+        <v>0.087404</v>
       </c>
     </row>
     <row r="747">
@@ -10125,10 +10125,10 @@
         </is>
       </c>
       <c r="B747" t="n">
-        <v>0.125832</v>
+        <v>0.141187</v>
       </c>
       <c r="C747" t="n">
-        <v>0.109137</v>
+        <v>0.08483300000000001</v>
       </c>
     </row>
     <row r="748">
@@ -10138,10 +10138,10 @@
         </is>
       </c>
       <c r="B748" t="n">
-        <v>0.126143</v>
+        <v>0.14215</v>
       </c>
       <c r="C748" t="n">
-        <v>0.106599</v>
+        <v>0.082262</v>
       </c>
     </row>
     <row r="749">
@@ -10151,10 +10151,10 @@
         </is>
       </c>
       <c r="B749" t="n">
-        <v>0.130809</v>
+        <v>0.14279</v>
       </c>
       <c r="C749" t="n">
-        <v>0.104061</v>
+        <v>0.079692</v>
       </c>
     </row>
     <row r="750">
@@ -10164,10 +10164,10 @@
         </is>
       </c>
       <c r="B750" t="n">
-        <v>0.131534</v>
+        <v>0.142892</v>
       </c>
       <c r="C750" t="n">
-        <v>0.101523</v>
+        <v>0.077121</v>
       </c>
     </row>
     <row r="751">
@@ -10177,10 +10177,10 @@
         </is>
       </c>
       <c r="B751" t="n">
-        <v>0.133027</v>
+        <v>0.144159</v>
       </c>
       <c r="C751" t="n">
-        <v>0.098985</v>
+        <v>0.07455000000000001</v>
       </c>
     </row>
     <row r="752">
@@ -10190,10 +10190,10 @@
         </is>
       </c>
       <c r="B752" t="n">
-        <v>0.136031</v>
+        <v>0.148048</v>
       </c>
       <c r="C752" t="n">
-        <v>0.096447</v>
+        <v>0.071979</v>
       </c>
     </row>
     <row r="753">
@@ -10203,10 +10203,10 @@
         </is>
       </c>
       <c r="B753" t="n">
-        <v>0.136377</v>
+        <v>0.15333</v>
       </c>
       <c r="C753" t="n">
-        <v>0.09390900000000001</v>
+        <v>0.069409</v>
       </c>
     </row>
     <row r="754">
@@ -10216,10 +10216,10 @@
         </is>
       </c>
       <c r="B754" t="n">
-        <v>0.136657</v>
+        <v>0.155915</v>
       </c>
       <c r="C754" t="n">
-        <v>0.09137099999999999</v>
+        <v>0.06683799999999999</v>
       </c>
     </row>
     <row r="755">
@@ -10229,10 +10229,10 @@
         </is>
       </c>
       <c r="B755" t="n">
-        <v>0.137347</v>
+        <v>0.159625</v>
       </c>
       <c r="C755" t="n">
-        <v>0.08883199999999999</v>
+        <v>0.064267</v>
       </c>
     </row>
     <row r="756">
@@ -10242,10 +10242,10 @@
         </is>
       </c>
       <c r="B756" t="n">
-        <v>0.140633</v>
+        <v>0.161123</v>
       </c>
       <c r="C756" t="n">
-        <v>0.086294</v>
+        <v>0.061697</v>
       </c>
     </row>
     <row r="757">
@@ -10255,10 +10255,10 @@
         </is>
       </c>
       <c r="B757" t="n">
-        <v>0.14119</v>
+        <v>0.162281</v>
       </c>
       <c r="C757" t="n">
-        <v>0.083756</v>
+        <v>0.059126</v>
       </c>
     </row>
     <row r="758">
@@ -10268,10 +10268,10 @@
         </is>
       </c>
       <c r="B758" t="n">
-        <v>0.142085</v>
+        <v>0.171113</v>
       </c>
       <c r="C758" t="n">
-        <v>0.081218</v>
+        <v>0.056555</v>
       </c>
     </row>
     <row r="759">
@@ -10281,10 +10281,10 @@
         </is>
       </c>
       <c r="B759" t="n">
-        <v>0.14288</v>
+        <v>0.177654</v>
       </c>
       <c r="C759" t="n">
-        <v>0.07868</v>
+        <v>0.053985</v>
       </c>
     </row>
     <row r="760">
@@ -10294,10 +10294,10 @@
         </is>
       </c>
       <c r="B760" t="n">
-        <v>0.143946</v>
+        <v>0.18041</v>
       </c>
       <c r="C760" t="n">
-        <v>0.076142</v>
+        <v>0.051414</v>
       </c>
     </row>
     <row r="761">
@@ -10307,10 +10307,10 @@
         </is>
       </c>
       <c r="B761" t="n">
-        <v>0.146383</v>
+        <v>0.182541</v>
       </c>
       <c r="C761" t="n">
-        <v>0.073604</v>
+        <v>0.048843</v>
       </c>
     </row>
     <row r="762">
@@ -10320,10 +10320,10 @@
         </is>
       </c>
       <c r="B762" t="n">
-        <v>0.153326</v>
+        <v>0.183618</v>
       </c>
       <c r="C762" t="n">
-        <v>0.071066</v>
+        <v>0.046272</v>
       </c>
     </row>
     <row r="763">
@@ -10333,10 +10333,10 @@
         </is>
       </c>
       <c r="B763" t="n">
-        <v>0.155822</v>
+        <v>0.18825</v>
       </c>
       <c r="C763" t="n">
-        <v>0.06852800000000001</v>
+        <v>0.043702</v>
       </c>
     </row>
     <row r="764">
@@ -10346,10 +10346,10 @@
         </is>
       </c>
       <c r="B764" t="n">
-        <v>0.159132</v>
+        <v>0.189738</v>
       </c>
       <c r="C764" t="n">
-        <v>0.06598999999999999</v>
+        <v>0.041131</v>
       </c>
     </row>
     <row r="765">
@@ -10359,10 +10359,10 @@
         </is>
       </c>
       <c r="B765" t="n">
-        <v>0.161128</v>
+        <v>0.189811</v>
       </c>
       <c r="C765" t="n">
-        <v>0.06345199999999999</v>
+        <v>0.03856</v>
       </c>
     </row>
     <row r="766">
@@ -10372,10 +10372,10 @@
         </is>
       </c>
       <c r="B766" t="n">
-        <v>0.161328</v>
+        <v>0.193578</v>
       </c>
       <c r="C766" t="n">
-        <v>0.060914</v>
+        <v>0.03599</v>
       </c>
     </row>
     <row r="767">
@@ -10385,10 +10385,10 @@
         </is>
       </c>
       <c r="B767" t="n">
-        <v>0.171011</v>
+        <v>0.200852</v>
       </c>
       <c r="C767" t="n">
-        <v>0.058376</v>
+        <v>0.033419</v>
       </c>
     </row>
     <row r="768">
@@ -10398,10 +10398,10 @@
         </is>
       </c>
       <c r="B768" t="n">
-        <v>0.176735</v>
+        <v>0.203281</v>
       </c>
       <c r="C768" t="n">
-        <v>0.055838</v>
+        <v>0.030848</v>
       </c>
     </row>
     <row r="769">
@@ -10411,10 +10411,10 @@
         </is>
       </c>
       <c r="B769" t="n">
-        <v>0.180146</v>
+        <v>0.207814</v>
       </c>
       <c r="C769" t="n">
-        <v>0.053299</v>
+        <v>0.028278</v>
       </c>
     </row>
     <row r="770">
@@ -10424,10 +10424,10 @@
         </is>
       </c>
       <c r="B770" t="n">
-        <v>0.182164</v>
+        <v>0.248561</v>
       </c>
       <c r="C770" t="n">
-        <v>0.050761</v>
+        <v>0.025707</v>
       </c>
     </row>
     <row r="771">
@@ -10437,10 +10437,10 @@
         </is>
       </c>
       <c r="B771" t="n">
-        <v>0.183245</v>
+        <v>0.250665</v>
       </c>
       <c r="C771" t="n">
-        <v>0.048223</v>
+        <v>0.023136</v>
       </c>
     </row>
     <row r="772">
@@ -10450,10 +10450,10 @@
         </is>
       </c>
       <c r="B772" t="n">
-        <v>0.184192</v>
+        <v>0.272427</v>
       </c>
       <c r="C772" t="n">
-        <v>0.045685</v>
+        <v>0.020566</v>
       </c>
     </row>
     <row r="773">
@@ -10463,10 +10463,10 @@
         </is>
       </c>
       <c r="B773" t="n">
-        <v>0.187522</v>
+        <v>0.276042</v>
       </c>
       <c r="C773" t="n">
-        <v>0.043147</v>
+        <v>0.017995</v>
       </c>
     </row>
     <row r="774">
@@ -10476,10 +10476,10 @@
         </is>
       </c>
       <c r="B774" t="n">
-        <v>0.1879</v>
+        <v>0.278909</v>
       </c>
       <c r="C774" t="n">
-        <v>0.040609</v>
+        <v>0.015424</v>
       </c>
     </row>
     <row r="775">
@@ -10489,10 +10489,10 @@
         </is>
       </c>
       <c r="B775" t="n">
-        <v>0.188467</v>
+        <v>0.287068</v>
       </c>
       <c r="C775" t="n">
-        <v>0.038071</v>
+        <v>0.012853</v>
       </c>
     </row>
     <row r="776">
@@ -10502,10 +10502,10 @@
         </is>
       </c>
       <c r="B776" t="n">
-        <v>0.189223</v>
+        <v>0.3424</v>
       </c>
       <c r="C776" t="n">
-        <v>0.035533</v>
+        <v>0.010283</v>
       </c>
     </row>
     <row r="777">
@@ -10515,10 +10515,10 @@
         </is>
       </c>
       <c r="B777" t="n">
-        <v>0.198508</v>
+        <v>0.350379</v>
       </c>
       <c r="C777" t="n">
-        <v>0.032995</v>
+        <v>0.007712</v>
       </c>
     </row>
     <row r="778">
@@ -10528,10 +10528,10 @@
         </is>
       </c>
       <c r="B778" t="n">
-        <v>0.199544</v>
+        <v>0.368328</v>
       </c>
       <c r="C778" t="n">
-        <v>0.030457</v>
+        <v>0.005141</v>
       </c>
     </row>
     <row r="779">
@@ -10541,140 +10541,10 @@
         </is>
       </c>
       <c r="B779" t="n">
-        <v>0.207823</v>
+        <v>0.511275</v>
       </c>
       <c r="C779" t="n">
-        <v>0.027919</v>
-      </c>
-    </row>
-    <row r="780">
-      <c r="A780" t="inlineStr">
-        <is>
-          <t>Adjusted target</t>
-        </is>
-      </c>
-      <c r="B780" t="n">
-        <v>0.247184</v>
-      </c>
-      <c r="C780" t="n">
-        <v>0.025381</v>
-      </c>
-    </row>
-    <row r="781">
-      <c r="A781" t="inlineStr">
-        <is>
-          <t>Adjusted target</t>
-        </is>
-      </c>
-      <c r="B781" t="n">
-        <v>0.247336</v>
-      </c>
-      <c r="C781" t="n">
-        <v>0.022843</v>
-      </c>
-    </row>
-    <row r="782">
-      <c r="A782" t="inlineStr">
-        <is>
-          <t>Adjusted target</t>
-        </is>
-      </c>
-      <c r="B782" t="n">
-        <v>0.263887</v>
-      </c>
-      <c r="C782" t="n">
-        <v>0.020305</v>
-      </c>
-    </row>
-    <row r="783">
-      <c r="A783" t="inlineStr">
-        <is>
-          <t>Adjusted target</t>
-        </is>
-      </c>
-      <c r="B783" t="n">
-        <v>0.267257</v>
-      </c>
-      <c r="C783" t="n">
-        <v>0.017766</v>
-      </c>
-    </row>
-    <row r="784">
-      <c r="A784" t="inlineStr">
-        <is>
-          <t>Adjusted target</t>
-        </is>
-      </c>
-      <c r="B784" t="n">
-        <v>0.271167</v>
-      </c>
-      <c r="C784" t="n">
-        <v>0.015228</v>
-      </c>
-    </row>
-    <row r="785">
-      <c r="A785" t="inlineStr">
-        <is>
-          <t>Adjusted target</t>
-        </is>
-      </c>
-      <c r="B785" t="n">
-        <v>0.27639</v>
-      </c>
-      <c r="C785" t="n">
-        <v>0.01269</v>
-      </c>
-    </row>
-    <row r="786">
-      <c r="A786" t="inlineStr">
-        <is>
-          <t>Adjusted target</t>
-        </is>
-      </c>
-      <c r="B786" t="n">
-        <v>0.334312</v>
-      </c>
-      <c r="C786" t="n">
-        <v>0.010152</v>
-      </c>
-    </row>
-    <row r="787">
-      <c r="A787" t="inlineStr">
-        <is>
-          <t>Adjusted target</t>
-        </is>
-      </c>
-      <c r="B787" t="n">
-        <v>0.349364</v>
-      </c>
-      <c r="C787" t="n">
-        <v>0.007614</v>
-      </c>
-    </row>
-    <row r="788">
-      <c r="A788" t="inlineStr">
-        <is>
-          <t>Adjusted target</t>
-        </is>
-      </c>
-      <c r="B788" t="n">
-        <v>0.362846</v>
-      </c>
-      <c r="C788" t="n">
-        <v>0.005076</v>
-      </c>
-    </row>
-    <row r="789">
-      <c r="A789" t="inlineStr">
-        <is>
-          <t>Adjusted target</t>
-        </is>
-      </c>
-      <c r="B789" t="n">
-        <v>0.507274</v>
-      </c>
-      <c r="C789" t="n">
-        <v>0.002538</v>
+        <v>0.002571</v>
       </c>
     </row>
   </sheetData>
